--- a/Test Cases.xlsx
+++ b/Test Cases.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
   <workbookPr hidePivotFieldList="1"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://endresshauser-my.sharepoint.com/personal/corbin_ferguson_endress_com/Documents/Thesis Work/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1418" documentId="11_AD4DB114E441178AC67DF4D41ED1D894683EDF27" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9E564A6C-B47C-4390-81F0-781612B005CA}"/>
+  <xr:revisionPtr revIDLastSave="1623" documentId="11_AD4DB114E441178AC67DF4D41ED1D894683EDF27" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F6880D38-75ED-44FD-ABA6-68371B1CE8AA}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="25440" windowHeight="15270" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="25440" windowHeight="15270" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tests" sheetId="7" r:id="rId1"/>
@@ -66,7 +66,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="522" uniqueCount="189">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="523" uniqueCount="190">
   <si>
     <t>Step</t>
   </si>
@@ -80,9 +80,6 @@
     <t>Test Case ID:</t>
   </si>
   <si>
-    <t>Test Priority (Low/Medium/High):</t>
-  </si>
-  <si>
     <t>Test Execution Date:</t>
   </si>
   <si>
@@ -105,9 +102,6 @@
   </si>
   <si>
     <t>New File Creation</t>
-  </si>
-  <si>
-    <t>Test Priority (Low/Medium/High): Low</t>
   </si>
   <si>
     <t>Description: Test the creation of an empty template file, overwriting the existing file.</t>
@@ -856,13 +850,22 @@
     <t>move to add another window</t>
   </si>
   <si>
-    <t>add another window</t>
-  </si>
-  <si>
     <t>"No" button press</t>
   </si>
   <si>
     <t>Description: Test the functionality of the Import Element block</t>
+  </si>
+  <si>
+    <t>TemplateFBAOI</t>
+  </si>
+  <si>
+    <t>add another from file window opens</t>
+  </si>
+  <si>
+    <t>Test Priority:</t>
+  </si>
+  <si>
+    <t>Test Priority: Low</t>
   </si>
 </sst>
 </file>
@@ -900,24 +903,36 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="1"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="1">
+  <borders count="3">
     <border>
       <left/>
       <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
       <top/>
       <bottom/>
       <diagonal/>
@@ -926,10 +941,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -942,13 +956,7 @@
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
@@ -957,25 +965,72 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" pivotButton="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2345,7 +2400,7 @@
   <cols>
     <col min="1" max="1" width="10.36328125" customWidth="1"/>
     <col min="2" max="2" width="34.1796875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="16.1796875" style="20" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="16.1796875" style="13" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="18.36328125" hidden="1" customWidth="1"/>
     <col min="5" max="5" width="13.453125" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="16.1796875" bestFit="1" customWidth="1"/>
@@ -2354,29 +2409,29 @@
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
+        <v>159</v>
+      </c>
+      <c r="B1" t="s">
+        <v>160</v>
+      </c>
+      <c r="C1" s="13" t="s">
         <v>161</v>
       </c>
-      <c r="B1" t="s">
-        <v>162</v>
-      </c>
-      <c r="C1" s="20" t="s">
+      <c r="D1" t="s">
         <v>163</v>
       </c>
-      <c r="D1" t="s">
-        <v>165</v>
-      </c>
       <c r="E1" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="G1">
         <f>COUNTIF(TestMaster[Test Status], "Not Implemented")</f>
         <v>15</v>
       </c>
-      <c r="H1" s="21" t="s">
+      <c r="H1" s="14" t="s">
+        <v>171</v>
+      </c>
+      <c r="I1" t="s">
         <v>173</v>
-      </c>
-      <c r="I1" t="s">
-        <v>175</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.35">
@@ -2388,23 +2443,23 @@
         <f t="array" ref="B2">'Element Import Testing'!A1:A1</f>
         <v>Import Select Redundant Name</v>
       </c>
-      <c r="C2" s="20" t="s">
-        <v>167</v>
+      <c r="C2" s="13" t="s">
+        <v>165</v>
       </c>
       <c r="D2" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="E2" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="G2">
         <f>COUNTIF(TestMaster[Test Status], "Pass")</f>
         <v>0</v>
       </c>
-      <c r="H2" s="22" t="s">
-        <v>167</v>
-      </c>
-      <c r="I2" s="19">
+      <c r="H2" s="15" t="s">
+        <v>165</v>
+      </c>
+      <c r="I2" s="12">
         <v>17</v>
       </c>
     </row>
@@ -2417,23 +2472,23 @@
         <f t="array" ref="B3">'Element Creation Testing'!A1:A1</f>
         <v>Element Quantity Creation</v>
       </c>
-      <c r="C3" s="20" t="s">
-        <v>167</v>
+      <c r="C3" s="13" t="s">
+        <v>165</v>
       </c>
       <c r="D3" t="s">
+        <v>166</v>
+      </c>
+      <c r="E3" t="s">
         <v>168</v>
-      </c>
-      <c r="E3" t="s">
-        <v>170</v>
       </c>
       <c r="G3">
         <f>COUNTIF(TestMaster[Test Status], "Fail")</f>
         <v>0</v>
       </c>
-      <c r="H3" s="22" t="s">
-        <v>174</v>
-      </c>
-      <c r="I3" s="19">
+      <c r="H3" s="15" t="s">
+        <v>172</v>
+      </c>
+      <c r="I3" s="12">
         <v>17</v>
       </c>
     </row>
@@ -2443,14 +2498,14 @@
         <v>3</v>
       </c>
       <c r="B4" t="str" cm="1">
-        <f t="array" ref="B4">'Element Creation Testing'!H1:H1</f>
+        <f t="array" ref="B4">'Element Creation Testing'!G1:G1</f>
         <v>Nameless Module Creation</v>
       </c>
-      <c r="C4" s="20" t="s">
-        <v>167</v>
+      <c r="C4" s="13" t="s">
+        <v>165</v>
       </c>
       <c r="E4" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="G4">
         <f>COUNTIF(TestMaster[Test Status], "Not Run")</f>
@@ -2463,14 +2518,14 @@
         <v>4</v>
       </c>
       <c r="B5" t="str" cm="1">
-        <f t="array" ref="B5">'Element Creation Testing'!O1:O1</f>
+        <f t="array" ref="B5">'Element Creation Testing'!M1:M1</f>
         <v>Redundant Element Creation</v>
       </c>
-      <c r="C5" s="20" t="s">
-        <v>167</v>
+      <c r="C5" s="13" t="s">
+        <v>165</v>
       </c>
       <c r="E5" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.35">
@@ -2482,11 +2537,11 @@
         <f>'Element Modification Testing'!A1</f>
         <v>No Element to Modify</v>
       </c>
-      <c r="C6" s="20" t="s">
-        <v>167</v>
+      <c r="C6" s="13" t="s">
+        <v>165</v>
       </c>
       <c r="E6" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.35">
@@ -2495,14 +2550,14 @@
         <v>6</v>
       </c>
       <c r="B7" t="str">
-        <f>'Element Modification Testing'!H1</f>
+        <f>'Element Modification Testing'!G1</f>
         <v>Completed Element Modification</v>
       </c>
-      <c r="C7" s="20" t="s">
-        <v>167</v>
+      <c r="C7" s="13" t="s">
+        <v>165</v>
       </c>
       <c r="E7" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.35">
@@ -2511,14 +2566,14 @@
         <v>7</v>
       </c>
       <c r="B8" t="str">
-        <f>'Element Modification Testing'!O1</f>
+        <f>'Element Modification Testing'!M1</f>
         <v>Modify into Redundant Element Name</v>
       </c>
-      <c r="C8" s="20" t="s">
-        <v>167</v>
+      <c r="C8" s="13" t="s">
+        <v>165</v>
       </c>
       <c r="E8" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.35">
@@ -2530,11 +2585,11 @@
         <f>'Element Deletion Testing'!A1</f>
         <v>Delete No Element Type</v>
       </c>
-      <c r="C9" s="20" t="s">
-        <v>167</v>
+      <c r="C9" s="13" t="s">
+        <v>165</v>
       </c>
       <c r="E9" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.35">
@@ -2543,14 +2598,14 @@
         <v>9</v>
       </c>
       <c r="B10" t="str">
-        <f>'Element Deletion Testing'!H1</f>
+        <f>'Element Deletion Testing'!G1</f>
         <v>Delete Element Found</v>
       </c>
-      <c r="C10" s="20" t="s">
-        <v>167</v>
+      <c r="C10" s="13" t="s">
+        <v>165</v>
       </c>
       <c r="E10" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.35">
@@ -2559,14 +2614,14 @@
         <v>10</v>
       </c>
       <c r="B11" t="str">
-        <f>'Element Deletion Testing'!O1</f>
+        <f>'Element Deletion Testing'!M1</f>
         <v>Delete Module by Port</v>
       </c>
-      <c r="C11" s="20" t="s">
-        <v>167</v>
+      <c r="C11" s="13" t="s">
+        <v>165</v>
       </c>
       <c r="E11" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.35">
@@ -2578,11 +2633,11 @@
         <f>'File Manipulation Testing'!A1</f>
         <v>New File Creation</v>
       </c>
-      <c r="C12" s="20" t="s">
-        <v>167</v>
+      <c r="C12" s="13" t="s">
+        <v>165</v>
       </c>
       <c r="E12" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.35">
@@ -2591,14 +2646,14 @@
         <v>12</v>
       </c>
       <c r="B13" t="str">
-        <f>'File Manipulation Testing'!H1</f>
+        <f>'File Manipulation Testing'!G1</f>
         <v>Save File</v>
       </c>
-      <c r="C13" s="20" t="s">
-        <v>167</v>
+      <c r="C13" s="13" t="s">
+        <v>165</v>
       </c>
       <c r="E13" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.35">
@@ -2607,14 +2662,14 @@
         <v>13</v>
       </c>
       <c r="B14" t="str">
-        <f>'File Manipulation Testing'!O1</f>
+        <f>'File Manipulation Testing'!M1</f>
         <v>Load File</v>
       </c>
-      <c r="C14" s="20" t="s">
-        <v>167</v>
+      <c r="C14" s="13" t="s">
+        <v>165</v>
       </c>
       <c r="E14" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.35">
@@ -2623,14 +2678,14 @@
         <v>14</v>
       </c>
       <c r="B15" t="str">
-        <f>'File Manipulation Testing'!V1</f>
+        <f>'File Manipulation Testing'!S1</f>
         <v>Validate File</v>
       </c>
-      <c r="C15" s="20" t="s">
-        <v>167</v>
+      <c r="C15" s="13" t="s">
+        <v>165</v>
       </c>
       <c r="E15" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.35">
@@ -2638,15 +2693,15 @@
         <f t="shared" si="0"/>
         <v>15</v>
       </c>
-      <c r="B16" s="19" t="str">
-        <f>'File Manipulation Testing'!AC1</f>
+      <c r="B16" s="12" t="str">
+        <f>'File Manipulation Testing'!Y1</f>
         <v>Exit</v>
       </c>
-      <c r="C16" s="20" t="s">
-        <v>167</v>
+      <c r="C16" s="13" t="s">
+        <v>165</v>
       </c>
       <c r="E16" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
     </row>
   </sheetData>
@@ -2704,370 +2759,393 @@
     <col min="1" max="1" width="6.36328125" customWidth="1"/>
     <col min="2" max="2" width="22.90625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="48.81640625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="59.26953125" style="4" customWidth="1"/>
+    <col min="4" max="4" width="56.7265625" style="3" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="18.36328125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="16.1796875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="16.1796875" style="23" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A1" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="B1" s="3"/>
-      <c r="C1" s="3"/>
-      <c r="D1" s="3"/>
-      <c r="E1" s="3"/>
-      <c r="F1" s="3"/>
+      <c r="A1" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="B1" s="17"/>
+      <c r="C1" s="17"/>
+      <c r="D1" s="17"/>
+      <c r="E1" s="17"/>
+      <c r="F1" s="24"/>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A2" s="3" t="s">
+      <c r="A2" s="17" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="3"/>
-      <c r="C2" s="5">
+      <c r="B2" s="17"/>
+      <c r="C2" s="18">
         <f>IFERROR(_xlfn.XLOOKUP(A1, TestMaster[Test Name], TestMaster[Test ID], "ID not found"), "")</f>
         <v>1</v>
       </c>
-      <c r="E2" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="F2" s="5"/>
+      <c r="D2" s="19"/>
+      <c r="E2" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="F2" s="21"/>
     </row>
     <row r="3" spans="1:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="B3" s="3"/>
-      <c r="C3" s="3"/>
-      <c r="D3" s="4" t="str">
+      <c r="A3" s="17" t="s">
+        <v>188</v>
+      </c>
+      <c r="B3" s="17"/>
+      <c r="C3" s="22" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(A1, TestMaster[Test Name], TestMaster[Test Priority], "Priority not found"), "")</f>
         <v>Medium</v>
       </c>
-      <c r="E3" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="F3" t="str">
+      <c r="D3" s="19"/>
+      <c r="E3" s="20" t="s">
+        <v>5</v>
+      </c>
+      <c r="F3" s="23" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(A1, TestMaster[Test Name], TestMaster[Test Status], "Status not found"), "")</f>
         <v>Not Implemented</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A4" s="3" t="s">
-        <v>188</v>
-      </c>
-      <c r="B4" s="3"/>
-      <c r="C4" s="3"/>
-      <c r="D4" s="3"/>
-      <c r="E4" s="3"/>
-      <c r="F4" s="3"/>
+      <c r="A4" s="17" t="s">
+        <v>185</v>
+      </c>
+      <c r="B4" s="17"/>
+      <c r="C4" s="17"/>
+      <c r="D4" s="17"/>
+      <c r="E4" s="17"/>
+      <c r="F4" s="24"/>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A5" s="3"/>
-      <c r="B5" s="3"/>
-      <c r="C5" s="3"/>
-      <c r="D5" s="3"/>
-      <c r="E5" s="3"/>
-      <c r="F5" s="3"/>
+      <c r="A5" s="17"/>
+      <c r="B5" s="17"/>
+      <c r="C5" s="17"/>
+      <c r="D5" s="17"/>
+      <c r="E5" s="17"/>
+      <c r="F5" s="24"/>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A6" s="3" t="s">
+      <c r="A6" s="17" t="s">
+        <v>7</v>
+      </c>
+      <c r="B6" s="17"/>
+      <c r="C6" s="17"/>
+      <c r="D6" s="17"/>
+      <c r="E6" s="17"/>
+      <c r="F6" s="24"/>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A7" s="25" t="s">
+        <v>0</v>
+      </c>
+      <c r="B7" s="25" t="s">
         <v>8</v>
       </c>
-      <c r="B6" s="3"/>
-      <c r="C6" s="3"/>
-      <c r="D6" s="3"/>
-      <c r="E6" s="3"/>
-      <c r="F6" s="3"/>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A7" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B7" s="1" t="s">
+      <c r="C7" s="25" t="s">
         <v>9</v>
       </c>
-      <c r="C7" s="1" t="s">
+      <c r="D7" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="E7" s="25" t="s">
         <v>10</v>
       </c>
-      <c r="D7" s="23" t="s">
+      <c r="F7" s="27" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" s="11" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="28">
         <v>1</v>
       </c>
-      <c r="E7" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="F7" s="1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" s="15" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="15">
-        <v>1</v>
-      </c>
-      <c r="B8" s="15" t="s">
+      <c r="B8" s="28" t="s">
+        <v>176</v>
+      </c>
+      <c r="C8" s="28" t="s">
+        <v>177</v>
+      </c>
+      <c r="D8" s="29" t="s">
         <v>178</v>
       </c>
-      <c r="C8" s="15" t="s">
-        <v>179</v>
-      </c>
-      <c r="D8" s="16" t="s">
-        <v>180</v>
-      </c>
+      <c r="E8" s="28"/>
+      <c r="F8" s="30"/>
     </row>
     <row r="9" spans="1:6" ht="29" x14ac:dyDescent="0.35">
-      <c r="A9" s="13">
+      <c r="A9" s="34">
         <f>A8+1</f>
         <v>2</v>
       </c>
-      <c r="B9" s="10" t="s">
-        <v>176</v>
-      </c>
-      <c r="C9" s="10" t="s">
-        <v>177</v>
-      </c>
-      <c r="D9" s="10" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A10" s="13">
+      <c r="B9" s="31" t="s">
+        <v>174</v>
+      </c>
+      <c r="C9" s="31" t="s">
+        <v>175</v>
+      </c>
+      <c r="D9" s="31" t="s">
+        <v>125</v>
+      </c>
+      <c r="E9" s="32"/>
+    </row>
+    <row r="10" spans="1:6" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A10" s="34">
         <f>A9+1</f>
         <v>3</v>
       </c>
-      <c r="B10" s="10" t="s">
-        <v>128</v>
-      </c>
-      <c r="C10" s="18" t="s">
-        <v>143</v>
-      </c>
-      <c r="D10" s="10" t="s">
-        <v>129</v>
-      </c>
+      <c r="B10" s="31" t="s">
+        <v>126</v>
+      </c>
+      <c r="C10" s="33" t="s">
+        <v>141</v>
+      </c>
+      <c r="D10" s="31" t="s">
+        <v>127</v>
+      </c>
+      <c r="E10" s="32"/>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A11" s="13">
+      <c r="A11" s="34">
         <f t="shared" ref="A11:A25" si="0">A10+1</f>
         <v>4</v>
       </c>
-      <c r="B11" s="10" t="s">
-        <v>181</v>
-      </c>
-      <c r="C11" s="10" t="s">
-        <v>144</v>
-      </c>
-      <c r="D11" s="10" t="s">
-        <v>186</v>
-      </c>
+      <c r="B11" s="31" t="s">
+        <v>179</v>
+      </c>
+      <c r="C11" s="31" t="s">
+        <v>142</v>
+      </c>
+      <c r="D11" s="31" t="s">
+        <v>187</v>
+      </c>
+      <c r="E11" s="32"/>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A12" s="13">
+      <c r="A12" s="34">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="B12" s="10" t="s">
-        <v>182</v>
-      </c>
-      <c r="C12" s="10" t="s">
-        <v>30</v>
-      </c>
-      <c r="D12" s="4" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A13" s="13">
+      <c r="B12" s="31" t="s">
+        <v>180</v>
+      </c>
+      <c r="C12" s="31" t="s">
+        <v>28</v>
+      </c>
+      <c r="D12" s="19" t="s">
+        <v>181</v>
+      </c>
+      <c r="E12" s="32"/>
+    </row>
+    <row r="13" spans="1:6" ht="29" x14ac:dyDescent="0.35">
+      <c r="A13" s="34">
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
-      <c r="B13" s="10" t="s">
-        <v>128</v>
-      </c>
-      <c r="C13" s="18" t="s">
-        <v>143</v>
-      </c>
-      <c r="D13" s="10" t="s">
-        <v>129</v>
-      </c>
+      <c r="B13" s="31" t="s">
+        <v>126</v>
+      </c>
+      <c r="C13" s="33" t="s">
+        <v>141</v>
+      </c>
+      <c r="D13" s="31" t="s">
+        <v>127</v>
+      </c>
+      <c r="E13" s="32"/>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A14" s="13">
+      <c r="A14" s="34">
         <f t="shared" si="0"/>
         <v>7</v>
       </c>
-      <c r="B14" s="10" t="s">
-        <v>181</v>
-      </c>
-      <c r="C14" s="10" t="s">
-        <v>144</v>
-      </c>
-      <c r="D14" s="10" t="s">
-        <v>185</v>
-      </c>
+      <c r="B14" s="31" t="s">
+        <v>179</v>
+      </c>
+      <c r="C14" s="31" t="s">
+        <v>142</v>
+      </c>
+      <c r="D14" s="31" t="s">
+        <v>183</v>
+      </c>
+      <c r="E14" s="32"/>
     </row>
     <row r="15" spans="1:6" ht="29" x14ac:dyDescent="0.35">
-      <c r="A15" s="13">
+      <c r="A15" s="34">
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
-      <c r="B15" t="s">
-        <v>109</v>
-      </c>
-      <c r="C15" t="s">
-        <v>113</v>
-      </c>
-      <c r="D15" s="4" t="s">
-        <v>184</v>
-      </c>
+      <c r="B15" s="32" t="s">
+        <v>107</v>
+      </c>
+      <c r="C15" s="32" t="s">
+        <v>111</v>
+      </c>
+      <c r="D15" s="19" t="s">
+        <v>182</v>
+      </c>
+      <c r="E15" s="32"/>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A16" s="13">
+      <c r="A16" s="34">
         <f t="shared" si="0"/>
         <v>9</v>
       </c>
-      <c r="B16" s="10" t="s">
-        <v>182</v>
-      </c>
-      <c r="C16" s="10" t="s">
-        <v>30</v>
-      </c>
-      <c r="D16" s="4" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A17" s="13">
+      <c r="B16" s="31" t="s">
+        <v>180</v>
+      </c>
+      <c r="C16" s="31" t="s">
+        <v>28</v>
+      </c>
+      <c r="D16" s="19" t="s">
+        <v>181</v>
+      </c>
+      <c r="E16" s="32"/>
+    </row>
+    <row r="17" spans="1:5" ht="29" x14ac:dyDescent="0.35">
+      <c r="A17" s="34">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="B17" s="10" t="s">
-        <v>128</v>
-      </c>
-      <c r="C17" s="18" t="s">
-        <v>143</v>
-      </c>
-      <c r="D17" s="10" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A18" s="13">
+      <c r="B17" s="31" t="s">
+        <v>126</v>
+      </c>
+      <c r="C17" s="33" t="s">
+        <v>141</v>
+      </c>
+      <c r="D17" s="31" t="s">
+        <v>127</v>
+      </c>
+      <c r="E17" s="32"/>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A18" s="34">
         <f t="shared" si="0"/>
         <v>11</v>
       </c>
-      <c r="B18" s="10" t="s">
-        <v>181</v>
-      </c>
-      <c r="C18" s="10" t="s">
-        <v>144</v>
-      </c>
-      <c r="D18" s="10" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A19" s="13">
+      <c r="B18" s="31" t="s">
+        <v>179</v>
+      </c>
+      <c r="C18" s="31" t="s">
+        <v>142</v>
+      </c>
+      <c r="D18" s="31" t="s">
+        <v>129</v>
+      </c>
+      <c r="E18" s="32"/>
+    </row>
+    <row r="19" spans="1:5" ht="29" x14ac:dyDescent="0.35">
+      <c r="A19" s="34">
         <f t="shared" si="0"/>
         <v>12</v>
       </c>
-      <c r="B19" t="s">
-        <v>109</v>
-      </c>
-      <c r="C19" t="s">
-        <v>125</v>
-      </c>
-      <c r="D19" s="4" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A20" s="13">
+      <c r="B19" s="32" t="s">
+        <v>107</v>
+      </c>
+      <c r="C19" s="32" t="s">
+        <v>123</v>
+      </c>
+      <c r="D19" s="19" t="s">
+        <v>153</v>
+      </c>
+      <c r="E19" s="32"/>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A20" s="34">
         <f t="shared" si="0"/>
         <v>13</v>
       </c>
-      <c r="B20" s="10" t="s">
-        <v>182</v>
-      </c>
-      <c r="C20" s="10" t="s">
-        <v>30</v>
-      </c>
-      <c r="D20" s="4" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A21" s="13">
+      <c r="B20" s="31" t="s">
+        <v>180</v>
+      </c>
+      <c r="C20" s="31" t="s">
+        <v>28</v>
+      </c>
+      <c r="D20" s="19" t="s">
+        <v>181</v>
+      </c>
+      <c r="E20" s="32"/>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A21" s="34">
         <f t="shared" si="0"/>
         <v>14</v>
       </c>
-      <c r="B21" t="s">
+      <c r="B21" s="32" t="s">
+        <v>107</v>
+      </c>
+      <c r="C21" s="32" t="s">
         <v>109</v>
       </c>
-      <c r="C21" t="s">
-        <v>111</v>
-      </c>
-      <c r="D21" s="4" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A22" s="13">
+      <c r="D21" s="19" t="s">
+        <v>157</v>
+      </c>
+      <c r="E21" s="32"/>
+    </row>
+    <row r="22" spans="1:5" ht="29" x14ac:dyDescent="0.35">
+      <c r="A22" s="34">
         <f t="shared" si="0"/>
         <v>15</v>
       </c>
-      <c r="B22" t="s">
-        <v>114</v>
-      </c>
-      <c r="D22" s="4" t="s">
+      <c r="B22" s="32" t="s">
         <v>112</v>
       </c>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A23" s="13">
+      <c r="C22" s="31" t="s">
+        <v>186</v>
+      </c>
+      <c r="D22" s="19" t="s">
+        <v>110</v>
+      </c>
+      <c r="E22" s="32"/>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A23" s="34">
         <f t="shared" si="0"/>
         <v>16</v>
       </c>
-      <c r="B23" t="s">
+      <c r="B23" s="32" t="s">
+        <v>107</v>
+      </c>
+      <c r="C23" s="32" t="s">
         <v>109</v>
       </c>
-      <c r="C23" t="s">
-        <v>111</v>
-      </c>
-      <c r="D23" s="4" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A24" s="13">
+      <c r="D23" s="19" t="s">
+        <v>157</v>
+      </c>
+      <c r="E23" s="32"/>
+    </row>
+    <row r="24" spans="1:5" ht="29" x14ac:dyDescent="0.35">
+      <c r="A24" s="34">
         <f t="shared" si="0"/>
         <v>17</v>
       </c>
-      <c r="B24" t="s">
-        <v>115</v>
-      </c>
-      <c r="C24" t="s">
-        <v>116</v>
-      </c>
-      <c r="D24" s="4" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A25" s="13">
+      <c r="B24" s="32" t="s">
+        <v>113</v>
+      </c>
+      <c r="C24" s="32" t="s">
+        <v>114</v>
+      </c>
+      <c r="D24" s="19" t="s">
+        <v>158</v>
+      </c>
+      <c r="E24" s="32"/>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A25" s="34">
         <f t="shared" si="0"/>
         <v>18</v>
       </c>
-      <c r="B25" s="10" t="s">
-        <v>182</v>
-      </c>
-      <c r="C25" s="10" t="s">
-        <v>187</v>
-      </c>
-      <c r="D25" s="4" t="s">
-        <v>42</v>
-      </c>
+      <c r="B25" s="31" t="s">
+        <v>180</v>
+      </c>
+      <c r="C25" s="31" t="s">
+        <v>184</v>
+      </c>
+      <c r="D25" s="19" t="s">
+        <v>40</v>
+      </c>
+      <c r="E25" s="32"/>
     </row>
   </sheetData>
   <mergeCells count="5">
-    <mergeCell ref="A3:C3"/>
+    <mergeCell ref="A3:B3"/>
     <mergeCell ref="A4:F5"/>
     <mergeCell ref="A6:F6"/>
     <mergeCell ref="A2:B2"/>
@@ -3079,632 +3157,656 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CA0AB6AA-BAF4-4C64-96FE-66D32370F298}">
-  <dimension ref="A1:U21"/>
+  <dimension ref="A1:R21"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="5" style="13" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="23.36328125" style="13" customWidth="1"/>
-    <col min="3" max="3" width="24.90625" style="13" customWidth="1"/>
-    <col min="4" max="4" width="35.54296875" style="13" customWidth="1"/>
-    <col min="5" max="5" width="18.36328125" style="13" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="16.1796875" style="13" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="9.1796875" style="17"/>
-    <col min="8" max="8" width="5" style="13" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="16.36328125" style="13" customWidth="1"/>
-    <col min="10" max="10" width="24.08984375" style="13" customWidth="1"/>
-    <col min="11" max="11" width="24" style="13" customWidth="1"/>
-    <col min="12" max="12" width="18.36328125" style="13" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="16.1796875" style="13" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="8.7265625" style="17"/>
-    <col min="15" max="15" width="5" style="13" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="21.81640625" style="13" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="25.6328125" style="13" customWidth="1"/>
-    <col min="18" max="18" width="23.90625" style="13" customWidth="1"/>
-    <col min="19" max="19" width="18.36328125" style="13" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="16.1796875" style="13" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="8.7265625" style="17"/>
-    <col min="22" max="16384" width="8.7265625" style="13"/>
+    <col min="1" max="1" width="5" style="10" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="34.453125" style="10" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="24.90625" style="10" customWidth="1"/>
+    <col min="4" max="4" width="35.54296875" style="10" customWidth="1"/>
+    <col min="5" max="5" width="18.36328125" style="10" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="16.1796875" style="35" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="5" style="10" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="29.1796875" style="10" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="24.08984375" style="10" customWidth="1"/>
+    <col min="10" max="10" width="24" style="10" customWidth="1"/>
+    <col min="11" max="11" width="18.36328125" style="10" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="16.1796875" style="35" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="5" style="10" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="29.1796875" style="10" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="25.6328125" style="10" customWidth="1"/>
+    <col min="16" max="16" width="23.90625" style="10" customWidth="1"/>
+    <col min="17" max="17" width="18.36328125" style="10" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="16.1796875" style="10" bestFit="1" customWidth="1"/>
+    <col min="19" max="16384" width="8.7265625" style="10"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="B1" s="3"/>
-      <c r="C1" s="3"/>
-      <c r="D1" s="3"/>
-      <c r="E1" s="3"/>
-      <c r="F1" s="3"/>
-      <c r="G1" s="2"/>
-      <c r="H1" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="I1" s="3"/>
-      <c r="J1" s="3"/>
-      <c r="K1" s="3"/>
-      <c r="L1" s="3"/>
-      <c r="M1" s="3"/>
-      <c r="N1" s="2"/>
-      <c r="O1" s="3" t="s">
-        <v>164</v>
-      </c>
-      <c r="P1" s="3"/>
-      <c r="Q1" s="3"/>
-      <c r="R1" s="3"/>
-      <c r="S1" s="3"/>
-      <c r="T1" s="3"/>
-      <c r="U1" s="2"/>
-    </row>
-    <row r="2" spans="1:21" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="3" t="s">
+    <row r="1" spans="1:18" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="17" t="s">
+        <v>14</v>
+      </c>
+      <c r="B1" s="17"/>
+      <c r="C1" s="17"/>
+      <c r="D1" s="17"/>
+      <c r="E1" s="17"/>
+      <c r="F1" s="24"/>
+      <c r="G1" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="H1" s="17"/>
+      <c r="I1" s="17"/>
+      <c r="J1" s="17"/>
+      <c r="K1" s="17"/>
+      <c r="L1" s="17"/>
+      <c r="M1" s="17" t="s">
+        <v>162</v>
+      </c>
+      <c r="N1" s="17"/>
+      <c r="O1" s="17"/>
+      <c r="P1" s="17"/>
+      <c r="Q1" s="17"/>
+      <c r="R1" s="17"/>
+    </row>
+    <row r="2" spans="1:18" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="17" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="3"/>
-      <c r="C2" s="3"/>
-      <c r="D2" s="5">
+      <c r="B2" s="17"/>
+      <c r="C2" s="20">
         <f>IFERROR(_xlfn.XLOOKUP(A1, TestMaster[Test Name], TestMaster[Test ID], "ID not found"), "")</f>
         <v>2</v>
       </c>
-      <c r="E2" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="F2" s="5"/>
-      <c r="G2" s="2"/>
-      <c r="H2" s="3" t="s">
+      <c r="D2" s="34"/>
+      <c r="E2" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="F2" s="21"/>
+      <c r="G2" s="17" t="s">
         <v>3</v>
       </c>
-      <c r="I2" s="3"/>
-      <c r="J2" s="3"/>
-      <c r="K2" s="5">
-        <f>IFERROR(_xlfn.XLOOKUP(H1, TestMaster[Test Name], TestMaster[Test ID], "ID not found"), "")</f>
+      <c r="H2" s="17"/>
+      <c r="I2" s="20">
+        <f>IFERROR(_xlfn.XLOOKUP(G1, TestMaster[Test Name], TestMaster[Test ID], "ID not found"), "")</f>
         <v>3</v>
       </c>
-      <c r="L2" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="M2" s="5"/>
-      <c r="N2" s="2"/>
-      <c r="O2" s="3" t="s">
+      <c r="J2" s="34"/>
+      <c r="K2" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="L2" s="21"/>
+      <c r="M2" s="17" t="s">
         <v>3</v>
       </c>
-      <c r="P2" s="3"/>
-      <c r="Q2" s="3"/>
-      <c r="R2" s="5">
-        <f>IFERROR(_xlfn.XLOOKUP(O1, TestMaster[Test Name], TestMaster[Test ID], "ID not found"), "")</f>
+      <c r="N2" s="17"/>
+      <c r="O2" s="20">
+        <f>IFERROR(_xlfn.XLOOKUP(M1, TestMaster[Test Name], TestMaster[Test ID], "ID not found"), "")</f>
         <v>4</v>
       </c>
-      <c r="S2" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="T2" s="5"/>
-      <c r="U2" s="2"/>
-    </row>
-    <row r="3" spans="1:21" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="3" t="s">
+      <c r="P2" s="34"/>
+      <c r="Q2" s="20" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="3"/>
-      <c r="C3" s="3"/>
-      <c r="D3" s="5" t="str">
+      <c r="R2" s="20"/>
+    </row>
+    <row r="3" spans="1:18" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="17" t="s">
+        <v>188</v>
+      </c>
+      <c r="B3" s="17"/>
+      <c r="C3" s="20" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(A1, TestMaster[Test Name], TestMaster[Test Priority], "Priority not found"), "")</f>
         <v>High</v>
       </c>
-      <c r="E3" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="F3" s="5" t="str">
+      <c r="D3" s="34"/>
+      <c r="E3" s="20" t="s">
+        <v>5</v>
+      </c>
+      <c r="F3" s="21" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(A1, TestMaster[Test Name], TestMaster[Test Status], "Status not found"), "")</f>
         <v>Not Implemented</v>
       </c>
-      <c r="G3" s="2"/>
-      <c r="H3" s="3" t="s">
+      <c r="G3" s="17" t="s">
+        <v>188</v>
+      </c>
+      <c r="H3" s="17"/>
+      <c r="I3" s="20" t="str">
+        <f>IFERROR(_xlfn.XLOOKUP(G1, TestMaster[Test Name], TestMaster[Test Priority], "Priority not found"), "")</f>
+        <v>Medium</v>
+      </c>
+      <c r="J3" s="34"/>
+      <c r="K3" s="20" t="s">
+        <v>5</v>
+      </c>
+      <c r="L3" s="21" t="str">
+        <f>IFERROR(_xlfn.XLOOKUP(G1, TestMaster[Test Name], TestMaster[Test Status], "Status not found"), "")</f>
+        <v>Not Implemented</v>
+      </c>
+      <c r="M3" s="17" t="s">
+        <v>188</v>
+      </c>
+      <c r="N3" s="17"/>
+      <c r="O3" s="20" t="str">
+        <f>IFERROR(_xlfn.XLOOKUP(M1, TestMaster[Test Name], TestMaster[Test Priority], "Priority not found"), "")</f>
+        <v>Low</v>
+      </c>
+      <c r="P3" s="34"/>
+      <c r="Q3" s="20" t="s">
+        <v>5</v>
+      </c>
+      <c r="R3" s="20" t="str">
+        <f>IFERROR(_xlfn.XLOOKUP(M1, TestMaster[Test Name], TestMaster[Test Status], "Status not found"), "")</f>
+        <v>Not Implemented</v>
+      </c>
+    </row>
+    <row r="4" spans="1:18" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="B4" s="17"/>
+      <c r="C4" s="17"/>
+      <c r="D4" s="17"/>
+      <c r="E4" s="17"/>
+      <c r="F4" s="24"/>
+      <c r="G4" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="H4" s="17"/>
+      <c r="I4" s="17"/>
+      <c r="J4" s="17"/>
+      <c r="K4" s="17"/>
+      <c r="L4" s="17"/>
+      <c r="M4" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="N4" s="17"/>
+      <c r="O4" s="17"/>
+      <c r="P4" s="17"/>
+      <c r="Q4" s="17"/>
+      <c r="R4" s="17"/>
+    </row>
+    <row r="5" spans="1:18" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="17"/>
+      <c r="B5" s="17"/>
+      <c r="C5" s="17"/>
+      <c r="D5" s="17"/>
+      <c r="E5" s="17"/>
+      <c r="F5" s="24"/>
+      <c r="G5" s="17"/>
+      <c r="H5" s="17"/>
+      <c r="I5" s="17"/>
+      <c r="J5" s="17"/>
+      <c r="K5" s="17"/>
+      <c r="L5" s="17"/>
+      <c r="M5" s="17"/>
+      <c r="N5" s="17"/>
+      <c r="O5" s="17"/>
+      <c r="P5" s="17"/>
+      <c r="Q5" s="17"/>
+      <c r="R5" s="17"/>
+    </row>
+    <row r="6" spans="1:18" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="17" t="s">
+        <v>7</v>
+      </c>
+      <c r="B6" s="17"/>
+      <c r="C6" s="17"/>
+      <c r="D6" s="17"/>
+      <c r="E6" s="17"/>
+      <c r="F6" s="24"/>
+      <c r="G6" s="17" t="s">
+        <v>7</v>
+      </c>
+      <c r="H6" s="17"/>
+      <c r="I6" s="17"/>
+      <c r="J6" s="17"/>
+      <c r="K6" s="17"/>
+      <c r="L6" s="17"/>
+      <c r="M6" s="17" t="s">
+        <v>7</v>
+      </c>
+      <c r="N6" s="17"/>
+      <c r="O6" s="17"/>
+      <c r="P6" s="17"/>
+      <c r="Q6" s="17"/>
+      <c r="R6" s="17"/>
+    </row>
+    <row r="7" spans="1:18" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="25" t="s">
+        <v>0</v>
+      </c>
+      <c r="B7" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="C7" s="25" t="s">
+        <v>9</v>
+      </c>
+      <c r="D7" s="25" t="s">
+        <v>1</v>
+      </c>
+      <c r="E7" s="25" t="s">
+        <v>10</v>
+      </c>
+      <c r="F7" s="27" t="s">
+        <v>2</v>
+      </c>
+      <c r="G7" s="25" t="s">
+        <v>0</v>
+      </c>
+      <c r="H7" s="36" t="s">
+        <v>8</v>
+      </c>
+      <c r="I7" s="25" t="s">
+        <v>9</v>
+      </c>
+      <c r="J7" s="25" t="s">
+        <v>1</v>
+      </c>
+      <c r="K7" s="25" t="s">
+        <v>10</v>
+      </c>
+      <c r="L7" s="27" t="s">
+        <v>2</v>
+      </c>
+      <c r="M7" s="25" t="s">
+        <v>0</v>
+      </c>
+      <c r="N7" s="36" t="s">
+        <v>8</v>
+      </c>
+      <c r="O7" s="25" t="s">
+        <v>9</v>
+      </c>
+      <c r="P7" s="25" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q7" s="25" t="s">
+        <v>10</v>
+      </c>
+      <c r="R7" s="25" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A8" s="34">
+        <v>1</v>
+      </c>
+      <c r="B8" s="31" t="s">
+        <v>124</v>
+      </c>
+      <c r="C8" s="31" t="s">
+        <v>27</v>
+      </c>
+      <c r="D8" s="31" t="s">
+        <v>125</v>
+      </c>
+      <c r="E8" s="34"/>
+      <c r="G8" s="34">
+        <v>1</v>
+      </c>
+      <c r="H8" s="34" t="s">
+        <v>124</v>
+      </c>
+      <c r="I8" s="31" t="s">
+        <v>27</v>
+      </c>
+      <c r="J8" s="31" t="s">
+        <v>125</v>
+      </c>
+      <c r="K8" s="34"/>
+      <c r="M8" s="34">
+        <v>1</v>
+      </c>
+      <c r="N8" s="34" t="s">
+        <v>124</v>
+      </c>
+      <c r="O8" s="31" t="s">
+        <v>27</v>
+      </c>
+      <c r="P8" s="31" t="s">
+        <v>125</v>
+      </c>
+      <c r="Q8" s="34"/>
+      <c r="R8" s="34"/>
+    </row>
+    <row r="9" spans="1:18" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A9" s="34">
+        <v>2</v>
+      </c>
+      <c r="B9" s="31" t="s">
+        <v>126</v>
+      </c>
+      <c r="C9" s="33" t="s">
+        <v>141</v>
+      </c>
+      <c r="D9" s="31" t="s">
+        <v>127</v>
+      </c>
+      <c r="E9" s="34"/>
+      <c r="G9" s="34">
+        <v>2</v>
+      </c>
+      <c r="H9" s="34" t="s">
+        <v>126</v>
+      </c>
+      <c r="I9" s="33" t="s">
+        <v>139</v>
+      </c>
+      <c r="J9" s="31" t="s">
+        <v>140</v>
+      </c>
+      <c r="K9" s="34"/>
+      <c r="M9" s="34">
+        <v>2</v>
+      </c>
+      <c r="N9" s="34" t="s">
+        <v>126</v>
+      </c>
+      <c r="O9" s="33" t="s">
+        <v>141</v>
+      </c>
+      <c r="P9" s="31" t="s">
+        <v>127</v>
+      </c>
+      <c r="Q9" s="34"/>
+      <c r="R9" s="34"/>
+    </row>
+    <row r="10" spans="1:18" ht="29" x14ac:dyDescent="0.35">
+      <c r="A10" s="34">
+        <v>3</v>
+      </c>
+      <c r="B10" s="31" t="s">
+        <v>128</v>
+      </c>
+      <c r="C10" s="31" t="s">
+        <v>142</v>
+      </c>
+      <c r="D10" s="31" t="s">
+        <v>129</v>
+      </c>
+      <c r="E10" s="34"/>
+      <c r="G10" s="34">
+        <v>3</v>
+      </c>
+      <c r="H10" s="34" t="s">
+        <v>128</v>
+      </c>
+      <c r="I10" s="31" t="s">
+        <v>143</v>
+      </c>
+      <c r="J10" s="31" t="s">
+        <v>129</v>
+      </c>
+      <c r="K10" s="34"/>
+      <c r="M10" s="34">
+        <v>3</v>
+      </c>
+      <c r="N10" s="34" t="s">
+        <v>128</v>
+      </c>
+      <c r="O10" s="31" t="s">
+        <v>142</v>
+      </c>
+      <c r="P10" s="31" t="s">
+        <v>129</v>
+      </c>
+      <c r="Q10" s="34"/>
+      <c r="R10" s="34"/>
+    </row>
+    <row r="11" spans="1:18" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A11" s="34">
         <v>4</v>
       </c>
-      <c r="I3" s="3"/>
-      <c r="J3" s="3"/>
-      <c r="K3" s="5" t="str">
-        <f>IFERROR(_xlfn.XLOOKUP(H1, TestMaster[Test Name], TestMaster[Test Priority], "Priority not found"), "")</f>
-        <v>Medium</v>
-      </c>
-      <c r="L3" s="5" t="s">
+      <c r="B11" s="31" t="s">
+        <v>130</v>
+      </c>
+      <c r="C11" s="31" t="s">
+        <v>131</v>
+      </c>
+      <c r="D11" s="31" t="s">
+        <v>132</v>
+      </c>
+      <c r="E11" s="34"/>
+      <c r="G11" s="34">
+        <v>4</v>
+      </c>
+      <c r="H11" s="34" t="s">
+        <v>130</v>
+      </c>
+      <c r="I11" s="31" t="s">
+        <v>131</v>
+      </c>
+      <c r="J11" s="31" t="s">
+        <v>144</v>
+      </c>
+      <c r="K11" s="34"/>
+      <c r="M11" s="34">
+        <v>4</v>
+      </c>
+      <c r="N11" s="34" t="s">
+        <v>130</v>
+      </c>
+      <c r="O11" s="31" t="s">
+        <v>151</v>
+      </c>
+      <c r="P11" s="31" t="s">
+        <v>132</v>
+      </c>
+      <c r="Q11" s="34"/>
+      <c r="R11" s="34"/>
+    </row>
+    <row r="12" spans="1:18" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A12" s="34">
+        <v>5</v>
+      </c>
+      <c r="B12" s="31" t="s">
+        <v>134</v>
+      </c>
+      <c r="C12" s="31" t="s">
+        <v>135</v>
+      </c>
+      <c r="D12" s="31" t="s">
+        <v>137</v>
+      </c>
+      <c r="E12" s="34"/>
+      <c r="G12" s="34"/>
+      <c r="H12" s="34"/>
+      <c r="I12" s="34"/>
+      <c r="J12" s="34"/>
+      <c r="K12" s="34"/>
+      <c r="M12" s="34">
+        <v>5</v>
+      </c>
+      <c r="N12" s="34" t="s">
+        <v>145</v>
+      </c>
+      <c r="O12" s="31" t="s">
+        <v>146</v>
+      </c>
+      <c r="P12" s="31" t="s">
+        <v>148</v>
+      </c>
+      <c r="Q12" s="34"/>
+      <c r="R12" s="34"/>
+    </row>
+    <row r="13" spans="1:18" ht="29" x14ac:dyDescent="0.35">
+      <c r="A13" s="34">
         <v>6</v>
       </c>
-      <c r="M3" s="5" t="str">
-        <f>IFERROR(_xlfn.XLOOKUP(H1, TestMaster[Test Name], TestMaster[Test Status], "Status not found"), "")</f>
-        <v>Not Implemented</v>
-      </c>
-      <c r="N3" s="2"/>
-      <c r="O3" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="P3" s="3"/>
-      <c r="Q3" s="3"/>
-      <c r="R3" s="5" t="str">
-        <f>IFERROR(_xlfn.XLOOKUP(O1, TestMaster[Test Name], TestMaster[Test Priority], "Priority not found"), "")</f>
-        <v>Low</v>
-      </c>
-      <c r="S3" s="5" t="s">
+      <c r="B13" s="31" t="s">
+        <v>136</v>
+      </c>
+      <c r="C13" s="31" t="s">
+        <v>133</v>
+      </c>
+      <c r="D13" s="31" t="s">
+        <v>138</v>
+      </c>
+      <c r="E13" s="34"/>
+      <c r="G13" s="34"/>
+      <c r="H13" s="34"/>
+      <c r="I13" s="34"/>
+      <c r="J13" s="34"/>
+      <c r="K13" s="34"/>
+      <c r="M13" s="34">
         <v>6</v>
       </c>
-      <c r="T3" s="5" t="str">
-        <f>IFERROR(_xlfn.XLOOKUP(O1, TestMaster[Test Name], TestMaster[Test Status], "Status not found"), "")</f>
-        <v>Not Implemented</v>
-      </c>
-      <c r="U3" s="2"/>
-    </row>
-    <row r="4" spans="1:21" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="3" t="s">
+      <c r="N13" s="34" t="s">
+        <v>147</v>
+      </c>
+      <c r="O13" s="31" t="s">
+        <v>146</v>
+      </c>
+      <c r="P13" s="31" t="s">
+        <v>149</v>
+      </c>
+      <c r="Q13" s="34"/>
+      <c r="R13" s="34"/>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="M14" s="32">
         <v>7</v>
       </c>
-      <c r="B4" s="3"/>
-      <c r="C4" s="3"/>
-      <c r="D4" s="3"/>
-      <c r="E4" s="3"/>
-      <c r="F4" s="3"/>
-      <c r="G4" s="2"/>
-      <c r="H4" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="I4" s="3"/>
-      <c r="J4" s="3"/>
-      <c r="K4" s="3"/>
-      <c r="L4" s="3"/>
-      <c r="M4" s="3"/>
-      <c r="N4" s="2"/>
-      <c r="O4" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="P4" s="3"/>
-      <c r="Q4" s="3"/>
-      <c r="R4" s="3"/>
-      <c r="S4" s="3"/>
-      <c r="T4" s="3"/>
-      <c r="U4" s="2"/>
-    </row>
-    <row r="5" spans="1:21" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="3"/>
-      <c r="B5" s="3"/>
-      <c r="C5" s="3"/>
-      <c r="D5" s="3"/>
-      <c r="E5" s="3"/>
-      <c r="F5" s="3"/>
-      <c r="G5" s="2"/>
-      <c r="H5" s="3"/>
-      <c r="I5" s="3"/>
-      <c r="J5" s="3"/>
-      <c r="K5" s="3"/>
-      <c r="L5" s="3"/>
-      <c r="M5" s="3"/>
-      <c r="N5" s="2"/>
-      <c r="O5" s="3"/>
-      <c r="P5" s="3"/>
-      <c r="Q5" s="3"/>
-      <c r="R5" s="3"/>
-      <c r="S5" s="3"/>
-      <c r="T5" s="3"/>
-      <c r="U5" s="2"/>
-    </row>
-    <row r="6" spans="1:21" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="3" t="s">
+      <c r="N14" s="20" t="s">
+        <v>107</v>
+      </c>
+      <c r="O14" s="32" t="s">
+        <v>111</v>
+      </c>
+      <c r="P14" s="32" t="s">
+        <v>150</v>
+      </c>
+      <c r="Q14" s="34"/>
+      <c r="R14" s="34"/>
+    </row>
+    <row r="15" spans="1:18" ht="29" x14ac:dyDescent="0.35">
+      <c r="M15" s="34">
         <v>8</v>
       </c>
-      <c r="B6" s="3"/>
-      <c r="C6" s="3"/>
-      <c r="D6" s="3"/>
-      <c r="E6" s="3"/>
-      <c r="F6" s="3"/>
-      <c r="G6" s="2"/>
-      <c r="H6" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="I6" s="3"/>
-      <c r="J6" s="3"/>
-      <c r="K6" s="3"/>
-      <c r="L6" s="3"/>
-      <c r="M6" s="3"/>
-      <c r="N6" s="2"/>
-      <c r="O6" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="P6" s="3"/>
-      <c r="Q6" s="3"/>
-      <c r="R6" s="3"/>
-      <c r="S6" s="3"/>
-      <c r="T6" s="3"/>
-      <c r="U6" s="2"/>
-    </row>
-    <row r="7" spans="1:21" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B7" s="1" t="s">
+      <c r="N15" s="34" t="s">
+        <v>152</v>
+      </c>
+      <c r="O15" s="34" t="s">
+        <v>146</v>
+      </c>
+      <c r="P15" s="31" t="s">
+        <v>149</v>
+      </c>
+      <c r="Q15" s="34"/>
+      <c r="R15" s="34"/>
+    </row>
+    <row r="16" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="M16" s="32">
         <v>9</v>
       </c>
-      <c r="C7" s="1" t="s">
+      <c r="N16" s="20" t="s">
+        <v>107</v>
+      </c>
+      <c r="O16" s="32" t="s">
+        <v>123</v>
+      </c>
+      <c r="P16" s="32" t="s">
+        <v>153</v>
+      </c>
+      <c r="Q16" s="34"/>
+      <c r="R16" s="34"/>
+    </row>
+    <row r="17" spans="13:18" ht="29" x14ac:dyDescent="0.35">
+      <c r="M17" s="32">
         <v>10</v>
       </c>
-      <c r="D7" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="E7" s="1" t="s">
+      <c r="N17" s="34" t="s">
+        <v>154</v>
+      </c>
+      <c r="O17" s="34" t="s">
+        <v>146</v>
+      </c>
+      <c r="P17" s="31" t="s">
+        <v>149</v>
+      </c>
+      <c r="Q17" s="34"/>
+      <c r="R17" s="34"/>
+    </row>
+    <row r="18" spans="13:18" x14ac:dyDescent="0.35">
+      <c r="M18" s="34">
         <v>11</v>
       </c>
-      <c r="F7" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="G7" s="2"/>
-      <c r="H7" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="I7" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="J7" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="K7" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="L7" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="M7" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="N7" s="2"/>
-      <c r="O7" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="P7" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="Q7" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="R7" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="S7" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="T7" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="U7" s="2"/>
-    </row>
-    <row r="8" spans="1:21" ht="29" x14ac:dyDescent="0.35">
-      <c r="A8" s="13">
-        <v>1</v>
-      </c>
-      <c r="B8" s="10" t="s">
-        <v>126</v>
-      </c>
-      <c r="C8" s="10" t="s">
-        <v>29</v>
-      </c>
-      <c r="D8" s="10" t="s">
-        <v>127</v>
-      </c>
-      <c r="H8" s="13">
-        <v>1</v>
-      </c>
-      <c r="I8" s="10" t="s">
-        <v>126</v>
-      </c>
-      <c r="J8" s="10" t="s">
-        <v>29</v>
-      </c>
-      <c r="K8" s="10" t="s">
-        <v>127</v>
-      </c>
-      <c r="O8" s="13">
-        <v>1</v>
-      </c>
-      <c r="P8" s="10" t="s">
-        <v>126</v>
-      </c>
-      <c r="Q8" s="10" t="s">
-        <v>29</v>
-      </c>
-      <c r="R8" s="10" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="9" spans="1:21" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A9" s="13">
-        <v>2</v>
-      </c>
-      <c r="B9" s="10" t="s">
-        <v>128</v>
-      </c>
-      <c r="C9" s="18" t="s">
-        <v>143</v>
-      </c>
-      <c r="D9" s="10" t="s">
-        <v>129</v>
-      </c>
-      <c r="H9" s="13">
-        <v>2</v>
-      </c>
-      <c r="I9" s="10" t="s">
-        <v>128</v>
-      </c>
-      <c r="J9" s="18" t="s">
-        <v>141</v>
-      </c>
-      <c r="K9" s="10" t="s">
-        <v>142</v>
-      </c>
-      <c r="O9" s="13">
-        <v>2</v>
-      </c>
-      <c r="P9" s="10" t="s">
-        <v>128</v>
-      </c>
-      <c r="Q9" s="18" t="s">
-        <v>143</v>
-      </c>
-      <c r="R9" s="10" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="10" spans="1:21" ht="29" x14ac:dyDescent="0.35">
-      <c r="A10" s="13">
-        <v>3</v>
-      </c>
-      <c r="B10" s="10" t="s">
-        <v>130</v>
-      </c>
-      <c r="C10" s="10" t="s">
-        <v>144</v>
-      </c>
-      <c r="D10" s="10" t="s">
-        <v>131</v>
-      </c>
-      <c r="H10" s="13">
-        <v>3</v>
-      </c>
-      <c r="I10" s="10" t="s">
-        <v>130</v>
-      </c>
-      <c r="J10" s="10" t="s">
-        <v>145</v>
-      </c>
-      <c r="K10" s="10" t="s">
-        <v>131</v>
-      </c>
-      <c r="O10" s="13">
-        <v>3</v>
-      </c>
-      <c r="P10" s="10" t="s">
-        <v>130</v>
-      </c>
-      <c r="Q10" s="10" t="s">
-        <v>144</v>
-      </c>
-      <c r="R10" s="10" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="11" spans="1:21" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A11" s="13">
-        <v>4</v>
-      </c>
-      <c r="B11" s="10" t="s">
-        <v>132</v>
-      </c>
-      <c r="C11" s="10" t="s">
-        <v>133</v>
-      </c>
-      <c r="D11" s="10" t="s">
-        <v>134</v>
-      </c>
-      <c r="H11" s="13">
-        <v>4</v>
-      </c>
-      <c r="I11" s="10" t="s">
-        <v>132</v>
-      </c>
-      <c r="J11" s="10" t="s">
-        <v>133</v>
-      </c>
-      <c r="K11" s="10" t="s">
+      <c r="N18" s="20" t="s">
+        <v>107</v>
+      </c>
+      <c r="O18" s="32" t="s">
+        <v>109</v>
+      </c>
+      <c r="P18" s="32" t="s">
+        <v>157</v>
+      </c>
+      <c r="Q18" s="34"/>
+      <c r="R18" s="34"/>
+    </row>
+    <row r="19" spans="13:18" x14ac:dyDescent="0.35">
+      <c r="M19" s="32">
+        <v>12</v>
+      </c>
+      <c r="N19" s="20" t="s">
+        <v>112</v>
+      </c>
+      <c r="O19" s="32" t="s">
         <v>146</v>
       </c>
-      <c r="O11" s="13">
-        <v>4</v>
-      </c>
-      <c r="P11" s="10" t="s">
-        <v>132</v>
-      </c>
-      <c r="Q11" s="10" t="s">
-        <v>153</v>
-      </c>
-      <c r="R11" s="10" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="12" spans="1:21" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A12" s="13">
-        <v>5</v>
-      </c>
-      <c r="B12" s="10" t="s">
-        <v>136</v>
-      </c>
-      <c r="C12" s="10" t="s">
-        <v>137</v>
-      </c>
-      <c r="D12" s="10" t="s">
-        <v>139</v>
-      </c>
-      <c r="O12" s="13">
-        <v>5</v>
-      </c>
-      <c r="P12" s="10" t="s">
-        <v>147</v>
-      </c>
-      <c r="Q12" s="10" t="s">
-        <v>148</v>
-      </c>
-      <c r="R12" s="10" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="13" spans="1:21" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A13" s="13">
-        <v>6</v>
-      </c>
-      <c r="B13" s="10" t="s">
-        <v>138</v>
-      </c>
-      <c r="C13" s="10" t="s">
-        <v>135</v>
-      </c>
-      <c r="D13" s="10" t="s">
-        <v>140</v>
-      </c>
-      <c r="O13" s="13">
-        <v>6</v>
-      </c>
-      <c r="P13" s="10" t="s">
-        <v>149</v>
-      </c>
-      <c r="Q13" s="10" t="s">
-        <v>148</v>
-      </c>
-      <c r="R13" s="10" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="14" spans="1:21" x14ac:dyDescent="0.35">
-      <c r="O14">
-        <v>7</v>
-      </c>
-      <c r="P14" t="s">
+      <c r="P19" s="32" t="s">
+        <v>110</v>
+      </c>
+      <c r="Q19" s="34"/>
+      <c r="R19" s="34"/>
+    </row>
+    <row r="20" spans="13:18" x14ac:dyDescent="0.35">
+      <c r="M20" s="34">
+        <v>13</v>
+      </c>
+      <c r="N20" s="20" t="s">
+        <v>107</v>
+      </c>
+      <c r="O20" s="32" t="s">
         <v>109</v>
       </c>
-      <c r="Q14" t="s">
+      <c r="P20" s="32" t="s">
+        <v>157</v>
+      </c>
+      <c r="Q20" s="34"/>
+      <c r="R20" s="34"/>
+    </row>
+    <row r="21" spans="13:18" x14ac:dyDescent="0.35">
+      <c r="M21" s="32">
+        <v>14</v>
+      </c>
+      <c r="N21" s="20" t="s">
         <v>113</v>
       </c>
-      <c r="R14" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="15" spans="1:21" ht="29" x14ac:dyDescent="0.35">
-      <c r="O15" s="13">
-        <v>8</v>
-      </c>
-      <c r="P15" s="13" t="s">
-        <v>154</v>
-      </c>
-      <c r="Q15" s="13" t="s">
-        <v>148</v>
-      </c>
-      <c r="R15" s="10" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="16" spans="1:21" x14ac:dyDescent="0.35">
-      <c r="O16">
-        <v>9</v>
-      </c>
-      <c r="P16" t="s">
-        <v>109</v>
-      </c>
-      <c r="Q16" t="s">
-        <v>125</v>
-      </c>
-      <c r="R16" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="17" spans="15:18" ht="29" x14ac:dyDescent="0.35">
-      <c r="O17">
-        <v>10</v>
-      </c>
-      <c r="P17" s="13" t="s">
-        <v>156</v>
-      </c>
-      <c r="Q17" s="13" t="s">
-        <v>148</v>
-      </c>
-      <c r="R17" s="10" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="18" spans="15:18" x14ac:dyDescent="0.35">
-      <c r="O18" s="13">
-        <v>11</v>
-      </c>
-      <c r="P18" t="s">
-        <v>109</v>
-      </c>
-      <c r="Q18" t="s">
-        <v>111</v>
-      </c>
-      <c r="R18" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="19" spans="15:18" x14ac:dyDescent="0.35">
-      <c r="O19">
-        <v>12</v>
-      </c>
-      <c r="P19" t="s">
+      <c r="O21" s="32" t="s">
         <v>114</v>
       </c>
-      <c r="Q19" t="s">
-        <v>148</v>
-      </c>
-      <c r="R19" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="20" spans="15:18" x14ac:dyDescent="0.35">
-      <c r="O20" s="13">
-        <v>13</v>
-      </c>
-      <c r="P20" t="s">
-        <v>109</v>
-      </c>
-      <c r="Q20" t="s">
-        <v>111</v>
-      </c>
-      <c r="R20" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="21" spans="15:18" x14ac:dyDescent="0.35">
-      <c r="O21">
-        <v>14</v>
-      </c>
-      <c r="P21" t="s">
-        <v>115</v>
-      </c>
-      <c r="Q21" t="s">
-        <v>116</v>
-      </c>
-      <c r="R21" t="s">
-        <v>160</v>
-      </c>
+      <c r="P21" s="32" t="s">
+        <v>158</v>
+      </c>
+      <c r="Q21" s="34"/>
+      <c r="R21" s="34"/>
     </row>
   </sheetData>
   <mergeCells count="15">
-    <mergeCell ref="O1:T1"/>
-    <mergeCell ref="O2:Q2"/>
-    <mergeCell ref="O3:Q3"/>
-    <mergeCell ref="H4:M5"/>
-    <mergeCell ref="H6:M6"/>
-    <mergeCell ref="O4:T5"/>
-    <mergeCell ref="O6:T6"/>
-    <mergeCell ref="H2:J2"/>
-    <mergeCell ref="H3:J3"/>
-    <mergeCell ref="H1:M1"/>
+    <mergeCell ref="M1:R1"/>
+    <mergeCell ref="M2:N2"/>
+    <mergeCell ref="M3:N3"/>
+    <mergeCell ref="G4:L5"/>
+    <mergeCell ref="G6:L6"/>
+    <mergeCell ref="M4:R5"/>
+    <mergeCell ref="M6:R6"/>
+    <mergeCell ref="G2:H2"/>
+    <mergeCell ref="G3:H3"/>
+    <mergeCell ref="G1:L1"/>
     <mergeCell ref="A4:F5"/>
     <mergeCell ref="A6:F6"/>
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A2:C2"/>
-    <mergeCell ref="A3:C3"/>
+    <mergeCell ref="A3:B3"/>
+    <mergeCell ref="A2:B2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3712,7 +3814,721 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{31B60B4E-CDD0-4CEE-BA63-4F898D2F5023}">
-  <dimension ref="A1:T25"/>
+  <dimension ref="A1:R25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="5" customWidth="1"/>
+    <col min="2" max="2" width="22.1796875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.54296875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="31.1796875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="18.36328125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="16.1796875" style="23" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="5" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="30.36328125" customWidth="1"/>
+    <col min="9" max="9" width="27.54296875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="30.26953125" customWidth="1"/>
+    <col min="11" max="11" width="18.36328125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="16.1796875" style="23" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="5" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="35.453125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="20.54296875" customWidth="1"/>
+    <col min="16" max="16" width="31.1796875" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="18.36328125" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="16.1796875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A1" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="B1" s="17"/>
+      <c r="C1" s="17"/>
+      <c r="D1" s="17"/>
+      <c r="E1" s="17"/>
+      <c r="F1" s="24"/>
+      <c r="G1" s="16" t="s">
+        <v>17</v>
+      </c>
+      <c r="H1" s="17"/>
+      <c r="I1" s="17"/>
+      <c r="J1" s="17"/>
+      <c r="K1" s="17"/>
+      <c r="L1" s="24"/>
+      <c r="M1" s="17" t="s">
+        <v>116</v>
+      </c>
+      <c r="N1" s="17"/>
+      <c r="O1" s="17"/>
+      <c r="P1" s="17"/>
+      <c r="Q1" s="17"/>
+      <c r="R1" s="17"/>
+    </row>
+    <row r="2" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A2" s="17" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" s="17"/>
+      <c r="C2" s="18">
+        <f>IFERROR(_xlfn.XLOOKUP(A1, TestMaster[Test Name], TestMaster[Test ID], "ID not found"), "")</f>
+        <v>5</v>
+      </c>
+      <c r="D2" s="32"/>
+      <c r="E2" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="F2" s="21"/>
+      <c r="G2" s="17" t="s">
+        <v>3</v>
+      </c>
+      <c r="H2" s="17"/>
+      <c r="I2" s="18">
+        <f>IFERROR(_xlfn.XLOOKUP(G1, TestMaster[Test Name], TestMaster[Test ID], "ID not found"), "")</f>
+        <v>6</v>
+      </c>
+      <c r="J2" s="32"/>
+      <c r="K2" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="L2" s="21"/>
+      <c r="M2" s="17" t="s">
+        <v>3</v>
+      </c>
+      <c r="N2" s="17"/>
+      <c r="O2" s="37">
+        <f>IFERROR(_xlfn.XLOOKUP(M1, TestMaster[Test Name], TestMaster[Test ID], "ID not found"), "")</f>
+        <v>7</v>
+      </c>
+      <c r="P2" s="32"/>
+      <c r="Q2" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="R2" s="20"/>
+    </row>
+    <row r="3" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A3" s="17" t="s">
+        <v>188</v>
+      </c>
+      <c r="B3" s="17"/>
+      <c r="C3" s="18" t="str">
+        <f>IFERROR(_xlfn.XLOOKUP(A1, TestMaster[Test Name], TestMaster[Test Priority], "Priority not found"), "")</f>
+        <v>Medium</v>
+      </c>
+      <c r="D3" s="32"/>
+      <c r="E3" s="20" t="s">
+        <v>5</v>
+      </c>
+      <c r="F3" s="21" t="str">
+        <f>IFERROR(_xlfn.XLOOKUP(A1, TestMaster[Test Name], TestMaster[Test Status], "Status not found"), "")</f>
+        <v>Not Implemented</v>
+      </c>
+      <c r="G3" s="17" t="s">
+        <v>188</v>
+      </c>
+      <c r="H3" s="17"/>
+      <c r="I3" s="18" t="str">
+        <f>IFERROR(_xlfn.XLOOKUP(G1, TestMaster[Test Name], TestMaster[Test Priority], "Priority not found"), "")</f>
+        <v>Medium</v>
+      </c>
+      <c r="J3" s="32"/>
+      <c r="K3" s="20" t="s">
+        <v>5</v>
+      </c>
+      <c r="L3" s="21" t="str">
+        <f>IFERROR(_xlfn.XLOOKUP(G1, TestMaster[Test Name], TestMaster[Test Status], "Status not found"), "")</f>
+        <v>Not Implemented</v>
+      </c>
+      <c r="M3" s="17" t="s">
+        <v>188</v>
+      </c>
+      <c r="N3" s="17"/>
+      <c r="O3" s="37" t="str">
+        <f>IFERROR(_xlfn.XLOOKUP(M1, TestMaster[Test Name], TestMaster[Test Priority], "Priority not found"), "")</f>
+        <v>Low</v>
+      </c>
+      <c r="P3" s="32"/>
+      <c r="Q3" s="20" t="s">
+        <v>5</v>
+      </c>
+      <c r="R3" s="20" t="str">
+        <f>IFERROR(_xlfn.XLOOKUP(M1, TestMaster[Test Name], TestMaster[Test Status], "Status not found"), "")</f>
+        <v>Not Implemented</v>
+      </c>
+    </row>
+    <row r="4" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A4" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="B4" s="17"/>
+      <c r="C4" s="17"/>
+      <c r="D4" s="17"/>
+      <c r="E4" s="17"/>
+      <c r="F4" s="24"/>
+      <c r="G4" s="16" t="s">
+        <v>6</v>
+      </c>
+      <c r="H4" s="17"/>
+      <c r="I4" s="17"/>
+      <c r="J4" s="17"/>
+      <c r="K4" s="17"/>
+      <c r="L4" s="24"/>
+      <c r="M4" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="N4" s="17"/>
+      <c r="O4" s="17"/>
+      <c r="P4" s="17"/>
+      <c r="Q4" s="17"/>
+      <c r="R4" s="17"/>
+    </row>
+    <row r="5" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A5" s="17"/>
+      <c r="B5" s="17"/>
+      <c r="C5" s="17"/>
+      <c r="D5" s="17"/>
+      <c r="E5" s="17"/>
+      <c r="F5" s="24"/>
+      <c r="G5" s="16"/>
+      <c r="H5" s="17"/>
+      <c r="I5" s="17"/>
+      <c r="J5" s="17"/>
+      <c r="K5" s="17"/>
+      <c r="L5" s="24"/>
+      <c r="M5" s="17"/>
+      <c r="N5" s="17"/>
+      <c r="O5" s="17"/>
+      <c r="P5" s="17"/>
+      <c r="Q5" s="17"/>
+      <c r="R5" s="17"/>
+    </row>
+    <row r="6" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A6" s="17" t="s">
+        <v>7</v>
+      </c>
+      <c r="B6" s="17"/>
+      <c r="C6" s="17"/>
+      <c r="D6" s="17"/>
+      <c r="E6" s="17"/>
+      <c r="F6" s="24"/>
+      <c r="G6" s="16" t="s">
+        <v>7</v>
+      </c>
+      <c r="H6" s="17"/>
+      <c r="I6" s="17"/>
+      <c r="J6" s="17"/>
+      <c r="K6" s="17"/>
+      <c r="L6" s="24"/>
+      <c r="M6" s="17" t="s">
+        <v>7</v>
+      </c>
+      <c r="N6" s="17"/>
+      <c r="O6" s="17"/>
+      <c r="P6" s="17"/>
+      <c r="Q6" s="17"/>
+      <c r="R6" s="17"/>
+    </row>
+    <row r="7" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A7" s="25" t="s">
+        <v>0</v>
+      </c>
+      <c r="B7" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="C7" s="25" t="s">
+        <v>9</v>
+      </c>
+      <c r="D7" s="25" t="s">
+        <v>1</v>
+      </c>
+      <c r="E7" s="25" t="s">
+        <v>10</v>
+      </c>
+      <c r="F7" s="27" t="s">
+        <v>2</v>
+      </c>
+      <c r="G7" s="25" t="s">
+        <v>0</v>
+      </c>
+      <c r="H7" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="I7" s="25" t="s">
+        <v>9</v>
+      </c>
+      <c r="J7" s="25" t="s">
+        <v>1</v>
+      </c>
+      <c r="K7" s="25" t="s">
+        <v>10</v>
+      </c>
+      <c r="L7" s="27" t="s">
+        <v>2</v>
+      </c>
+      <c r="M7" s="25" t="s">
+        <v>0</v>
+      </c>
+      <c r="N7" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="O7" s="25" t="s">
+        <v>9</v>
+      </c>
+      <c r="P7" s="25" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q7" s="25" t="s">
+        <v>10</v>
+      </c>
+      <c r="R7" s="25" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:18" s="4" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="34">
+        <v>1</v>
+      </c>
+      <c r="B8" s="34" t="s">
+        <v>88</v>
+      </c>
+      <c r="C8" s="34" t="s">
+        <v>27</v>
+      </c>
+      <c r="D8" s="34" t="s">
+        <v>74</v>
+      </c>
+      <c r="E8" s="20"/>
+      <c r="F8" s="21"/>
+      <c r="G8" s="20">
+        <v>1</v>
+      </c>
+      <c r="H8" s="34" t="s">
+        <v>88</v>
+      </c>
+      <c r="I8" s="34" t="s">
+        <v>27</v>
+      </c>
+      <c r="J8" s="34" t="s">
+        <v>77</v>
+      </c>
+      <c r="K8" s="20"/>
+      <c r="L8" s="21"/>
+      <c r="M8" s="20">
+        <v>1</v>
+      </c>
+      <c r="N8" s="34" t="s">
+        <v>88</v>
+      </c>
+      <c r="O8" s="34" t="s">
+        <v>27</v>
+      </c>
+      <c r="P8" s="34" t="s">
+        <v>77</v>
+      </c>
+      <c r="Q8" s="20"/>
+      <c r="R8" s="20"/>
+    </row>
+    <row r="9" spans="1:18" s="4" customFormat="1" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A9" s="34">
+        <v>2</v>
+      </c>
+      <c r="B9" s="34" t="s">
+        <v>56</v>
+      </c>
+      <c r="C9" s="34" t="s">
+        <v>27</v>
+      </c>
+      <c r="D9" s="34" t="s">
+        <v>40</v>
+      </c>
+      <c r="E9" s="20"/>
+      <c r="F9" s="21"/>
+      <c r="G9" s="20">
+        <v>2</v>
+      </c>
+      <c r="H9" s="31" t="s">
+        <v>75</v>
+      </c>
+      <c r="I9" s="31" t="s">
+        <v>78</v>
+      </c>
+      <c r="J9" s="31" t="s">
+        <v>80</v>
+      </c>
+      <c r="K9" s="20"/>
+      <c r="L9" s="21"/>
+      <c r="M9" s="20">
+        <v>2</v>
+      </c>
+      <c r="N9" s="31" t="s">
+        <v>75</v>
+      </c>
+      <c r="O9" s="31" t="s">
+        <v>78</v>
+      </c>
+      <c r="P9" s="31" t="s">
+        <v>80</v>
+      </c>
+      <c r="Q9" s="20"/>
+      <c r="R9" s="20"/>
+    </row>
+    <row r="10" spans="1:18" ht="29" x14ac:dyDescent="0.35">
+      <c r="G10" s="32">
+        <v>3</v>
+      </c>
+      <c r="H10" s="31" t="s">
+        <v>117</v>
+      </c>
+      <c r="I10" s="31" t="s">
+        <v>100</v>
+      </c>
+      <c r="J10" s="31" t="s">
+        <v>105</v>
+      </c>
+      <c r="K10" s="32"/>
+      <c r="M10" s="32">
+        <v>3</v>
+      </c>
+      <c r="N10" s="31" t="s">
+        <v>120</v>
+      </c>
+      <c r="O10" s="31" t="s">
+        <v>100</v>
+      </c>
+      <c r="P10" s="31" t="s">
+        <v>105</v>
+      </c>
+      <c r="Q10" s="32"/>
+      <c r="R10" s="32"/>
+    </row>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="G11" s="32">
+        <v>4</v>
+      </c>
+      <c r="H11" s="32" t="s">
+        <v>89</v>
+      </c>
+      <c r="I11" s="32" t="s">
+        <v>92</v>
+      </c>
+      <c r="J11" s="32" t="s">
+        <v>91</v>
+      </c>
+      <c r="K11" s="32"/>
+      <c r="M11" s="32">
+        <v>4</v>
+      </c>
+      <c r="N11" s="32" t="s">
+        <v>121</v>
+      </c>
+      <c r="O11" s="32" t="s">
+        <v>90</v>
+      </c>
+      <c r="P11" s="32" t="s">
+        <v>91</v>
+      </c>
+      <c r="Q11" s="32"/>
+      <c r="R11" s="32"/>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="G12" s="32">
+        <v>5</v>
+      </c>
+      <c r="H12" s="32" t="s">
+        <v>94</v>
+      </c>
+      <c r="I12" s="32" t="s">
+        <v>96</v>
+      </c>
+      <c r="J12" s="32" t="s">
+        <v>98</v>
+      </c>
+      <c r="K12" s="32"/>
+      <c r="M12" s="32">
+        <v>5</v>
+      </c>
+      <c r="N12" s="32" t="s">
+        <v>118</v>
+      </c>
+      <c r="O12" s="32" t="s">
+        <v>96</v>
+      </c>
+      <c r="P12" s="32" t="s">
+        <v>93</v>
+      </c>
+      <c r="Q12" s="32"/>
+      <c r="R12" s="32"/>
+    </row>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="G13" s="32">
+        <v>6</v>
+      </c>
+      <c r="H13" s="32" t="s">
+        <v>95</v>
+      </c>
+      <c r="I13" s="32" t="s">
+        <v>97</v>
+      </c>
+      <c r="J13" s="32" t="s">
+        <v>99</v>
+      </c>
+      <c r="K13" s="32"/>
+      <c r="M13" s="32">
+        <v>6</v>
+      </c>
+      <c r="N13" s="32" t="s">
+        <v>107</v>
+      </c>
+      <c r="O13" s="32" t="s">
+        <v>111</v>
+      </c>
+      <c r="P13" s="32" t="s">
+        <v>156</v>
+      </c>
+      <c r="Q13" s="32"/>
+      <c r="R13" s="32"/>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="G14" s="32">
+        <v>7</v>
+      </c>
+      <c r="H14" s="32" t="s">
+        <v>101</v>
+      </c>
+      <c r="I14" s="32"/>
+      <c r="J14" s="32"/>
+      <c r="K14" s="32"/>
+      <c r="M14" s="32">
+        <v>8</v>
+      </c>
+      <c r="N14" s="32" t="s">
+        <v>119</v>
+      </c>
+      <c r="O14" s="32" t="s">
+        <v>90</v>
+      </c>
+      <c r="P14" s="32" t="s">
+        <v>91</v>
+      </c>
+      <c r="Q14" s="32"/>
+      <c r="R14" s="32"/>
+    </row>
+    <row r="15" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="G15" s="32">
+        <v>8</v>
+      </c>
+      <c r="H15" s="32" t="s">
+        <v>89</v>
+      </c>
+      <c r="I15" s="32" t="s">
+        <v>92</v>
+      </c>
+      <c r="J15" s="32" t="s">
+        <v>91</v>
+      </c>
+      <c r="K15" s="32"/>
+      <c r="M15" s="32">
+        <v>9</v>
+      </c>
+      <c r="N15" s="32" t="s">
+        <v>122</v>
+      </c>
+      <c r="O15" s="32" t="s">
+        <v>96</v>
+      </c>
+      <c r="P15" s="32" t="s">
+        <v>93</v>
+      </c>
+      <c r="Q15" s="32"/>
+      <c r="R15" s="32"/>
+    </row>
+    <row r="16" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="G16" s="32">
+        <v>9</v>
+      </c>
+      <c r="H16" s="32" t="s">
+        <v>94</v>
+      </c>
+      <c r="I16" s="32" t="s">
+        <v>96</v>
+      </c>
+      <c r="J16" s="32" t="s">
+        <v>98</v>
+      </c>
+      <c r="K16" s="32"/>
+      <c r="M16" s="32">
+        <v>10</v>
+      </c>
+      <c r="N16" s="32" t="s">
+        <v>107</v>
+      </c>
+      <c r="O16" s="32" t="s">
+        <v>123</v>
+      </c>
+      <c r="P16" s="32" t="s">
+        <v>155</v>
+      </c>
+      <c r="Q16" s="32"/>
+      <c r="R16" s="32"/>
+    </row>
+    <row r="17" spans="7:11" x14ac:dyDescent="0.35">
+      <c r="G17" s="32">
+        <v>10</v>
+      </c>
+      <c r="H17" s="32" t="s">
+        <v>95</v>
+      </c>
+      <c r="I17" s="32" t="s">
+        <v>97</v>
+      </c>
+      <c r="J17" s="32" t="s">
+        <v>99</v>
+      </c>
+      <c r="K17" s="32"/>
+    </row>
+    <row r="18" spans="7:11" x14ac:dyDescent="0.35">
+      <c r="G18" s="32">
+        <v>11</v>
+      </c>
+      <c r="H18" s="32" t="s">
+        <v>102</v>
+      </c>
+      <c r="I18" s="32" t="s">
+        <v>103</v>
+      </c>
+      <c r="J18" s="32" t="s">
+        <v>104</v>
+      </c>
+      <c r="K18" s="32"/>
+    </row>
+    <row r="19" spans="7:11" x14ac:dyDescent="0.35">
+      <c r="G19" s="32">
+        <v>12</v>
+      </c>
+      <c r="H19" s="32" t="s">
+        <v>89</v>
+      </c>
+      <c r="I19" s="32" t="s">
+        <v>90</v>
+      </c>
+      <c r="J19" s="32" t="s">
+        <v>91</v>
+      </c>
+      <c r="K19" s="32"/>
+    </row>
+    <row r="20" spans="7:11" x14ac:dyDescent="0.35">
+      <c r="G20" s="32">
+        <v>13</v>
+      </c>
+      <c r="H20" s="32" t="s">
+        <v>106</v>
+      </c>
+      <c r="I20" s="32" t="s">
+        <v>96</v>
+      </c>
+      <c r="J20" s="32" t="s">
+        <v>93</v>
+      </c>
+      <c r="K20" s="32"/>
+    </row>
+    <row r="21" spans="7:11" x14ac:dyDescent="0.35">
+      <c r="G21" s="32">
+        <v>14</v>
+      </c>
+      <c r="H21" s="32" t="s">
+        <v>107</v>
+      </c>
+      <c r="I21" s="32" t="s">
+        <v>109</v>
+      </c>
+      <c r="J21" s="32" t="s">
+        <v>108</v>
+      </c>
+      <c r="K21" s="32"/>
+    </row>
+    <row r="22" spans="7:11" x14ac:dyDescent="0.35">
+      <c r="G22" s="32">
+        <v>15</v>
+      </c>
+      <c r="H22" s="32" t="s">
+        <v>112</v>
+      </c>
+      <c r="I22" s="32" t="s">
+        <v>96</v>
+      </c>
+      <c r="J22" s="32" t="s">
+        <v>110</v>
+      </c>
+      <c r="K22" s="32"/>
+    </row>
+    <row r="23" spans="7:11" x14ac:dyDescent="0.35">
+      <c r="G23" s="32">
+        <v>16</v>
+      </c>
+      <c r="H23" s="32" t="s">
+        <v>107</v>
+      </c>
+      <c r="I23" s="32" t="s">
+        <v>109</v>
+      </c>
+      <c r="J23" s="32" t="s">
+        <v>108</v>
+      </c>
+      <c r="K23" s="32"/>
+    </row>
+    <row r="24" spans="7:11" x14ac:dyDescent="0.35">
+      <c r="G24" s="32">
+        <v>17</v>
+      </c>
+      <c r="H24" s="32" t="s">
+        <v>113</v>
+      </c>
+      <c r="I24" s="32" t="s">
+        <v>114</v>
+      </c>
+      <c r="J24" s="32" t="s">
+        <v>115</v>
+      </c>
+      <c r="K24" s="32"/>
+    </row>
+    <row r="25" spans="7:11" x14ac:dyDescent="0.35">
+      <c r="G25" s="32">
+        <v>18</v>
+      </c>
+      <c r="H25" s="32" t="s">
+        <v>102</v>
+      </c>
+      <c r="I25" s="32" t="s">
+        <v>103</v>
+      </c>
+      <c r="J25" s="32" t="s">
+        <v>40</v>
+      </c>
+      <c r="K25" s="32"/>
+    </row>
+  </sheetData>
+  <mergeCells count="15">
+    <mergeCell ref="M1:R1"/>
+    <mergeCell ref="M2:N2"/>
+    <mergeCell ref="M3:N3"/>
+    <mergeCell ref="G4:L5"/>
+    <mergeCell ref="G6:L6"/>
+    <mergeCell ref="M4:R5"/>
+    <mergeCell ref="M6:R6"/>
+    <mergeCell ref="G2:H2"/>
+    <mergeCell ref="G3:H3"/>
+    <mergeCell ref="G1:L1"/>
+    <mergeCell ref="A4:F5"/>
+    <mergeCell ref="A6:F6"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="A3:B3"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{791F26CA-73F7-4CFD-B892-FF534C61ED87}">
+  <dimension ref="A1:S11"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="5" bestFit="1" customWidth="1"/>
@@ -3720,1087 +4536,422 @@
     <col min="3" max="3" width="11.54296875" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="31.1796875" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="18.36328125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="16.1796875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="9.1796875" style="2"/>
-    <col min="8" max="8" width="5" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="23.81640625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="27.54296875" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="30.26953125" customWidth="1"/>
-    <col min="12" max="12" width="18.36328125" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="16.1796875" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="8.7265625" style="2"/>
-    <col min="15" max="15" width="5" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="30.36328125" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="20.54296875" customWidth="1"/>
-    <col min="18" max="18" width="31.1796875" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="18.36328125" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="16.1796875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="16.1796875" style="23" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="5" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="22.36328125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="19.7265625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="28.6328125" customWidth="1"/>
+    <col min="11" max="11" width="18.36328125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="16.1796875" style="23" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="5" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="22.36328125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="22.90625" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="32.36328125" customWidth="1"/>
+    <col min="17" max="17" width="18.36328125" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="16.1796875" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="8.7265625" style="7"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" x14ac:dyDescent="0.35">
-      <c r="A1" s="3" t="s">
+    <row r="1" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A1" s="17" t="s">
         <v>18</v>
       </c>
-      <c r="B1" s="3"/>
-      <c r="C1" s="3"/>
-      <c r="D1" s="3"/>
-      <c r="E1" s="3"/>
-      <c r="F1" s="3"/>
-      <c r="H1" s="3" t="s">
+      <c r="B1" s="17"/>
+      <c r="C1" s="17"/>
+      <c r="D1" s="17"/>
+      <c r="E1" s="17"/>
+      <c r="F1" s="24"/>
+      <c r="G1" s="16" t="s">
         <v>19</v>
       </c>
-      <c r="I1" s="3"/>
-      <c r="J1" s="3"/>
-      <c r="K1" s="3"/>
-      <c r="L1" s="3"/>
-      <c r="M1" s="3"/>
-      <c r="O1" s="3" t="s">
-        <v>118</v>
-      </c>
-      <c r="P1" s="3"/>
-      <c r="Q1" s="3"/>
-      <c r="R1" s="3"/>
-      <c r="S1" s="3"/>
-      <c r="T1" s="3"/>
-    </row>
-    <row r="2" spans="1:20" x14ac:dyDescent="0.35">
-      <c r="A2" s="3" t="s">
+      <c r="H1" s="17"/>
+      <c r="I1" s="17"/>
+      <c r="J1" s="17"/>
+      <c r="K1" s="17"/>
+      <c r="L1" s="24"/>
+      <c r="M1" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="N1" s="17"/>
+      <c r="O1" s="17"/>
+      <c r="P1" s="17"/>
+      <c r="Q1" s="17"/>
+      <c r="R1" s="17"/>
+    </row>
+    <row r="2" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A2" s="17" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="3"/>
-      <c r="C2" s="3"/>
-      <c r="D2" s="5">
+      <c r="B2" s="17"/>
+      <c r="C2" s="18">
         <f>IFERROR(_xlfn.XLOOKUP(A1, TestMaster[Test Name], TestMaster[Test ID], "ID not found"), "")</f>
-        <v>5</v>
-      </c>
-      <c r="E2" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="F2" s="5"/>
-      <c r="H2" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D2" s="32"/>
+      <c r="E2" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="F2" s="21"/>
+      <c r="G2" s="17" t="s">
         <v>3</v>
       </c>
-      <c r="I2" s="3"/>
-      <c r="J2" s="3"/>
-      <c r="K2" s="5">
-        <f>IFERROR(_xlfn.XLOOKUP(H1, TestMaster[Test Name], TestMaster[Test ID], "ID not found"), "")</f>
-        <v>6</v>
-      </c>
-      <c r="L2" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="M2" s="5"/>
-      <c r="O2" s="3" t="s">
+      <c r="H2" s="17"/>
+      <c r="I2" s="18">
+        <f>IFERROR(_xlfn.XLOOKUP(G1, TestMaster[Test Name], TestMaster[Test ID], "ID not found"), "")</f>
+        <v>9</v>
+      </c>
+      <c r="J2" s="32"/>
+      <c r="K2" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="L2" s="21"/>
+      <c r="M2" s="17" t="s">
         <v>3</v>
       </c>
-      <c r="P2" s="3"/>
-      <c r="Q2" s="3"/>
-      <c r="R2" s="5">
-        <f>IFERROR(_xlfn.XLOOKUP(O1, TestMaster[Test Name], TestMaster[Test ID], "ID not found"), "")</f>
-        <v>7</v>
-      </c>
-      <c r="S2" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="T2" s="5"/>
-    </row>
-    <row r="3" spans="1:20" x14ac:dyDescent="0.35">
-      <c r="A3" s="3" t="s">
+      <c r="N2" s="17"/>
+      <c r="O2" s="18">
+        <f>IFERROR(_xlfn.XLOOKUP(M1, TestMaster[Test Name], TestMaster[Test ID], "ID not found"), "")</f>
+        <v>10</v>
+      </c>
+      <c r="P2" s="32"/>
+      <c r="Q2" s="20" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="3"/>
-      <c r="C3" s="3"/>
-      <c r="D3" s="5" t="str">
+      <c r="R2" s="20"/>
+    </row>
+    <row r="3" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A3" s="17" t="s">
+        <v>188</v>
+      </c>
+      <c r="B3" s="17"/>
+      <c r="C3" s="18" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(A1, TestMaster[Test Name], TestMaster[Test Priority], "Priority not found"), "")</f>
         <v>Medium</v>
       </c>
-      <c r="E3" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="F3" s="5" t="str">
+      <c r="D3" s="32"/>
+      <c r="E3" s="20" t="s">
+        <v>5</v>
+      </c>
+      <c r="F3" s="21" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(A1, TestMaster[Test Name], TestMaster[Test Status], "Status not found"), "")</f>
         <v>Not Implemented</v>
       </c>
-      <c r="H3" s="3" t="s">
+      <c r="G3" s="17" t="s">
+        <v>188</v>
+      </c>
+      <c r="H3" s="17"/>
+      <c r="I3" s="18" t="str">
+        <f>IFERROR(_xlfn.XLOOKUP(G1, TestMaster[Test Name], TestMaster[Test Priority], "Priority not found"), "")</f>
+        <v>Medium</v>
+      </c>
+      <c r="J3" s="32"/>
+      <c r="K3" s="20" t="s">
+        <v>5</v>
+      </c>
+      <c r="L3" s="21" t="str">
+        <f>IFERROR(_xlfn.XLOOKUP(G1, TestMaster[Test Name], TestMaster[Test Status], "Status not found"), "")</f>
+        <v>Not Implemented</v>
+      </c>
+      <c r="M3" s="17" t="s">
+        <v>188</v>
+      </c>
+      <c r="N3" s="17"/>
+      <c r="O3" s="18" t="str">
+        <f>IFERROR(_xlfn.XLOOKUP(M1, TestMaster[Test Name], TestMaster[Test Priority], "Priority not found"), "")</f>
+        <v>Low</v>
+      </c>
+      <c r="P3" s="32"/>
+      <c r="Q3" s="20" t="s">
+        <v>5</v>
+      </c>
+      <c r="R3" s="20" t="str">
+        <f>IFERROR(_xlfn.XLOOKUP(M1, TestMaster[Test Name], TestMaster[Test Status], "Status not found"), "")</f>
+        <v>Not Implemented</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A4" s="39" t="s">
+        <v>71</v>
+      </c>
+      <c r="B4" s="39"/>
+      <c r="C4" s="39"/>
+      <c r="D4" s="39"/>
+      <c r="E4" s="39"/>
+      <c r="F4" s="40"/>
+      <c r="G4" s="38" t="s">
+        <v>6</v>
+      </c>
+      <c r="H4" s="39"/>
+      <c r="I4" s="39"/>
+      <c r="J4" s="39"/>
+      <c r="K4" s="39"/>
+      <c r="L4" s="40"/>
+      <c r="M4" s="39" t="s">
+        <v>6</v>
+      </c>
+      <c r="N4" s="39"/>
+      <c r="O4" s="39"/>
+      <c r="P4" s="39"/>
+      <c r="Q4" s="39"/>
+      <c r="R4" s="39"/>
+    </row>
+    <row r="5" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A5" s="39"/>
+      <c r="B5" s="39"/>
+      <c r="C5" s="39"/>
+      <c r="D5" s="39"/>
+      <c r="E5" s="39"/>
+      <c r="F5" s="40"/>
+      <c r="G5" s="38"/>
+      <c r="H5" s="39"/>
+      <c r="I5" s="39"/>
+      <c r="J5" s="39"/>
+      <c r="K5" s="39"/>
+      <c r="L5" s="40"/>
+      <c r="M5" s="39"/>
+      <c r="N5" s="39"/>
+      <c r="O5" s="39"/>
+      <c r="P5" s="39"/>
+      <c r="Q5" s="39"/>
+      <c r="R5" s="39"/>
+    </row>
+    <row r="6" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A6" s="17" t="s">
+        <v>72</v>
+      </c>
+      <c r="B6" s="17"/>
+      <c r="C6" s="17"/>
+      <c r="D6" s="17"/>
+      <c r="E6" s="17"/>
+      <c r="F6" s="24"/>
+      <c r="G6" s="16" t="s">
+        <v>7</v>
+      </c>
+      <c r="H6" s="17"/>
+      <c r="I6" s="17"/>
+      <c r="J6" s="17"/>
+      <c r="K6" s="17"/>
+      <c r="L6" s="24"/>
+      <c r="M6" s="17" t="s">
+        <v>7</v>
+      </c>
+      <c r="N6" s="17"/>
+      <c r="O6" s="17"/>
+      <c r="P6" s="17"/>
+      <c r="Q6" s="17"/>
+      <c r="R6" s="17"/>
+    </row>
+    <row r="7" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A7" s="25" t="s">
+        <v>0</v>
+      </c>
+      <c r="B7" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="C7" s="25" t="s">
+        <v>9</v>
+      </c>
+      <c r="D7" s="25" t="s">
+        <v>1</v>
+      </c>
+      <c r="E7" s="25" t="s">
+        <v>10</v>
+      </c>
+      <c r="F7" s="27" t="s">
+        <v>2</v>
+      </c>
+      <c r="G7" s="25" t="s">
+        <v>0</v>
+      </c>
+      <c r="H7" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="I7" s="25" t="s">
+        <v>9</v>
+      </c>
+      <c r="J7" s="25" t="s">
+        <v>1</v>
+      </c>
+      <c r="K7" s="25" t="s">
+        <v>10</v>
+      </c>
+      <c r="L7" s="27" t="s">
+        <v>2</v>
+      </c>
+      <c r="M7" s="25" t="s">
+        <v>0</v>
+      </c>
+      <c r="N7" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="O7" s="25" t="s">
+        <v>9</v>
+      </c>
+      <c r="P7" s="25" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q7" s="25" t="s">
+        <v>10</v>
+      </c>
+      <c r="R7" s="25" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:19" s="8" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="31">
+        <v>1</v>
+      </c>
+      <c r="B8" s="31" t="s">
+        <v>73</v>
+      </c>
+      <c r="C8" s="31" t="s">
+        <v>27</v>
+      </c>
+      <c r="D8" s="31" t="s">
+        <v>74</v>
+      </c>
+      <c r="E8" s="31"/>
+      <c r="F8" s="41"/>
+      <c r="G8" s="31">
+        <v>1</v>
+      </c>
+      <c r="H8" s="31" t="s">
+        <v>73</v>
+      </c>
+      <c r="I8" s="31" t="s">
+        <v>27</v>
+      </c>
+      <c r="J8" s="31" t="s">
+        <v>77</v>
+      </c>
+      <c r="K8" s="31"/>
+      <c r="L8" s="41"/>
+      <c r="M8" s="31">
+        <v>1</v>
+      </c>
+      <c r="N8" s="31" t="s">
+        <v>73</v>
+      </c>
+      <c r="O8" s="31" t="s">
+        <v>27</v>
+      </c>
+      <c r="P8" s="31" t="s">
+        <v>77</v>
+      </c>
+      <c r="Q8" s="31"/>
+      <c r="R8" s="31"/>
+      <c r="S8" s="9"/>
+    </row>
+    <row r="9" spans="1:19" s="8" customFormat="1" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A9" s="31">
+        <v>2</v>
+      </c>
+      <c r="B9" s="31" t="s">
+        <v>56</v>
+      </c>
+      <c r="C9" s="31" t="s">
+        <v>27</v>
+      </c>
+      <c r="D9" s="31" t="s">
+        <v>40</v>
+      </c>
+      <c r="E9" s="31"/>
+      <c r="F9" s="41"/>
+      <c r="G9" s="31">
+        <v>2</v>
+      </c>
+      <c r="H9" s="31" t="s">
+        <v>75</v>
+      </c>
+      <c r="I9" s="31" t="s">
+        <v>78</v>
+      </c>
+      <c r="J9" s="31" t="s">
+        <v>80</v>
+      </c>
+      <c r="K9" s="31"/>
+      <c r="L9" s="41"/>
+      <c r="M9" s="31">
+        <v>2</v>
+      </c>
+      <c r="N9" s="31" t="s">
+        <v>75</v>
+      </c>
+      <c r="O9" s="31" t="s">
+        <v>82</v>
+      </c>
+      <c r="P9" s="31" t="s">
+        <v>81</v>
+      </c>
+      <c r="Q9" s="31"/>
+      <c r="R9" s="31"/>
+      <c r="S9" s="9"/>
+    </row>
+    <row r="10" spans="1:19" s="8" customFormat="1" ht="29" x14ac:dyDescent="0.35">
+      <c r="F10" s="41"/>
+      <c r="G10" s="31">
+        <v>3</v>
+      </c>
+      <c r="H10" s="31" t="s">
+        <v>76</v>
+      </c>
+      <c r="I10" s="31" t="s">
+        <v>79</v>
+      </c>
+      <c r="J10" s="31" t="s">
+        <v>87</v>
+      </c>
+      <c r="K10" s="31"/>
+      <c r="L10" s="41"/>
+      <c r="M10" s="31">
+        <v>3</v>
+      </c>
+      <c r="N10" s="31" t="s">
+        <v>76</v>
+      </c>
+      <c r="O10" s="31" t="s">
+        <v>79</v>
+      </c>
+      <c r="P10" s="31" t="s">
+        <v>83</v>
+      </c>
+      <c r="Q10" s="31"/>
+      <c r="R10" s="31"/>
+      <c r="S10" s="9"/>
+    </row>
+    <row r="11" spans="1:19" ht="29" x14ac:dyDescent="0.35">
+      <c r="M11" s="31">
         <v>4</v>
       </c>
-      <c r="I3" s="3"/>
-      <c r="J3" s="3"/>
-      <c r="K3" s="5" t="str">
-        <f>IFERROR(_xlfn.XLOOKUP(H1, TestMaster[Test Name], TestMaster[Test Priority], "Priority not found"), "")</f>
-        <v>Medium</v>
-      </c>
-      <c r="L3" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="M3" s="5" t="str">
-        <f>IFERROR(_xlfn.XLOOKUP(H1, TestMaster[Test Name], TestMaster[Test Status], "Status not found"), "")</f>
-        <v>Not Implemented</v>
-      </c>
-      <c r="O3" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="P3" s="3"/>
-      <c r="Q3" s="3"/>
-      <c r="R3" s="5" t="str">
-        <f>IFERROR(_xlfn.XLOOKUP(O1, TestMaster[Test Name], TestMaster[Test Priority], "Priority not found"), "")</f>
-        <v>Low</v>
-      </c>
-      <c r="S3" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="T3" s="5" t="str">
-        <f>IFERROR(_xlfn.XLOOKUP(O1, TestMaster[Test Name], TestMaster[Test Status], "Status not found"), "")</f>
-        <v>Not Implemented</v>
-      </c>
-    </row>
-    <row r="4" spans="1:20" x14ac:dyDescent="0.35">
-      <c r="A4" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="B4" s="3"/>
-      <c r="C4" s="3"/>
-      <c r="D4" s="3"/>
-      <c r="E4" s="3"/>
-      <c r="F4" s="3"/>
-      <c r="H4" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="I4" s="3"/>
-      <c r="J4" s="3"/>
-      <c r="K4" s="3"/>
-      <c r="L4" s="3"/>
-      <c r="M4" s="3"/>
-      <c r="O4" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="P4" s="3"/>
-      <c r="Q4" s="3"/>
-      <c r="R4" s="3"/>
-      <c r="S4" s="3"/>
-      <c r="T4" s="3"/>
-    </row>
-    <row r="5" spans="1:20" x14ac:dyDescent="0.35">
-      <c r="A5" s="3"/>
-      <c r="B5" s="3"/>
-      <c r="C5" s="3"/>
-      <c r="D5" s="3"/>
-      <c r="E5" s="3"/>
-      <c r="F5" s="3"/>
-      <c r="H5" s="3"/>
-      <c r="I5" s="3"/>
-      <c r="J5" s="3"/>
-      <c r="K5" s="3"/>
-      <c r="L5" s="3"/>
-      <c r="M5" s="3"/>
-      <c r="O5" s="3"/>
-      <c r="P5" s="3"/>
-      <c r="Q5" s="3"/>
-      <c r="R5" s="3"/>
-      <c r="S5" s="3"/>
-      <c r="T5" s="3"/>
-    </row>
-    <row r="6" spans="1:20" x14ac:dyDescent="0.35">
-      <c r="A6" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="B6" s="3"/>
-      <c r="C6" s="3"/>
-      <c r="D6" s="3"/>
-      <c r="E6" s="3"/>
-      <c r="F6" s="3"/>
-      <c r="H6" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="I6" s="3"/>
-      <c r="J6" s="3"/>
-      <c r="K6" s="3"/>
-      <c r="L6" s="3"/>
-      <c r="M6" s="3"/>
-      <c r="O6" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="P6" s="3"/>
-      <c r="Q6" s="3"/>
-      <c r="R6" s="3"/>
-      <c r="S6" s="3"/>
-      <c r="T6" s="3"/>
-    </row>
-    <row r="7" spans="1:20" x14ac:dyDescent="0.35">
-      <c r="A7" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="E7" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="F7" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="H7" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="I7" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="J7" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="K7" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="L7" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="M7" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="O7" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="P7" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="Q7" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="R7" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="S7" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="T7" s="1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="8" spans="1:20" s="5" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="13">
-        <v>1</v>
-      </c>
-      <c r="B8" s="13" t="s">
-        <v>90</v>
-      </c>
-      <c r="C8" s="13" t="s">
-        <v>29</v>
-      </c>
-      <c r="D8" s="13" t="s">
-        <v>76</v>
-      </c>
-      <c r="G8" s="14"/>
-      <c r="H8" s="5">
-        <v>1</v>
-      </c>
-      <c r="I8" s="13" t="s">
-        <v>90</v>
-      </c>
-      <c r="J8" s="13" t="s">
-        <v>29</v>
-      </c>
-      <c r="K8" s="13" t="s">
-        <v>79</v>
-      </c>
-      <c r="N8" s="14"/>
-      <c r="O8" s="5">
-        <v>1</v>
-      </c>
-      <c r="P8" s="13" t="s">
-        <v>90</v>
-      </c>
-      <c r="Q8" s="13" t="s">
-        <v>29</v>
-      </c>
-      <c r="R8" s="13" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="9" spans="1:20" s="5" customFormat="1" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A9" s="13">
-        <v>2</v>
-      </c>
-      <c r="B9" s="13" t="s">
-        <v>58</v>
-      </c>
-      <c r="C9" s="13" t="s">
-        <v>29</v>
-      </c>
-      <c r="D9" s="13" t="s">
-        <v>42</v>
-      </c>
-      <c r="G9" s="14"/>
-      <c r="H9" s="5">
-        <v>2</v>
-      </c>
-      <c r="I9" s="10" t="s">
-        <v>77</v>
-      </c>
-      <c r="J9" s="10" t="s">
-        <v>80</v>
-      </c>
-      <c r="K9" s="10" t="s">
-        <v>82</v>
-      </c>
-      <c r="N9" s="14"/>
-      <c r="O9" s="5">
-        <v>2</v>
-      </c>
-      <c r="P9" s="10" t="s">
-        <v>77</v>
-      </c>
-      <c r="Q9" s="10" t="s">
-        <v>80</v>
-      </c>
-      <c r="R9" s="10" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="10" spans="1:20" ht="29" x14ac:dyDescent="0.35">
-      <c r="H10">
-        <v>3</v>
-      </c>
-      <c r="I10" s="10" t="s">
-        <v>119</v>
-      </c>
-      <c r="J10" s="10" t="s">
-        <v>102</v>
-      </c>
-      <c r="K10" s="10" t="s">
-        <v>107</v>
-      </c>
-      <c r="O10">
-        <v>3</v>
-      </c>
-      <c r="P10" s="10" t="s">
-        <v>122</v>
-      </c>
-      <c r="Q10" s="10" t="s">
-        <v>102</v>
-      </c>
-      <c r="R10" s="10" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="11" spans="1:20" x14ac:dyDescent="0.35">
-      <c r="H11">
-        <v>4</v>
-      </c>
-      <c r="I11" t="s">
-        <v>91</v>
-      </c>
-      <c r="J11" t="s">
-        <v>94</v>
-      </c>
-      <c r="K11" t="s">
-        <v>93</v>
-      </c>
-      <c r="O11">
-        <v>4</v>
-      </c>
-      <c r="P11" t="s">
-        <v>123</v>
-      </c>
-      <c r="Q11" t="s">
-        <v>92</v>
-      </c>
-      <c r="R11" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="12" spans="1:20" x14ac:dyDescent="0.35">
-      <c r="H12">
-        <v>5</v>
-      </c>
-      <c r="I12" t="s">
-        <v>96</v>
-      </c>
-      <c r="J12" t="s">
-        <v>98</v>
-      </c>
-      <c r="K12" t="s">
-        <v>100</v>
-      </c>
-      <c r="O12">
-        <v>5</v>
-      </c>
-      <c r="P12" t="s">
-        <v>120</v>
-      </c>
-      <c r="Q12" t="s">
-        <v>98</v>
-      </c>
-      <c r="R12" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="13" spans="1:20" x14ac:dyDescent="0.35">
-      <c r="H13">
-        <v>6</v>
-      </c>
-      <c r="I13" t="s">
-        <v>97</v>
-      </c>
-      <c r="J13" t="s">
-        <v>99</v>
-      </c>
-      <c r="K13" t="s">
-        <v>101</v>
-      </c>
-      <c r="O13">
-        <v>6</v>
-      </c>
-      <c r="P13" t="s">
-        <v>109</v>
-      </c>
-      <c r="Q13" t="s">
-        <v>113</v>
-      </c>
-      <c r="R13" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="14" spans="1:20" x14ac:dyDescent="0.35">
-      <c r="H14">
-        <v>7</v>
-      </c>
-      <c r="I14" t="s">
-        <v>103</v>
-      </c>
-      <c r="O14">
-        <v>8</v>
-      </c>
-      <c r="P14" t="s">
-        <v>121</v>
-      </c>
-      <c r="Q14" t="s">
-        <v>92</v>
-      </c>
-      <c r="R14" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="15" spans="1:20" x14ac:dyDescent="0.35">
-      <c r="H15">
-        <v>8</v>
-      </c>
-      <c r="I15" t="s">
-        <v>91</v>
-      </c>
-      <c r="J15" t="s">
-        <v>94</v>
-      </c>
-      <c r="K15" t="s">
-        <v>93</v>
-      </c>
-      <c r="O15">
-        <v>9</v>
-      </c>
-      <c r="P15" t="s">
-        <v>124</v>
-      </c>
-      <c r="Q15" t="s">
-        <v>98</v>
-      </c>
-      <c r="R15" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="16" spans="1:20" x14ac:dyDescent="0.35">
-      <c r="H16">
-        <v>9</v>
-      </c>
-      <c r="I16" t="s">
-        <v>96</v>
-      </c>
-      <c r="J16" t="s">
-        <v>98</v>
-      </c>
-      <c r="K16" t="s">
-        <v>100</v>
-      </c>
-      <c r="O16">
-        <v>10</v>
-      </c>
-      <c r="P16" t="s">
-        <v>109</v>
-      </c>
-      <c r="Q16" t="s">
-        <v>125</v>
-      </c>
-      <c r="R16" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="17" spans="8:11" x14ac:dyDescent="0.35">
-      <c r="H17">
-        <v>10</v>
-      </c>
-      <c r="I17" t="s">
-        <v>97</v>
-      </c>
-      <c r="J17" t="s">
-        <v>99</v>
-      </c>
-      <c r="K17" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="18" spans="8:11" x14ac:dyDescent="0.35">
-      <c r="H18">
-        <v>11</v>
-      </c>
-      <c r="I18" t="s">
-        <v>104</v>
-      </c>
-      <c r="J18" t="s">
-        <v>105</v>
-      </c>
-      <c r="K18" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="19" spans="8:11" x14ac:dyDescent="0.35">
-      <c r="H19">
-        <v>12</v>
-      </c>
-      <c r="I19" t="s">
-        <v>91</v>
-      </c>
-      <c r="J19" t="s">
-        <v>92</v>
-      </c>
-      <c r="K19" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="20" spans="8:11" x14ac:dyDescent="0.35">
-      <c r="H20">
-        <v>13</v>
-      </c>
-      <c r="I20" t="s">
-        <v>108</v>
-      </c>
-      <c r="J20" t="s">
-        <v>98</v>
-      </c>
-      <c r="K20" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="21" spans="8:11" x14ac:dyDescent="0.35">
-      <c r="H21">
-        <v>14</v>
-      </c>
-      <c r="I21" t="s">
-        <v>109</v>
-      </c>
-      <c r="J21" t="s">
-        <v>111</v>
-      </c>
-      <c r="K21" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="22" spans="8:11" x14ac:dyDescent="0.35">
-      <c r="H22">
-        <v>15</v>
-      </c>
-      <c r="I22" t="s">
-        <v>114</v>
-      </c>
-      <c r="J22" t="s">
-        <v>98</v>
-      </c>
-      <c r="K22" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="23" spans="8:11" x14ac:dyDescent="0.35">
-      <c r="H23">
-        <v>16</v>
-      </c>
-      <c r="I23" t="s">
-        <v>109</v>
-      </c>
-      <c r="J23" t="s">
-        <v>111</v>
-      </c>
-      <c r="K23" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="24" spans="8:11" x14ac:dyDescent="0.35">
-      <c r="H24">
-        <v>17</v>
-      </c>
-      <c r="I24" t="s">
-        <v>115</v>
-      </c>
-      <c r="J24" t="s">
-        <v>116</v>
-      </c>
-      <c r="K24" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="25" spans="8:11" x14ac:dyDescent="0.35">
-      <c r="H25">
-        <v>18</v>
-      </c>
-      <c r="I25" t="s">
-        <v>104</v>
-      </c>
-      <c r="J25" t="s">
-        <v>105</v>
-      </c>
-      <c r="K25" t="s">
-        <v>42</v>
-      </c>
+      <c r="N11" s="31" t="s">
+        <v>84</v>
+      </c>
+      <c r="O11" s="31" t="s">
+        <v>85</v>
+      </c>
+      <c r="P11" s="31" t="s">
+        <v>86</v>
+      </c>
+      <c r="Q11" s="32"/>
+      <c r="R11" s="32"/>
     </row>
   </sheetData>
   <mergeCells count="15">
-    <mergeCell ref="O1:T1"/>
-    <mergeCell ref="O2:Q2"/>
-    <mergeCell ref="O3:Q3"/>
-    <mergeCell ref="H4:M5"/>
-    <mergeCell ref="H6:M6"/>
-    <mergeCell ref="O4:T5"/>
-    <mergeCell ref="O6:T6"/>
-    <mergeCell ref="H2:J2"/>
-    <mergeCell ref="H3:J3"/>
-    <mergeCell ref="H1:M1"/>
+    <mergeCell ref="M1:R1"/>
+    <mergeCell ref="M2:N2"/>
+    <mergeCell ref="M3:N3"/>
+    <mergeCell ref="G4:L5"/>
+    <mergeCell ref="G6:L6"/>
+    <mergeCell ref="M4:R5"/>
+    <mergeCell ref="M6:R6"/>
+    <mergeCell ref="G2:H2"/>
+    <mergeCell ref="G3:H3"/>
+    <mergeCell ref="G1:L1"/>
     <mergeCell ref="A4:F5"/>
     <mergeCell ref="A6:F6"/>
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A2:C2"/>
-    <mergeCell ref="A3:C3"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{791F26CA-73F7-4CFD-B892-FF534C61ED87}">
-  <dimension ref="A1:U11"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="1" max="1" width="5" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="21.90625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.54296875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="31.1796875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="18.36328125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="16.1796875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="9.1796875" style="2"/>
-    <col min="8" max="8" width="5" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="21.90625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="19.7265625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="28.6328125" customWidth="1"/>
-    <col min="12" max="12" width="18.36328125" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="16.1796875" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="8.7265625" style="2"/>
-    <col min="15" max="15" width="5" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="22.36328125" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="22.90625" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="32.36328125" customWidth="1"/>
-    <col min="19" max="19" width="18.36328125" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="16.1796875" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="8.7265625" style="8"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:21" x14ac:dyDescent="0.35">
-      <c r="A1" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="B1" s="3"/>
-      <c r="C1" s="3"/>
-      <c r="D1" s="3"/>
-      <c r="E1" s="3"/>
-      <c r="F1" s="3"/>
-      <c r="H1" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="I1" s="3"/>
-      <c r="J1" s="3"/>
-      <c r="K1" s="3"/>
-      <c r="L1" s="3"/>
-      <c r="M1" s="3"/>
-      <c r="O1" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="P1" s="3"/>
-      <c r="Q1" s="3"/>
-      <c r="R1" s="3"/>
-      <c r="S1" s="3"/>
-      <c r="T1" s="3"/>
-    </row>
-    <row r="2" spans="1:21" x14ac:dyDescent="0.35">
-      <c r="A2" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2" s="3"/>
-      <c r="C2" s="3"/>
-      <c r="D2" s="5">
-        <f>IFERROR(_xlfn.XLOOKUP(A1, TestMaster[Test Name], TestMaster[Test ID], "ID not found"), "")</f>
-        <v>8</v>
-      </c>
-      <c r="E2" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="F2" s="5"/>
-      <c r="H2" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I2" s="3"/>
-      <c r="J2" s="3"/>
-      <c r="K2" s="5">
-        <f>IFERROR(_xlfn.XLOOKUP(H1, TestMaster[Test Name], TestMaster[Test ID], "ID not found"), "")</f>
-        <v>9</v>
-      </c>
-      <c r="L2" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="M2" s="5"/>
-      <c r="O2" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P2" s="3"/>
-      <c r="Q2" s="3"/>
-      <c r="R2" s="5">
-        <f>IFERROR(_xlfn.XLOOKUP(O1, TestMaster[Test Name], TestMaster[Test ID], "ID not found"), "")</f>
-        <v>10</v>
-      </c>
-      <c r="S2" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="T2" s="5"/>
-    </row>
-    <row r="3" spans="1:21" x14ac:dyDescent="0.35">
-      <c r="A3" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="B3" s="3"/>
-      <c r="C3" s="3"/>
-      <c r="D3" s="5" t="str">
-        <f>IFERROR(_xlfn.XLOOKUP(A1, TestMaster[Test Name], TestMaster[Test Priority], "Priority not found"), "")</f>
-        <v>Medium</v>
-      </c>
-      <c r="E3" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="F3" s="5" t="str">
-        <f>IFERROR(_xlfn.XLOOKUP(A1, TestMaster[Test Name], TestMaster[Test Status], "Status not found"), "")</f>
-        <v>Not Implemented</v>
-      </c>
-      <c r="H3" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I3" s="3"/>
-      <c r="J3" s="3"/>
-      <c r="K3" s="5" t="str">
-        <f>IFERROR(_xlfn.XLOOKUP(H1, TestMaster[Test Name], TestMaster[Test Priority], "Priority not found"), "")</f>
-        <v>Medium</v>
-      </c>
-      <c r="L3" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="M3" s="5" t="str">
-        <f>IFERROR(_xlfn.XLOOKUP(H1, TestMaster[Test Name], TestMaster[Test Status], "Status not found"), "")</f>
-        <v>Not Implemented</v>
-      </c>
-      <c r="O3" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="P3" s="3"/>
-      <c r="Q3" s="3"/>
-      <c r="R3" s="5" t="str">
-        <f>IFERROR(_xlfn.XLOOKUP(O1, TestMaster[Test Name], TestMaster[Test Priority], "Priority not found"), "")</f>
-        <v>Low</v>
-      </c>
-      <c r="S3" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="T3" s="5" t="str">
-        <f>IFERROR(_xlfn.XLOOKUP(O1, TestMaster[Test Name], TestMaster[Test Status], "Status not found"), "")</f>
-        <v>Not Implemented</v>
-      </c>
-    </row>
-    <row r="4" spans="1:21" x14ac:dyDescent="0.35">
-      <c r="A4" s="7" t="s">
-        <v>73</v>
-      </c>
-      <c r="B4" s="7"/>
-      <c r="C4" s="7"/>
-      <c r="D4" s="7"/>
-      <c r="E4" s="7"/>
-      <c r="F4" s="7"/>
-      <c r="H4" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="I4" s="7"/>
-      <c r="J4" s="7"/>
-      <c r="K4" s="7"/>
-      <c r="L4" s="7"/>
-      <c r="M4" s="7"/>
-      <c r="O4" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="P4" s="7"/>
-      <c r="Q4" s="7"/>
-      <c r="R4" s="7"/>
-      <c r="S4" s="7"/>
-      <c r="T4" s="7"/>
-    </row>
-    <row r="5" spans="1:21" x14ac:dyDescent="0.35">
-      <c r="A5" s="7"/>
-      <c r="B5" s="7"/>
-      <c r="C5" s="7"/>
-      <c r="D5" s="7"/>
-      <c r="E5" s="7"/>
-      <c r="F5" s="7"/>
-      <c r="H5" s="7"/>
-      <c r="I5" s="7"/>
-      <c r="J5" s="7"/>
-      <c r="K5" s="7"/>
-      <c r="L5" s="7"/>
-      <c r="M5" s="7"/>
-      <c r="O5" s="7"/>
-      <c r="P5" s="7"/>
-      <c r="Q5" s="7"/>
-      <c r="R5" s="7"/>
-      <c r="S5" s="7"/>
-      <c r="T5" s="7"/>
-    </row>
-    <row r="6" spans="1:21" x14ac:dyDescent="0.35">
-      <c r="A6" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="B6" s="3"/>
-      <c r="C6" s="3"/>
-      <c r="D6" s="3"/>
-      <c r="E6" s="3"/>
-      <c r="F6" s="3"/>
-      <c r="H6" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="I6" s="3"/>
-      <c r="J6" s="3"/>
-      <c r="K6" s="3"/>
-      <c r="L6" s="3"/>
-      <c r="M6" s="3"/>
-      <c r="O6" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="P6" s="3"/>
-      <c r="Q6" s="3"/>
-      <c r="R6" s="3"/>
-      <c r="S6" s="3"/>
-      <c r="T6" s="3"/>
-    </row>
-    <row r="7" spans="1:21" x14ac:dyDescent="0.35">
-      <c r="A7" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="E7" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="F7" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="H7" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="I7" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="J7" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="K7" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="L7" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="M7" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="O7" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="P7" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="Q7" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="R7" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="S7" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="T7" s="1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="8" spans="1:21" s="10" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="10">
-        <v>1</v>
-      </c>
-      <c r="B8" s="10" t="s">
-        <v>75</v>
-      </c>
-      <c r="C8" s="10" t="s">
-        <v>29</v>
-      </c>
-      <c r="D8" s="10" t="s">
-        <v>76</v>
-      </c>
-      <c r="G8" s="11"/>
-      <c r="H8" s="10">
-        <v>1</v>
-      </c>
-      <c r="I8" s="10" t="s">
-        <v>75</v>
-      </c>
-      <c r="J8" s="10" t="s">
-        <v>29</v>
-      </c>
-      <c r="K8" s="10" t="s">
-        <v>79</v>
-      </c>
-      <c r="N8" s="11"/>
-      <c r="O8" s="10">
-        <v>1</v>
-      </c>
-      <c r="P8" s="10" t="s">
-        <v>75</v>
-      </c>
-      <c r="Q8" s="10" t="s">
-        <v>29</v>
-      </c>
-      <c r="R8" s="10" t="s">
-        <v>79</v>
-      </c>
-      <c r="U8" s="12"/>
-    </row>
-    <row r="9" spans="1:21" s="10" customFormat="1" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A9" s="10">
-        <v>2</v>
-      </c>
-      <c r="B9" s="10" t="s">
-        <v>58</v>
-      </c>
-      <c r="C9" s="10" t="s">
-        <v>29</v>
-      </c>
-      <c r="D9" s="10" t="s">
-        <v>42</v>
-      </c>
-      <c r="G9" s="11"/>
-      <c r="H9" s="10">
-        <v>2</v>
-      </c>
-      <c r="I9" s="10" t="s">
-        <v>77</v>
-      </c>
-      <c r="J9" s="10" t="s">
-        <v>80</v>
-      </c>
-      <c r="K9" s="10" t="s">
-        <v>82</v>
-      </c>
-      <c r="N9" s="11"/>
-      <c r="O9" s="10">
-        <v>2</v>
-      </c>
-      <c r="P9" s="10" t="s">
-        <v>77</v>
-      </c>
-      <c r="Q9" s="10" t="s">
-        <v>84</v>
-      </c>
-      <c r="R9" s="10" t="s">
-        <v>83</v>
-      </c>
-      <c r="U9" s="12"/>
-    </row>
-    <row r="10" spans="1:21" s="10" customFormat="1" ht="29" x14ac:dyDescent="0.35">
-      <c r="G10" s="11"/>
-      <c r="H10" s="10">
-        <v>3</v>
-      </c>
-      <c r="I10" s="10" t="s">
-        <v>78</v>
-      </c>
-      <c r="J10" s="10" t="s">
-        <v>81</v>
-      </c>
-      <c r="K10" s="10" t="s">
-        <v>89</v>
-      </c>
-      <c r="N10" s="11"/>
-      <c r="O10" s="10">
-        <v>3</v>
-      </c>
-      <c r="P10" s="10" t="s">
-        <v>78</v>
-      </c>
-      <c r="Q10" s="10" t="s">
-        <v>81</v>
-      </c>
-      <c r="R10" s="10" t="s">
-        <v>85</v>
-      </c>
-      <c r="U10" s="12"/>
-    </row>
-    <row r="11" spans="1:21" ht="29" x14ac:dyDescent="0.35">
-      <c r="O11" s="10">
-        <v>4</v>
-      </c>
-      <c r="P11" s="10" t="s">
-        <v>86</v>
-      </c>
-      <c r="Q11" s="10" t="s">
-        <v>87</v>
-      </c>
-      <c r="R11" s="10" t="s">
-        <v>88</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="15">
-    <mergeCell ref="O1:T1"/>
-    <mergeCell ref="O2:Q2"/>
-    <mergeCell ref="O3:Q3"/>
-    <mergeCell ref="H4:M5"/>
-    <mergeCell ref="H6:M6"/>
-    <mergeCell ref="O4:T5"/>
-    <mergeCell ref="O6:T6"/>
-    <mergeCell ref="H2:J2"/>
-    <mergeCell ref="H3:J3"/>
-    <mergeCell ref="H1:M1"/>
-    <mergeCell ref="A4:F5"/>
-    <mergeCell ref="A6:F6"/>
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A2:C2"/>
-    <mergeCell ref="A3:C3"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="A3:B3"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -4808,7 +4959,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E4413619-C528-4B04-A1ED-B4C77CA83066}">
-  <dimension ref="A1:AH13"/>
+  <dimension ref="A1:AD13"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="5" bestFit="1" customWidth="1"/>
@@ -4816,679 +4967,673 @@
     <col min="3" max="3" width="17.54296875" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="15.26953125" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="18.36328125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="9.1796875" style="2"/>
-    <col min="8" max="8" width="5" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="23.7265625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="48.81640625" customWidth="1"/>
-    <col min="11" max="11" width="17.54296875" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="18.36328125" customWidth="1"/>
-    <col min="14" max="14" width="8.7265625" style="2"/>
-    <col min="15" max="15" width="5" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="21.54296875" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="30.81640625" customWidth="1"/>
-    <col min="18" max="18" width="15.26953125" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="18.36328125" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="8.7265625" style="2"/>
-    <col min="22" max="22" width="5" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="23.26953125" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="41" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="15.26953125" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="18.36328125" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="8.7265625" style="2"/>
-    <col min="29" max="29" width="5" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="19.1796875" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="11.54296875" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="15.26953125" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="18.36328125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="8.7265625" style="23"/>
+    <col min="7" max="7" width="5" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="23.7265625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="48.81640625" customWidth="1"/>
+    <col min="10" max="10" width="17.54296875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="18.36328125" customWidth="1"/>
+    <col min="12" max="12" width="8.7265625" style="23"/>
+    <col min="13" max="13" width="5" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="21.54296875" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="30.81640625" customWidth="1"/>
+    <col min="16" max="16" width="15.26953125" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="18.36328125" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="8.7265625" style="23"/>
+    <col min="19" max="19" width="5" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="23.26953125" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="41" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="15.26953125" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="18.36328125" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="8.7265625" style="23"/>
+    <col min="25" max="25" width="5" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="19.1796875" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="11.54296875" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="15.26953125" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="18.36328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:34" x14ac:dyDescent="0.35">
-      <c r="A1" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="B1" s="3"/>
-      <c r="C1" s="3"/>
-      <c r="D1" s="3"/>
-      <c r="E1" s="3"/>
-      <c r="F1" s="3"/>
-      <c r="H1" s="3" t="s">
+    <row r="1" spans="1:30" x14ac:dyDescent="0.35">
+      <c r="A1" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="B1" s="17"/>
+      <c r="C1" s="17"/>
+      <c r="D1" s="17"/>
+      <c r="E1" s="17"/>
+      <c r="F1" s="24"/>
+      <c r="G1" s="17" t="s">
+        <v>21</v>
+      </c>
+      <c r="H1" s="17"/>
+      <c r="I1" s="17"/>
+      <c r="J1" s="17"/>
+      <c r="K1" s="17"/>
+      <c r="L1" s="24"/>
+      <c r="M1" s="16" t="s">
+        <v>22</v>
+      </c>
+      <c r="N1" s="17"/>
+      <c r="O1" s="17"/>
+      <c r="P1" s="17"/>
+      <c r="Q1" s="17"/>
+      <c r="R1" s="24"/>
+      <c r="S1" s="17" t="s">
         <v>23</v>
       </c>
-      <c r="I1" s="3"/>
-      <c r="J1" s="3"/>
-      <c r="K1" s="3"/>
-      <c r="L1" s="3"/>
-      <c r="M1" s="3"/>
-      <c r="O1" s="3" t="s">
+      <c r="T1" s="17"/>
+      <c r="U1" s="17"/>
+      <c r="V1" s="17"/>
+      <c r="W1" s="17"/>
+      <c r="X1" s="24"/>
+      <c r="Y1" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="P1" s="3"/>
-      <c r="Q1" s="3"/>
-      <c r="R1" s="3"/>
-      <c r="S1" s="3"/>
-      <c r="T1" s="3"/>
-      <c r="V1" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="W1" s="3"/>
-      <c r="X1" s="3"/>
-      <c r="Y1" s="3"/>
-      <c r="Z1" s="3"/>
-      <c r="AA1" s="3"/>
-      <c r="AC1" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="AD1" s="3"/>
-      <c r="AE1" s="3"/>
-      <c r="AF1" s="3"/>
-      <c r="AG1" s="3"/>
-      <c r="AH1" s="3"/>
-    </row>
-    <row r="2" spans="1:34" x14ac:dyDescent="0.35">
-      <c r="A2" s="3" t="s">
+      <c r="Z1" s="2"/>
+      <c r="AA1" s="2"/>
+      <c r="AB1" s="2"/>
+      <c r="AC1" s="2"/>
+      <c r="AD1" s="2"/>
+    </row>
+    <row r="2" spans="1:30" x14ac:dyDescent="0.35">
+      <c r="A2" s="17" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="3"/>
-      <c r="C2" s="3"/>
-      <c r="D2" s="5">
+      <c r="B2" s="17"/>
+      <c r="C2" s="20">
         <f>IFERROR(_xlfn.XLOOKUP(A1, TestMaster[Test Name], TestMaster[Test ID], "ID not found"), "")</f>
         <v>11</v>
       </c>
-      <c r="E2" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="F2" s="5"/>
-      <c r="H2" s="3" t="s">
+      <c r="D2" s="32"/>
+      <c r="E2" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="F2" s="21"/>
+      <c r="G2" s="17" t="s">
         <v>3</v>
       </c>
-      <c r="I2" s="3"/>
-      <c r="J2" s="3"/>
-      <c r="K2" s="5">
-        <f>IFERROR(_xlfn.XLOOKUP(H1, TestMaster[Test Name], TestMaster[Test ID], "ID not found"), "")</f>
+      <c r="H2" s="17"/>
+      <c r="I2" s="18">
+        <f>IFERROR(_xlfn.XLOOKUP(G1, TestMaster[Test Name], TestMaster[Test ID], "ID not found"), "")</f>
         <v>12</v>
       </c>
-      <c r="L2" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="M2" s="5"/>
-      <c r="O2" s="3" t="s">
+      <c r="J2" s="32"/>
+      <c r="K2" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="L2" s="21"/>
+      <c r="M2" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="P2" s="3"/>
-      <c r="Q2" s="3"/>
-      <c r="R2" s="5">
-        <f>IFERROR(_xlfn.XLOOKUP(O1, TestMaster[Test Name], TestMaster[Test ID], "ID not found"), "")</f>
+      <c r="N2" s="2"/>
+      <c r="O2" s="15">
+        <f>IFERROR(_xlfn.XLOOKUP(M1, TestMaster[Test Name], TestMaster[Test ID], "ID not found"), "")</f>
         <v>13</v>
       </c>
-      <c r="S2" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="T2" s="5"/>
-      <c r="V2" s="3" t="s">
+      <c r="Q2" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="R2" s="21"/>
+      <c r="S2" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="W2" s="3"/>
-      <c r="X2" s="3"/>
-      <c r="Y2" s="5">
-        <f>IFERROR(_xlfn.XLOOKUP(V1, TestMaster[Test Name], TestMaster[Test ID], "ID not found"), "")</f>
+      <c r="T2" s="2"/>
+      <c r="U2" s="15">
+        <f>IFERROR(_xlfn.XLOOKUP(S1, TestMaster[Test Name], TestMaster[Test ID], "ID not found"), "")</f>
         <v>14</v>
       </c>
-      <c r="Z2" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="AA2" s="5"/>
-      <c r="AC2" s="3" t="s">
+      <c r="W2" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="X2" s="21"/>
+      <c r="Y2" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="AD2" s="3"/>
-      <c r="AE2" s="3"/>
-      <c r="AF2" s="5">
-        <f>IFERROR(_xlfn.XLOOKUP(AC1, TestMaster[Test Name], TestMaster[Test ID], "ID not found"), "")</f>
+      <c r="Z2" s="2"/>
+      <c r="AA2" s="15">
+        <f>IFERROR(_xlfn.XLOOKUP(Y1, TestMaster[Test Name], TestMaster[Test ID], "ID not found"), "")</f>
         <v>15</v>
       </c>
-      <c r="AG2" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="AH2" s="5"/>
-    </row>
-    <row r="3" spans="1:34" x14ac:dyDescent="0.35">
-      <c r="A3" s="3" t="s">
+      <c r="AC2" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="3"/>
-      <c r="C3" s="3"/>
-      <c r="D3" s="5" t="str">
+      <c r="AD2" s="4"/>
+    </row>
+    <row r="3" spans="1:30" x14ac:dyDescent="0.35">
+      <c r="A3" s="17" t="s">
+        <v>188</v>
+      </c>
+      <c r="B3" s="17"/>
+      <c r="C3" s="20" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(A1, TestMaster[Test Name], TestMaster[Test Priority], "Priority not found"), "")</f>
         <v>High</v>
       </c>
-      <c r="E3" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="F3" s="5" t="str">
+      <c r="D3" s="32"/>
+      <c r="E3" s="20" t="s">
+        <v>5</v>
+      </c>
+      <c r="F3" s="21" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(A1, TestMaster[Test Name], TestMaster[Test Priority], "Priority not found"), "")</f>
         <v>High</v>
       </c>
-      <c r="H3" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="I3" s="3"/>
-      <c r="J3" s="3"/>
-      <c r="K3" s="5" t="str">
-        <f>IFERROR(_xlfn.XLOOKUP(H1, TestMaster[Test Name], TestMaster[Test Priority], "Priority not found"), "")</f>
+      <c r="G3" s="17" t="s">
+        <v>189</v>
+      </c>
+      <c r="H3" s="17"/>
+      <c r="I3" s="18" t="str">
+        <f>IFERROR(_xlfn.XLOOKUP(G1, TestMaster[Test Name], TestMaster[Test Priority], "Priority not found"), "")</f>
         <v>High</v>
       </c>
-      <c r="L3" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="M3" s="5" t="str">
-        <f>IFERROR(_xlfn.XLOOKUP(H1, TestMaster[Test Name], TestMaster[Test Priority], "Priority not found"), "")</f>
+      <c r="J3" s="32"/>
+      <c r="K3" s="20" t="s">
+        <v>5</v>
+      </c>
+      <c r="L3" s="21" t="str">
+        <f>IFERROR(_xlfn.XLOOKUP(G1, TestMaster[Test Name], TestMaster[Test Priority], "Priority not found"), "")</f>
         <v>High</v>
       </c>
-      <c r="O3" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="P3" s="3"/>
-      <c r="Q3" s="3"/>
-      <c r="R3" s="5" t="str">
-        <f>IFERROR(_xlfn.XLOOKUP(O1, TestMaster[Test Name], TestMaster[Test Priority], "Priority not found"), "")</f>
+      <c r="M3" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="N3" s="2"/>
+      <c r="O3" s="15" t="str">
+        <f>IFERROR(_xlfn.XLOOKUP(M1, TestMaster[Test Name], TestMaster[Test Priority], "Priority not found"), "")</f>
         <v>Medium</v>
       </c>
-      <c r="S3" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="T3" s="5" t="str">
-        <f>IFERROR(_xlfn.XLOOKUP(O1, TestMaster[Test Name], TestMaster[Test Priority], "Priority not found"), "")</f>
+      <c r="Q3" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="R3" s="21" t="str">
+        <f>IFERROR(_xlfn.XLOOKUP(M1, TestMaster[Test Name], TestMaster[Test Priority], "Priority not found"), "")</f>
         <v>Medium</v>
       </c>
-      <c r="V3" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="W3" s="3"/>
-      <c r="X3" s="3"/>
-      <c r="Y3" s="5" t="str">
-        <f>IFERROR(_xlfn.XLOOKUP(V1, TestMaster[Test Name], TestMaster[Test Priority], "Priority not found"), "")</f>
+      <c r="S3" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="T3" s="2"/>
+      <c r="U3" s="15" t="str">
+        <f>IFERROR(_xlfn.XLOOKUP(S1, TestMaster[Test Name], TestMaster[Test Priority], "Priority not found"), "")</f>
         <v>Low</v>
       </c>
-      <c r="Z3" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="AA3" s="5" t="str">
-        <f>IFERROR(_xlfn.XLOOKUP(V1, TestMaster[Test Name], TestMaster[Test Priority], "Priority not found"), "")</f>
+      <c r="W3" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="X3" s="21" t="str">
+        <f>IFERROR(_xlfn.XLOOKUP(S1, TestMaster[Test Name], TestMaster[Test Priority], "Priority not found"), "")</f>
         <v>Low</v>
       </c>
-      <c r="AC3" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AD3" s="3"/>
-      <c r="AE3" s="3"/>
-      <c r="AF3" s="5" t="str">
-        <f>IFERROR(_xlfn.XLOOKUP(AC1, TestMaster[Test Name], TestMaster[Test Priority], "Priority not found"), "")</f>
+      <c r="Y3" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="Z3" s="2"/>
+      <c r="AA3" s="15" t="str">
+        <f>IFERROR(_xlfn.XLOOKUP(Y1, TestMaster[Test Name], TestMaster[Test Priority], "Priority not found"), "")</f>
         <v>High</v>
       </c>
-      <c r="AG3" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="AH3" s="5" t="str">
-        <f>IFERROR(_xlfn.XLOOKUP(AC1, TestMaster[Test Name], TestMaster[Test Priority], "Priority not found"), "")</f>
+      <c r="AC3" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD3" s="4" t="str">
+        <f>IFERROR(_xlfn.XLOOKUP(Y1, TestMaster[Test Name], TestMaster[Test Priority], "Priority not found"), "")</f>
         <v>High</v>
       </c>
     </row>
-    <row r="4" spans="1:34" s="4" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="B4" s="7"/>
-      <c r="C4" s="7"/>
-      <c r="D4" s="7"/>
-      <c r="E4" s="7"/>
-      <c r="F4" s="7"/>
-      <c r="G4" s="9"/>
-      <c r="H4" s="7" t="s">
+    <row r="4" spans="1:30" s="3" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="39" t="s">
+        <v>12</v>
+      </c>
+      <c r="B4" s="39"/>
+      <c r="C4" s="39"/>
+      <c r="D4" s="39"/>
+      <c r="E4" s="39"/>
+      <c r="F4" s="40"/>
+      <c r="G4" s="39" t="s">
+        <v>68</v>
+      </c>
+      <c r="H4" s="39"/>
+      <c r="I4" s="39"/>
+      <c r="J4" s="39"/>
+      <c r="K4" s="39"/>
+      <c r="L4" s="40"/>
+      <c r="M4" s="38" t="s">
+        <v>12</v>
+      </c>
+      <c r="N4" s="39"/>
+      <c r="O4" s="39"/>
+      <c r="P4" s="39"/>
+      <c r="Q4" s="39"/>
+      <c r="R4" s="40"/>
+      <c r="S4" s="39" t="s">
+        <v>12</v>
+      </c>
+      <c r="T4" s="39"/>
+      <c r="U4" s="39"/>
+      <c r="V4" s="39"/>
+      <c r="W4" s="39"/>
+      <c r="X4" s="40"/>
+      <c r="Y4" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="Z4" s="6"/>
+      <c r="AA4" s="6"/>
+      <c r="AB4" s="6"/>
+      <c r="AC4" s="6"/>
+      <c r="AD4" s="6"/>
+    </row>
+    <row r="5" spans="1:30" s="3" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="39"/>
+      <c r="B5" s="39"/>
+      <c r="C5" s="39"/>
+      <c r="D5" s="39"/>
+      <c r="E5" s="39"/>
+      <c r="F5" s="40"/>
+      <c r="G5" s="39"/>
+      <c r="H5" s="39"/>
+      <c r="I5" s="39"/>
+      <c r="J5" s="39"/>
+      <c r="K5" s="39"/>
+      <c r="L5" s="40"/>
+      <c r="M5" s="38"/>
+      <c r="N5" s="39"/>
+      <c r="O5" s="39"/>
+      <c r="P5" s="39"/>
+      <c r="Q5" s="39"/>
+      <c r="R5" s="40"/>
+      <c r="S5" s="39"/>
+      <c r="T5" s="39"/>
+      <c r="U5" s="39"/>
+      <c r="V5" s="39"/>
+      <c r="W5" s="39"/>
+      <c r="X5" s="40"/>
+      <c r="Y5" s="6"/>
+      <c r="Z5" s="6"/>
+      <c r="AA5" s="6"/>
+      <c r="AB5" s="6"/>
+      <c r="AC5" s="6"/>
+      <c r="AD5" s="6"/>
+    </row>
+    <row r="6" spans="1:30" x14ac:dyDescent="0.35">
+      <c r="A6" s="17" t="s">
+        <v>69</v>
+      </c>
+      <c r="B6" s="17"/>
+      <c r="C6" s="17"/>
+      <c r="D6" s="17"/>
+      <c r="E6" s="17"/>
+      <c r="F6" s="24"/>
+      <c r="G6" s="17" t="s">
+        <v>69</v>
+      </c>
+      <c r="H6" s="17"/>
+      <c r="I6" s="17"/>
+      <c r="J6" s="17"/>
+      <c r="K6" s="17"/>
+      <c r="L6" s="24"/>
+      <c r="M6" s="16" t="s">
         <v>70</v>
       </c>
-      <c r="I4" s="7"/>
-      <c r="J4" s="7"/>
-      <c r="K4" s="7"/>
-      <c r="L4" s="7"/>
-      <c r="M4" s="7"/>
-      <c r="N4" s="9"/>
-      <c r="O4" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="P4" s="7"/>
-      <c r="Q4" s="7"/>
-      <c r="R4" s="7"/>
-      <c r="S4" s="7"/>
-      <c r="T4" s="7"/>
-      <c r="U4" s="9"/>
-      <c r="V4" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="W4" s="7"/>
-      <c r="X4" s="7"/>
-      <c r="Y4" s="7"/>
-      <c r="Z4" s="7"/>
-      <c r="AA4" s="7"/>
-      <c r="AB4" s="9"/>
-      <c r="AC4" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="AD4" s="7"/>
-      <c r="AE4" s="7"/>
-      <c r="AF4" s="7"/>
-      <c r="AG4" s="7"/>
-      <c r="AH4" s="7"/>
-    </row>
-    <row r="5" spans="1:34" s="4" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="7"/>
-      <c r="B5" s="7"/>
-      <c r="C5" s="7"/>
-      <c r="D5" s="7"/>
-      <c r="E5" s="7"/>
-      <c r="F5" s="7"/>
-      <c r="G5" s="9"/>
-      <c r="H5" s="7"/>
-      <c r="I5" s="7"/>
-      <c r="J5" s="7"/>
-      <c r="K5" s="7"/>
-      <c r="L5" s="7"/>
-      <c r="M5" s="7"/>
-      <c r="N5" s="9"/>
-      <c r="O5" s="7"/>
-      <c r="P5" s="7"/>
-      <c r="Q5" s="7"/>
-      <c r="R5" s="7"/>
-      <c r="S5" s="7"/>
-      <c r="T5" s="7"/>
-      <c r="U5" s="9"/>
-      <c r="V5" s="7"/>
-      <c r="W5" s="7"/>
-      <c r="X5" s="7"/>
-      <c r="Y5" s="7"/>
-      <c r="Z5" s="7"/>
-      <c r="AA5" s="7"/>
-      <c r="AB5" s="9"/>
-      <c r="AC5" s="7"/>
-      <c r="AD5" s="7"/>
-      <c r="AE5" s="7"/>
-      <c r="AF5" s="7"/>
-      <c r="AG5" s="7"/>
-      <c r="AH5" s="7"/>
-    </row>
-    <row r="6" spans="1:34" x14ac:dyDescent="0.35">
-      <c r="A6" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="B6" s="3"/>
-      <c r="C6" s="3"/>
-      <c r="D6" s="3"/>
-      <c r="E6" s="3"/>
-      <c r="F6" s="3"/>
-      <c r="H6" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="I6" s="3"/>
-      <c r="J6" s="3"/>
-      <c r="K6" s="3"/>
-      <c r="L6" s="3"/>
-      <c r="M6" s="3"/>
-      <c r="O6" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="P6" s="3"/>
-      <c r="Q6" s="3"/>
-      <c r="R6" s="3"/>
-      <c r="S6" s="3"/>
-      <c r="T6" s="3"/>
-      <c r="V6" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="W6" s="3"/>
-      <c r="X6" s="3"/>
-      <c r="Y6" s="3"/>
-      <c r="Z6" s="3"/>
-      <c r="AA6" s="3"/>
-      <c r="AC6" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="AD6" s="3"/>
-      <c r="AE6" s="3"/>
-      <c r="AF6" s="3"/>
-      <c r="AG6" s="3"/>
-      <c r="AH6" s="3"/>
-    </row>
-    <row r="7" spans="1:34" x14ac:dyDescent="0.35">
-      <c r="A7" s="1" t="s">
+      <c r="N6" s="17"/>
+      <c r="O6" s="17"/>
+      <c r="P6" s="17"/>
+      <c r="Q6" s="17"/>
+      <c r="R6" s="24"/>
+      <c r="S6" s="17" t="s">
+        <v>53</v>
+      </c>
+      <c r="T6" s="17"/>
+      <c r="U6" s="17"/>
+      <c r="V6" s="17"/>
+      <c r="W6" s="17"/>
+      <c r="X6" s="24"/>
+      <c r="Y6" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="Z6" s="2"/>
+      <c r="AA6" s="2"/>
+      <c r="AB6" s="2"/>
+      <c r="AC6" s="2"/>
+      <c r="AD6" s="2"/>
+    </row>
+    <row r="7" spans="1:30" x14ac:dyDescent="0.35">
+      <c r="A7" s="25" t="s">
         <v>0</v>
       </c>
-      <c r="B7" s="1" t="s">
+      <c r="B7" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="C7" s="25" t="s">
         <v>9</v>
       </c>
-      <c r="C7" s="1" t="s">
+      <c r="D7" s="25" t="s">
+        <v>1</v>
+      </c>
+      <c r="E7" s="25" t="s">
         <v>10</v>
       </c>
-      <c r="D7" s="1" t="s">
+      <c r="F7" s="27" t="s">
+        <v>2</v>
+      </c>
+      <c r="G7" s="25" t="s">
+        <v>0</v>
+      </c>
+      <c r="H7" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="I7" s="25" t="s">
+        <v>9</v>
+      </c>
+      <c r="J7" s="25" t="s">
         <v>1</v>
       </c>
-      <c r="E7" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="F7" s="1" t="s">
+      <c r="K7" s="25" t="s">
+        <v>10</v>
+      </c>
+      <c r="L7" s="27" t="s">
         <v>2</v>
       </c>
-      <c r="H7" s="1" t="s">
+      <c r="M7" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="I7" s="1" t="s">
+      <c r="N7" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="O7" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="J7" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="K7" s="1" t="s">
+      <c r="P7" s="1" t="s">
         <v>1</v>
-      </c>
-      <c r="L7" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="M7" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="O7" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="P7" s="1" t="s">
-        <v>9</v>
       </c>
       <c r="Q7" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="R7" s="1" t="s">
+      <c r="R7" s="27" t="s">
+        <v>2</v>
+      </c>
+      <c r="S7" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="T7" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="U7" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="V7" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="S7" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="T7" s="1" t="s">
+      <c r="W7" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="X7" s="27" t="s">
         <v>2</v>
       </c>
-      <c r="V7" s="1" t="s">
+      <c r="Y7" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="W7" s="1" t="s">
+      <c r="Z7" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="AA7" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="X7" s="1" t="s">
+      <c r="AB7" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="AC7" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="Y7" s="1" t="s">
+      <c r="AD7" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:30" x14ac:dyDescent="0.35">
+      <c r="A8" s="32">
         <v>1</v>
       </c>
-      <c r="Z7" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="AA7" s="1" t="s">
+      <c r="B8" s="32" t="s">
+        <v>25</v>
+      </c>
+      <c r="C8" s="32" t="s">
+        <v>27</v>
+      </c>
+      <c r="D8" s="32" t="s">
+        <v>38</v>
+      </c>
+      <c r="E8" s="32"/>
+      <c r="G8" s="32">
+        <v>1</v>
+      </c>
+      <c r="H8" s="32" t="s">
+        <v>34</v>
+      </c>
+      <c r="I8" s="32" t="s">
+        <v>27</v>
+      </c>
+      <c r="J8" s="32" t="s">
+        <v>36</v>
+      </c>
+      <c r="K8" s="32"/>
+      <c r="M8">
+        <v>1</v>
+      </c>
+      <c r="N8" t="s">
+        <v>41</v>
+      </c>
+      <c r="O8" t="s">
+        <v>27</v>
+      </c>
+      <c r="P8" t="s">
+        <v>42</v>
+      </c>
+      <c r="S8">
+        <v>1</v>
+      </c>
+      <c r="T8" t="s">
+        <v>52</v>
+      </c>
+      <c r="U8" t="s">
+        <v>57</v>
+      </c>
+      <c r="Y8">
+        <v>1</v>
+      </c>
+      <c r="Z8" t="s">
+        <v>63</v>
+      </c>
+      <c r="AA8" t="s">
+        <v>67</v>
+      </c>
+      <c r="AB8" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="9" spans="1:30" ht="58" x14ac:dyDescent="0.35">
+      <c r="A9" s="32">
         <v>2</v>
       </c>
-      <c r="AC7" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="AD7" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="AE7" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="AF7" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="AG7" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="AH7" s="1" t="s">
+      <c r="B9" s="32" t="s">
+        <v>49</v>
+      </c>
+      <c r="C9" s="32" t="s">
+        <v>28</v>
+      </c>
+      <c r="D9" s="32" t="s">
+        <v>39</v>
+      </c>
+      <c r="E9" s="32"/>
+      <c r="G9" s="32">
         <v>2</v>
       </c>
-    </row>
-    <row r="8" spans="1:34" x14ac:dyDescent="0.35">
-      <c r="A8">
-        <v>1</v>
-      </c>
-      <c r="B8" t="s">
+      <c r="H9" s="32" t="s">
+        <v>35</v>
+      </c>
+      <c r="I9" s="19" t="s">
+        <v>37</v>
+      </c>
+      <c r="J9" s="19" t="s">
+        <v>59</v>
+      </c>
+      <c r="K9" s="32"/>
+      <c r="M9">
+        <v>2</v>
+      </c>
+      <c r="N9" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="O9" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="P9" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="S9">
+        <v>2</v>
+      </c>
+      <c r="T9" t="s">
+        <v>56</v>
+      </c>
+      <c r="U9" t="s">
+        <v>58</v>
+      </c>
+      <c r="Y9">
+        <v>2</v>
+      </c>
+      <c r="Z9" t="s">
+        <v>64</v>
+      </c>
+      <c r="AA9" t="s">
         <v>27</v>
       </c>
-      <c r="C8" t="s">
+      <c r="AB9" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="10" spans="1:30" x14ac:dyDescent="0.35">
+      <c r="A10" s="32">
+        <v>3</v>
+      </c>
+      <c r="B10" s="32" t="s">
+        <v>26</v>
+      </c>
+      <c r="C10" s="32" t="s">
         <v>29</v>
       </c>
-      <c r="D8" t="s">
+      <c r="D10" s="32" t="s">
         <v>40</v>
       </c>
-      <c r="H8">
-        <v>1</v>
-      </c>
-      <c r="I8" t="s">
-        <v>36</v>
-      </c>
-      <c r="J8" t="s">
-        <v>29</v>
-      </c>
-      <c r="K8" t="s">
+      <c r="E10" s="32"/>
+      <c r="G10" s="20">
+        <v>3</v>
+      </c>
+      <c r="H10" s="20" t="s">
+        <v>50</v>
+      </c>
+      <c r="I10" s="32" t="s">
+        <v>51</v>
+      </c>
+      <c r="J10" s="32" t="s">
+        <v>60</v>
+      </c>
+      <c r="K10" s="32"/>
+      <c r="M10">
+        <v>3</v>
+      </c>
+      <c r="N10" t="s">
+        <v>46</v>
+      </c>
+      <c r="O10" t="s">
+        <v>47</v>
+      </c>
+      <c r="P10" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="S10">
+        <v>3</v>
+      </c>
+      <c r="T10" t="s">
+        <v>55</v>
+      </c>
+      <c r="U10" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="11" spans="1:30" x14ac:dyDescent="0.35">
+      <c r="A11" s="32">
+        <v>4</v>
+      </c>
+      <c r="B11" s="32" t="s">
+        <v>30</v>
+      </c>
+      <c r="C11" s="32" t="s">
+        <v>31</v>
+      </c>
+      <c r="D11" s="32" t="s">
         <v>38</v>
       </c>
-      <c r="O8">
-        <v>1</v>
-      </c>
-      <c r="P8" t="s">
-        <v>43</v>
-      </c>
-      <c r="Q8" t="s">
-        <v>29</v>
-      </c>
-      <c r="R8" t="s">
-        <v>44</v>
-      </c>
-      <c r="V8">
-        <v>1</v>
-      </c>
-      <c r="W8" t="s">
+      <c r="E11" s="32"/>
+      <c r="S11">
+        <v>4</v>
+      </c>
+      <c r="T11" t="s">
+        <v>52</v>
+      </c>
+      <c r="U11" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="12" spans="1:30" x14ac:dyDescent="0.35">
+      <c r="A12" s="32">
+        <v>5</v>
+      </c>
+      <c r="B12" s="32" t="s">
+        <v>32</v>
+      </c>
+      <c r="C12" s="32" t="s">
+        <v>33</v>
+      </c>
+      <c r="D12" s="32" t="s">
+        <v>40</v>
+      </c>
+      <c r="E12" s="32"/>
+      <c r="S12">
+        <v>5</v>
+      </c>
+      <c r="T12" t="s">
         <v>54</v>
       </c>
-      <c r="X8" t="s">
-        <v>59</v>
-      </c>
-      <c r="AC8">
-        <v>1</v>
-      </c>
-      <c r="AD8" t="s">
-        <v>65</v>
-      </c>
-      <c r="AE8" t="s">
-        <v>69</v>
-      </c>
-      <c r="AF8" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="9" spans="1:34" ht="58" x14ac:dyDescent="0.35">
-      <c r="A9">
-        <v>2</v>
-      </c>
-      <c r="B9" t="s">
-        <v>51</v>
-      </c>
-      <c r="C9" t="s">
-        <v>30</v>
-      </c>
-      <c r="D9" t="s">
-        <v>41</v>
-      </c>
-      <c r="H9">
-        <v>2</v>
-      </c>
-      <c r="I9" t="s">
-        <v>37</v>
-      </c>
-      <c r="J9" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="K9" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="O9">
-        <v>2</v>
-      </c>
-      <c r="P9" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="Q9" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="R9" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="V9">
-        <v>2</v>
-      </c>
-      <c r="W9" t="s">
+      <c r="U12" t="s">
         <v>58</v>
       </c>
-      <c r="X9" t="s">
-        <v>60</v>
-      </c>
-      <c r="AC9">
-        <v>2</v>
-      </c>
-      <c r="AD9" t="s">
-        <v>66</v>
-      </c>
-      <c r="AE9" t="s">
-        <v>29</v>
-      </c>
-      <c r="AF9" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="10" spans="1:34" x14ac:dyDescent="0.35">
-      <c r="A10">
-        <v>3</v>
-      </c>
-      <c r="B10" t="s">
-        <v>28</v>
-      </c>
-      <c r="C10" t="s">
-        <v>31</v>
-      </c>
-      <c r="D10" t="s">
-        <v>42</v>
-      </c>
-      <c r="H10" s="5">
-        <v>3</v>
-      </c>
-      <c r="I10" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="J10" t="s">
-        <v>53</v>
-      </c>
-      <c r="K10" t="s">
-        <v>62</v>
-      </c>
-      <c r="O10">
-        <v>3</v>
-      </c>
-      <c r="P10" t="s">
-        <v>48</v>
-      </c>
-      <c r="Q10" t="s">
-        <v>49</v>
-      </c>
-      <c r="R10" s="6" t="s">
-        <v>50</v>
-      </c>
-      <c r="V10">
-        <v>3</v>
-      </c>
-      <c r="W10" t="s">
-        <v>57</v>
-      </c>
-      <c r="X10" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="11" spans="1:34" x14ac:dyDescent="0.35">
-      <c r="A11">
-        <v>4</v>
-      </c>
-      <c r="B11" t="s">
-        <v>32</v>
-      </c>
-      <c r="C11" t="s">
-        <v>33</v>
-      </c>
-      <c r="D11" t="s">
-        <v>40</v>
-      </c>
-      <c r="V11">
-        <v>4</v>
-      </c>
-      <c r="W11" t="s">
-        <v>54</v>
-      </c>
-      <c r="X11" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="12" spans="1:34" x14ac:dyDescent="0.35">
-      <c r="A12">
-        <v>5</v>
-      </c>
-      <c r="B12" t="s">
-        <v>34</v>
-      </c>
-      <c r="C12" t="s">
-        <v>35</v>
-      </c>
-      <c r="D12" t="s">
-        <v>42</v>
-      </c>
-      <c r="V12">
-        <v>5</v>
-      </c>
-      <c r="W12" t="s">
-        <v>56</v>
-      </c>
-      <c r="X12" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="13" spans="1:34" x14ac:dyDescent="0.35">
-      <c r="A13" s="5"/>
-      <c r="B13" s="5"/>
-      <c r="C13" s="5"/>
+    </row>
+    <row r="13" spans="1:30" x14ac:dyDescent="0.35">
+      <c r="A13" s="4"/>
+      <c r="B13" s="4"/>
+      <c r="C13" s="4"/>
     </row>
   </sheetData>
   <mergeCells count="25">
-    <mergeCell ref="A3:C3"/>
-    <mergeCell ref="H3:J3"/>
-    <mergeCell ref="O3:Q3"/>
-    <mergeCell ref="A2:C2"/>
-    <mergeCell ref="H2:J2"/>
-    <mergeCell ref="AC1:AH1"/>
-    <mergeCell ref="AC2:AE2"/>
-    <mergeCell ref="AC3:AE3"/>
-    <mergeCell ref="V4:AA5"/>
-    <mergeCell ref="V6:AA6"/>
-    <mergeCell ref="AC4:AH5"/>
-    <mergeCell ref="AC6:AH6"/>
-    <mergeCell ref="V2:X2"/>
-    <mergeCell ref="V3:X3"/>
-    <mergeCell ref="V1:AA1"/>
-    <mergeCell ref="O1:T1"/>
-    <mergeCell ref="O2:Q2"/>
-    <mergeCell ref="H4:M5"/>
-    <mergeCell ref="H6:M6"/>
-    <mergeCell ref="O4:T5"/>
-    <mergeCell ref="O6:T6"/>
-    <mergeCell ref="H1:M1"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="A3:B3"/>
+    <mergeCell ref="G2:H2"/>
+    <mergeCell ref="G3:H3"/>
+    <mergeCell ref="M2:N2"/>
+    <mergeCell ref="M3:N3"/>
+    <mergeCell ref="Y1:AD1"/>
+    <mergeCell ref="Y2:Z2"/>
+    <mergeCell ref="Y3:Z3"/>
+    <mergeCell ref="S4:X5"/>
+    <mergeCell ref="S6:X6"/>
+    <mergeCell ref="Y4:AD5"/>
+    <mergeCell ref="Y6:AD6"/>
+    <mergeCell ref="S2:T2"/>
+    <mergeCell ref="S3:T3"/>
+    <mergeCell ref="S1:X1"/>
+    <mergeCell ref="M1:R1"/>
+    <mergeCell ref="G4:L5"/>
+    <mergeCell ref="G6:L6"/>
+    <mergeCell ref="M4:R5"/>
+    <mergeCell ref="M6:R6"/>
+    <mergeCell ref="G1:L1"/>
     <mergeCell ref="A4:F5"/>
     <mergeCell ref="A6:F6"/>
     <mergeCell ref="A1:F1"/>

--- a/Test Cases.xlsx
+++ b/Test Cases.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://endresshauser-my.sharepoint.com/personal/corbin_ferguson_endress_com/Documents/Thesis Work/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1623" documentId="11_AD4DB114E441178AC67DF4D41ED1D894683EDF27" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F6880D38-75ED-44FD-ABA6-68371B1CE8AA}"/>
+  <xr:revisionPtr revIDLastSave="1627" documentId="11_AD4DB114E441178AC67DF4D41ED1D894683EDF27" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{361B8735-BBF4-43CD-ABC6-232ECC75B30E}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="25440" windowHeight="15270" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-36110" yWindow="2970" windowWidth="19420" windowHeight="10300" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tests" sheetId="7" r:id="rId1"/>
@@ -22,7 +22,7 @@
   </sheets>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="19" r:id="rId7"/>
+    <pivotCache cacheId="0" r:id="rId7"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
   <metadataTypes count="1">
     <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
   </metadataTypes>
@@ -66,7 +66,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="523" uniqueCount="190">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="523" uniqueCount="191">
   <si>
     <t>Step</t>
   </si>
@@ -670,9 +670,6 @@
     <t>"Cancel" button press</t>
   </si>
   <si>
-    <t>"Select Element" button pressed</t>
-  </si>
-  <si>
     <t>open type select window</t>
   </si>
   <si>
@@ -866,6 +863,12 @@
   </si>
   <si>
     <t>Test Priority: Low</t>
+  </si>
+  <si>
+    <t>Select Quantity</t>
+  </si>
+  <si>
+    <t>"Create Element" button pressed</t>
   </si>
 </sst>
 </file>
@@ -941,96 +944,58 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="42">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" pivotButton="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1222,6 +1187,18 @@
           </c:extLst>
         </c:dLbl>
       </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="1"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+      </c:pivotFmt>
     </c:pivotFmts>
     <c:plotArea>
       <c:layout/>
@@ -1253,6 +1230,11 @@
               </a:ln>
               <a:effectLst/>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000001-6965-4BB0-963B-D0828DC189BE}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:cat>
             <c:strRef>
@@ -2061,7 +2043,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{271A9901-5E04-4A3B-B526-FF91A8F26FEF}" name="PivotTable1" cacheId="19" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="2">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{271A9901-5E04-4A3B-B526-FF91A8F26FEF}" name="PivotTable1" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="2">
   <location ref="H1:I3" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="1">
     <pivotField axis="axisRow" dataField="1" showAll="0">
@@ -2091,11 +2073,23 @@
   <dataFields count="1">
     <dataField name="Count of Test Status" fld="0" subtotal="count" baseField="0" baseItem="0"/>
   </dataFields>
-  <chartFormats count="1">
+  <chartFormats count="2">
     <chartFormat chart="0" format="0" series="1">
       <pivotArea type="data" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="0" format="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="0" count="1" selected="0">
             <x v="0"/>
           </reference>
         </references>
@@ -2396,45 +2390,45 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F8512478-31DB-4352-AB46-996C676231F3}">
   <dimension ref="A1:I16"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="10.36328125" customWidth="1"/>
-    <col min="2" max="2" width="34.1796875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="16.1796875" style="13" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="18.36328125" hidden="1" customWidth="1"/>
-    <col min="5" max="5" width="13.453125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="16.1796875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.42578125" customWidth="1"/>
+    <col min="2" max="2" width="34.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="16.140625" style="6" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="18.42578125" hidden="1" customWidth="1"/>
+    <col min="5" max="5" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="16.140625" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="18" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
+        <v>158</v>
+      </c>
+      <c r="B1" t="s">
         <v>159</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" s="6" t="s">
         <v>160</v>
       </c>
-      <c r="C1" s="13" t="s">
-        <v>161</v>
-      </c>
       <c r="D1" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="E1" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="G1">
         <f>COUNTIF(TestMaster[Test Status], "Not Implemented")</f>
         <v>15</v>
       </c>
-      <c r="H1" s="14" t="s">
-        <v>171</v>
+      <c r="H1" s="7" t="s">
+        <v>170</v>
       </c>
       <c r="I1" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.35">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2">
         <f t="shared" ref="A2:A16" si="0">ROW()-1</f>
         <v>1</v>
@@ -2443,27 +2437,27 @@
         <f t="array" ref="B2">'Element Import Testing'!A1:A1</f>
         <v>Import Select Redundant Name</v>
       </c>
-      <c r="C2" s="13" t="s">
-        <v>165</v>
+      <c r="C2" s="6" t="s">
+        <v>164</v>
       </c>
       <c r="D2" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="E2" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="G2">
         <f>COUNTIF(TestMaster[Test Status], "Pass")</f>
         <v>0</v>
       </c>
-      <c r="H2" s="15" t="s">
-        <v>165</v>
-      </c>
-      <c r="I2" s="12">
+      <c r="H2" s="8" t="s">
+        <v>164</v>
+      </c>
+      <c r="I2">
         <v>17</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3">
         <f t="shared" si="0"/>
         <v>2</v>
@@ -2472,27 +2466,27 @@
         <f t="array" ref="B3">'Element Creation Testing'!A1:A1</f>
         <v>Element Quantity Creation</v>
       </c>
-      <c r="C3" s="13" t="s">
+      <c r="C3" s="6" t="s">
+        <v>164</v>
+      </c>
+      <c r="D3" t="s">
         <v>165</v>
       </c>
-      <c r="D3" t="s">
-        <v>166</v>
-      </c>
       <c r="E3" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="G3">
         <f>COUNTIF(TestMaster[Test Status], "Fail")</f>
         <v>0</v>
       </c>
-      <c r="H3" s="15" t="s">
-        <v>172</v>
-      </c>
-      <c r="I3" s="12">
+      <c r="H3" s="8" t="s">
+        <v>171</v>
+      </c>
+      <c r="I3">
         <v>17</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4">
         <f t="shared" si="0"/>
         <v>3</v>
@@ -2501,18 +2495,18 @@
         <f t="array" ref="B4">'Element Creation Testing'!G1:G1</f>
         <v>Nameless Module Creation</v>
       </c>
-      <c r="C4" s="13" t="s">
-        <v>165</v>
+      <c r="C4" s="6" t="s">
+        <v>164</v>
       </c>
       <c r="E4" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="G4">
         <f>COUNTIF(TestMaster[Test Status], "Not Run")</f>
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5">
         <f t="shared" si="0"/>
         <v>4</v>
@@ -2521,14 +2515,14 @@
         <f t="array" ref="B5">'Element Creation Testing'!M1:M1</f>
         <v>Redundant Element Creation</v>
       </c>
-      <c r="C5" s="13" t="s">
-        <v>165</v>
+      <c r="C5" s="6" t="s">
+        <v>164</v>
       </c>
       <c r="E5" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.35">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6">
         <f t="shared" si="0"/>
         <v>5</v>
@@ -2537,14 +2531,14 @@
         <f>'Element Modification Testing'!A1</f>
         <v>No Element to Modify</v>
       </c>
-      <c r="C6" s="13" t="s">
-        <v>165</v>
+      <c r="C6" s="6" t="s">
+        <v>164</v>
       </c>
       <c r="E6" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.35">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7">
         <f t="shared" si="0"/>
         <v>6</v>
@@ -2553,14 +2547,14 @@
         <f>'Element Modification Testing'!G1</f>
         <v>Completed Element Modification</v>
       </c>
-      <c r="C7" s="13" t="s">
-        <v>165</v>
+      <c r="C7" s="6" t="s">
+        <v>164</v>
       </c>
       <c r="E7" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.35">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8">
         <f t="shared" si="0"/>
         <v>7</v>
@@ -2569,14 +2563,14 @@
         <f>'Element Modification Testing'!M1</f>
         <v>Modify into Redundant Element Name</v>
       </c>
-      <c r="C8" s="13" t="s">
-        <v>165</v>
+      <c r="C8" s="6" t="s">
+        <v>164</v>
       </c>
       <c r="E8" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.35">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9">
         <f t="shared" si="0"/>
         <v>8</v>
@@ -2585,14 +2579,14 @@
         <f>'Element Deletion Testing'!A1</f>
         <v>Delete No Element Type</v>
       </c>
-      <c r="C9" s="13" t="s">
-        <v>165</v>
+      <c r="C9" s="6" t="s">
+        <v>164</v>
       </c>
       <c r="E9" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.35">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10">
         <f t="shared" si="0"/>
         <v>9</v>
@@ -2601,14 +2595,14 @@
         <f>'Element Deletion Testing'!G1</f>
         <v>Delete Element Found</v>
       </c>
-      <c r="C10" s="13" t="s">
-        <v>165</v>
+      <c r="C10" s="6" t="s">
+        <v>164</v>
       </c>
       <c r="E10" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.35">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11">
         <f t="shared" si="0"/>
         <v>10</v>
@@ -2617,14 +2611,14 @@
         <f>'Element Deletion Testing'!M1</f>
         <v>Delete Module by Port</v>
       </c>
-      <c r="C11" s="13" t="s">
-        <v>165</v>
+      <c r="C11" s="6" t="s">
+        <v>164</v>
       </c>
       <c r="E11" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.35">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12">
         <f t="shared" si="0"/>
         <v>11</v>
@@ -2633,14 +2627,14 @@
         <f>'File Manipulation Testing'!A1</f>
         <v>New File Creation</v>
       </c>
-      <c r="C12" s="13" t="s">
-        <v>165</v>
+      <c r="C12" s="6" t="s">
+        <v>164</v>
       </c>
       <c r="E12" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.35">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13">
         <f t="shared" si="0"/>
         <v>12</v>
@@ -2649,14 +2643,14 @@
         <f>'File Manipulation Testing'!G1</f>
         <v>Save File</v>
       </c>
-      <c r="C13" s="13" t="s">
-        <v>165</v>
+      <c r="C13" s="6" t="s">
+        <v>164</v>
       </c>
       <c r="E13" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.35">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A14">
         <f t="shared" si="0"/>
         <v>13</v>
@@ -2665,14 +2659,14 @@
         <f>'File Manipulation Testing'!M1</f>
         <v>Load File</v>
       </c>
-      <c r="C14" s="13" t="s">
-        <v>165</v>
+      <c r="C14" s="6" t="s">
+        <v>164</v>
       </c>
       <c r="E14" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.35">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A15">
         <f t="shared" si="0"/>
         <v>14</v>
@@ -2681,43 +2675,31 @@
         <f>'File Manipulation Testing'!S1</f>
         <v>Validate File</v>
       </c>
-      <c r="C15" s="13" t="s">
-        <v>165</v>
+      <c r="C15" s="6" t="s">
+        <v>164</v>
       </c>
       <c r="E15" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.35">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A16">
         <f t="shared" si="0"/>
         <v>15</v>
       </c>
-      <c r="B16" s="12" t="str">
+      <c r="B16" t="str">
         <f>'File Manipulation Testing'!Y1</f>
         <v>Exit</v>
       </c>
-      <c r="C16" s="13" t="s">
-        <v>165</v>
+      <c r="C16" s="6" t="s">
+        <v>164</v>
       </c>
       <c r="E16" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
-  <conditionalFormatting sqref="C17:C1048576">
-    <cfRule type="colorScale" priority="5">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
   <conditionalFormatting sqref="C1:C1048576">
     <cfRule type="containsText" dxfId="3" priority="1" operator="containsText" text="Not Run">
       <formula>NOT(ISERROR(SEARCH("Not Run",C1)))</formula>
@@ -2730,6 +2712,18 @@
     </cfRule>
     <cfRule type="containsText" dxfId="0" priority="4" operator="containsText" text="Not Implemented">
       <formula>NOT(ISERROR(SEARCH("Not Implemented",C1)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C17:C1048576">
+    <cfRule type="colorScale" priority="5">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="2">
@@ -2754,394 +2748,372 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B60DAC1D-2E28-4DF7-A44B-A179A310D91E}">
   <dimension ref="A1:F25"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="6.36328125" customWidth="1"/>
-    <col min="2" max="2" width="22.90625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="48.81640625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="56.7265625" style="3" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="18.36328125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="16.1796875" style="23" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="6.42578125" customWidth="1"/>
+    <col min="2" max="2" width="22.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="48.85546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="56.7109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="18.42578125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="16.140625" style="9" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A1" s="17" t="s">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1" s="16" t="s">
         <v>13</v>
       </c>
-      <c r="B1" s="17"/>
-      <c r="C1" s="17"/>
-      <c r="D1" s="17"/>
-      <c r="E1" s="17"/>
-      <c r="F1" s="24"/>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A2" s="17" t="s">
+      <c r="B1" s="16"/>
+      <c r="C1" s="16"/>
+      <c r="D1" s="16"/>
+      <c r="E1" s="16"/>
+      <c r="F1" s="17"/>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2" s="16" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="17"/>
-      <c r="C2" s="18">
+      <c r="B2" s="16"/>
+      <c r="C2" s="8">
         <f>IFERROR(_xlfn.XLOOKUP(A1, TestMaster[Test Name], TestMaster[Test ID], "ID not found"), "")</f>
         <v>1</v>
       </c>
-      <c r="D2" s="19"/>
-      <c r="E2" s="20" t="s">
+      <c r="E2" t="s">
         <v>4</v>
       </c>
-      <c r="F2" s="21"/>
-    </row>
-    <row r="3" spans="1:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="17" t="s">
-        <v>188</v>
-      </c>
-      <c r="B3" s="17"/>
-      <c r="C3" s="22" t="str">
+    </row>
+    <row r="3" spans="1:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="16" t="s">
+        <v>187</v>
+      </c>
+      <c r="B3" s="16"/>
+      <c r="C3" s="10" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(A1, TestMaster[Test Name], TestMaster[Test Priority], "Priority not found"), "")</f>
         <v>Medium</v>
       </c>
-      <c r="D3" s="19"/>
-      <c r="E3" s="20" t="s">
+      <c r="E3" t="s">
         <v>5</v>
       </c>
-      <c r="F3" s="23" t="str">
+      <c r="F3" s="9" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(A1, TestMaster[Test Name], TestMaster[Test Status], "Status not found"), "")</f>
         <v>Not Implemented</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A4" s="17" t="s">
-        <v>185</v>
-      </c>
-      <c r="B4" s="17"/>
-      <c r="C4" s="17"/>
-      <c r="D4" s="17"/>
-      <c r="E4" s="17"/>
-      <c r="F4" s="24"/>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A5" s="17"/>
-      <c r="B5" s="17"/>
-      <c r="C5" s="17"/>
-      <c r="D5" s="17"/>
-      <c r="E5" s="17"/>
-      <c r="F5" s="24"/>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A6" s="17" t="s">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" s="16" t="s">
+        <v>184</v>
+      </c>
+      <c r="B4" s="16"/>
+      <c r="C4" s="16"/>
+      <c r="D4" s="16"/>
+      <c r="E4" s="16"/>
+      <c r="F4" s="17"/>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" s="16"/>
+      <c r="B5" s="16"/>
+      <c r="C5" s="16"/>
+      <c r="D5" s="16"/>
+      <c r="E5" s="16"/>
+      <c r="F5" s="17"/>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" s="16" t="s">
         <v>7</v>
       </c>
-      <c r="B6" s="17"/>
-      <c r="C6" s="17"/>
-      <c r="D6" s="17"/>
-      <c r="E6" s="17"/>
-      <c r="F6" s="24"/>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A7" s="25" t="s">
+      <c r="B6" s="16"/>
+      <c r="C6" s="16"/>
+      <c r="D6" s="16"/>
+      <c r="E6" s="16"/>
+      <c r="F6" s="17"/>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B7" s="25" t="s">
+      <c r="B7" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C7" s="25" t="s">
+      <c r="C7" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="D7" s="26" t="s">
+      <c r="D7" s="11" t="s">
         <v>1</v>
       </c>
-      <c r="E7" s="25" t="s">
+      <c r="E7" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="F7" s="27" t="s">
+      <c r="F7" s="12" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="8" spans="1:6" s="11" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="28">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A8">
         <v>1</v>
       </c>
-      <c r="B8" s="28" t="s">
+      <c r="B8" t="s">
+        <v>175</v>
+      </c>
+      <c r="C8" t="s">
         <v>176</v>
       </c>
-      <c r="C8" s="28" t="s">
+      <c r="D8" s="2" t="s">
         <v>177</v>
       </c>
-      <c r="D8" s="29" t="s">
-        <v>178</v>
-      </c>
-      <c r="E8" s="28"/>
-      <c r="F8" s="30"/>
-    </row>
-    <row r="9" spans="1:6" ht="29" x14ac:dyDescent="0.35">
-      <c r="A9" s="34">
+    </row>
+    <row r="9" spans="1:6" ht="45" x14ac:dyDescent="0.25">
+      <c r="A9" s="5">
         <f>A8+1</f>
         <v>2</v>
       </c>
-      <c r="B9" s="31" t="s">
+      <c r="B9" s="4" t="s">
+        <v>173</v>
+      </c>
+      <c r="C9" s="4" t="s">
         <v>174</v>
       </c>
-      <c r="C9" s="31" t="s">
-        <v>175</v>
-      </c>
-      <c r="D9" s="31" t="s">
-        <v>125</v>
-      </c>
-      <c r="E9" s="32"/>
-    </row>
-    <row r="10" spans="1:6" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A10" s="34">
+      <c r="D9" s="4" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+      <c r="A10" s="5">
         <f>A9+1</f>
         <v>3</v>
       </c>
-      <c r="B10" s="31" t="s">
+      <c r="B10" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="D10" s="4" t="s">
         <v>126</v>
       </c>
-      <c r="C10" s="33" t="s">
-        <v>141</v>
-      </c>
-      <c r="D10" s="31" t="s">
-        <v>127</v>
-      </c>
-      <c r="E10" s="32"/>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A11" s="34">
+    </row>
+    <row r="11" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+      <c r="A11" s="5">
         <f t="shared" ref="A11:A25" si="0">A10+1</f>
         <v>4</v>
       </c>
-      <c r="B11" s="31" t="s">
-        <v>179</v>
-      </c>
-      <c r="C11" s="31" t="s">
-        <v>142</v>
-      </c>
-      <c r="D11" s="31" t="s">
-        <v>187</v>
-      </c>
-      <c r="E11" s="32"/>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A12" s="34">
+      <c r="B11" s="4" t="s">
+        <v>178</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="D11" s="4" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A12" s="5">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="B12" s="31" t="s">
+      <c r="B12" s="4" t="s">
+        <v>179</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="D12" s="2" t="s">
         <v>180</v>
       </c>
-      <c r="C12" s="31" t="s">
-        <v>28</v>
-      </c>
-      <c r="D12" s="19" t="s">
-        <v>181</v>
-      </c>
-      <c r="E12" s="32"/>
-    </row>
-    <row r="13" spans="1:6" ht="29" x14ac:dyDescent="0.35">
-      <c r="A13" s="34">
+    </row>
+    <row r="13" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+      <c r="A13" s="5">
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
-      <c r="B13" s="31" t="s">
+      <c r="B13" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="D13" s="4" t="s">
         <v>126</v>
       </c>
-      <c r="C13" s="33" t="s">
-        <v>141</v>
-      </c>
-      <c r="D13" s="31" t="s">
-        <v>127</v>
-      </c>
-      <c r="E13" s="32"/>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A14" s="34">
+    </row>
+    <row r="14" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+      <c r="A14" s="5">
         <f t="shared" si="0"/>
         <v>7</v>
       </c>
-      <c r="B14" s="31" t="s">
-        <v>179</v>
-      </c>
-      <c r="C14" s="31" t="s">
-        <v>142</v>
-      </c>
-      <c r="D14" s="31" t="s">
-        <v>183</v>
-      </c>
-      <c r="E14" s="32"/>
-    </row>
-    <row r="15" spans="1:6" ht="29" x14ac:dyDescent="0.35">
-      <c r="A15" s="34">
+      <c r="B14" s="4" t="s">
+        <v>178</v>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="D14" s="4" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+      <c r="A15" s="5">
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
-      <c r="B15" s="32" t="s">
+      <c r="B15" t="s">
         <v>107</v>
       </c>
-      <c r="C15" s="32" t="s">
+      <c r="C15" t="s">
         <v>111</v>
       </c>
-      <c r="D15" s="19" t="s">
-        <v>182</v>
-      </c>
-      <c r="E15" s="32"/>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A16" s="34">
+      <c r="D15" s="2" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A16" s="5">
         <f t="shared" si="0"/>
         <v>9</v>
       </c>
-      <c r="B16" s="31" t="s">
+      <c r="B16" s="4" t="s">
+        <v>179</v>
+      </c>
+      <c r="C16" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="D16" s="2" t="s">
         <v>180</v>
       </c>
-      <c r="C16" s="31" t="s">
-        <v>28</v>
-      </c>
-      <c r="D16" s="19" t="s">
-        <v>181</v>
-      </c>
-      <c r="E16" s="32"/>
-    </row>
-    <row r="17" spans="1:5" ht="29" x14ac:dyDescent="0.35">
-      <c r="A17" s="34">
+    </row>
+    <row r="17" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+      <c r="A17" s="5">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="B17" s="31" t="s">
+      <c r="B17" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="C17" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="D17" s="4" t="s">
         <v>126</v>
       </c>
-      <c r="C17" s="33" t="s">
-        <v>141</v>
-      </c>
-      <c r="D17" s="31" t="s">
-        <v>127</v>
-      </c>
-      <c r="E17" s="32"/>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A18" s="34">
+    </row>
+    <row r="18" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+      <c r="A18" s="5">
         <f t="shared" si="0"/>
         <v>11</v>
       </c>
-      <c r="B18" s="31" t="s">
-        <v>179</v>
-      </c>
-      <c r="C18" s="31" t="s">
-        <v>142</v>
-      </c>
-      <c r="D18" s="31" t="s">
-        <v>129</v>
-      </c>
-      <c r="E18" s="32"/>
-    </row>
-    <row r="19" spans="1:5" ht="29" x14ac:dyDescent="0.35">
-      <c r="A19" s="34">
+      <c r="B18" s="4" t="s">
+        <v>178</v>
+      </c>
+      <c r="C18" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="D18" s="4" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A19" s="5">
         <f t="shared" si="0"/>
         <v>12</v>
       </c>
-      <c r="B19" s="32" t="s">
+      <c r="B19" t="s">
         <v>107</v>
       </c>
-      <c r="C19" s="32" t="s">
+      <c r="C19" t="s">
         <v>123</v>
       </c>
-      <c r="D19" s="19" t="s">
-        <v>153</v>
-      </c>
-      <c r="E19" s="32"/>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A20" s="34">
+      <c r="D19" s="2" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A20" s="5">
         <f t="shared" si="0"/>
         <v>13</v>
       </c>
-      <c r="B20" s="31" t="s">
+      <c r="B20" s="4" t="s">
+        <v>179</v>
+      </c>
+      <c r="C20" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="D20" s="2" t="s">
         <v>180</v>
       </c>
-      <c r="C20" s="31" t="s">
-        <v>28</v>
-      </c>
-      <c r="D20" s="19" t="s">
-        <v>181</v>
-      </c>
-      <c r="E20" s="32"/>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A21" s="34">
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A21" s="5">
         <f t="shared" si="0"/>
         <v>14</v>
       </c>
-      <c r="B21" s="32" t="s">
+      <c r="B21" t="s">
         <v>107</v>
       </c>
-      <c r="C21" s="32" t="s">
+      <c r="C21" t="s">
         <v>109</v>
       </c>
-      <c r="D21" s="19" t="s">
-        <v>157</v>
-      </c>
-      <c r="E21" s="32"/>
-    </row>
-    <row r="22" spans="1:5" ht="29" x14ac:dyDescent="0.35">
-      <c r="A22" s="34">
+      <c r="D21" s="2" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A22" s="5">
         <f t="shared" si="0"/>
         <v>15</v>
       </c>
-      <c r="B22" s="32" t="s">
+      <c r="B22" t="s">
         <v>112</v>
       </c>
-      <c r="C22" s="31" t="s">
-        <v>186</v>
-      </c>
-      <c r="D22" s="19" t="s">
+      <c r="C22" s="4" t="s">
+        <v>185</v>
+      </c>
+      <c r="D22" s="2" t="s">
         <v>110</v>
       </c>
-      <c r="E22" s="32"/>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A23" s="34">
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A23" s="5">
         <f t="shared" si="0"/>
         <v>16</v>
       </c>
-      <c r="B23" s="32" t="s">
+      <c r="B23" t="s">
         <v>107</v>
       </c>
-      <c r="C23" s="32" t="s">
+      <c r="C23" t="s">
         <v>109</v>
       </c>
-      <c r="D23" s="19" t="s">
-        <v>157</v>
-      </c>
-      <c r="E23" s="32"/>
-    </row>
-    <row r="24" spans="1:5" ht="29" x14ac:dyDescent="0.35">
-      <c r="A24" s="34">
+      <c r="D23" s="2" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A24" s="5">
         <f t="shared" si="0"/>
         <v>17</v>
       </c>
-      <c r="B24" s="32" t="s">
+      <c r="B24" t="s">
         <v>113</v>
       </c>
-      <c r="C24" s="32" t="s">
+      <c r="C24" t="s">
         <v>114</v>
       </c>
-      <c r="D24" s="19" t="s">
-        <v>158</v>
-      </c>
-      <c r="E24" s="32"/>
-    </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A25" s="34">
+      <c r="D24" s="2" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A25" s="5">
         <f t="shared" si="0"/>
         <v>18</v>
       </c>
-      <c r="B25" s="31" t="s">
-        <v>180</v>
-      </c>
-      <c r="C25" s="31" t="s">
-        <v>184</v>
-      </c>
-      <c r="D25" s="19" t="s">
+      <c r="B25" s="4" t="s">
+        <v>179</v>
+      </c>
+      <c r="C25" s="4" t="s">
+        <v>183</v>
+      </c>
+      <c r="D25" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="E25" s="32"/>
     </row>
   </sheetData>
   <mergeCells count="5">
@@ -3158,640 +3130,596 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CA0AB6AA-BAF4-4C64-96FE-66D32370F298}">
   <dimension ref="A1:R21"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="5" style="10" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="34.453125" style="10" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="24.90625" style="10" customWidth="1"/>
-    <col min="4" max="4" width="35.54296875" style="10" customWidth="1"/>
-    <col min="5" max="5" width="18.36328125" style="10" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="16.1796875" style="35" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="5" style="10" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="29.1796875" style="10" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="24.08984375" style="10" customWidth="1"/>
-    <col min="10" max="10" width="24" style="10" customWidth="1"/>
-    <col min="11" max="11" width="18.36328125" style="10" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="16.1796875" style="35" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="5" style="10" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="29.1796875" style="10" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="25.6328125" style="10" customWidth="1"/>
-    <col min="16" max="16" width="23.90625" style="10" customWidth="1"/>
-    <col min="17" max="17" width="18.36328125" style="10" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="16.1796875" style="10" bestFit="1" customWidth="1"/>
-    <col min="19" max="16384" width="8.7265625" style="10"/>
+    <col min="1" max="1" width="5" style="5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="34.42578125" style="5" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="24.85546875" style="5" customWidth="1"/>
+    <col min="4" max="4" width="35.5703125" style="5" customWidth="1"/>
+    <col min="5" max="5" width="18.42578125" style="5" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="16.140625" style="13" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="5" style="5" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="29.140625" style="5" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="24.140625" style="5" customWidth="1"/>
+    <col min="10" max="10" width="24" style="5" customWidth="1"/>
+    <col min="11" max="11" width="18.42578125" style="5" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="16.140625" style="13" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="5" style="5" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="29.140625" style="5" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="25.5703125" style="5" customWidth="1"/>
+    <col min="16" max="16" width="23.85546875" style="5" customWidth="1"/>
+    <col min="17" max="17" width="18.42578125" style="5" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="16.140625" style="5" bestFit="1" customWidth="1"/>
+    <col min="19" max="16384" width="8.7109375" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="17" t="s">
+    <row r="1" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="16" t="s">
         <v>14</v>
       </c>
-      <c r="B1" s="17"/>
-      <c r="C1" s="17"/>
-      <c r="D1" s="17"/>
-      <c r="E1" s="17"/>
-      <c r="F1" s="24"/>
-      <c r="G1" s="17" t="s">
+      <c r="B1" s="16"/>
+      <c r="C1" s="16"/>
+      <c r="D1" s="16"/>
+      <c r="E1" s="16"/>
+      <c r="F1" s="17"/>
+      <c r="G1" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="H1" s="17"/>
-      <c r="I1" s="17"/>
-      <c r="J1" s="17"/>
-      <c r="K1" s="17"/>
-      <c r="L1" s="17"/>
-      <c r="M1" s="17" t="s">
-        <v>162</v>
-      </c>
-      <c r="N1" s="17"/>
-      <c r="O1" s="17"/>
-      <c r="P1" s="17"/>
-      <c r="Q1" s="17"/>
-      <c r="R1" s="17"/>
-    </row>
-    <row r="2" spans="1:18" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="17" t="s">
+      <c r="H1" s="16"/>
+      <c r="I1" s="16"/>
+      <c r="J1" s="16"/>
+      <c r="K1" s="16"/>
+      <c r="L1" s="16"/>
+      <c r="M1" s="16" t="s">
+        <v>161</v>
+      </c>
+      <c r="N1" s="16"/>
+      <c r="O1" s="16"/>
+      <c r="P1" s="16"/>
+      <c r="Q1" s="16"/>
+      <c r="R1" s="16"/>
+    </row>
+    <row r="2" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="16" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="17"/>
-      <c r="C2" s="20">
+      <c r="B2" s="16"/>
+      <c r="C2">
         <f>IFERROR(_xlfn.XLOOKUP(A1, TestMaster[Test Name], TestMaster[Test ID], "ID not found"), "")</f>
         <v>2</v>
       </c>
-      <c r="D2" s="34"/>
-      <c r="E2" s="20" t="s">
+      <c r="D2" s="5"/>
+      <c r="E2" t="s">
         <v>4</v>
       </c>
-      <c r="F2" s="21"/>
-      <c r="G2" s="17" t="s">
+      <c r="F2" s="9"/>
+      <c r="G2" s="16" t="s">
         <v>3</v>
       </c>
-      <c r="H2" s="17"/>
-      <c r="I2" s="20">
+      <c r="H2" s="16"/>
+      <c r="I2">
         <f>IFERROR(_xlfn.XLOOKUP(G1, TestMaster[Test Name], TestMaster[Test ID], "ID not found"), "")</f>
         <v>3</v>
       </c>
-      <c r="J2" s="34"/>
-      <c r="K2" s="20" t="s">
+      <c r="J2" s="5"/>
+      <c r="K2" t="s">
         <v>4</v>
       </c>
-      <c r="L2" s="21"/>
-      <c r="M2" s="17" t="s">
+      <c r="L2" s="9"/>
+      <c r="M2" s="16" t="s">
         <v>3</v>
       </c>
-      <c r="N2" s="17"/>
-      <c r="O2" s="20">
+      <c r="N2" s="16"/>
+      <c r="O2">
         <f>IFERROR(_xlfn.XLOOKUP(M1, TestMaster[Test Name], TestMaster[Test ID], "ID not found"), "")</f>
         <v>4</v>
       </c>
-      <c r="P2" s="34"/>
-      <c r="Q2" s="20" t="s">
+      <c r="P2" s="5"/>
+      <c r="Q2" t="s">
         <v>4</v>
       </c>
-      <c r="R2" s="20"/>
-    </row>
-    <row r="3" spans="1:18" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="17" t="s">
-        <v>188</v>
-      </c>
-      <c r="B3" s="17"/>
-      <c r="C3" s="20" t="str">
+    </row>
+    <row r="3" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="16" t="s">
+        <v>187</v>
+      </c>
+      <c r="B3" s="16"/>
+      <c r="C3" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(A1, TestMaster[Test Name], TestMaster[Test Priority], "Priority not found"), "")</f>
         <v>High</v>
       </c>
-      <c r="D3" s="34"/>
-      <c r="E3" s="20" t="s">
+      <c r="D3" s="5"/>
+      <c r="E3" t="s">
         <v>5</v>
       </c>
-      <c r="F3" s="21" t="str">
+      <c r="F3" s="9" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(A1, TestMaster[Test Name], TestMaster[Test Status], "Status not found"), "")</f>
         <v>Not Implemented</v>
       </c>
-      <c r="G3" s="17" t="s">
-        <v>188</v>
-      </c>
-      <c r="H3" s="17"/>
-      <c r="I3" s="20" t="str">
+      <c r="G3" s="16" t="s">
+        <v>187</v>
+      </c>
+      <c r="H3" s="16"/>
+      <c r="I3" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(G1, TestMaster[Test Name], TestMaster[Test Priority], "Priority not found"), "")</f>
         <v>Medium</v>
       </c>
-      <c r="J3" s="34"/>
-      <c r="K3" s="20" t="s">
+      <c r="J3" s="5"/>
+      <c r="K3" t="s">
         <v>5</v>
       </c>
-      <c r="L3" s="21" t="str">
+      <c r="L3" s="9" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(G1, TestMaster[Test Name], TestMaster[Test Status], "Status not found"), "")</f>
         <v>Not Implemented</v>
       </c>
-      <c r="M3" s="17" t="s">
-        <v>188</v>
-      </c>
-      <c r="N3" s="17"/>
-      <c r="O3" s="20" t="str">
+      <c r="M3" s="16" t="s">
+        <v>187</v>
+      </c>
+      <c r="N3" s="16"/>
+      <c r="O3" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(M1, TestMaster[Test Name], TestMaster[Test Priority], "Priority not found"), "")</f>
         <v>Low</v>
       </c>
-      <c r="P3" s="34"/>
-      <c r="Q3" s="20" t="s">
+      <c r="P3" s="5"/>
+      <c r="Q3" t="s">
         <v>5</v>
       </c>
-      <c r="R3" s="20" t="str">
+      <c r="R3" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(M1, TestMaster[Test Name], TestMaster[Test Status], "Status not found"), "")</f>
         <v>Not Implemented</v>
       </c>
     </row>
-    <row r="4" spans="1:18" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="17" t="s">
+    <row r="4" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="16" t="s">
         <v>6</v>
       </c>
-      <c r="B4" s="17"/>
-      <c r="C4" s="17"/>
-      <c r="D4" s="17"/>
-      <c r="E4" s="17"/>
-      <c r="F4" s="24"/>
-      <c r="G4" s="17" t="s">
+      <c r="B4" s="16"/>
+      <c r="C4" s="16"/>
+      <c r="D4" s="16"/>
+      <c r="E4" s="16"/>
+      <c r="F4" s="17"/>
+      <c r="G4" s="16" t="s">
         <v>6</v>
       </c>
-      <c r="H4" s="17"/>
-      <c r="I4" s="17"/>
-      <c r="J4" s="17"/>
-      <c r="K4" s="17"/>
-      <c r="L4" s="17"/>
-      <c r="M4" s="17" t="s">
+      <c r="H4" s="16"/>
+      <c r="I4" s="16"/>
+      <c r="J4" s="16"/>
+      <c r="K4" s="16"/>
+      <c r="L4" s="16"/>
+      <c r="M4" s="16" t="s">
         <v>6</v>
       </c>
-      <c r="N4" s="17"/>
-      <c r="O4" s="17"/>
-      <c r="P4" s="17"/>
-      <c r="Q4" s="17"/>
-      <c r="R4" s="17"/>
-    </row>
-    <row r="5" spans="1:18" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="17"/>
-      <c r="B5" s="17"/>
-      <c r="C5" s="17"/>
-      <c r="D5" s="17"/>
-      <c r="E5" s="17"/>
-      <c r="F5" s="24"/>
-      <c r="G5" s="17"/>
-      <c r="H5" s="17"/>
-      <c r="I5" s="17"/>
-      <c r="J5" s="17"/>
-      <c r="K5" s="17"/>
-      <c r="L5" s="17"/>
-      <c r="M5" s="17"/>
-      <c r="N5" s="17"/>
-      <c r="O5" s="17"/>
-      <c r="P5" s="17"/>
-      <c r="Q5" s="17"/>
-      <c r="R5" s="17"/>
-    </row>
-    <row r="6" spans="1:18" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="17" t="s">
+      <c r="N4" s="16"/>
+      <c r="O4" s="16"/>
+      <c r="P4" s="16"/>
+      <c r="Q4" s="16"/>
+      <c r="R4" s="16"/>
+    </row>
+    <row r="5" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="16"/>
+      <c r="B5" s="16"/>
+      <c r="C5" s="16"/>
+      <c r="D5" s="16"/>
+      <c r="E5" s="16"/>
+      <c r="F5" s="17"/>
+      <c r="G5" s="16"/>
+      <c r="H5" s="16"/>
+      <c r="I5" s="16"/>
+      <c r="J5" s="16"/>
+      <c r="K5" s="16"/>
+      <c r="L5" s="16"/>
+      <c r="M5" s="16"/>
+      <c r="N5" s="16"/>
+      <c r="O5" s="16"/>
+      <c r="P5" s="16"/>
+      <c r="Q5" s="16"/>
+      <c r="R5" s="16"/>
+    </row>
+    <row r="6" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="16" t="s">
         <v>7</v>
       </c>
-      <c r="B6" s="17"/>
-      <c r="C6" s="17"/>
-      <c r="D6" s="17"/>
-      <c r="E6" s="17"/>
-      <c r="F6" s="24"/>
-      <c r="G6" s="17" t="s">
+      <c r="B6" s="16"/>
+      <c r="C6" s="16"/>
+      <c r="D6" s="16"/>
+      <c r="E6" s="16"/>
+      <c r="F6" s="17"/>
+      <c r="G6" s="16" t="s">
         <v>7</v>
       </c>
-      <c r="H6" s="17"/>
-      <c r="I6" s="17"/>
-      <c r="J6" s="17"/>
-      <c r="K6" s="17"/>
-      <c r="L6" s="17"/>
-      <c r="M6" s="17" t="s">
+      <c r="H6" s="16"/>
+      <c r="I6" s="16"/>
+      <c r="J6" s="16"/>
+      <c r="K6" s="16"/>
+      <c r="L6" s="16"/>
+      <c r="M6" s="16" t="s">
         <v>7</v>
       </c>
-      <c r="N6" s="17"/>
-      <c r="O6" s="17"/>
-      <c r="P6" s="17"/>
-      <c r="Q6" s="17"/>
-      <c r="R6" s="17"/>
-    </row>
-    <row r="7" spans="1:18" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="25" t="s">
+      <c r="N6" s="16"/>
+      <c r="O6" s="16"/>
+      <c r="P6" s="16"/>
+      <c r="Q6" s="16"/>
+      <c r="R6" s="16"/>
+    </row>
+    <row r="7" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B7" s="25" t="s">
+      <c r="B7" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C7" s="25" t="s">
+      <c r="C7" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="D7" s="25" t="s">
+      <c r="D7" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="E7" s="25" t="s">
+      <c r="E7" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="F7" s="27" t="s">
+      <c r="F7" s="12" t="s">
         <v>2</v>
       </c>
-      <c r="G7" s="25" t="s">
+      <c r="G7" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="H7" s="36" t="s">
+      <c r="H7" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="I7" s="25" t="s">
+      <c r="I7" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="J7" s="25" t="s">
+      <c r="J7" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="K7" s="25" t="s">
+      <c r="K7" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="L7" s="27" t="s">
+      <c r="L7" s="12" t="s">
         <v>2</v>
       </c>
-      <c r="M7" s="25" t="s">
+      <c r="M7" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="N7" s="36" t="s">
+      <c r="N7" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="O7" s="25" t="s">
+      <c r="O7" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="P7" s="25" t="s">
+      <c r="P7" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="Q7" s="25" t="s">
+      <c r="Q7" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="R7" s="25" t="s">
+      <c r="R7" s="1" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A8" s="34">
+    <row r="8" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A8" s="5">
         <v>1</v>
       </c>
-      <c r="B8" s="31" t="s">
+      <c r="B8" s="4" t="s">
+        <v>190</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="D8" s="4" t="s">
         <v>124</v>
       </c>
-      <c r="C8" s="31" t="s">
+      <c r="G8" s="5">
+        <v>1</v>
+      </c>
+      <c r="H8" s="5" t="s">
+        <v>190</v>
+      </c>
+      <c r="I8" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="D8" s="31" t="s">
+      <c r="J8" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="M8" s="5">
+        <v>1</v>
+      </c>
+      <c r="N8" s="5" t="s">
+        <v>190</v>
+      </c>
+      <c r="O8" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="P8" s="4" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18" ht="45" x14ac:dyDescent="0.25">
+      <c r="A9" s="5">
+        <v>2</v>
+      </c>
+      <c r="B9" s="4" t="s">
         <v>125</v>
       </c>
-      <c r="E8" s="34"/>
-      <c r="G8" s="34">
-        <v>1</v>
-      </c>
-      <c r="H8" s="34" t="s">
-        <v>124</v>
-      </c>
-      <c r="I8" s="31" t="s">
-        <v>27</v>
-      </c>
-      <c r="J8" s="31" t="s">
+      <c r="C9" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="G9" s="5">
+        <v>2</v>
+      </c>
+      <c r="H9" s="5" t="s">
         <v>125</v>
       </c>
-      <c r="K8" s="34"/>
-      <c r="M8" s="34">
-        <v>1</v>
-      </c>
-      <c r="N8" s="34" t="s">
-        <v>124</v>
-      </c>
-      <c r="O8" s="31" t="s">
-        <v>27</v>
-      </c>
-      <c r="P8" s="31" t="s">
+      <c r="I9" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="J9" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="M9" s="5">
+        <v>2</v>
+      </c>
+      <c r="N9" s="5" t="s">
         <v>125</v>
       </c>
-      <c r="Q8" s="34"/>
-      <c r="R8" s="34"/>
-    </row>
-    <row r="9" spans="1:18" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A9" s="34">
-        <v>2</v>
-      </c>
-      <c r="B9" s="31" t="s">
+      <c r="O9" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="P9" s="4" t="s">
         <v>126</v>
       </c>
-      <c r="C9" s="33" t="s">
+    </row>
+    <row r="10" spans="1:18" ht="45" x14ac:dyDescent="0.25">
+      <c r="A10" s="5">
+        <v>3</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>127</v>
+      </c>
+      <c r="C10" s="4" t="s">
         <v>141</v>
       </c>
-      <c r="D9" s="31" t="s">
+      <c r="D10" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="G10" s="5">
+        <v>3</v>
+      </c>
+      <c r="H10" s="5" t="s">
         <v>127</v>
       </c>
-      <c r="E9" s="34"/>
-      <c r="G9" s="34">
-        <v>2</v>
-      </c>
-      <c r="H9" s="34" t="s">
-        <v>126</v>
-      </c>
-      <c r="I9" s="33" t="s">
-        <v>139</v>
-      </c>
-      <c r="J9" s="31" t="s">
-        <v>140</v>
-      </c>
-      <c r="K9" s="34"/>
-      <c r="M9" s="34">
-        <v>2</v>
-      </c>
-      <c r="N9" s="34" t="s">
-        <v>126</v>
-      </c>
-      <c r="O9" s="33" t="s">
+      <c r="I10" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="J10" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="M10" s="5">
+        <v>3</v>
+      </c>
+      <c r="N10" s="5" t="s">
+        <v>127</v>
+      </c>
+      <c r="O10" s="4" t="s">
         <v>141</v>
       </c>
-      <c r="P9" s="31" t="s">
-        <v>127</v>
-      </c>
-      <c r="Q9" s="34"/>
-      <c r="R9" s="34"/>
-    </row>
-    <row r="10" spans="1:18" ht="29" x14ac:dyDescent="0.35">
-      <c r="A10" s="34">
-        <v>3</v>
-      </c>
-      <c r="B10" s="31" t="s">
+      <c r="P10" s="4" t="s">
         <v>128</v>
       </c>
-      <c r="C10" s="31" t="s">
-        <v>142</v>
-      </c>
-      <c r="D10" s="31" t="s">
+    </row>
+    <row r="11" spans="1:18" ht="45" x14ac:dyDescent="0.25">
+      <c r="A11" s="5">
+        <v>4</v>
+      </c>
+      <c r="B11" s="4" t="s">
         <v>129</v>
       </c>
-      <c r="E10" s="34"/>
-      <c r="G10" s="34">
-        <v>3</v>
-      </c>
-      <c r="H10" s="34" t="s">
-        <v>128</v>
-      </c>
-      <c r="I10" s="31" t="s">
+      <c r="C11" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="D11" s="4" t="s">
+        <v>131</v>
+      </c>
+      <c r="G11" s="5">
+        <v>4</v>
+      </c>
+      <c r="H11" s="5" t="s">
+        <v>189</v>
+      </c>
+      <c r="I11" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="J11" s="4" t="s">
         <v>143</v>
       </c>
-      <c r="J10" s="31" t="s">
+      <c r="M11" s="5">
+        <v>4</v>
+      </c>
+      <c r="N11" s="5" t="s">
         <v>129</v>
       </c>
-      <c r="K10" s="34"/>
-      <c r="M10" s="34">
-        <v>3</v>
-      </c>
-      <c r="N10" s="34" t="s">
-        <v>128</v>
-      </c>
-      <c r="O10" s="31" t="s">
-        <v>142</v>
-      </c>
-      <c r="P10" s="31" t="s">
-        <v>129</v>
-      </c>
-      <c r="Q10" s="34"/>
-      <c r="R10" s="34"/>
-    </row>
-    <row r="11" spans="1:18" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A11" s="34">
-        <v>4</v>
-      </c>
-      <c r="B11" s="31" t="s">
-        <v>130</v>
-      </c>
-      <c r="C11" s="31" t="s">
+      <c r="O11" s="4" t="s">
+        <v>150</v>
+      </c>
+      <c r="P11" s="4" t="s">
         <v>131</v>
       </c>
-      <c r="D11" s="31" t="s">
+    </row>
+    <row r="12" spans="1:18" ht="45" x14ac:dyDescent="0.25">
+      <c r="A12" s="5">
+        <v>5</v>
+      </c>
+      <c r="B12" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>134</v>
+      </c>
+      <c r="D12" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="M12" s="5">
+        <v>5</v>
+      </c>
+      <c r="N12" s="5" t="s">
+        <v>144</v>
+      </c>
+      <c r="O12" s="4" t="s">
+        <v>145</v>
+      </c>
+      <c r="P12" s="4" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="13" spans="1:18" ht="45" x14ac:dyDescent="0.25">
+      <c r="A13" s="5">
+        <v>6</v>
+      </c>
+      <c r="B13" s="4" t="s">
+        <v>135</v>
+      </c>
+      <c r="C13" s="4" t="s">
         <v>132</v>
       </c>
-      <c r="E11" s="34"/>
-      <c r="G11" s="34">
-        <v>4</v>
-      </c>
-      <c r="H11" s="34" t="s">
-        <v>130</v>
-      </c>
-      <c r="I11" s="31" t="s">
-        <v>131</v>
-      </c>
-      <c r="J11" s="31" t="s">
-        <v>144</v>
-      </c>
-      <c r="K11" s="34"/>
-      <c r="M11" s="34">
-        <v>4</v>
-      </c>
-      <c r="N11" s="34" t="s">
-        <v>130</v>
-      </c>
-      <c r="O11" s="31" t="s">
+      <c r="D13" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="M13" s="5">
+        <v>6</v>
+      </c>
+      <c r="N13" s="5" t="s">
+        <v>146</v>
+      </c>
+      <c r="O13" s="4" t="s">
+        <v>145</v>
+      </c>
+      <c r="P13" s="4" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="M14">
+        <v>7</v>
+      </c>
+      <c r="N14" t="s">
+        <v>107</v>
+      </c>
+      <c r="O14" t="s">
+        <v>111</v>
+      </c>
+      <c r="P14" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="15" spans="1:18" ht="45" x14ac:dyDescent="0.25">
+      <c r="M15" s="5">
+        <v>8</v>
+      </c>
+      <c r="N15" s="5" t="s">
         <v>151</v>
       </c>
-      <c r="P11" s="31" t="s">
-        <v>132</v>
-      </c>
-      <c r="Q11" s="34"/>
-      <c r="R11" s="34"/>
-    </row>
-    <row r="12" spans="1:18" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A12" s="34">
-        <v>5</v>
-      </c>
-      <c r="B12" s="31" t="s">
-        <v>134</v>
-      </c>
-      <c r="C12" s="31" t="s">
-        <v>135</v>
-      </c>
-      <c r="D12" s="31" t="s">
-        <v>137</v>
-      </c>
-      <c r="E12" s="34"/>
-      <c r="G12" s="34"/>
-      <c r="H12" s="34"/>
-      <c r="I12" s="34"/>
-      <c r="J12" s="34"/>
-      <c r="K12" s="34"/>
-      <c r="M12" s="34">
-        <v>5</v>
-      </c>
-      <c r="N12" s="34" t="s">
+      <c r="O15" s="5" t="s">
         <v>145</v>
       </c>
-      <c r="O12" s="31" t="s">
-        <v>146</v>
-      </c>
-      <c r="P12" s="31" t="s">
+      <c r="P15" s="4" t="s">
         <v>148</v>
       </c>
-      <c r="Q12" s="34"/>
-      <c r="R12" s="34"/>
-    </row>
-    <row r="13" spans="1:18" ht="29" x14ac:dyDescent="0.35">
-      <c r="A13" s="34">
-        <v>6</v>
-      </c>
-      <c r="B13" s="31" t="s">
-        <v>136</v>
-      </c>
-      <c r="C13" s="31" t="s">
-        <v>133</v>
-      </c>
-      <c r="D13" s="31" t="s">
-        <v>138</v>
-      </c>
-      <c r="E13" s="34"/>
-      <c r="G13" s="34"/>
-      <c r="H13" s="34"/>
-      <c r="I13" s="34"/>
-      <c r="J13" s="34"/>
-      <c r="K13" s="34"/>
-      <c r="M13" s="34">
-        <v>6</v>
-      </c>
-      <c r="N13" s="34" t="s">
-        <v>147</v>
-      </c>
-      <c r="O13" s="31" t="s">
-        <v>146</v>
-      </c>
-      <c r="P13" s="31" t="s">
-        <v>149</v>
-      </c>
-      <c r="Q13" s="34"/>
-      <c r="R13" s="34"/>
-    </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="M14" s="32">
-        <v>7</v>
-      </c>
-      <c r="N14" s="20" t="s">
+    </row>
+    <row r="16" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="M16">
+        <v>9</v>
+      </c>
+      <c r="N16" t="s">
         <v>107</v>
       </c>
-      <c r="O14" s="32" t="s">
-        <v>111</v>
-      </c>
-      <c r="P14" s="32" t="s">
-        <v>150</v>
-      </c>
-      <c r="Q14" s="34"/>
-      <c r="R14" s="34"/>
-    </row>
-    <row r="15" spans="1:18" ht="29" x14ac:dyDescent="0.35">
-      <c r="M15" s="34">
-        <v>8</v>
-      </c>
-      <c r="N15" s="34" t="s">
+      <c r="O16" t="s">
+        <v>123</v>
+      </c>
+      <c r="P16" t="s">
         <v>152</v>
       </c>
-      <c r="O15" s="34" t="s">
-        <v>146</v>
-      </c>
-      <c r="P15" s="31" t="s">
-        <v>149</v>
-      </c>
-      <c r="Q15" s="34"/>
-      <c r="R15" s="34"/>
-    </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="M16" s="32">
-        <v>9</v>
-      </c>
-      <c r="N16" s="20" t="s">
+    </row>
+    <row r="17" spans="13:16" ht="45" x14ac:dyDescent="0.25">
+      <c r="M17">
+        <v>10</v>
+      </c>
+      <c r="N17" s="5" t="s">
+        <v>153</v>
+      </c>
+      <c r="O17" s="5" t="s">
+        <v>145</v>
+      </c>
+      <c r="P17" s="4" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="18" spans="13:16" x14ac:dyDescent="0.25">
+      <c r="M18" s="5">
+        <v>11</v>
+      </c>
+      <c r="N18" t="s">
         <v>107</v>
       </c>
-      <c r="O16" s="32" t="s">
-        <v>123</v>
-      </c>
-      <c r="P16" s="32" t="s">
-        <v>153</v>
-      </c>
-      <c r="Q16" s="34"/>
-      <c r="R16" s="34"/>
-    </row>
-    <row r="17" spans="13:18" ht="29" x14ac:dyDescent="0.35">
-      <c r="M17" s="32">
-        <v>10</v>
-      </c>
-      <c r="N17" s="34" t="s">
-        <v>154</v>
-      </c>
-      <c r="O17" s="34" t="s">
-        <v>146</v>
-      </c>
-      <c r="P17" s="31" t="s">
-        <v>149</v>
-      </c>
-      <c r="Q17" s="34"/>
-      <c r="R17" s="34"/>
-    </row>
-    <row r="18" spans="13:18" x14ac:dyDescent="0.35">
-      <c r="M18" s="34">
-        <v>11</v>
-      </c>
-      <c r="N18" s="20" t="s">
+      <c r="O18" t="s">
+        <v>109</v>
+      </c>
+      <c r="P18" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="19" spans="13:16" x14ac:dyDescent="0.25">
+      <c r="M19">
+        <v>12</v>
+      </c>
+      <c r="N19" t="s">
+        <v>112</v>
+      </c>
+      <c r="O19" t="s">
+        <v>145</v>
+      </c>
+      <c r="P19" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="20" spans="13:16" x14ac:dyDescent="0.25">
+      <c r="M20" s="5">
+        <v>13</v>
+      </c>
+      <c r="N20" t="s">
         <v>107</v>
       </c>
-      <c r="O18" s="32" t="s">
+      <c r="O20" t="s">
         <v>109</v>
       </c>
-      <c r="P18" s="32" t="s">
+      <c r="P20" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="21" spans="13:16" x14ac:dyDescent="0.25">
+      <c r="M21">
+        <v>14</v>
+      </c>
+      <c r="N21" t="s">
+        <v>113</v>
+      </c>
+      <c r="O21" t="s">
+        <v>114</v>
+      </c>
+      <c r="P21" t="s">
         <v>157</v>
       </c>
-      <c r="Q18" s="34"/>
-      <c r="R18" s="34"/>
-    </row>
-    <row r="19" spans="13:18" x14ac:dyDescent="0.35">
-      <c r="M19" s="32">
-        <v>12</v>
-      </c>
-      <c r="N19" s="20" t="s">
-        <v>112</v>
-      </c>
-      <c r="O19" s="32" t="s">
-        <v>146</v>
-      </c>
-      <c r="P19" s="32" t="s">
-        <v>110</v>
-      </c>
-      <c r="Q19" s="34"/>
-      <c r="R19" s="34"/>
-    </row>
-    <row r="20" spans="13:18" x14ac:dyDescent="0.35">
-      <c r="M20" s="34">
-        <v>13</v>
-      </c>
-      <c r="N20" s="20" t="s">
-        <v>107</v>
-      </c>
-      <c r="O20" s="32" t="s">
-        <v>109</v>
-      </c>
-      <c r="P20" s="32" t="s">
-        <v>157</v>
-      </c>
-      <c r="Q20" s="34"/>
-      <c r="R20" s="34"/>
-    </row>
-    <row r="21" spans="13:18" x14ac:dyDescent="0.35">
-      <c r="M21" s="32">
-        <v>14</v>
-      </c>
-      <c r="N21" s="20" t="s">
-        <v>113</v>
-      </c>
-      <c r="O21" s="32" t="s">
-        <v>114</v>
-      </c>
-      <c r="P21" s="32" t="s">
-        <v>158</v>
-      </c>
-      <c r="Q21" s="34"/>
-      <c r="R21" s="34"/>
     </row>
   </sheetData>
   <mergeCells count="15">
+    <mergeCell ref="A4:F5"/>
+    <mergeCell ref="A6:F6"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A3:B3"/>
+    <mergeCell ref="A2:B2"/>
     <mergeCell ref="M1:R1"/>
     <mergeCell ref="M2:N2"/>
     <mergeCell ref="M3:N3"/>
@@ -3802,11 +3730,6 @@
     <mergeCell ref="G2:H2"/>
     <mergeCell ref="G3:H3"/>
     <mergeCell ref="G1:L1"/>
-    <mergeCell ref="A4:F5"/>
-    <mergeCell ref="A6:F6"/>
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A3:B3"/>
-    <mergeCell ref="A2:B2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3815,697 +3738,649 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{31B60B4E-CDD0-4CEE-BA63-4F898D2F5023}">
   <dimension ref="A1:R25"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5" customWidth="1"/>
-    <col min="2" max="2" width="22.1796875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.54296875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="31.1796875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="18.36328125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="16.1796875" style="23" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="22.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.5703125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="31.140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="18.42578125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="16.140625" style="9" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="5" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="30.36328125" customWidth="1"/>
-    <col min="9" max="9" width="27.54296875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="30.26953125" customWidth="1"/>
-    <col min="11" max="11" width="18.36328125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="16.1796875" style="23" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="30.42578125" customWidth="1"/>
+    <col min="9" max="9" width="27.5703125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="30.28515625" customWidth="1"/>
+    <col min="11" max="11" width="18.42578125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="16.140625" style="9" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="5" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="35.453125" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="20.54296875" customWidth="1"/>
-    <col min="16" max="16" width="31.1796875" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="18.36328125" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="16.1796875" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="35.42578125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="20.5703125" customWidth="1"/>
+    <col min="16" max="16" width="31.140625" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="18.42578125" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="16.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A1" s="17" t="s">
+    <row r="1" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A1" s="16" t="s">
         <v>16</v>
       </c>
-      <c r="B1" s="17"/>
-      <c r="C1" s="17"/>
-      <c r="D1" s="17"/>
-      <c r="E1" s="17"/>
-      <c r="F1" s="24"/>
-      <c r="G1" s="16" t="s">
+      <c r="B1" s="16"/>
+      <c r="C1" s="16"/>
+      <c r="D1" s="16"/>
+      <c r="E1" s="16"/>
+      <c r="F1" s="17"/>
+      <c r="G1" s="18" t="s">
         <v>17</v>
       </c>
-      <c r="H1" s="17"/>
-      <c r="I1" s="17"/>
-      <c r="J1" s="17"/>
-      <c r="K1" s="17"/>
-      <c r="L1" s="24"/>
-      <c r="M1" s="17" t="s">
+      <c r="H1" s="16"/>
+      <c r="I1" s="16"/>
+      <c r="J1" s="16"/>
+      <c r="K1" s="16"/>
+      <c r="L1" s="17"/>
+      <c r="M1" s="16" t="s">
         <v>116</v>
       </c>
-      <c r="N1" s="17"/>
-      <c r="O1" s="17"/>
-      <c r="P1" s="17"/>
-      <c r="Q1" s="17"/>
-      <c r="R1" s="17"/>
-    </row>
-    <row r="2" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A2" s="17" t="s">
+      <c r="N1" s="16"/>
+      <c r="O1" s="16"/>
+      <c r="P1" s="16"/>
+      <c r="Q1" s="16"/>
+      <c r="R1" s="16"/>
+    </row>
+    <row r="2" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A2" s="16" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="17"/>
-      <c r="C2" s="18">
+      <c r="B2" s="16"/>
+      <c r="C2" s="8">
         <f>IFERROR(_xlfn.XLOOKUP(A1, TestMaster[Test Name], TestMaster[Test ID], "ID not found"), "")</f>
         <v>5</v>
       </c>
-      <c r="D2" s="32"/>
-      <c r="E2" s="20" t="s">
+      <c r="E2" t="s">
         <v>4</v>
       </c>
-      <c r="F2" s="21"/>
-      <c r="G2" s="17" t="s">
+      <c r="G2" s="16" t="s">
         <v>3</v>
       </c>
-      <c r="H2" s="17"/>
-      <c r="I2" s="18">
+      <c r="H2" s="16"/>
+      <c r="I2" s="8">
         <f>IFERROR(_xlfn.XLOOKUP(G1, TestMaster[Test Name], TestMaster[Test ID], "ID not found"), "")</f>
         <v>6</v>
       </c>
-      <c r="J2" s="32"/>
-      <c r="K2" s="20" t="s">
+      <c r="K2" t="s">
         <v>4</v>
       </c>
-      <c r="L2" s="21"/>
-      <c r="M2" s="17" t="s">
+      <c r="M2" s="16" t="s">
         <v>3</v>
       </c>
-      <c r="N2" s="17"/>
-      <c r="O2" s="37">
+      <c r="N2" s="16"/>
+      <c r="O2" s="14">
         <f>IFERROR(_xlfn.XLOOKUP(M1, TestMaster[Test Name], TestMaster[Test ID], "ID not found"), "")</f>
         <v>7</v>
       </c>
-      <c r="P2" s="32"/>
-      <c r="Q2" s="20" t="s">
+      <c r="Q2" t="s">
         <v>4</v>
       </c>
-      <c r="R2" s="20"/>
-    </row>
-    <row r="3" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A3" s="17" t="s">
-        <v>188</v>
-      </c>
-      <c r="B3" s="17"/>
-      <c r="C3" s="18" t="str">
+    </row>
+    <row r="3" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A3" s="16" t="s">
+        <v>187</v>
+      </c>
+      <c r="B3" s="16"/>
+      <c r="C3" s="8" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(A1, TestMaster[Test Name], TestMaster[Test Priority], "Priority not found"), "")</f>
         <v>Medium</v>
       </c>
-      <c r="D3" s="32"/>
-      <c r="E3" s="20" t="s">
+      <c r="E3" t="s">
         <v>5</v>
       </c>
-      <c r="F3" s="21" t="str">
+      <c r="F3" s="9" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(A1, TestMaster[Test Name], TestMaster[Test Status], "Status not found"), "")</f>
         <v>Not Implemented</v>
       </c>
-      <c r="G3" s="17" t="s">
-        <v>188</v>
-      </c>
-      <c r="H3" s="17"/>
-      <c r="I3" s="18" t="str">
+      <c r="G3" s="16" t="s">
+        <v>187</v>
+      </c>
+      <c r="H3" s="16"/>
+      <c r="I3" s="8" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(G1, TestMaster[Test Name], TestMaster[Test Priority], "Priority not found"), "")</f>
         <v>Medium</v>
       </c>
-      <c r="J3" s="32"/>
-      <c r="K3" s="20" t="s">
+      <c r="K3" t="s">
         <v>5</v>
       </c>
-      <c r="L3" s="21" t="str">
+      <c r="L3" s="9" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(G1, TestMaster[Test Name], TestMaster[Test Status], "Status not found"), "")</f>
         <v>Not Implemented</v>
       </c>
-      <c r="M3" s="17" t="s">
-        <v>188</v>
-      </c>
-      <c r="N3" s="17"/>
-      <c r="O3" s="37" t="str">
+      <c r="M3" s="16" t="s">
+        <v>187</v>
+      </c>
+      <c r="N3" s="16"/>
+      <c r="O3" s="14" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(M1, TestMaster[Test Name], TestMaster[Test Priority], "Priority not found"), "")</f>
         <v>Low</v>
       </c>
-      <c r="P3" s="32"/>
-      <c r="Q3" s="20" t="s">
+      <c r="Q3" t="s">
         <v>5</v>
       </c>
-      <c r="R3" s="20" t="str">
+      <c r="R3" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(M1, TestMaster[Test Name], TestMaster[Test Status], "Status not found"), "")</f>
         <v>Not Implemented</v>
       </c>
     </row>
-    <row r="4" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A4" s="17" t="s">
+    <row r="4" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A4" s="16" t="s">
         <v>6</v>
       </c>
-      <c r="B4" s="17"/>
-      <c r="C4" s="17"/>
-      <c r="D4" s="17"/>
-      <c r="E4" s="17"/>
-      <c r="F4" s="24"/>
-      <c r="G4" s="16" t="s">
+      <c r="B4" s="16"/>
+      <c r="C4" s="16"/>
+      <c r="D4" s="16"/>
+      <c r="E4" s="16"/>
+      <c r="F4" s="17"/>
+      <c r="G4" s="18" t="s">
         <v>6</v>
       </c>
-      <c r="H4" s="17"/>
-      <c r="I4" s="17"/>
-      <c r="J4" s="17"/>
-      <c r="K4" s="17"/>
-      <c r="L4" s="24"/>
-      <c r="M4" s="17" t="s">
+      <c r="H4" s="16"/>
+      <c r="I4" s="16"/>
+      <c r="J4" s="16"/>
+      <c r="K4" s="16"/>
+      <c r="L4" s="17"/>
+      <c r="M4" s="16" t="s">
         <v>6</v>
       </c>
-      <c r="N4" s="17"/>
-      <c r="O4" s="17"/>
-      <c r="P4" s="17"/>
-      <c r="Q4" s="17"/>
-      <c r="R4" s="17"/>
-    </row>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A5" s="17"/>
-      <c r="B5" s="17"/>
-      <c r="C5" s="17"/>
-      <c r="D5" s="17"/>
-      <c r="E5" s="17"/>
-      <c r="F5" s="24"/>
-      <c r="G5" s="16"/>
-      <c r="H5" s="17"/>
-      <c r="I5" s="17"/>
-      <c r="J5" s="17"/>
-      <c r="K5" s="17"/>
-      <c r="L5" s="24"/>
-      <c r="M5" s="17"/>
-      <c r="N5" s="17"/>
-      <c r="O5" s="17"/>
-      <c r="P5" s="17"/>
-      <c r="Q5" s="17"/>
-      <c r="R5" s="17"/>
-    </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A6" s="17" t="s">
+      <c r="N4" s="16"/>
+      <c r="O4" s="16"/>
+      <c r="P4" s="16"/>
+      <c r="Q4" s="16"/>
+      <c r="R4" s="16"/>
+    </row>
+    <row r="5" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A5" s="16"/>
+      <c r="B5" s="16"/>
+      <c r="C5" s="16"/>
+      <c r="D5" s="16"/>
+      <c r="E5" s="16"/>
+      <c r="F5" s="17"/>
+      <c r="G5" s="18"/>
+      <c r="H5" s="16"/>
+      <c r="I5" s="16"/>
+      <c r="J5" s="16"/>
+      <c r="K5" s="16"/>
+      <c r="L5" s="17"/>
+      <c r="M5" s="16"/>
+      <c r="N5" s="16"/>
+      <c r="O5" s="16"/>
+      <c r="P5" s="16"/>
+      <c r="Q5" s="16"/>
+      <c r="R5" s="16"/>
+    </row>
+    <row r="6" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A6" s="16" t="s">
         <v>7</v>
       </c>
-      <c r="B6" s="17"/>
-      <c r="C6" s="17"/>
-      <c r="D6" s="17"/>
-      <c r="E6" s="17"/>
-      <c r="F6" s="24"/>
-      <c r="G6" s="16" t="s">
+      <c r="B6" s="16"/>
+      <c r="C6" s="16"/>
+      <c r="D6" s="16"/>
+      <c r="E6" s="16"/>
+      <c r="F6" s="17"/>
+      <c r="G6" s="18" t="s">
         <v>7</v>
       </c>
-      <c r="H6" s="17"/>
-      <c r="I6" s="17"/>
-      <c r="J6" s="17"/>
-      <c r="K6" s="17"/>
-      <c r="L6" s="24"/>
-      <c r="M6" s="17" t="s">
+      <c r="H6" s="16"/>
+      <c r="I6" s="16"/>
+      <c r="J6" s="16"/>
+      <c r="K6" s="16"/>
+      <c r="L6" s="17"/>
+      <c r="M6" s="16" t="s">
         <v>7</v>
       </c>
-      <c r="N6" s="17"/>
-      <c r="O6" s="17"/>
-      <c r="P6" s="17"/>
-      <c r="Q6" s="17"/>
-      <c r="R6" s="17"/>
-    </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A7" s="25" t="s">
+      <c r="N6" s="16"/>
+      <c r="O6" s="16"/>
+      <c r="P6" s="16"/>
+      <c r="Q6" s="16"/>
+      <c r="R6" s="16"/>
+    </row>
+    <row r="7" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A7" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B7" s="25" t="s">
+      <c r="B7" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C7" s="25" t="s">
+      <c r="C7" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="D7" s="25" t="s">
+      <c r="D7" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="E7" s="25" t="s">
+      <c r="E7" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="F7" s="27" t="s">
+      <c r="F7" s="12" t="s">
         <v>2</v>
       </c>
-      <c r="G7" s="25" t="s">
+      <c r="G7" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="H7" s="25" t="s">
+      <c r="H7" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="I7" s="25" t="s">
+      <c r="I7" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="J7" s="25" t="s">
+      <c r="J7" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="K7" s="25" t="s">
+      <c r="K7" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="L7" s="27" t="s">
+      <c r="L7" s="12" t="s">
         <v>2</v>
       </c>
-      <c r="M7" s="25" t="s">
+      <c r="M7" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="N7" s="25" t="s">
+      <c r="N7" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="O7" s="25" t="s">
+      <c r="O7" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="P7" s="25" t="s">
+      <c r="P7" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="Q7" s="25" t="s">
+      <c r="Q7" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="R7" s="25" t="s">
+      <c r="R7" s="1" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="8" spans="1:18" s="4" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="34">
+    <row r="8" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A8" s="5">
         <v>1</v>
       </c>
-      <c r="B8" s="34" t="s">
+      <c r="B8" s="5" t="s">
         <v>88</v>
       </c>
-      <c r="C8" s="34" t="s">
+      <c r="C8" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="D8" s="34" t="s">
+      <c r="D8" s="5" t="s">
         <v>74</v>
       </c>
-      <c r="E8" s="20"/>
-      <c r="F8" s="21"/>
-      <c r="G8" s="20">
+      <c r="G8">
         <v>1</v>
       </c>
-      <c r="H8" s="34" t="s">
+      <c r="H8" s="5" t="s">
         <v>88</v>
       </c>
-      <c r="I8" s="34" t="s">
+      <c r="I8" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="J8" s="34" t="s">
+      <c r="J8" s="5" t="s">
         <v>77</v>
       </c>
-      <c r="K8" s="20"/>
-      <c r="L8" s="21"/>
-      <c r="M8" s="20">
+      <c r="M8">
         <v>1</v>
       </c>
-      <c r="N8" s="34" t="s">
+      <c r="N8" s="5" t="s">
         <v>88</v>
       </c>
-      <c r="O8" s="34" t="s">
+      <c r="O8" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="P8" s="34" t="s">
+      <c r="P8" s="5" t="s">
         <v>77</v>
       </c>
-      <c r="Q8" s="20"/>
-      <c r="R8" s="20"/>
-    </row>
-    <row r="9" spans="1:18" s="4" customFormat="1" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A9" s="34">
+    </row>
+    <row r="9" spans="1:18" ht="45" x14ac:dyDescent="0.25">
+      <c r="A9" s="5">
         <v>2</v>
       </c>
-      <c r="B9" s="34" t="s">
+      <c r="B9" s="5" t="s">
         <v>56</v>
       </c>
-      <c r="C9" s="34" t="s">
+      <c r="C9" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="D9" s="34" t="s">
+      <c r="D9" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="E9" s="20"/>
-      <c r="F9" s="21"/>
-      <c r="G9" s="20">
+      <c r="G9">
         <v>2</v>
       </c>
-      <c r="H9" s="31" t="s">
+      <c r="H9" s="4" t="s">
         <v>75</v>
       </c>
-      <c r="I9" s="31" t="s">
+      <c r="I9" s="4" t="s">
         <v>78</v>
       </c>
-      <c r="J9" s="31" t="s">
+      <c r="J9" s="4" t="s">
         <v>80</v>
       </c>
-      <c r="K9" s="20"/>
-      <c r="L9" s="21"/>
-      <c r="M9" s="20">
+      <c r="M9">
         <v>2</v>
       </c>
-      <c r="N9" s="31" t="s">
+      <c r="N9" s="4" t="s">
         <v>75</v>
       </c>
-      <c r="O9" s="31" t="s">
+      <c r="O9" s="4" t="s">
         <v>78</v>
       </c>
-      <c r="P9" s="31" t="s">
+      <c r="P9" s="4" t="s">
         <v>80</v>
       </c>
-      <c r="Q9" s="20"/>
-      <c r="R9" s="20"/>
-    </row>
-    <row r="10" spans="1:18" ht="29" x14ac:dyDescent="0.35">
-      <c r="G10" s="32">
+    </row>
+    <row r="10" spans="1:18" ht="45" x14ac:dyDescent="0.25">
+      <c r="G10">
         <v>3</v>
       </c>
-      <c r="H10" s="31" t="s">
+      <c r="H10" s="4" t="s">
         <v>117</v>
       </c>
-      <c r="I10" s="31" t="s">
+      <c r="I10" s="4" t="s">
         <v>100</v>
       </c>
-      <c r="J10" s="31" t="s">
+      <c r="J10" s="4" t="s">
         <v>105</v>
       </c>
-      <c r="K10" s="32"/>
-      <c r="M10" s="32">
+      <c r="M10">
         <v>3</v>
       </c>
-      <c r="N10" s="31" t="s">
+      <c r="N10" s="4" t="s">
         <v>120</v>
       </c>
-      <c r="O10" s="31" t="s">
+      <c r="O10" s="4" t="s">
         <v>100</v>
       </c>
-      <c r="P10" s="31" t="s">
+      <c r="P10" s="4" t="s">
         <v>105</v>
       </c>
-      <c r="Q10" s="32"/>
-      <c r="R10" s="32"/>
-    </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="G11" s="32">
+    </row>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="G11">
         <v>4</v>
       </c>
-      <c r="H11" s="32" t="s">
+      <c r="H11" t="s">
         <v>89</v>
       </c>
-      <c r="I11" s="32" t="s">
+      <c r="I11" t="s">
         <v>92</v>
       </c>
-      <c r="J11" s="32" t="s">
+      <c r="J11" t="s">
         <v>91</v>
       </c>
-      <c r="K11" s="32"/>
-      <c r="M11" s="32">
+      <c r="M11">
         <v>4</v>
       </c>
-      <c r="N11" s="32" t="s">
+      <c r="N11" t="s">
         <v>121</v>
       </c>
-      <c r="O11" s="32" t="s">
+      <c r="O11" t="s">
         <v>90</v>
       </c>
-      <c r="P11" s="32" t="s">
+      <c r="P11" t="s">
         <v>91</v>
       </c>
-      <c r="Q11" s="32"/>
-      <c r="R11" s="32"/>
-    </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="G12" s="32">
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="G12">
         <v>5</v>
       </c>
-      <c r="H12" s="32" t="s">
+      <c r="H12" t="s">
         <v>94</v>
       </c>
-      <c r="I12" s="32" t="s">
+      <c r="I12" t="s">
         <v>96</v>
       </c>
-      <c r="J12" s="32" t="s">
+      <c r="J12" t="s">
         <v>98</v>
       </c>
-      <c r="K12" s="32"/>
-      <c r="M12" s="32">
+      <c r="M12">
         <v>5</v>
       </c>
-      <c r="N12" s="32" t="s">
+      <c r="N12" t="s">
         <v>118</v>
       </c>
-      <c r="O12" s="32" t="s">
+      <c r="O12" t="s">
         <v>96</v>
       </c>
-      <c r="P12" s="32" t="s">
+      <c r="P12" t="s">
         <v>93</v>
       </c>
-      <c r="Q12" s="32"/>
-      <c r="R12" s="32"/>
-    </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="G13" s="32">
+    </row>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="G13">
         <v>6</v>
       </c>
-      <c r="H13" s="32" t="s">
+      <c r="H13" t="s">
         <v>95</v>
       </c>
-      <c r="I13" s="32" t="s">
+      <c r="I13" t="s">
         <v>97</v>
       </c>
-      <c r="J13" s="32" t="s">
+      <c r="J13" t="s">
         <v>99</v>
       </c>
-      <c r="K13" s="32"/>
-      <c r="M13" s="32">
+      <c r="M13">
         <v>6</v>
       </c>
-      <c r="N13" s="32" t="s">
+      <c r="N13" t="s">
         <v>107</v>
       </c>
-      <c r="O13" s="32" t="s">
+      <c r="O13" t="s">
         <v>111</v>
       </c>
-      <c r="P13" s="32" t="s">
-        <v>156</v>
-      </c>
-      <c r="Q13" s="32"/>
-      <c r="R13" s="32"/>
-    </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="G14" s="32">
+      <c r="P13" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="G14">
         <v>7</v>
       </c>
-      <c r="H14" s="32" t="s">
+      <c r="H14" t="s">
         <v>101</v>
       </c>
-      <c r="I14" s="32"/>
-      <c r="J14" s="32"/>
-      <c r="K14" s="32"/>
-      <c r="M14" s="32">
+      <c r="M14">
         <v>8</v>
       </c>
-      <c r="N14" s="32" t="s">
+      <c r="N14" t="s">
         <v>119</v>
       </c>
-      <c r="O14" s="32" t="s">
+      <c r="O14" t="s">
         <v>90</v>
       </c>
-      <c r="P14" s="32" t="s">
+      <c r="P14" t="s">
         <v>91</v>
       </c>
-      <c r="Q14" s="32"/>
-      <c r="R14" s="32"/>
-    </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="G15" s="32">
+    </row>
+    <row r="15" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="G15">
         <v>8</v>
       </c>
-      <c r="H15" s="32" t="s">
+      <c r="H15" t="s">
         <v>89</v>
       </c>
-      <c r="I15" s="32" t="s">
+      <c r="I15" t="s">
         <v>92</v>
       </c>
-      <c r="J15" s="32" t="s">
+      <c r="J15" t="s">
         <v>91</v>
       </c>
-      <c r="K15" s="32"/>
-      <c r="M15" s="32">
+      <c r="M15">
         <v>9</v>
       </c>
-      <c r="N15" s="32" t="s">
+      <c r="N15" t="s">
         <v>122</v>
       </c>
-      <c r="O15" s="32" t="s">
+      <c r="O15" t="s">
         <v>96</v>
       </c>
-      <c r="P15" s="32" t="s">
+      <c r="P15" t="s">
         <v>93</v>
       </c>
-      <c r="Q15" s="32"/>
-      <c r="R15" s="32"/>
-    </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="G16" s="32">
+    </row>
+    <row r="16" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="G16">
         <v>9</v>
       </c>
-      <c r="H16" s="32" t="s">
+      <c r="H16" t="s">
         <v>94</v>
       </c>
-      <c r="I16" s="32" t="s">
+      <c r="I16" t="s">
         <v>96</v>
       </c>
-      <c r="J16" s="32" t="s">
+      <c r="J16" t="s">
         <v>98</v>
       </c>
-      <c r="K16" s="32"/>
-      <c r="M16" s="32">
+      <c r="M16">
         <v>10</v>
       </c>
-      <c r="N16" s="32" t="s">
+      <c r="N16" t="s">
         <v>107</v>
       </c>
-      <c r="O16" s="32" t="s">
+      <c r="O16" t="s">
         <v>123</v>
       </c>
-      <c r="P16" s="32" t="s">
-        <v>155</v>
-      </c>
-      <c r="Q16" s="32"/>
-      <c r="R16" s="32"/>
-    </row>
-    <row r="17" spans="7:11" x14ac:dyDescent="0.35">
-      <c r="G17" s="32">
+      <c r="P16" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="17" spans="7:10" x14ac:dyDescent="0.25">
+      <c r="G17">
         <v>10</v>
       </c>
-      <c r="H17" s="32" t="s">
+      <c r="H17" t="s">
         <v>95</v>
       </c>
-      <c r="I17" s="32" t="s">
+      <c r="I17" t="s">
         <v>97</v>
       </c>
-      <c r="J17" s="32" t="s">
+      <c r="J17" t="s">
         <v>99</v>
       </c>
-      <c r="K17" s="32"/>
-    </row>
-    <row r="18" spans="7:11" x14ac:dyDescent="0.35">
-      <c r="G18" s="32">
+    </row>
+    <row r="18" spans="7:10" x14ac:dyDescent="0.25">
+      <c r="G18">
         <v>11</v>
       </c>
-      <c r="H18" s="32" t="s">
+      <c r="H18" t="s">
         <v>102</v>
       </c>
-      <c r="I18" s="32" t="s">
+      <c r="I18" t="s">
         <v>103</v>
       </c>
-      <c r="J18" s="32" t="s">
+      <c r="J18" t="s">
         <v>104</v>
       </c>
-      <c r="K18" s="32"/>
-    </row>
-    <row r="19" spans="7:11" x14ac:dyDescent="0.35">
-      <c r="G19" s="32">
+    </row>
+    <row r="19" spans="7:10" x14ac:dyDescent="0.25">
+      <c r="G19">
         <v>12</v>
       </c>
-      <c r="H19" s="32" t="s">
+      <c r="H19" t="s">
         <v>89</v>
       </c>
-      <c r="I19" s="32" t="s">
+      <c r="I19" t="s">
         <v>90</v>
       </c>
-      <c r="J19" s="32" t="s">
+      <c r="J19" t="s">
         <v>91</v>
       </c>
-      <c r="K19" s="32"/>
-    </row>
-    <row r="20" spans="7:11" x14ac:dyDescent="0.35">
-      <c r="G20" s="32">
+    </row>
+    <row r="20" spans="7:10" x14ac:dyDescent="0.25">
+      <c r="G20">
         <v>13</v>
       </c>
-      <c r="H20" s="32" t="s">
+      <c r="H20" t="s">
         <v>106</v>
       </c>
-      <c r="I20" s="32" t="s">
+      <c r="I20" t="s">
         <v>96</v>
       </c>
-      <c r="J20" s="32" t="s">
+      <c r="J20" t="s">
         <v>93</v>
       </c>
-      <c r="K20" s="32"/>
-    </row>
-    <row r="21" spans="7:11" x14ac:dyDescent="0.35">
-      <c r="G21" s="32">
+    </row>
+    <row r="21" spans="7:10" x14ac:dyDescent="0.25">
+      <c r="G21">
         <v>14</v>
       </c>
-      <c r="H21" s="32" t="s">
+      <c r="H21" t="s">
         <v>107</v>
       </c>
-      <c r="I21" s="32" t="s">
+      <c r="I21" t="s">
         <v>109</v>
       </c>
-      <c r="J21" s="32" t="s">
+      <c r="J21" t="s">
         <v>108</v>
       </c>
-      <c r="K21" s="32"/>
-    </row>
-    <row r="22" spans="7:11" x14ac:dyDescent="0.35">
-      <c r="G22" s="32">
+    </row>
+    <row r="22" spans="7:10" x14ac:dyDescent="0.25">
+      <c r="G22">
         <v>15</v>
       </c>
-      <c r="H22" s="32" t="s">
+      <c r="H22" t="s">
         <v>112</v>
       </c>
-      <c r="I22" s="32" t="s">
+      <c r="I22" t="s">
         <v>96</v>
       </c>
-      <c r="J22" s="32" t="s">
+      <c r="J22" t="s">
         <v>110</v>
       </c>
-      <c r="K22" s="32"/>
-    </row>
-    <row r="23" spans="7:11" x14ac:dyDescent="0.35">
-      <c r="G23" s="32">
+    </row>
+    <row r="23" spans="7:10" x14ac:dyDescent="0.25">
+      <c r="G23">
         <v>16</v>
       </c>
-      <c r="H23" s="32" t="s">
+      <c r="H23" t="s">
         <v>107</v>
       </c>
-      <c r="I23" s="32" t="s">
+      <c r="I23" t="s">
         <v>109</v>
       </c>
-      <c r="J23" s="32" t="s">
+      <c r="J23" t="s">
         <v>108</v>
       </c>
-      <c r="K23" s="32"/>
-    </row>
-    <row r="24" spans="7:11" x14ac:dyDescent="0.35">
-      <c r="G24" s="32">
+    </row>
+    <row r="24" spans="7:10" x14ac:dyDescent="0.25">
+      <c r="G24">
         <v>17</v>
       </c>
-      <c r="H24" s="32" t="s">
+      <c r="H24" t="s">
         <v>113</v>
       </c>
-      <c r="I24" s="32" t="s">
+      <c r="I24" t="s">
         <v>114</v>
       </c>
-      <c r="J24" s="32" t="s">
+      <c r="J24" t="s">
         <v>115</v>
       </c>
-      <c r="K24" s="32"/>
-    </row>
-    <row r="25" spans="7:11" x14ac:dyDescent="0.35">
-      <c r="G25" s="32">
+    </row>
+    <row r="25" spans="7:10" x14ac:dyDescent="0.25">
+      <c r="G25">
         <v>18</v>
       </c>
-      <c r="H25" s="32" t="s">
+      <c r="H25" t="s">
         <v>102</v>
       </c>
-      <c r="I25" s="32" t="s">
+      <c r="I25" t="s">
         <v>103</v>
       </c>
-      <c r="J25" s="32" t="s">
+      <c r="J25" t="s">
         <v>40</v>
       </c>
-      <c r="K25" s="32"/>
     </row>
   </sheetData>
   <mergeCells count="15">
+    <mergeCell ref="A4:F5"/>
+    <mergeCell ref="A6:F6"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="A3:B3"/>
     <mergeCell ref="M1:R1"/>
     <mergeCell ref="M2:N2"/>
     <mergeCell ref="M3:N3"/>
@@ -4516,11 +4391,6 @@
     <mergeCell ref="G2:H2"/>
     <mergeCell ref="G3:H3"/>
     <mergeCell ref="G1:L1"/>
-    <mergeCell ref="A4:F5"/>
-    <mergeCell ref="A6:F6"/>
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="A3:B3"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -4528,415 +4398,395 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{791F26CA-73F7-4CFD-B892-FF534C61ED87}">
-  <dimension ref="A1:S11"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:R11"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="21.90625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.54296875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="31.1796875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="18.36328125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="16.1796875" style="23" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="21.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.5703125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="31.140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="18.42578125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="16.140625" style="9" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="5" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="22.36328125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="19.7265625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="28.6328125" customWidth="1"/>
-    <col min="11" max="11" width="18.36328125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="16.1796875" style="23" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="22.42578125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="19.7109375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="28.5703125" customWidth="1"/>
+    <col min="11" max="11" width="18.42578125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="16.140625" style="9" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="5" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="22.36328125" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="22.90625" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="32.36328125" customWidth="1"/>
-    <col min="17" max="17" width="18.36328125" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="16.1796875" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="8.7265625" style="7"/>
+    <col min="14" max="14" width="22.42578125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="22.85546875" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="32.42578125" customWidth="1"/>
+    <col min="17" max="17" width="18.42578125" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="16.140625" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="8.7109375"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" x14ac:dyDescent="0.35">
-      <c r="A1" s="17" t="s">
+    <row r="1" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A1" s="16" t="s">
         <v>18</v>
       </c>
-      <c r="B1" s="17"/>
-      <c r="C1" s="17"/>
-      <c r="D1" s="17"/>
-      <c r="E1" s="17"/>
-      <c r="F1" s="24"/>
-      <c r="G1" s="16" t="s">
+      <c r="B1" s="16"/>
+      <c r="C1" s="16"/>
+      <c r="D1" s="16"/>
+      <c r="E1" s="16"/>
+      <c r="F1" s="17"/>
+      <c r="G1" s="18" t="s">
         <v>19</v>
       </c>
-      <c r="H1" s="17"/>
-      <c r="I1" s="17"/>
-      <c r="J1" s="17"/>
-      <c r="K1" s="17"/>
-      <c r="L1" s="24"/>
-      <c r="M1" s="17" t="s">
+      <c r="H1" s="16"/>
+      <c r="I1" s="16"/>
+      <c r="J1" s="16"/>
+      <c r="K1" s="16"/>
+      <c r="L1" s="17"/>
+      <c r="M1" s="16" t="s">
         <v>20</v>
       </c>
-      <c r="N1" s="17"/>
-      <c r="O1" s="17"/>
-      <c r="P1" s="17"/>
-      <c r="Q1" s="17"/>
-      <c r="R1" s="17"/>
-    </row>
-    <row r="2" spans="1:19" x14ac:dyDescent="0.35">
-      <c r="A2" s="17" t="s">
+      <c r="N1" s="16"/>
+      <c r="O1" s="16"/>
+      <c r="P1" s="16"/>
+      <c r="Q1" s="16"/>
+      <c r="R1" s="16"/>
+    </row>
+    <row r="2" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A2" s="16" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="17"/>
-      <c r="C2" s="18">
+      <c r="B2" s="16"/>
+      <c r="C2" s="8">
         <f>IFERROR(_xlfn.XLOOKUP(A1, TestMaster[Test Name], TestMaster[Test ID], "ID not found"), "")</f>
         <v>8</v>
       </c>
-      <c r="D2" s="32"/>
-      <c r="E2" s="20" t="s">
+      <c r="E2" t="s">
         <v>4</v>
       </c>
-      <c r="F2" s="21"/>
-      <c r="G2" s="17" t="s">
+      <c r="G2" s="16" t="s">
         <v>3</v>
       </c>
-      <c r="H2" s="17"/>
-      <c r="I2" s="18">
+      <c r="H2" s="16"/>
+      <c r="I2" s="8">
         <f>IFERROR(_xlfn.XLOOKUP(G1, TestMaster[Test Name], TestMaster[Test ID], "ID not found"), "")</f>
         <v>9</v>
       </c>
-      <c r="J2" s="32"/>
-      <c r="K2" s="20" t="s">
+      <c r="K2" t="s">
         <v>4</v>
       </c>
-      <c r="L2" s="21"/>
-      <c r="M2" s="17" t="s">
+      <c r="M2" s="16" t="s">
         <v>3</v>
       </c>
-      <c r="N2" s="17"/>
-      <c r="O2" s="18">
+      <c r="N2" s="16"/>
+      <c r="O2" s="8">
         <f>IFERROR(_xlfn.XLOOKUP(M1, TestMaster[Test Name], TestMaster[Test ID], "ID not found"), "")</f>
         <v>10</v>
       </c>
-      <c r="P2" s="32"/>
-      <c r="Q2" s="20" t="s">
+      <c r="Q2" t="s">
         <v>4</v>
       </c>
-      <c r="R2" s="20"/>
-    </row>
-    <row r="3" spans="1:19" x14ac:dyDescent="0.35">
-      <c r="A3" s="17" t="s">
-        <v>188</v>
-      </c>
-      <c r="B3" s="17"/>
-      <c r="C3" s="18" t="str">
+    </row>
+    <row r="3" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A3" s="16" t="s">
+        <v>187</v>
+      </c>
+      <c r="B3" s="16"/>
+      <c r="C3" s="8" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(A1, TestMaster[Test Name], TestMaster[Test Priority], "Priority not found"), "")</f>
         <v>Medium</v>
       </c>
-      <c r="D3" s="32"/>
-      <c r="E3" s="20" t="s">
+      <c r="E3" t="s">
         <v>5</v>
       </c>
-      <c r="F3" s="21" t="str">
+      <c r="F3" s="9" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(A1, TestMaster[Test Name], TestMaster[Test Status], "Status not found"), "")</f>
         <v>Not Implemented</v>
       </c>
-      <c r="G3" s="17" t="s">
-        <v>188</v>
-      </c>
-      <c r="H3" s="17"/>
-      <c r="I3" s="18" t="str">
+      <c r="G3" s="16" t="s">
+        <v>187</v>
+      </c>
+      <c r="H3" s="16"/>
+      <c r="I3" s="8" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(G1, TestMaster[Test Name], TestMaster[Test Priority], "Priority not found"), "")</f>
         <v>Medium</v>
       </c>
-      <c r="J3" s="32"/>
-      <c r="K3" s="20" t="s">
+      <c r="K3" t="s">
         <v>5</v>
       </c>
-      <c r="L3" s="21" t="str">
+      <c r="L3" s="9" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(G1, TestMaster[Test Name], TestMaster[Test Status], "Status not found"), "")</f>
         <v>Not Implemented</v>
       </c>
-      <c r="M3" s="17" t="s">
-        <v>188</v>
-      </c>
-      <c r="N3" s="17"/>
-      <c r="O3" s="18" t="str">
+      <c r="M3" s="16" t="s">
+        <v>187</v>
+      </c>
+      <c r="N3" s="16"/>
+      <c r="O3" s="8" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(M1, TestMaster[Test Name], TestMaster[Test Priority], "Priority not found"), "")</f>
         <v>Low</v>
       </c>
-      <c r="P3" s="32"/>
-      <c r="Q3" s="20" t="s">
+      <c r="Q3" t="s">
         <v>5</v>
       </c>
-      <c r="R3" s="20" t="str">
+      <c r="R3" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(M1, TestMaster[Test Name], TestMaster[Test Status], "Status not found"), "")</f>
         <v>Not Implemented</v>
       </c>
     </row>
-    <row r="4" spans="1:19" x14ac:dyDescent="0.35">
-      <c r="A4" s="39" t="s">
+    <row r="4" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A4" s="20" t="s">
         <v>71</v>
       </c>
-      <c r="B4" s="39"/>
-      <c r="C4" s="39"/>
-      <c r="D4" s="39"/>
-      <c r="E4" s="39"/>
-      <c r="F4" s="40"/>
-      <c r="G4" s="38" t="s">
+      <c r="B4" s="20"/>
+      <c r="C4" s="20"/>
+      <c r="D4" s="20"/>
+      <c r="E4" s="20"/>
+      <c r="F4" s="21"/>
+      <c r="G4" s="19" t="s">
         <v>6</v>
       </c>
-      <c r="H4" s="39"/>
-      <c r="I4" s="39"/>
-      <c r="J4" s="39"/>
-      <c r="K4" s="39"/>
-      <c r="L4" s="40"/>
-      <c r="M4" s="39" t="s">
+      <c r="H4" s="20"/>
+      <c r="I4" s="20"/>
+      <c r="J4" s="20"/>
+      <c r="K4" s="20"/>
+      <c r="L4" s="21"/>
+      <c r="M4" s="20" t="s">
         <v>6</v>
       </c>
-      <c r="N4" s="39"/>
-      <c r="O4" s="39"/>
-      <c r="P4" s="39"/>
-      <c r="Q4" s="39"/>
-      <c r="R4" s="39"/>
-    </row>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.35">
-      <c r="A5" s="39"/>
-      <c r="B5" s="39"/>
-      <c r="C5" s="39"/>
-      <c r="D5" s="39"/>
-      <c r="E5" s="39"/>
-      <c r="F5" s="40"/>
-      <c r="G5" s="38"/>
-      <c r="H5" s="39"/>
-      <c r="I5" s="39"/>
-      <c r="J5" s="39"/>
-      <c r="K5" s="39"/>
-      <c r="L5" s="40"/>
-      <c r="M5" s="39"/>
-      <c r="N5" s="39"/>
-      <c r="O5" s="39"/>
-      <c r="P5" s="39"/>
-      <c r="Q5" s="39"/>
-      <c r="R5" s="39"/>
-    </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.35">
-      <c r="A6" s="17" t="s">
+      <c r="N4" s="20"/>
+      <c r="O4" s="20"/>
+      <c r="P4" s="20"/>
+      <c r="Q4" s="20"/>
+      <c r="R4" s="20"/>
+    </row>
+    <row r="5" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A5" s="20"/>
+      <c r="B5" s="20"/>
+      <c r="C5" s="20"/>
+      <c r="D5" s="20"/>
+      <c r="E5" s="20"/>
+      <c r="F5" s="21"/>
+      <c r="G5" s="19"/>
+      <c r="H5" s="20"/>
+      <c r="I5" s="20"/>
+      <c r="J5" s="20"/>
+      <c r="K5" s="20"/>
+      <c r="L5" s="21"/>
+      <c r="M5" s="20"/>
+      <c r="N5" s="20"/>
+      <c r="O5" s="20"/>
+      <c r="P5" s="20"/>
+      <c r="Q5" s="20"/>
+      <c r="R5" s="20"/>
+    </row>
+    <row r="6" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A6" s="16" t="s">
         <v>72</v>
       </c>
-      <c r="B6" s="17"/>
-      <c r="C6" s="17"/>
-      <c r="D6" s="17"/>
-      <c r="E6" s="17"/>
-      <c r="F6" s="24"/>
-      <c r="G6" s="16" t="s">
+      <c r="B6" s="16"/>
+      <c r="C6" s="16"/>
+      <c r="D6" s="16"/>
+      <c r="E6" s="16"/>
+      <c r="F6" s="17"/>
+      <c r="G6" s="18" t="s">
         <v>7</v>
       </c>
-      <c r="H6" s="17"/>
-      <c r="I6" s="17"/>
-      <c r="J6" s="17"/>
-      <c r="K6" s="17"/>
-      <c r="L6" s="24"/>
-      <c r="M6" s="17" t="s">
+      <c r="H6" s="16"/>
+      <c r="I6" s="16"/>
+      <c r="J6" s="16"/>
+      <c r="K6" s="16"/>
+      <c r="L6" s="17"/>
+      <c r="M6" s="16" t="s">
         <v>7</v>
       </c>
-      <c r="N6" s="17"/>
-      <c r="O6" s="17"/>
-      <c r="P6" s="17"/>
-      <c r="Q6" s="17"/>
-      <c r="R6" s="17"/>
-    </row>
-    <row r="7" spans="1:19" x14ac:dyDescent="0.35">
-      <c r="A7" s="25" t="s">
+      <c r="N6" s="16"/>
+      <c r="O6" s="16"/>
+      <c r="P6" s="16"/>
+      <c r="Q6" s="16"/>
+      <c r="R6" s="16"/>
+    </row>
+    <row r="7" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A7" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B7" s="25" t="s">
+      <c r="B7" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C7" s="25" t="s">
+      <c r="C7" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="D7" s="25" t="s">
+      <c r="D7" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="E7" s="25" t="s">
+      <c r="E7" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="F7" s="27" t="s">
+      <c r="F7" s="12" t="s">
         <v>2</v>
       </c>
-      <c r="G7" s="25" t="s">
+      <c r="G7" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="H7" s="25" t="s">
+      <c r="H7" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="I7" s="25" t="s">
+      <c r="I7" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="J7" s="25" t="s">
+      <c r="J7" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="K7" s="25" t="s">
+      <c r="K7" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="L7" s="27" t="s">
+      <c r="L7" s="12" t="s">
         <v>2</v>
       </c>
-      <c r="M7" s="25" t="s">
+      <c r="M7" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="N7" s="25" t="s">
+      <c r="N7" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="O7" s="25" t="s">
+      <c r="O7" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="P7" s="25" t="s">
+      <c r="P7" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="Q7" s="25" t="s">
+      <c r="Q7" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="R7" s="25" t="s">
+      <c r="R7" s="1" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="8" spans="1:19" s="8" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="31">
+    <row r="8" spans="1:18" s="4" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A8" s="4">
         <v>1</v>
       </c>
-      <c r="B8" s="31" t="s">
+      <c r="B8" s="4" t="s">
         <v>73</v>
       </c>
-      <c r="C8" s="31" t="s">
+      <c r="C8" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="D8" s="31" t="s">
+      <c r="D8" s="4" t="s">
         <v>74</v>
       </c>
-      <c r="E8" s="31"/>
-      <c r="F8" s="41"/>
-      <c r="G8" s="31">
+      <c r="F8" s="15"/>
+      <c r="G8" s="4">
         <v>1</v>
       </c>
-      <c r="H8" s="31" t="s">
+      <c r="H8" s="4" t="s">
         <v>73</v>
       </c>
-      <c r="I8" s="31" t="s">
+      <c r="I8" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="J8" s="31" t="s">
+      <c r="J8" s="4" t="s">
         <v>77</v>
       </c>
-      <c r="K8" s="31"/>
-      <c r="L8" s="41"/>
-      <c r="M8" s="31">
+      <c r="L8" s="15"/>
+      <c r="M8" s="4">
         <v>1</v>
       </c>
-      <c r="N8" s="31" t="s">
+      <c r="N8" s="4" t="s">
         <v>73</v>
       </c>
-      <c r="O8" s="31" t="s">
+      <c r="O8" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="P8" s="31" t="s">
+      <c r="P8" s="4" t="s">
         <v>77</v>
       </c>
-      <c r="Q8" s="31"/>
-      <c r="R8" s="31"/>
-      <c r="S8" s="9"/>
-    </row>
-    <row r="9" spans="1:19" s="8" customFormat="1" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A9" s="31">
+    </row>
+    <row r="9" spans="1:18" s="4" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+      <c r="A9" s="4">
         <v>2</v>
       </c>
-      <c r="B9" s="31" t="s">
+      <c r="B9" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="C9" s="31" t="s">
+      <c r="C9" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="D9" s="31" t="s">
+      <c r="D9" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="E9" s="31"/>
-      <c r="F9" s="41"/>
-      <c r="G9" s="31">
+      <c r="F9" s="15"/>
+      <c r="G9" s="4">
         <v>2</v>
       </c>
-      <c r="H9" s="31" t="s">
+      <c r="H9" s="4" t="s">
         <v>75</v>
       </c>
-      <c r="I9" s="31" t="s">
+      <c r="I9" s="4" t="s">
         <v>78</v>
       </c>
-      <c r="J9" s="31" t="s">
+      <c r="J9" s="4" t="s">
         <v>80</v>
       </c>
-      <c r="K9" s="31"/>
-      <c r="L9" s="41"/>
-      <c r="M9" s="31">
+      <c r="L9" s="15"/>
+      <c r="M9" s="4">
         <v>2</v>
       </c>
-      <c r="N9" s="31" t="s">
+      <c r="N9" s="4" t="s">
         <v>75</v>
       </c>
-      <c r="O9" s="31" t="s">
+      <c r="O9" s="4" t="s">
         <v>82</v>
       </c>
-      <c r="P9" s="31" t="s">
+      <c r="P9" s="4" t="s">
         <v>81</v>
       </c>
-      <c r="Q9" s="31"/>
-      <c r="R9" s="31"/>
-      <c r="S9" s="9"/>
-    </row>
-    <row r="10" spans="1:19" s="8" customFormat="1" ht="29" x14ac:dyDescent="0.35">
-      <c r="F10" s="41"/>
-      <c r="G10" s="31">
+    </row>
+    <row r="10" spans="1:18" s="4" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+      <c r="F10" s="15"/>
+      <c r="G10" s="4">
         <v>3</v>
       </c>
-      <c r="H10" s="31" t="s">
+      <c r="H10" s="4" t="s">
         <v>76</v>
       </c>
-      <c r="I10" s="31" t="s">
+      <c r="I10" s="4" t="s">
         <v>79</v>
       </c>
-      <c r="J10" s="31" t="s">
+      <c r="J10" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="K10" s="31"/>
-      <c r="L10" s="41"/>
-      <c r="M10" s="31">
+      <c r="L10" s="15"/>
+      <c r="M10" s="4">
         <v>3</v>
       </c>
-      <c r="N10" s="31" t="s">
+      <c r="N10" s="4" t="s">
         <v>76</v>
       </c>
-      <c r="O10" s="31" t="s">
+      <c r="O10" s="4" t="s">
         <v>79</v>
       </c>
-      <c r="P10" s="31" t="s">
+      <c r="P10" s="4" t="s">
         <v>83</v>
       </c>
-      <c r="Q10" s="31"/>
-      <c r="R10" s="31"/>
-      <c r="S10" s="9"/>
-    </row>
-    <row r="11" spans="1:19" ht="29" x14ac:dyDescent="0.35">
-      <c r="M11" s="31">
+    </row>
+    <row r="11" spans="1:18" ht="30" x14ac:dyDescent="0.25">
+      <c r="M11" s="4">
         <v>4</v>
       </c>
-      <c r="N11" s="31" t="s">
+      <c r="N11" s="4" t="s">
         <v>84</v>
       </c>
-      <c r="O11" s="31" t="s">
+      <c r="O11" s="4" t="s">
         <v>85</v>
       </c>
-      <c r="P11" s="31" t="s">
+      <c r="P11" s="4" t="s">
         <v>86</v>
       </c>
-      <c r="Q11" s="32"/>
-      <c r="R11" s="32"/>
     </row>
   </sheetData>
   <mergeCells count="15">
+    <mergeCell ref="A4:F5"/>
+    <mergeCell ref="A6:F6"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="A3:B3"/>
     <mergeCell ref="M1:R1"/>
     <mergeCell ref="M2:N2"/>
     <mergeCell ref="M3:N3"/>
@@ -4947,11 +4797,6 @@
     <mergeCell ref="G2:H2"/>
     <mergeCell ref="G3:H3"/>
     <mergeCell ref="G1:L1"/>
-    <mergeCell ref="A4:F5"/>
-    <mergeCell ref="A6:F6"/>
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="A3:B3"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -4959,376 +4804,367 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E4413619-C528-4B04-A1ED-B4C77CA83066}">
-  <dimension ref="A1:AD13"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:AD12"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="25.08984375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="17.54296875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="15.26953125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="18.36328125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="8.7265625" style="23"/>
+    <col min="2" max="2" width="25.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17.5703125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15.28515625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="18.42578125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="8.7109375" style="9"/>
     <col min="7" max="7" width="5" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="23.7265625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="48.81640625" customWidth="1"/>
-    <col min="10" max="10" width="17.54296875" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="18.36328125" customWidth="1"/>
-    <col min="12" max="12" width="8.7265625" style="23"/>
+    <col min="8" max="8" width="23.7109375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="48.85546875" customWidth="1"/>
+    <col min="10" max="10" width="17.5703125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="18.42578125" customWidth="1"/>
+    <col min="12" max="12" width="8.7109375" style="9"/>
     <col min="13" max="13" width="5" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="21.54296875" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="30.81640625" customWidth="1"/>
-    <col min="16" max="16" width="15.26953125" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="18.36328125" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="8.7265625" style="23"/>
+    <col min="14" max="14" width="21.5703125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="30.85546875" customWidth="1"/>
+    <col min="16" max="16" width="15.28515625" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="18.42578125" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="8.7109375" style="9"/>
     <col min="19" max="19" width="5" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="23.26953125" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="23.28515625" bestFit="1" customWidth="1"/>
     <col min="21" max="21" width="41" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="15.26953125" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="18.36328125" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="8.7265625" style="23"/>
+    <col min="22" max="22" width="15.28515625" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="18.42578125" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="8.7109375" style="9"/>
     <col min="25" max="25" width="5" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="19.1796875" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="11.54296875" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="15.26953125" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="18.36328125" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="19.140625" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="11.5703125" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="15.28515625" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="18.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:30" x14ac:dyDescent="0.35">
-      <c r="A1" s="17" t="s">
+    <row r="1" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="A1" s="16" t="s">
         <v>11</v>
       </c>
-      <c r="B1" s="17"/>
-      <c r="C1" s="17"/>
-      <c r="D1" s="17"/>
-      <c r="E1" s="17"/>
-      <c r="F1" s="24"/>
-      <c r="G1" s="17" t="s">
+      <c r="B1" s="16"/>
+      <c r="C1" s="16"/>
+      <c r="D1" s="16"/>
+      <c r="E1" s="16"/>
+      <c r="F1" s="17"/>
+      <c r="G1" s="16" t="s">
         <v>21</v>
       </c>
-      <c r="H1" s="17"/>
-      <c r="I1" s="17"/>
-      <c r="J1" s="17"/>
-      <c r="K1" s="17"/>
-      <c r="L1" s="24"/>
-      <c r="M1" s="16" t="s">
+      <c r="H1" s="16"/>
+      <c r="I1" s="16"/>
+      <c r="J1" s="16"/>
+      <c r="K1" s="16"/>
+      <c r="L1" s="17"/>
+      <c r="M1" s="18" t="s">
         <v>22</v>
       </c>
-      <c r="N1" s="17"/>
-      <c r="O1" s="17"/>
-      <c r="P1" s="17"/>
-      <c r="Q1" s="17"/>
-      <c r="R1" s="24"/>
-      <c r="S1" s="17" t="s">
+      <c r="N1" s="16"/>
+      <c r="O1" s="16"/>
+      <c r="P1" s="16"/>
+      <c r="Q1" s="16"/>
+      <c r="R1" s="17"/>
+      <c r="S1" s="16" t="s">
         <v>23</v>
       </c>
-      <c r="T1" s="17"/>
-      <c r="U1" s="17"/>
-      <c r="V1" s="17"/>
-      <c r="W1" s="17"/>
-      <c r="X1" s="24"/>
-      <c r="Y1" s="2" t="s">
+      <c r="T1" s="16"/>
+      <c r="U1" s="16"/>
+      <c r="V1" s="16"/>
+      <c r="W1" s="16"/>
+      <c r="X1" s="17"/>
+      <c r="Y1" s="16" t="s">
         <v>24</v>
       </c>
-      <c r="Z1" s="2"/>
-      <c r="AA1" s="2"/>
-      <c r="AB1" s="2"/>
-      <c r="AC1" s="2"/>
-      <c r="AD1" s="2"/>
-    </row>
-    <row r="2" spans="1:30" x14ac:dyDescent="0.35">
-      <c r="A2" s="17" t="s">
+      <c r="Z1" s="16"/>
+      <c r="AA1" s="16"/>
+      <c r="AB1" s="16"/>
+      <c r="AC1" s="16"/>
+      <c r="AD1" s="16"/>
+    </row>
+    <row r="2" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="A2" s="16" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="17"/>
-      <c r="C2" s="20">
+      <c r="B2" s="16"/>
+      <c r="C2">
         <f>IFERROR(_xlfn.XLOOKUP(A1, TestMaster[Test Name], TestMaster[Test ID], "ID not found"), "")</f>
         <v>11</v>
       </c>
-      <c r="D2" s="32"/>
-      <c r="E2" s="20" t="s">
+      <c r="E2" t="s">
         <v>4</v>
       </c>
-      <c r="F2" s="21"/>
-      <c r="G2" s="17" t="s">
+      <c r="G2" s="16" t="s">
         <v>3</v>
       </c>
-      <c r="H2" s="17"/>
-      <c r="I2" s="18">
+      <c r="H2" s="16"/>
+      <c r="I2" s="8">
         <f>IFERROR(_xlfn.XLOOKUP(G1, TestMaster[Test Name], TestMaster[Test ID], "ID not found"), "")</f>
         <v>12</v>
       </c>
-      <c r="J2" s="32"/>
-      <c r="K2" s="20" t="s">
+      <c r="K2" t="s">
         <v>4</v>
       </c>
-      <c r="L2" s="21"/>
-      <c r="M2" s="2" t="s">
+      <c r="M2" s="16" t="s">
         <v>3</v>
       </c>
-      <c r="N2" s="2"/>
-      <c r="O2" s="15">
+      <c r="N2" s="16"/>
+      <c r="O2" s="8">
         <f>IFERROR(_xlfn.XLOOKUP(M1, TestMaster[Test Name], TestMaster[Test ID], "ID not found"), "")</f>
         <v>13</v>
       </c>
-      <c r="Q2" s="4" t="s">
+      <c r="Q2" t="s">
         <v>4</v>
       </c>
-      <c r="R2" s="21"/>
-      <c r="S2" s="2" t="s">
+      <c r="S2" s="16" t="s">
         <v>3</v>
       </c>
-      <c r="T2" s="2"/>
-      <c r="U2" s="15">
+      <c r="T2" s="16"/>
+      <c r="U2" s="8">
         <f>IFERROR(_xlfn.XLOOKUP(S1, TestMaster[Test Name], TestMaster[Test ID], "ID not found"), "")</f>
         <v>14</v>
       </c>
-      <c r="W2" s="4" t="s">
+      <c r="W2" t="s">
         <v>4</v>
       </c>
-      <c r="X2" s="21"/>
-      <c r="Y2" s="2" t="s">
+      <c r="Y2" s="16" t="s">
         <v>3</v>
       </c>
-      <c r="Z2" s="2"/>
-      <c r="AA2" s="15">
+      <c r="Z2" s="16"/>
+      <c r="AA2" s="8">
         <f>IFERROR(_xlfn.XLOOKUP(Y1, TestMaster[Test Name], TestMaster[Test ID], "ID not found"), "")</f>
         <v>15</v>
       </c>
-      <c r="AC2" s="4" t="s">
+      <c r="AC2" t="s">
         <v>4</v>
       </c>
-      <c r="AD2" s="4"/>
-    </row>
-    <row r="3" spans="1:30" x14ac:dyDescent="0.35">
-      <c r="A3" s="17" t="s">
-        <v>188</v>
-      </c>
-      <c r="B3" s="17"/>
-      <c r="C3" s="20" t="str">
+    </row>
+    <row r="3" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="A3" s="16" t="s">
+        <v>187</v>
+      </c>
+      <c r="B3" s="16"/>
+      <c r="C3" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(A1, TestMaster[Test Name], TestMaster[Test Priority], "Priority not found"), "")</f>
         <v>High</v>
       </c>
-      <c r="D3" s="32"/>
-      <c r="E3" s="20" t="s">
+      <c r="E3" t="s">
         <v>5</v>
       </c>
-      <c r="F3" s="21" t="str">
+      <c r="F3" s="9" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(A1, TestMaster[Test Name], TestMaster[Test Priority], "Priority not found"), "")</f>
         <v>High</v>
       </c>
-      <c r="G3" s="17" t="s">
-        <v>189</v>
-      </c>
-      <c r="H3" s="17"/>
-      <c r="I3" s="18" t="str">
+      <c r="G3" s="16" t="s">
+        <v>188</v>
+      </c>
+      <c r="H3" s="16"/>
+      <c r="I3" s="8" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(G1, TestMaster[Test Name], TestMaster[Test Priority], "Priority not found"), "")</f>
         <v>High</v>
       </c>
-      <c r="J3" s="32"/>
-      <c r="K3" s="20" t="s">
+      <c r="K3" t="s">
         <v>5</v>
       </c>
-      <c r="L3" s="21" t="str">
+      <c r="L3" s="9" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(G1, TestMaster[Test Name], TestMaster[Test Priority], "Priority not found"), "")</f>
         <v>High</v>
       </c>
-      <c r="M3" s="2" t="s">
-        <v>188</v>
-      </c>
-      <c r="N3" s="2"/>
-      <c r="O3" s="15" t="str">
+      <c r="M3" s="16" t="s">
+        <v>187</v>
+      </c>
+      <c r="N3" s="16"/>
+      <c r="O3" s="8" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(M1, TestMaster[Test Name], TestMaster[Test Priority], "Priority not found"), "")</f>
         <v>Medium</v>
       </c>
-      <c r="Q3" s="4" t="s">
+      <c r="Q3" t="s">
         <v>5</v>
       </c>
-      <c r="R3" s="21" t="str">
+      <c r="R3" s="9" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(M1, TestMaster[Test Name], TestMaster[Test Priority], "Priority not found"), "")</f>
         <v>Medium</v>
       </c>
-      <c r="S3" s="2" t="s">
-        <v>188</v>
-      </c>
-      <c r="T3" s="2"/>
-      <c r="U3" s="15" t="str">
+      <c r="S3" s="16" t="s">
+        <v>187</v>
+      </c>
+      <c r="T3" s="16"/>
+      <c r="U3" s="8" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(S1, TestMaster[Test Name], TestMaster[Test Priority], "Priority not found"), "")</f>
         <v>Low</v>
       </c>
-      <c r="W3" s="4" t="s">
+      <c r="W3" t="s">
         <v>5</v>
       </c>
-      <c r="X3" s="21" t="str">
+      <c r="X3" s="9" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(S1, TestMaster[Test Name], TestMaster[Test Priority], "Priority not found"), "")</f>
         <v>Low</v>
       </c>
-      <c r="Y3" s="2" t="s">
-        <v>188</v>
-      </c>
-      <c r="Z3" s="2"/>
-      <c r="AA3" s="15" t="str">
+      <c r="Y3" s="16" t="s">
+        <v>187</v>
+      </c>
+      <c r="Z3" s="16"/>
+      <c r="AA3" s="8" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(Y1, TestMaster[Test Name], TestMaster[Test Priority], "Priority not found"), "")</f>
         <v>High</v>
       </c>
-      <c r="AC3" s="4" t="s">
+      <c r="AC3" t="s">
         <v>5</v>
       </c>
-      <c r="AD3" s="4" t="str">
+      <c r="AD3" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(Y1, TestMaster[Test Name], TestMaster[Test Priority], "Priority not found"), "")</f>
         <v>High</v>
       </c>
     </row>
-    <row r="4" spans="1:30" s="3" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="39" t="s">
+    <row r="4" spans="1:30" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="20" t="s">
         <v>12</v>
       </c>
-      <c r="B4" s="39"/>
-      <c r="C4" s="39"/>
-      <c r="D4" s="39"/>
-      <c r="E4" s="39"/>
-      <c r="F4" s="40"/>
-      <c r="G4" s="39" t="s">
+      <c r="B4" s="20"/>
+      <c r="C4" s="20"/>
+      <c r="D4" s="20"/>
+      <c r="E4" s="20"/>
+      <c r="F4" s="21"/>
+      <c r="G4" s="20" t="s">
         <v>68</v>
       </c>
-      <c r="H4" s="39"/>
-      <c r="I4" s="39"/>
-      <c r="J4" s="39"/>
-      <c r="K4" s="39"/>
-      <c r="L4" s="40"/>
-      <c r="M4" s="38" t="s">
+      <c r="H4" s="20"/>
+      <c r="I4" s="20"/>
+      <c r="J4" s="20"/>
+      <c r="K4" s="20"/>
+      <c r="L4" s="21"/>
+      <c r="M4" s="19" t="s">
         <v>12</v>
       </c>
-      <c r="N4" s="39"/>
-      <c r="O4" s="39"/>
-      <c r="P4" s="39"/>
-      <c r="Q4" s="39"/>
-      <c r="R4" s="40"/>
-      <c r="S4" s="39" t="s">
+      <c r="N4" s="20"/>
+      <c r="O4" s="20"/>
+      <c r="P4" s="20"/>
+      <c r="Q4" s="20"/>
+      <c r="R4" s="21"/>
+      <c r="S4" s="20" t="s">
         <v>12</v>
       </c>
-      <c r="T4" s="39"/>
-      <c r="U4" s="39"/>
-      <c r="V4" s="39"/>
-      <c r="W4" s="39"/>
-      <c r="X4" s="40"/>
-      <c r="Y4" s="6" t="s">
+      <c r="T4" s="20"/>
+      <c r="U4" s="20"/>
+      <c r="V4" s="20"/>
+      <c r="W4" s="20"/>
+      <c r="X4" s="21"/>
+      <c r="Y4" s="20" t="s">
         <v>12</v>
       </c>
-      <c r="Z4" s="6"/>
-      <c r="AA4" s="6"/>
-      <c r="AB4" s="6"/>
-      <c r="AC4" s="6"/>
-      <c r="AD4" s="6"/>
-    </row>
-    <row r="5" spans="1:30" s="3" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="39"/>
-      <c r="B5" s="39"/>
-      <c r="C5" s="39"/>
-      <c r="D5" s="39"/>
-      <c r="E5" s="39"/>
-      <c r="F5" s="40"/>
-      <c r="G5" s="39"/>
-      <c r="H5" s="39"/>
-      <c r="I5" s="39"/>
-      <c r="J5" s="39"/>
-      <c r="K5" s="39"/>
-      <c r="L5" s="40"/>
-      <c r="M5" s="38"/>
-      <c r="N5" s="39"/>
-      <c r="O5" s="39"/>
-      <c r="P5" s="39"/>
-      <c r="Q5" s="39"/>
-      <c r="R5" s="40"/>
-      <c r="S5" s="39"/>
-      <c r="T5" s="39"/>
-      <c r="U5" s="39"/>
-      <c r="V5" s="39"/>
-      <c r="W5" s="39"/>
-      <c r="X5" s="40"/>
-      <c r="Y5" s="6"/>
-      <c r="Z5" s="6"/>
-      <c r="AA5" s="6"/>
-      <c r="AB5" s="6"/>
-      <c r="AC5" s="6"/>
-      <c r="AD5" s="6"/>
-    </row>
-    <row r="6" spans="1:30" x14ac:dyDescent="0.35">
-      <c r="A6" s="17" t="s">
+      <c r="Z4" s="20"/>
+      <c r="AA4" s="20"/>
+      <c r="AB4" s="20"/>
+      <c r="AC4" s="20"/>
+      <c r="AD4" s="20"/>
+    </row>
+    <row r="5" spans="1:30" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="20"/>
+      <c r="B5" s="20"/>
+      <c r="C5" s="20"/>
+      <c r="D5" s="20"/>
+      <c r="E5" s="20"/>
+      <c r="F5" s="21"/>
+      <c r="G5" s="20"/>
+      <c r="H5" s="20"/>
+      <c r="I5" s="20"/>
+      <c r="J5" s="20"/>
+      <c r="K5" s="20"/>
+      <c r="L5" s="21"/>
+      <c r="M5" s="19"/>
+      <c r="N5" s="20"/>
+      <c r="O5" s="20"/>
+      <c r="P5" s="20"/>
+      <c r="Q5" s="20"/>
+      <c r="R5" s="21"/>
+      <c r="S5" s="20"/>
+      <c r="T5" s="20"/>
+      <c r="U5" s="20"/>
+      <c r="V5" s="20"/>
+      <c r="W5" s="20"/>
+      <c r="X5" s="21"/>
+      <c r="Y5" s="20"/>
+      <c r="Z5" s="20"/>
+      <c r="AA5" s="20"/>
+      <c r="AB5" s="20"/>
+      <c r="AC5" s="20"/>
+      <c r="AD5" s="20"/>
+    </row>
+    <row r="6" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="A6" s="16" t="s">
         <v>69</v>
       </c>
-      <c r="B6" s="17"/>
-      <c r="C6" s="17"/>
-      <c r="D6" s="17"/>
-      <c r="E6" s="17"/>
-      <c r="F6" s="24"/>
-      <c r="G6" s="17" t="s">
+      <c r="B6" s="16"/>
+      <c r="C6" s="16"/>
+      <c r="D6" s="16"/>
+      <c r="E6" s="16"/>
+      <c r="F6" s="17"/>
+      <c r="G6" s="16" t="s">
         <v>69</v>
       </c>
-      <c r="H6" s="17"/>
-      <c r="I6" s="17"/>
-      <c r="J6" s="17"/>
-      <c r="K6" s="17"/>
-      <c r="L6" s="24"/>
-      <c r="M6" s="16" t="s">
+      <c r="H6" s="16"/>
+      <c r="I6" s="16"/>
+      <c r="J6" s="16"/>
+      <c r="K6" s="16"/>
+      <c r="L6" s="17"/>
+      <c r="M6" s="18" t="s">
         <v>70</v>
       </c>
-      <c r="N6" s="17"/>
-      <c r="O6" s="17"/>
-      <c r="P6" s="17"/>
-      <c r="Q6" s="17"/>
-      <c r="R6" s="24"/>
-      <c r="S6" s="17" t="s">
+      <c r="N6" s="16"/>
+      <c r="O6" s="16"/>
+      <c r="P6" s="16"/>
+      <c r="Q6" s="16"/>
+      <c r="R6" s="17"/>
+      <c r="S6" s="16" t="s">
         <v>53</v>
       </c>
-      <c r="T6" s="17"/>
-      <c r="U6" s="17"/>
-      <c r="V6" s="17"/>
-      <c r="W6" s="17"/>
-      <c r="X6" s="24"/>
-      <c r="Y6" s="2" t="s">
+      <c r="T6" s="16"/>
+      <c r="U6" s="16"/>
+      <c r="V6" s="16"/>
+      <c r="W6" s="16"/>
+      <c r="X6" s="17"/>
+      <c r="Y6" s="16" t="s">
         <v>69</v>
       </c>
-      <c r="Z6" s="2"/>
-      <c r="AA6" s="2"/>
-      <c r="AB6" s="2"/>
-      <c r="AC6" s="2"/>
-      <c r="AD6" s="2"/>
-    </row>
-    <row r="7" spans="1:30" x14ac:dyDescent="0.35">
-      <c r="A7" s="25" t="s">
+      <c r="Z6" s="16"/>
+      <c r="AA6" s="16"/>
+      <c r="AB6" s="16"/>
+      <c r="AC6" s="16"/>
+      <c r="AD6" s="16"/>
+    </row>
+    <row r="7" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="A7" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B7" s="25" t="s">
+      <c r="B7" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C7" s="25" t="s">
+      <c r="C7" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="D7" s="25" t="s">
+      <c r="D7" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="E7" s="25" t="s">
+      <c r="E7" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="F7" s="27" t="s">
+      <c r="F7" s="12" t="s">
         <v>2</v>
       </c>
-      <c r="G7" s="25" t="s">
+      <c r="G7" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="H7" s="25" t="s">
+      <c r="H7" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="I7" s="25" t="s">
+      <c r="I7" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="J7" s="25" t="s">
+      <c r="J7" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="K7" s="25" t="s">
+      <c r="K7" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="L7" s="27" t="s">
+      <c r="L7" s="12" t="s">
         <v>2</v>
       </c>
       <c r="M7" s="1" t="s">
@@ -5346,7 +5182,7 @@
       <c r="Q7" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="R7" s="27" t="s">
+      <c r="R7" s="12" t="s">
         <v>2</v>
       </c>
       <c r="S7" s="1" t="s">
@@ -5364,7 +5200,7 @@
       <c r="W7" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="X7" s="27" t="s">
+      <c r="X7" s="12" t="s">
         <v>2</v>
       </c>
       <c r="Y7" s="1" t="s">
@@ -5386,33 +5222,31 @@
         <v>2</v>
       </c>
     </row>
-    <row r="8" spans="1:30" x14ac:dyDescent="0.35">
-      <c r="A8" s="32">
+    <row r="8" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="A8">
         <v>1</v>
       </c>
-      <c r="B8" s="32" t="s">
+      <c r="B8" t="s">
         <v>25</v>
       </c>
-      <c r="C8" s="32" t="s">
+      <c r="C8" t="s">
         <v>27</v>
       </c>
-      <c r="D8" s="32" t="s">
+      <c r="D8" t="s">
         <v>38</v>
       </c>
-      <c r="E8" s="32"/>
-      <c r="G8" s="32">
+      <c r="G8">
         <v>1</v>
       </c>
-      <c r="H8" s="32" t="s">
+      <c r="H8" t="s">
         <v>34</v>
       </c>
-      <c r="I8" s="32" t="s">
+      <c r="I8" t="s">
         <v>27</v>
       </c>
-      <c r="J8" s="32" t="s">
+      <c r="J8" t="s">
         <v>36</v>
       </c>
-      <c r="K8" s="32"/>
       <c r="M8">
         <v>1</v>
       </c>
@@ -5447,43 +5281,41 @@
         <v>66</v>
       </c>
     </row>
-    <row r="9" spans="1:30" ht="58" x14ac:dyDescent="0.35">
-      <c r="A9" s="32">
+    <row r="9" spans="1:30" ht="75" x14ac:dyDescent="0.25">
+      <c r="A9">
         <v>2</v>
       </c>
-      <c r="B9" s="32" t="s">
+      <c r="B9" t="s">
         <v>49</v>
       </c>
-      <c r="C9" s="32" t="s">
+      <c r="C9" t="s">
         <v>28</v>
       </c>
-      <c r="D9" s="32" t="s">
+      <c r="D9" t="s">
         <v>39</v>
       </c>
-      <c r="E9" s="32"/>
-      <c r="G9" s="32">
+      <c r="G9">
         <v>2</v>
       </c>
-      <c r="H9" s="32" t="s">
+      <c r="H9" t="s">
         <v>35</v>
       </c>
-      <c r="I9" s="19" t="s">
+      <c r="I9" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="J9" s="19" t="s">
+      <c r="J9" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="K9" s="32"/>
       <c r="M9">
         <v>2</v>
       </c>
-      <c r="N9" s="3" t="s">
+      <c r="N9" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="O9" s="3" t="s">
+      <c r="O9" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="P9" s="3" t="s">
+      <c r="P9" s="2" t="s">
         <v>45</v>
       </c>
       <c r="S9">
@@ -5508,33 +5340,31 @@
         <v>65</v>
       </c>
     </row>
-    <row r="10" spans="1:30" x14ac:dyDescent="0.35">
-      <c r="A10" s="32">
+    <row r="10" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="A10">
         <v>3</v>
       </c>
-      <c r="B10" s="32" t="s">
+      <c r="B10" t="s">
         <v>26</v>
       </c>
-      <c r="C10" s="32" t="s">
+      <c r="C10" t="s">
         <v>29</v>
       </c>
-      <c r="D10" s="32" t="s">
+      <c r="D10" t="s">
         <v>40</v>
       </c>
-      <c r="E10" s="32"/>
-      <c r="G10" s="20">
+      <c r="G10">
         <v>3</v>
       </c>
-      <c r="H10" s="20" t="s">
+      <c r="H10" t="s">
         <v>50</v>
       </c>
-      <c r="I10" s="32" t="s">
+      <c r="I10" t="s">
         <v>51</v>
       </c>
-      <c r="J10" s="32" t="s">
+      <c r="J10" t="s">
         <v>60</v>
       </c>
-      <c r="K10" s="32"/>
       <c r="M10">
         <v>3</v>
       </c>
@@ -5544,7 +5374,7 @@
       <c r="O10" t="s">
         <v>47</v>
       </c>
-      <c r="P10" s="5" t="s">
+      <c r="P10" s="3" t="s">
         <v>48</v>
       </c>
       <c r="S10">
@@ -5557,20 +5387,19 @@
         <v>61</v>
       </c>
     </row>
-    <row r="11" spans="1:30" x14ac:dyDescent="0.35">
-      <c r="A11" s="32">
+    <row r="11" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="A11">
         <v>4</v>
       </c>
-      <c r="B11" s="32" t="s">
+      <c r="B11" t="s">
         <v>30</v>
       </c>
-      <c r="C11" s="32" t="s">
+      <c r="C11" t="s">
         <v>31</v>
       </c>
-      <c r="D11" s="32" t="s">
+      <c r="D11" t="s">
         <v>38</v>
       </c>
-      <c r="E11" s="32"/>
       <c r="S11">
         <v>4</v>
       </c>
@@ -5581,20 +5410,19 @@
         <v>62</v>
       </c>
     </row>
-    <row r="12" spans="1:30" x14ac:dyDescent="0.35">
-      <c r="A12" s="32">
+    <row r="12" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="A12">
         <v>5</v>
       </c>
-      <c r="B12" s="32" t="s">
+      <c r="B12" t="s">
         <v>32</v>
       </c>
-      <c r="C12" s="32" t="s">
+      <c r="C12" t="s">
         <v>33</v>
       </c>
-      <c r="D12" s="32" t="s">
+      <c r="D12" t="s">
         <v>40</v>
       </c>
-      <c r="E12" s="32"/>
       <c r="S12">
         <v>5</v>
       </c>
@@ -5605,19 +5433,17 @@
         <v>58</v>
       </c>
     </row>
-    <row r="13" spans="1:30" x14ac:dyDescent="0.35">
-      <c r="A13" s="4"/>
-      <c r="B13" s="4"/>
-      <c r="C13" s="4"/>
-    </row>
   </sheetData>
   <mergeCells count="25">
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="A3:B3"/>
-    <mergeCell ref="G2:H2"/>
-    <mergeCell ref="G3:H3"/>
-    <mergeCell ref="M2:N2"/>
-    <mergeCell ref="M3:N3"/>
+    <mergeCell ref="A4:F5"/>
+    <mergeCell ref="A6:F6"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="M1:R1"/>
+    <mergeCell ref="G4:L5"/>
+    <mergeCell ref="G6:L6"/>
+    <mergeCell ref="M4:R5"/>
+    <mergeCell ref="M6:R6"/>
+    <mergeCell ref="G1:L1"/>
     <mergeCell ref="Y1:AD1"/>
     <mergeCell ref="Y2:Z2"/>
     <mergeCell ref="Y3:Z3"/>
@@ -5628,15 +5454,12 @@
     <mergeCell ref="S2:T2"/>
     <mergeCell ref="S3:T3"/>
     <mergeCell ref="S1:X1"/>
-    <mergeCell ref="M1:R1"/>
-    <mergeCell ref="G4:L5"/>
-    <mergeCell ref="G6:L6"/>
-    <mergeCell ref="M4:R5"/>
-    <mergeCell ref="M6:R6"/>
-    <mergeCell ref="G1:L1"/>
-    <mergeCell ref="A4:F5"/>
-    <mergeCell ref="A6:F6"/>
-    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="A3:B3"/>
+    <mergeCell ref="G2:H2"/>
+    <mergeCell ref="G3:H3"/>
+    <mergeCell ref="M2:N2"/>
+    <mergeCell ref="M3:N3"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Test Cases.xlsx
+++ b/Test Cases.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
   <workbookPr hidePivotFieldList="1"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://endresshauser-my.sharepoint.com/personal/corbin_ferguson_endress_com/Documents/Thesis Work/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1623" documentId="11_AD4DB114E441178AC67DF4D41ED1D894683EDF27" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F6880D38-75ED-44FD-ABA6-68371B1CE8AA}"/>
+  <xr:revisionPtr revIDLastSave="1627" documentId="11_AD4DB114E441178AC67DF4D41ED1D894683EDF27" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{361B8735-BBF4-43CD-ABC6-232ECC75B30E}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="25440" windowHeight="15270" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-4485" windowWidth="25440" windowHeight="15270" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tests" sheetId="7" r:id="rId1"/>
@@ -22,8 +22,9 @@
   </sheets>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="19" r:id="rId7"/>
+    <pivotCache cacheId="0" r:id="rId7"/>
   </pivotCaches>
+  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -44,7 +45,7 @@
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
   <metadataTypes count="1">
     <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
   </metadataTypes>
@@ -66,7 +67,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="523" uniqueCount="190">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="523" uniqueCount="191">
   <si>
     <t>Step</t>
   </si>
@@ -670,9 +671,6 @@
     <t>"Cancel" button press</t>
   </si>
   <si>
-    <t>"Select Element" button pressed</t>
-  </si>
-  <si>
     <t>open type select window</t>
   </si>
   <si>
@@ -866,6 +864,12 @@
   </si>
   <si>
     <t>Test Priority: Low</t>
+  </si>
+  <si>
+    <t>Select Quantity</t>
+  </si>
+  <si>
+    <t>"Create Element" button pressed</t>
   </si>
 </sst>
 </file>
@@ -941,96 +945,58 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="42">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" pivotButton="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1222,6 +1188,18 @@
           </c:extLst>
         </c:dLbl>
       </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="1"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+      </c:pivotFmt>
     </c:pivotFmts>
     <c:plotArea>
       <c:layout/>
@@ -1253,6 +1231,11 @@
               </a:ln>
               <a:effectLst/>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000001-6965-4BB0-963B-D0828DC189BE}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:cat>
             <c:strRef>
@@ -2061,7 +2044,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{271A9901-5E04-4A3B-B526-FF91A8F26FEF}" name="PivotTable1" cacheId="19" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="2">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{271A9901-5E04-4A3B-B526-FF91A8F26FEF}" name="PivotTable1" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="2">
   <location ref="H1:I3" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="1">
     <pivotField axis="axisRow" dataField="1" showAll="0">
@@ -2091,11 +2074,23 @@
   <dataFields count="1">
     <dataField name="Count of Test Status" fld="0" subtotal="count" baseField="0" baseItem="0"/>
   </dataFields>
-  <chartFormats count="1">
+  <chartFormats count="2">
     <chartFormat chart="0" format="0" series="1">
       <pivotArea type="data" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="0" format="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="0" count="1" selected="0">
             <x v="0"/>
           </reference>
         </references>
@@ -2396,45 +2391,45 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F8512478-31DB-4352-AB46-996C676231F3}">
   <dimension ref="A1:I16"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="10.36328125" customWidth="1"/>
-    <col min="2" max="2" width="34.1796875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="16.1796875" style="13" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="18.36328125" hidden="1" customWidth="1"/>
-    <col min="5" max="5" width="13.453125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="16.1796875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.42578125" customWidth="1"/>
+    <col min="2" max="2" width="34.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="16.140625" style="6" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="18.42578125" hidden="1" customWidth="1"/>
+    <col min="5" max="5" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="16.140625" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="18" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
+        <v>158</v>
+      </c>
+      <c r="B1" t="s">
         <v>159</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" s="6" t="s">
         <v>160</v>
       </c>
-      <c r="C1" s="13" t="s">
-        <v>161</v>
-      </c>
       <c r="D1" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="E1" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="G1">
         <f>COUNTIF(TestMaster[Test Status], "Not Implemented")</f>
         <v>15</v>
       </c>
-      <c r="H1" s="14" t="s">
-        <v>171</v>
+      <c r="H1" s="7" t="s">
+        <v>170</v>
       </c>
       <c r="I1" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.35">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2">
         <f t="shared" ref="A2:A16" si="0">ROW()-1</f>
         <v>1</v>
@@ -2443,27 +2438,27 @@
         <f t="array" ref="B2">'Element Import Testing'!A1:A1</f>
         <v>Import Select Redundant Name</v>
       </c>
-      <c r="C2" s="13" t="s">
-        <v>165</v>
+      <c r="C2" s="6" t="s">
+        <v>164</v>
       </c>
       <c r="D2" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="E2" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="G2">
         <f>COUNTIF(TestMaster[Test Status], "Pass")</f>
         <v>0</v>
       </c>
-      <c r="H2" s="15" t="s">
-        <v>165</v>
-      </c>
-      <c r="I2" s="12">
+      <c r="H2" s="8" t="s">
+        <v>164</v>
+      </c>
+      <c r="I2">
         <v>17</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3">
         <f t="shared" si="0"/>
         <v>2</v>
@@ -2472,27 +2467,27 @@
         <f t="array" ref="B3">'Element Creation Testing'!A1:A1</f>
         <v>Element Quantity Creation</v>
       </c>
-      <c r="C3" s="13" t="s">
+      <c r="C3" s="6" t="s">
+        <v>164</v>
+      </c>
+      <c r="D3" t="s">
         <v>165</v>
       </c>
-      <c r="D3" t="s">
-        <v>166</v>
-      </c>
       <c r="E3" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="G3">
         <f>COUNTIF(TestMaster[Test Status], "Fail")</f>
         <v>0</v>
       </c>
-      <c r="H3" s="15" t="s">
-        <v>172</v>
-      </c>
-      <c r="I3" s="12">
+      <c r="H3" s="8" t="s">
+        <v>171</v>
+      </c>
+      <c r="I3">
         <v>17</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4">
         <f t="shared" si="0"/>
         <v>3</v>
@@ -2501,18 +2496,18 @@
         <f t="array" ref="B4">'Element Creation Testing'!G1:G1</f>
         <v>Nameless Module Creation</v>
       </c>
-      <c r="C4" s="13" t="s">
-        <v>165</v>
+      <c r="C4" s="6" t="s">
+        <v>164</v>
       </c>
       <c r="E4" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="G4">
         <f>COUNTIF(TestMaster[Test Status], "Not Run")</f>
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5">
         <f t="shared" si="0"/>
         <v>4</v>
@@ -2521,14 +2516,14 @@
         <f t="array" ref="B5">'Element Creation Testing'!M1:M1</f>
         <v>Redundant Element Creation</v>
       </c>
-      <c r="C5" s="13" t="s">
-        <v>165</v>
+      <c r="C5" s="6" t="s">
+        <v>164</v>
       </c>
       <c r="E5" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.35">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6">
         <f t="shared" si="0"/>
         <v>5</v>
@@ -2537,14 +2532,14 @@
         <f>'Element Modification Testing'!A1</f>
         <v>No Element to Modify</v>
       </c>
-      <c r="C6" s="13" t="s">
-        <v>165</v>
+      <c r="C6" s="6" t="s">
+        <v>164</v>
       </c>
       <c r="E6" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.35">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7">
         <f t="shared" si="0"/>
         <v>6</v>
@@ -2553,14 +2548,14 @@
         <f>'Element Modification Testing'!G1</f>
         <v>Completed Element Modification</v>
       </c>
-      <c r="C7" s="13" t="s">
-        <v>165</v>
+      <c r="C7" s="6" t="s">
+        <v>164</v>
       </c>
       <c r="E7" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.35">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8">
         <f t="shared" si="0"/>
         <v>7</v>
@@ -2569,14 +2564,14 @@
         <f>'Element Modification Testing'!M1</f>
         <v>Modify into Redundant Element Name</v>
       </c>
-      <c r="C8" s="13" t="s">
-        <v>165</v>
+      <c r="C8" s="6" t="s">
+        <v>164</v>
       </c>
       <c r="E8" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.35">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9">
         <f t="shared" si="0"/>
         <v>8</v>
@@ -2585,14 +2580,14 @@
         <f>'Element Deletion Testing'!A1</f>
         <v>Delete No Element Type</v>
       </c>
-      <c r="C9" s="13" t="s">
-        <v>165</v>
+      <c r="C9" s="6" t="s">
+        <v>164</v>
       </c>
       <c r="E9" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.35">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10">
         <f t="shared" si="0"/>
         <v>9</v>
@@ -2601,14 +2596,14 @@
         <f>'Element Deletion Testing'!G1</f>
         <v>Delete Element Found</v>
       </c>
-      <c r="C10" s="13" t="s">
-        <v>165</v>
+      <c r="C10" s="6" t="s">
+        <v>164</v>
       </c>
       <c r="E10" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.35">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11">
         <f t="shared" si="0"/>
         <v>10</v>
@@ -2617,14 +2612,14 @@
         <f>'Element Deletion Testing'!M1</f>
         <v>Delete Module by Port</v>
       </c>
-      <c r="C11" s="13" t="s">
-        <v>165</v>
+      <c r="C11" s="6" t="s">
+        <v>164</v>
       </c>
       <c r="E11" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.35">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12">
         <f t="shared" si="0"/>
         <v>11</v>
@@ -2633,14 +2628,14 @@
         <f>'File Manipulation Testing'!A1</f>
         <v>New File Creation</v>
       </c>
-      <c r="C12" s="13" t="s">
-        <v>165</v>
+      <c r="C12" s="6" t="s">
+        <v>164</v>
       </c>
       <c r="E12" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.35">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13">
         <f t="shared" si="0"/>
         <v>12</v>
@@ -2649,14 +2644,14 @@
         <f>'File Manipulation Testing'!G1</f>
         <v>Save File</v>
       </c>
-      <c r="C13" s="13" t="s">
-        <v>165</v>
+      <c r="C13" s="6" t="s">
+        <v>164</v>
       </c>
       <c r="E13" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.35">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A14">
         <f t="shared" si="0"/>
         <v>13</v>
@@ -2665,14 +2660,14 @@
         <f>'File Manipulation Testing'!M1</f>
         <v>Load File</v>
       </c>
-      <c r="C14" s="13" t="s">
-        <v>165</v>
+      <c r="C14" s="6" t="s">
+        <v>164</v>
       </c>
       <c r="E14" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.35">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A15">
         <f t="shared" si="0"/>
         <v>14</v>
@@ -2681,43 +2676,31 @@
         <f>'File Manipulation Testing'!S1</f>
         <v>Validate File</v>
       </c>
-      <c r="C15" s="13" t="s">
-        <v>165</v>
+      <c r="C15" s="6" t="s">
+        <v>164</v>
       </c>
       <c r="E15" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.35">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A16">
         <f t="shared" si="0"/>
         <v>15</v>
       </c>
-      <c r="B16" s="12" t="str">
+      <c r="B16" t="str">
         <f>'File Manipulation Testing'!Y1</f>
         <v>Exit</v>
       </c>
-      <c r="C16" s="13" t="s">
-        <v>165</v>
+      <c r="C16" s="6" t="s">
+        <v>164</v>
       </c>
       <c r="E16" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
-  <conditionalFormatting sqref="C17:C1048576">
-    <cfRule type="colorScale" priority="5">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
   <conditionalFormatting sqref="C1:C1048576">
     <cfRule type="containsText" dxfId="3" priority="1" operator="containsText" text="Not Run">
       <formula>NOT(ISERROR(SEARCH("Not Run",C1)))</formula>
@@ -2730,6 +2713,18 @@
     </cfRule>
     <cfRule type="containsText" dxfId="0" priority="4" operator="containsText" text="Not Implemented">
       <formula>NOT(ISERROR(SEARCH("Not Implemented",C1)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C17:C1048576">
+    <cfRule type="colorScale" priority="5">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="2">
@@ -2754,394 +2749,372 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B60DAC1D-2E28-4DF7-A44B-A179A310D91E}">
   <dimension ref="A1:F25"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="6.36328125" customWidth="1"/>
-    <col min="2" max="2" width="22.90625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="48.81640625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="56.7265625" style="3" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="18.36328125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="16.1796875" style="23" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="6.42578125" customWidth="1"/>
+    <col min="2" max="2" width="22.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="48.85546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="56.7109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="18.42578125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="16.140625" style="9" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A1" s="17" t="s">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1" s="16" t="s">
         <v>13</v>
       </c>
-      <c r="B1" s="17"/>
-      <c r="C1" s="17"/>
-      <c r="D1" s="17"/>
-      <c r="E1" s="17"/>
-      <c r="F1" s="24"/>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A2" s="17" t="s">
+      <c r="B1" s="16"/>
+      <c r="C1" s="16"/>
+      <c r="D1" s="16"/>
+      <c r="E1" s="16"/>
+      <c r="F1" s="17"/>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2" s="16" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="17"/>
-      <c r="C2" s="18">
+      <c r="B2" s="16"/>
+      <c r="C2" s="8">
         <f>IFERROR(_xlfn.XLOOKUP(A1, TestMaster[Test Name], TestMaster[Test ID], "ID not found"), "")</f>
         <v>1</v>
       </c>
-      <c r="D2" s="19"/>
-      <c r="E2" s="20" t="s">
+      <c r="E2" t="s">
         <v>4</v>
       </c>
-      <c r="F2" s="21"/>
-    </row>
-    <row r="3" spans="1:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="17" t="s">
-        <v>188</v>
-      </c>
-      <c r="B3" s="17"/>
-      <c r="C3" s="22" t="str">
+    </row>
+    <row r="3" spans="1:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="16" t="s">
+        <v>187</v>
+      </c>
+      <c r="B3" s="16"/>
+      <c r="C3" s="10" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(A1, TestMaster[Test Name], TestMaster[Test Priority], "Priority not found"), "")</f>
         <v>Medium</v>
       </c>
-      <c r="D3" s="19"/>
-      <c r="E3" s="20" t="s">
+      <c r="E3" t="s">
         <v>5</v>
       </c>
-      <c r="F3" s="23" t="str">
+      <c r="F3" s="9" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(A1, TestMaster[Test Name], TestMaster[Test Status], "Status not found"), "")</f>
         <v>Not Implemented</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A4" s="17" t="s">
-        <v>185</v>
-      </c>
-      <c r="B4" s="17"/>
-      <c r="C4" s="17"/>
-      <c r="D4" s="17"/>
-      <c r="E4" s="17"/>
-      <c r="F4" s="24"/>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A5" s="17"/>
-      <c r="B5" s="17"/>
-      <c r="C5" s="17"/>
-      <c r="D5" s="17"/>
-      <c r="E5" s="17"/>
-      <c r="F5" s="24"/>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A6" s="17" t="s">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" s="16" t="s">
+        <v>184</v>
+      </c>
+      <c r="B4" s="16"/>
+      <c r="C4" s="16"/>
+      <c r="D4" s="16"/>
+      <c r="E4" s="16"/>
+      <c r="F4" s="17"/>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" s="16"/>
+      <c r="B5" s="16"/>
+      <c r="C5" s="16"/>
+      <c r="D5" s="16"/>
+      <c r="E5" s="16"/>
+      <c r="F5" s="17"/>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" s="16" t="s">
         <v>7</v>
       </c>
-      <c r="B6" s="17"/>
-      <c r="C6" s="17"/>
-      <c r="D6" s="17"/>
-      <c r="E6" s="17"/>
-      <c r="F6" s="24"/>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A7" s="25" t="s">
+      <c r="B6" s="16"/>
+      <c r="C6" s="16"/>
+      <c r="D6" s="16"/>
+      <c r="E6" s="16"/>
+      <c r="F6" s="17"/>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B7" s="25" t="s">
+      <c r="B7" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C7" s="25" t="s">
+      <c r="C7" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="D7" s="26" t="s">
+      <c r="D7" s="11" t="s">
         <v>1</v>
       </c>
-      <c r="E7" s="25" t="s">
+      <c r="E7" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="F7" s="27" t="s">
+      <c r="F7" s="12" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="8" spans="1:6" s="11" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="28">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A8">
         <v>1</v>
       </c>
-      <c r="B8" s="28" t="s">
+      <c r="B8" t="s">
+        <v>175</v>
+      </c>
+      <c r="C8" t="s">
         <v>176</v>
       </c>
-      <c r="C8" s="28" t="s">
+      <c r="D8" s="2" t="s">
         <v>177</v>
       </c>
-      <c r="D8" s="29" t="s">
-        <v>178</v>
-      </c>
-      <c r="E8" s="28"/>
-      <c r="F8" s="30"/>
-    </row>
-    <row r="9" spans="1:6" ht="29" x14ac:dyDescent="0.35">
-      <c r="A9" s="34">
+    </row>
+    <row r="9" spans="1:6" ht="45" x14ac:dyDescent="0.25">
+      <c r="A9" s="5">
         <f>A8+1</f>
         <v>2</v>
       </c>
-      <c r="B9" s="31" t="s">
+      <c r="B9" s="4" t="s">
+        <v>173</v>
+      </c>
+      <c r="C9" s="4" t="s">
         <v>174</v>
       </c>
-      <c r="C9" s="31" t="s">
-        <v>175</v>
-      </c>
-      <c r="D9" s="31" t="s">
-        <v>125</v>
-      </c>
-      <c r="E9" s="32"/>
-    </row>
-    <row r="10" spans="1:6" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A10" s="34">
+      <c r="D9" s="4" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+      <c r="A10" s="5">
         <f>A9+1</f>
         <v>3</v>
       </c>
-      <c r="B10" s="31" t="s">
+      <c r="B10" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="D10" s="4" t="s">
         <v>126</v>
       </c>
-      <c r="C10" s="33" t="s">
-        <v>141</v>
-      </c>
-      <c r="D10" s="31" t="s">
-        <v>127</v>
-      </c>
-      <c r="E10" s="32"/>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A11" s="34">
+    </row>
+    <row r="11" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+      <c r="A11" s="5">
         <f t="shared" ref="A11:A25" si="0">A10+1</f>
         <v>4</v>
       </c>
-      <c r="B11" s="31" t="s">
-        <v>179</v>
-      </c>
-      <c r="C11" s="31" t="s">
-        <v>142</v>
-      </c>
-      <c r="D11" s="31" t="s">
-        <v>187</v>
-      </c>
-      <c r="E11" s="32"/>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A12" s="34">
+      <c r="B11" s="4" t="s">
+        <v>178</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="D11" s="4" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A12" s="5">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="B12" s="31" t="s">
+      <c r="B12" s="4" t="s">
+        <v>179</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="D12" s="2" t="s">
         <v>180</v>
       </c>
-      <c r="C12" s="31" t="s">
-        <v>28</v>
-      </c>
-      <c r="D12" s="19" t="s">
-        <v>181</v>
-      </c>
-      <c r="E12" s="32"/>
-    </row>
-    <row r="13" spans="1:6" ht="29" x14ac:dyDescent="0.35">
-      <c r="A13" s="34">
+    </row>
+    <row r="13" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+      <c r="A13" s="5">
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
-      <c r="B13" s="31" t="s">
+      <c r="B13" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="D13" s="4" t="s">
         <v>126</v>
       </c>
-      <c r="C13" s="33" t="s">
-        <v>141</v>
-      </c>
-      <c r="D13" s="31" t="s">
-        <v>127</v>
-      </c>
-      <c r="E13" s="32"/>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A14" s="34">
+    </row>
+    <row r="14" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+      <c r="A14" s="5">
         <f t="shared" si="0"/>
         <v>7</v>
       </c>
-      <c r="B14" s="31" t="s">
-        <v>179</v>
-      </c>
-      <c r="C14" s="31" t="s">
-        <v>142</v>
-      </c>
-      <c r="D14" s="31" t="s">
-        <v>183</v>
-      </c>
-      <c r="E14" s="32"/>
-    </row>
-    <row r="15" spans="1:6" ht="29" x14ac:dyDescent="0.35">
-      <c r="A15" s="34">
+      <c r="B14" s="4" t="s">
+        <v>178</v>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="D14" s="4" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+      <c r="A15" s="5">
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
-      <c r="B15" s="32" t="s">
+      <c r="B15" t="s">
         <v>107</v>
       </c>
-      <c r="C15" s="32" t="s">
+      <c r="C15" t="s">
         <v>111</v>
       </c>
-      <c r="D15" s="19" t="s">
-        <v>182</v>
-      </c>
-      <c r="E15" s="32"/>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A16" s="34">
+      <c r="D15" s="2" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A16" s="5">
         <f t="shared" si="0"/>
         <v>9</v>
       </c>
-      <c r="B16" s="31" t="s">
+      <c r="B16" s="4" t="s">
+        <v>179</v>
+      </c>
+      <c r="C16" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="D16" s="2" t="s">
         <v>180</v>
       </c>
-      <c r="C16" s="31" t="s">
-        <v>28</v>
-      </c>
-      <c r="D16" s="19" t="s">
-        <v>181</v>
-      </c>
-      <c r="E16" s="32"/>
-    </row>
-    <row r="17" spans="1:5" ht="29" x14ac:dyDescent="0.35">
-      <c r="A17" s="34">
+    </row>
+    <row r="17" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+      <c r="A17" s="5">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="B17" s="31" t="s">
+      <c r="B17" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="C17" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="D17" s="4" t="s">
         <v>126</v>
       </c>
-      <c r="C17" s="33" t="s">
-        <v>141</v>
-      </c>
-      <c r="D17" s="31" t="s">
-        <v>127</v>
-      </c>
-      <c r="E17" s="32"/>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A18" s="34">
+    </row>
+    <row r="18" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+      <c r="A18" s="5">
         <f t="shared" si="0"/>
         <v>11</v>
       </c>
-      <c r="B18" s="31" t="s">
-        <v>179</v>
-      </c>
-      <c r="C18" s="31" t="s">
-        <v>142</v>
-      </c>
-      <c r="D18" s="31" t="s">
-        <v>129</v>
-      </c>
-      <c r="E18" s="32"/>
-    </row>
-    <row r="19" spans="1:5" ht="29" x14ac:dyDescent="0.35">
-      <c r="A19" s="34">
+      <c r="B18" s="4" t="s">
+        <v>178</v>
+      </c>
+      <c r="C18" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="D18" s="4" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A19" s="5">
         <f t="shared" si="0"/>
         <v>12</v>
       </c>
-      <c r="B19" s="32" t="s">
+      <c r="B19" t="s">
         <v>107</v>
       </c>
-      <c r="C19" s="32" t="s">
+      <c r="C19" t="s">
         <v>123</v>
       </c>
-      <c r="D19" s="19" t="s">
-        <v>153</v>
-      </c>
-      <c r="E19" s="32"/>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A20" s="34">
+      <c r="D19" s="2" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A20" s="5">
         <f t="shared" si="0"/>
         <v>13</v>
       </c>
-      <c r="B20" s="31" t="s">
+      <c r="B20" s="4" t="s">
+        <v>179</v>
+      </c>
+      <c r="C20" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="D20" s="2" t="s">
         <v>180</v>
       </c>
-      <c r="C20" s="31" t="s">
-        <v>28</v>
-      </c>
-      <c r="D20" s="19" t="s">
-        <v>181</v>
-      </c>
-      <c r="E20" s="32"/>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A21" s="34">
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A21" s="5">
         <f t="shared" si="0"/>
         <v>14</v>
       </c>
-      <c r="B21" s="32" t="s">
+      <c r="B21" t="s">
         <v>107</v>
       </c>
-      <c r="C21" s="32" t="s">
+      <c r="C21" t="s">
         <v>109</v>
       </c>
-      <c r="D21" s="19" t="s">
-        <v>157</v>
-      </c>
-      <c r="E21" s="32"/>
-    </row>
-    <row r="22" spans="1:5" ht="29" x14ac:dyDescent="0.35">
-      <c r="A22" s="34">
+      <c r="D21" s="2" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A22" s="5">
         <f t="shared" si="0"/>
         <v>15</v>
       </c>
-      <c r="B22" s="32" t="s">
+      <c r="B22" t="s">
         <v>112</v>
       </c>
-      <c r="C22" s="31" t="s">
-        <v>186</v>
-      </c>
-      <c r="D22" s="19" t="s">
+      <c r="C22" s="4" t="s">
+        <v>185</v>
+      </c>
+      <c r="D22" s="2" t="s">
         <v>110</v>
       </c>
-      <c r="E22" s="32"/>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A23" s="34">
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A23" s="5">
         <f t="shared" si="0"/>
         <v>16</v>
       </c>
-      <c r="B23" s="32" t="s">
+      <c r="B23" t="s">
         <v>107</v>
       </c>
-      <c r="C23" s="32" t="s">
+      <c r="C23" t="s">
         <v>109</v>
       </c>
-      <c r="D23" s="19" t="s">
-        <v>157</v>
-      </c>
-      <c r="E23" s="32"/>
-    </row>
-    <row r="24" spans="1:5" ht="29" x14ac:dyDescent="0.35">
-      <c r="A24" s="34">
+      <c r="D23" s="2" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A24" s="5">
         <f t="shared" si="0"/>
         <v>17</v>
       </c>
-      <c r="B24" s="32" t="s">
+      <c r="B24" t="s">
         <v>113</v>
       </c>
-      <c r="C24" s="32" t="s">
+      <c r="C24" t="s">
         <v>114</v>
       </c>
-      <c r="D24" s="19" t="s">
-        <v>158</v>
-      </c>
-      <c r="E24" s="32"/>
-    </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A25" s="34">
+      <c r="D24" s="2" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A25" s="5">
         <f t="shared" si="0"/>
         <v>18</v>
       </c>
-      <c r="B25" s="31" t="s">
-        <v>180</v>
-      </c>
-      <c r="C25" s="31" t="s">
-        <v>184</v>
-      </c>
-      <c r="D25" s="19" t="s">
+      <c r="B25" s="4" t="s">
+        <v>179</v>
+      </c>
+      <c r="C25" s="4" t="s">
+        <v>183</v>
+      </c>
+      <c r="D25" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="E25" s="32"/>
     </row>
   </sheetData>
   <mergeCells count="5">
@@ -3158,637 +3131,588 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CA0AB6AA-BAF4-4C64-96FE-66D32370F298}">
   <dimension ref="A1:R21"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="5" style="10" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="34.453125" style="10" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="24.90625" style="10" customWidth="1"/>
-    <col min="4" max="4" width="35.54296875" style="10" customWidth="1"/>
-    <col min="5" max="5" width="18.36328125" style="10" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="16.1796875" style="35" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="5" style="10" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="29.1796875" style="10" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="24.08984375" style="10" customWidth="1"/>
-    <col min="10" max="10" width="24" style="10" customWidth="1"/>
-    <col min="11" max="11" width="18.36328125" style="10" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="16.1796875" style="35" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="5" style="10" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="29.1796875" style="10" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="25.6328125" style="10" customWidth="1"/>
-    <col min="16" max="16" width="23.90625" style="10" customWidth="1"/>
-    <col min="17" max="17" width="18.36328125" style="10" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="16.1796875" style="10" bestFit="1" customWidth="1"/>
-    <col min="19" max="16384" width="8.7265625" style="10"/>
+    <col min="1" max="1" width="5" style="5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="34.42578125" style="5" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="24.85546875" style="5" customWidth="1"/>
+    <col min="4" max="4" width="35.5703125" style="5" customWidth="1"/>
+    <col min="5" max="5" width="18.42578125" style="5" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="16.140625" style="13" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="5" style="5" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="29.140625" style="5" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="24.140625" style="5" customWidth="1"/>
+    <col min="10" max="10" width="24" style="5" customWidth="1"/>
+    <col min="11" max="11" width="18.42578125" style="5" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="16.140625" style="13" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="5" style="5" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="29.140625" style="5" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="25.5703125" style="5" customWidth="1"/>
+    <col min="16" max="16" width="23.85546875" style="5" customWidth="1"/>
+    <col min="17" max="17" width="18.42578125" style="5" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="16.140625" style="5" bestFit="1" customWidth="1"/>
+    <col min="19" max="16384" width="8.7109375" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="17" t="s">
+    <row r="1" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="16" t="s">
         <v>14</v>
       </c>
-      <c r="B1" s="17"/>
-      <c r="C1" s="17"/>
-      <c r="D1" s="17"/>
-      <c r="E1" s="17"/>
-      <c r="F1" s="24"/>
-      <c r="G1" s="17" t="s">
+      <c r="B1" s="16"/>
+      <c r="C1" s="16"/>
+      <c r="D1" s="16"/>
+      <c r="E1" s="16"/>
+      <c r="F1" s="17"/>
+      <c r="G1" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="H1" s="17"/>
-      <c r="I1" s="17"/>
-      <c r="J1" s="17"/>
-      <c r="K1" s="17"/>
-      <c r="L1" s="17"/>
-      <c r="M1" s="17" t="s">
-        <v>162</v>
-      </c>
-      <c r="N1" s="17"/>
-      <c r="O1" s="17"/>
-      <c r="P1" s="17"/>
-      <c r="Q1" s="17"/>
-      <c r="R1" s="17"/>
-    </row>
-    <row r="2" spans="1:18" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="17" t="s">
+      <c r="H1" s="16"/>
+      <c r="I1" s="16"/>
+      <c r="J1" s="16"/>
+      <c r="K1" s="16"/>
+      <c r="L1" s="16"/>
+      <c r="M1" s="16" t="s">
+        <v>161</v>
+      </c>
+      <c r="N1" s="16"/>
+      <c r="O1" s="16"/>
+      <c r="P1" s="16"/>
+      <c r="Q1" s="16"/>
+      <c r="R1" s="16"/>
+    </row>
+    <row r="2" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="16" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="17"/>
-      <c r="C2" s="20">
+      <c r="B2" s="16"/>
+      <c r="C2">
         <f>IFERROR(_xlfn.XLOOKUP(A1, TestMaster[Test Name], TestMaster[Test ID], "ID not found"), "")</f>
         <v>2</v>
       </c>
-      <c r="D2" s="34"/>
-      <c r="E2" s="20" t="s">
+      <c r="D2" s="5"/>
+      <c r="E2" t="s">
         <v>4</v>
       </c>
-      <c r="F2" s="21"/>
-      <c r="G2" s="17" t="s">
+      <c r="F2" s="9"/>
+      <c r="G2" s="16" t="s">
         <v>3</v>
       </c>
-      <c r="H2" s="17"/>
-      <c r="I2" s="20">
+      <c r="H2" s="16"/>
+      <c r="I2">
         <f>IFERROR(_xlfn.XLOOKUP(G1, TestMaster[Test Name], TestMaster[Test ID], "ID not found"), "")</f>
         <v>3</v>
       </c>
-      <c r="J2" s="34"/>
-      <c r="K2" s="20" t="s">
+      <c r="J2" s="5"/>
+      <c r="K2" t="s">
         <v>4</v>
       </c>
-      <c r="L2" s="21"/>
-      <c r="M2" s="17" t="s">
+      <c r="L2" s="9"/>
+      <c r="M2" s="16" t="s">
         <v>3</v>
       </c>
-      <c r="N2" s="17"/>
-      <c r="O2" s="20">
+      <c r="N2" s="16"/>
+      <c r="O2">
         <f>IFERROR(_xlfn.XLOOKUP(M1, TestMaster[Test Name], TestMaster[Test ID], "ID not found"), "")</f>
         <v>4</v>
       </c>
-      <c r="P2" s="34"/>
-      <c r="Q2" s="20" t="s">
+      <c r="P2" s="5"/>
+      <c r="Q2" t="s">
         <v>4</v>
       </c>
-      <c r="R2" s="20"/>
-    </row>
-    <row r="3" spans="1:18" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="17" t="s">
-        <v>188</v>
-      </c>
-      <c r="B3" s="17"/>
-      <c r="C3" s="20" t="str">
+    </row>
+    <row r="3" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="16" t="s">
+        <v>187</v>
+      </c>
+      <c r="B3" s="16"/>
+      <c r="C3" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(A1, TestMaster[Test Name], TestMaster[Test Priority], "Priority not found"), "")</f>
         <v>High</v>
       </c>
-      <c r="D3" s="34"/>
-      <c r="E3" s="20" t="s">
+      <c r="D3" s="5"/>
+      <c r="E3" t="s">
         <v>5</v>
       </c>
-      <c r="F3" s="21" t="str">
+      <c r="F3" s="9" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(A1, TestMaster[Test Name], TestMaster[Test Status], "Status not found"), "")</f>
         <v>Not Implemented</v>
       </c>
-      <c r="G3" s="17" t="s">
-        <v>188</v>
-      </c>
-      <c r="H3" s="17"/>
-      <c r="I3" s="20" t="str">
+      <c r="G3" s="16" t="s">
+        <v>187</v>
+      </c>
+      <c r="H3" s="16"/>
+      <c r="I3" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(G1, TestMaster[Test Name], TestMaster[Test Priority], "Priority not found"), "")</f>
         <v>Medium</v>
       </c>
-      <c r="J3" s="34"/>
-      <c r="K3" s="20" t="s">
+      <c r="J3" s="5"/>
+      <c r="K3" t="s">
         <v>5</v>
       </c>
-      <c r="L3" s="21" t="str">
+      <c r="L3" s="9" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(G1, TestMaster[Test Name], TestMaster[Test Status], "Status not found"), "")</f>
         <v>Not Implemented</v>
       </c>
-      <c r="M3" s="17" t="s">
-        <v>188</v>
-      </c>
-      <c r="N3" s="17"/>
-      <c r="O3" s="20" t="str">
+      <c r="M3" s="16" t="s">
+        <v>187</v>
+      </c>
+      <c r="N3" s="16"/>
+      <c r="O3" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(M1, TestMaster[Test Name], TestMaster[Test Priority], "Priority not found"), "")</f>
         <v>Low</v>
       </c>
-      <c r="P3" s="34"/>
-      <c r="Q3" s="20" t="s">
+      <c r="P3" s="5"/>
+      <c r="Q3" t="s">
         <v>5</v>
       </c>
-      <c r="R3" s="20" t="str">
+      <c r="R3" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(M1, TestMaster[Test Name], TestMaster[Test Status], "Status not found"), "")</f>
         <v>Not Implemented</v>
       </c>
     </row>
-    <row r="4" spans="1:18" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="17" t="s">
+    <row r="4" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="16" t="s">
         <v>6</v>
       </c>
-      <c r="B4" s="17"/>
-      <c r="C4" s="17"/>
-      <c r="D4" s="17"/>
-      <c r="E4" s="17"/>
-      <c r="F4" s="24"/>
-      <c r="G4" s="17" t="s">
+      <c r="B4" s="16"/>
+      <c r="C4" s="16"/>
+      <c r="D4" s="16"/>
+      <c r="E4" s="16"/>
+      <c r="F4" s="17"/>
+      <c r="G4" s="16" t="s">
         <v>6</v>
       </c>
-      <c r="H4" s="17"/>
-      <c r="I4" s="17"/>
-      <c r="J4" s="17"/>
-      <c r="K4" s="17"/>
-      <c r="L4" s="17"/>
-      <c r="M4" s="17" t="s">
+      <c r="H4" s="16"/>
+      <c r="I4" s="16"/>
+      <c r="J4" s="16"/>
+      <c r="K4" s="16"/>
+      <c r="L4" s="16"/>
+      <c r="M4" s="16" t="s">
         <v>6</v>
       </c>
-      <c r="N4" s="17"/>
-      <c r="O4" s="17"/>
-      <c r="P4" s="17"/>
-      <c r="Q4" s="17"/>
-      <c r="R4" s="17"/>
-    </row>
-    <row r="5" spans="1:18" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="17"/>
-      <c r="B5" s="17"/>
-      <c r="C5" s="17"/>
-      <c r="D5" s="17"/>
-      <c r="E5" s="17"/>
-      <c r="F5" s="24"/>
-      <c r="G5" s="17"/>
-      <c r="H5" s="17"/>
-      <c r="I5" s="17"/>
-      <c r="J5" s="17"/>
-      <c r="K5" s="17"/>
-      <c r="L5" s="17"/>
-      <c r="M5" s="17"/>
-      <c r="N5" s="17"/>
-      <c r="O5" s="17"/>
-      <c r="P5" s="17"/>
-      <c r="Q5" s="17"/>
-      <c r="R5" s="17"/>
-    </row>
-    <row r="6" spans="1:18" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="17" t="s">
+      <c r="N4" s="16"/>
+      <c r="O4" s="16"/>
+      <c r="P4" s="16"/>
+      <c r="Q4" s="16"/>
+      <c r="R4" s="16"/>
+    </row>
+    <row r="5" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="16"/>
+      <c r="B5" s="16"/>
+      <c r="C5" s="16"/>
+      <c r="D5" s="16"/>
+      <c r="E5" s="16"/>
+      <c r="F5" s="17"/>
+      <c r="G5" s="16"/>
+      <c r="H5" s="16"/>
+      <c r="I5" s="16"/>
+      <c r="J5" s="16"/>
+      <c r="K5" s="16"/>
+      <c r="L5" s="16"/>
+      <c r="M5" s="16"/>
+      <c r="N5" s="16"/>
+      <c r="O5" s="16"/>
+      <c r="P5" s="16"/>
+      <c r="Q5" s="16"/>
+      <c r="R5" s="16"/>
+    </row>
+    <row r="6" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="16" t="s">
         <v>7</v>
       </c>
-      <c r="B6" s="17"/>
-      <c r="C6" s="17"/>
-      <c r="D6" s="17"/>
-      <c r="E6" s="17"/>
-      <c r="F6" s="24"/>
-      <c r="G6" s="17" t="s">
+      <c r="B6" s="16"/>
+      <c r="C6" s="16"/>
+      <c r="D6" s="16"/>
+      <c r="E6" s="16"/>
+      <c r="F6" s="17"/>
+      <c r="G6" s="16" t="s">
         <v>7</v>
       </c>
-      <c r="H6" s="17"/>
-      <c r="I6" s="17"/>
-      <c r="J6" s="17"/>
-      <c r="K6" s="17"/>
-      <c r="L6" s="17"/>
-      <c r="M6" s="17" t="s">
+      <c r="H6" s="16"/>
+      <c r="I6" s="16"/>
+      <c r="J6" s="16"/>
+      <c r="K6" s="16"/>
+      <c r="L6" s="16"/>
+      <c r="M6" s="16" t="s">
         <v>7</v>
       </c>
-      <c r="N6" s="17"/>
-      <c r="O6" s="17"/>
-      <c r="P6" s="17"/>
-      <c r="Q6" s="17"/>
-      <c r="R6" s="17"/>
-    </row>
-    <row r="7" spans="1:18" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="25" t="s">
+      <c r="N6" s="16"/>
+      <c r="O6" s="16"/>
+      <c r="P6" s="16"/>
+      <c r="Q6" s="16"/>
+      <c r="R6" s="16"/>
+    </row>
+    <row r="7" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B7" s="25" t="s">
+      <c r="B7" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C7" s="25" t="s">
+      <c r="C7" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="D7" s="25" t="s">
+      <c r="D7" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="E7" s="25" t="s">
+      <c r="E7" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="F7" s="27" t="s">
+      <c r="F7" s="12" t="s">
         <v>2</v>
       </c>
-      <c r="G7" s="25" t="s">
+      <c r="G7" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="H7" s="36" t="s">
+      <c r="H7" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="I7" s="25" t="s">
+      <c r="I7" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="J7" s="25" t="s">
+      <c r="J7" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="K7" s="25" t="s">
+      <c r="K7" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="L7" s="27" t="s">
+      <c r="L7" s="12" t="s">
         <v>2</v>
       </c>
-      <c r="M7" s="25" t="s">
+      <c r="M7" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="N7" s="36" t="s">
+      <c r="N7" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="O7" s="25" t="s">
+      <c r="O7" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="P7" s="25" t="s">
+      <c r="P7" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="Q7" s="25" t="s">
+      <c r="Q7" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="R7" s="25" t="s">
+      <c r="R7" s="1" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A8" s="34">
+    <row r="8" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A8" s="5">
         <v>1</v>
       </c>
-      <c r="B8" s="31" t="s">
+      <c r="B8" s="4" t="s">
+        <v>190</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="D8" s="4" t="s">
         <v>124</v>
       </c>
-      <c r="C8" s="31" t="s">
+      <c r="G8" s="5">
+        <v>1</v>
+      </c>
+      <c r="H8" s="5" t="s">
+        <v>190</v>
+      </c>
+      <c r="I8" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="D8" s="31" t="s">
+      <c r="J8" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="M8" s="5">
+        <v>1</v>
+      </c>
+      <c r="N8" s="5" t="s">
+        <v>190</v>
+      </c>
+      <c r="O8" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="P8" s="4" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18" ht="45" x14ac:dyDescent="0.25">
+      <c r="A9" s="5">
+        <v>2</v>
+      </c>
+      <c r="B9" s="4" t="s">
         <v>125</v>
       </c>
-      <c r="E8" s="34"/>
-      <c r="G8" s="34">
-        <v>1</v>
-      </c>
-      <c r="H8" s="34" t="s">
-        <v>124</v>
-      </c>
-      <c r="I8" s="31" t="s">
-        <v>27</v>
-      </c>
-      <c r="J8" s="31" t="s">
+      <c r="C9" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="G9" s="5">
+        <v>2</v>
+      </c>
+      <c r="H9" s="5" t="s">
         <v>125</v>
       </c>
-      <c r="K8" s="34"/>
-      <c r="M8" s="34">
-        <v>1</v>
-      </c>
-      <c r="N8" s="34" t="s">
-        <v>124</v>
-      </c>
-      <c r="O8" s="31" t="s">
-        <v>27</v>
-      </c>
-      <c r="P8" s="31" t="s">
+      <c r="I9" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="J9" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="M9" s="5">
+        <v>2</v>
+      </c>
+      <c r="N9" s="5" t="s">
         <v>125</v>
       </c>
-      <c r="Q8" s="34"/>
-      <c r="R8" s="34"/>
-    </row>
-    <row r="9" spans="1:18" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A9" s="34">
-        <v>2</v>
-      </c>
-      <c r="B9" s="31" t="s">
+      <c r="O9" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="P9" s="4" t="s">
         <v>126</v>
       </c>
-      <c r="C9" s="33" t="s">
+    </row>
+    <row r="10" spans="1:18" ht="45" x14ac:dyDescent="0.25">
+      <c r="A10" s="5">
+        <v>3</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>127</v>
+      </c>
+      <c r="C10" s="4" t="s">
         <v>141</v>
       </c>
-      <c r="D9" s="31" t="s">
+      <c r="D10" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="G10" s="5">
+        <v>3</v>
+      </c>
+      <c r="H10" s="5" t="s">
         <v>127</v>
       </c>
-      <c r="E9" s="34"/>
-      <c r="G9" s="34">
-        <v>2</v>
-      </c>
-      <c r="H9" s="34" t="s">
-        <v>126</v>
-      </c>
-      <c r="I9" s="33" t="s">
-        <v>139</v>
-      </c>
-      <c r="J9" s="31" t="s">
-        <v>140</v>
-      </c>
-      <c r="K9" s="34"/>
-      <c r="M9" s="34">
-        <v>2</v>
-      </c>
-      <c r="N9" s="34" t="s">
-        <v>126</v>
-      </c>
-      <c r="O9" s="33" t="s">
+      <c r="I10" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="J10" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="M10" s="5">
+        <v>3</v>
+      </c>
+      <c r="N10" s="5" t="s">
+        <v>127</v>
+      </c>
+      <c r="O10" s="4" t="s">
         <v>141</v>
       </c>
-      <c r="P9" s="31" t="s">
-        <v>127</v>
-      </c>
-      <c r="Q9" s="34"/>
-      <c r="R9" s="34"/>
-    </row>
-    <row r="10" spans="1:18" ht="29" x14ac:dyDescent="0.35">
-      <c r="A10" s="34">
-        <v>3</v>
-      </c>
-      <c r="B10" s="31" t="s">
+      <c r="P10" s="4" t="s">
         <v>128</v>
       </c>
-      <c r="C10" s="31" t="s">
-        <v>142</v>
-      </c>
-      <c r="D10" s="31" t="s">
+    </row>
+    <row r="11" spans="1:18" ht="45" x14ac:dyDescent="0.25">
+      <c r="A11" s="5">
+        <v>4</v>
+      </c>
+      <c r="B11" s="4" t="s">
         <v>129</v>
       </c>
-      <c r="E10" s="34"/>
-      <c r="G10" s="34">
-        <v>3</v>
-      </c>
-      <c r="H10" s="34" t="s">
-        <v>128</v>
-      </c>
-      <c r="I10" s="31" t="s">
+      <c r="C11" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="D11" s="4" t="s">
+        <v>131</v>
+      </c>
+      <c r="G11" s="5">
+        <v>4</v>
+      </c>
+      <c r="H11" s="5" t="s">
+        <v>189</v>
+      </c>
+      <c r="I11" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="J11" s="4" t="s">
         <v>143</v>
       </c>
-      <c r="J10" s="31" t="s">
+      <c r="M11" s="5">
+        <v>4</v>
+      </c>
+      <c r="N11" s="5" t="s">
         <v>129</v>
       </c>
-      <c r="K10" s="34"/>
-      <c r="M10" s="34">
-        <v>3</v>
-      </c>
-      <c r="N10" s="34" t="s">
-        <v>128</v>
-      </c>
-      <c r="O10" s="31" t="s">
-        <v>142</v>
-      </c>
-      <c r="P10" s="31" t="s">
-        <v>129</v>
-      </c>
-      <c r="Q10" s="34"/>
-      <c r="R10" s="34"/>
-    </row>
-    <row r="11" spans="1:18" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A11" s="34">
-        <v>4</v>
-      </c>
-      <c r="B11" s="31" t="s">
-        <v>130</v>
-      </c>
-      <c r="C11" s="31" t="s">
+      <c r="O11" s="4" t="s">
+        <v>150</v>
+      </c>
+      <c r="P11" s="4" t="s">
         <v>131</v>
       </c>
-      <c r="D11" s="31" t="s">
+    </row>
+    <row r="12" spans="1:18" ht="45" x14ac:dyDescent="0.25">
+      <c r="A12" s="5">
+        <v>5</v>
+      </c>
+      <c r="B12" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>134</v>
+      </c>
+      <c r="D12" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="M12" s="5">
+        <v>5</v>
+      </c>
+      <c r="N12" s="5" t="s">
+        <v>144</v>
+      </c>
+      <c r="O12" s="4" t="s">
+        <v>145</v>
+      </c>
+      <c r="P12" s="4" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="13" spans="1:18" ht="45" x14ac:dyDescent="0.25">
+      <c r="A13" s="5">
+        <v>6</v>
+      </c>
+      <c r="B13" s="4" t="s">
+        <v>135</v>
+      </c>
+      <c r="C13" s="4" t="s">
         <v>132</v>
       </c>
-      <c r="E11" s="34"/>
-      <c r="G11" s="34">
-        <v>4</v>
-      </c>
-      <c r="H11" s="34" t="s">
-        <v>130</v>
-      </c>
-      <c r="I11" s="31" t="s">
-        <v>131</v>
-      </c>
-      <c r="J11" s="31" t="s">
-        <v>144</v>
-      </c>
-      <c r="K11" s="34"/>
-      <c r="M11" s="34">
-        <v>4</v>
-      </c>
-      <c r="N11" s="34" t="s">
-        <v>130</v>
-      </c>
-      <c r="O11" s="31" t="s">
+      <c r="D13" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="M13" s="5">
+        <v>6</v>
+      </c>
+      <c r="N13" s="5" t="s">
+        <v>146</v>
+      </c>
+      <c r="O13" s="4" t="s">
+        <v>145</v>
+      </c>
+      <c r="P13" s="4" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="M14">
+        <v>7</v>
+      </c>
+      <c r="N14" t="s">
+        <v>107</v>
+      </c>
+      <c r="O14" t="s">
+        <v>111</v>
+      </c>
+      <c r="P14" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="15" spans="1:18" ht="45" x14ac:dyDescent="0.25">
+      <c r="M15" s="5">
+        <v>8</v>
+      </c>
+      <c r="N15" s="5" t="s">
         <v>151</v>
       </c>
-      <c r="P11" s="31" t="s">
-        <v>132</v>
-      </c>
-      <c r="Q11" s="34"/>
-      <c r="R11" s="34"/>
-    </row>
-    <row r="12" spans="1:18" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A12" s="34">
-        <v>5</v>
-      </c>
-      <c r="B12" s="31" t="s">
-        <v>134</v>
-      </c>
-      <c r="C12" s="31" t="s">
-        <v>135</v>
-      </c>
-      <c r="D12" s="31" t="s">
-        <v>137</v>
-      </c>
-      <c r="E12" s="34"/>
-      <c r="G12" s="34"/>
-      <c r="H12" s="34"/>
-      <c r="I12" s="34"/>
-      <c r="J12" s="34"/>
-      <c r="K12" s="34"/>
-      <c r="M12" s="34">
-        <v>5</v>
-      </c>
-      <c r="N12" s="34" t="s">
+      <c r="O15" s="5" t="s">
         <v>145</v>
       </c>
-      <c r="O12" s="31" t="s">
-        <v>146</v>
-      </c>
-      <c r="P12" s="31" t="s">
+      <c r="P15" s="4" t="s">
         <v>148</v>
       </c>
-      <c r="Q12" s="34"/>
-      <c r="R12" s="34"/>
-    </row>
-    <row r="13" spans="1:18" ht="29" x14ac:dyDescent="0.35">
-      <c r="A13" s="34">
-        <v>6</v>
-      </c>
-      <c r="B13" s="31" t="s">
-        <v>136</v>
-      </c>
-      <c r="C13" s="31" t="s">
-        <v>133</v>
-      </c>
-      <c r="D13" s="31" t="s">
-        <v>138</v>
-      </c>
-      <c r="E13" s="34"/>
-      <c r="G13" s="34"/>
-      <c r="H13" s="34"/>
-      <c r="I13" s="34"/>
-      <c r="J13" s="34"/>
-      <c r="K13" s="34"/>
-      <c r="M13" s="34">
-        <v>6</v>
-      </c>
-      <c r="N13" s="34" t="s">
-        <v>147</v>
-      </c>
-      <c r="O13" s="31" t="s">
-        <v>146</v>
-      </c>
-      <c r="P13" s="31" t="s">
-        <v>149</v>
-      </c>
-      <c r="Q13" s="34"/>
-      <c r="R13" s="34"/>
-    </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="M14" s="32">
-        <v>7</v>
-      </c>
-      <c r="N14" s="20" t="s">
+    </row>
+    <row r="16" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="M16">
+        <v>9</v>
+      </c>
+      <c r="N16" t="s">
         <v>107</v>
       </c>
-      <c r="O14" s="32" t="s">
-        <v>111</v>
-      </c>
-      <c r="P14" s="32" t="s">
-        <v>150</v>
-      </c>
-      <c r="Q14" s="34"/>
-      <c r="R14" s="34"/>
-    </row>
-    <row r="15" spans="1:18" ht="29" x14ac:dyDescent="0.35">
-      <c r="M15" s="34">
-        <v>8</v>
-      </c>
-      <c r="N15" s="34" t="s">
+      <c r="O16" t="s">
+        <v>123</v>
+      </c>
+      <c r="P16" t="s">
         <v>152</v>
       </c>
-      <c r="O15" s="34" t="s">
-        <v>146</v>
-      </c>
-      <c r="P15" s="31" t="s">
-        <v>149</v>
-      </c>
-      <c r="Q15" s="34"/>
-      <c r="R15" s="34"/>
-    </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="M16" s="32">
-        <v>9</v>
-      </c>
-      <c r="N16" s="20" t="s">
+    </row>
+    <row r="17" spans="13:16" ht="45" x14ac:dyDescent="0.25">
+      <c r="M17">
+        <v>10</v>
+      </c>
+      <c r="N17" s="5" t="s">
+        <v>153</v>
+      </c>
+      <c r="O17" s="5" t="s">
+        <v>145</v>
+      </c>
+      <c r="P17" s="4" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="18" spans="13:16" x14ac:dyDescent="0.25">
+      <c r="M18" s="5">
+        <v>11</v>
+      </c>
+      <c r="N18" t="s">
         <v>107</v>
       </c>
-      <c r="O16" s="32" t="s">
-        <v>123</v>
-      </c>
-      <c r="P16" s="32" t="s">
-        <v>153</v>
-      </c>
-      <c r="Q16" s="34"/>
-      <c r="R16" s="34"/>
-    </row>
-    <row r="17" spans="13:18" ht="29" x14ac:dyDescent="0.35">
-      <c r="M17" s="32">
-        <v>10</v>
-      </c>
-      <c r="N17" s="34" t="s">
-        <v>154</v>
-      </c>
-      <c r="O17" s="34" t="s">
-        <v>146</v>
-      </c>
-      <c r="P17" s="31" t="s">
-        <v>149</v>
-      </c>
-      <c r="Q17" s="34"/>
-      <c r="R17" s="34"/>
-    </row>
-    <row r="18" spans="13:18" x14ac:dyDescent="0.35">
-      <c r="M18" s="34">
-        <v>11</v>
-      </c>
-      <c r="N18" s="20" t="s">
+      <c r="O18" t="s">
+        <v>109</v>
+      </c>
+      <c r="P18" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="19" spans="13:16" x14ac:dyDescent="0.25">
+      <c r="M19">
+        <v>12</v>
+      </c>
+      <c r="N19" t="s">
+        <v>112</v>
+      </c>
+      <c r="O19" t="s">
+        <v>145</v>
+      </c>
+      <c r="P19" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="20" spans="13:16" x14ac:dyDescent="0.25">
+      <c r="M20" s="5">
+        <v>13</v>
+      </c>
+      <c r="N20" t="s">
         <v>107</v>
       </c>
-      <c r="O18" s="32" t="s">
+      <c r="O20" t="s">
         <v>109</v>
       </c>
-      <c r="P18" s="32" t="s">
+      <c r="P20" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="21" spans="13:16" x14ac:dyDescent="0.25">
+      <c r="M21">
+        <v>14</v>
+      </c>
+      <c r="N21" t="s">
+        <v>113</v>
+      </c>
+      <c r="O21" t="s">
+        <v>114</v>
+      </c>
+      <c r="P21" t="s">
         <v>157</v>
       </c>
-      <c r="Q18" s="34"/>
-      <c r="R18" s="34"/>
-    </row>
-    <row r="19" spans="13:18" x14ac:dyDescent="0.35">
-      <c r="M19" s="32">
-        <v>12</v>
-      </c>
-      <c r="N19" s="20" t="s">
-        <v>112</v>
-      </c>
-      <c r="O19" s="32" t="s">
-        <v>146</v>
-      </c>
-      <c r="P19" s="32" t="s">
-        <v>110</v>
-      </c>
-      <c r="Q19" s="34"/>
-      <c r="R19" s="34"/>
-    </row>
-    <row r="20" spans="13:18" x14ac:dyDescent="0.35">
-      <c r="M20" s="34">
-        <v>13</v>
-      </c>
-      <c r="N20" s="20" t="s">
-        <v>107</v>
-      </c>
-      <c r="O20" s="32" t="s">
-        <v>109</v>
-      </c>
-      <c r="P20" s="32" t="s">
-        <v>157</v>
-      </c>
-      <c r="Q20" s="34"/>
-      <c r="R20" s="34"/>
-    </row>
-    <row r="21" spans="13:18" x14ac:dyDescent="0.35">
-      <c r="M21" s="32">
-        <v>14</v>
-      </c>
-      <c r="N21" s="20" t="s">
-        <v>113</v>
-      </c>
-      <c r="O21" s="32" t="s">
-        <v>114</v>
-      </c>
-      <c r="P21" s="32" t="s">
-        <v>158</v>
-      </c>
-      <c r="Q21" s="34"/>
-      <c r="R21" s="34"/>
     </row>
   </sheetData>
   <mergeCells count="15">
@@ -3815,694 +3739,641 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{31B60B4E-CDD0-4CEE-BA63-4F898D2F5023}">
   <dimension ref="A1:R25"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5" customWidth="1"/>
-    <col min="2" max="2" width="22.1796875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.54296875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="31.1796875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="18.36328125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="16.1796875" style="23" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="22.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.5703125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="31.140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="18.42578125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="16.140625" style="9" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="5" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="30.36328125" customWidth="1"/>
-    <col min="9" max="9" width="27.54296875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="30.26953125" customWidth="1"/>
-    <col min="11" max="11" width="18.36328125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="16.1796875" style="23" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="30.42578125" customWidth="1"/>
+    <col min="9" max="9" width="27.5703125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="30.28515625" customWidth="1"/>
+    <col min="11" max="11" width="18.42578125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="16.140625" style="9" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="5" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="35.453125" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="20.54296875" customWidth="1"/>
-    <col min="16" max="16" width="31.1796875" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="18.36328125" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="16.1796875" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="35.42578125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="20.5703125" customWidth="1"/>
+    <col min="16" max="16" width="31.140625" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="18.42578125" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="16.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A1" s="17" t="s">
+    <row r="1" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A1" s="16" t="s">
         <v>16</v>
       </c>
-      <c r="B1" s="17"/>
-      <c r="C1" s="17"/>
-      <c r="D1" s="17"/>
-      <c r="E1" s="17"/>
-      <c r="F1" s="24"/>
-      <c r="G1" s="16" t="s">
+      <c r="B1" s="16"/>
+      <c r="C1" s="16"/>
+      <c r="D1" s="16"/>
+      <c r="E1" s="16"/>
+      <c r="F1" s="17"/>
+      <c r="G1" s="18" t="s">
         <v>17</v>
       </c>
-      <c r="H1" s="17"/>
-      <c r="I1" s="17"/>
-      <c r="J1" s="17"/>
-      <c r="K1" s="17"/>
-      <c r="L1" s="24"/>
-      <c r="M1" s="17" t="s">
+      <c r="H1" s="16"/>
+      <c r="I1" s="16"/>
+      <c r="J1" s="16"/>
+      <c r="K1" s="16"/>
+      <c r="L1" s="17"/>
+      <c r="M1" s="16" t="s">
         <v>116</v>
       </c>
-      <c r="N1" s="17"/>
-      <c r="O1" s="17"/>
-      <c r="P1" s="17"/>
-      <c r="Q1" s="17"/>
-      <c r="R1" s="17"/>
-    </row>
-    <row r="2" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A2" s="17" t="s">
+      <c r="N1" s="16"/>
+      <c r="O1" s="16"/>
+      <c r="P1" s="16"/>
+      <c r="Q1" s="16"/>
+      <c r="R1" s="16"/>
+    </row>
+    <row r="2" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A2" s="16" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="17"/>
-      <c r="C2" s="18">
+      <c r="B2" s="16"/>
+      <c r="C2" s="8">
         <f>IFERROR(_xlfn.XLOOKUP(A1, TestMaster[Test Name], TestMaster[Test ID], "ID not found"), "")</f>
         <v>5</v>
       </c>
-      <c r="D2" s="32"/>
-      <c r="E2" s="20" t="s">
+      <c r="E2" t="s">
         <v>4</v>
       </c>
-      <c r="F2" s="21"/>
-      <c r="G2" s="17" t="s">
+      <c r="G2" s="16" t="s">
         <v>3</v>
       </c>
-      <c r="H2" s="17"/>
-      <c r="I2" s="18">
+      <c r="H2" s="16"/>
+      <c r="I2" s="8">
         <f>IFERROR(_xlfn.XLOOKUP(G1, TestMaster[Test Name], TestMaster[Test ID], "ID not found"), "")</f>
         <v>6</v>
       </c>
-      <c r="J2" s="32"/>
-      <c r="K2" s="20" t="s">
+      <c r="K2" t="s">
         <v>4</v>
       </c>
-      <c r="L2" s="21"/>
-      <c r="M2" s="17" t="s">
+      <c r="M2" s="16" t="s">
         <v>3</v>
       </c>
-      <c r="N2" s="17"/>
-      <c r="O2" s="37">
+      <c r="N2" s="16"/>
+      <c r="O2" s="14">
         <f>IFERROR(_xlfn.XLOOKUP(M1, TestMaster[Test Name], TestMaster[Test ID], "ID not found"), "")</f>
         <v>7</v>
       </c>
-      <c r="P2" s="32"/>
-      <c r="Q2" s="20" t="s">
+      <c r="Q2" t="s">
         <v>4</v>
       </c>
-      <c r="R2" s="20"/>
-    </row>
-    <row r="3" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A3" s="17" t="s">
-        <v>188</v>
-      </c>
-      <c r="B3" s="17"/>
-      <c r="C3" s="18" t="str">
+    </row>
+    <row r="3" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A3" s="16" t="s">
+        <v>187</v>
+      </c>
+      <c r="B3" s="16"/>
+      <c r="C3" s="8" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(A1, TestMaster[Test Name], TestMaster[Test Priority], "Priority not found"), "")</f>
         <v>Medium</v>
       </c>
-      <c r="D3" s="32"/>
-      <c r="E3" s="20" t="s">
+      <c r="E3" t="s">
         <v>5</v>
       </c>
-      <c r="F3" s="21" t="str">
+      <c r="F3" s="9" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(A1, TestMaster[Test Name], TestMaster[Test Status], "Status not found"), "")</f>
         <v>Not Implemented</v>
       </c>
-      <c r="G3" s="17" t="s">
-        <v>188</v>
-      </c>
-      <c r="H3" s="17"/>
-      <c r="I3" s="18" t="str">
+      <c r="G3" s="16" t="s">
+        <v>187</v>
+      </c>
+      <c r="H3" s="16"/>
+      <c r="I3" s="8" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(G1, TestMaster[Test Name], TestMaster[Test Priority], "Priority not found"), "")</f>
         <v>Medium</v>
       </c>
-      <c r="J3" s="32"/>
-      <c r="K3" s="20" t="s">
+      <c r="K3" t="s">
         <v>5</v>
       </c>
-      <c r="L3" s="21" t="str">
+      <c r="L3" s="9" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(G1, TestMaster[Test Name], TestMaster[Test Status], "Status not found"), "")</f>
         <v>Not Implemented</v>
       </c>
-      <c r="M3" s="17" t="s">
-        <v>188</v>
-      </c>
-      <c r="N3" s="17"/>
-      <c r="O3" s="37" t="str">
+      <c r="M3" s="16" t="s">
+        <v>187</v>
+      </c>
+      <c r="N3" s="16"/>
+      <c r="O3" s="14" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(M1, TestMaster[Test Name], TestMaster[Test Priority], "Priority not found"), "")</f>
         <v>Low</v>
       </c>
-      <c r="P3" s="32"/>
-      <c r="Q3" s="20" t="s">
+      <c r="Q3" t="s">
         <v>5</v>
       </c>
-      <c r="R3" s="20" t="str">
+      <c r="R3" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(M1, TestMaster[Test Name], TestMaster[Test Status], "Status not found"), "")</f>
         <v>Not Implemented</v>
       </c>
     </row>
-    <row r="4" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A4" s="17" t="s">
+    <row r="4" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A4" s="16" t="s">
         <v>6</v>
       </c>
-      <c r="B4" s="17"/>
-      <c r="C4" s="17"/>
-      <c r="D4" s="17"/>
-      <c r="E4" s="17"/>
-      <c r="F4" s="24"/>
-      <c r="G4" s="16" t="s">
+      <c r="B4" s="16"/>
+      <c r="C4" s="16"/>
+      <c r="D4" s="16"/>
+      <c r="E4" s="16"/>
+      <c r="F4" s="17"/>
+      <c r="G4" s="18" t="s">
         <v>6</v>
       </c>
-      <c r="H4" s="17"/>
-      <c r="I4" s="17"/>
-      <c r="J4" s="17"/>
-      <c r="K4" s="17"/>
-      <c r="L4" s="24"/>
-      <c r="M4" s="17" t="s">
+      <c r="H4" s="16"/>
+      <c r="I4" s="16"/>
+      <c r="J4" s="16"/>
+      <c r="K4" s="16"/>
+      <c r="L4" s="17"/>
+      <c r="M4" s="16" t="s">
         <v>6</v>
       </c>
-      <c r="N4" s="17"/>
-      <c r="O4" s="17"/>
-      <c r="P4" s="17"/>
-      <c r="Q4" s="17"/>
-      <c r="R4" s="17"/>
-    </row>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A5" s="17"/>
-      <c r="B5" s="17"/>
-      <c r="C5" s="17"/>
-      <c r="D5" s="17"/>
-      <c r="E5" s="17"/>
-      <c r="F5" s="24"/>
-      <c r="G5" s="16"/>
-      <c r="H5" s="17"/>
-      <c r="I5" s="17"/>
-      <c r="J5" s="17"/>
-      <c r="K5" s="17"/>
-      <c r="L5" s="24"/>
-      <c r="M5" s="17"/>
-      <c r="N5" s="17"/>
-      <c r="O5" s="17"/>
-      <c r="P5" s="17"/>
-      <c r="Q5" s="17"/>
-      <c r="R5" s="17"/>
-    </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A6" s="17" t="s">
+      <c r="N4" s="16"/>
+      <c r="O4" s="16"/>
+      <c r="P4" s="16"/>
+      <c r="Q4" s="16"/>
+      <c r="R4" s="16"/>
+    </row>
+    <row r="5" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A5" s="16"/>
+      <c r="B5" s="16"/>
+      <c r="C5" s="16"/>
+      <c r="D5" s="16"/>
+      <c r="E5" s="16"/>
+      <c r="F5" s="17"/>
+      <c r="G5" s="18"/>
+      <c r="H5" s="16"/>
+      <c r="I5" s="16"/>
+      <c r="J5" s="16"/>
+      <c r="K5" s="16"/>
+      <c r="L5" s="17"/>
+      <c r="M5" s="16"/>
+      <c r="N5" s="16"/>
+      <c r="O5" s="16"/>
+      <c r="P5" s="16"/>
+      <c r="Q5" s="16"/>
+      <c r="R5" s="16"/>
+    </row>
+    <row r="6" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A6" s="16" t="s">
         <v>7</v>
       </c>
-      <c r="B6" s="17"/>
-      <c r="C6" s="17"/>
-      <c r="D6" s="17"/>
-      <c r="E6" s="17"/>
-      <c r="F6" s="24"/>
-      <c r="G6" s="16" t="s">
+      <c r="B6" s="16"/>
+      <c r="C6" s="16"/>
+      <c r="D6" s="16"/>
+      <c r="E6" s="16"/>
+      <c r="F6" s="17"/>
+      <c r="G6" s="18" t="s">
         <v>7</v>
       </c>
-      <c r="H6" s="17"/>
-      <c r="I6" s="17"/>
-      <c r="J6" s="17"/>
-      <c r="K6" s="17"/>
-      <c r="L6" s="24"/>
-      <c r="M6" s="17" t="s">
+      <c r="H6" s="16"/>
+      <c r="I6" s="16"/>
+      <c r="J6" s="16"/>
+      <c r="K6" s="16"/>
+      <c r="L6" s="17"/>
+      <c r="M6" s="16" t="s">
         <v>7</v>
       </c>
-      <c r="N6" s="17"/>
-      <c r="O6" s="17"/>
-      <c r="P6" s="17"/>
-      <c r="Q6" s="17"/>
-      <c r="R6" s="17"/>
-    </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A7" s="25" t="s">
+      <c r="N6" s="16"/>
+      <c r="O6" s="16"/>
+      <c r="P6" s="16"/>
+      <c r="Q6" s="16"/>
+      <c r="R6" s="16"/>
+    </row>
+    <row r="7" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A7" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B7" s="25" t="s">
+      <c r="B7" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C7" s="25" t="s">
+      <c r="C7" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="D7" s="25" t="s">
+      <c r="D7" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="E7" s="25" t="s">
+      <c r="E7" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="F7" s="27" t="s">
+      <c r="F7" s="12" t="s">
         <v>2</v>
       </c>
-      <c r="G7" s="25" t="s">
+      <c r="G7" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="H7" s="25" t="s">
+      <c r="H7" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="I7" s="25" t="s">
+      <c r="I7" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="J7" s="25" t="s">
+      <c r="J7" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="K7" s="25" t="s">
+      <c r="K7" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="L7" s="27" t="s">
+      <c r="L7" s="12" t="s">
         <v>2</v>
       </c>
-      <c r="M7" s="25" t="s">
+      <c r="M7" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="N7" s="25" t="s">
+      <c r="N7" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="O7" s="25" t="s">
+      <c r="O7" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="P7" s="25" t="s">
+      <c r="P7" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="Q7" s="25" t="s">
+      <c r="Q7" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="R7" s="25" t="s">
+      <c r="R7" s="1" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="8" spans="1:18" s="4" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="34">
+    <row r="8" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A8" s="5">
         <v>1</v>
       </c>
-      <c r="B8" s="34" t="s">
+      <c r="B8" s="5" t="s">
         <v>88</v>
       </c>
-      <c r="C8" s="34" t="s">
+      <c r="C8" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="D8" s="34" t="s">
+      <c r="D8" s="5" t="s">
         <v>74</v>
       </c>
-      <c r="E8" s="20"/>
-      <c r="F8" s="21"/>
-      <c r="G8" s="20">
+      <c r="G8">
         <v>1</v>
       </c>
-      <c r="H8" s="34" t="s">
+      <c r="H8" s="5" t="s">
         <v>88</v>
       </c>
-      <c r="I8" s="34" t="s">
+      <c r="I8" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="J8" s="34" t="s">
+      <c r="J8" s="5" t="s">
         <v>77</v>
       </c>
-      <c r="K8" s="20"/>
-      <c r="L8" s="21"/>
-      <c r="M8" s="20">
+      <c r="M8">
         <v>1</v>
       </c>
-      <c r="N8" s="34" t="s">
+      <c r="N8" s="5" t="s">
         <v>88</v>
       </c>
-      <c r="O8" s="34" t="s">
+      <c r="O8" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="P8" s="34" t="s">
+      <c r="P8" s="5" t="s">
         <v>77</v>
       </c>
-      <c r="Q8" s="20"/>
-      <c r="R8" s="20"/>
-    </row>
-    <row r="9" spans="1:18" s="4" customFormat="1" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A9" s="34">
+    </row>
+    <row r="9" spans="1:18" ht="45" x14ac:dyDescent="0.25">
+      <c r="A9" s="5">
         <v>2</v>
       </c>
-      <c r="B9" s="34" t="s">
+      <c r="B9" s="5" t="s">
         <v>56</v>
       </c>
-      <c r="C9" s="34" t="s">
+      <c r="C9" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="D9" s="34" t="s">
+      <c r="D9" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="E9" s="20"/>
-      <c r="F9" s="21"/>
-      <c r="G9" s="20">
+      <c r="G9">
         <v>2</v>
       </c>
-      <c r="H9" s="31" t="s">
+      <c r="H9" s="4" t="s">
         <v>75</v>
       </c>
-      <c r="I9" s="31" t="s">
+      <c r="I9" s="4" t="s">
         <v>78</v>
       </c>
-      <c r="J9" s="31" t="s">
+      <c r="J9" s="4" t="s">
         <v>80</v>
       </c>
-      <c r="K9" s="20"/>
-      <c r="L9" s="21"/>
-      <c r="M9" s="20">
+      <c r="M9">
         <v>2</v>
       </c>
-      <c r="N9" s="31" t="s">
+      <c r="N9" s="4" t="s">
         <v>75</v>
       </c>
-      <c r="O9" s="31" t="s">
+      <c r="O9" s="4" t="s">
         <v>78</v>
       </c>
-      <c r="P9" s="31" t="s">
+      <c r="P9" s="4" t="s">
         <v>80</v>
       </c>
-      <c r="Q9" s="20"/>
-      <c r="R9" s="20"/>
-    </row>
-    <row r="10" spans="1:18" ht="29" x14ac:dyDescent="0.35">
-      <c r="G10" s="32">
+    </row>
+    <row r="10" spans="1:18" ht="45" x14ac:dyDescent="0.25">
+      <c r="G10">
         <v>3</v>
       </c>
-      <c r="H10" s="31" t="s">
+      <c r="H10" s="4" t="s">
         <v>117</v>
       </c>
-      <c r="I10" s="31" t="s">
+      <c r="I10" s="4" t="s">
         <v>100</v>
       </c>
-      <c r="J10" s="31" t="s">
+      <c r="J10" s="4" t="s">
         <v>105</v>
       </c>
-      <c r="K10" s="32"/>
-      <c r="M10" s="32">
+      <c r="M10">
         <v>3</v>
       </c>
-      <c r="N10" s="31" t="s">
+      <c r="N10" s="4" t="s">
         <v>120</v>
       </c>
-      <c r="O10" s="31" t="s">
+      <c r="O10" s="4" t="s">
         <v>100</v>
       </c>
-      <c r="P10" s="31" t="s">
+      <c r="P10" s="4" t="s">
         <v>105</v>
       </c>
-      <c r="Q10" s="32"/>
-      <c r="R10" s="32"/>
-    </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="G11" s="32">
+    </row>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="G11">
         <v>4</v>
       </c>
-      <c r="H11" s="32" t="s">
+      <c r="H11" t="s">
         <v>89</v>
       </c>
-      <c r="I11" s="32" t="s">
+      <c r="I11" t="s">
         <v>92</v>
       </c>
-      <c r="J11" s="32" t="s">
+      <c r="J11" t="s">
         <v>91</v>
       </c>
-      <c r="K11" s="32"/>
-      <c r="M11" s="32">
+      <c r="M11">
         <v>4</v>
       </c>
-      <c r="N11" s="32" t="s">
+      <c r="N11" t="s">
         <v>121</v>
       </c>
-      <c r="O11" s="32" t="s">
+      <c r="O11" t="s">
         <v>90</v>
       </c>
-      <c r="P11" s="32" t="s">
+      <c r="P11" t="s">
         <v>91</v>
       </c>
-      <c r="Q11" s="32"/>
-      <c r="R11" s="32"/>
-    </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="G12" s="32">
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="G12">
         <v>5</v>
       </c>
-      <c r="H12" s="32" t="s">
+      <c r="H12" t="s">
         <v>94</v>
       </c>
-      <c r="I12" s="32" t="s">
+      <c r="I12" t="s">
         <v>96</v>
       </c>
-      <c r="J12" s="32" t="s">
+      <c r="J12" t="s">
         <v>98</v>
       </c>
-      <c r="K12" s="32"/>
-      <c r="M12" s="32">
+      <c r="M12">
         <v>5</v>
       </c>
-      <c r="N12" s="32" t="s">
+      <c r="N12" t="s">
         <v>118</v>
       </c>
-      <c r="O12" s="32" t="s">
+      <c r="O12" t="s">
         <v>96</v>
       </c>
-      <c r="P12" s="32" t="s">
+      <c r="P12" t="s">
         <v>93</v>
       </c>
-      <c r="Q12" s="32"/>
-      <c r="R12" s="32"/>
-    </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="G13" s="32">
+    </row>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="G13">
         <v>6</v>
       </c>
-      <c r="H13" s="32" t="s">
+      <c r="H13" t="s">
         <v>95</v>
       </c>
-      <c r="I13" s="32" t="s">
+      <c r="I13" t="s">
         <v>97</v>
       </c>
-      <c r="J13" s="32" t="s">
+      <c r="J13" t="s">
         <v>99</v>
       </c>
-      <c r="K13" s="32"/>
-      <c r="M13" s="32">
+      <c r="M13">
         <v>6</v>
       </c>
-      <c r="N13" s="32" t="s">
+      <c r="N13" t="s">
         <v>107</v>
       </c>
-      <c r="O13" s="32" t="s">
+      <c r="O13" t="s">
         <v>111</v>
       </c>
-      <c r="P13" s="32" t="s">
-        <v>156</v>
-      </c>
-      <c r="Q13" s="32"/>
-      <c r="R13" s="32"/>
-    </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="G14" s="32">
+      <c r="P13" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="G14">
         <v>7</v>
       </c>
-      <c r="H14" s="32" t="s">
+      <c r="H14" t="s">
         <v>101</v>
       </c>
-      <c r="I14" s="32"/>
-      <c r="J14" s="32"/>
-      <c r="K14" s="32"/>
-      <c r="M14" s="32">
+      <c r="M14">
         <v>8</v>
       </c>
-      <c r="N14" s="32" t="s">
+      <c r="N14" t="s">
         <v>119</v>
       </c>
-      <c r="O14" s="32" t="s">
+      <c r="O14" t="s">
         <v>90</v>
       </c>
-      <c r="P14" s="32" t="s">
+      <c r="P14" t="s">
         <v>91</v>
       </c>
-      <c r="Q14" s="32"/>
-      <c r="R14" s="32"/>
-    </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="G15" s="32">
+    </row>
+    <row r="15" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="G15">
         <v>8</v>
       </c>
-      <c r="H15" s="32" t="s">
+      <c r="H15" t="s">
         <v>89</v>
       </c>
-      <c r="I15" s="32" t="s">
+      <c r="I15" t="s">
         <v>92</v>
       </c>
-      <c r="J15" s="32" t="s">
+      <c r="J15" t="s">
         <v>91</v>
       </c>
-      <c r="K15" s="32"/>
-      <c r="M15" s="32">
+      <c r="M15">
         <v>9</v>
       </c>
-      <c r="N15" s="32" t="s">
+      <c r="N15" t="s">
         <v>122</v>
       </c>
-      <c r="O15" s="32" t="s">
+      <c r="O15" t="s">
         <v>96</v>
       </c>
-      <c r="P15" s="32" t="s">
+      <c r="P15" t="s">
         <v>93</v>
       </c>
-      <c r="Q15" s="32"/>
-      <c r="R15" s="32"/>
-    </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="G16" s="32">
+    </row>
+    <row r="16" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="G16">
         <v>9</v>
       </c>
-      <c r="H16" s="32" t="s">
+      <c r="H16" t="s">
         <v>94</v>
       </c>
-      <c r="I16" s="32" t="s">
+      <c r="I16" t="s">
         <v>96</v>
       </c>
-      <c r="J16" s="32" t="s">
+      <c r="J16" t="s">
         <v>98</v>
       </c>
-      <c r="K16" s="32"/>
-      <c r="M16" s="32">
+      <c r="M16">
         <v>10</v>
       </c>
-      <c r="N16" s="32" t="s">
+      <c r="N16" t="s">
         <v>107</v>
       </c>
-      <c r="O16" s="32" t="s">
+      <c r="O16" t="s">
         <v>123</v>
       </c>
-      <c r="P16" s="32" t="s">
-        <v>155</v>
-      </c>
-      <c r="Q16" s="32"/>
-      <c r="R16" s="32"/>
-    </row>
-    <row r="17" spans="7:11" x14ac:dyDescent="0.35">
-      <c r="G17" s="32">
+      <c r="P16" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="17" spans="7:10" x14ac:dyDescent="0.25">
+      <c r="G17">
         <v>10</v>
       </c>
-      <c r="H17" s="32" t="s">
+      <c r="H17" t="s">
         <v>95</v>
       </c>
-      <c r="I17" s="32" t="s">
+      <c r="I17" t="s">
         <v>97</v>
       </c>
-      <c r="J17" s="32" t="s">
+      <c r="J17" t="s">
         <v>99</v>
       </c>
-      <c r="K17" s="32"/>
-    </row>
-    <row r="18" spans="7:11" x14ac:dyDescent="0.35">
-      <c r="G18" s="32">
+    </row>
+    <row r="18" spans="7:10" x14ac:dyDescent="0.25">
+      <c r="G18">
         <v>11</v>
       </c>
-      <c r="H18" s="32" t="s">
+      <c r="H18" t="s">
         <v>102</v>
       </c>
-      <c r="I18" s="32" t="s">
+      <c r="I18" t="s">
         <v>103</v>
       </c>
-      <c r="J18" s="32" t="s">
+      <c r="J18" t="s">
         <v>104</v>
       </c>
-      <c r="K18" s="32"/>
-    </row>
-    <row r="19" spans="7:11" x14ac:dyDescent="0.35">
-      <c r="G19" s="32">
+    </row>
+    <row r="19" spans="7:10" x14ac:dyDescent="0.25">
+      <c r="G19">
         <v>12</v>
       </c>
-      <c r="H19" s="32" t="s">
+      <c r="H19" t="s">
         <v>89</v>
       </c>
-      <c r="I19" s="32" t="s">
+      <c r="I19" t="s">
         <v>90</v>
       </c>
-      <c r="J19" s="32" t="s">
+      <c r="J19" t="s">
         <v>91</v>
       </c>
-      <c r="K19" s="32"/>
-    </row>
-    <row r="20" spans="7:11" x14ac:dyDescent="0.35">
-      <c r="G20" s="32">
+    </row>
+    <row r="20" spans="7:10" x14ac:dyDescent="0.25">
+      <c r="G20">
         <v>13</v>
       </c>
-      <c r="H20" s="32" t="s">
+      <c r="H20" t="s">
         <v>106</v>
       </c>
-      <c r="I20" s="32" t="s">
+      <c r="I20" t="s">
         <v>96</v>
       </c>
-      <c r="J20" s="32" t="s">
+      <c r="J20" t="s">
         <v>93</v>
       </c>
-      <c r="K20" s="32"/>
-    </row>
-    <row r="21" spans="7:11" x14ac:dyDescent="0.35">
-      <c r="G21" s="32">
+    </row>
+    <row r="21" spans="7:10" x14ac:dyDescent="0.25">
+      <c r="G21">
         <v>14</v>
       </c>
-      <c r="H21" s="32" t="s">
+      <c r="H21" t="s">
         <v>107</v>
       </c>
-      <c r="I21" s="32" t="s">
+      <c r="I21" t="s">
         <v>109</v>
       </c>
-      <c r="J21" s="32" t="s">
+      <c r="J21" t="s">
         <v>108</v>
       </c>
-      <c r="K21" s="32"/>
-    </row>
-    <row r="22" spans="7:11" x14ac:dyDescent="0.35">
-      <c r="G22" s="32">
+    </row>
+    <row r="22" spans="7:10" x14ac:dyDescent="0.25">
+      <c r="G22">
         <v>15</v>
       </c>
-      <c r="H22" s="32" t="s">
+      <c r="H22" t="s">
         <v>112</v>
       </c>
-      <c r="I22" s="32" t="s">
+      <c r="I22" t="s">
         <v>96</v>
       </c>
-      <c r="J22" s="32" t="s">
+      <c r="J22" t="s">
         <v>110</v>
       </c>
-      <c r="K22" s="32"/>
-    </row>
-    <row r="23" spans="7:11" x14ac:dyDescent="0.35">
-      <c r="G23" s="32">
+    </row>
+    <row r="23" spans="7:10" x14ac:dyDescent="0.25">
+      <c r="G23">
         <v>16</v>
       </c>
-      <c r="H23" s="32" t="s">
+      <c r="H23" t="s">
         <v>107</v>
       </c>
-      <c r="I23" s="32" t="s">
+      <c r="I23" t="s">
         <v>109</v>
       </c>
-      <c r="J23" s="32" t="s">
+      <c r="J23" t="s">
         <v>108</v>
       </c>
-      <c r="K23" s="32"/>
-    </row>
-    <row r="24" spans="7:11" x14ac:dyDescent="0.35">
-      <c r="G24" s="32">
+    </row>
+    <row r="24" spans="7:10" x14ac:dyDescent="0.25">
+      <c r="G24">
         <v>17</v>
       </c>
-      <c r="H24" s="32" t="s">
+      <c r="H24" t="s">
         <v>113</v>
       </c>
-      <c r="I24" s="32" t="s">
+      <c r="I24" t="s">
         <v>114</v>
       </c>
-      <c r="J24" s="32" t="s">
+      <c r="J24" t="s">
         <v>115</v>
       </c>
-      <c r="K24" s="32"/>
-    </row>
-    <row r="25" spans="7:11" x14ac:dyDescent="0.35">
-      <c r="G25" s="32">
+    </row>
+    <row r="25" spans="7:10" x14ac:dyDescent="0.25">
+      <c r="G25">
         <v>18</v>
       </c>
-      <c r="H25" s="32" t="s">
+      <c r="H25" t="s">
         <v>102</v>
       </c>
-      <c r="I25" s="32" t="s">
+      <c r="I25" t="s">
         <v>103</v>
       </c>
-      <c r="J25" s="32" t="s">
+      <c r="J25" t="s">
         <v>40</v>
       </c>
-      <c r="K25" s="32"/>
     </row>
   </sheetData>
   <mergeCells count="15">
@@ -4528,412 +4399,387 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{791F26CA-73F7-4CFD-B892-FF534C61ED87}">
-  <dimension ref="A1:S11"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:R11"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="21.90625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.54296875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="31.1796875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="18.36328125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="16.1796875" style="23" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="21.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.5703125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="31.140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="18.42578125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="16.140625" style="9" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="5" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="22.36328125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="19.7265625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="28.6328125" customWidth="1"/>
-    <col min="11" max="11" width="18.36328125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="16.1796875" style="23" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="22.42578125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="19.7109375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="28.5703125" customWidth="1"/>
+    <col min="11" max="11" width="18.42578125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="16.140625" style="9" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="5" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="22.36328125" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="22.90625" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="32.36328125" customWidth="1"/>
-    <col min="17" max="17" width="18.36328125" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="16.1796875" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="8.7265625" style="7"/>
+    <col min="14" max="14" width="22.42578125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="22.85546875" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="32.42578125" customWidth="1"/>
+    <col min="17" max="17" width="18.42578125" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="16.140625" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="8.7109375"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" x14ac:dyDescent="0.35">
-      <c r="A1" s="17" t="s">
+    <row r="1" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A1" s="16" t="s">
         <v>18</v>
       </c>
-      <c r="B1" s="17"/>
-      <c r="C1" s="17"/>
-      <c r="D1" s="17"/>
-      <c r="E1" s="17"/>
-      <c r="F1" s="24"/>
-      <c r="G1" s="16" t="s">
+      <c r="B1" s="16"/>
+      <c r="C1" s="16"/>
+      <c r="D1" s="16"/>
+      <c r="E1" s="16"/>
+      <c r="F1" s="17"/>
+      <c r="G1" s="18" t="s">
         <v>19</v>
       </c>
-      <c r="H1" s="17"/>
-      <c r="I1" s="17"/>
-      <c r="J1" s="17"/>
-      <c r="K1" s="17"/>
-      <c r="L1" s="24"/>
-      <c r="M1" s="17" t="s">
+      <c r="H1" s="16"/>
+      <c r="I1" s="16"/>
+      <c r="J1" s="16"/>
+      <c r="K1" s="16"/>
+      <c r="L1" s="17"/>
+      <c r="M1" s="16" t="s">
         <v>20</v>
       </c>
-      <c r="N1" s="17"/>
-      <c r="O1" s="17"/>
-      <c r="P1" s="17"/>
-      <c r="Q1" s="17"/>
-      <c r="R1" s="17"/>
-    </row>
-    <row r="2" spans="1:19" x14ac:dyDescent="0.35">
-      <c r="A2" s="17" t="s">
+      <c r="N1" s="16"/>
+      <c r="O1" s="16"/>
+      <c r="P1" s="16"/>
+      <c r="Q1" s="16"/>
+      <c r="R1" s="16"/>
+    </row>
+    <row r="2" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A2" s="16" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="17"/>
-      <c r="C2" s="18">
+      <c r="B2" s="16"/>
+      <c r="C2" s="8">
         <f>IFERROR(_xlfn.XLOOKUP(A1, TestMaster[Test Name], TestMaster[Test ID], "ID not found"), "")</f>
         <v>8</v>
       </c>
-      <c r="D2" s="32"/>
-      <c r="E2" s="20" t="s">
+      <c r="E2" t="s">
         <v>4</v>
       </c>
-      <c r="F2" s="21"/>
-      <c r="G2" s="17" t="s">
+      <c r="G2" s="16" t="s">
         <v>3</v>
       </c>
-      <c r="H2" s="17"/>
-      <c r="I2" s="18">
+      <c r="H2" s="16"/>
+      <c r="I2" s="8">
         <f>IFERROR(_xlfn.XLOOKUP(G1, TestMaster[Test Name], TestMaster[Test ID], "ID not found"), "")</f>
         <v>9</v>
       </c>
-      <c r="J2" s="32"/>
-      <c r="K2" s="20" t="s">
+      <c r="K2" t="s">
         <v>4</v>
       </c>
-      <c r="L2" s="21"/>
-      <c r="M2" s="17" t="s">
+      <c r="M2" s="16" t="s">
         <v>3</v>
       </c>
-      <c r="N2" s="17"/>
-      <c r="O2" s="18">
+      <c r="N2" s="16"/>
+      <c r="O2" s="8">
         <f>IFERROR(_xlfn.XLOOKUP(M1, TestMaster[Test Name], TestMaster[Test ID], "ID not found"), "")</f>
         <v>10</v>
       </c>
-      <c r="P2" s="32"/>
-      <c r="Q2" s="20" t="s">
+      <c r="Q2" t="s">
         <v>4</v>
       </c>
-      <c r="R2" s="20"/>
-    </row>
-    <row r="3" spans="1:19" x14ac:dyDescent="0.35">
-      <c r="A3" s="17" t="s">
-        <v>188</v>
-      </c>
-      <c r="B3" s="17"/>
-      <c r="C3" s="18" t="str">
+    </row>
+    <row r="3" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A3" s="16" t="s">
+        <v>187</v>
+      </c>
+      <c r="B3" s="16"/>
+      <c r="C3" s="8" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(A1, TestMaster[Test Name], TestMaster[Test Priority], "Priority not found"), "")</f>
         <v>Medium</v>
       </c>
-      <c r="D3" s="32"/>
-      <c r="E3" s="20" t="s">
+      <c r="E3" t="s">
         <v>5</v>
       </c>
-      <c r="F3" s="21" t="str">
+      <c r="F3" s="9" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(A1, TestMaster[Test Name], TestMaster[Test Status], "Status not found"), "")</f>
         <v>Not Implemented</v>
       </c>
-      <c r="G3" s="17" t="s">
-        <v>188</v>
-      </c>
-      <c r="H3" s="17"/>
-      <c r="I3" s="18" t="str">
+      <c r="G3" s="16" t="s">
+        <v>187</v>
+      </c>
+      <c r="H3" s="16"/>
+      <c r="I3" s="8" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(G1, TestMaster[Test Name], TestMaster[Test Priority], "Priority not found"), "")</f>
         <v>Medium</v>
       </c>
-      <c r="J3" s="32"/>
-      <c r="K3" s="20" t="s">
+      <c r="K3" t="s">
         <v>5</v>
       </c>
-      <c r="L3" s="21" t="str">
+      <c r="L3" s="9" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(G1, TestMaster[Test Name], TestMaster[Test Status], "Status not found"), "")</f>
         <v>Not Implemented</v>
       </c>
-      <c r="M3" s="17" t="s">
-        <v>188</v>
-      </c>
-      <c r="N3" s="17"/>
-      <c r="O3" s="18" t="str">
+      <c r="M3" s="16" t="s">
+        <v>187</v>
+      </c>
+      <c r="N3" s="16"/>
+      <c r="O3" s="8" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(M1, TestMaster[Test Name], TestMaster[Test Priority], "Priority not found"), "")</f>
         <v>Low</v>
       </c>
-      <c r="P3" s="32"/>
-      <c r="Q3" s="20" t="s">
+      <c r="Q3" t="s">
         <v>5</v>
       </c>
-      <c r="R3" s="20" t="str">
+      <c r="R3" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(M1, TestMaster[Test Name], TestMaster[Test Status], "Status not found"), "")</f>
         <v>Not Implemented</v>
       </c>
     </row>
-    <row r="4" spans="1:19" x14ac:dyDescent="0.35">
-      <c r="A4" s="39" t="s">
+    <row r="4" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A4" s="19" t="s">
         <v>71</v>
       </c>
-      <c r="B4" s="39"/>
-      <c r="C4" s="39"/>
-      <c r="D4" s="39"/>
-      <c r="E4" s="39"/>
-      <c r="F4" s="40"/>
-      <c r="G4" s="38" t="s">
+      <c r="B4" s="19"/>
+      <c r="C4" s="19"/>
+      <c r="D4" s="19"/>
+      <c r="E4" s="19"/>
+      <c r="F4" s="20"/>
+      <c r="G4" s="21" t="s">
         <v>6</v>
       </c>
-      <c r="H4" s="39"/>
-      <c r="I4" s="39"/>
-      <c r="J4" s="39"/>
-      <c r="K4" s="39"/>
-      <c r="L4" s="40"/>
-      <c r="M4" s="39" t="s">
+      <c r="H4" s="19"/>
+      <c r="I4" s="19"/>
+      <c r="J4" s="19"/>
+      <c r="K4" s="19"/>
+      <c r="L4" s="20"/>
+      <c r="M4" s="19" t="s">
         <v>6</v>
       </c>
-      <c r="N4" s="39"/>
-      <c r="O4" s="39"/>
-      <c r="P4" s="39"/>
-      <c r="Q4" s="39"/>
-      <c r="R4" s="39"/>
-    </row>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.35">
-      <c r="A5" s="39"/>
-      <c r="B5" s="39"/>
-      <c r="C5" s="39"/>
-      <c r="D5" s="39"/>
-      <c r="E5" s="39"/>
-      <c r="F5" s="40"/>
-      <c r="G5" s="38"/>
-      <c r="H5" s="39"/>
-      <c r="I5" s="39"/>
-      <c r="J5" s="39"/>
-      <c r="K5" s="39"/>
-      <c r="L5" s="40"/>
-      <c r="M5" s="39"/>
-      <c r="N5" s="39"/>
-      <c r="O5" s="39"/>
-      <c r="P5" s="39"/>
-      <c r="Q5" s="39"/>
-      <c r="R5" s="39"/>
-    </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.35">
-      <c r="A6" s="17" t="s">
+      <c r="N4" s="19"/>
+      <c r="O4" s="19"/>
+      <c r="P4" s="19"/>
+      <c r="Q4" s="19"/>
+      <c r="R4" s="19"/>
+    </row>
+    <row r="5" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A5" s="19"/>
+      <c r="B5" s="19"/>
+      <c r="C5" s="19"/>
+      <c r="D5" s="19"/>
+      <c r="E5" s="19"/>
+      <c r="F5" s="20"/>
+      <c r="G5" s="21"/>
+      <c r="H5" s="19"/>
+      <c r="I5" s="19"/>
+      <c r="J5" s="19"/>
+      <c r="K5" s="19"/>
+      <c r="L5" s="20"/>
+      <c r="M5" s="19"/>
+      <c r="N5" s="19"/>
+      <c r="O5" s="19"/>
+      <c r="P5" s="19"/>
+      <c r="Q5" s="19"/>
+      <c r="R5" s="19"/>
+    </row>
+    <row r="6" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A6" s="16" t="s">
         <v>72</v>
       </c>
-      <c r="B6" s="17"/>
-      <c r="C6" s="17"/>
-      <c r="D6" s="17"/>
-      <c r="E6" s="17"/>
-      <c r="F6" s="24"/>
-      <c r="G6" s="16" t="s">
+      <c r="B6" s="16"/>
+      <c r="C6" s="16"/>
+      <c r="D6" s="16"/>
+      <c r="E6" s="16"/>
+      <c r="F6" s="17"/>
+      <c r="G6" s="18" t="s">
         <v>7</v>
       </c>
-      <c r="H6" s="17"/>
-      <c r="I6" s="17"/>
-      <c r="J6" s="17"/>
-      <c r="K6" s="17"/>
-      <c r="L6" s="24"/>
-      <c r="M6" s="17" t="s">
+      <c r="H6" s="16"/>
+      <c r="I6" s="16"/>
+      <c r="J6" s="16"/>
+      <c r="K6" s="16"/>
+      <c r="L6" s="17"/>
+      <c r="M6" s="16" t="s">
         <v>7</v>
       </c>
-      <c r="N6" s="17"/>
-      <c r="O6" s="17"/>
-      <c r="P6" s="17"/>
-      <c r="Q6" s="17"/>
-      <c r="R6" s="17"/>
-    </row>
-    <row r="7" spans="1:19" x14ac:dyDescent="0.35">
-      <c r="A7" s="25" t="s">
+      <c r="N6" s="16"/>
+      <c r="O6" s="16"/>
+      <c r="P6" s="16"/>
+      <c r="Q6" s="16"/>
+      <c r="R6" s="16"/>
+    </row>
+    <row r="7" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A7" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B7" s="25" t="s">
+      <c r="B7" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C7" s="25" t="s">
+      <c r="C7" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="D7" s="25" t="s">
+      <c r="D7" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="E7" s="25" t="s">
+      <c r="E7" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="F7" s="27" t="s">
+      <c r="F7" s="12" t="s">
         <v>2</v>
       </c>
-      <c r="G7" s="25" t="s">
+      <c r="G7" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="H7" s="25" t="s">
+      <c r="H7" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="I7" s="25" t="s">
+      <c r="I7" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="J7" s="25" t="s">
+      <c r="J7" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="K7" s="25" t="s">
+      <c r="K7" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="L7" s="27" t="s">
+      <c r="L7" s="12" t="s">
         <v>2</v>
       </c>
-      <c r="M7" s="25" t="s">
+      <c r="M7" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="N7" s="25" t="s">
+      <c r="N7" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="O7" s="25" t="s">
+      <c r="O7" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="P7" s="25" t="s">
+      <c r="P7" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="Q7" s="25" t="s">
+      <c r="Q7" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="R7" s="25" t="s">
+      <c r="R7" s="1" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="8" spans="1:19" s="8" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="31">
+    <row r="8" spans="1:18" s="4" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A8" s="4">
         <v>1</v>
       </c>
-      <c r="B8" s="31" t="s">
+      <c r="B8" s="4" t="s">
         <v>73</v>
       </c>
-      <c r="C8" s="31" t="s">
+      <c r="C8" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="D8" s="31" t="s">
+      <c r="D8" s="4" t="s">
         <v>74</v>
       </c>
-      <c r="E8" s="31"/>
-      <c r="F8" s="41"/>
-      <c r="G8" s="31">
+      <c r="F8" s="15"/>
+      <c r="G8" s="4">
         <v>1</v>
       </c>
-      <c r="H8" s="31" t="s">
+      <c r="H8" s="4" t="s">
         <v>73</v>
       </c>
-      <c r="I8" s="31" t="s">
+      <c r="I8" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="J8" s="31" t="s">
+      <c r="J8" s="4" t="s">
         <v>77</v>
       </c>
-      <c r="K8" s="31"/>
-      <c r="L8" s="41"/>
-      <c r="M8" s="31">
+      <c r="L8" s="15"/>
+      <c r="M8" s="4">
         <v>1</v>
       </c>
-      <c r="N8" s="31" t="s">
+      <c r="N8" s="4" t="s">
         <v>73</v>
       </c>
-      <c r="O8" s="31" t="s">
+      <c r="O8" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="P8" s="31" t="s">
+      <c r="P8" s="4" t="s">
         <v>77</v>
       </c>
-      <c r="Q8" s="31"/>
-      <c r="R8" s="31"/>
-      <c r="S8" s="9"/>
-    </row>
-    <row r="9" spans="1:19" s="8" customFormat="1" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A9" s="31">
+    </row>
+    <row r="9" spans="1:18" s="4" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+      <c r="A9" s="4">
         <v>2</v>
       </c>
-      <c r="B9" s="31" t="s">
+      <c r="B9" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="C9" s="31" t="s">
+      <c r="C9" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="D9" s="31" t="s">
+      <c r="D9" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="E9" s="31"/>
-      <c r="F9" s="41"/>
-      <c r="G9" s="31">
+      <c r="F9" s="15"/>
+      <c r="G9" s="4">
         <v>2</v>
       </c>
-      <c r="H9" s="31" t="s">
+      <c r="H9" s="4" t="s">
         <v>75</v>
       </c>
-      <c r="I9" s="31" t="s">
+      <c r="I9" s="4" t="s">
         <v>78</v>
       </c>
-      <c r="J9" s="31" t="s">
+      <c r="J9" s="4" t="s">
         <v>80</v>
       </c>
-      <c r="K9" s="31"/>
-      <c r="L9" s="41"/>
-      <c r="M9" s="31">
+      <c r="L9" s="15"/>
+      <c r="M9" s="4">
         <v>2</v>
       </c>
-      <c r="N9" s="31" t="s">
+      <c r="N9" s="4" t="s">
         <v>75</v>
       </c>
-      <c r="O9" s="31" t="s">
+      <c r="O9" s="4" t="s">
         <v>82</v>
       </c>
-      <c r="P9" s="31" t="s">
+      <c r="P9" s="4" t="s">
         <v>81</v>
       </c>
-      <c r="Q9" s="31"/>
-      <c r="R9" s="31"/>
-      <c r="S9" s="9"/>
-    </row>
-    <row r="10" spans="1:19" s="8" customFormat="1" ht="29" x14ac:dyDescent="0.35">
-      <c r="F10" s="41"/>
-      <c r="G10" s="31">
+    </row>
+    <row r="10" spans="1:18" s="4" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+      <c r="F10" s="15"/>
+      <c r="G10" s="4">
         <v>3</v>
       </c>
-      <c r="H10" s="31" t="s">
+      <c r="H10" s="4" t="s">
         <v>76</v>
       </c>
-      <c r="I10" s="31" t="s">
+      <c r="I10" s="4" t="s">
         <v>79</v>
       </c>
-      <c r="J10" s="31" t="s">
+      <c r="J10" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="K10" s="31"/>
-      <c r="L10" s="41"/>
-      <c r="M10" s="31">
+      <c r="L10" s="15"/>
+      <c r="M10" s="4">
         <v>3</v>
       </c>
-      <c r="N10" s="31" t="s">
+      <c r="N10" s="4" t="s">
         <v>76</v>
       </c>
-      <c r="O10" s="31" t="s">
+      <c r="O10" s="4" t="s">
         <v>79</v>
       </c>
-      <c r="P10" s="31" t="s">
+      <c r="P10" s="4" t="s">
         <v>83</v>
       </c>
-      <c r="Q10" s="31"/>
-      <c r="R10" s="31"/>
-      <c r="S10" s="9"/>
-    </row>
-    <row r="11" spans="1:19" ht="29" x14ac:dyDescent="0.35">
-      <c r="M11" s="31">
+    </row>
+    <row r="11" spans="1:18" ht="30" x14ac:dyDescent="0.25">
+      <c r="M11" s="4">
         <v>4</v>
       </c>
-      <c r="N11" s="31" t="s">
+      <c r="N11" s="4" t="s">
         <v>84</v>
       </c>
-      <c r="O11" s="31" t="s">
+      <c r="O11" s="4" t="s">
         <v>85</v>
       </c>
-      <c r="P11" s="31" t="s">
+      <c r="P11" s="4" t="s">
         <v>86</v>
       </c>
-      <c r="Q11" s="32"/>
-      <c r="R11" s="32"/>
     </row>
   </sheetData>
   <mergeCells count="15">
@@ -4959,376 +4805,367 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E4413619-C528-4B04-A1ED-B4C77CA83066}">
-  <dimension ref="A1:AD13"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:AD12"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="25.08984375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="17.54296875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="15.26953125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="18.36328125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="8.7265625" style="23"/>
+    <col min="2" max="2" width="25.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17.5703125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15.28515625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="18.42578125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="8.7109375" style="9"/>
     <col min="7" max="7" width="5" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="23.7265625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="48.81640625" customWidth="1"/>
-    <col min="10" max="10" width="17.54296875" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="18.36328125" customWidth="1"/>
-    <col min="12" max="12" width="8.7265625" style="23"/>
+    <col min="8" max="8" width="23.7109375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="48.85546875" customWidth="1"/>
+    <col min="10" max="10" width="17.5703125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="18.42578125" customWidth="1"/>
+    <col min="12" max="12" width="8.7109375" style="9"/>
     <col min="13" max="13" width="5" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="21.54296875" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="30.81640625" customWidth="1"/>
-    <col min="16" max="16" width="15.26953125" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="18.36328125" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="8.7265625" style="23"/>
+    <col min="14" max="14" width="21.5703125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="30.85546875" customWidth="1"/>
+    <col min="16" max="16" width="15.28515625" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="18.42578125" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="8.7109375" style="9"/>
     <col min="19" max="19" width="5" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="23.26953125" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="23.28515625" bestFit="1" customWidth="1"/>
     <col min="21" max="21" width="41" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="15.26953125" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="18.36328125" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="8.7265625" style="23"/>
+    <col min="22" max="22" width="15.28515625" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="18.42578125" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="8.7109375" style="9"/>
     <col min="25" max="25" width="5" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="19.1796875" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="11.54296875" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="15.26953125" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="18.36328125" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="19.140625" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="11.5703125" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="15.28515625" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="18.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:30" x14ac:dyDescent="0.35">
-      <c r="A1" s="17" t="s">
+    <row r="1" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="A1" s="16" t="s">
         <v>11</v>
       </c>
-      <c r="B1" s="17"/>
-      <c r="C1" s="17"/>
-      <c r="D1" s="17"/>
-      <c r="E1" s="17"/>
-      <c r="F1" s="24"/>
-      <c r="G1" s="17" t="s">
+      <c r="B1" s="16"/>
+      <c r="C1" s="16"/>
+      <c r="D1" s="16"/>
+      <c r="E1" s="16"/>
+      <c r="F1" s="17"/>
+      <c r="G1" s="16" t="s">
         <v>21</v>
       </c>
-      <c r="H1" s="17"/>
-      <c r="I1" s="17"/>
-      <c r="J1" s="17"/>
-      <c r="K1" s="17"/>
-      <c r="L1" s="24"/>
-      <c r="M1" s="16" t="s">
+      <c r="H1" s="16"/>
+      <c r="I1" s="16"/>
+      <c r="J1" s="16"/>
+      <c r="K1" s="16"/>
+      <c r="L1" s="17"/>
+      <c r="M1" s="18" t="s">
         <v>22</v>
       </c>
-      <c r="N1" s="17"/>
-      <c r="O1" s="17"/>
-      <c r="P1" s="17"/>
-      <c r="Q1" s="17"/>
-      <c r="R1" s="24"/>
-      <c r="S1" s="17" t="s">
+      <c r="N1" s="16"/>
+      <c r="O1" s="16"/>
+      <c r="P1" s="16"/>
+      <c r="Q1" s="16"/>
+      <c r="R1" s="17"/>
+      <c r="S1" s="16" t="s">
         <v>23</v>
       </c>
-      <c r="T1" s="17"/>
-      <c r="U1" s="17"/>
-      <c r="V1" s="17"/>
-      <c r="W1" s="17"/>
-      <c r="X1" s="24"/>
-      <c r="Y1" s="2" t="s">
+      <c r="T1" s="16"/>
+      <c r="U1" s="16"/>
+      <c r="V1" s="16"/>
+      <c r="W1" s="16"/>
+      <c r="X1" s="17"/>
+      <c r="Y1" s="16" t="s">
         <v>24</v>
       </c>
-      <c r="Z1" s="2"/>
-      <c r="AA1" s="2"/>
-      <c r="AB1" s="2"/>
-      <c r="AC1" s="2"/>
-      <c r="AD1" s="2"/>
-    </row>
-    <row r="2" spans="1:30" x14ac:dyDescent="0.35">
-      <c r="A2" s="17" t="s">
+      <c r="Z1" s="16"/>
+      <c r="AA1" s="16"/>
+      <c r="AB1" s="16"/>
+      <c r="AC1" s="16"/>
+      <c r="AD1" s="16"/>
+    </row>
+    <row r="2" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="A2" s="16" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="17"/>
-      <c r="C2" s="20">
+      <c r="B2" s="16"/>
+      <c r="C2">
         <f>IFERROR(_xlfn.XLOOKUP(A1, TestMaster[Test Name], TestMaster[Test ID], "ID not found"), "")</f>
         <v>11</v>
       </c>
-      <c r="D2" s="32"/>
-      <c r="E2" s="20" t="s">
+      <c r="E2" t="s">
         <v>4</v>
       </c>
-      <c r="F2" s="21"/>
-      <c r="G2" s="17" t="s">
+      <c r="G2" s="16" t="s">
         <v>3</v>
       </c>
-      <c r="H2" s="17"/>
-      <c r="I2" s="18">
+      <c r="H2" s="16"/>
+      <c r="I2" s="8">
         <f>IFERROR(_xlfn.XLOOKUP(G1, TestMaster[Test Name], TestMaster[Test ID], "ID not found"), "")</f>
         <v>12</v>
       </c>
-      <c r="J2" s="32"/>
-      <c r="K2" s="20" t="s">
+      <c r="K2" t="s">
         <v>4</v>
       </c>
-      <c r="L2" s="21"/>
-      <c r="M2" s="2" t="s">
+      <c r="M2" s="16" t="s">
         <v>3</v>
       </c>
-      <c r="N2" s="2"/>
-      <c r="O2" s="15">
+      <c r="N2" s="16"/>
+      <c r="O2" s="8">
         <f>IFERROR(_xlfn.XLOOKUP(M1, TestMaster[Test Name], TestMaster[Test ID], "ID not found"), "")</f>
         <v>13</v>
       </c>
-      <c r="Q2" s="4" t="s">
+      <c r="Q2" t="s">
         <v>4</v>
       </c>
-      <c r="R2" s="21"/>
-      <c r="S2" s="2" t="s">
+      <c r="S2" s="16" t="s">
         <v>3</v>
       </c>
-      <c r="T2" s="2"/>
-      <c r="U2" s="15">
+      <c r="T2" s="16"/>
+      <c r="U2" s="8">
         <f>IFERROR(_xlfn.XLOOKUP(S1, TestMaster[Test Name], TestMaster[Test ID], "ID not found"), "")</f>
         <v>14</v>
       </c>
-      <c r="W2" s="4" t="s">
+      <c r="W2" t="s">
         <v>4</v>
       </c>
-      <c r="X2" s="21"/>
-      <c r="Y2" s="2" t="s">
+      <c r="Y2" s="16" t="s">
         <v>3</v>
       </c>
-      <c r="Z2" s="2"/>
-      <c r="AA2" s="15">
+      <c r="Z2" s="16"/>
+      <c r="AA2" s="8">
         <f>IFERROR(_xlfn.XLOOKUP(Y1, TestMaster[Test Name], TestMaster[Test ID], "ID not found"), "")</f>
         <v>15</v>
       </c>
-      <c r="AC2" s="4" t="s">
+      <c r="AC2" t="s">
         <v>4</v>
       </c>
-      <c r="AD2" s="4"/>
-    </row>
-    <row r="3" spans="1:30" x14ac:dyDescent="0.35">
-      <c r="A3" s="17" t="s">
-        <v>188</v>
-      </c>
-      <c r="B3" s="17"/>
-      <c r="C3" s="20" t="str">
+    </row>
+    <row r="3" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="A3" s="16" t="s">
+        <v>187</v>
+      </c>
+      <c r="B3" s="16"/>
+      <c r="C3" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(A1, TestMaster[Test Name], TestMaster[Test Priority], "Priority not found"), "")</f>
         <v>High</v>
       </c>
-      <c r="D3" s="32"/>
-      <c r="E3" s="20" t="s">
+      <c r="E3" t="s">
         <v>5</v>
       </c>
-      <c r="F3" s="21" t="str">
+      <c r="F3" s="9" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(A1, TestMaster[Test Name], TestMaster[Test Priority], "Priority not found"), "")</f>
         <v>High</v>
       </c>
-      <c r="G3" s="17" t="s">
-        <v>189</v>
-      </c>
-      <c r="H3" s="17"/>
-      <c r="I3" s="18" t="str">
+      <c r="G3" s="16" t="s">
+        <v>188</v>
+      </c>
+      <c r="H3" s="16"/>
+      <c r="I3" s="8" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(G1, TestMaster[Test Name], TestMaster[Test Priority], "Priority not found"), "")</f>
         <v>High</v>
       </c>
-      <c r="J3" s="32"/>
-      <c r="K3" s="20" t="s">
+      <c r="K3" t="s">
         <v>5</v>
       </c>
-      <c r="L3" s="21" t="str">
+      <c r="L3" s="9" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(G1, TestMaster[Test Name], TestMaster[Test Priority], "Priority not found"), "")</f>
         <v>High</v>
       </c>
-      <c r="M3" s="2" t="s">
-        <v>188</v>
-      </c>
-      <c r="N3" s="2"/>
-      <c r="O3" s="15" t="str">
+      <c r="M3" s="16" t="s">
+        <v>187</v>
+      </c>
+      <c r="N3" s="16"/>
+      <c r="O3" s="8" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(M1, TestMaster[Test Name], TestMaster[Test Priority], "Priority not found"), "")</f>
         <v>Medium</v>
       </c>
-      <c r="Q3" s="4" t="s">
+      <c r="Q3" t="s">
         <v>5</v>
       </c>
-      <c r="R3" s="21" t="str">
+      <c r="R3" s="9" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(M1, TestMaster[Test Name], TestMaster[Test Priority], "Priority not found"), "")</f>
         <v>Medium</v>
       </c>
-      <c r="S3" s="2" t="s">
-        <v>188</v>
-      </c>
-      <c r="T3" s="2"/>
-      <c r="U3" s="15" t="str">
+      <c r="S3" s="16" t="s">
+        <v>187</v>
+      </c>
+      <c r="T3" s="16"/>
+      <c r="U3" s="8" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(S1, TestMaster[Test Name], TestMaster[Test Priority], "Priority not found"), "")</f>
         <v>Low</v>
       </c>
-      <c r="W3" s="4" t="s">
+      <c r="W3" t="s">
         <v>5</v>
       </c>
-      <c r="X3" s="21" t="str">
+      <c r="X3" s="9" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(S1, TestMaster[Test Name], TestMaster[Test Priority], "Priority not found"), "")</f>
         <v>Low</v>
       </c>
-      <c r="Y3" s="2" t="s">
-        <v>188</v>
-      </c>
-      <c r="Z3" s="2"/>
-      <c r="AA3" s="15" t="str">
+      <c r="Y3" s="16" t="s">
+        <v>187</v>
+      </c>
+      <c r="Z3" s="16"/>
+      <c r="AA3" s="8" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(Y1, TestMaster[Test Name], TestMaster[Test Priority], "Priority not found"), "")</f>
         <v>High</v>
       </c>
-      <c r="AC3" s="4" t="s">
+      <c r="AC3" t="s">
         <v>5</v>
       </c>
-      <c r="AD3" s="4" t="str">
+      <c r="AD3" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(Y1, TestMaster[Test Name], TestMaster[Test Priority], "Priority not found"), "")</f>
         <v>High</v>
       </c>
     </row>
-    <row r="4" spans="1:30" s="3" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="39" t="s">
+    <row r="4" spans="1:30" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="19" t="s">
         <v>12</v>
       </c>
-      <c r="B4" s="39"/>
-      <c r="C4" s="39"/>
-      <c r="D4" s="39"/>
-      <c r="E4" s="39"/>
-      <c r="F4" s="40"/>
-      <c r="G4" s="39" t="s">
+      <c r="B4" s="19"/>
+      <c r="C4" s="19"/>
+      <c r="D4" s="19"/>
+      <c r="E4" s="19"/>
+      <c r="F4" s="20"/>
+      <c r="G4" s="19" t="s">
         <v>68</v>
       </c>
-      <c r="H4" s="39"/>
-      <c r="I4" s="39"/>
-      <c r="J4" s="39"/>
-      <c r="K4" s="39"/>
-      <c r="L4" s="40"/>
-      <c r="M4" s="38" t="s">
+      <c r="H4" s="19"/>
+      <c r="I4" s="19"/>
+      <c r="J4" s="19"/>
+      <c r="K4" s="19"/>
+      <c r="L4" s="20"/>
+      <c r="M4" s="21" t="s">
         <v>12</v>
       </c>
-      <c r="N4" s="39"/>
-      <c r="O4" s="39"/>
-      <c r="P4" s="39"/>
-      <c r="Q4" s="39"/>
-      <c r="R4" s="40"/>
-      <c r="S4" s="39" t="s">
+      <c r="N4" s="19"/>
+      <c r="O4" s="19"/>
+      <c r="P4" s="19"/>
+      <c r="Q4" s="19"/>
+      <c r="R4" s="20"/>
+      <c r="S4" s="19" t="s">
         <v>12</v>
       </c>
-      <c r="T4" s="39"/>
-      <c r="U4" s="39"/>
-      <c r="V4" s="39"/>
-      <c r="W4" s="39"/>
-      <c r="X4" s="40"/>
-      <c r="Y4" s="6" t="s">
+      <c r="T4" s="19"/>
+      <c r="U4" s="19"/>
+      <c r="V4" s="19"/>
+      <c r="W4" s="19"/>
+      <c r="X4" s="20"/>
+      <c r="Y4" s="19" t="s">
         <v>12</v>
       </c>
-      <c r="Z4" s="6"/>
-      <c r="AA4" s="6"/>
-      <c r="AB4" s="6"/>
-      <c r="AC4" s="6"/>
-      <c r="AD4" s="6"/>
-    </row>
-    <row r="5" spans="1:30" s="3" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="39"/>
-      <c r="B5" s="39"/>
-      <c r="C5" s="39"/>
-      <c r="D5" s="39"/>
-      <c r="E5" s="39"/>
-      <c r="F5" s="40"/>
-      <c r="G5" s="39"/>
-      <c r="H5" s="39"/>
-      <c r="I5" s="39"/>
-      <c r="J5" s="39"/>
-      <c r="K5" s="39"/>
-      <c r="L5" s="40"/>
-      <c r="M5" s="38"/>
-      <c r="N5" s="39"/>
-      <c r="O5" s="39"/>
-      <c r="P5" s="39"/>
-      <c r="Q5" s="39"/>
-      <c r="R5" s="40"/>
-      <c r="S5" s="39"/>
-      <c r="T5" s="39"/>
-      <c r="U5" s="39"/>
-      <c r="V5" s="39"/>
-      <c r="W5" s="39"/>
-      <c r="X5" s="40"/>
-      <c r="Y5" s="6"/>
-      <c r="Z5" s="6"/>
-      <c r="AA5" s="6"/>
-      <c r="AB5" s="6"/>
-      <c r="AC5" s="6"/>
-      <c r="AD5" s="6"/>
-    </row>
-    <row r="6" spans="1:30" x14ac:dyDescent="0.35">
-      <c r="A6" s="17" t="s">
+      <c r="Z4" s="19"/>
+      <c r="AA4" s="19"/>
+      <c r="AB4" s="19"/>
+      <c r="AC4" s="19"/>
+      <c r="AD4" s="19"/>
+    </row>
+    <row r="5" spans="1:30" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="19"/>
+      <c r="B5" s="19"/>
+      <c r="C5" s="19"/>
+      <c r="D5" s="19"/>
+      <c r="E5" s="19"/>
+      <c r="F5" s="20"/>
+      <c r="G5" s="19"/>
+      <c r="H5" s="19"/>
+      <c r="I5" s="19"/>
+      <c r="J5" s="19"/>
+      <c r="K5" s="19"/>
+      <c r="L5" s="20"/>
+      <c r="M5" s="21"/>
+      <c r="N5" s="19"/>
+      <c r="O5" s="19"/>
+      <c r="P5" s="19"/>
+      <c r="Q5" s="19"/>
+      <c r="R5" s="20"/>
+      <c r="S5" s="19"/>
+      <c r="T5" s="19"/>
+      <c r="U5" s="19"/>
+      <c r="V5" s="19"/>
+      <c r="W5" s="19"/>
+      <c r="X5" s="20"/>
+      <c r="Y5" s="19"/>
+      <c r="Z5" s="19"/>
+      <c r="AA5" s="19"/>
+      <c r="AB5" s="19"/>
+      <c r="AC5" s="19"/>
+      <c r="AD5" s="19"/>
+    </row>
+    <row r="6" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="A6" s="16" t="s">
         <v>69</v>
       </c>
-      <c r="B6" s="17"/>
-      <c r="C6" s="17"/>
-      <c r="D6" s="17"/>
-      <c r="E6" s="17"/>
-      <c r="F6" s="24"/>
-      <c r="G6" s="17" t="s">
+      <c r="B6" s="16"/>
+      <c r="C6" s="16"/>
+      <c r="D6" s="16"/>
+      <c r="E6" s="16"/>
+      <c r="F6" s="17"/>
+      <c r="G6" s="16" t="s">
         <v>69</v>
       </c>
-      <c r="H6" s="17"/>
-      <c r="I6" s="17"/>
-      <c r="J6" s="17"/>
-      <c r="K6" s="17"/>
-      <c r="L6" s="24"/>
-      <c r="M6" s="16" t="s">
+      <c r="H6" s="16"/>
+      <c r="I6" s="16"/>
+      <c r="J6" s="16"/>
+      <c r="K6" s="16"/>
+      <c r="L6" s="17"/>
+      <c r="M6" s="18" t="s">
         <v>70</v>
       </c>
-      <c r="N6" s="17"/>
-      <c r="O6" s="17"/>
-      <c r="P6" s="17"/>
-      <c r="Q6" s="17"/>
-      <c r="R6" s="24"/>
-      <c r="S6" s="17" t="s">
+      <c r="N6" s="16"/>
+      <c r="O6" s="16"/>
+      <c r="P6" s="16"/>
+      <c r="Q6" s="16"/>
+      <c r="R6" s="17"/>
+      <c r="S6" s="16" t="s">
         <v>53</v>
       </c>
-      <c r="T6" s="17"/>
-      <c r="U6" s="17"/>
-      <c r="V6" s="17"/>
-      <c r="W6" s="17"/>
-      <c r="X6" s="24"/>
-      <c r="Y6" s="2" t="s">
+      <c r="T6" s="16"/>
+      <c r="U6" s="16"/>
+      <c r="V6" s="16"/>
+      <c r="W6" s="16"/>
+      <c r="X6" s="17"/>
+      <c r="Y6" s="16" t="s">
         <v>69</v>
       </c>
-      <c r="Z6" s="2"/>
-      <c r="AA6" s="2"/>
-      <c r="AB6" s="2"/>
-      <c r="AC6" s="2"/>
-      <c r="AD6" s="2"/>
-    </row>
-    <row r="7" spans="1:30" x14ac:dyDescent="0.35">
-      <c r="A7" s="25" t="s">
+      <c r="Z6" s="16"/>
+      <c r="AA6" s="16"/>
+      <c r="AB6" s="16"/>
+      <c r="AC6" s="16"/>
+      <c r="AD6" s="16"/>
+    </row>
+    <row r="7" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="A7" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B7" s="25" t="s">
+      <c r="B7" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C7" s="25" t="s">
+      <c r="C7" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="D7" s="25" t="s">
+      <c r="D7" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="E7" s="25" t="s">
+      <c r="E7" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="F7" s="27" t="s">
+      <c r="F7" s="12" t="s">
         <v>2</v>
       </c>
-      <c r="G7" s="25" t="s">
+      <c r="G7" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="H7" s="25" t="s">
+      <c r="H7" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="I7" s="25" t="s">
+      <c r="I7" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="J7" s="25" t="s">
+      <c r="J7" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="K7" s="25" t="s">
+      <c r="K7" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="L7" s="27" t="s">
+      <c r="L7" s="12" t="s">
         <v>2</v>
       </c>
       <c r="M7" s="1" t="s">
@@ -5346,7 +5183,7 @@
       <c r="Q7" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="R7" s="27" t="s">
+      <c r="R7" s="12" t="s">
         <v>2</v>
       </c>
       <c r="S7" s="1" t="s">
@@ -5364,7 +5201,7 @@
       <c r="W7" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="X7" s="27" t="s">
+      <c r="X7" s="12" t="s">
         <v>2</v>
       </c>
       <c r="Y7" s="1" t="s">
@@ -5386,33 +5223,31 @@
         <v>2</v>
       </c>
     </row>
-    <row r="8" spans="1:30" x14ac:dyDescent="0.35">
-      <c r="A8" s="32">
+    <row r="8" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="A8">
         <v>1</v>
       </c>
-      <c r="B8" s="32" t="s">
+      <c r="B8" t="s">
         <v>25</v>
       </c>
-      <c r="C8" s="32" t="s">
+      <c r="C8" t="s">
         <v>27</v>
       </c>
-      <c r="D8" s="32" t="s">
+      <c r="D8" t="s">
         <v>38</v>
       </c>
-      <c r="E8" s="32"/>
-      <c r="G8" s="32">
+      <c r="G8">
         <v>1</v>
       </c>
-      <c r="H8" s="32" t="s">
+      <c r="H8" t="s">
         <v>34</v>
       </c>
-      <c r="I8" s="32" t="s">
+      <c r="I8" t="s">
         <v>27</v>
       </c>
-      <c r="J8" s="32" t="s">
+      <c r="J8" t="s">
         <v>36</v>
       </c>
-      <c r="K8" s="32"/>
       <c r="M8">
         <v>1</v>
       </c>
@@ -5447,43 +5282,41 @@
         <v>66</v>
       </c>
     </row>
-    <row r="9" spans="1:30" ht="58" x14ac:dyDescent="0.35">
-      <c r="A9" s="32">
+    <row r="9" spans="1:30" ht="75" x14ac:dyDescent="0.25">
+      <c r="A9">
         <v>2</v>
       </c>
-      <c r="B9" s="32" t="s">
+      <c r="B9" t="s">
         <v>49</v>
       </c>
-      <c r="C9" s="32" t="s">
+      <c r="C9" t="s">
         <v>28</v>
       </c>
-      <c r="D9" s="32" t="s">
+      <c r="D9" t="s">
         <v>39</v>
       </c>
-      <c r="E9" s="32"/>
-      <c r="G9" s="32">
+      <c r="G9">
         <v>2</v>
       </c>
-      <c r="H9" s="32" t="s">
+      <c r="H9" t="s">
         <v>35</v>
       </c>
-      <c r="I9" s="19" t="s">
+      <c r="I9" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="J9" s="19" t="s">
+      <c r="J9" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="K9" s="32"/>
       <c r="M9">
         <v>2</v>
       </c>
-      <c r="N9" s="3" t="s">
+      <c r="N9" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="O9" s="3" t="s">
+      <c r="O9" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="P9" s="3" t="s">
+      <c r="P9" s="2" t="s">
         <v>45</v>
       </c>
       <c r="S9">
@@ -5508,33 +5341,31 @@
         <v>65</v>
       </c>
     </row>
-    <row r="10" spans="1:30" x14ac:dyDescent="0.35">
-      <c r="A10" s="32">
+    <row r="10" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="A10">
         <v>3</v>
       </c>
-      <c r="B10" s="32" t="s">
+      <c r="B10" t="s">
         <v>26</v>
       </c>
-      <c r="C10" s="32" t="s">
+      <c r="C10" t="s">
         <v>29</v>
       </c>
-      <c r="D10" s="32" t="s">
+      <c r="D10" t="s">
         <v>40</v>
       </c>
-      <c r="E10" s="32"/>
-      <c r="G10" s="20">
+      <c r="G10">
         <v>3</v>
       </c>
-      <c r="H10" s="20" t="s">
+      <c r="H10" t="s">
         <v>50</v>
       </c>
-      <c r="I10" s="32" t="s">
+      <c r="I10" t="s">
         <v>51</v>
       </c>
-      <c r="J10" s="32" t="s">
+      <c r="J10" t="s">
         <v>60</v>
       </c>
-      <c r="K10" s="32"/>
       <c r="M10">
         <v>3</v>
       </c>
@@ -5544,7 +5375,7 @@
       <c r="O10" t="s">
         <v>47</v>
       </c>
-      <c r="P10" s="5" t="s">
+      <c r="P10" s="3" t="s">
         <v>48</v>
       </c>
       <c r="S10">
@@ -5557,20 +5388,19 @@
         <v>61</v>
       </c>
     </row>
-    <row r="11" spans="1:30" x14ac:dyDescent="0.35">
-      <c r="A11" s="32">
+    <row r="11" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="A11">
         <v>4</v>
       </c>
-      <c r="B11" s="32" t="s">
+      <c r="B11" t="s">
         <v>30</v>
       </c>
-      <c r="C11" s="32" t="s">
+      <c r="C11" t="s">
         <v>31</v>
       </c>
-      <c r="D11" s="32" t="s">
+      <c r="D11" t="s">
         <v>38</v>
       </c>
-      <c r="E11" s="32"/>
       <c r="S11">
         <v>4</v>
       </c>
@@ -5581,20 +5411,19 @@
         <v>62</v>
       </c>
     </row>
-    <row r="12" spans="1:30" x14ac:dyDescent="0.35">
-      <c r="A12" s="32">
+    <row r="12" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="A12">
         <v>5</v>
       </c>
-      <c r="B12" s="32" t="s">
+      <c r="B12" t="s">
         <v>32</v>
       </c>
-      <c r="C12" s="32" t="s">
+      <c r="C12" t="s">
         <v>33</v>
       </c>
-      <c r="D12" s="32" t="s">
+      <c r="D12" t="s">
         <v>40</v>
       </c>
-      <c r="E12" s="32"/>
       <c r="S12">
         <v>5</v>
       </c>
@@ -5605,19 +5434,8 @@
         <v>58</v>
       </c>
     </row>
-    <row r="13" spans="1:30" x14ac:dyDescent="0.35">
-      <c r="A13" s="4"/>
-      <c r="B13" s="4"/>
-      <c r="C13" s="4"/>
-    </row>
   </sheetData>
   <mergeCells count="25">
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="A3:B3"/>
-    <mergeCell ref="G2:H2"/>
-    <mergeCell ref="G3:H3"/>
-    <mergeCell ref="M2:N2"/>
-    <mergeCell ref="M3:N3"/>
     <mergeCell ref="Y1:AD1"/>
     <mergeCell ref="Y2:Z2"/>
     <mergeCell ref="Y3:Z3"/>
@@ -5628,15 +5446,21 @@
     <mergeCell ref="S2:T2"/>
     <mergeCell ref="S3:T3"/>
     <mergeCell ref="S1:X1"/>
+    <mergeCell ref="A4:F5"/>
+    <mergeCell ref="A6:F6"/>
+    <mergeCell ref="A1:F1"/>
     <mergeCell ref="M1:R1"/>
     <mergeCell ref="G4:L5"/>
     <mergeCell ref="G6:L6"/>
     <mergeCell ref="M4:R5"/>
     <mergeCell ref="M6:R6"/>
     <mergeCell ref="G1:L1"/>
-    <mergeCell ref="A4:F5"/>
-    <mergeCell ref="A6:F6"/>
-    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="A3:B3"/>
+    <mergeCell ref="G2:H2"/>
+    <mergeCell ref="G3:H3"/>
+    <mergeCell ref="M2:N2"/>
+    <mergeCell ref="M3:N3"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Test Cases.xlsx
+++ b/Test Cases.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://endresshauser-my.sharepoint.com/personal/corbin_ferguson_endress_com/Documents/Thesis Work/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1627" documentId="11_AD4DB114E441178AC67DF4D41ED1D894683EDF27" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{361B8735-BBF4-43CD-ABC6-232ECC75B30E}"/>
+  <xr:revisionPtr revIDLastSave="1637" documentId="11_AD4DB114E441178AC67DF4D41ED1D894683EDF27" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1D848577-258C-4138-9A60-41B0653B7391}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-4485" windowWidth="25440" windowHeight="15270" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="53880" yWindow="-5145" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tests" sheetId="7" r:id="rId1"/>
@@ -24,7 +24,6 @@
   <pivotCaches>
     <pivotCache cacheId="0" r:id="rId7"/>
   </pivotCaches>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -67,7 +66,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="523" uniqueCount="191">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="526" uniqueCount="194">
   <si>
     <t>Step</t>
   </si>
@@ -139,9 +138,6 @@
   </si>
   <si>
     <t>Validate File</t>
-  </si>
-  <si>
-    <t>Exit</t>
   </si>
   <si>
     <t>"New File" Button Pressed</t>
@@ -870,6 +866,18 @@
   </si>
   <si>
     <t>"Create Element" button pressed</t>
+  </si>
+  <si>
+    <t>ActionSelectLayout</t>
+  </si>
+  <si>
+    <t>Verify Buttons found</t>
+  </si>
+  <si>
+    <t>ImportElementButton, "CreateElementButton", "ModifyElementButton", "DeleteElementButton", "NewFileButton", "LoadFileButton", "ValidateFileButton", "SaveFileButton", "ExitActionSelect", "Minimize", "Maximize", "Close"</t>
+  </si>
+  <si>
+    <t>button names match list</t>
   </si>
 </sst>
 </file>
@@ -989,13 +997,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1960,10 +1968,6 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
-</file>
-
 <file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Corbin Ferguson" refreshedDate="46035.626586689817" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="17" xr:uid="{32ED145B-7CBC-4C3A-9787-F34239E1DCF7}">
   <cacheSource type="worksheet">
@@ -2391,45 +2395,45 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F8512478-31DB-4352-AB46-996C676231F3}">
   <dimension ref="A1:I16"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="10.42578125" customWidth="1"/>
-    <col min="2" max="2" width="34.140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="16.140625" style="6" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="18.42578125" hidden="1" customWidth="1"/>
-    <col min="5" max="5" width="13.42578125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="16.140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.453125" customWidth="1"/>
+    <col min="2" max="2" width="34.1796875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="16.1796875" style="6" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="18.453125" hidden="1" customWidth="1"/>
+    <col min="5" max="5" width="13.453125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="16.1796875" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="18" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
+        <v>157</v>
+      </c>
+      <c r="B1" t="s">
         <v>158</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" s="6" t="s">
         <v>159</v>
       </c>
-      <c r="C1" s="6" t="s">
-        <v>160</v>
-      </c>
       <c r="D1" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="E1" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="G1">
         <f>COUNTIF(TestMaster[Test Status], "Not Implemented")</f>
         <v>15</v>
       </c>
       <c r="H1" s="7" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="I1" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A2">
         <f t="shared" ref="A2:A16" si="0">ROW()-1</f>
         <v>1</v>
@@ -2439,26 +2443,26 @@
         <v>Import Select Redundant Name</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="D2" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="E2" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="G2">
         <f>COUNTIF(TestMaster[Test Status], "Pass")</f>
         <v>0</v>
       </c>
       <c r="H2" s="8" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="I2">
         <v>17</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A3">
         <f t="shared" si="0"/>
         <v>2</v>
@@ -2468,26 +2472,26 @@
         <v>Element Quantity Creation</v>
       </c>
       <c r="C3" s="6" t="s">
+        <v>163</v>
+      </c>
+      <c r="D3" t="s">
         <v>164</v>
       </c>
-      <c r="D3" t="s">
-        <v>165</v>
-      </c>
       <c r="E3" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="G3">
         <f>COUNTIF(TestMaster[Test Status], "Fail")</f>
         <v>0</v>
       </c>
       <c r="H3" s="8" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="I3">
         <v>17</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A4">
         <f t="shared" si="0"/>
         <v>3</v>
@@ -2497,17 +2501,17 @@
         <v>Nameless Module Creation</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="E4" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="G4">
         <f>COUNTIF(TestMaster[Test Status], "Not Run")</f>
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A5">
         <f t="shared" si="0"/>
         <v>4</v>
@@ -2517,13 +2521,13 @@
         <v>Redundant Element Creation</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="E5" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A6">
         <f t="shared" si="0"/>
         <v>5</v>
@@ -2533,13 +2537,13 @@
         <v>No Element to Modify</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="E6" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A7">
         <f t="shared" si="0"/>
         <v>6</v>
@@ -2549,13 +2553,13 @@
         <v>Completed Element Modification</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="E7" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A8">
         <f t="shared" si="0"/>
         <v>7</v>
@@ -2565,13 +2569,13 @@
         <v>Modify into Redundant Element Name</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="E8" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A9">
         <f t="shared" si="0"/>
         <v>8</v>
@@ -2581,13 +2585,13 @@
         <v>Delete No Element Type</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="E9" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A10">
         <f t="shared" si="0"/>
         <v>9</v>
@@ -2597,13 +2601,13 @@
         <v>Delete Element Found</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="E10" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A11">
         <f t="shared" si="0"/>
         <v>10</v>
@@ -2613,13 +2617,13 @@
         <v>Delete Module by Port</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="E11" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A12">
         <f t="shared" si="0"/>
         <v>11</v>
@@ -2629,13 +2633,13 @@
         <v>New File Creation</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="E12" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A13">
         <f t="shared" si="0"/>
         <v>12</v>
@@ -2645,13 +2649,13 @@
         <v>Save File</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="E13" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A14">
         <f t="shared" si="0"/>
         <v>13</v>
@@ -2661,13 +2665,13 @@
         <v>Load File</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="E14" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A15">
         <f t="shared" si="0"/>
         <v>14</v>
@@ -2677,26 +2681,26 @@
         <v>Validate File</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="E15" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A16">
         <f t="shared" si="0"/>
         <v>15</v>
       </c>
       <c r="B16" t="str">
         <f>'File Manipulation Testing'!Y1</f>
-        <v>Exit</v>
+        <v>ActionSelectLayout</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="E16" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
   </sheetData>
@@ -2749,17 +2753,17 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B60DAC1D-2E28-4DF7-A44B-A179A310D91E}">
   <dimension ref="A1:F25"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="6.42578125" customWidth="1"/>
-    <col min="2" max="2" width="22.85546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="48.85546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="56.7109375" style="2" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="18.42578125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="16.140625" style="9" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="6.453125" customWidth="1"/>
+    <col min="2" max="2" width="22.81640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="48.81640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="56.7265625" style="2" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="18.453125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="16.1796875" style="9" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1" s="16" t="s">
         <v>13</v>
       </c>
@@ -2769,7 +2773,7 @@
       <c r="E1" s="16"/>
       <c r="F1" s="17"/>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A2" s="16" t="s">
         <v>3</v>
       </c>
@@ -2782,9 +2786,9 @@
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="16" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B3" s="16"/>
       <c r="C3" s="10" t="str">
@@ -2799,9 +2803,9 @@
         <v>Not Implemented</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A4" s="16" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B4" s="16"/>
       <c r="C4" s="16"/>
@@ -2809,7 +2813,7 @@
       <c r="E4" s="16"/>
       <c r="F4" s="17"/>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A5" s="16"/>
       <c r="B5" s="16"/>
       <c r="C5" s="16"/>
@@ -2817,7 +2821,7 @@
       <c r="E5" s="16"/>
       <c r="F5" s="17"/>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A6" s="16" t="s">
         <v>7</v>
       </c>
@@ -2827,7 +2831,7 @@
       <c r="E6" s="16"/>
       <c r="F6" s="17"/>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A7" s="1" t="s">
         <v>0</v>
       </c>
@@ -2847,273 +2851,273 @@
         <v>2</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A8">
         <v>1</v>
       </c>
       <c r="B8" t="s">
+        <v>174</v>
+      </c>
+      <c r="C8" t="s">
         <v>175</v>
       </c>
-      <c r="C8" t="s">
+      <c r="D8" s="2" t="s">
         <v>176</v>
       </c>
-      <c r="D8" s="2" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" ht="45" x14ac:dyDescent="0.25">
+    </row>
+    <row r="9" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A9" s="5">
         <f>A8+1</f>
         <v>2</v>
       </c>
       <c r="B9" s="4" t="s">
+        <v>172</v>
+      </c>
+      <c r="C9" s="4" t="s">
         <v>173</v>
       </c>
-      <c r="C9" s="4" t="s">
-        <v>174</v>
-      </c>
       <c r="D9" s="4" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A10" s="5">
         <f>A9+1</f>
         <v>3</v>
       </c>
       <c r="B10" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="D10" s="4" t="s">
         <v>125</v>
       </c>
-      <c r="C10" s="4" t="s">
-        <v>140</v>
-      </c>
-      <c r="D10" s="4" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A11" s="5">
         <f t="shared" ref="A11:A25" si="0">A10+1</f>
         <v>4</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A12" s="5">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
       <c r="B12" s="4" t="s">
+        <v>178</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="D12" s="2" t="s">
         <v>179</v>
       </c>
-      <c r="C12" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A13" s="5">
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
       <c r="B13" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="D13" s="4" t="s">
         <v>125</v>
       </c>
-      <c r="C13" s="4" t="s">
-        <v>140</v>
-      </c>
-      <c r="D13" s="4" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A14" s="5">
         <f t="shared" si="0"/>
         <v>7</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A15" s="5">
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
       <c r="B15" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C15" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A16" s="5">
         <f t="shared" si="0"/>
         <v>9</v>
       </c>
       <c r="B16" s="4" t="s">
+        <v>178</v>
+      </c>
+      <c r="C16" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="D16" s="2" t="s">
         <v>179</v>
       </c>
-      <c r="C16" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="D16" s="2" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A17" s="5">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
       <c r="B17" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="C17" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="D17" s="4" t="s">
         <v>125</v>
       </c>
-      <c r="C17" s="4" t="s">
-        <v>140</v>
-      </c>
-      <c r="D17" s="4" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A18" s="5">
         <f t="shared" si="0"/>
         <v>11</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D18" s="4" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A19" s="5">
         <f t="shared" si="0"/>
         <v>12</v>
       </c>
       <c r="B19" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C19" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A20" s="5">
         <f t="shared" si="0"/>
         <v>13</v>
       </c>
       <c r="B20" s="4" t="s">
+        <v>178</v>
+      </c>
+      <c r="C20" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="D20" s="2" t="s">
         <v>179</v>
       </c>
-      <c r="C20" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="D20" s="2" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A21" s="5">
         <f t="shared" si="0"/>
         <v>14</v>
       </c>
       <c r="B21" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C21" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A22" s="5">
         <f t="shared" si="0"/>
         <v>15</v>
       </c>
       <c r="B22" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A23" s="5">
         <f t="shared" si="0"/>
         <v>16</v>
       </c>
       <c r="B23" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C23" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A24" s="5">
         <f t="shared" si="0"/>
         <v>17</v>
       </c>
       <c r="B24" t="s">
+        <v>112</v>
+      </c>
+      <c r="C24" t="s">
         <v>113</v>
       </c>
-      <c r="C24" t="s">
-        <v>114</v>
-      </c>
       <c r="D24" s="2" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A25" s="5">
         <f t="shared" si="0"/>
         <v>18</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
   </sheetData>
@@ -3131,30 +3135,30 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CA0AB6AA-BAF4-4C64-96FE-66D32370F298}">
   <dimension ref="A1:R21"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="5" style="5" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="34.42578125" style="5" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="24.85546875" style="5" customWidth="1"/>
-    <col min="4" max="4" width="35.5703125" style="5" customWidth="1"/>
-    <col min="5" max="5" width="18.42578125" style="5" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="16.140625" style="13" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="34.453125" style="5" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="24.81640625" style="5" customWidth="1"/>
+    <col min="4" max="4" width="35.54296875" style="5" customWidth="1"/>
+    <col min="5" max="5" width="18.453125" style="5" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="16.1796875" style="13" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="5" style="5" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="29.140625" style="5" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="24.140625" style="5" customWidth="1"/>
+    <col min="8" max="8" width="29.1796875" style="5" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="24.1796875" style="5" customWidth="1"/>
     <col min="10" max="10" width="24" style="5" customWidth="1"/>
-    <col min="11" max="11" width="18.42578125" style="5" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="16.140625" style="13" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="18.453125" style="5" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="16.1796875" style="13" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="5" style="5" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="29.140625" style="5" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="25.5703125" style="5" customWidth="1"/>
-    <col min="16" max="16" width="23.85546875" style="5" customWidth="1"/>
-    <col min="17" max="17" width="18.42578125" style="5" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="16.140625" style="5" bestFit="1" customWidth="1"/>
-    <col min="19" max="16384" width="8.7109375" style="5"/>
+    <col min="14" max="14" width="29.1796875" style="5" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="25.54296875" style="5" customWidth="1"/>
+    <col min="16" max="16" width="23.81640625" style="5" customWidth="1"/>
+    <col min="17" max="17" width="18.453125" style="5" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="16.1796875" style="5" bestFit="1" customWidth="1"/>
+    <col min="19" max="16384" width="8.7265625" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:18" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A1" s="16" t="s">
         <v>14</v>
       </c>
@@ -3172,7 +3176,7 @@
       <c r="K1" s="16"/>
       <c r="L1" s="16"/>
       <c r="M1" s="16" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="N1" s="16"/>
       <c r="O1" s="16"/>
@@ -3180,7 +3184,7 @@
       <c r="Q1" s="16"/>
       <c r="R1" s="16"/>
     </row>
-    <row r="2" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:18" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A2" s="16" t="s">
         <v>3</v>
       </c>
@@ -3220,9 +3224,9 @@
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:18" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A3" s="16" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B3" s="16"/>
       <c r="C3" t="str">
@@ -3238,7 +3242,7 @@
         <v>Not Implemented</v>
       </c>
       <c r="G3" s="16" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="H3" s="16"/>
       <c r="I3" t="str">
@@ -3254,7 +3258,7 @@
         <v>Not Implemented</v>
       </c>
       <c r="M3" s="16" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="N3" s="16"/>
       <c r="O3" t="str">
@@ -3270,7 +3274,7 @@
         <v>Not Implemented</v>
       </c>
     </row>
-    <row r="4" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:18" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A4" s="16" t="s">
         <v>6</v>
       </c>
@@ -3296,7 +3300,7 @@
       <c r="Q4" s="16"/>
       <c r="R4" s="16"/>
     </row>
-    <row r="5" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:18" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A5" s="16"/>
       <c r="B5" s="16"/>
       <c r="C5" s="16"/>
@@ -3316,7 +3320,7 @@
       <c r="Q5" s="16"/>
       <c r="R5" s="16"/>
     </row>
-    <row r="6" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:18" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A6" s="16" t="s">
         <v>7</v>
       </c>
@@ -3342,7 +3346,7 @@
       <c r="Q6" s="16"/>
       <c r="R6" s="16"/>
     </row>
-    <row r="7" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:18" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A7" s="1" t="s">
         <v>0</v>
       </c>
@@ -3398,324 +3402,329 @@
         <v>2</v>
       </c>
     </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A8" s="5">
         <v>1</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="G8" s="5">
         <v>1</v>
       </c>
       <c r="H8" s="5" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="I8" s="4" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="J8" s="4" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="M8" s="5">
         <v>1</v>
       </c>
       <c r="N8" s="5" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="O8" s="4" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="P8" s="4" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="9" spans="1:18" ht="45" x14ac:dyDescent="0.25">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A9" s="5">
         <v>2</v>
       </c>
       <c r="B9" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="D9" s="4" t="s">
         <v>125</v>
-      </c>
-      <c r="C9" s="4" t="s">
-        <v>140</v>
-      </c>
-      <c r="D9" s="4" t="s">
-        <v>126</v>
       </c>
       <c r="G9" s="5">
         <v>2</v>
       </c>
       <c r="H9" s="5" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="I9" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="J9" s="4" t="s">
         <v>138</v>
-      </c>
-      <c r="J9" s="4" t="s">
-        <v>139</v>
       </c>
       <c r="M9" s="5">
         <v>2</v>
       </c>
       <c r="N9" s="5" t="s">
+        <v>124</v>
+      </c>
+      <c r="O9" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="P9" s="4" t="s">
         <v>125</v>
       </c>
-      <c r="O9" s="4" t="s">
-        <v>140</v>
-      </c>
-      <c r="P9" s="4" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="10" spans="1:18" ht="45" x14ac:dyDescent="0.25">
+    </row>
+    <row r="10" spans="1:18" ht="29" x14ac:dyDescent="0.35">
       <c r="A10" s="5">
         <v>3</v>
       </c>
       <c r="B10" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="D10" s="4" t="s">
         <v>127</v>
-      </c>
-      <c r="C10" s="4" t="s">
-        <v>141</v>
-      </c>
-      <c r="D10" s="4" t="s">
-        <v>128</v>
       </c>
       <c r="G10" s="5">
         <v>3</v>
       </c>
       <c r="H10" s="5" t="s">
+        <v>126</v>
+      </c>
+      <c r="I10" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="J10" s="4" t="s">
         <v>127</v>
-      </c>
-      <c r="I10" s="4" t="s">
-        <v>142</v>
-      </c>
-      <c r="J10" s="4" t="s">
-        <v>128</v>
       </c>
       <c r="M10" s="5">
         <v>3</v>
       </c>
       <c r="N10" s="5" t="s">
+        <v>126</v>
+      </c>
+      <c r="O10" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="P10" s="4" t="s">
         <v>127</v>
       </c>
-      <c r="O10" s="4" t="s">
-        <v>141</v>
-      </c>
-      <c r="P10" s="4" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="11" spans="1:18" ht="45" x14ac:dyDescent="0.25">
+    </row>
+    <row r="11" spans="1:18" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A11" s="5">
         <v>4</v>
       </c>
       <c r="B11" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="C11" s="4" t="s">
         <v>129</v>
       </c>
-      <c r="C11" s="4" t="s">
+      <c r="D11" s="4" t="s">
         <v>130</v>
-      </c>
-      <c r="D11" s="4" t="s">
-        <v>131</v>
       </c>
       <c r="G11" s="5">
         <v>4</v>
       </c>
       <c r="H11" s="5" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="I11" s="4" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="J11" s="4" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="M11" s="5">
         <v>4</v>
       </c>
       <c r="N11" s="5" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="O11" s="4" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="P11" s="4" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="12" spans="1:18" ht="45" x14ac:dyDescent="0.25">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="12" spans="1:18" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A12" s="5">
         <v>5</v>
       </c>
       <c r="B12" s="4" t="s">
+        <v>132</v>
+      </c>
+      <c r="C12" s="4" t="s">
         <v>133</v>
       </c>
-      <c r="C12" s="4" t="s">
-        <v>134</v>
-      </c>
       <c r="D12" s="4" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="M12" s="5">
         <v>5</v>
       </c>
       <c r="N12" s="5" t="s">
+        <v>143</v>
+      </c>
+      <c r="O12" s="4" t="s">
         <v>144</v>
       </c>
-      <c r="O12" s="4" t="s">
-        <v>145</v>
-      </c>
       <c r="P12" s="4" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="13" spans="1:18" ht="45" x14ac:dyDescent="0.25">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="13" spans="1:18" ht="29" x14ac:dyDescent="0.35">
       <c r="A13" s="5">
         <v>6</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="M13" s="5">
         <v>6</v>
       </c>
       <c r="N13" s="5" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="O13" s="4" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="P13" s="4" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.25">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.35">
       <c r="M14">
         <v>7</v>
       </c>
       <c r="N14" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="O14" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="P14" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="15" spans="1:18" ht="45" x14ac:dyDescent="0.25">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="15" spans="1:18" ht="29" x14ac:dyDescent="0.35">
       <c r="M15" s="5">
         <v>8</v>
       </c>
       <c r="N15" s="5" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="O15" s="5" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="P15" s="4" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.25">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="16" spans="1:18" x14ac:dyDescent="0.35">
       <c r="M16">
         <v>9</v>
       </c>
       <c r="N16" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="O16" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="P16" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="17" spans="13:16" ht="45" x14ac:dyDescent="0.25">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="17" spans="13:16" ht="29" x14ac:dyDescent="0.35">
       <c r="M17">
         <v>10</v>
       </c>
       <c r="N17" s="5" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="O17" s="5" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="P17" s="4" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="18" spans="13:16" x14ac:dyDescent="0.25">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="18" spans="13:16" x14ac:dyDescent="0.35">
       <c r="M18" s="5">
         <v>11</v>
       </c>
       <c r="N18" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="O18" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="P18" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="19" spans="13:16" x14ac:dyDescent="0.25">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="19" spans="13:16" x14ac:dyDescent="0.35">
       <c r="M19">
         <v>12</v>
       </c>
       <c r="N19" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="O19" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="P19" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="20" spans="13:16" x14ac:dyDescent="0.25">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="20" spans="13:16" x14ac:dyDescent="0.35">
       <c r="M20" s="5">
         <v>13</v>
       </c>
       <c r="N20" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="O20" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="P20" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="21" spans="13:16" x14ac:dyDescent="0.25">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="21" spans="13:16" x14ac:dyDescent="0.35">
       <c r="M21">
         <v>14</v>
       </c>
       <c r="N21" t="s">
+        <v>112</v>
+      </c>
+      <c r="O21" t="s">
         <v>113</v>
       </c>
-      <c r="O21" t="s">
-        <v>114</v>
-      </c>
       <c r="P21" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="15">
+    <mergeCell ref="A4:F5"/>
+    <mergeCell ref="A6:F6"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A3:B3"/>
+    <mergeCell ref="A2:B2"/>
     <mergeCell ref="M1:R1"/>
     <mergeCell ref="M2:N2"/>
     <mergeCell ref="M3:N3"/>
@@ -3726,11 +3735,6 @@
     <mergeCell ref="G2:H2"/>
     <mergeCell ref="G3:H3"/>
     <mergeCell ref="G1:L1"/>
-    <mergeCell ref="A4:F5"/>
-    <mergeCell ref="A6:F6"/>
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A3:B3"/>
-    <mergeCell ref="A2:B2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3739,29 +3743,29 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{31B60B4E-CDD0-4CEE-BA63-4F898D2F5023}">
   <dimension ref="A1:R25"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="5" customWidth="1"/>
-    <col min="2" max="2" width="22.140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.5703125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="31.140625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="18.42578125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="16.140625" style="9" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="22.1796875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.54296875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="31.1796875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="18.453125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="16.1796875" style="9" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="5" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="30.42578125" customWidth="1"/>
-    <col min="9" max="9" width="27.5703125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="30.28515625" customWidth="1"/>
-    <col min="11" max="11" width="18.42578125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="16.140625" style="9" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="30.453125" customWidth="1"/>
+    <col min="9" max="9" width="27.54296875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="30.26953125" customWidth="1"/>
+    <col min="11" max="11" width="18.453125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="16.1796875" style="9" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="5" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="35.42578125" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="20.5703125" customWidth="1"/>
-    <col min="16" max="16" width="31.140625" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="18.42578125" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="16.140625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="35.453125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="20.54296875" customWidth="1"/>
+    <col min="16" max="16" width="31.1796875" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="18.453125" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="16.1796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A1" s="16" t="s">
         <v>16</v>
       </c>
@@ -3779,7 +3783,7 @@
       <c r="K1" s="16"/>
       <c r="L1" s="17"/>
       <c r="M1" s="16" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="N1" s="16"/>
       <c r="O1" s="16"/>
@@ -3787,7 +3791,7 @@
       <c r="Q1" s="16"/>
       <c r="R1" s="16"/>
     </row>
-    <row r="2" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A2" s="16" t="s">
         <v>3</v>
       </c>
@@ -3822,9 +3826,9 @@
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A3" s="16" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B3" s="16"/>
       <c r="C3" s="8" t="str">
@@ -3839,7 +3843,7 @@
         <v>Not Implemented</v>
       </c>
       <c r="G3" s="16" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="H3" s="16"/>
       <c r="I3" s="8" t="str">
@@ -3854,7 +3858,7 @@
         <v>Not Implemented</v>
       </c>
       <c r="M3" s="16" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="N3" s="16"/>
       <c r="O3" s="14" t="str">
@@ -3869,7 +3873,7 @@
         <v>Not Implemented</v>
       </c>
     </row>
-    <row r="4" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A4" s="16" t="s">
         <v>6</v>
       </c>
@@ -3895,7 +3899,7 @@
       <c r="Q4" s="16"/>
       <c r="R4" s="16"/>
     </row>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A5" s="16"/>
       <c r="B5" s="16"/>
       <c r="C5" s="16"/>
@@ -3915,7 +3919,7 @@
       <c r="Q5" s="16"/>
       <c r="R5" s="16"/>
     </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A6" s="16" t="s">
         <v>7</v>
       </c>
@@ -3941,7 +3945,7 @@
       <c r="Q6" s="16"/>
       <c r="R6" s="16"/>
     </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A7" s="1" t="s">
         <v>0</v>
       </c>
@@ -3997,386 +4001,391 @@
         <v>2</v>
       </c>
     </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A8" s="5">
         <v>1</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="G8">
         <v>1</v>
       </c>
       <c r="H8" s="5" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="I8" s="5" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="J8" s="5" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="M8">
         <v>1</v>
       </c>
       <c r="N8" s="5" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="O8" s="5" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="P8" s="5" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="9" spans="1:18" ht="45" x14ac:dyDescent="0.25">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A9" s="5">
         <v>2</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G9">
         <v>2</v>
       </c>
       <c r="H9" s="4" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="I9" s="4" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="J9" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="M9">
         <v>2</v>
       </c>
       <c r="N9" s="4" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="O9" s="4" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="P9" s="4" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="10" spans="1:18" ht="45" x14ac:dyDescent="0.25">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="10" spans="1:18" ht="29" x14ac:dyDescent="0.35">
       <c r="G10">
         <v>3</v>
       </c>
       <c r="H10" s="4" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="I10" s="4" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="J10" s="4" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="M10">
         <v>3</v>
       </c>
       <c r="N10" s="4" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="O10" s="4" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="P10" s="4" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.25">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.35">
       <c r="G11">
         <v>4</v>
       </c>
       <c r="H11" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="I11" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="J11" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="M11">
         <v>4</v>
       </c>
       <c r="N11" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="O11" t="s">
+        <v>89</v>
+      </c>
+      <c r="P11" t="s">
         <v>90</v>
       </c>
-      <c r="P11" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.25">
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.35">
       <c r="G12">
         <v>5</v>
       </c>
       <c r="H12" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="I12" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="J12" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="M12">
         <v>5</v>
       </c>
       <c r="N12" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="O12" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="P12" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.25">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.35">
       <c r="G13">
         <v>6</v>
       </c>
       <c r="H13" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="I13" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="J13" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="M13">
         <v>6</v>
       </c>
       <c r="N13" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="O13" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="P13" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.25">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.35">
       <c r="G14">
         <v>7</v>
       </c>
       <c r="H14" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="M14">
         <v>8</v>
       </c>
       <c r="N14" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="O14" t="s">
+        <v>89</v>
+      </c>
+      <c r="P14" t="s">
         <v>90</v>
       </c>
-      <c r="P14" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.25">
+    </row>
+    <row r="15" spans="1:18" x14ac:dyDescent="0.35">
       <c r="G15">
         <v>8</v>
       </c>
       <c r="H15" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="I15" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="J15" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="M15">
         <v>9</v>
       </c>
       <c r="N15" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="O15" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="P15" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.25">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="16" spans="1:18" x14ac:dyDescent="0.35">
       <c r="G16">
         <v>9</v>
       </c>
       <c r="H16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="I16" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="J16" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="M16">
         <v>10</v>
       </c>
       <c r="N16" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="O16" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="P16" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="17" spans="7:10" x14ac:dyDescent="0.25">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="17" spans="7:10" x14ac:dyDescent="0.35">
       <c r="G17">
         <v>10</v>
       </c>
       <c r="H17" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="I17" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="J17" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="18" spans="7:10" x14ac:dyDescent="0.25">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="18" spans="7:10" x14ac:dyDescent="0.35">
       <c r="G18">
         <v>11</v>
       </c>
       <c r="H18" t="s">
+        <v>101</v>
+      </c>
+      <c r="I18" t="s">
         <v>102</v>
       </c>
-      <c r="I18" t="s">
+      <c r="J18" t="s">
         <v>103</v>
       </c>
-      <c r="J18" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="19" spans="7:10" x14ac:dyDescent="0.25">
+    </row>
+    <row r="19" spans="7:10" x14ac:dyDescent="0.35">
       <c r="G19">
         <v>12</v>
       </c>
       <c r="H19" t="s">
+        <v>88</v>
+      </c>
+      <c r="I19" t="s">
         <v>89</v>
       </c>
-      <c r="I19" t="s">
+      <c r="J19" t="s">
         <v>90</v>
       </c>
-      <c r="J19" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="20" spans="7:10" x14ac:dyDescent="0.25">
+    </row>
+    <row r="20" spans="7:10" x14ac:dyDescent="0.35">
       <c r="G20">
         <v>13</v>
       </c>
       <c r="H20" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="I20" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="J20" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="21" spans="7:10" x14ac:dyDescent="0.25">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="21" spans="7:10" x14ac:dyDescent="0.35">
       <c r="G21">
         <v>14</v>
       </c>
       <c r="H21" t="s">
+        <v>106</v>
+      </c>
+      <c r="I21" t="s">
+        <v>108</v>
+      </c>
+      <c r="J21" t="s">
         <v>107</v>
       </c>
-      <c r="I21" t="s">
-        <v>109</v>
-      </c>
-      <c r="J21" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="22" spans="7:10" x14ac:dyDescent="0.25">
+    </row>
+    <row r="22" spans="7:10" x14ac:dyDescent="0.35">
       <c r="G22">
         <v>15</v>
       </c>
       <c r="H22" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="I22" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="J22" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="23" spans="7:10" x14ac:dyDescent="0.25">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="23" spans="7:10" x14ac:dyDescent="0.35">
       <c r="G23">
         <v>16</v>
       </c>
       <c r="H23" t="s">
+        <v>106</v>
+      </c>
+      <c r="I23" t="s">
+        <v>108</v>
+      </c>
+      <c r="J23" t="s">
         <v>107</v>
       </c>
-      <c r="I23" t="s">
-        <v>109</v>
-      </c>
-      <c r="J23" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="24" spans="7:10" x14ac:dyDescent="0.25">
+    </row>
+    <row r="24" spans="7:10" x14ac:dyDescent="0.35">
       <c r="G24">
         <v>17</v>
       </c>
       <c r="H24" t="s">
+        <v>112</v>
+      </c>
+      <c r="I24" t="s">
         <v>113</v>
       </c>
-      <c r="I24" t="s">
+      <c r="J24" t="s">
         <v>114</v>
       </c>
-      <c r="J24" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="25" spans="7:10" x14ac:dyDescent="0.25">
+    </row>
+    <row r="25" spans="7:10" x14ac:dyDescent="0.35">
       <c r="G25">
         <v>18</v>
       </c>
       <c r="H25" t="s">
+        <v>101</v>
+      </c>
+      <c r="I25" t="s">
         <v>102</v>
       </c>
-      <c r="I25" t="s">
-        <v>103</v>
-      </c>
       <c r="J25" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="15">
+    <mergeCell ref="A4:F5"/>
+    <mergeCell ref="A6:F6"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="A3:B3"/>
     <mergeCell ref="M1:R1"/>
     <mergeCell ref="M2:N2"/>
     <mergeCell ref="M3:N3"/>
@@ -4387,11 +4396,6 @@
     <mergeCell ref="G2:H2"/>
     <mergeCell ref="G3:H3"/>
     <mergeCell ref="G1:L1"/>
-    <mergeCell ref="A4:F5"/>
-    <mergeCell ref="A6:F6"/>
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="A3:B3"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -4400,30 +4404,29 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{791F26CA-73F7-4CFD-B892-FF534C61ED87}">
   <dimension ref="A1:R11"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="5" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="21.85546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.5703125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="31.140625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="18.42578125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="16.140625" style="9" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="21.81640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.54296875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="31.1796875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="18.453125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="16.1796875" style="9" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="5" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="22.42578125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="19.7109375" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="28.5703125" customWidth="1"/>
-    <col min="11" max="11" width="18.42578125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="16.140625" style="9" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="22.453125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="19.7265625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="28.54296875" customWidth="1"/>
+    <col min="11" max="11" width="18.453125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="16.1796875" style="9" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="5" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="22.42578125" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="22.85546875" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="32.42578125" customWidth="1"/>
-    <col min="17" max="17" width="18.42578125" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="16.140625" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="8.7109375"/>
+    <col min="14" max="14" width="22.453125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="22.81640625" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="32.453125" customWidth="1"/>
+    <col min="17" max="17" width="18.453125" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="16.1796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A1" s="16" t="s">
         <v>18</v>
       </c>
@@ -4449,7 +4452,7 @@
       <c r="Q1" s="16"/>
       <c r="R1" s="16"/>
     </row>
-    <row r="2" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A2" s="16" t="s">
         <v>3</v>
       </c>
@@ -4484,9 +4487,9 @@
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A3" s="16" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B3" s="16"/>
       <c r="C3" s="8" t="str">
@@ -4501,7 +4504,7 @@
         <v>Not Implemented</v>
       </c>
       <c r="G3" s="16" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="H3" s="16"/>
       <c r="I3" s="8" t="str">
@@ -4516,7 +4519,7 @@
         <v>Not Implemented</v>
       </c>
       <c r="M3" s="16" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="N3" s="16"/>
       <c r="O3" s="8" t="str">
@@ -4531,55 +4534,55 @@
         <v>Not Implemented</v>
       </c>
     </row>
-    <row r="4" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A4" s="19" t="s">
+    <row r="4" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A4" s="20" t="s">
+        <v>70</v>
+      </c>
+      <c r="B4" s="20"/>
+      <c r="C4" s="20"/>
+      <c r="D4" s="20"/>
+      <c r="E4" s="20"/>
+      <c r="F4" s="21"/>
+      <c r="G4" s="19" t="s">
+        <v>6</v>
+      </c>
+      <c r="H4" s="20"/>
+      <c r="I4" s="20"/>
+      <c r="J4" s="20"/>
+      <c r="K4" s="20"/>
+      <c r="L4" s="21"/>
+      <c r="M4" s="20" t="s">
+        <v>6</v>
+      </c>
+      <c r="N4" s="20"/>
+      <c r="O4" s="20"/>
+      <c r="P4" s="20"/>
+      <c r="Q4" s="20"/>
+      <c r="R4" s="20"/>
+    </row>
+    <row r="5" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A5" s="20"/>
+      <c r="B5" s="20"/>
+      <c r="C5" s="20"/>
+      <c r="D5" s="20"/>
+      <c r="E5" s="20"/>
+      <c r="F5" s="21"/>
+      <c r="G5" s="19"/>
+      <c r="H5" s="20"/>
+      <c r="I5" s="20"/>
+      <c r="J5" s="20"/>
+      <c r="K5" s="20"/>
+      <c r="L5" s="21"/>
+      <c r="M5" s="20"/>
+      <c r="N5" s="20"/>
+      <c r="O5" s="20"/>
+      <c r="P5" s="20"/>
+      <c r="Q5" s="20"/>
+      <c r="R5" s="20"/>
+    </row>
+    <row r="6" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A6" s="16" t="s">
         <v>71</v>
-      </c>
-      <c r="B4" s="19"/>
-      <c r="C4" s="19"/>
-      <c r="D4" s="19"/>
-      <c r="E4" s="19"/>
-      <c r="F4" s="20"/>
-      <c r="G4" s="21" t="s">
-        <v>6</v>
-      </c>
-      <c r="H4" s="19"/>
-      <c r="I4" s="19"/>
-      <c r="J4" s="19"/>
-      <c r="K4" s="19"/>
-      <c r="L4" s="20"/>
-      <c r="M4" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="N4" s="19"/>
-      <c r="O4" s="19"/>
-      <c r="P4" s="19"/>
-      <c r="Q4" s="19"/>
-      <c r="R4" s="19"/>
-    </row>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A5" s="19"/>
-      <c r="B5" s="19"/>
-      <c r="C5" s="19"/>
-      <c r="D5" s="19"/>
-      <c r="E5" s="19"/>
-      <c r="F5" s="20"/>
-      <c r="G5" s="21"/>
-      <c r="H5" s="19"/>
-      <c r="I5" s="19"/>
-      <c r="J5" s="19"/>
-      <c r="K5" s="19"/>
-      <c r="L5" s="20"/>
-      <c r="M5" s="19"/>
-      <c r="N5" s="19"/>
-      <c r="O5" s="19"/>
-      <c r="P5" s="19"/>
-      <c r="Q5" s="19"/>
-      <c r="R5" s="19"/>
-    </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A6" s="16" t="s">
-        <v>72</v>
       </c>
       <c r="B6" s="16"/>
       <c r="C6" s="16"/>
@@ -4603,7 +4606,7 @@
       <c r="Q6" s="16"/>
       <c r="R6" s="16"/>
     </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A7" s="1" t="s">
         <v>0</v>
       </c>
@@ -4659,130 +4662,135 @@
         <v>2</v>
       </c>
     </row>
-    <row r="8" spans="1:18" s="4" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:18" s="4" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A8" s="4">
         <v>1</v>
       </c>
       <c r="B8" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="D8" s="4" t="s">
         <v>73</v>
-      </c>
-      <c r="C8" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="D8" s="4" t="s">
-        <v>74</v>
       </c>
       <c r="F8" s="15"/>
       <c r="G8" s="4">
         <v>1</v>
       </c>
       <c r="H8" s="4" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="I8" s="4" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="J8" s="4" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="L8" s="15"/>
       <c r="M8" s="4">
         <v>1</v>
       </c>
       <c r="N8" s="4" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="O8" s="4" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="P8" s="4" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="9" spans="1:18" s="4" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18" s="4" customFormat="1" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A9" s="4">
         <v>2</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F9" s="15"/>
       <c r="G9" s="4">
         <v>2</v>
       </c>
       <c r="H9" s="4" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="I9" s="4" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="J9" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="L9" s="15"/>
       <c r="M9" s="4">
         <v>2</v>
       </c>
       <c r="N9" s="4" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="O9" s="4" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="P9" s="4" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="10" spans="1:18" s="4" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="10" spans="1:18" s="4" customFormat="1" ht="29" x14ac:dyDescent="0.35">
       <c r="F10" s="15"/>
       <c r="G10" s="4">
         <v>3</v>
       </c>
       <c r="H10" s="4" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="I10" s="4" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="J10" s="4" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="L10" s="15"/>
       <c r="M10" s="4">
         <v>3</v>
       </c>
       <c r="N10" s="4" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="O10" s="4" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="P10" s="4" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="11" spans="1:18" ht="30" x14ac:dyDescent="0.25">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="11" spans="1:18" ht="29" x14ac:dyDescent="0.35">
       <c r="M11" s="4">
         <v>4</v>
       </c>
       <c r="N11" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="O11" s="4" t="s">
         <v>84</v>
       </c>
-      <c r="O11" s="4" t="s">
+      <c r="P11" s="4" t="s">
         <v>85</v>
-      </c>
-      <c r="P11" s="4" t="s">
-        <v>86</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="15">
+    <mergeCell ref="A4:F5"/>
+    <mergeCell ref="A6:F6"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="A3:B3"/>
     <mergeCell ref="M1:R1"/>
     <mergeCell ref="M2:N2"/>
     <mergeCell ref="M3:N3"/>
@@ -4793,11 +4801,6 @@
     <mergeCell ref="G2:H2"/>
     <mergeCell ref="G3:H3"/>
     <mergeCell ref="G1:L1"/>
-    <mergeCell ref="A4:F5"/>
-    <mergeCell ref="A6:F6"/>
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="A3:B3"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -4806,40 +4809,40 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E4413619-C528-4B04-A1ED-B4C77CA83066}">
   <dimension ref="A1:AD12"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="5" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="25.140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="17.5703125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="15.28515625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="18.42578125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="8.7109375" style="9"/>
+    <col min="2" max="2" width="25.1796875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17.54296875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15.26953125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="18.453125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="8.7265625" style="9"/>
     <col min="7" max="7" width="5" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="23.7109375" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="48.85546875" customWidth="1"/>
-    <col min="10" max="10" width="17.5703125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="18.42578125" customWidth="1"/>
-    <col min="12" max="12" width="8.7109375" style="9"/>
+    <col min="8" max="8" width="23.7265625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="48.81640625" customWidth="1"/>
+    <col min="10" max="10" width="17.54296875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="18.453125" customWidth="1"/>
+    <col min="12" max="12" width="8.7265625" style="9"/>
     <col min="13" max="13" width="5" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="21.5703125" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="30.85546875" customWidth="1"/>
-    <col min="16" max="16" width="15.28515625" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="18.42578125" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="8.7109375" style="9"/>
+    <col min="14" max="14" width="21.54296875" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="30.81640625" customWidth="1"/>
+    <col min="16" max="16" width="15.26953125" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="18.453125" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="8.7265625" style="9"/>
     <col min="19" max="19" width="5" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="23.28515625" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="23.26953125" bestFit="1" customWidth="1"/>
     <col min="21" max="21" width="41" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="15.28515625" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="18.42578125" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="8.7109375" style="9"/>
+    <col min="22" max="22" width="15.26953125" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="18.453125" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="8.7265625" style="9"/>
     <col min="25" max="25" width="5" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="19.140625" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="11.5703125" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="15.28515625" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="18.42578125" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="19.1796875" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="11.54296875" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="15.26953125" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="18.453125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A1" s="16" t="s">
         <v>11</v>
       </c>
@@ -4873,7 +4876,7 @@
       <c r="W1" s="16"/>
       <c r="X1" s="17"/>
       <c r="Y1" s="16" t="s">
-        <v>24</v>
+        <v>190</v>
       </c>
       <c r="Z1" s="16"/>
       <c r="AA1" s="16"/>
@@ -4881,7 +4884,7 @@
       <c r="AC1" s="16"/>
       <c r="AD1" s="16"/>
     </row>
-    <row r="2" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A2" s="16" t="s">
         <v>3</v>
       </c>
@@ -4938,9 +4941,9 @@
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A3" s="16" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B3" s="16"/>
       <c r="C3" t="str">
@@ -4955,7 +4958,7 @@
         <v>High</v>
       </c>
       <c r="G3" s="16" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="H3" s="16"/>
       <c r="I3" s="8" t="str">
@@ -4970,7 +4973,7 @@
         <v>High</v>
       </c>
       <c r="M3" s="16" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="N3" s="16"/>
       <c r="O3" s="8" t="str">
@@ -4985,7 +4988,7 @@
         <v>Medium</v>
       </c>
       <c r="S3" s="16" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="T3" s="16"/>
       <c r="U3" s="8" t="str">
@@ -5000,7 +5003,7 @@
         <v>Low</v>
       </c>
       <c r="Y3" s="16" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="Z3" s="16"/>
       <c r="AA3" s="8" t="str">
@@ -5015,83 +5018,83 @@
         <v>High</v>
       </c>
     </row>
-    <row r="4" spans="1:30" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="19" t="s">
+    <row r="4" spans="1:30" s="2" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="20" t="s">
         <v>12</v>
       </c>
-      <c r="B4" s="19"/>
-      <c r="C4" s="19"/>
-      <c r="D4" s="19"/>
-      <c r="E4" s="19"/>
-      <c r="F4" s="20"/>
-      <c r="G4" s="19" t="s">
+      <c r="B4" s="20"/>
+      <c r="C4" s="20"/>
+      <c r="D4" s="20"/>
+      <c r="E4" s="20"/>
+      <c r="F4" s="21"/>
+      <c r="G4" s="20" t="s">
+        <v>67</v>
+      </c>
+      <c r="H4" s="20"/>
+      <c r="I4" s="20"/>
+      <c r="J4" s="20"/>
+      <c r="K4" s="20"/>
+      <c r="L4" s="21"/>
+      <c r="M4" s="19" t="s">
+        <v>12</v>
+      </c>
+      <c r="N4" s="20"/>
+      <c r="O4" s="20"/>
+      <c r="P4" s="20"/>
+      <c r="Q4" s="20"/>
+      <c r="R4" s="21"/>
+      <c r="S4" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="T4" s="20"/>
+      <c r="U4" s="20"/>
+      <c r="V4" s="20"/>
+      <c r="W4" s="20"/>
+      <c r="X4" s="21"/>
+      <c r="Y4" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="Z4" s="20"/>
+      <c r="AA4" s="20"/>
+      <c r="AB4" s="20"/>
+      <c r="AC4" s="20"/>
+      <c r="AD4" s="20"/>
+    </row>
+    <row r="5" spans="1:30" s="2" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="20"/>
+      <c r="B5" s="20"/>
+      <c r="C5" s="20"/>
+      <c r="D5" s="20"/>
+      <c r="E5" s="20"/>
+      <c r="F5" s="21"/>
+      <c r="G5" s="20"/>
+      <c r="H5" s="20"/>
+      <c r="I5" s="20"/>
+      <c r="J5" s="20"/>
+      <c r="K5" s="20"/>
+      <c r="L5" s="21"/>
+      <c r="M5" s="19"/>
+      <c r="N5" s="20"/>
+      <c r="O5" s="20"/>
+      <c r="P5" s="20"/>
+      <c r="Q5" s="20"/>
+      <c r="R5" s="21"/>
+      <c r="S5" s="20"/>
+      <c r="T5" s="20"/>
+      <c r="U5" s="20"/>
+      <c r="V5" s="20"/>
+      <c r="W5" s="20"/>
+      <c r="X5" s="21"/>
+      <c r="Y5" s="20"/>
+      <c r="Z5" s="20"/>
+      <c r="AA5" s="20"/>
+      <c r="AB5" s="20"/>
+      <c r="AC5" s="20"/>
+      <c r="AD5" s="20"/>
+    </row>
+    <row r="6" spans="1:30" x14ac:dyDescent="0.35">
+      <c r="A6" s="16" t="s">
         <v>68</v>
-      </c>
-      <c r="H4" s="19"/>
-      <c r="I4" s="19"/>
-      <c r="J4" s="19"/>
-      <c r="K4" s="19"/>
-      <c r="L4" s="20"/>
-      <c r="M4" s="21" t="s">
-        <v>12</v>
-      </c>
-      <c r="N4" s="19"/>
-      <c r="O4" s="19"/>
-      <c r="P4" s="19"/>
-      <c r="Q4" s="19"/>
-      <c r="R4" s="20"/>
-      <c r="S4" s="19" t="s">
-        <v>12</v>
-      </c>
-      <c r="T4" s="19"/>
-      <c r="U4" s="19"/>
-      <c r="V4" s="19"/>
-      <c r="W4" s="19"/>
-      <c r="X4" s="20"/>
-      <c r="Y4" s="19" t="s">
-        <v>12</v>
-      </c>
-      <c r="Z4" s="19"/>
-      <c r="AA4" s="19"/>
-      <c r="AB4" s="19"/>
-      <c r="AC4" s="19"/>
-      <c r="AD4" s="19"/>
-    </row>
-    <row r="5" spans="1:30" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="19"/>
-      <c r="B5" s="19"/>
-      <c r="C5" s="19"/>
-      <c r="D5" s="19"/>
-      <c r="E5" s="19"/>
-      <c r="F5" s="20"/>
-      <c r="G5" s="19"/>
-      <c r="H5" s="19"/>
-      <c r="I5" s="19"/>
-      <c r="J5" s="19"/>
-      <c r="K5" s="19"/>
-      <c r="L5" s="20"/>
-      <c r="M5" s="21"/>
-      <c r="N5" s="19"/>
-      <c r="O5" s="19"/>
-      <c r="P5" s="19"/>
-      <c r="Q5" s="19"/>
-      <c r="R5" s="20"/>
-      <c r="S5" s="19"/>
-      <c r="T5" s="19"/>
-      <c r="U5" s="19"/>
-      <c r="V5" s="19"/>
-      <c r="W5" s="19"/>
-      <c r="X5" s="20"/>
-      <c r="Y5" s="19"/>
-      <c r="Z5" s="19"/>
-      <c r="AA5" s="19"/>
-      <c r="AB5" s="19"/>
-      <c r="AC5" s="19"/>
-      <c r="AD5" s="19"/>
-    </row>
-    <row r="6" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A6" s="16" t="s">
-        <v>69</v>
       </c>
       <c r="B6" s="16"/>
       <c r="C6" s="16"/>
@@ -5099,7 +5102,7 @@
       <c r="E6" s="16"/>
       <c r="F6" s="17"/>
       <c r="G6" s="16" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="H6" s="16"/>
       <c r="I6" s="16"/>
@@ -5107,7 +5110,7 @@
       <c r="K6" s="16"/>
       <c r="L6" s="17"/>
       <c r="M6" s="18" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="N6" s="16"/>
       <c r="O6" s="16"/>
@@ -5115,7 +5118,7 @@
       <c r="Q6" s="16"/>
       <c r="R6" s="17"/>
       <c r="S6" s="16" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="T6" s="16"/>
       <c r="U6" s="16"/>
@@ -5123,7 +5126,7 @@
       <c r="W6" s="16"/>
       <c r="X6" s="17"/>
       <c r="Y6" s="16" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="Z6" s="16"/>
       <c r="AA6" s="16"/>
@@ -5131,7 +5134,7 @@
       <c r="AC6" s="16"/>
       <c r="AD6" s="16"/>
     </row>
-    <row r="7" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A7" s="1" t="s">
         <v>0</v>
       </c>
@@ -5223,229 +5226,231 @@
         <v>2</v>
       </c>
     </row>
-    <row r="8" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A8">
         <v>1</v>
       </c>
       <c r="B8" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C8" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D8" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="G8">
         <v>1</v>
       </c>
       <c r="H8" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="I8" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="J8" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="M8">
         <v>1</v>
       </c>
       <c r="N8" t="s">
+        <v>40</v>
+      </c>
+      <c r="O8" t="s">
+        <v>26</v>
+      </c>
+      <c r="P8" t="s">
         <v>41</v>
-      </c>
-      <c r="O8" t="s">
-        <v>27</v>
-      </c>
-      <c r="P8" t="s">
-        <v>42</v>
       </c>
       <c r="S8">
         <v>1</v>
       </c>
       <c r="T8" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="U8" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="Y8">
         <v>1</v>
       </c>
       <c r="Z8" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="AA8" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="AB8" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="9" spans="1:30" ht="75" x14ac:dyDescent="0.25">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="9" spans="1:30" ht="58" x14ac:dyDescent="0.35">
       <c r="A9">
         <v>2</v>
       </c>
       <c r="B9" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C9" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D9" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G9">
         <v>2</v>
       </c>
       <c r="H9" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="M9">
         <v>2</v>
       </c>
       <c r="N9" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="O9" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="O9" s="2" t="s">
+      <c r="P9" s="2" t="s">
         <v>44</v>
-      </c>
-      <c r="P9" s="2" t="s">
-        <v>45</v>
       </c>
       <c r="S9">
         <v>2</v>
       </c>
       <c r="T9" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="U9" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="Y9">
         <v>2</v>
       </c>
       <c r="Z9" t="s">
-        <v>64</v>
+        <v>191</v>
       </c>
       <c r="AA9" t="s">
-        <v>27</v>
+        <v>192</v>
       </c>
       <c r="AB9" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="10" spans="1:30" x14ac:dyDescent="0.25">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="10" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A10">
         <v>3</v>
       </c>
       <c r="B10" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C10" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D10" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G10">
         <v>3</v>
       </c>
       <c r="H10" t="s">
+        <v>49</v>
+      </c>
+      <c r="I10" t="s">
         <v>50</v>
       </c>
-      <c r="I10" t="s">
-        <v>51</v>
-      </c>
       <c r="J10" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="M10">
         <v>3</v>
       </c>
       <c r="N10" t="s">
+        <v>45</v>
+      </c>
+      <c r="O10" t="s">
         <v>46</v>
       </c>
-      <c r="O10" t="s">
+      <c r="P10" s="3" t="s">
         <v>47</v>
-      </c>
-      <c r="P10" s="3" t="s">
-        <v>48</v>
       </c>
       <c r="S10">
         <v>3</v>
       </c>
       <c r="T10" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="U10" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="11" spans="1:30" x14ac:dyDescent="0.25">
+        <v>60</v>
+      </c>
+      <c r="Y10">
+        <v>3</v>
+      </c>
+      <c r="Z10" t="s">
+        <v>63</v>
+      </c>
+      <c r="AA10" t="s">
+        <v>26</v>
+      </c>
+      <c r="AB10" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="11" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A11">
         <v>4</v>
       </c>
       <c r="B11" t="s">
+        <v>29</v>
+      </c>
+      <c r="C11" t="s">
         <v>30</v>
       </c>
-      <c r="C11" t="s">
-        <v>31</v>
-      </c>
       <c r="D11" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="S11">
         <v>4</v>
       </c>
       <c r="T11" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="U11" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="12" spans="1:30" x14ac:dyDescent="0.25">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="12" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A12">
         <v>5</v>
       </c>
       <c r="B12" t="s">
+        <v>31</v>
+      </c>
+      <c r="C12" t="s">
         <v>32</v>
       </c>
-      <c r="C12" t="s">
-        <v>33</v>
-      </c>
       <c r="D12" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="S12">
         <v>5</v>
       </c>
       <c r="T12" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="U12" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="25">
-    <mergeCell ref="Y1:AD1"/>
-    <mergeCell ref="Y2:Z2"/>
-    <mergeCell ref="Y3:Z3"/>
-    <mergeCell ref="S4:X5"/>
-    <mergeCell ref="S6:X6"/>
-    <mergeCell ref="Y4:AD5"/>
-    <mergeCell ref="Y6:AD6"/>
-    <mergeCell ref="S2:T2"/>
-    <mergeCell ref="S3:T3"/>
-    <mergeCell ref="S1:X1"/>
     <mergeCell ref="A4:F5"/>
     <mergeCell ref="A6:F6"/>
     <mergeCell ref="A1:F1"/>
@@ -5461,6 +5466,16 @@
     <mergeCell ref="G3:H3"/>
     <mergeCell ref="M2:N2"/>
     <mergeCell ref="M3:N3"/>
+    <mergeCell ref="Y1:AD1"/>
+    <mergeCell ref="Y2:Z2"/>
+    <mergeCell ref="Y3:Z3"/>
+    <mergeCell ref="S4:X5"/>
+    <mergeCell ref="S6:X6"/>
+    <mergeCell ref="Y4:AD5"/>
+    <mergeCell ref="Y6:AD6"/>
+    <mergeCell ref="S2:T2"/>
+    <mergeCell ref="S3:T3"/>
+    <mergeCell ref="S1:X1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Test Cases.xlsx
+++ b/Test Cases.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://endresshauser-my.sharepoint.com/personal/corbin_ferguson_endress_com/Documents/Thesis Work/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1637" documentId="11_AD4DB114E441178AC67DF4D41ED1D894683EDF27" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1D848577-258C-4138-9A60-41B0653B7391}"/>
+  <xr:revisionPtr revIDLastSave="1699" documentId="11_AD4DB114E441178AC67DF4D41ED1D894683EDF27" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F63269EF-56D4-480B-B9BE-A1F71BFA4520}"/>
   <bookViews>
     <workbookView xWindow="53880" yWindow="-5145" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -66,7 +66,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="526" uniqueCount="194">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="495" uniqueCount="187">
   <si>
     <t>Step</t>
   </si>
@@ -101,12 +101,6 @@
     <t>Status</t>
   </si>
   <si>
-    <t>New File Creation</t>
-  </si>
-  <si>
-    <t>Description: Test the creation of an empty template file, overwriting the existing file.</t>
-  </si>
-  <si>
     <t>Import Select Redundant Name</t>
   </si>
   <si>
@@ -131,15 +125,6 @@
     <t>Delete Module by Port</t>
   </si>
   <si>
-    <t>Save File</t>
-  </si>
-  <si>
-    <t>Load File</t>
-  </si>
-  <si>
-    <t>Validate File</t>
-  </si>
-  <si>
     <t>"New File" Button Pressed</t>
   </si>
   <si>
@@ -155,18 +140,6 @@
     <t>"ok" button Press</t>
   </si>
   <si>
-    <t>Repeat step 1</t>
-  </si>
-  <si>
-    <t>"new" button press</t>
-  </si>
-  <si>
-    <t>Cancel File Creation</t>
-  </si>
-  <si>
-    <t>"No Button Press"</t>
-  </si>
-  <si>
     <t>"Save File" Button Pressed</t>
   </si>
   <si>
@@ -197,64 +170,18 @@
     <t>File to load selected</t>
   </si>
   <si>
-    <t>C:\Users\i01505732\OneDrive - Endress+Hauser\Thesis Work\CodeProjects\L5XFiles\TemplateFiles\BasicControllertags.L5X</t>
-  </si>
-  <si>
     <t>doc object in Execute.cs updated to new object</t>
   </si>
   <si>
-    <t>Verify New File Loaded</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Check </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>one of the subobjects</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>subobject</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> exists</t>
-    </r>
-  </si>
-  <si>
     <t>Confirm File Creation</t>
   </si>
   <si>
-    <t>Verify File Saved</t>
-  </si>
-  <si>
-    <t>Check file exists at expected location</t>
-  </si>
-  <si>
     <t>"Validate" button pressed</t>
   </si>
   <si>
     <t>Preconditions: Empty template file loaded into application</t>
   </si>
   <si>
-    <t>"Ok"</t>
-  </si>
-  <si>
     <t>Load File with error</t>
   </si>
   <si>
@@ -270,9 +197,6 @@
     <t>New file created at location, return to action select window</t>
   </si>
   <si>
-    <t>File found</t>
-  </si>
-  <si>
     <t>File successfully loaded</t>
   </si>
   <si>
@@ -294,13 +218,7 @@
     <t>Launch exe</t>
   </si>
   <si>
-    <t>Description: Test the saving of a file.</t>
-  </si>
-  <si>
     <t>Preconditions: None</t>
-  </si>
-  <si>
-    <t>Preconditions: File to load.</t>
   </si>
   <si>
     <t>Description: Testing that attempting to delete an element when no element exists causes a popup</t>
@@ -859,9 +777,6 @@
     <t>Test Priority:</t>
   </si>
   <si>
-    <t>Test Priority: Low</t>
-  </si>
-  <si>
     <t>Select Quantity</t>
   </si>
   <si>
@@ -878,6 +793,45 @@
   </si>
   <si>
     <t>button names match list</t>
+  </si>
+  <si>
+    <t>Verify all buttons onscreen</t>
+  </si>
+  <si>
+    <t>buttons</t>
+  </si>
+  <si>
+    <t>no buttons found offscreen</t>
+  </si>
+  <si>
+    <t>Description: Test that the ActionSelect window launches with all necessary buttons, and that the exit button closes the window.</t>
+  </si>
+  <si>
+    <t>FileManagementTesting</t>
+  </si>
+  <si>
+    <t>"Ok" pressed</t>
+  </si>
+  <si>
+    <t>Description: Test that the file manipulation buttons are functional.</t>
+  </si>
+  <si>
+    <t>ValidateFileButton</t>
+  </si>
+  <si>
+    <t>OK</t>
+  </si>
+  <si>
+    <t>LoadFileButton</t>
+  </si>
+  <si>
+    <t>.\Thesis Work\CodeProjects\L5XFiles\TestingFiles\BrokenXML.L5X</t>
+  </si>
+  <si>
+    <t>Description: Test that action select cannot be manipulated during operations.</t>
+  </si>
+  <si>
+    <t>ActionSelectLosecontrol</t>
   </si>
 </sst>
 </file>
@@ -953,13 +907,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -1004,6 +957,19 @@
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1939,7 +1905,7 @@
     <xdr:to>
       <xdr:col>13</xdr:col>
       <xdr:colOff>217487</xdr:colOff>
-      <xdr:row>15</xdr:row>
+      <xdr:row>12</xdr:row>
       <xdr:rowOff>66675</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
@@ -2114,8 +2080,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{8C34A821-A8AD-4FEE-8065-115AD927679E}" name="TestMaster" displayName="TestMaster" ref="A1:E16">
-  <autoFilter ref="A1:E16" xr:uid="{8C34A821-A8AD-4FEE-8065-115AD927679E}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{8C34A821-A8AD-4FEE-8065-115AD927679E}" name="TestMaster" displayName="TestMaster" ref="A1:E14">
+  <autoFilter ref="A1:E14" xr:uid="{8C34A821-A8AD-4FEE-8065-115AD927679E}"/>
   <tableColumns count="5">
     <tableColumn id="1" xr3:uid="{0D10C69B-6EC1-4AEC-8C25-C7145B24EE5C}" name="Test ID" totalsRowLabel="Total" dataDxfId="6">
       <calculatedColumnFormula>ROW()-1</calculatedColumnFormula>
@@ -2394,12 +2360,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F8512478-31DB-4352-AB46-996C676231F3}">
-  <dimension ref="A1:I16"/>
+  <dimension ref="A1:I14"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="10.453125" customWidth="1"/>
     <col min="2" max="2" width="34.1796875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="16.1796875" style="6" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="16.1796875" style="5" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="18.453125" hidden="1" customWidth="1"/>
     <col min="5" max="5" width="13.453125" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="16.1796875" bestFit="1" customWidth="1"/>
@@ -2408,55 +2374,55 @@
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
-        <v>157</v>
+        <v>138</v>
       </c>
       <c r="B1" t="s">
-        <v>158</v>
-      </c>
-      <c r="C1" s="6" t="s">
-        <v>159</v>
+        <v>139</v>
+      </c>
+      <c r="C1" s="5" t="s">
+        <v>140</v>
       </c>
       <c r="D1" t="s">
-        <v>161</v>
+        <v>142</v>
       </c>
       <c r="E1" t="s">
-        <v>165</v>
+        <v>146</v>
       </c>
       <c r="G1">
         <f>COUNTIF(TestMaster[Test Status], "Not Implemented")</f>
-        <v>15</v>
-      </c>
-      <c r="H1" s="7" t="s">
-        <v>169</v>
+        <v>13</v>
+      </c>
+      <c r="H1" s="6" t="s">
+        <v>150</v>
       </c>
       <c r="I1" t="s">
-        <v>171</v>
+        <v>152</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A2">
-        <f t="shared" ref="A2:A16" si="0">ROW()-1</f>
+        <f t="shared" ref="A2:A13" si="0">ROW()-1</f>
         <v>1</v>
       </c>
       <c r="B2" t="str" cm="1">
         <f t="array" ref="B2">'Element Import Testing'!A1:A1</f>
         <v>Import Select Redundant Name</v>
       </c>
-      <c r="C2" s="6" t="s">
-        <v>163</v>
+      <c r="C2" s="5" t="s">
+        <v>144</v>
       </c>
       <c r="D2" t="s">
-        <v>162</v>
+        <v>143</v>
       </c>
       <c r="E2" t="s">
-        <v>167</v>
+        <v>148</v>
       </c>
       <c r="G2">
         <f>COUNTIF(TestMaster[Test Status], "Pass")</f>
         <v>0</v>
       </c>
-      <c r="H2" s="8" t="s">
-        <v>163</v>
+      <c r="H2" s="7" t="s">
+        <v>144</v>
       </c>
       <c r="I2">
         <v>17</v>
@@ -2471,21 +2437,21 @@
         <f t="array" ref="B3">'Element Creation Testing'!A1:A1</f>
         <v>Element Quantity Creation</v>
       </c>
-      <c r="C3" s="6" t="s">
-        <v>163</v>
+      <c r="C3" s="5" t="s">
+        <v>144</v>
       </c>
       <c r="D3" t="s">
-        <v>164</v>
+        <v>145</v>
       </c>
       <c r="E3" t="s">
-        <v>166</v>
+        <v>147</v>
       </c>
       <c r="G3">
         <f>COUNTIF(TestMaster[Test Status], "Fail")</f>
         <v>0</v>
       </c>
-      <c r="H3" s="8" t="s">
-        <v>170</v>
+      <c r="H3" s="7" t="s">
+        <v>151</v>
       </c>
       <c r="I3">
         <v>17</v>
@@ -2500,11 +2466,11 @@
         <f t="array" ref="B4">'Element Creation Testing'!G1:G1</f>
         <v>Nameless Module Creation</v>
       </c>
-      <c r="C4" s="6" t="s">
-        <v>163</v>
+      <c r="C4" s="5" t="s">
+        <v>144</v>
       </c>
       <c r="E4" t="s">
-        <v>167</v>
+        <v>148</v>
       </c>
       <c r="G4">
         <f>COUNTIF(TestMaster[Test Status], "Not Run")</f>
@@ -2520,11 +2486,11 @@
         <f t="array" ref="B5">'Element Creation Testing'!M1:M1</f>
         <v>Redundant Element Creation</v>
       </c>
-      <c r="C5" s="6" t="s">
-        <v>163</v>
+      <c r="C5" s="5" t="s">
+        <v>144</v>
       </c>
       <c r="E5" t="s">
-        <v>168</v>
+        <v>149</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.35">
@@ -2536,11 +2502,11 @@
         <f>'Element Modification Testing'!A1</f>
         <v>No Element to Modify</v>
       </c>
-      <c r="C6" s="6" t="s">
-        <v>163</v>
+      <c r="C6" s="5" t="s">
+        <v>144</v>
       </c>
       <c r="E6" t="s">
-        <v>167</v>
+        <v>148</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.35">
@@ -2552,11 +2518,11 @@
         <f>'Element Modification Testing'!G1</f>
         <v>Completed Element Modification</v>
       </c>
-      <c r="C7" s="6" t="s">
-        <v>163</v>
+      <c r="C7" s="5" t="s">
+        <v>144</v>
       </c>
       <c r="E7" t="s">
-        <v>167</v>
+        <v>148</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.35">
@@ -2568,11 +2534,11 @@
         <f>'Element Modification Testing'!M1</f>
         <v>Modify into Redundant Element Name</v>
       </c>
-      <c r="C8" s="6" t="s">
-        <v>163</v>
+      <c r="C8" s="5" t="s">
+        <v>144</v>
       </c>
       <c r="E8" t="s">
-        <v>168</v>
+        <v>149</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.35">
@@ -2584,11 +2550,11 @@
         <f>'Element Deletion Testing'!A1</f>
         <v>Delete No Element Type</v>
       </c>
-      <c r="C9" s="6" t="s">
-        <v>163</v>
+      <c r="C9" s="5" t="s">
+        <v>144</v>
       </c>
       <c r="E9" t="s">
-        <v>167</v>
+        <v>148</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.35">
@@ -2600,11 +2566,11 @@
         <f>'Element Deletion Testing'!G1</f>
         <v>Delete Element Found</v>
       </c>
-      <c r="C10" s="6" t="s">
-        <v>163</v>
+      <c r="C10" s="5" t="s">
+        <v>144</v>
       </c>
       <c r="E10" t="s">
-        <v>167</v>
+        <v>148</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.35">
@@ -2616,11 +2582,11 @@
         <f>'Element Deletion Testing'!M1</f>
         <v>Delete Module by Port</v>
       </c>
-      <c r="C11" s="6" t="s">
-        <v>163</v>
+      <c r="C11" s="5" t="s">
+        <v>144</v>
       </c>
       <c r="E11" t="s">
-        <v>168</v>
+        <v>149</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.35">
@@ -2630,13 +2596,13 @@
       </c>
       <c r="B12" t="str">
         <f>'File Manipulation Testing'!A1</f>
-        <v>New File Creation</v>
-      </c>
-      <c r="C12" s="6" t="s">
-        <v>163</v>
+        <v>FileManagementTesting</v>
+      </c>
+      <c r="C12" s="5" t="s">
+        <v>144</v>
       </c>
       <c r="E12" t="s">
-        <v>166</v>
+        <v>147</v>
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.35">
@@ -2646,61 +2612,29 @@
       </c>
       <c r="B13" t="str">
         <f>'File Manipulation Testing'!G1</f>
-        <v>Save File</v>
-      </c>
-      <c r="C13" s="6" t="s">
-        <v>163</v>
+        <v>ActionSelectLayout</v>
+      </c>
+      <c r="C13" s="5" t="s">
+        <v>144</v>
       </c>
       <c r="E13" t="s">
-        <v>166</v>
+        <v>147</v>
       </c>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A14">
-        <f t="shared" si="0"/>
+      <c r="A14" s="21">
+        <f>ROW()-1</f>
         <v>13</v>
       </c>
-      <c r="B14" t="str">
+      <c r="B14" s="21" t="str">
         <f>'File Manipulation Testing'!M1</f>
-        <v>Load File</v>
-      </c>
-      <c r="C14" s="6" t="s">
-        <v>163</v>
+        <v>ActionSelectLosecontrol</v>
+      </c>
+      <c r="C14" s="5" t="s">
+        <v>144</v>
       </c>
       <c r="E14" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A15">
-        <f t="shared" si="0"/>
-        <v>14</v>
-      </c>
-      <c r="B15" t="str">
-        <f>'File Manipulation Testing'!S1</f>
-        <v>Validate File</v>
-      </c>
-      <c r="C15" s="6" t="s">
-        <v>163</v>
-      </c>
-      <c r="E15" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A16">
-        <f t="shared" si="0"/>
-        <v>15</v>
-      </c>
-      <c r="B16" t="str">
-        <f>'File Manipulation Testing'!Y1</f>
-        <v>ActionSelectLayout</v>
-      </c>
-      <c r="C16" s="6" t="s">
-        <v>163</v>
-      </c>
-      <c r="E16" t="s">
-        <v>166</v>
+        <v>148</v>
       </c>
     </row>
   </sheetData>
@@ -2719,7 +2653,7 @@
       <formula>NOT(ISERROR(SEARCH("Not Implemented",C1)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C17:C1048576">
+  <conditionalFormatting sqref="C15:C1048576">
     <cfRule type="colorScale" priority="5">
       <colorScale>
         <cfvo type="min"/>
@@ -2733,7 +2667,7 @@
   </conditionalFormatting>
   <dataValidations count="2">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C1:C1048576" xr:uid="{130BDE1A-E0D9-44C7-AF19-F67B1FE4D5D4}">
-      <formula1>$D$2:$D$16</formula1>
+      <formula1>$D$2:$D$14</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E2:E1048576" xr:uid="{0649BA16-611B-4B21-AD1C-F4AC893E68EF}">
       <formula1>"Low,Medium,High"</formula1>
@@ -2760,25 +2694,25 @@
     <col min="3" max="3" width="48.81640625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="56.7265625" style="2" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="18.453125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="16.1796875" style="9" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="16.1796875" style="8" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A1" s="16" t="s">
-        <v>13</v>
-      </c>
-      <c r="B1" s="16"/>
-      <c r="C1" s="16"/>
-      <c r="D1" s="16"/>
-      <c r="E1" s="16"/>
-      <c r="F1" s="17"/>
+      <c r="A1" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="B1" s="15"/>
+      <c r="C1" s="15"/>
+      <c r="D1" s="15"/>
+      <c r="E1" s="15"/>
+      <c r="F1" s="16"/>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A2" s="16" t="s">
+      <c r="A2" s="15" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="16"/>
-      <c r="C2" s="8">
+      <c r="B2" s="15"/>
+      <c r="C2" s="7">
         <f>IFERROR(_xlfn.XLOOKUP(A1, TestMaster[Test Name], TestMaster[Test ID], "ID not found"), "")</f>
         <v>1</v>
       </c>
@@ -2787,49 +2721,49 @@
       </c>
     </row>
     <row r="3" spans="1:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="16" t="s">
-        <v>186</v>
-      </c>
-      <c r="B3" s="16"/>
-      <c r="C3" s="10" t="str">
+      <c r="A3" s="15" t="s">
+        <v>167</v>
+      </c>
+      <c r="B3" s="15"/>
+      <c r="C3" s="9" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(A1, TestMaster[Test Name], TestMaster[Test Priority], "Priority not found"), "")</f>
         <v>Medium</v>
       </c>
       <c r="E3" t="s">
         <v>5</v>
       </c>
-      <c r="F3" s="9" t="str">
+      <c r="F3" s="8" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(A1, TestMaster[Test Name], TestMaster[Test Status], "Status not found"), "")</f>
         <v>Not Implemented</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A4" s="16" t="s">
-        <v>183</v>
-      </c>
-      <c r="B4" s="16"/>
-      <c r="C4" s="16"/>
-      <c r="D4" s="16"/>
-      <c r="E4" s="16"/>
-      <c r="F4" s="17"/>
+      <c r="A4" s="15" t="s">
+        <v>164</v>
+      </c>
+      <c r="B4" s="15"/>
+      <c r="C4" s="15"/>
+      <c r="D4" s="15"/>
+      <c r="E4" s="15"/>
+      <c r="F4" s="16"/>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A5" s="16"/>
-      <c r="B5" s="16"/>
-      <c r="C5" s="16"/>
-      <c r="D5" s="16"/>
-      <c r="E5" s="16"/>
-      <c r="F5" s="17"/>
+      <c r="A5" s="15"/>
+      <c r="B5" s="15"/>
+      <c r="C5" s="15"/>
+      <c r="D5" s="15"/>
+      <c r="E5" s="15"/>
+      <c r="F5" s="16"/>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A6" s="16" t="s">
+      <c r="A6" s="15" t="s">
         <v>7</v>
       </c>
-      <c r="B6" s="16"/>
-      <c r="C6" s="16"/>
-      <c r="D6" s="16"/>
-      <c r="E6" s="16"/>
-      <c r="F6" s="17"/>
+      <c r="B6" s="15"/>
+      <c r="C6" s="15"/>
+      <c r="D6" s="15"/>
+      <c r="E6" s="15"/>
+      <c r="F6" s="16"/>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A7" s="1" t="s">
@@ -2841,13 +2775,13 @@
       <c r="C7" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="D7" s="11" t="s">
+      <c r="D7" s="10" t="s">
         <v>1</v>
       </c>
       <c r="E7" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="F7" s="12" t="s">
+      <c r="F7" s="11" t="s">
         <v>2</v>
       </c>
     </row>
@@ -2856,268 +2790,268 @@
         <v>1</v>
       </c>
       <c r="B8" t="s">
-        <v>174</v>
+        <v>155</v>
       </c>
       <c r="C8" t="s">
-        <v>175</v>
+        <v>156</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>176</v>
+        <v>157</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="29" x14ac:dyDescent="0.35">
-      <c r="A9" s="5">
+      <c r="A9" s="4">
         <f>A8+1</f>
         <v>2</v>
       </c>
-      <c r="B9" s="4" t="s">
-        <v>172</v>
-      </c>
-      <c r="C9" s="4" t="s">
-        <v>173</v>
-      </c>
-      <c r="D9" s="4" t="s">
-        <v>123</v>
+      <c r="B9" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>104</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A10" s="5">
+      <c r="A10" s="4">
         <f>A9+1</f>
         <v>3</v>
       </c>
-      <c r="B10" s="4" t="s">
-        <v>124</v>
-      </c>
-      <c r="C10" s="4" t="s">
-        <v>139</v>
-      </c>
-      <c r="D10" s="4" t="s">
-        <v>125</v>
+      <c r="B10" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>106</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A11" s="5">
+      <c r="A11" s="4">
         <f t="shared" ref="A11:A25" si="0">A10+1</f>
         <v>4</v>
       </c>
-      <c r="B11" s="4" t="s">
-        <v>177</v>
-      </c>
-      <c r="C11" s="4" t="s">
-        <v>140</v>
-      </c>
-      <c r="D11" s="4" t="s">
-        <v>185</v>
+      <c r="B11" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>166</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A12" s="5">
+      <c r="A12" s="4">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="B12" s="4" t="s">
-        <v>178</v>
-      </c>
-      <c r="C12" s="4" t="s">
-        <v>27</v>
+      <c r="B12" s="3" t="s">
+        <v>159</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>22</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>179</v>
+        <v>160</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A13" s="5">
+      <c r="A13" s="4">
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
-      <c r="B13" s="4" t="s">
-        <v>124</v>
-      </c>
-      <c r="C13" s="4" t="s">
-        <v>139</v>
-      </c>
-      <c r="D13" s="4" t="s">
-        <v>125</v>
+      <c r="B13" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>106</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A14" s="5">
+      <c r="A14" s="4">
         <f t="shared" si="0"/>
         <v>7</v>
       </c>
-      <c r="B14" s="4" t="s">
-        <v>177</v>
-      </c>
-      <c r="C14" s="4" t="s">
-        <v>140</v>
-      </c>
-      <c r="D14" s="4" t="s">
-        <v>181</v>
+      <c r="B14" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="D14" s="3" t="s">
+        <v>162</v>
       </c>
     </row>
     <row r="15" spans="1:6" ht="29" x14ac:dyDescent="0.35">
-      <c r="A15" s="5">
+      <c r="A15" s="4">
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
       <c r="B15" t="s">
-        <v>106</v>
+        <v>87</v>
       </c>
       <c r="C15" t="s">
-        <v>110</v>
+        <v>91</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>180</v>
+        <v>161</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A16" s="5">
+      <c r="A16" s="4">
         <f t="shared" si="0"/>
         <v>9</v>
       </c>
-      <c r="B16" s="4" t="s">
-        <v>178</v>
-      </c>
-      <c r="C16" s="4" t="s">
-        <v>27</v>
+      <c r="B16" s="3" t="s">
+        <v>159</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>22</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>179</v>
+        <v>160</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A17" s="5">
+      <c r="A17" s="4">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="B17" s="4" t="s">
-        <v>124</v>
-      </c>
-      <c r="C17" s="4" t="s">
-        <v>139</v>
-      </c>
-      <c r="D17" s="4" t="s">
-        <v>125</v>
+      <c r="B17" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="D17" s="3" t="s">
+        <v>106</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A18" s="5">
+      <c r="A18" s="4">
         <f t="shared" si="0"/>
         <v>11</v>
       </c>
-      <c r="B18" s="4" t="s">
-        <v>177</v>
-      </c>
-      <c r="C18" s="4" t="s">
-        <v>140</v>
-      </c>
-      <c r="D18" s="4" t="s">
-        <v>127</v>
+      <c r="B18" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="D18" s="3" t="s">
+        <v>108</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A19" s="5">
+      <c r="A19" s="4">
         <f t="shared" si="0"/>
         <v>12</v>
       </c>
       <c r="B19" t="s">
-        <v>106</v>
+        <v>87</v>
       </c>
       <c r="C19" t="s">
-        <v>122</v>
+        <v>103</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>151</v>
+        <v>132</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A20" s="5">
+      <c r="A20" s="4">
         <f t="shared" si="0"/>
         <v>13</v>
       </c>
-      <c r="B20" s="4" t="s">
-        <v>178</v>
-      </c>
-      <c r="C20" s="4" t="s">
-        <v>27</v>
+      <c r="B20" s="3" t="s">
+        <v>159</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>22</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>179</v>
+        <v>160</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A21" s="5">
+      <c r="A21" s="4">
         <f t="shared" si="0"/>
         <v>14</v>
       </c>
       <c r="B21" t="s">
-        <v>106</v>
+        <v>87</v>
       </c>
       <c r="C21" t="s">
-        <v>108</v>
+        <v>89</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>155</v>
+        <v>136</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A22" s="5">
+      <c r="A22" s="4">
         <f t="shared" si="0"/>
         <v>15</v>
       </c>
       <c r="B22" t="s">
-        <v>111</v>
-      </c>
-      <c r="C22" s="4" t="s">
-        <v>184</v>
+        <v>92</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>165</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>109</v>
+        <v>90</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A23" s="5">
+      <c r="A23" s="4">
         <f t="shared" si="0"/>
         <v>16</v>
       </c>
       <c r="B23" t="s">
-        <v>106</v>
+        <v>87</v>
       </c>
       <c r="C23" t="s">
-        <v>108</v>
+        <v>89</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>155</v>
+        <v>136</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A24" s="5">
+      <c r="A24" s="4">
         <f t="shared" si="0"/>
         <v>17</v>
       </c>
       <c r="B24" t="s">
-        <v>112</v>
+        <v>93</v>
       </c>
       <c r="C24" t="s">
-        <v>113</v>
+        <v>94</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>156</v>
+        <v>137</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A25" s="5">
+      <c r="A25" s="4">
         <f t="shared" si="0"/>
         <v>18</v>
       </c>
-      <c r="B25" s="4" t="s">
-        <v>178</v>
-      </c>
-      <c r="C25" s="4" t="s">
-        <v>182</v>
+      <c r="B25" s="3" t="s">
+        <v>159</v>
+      </c>
+      <c r="C25" s="3" t="s">
+        <v>163</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
     </row>
   </sheetData>
@@ -3137,135 +3071,135 @@
   <dimension ref="A1:R21"/>
   <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="5" style="5" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="34.453125" style="5" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="24.81640625" style="5" customWidth="1"/>
-    <col min="4" max="4" width="35.54296875" style="5" customWidth="1"/>
-    <col min="5" max="5" width="18.453125" style="5" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="16.1796875" style="13" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="5" style="5" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="29.1796875" style="5" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="24.1796875" style="5" customWidth="1"/>
-    <col min="10" max="10" width="24" style="5" customWidth="1"/>
-    <col min="11" max="11" width="18.453125" style="5" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="16.1796875" style="13" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="5" style="5" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="29.1796875" style="5" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="25.54296875" style="5" customWidth="1"/>
-    <col min="16" max="16" width="23.81640625" style="5" customWidth="1"/>
-    <col min="17" max="17" width="18.453125" style="5" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="16.1796875" style="5" bestFit="1" customWidth="1"/>
-    <col min="19" max="16384" width="8.7265625" style="5"/>
+    <col min="1" max="1" width="5" style="4" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="34.453125" style="4" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="24.81640625" style="4" customWidth="1"/>
+    <col min="4" max="4" width="35.54296875" style="4" customWidth="1"/>
+    <col min="5" max="5" width="18.453125" style="4" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="16.1796875" style="12" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="5" style="4" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="29.1796875" style="4" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="24.1796875" style="4" customWidth="1"/>
+    <col min="10" max="10" width="24" style="4" customWidth="1"/>
+    <col min="11" max="11" width="18.453125" style="4" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="16.1796875" style="12" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="5" style="4" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="29.1796875" style="4" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="25.54296875" style="4" customWidth="1"/>
+    <col min="16" max="16" width="23.81640625" style="4" customWidth="1"/>
+    <col min="17" max="17" width="18.453125" style="4" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="16.1796875" style="4" bestFit="1" customWidth="1"/>
+    <col min="19" max="16384" width="8.7265625" style="4"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:18" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="16" t="s">
-        <v>14</v>
-      </c>
-      <c r="B1" s="16"/>
-      <c r="C1" s="16"/>
-      <c r="D1" s="16"/>
-      <c r="E1" s="16"/>
-      <c r="F1" s="17"/>
-      <c r="G1" s="16" t="s">
-        <v>15</v>
-      </c>
-      <c r="H1" s="16"/>
-      <c r="I1" s="16"/>
-      <c r="J1" s="16"/>
-      <c r="K1" s="16"/>
-      <c r="L1" s="16"/>
-      <c r="M1" s="16" t="s">
-        <v>160</v>
-      </c>
-      <c r="N1" s="16"/>
-      <c r="O1" s="16"/>
-      <c r="P1" s="16"/>
-      <c r="Q1" s="16"/>
-      <c r="R1" s="16"/>
+      <c r="A1" s="15" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1" s="15"/>
+      <c r="C1" s="15"/>
+      <c r="D1" s="15"/>
+      <c r="E1" s="15"/>
+      <c r="F1" s="16"/>
+      <c r="G1" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="H1" s="15"/>
+      <c r="I1" s="15"/>
+      <c r="J1" s="15"/>
+      <c r="K1" s="15"/>
+      <c r="L1" s="15"/>
+      <c r="M1" s="15" t="s">
+        <v>141</v>
+      </c>
+      <c r="N1" s="15"/>
+      <c r="O1" s="15"/>
+      <c r="P1" s="15"/>
+      <c r="Q1" s="15"/>
+      <c r="R1" s="15"/>
     </row>
     <row r="2" spans="1:18" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="16" t="s">
+      <c r="A2" s="15" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="16"/>
+      <c r="B2" s="15"/>
       <c r="C2">
         <f>IFERROR(_xlfn.XLOOKUP(A1, TestMaster[Test Name], TestMaster[Test ID], "ID not found"), "")</f>
         <v>2</v>
       </c>
-      <c r="D2" s="5"/>
+      <c r="D2" s="4"/>
       <c r="E2" t="s">
         <v>4</v>
       </c>
-      <c r="F2" s="9"/>
-      <c r="G2" s="16" t="s">
+      <c r="F2" s="8"/>
+      <c r="G2" s="15" t="s">
         <v>3</v>
       </c>
-      <c r="H2" s="16"/>
+      <c r="H2" s="15"/>
       <c r="I2">
         <f>IFERROR(_xlfn.XLOOKUP(G1, TestMaster[Test Name], TestMaster[Test ID], "ID not found"), "")</f>
         <v>3</v>
       </c>
-      <c r="J2" s="5"/>
+      <c r="J2" s="4"/>
       <c r="K2" t="s">
         <v>4</v>
       </c>
-      <c r="L2" s="9"/>
-      <c r="M2" s="16" t="s">
+      <c r="L2" s="8"/>
+      <c r="M2" s="15" t="s">
         <v>3</v>
       </c>
-      <c r="N2" s="16"/>
+      <c r="N2" s="15"/>
       <c r="O2">
         <f>IFERROR(_xlfn.XLOOKUP(M1, TestMaster[Test Name], TestMaster[Test ID], "ID not found"), "")</f>
         <v>4</v>
       </c>
-      <c r="P2" s="5"/>
+      <c r="P2" s="4"/>
       <c r="Q2" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="3" spans="1:18" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="16" t="s">
-        <v>186</v>
-      </c>
-      <c r="B3" s="16"/>
+      <c r="A3" s="15" t="s">
+        <v>167</v>
+      </c>
+      <c r="B3" s="15"/>
       <c r="C3" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(A1, TestMaster[Test Name], TestMaster[Test Priority], "Priority not found"), "")</f>
         <v>High</v>
       </c>
-      <c r="D3" s="5"/>
+      <c r="D3" s="4"/>
       <c r="E3" t="s">
         <v>5</v>
       </c>
-      <c r="F3" s="9" t="str">
+      <c r="F3" s="8" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(A1, TestMaster[Test Name], TestMaster[Test Status], "Status not found"), "")</f>
         <v>Not Implemented</v>
       </c>
-      <c r="G3" s="16" t="s">
-        <v>186</v>
-      </c>
-      <c r="H3" s="16"/>
+      <c r="G3" s="15" t="s">
+        <v>167</v>
+      </c>
+      <c r="H3" s="15"/>
       <c r="I3" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(G1, TestMaster[Test Name], TestMaster[Test Priority], "Priority not found"), "")</f>
         <v>Medium</v>
       </c>
-      <c r="J3" s="5"/>
+      <c r="J3" s="4"/>
       <c r="K3" t="s">
         <v>5</v>
       </c>
-      <c r="L3" s="9" t="str">
+      <c r="L3" s="8" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(G1, TestMaster[Test Name], TestMaster[Test Status], "Status not found"), "")</f>
         <v>Not Implemented</v>
       </c>
-      <c r="M3" s="16" t="s">
-        <v>186</v>
-      </c>
-      <c r="N3" s="16"/>
+      <c r="M3" s="15" t="s">
+        <v>167</v>
+      </c>
+      <c r="N3" s="15"/>
       <c r="O3" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(M1, TestMaster[Test Name], TestMaster[Test Priority], "Priority not found"), "")</f>
         <v>Low</v>
       </c>
-      <c r="P3" s="5"/>
+      <c r="P3" s="4"/>
       <c r="Q3" t="s">
         <v>5</v>
       </c>
@@ -3275,76 +3209,76 @@
       </c>
     </row>
     <row r="4" spans="1:18" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="16" t="s">
+      <c r="A4" s="15" t="s">
         <v>6</v>
       </c>
-      <c r="B4" s="16"/>
-      <c r="C4" s="16"/>
-      <c r="D4" s="16"/>
-      <c r="E4" s="16"/>
-      <c r="F4" s="17"/>
-      <c r="G4" s="16" t="s">
+      <c r="B4" s="15"/>
+      <c r="C4" s="15"/>
+      <c r="D4" s="15"/>
+      <c r="E4" s="15"/>
+      <c r="F4" s="16"/>
+      <c r="G4" s="15" t="s">
         <v>6</v>
       </c>
-      <c r="H4" s="16"/>
-      <c r="I4" s="16"/>
-      <c r="J4" s="16"/>
-      <c r="K4" s="16"/>
-      <c r="L4" s="16"/>
-      <c r="M4" s="16" t="s">
+      <c r="H4" s="15"/>
+      <c r="I4" s="15"/>
+      <c r="J4" s="15"/>
+      <c r="K4" s="15"/>
+      <c r="L4" s="15"/>
+      <c r="M4" s="15" t="s">
         <v>6</v>
       </c>
-      <c r="N4" s="16"/>
-      <c r="O4" s="16"/>
-      <c r="P4" s="16"/>
-      <c r="Q4" s="16"/>
-      <c r="R4" s="16"/>
+      <c r="N4" s="15"/>
+      <c r="O4" s="15"/>
+      <c r="P4" s="15"/>
+      <c r="Q4" s="15"/>
+      <c r="R4" s="15"/>
     </row>
     <row r="5" spans="1:18" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="16"/>
-      <c r="B5" s="16"/>
-      <c r="C5" s="16"/>
-      <c r="D5" s="16"/>
-      <c r="E5" s="16"/>
-      <c r="F5" s="17"/>
-      <c r="G5" s="16"/>
-      <c r="H5" s="16"/>
-      <c r="I5" s="16"/>
-      <c r="J5" s="16"/>
-      <c r="K5" s="16"/>
-      <c r="L5" s="16"/>
-      <c r="M5" s="16"/>
-      <c r="N5" s="16"/>
-      <c r="O5" s="16"/>
-      <c r="P5" s="16"/>
-      <c r="Q5" s="16"/>
-      <c r="R5" s="16"/>
+      <c r="A5" s="15"/>
+      <c r="B5" s="15"/>
+      <c r="C5" s="15"/>
+      <c r="D5" s="15"/>
+      <c r="E5" s="15"/>
+      <c r="F5" s="16"/>
+      <c r="G5" s="15"/>
+      <c r="H5" s="15"/>
+      <c r="I5" s="15"/>
+      <c r="J5" s="15"/>
+      <c r="K5" s="15"/>
+      <c r="L5" s="15"/>
+      <c r="M5" s="15"/>
+      <c r="N5" s="15"/>
+      <c r="O5" s="15"/>
+      <c r="P5" s="15"/>
+      <c r="Q5" s="15"/>
+      <c r="R5" s="15"/>
     </row>
     <row r="6" spans="1:18" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="16" t="s">
+      <c r="A6" s="15" t="s">
         <v>7</v>
       </c>
-      <c r="B6" s="16"/>
-      <c r="C6" s="16"/>
-      <c r="D6" s="16"/>
-      <c r="E6" s="16"/>
-      <c r="F6" s="17"/>
-      <c r="G6" s="16" t="s">
+      <c r="B6" s="15"/>
+      <c r="C6" s="15"/>
+      <c r="D6" s="15"/>
+      <c r="E6" s="15"/>
+      <c r="F6" s="16"/>
+      <c r="G6" s="15" t="s">
         <v>7</v>
       </c>
-      <c r="H6" s="16"/>
-      <c r="I6" s="16"/>
-      <c r="J6" s="16"/>
-      <c r="K6" s="16"/>
-      <c r="L6" s="16"/>
-      <c r="M6" s="16" t="s">
+      <c r="H6" s="15"/>
+      <c r="I6" s="15"/>
+      <c r="J6" s="15"/>
+      <c r="K6" s="15"/>
+      <c r="L6" s="15"/>
+      <c r="M6" s="15" t="s">
         <v>7</v>
       </c>
-      <c r="N6" s="16"/>
-      <c r="O6" s="16"/>
-      <c r="P6" s="16"/>
-      <c r="Q6" s="16"/>
-      <c r="R6" s="16"/>
+      <c r="N6" s="15"/>
+      <c r="O6" s="15"/>
+      <c r="P6" s="15"/>
+      <c r="Q6" s="15"/>
+      <c r="R6" s="15"/>
     </row>
     <row r="7" spans="1:18" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A7" s="1" t="s">
@@ -3362,7 +3296,7 @@
       <c r="E7" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="F7" s="12" t="s">
+      <c r="F7" s="11" t="s">
         <v>2</v>
       </c>
       <c r="G7" s="1" t="s">
@@ -3380,7 +3314,7 @@
       <c r="K7" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="L7" s="12" t="s">
+      <c r="L7" s="11" t="s">
         <v>2</v>
       </c>
       <c r="M7" s="1" t="s">
@@ -3403,207 +3337,207 @@
       </c>
     </row>
     <row r="8" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A8" s="5">
+      <c r="A8" s="4">
         <v>1</v>
       </c>
-      <c r="B8" s="4" t="s">
-        <v>189</v>
-      </c>
-      <c r="C8" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="D8" s="4" t="s">
+      <c r="B8" s="3" t="s">
+        <v>169</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="G8" s="4">
+        <v>1</v>
+      </c>
+      <c r="H8" s="4" t="s">
+        <v>169</v>
+      </c>
+      <c r="I8" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="J8" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="M8" s="4">
+        <v>1</v>
+      </c>
+      <c r="N8" s="4" t="s">
+        <v>169</v>
+      </c>
+      <c r="O8" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="P8" s="3" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A9" s="4">
+        <v>2</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="G9" s="4">
+        <v>2</v>
+      </c>
+      <c r="H9" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="I9" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="J9" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="M9" s="4">
+        <v>2</v>
+      </c>
+      <c r="N9" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="O9" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="P9" s="3" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="10" spans="1:18" ht="29" x14ac:dyDescent="0.35">
+      <c r="A10" s="4">
+        <v>3</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="G10" s="4">
+        <v>3</v>
+      </c>
+      <c r="H10" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="I10" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="J10" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="M10" s="4">
+        <v>3</v>
+      </c>
+      <c r="N10" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="O10" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="P10" s="3" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="11" spans="1:18" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A11" s="4">
+        <v>4</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="G11" s="4">
+        <v>4</v>
+      </c>
+      <c r="H11" s="4" t="s">
+        <v>168</v>
+      </c>
+      <c r="I11" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="J11" s="3" t="s">
         <v>123</v>
       </c>
-      <c r="G8" s="5">
-        <v>1</v>
-      </c>
-      <c r="H8" s="5" t="s">
-        <v>189</v>
-      </c>
-      <c r="I8" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="J8" s="4" t="s">
-        <v>123</v>
-      </c>
-      <c r="M8" s="5">
-        <v>1</v>
-      </c>
-      <c r="N8" s="5" t="s">
-        <v>189</v>
-      </c>
-      <c r="O8" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="P8" s="4" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="9" spans="1:18" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A9" s="5">
-        <v>2</v>
-      </c>
-      <c r="B9" s="4" t="s">
+      <c r="M11" s="4">
+        <v>4</v>
+      </c>
+      <c r="N11" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="O11" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="P11" s="3" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="12" spans="1:18" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A12" s="4">
+        <v>5</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="M12" s="4">
+        <v>5</v>
+      </c>
+      <c r="N12" s="4" t="s">
         <v>124</v>
       </c>
-      <c r="C9" s="4" t="s">
-        <v>139</v>
-      </c>
-      <c r="D9" s="4" t="s">
+      <c r="O12" s="3" t="s">
         <v>125</v>
       </c>
-      <c r="G9" s="5">
-        <v>2</v>
-      </c>
-      <c r="H9" s="5" t="s">
-        <v>124</v>
-      </c>
-      <c r="I9" s="4" t="s">
-        <v>137</v>
-      </c>
-      <c r="J9" s="4" t="s">
-        <v>138</v>
-      </c>
-      <c r="M9" s="5">
-        <v>2</v>
-      </c>
-      <c r="N9" s="5" t="s">
-        <v>124</v>
-      </c>
-      <c r="O9" s="4" t="s">
-        <v>139</v>
-      </c>
-      <c r="P9" s="4" t="s">
+      <c r="P12" s="3" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="13" spans="1:18" ht="29" x14ac:dyDescent="0.35">
+      <c r="A13" s="4">
+        <v>6</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="M13" s="4">
+        <v>6</v>
+      </c>
+      <c r="N13" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="O13" s="3" t="s">
         <v>125</v>
       </c>
-    </row>
-    <row r="10" spans="1:18" ht="29" x14ac:dyDescent="0.35">
-      <c r="A10" s="5">
-        <v>3</v>
-      </c>
-      <c r="B10" s="4" t="s">
-        <v>126</v>
-      </c>
-      <c r="C10" s="4" t="s">
-        <v>140</v>
-      </c>
-      <c r="D10" s="4" t="s">
-        <v>127</v>
-      </c>
-      <c r="G10" s="5">
-        <v>3</v>
-      </c>
-      <c r="H10" s="5" t="s">
-        <v>126</v>
-      </c>
-      <c r="I10" s="4" t="s">
-        <v>141</v>
-      </c>
-      <c r="J10" s="4" t="s">
-        <v>127</v>
-      </c>
-      <c r="M10" s="5">
-        <v>3</v>
-      </c>
-      <c r="N10" s="5" t="s">
-        <v>126</v>
-      </c>
-      <c r="O10" s="4" t="s">
-        <v>140</v>
-      </c>
-      <c r="P10" s="4" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="11" spans="1:18" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A11" s="5">
-        <v>4</v>
-      </c>
-      <c r="B11" s="4" t="s">
+      <c r="P13" s="3" t="s">
         <v>128</v>
-      </c>
-      <c r="C11" s="4" t="s">
-        <v>129</v>
-      </c>
-      <c r="D11" s="4" t="s">
-        <v>130</v>
-      </c>
-      <c r="G11" s="5">
-        <v>4</v>
-      </c>
-      <c r="H11" s="5" t="s">
-        <v>188</v>
-      </c>
-      <c r="I11" s="4" t="s">
-        <v>129</v>
-      </c>
-      <c r="J11" s="4" t="s">
-        <v>142</v>
-      </c>
-      <c r="M11" s="5">
-        <v>4</v>
-      </c>
-      <c r="N11" s="5" t="s">
-        <v>128</v>
-      </c>
-      <c r="O11" s="4" t="s">
-        <v>149</v>
-      </c>
-      <c r="P11" s="4" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="12" spans="1:18" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A12" s="5">
-        <v>5</v>
-      </c>
-      <c r="B12" s="4" t="s">
-        <v>132</v>
-      </c>
-      <c r="C12" s="4" t="s">
-        <v>133</v>
-      </c>
-      <c r="D12" s="4" t="s">
-        <v>135</v>
-      </c>
-      <c r="M12" s="5">
-        <v>5</v>
-      </c>
-      <c r="N12" s="5" t="s">
-        <v>143</v>
-      </c>
-      <c r="O12" s="4" t="s">
-        <v>144</v>
-      </c>
-      <c r="P12" s="4" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="13" spans="1:18" ht="29" x14ac:dyDescent="0.35">
-      <c r="A13" s="5">
-        <v>6</v>
-      </c>
-      <c r="B13" s="4" t="s">
-        <v>134</v>
-      </c>
-      <c r="C13" s="4" t="s">
-        <v>131</v>
-      </c>
-      <c r="D13" s="4" t="s">
-        <v>136</v>
-      </c>
-      <c r="M13" s="5">
-        <v>6</v>
-      </c>
-      <c r="N13" s="5" t="s">
-        <v>145</v>
-      </c>
-      <c r="O13" s="4" t="s">
-        <v>144</v>
-      </c>
-      <c r="P13" s="4" t="s">
-        <v>147</v>
       </c>
     </row>
     <row r="14" spans="1:18" x14ac:dyDescent="0.35">
@@ -3611,27 +3545,27 @@
         <v>7</v>
       </c>
       <c r="N14" t="s">
-        <v>106</v>
+        <v>87</v>
       </c>
       <c r="O14" t="s">
-        <v>110</v>
+        <v>91</v>
       </c>
       <c r="P14" t="s">
-        <v>148</v>
+        <v>129</v>
       </c>
     </row>
     <row r="15" spans="1:18" ht="29" x14ac:dyDescent="0.35">
-      <c r="M15" s="5">
+      <c r="M15" s="4">
         <v>8</v>
       </c>
-      <c r="N15" s="5" t="s">
-        <v>150</v>
-      </c>
-      <c r="O15" s="5" t="s">
-        <v>144</v>
-      </c>
-      <c r="P15" s="4" t="s">
-        <v>147</v>
+      <c r="N15" s="4" t="s">
+        <v>131</v>
+      </c>
+      <c r="O15" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="P15" s="3" t="s">
+        <v>128</v>
       </c>
     </row>
     <row r="16" spans="1:18" x14ac:dyDescent="0.35">
@@ -3639,41 +3573,41 @@
         <v>9</v>
       </c>
       <c r="N16" t="s">
-        <v>106</v>
+        <v>87</v>
       </c>
       <c r="O16" t="s">
-        <v>122</v>
+        <v>103</v>
       </c>
       <c r="P16" t="s">
-        <v>151</v>
+        <v>132</v>
       </c>
     </row>
     <row r="17" spans="13:16" ht="29" x14ac:dyDescent="0.35">
       <c r="M17">
         <v>10</v>
       </c>
-      <c r="N17" s="5" t="s">
-        <v>152</v>
-      </c>
-      <c r="O17" s="5" t="s">
-        <v>144</v>
-      </c>
-      <c r="P17" s="4" t="s">
-        <v>147</v>
+      <c r="N17" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="O17" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="P17" s="3" t="s">
+        <v>128</v>
       </c>
     </row>
     <row r="18" spans="13:16" x14ac:dyDescent="0.35">
-      <c r="M18" s="5">
+      <c r="M18" s="4">
         <v>11</v>
       </c>
       <c r="N18" t="s">
-        <v>106</v>
+        <v>87</v>
       </c>
       <c r="O18" t="s">
-        <v>108</v>
+        <v>89</v>
       </c>
       <c r="P18" t="s">
-        <v>155</v>
+        <v>136</v>
       </c>
     </row>
     <row r="19" spans="13:16" x14ac:dyDescent="0.35">
@@ -3681,27 +3615,27 @@
         <v>12</v>
       </c>
       <c r="N19" t="s">
-        <v>111</v>
+        <v>92</v>
       </c>
       <c r="O19" t="s">
-        <v>144</v>
+        <v>125</v>
       </c>
       <c r="P19" t="s">
-        <v>109</v>
+        <v>90</v>
       </c>
     </row>
     <row r="20" spans="13:16" x14ac:dyDescent="0.35">
-      <c r="M20" s="5">
+      <c r="M20" s="4">
         <v>13</v>
       </c>
       <c r="N20" t="s">
-        <v>106</v>
+        <v>87</v>
       </c>
       <c r="O20" t="s">
-        <v>108</v>
+        <v>89</v>
       </c>
       <c r="P20" t="s">
-        <v>155</v>
+        <v>136</v>
       </c>
     </row>
     <row r="21" spans="13:16" x14ac:dyDescent="0.35">
@@ -3709,13 +3643,13 @@
         <v>14</v>
       </c>
       <c r="N21" t="s">
-        <v>112</v>
+        <v>93</v>
       </c>
       <c r="O21" t="s">
-        <v>113</v>
+        <v>94</v>
       </c>
       <c r="P21" t="s">
-        <v>156</v>
+        <v>137</v>
       </c>
     </row>
   </sheetData>
@@ -3750,13 +3684,13 @@
     <col min="3" max="3" width="11.54296875" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="31.1796875" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="18.453125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="16.1796875" style="9" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="16.1796875" style="8" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="5" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="30.453125" customWidth="1"/>
     <col min="9" max="9" width="27.54296875" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="30.26953125" customWidth="1"/>
     <col min="11" max="11" width="18.453125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="16.1796875" style="9" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="16.1796875" style="8" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="5" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="35.453125" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="20.54296875" customWidth="1"/>
@@ -3766,59 +3700,59 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A1" s="16" t="s">
-        <v>16</v>
-      </c>
-      <c r="B1" s="16"/>
-      <c r="C1" s="16"/>
-      <c r="D1" s="16"/>
-      <c r="E1" s="16"/>
-      <c r="F1" s="17"/>
-      <c r="G1" s="18" t="s">
-        <v>17</v>
-      </c>
-      <c r="H1" s="16"/>
-      <c r="I1" s="16"/>
-      <c r="J1" s="16"/>
-      <c r="K1" s="16"/>
-      <c r="L1" s="17"/>
-      <c r="M1" s="16" t="s">
-        <v>115</v>
-      </c>
-      <c r="N1" s="16"/>
-      <c r="O1" s="16"/>
-      <c r="P1" s="16"/>
-      <c r="Q1" s="16"/>
-      <c r="R1" s="16"/>
+      <c r="A1" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="B1" s="15"/>
+      <c r="C1" s="15"/>
+      <c r="D1" s="15"/>
+      <c r="E1" s="15"/>
+      <c r="F1" s="16"/>
+      <c r="G1" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="H1" s="15"/>
+      <c r="I1" s="15"/>
+      <c r="J1" s="15"/>
+      <c r="K1" s="15"/>
+      <c r="L1" s="16"/>
+      <c r="M1" s="15" t="s">
+        <v>96</v>
+      </c>
+      <c r="N1" s="15"/>
+      <c r="O1" s="15"/>
+      <c r="P1" s="15"/>
+      <c r="Q1" s="15"/>
+      <c r="R1" s="15"/>
     </row>
     <row r="2" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A2" s="16" t="s">
+      <c r="A2" s="15" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="16"/>
-      <c r="C2" s="8">
+      <c r="B2" s="15"/>
+      <c r="C2" s="7">
         <f>IFERROR(_xlfn.XLOOKUP(A1, TestMaster[Test Name], TestMaster[Test ID], "ID not found"), "")</f>
         <v>5</v>
       </c>
       <c r="E2" t="s">
         <v>4</v>
       </c>
-      <c r="G2" s="16" t="s">
+      <c r="G2" s="15" t="s">
         <v>3</v>
       </c>
-      <c r="H2" s="16"/>
-      <c r="I2" s="8">
+      <c r="H2" s="15"/>
+      <c r="I2" s="7">
         <f>IFERROR(_xlfn.XLOOKUP(G1, TestMaster[Test Name], TestMaster[Test ID], "ID not found"), "")</f>
         <v>6</v>
       </c>
       <c r="K2" t="s">
         <v>4</v>
       </c>
-      <c r="M2" s="16" t="s">
+      <c r="M2" s="15" t="s">
         <v>3</v>
       </c>
-      <c r="N2" s="16"/>
-      <c r="O2" s="14">
+      <c r="N2" s="15"/>
+      <c r="O2" s="13">
         <f>IFERROR(_xlfn.XLOOKUP(M1, TestMaster[Test Name], TestMaster[Test ID], "ID not found"), "")</f>
         <v>7</v>
       </c>
@@ -3827,41 +3761,41 @@
       </c>
     </row>
     <row r="3" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A3" s="16" t="s">
-        <v>186</v>
-      </c>
-      <c r="B3" s="16"/>
-      <c r="C3" s="8" t="str">
+      <c r="A3" s="15" t="s">
+        <v>167</v>
+      </c>
+      <c r="B3" s="15"/>
+      <c r="C3" s="7" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(A1, TestMaster[Test Name], TestMaster[Test Priority], "Priority not found"), "")</f>
         <v>Medium</v>
       </c>
       <c r="E3" t="s">
         <v>5</v>
       </c>
-      <c r="F3" s="9" t="str">
+      <c r="F3" s="8" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(A1, TestMaster[Test Name], TestMaster[Test Status], "Status not found"), "")</f>
         <v>Not Implemented</v>
       </c>
-      <c r="G3" s="16" t="s">
-        <v>186</v>
-      </c>
-      <c r="H3" s="16"/>
-      <c r="I3" s="8" t="str">
+      <c r="G3" s="15" t="s">
+        <v>167</v>
+      </c>
+      <c r="H3" s="15"/>
+      <c r="I3" s="7" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(G1, TestMaster[Test Name], TestMaster[Test Priority], "Priority not found"), "")</f>
         <v>Medium</v>
       </c>
       <c r="K3" t="s">
         <v>5</v>
       </c>
-      <c r="L3" s="9" t="str">
+      <c r="L3" s="8" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(G1, TestMaster[Test Name], TestMaster[Test Status], "Status not found"), "")</f>
         <v>Not Implemented</v>
       </c>
-      <c r="M3" s="16" t="s">
-        <v>186</v>
-      </c>
-      <c r="N3" s="16"/>
-      <c r="O3" s="14" t="str">
+      <c r="M3" s="15" t="s">
+        <v>167</v>
+      </c>
+      <c r="N3" s="15"/>
+      <c r="O3" s="13" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(M1, TestMaster[Test Name], TestMaster[Test Priority], "Priority not found"), "")</f>
         <v>Low</v>
       </c>
@@ -3874,76 +3808,76 @@
       </c>
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A4" s="16" t="s">
+      <c r="A4" s="15" t="s">
         <v>6</v>
       </c>
-      <c r="B4" s="16"/>
-      <c r="C4" s="16"/>
-      <c r="D4" s="16"/>
-      <c r="E4" s="16"/>
-      <c r="F4" s="17"/>
-      <c r="G4" s="18" t="s">
+      <c r="B4" s="15"/>
+      <c r="C4" s="15"/>
+      <c r="D4" s="15"/>
+      <c r="E4" s="15"/>
+      <c r="F4" s="16"/>
+      <c r="G4" s="17" t="s">
         <v>6</v>
       </c>
-      <c r="H4" s="16"/>
-      <c r="I4" s="16"/>
-      <c r="J4" s="16"/>
-      <c r="K4" s="16"/>
-      <c r="L4" s="17"/>
-      <c r="M4" s="16" t="s">
+      <c r="H4" s="15"/>
+      <c r="I4" s="15"/>
+      <c r="J4" s="15"/>
+      <c r="K4" s="15"/>
+      <c r="L4" s="16"/>
+      <c r="M4" s="15" t="s">
         <v>6</v>
       </c>
-      <c r="N4" s="16"/>
-      <c r="O4" s="16"/>
-      <c r="P4" s="16"/>
-      <c r="Q4" s="16"/>
-      <c r="R4" s="16"/>
+      <c r="N4" s="15"/>
+      <c r="O4" s="15"/>
+      <c r="P4" s="15"/>
+      <c r="Q4" s="15"/>
+      <c r="R4" s="15"/>
     </row>
     <row r="5" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A5" s="16"/>
-      <c r="B5" s="16"/>
-      <c r="C5" s="16"/>
-      <c r="D5" s="16"/>
-      <c r="E5" s="16"/>
-      <c r="F5" s="17"/>
-      <c r="G5" s="18"/>
-      <c r="H5" s="16"/>
-      <c r="I5" s="16"/>
-      <c r="J5" s="16"/>
-      <c r="K5" s="16"/>
-      <c r="L5" s="17"/>
-      <c r="M5" s="16"/>
-      <c r="N5" s="16"/>
-      <c r="O5" s="16"/>
-      <c r="P5" s="16"/>
-      <c r="Q5" s="16"/>
-      <c r="R5" s="16"/>
+      <c r="A5" s="15"/>
+      <c r="B5" s="15"/>
+      <c r="C5" s="15"/>
+      <c r="D5" s="15"/>
+      <c r="E5" s="15"/>
+      <c r="F5" s="16"/>
+      <c r="G5" s="17"/>
+      <c r="H5" s="15"/>
+      <c r="I5" s="15"/>
+      <c r="J5" s="15"/>
+      <c r="K5" s="15"/>
+      <c r="L5" s="16"/>
+      <c r="M5" s="15"/>
+      <c r="N5" s="15"/>
+      <c r="O5" s="15"/>
+      <c r="P5" s="15"/>
+      <c r="Q5" s="15"/>
+      <c r="R5" s="15"/>
     </row>
     <row r="6" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A6" s="16" t="s">
+      <c r="A6" s="15" t="s">
         <v>7</v>
       </c>
-      <c r="B6" s="16"/>
-      <c r="C6" s="16"/>
-      <c r="D6" s="16"/>
-      <c r="E6" s="16"/>
-      <c r="F6" s="17"/>
-      <c r="G6" s="18" t="s">
+      <c r="B6" s="15"/>
+      <c r="C6" s="15"/>
+      <c r="D6" s="15"/>
+      <c r="E6" s="15"/>
+      <c r="F6" s="16"/>
+      <c r="G6" s="17" t="s">
         <v>7</v>
       </c>
-      <c r="H6" s="16"/>
-      <c r="I6" s="16"/>
-      <c r="J6" s="16"/>
-      <c r="K6" s="16"/>
-      <c r="L6" s="17"/>
-      <c r="M6" s="16" t="s">
+      <c r="H6" s="15"/>
+      <c r="I6" s="15"/>
+      <c r="J6" s="15"/>
+      <c r="K6" s="15"/>
+      <c r="L6" s="16"/>
+      <c r="M6" s="15" t="s">
         <v>7</v>
       </c>
-      <c r="N6" s="16"/>
-      <c r="O6" s="16"/>
-      <c r="P6" s="16"/>
-      <c r="Q6" s="16"/>
-      <c r="R6" s="16"/>
+      <c r="N6" s="15"/>
+      <c r="O6" s="15"/>
+      <c r="P6" s="15"/>
+      <c r="Q6" s="15"/>
+      <c r="R6" s="15"/>
     </row>
     <row r="7" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A7" s="1" t="s">
@@ -3961,7 +3895,7 @@
       <c r="E7" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="F7" s="12" t="s">
+      <c r="F7" s="11" t="s">
         <v>2</v>
       </c>
       <c r="G7" s="1" t="s">
@@ -3979,7 +3913,7 @@
       <c r="K7" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="L7" s="12" t="s">
+      <c r="L7" s="11" t="s">
         <v>2</v>
       </c>
       <c r="M7" s="1" t="s">
@@ -4002,105 +3936,105 @@
       </c>
     </row>
     <row r="8" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A8" s="5">
+      <c r="A8" s="4">
         <v>1</v>
       </c>
-      <c r="B8" s="5" t="s">
-        <v>87</v>
-      </c>
-      <c r="C8" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="D8" s="5" t="s">
-        <v>73</v>
+      <c r="B8" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>54</v>
       </c>
       <c r="G8">
         <v>1</v>
       </c>
-      <c r="H8" s="5" t="s">
-        <v>87</v>
-      </c>
-      <c r="I8" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="J8" s="5" t="s">
-        <v>76</v>
+      <c r="H8" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="I8" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="J8" s="4" t="s">
+        <v>57</v>
       </c>
       <c r="M8">
         <v>1</v>
       </c>
-      <c r="N8" s="5" t="s">
-        <v>87</v>
-      </c>
-      <c r="O8" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="P8" s="5" t="s">
-        <v>76</v>
+      <c r="N8" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="O8" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="P8" s="4" t="s">
+        <v>57</v>
       </c>
     </row>
     <row r="9" spans="1:18" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A9" s="5">
+      <c r="A9" s="4">
         <v>2</v>
       </c>
-      <c r="B9" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="C9" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="D9" s="5" t="s">
+      <c r="B9" s="4" t="s">
         <v>39</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>30</v>
       </c>
       <c r="G9">
         <v>2</v>
       </c>
-      <c r="H9" s="4" t="s">
-        <v>74</v>
-      </c>
-      <c r="I9" s="4" t="s">
-        <v>77</v>
-      </c>
-      <c r="J9" s="4" t="s">
-        <v>79</v>
+      <c r="H9" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="I9" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="J9" s="3" t="s">
+        <v>60</v>
       </c>
       <c r="M9">
         <v>2</v>
       </c>
-      <c r="N9" s="4" t="s">
-        <v>74</v>
-      </c>
-      <c r="O9" s="4" t="s">
-        <v>77</v>
-      </c>
-      <c r="P9" s="4" t="s">
-        <v>79</v>
+      <c r="N9" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="O9" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="P9" s="3" t="s">
+        <v>60</v>
       </c>
     </row>
     <row r="10" spans="1:18" ht="29" x14ac:dyDescent="0.35">
       <c r="G10">
         <v>3</v>
       </c>
-      <c r="H10" s="4" t="s">
-        <v>116</v>
-      </c>
-      <c r="I10" s="4" t="s">
-        <v>99</v>
-      </c>
-      <c r="J10" s="4" t="s">
-        <v>104</v>
+      <c r="H10" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="I10" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="J10" s="3" t="s">
+        <v>85</v>
       </c>
       <c r="M10">
         <v>3</v>
       </c>
-      <c r="N10" s="4" t="s">
-        <v>119</v>
-      </c>
-      <c r="O10" s="4" t="s">
-        <v>99</v>
-      </c>
-      <c r="P10" s="4" t="s">
-        <v>104</v>
+      <c r="N10" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="O10" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="P10" s="3" t="s">
+        <v>85</v>
       </c>
     </row>
     <row r="11" spans="1:18" x14ac:dyDescent="0.35">
@@ -4108,25 +4042,25 @@
         <v>4</v>
       </c>
       <c r="H11" t="s">
-        <v>88</v>
+        <v>69</v>
       </c>
       <c r="I11" t="s">
-        <v>91</v>
+        <v>72</v>
       </c>
       <c r="J11" t="s">
-        <v>90</v>
+        <v>71</v>
       </c>
       <c r="M11">
         <v>4</v>
       </c>
       <c r="N11" t="s">
-        <v>120</v>
+        <v>101</v>
       </c>
       <c r="O11" t="s">
-        <v>89</v>
+        <v>70</v>
       </c>
       <c r="P11" t="s">
-        <v>90</v>
+        <v>71</v>
       </c>
     </row>
     <row r="12" spans="1:18" x14ac:dyDescent="0.35">
@@ -4134,25 +4068,25 @@
         <v>5</v>
       </c>
       <c r="H12" t="s">
-        <v>93</v>
+        <v>74</v>
       </c>
       <c r="I12" t="s">
-        <v>95</v>
+        <v>76</v>
       </c>
       <c r="J12" t="s">
-        <v>97</v>
+        <v>78</v>
       </c>
       <c r="M12">
         <v>5</v>
       </c>
       <c r="N12" t="s">
-        <v>117</v>
+        <v>98</v>
       </c>
       <c r="O12" t="s">
-        <v>95</v>
+        <v>76</v>
       </c>
       <c r="P12" t="s">
-        <v>92</v>
+        <v>73</v>
       </c>
     </row>
     <row r="13" spans="1:18" x14ac:dyDescent="0.35">
@@ -4160,25 +4094,25 @@
         <v>6</v>
       </c>
       <c r="H13" t="s">
-        <v>94</v>
+        <v>75</v>
       </c>
       <c r="I13" t="s">
-        <v>96</v>
+        <v>77</v>
       </c>
       <c r="J13" t="s">
-        <v>98</v>
+        <v>79</v>
       </c>
       <c r="M13">
         <v>6</v>
       </c>
       <c r="N13" t="s">
-        <v>106</v>
+        <v>87</v>
       </c>
       <c r="O13" t="s">
-        <v>110</v>
+        <v>91</v>
       </c>
       <c r="P13" t="s">
-        <v>154</v>
+        <v>135</v>
       </c>
     </row>
     <row r="14" spans="1:18" x14ac:dyDescent="0.35">
@@ -4186,19 +4120,19 @@
         <v>7</v>
       </c>
       <c r="H14" t="s">
-        <v>100</v>
+        <v>81</v>
       </c>
       <c r="M14">
         <v>8</v>
       </c>
       <c r="N14" t="s">
-        <v>118</v>
+        <v>99</v>
       </c>
       <c r="O14" t="s">
-        <v>89</v>
+        <v>70</v>
       </c>
       <c r="P14" t="s">
-        <v>90</v>
+        <v>71</v>
       </c>
     </row>
     <row r="15" spans="1:18" x14ac:dyDescent="0.35">
@@ -4206,25 +4140,25 @@
         <v>8</v>
       </c>
       <c r="H15" t="s">
-        <v>88</v>
+        <v>69</v>
       </c>
       <c r="I15" t="s">
-        <v>91</v>
+        <v>72</v>
       </c>
       <c r="J15" t="s">
-        <v>90</v>
+        <v>71</v>
       </c>
       <c r="M15">
         <v>9</v>
       </c>
       <c r="N15" t="s">
-        <v>121</v>
+        <v>102</v>
       </c>
       <c r="O15" t="s">
-        <v>95</v>
+        <v>76</v>
       </c>
       <c r="P15" t="s">
-        <v>92</v>
+        <v>73</v>
       </c>
     </row>
     <row r="16" spans="1:18" x14ac:dyDescent="0.35">
@@ -4232,25 +4166,25 @@
         <v>9</v>
       </c>
       <c r="H16" t="s">
-        <v>93</v>
+        <v>74</v>
       </c>
       <c r="I16" t="s">
-        <v>95</v>
+        <v>76</v>
       </c>
       <c r="J16" t="s">
-        <v>97</v>
+        <v>78</v>
       </c>
       <c r="M16">
         <v>10</v>
       </c>
       <c r="N16" t="s">
-        <v>106</v>
+        <v>87</v>
       </c>
       <c r="O16" t="s">
-        <v>122</v>
+        <v>103</v>
       </c>
       <c r="P16" t="s">
-        <v>153</v>
+        <v>134</v>
       </c>
     </row>
     <row r="17" spans="7:10" x14ac:dyDescent="0.35">
@@ -4258,13 +4192,13 @@
         <v>10</v>
       </c>
       <c r="H17" t="s">
-        <v>94</v>
+        <v>75</v>
       </c>
       <c r="I17" t="s">
-        <v>96</v>
+        <v>77</v>
       </c>
       <c r="J17" t="s">
-        <v>98</v>
+        <v>79</v>
       </c>
     </row>
     <row r="18" spans="7:10" x14ac:dyDescent="0.35">
@@ -4272,13 +4206,13 @@
         <v>11</v>
       </c>
       <c r="H18" t="s">
-        <v>101</v>
+        <v>82</v>
       </c>
       <c r="I18" t="s">
-        <v>102</v>
+        <v>83</v>
       </c>
       <c r="J18" t="s">
-        <v>103</v>
+        <v>84</v>
       </c>
     </row>
     <row r="19" spans="7:10" x14ac:dyDescent="0.35">
@@ -4286,13 +4220,13 @@
         <v>12</v>
       </c>
       <c r="H19" t="s">
-        <v>88</v>
+        <v>69</v>
       </c>
       <c r="I19" t="s">
-        <v>89</v>
+        <v>70</v>
       </c>
       <c r="J19" t="s">
-        <v>90</v>
+        <v>71</v>
       </c>
     </row>
     <row r="20" spans="7:10" x14ac:dyDescent="0.35">
@@ -4300,13 +4234,13 @@
         <v>13</v>
       </c>
       <c r="H20" t="s">
-        <v>105</v>
+        <v>86</v>
       </c>
       <c r="I20" t="s">
-        <v>95</v>
+        <v>76</v>
       </c>
       <c r="J20" t="s">
-        <v>92</v>
+        <v>73</v>
       </c>
     </row>
     <row r="21" spans="7:10" x14ac:dyDescent="0.35">
@@ -4314,13 +4248,13 @@
         <v>14</v>
       </c>
       <c r="H21" t="s">
-        <v>106</v>
+        <v>87</v>
       </c>
       <c r="I21" t="s">
-        <v>108</v>
+        <v>89</v>
       </c>
       <c r="J21" t="s">
-        <v>107</v>
+        <v>88</v>
       </c>
     </row>
     <row r="22" spans="7:10" x14ac:dyDescent="0.35">
@@ -4328,13 +4262,13 @@
         <v>15</v>
       </c>
       <c r="H22" t="s">
-        <v>111</v>
+        <v>92</v>
       </c>
       <c r="I22" t="s">
-        <v>95</v>
+        <v>76</v>
       </c>
       <c r="J22" t="s">
-        <v>109</v>
+        <v>90</v>
       </c>
     </row>
     <row r="23" spans="7:10" x14ac:dyDescent="0.35">
@@ -4342,13 +4276,13 @@
         <v>16</v>
       </c>
       <c r="H23" t="s">
-        <v>106</v>
+        <v>87</v>
       </c>
       <c r="I23" t="s">
-        <v>108</v>
+        <v>89</v>
       </c>
       <c r="J23" t="s">
-        <v>107</v>
+        <v>88</v>
       </c>
     </row>
     <row r="24" spans="7:10" x14ac:dyDescent="0.35">
@@ -4356,13 +4290,13 @@
         <v>17</v>
       </c>
       <c r="H24" t="s">
-        <v>112</v>
+        <v>93</v>
       </c>
       <c r="I24" t="s">
-        <v>113</v>
+        <v>94</v>
       </c>
       <c r="J24" t="s">
-        <v>114</v>
+        <v>95</v>
       </c>
     </row>
     <row r="25" spans="7:10" x14ac:dyDescent="0.35">
@@ -4370,13 +4304,13 @@
         <v>18</v>
       </c>
       <c r="H25" t="s">
-        <v>101</v>
+        <v>82</v>
       </c>
       <c r="I25" t="s">
-        <v>102</v>
+        <v>83</v>
       </c>
       <c r="J25" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
     </row>
   </sheetData>
@@ -4411,13 +4345,13 @@
     <col min="3" max="3" width="11.54296875" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="31.1796875" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="18.453125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="16.1796875" style="9" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="16.1796875" style="8" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="5" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="22.453125" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="19.7265625" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="28.54296875" customWidth="1"/>
     <col min="11" max="11" width="18.453125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="16.1796875" style="9" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="16.1796875" style="8" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="5" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="22.453125" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="22.81640625" bestFit="1" customWidth="1"/>
@@ -4427,59 +4361,59 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A1" s="16" t="s">
+      <c r="A1" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="B1" s="15"/>
+      <c r="C1" s="15"/>
+      <c r="D1" s="15"/>
+      <c r="E1" s="15"/>
+      <c r="F1" s="16"/>
+      <c r="G1" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="H1" s="15"/>
+      <c r="I1" s="15"/>
+      <c r="J1" s="15"/>
+      <c r="K1" s="15"/>
+      <c r="L1" s="16"/>
+      <c r="M1" s="15" t="s">
         <v>18</v>
       </c>
-      <c r="B1" s="16"/>
-      <c r="C1" s="16"/>
-      <c r="D1" s="16"/>
-      <c r="E1" s="16"/>
-      <c r="F1" s="17"/>
-      <c r="G1" s="18" t="s">
-        <v>19</v>
-      </c>
-      <c r="H1" s="16"/>
-      <c r="I1" s="16"/>
-      <c r="J1" s="16"/>
-      <c r="K1" s="16"/>
-      <c r="L1" s="17"/>
-      <c r="M1" s="16" t="s">
-        <v>20</v>
-      </c>
-      <c r="N1" s="16"/>
-      <c r="O1" s="16"/>
-      <c r="P1" s="16"/>
-      <c r="Q1" s="16"/>
-      <c r="R1" s="16"/>
+      <c r="N1" s="15"/>
+      <c r="O1" s="15"/>
+      <c r="P1" s="15"/>
+      <c r="Q1" s="15"/>
+      <c r="R1" s="15"/>
     </row>
     <row r="2" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A2" s="16" t="s">
+      <c r="A2" s="15" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="16"/>
-      <c r="C2" s="8">
+      <c r="B2" s="15"/>
+      <c r="C2" s="7">
         <f>IFERROR(_xlfn.XLOOKUP(A1, TestMaster[Test Name], TestMaster[Test ID], "ID not found"), "")</f>
         <v>8</v>
       </c>
       <c r="E2" t="s">
         <v>4</v>
       </c>
-      <c r="G2" s="16" t="s">
+      <c r="G2" s="15" t="s">
         <v>3</v>
       </c>
-      <c r="H2" s="16"/>
-      <c r="I2" s="8">
+      <c r="H2" s="15"/>
+      <c r="I2" s="7">
         <f>IFERROR(_xlfn.XLOOKUP(G1, TestMaster[Test Name], TestMaster[Test ID], "ID not found"), "")</f>
         <v>9</v>
       </c>
       <c r="K2" t="s">
         <v>4</v>
       </c>
-      <c r="M2" s="16" t="s">
+      <c r="M2" s="15" t="s">
         <v>3</v>
       </c>
-      <c r="N2" s="16"/>
-      <c r="O2" s="8">
+      <c r="N2" s="15"/>
+      <c r="O2" s="7">
         <f>IFERROR(_xlfn.XLOOKUP(M1, TestMaster[Test Name], TestMaster[Test ID], "ID not found"), "")</f>
         <v>10</v>
       </c>
@@ -4488,41 +4422,41 @@
       </c>
     </row>
     <row r="3" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A3" s="16" t="s">
-        <v>186</v>
-      </c>
-      <c r="B3" s="16"/>
-      <c r="C3" s="8" t="str">
+      <c r="A3" s="15" t="s">
+        <v>167</v>
+      </c>
+      <c r="B3" s="15"/>
+      <c r="C3" s="7" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(A1, TestMaster[Test Name], TestMaster[Test Priority], "Priority not found"), "")</f>
         <v>Medium</v>
       </c>
       <c r="E3" t="s">
         <v>5</v>
       </c>
-      <c r="F3" s="9" t="str">
+      <c r="F3" s="8" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(A1, TestMaster[Test Name], TestMaster[Test Status], "Status not found"), "")</f>
         <v>Not Implemented</v>
       </c>
-      <c r="G3" s="16" t="s">
-        <v>186</v>
-      </c>
-      <c r="H3" s="16"/>
-      <c r="I3" s="8" t="str">
+      <c r="G3" s="15" t="s">
+        <v>167</v>
+      </c>
+      <c r="H3" s="15"/>
+      <c r="I3" s="7" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(G1, TestMaster[Test Name], TestMaster[Test Priority], "Priority not found"), "")</f>
         <v>Medium</v>
       </c>
       <c r="K3" t="s">
         <v>5</v>
       </c>
-      <c r="L3" s="9" t="str">
+      <c r="L3" s="8" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(G1, TestMaster[Test Name], TestMaster[Test Status], "Status not found"), "")</f>
         <v>Not Implemented</v>
       </c>
-      <c r="M3" s="16" t="s">
-        <v>186</v>
-      </c>
-      <c r="N3" s="16"/>
-      <c r="O3" s="8" t="str">
+      <c r="M3" s="15" t="s">
+        <v>167</v>
+      </c>
+      <c r="N3" s="15"/>
+      <c r="O3" s="7" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(M1, TestMaster[Test Name], TestMaster[Test Priority], "Priority not found"), "")</f>
         <v>Low</v>
       </c>
@@ -4535,76 +4469,76 @@
       </c>
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A4" s="20" t="s">
-        <v>70</v>
-      </c>
-      <c r="B4" s="20"/>
-      <c r="C4" s="20"/>
-      <c r="D4" s="20"/>
-      <c r="E4" s="20"/>
-      <c r="F4" s="21"/>
-      <c r="G4" s="19" t="s">
+      <c r="A4" s="19" t="s">
+        <v>51</v>
+      </c>
+      <c r="B4" s="19"/>
+      <c r="C4" s="19"/>
+      <c r="D4" s="19"/>
+      <c r="E4" s="19"/>
+      <c r="F4" s="20"/>
+      <c r="G4" s="18" t="s">
         <v>6</v>
       </c>
-      <c r="H4" s="20"/>
-      <c r="I4" s="20"/>
-      <c r="J4" s="20"/>
-      <c r="K4" s="20"/>
-      <c r="L4" s="21"/>
-      <c r="M4" s="20" t="s">
+      <c r="H4" s="19"/>
+      <c r="I4" s="19"/>
+      <c r="J4" s="19"/>
+      <c r="K4" s="19"/>
+      <c r="L4" s="20"/>
+      <c r="M4" s="19" t="s">
         <v>6</v>
       </c>
-      <c r="N4" s="20"/>
-      <c r="O4" s="20"/>
-      <c r="P4" s="20"/>
-      <c r="Q4" s="20"/>
-      <c r="R4" s="20"/>
+      <c r="N4" s="19"/>
+      <c r="O4" s="19"/>
+      <c r="P4" s="19"/>
+      <c r="Q4" s="19"/>
+      <c r="R4" s="19"/>
     </row>
     <row r="5" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A5" s="20"/>
-      <c r="B5" s="20"/>
-      <c r="C5" s="20"/>
-      <c r="D5" s="20"/>
-      <c r="E5" s="20"/>
-      <c r="F5" s="21"/>
-      <c r="G5" s="19"/>
-      <c r="H5" s="20"/>
-      <c r="I5" s="20"/>
-      <c r="J5" s="20"/>
-      <c r="K5" s="20"/>
-      <c r="L5" s="21"/>
-      <c r="M5" s="20"/>
-      <c r="N5" s="20"/>
-      <c r="O5" s="20"/>
-      <c r="P5" s="20"/>
-      <c r="Q5" s="20"/>
-      <c r="R5" s="20"/>
+      <c r="A5" s="19"/>
+      <c r="B5" s="19"/>
+      <c r="C5" s="19"/>
+      <c r="D5" s="19"/>
+      <c r="E5" s="19"/>
+      <c r="F5" s="20"/>
+      <c r="G5" s="18"/>
+      <c r="H5" s="19"/>
+      <c r="I5" s="19"/>
+      <c r="J5" s="19"/>
+      <c r="K5" s="19"/>
+      <c r="L5" s="20"/>
+      <c r="M5" s="19"/>
+      <c r="N5" s="19"/>
+      <c r="O5" s="19"/>
+      <c r="P5" s="19"/>
+      <c r="Q5" s="19"/>
+      <c r="R5" s="19"/>
     </row>
     <row r="6" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A6" s="16" t="s">
-        <v>71</v>
-      </c>
-      <c r="B6" s="16"/>
-      <c r="C6" s="16"/>
-      <c r="D6" s="16"/>
-      <c r="E6" s="16"/>
-      <c r="F6" s="17"/>
-      <c r="G6" s="18" t="s">
+      <c r="A6" s="15" t="s">
+        <v>52</v>
+      </c>
+      <c r="B6" s="15"/>
+      <c r="C6" s="15"/>
+      <c r="D6" s="15"/>
+      <c r="E6" s="15"/>
+      <c r="F6" s="16"/>
+      <c r="G6" s="17" t="s">
         <v>7</v>
       </c>
-      <c r="H6" s="16"/>
-      <c r="I6" s="16"/>
-      <c r="J6" s="16"/>
-      <c r="K6" s="16"/>
-      <c r="L6" s="17"/>
-      <c r="M6" s="16" t="s">
+      <c r="H6" s="15"/>
+      <c r="I6" s="15"/>
+      <c r="J6" s="15"/>
+      <c r="K6" s="15"/>
+      <c r="L6" s="16"/>
+      <c r="M6" s="15" t="s">
         <v>7</v>
       </c>
-      <c r="N6" s="16"/>
-      <c r="O6" s="16"/>
-      <c r="P6" s="16"/>
-      <c r="Q6" s="16"/>
-      <c r="R6" s="16"/>
+      <c r="N6" s="15"/>
+      <c r="O6" s="15"/>
+      <c r="P6" s="15"/>
+      <c r="Q6" s="15"/>
+      <c r="R6" s="15"/>
     </row>
     <row r="7" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A7" s="1" t="s">
@@ -4622,7 +4556,7 @@
       <c r="E7" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="F7" s="12" t="s">
+      <c r="F7" s="11" t="s">
         <v>2</v>
       </c>
       <c r="G7" s="1" t="s">
@@ -4640,7 +4574,7 @@
       <c r="K7" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="L7" s="12" t="s">
+      <c r="L7" s="11" t="s">
         <v>2</v>
       </c>
       <c r="M7" s="1" t="s">
@@ -4662,126 +4596,126 @@
         <v>2</v>
       </c>
     </row>
-    <row r="8" spans="1:18" s="4" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="4">
+    <row r="8" spans="1:18" s="3" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="3">
         <v>1</v>
       </c>
-      <c r="B8" s="4" t="s">
-        <v>72</v>
-      </c>
-      <c r="C8" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="D8" s="4" t="s">
-        <v>73</v>
-      </c>
-      <c r="F8" s="15"/>
-      <c r="G8" s="4">
+      <c r="B8" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="F8" s="14"/>
+      <c r="G8" s="3">
         <v>1</v>
       </c>
-      <c r="H8" s="4" t="s">
-        <v>72</v>
-      </c>
-      <c r="I8" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="J8" s="4" t="s">
-        <v>76</v>
-      </c>
-      <c r="L8" s="15"/>
-      <c r="M8" s="4">
+      <c r="H8" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="I8" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="J8" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="L8" s="14"/>
+      <c r="M8" s="3">
         <v>1</v>
       </c>
-      <c r="N8" s="4" t="s">
-        <v>72</v>
-      </c>
-      <c r="O8" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="P8" s="4" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="9" spans="1:18" s="4" customFormat="1" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A9" s="4">
+      <c r="N8" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="O8" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="P8" s="3" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18" s="3" customFormat="1" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A9" s="3">
         <v>2</v>
       </c>
-      <c r="B9" s="4" t="s">
+      <c r="B9" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="F9" s="14"/>
+      <c r="G9" s="3">
+        <v>2</v>
+      </c>
+      <c r="H9" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="C9" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="D9" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="F9" s="15"/>
-      <c r="G9" s="4">
+      <c r="I9" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="J9" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="L9" s="14"/>
+      <c r="M9" s="3">
         <v>2</v>
       </c>
-      <c r="H9" s="4" t="s">
-        <v>74</v>
-      </c>
-      <c r="I9" s="4" t="s">
-        <v>77</v>
-      </c>
-      <c r="J9" s="4" t="s">
-        <v>79</v>
-      </c>
-      <c r="L9" s="15"/>
-      <c r="M9" s="4">
-        <v>2</v>
-      </c>
-      <c r="N9" s="4" t="s">
-        <v>74</v>
-      </c>
-      <c r="O9" s="4" t="s">
-        <v>81</v>
-      </c>
-      <c r="P9" s="4" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="10" spans="1:18" s="4" customFormat="1" ht="29" x14ac:dyDescent="0.35">
-      <c r="F10" s="15"/>
-      <c r="G10" s="4">
+      <c r="N9" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="O9" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="P9" s="3" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="10" spans="1:18" s="3" customFormat="1" ht="29" x14ac:dyDescent="0.35">
+      <c r="F10" s="14"/>
+      <c r="G10" s="3">
         <v>3</v>
       </c>
-      <c r="H10" s="4" t="s">
-        <v>75</v>
-      </c>
-      <c r="I10" s="4" t="s">
-        <v>78</v>
-      </c>
-      <c r="J10" s="4" t="s">
-        <v>86</v>
-      </c>
-      <c r="L10" s="15"/>
-      <c r="M10" s="4">
+      <c r="H10" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="I10" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="J10" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="L10" s="14"/>
+      <c r="M10" s="3">
         <v>3</v>
       </c>
-      <c r="N10" s="4" t="s">
-        <v>75</v>
-      </c>
-      <c r="O10" s="4" t="s">
-        <v>78</v>
-      </c>
-      <c r="P10" s="4" t="s">
-        <v>82</v>
+      <c r="N10" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="O10" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="P10" s="3" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="11" spans="1:18" ht="29" x14ac:dyDescent="0.35">
-      <c r="M11" s="4">
+      <c r="M11" s="3">
         <v>4</v>
       </c>
-      <c r="N11" s="4" t="s">
-        <v>83</v>
-      </c>
-      <c r="O11" s="4" t="s">
-        <v>84</v>
-      </c>
-      <c r="P11" s="4" t="s">
-        <v>85</v>
+      <c r="N11" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="O11" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="P11" s="3" t="s">
+        <v>66</v>
       </c>
     </row>
   </sheetData>
@@ -4808,333 +4742,212 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E4413619-C528-4B04-A1ED-B4C77CA83066}">
-  <dimension ref="A1:AD12"/>
+  <dimension ref="A1:R21"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="5" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="25.1796875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="17.54296875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="23.26953125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="41" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="15.26953125" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="18.453125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="8.7265625" style="9"/>
+    <col min="6" max="6" width="8.7265625" style="8"/>
     <col min="7" max="7" width="5" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="23.7265625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="48.81640625" customWidth="1"/>
-    <col min="10" max="10" width="17.54296875" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="18.453125" customWidth="1"/>
-    <col min="12" max="12" width="8.7265625" style="9"/>
-    <col min="13" max="13" width="5" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="21.54296875" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="30.81640625" customWidth="1"/>
-    <col min="16" max="16" width="15.26953125" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="18.453125" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="8.7265625" style="9"/>
-    <col min="19" max="19" width="5" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="23.26953125" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="41" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="15.26953125" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="18.453125" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="8.7265625" style="9"/>
-    <col min="25" max="25" width="5" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="19.1796875" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="11.54296875" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="15.26953125" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="18.453125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="19.1796875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="27.36328125" customWidth="1"/>
+    <col min="10" max="10" width="15.26953125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="18.453125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="8.7265625" style="23"/>
+    <col min="14" max="14" width="23.26953125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="17.1796875" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="41" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="18.36328125" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="8" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:30" x14ac:dyDescent="0.35">
-      <c r="A1" s="16" t="s">
-        <v>11</v>
-      </c>
-      <c r="B1" s="16"/>
-      <c r="C1" s="16"/>
-      <c r="D1" s="16"/>
-      <c r="E1" s="16"/>
-      <c r="F1" s="17"/>
-      <c r="G1" s="16" t="s">
-        <v>21</v>
-      </c>
-      <c r="H1" s="16"/>
-      <c r="I1" s="16"/>
-      <c r="J1" s="16"/>
-      <c r="K1" s="16"/>
-      <c r="L1" s="17"/>
-      <c r="M1" s="18" t="s">
-        <v>22</v>
-      </c>
-      <c r="N1" s="16"/>
-      <c r="O1" s="16"/>
-      <c r="P1" s="16"/>
-      <c r="Q1" s="16"/>
-      <c r="R1" s="17"/>
-      <c r="S1" s="16" t="s">
-        <v>23</v>
-      </c>
-      <c r="T1" s="16"/>
-      <c r="U1" s="16"/>
-      <c r="V1" s="16"/>
-      <c r="W1" s="16"/>
-      <c r="X1" s="17"/>
-      <c r="Y1" s="16" t="s">
-        <v>190</v>
-      </c>
-      <c r="Z1" s="16"/>
-      <c r="AA1" s="16"/>
-      <c r="AB1" s="16"/>
-      <c r="AC1" s="16"/>
-      <c r="AD1" s="16"/>
-    </row>
-    <row r="2" spans="1:30" x14ac:dyDescent="0.35">
-      <c r="A2" s="16" t="s">
+    <row r="1" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A1" s="15" t="s">
+        <v>178</v>
+      </c>
+      <c r="B1" s="15"/>
+      <c r="C1" s="15"/>
+      <c r="D1" s="15"/>
+      <c r="E1" s="15"/>
+      <c r="F1" s="16"/>
+      <c r="G1" s="15" t="s">
+        <v>170</v>
+      </c>
+      <c r="H1" s="15"/>
+      <c r="I1" s="15"/>
+      <c r="J1" s="15"/>
+      <c r="K1" s="15"/>
+      <c r="L1" s="15"/>
+      <c r="M1" s="17" t="s">
+        <v>186</v>
+      </c>
+      <c r="N1" s="24"/>
+      <c r="O1" s="24"/>
+      <c r="P1" s="24"/>
+      <c r="Q1" s="24"/>
+      <c r="R1" s="16"/>
+    </row>
+    <row r="2" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A2" s="15" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="16"/>
-      <c r="C2">
+      <c r="B2" s="15"/>
+      <c r="C2" s="7">
         <f>IFERROR(_xlfn.XLOOKUP(A1, TestMaster[Test Name], TestMaster[Test ID], "ID not found"), "")</f>
         <v>11</v>
       </c>
       <c r="E2" t="s">
         <v>4</v>
       </c>
-      <c r="G2" s="16" t="s">
+      <c r="G2" s="15" t="s">
         <v>3</v>
       </c>
-      <c r="H2" s="16"/>
-      <c r="I2" s="8">
+      <c r="H2" s="15"/>
+      <c r="I2" s="7">
         <f>IFERROR(_xlfn.XLOOKUP(G1, TestMaster[Test Name], TestMaster[Test ID], "ID not found"), "")</f>
         <v>12</v>
       </c>
       <c r="K2" t="s">
         <v>4</v>
       </c>
-      <c r="M2" s="16" t="s">
+      <c r="M2" s="17" t="s">
         <v>3</v>
       </c>
-      <c r="N2" s="16"/>
-      <c r="O2" s="8">
+      <c r="N2" s="24"/>
+      <c r="O2" s="25">
         <f>IFERROR(_xlfn.XLOOKUP(M1, TestMaster[Test Name], TestMaster[Test ID], "ID not found"), "")</f>
         <v>13</v>
       </c>
-      <c r="Q2" t="s">
+      <c r="P2" s="26"/>
+      <c r="Q2" s="26" t="s">
         <v>4</v>
       </c>
-      <c r="S2" s="16" t="s">
-        <v>3</v>
-      </c>
-      <c r="T2" s="16"/>
-      <c r="U2" s="8">
-        <f>IFERROR(_xlfn.XLOOKUP(S1, TestMaster[Test Name], TestMaster[Test ID], "ID not found"), "")</f>
-        <v>14</v>
-      </c>
-      <c r="W2" t="s">
-        <v>4</v>
-      </c>
-      <c r="Y2" s="16" t="s">
-        <v>3</v>
-      </c>
-      <c r="Z2" s="16"/>
-      <c r="AA2" s="8">
-        <f>IFERROR(_xlfn.XLOOKUP(Y1, TestMaster[Test Name], TestMaster[Test ID], "ID not found"), "")</f>
-        <v>15</v>
-      </c>
-      <c r="AC2" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="3" spans="1:30" x14ac:dyDescent="0.35">
-      <c r="A3" s="16" t="s">
-        <v>186</v>
-      </c>
-      <c r="B3" s="16"/>
-      <c r="C3" t="str">
+      <c r="R2" s="8"/>
+    </row>
+    <row r="3" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A3" s="15" t="s">
+        <v>167</v>
+      </c>
+      <c r="B3" s="15"/>
+      <c r="C3" s="7" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(A1, TestMaster[Test Name], TestMaster[Test Priority], "Priority not found"), "")</f>
         <v>High</v>
       </c>
       <c r="E3" t="s">
         <v>5</v>
       </c>
-      <c r="F3" s="9" t="str">
+      <c r="F3" s="8" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(A1, TestMaster[Test Name], TestMaster[Test Priority], "Priority not found"), "")</f>
         <v>High</v>
       </c>
-      <c r="G3" s="16" t="s">
-        <v>187</v>
-      </c>
-      <c r="H3" s="16"/>
-      <c r="I3" s="8" t="str">
+      <c r="G3" s="15" t="s">
+        <v>167</v>
+      </c>
+      <c r="H3" s="15"/>
+      <c r="I3" s="7" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(G1, TestMaster[Test Name], TestMaster[Test Priority], "Priority not found"), "")</f>
         <v>High</v>
       </c>
       <c r="K3" t="s">
         <v>5</v>
       </c>
-      <c r="L3" s="9" t="str">
+      <c r="L3" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(G1, TestMaster[Test Name], TestMaster[Test Priority], "Priority not found"), "")</f>
         <v>High</v>
       </c>
-      <c r="M3" s="16" t="s">
-        <v>186</v>
-      </c>
-      <c r="N3" s="16"/>
-      <c r="O3" s="8" t="str">
+      <c r="M3" s="17" t="s">
+        <v>167</v>
+      </c>
+      <c r="N3" s="24"/>
+      <c r="O3" s="25" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(M1, TestMaster[Test Name], TestMaster[Test Priority], "Priority not found"), "")</f>
         <v>Medium</v>
       </c>
-      <c r="Q3" t="s">
+      <c r="P3" s="26"/>
+      <c r="Q3" s="26" t="s">
         <v>5</v>
       </c>
-      <c r="R3" s="9" t="str">
+      <c r="R3" s="8" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(M1, TestMaster[Test Name], TestMaster[Test Priority], "Priority not found"), "")</f>
         <v>Medium</v>
       </c>
-      <c r="S3" s="16" t="s">
-        <v>186</v>
-      </c>
-      <c r="T3" s="16"/>
-      <c r="U3" s="8" t="str">
-        <f>IFERROR(_xlfn.XLOOKUP(S1, TestMaster[Test Name], TestMaster[Test Priority], "Priority not found"), "")</f>
-        <v>Low</v>
-      </c>
-      <c r="W3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X3" s="9" t="str">
-        <f>IFERROR(_xlfn.XLOOKUP(S1, TestMaster[Test Name], TestMaster[Test Priority], "Priority not found"), "")</f>
-        <v>Low</v>
-      </c>
-      <c r="Y3" s="16" t="s">
-        <v>186</v>
-      </c>
-      <c r="Z3" s="16"/>
-      <c r="AA3" s="8" t="str">
-        <f>IFERROR(_xlfn.XLOOKUP(Y1, TestMaster[Test Name], TestMaster[Test Priority], "Priority not found"), "")</f>
-        <v>High</v>
-      </c>
-      <c r="AC3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AD3" t="str">
-        <f>IFERROR(_xlfn.XLOOKUP(Y1, TestMaster[Test Name], TestMaster[Test Priority], "Priority not found"), "")</f>
-        <v>High</v>
-      </c>
-    </row>
-    <row r="4" spans="1:30" s="2" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="20" t="s">
-        <v>12</v>
-      </c>
-      <c r="B4" s="20"/>
-      <c r="C4" s="20"/>
-      <c r="D4" s="20"/>
-      <c r="E4" s="20"/>
-      <c r="F4" s="21"/>
-      <c r="G4" s="20" t="s">
-        <v>67</v>
-      </c>
-      <c r="H4" s="20"/>
-      <c r="I4" s="20"/>
-      <c r="J4" s="20"/>
-      <c r="K4" s="20"/>
-      <c r="L4" s="21"/>
-      <c r="M4" s="19" t="s">
-        <v>12</v>
-      </c>
-      <c r="N4" s="20"/>
-      <c r="O4" s="20"/>
-      <c r="P4" s="20"/>
-      <c r="Q4" s="20"/>
-      <c r="R4" s="21"/>
-      <c r="S4" s="20" t="s">
-        <v>12</v>
-      </c>
-      <c r="T4" s="20"/>
-      <c r="U4" s="20"/>
-      <c r="V4" s="20"/>
-      <c r="W4" s="20"/>
-      <c r="X4" s="21"/>
-      <c r="Y4" s="20" t="s">
-        <v>12</v>
-      </c>
-      <c r="Z4" s="20"/>
-      <c r="AA4" s="20"/>
-      <c r="AB4" s="20"/>
-      <c r="AC4" s="20"/>
-      <c r="AD4" s="20"/>
-    </row>
-    <row r="5" spans="1:30" s="2" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="20"/>
-      <c r="B5" s="20"/>
-      <c r="C5" s="20"/>
-      <c r="D5" s="20"/>
-      <c r="E5" s="20"/>
-      <c r="F5" s="21"/>
-      <c r="G5" s="20"/>
-      <c r="H5" s="20"/>
-      <c r="I5" s="20"/>
-      <c r="J5" s="20"/>
-      <c r="K5" s="20"/>
-      <c r="L5" s="21"/>
-      <c r="M5" s="19"/>
-      <c r="N5" s="20"/>
-      <c r="O5" s="20"/>
-      <c r="P5" s="20"/>
-      <c r="Q5" s="20"/>
-      <c r="R5" s="21"/>
-      <c r="S5" s="20"/>
-      <c r="T5" s="20"/>
-      <c r="U5" s="20"/>
-      <c r="V5" s="20"/>
-      <c r="W5" s="20"/>
-      <c r="X5" s="21"/>
-      <c r="Y5" s="20"/>
-      <c r="Z5" s="20"/>
-      <c r="AA5" s="20"/>
-      <c r="AB5" s="20"/>
-      <c r="AC5" s="20"/>
-      <c r="AD5" s="20"/>
-    </row>
-    <row r="6" spans="1:30" x14ac:dyDescent="0.35">
-      <c r="A6" s="16" t="s">
-        <v>68</v>
-      </c>
-      <c r="B6" s="16"/>
-      <c r="C6" s="16"/>
-      <c r="D6" s="16"/>
-      <c r="E6" s="16"/>
-      <c r="F6" s="17"/>
-      <c r="G6" s="16" t="s">
-        <v>68</v>
-      </c>
-      <c r="H6" s="16"/>
-      <c r="I6" s="16"/>
-      <c r="J6" s="16"/>
-      <c r="K6" s="16"/>
-      <c r="L6" s="17"/>
-      <c r="M6" s="18" t="s">
-        <v>69</v>
-      </c>
-      <c r="N6" s="16"/>
-      <c r="O6" s="16"/>
-      <c r="P6" s="16"/>
-      <c r="Q6" s="16"/>
-      <c r="R6" s="17"/>
-      <c r="S6" s="16" t="s">
-        <v>52</v>
-      </c>
-      <c r="T6" s="16"/>
-      <c r="U6" s="16"/>
-      <c r="V6" s="16"/>
-      <c r="W6" s="16"/>
-      <c r="X6" s="17"/>
-      <c r="Y6" s="16" t="s">
-        <v>68</v>
-      </c>
-      <c r="Z6" s="16"/>
-      <c r="AA6" s="16"/>
-      <c r="AB6" s="16"/>
-      <c r="AC6" s="16"/>
-      <c r="AD6" s="16"/>
-    </row>
-    <row r="7" spans="1:30" x14ac:dyDescent="0.35">
+    </row>
+    <row r="4" spans="1:18" s="2" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="19" t="s">
+        <v>180</v>
+      </c>
+      <c r="B4" s="19"/>
+      <c r="C4" s="19"/>
+      <c r="D4" s="19"/>
+      <c r="E4" s="19"/>
+      <c r="F4" s="20"/>
+      <c r="G4" s="19" t="s">
+        <v>177</v>
+      </c>
+      <c r="H4" s="19"/>
+      <c r="I4" s="19"/>
+      <c r="J4" s="19"/>
+      <c r="K4" s="19"/>
+      <c r="L4" s="19"/>
+      <c r="M4" s="18" t="s">
+        <v>185</v>
+      </c>
+      <c r="N4" s="27"/>
+      <c r="O4" s="27"/>
+      <c r="P4" s="27"/>
+      <c r="Q4" s="27"/>
+      <c r="R4" s="20"/>
+    </row>
+    <row r="5" spans="1:18" s="2" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="19"/>
+      <c r="B5" s="19"/>
+      <c r="C5" s="19"/>
+      <c r="D5" s="19"/>
+      <c r="E5" s="19"/>
+      <c r="F5" s="20"/>
+      <c r="G5" s="19"/>
+      <c r="H5" s="19"/>
+      <c r="I5" s="19"/>
+      <c r="J5" s="19"/>
+      <c r="K5" s="19"/>
+      <c r="L5" s="19"/>
+      <c r="M5" s="18"/>
+      <c r="N5" s="27"/>
+      <c r="O5" s="27"/>
+      <c r="P5" s="27"/>
+      <c r="Q5" s="27"/>
+      <c r="R5" s="20"/>
+    </row>
+    <row r="6" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A6" s="15" t="s">
+        <v>37</v>
+      </c>
+      <c r="B6" s="15"/>
+      <c r="C6" s="15"/>
+      <c r="D6" s="15"/>
+      <c r="E6" s="15"/>
+      <c r="F6" s="16"/>
+      <c r="G6" s="15" t="s">
+        <v>50</v>
+      </c>
+      <c r="H6" s="15"/>
+      <c r="I6" s="15"/>
+      <c r="J6" s="15"/>
+      <c r="K6" s="15"/>
+      <c r="L6" s="15"/>
+      <c r="M6" s="17" t="s">
+        <v>50</v>
+      </c>
+      <c r="N6" s="24"/>
+      <c r="O6" s="24"/>
+      <c r="P6" s="24"/>
+      <c r="Q6" s="24"/>
+      <c r="R6" s="16"/>
+    </row>
+    <row r="7" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A7" s="1" t="s">
         <v>0</v>
       </c>
@@ -5150,7 +4963,7 @@
       <c r="E7" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="F7" s="12" t="s">
+      <c r="F7" s="11" t="s">
         <v>2</v>
       </c>
       <c r="G7" s="1" t="s">
@@ -5168,10 +4981,10 @@
       <c r="K7" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="L7" s="12" t="s">
+      <c r="L7" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="M7" s="1" t="s">
+      <c r="M7" s="22" t="s">
         <v>0</v>
       </c>
       <c r="N7" s="1" t="s">
@@ -5186,296 +4999,281 @@
       <c r="Q7" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="R7" s="12" t="s">
+      <c r="R7" s="11" t="s">
         <v>2</v>
       </c>
-      <c r="S7" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="T7" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="U7" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="V7" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="W7" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="X7" s="12" t="s">
-        <v>2</v>
-      </c>
-      <c r="Y7" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="Z7" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="AA7" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="AB7" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="AC7" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="AD7" s="1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="8" spans="1:30" x14ac:dyDescent="0.35">
+    </row>
+    <row r="8" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A8">
         <v>1</v>
       </c>
       <c r="B8" t="s">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="C8" t="s">
-        <v>26</v>
+        <v>181</v>
       </c>
       <c r="D8" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="G8">
         <v>1</v>
       </c>
       <c r="H8" t="s">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="I8" t="s">
-        <v>26</v>
+        <v>49</v>
       </c>
       <c r="J8" t="s">
-        <v>35</v>
-      </c>
-      <c r="M8">
+        <v>48</v>
+      </c>
+      <c r="M8" s="23">
         <v>1</v>
       </c>
-      <c r="N8" t="s">
-        <v>40</v>
-      </c>
-      <c r="O8" t="s">
-        <v>26</v>
-      </c>
-      <c r="P8" t="s">
-        <v>41</v>
-      </c>
-      <c r="S8">
-        <v>1</v>
-      </c>
-      <c r="T8" t="s">
-        <v>51</v>
-      </c>
-      <c r="U8" t="s">
-        <v>56</v>
-      </c>
-      <c r="Y8">
-        <v>1</v>
-      </c>
-      <c r="Z8" t="s">
-        <v>62</v>
-      </c>
-      <c r="AA8" t="s">
-        <v>66</v>
-      </c>
-      <c r="AB8" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="9" spans="1:30" ht="58" x14ac:dyDescent="0.35">
+      <c r="R8" s="8"/>
+    </row>
+    <row r="9" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A9">
         <v>2</v>
       </c>
       <c r="B9" t="s">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="C9" t="s">
-        <v>27</v>
+        <v>182</v>
       </c>
       <c r="D9" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="G9">
         <v>2</v>
       </c>
       <c r="H9" t="s">
-        <v>34</v>
-      </c>
-      <c r="I9" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="J9" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="M9">
+        <v>171</v>
+      </c>
+      <c r="I9" t="s">
+        <v>172</v>
+      </c>
+      <c r="J9" t="s">
+        <v>173</v>
+      </c>
+      <c r="M9" s="23">
         <v>2</v>
       </c>
-      <c r="N9" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="O9" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="P9" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="S9">
-        <v>2</v>
-      </c>
-      <c r="T9" t="s">
-        <v>55</v>
-      </c>
-      <c r="U9" t="s">
-        <v>57</v>
-      </c>
-      <c r="Y9">
-        <v>2</v>
-      </c>
-      <c r="Z9" t="s">
-        <v>191</v>
-      </c>
-      <c r="AA9" t="s">
-        <v>192</v>
-      </c>
-      <c r="AB9" t="s">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="10" spans="1:30" x14ac:dyDescent="0.35">
+      <c r="R9" s="8"/>
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A10">
         <v>3</v>
       </c>
       <c r="B10" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="C10" t="s">
-        <v>28</v>
+        <v>183</v>
       </c>
       <c r="D10" t="s">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="G10">
         <v>3</v>
       </c>
       <c r="H10" t="s">
-        <v>49</v>
+        <v>174</v>
       </c>
       <c r="I10" t="s">
-        <v>50</v>
+        <v>175</v>
       </c>
       <c r="J10" t="s">
-        <v>59</v>
-      </c>
-      <c r="M10">
+        <v>176</v>
+      </c>
+      <c r="M10" s="23">
         <v>3</v>
       </c>
-      <c r="N10" t="s">
-        <v>45</v>
-      </c>
-      <c r="O10" t="s">
-        <v>46</v>
-      </c>
-      <c r="P10" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="S10">
-        <v>3</v>
-      </c>
-      <c r="T10" t="s">
-        <v>54</v>
-      </c>
-      <c r="U10" t="s">
-        <v>60</v>
-      </c>
-      <c r="Y10">
-        <v>3</v>
-      </c>
-      <c r="Z10" t="s">
-        <v>63</v>
-      </c>
-      <c r="AA10" t="s">
-        <v>26</v>
-      </c>
-      <c r="AB10" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="11" spans="1:30" x14ac:dyDescent="0.35">
+      <c r="R10" s="8"/>
+    </row>
+    <row r="11" spans="1:18" ht="58" x14ac:dyDescent="0.35">
       <c r="A11">
         <v>4</v>
       </c>
-      <c r="B11" t="s">
-        <v>29</v>
-      </c>
-      <c r="C11" t="s">
-        <v>30</v>
-      </c>
-      <c r="D11" t="s">
-        <v>37</v>
-      </c>
-      <c r="S11">
+      <c r="B11" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="G11">
         <v>4</v>
       </c>
-      <c r="T11" t="s">
-        <v>51</v>
-      </c>
-      <c r="U11" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="12" spans="1:30" x14ac:dyDescent="0.35">
+      <c r="H11" t="s">
+        <v>46</v>
+      </c>
+      <c r="I11" t="s">
+        <v>21</v>
+      </c>
+      <c r="J11" t="s">
+        <v>47</v>
+      </c>
+      <c r="M11" s="23">
+        <v>4</v>
+      </c>
+      <c r="N11" s="2"/>
+      <c r="O11" s="2"/>
+      <c r="P11" s="2"/>
+      <c r="R11" s="8"/>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A12">
         <v>5</v>
       </c>
       <c r="B12" t="s">
-        <v>31</v>
-      </c>
-      <c r="C12" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="D12" t="s">
-        <v>39</v>
-      </c>
-      <c r="S12">
-        <v>5</v>
-      </c>
-      <c r="T12" t="s">
-        <v>53</v>
-      </c>
-      <c r="U12" t="s">
-        <v>57</v>
+        <v>43</v>
+      </c>
+    </row>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A13">
+        <v>6</v>
+      </c>
+      <c r="B13" t="s">
+        <v>36</v>
+      </c>
+      <c r="D13" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A14">
+        <v>7</v>
+      </c>
+      <c r="B14" t="s">
+        <v>179</v>
+      </c>
+      <c r="D14" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="15" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A15">
+        <v>8</v>
+      </c>
+      <c r="B15" t="s">
+        <v>35</v>
+      </c>
+      <c r="C15" t="s">
+        <v>163</v>
+      </c>
+      <c r="D15" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="16" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A16">
+        <v>9</v>
+      </c>
+      <c r="B16" t="s">
+        <v>20</v>
+      </c>
+      <c r="C16" t="s">
+        <v>23</v>
+      </c>
+      <c r="D16" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A17">
+        <v>10</v>
+      </c>
+      <c r="B17" t="s">
+        <v>24</v>
+      </c>
+      <c r="C17" t="s">
+        <v>21</v>
+      </c>
+      <c r="D17" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" ht="72.5" x14ac:dyDescent="0.35">
+      <c r="A18">
+        <v>11</v>
+      </c>
+      <c r="B18" t="s">
+        <v>25</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A19">
+        <v>12</v>
+      </c>
+      <c r="B19" t="s">
+        <v>19</v>
+      </c>
+      <c r="C19" t="s">
+        <v>21</v>
+      </c>
+      <c r="D19" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A20">
+        <v>13</v>
+      </c>
+      <c r="B20" t="s">
+        <v>35</v>
+      </c>
+      <c r="C20" t="s">
+        <v>22</v>
+      </c>
+      <c r="D20" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A21">
+        <v>14</v>
+      </c>
+      <c r="B21" t="s">
+        <v>20</v>
+      </c>
+      <c r="C21" t="s">
+        <v>23</v>
+      </c>
+      <c r="D21" t="s">
+        <v>30</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="25">
-    <mergeCell ref="A4:F5"/>
-    <mergeCell ref="A6:F6"/>
-    <mergeCell ref="A1:F1"/>
+  <mergeCells count="15">
     <mergeCell ref="M1:R1"/>
-    <mergeCell ref="G4:L5"/>
-    <mergeCell ref="G6:L6"/>
+    <mergeCell ref="M2:N2"/>
+    <mergeCell ref="M3:N3"/>
     <mergeCell ref="M4:R5"/>
     <mergeCell ref="M6:R6"/>
     <mergeCell ref="G1:L1"/>
+    <mergeCell ref="G2:H2"/>
+    <mergeCell ref="G3:H3"/>
+    <mergeCell ref="A4:F5"/>
+    <mergeCell ref="A6:F6"/>
+    <mergeCell ref="G4:L5"/>
+    <mergeCell ref="G6:L6"/>
     <mergeCell ref="A2:B2"/>
     <mergeCell ref="A3:B3"/>
-    <mergeCell ref="G2:H2"/>
-    <mergeCell ref="G3:H3"/>
-    <mergeCell ref="M2:N2"/>
-    <mergeCell ref="M3:N3"/>
-    <mergeCell ref="Y1:AD1"/>
-    <mergeCell ref="Y2:Z2"/>
-    <mergeCell ref="Y3:Z3"/>
-    <mergeCell ref="S4:X5"/>
-    <mergeCell ref="S6:X6"/>
-    <mergeCell ref="Y4:AD5"/>
-    <mergeCell ref="Y6:AD6"/>
-    <mergeCell ref="S2:T2"/>
-    <mergeCell ref="S3:T3"/>
-    <mergeCell ref="S1:X1"/>
+    <mergeCell ref="A1:F1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Test Cases.xlsx
+++ b/Test Cases.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://endresshauser-my.sharepoint.com/personal/corbin_ferguson_endress_com/Documents/Thesis Work/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1699" documentId="11_AD4DB114E441178AC67DF4D41ED1D894683EDF27" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F63269EF-56D4-480B-B9BE-A1F71BFA4520}"/>
+  <xr:revisionPtr revIDLastSave="1708" documentId="11_AD4DB114E441178AC67DF4D41ED1D894683EDF27" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C6CF5F09-A140-4CE7-B7DC-37D3CDB6428F}"/>
   <bookViews>
     <workbookView xWindow="53880" yWindow="-5145" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -66,7 +66,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="495" uniqueCount="187">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="496" uniqueCount="187">
   <si>
     <t>Step</t>
   </si>
@@ -170,9 +170,6 @@
     <t>File to load selected</t>
   </si>
   <si>
-    <t>doc object in Execute.cs updated to new object</t>
-  </si>
-  <si>
     <t>Confirm File Creation</t>
   </si>
   <si>
@@ -182,9 +179,6 @@
     <t>Preconditions: Empty template file loaded into application</t>
   </si>
   <si>
-    <t>Load File with error</t>
-  </si>
-  <si>
     <t>"Ok" button pressed</t>
   </si>
   <si>
@@ -195,9 +189,6 @@
   </si>
   <si>
     <t>New file created at location, return to action select window</t>
-  </si>
-  <si>
-    <t>File successfully loaded</t>
   </si>
   <si>
     <t>Error window appears with errors displayed</t>
@@ -832,6 +823,15 @@
   </si>
   <si>
     <t>ActionSelectLosecontrol</t>
+  </si>
+  <si>
+    <t>File successfully loaded, return to actionSelect</t>
+  </si>
+  <si>
+    <t>SaveFileButton</t>
+  </si>
+  <si>
+    <t>NewFileButton</t>
   </si>
 </sst>
 </file>
@@ -907,7 +907,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -941,6 +941,8 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -950,26 +952,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1934,6 +1923,10 @@
 </xdr:wsDr>
 </file>
 
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+</file>
+
 <file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Corbin Ferguson" refreshedDate="46035.626586689817" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="17" xr:uid="{32ED145B-7CBC-4C3A-9787-F34239E1DCF7}">
   <cacheSource type="worksheet">
@@ -2374,29 +2367,29 @@
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="B1" t="s">
+        <v>136</v>
+      </c>
+      <c r="C1" s="5" t="s">
+        <v>137</v>
+      </c>
+      <c r="D1" t="s">
         <v>139</v>
       </c>
-      <c r="C1" s="5" t="s">
-        <v>140</v>
-      </c>
-      <c r="D1" t="s">
-        <v>142</v>
-      </c>
       <c r="E1" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="G1">
         <f>COUNTIF(TestMaster[Test Status], "Not Implemented")</f>
         <v>13</v>
       </c>
       <c r="H1" s="6" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="I1" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.35">
@@ -2409,20 +2402,20 @@
         <v>Import Select Redundant Name</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="D2" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="E2" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="G2">
         <f>COUNTIF(TestMaster[Test Status], "Pass")</f>
         <v>0</v>
       </c>
       <c r="H2" s="7" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="I2">
         <v>17</v>
@@ -2438,20 +2431,20 @@
         <v>Element Quantity Creation</v>
       </c>
       <c r="C3" s="5" t="s">
+        <v>141</v>
+      </c>
+      <c r="D3" t="s">
+        <v>142</v>
+      </c>
+      <c r="E3" t="s">
         <v>144</v>
-      </c>
-      <c r="D3" t="s">
-        <v>145</v>
-      </c>
-      <c r="E3" t="s">
-        <v>147</v>
       </c>
       <c r="G3">
         <f>COUNTIF(TestMaster[Test Status], "Fail")</f>
         <v>0</v>
       </c>
       <c r="H3" s="7" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="I3">
         <v>17</v>
@@ -2467,10 +2460,10 @@
         <v>Nameless Module Creation</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="E4" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="G4">
         <f>COUNTIF(TestMaster[Test Status], "Not Run")</f>
@@ -2487,10 +2480,10 @@
         <v>Redundant Element Creation</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="E5" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.35">
@@ -2503,10 +2496,10 @@
         <v>No Element to Modify</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="E6" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.35">
@@ -2519,10 +2512,10 @@
         <v>Completed Element Modification</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="E7" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.35">
@@ -2535,10 +2528,10 @@
         <v>Modify into Redundant Element Name</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="E8" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.35">
@@ -2551,10 +2544,10 @@
         <v>Delete No Element Type</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="E9" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.35">
@@ -2567,10 +2560,10 @@
         <v>Delete Element Found</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="E10" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.35">
@@ -2583,10 +2576,10 @@
         <v>Delete Module by Port</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="E11" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.35">
@@ -2599,10 +2592,10 @@
         <v>FileManagementTesting</v>
       </c>
       <c r="C12" s="5" t="s">
+        <v>141</v>
+      </c>
+      <c r="E12" t="s">
         <v>144</v>
-      </c>
-      <c r="E12" t="s">
-        <v>147</v>
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.35">
@@ -2615,26 +2608,26 @@
         <v>ActionSelectLayout</v>
       </c>
       <c r="C13" s="5" t="s">
+        <v>141</v>
+      </c>
+      <c r="E13" t="s">
         <v>144</v>
       </c>
-      <c r="E13" t="s">
-        <v>147</v>
-      </c>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A14" s="21">
+      <c r="A14">
         <f>ROW()-1</f>
         <v>13</v>
       </c>
-      <c r="B14" s="21" t="str">
+      <c r="B14" t="str">
         <f>'File Manipulation Testing'!M1</f>
         <v>ActionSelectLosecontrol</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="E14" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
     </row>
   </sheetData>
@@ -2698,20 +2691,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A1" s="15" t="s">
+      <c r="A1" s="17" t="s">
         <v>11</v>
       </c>
-      <c r="B1" s="15"/>
-      <c r="C1" s="15"/>
-      <c r="D1" s="15"/>
-      <c r="E1" s="15"/>
-      <c r="F1" s="16"/>
+      <c r="B1" s="17"/>
+      <c r="C1" s="17"/>
+      <c r="D1" s="17"/>
+      <c r="E1" s="17"/>
+      <c r="F1" s="18"/>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A2" s="15" t="s">
+      <c r="A2" s="17" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="15"/>
+      <c r="B2" s="17"/>
       <c r="C2" s="7">
         <f>IFERROR(_xlfn.XLOOKUP(A1, TestMaster[Test Name], TestMaster[Test ID], "ID not found"), "")</f>
         <v>1</v>
@@ -2721,10 +2714,10 @@
       </c>
     </row>
     <row r="3" spans="1:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="15" t="s">
-        <v>167</v>
-      </c>
-      <c r="B3" s="15"/>
+      <c r="A3" s="17" t="s">
+        <v>164</v>
+      </c>
+      <c r="B3" s="17"/>
       <c r="C3" s="9" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(A1, TestMaster[Test Name], TestMaster[Test Priority], "Priority not found"), "")</f>
         <v>Medium</v>
@@ -2738,32 +2731,32 @@
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A4" s="15" t="s">
-        <v>164</v>
-      </c>
-      <c r="B4" s="15"/>
-      <c r="C4" s="15"/>
-      <c r="D4" s="15"/>
-      <c r="E4" s="15"/>
-      <c r="F4" s="16"/>
+      <c r="A4" s="17" t="s">
+        <v>161</v>
+      </c>
+      <c r="B4" s="17"/>
+      <c r="C4" s="17"/>
+      <c r="D4" s="17"/>
+      <c r="E4" s="17"/>
+      <c r="F4" s="18"/>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A5" s="15"/>
-      <c r="B5" s="15"/>
-      <c r="C5" s="15"/>
-      <c r="D5" s="15"/>
-      <c r="E5" s="15"/>
-      <c r="F5" s="16"/>
+      <c r="A5" s="17"/>
+      <c r="B5" s="17"/>
+      <c r="C5" s="17"/>
+      <c r="D5" s="17"/>
+      <c r="E5" s="17"/>
+      <c r="F5" s="18"/>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A6" s="15" t="s">
+      <c r="A6" s="17" t="s">
         <v>7</v>
       </c>
-      <c r="B6" s="15"/>
-      <c r="C6" s="15"/>
-      <c r="D6" s="15"/>
-      <c r="E6" s="15"/>
-      <c r="F6" s="16"/>
+      <c r="B6" s="17"/>
+      <c r="C6" s="17"/>
+      <c r="D6" s="17"/>
+      <c r="E6" s="17"/>
+      <c r="F6" s="18"/>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A7" s="1" t="s">
@@ -2790,13 +2783,13 @@
         <v>1</v>
       </c>
       <c r="B8" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="C8" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="29" x14ac:dyDescent="0.35">
@@ -2805,13 +2798,13 @@
         <v>2</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.35">
@@ -2820,13 +2813,13 @@
         <v>3</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.35">
@@ -2835,13 +2828,13 @@
         <v>4</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.35">
@@ -2850,13 +2843,13 @@
         <v>5</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="C12" s="3" t="s">
         <v>22</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.35">
@@ -2865,13 +2858,13 @@
         <v>6</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.35">
@@ -2880,13 +2873,13 @@
         <v>7</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
     </row>
     <row r="15" spans="1:6" ht="29" x14ac:dyDescent="0.35">
@@ -2895,13 +2888,13 @@
         <v>8</v>
       </c>
       <c r="B15" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="C15" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.35">
@@ -2910,13 +2903,13 @@
         <v>9</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="C16" s="3" t="s">
         <v>22</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.35">
@@ -2925,13 +2918,13 @@
         <v>10</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.35">
@@ -2940,13 +2933,13 @@
         <v>11</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.35">
@@ -2955,13 +2948,13 @@
         <v>12</v>
       </c>
       <c r="B19" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="C19" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.35">
@@ -2970,13 +2963,13 @@
         <v>13</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="C20" s="3" t="s">
         <v>22</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.35">
@@ -2985,13 +2978,13 @@
         <v>14</v>
       </c>
       <c r="B21" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="C21" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.35">
@@ -3000,13 +2993,13 @@
         <v>15</v>
       </c>
       <c r="B22" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.35">
@@ -3015,13 +3008,13 @@
         <v>16</v>
       </c>
       <c r="B23" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="C23" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.35">
@@ -3030,13 +3023,13 @@
         <v>17</v>
       </c>
       <c r="B24" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="C24" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.35">
@@ -3045,10 +3038,10 @@
         <v>18</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="D25" s="2" t="s">
         <v>30</v>
@@ -3093,36 +3086,36 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:18" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="15" t="s">
+      <c r="A1" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="B1" s="15"/>
-      <c r="C1" s="15"/>
-      <c r="D1" s="15"/>
-      <c r="E1" s="15"/>
-      <c r="F1" s="16"/>
-      <c r="G1" s="15" t="s">
+      <c r="B1" s="17"/>
+      <c r="C1" s="17"/>
+      <c r="D1" s="17"/>
+      <c r="E1" s="17"/>
+      <c r="F1" s="18"/>
+      <c r="G1" s="17" t="s">
         <v>13</v>
       </c>
-      <c r="H1" s="15"/>
-      <c r="I1" s="15"/>
-      <c r="J1" s="15"/>
-      <c r="K1" s="15"/>
-      <c r="L1" s="15"/>
-      <c r="M1" s="15" t="s">
-        <v>141</v>
-      </c>
-      <c r="N1" s="15"/>
-      <c r="O1" s="15"/>
-      <c r="P1" s="15"/>
-      <c r="Q1" s="15"/>
-      <c r="R1" s="15"/>
+      <c r="H1" s="17"/>
+      <c r="I1" s="17"/>
+      <c r="J1" s="17"/>
+      <c r="K1" s="17"/>
+      <c r="L1" s="17"/>
+      <c r="M1" s="17" t="s">
+        <v>138</v>
+      </c>
+      <c r="N1" s="17"/>
+      <c r="O1" s="17"/>
+      <c r="P1" s="17"/>
+      <c r="Q1" s="17"/>
+      <c r="R1" s="17"/>
     </row>
     <row r="2" spans="1:18" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="15" t="s">
+      <c r="A2" s="17" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="15"/>
+      <c r="B2" s="17"/>
       <c r="C2">
         <f>IFERROR(_xlfn.XLOOKUP(A1, TestMaster[Test Name], TestMaster[Test ID], "ID not found"), "")</f>
         <v>2</v>
@@ -3132,10 +3125,10 @@
         <v>4</v>
       </c>
       <c r="F2" s="8"/>
-      <c r="G2" s="15" t="s">
+      <c r="G2" s="17" t="s">
         <v>3</v>
       </c>
-      <c r="H2" s="15"/>
+      <c r="H2" s="17"/>
       <c r="I2">
         <f>IFERROR(_xlfn.XLOOKUP(G1, TestMaster[Test Name], TestMaster[Test ID], "ID not found"), "")</f>
         <v>3</v>
@@ -3145,10 +3138,10 @@
         <v>4</v>
       </c>
       <c r="L2" s="8"/>
-      <c r="M2" s="15" t="s">
+      <c r="M2" s="17" t="s">
         <v>3</v>
       </c>
-      <c r="N2" s="15"/>
+      <c r="N2" s="17"/>
       <c r="O2">
         <f>IFERROR(_xlfn.XLOOKUP(M1, TestMaster[Test Name], TestMaster[Test ID], "ID not found"), "")</f>
         <v>4</v>
@@ -3159,10 +3152,10 @@
       </c>
     </row>
     <row r="3" spans="1:18" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="15" t="s">
-        <v>167</v>
-      </c>
-      <c r="B3" s="15"/>
+      <c r="A3" s="17" t="s">
+        <v>164</v>
+      </c>
+      <c r="B3" s="17"/>
       <c r="C3" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(A1, TestMaster[Test Name], TestMaster[Test Priority], "Priority not found"), "")</f>
         <v>High</v>
@@ -3175,10 +3168,10 @@
         <f>IFERROR(_xlfn.XLOOKUP(A1, TestMaster[Test Name], TestMaster[Test Status], "Status not found"), "")</f>
         <v>Not Implemented</v>
       </c>
-      <c r="G3" s="15" t="s">
-        <v>167</v>
-      </c>
-      <c r="H3" s="15"/>
+      <c r="G3" s="17" t="s">
+        <v>164</v>
+      </c>
+      <c r="H3" s="17"/>
       <c r="I3" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(G1, TestMaster[Test Name], TestMaster[Test Priority], "Priority not found"), "")</f>
         <v>Medium</v>
@@ -3191,10 +3184,10 @@
         <f>IFERROR(_xlfn.XLOOKUP(G1, TestMaster[Test Name], TestMaster[Test Status], "Status not found"), "")</f>
         <v>Not Implemented</v>
       </c>
-      <c r="M3" s="15" t="s">
-        <v>167</v>
-      </c>
-      <c r="N3" s="15"/>
+      <c r="M3" s="17" t="s">
+        <v>164</v>
+      </c>
+      <c r="N3" s="17"/>
       <c r="O3" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(M1, TestMaster[Test Name], TestMaster[Test Priority], "Priority not found"), "")</f>
         <v>Low</v>
@@ -3209,76 +3202,76 @@
       </c>
     </row>
     <row r="4" spans="1:18" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="15" t="s">
+      <c r="A4" s="17" t="s">
         <v>6</v>
       </c>
-      <c r="B4" s="15"/>
-      <c r="C4" s="15"/>
-      <c r="D4" s="15"/>
-      <c r="E4" s="15"/>
-      <c r="F4" s="16"/>
-      <c r="G4" s="15" t="s">
+      <c r="B4" s="17"/>
+      <c r="C4" s="17"/>
+      <c r="D4" s="17"/>
+      <c r="E4" s="17"/>
+      <c r="F4" s="18"/>
+      <c r="G4" s="17" t="s">
         <v>6</v>
       </c>
-      <c r="H4" s="15"/>
-      <c r="I4" s="15"/>
-      <c r="J4" s="15"/>
-      <c r="K4" s="15"/>
-      <c r="L4" s="15"/>
-      <c r="M4" s="15" t="s">
+      <c r="H4" s="17"/>
+      <c r="I4" s="17"/>
+      <c r="J4" s="17"/>
+      <c r="K4" s="17"/>
+      <c r="L4" s="17"/>
+      <c r="M4" s="17" t="s">
         <v>6</v>
       </c>
-      <c r="N4" s="15"/>
-      <c r="O4" s="15"/>
-      <c r="P4" s="15"/>
-      <c r="Q4" s="15"/>
-      <c r="R4" s="15"/>
+      <c r="N4" s="17"/>
+      <c r="O4" s="17"/>
+      <c r="P4" s="17"/>
+      <c r="Q4" s="17"/>
+      <c r="R4" s="17"/>
     </row>
     <row r="5" spans="1:18" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="15"/>
-      <c r="B5" s="15"/>
-      <c r="C5" s="15"/>
-      <c r="D5" s="15"/>
-      <c r="E5" s="15"/>
-      <c r="F5" s="16"/>
-      <c r="G5" s="15"/>
-      <c r="H5" s="15"/>
-      <c r="I5" s="15"/>
-      <c r="J5" s="15"/>
-      <c r="K5" s="15"/>
-      <c r="L5" s="15"/>
-      <c r="M5" s="15"/>
-      <c r="N5" s="15"/>
-      <c r="O5" s="15"/>
-      <c r="P5" s="15"/>
-      <c r="Q5" s="15"/>
-      <c r="R5" s="15"/>
+      <c r="A5" s="17"/>
+      <c r="B5" s="17"/>
+      <c r="C5" s="17"/>
+      <c r="D5" s="17"/>
+      <c r="E5" s="17"/>
+      <c r="F5" s="18"/>
+      <c r="G5" s="17"/>
+      <c r="H5" s="17"/>
+      <c r="I5" s="17"/>
+      <c r="J5" s="17"/>
+      <c r="K5" s="17"/>
+      <c r="L5" s="17"/>
+      <c r="M5" s="17"/>
+      <c r="N5" s="17"/>
+      <c r="O5" s="17"/>
+      <c r="P5" s="17"/>
+      <c r="Q5" s="17"/>
+      <c r="R5" s="17"/>
     </row>
     <row r="6" spans="1:18" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="15" t="s">
+      <c r="A6" s="17" t="s">
         <v>7</v>
       </c>
-      <c r="B6" s="15"/>
-      <c r="C6" s="15"/>
-      <c r="D6" s="15"/>
-      <c r="E6" s="15"/>
-      <c r="F6" s="16"/>
-      <c r="G6" s="15" t="s">
+      <c r="B6" s="17"/>
+      <c r="C6" s="17"/>
+      <c r="D6" s="17"/>
+      <c r="E6" s="17"/>
+      <c r="F6" s="18"/>
+      <c r="G6" s="17" t="s">
         <v>7</v>
       </c>
-      <c r="H6" s="15"/>
-      <c r="I6" s="15"/>
-      <c r="J6" s="15"/>
-      <c r="K6" s="15"/>
-      <c r="L6" s="15"/>
-      <c r="M6" s="15" t="s">
+      <c r="H6" s="17"/>
+      <c r="I6" s="17"/>
+      <c r="J6" s="17"/>
+      <c r="K6" s="17"/>
+      <c r="L6" s="17"/>
+      <c r="M6" s="17" t="s">
         <v>7</v>
       </c>
-      <c r="N6" s="15"/>
-      <c r="O6" s="15"/>
-      <c r="P6" s="15"/>
-      <c r="Q6" s="15"/>
-      <c r="R6" s="15"/>
+      <c r="N6" s="17"/>
+      <c r="O6" s="17"/>
+      <c r="P6" s="17"/>
+      <c r="Q6" s="17"/>
+      <c r="R6" s="17"/>
     </row>
     <row r="7" spans="1:18" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A7" s="1" t="s">
@@ -3341,37 +3334,37 @@
         <v>1</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="C8" s="3" t="s">
         <v>21</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="G8" s="4">
         <v>1</v>
       </c>
       <c r="H8" s="4" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="I8" s="3" t="s">
         <v>21</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="M8" s="4">
         <v>1</v>
       </c>
       <c r="N8" s="4" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="O8" s="3" t="s">
         <v>21</v>
       </c>
       <c r="P8" s="3" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
     </row>
     <row r="9" spans="1:18" ht="43.5" x14ac:dyDescent="0.35">
@@ -3379,37 +3372,37 @@
         <v>2</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="G9" s="4">
         <v>2</v>
       </c>
       <c r="H9" s="4" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="M9" s="4">
         <v>2</v>
       </c>
       <c r="N9" s="4" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="O9" s="3" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="P9" s="3" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
     </row>
     <row r="10" spans="1:18" ht="29" x14ac:dyDescent="0.35">
@@ -3417,37 +3410,37 @@
         <v>3</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="G10" s="4">
         <v>3</v>
       </c>
       <c r="H10" s="4" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="M10" s="4">
         <v>3</v>
       </c>
       <c r="N10" s="4" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="O10" s="3" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="P10" s="3" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
     </row>
     <row r="11" spans="1:18" ht="43.5" x14ac:dyDescent="0.35">
@@ -3455,37 +3448,37 @@
         <v>4</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="G11" s="4">
         <v>4</v>
       </c>
       <c r="H11" s="4" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="M11" s="4">
         <v>4</v>
       </c>
       <c r="N11" s="4" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="O11" s="3" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="P11" s="3" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
     </row>
     <row r="12" spans="1:18" ht="43.5" x14ac:dyDescent="0.35">
@@ -3493,25 +3486,25 @@
         <v>5</v>
       </c>
       <c r="B12" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="D12" s="3" t="s">
         <v>113</v>
-      </c>
-      <c r="C12" s="3" t="s">
-        <v>114</v>
-      </c>
-      <c r="D12" s="3" t="s">
-        <v>116</v>
       </c>
       <c r="M12" s="4">
         <v>5</v>
       </c>
       <c r="N12" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="O12" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="P12" s="3" t="s">
         <v>124</v>
-      </c>
-      <c r="O12" s="3" t="s">
-        <v>125</v>
-      </c>
-      <c r="P12" s="3" t="s">
-        <v>127</v>
       </c>
     </row>
     <row r="13" spans="1:18" ht="29" x14ac:dyDescent="0.35">
@@ -3519,25 +3512,25 @@
         <v>6</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="M13" s="4">
         <v>6</v>
       </c>
       <c r="N13" s="4" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="O13" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="P13" s="3" t="s">
         <v>125</v>
-      </c>
-      <c r="P13" s="3" t="s">
-        <v>128</v>
       </c>
     </row>
     <row r="14" spans="1:18" x14ac:dyDescent="0.35">
@@ -3545,13 +3538,13 @@
         <v>7</v>
       </c>
       <c r="N14" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="O14" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="P14" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
     </row>
     <row r="15" spans="1:18" ht="29" x14ac:dyDescent="0.35">
@@ -3559,13 +3552,13 @@
         <v>8</v>
       </c>
       <c r="N15" s="4" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="O15" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="P15" s="3" t="s">
         <v>125</v>
-      </c>
-      <c r="P15" s="3" t="s">
-        <v>128</v>
       </c>
     </row>
     <row r="16" spans="1:18" x14ac:dyDescent="0.35">
@@ -3573,13 +3566,13 @@
         <v>9</v>
       </c>
       <c r="N16" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="O16" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="P16" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
     </row>
     <row r="17" spans="13:16" ht="29" x14ac:dyDescent="0.35">
@@ -3587,13 +3580,13 @@
         <v>10</v>
       </c>
       <c r="N17" s="4" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="O17" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="P17" s="3" t="s">
         <v>125</v>
-      </c>
-      <c r="P17" s="3" t="s">
-        <v>128</v>
       </c>
     </row>
     <row r="18" spans="13:16" x14ac:dyDescent="0.35">
@@ -3601,13 +3594,13 @@
         <v>11</v>
       </c>
       <c r="N18" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="O18" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="P18" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
     </row>
     <row r="19" spans="13:16" x14ac:dyDescent="0.35">
@@ -3615,13 +3608,13 @@
         <v>12</v>
       </c>
       <c r="N19" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="O19" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="P19" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
     </row>
     <row r="20" spans="13:16" x14ac:dyDescent="0.35">
@@ -3629,13 +3622,13 @@
         <v>13</v>
       </c>
       <c r="N20" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="O20" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="P20" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
     </row>
     <row r="21" spans="13:16" x14ac:dyDescent="0.35">
@@ -3643,22 +3636,17 @@
         <v>14</v>
       </c>
       <c r="N21" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="O21" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="P21" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="15">
-    <mergeCell ref="A4:F5"/>
-    <mergeCell ref="A6:F6"/>
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A3:B3"/>
-    <mergeCell ref="A2:B2"/>
     <mergeCell ref="M1:R1"/>
     <mergeCell ref="M2:N2"/>
     <mergeCell ref="M3:N3"/>
@@ -3669,6 +3657,11 @@
     <mergeCell ref="G2:H2"/>
     <mergeCell ref="G3:H3"/>
     <mergeCell ref="G1:L1"/>
+    <mergeCell ref="A4:F5"/>
+    <mergeCell ref="A6:F6"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A3:B3"/>
+    <mergeCell ref="A2:B2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3700,36 +3693,36 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A1" s="15" t="s">
+      <c r="A1" s="17" t="s">
         <v>14</v>
       </c>
-      <c r="B1" s="15"/>
-      <c r="C1" s="15"/>
-      <c r="D1" s="15"/>
-      <c r="E1" s="15"/>
-      <c r="F1" s="16"/>
-      <c r="G1" s="17" t="s">
+      <c r="B1" s="17"/>
+      <c r="C1" s="17"/>
+      <c r="D1" s="17"/>
+      <c r="E1" s="17"/>
+      <c r="F1" s="18"/>
+      <c r="G1" s="19" t="s">
         <v>15</v>
       </c>
-      <c r="H1" s="15"/>
-      <c r="I1" s="15"/>
-      <c r="J1" s="15"/>
-      <c r="K1" s="15"/>
-      <c r="L1" s="16"/>
-      <c r="M1" s="15" t="s">
-        <v>96</v>
-      </c>
-      <c r="N1" s="15"/>
-      <c r="O1" s="15"/>
-      <c r="P1" s="15"/>
-      <c r="Q1" s="15"/>
-      <c r="R1" s="15"/>
+      <c r="H1" s="17"/>
+      <c r="I1" s="17"/>
+      <c r="J1" s="17"/>
+      <c r="K1" s="17"/>
+      <c r="L1" s="18"/>
+      <c r="M1" s="17" t="s">
+        <v>93</v>
+      </c>
+      <c r="N1" s="17"/>
+      <c r="O1" s="17"/>
+      <c r="P1" s="17"/>
+      <c r="Q1" s="17"/>
+      <c r="R1" s="17"/>
     </row>
     <row r="2" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A2" s="15" t="s">
+      <c r="A2" s="17" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="15"/>
+      <c r="B2" s="17"/>
       <c r="C2" s="7">
         <f>IFERROR(_xlfn.XLOOKUP(A1, TestMaster[Test Name], TestMaster[Test ID], "ID not found"), "")</f>
         <v>5</v>
@@ -3737,10 +3730,10 @@
       <c r="E2" t="s">
         <v>4</v>
       </c>
-      <c r="G2" s="15" t="s">
+      <c r="G2" s="17" t="s">
         <v>3</v>
       </c>
-      <c r="H2" s="15"/>
+      <c r="H2" s="17"/>
       <c r="I2" s="7">
         <f>IFERROR(_xlfn.XLOOKUP(G1, TestMaster[Test Name], TestMaster[Test ID], "ID not found"), "")</f>
         <v>6</v>
@@ -3748,10 +3741,10 @@
       <c r="K2" t="s">
         <v>4</v>
       </c>
-      <c r="M2" s="15" t="s">
+      <c r="M2" s="17" t="s">
         <v>3</v>
       </c>
-      <c r="N2" s="15"/>
+      <c r="N2" s="17"/>
       <c r="O2" s="13">
         <f>IFERROR(_xlfn.XLOOKUP(M1, TestMaster[Test Name], TestMaster[Test ID], "ID not found"), "")</f>
         <v>7</v>
@@ -3761,10 +3754,10 @@
       </c>
     </row>
     <row r="3" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A3" s="15" t="s">
-        <v>167</v>
-      </c>
-      <c r="B3" s="15"/>
+      <c r="A3" s="17" t="s">
+        <v>164</v>
+      </c>
+      <c r="B3" s="17"/>
       <c r="C3" s="7" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(A1, TestMaster[Test Name], TestMaster[Test Priority], "Priority not found"), "")</f>
         <v>Medium</v>
@@ -3776,10 +3769,10 @@
         <f>IFERROR(_xlfn.XLOOKUP(A1, TestMaster[Test Name], TestMaster[Test Status], "Status not found"), "")</f>
         <v>Not Implemented</v>
       </c>
-      <c r="G3" s="15" t="s">
-        <v>167</v>
-      </c>
-      <c r="H3" s="15"/>
+      <c r="G3" s="17" t="s">
+        <v>164</v>
+      </c>
+      <c r="H3" s="17"/>
       <c r="I3" s="7" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(G1, TestMaster[Test Name], TestMaster[Test Priority], "Priority not found"), "")</f>
         <v>Medium</v>
@@ -3791,10 +3784,10 @@
         <f>IFERROR(_xlfn.XLOOKUP(G1, TestMaster[Test Name], TestMaster[Test Status], "Status not found"), "")</f>
         <v>Not Implemented</v>
       </c>
-      <c r="M3" s="15" t="s">
-        <v>167</v>
-      </c>
-      <c r="N3" s="15"/>
+      <c r="M3" s="17" t="s">
+        <v>164</v>
+      </c>
+      <c r="N3" s="17"/>
       <c r="O3" s="13" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(M1, TestMaster[Test Name], TestMaster[Test Priority], "Priority not found"), "")</f>
         <v>Low</v>
@@ -3808,76 +3801,76 @@
       </c>
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A4" s="15" t="s">
+      <c r="A4" s="17" t="s">
         <v>6</v>
       </c>
-      <c r="B4" s="15"/>
-      <c r="C4" s="15"/>
-      <c r="D4" s="15"/>
-      <c r="E4" s="15"/>
-      <c r="F4" s="16"/>
-      <c r="G4" s="17" t="s">
+      <c r="B4" s="17"/>
+      <c r="C4" s="17"/>
+      <c r="D4" s="17"/>
+      <c r="E4" s="17"/>
+      <c r="F4" s="18"/>
+      <c r="G4" s="19" t="s">
         <v>6</v>
       </c>
-      <c r="H4" s="15"/>
-      <c r="I4" s="15"/>
-      <c r="J4" s="15"/>
-      <c r="K4" s="15"/>
-      <c r="L4" s="16"/>
-      <c r="M4" s="15" t="s">
+      <c r="H4" s="17"/>
+      <c r="I4" s="17"/>
+      <c r="J4" s="17"/>
+      <c r="K4" s="17"/>
+      <c r="L4" s="18"/>
+      <c r="M4" s="17" t="s">
         <v>6</v>
       </c>
-      <c r="N4" s="15"/>
-      <c r="O4" s="15"/>
-      <c r="P4" s="15"/>
-      <c r="Q4" s="15"/>
-      <c r="R4" s="15"/>
+      <c r="N4" s="17"/>
+      <c r="O4" s="17"/>
+      <c r="P4" s="17"/>
+      <c r="Q4" s="17"/>
+      <c r="R4" s="17"/>
     </row>
     <row r="5" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A5" s="15"/>
-      <c r="B5" s="15"/>
-      <c r="C5" s="15"/>
-      <c r="D5" s="15"/>
-      <c r="E5" s="15"/>
-      <c r="F5" s="16"/>
-      <c r="G5" s="17"/>
-      <c r="H5" s="15"/>
-      <c r="I5" s="15"/>
-      <c r="J5" s="15"/>
-      <c r="K5" s="15"/>
-      <c r="L5" s="16"/>
-      <c r="M5" s="15"/>
-      <c r="N5" s="15"/>
-      <c r="O5" s="15"/>
-      <c r="P5" s="15"/>
-      <c r="Q5" s="15"/>
-      <c r="R5" s="15"/>
+      <c r="A5" s="17"/>
+      <c r="B5" s="17"/>
+      <c r="C5" s="17"/>
+      <c r="D5" s="17"/>
+      <c r="E5" s="17"/>
+      <c r="F5" s="18"/>
+      <c r="G5" s="19"/>
+      <c r="H5" s="17"/>
+      <c r="I5" s="17"/>
+      <c r="J5" s="17"/>
+      <c r="K5" s="17"/>
+      <c r="L5" s="18"/>
+      <c r="M5" s="17"/>
+      <c r="N5" s="17"/>
+      <c r="O5" s="17"/>
+      <c r="P5" s="17"/>
+      <c r="Q5" s="17"/>
+      <c r="R5" s="17"/>
     </row>
     <row r="6" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A6" s="15" t="s">
+      <c r="A6" s="17" t="s">
         <v>7</v>
       </c>
-      <c r="B6" s="15"/>
-      <c r="C6" s="15"/>
-      <c r="D6" s="15"/>
-      <c r="E6" s="15"/>
-      <c r="F6" s="16"/>
-      <c r="G6" s="17" t="s">
+      <c r="B6" s="17"/>
+      <c r="C6" s="17"/>
+      <c r="D6" s="17"/>
+      <c r="E6" s="17"/>
+      <c r="F6" s="18"/>
+      <c r="G6" s="19" t="s">
         <v>7</v>
       </c>
-      <c r="H6" s="15"/>
-      <c r="I6" s="15"/>
-      <c r="J6" s="15"/>
-      <c r="K6" s="15"/>
-      <c r="L6" s="16"/>
-      <c r="M6" s="15" t="s">
+      <c r="H6" s="17"/>
+      <c r="I6" s="17"/>
+      <c r="J6" s="17"/>
+      <c r="K6" s="17"/>
+      <c r="L6" s="18"/>
+      <c r="M6" s="17" t="s">
         <v>7</v>
       </c>
-      <c r="N6" s="15"/>
-      <c r="O6" s="15"/>
-      <c r="P6" s="15"/>
-      <c r="Q6" s="15"/>
-      <c r="R6" s="15"/>
+      <c r="N6" s="17"/>
+      <c r="O6" s="17"/>
+      <c r="P6" s="17"/>
+      <c r="Q6" s="17"/>
+      <c r="R6" s="17"/>
     </row>
     <row r="7" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A7" s="1" t="s">
@@ -3940,37 +3933,37 @@
         <v>1</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="C8" s="4" t="s">
         <v>21</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="G8">
         <v>1</v>
       </c>
       <c r="H8" s="4" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="I8" s="4" t="s">
         <v>21</v>
       </c>
       <c r="J8" s="4" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="M8">
         <v>1</v>
       </c>
       <c r="N8" s="4" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="O8" s="4" t="s">
         <v>21</v>
       </c>
       <c r="P8" s="4" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
     </row>
     <row r="9" spans="1:18" ht="43.5" x14ac:dyDescent="0.35">
@@ -3978,7 +3971,7 @@
         <v>2</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C9" s="4" t="s">
         <v>21</v>
@@ -3990,25 +3983,25 @@
         <v>2</v>
       </c>
       <c r="H9" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="I9" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="I9" s="3" t="s">
-        <v>58</v>
-      </c>
       <c r="J9" s="3" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="M9">
         <v>2</v>
       </c>
       <c r="N9" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="O9" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="O9" s="3" t="s">
-        <v>58</v>
-      </c>
       <c r="P9" s="3" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
     </row>
     <row r="10" spans="1:18" ht="29" x14ac:dyDescent="0.35">
@@ -4016,25 +4009,25 @@
         <v>3</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="M10">
         <v>3</v>
       </c>
       <c r="N10" s="3" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="O10" s="3" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="P10" s="3" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
     </row>
     <row r="11" spans="1:18" x14ac:dyDescent="0.35">
@@ -4042,25 +4035,25 @@
         <v>4</v>
       </c>
       <c r="H11" t="s">
+        <v>66</v>
+      </c>
+      <c r="I11" t="s">
         <v>69</v>
       </c>
-      <c r="I11" t="s">
-        <v>72</v>
-      </c>
       <c r="J11" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="M11">
         <v>4</v>
       </c>
       <c r="N11" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="O11" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="P11" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
     </row>
     <row r="12" spans="1:18" x14ac:dyDescent="0.35">
@@ -4068,25 +4061,25 @@
         <v>5</v>
       </c>
       <c r="H12" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="I12" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="J12" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="M12">
         <v>5</v>
       </c>
       <c r="N12" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="O12" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="P12" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
     </row>
     <row r="13" spans="1:18" x14ac:dyDescent="0.35">
@@ -4094,25 +4087,25 @@
         <v>6</v>
       </c>
       <c r="H13" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="I13" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="J13" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="M13">
         <v>6</v>
       </c>
       <c r="N13" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="O13" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="P13" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
     </row>
     <row r="14" spans="1:18" x14ac:dyDescent="0.35">
@@ -4120,19 +4113,19 @@
         <v>7</v>
       </c>
       <c r="H14" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="M14">
         <v>8</v>
       </c>
       <c r="N14" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="O14" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="P14" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
     </row>
     <row r="15" spans="1:18" x14ac:dyDescent="0.35">
@@ -4140,25 +4133,25 @@
         <v>8</v>
       </c>
       <c r="H15" t="s">
+        <v>66</v>
+      </c>
+      <c r="I15" t="s">
         <v>69</v>
       </c>
-      <c r="I15" t="s">
-        <v>72</v>
-      </c>
       <c r="J15" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="M15">
         <v>9</v>
       </c>
       <c r="N15" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="O15" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="P15" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
     </row>
     <row r="16" spans="1:18" x14ac:dyDescent="0.35">
@@ -4166,25 +4159,25 @@
         <v>9</v>
       </c>
       <c r="H16" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="I16" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="J16" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="M16">
         <v>10</v>
       </c>
       <c r="N16" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="O16" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="P16" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
     </row>
     <row r="17" spans="7:10" x14ac:dyDescent="0.35">
@@ -4192,13 +4185,13 @@
         <v>10</v>
       </c>
       <c r="H17" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="I17" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="J17" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
     </row>
     <row r="18" spans="7:10" x14ac:dyDescent="0.35">
@@ -4206,13 +4199,13 @@
         <v>11</v>
       </c>
       <c r="H18" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="I18" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="J18" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
     </row>
     <row r="19" spans="7:10" x14ac:dyDescent="0.35">
@@ -4220,13 +4213,13 @@
         <v>12</v>
       </c>
       <c r="H19" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="I19" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="J19" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
     </row>
     <row r="20" spans="7:10" x14ac:dyDescent="0.35">
@@ -4234,13 +4227,13 @@
         <v>13</v>
       </c>
       <c r="H20" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="I20" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="J20" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
     </row>
     <row r="21" spans="7:10" x14ac:dyDescent="0.35">
@@ -4248,13 +4241,13 @@
         <v>14</v>
       </c>
       <c r="H21" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="I21" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="J21" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
     </row>
     <row r="22" spans="7:10" x14ac:dyDescent="0.35">
@@ -4262,13 +4255,13 @@
         <v>15</v>
       </c>
       <c r="H22" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="I22" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="J22" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
     </row>
     <row r="23" spans="7:10" x14ac:dyDescent="0.35">
@@ -4276,13 +4269,13 @@
         <v>16</v>
       </c>
       <c r="H23" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="I23" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="J23" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
     </row>
     <row r="24" spans="7:10" x14ac:dyDescent="0.35">
@@ -4290,13 +4283,13 @@
         <v>17</v>
       </c>
       <c r="H24" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="I24" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="J24" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
     </row>
     <row r="25" spans="7:10" x14ac:dyDescent="0.35">
@@ -4304,10 +4297,10 @@
         <v>18</v>
       </c>
       <c r="H25" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="I25" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="J25" t="s">
         <v>30</v>
@@ -4315,11 +4308,6 @@
     </row>
   </sheetData>
   <mergeCells count="15">
-    <mergeCell ref="A4:F5"/>
-    <mergeCell ref="A6:F6"/>
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="A3:B3"/>
     <mergeCell ref="M1:R1"/>
     <mergeCell ref="M2:N2"/>
     <mergeCell ref="M3:N3"/>
@@ -4330,6 +4318,11 @@
     <mergeCell ref="G2:H2"/>
     <mergeCell ref="G3:H3"/>
     <mergeCell ref="G1:L1"/>
+    <mergeCell ref="A4:F5"/>
+    <mergeCell ref="A6:F6"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="A3:B3"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -4361,36 +4354,36 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A1" s="15" t="s">
+      <c r="A1" s="17" t="s">
         <v>16</v>
       </c>
-      <c r="B1" s="15"/>
-      <c r="C1" s="15"/>
-      <c r="D1" s="15"/>
-      <c r="E1" s="15"/>
-      <c r="F1" s="16"/>
-      <c r="G1" s="17" t="s">
+      <c r="B1" s="17"/>
+      <c r="C1" s="17"/>
+      <c r="D1" s="17"/>
+      <c r="E1" s="17"/>
+      <c r="F1" s="18"/>
+      <c r="G1" s="19" t="s">
         <v>17</v>
       </c>
-      <c r="H1" s="15"/>
-      <c r="I1" s="15"/>
-      <c r="J1" s="15"/>
-      <c r="K1" s="15"/>
-      <c r="L1" s="16"/>
-      <c r="M1" s="15" t="s">
+      <c r="H1" s="17"/>
+      <c r="I1" s="17"/>
+      <c r="J1" s="17"/>
+      <c r="K1" s="17"/>
+      <c r="L1" s="18"/>
+      <c r="M1" s="17" t="s">
         <v>18</v>
       </c>
-      <c r="N1" s="15"/>
-      <c r="O1" s="15"/>
-      <c r="P1" s="15"/>
-      <c r="Q1" s="15"/>
-      <c r="R1" s="15"/>
+      <c r="N1" s="17"/>
+      <c r="O1" s="17"/>
+      <c r="P1" s="17"/>
+      <c r="Q1" s="17"/>
+      <c r="R1" s="17"/>
     </row>
     <row r="2" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A2" s="15" t="s">
+      <c r="A2" s="17" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="15"/>
+      <c r="B2" s="17"/>
       <c r="C2" s="7">
         <f>IFERROR(_xlfn.XLOOKUP(A1, TestMaster[Test Name], TestMaster[Test ID], "ID not found"), "")</f>
         <v>8</v>
@@ -4398,10 +4391,10 @@
       <c r="E2" t="s">
         <v>4</v>
       </c>
-      <c r="G2" s="15" t="s">
+      <c r="G2" s="17" t="s">
         <v>3</v>
       </c>
-      <c r="H2" s="15"/>
+      <c r="H2" s="17"/>
       <c r="I2" s="7">
         <f>IFERROR(_xlfn.XLOOKUP(G1, TestMaster[Test Name], TestMaster[Test ID], "ID not found"), "")</f>
         <v>9</v>
@@ -4409,10 +4402,10 @@
       <c r="K2" t="s">
         <v>4</v>
       </c>
-      <c r="M2" s="15" t="s">
+      <c r="M2" s="17" t="s">
         <v>3</v>
       </c>
-      <c r="N2" s="15"/>
+      <c r="N2" s="17"/>
       <c r="O2" s="7">
         <f>IFERROR(_xlfn.XLOOKUP(M1, TestMaster[Test Name], TestMaster[Test ID], "ID not found"), "")</f>
         <v>10</v>
@@ -4422,10 +4415,10 @@
       </c>
     </row>
     <row r="3" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A3" s="15" t="s">
-        <v>167</v>
-      </c>
-      <c r="B3" s="15"/>
+      <c r="A3" s="17" t="s">
+        <v>164</v>
+      </c>
+      <c r="B3" s="17"/>
       <c r="C3" s="7" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(A1, TestMaster[Test Name], TestMaster[Test Priority], "Priority not found"), "")</f>
         <v>Medium</v>
@@ -4437,10 +4430,10 @@
         <f>IFERROR(_xlfn.XLOOKUP(A1, TestMaster[Test Name], TestMaster[Test Status], "Status not found"), "")</f>
         <v>Not Implemented</v>
       </c>
-      <c r="G3" s="15" t="s">
-        <v>167</v>
-      </c>
-      <c r="H3" s="15"/>
+      <c r="G3" s="17" t="s">
+        <v>164</v>
+      </c>
+      <c r="H3" s="17"/>
       <c r="I3" s="7" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(G1, TestMaster[Test Name], TestMaster[Test Priority], "Priority not found"), "")</f>
         <v>Medium</v>
@@ -4452,10 +4445,10 @@
         <f>IFERROR(_xlfn.XLOOKUP(G1, TestMaster[Test Name], TestMaster[Test Status], "Status not found"), "")</f>
         <v>Not Implemented</v>
       </c>
-      <c r="M3" s="15" t="s">
-        <v>167</v>
-      </c>
-      <c r="N3" s="15"/>
+      <c r="M3" s="17" t="s">
+        <v>164</v>
+      </c>
+      <c r="N3" s="17"/>
       <c r="O3" s="7" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(M1, TestMaster[Test Name], TestMaster[Test Priority], "Priority not found"), "")</f>
         <v>Low</v>
@@ -4469,76 +4462,76 @@
       </c>
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A4" s="19" t="s">
-        <v>51</v>
-      </c>
-      <c r="B4" s="19"/>
-      <c r="C4" s="19"/>
-      <c r="D4" s="19"/>
-      <c r="E4" s="19"/>
-      <c r="F4" s="20"/>
-      <c r="G4" s="18" t="s">
+      <c r="A4" s="20" t="s">
+        <v>48</v>
+      </c>
+      <c r="B4" s="20"/>
+      <c r="C4" s="20"/>
+      <c r="D4" s="20"/>
+      <c r="E4" s="20"/>
+      <c r="F4" s="21"/>
+      <c r="G4" s="22" t="s">
         <v>6</v>
       </c>
-      <c r="H4" s="19"/>
-      <c r="I4" s="19"/>
-      <c r="J4" s="19"/>
-      <c r="K4" s="19"/>
-      <c r="L4" s="20"/>
-      <c r="M4" s="19" t="s">
+      <c r="H4" s="20"/>
+      <c r="I4" s="20"/>
+      <c r="J4" s="20"/>
+      <c r="K4" s="20"/>
+      <c r="L4" s="21"/>
+      <c r="M4" s="20" t="s">
         <v>6</v>
       </c>
-      <c r="N4" s="19"/>
-      <c r="O4" s="19"/>
-      <c r="P4" s="19"/>
-      <c r="Q4" s="19"/>
-      <c r="R4" s="19"/>
+      <c r="N4" s="20"/>
+      <c r="O4" s="20"/>
+      <c r="P4" s="20"/>
+      <c r="Q4" s="20"/>
+      <c r="R4" s="20"/>
     </row>
     <row r="5" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A5" s="19"/>
-      <c r="B5" s="19"/>
-      <c r="C5" s="19"/>
-      <c r="D5" s="19"/>
-      <c r="E5" s="19"/>
-      <c r="F5" s="20"/>
-      <c r="G5" s="18"/>
-      <c r="H5" s="19"/>
-      <c r="I5" s="19"/>
-      <c r="J5" s="19"/>
-      <c r="K5" s="19"/>
-      <c r="L5" s="20"/>
-      <c r="M5" s="19"/>
-      <c r="N5" s="19"/>
-      <c r="O5" s="19"/>
-      <c r="P5" s="19"/>
-      <c r="Q5" s="19"/>
-      <c r="R5" s="19"/>
+      <c r="A5" s="20"/>
+      <c r="B5" s="20"/>
+      <c r="C5" s="20"/>
+      <c r="D5" s="20"/>
+      <c r="E5" s="20"/>
+      <c r="F5" s="21"/>
+      <c r="G5" s="22"/>
+      <c r="H5" s="20"/>
+      <c r="I5" s="20"/>
+      <c r="J5" s="20"/>
+      <c r="K5" s="20"/>
+      <c r="L5" s="21"/>
+      <c r="M5" s="20"/>
+      <c r="N5" s="20"/>
+      <c r="O5" s="20"/>
+      <c r="P5" s="20"/>
+      <c r="Q5" s="20"/>
+      <c r="R5" s="20"/>
     </row>
     <row r="6" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A6" s="15" t="s">
-        <v>52</v>
-      </c>
-      <c r="B6" s="15"/>
-      <c r="C6" s="15"/>
-      <c r="D6" s="15"/>
-      <c r="E6" s="15"/>
-      <c r="F6" s="16"/>
-      <c r="G6" s="17" t="s">
+      <c r="A6" s="17" t="s">
+        <v>49</v>
+      </c>
+      <c r="B6" s="17"/>
+      <c r="C6" s="17"/>
+      <c r="D6" s="17"/>
+      <c r="E6" s="17"/>
+      <c r="F6" s="18"/>
+      <c r="G6" s="19" t="s">
         <v>7</v>
       </c>
-      <c r="H6" s="15"/>
-      <c r="I6" s="15"/>
-      <c r="J6" s="15"/>
-      <c r="K6" s="15"/>
-      <c r="L6" s="16"/>
-      <c r="M6" s="15" t="s">
+      <c r="H6" s="17"/>
+      <c r="I6" s="17"/>
+      <c r="J6" s="17"/>
+      <c r="K6" s="17"/>
+      <c r="L6" s="18"/>
+      <c r="M6" s="17" t="s">
         <v>7</v>
       </c>
-      <c r="N6" s="15"/>
-      <c r="O6" s="15"/>
-      <c r="P6" s="15"/>
-      <c r="Q6" s="15"/>
-      <c r="R6" s="15"/>
+      <c r="N6" s="17"/>
+      <c r="O6" s="17"/>
+      <c r="P6" s="17"/>
+      <c r="Q6" s="17"/>
+      <c r="R6" s="17"/>
     </row>
     <row r="7" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A7" s="1" t="s">
@@ -4601,39 +4594,39 @@
         <v>1</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="C8" s="3" t="s">
         <v>21</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="F8" s="14"/>
       <c r="G8" s="3">
         <v>1</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="I8" s="3" t="s">
         <v>21</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="L8" s="14"/>
       <c r="M8" s="3">
         <v>1</v>
       </c>
       <c r="N8" s="3" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="O8" s="3" t="s">
         <v>21</v>
       </c>
       <c r="P8" s="3" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
     </row>
     <row r="9" spans="1:18" s="3" customFormat="1" ht="43.5" x14ac:dyDescent="0.35">
@@ -4641,7 +4634,7 @@
         <v>2</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C9" s="3" t="s">
         <v>21</v>
@@ -4654,26 +4647,26 @@
         <v>2</v>
       </c>
       <c r="H9" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="I9" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="I9" s="3" t="s">
-        <v>58</v>
-      </c>
       <c r="J9" s="3" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="L9" s="14"/>
       <c r="M9" s="3">
         <v>2</v>
       </c>
       <c r="N9" s="3" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="O9" s="3" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="P9" s="3" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="10" spans="1:18" s="3" customFormat="1" ht="29" x14ac:dyDescent="0.35">
@@ -4682,26 +4675,26 @@
         <v>3</v>
       </c>
       <c r="H10" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="I10" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="I10" s="3" t="s">
-        <v>59</v>
-      </c>
       <c r="J10" s="3" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="L10" s="14"/>
       <c r="M10" s="3">
         <v>3</v>
       </c>
       <c r="N10" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="O10" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="O10" s="3" t="s">
-        <v>59</v>
-      </c>
       <c r="P10" s="3" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
     </row>
     <row r="11" spans="1:18" ht="29" x14ac:dyDescent="0.35">
@@ -4709,22 +4702,17 @@
         <v>4</v>
       </c>
       <c r="N11" s="3" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="O11" s="3" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="P11" s="3" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="15">
-    <mergeCell ref="A4:F5"/>
-    <mergeCell ref="A6:F6"/>
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="A3:B3"/>
     <mergeCell ref="M1:R1"/>
     <mergeCell ref="M2:N2"/>
     <mergeCell ref="M3:N3"/>
@@ -4735,6 +4723,11 @@
     <mergeCell ref="G2:H2"/>
     <mergeCell ref="G3:H3"/>
     <mergeCell ref="G1:L1"/>
+    <mergeCell ref="A4:F5"/>
+    <mergeCell ref="A6:F6"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="A3:B3"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -4756,7 +4749,7 @@
     <col min="9" max="9" width="27.36328125" customWidth="1"/>
     <col min="10" max="10" width="15.26953125" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="18.453125" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="8.7265625" style="23"/>
+    <col min="13" max="13" width="8.7265625" style="16"/>
     <col min="14" max="14" width="23.26953125" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="17.1796875" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="41" bestFit="1" customWidth="1"/>
@@ -4765,36 +4758,36 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A1" s="15" t="s">
-        <v>178</v>
-      </c>
-      <c r="B1" s="15"/>
-      <c r="C1" s="15"/>
-      <c r="D1" s="15"/>
-      <c r="E1" s="15"/>
-      <c r="F1" s="16"/>
-      <c r="G1" s="15" t="s">
-        <v>170</v>
-      </c>
-      <c r="H1" s="15"/>
-      <c r="I1" s="15"/>
-      <c r="J1" s="15"/>
-      <c r="K1" s="15"/>
-      <c r="L1" s="15"/>
-      <c r="M1" s="17" t="s">
-        <v>186</v>
-      </c>
-      <c r="N1" s="24"/>
-      <c r="O1" s="24"/>
-      <c r="P1" s="24"/>
-      <c r="Q1" s="24"/>
-      <c r="R1" s="16"/>
+      <c r="A1" s="17" t="s">
+        <v>175</v>
+      </c>
+      <c r="B1" s="17"/>
+      <c r="C1" s="17"/>
+      <c r="D1" s="17"/>
+      <c r="E1" s="17"/>
+      <c r="F1" s="18"/>
+      <c r="G1" s="17" t="s">
+        <v>167</v>
+      </c>
+      <c r="H1" s="17"/>
+      <c r="I1" s="17"/>
+      <c r="J1" s="17"/>
+      <c r="K1" s="17"/>
+      <c r="L1" s="17"/>
+      <c r="M1" s="19" t="s">
+        <v>183</v>
+      </c>
+      <c r="N1" s="17"/>
+      <c r="O1" s="17"/>
+      <c r="P1" s="17"/>
+      <c r="Q1" s="17"/>
+      <c r="R1" s="18"/>
     </row>
     <row r="2" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A2" s="15" t="s">
+      <c r="A2" s="17" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="15"/>
+      <c r="B2" s="17"/>
       <c r="C2" s="7">
         <f>IFERROR(_xlfn.XLOOKUP(A1, TestMaster[Test Name], TestMaster[Test ID], "ID not found"), "")</f>
         <v>11</v>
@@ -4802,10 +4795,10 @@
       <c r="E2" t="s">
         <v>4</v>
       </c>
-      <c r="G2" s="15" t="s">
+      <c r="G2" s="17" t="s">
         <v>3</v>
       </c>
-      <c r="H2" s="15"/>
+      <c r="H2" s="17"/>
       <c r="I2" s="7">
         <f>IFERROR(_xlfn.XLOOKUP(G1, TestMaster[Test Name], TestMaster[Test ID], "ID not found"), "")</f>
         <v>12</v>
@@ -4813,25 +4806,24 @@
       <c r="K2" t="s">
         <v>4</v>
       </c>
-      <c r="M2" s="17" t="s">
+      <c r="M2" s="19" t="s">
         <v>3</v>
       </c>
-      <c r="N2" s="24"/>
-      <c r="O2" s="25">
+      <c r="N2" s="17"/>
+      <c r="O2" s="7">
         <f>IFERROR(_xlfn.XLOOKUP(M1, TestMaster[Test Name], TestMaster[Test ID], "ID not found"), "")</f>
         <v>13</v>
       </c>
-      <c r="P2" s="26"/>
-      <c r="Q2" s="26" t="s">
+      <c r="Q2" t="s">
         <v>4</v>
       </c>
       <c r="R2" s="8"/>
     </row>
     <row r="3" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A3" s="15" t="s">
-        <v>167</v>
-      </c>
-      <c r="B3" s="15"/>
+      <c r="A3" s="17" t="s">
+        <v>164</v>
+      </c>
+      <c r="B3" s="17"/>
       <c r="C3" s="7" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(A1, TestMaster[Test Name], TestMaster[Test Priority], "Priority not found"), "")</f>
         <v>High</v>
@@ -4843,10 +4835,10 @@
         <f>IFERROR(_xlfn.XLOOKUP(A1, TestMaster[Test Name], TestMaster[Test Priority], "Priority not found"), "")</f>
         <v>High</v>
       </c>
-      <c r="G3" s="15" t="s">
-        <v>167</v>
-      </c>
-      <c r="H3" s="15"/>
+      <c r="G3" s="17" t="s">
+        <v>164</v>
+      </c>
+      <c r="H3" s="17"/>
       <c r="I3" s="7" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(G1, TestMaster[Test Name], TestMaster[Test Priority], "Priority not found"), "")</f>
         <v>High</v>
@@ -4858,16 +4850,15 @@
         <f>IFERROR(_xlfn.XLOOKUP(G1, TestMaster[Test Name], TestMaster[Test Priority], "Priority not found"), "")</f>
         <v>High</v>
       </c>
-      <c r="M3" s="17" t="s">
-        <v>167</v>
-      </c>
-      <c r="N3" s="24"/>
-      <c r="O3" s="25" t="str">
+      <c r="M3" s="19" t="s">
+        <v>164</v>
+      </c>
+      <c r="N3" s="17"/>
+      <c r="O3" s="7" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(M1, TestMaster[Test Name], TestMaster[Test Priority], "Priority not found"), "")</f>
         <v>Medium</v>
       </c>
-      <c r="P3" s="26"/>
-      <c r="Q3" s="26" t="s">
+      <c r="Q3" t="s">
         <v>5</v>
       </c>
       <c r="R3" s="8" t="str">
@@ -4876,76 +4867,76 @@
       </c>
     </row>
     <row r="4" spans="1:18" s="2" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="19" t="s">
-        <v>180</v>
-      </c>
-      <c r="B4" s="19"/>
-      <c r="C4" s="19"/>
-      <c r="D4" s="19"/>
-      <c r="E4" s="19"/>
-      <c r="F4" s="20"/>
-      <c r="G4" s="19" t="s">
+      <c r="A4" s="20" t="s">
         <v>177</v>
       </c>
-      <c r="H4" s="19"/>
-      <c r="I4" s="19"/>
-      <c r="J4" s="19"/>
-      <c r="K4" s="19"/>
-      <c r="L4" s="19"/>
-      <c r="M4" s="18" t="s">
-        <v>185</v>
-      </c>
-      <c r="N4" s="27"/>
-      <c r="O4" s="27"/>
-      <c r="P4" s="27"/>
-      <c r="Q4" s="27"/>
-      <c r="R4" s="20"/>
+      <c r="B4" s="20"/>
+      <c r="C4" s="20"/>
+      <c r="D4" s="20"/>
+      <c r="E4" s="20"/>
+      <c r="F4" s="21"/>
+      <c r="G4" s="20" t="s">
+        <v>174</v>
+      </c>
+      <c r="H4" s="20"/>
+      <c r="I4" s="20"/>
+      <c r="J4" s="20"/>
+      <c r="K4" s="20"/>
+      <c r="L4" s="20"/>
+      <c r="M4" s="22" t="s">
+        <v>182</v>
+      </c>
+      <c r="N4" s="20"/>
+      <c r="O4" s="20"/>
+      <c r="P4" s="20"/>
+      <c r="Q4" s="20"/>
+      <c r="R4" s="21"/>
     </row>
     <row r="5" spans="1:18" s="2" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="19"/>
-      <c r="B5" s="19"/>
-      <c r="C5" s="19"/>
-      <c r="D5" s="19"/>
-      <c r="E5" s="19"/>
-      <c r="F5" s="20"/>
-      <c r="G5" s="19"/>
-      <c r="H5" s="19"/>
-      <c r="I5" s="19"/>
-      <c r="J5" s="19"/>
-      <c r="K5" s="19"/>
-      <c r="L5" s="19"/>
-      <c r="M5" s="18"/>
-      <c r="N5" s="27"/>
-      <c r="O5" s="27"/>
-      <c r="P5" s="27"/>
-      <c r="Q5" s="27"/>
-      <c r="R5" s="20"/>
+      <c r="A5" s="20"/>
+      <c r="B5" s="20"/>
+      <c r="C5" s="20"/>
+      <c r="D5" s="20"/>
+      <c r="E5" s="20"/>
+      <c r="F5" s="21"/>
+      <c r="G5" s="20"/>
+      <c r="H5" s="20"/>
+      <c r="I5" s="20"/>
+      <c r="J5" s="20"/>
+      <c r="K5" s="20"/>
+      <c r="L5" s="20"/>
+      <c r="M5" s="22"/>
+      <c r="N5" s="20"/>
+      <c r="O5" s="20"/>
+      <c r="P5" s="20"/>
+      <c r="Q5" s="20"/>
+      <c r="R5" s="21"/>
     </row>
     <row r="6" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A6" s="15" t="s">
-        <v>37</v>
-      </c>
-      <c r="B6" s="15"/>
-      <c r="C6" s="15"/>
-      <c r="D6" s="15"/>
-      <c r="E6" s="15"/>
-      <c r="F6" s="16"/>
-      <c r="G6" s="15" t="s">
-        <v>50</v>
-      </c>
-      <c r="H6" s="15"/>
-      <c r="I6" s="15"/>
-      <c r="J6" s="15"/>
-      <c r="K6" s="15"/>
-      <c r="L6" s="15"/>
-      <c r="M6" s="17" t="s">
-        <v>50</v>
-      </c>
-      <c r="N6" s="24"/>
-      <c r="O6" s="24"/>
-      <c r="P6" s="24"/>
-      <c r="Q6" s="24"/>
-      <c r="R6" s="16"/>
+      <c r="A6" s="17" t="s">
+        <v>36</v>
+      </c>
+      <c r="B6" s="17"/>
+      <c r="C6" s="17"/>
+      <c r="D6" s="17"/>
+      <c r="E6" s="17"/>
+      <c r="F6" s="18"/>
+      <c r="G6" s="17" t="s">
+        <v>47</v>
+      </c>
+      <c r="H6" s="17"/>
+      <c r="I6" s="17"/>
+      <c r="J6" s="17"/>
+      <c r="K6" s="17"/>
+      <c r="L6" s="17"/>
+      <c r="M6" s="19" t="s">
+        <v>47</v>
+      </c>
+      <c r="N6" s="17"/>
+      <c r="O6" s="17"/>
+      <c r="P6" s="17"/>
+      <c r="Q6" s="17"/>
+      <c r="R6" s="18"/>
     </row>
     <row r="7" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A7" s="1" t="s">
@@ -4984,7 +4975,7 @@
       <c r="L7" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="M7" s="22" t="s">
+      <c r="M7" s="15" t="s">
         <v>0</v>
       </c>
       <c r="N7" s="1" t="s">
@@ -5008,27 +4999,27 @@
         <v>1</v>
       </c>
       <c r="B8" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C8" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="D8" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="G8">
         <v>1</v>
       </c>
       <c r="H8" t="s">
+        <v>42</v>
+      </c>
+      <c r="I8" t="s">
+        <v>46</v>
+      </c>
+      <c r="J8" t="s">
         <v>45</v>
       </c>
-      <c r="I8" t="s">
-        <v>49</v>
-      </c>
-      <c r="J8" t="s">
-        <v>48</v>
-      </c>
-      <c r="M8" s="23">
+      <c r="M8" s="16">
         <v>1</v>
       </c>
       <c r="R8" s="8"/>
@@ -5038,27 +5029,27 @@
         <v>2</v>
       </c>
       <c r="B9" t="s">
+        <v>37</v>
+      </c>
+      <c r="C9" t="s">
+        <v>179</v>
+      </c>
+      <c r="D9" t="s">
         <v>39</v>
-      </c>
-      <c r="C9" t="s">
-        <v>182</v>
-      </c>
-      <c r="D9" t="s">
-        <v>41</v>
       </c>
       <c r="G9">
         <v>2</v>
       </c>
       <c r="H9" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="I9" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="J9" t="s">
-        <v>173</v>
-      </c>
-      <c r="M9" s="23">
+        <v>170</v>
+      </c>
+      <c r="M9" s="16">
         <v>2</v>
       </c>
       <c r="R9" s="8"/>
@@ -5071,7 +5062,7 @@
         <v>31</v>
       </c>
       <c r="C10" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="D10" t="s">
         <v>32</v>
@@ -5080,20 +5071,20 @@
         <v>3</v>
       </c>
       <c r="H10" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="I10" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="J10" t="s">
-        <v>176</v>
-      </c>
-      <c r="M10" s="23">
+        <v>173</v>
+      </c>
+      <c r="M10" s="16">
         <v>3</v>
       </c>
       <c r="R10" s="8"/>
     </row>
-    <row r="11" spans="1:18" ht="58" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:18" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A11">
         <v>4</v>
       </c>
@@ -5101,24 +5092,24 @@
         <v>33</v>
       </c>
       <c r="C11" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="D11" t="s">
         <v>184</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>34</v>
       </c>
       <c r="G11">
         <v>4</v>
       </c>
       <c r="H11" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="I11" t="s">
         <v>21</v>
       </c>
       <c r="J11" t="s">
-        <v>47</v>
-      </c>
-      <c r="M11" s="23">
+        <v>44</v>
+      </c>
+      <c r="M11" s="16">
         <v>4</v>
       </c>
       <c r="N11" s="2"/>
@@ -5131,10 +5122,10 @@
         <v>5</v>
       </c>
       <c r="B12" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="D12" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
     </row>
     <row r="13" spans="1:18" x14ac:dyDescent="0.35">
@@ -5142,10 +5133,13 @@
         <v>6</v>
       </c>
       <c r="B13" t="s">
-        <v>36</v>
+        <v>176</v>
+      </c>
+      <c r="C13" t="s">
+        <v>23</v>
       </c>
       <c r="D13" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
     </row>
     <row r="14" spans="1:18" x14ac:dyDescent="0.35">
@@ -5153,10 +5147,10 @@
         <v>7</v>
       </c>
       <c r="B14" t="s">
-        <v>179</v>
-      </c>
-      <c r="D14" t="s">
-        <v>41</v>
+        <v>19</v>
+      </c>
+      <c r="C14" t="s">
+        <v>186</v>
       </c>
     </row>
     <row r="15" spans="1:18" x14ac:dyDescent="0.35">
@@ -5164,10 +5158,10 @@
         <v>8</v>
       </c>
       <c r="B15" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C15" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="D15" t="s">
         <v>29</v>
@@ -5195,7 +5189,7 @@
         <v>24</v>
       </c>
       <c r="C17" t="s">
-        <v>21</v>
+        <v>185</v>
       </c>
       <c r="D17" t="s">
         <v>26</v>
@@ -5212,7 +5206,7 @@
         <v>27</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.35">
@@ -5234,7 +5228,7 @@
         <v>13</v>
       </c>
       <c r="B20" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C20" t="s">
         <v>22</v>
@@ -5259,11 +5253,6 @@
     </row>
   </sheetData>
   <mergeCells count="15">
-    <mergeCell ref="M1:R1"/>
-    <mergeCell ref="M2:N2"/>
-    <mergeCell ref="M3:N3"/>
-    <mergeCell ref="M4:R5"/>
-    <mergeCell ref="M6:R6"/>
     <mergeCell ref="G1:L1"/>
     <mergeCell ref="G2:H2"/>
     <mergeCell ref="G3:H3"/>
@@ -5274,6 +5263,11 @@
     <mergeCell ref="A2:B2"/>
     <mergeCell ref="A3:B3"/>
     <mergeCell ref="A1:F1"/>
+    <mergeCell ref="M1:R1"/>
+    <mergeCell ref="M2:N2"/>
+    <mergeCell ref="M3:N3"/>
+    <mergeCell ref="M4:R5"/>
+    <mergeCell ref="M6:R6"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Test Cases.xlsx
+++ b/Test Cases.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://endresshauser-my.sharepoint.com/personal/corbin_ferguson_endress_com/Documents/Thesis Work/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://endresshauser-my.sharepoint.com/personal/corbin_ferguson_endress_com/Documents/ThesisBuildTool/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="115" documentId="8_{ACB02C7F-D6E2-4966-A33B-F6A9CC3422F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2F3F3FC7-1932-4DD2-8508-FCA184BB33AC}"/>
+  <xr:revisionPtr revIDLastSave="131" documentId="8_{ACB02C7F-D6E2-4966-A33B-F6A9CC3422F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7377F82A-2F94-43B5-9485-E298E2C17E11}"/>
   <bookViews>
-    <workbookView xWindow="53880" yWindow="-5145" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="25440" windowHeight="15270" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tests" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1753" uniqueCount="316">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1755" uniqueCount="318">
   <si>
     <t>Test ID</t>
   </si>
@@ -988,6 +988,12 @@
   </si>
   <si>
     <t>Skipped</t>
+  </si>
+  <si>
+    <t>Description: Test that the standard creation of multiple elements works.</t>
+  </si>
+  <si>
+    <t>Textinput REGEX works</t>
   </si>
 </sst>
 </file>
@@ -1072,7 +1078,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="33">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -1110,6 +1116,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1140,23 +1149,17 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="10">
+  <dxfs count="6">
     <dxf>
       <fill>
         <patternFill>
@@ -1186,39 +1189,11 @@
       </fill>
     </dxf>
     <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
+      <numFmt numFmtId="30" formatCode="@"/>
     </dxf>
     <dxf>
       <numFmt numFmtId="0" formatCode="General"/>
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="30" formatCode="@"/>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -1449,7 +1424,7 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="4"/>
                 <c:pt idx="0">
-                  <c:v>11</c:v>
+                  <c:v>12</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>32</c:v>
@@ -1594,13 +1569,13 @@
     <sortCondition ref="E1:E72"/>
   </sortState>
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Test ID" totalsRowLabel="Total" dataDxfId="8">
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Test ID" totalsRowLabel="Total" dataDxfId="5">
       <calculatedColumnFormula>ROW()-1</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Test Name">
       <calculatedColumnFormula array="1">Import!#REF!</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Test Status" dataDxfId="9"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Test Status" dataDxfId="4"/>
     <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="Test Priority"/>
     <tableColumn id="2" xr3:uid="{96660FC9-708C-4193-8B48-B2CC427B7A8B}" name="Namespace"/>
   </tableColumns>
@@ -1872,19 +1847,19 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:H72"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9" style="6" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="69" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="16.1796875" style="5" customWidth="1"/>
-    <col min="4" max="4" width="13.453125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="19.90625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="15.81640625" customWidth="1"/>
-    <col min="7" max="7" width="16.1796875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="16.140625" style="5" customWidth="1"/>
+    <col min="4" max="4" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="19.85546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="15.85546875" customWidth="1"/>
+    <col min="7" max="7" width="16.140625" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="18" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
@@ -1905,12 +1880,12 @@
       </c>
       <c r="H1">
         <f>COUNTIF(TestMaster[Test Status], "Not Implemented")</f>
-        <v>11</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A2" s="32">
-        <f>ROW()-1</f>
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A2" s="6">
+        <f t="shared" ref="A2:A33" si="0">ROW()-1</f>
         <v>1</v>
       </c>
       <c r="B2" t="str">
@@ -1931,9 +1906,9 @@
         <v>32</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A3" s="32">
-        <f>ROW()-1</f>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3" s="6">
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
       <c r="B3" t="str">
@@ -1954,9 +1929,9 @@
         <v>15</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A4" s="32">
-        <f>ROW()-1</f>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4" s="6">
+        <f t="shared" si="0"/>
         <v>3</v>
       </c>
       <c r="B4" t="str">
@@ -1977,9 +1952,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A5" s="32">
-        <f>ROW()-1</f>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A5" s="6">
+        <f t="shared" si="0"/>
         <v>4</v>
       </c>
       <c r="B5" t="str">
@@ -1993,9 +1968,9 @@
         <v>304</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A6" s="32">
-        <f>ROW()-1</f>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A6" s="6">
+        <f t="shared" si="0"/>
         <v>5</v>
       </c>
       <c r="B6" t="str">
@@ -2009,9 +1984,9 @@
         <v>304</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A7" s="32">
-        <f>ROW()-1</f>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A7" s="6">
+        <f t="shared" si="0"/>
         <v>6</v>
       </c>
       <c r="B7" t="str">
@@ -2025,9 +2000,9 @@
         <v>304</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A8" s="32">
-        <f>ROW()-1</f>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A8" s="6">
+        <f t="shared" si="0"/>
         <v>7</v>
       </c>
       <c r="B8" t="str">
@@ -2041,9 +2016,9 @@
         <v>304</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A9" s="32">
-        <f>ROW()-1</f>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A9" s="6">
+        <f t="shared" si="0"/>
         <v>8</v>
       </c>
       <c r="B9" t="str">
@@ -2057,9 +2032,9 @@
         <v>304</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A10" s="32">
-        <f>ROW()-1</f>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A10" s="6">
+        <f t="shared" si="0"/>
         <v>9</v>
       </c>
       <c r="B10" t="str">
@@ -2076,9 +2051,9 @@
         <v>304</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A11" s="32">
-        <f>ROW()-1</f>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A11" s="6">
+        <f t="shared" si="0"/>
         <v>10</v>
       </c>
       <c r="B11" t="str">
@@ -2092,9 +2067,9 @@
         <v>304</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A12" s="32">
-        <f>ROW()-1</f>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A12" s="6">
+        <f t="shared" si="0"/>
         <v>11</v>
       </c>
       <c r="B12" t="str">
@@ -2108,9 +2083,9 @@
         <v>304</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A13" s="32">
-        <f>ROW()-1</f>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A13" s="6">
+        <f t="shared" si="0"/>
         <v>12</v>
       </c>
       <c r="B13" t="str">
@@ -2124,9 +2099,9 @@
         <v>304</v>
       </c>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A14" s="32">
-        <f>ROW()-1</f>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A14" s="6">
+        <f t="shared" si="0"/>
         <v>13</v>
       </c>
       <c r="B14" t="str">
@@ -2140,9 +2115,9 @@
         <v>304</v>
       </c>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A15" s="32">
-        <f>ROW()-1</f>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A15" s="6">
+        <f t="shared" si="0"/>
         <v>14</v>
       </c>
       <c r="B15" t="str">
@@ -2156,9 +2131,9 @@
         <v>304</v>
       </c>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A16" s="32">
-        <f>ROW()-1</f>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A16" s="6">
+        <f t="shared" si="0"/>
         <v>15</v>
       </c>
       <c r="B16" t="str">
@@ -2171,11 +2146,11 @@
       <c r="E16" t="s">
         <v>304</v>
       </c>
-      <c r="G16" s="31"/>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A17" s="32">
-        <f>ROW()-1</f>
+      <c r="G16" s="17"/>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A17" s="6">
+        <f t="shared" si="0"/>
         <v>16</v>
       </c>
       <c r="B17" t="str">
@@ -2189,9 +2164,9 @@
         <v>304</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A18" s="32">
-        <f>ROW()-1</f>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A18" s="6">
+        <f t="shared" si="0"/>
         <v>17</v>
       </c>
       <c r="B18" t="str">
@@ -2205,9 +2180,9 @@
         <v>304</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A19" s="32">
-        <f>ROW()-1</f>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A19" s="6">
+        <f t="shared" si="0"/>
         <v>18</v>
       </c>
       <c r="B19" t="str">
@@ -2221,9 +2196,9 @@
         <v>304</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A20" s="32">
-        <f>ROW()-1</f>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A20" s="6">
+        <f t="shared" si="0"/>
         <v>19</v>
       </c>
       <c r="B20" t="str">
@@ -2237,9 +2212,9 @@
         <v>304</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A21" s="32">
-        <f>ROW()-1</f>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A21" s="6">
+        <f t="shared" si="0"/>
         <v>20</v>
       </c>
       <c r="B21" t="str">
@@ -2253,9 +2228,9 @@
         <v>304</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A22" s="32">
-        <f>ROW()-1</f>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A22" s="6">
+        <f t="shared" si="0"/>
         <v>21</v>
       </c>
       <c r="B22" t="str">
@@ -2272,9 +2247,9 @@
         <v>304</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A23" s="32">
-        <f>ROW()-1</f>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A23" s="6">
+        <f t="shared" si="0"/>
         <v>22</v>
       </c>
       <c r="B23" t="str">
@@ -2291,9 +2266,9 @@
         <v>304</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A24" s="32">
-        <f>ROW()-1</f>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A24" s="6">
+        <f t="shared" si="0"/>
         <v>23</v>
       </c>
       <c r="B24" t="str">
@@ -2310,9 +2285,9 @@
         <v>304</v>
       </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" s="6">
-        <f>ROW()-1</f>
+        <f t="shared" si="0"/>
         <v>24</v>
       </c>
       <c r="B25" t="str">
@@ -2329,9 +2304,9 @@
         <v>305</v>
       </c>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" s="6">
-        <f>ROW()-1</f>
+        <f t="shared" si="0"/>
         <v>25</v>
       </c>
       <c r="B26" t="str">
@@ -2348,9 +2323,9 @@
         <v>305</v>
       </c>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" s="6">
-        <f>ROW()-1</f>
+        <f t="shared" si="0"/>
         <v>26</v>
       </c>
       <c r="B27" t="str">
@@ -2367,9 +2342,9 @@
         <v>305</v>
       </c>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" s="6">
-        <f>ROW()-1</f>
+        <f t="shared" si="0"/>
         <v>27</v>
       </c>
       <c r="B28" t="str">
@@ -2386,9 +2361,9 @@
         <v>306</v>
       </c>
     </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" s="6">
-        <f>ROW()-1</f>
+        <f t="shared" si="0"/>
         <v>28</v>
       </c>
       <c r="B29" t="str">
@@ -2405,9 +2380,9 @@
         <v>306</v>
       </c>
     </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" s="6">
-        <f>ROW()-1</f>
+        <f t="shared" si="0"/>
         <v>29</v>
       </c>
       <c r="B30" t="str">
@@ -2424,9 +2399,9 @@
         <v>306</v>
       </c>
     </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" s="6">
-        <f>ROW()-1</f>
+        <f t="shared" si="0"/>
         <v>30</v>
       </c>
       <c r="B31" t="str">
@@ -2443,9 +2418,9 @@
         <v>307</v>
       </c>
     </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" s="6">
-        <f>ROW()-1</f>
+        <f t="shared" si="0"/>
         <v>31</v>
       </c>
       <c r="B32" t="str">
@@ -2462,9 +2437,9 @@
         <v>307</v>
       </c>
     </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" s="6">
-        <f>ROW()-1</f>
+        <f t="shared" si="0"/>
         <v>32</v>
       </c>
       <c r="B33" t="str">
@@ -2481,9 +2456,9 @@
         <v>307</v>
       </c>
     </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34" s="6">
-        <f>ROW()-1</f>
+        <f t="shared" ref="A34:A65" si="1">ROW()-1</f>
         <v>33</v>
       </c>
       <c r="B34" t="str">
@@ -2500,9 +2475,9 @@
         <v>308</v>
       </c>
     </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A35" s="6">
-        <f>ROW()-1</f>
+        <f t="shared" si="1"/>
         <v>34</v>
       </c>
       <c r="B35" t="str">
@@ -2519,9 +2494,9 @@
         <v>309</v>
       </c>
     </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A36" s="6">
-        <f>ROW()-1</f>
+        <f t="shared" si="1"/>
         <v>35</v>
       </c>
       <c r="B36" t="str">
@@ -2538,9 +2513,9 @@
         <v>309</v>
       </c>
     </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A37" s="6">
-        <f>ROW()-1</f>
+        <f t="shared" si="1"/>
         <v>36</v>
       </c>
       <c r="B37" t="str">
@@ -2557,9 +2532,9 @@
         <v>309</v>
       </c>
     </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A38" s="32">
-        <f>ROW()-1</f>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A38" s="6">
+        <f t="shared" si="1"/>
         <v>37</v>
       </c>
       <c r="B38" t="str">
@@ -2573,9 +2548,9 @@
         <v>303</v>
       </c>
     </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A39" s="32">
-        <f>ROW()-1</f>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A39" s="6">
+        <f t="shared" si="1"/>
         <v>38</v>
       </c>
       <c r="B39" t="str">
@@ -2589,9 +2564,9 @@
         <v>303</v>
       </c>
     </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A40" s="32">
-        <f>ROW()-1</f>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A40" s="6">
+        <f t="shared" si="1"/>
         <v>39</v>
       </c>
       <c r="B40" t="str">
@@ -2605,9 +2580,9 @@
         <v>303</v>
       </c>
     </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A41" s="32">
-        <f>ROW()-1</f>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A41" s="6">
+        <f t="shared" si="1"/>
         <v>40</v>
       </c>
       <c r="B41" t="str">
@@ -2621,9 +2596,9 @@
         <v>303</v>
       </c>
     </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A42" s="32">
-        <f>ROW()-1</f>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A42" s="6">
+        <f t="shared" si="1"/>
         <v>41</v>
       </c>
       <c r="B42" t="str">
@@ -2637,9 +2612,9 @@
         <v>303</v>
       </c>
     </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A43" s="32">
-        <f>ROW()-1</f>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A43" s="6">
+        <f t="shared" si="1"/>
         <v>42</v>
       </c>
       <c r="B43" t="str">
@@ -2653,9 +2628,9 @@
         <v>303</v>
       </c>
     </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A44" s="32">
-        <f>ROW()-1</f>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A44" s="6">
+        <f t="shared" si="1"/>
         <v>43</v>
       </c>
       <c r="B44" t="str">
@@ -2669,9 +2644,9 @@
         <v>303</v>
       </c>
     </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A45" s="32">
-        <f>ROW()-1</f>
+    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A45" s="6">
+        <f t="shared" si="1"/>
         <v>44</v>
       </c>
       <c r="B45" t="str">
@@ -2685,9 +2660,9 @@
         <v>303</v>
       </c>
     </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A46" s="32">
-        <f>ROW()-1</f>
+    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A46" s="6">
+        <f t="shared" si="1"/>
         <v>45</v>
       </c>
       <c r="B46" t="str">
@@ -2701,9 +2676,9 @@
         <v>303</v>
       </c>
     </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A47" s="32">
-        <f>ROW()-1</f>
+    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A47" s="6">
+        <f t="shared" si="1"/>
         <v>46</v>
       </c>
       <c r="B47" t="str">
@@ -2717,9 +2692,9 @@
         <v>303</v>
       </c>
     </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A48" s="32">
-        <f>ROW()-1</f>
+    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A48" s="6">
+        <f t="shared" si="1"/>
         <v>47</v>
       </c>
       <c r="B48" t="str">
@@ -2733,9 +2708,9 @@
         <v>303</v>
       </c>
     </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A49" s="32">
-        <f>ROW()-1</f>
+    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A49" s="6">
+        <f t="shared" si="1"/>
         <v>48</v>
       </c>
       <c r="B49" t="str">
@@ -2749,9 +2724,9 @@
         <v>303</v>
       </c>
     </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A50" s="32">
-        <f>ROW()-1</f>
+    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A50" s="6">
+        <f t="shared" si="1"/>
         <v>49</v>
       </c>
       <c r="B50" t="str">
@@ -2765,9 +2740,9 @@
         <v>303</v>
       </c>
     </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A51" s="32">
-        <f>ROW()-1</f>
+    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A51" s="6">
+        <f t="shared" si="1"/>
         <v>50</v>
       </c>
       <c r="B51" t="str">
@@ -2781,9 +2756,9 @@
         <v>303</v>
       </c>
     </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A52" s="32">
-        <f>ROW()-1</f>
+    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A52" s="6">
+        <f t="shared" si="1"/>
         <v>51</v>
       </c>
       <c r="B52" t="str">
@@ -2797,9 +2772,9 @@
         <v>303</v>
       </c>
     </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A53" s="32">
-        <f>ROW()-1</f>
+    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A53" s="6">
+        <f t="shared" si="1"/>
         <v>52</v>
       </c>
       <c r="B53" t="str">
@@ -2813,9 +2788,9 @@
         <v>303</v>
       </c>
     </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A54" s="32">
-        <f>ROW()-1</f>
+    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A54" s="6">
+        <f t="shared" si="1"/>
         <v>53</v>
       </c>
       <c r="B54" t="str">
@@ -2829,9 +2804,9 @@
         <v>303</v>
       </c>
     </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A55" s="32">
-        <f>ROW()-1</f>
+    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A55" s="6">
+        <f t="shared" si="1"/>
         <v>54</v>
       </c>
       <c r="B55" t="str">
@@ -2845,9 +2820,9 @@
         <v>303</v>
       </c>
     </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A56" s="32">
-        <f>ROW()-1</f>
+    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A56" s="6">
+        <f t="shared" si="1"/>
         <v>55</v>
       </c>
       <c r="B56" t="str">
@@ -2861,9 +2836,9 @@
         <v>303</v>
       </c>
     </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A57" s="32">
-        <f>ROW()-1</f>
+    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A57" s="6">
+        <f t="shared" si="1"/>
         <v>56</v>
       </c>
       <c r="B57" t="str">
@@ -2877,9 +2852,9 @@
         <v>303</v>
       </c>
     </row>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A58" s="32">
-        <f>ROW()-1</f>
+    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A58" s="6">
+        <f t="shared" si="1"/>
         <v>57</v>
       </c>
       <c r="B58" t="str">
@@ -2893,9 +2868,9 @@
         <v>303</v>
       </c>
     </row>
-    <row r="59" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A59" s="32">
-        <f>ROW()-1</f>
+    <row r="59" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A59" s="6">
+        <f t="shared" si="1"/>
         <v>58</v>
       </c>
       <c r="B59" t="str">
@@ -2909,9 +2884,9 @@
         <v>303</v>
       </c>
     </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A60" s="32">
-        <f>ROW()-1</f>
+    <row r="60" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A60" s="6">
+        <f t="shared" si="1"/>
         <v>59</v>
       </c>
       <c r="B60" t="str">
@@ -2925,90 +2900,96 @@
         <v>303</v>
       </c>
     </row>
-    <row r="61" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A61" s="32">
-        <f>ROW()-1</f>
+    <row r="61" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A61" s="6">
+        <f t="shared" si="1"/>
         <v>60</v>
       </c>
-    </row>
-    <row r="62" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A62" s="32">
-        <f>ROW()-1</f>
+      <c r="B61" t="s">
+        <v>317</v>
+      </c>
+      <c r="C61" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A62" s="6">
+        <f t="shared" si="1"/>
         <v>61</v>
       </c>
     </row>
-    <row r="63" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A63" s="32">
-        <f>ROW()-1</f>
+    <row r="63" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A63" s="6">
+        <f t="shared" si="1"/>
         <v>62</v>
       </c>
     </row>
-    <row r="64" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A64" s="32">
-        <f>ROW()-1</f>
+    <row r="64" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A64" s="6">
+        <f t="shared" si="1"/>
         <v>63</v>
       </c>
     </row>
-    <row r="65" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A65" s="32">
-        <f>ROW()-1</f>
+    <row r="65" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A65" s="6">
+        <f t="shared" si="1"/>
         <v>64</v>
       </c>
     </row>
-    <row r="66" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A66" s="32">
-        <f>ROW()-1</f>
+    <row r="66" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A66" s="6">
+        <f t="shared" ref="A66:A72" si="2">ROW()-1</f>
         <v>65</v>
       </c>
     </row>
-    <row r="67" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A67" s="32">
-        <f>ROW()-1</f>
+    <row r="67" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A67" s="6">
+        <f t="shared" si="2"/>
         <v>66</v>
       </c>
     </row>
-    <row r="68" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A68" s="32">
-        <f>ROW()-1</f>
+    <row r="68" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A68" s="6">
+        <f t="shared" si="2"/>
         <v>67</v>
       </c>
     </row>
-    <row r="69" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A69" s="32">
-        <f>ROW()-1</f>
+    <row r="69" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A69" s="6">
+        <f t="shared" si="2"/>
         <v>68</v>
       </c>
     </row>
-    <row r="70" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A70" s="32">
-        <f>ROW()-1</f>
+    <row r="70" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A70" s="6">
+        <f t="shared" si="2"/>
         <v>69</v>
       </c>
     </row>
-    <row r="71" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A71" s="32">
-        <f>ROW()-1</f>
+    <row r="71" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A71" s="6">
+        <f t="shared" si="2"/>
         <v>70</v>
       </c>
     </row>
-    <row r="72" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A72" s="32">
-        <f>ROW()-1</f>
+    <row r="72" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A72" s="6">
+        <f t="shared" si="2"/>
         <v>71</v>
       </c>
     </row>
   </sheetData>
   <conditionalFormatting sqref="C1:C1048576">
-    <cfRule type="containsText" dxfId="4" priority="1" operator="containsText" text="Skipped">
+    <cfRule type="containsText" dxfId="3" priority="1" operator="containsText" text="Skipped">
       <formula>NOT(ISERROR(SEARCH("Skipped",C1)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="7" priority="2" operator="containsText" text="Fail">
+    <cfRule type="containsText" dxfId="2" priority="2" operator="containsText" text="Fail">
       <formula>NOT(ISERROR(SEARCH("Fail",C1)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="6" priority="3" operator="containsText" text="Pass">
+    <cfRule type="containsText" dxfId="1" priority="3" operator="containsText" text="Pass">
       <formula>NOT(ISERROR(SEARCH("Pass",C1)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="5" priority="4" operator="containsText" text="Not Implemented">
+    <cfRule type="containsText" dxfId="0" priority="4" operator="containsText" text="Not Implemented">
       <formula>NOT(ISERROR(SEARCH("Not Implemented",C1)))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -3043,31 +3024,31 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:F25"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="6.453125" customWidth="1"/>
-    <col min="2" max="2" width="22.81640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="48.81640625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="56.7265625" style="2" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="18.453125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="16.1796875" style="7" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="6.42578125" customWidth="1"/>
+    <col min="2" max="2" width="22.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="48.85546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="56.7109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="18.42578125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="16.140625" style="7" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A1" s="19" t="s">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1" s="20" t="s">
         <v>9</v>
       </c>
-      <c r="B1" s="18"/>
-      <c r="C1" s="18"/>
-      <c r="D1" s="20"/>
-      <c r="E1" s="18"/>
-      <c r="F1" s="21"/>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A2" s="17" t="s">
+      <c r="B1" s="19"/>
+      <c r="C1" s="19"/>
+      <c r="D1" s="21"/>
+      <c r="E1" s="19"/>
+      <c r="F1" s="22"/>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2" s="18" t="s">
         <v>10</v>
       </c>
-      <c r="B2" s="18"/>
+      <c r="B2" s="19"/>
       <c r="C2" s="6">
         <f>IFERROR(_xlfn.XLOOKUP(A1, TestMaster[Test Name], TestMaster[Test ID], "ID not found"), "")</f>
         <v>33</v>
@@ -3076,11 +3057,11 @@
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="1:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="17" t="s">
+    <row r="3" spans="1:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="18" t="s">
         <v>12</v>
       </c>
-      <c r="B3" s="18"/>
+      <c r="B3" s="19"/>
       <c r="C3" s="8" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(A1, TestMaster[Test Name], TestMaster[Test Priority], "Priority not found"), "")</f>
         <v>Medium</v>
@@ -3093,35 +3074,35 @@
         <v>Not Implemented</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A4" s="19" t="s">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" s="20" t="s">
         <v>14</v>
       </c>
-      <c r="B4" s="18"/>
-      <c r="C4" s="18"/>
-      <c r="D4" s="20"/>
-      <c r="E4" s="18"/>
-      <c r="F4" s="21"/>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A5" s="18"/>
-      <c r="B5" s="18"/>
-      <c r="C5" s="18"/>
-      <c r="D5" s="20"/>
-      <c r="E5" s="18"/>
-      <c r="F5" s="21"/>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A6" s="19" t="s">
+      <c r="B4" s="19"/>
+      <c r="C4" s="19"/>
+      <c r="D4" s="21"/>
+      <c r="E4" s="19"/>
+      <c r="F4" s="22"/>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" s="19"/>
+      <c r="B5" s="19"/>
+      <c r="C5" s="19"/>
+      <c r="D5" s="21"/>
+      <c r="E5" s="19"/>
+      <c r="F5" s="22"/>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" s="20" t="s">
         <v>15</v>
       </c>
-      <c r="B6" s="18"/>
-      <c r="C6" s="18"/>
-      <c r="D6" s="20"/>
-      <c r="E6" s="18"/>
-      <c r="F6" s="21"/>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B6" s="19"/>
+      <c r="C6" s="19"/>
+      <c r="D6" s="21"/>
+      <c r="E6" s="19"/>
+      <c r="F6" s="22"/>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>16</v>
       </c>
@@ -3141,7 +3122,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>1</v>
       </c>
@@ -3155,7 +3136,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="9" spans="1:6" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:6" ht="29.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="4">
         <f t="shared" ref="A9:A25" si="0">A8+1</f>
         <v>2</v>
@@ -3170,7 +3151,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A10" s="4">
         <f t="shared" si="0"/>
         <v>3</v>
@@ -3185,7 +3166,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A11" s="4">
         <f t="shared" si="0"/>
         <v>4</v>
@@ -3200,7 +3181,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="4">
         <f t="shared" si="0"/>
         <v>5</v>
@@ -3215,7 +3196,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A13" s="4">
         <f t="shared" si="0"/>
         <v>6</v>
@@ -3230,7 +3211,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A14" s="4">
         <f t="shared" si="0"/>
         <v>7</v>
@@ -3245,7 +3226,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="15" spans="1:6" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:6" ht="29.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="4">
         <f t="shared" si="0"/>
         <v>8</v>
@@ -3260,7 +3241,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="4">
         <f t="shared" si="0"/>
         <v>9</v>
@@ -3275,7 +3256,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A17" s="4">
         <f t="shared" si="0"/>
         <v>10</v>
@@ -3290,7 +3271,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A18" s="4">
         <f t="shared" si="0"/>
         <v>11</v>
@@ -3305,7 +3286,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" s="4">
         <f t="shared" si="0"/>
         <v>12</v>
@@ -3320,7 +3301,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" s="4">
         <f t="shared" si="0"/>
         <v>13</v>
@@ -3335,7 +3316,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21" s="4">
         <f t="shared" si="0"/>
         <v>14</v>
@@ -3350,7 +3331,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A22" s="4">
         <f t="shared" si="0"/>
         <v>15</v>
@@ -3365,7 +3346,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A23" s="4">
         <f t="shared" si="0"/>
         <v>16</v>
@@ -3380,7 +3361,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A24" s="4">
         <f t="shared" si="0"/>
         <v>17</v>
@@ -3395,7 +3376,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A25" s="4">
         <f t="shared" si="0"/>
         <v>18</v>
@@ -3424,62 +3405,73 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:R21"/>
-  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:Y21"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5" style="4" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="34.453125" style="4" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="24.81640625" style="4" customWidth="1"/>
-    <col min="4" max="4" width="35.54296875" style="4" customWidth="1"/>
-    <col min="5" max="5" width="18.453125" style="4" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="16.1796875" style="11" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="34.42578125" style="4" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="24.85546875" style="4" customWidth="1"/>
+    <col min="4" max="4" width="35.5703125" style="4" customWidth="1"/>
+    <col min="5" max="5" width="18.42578125" style="4" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="16.140625" style="11" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="5" style="4" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="29.1796875" style="4" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="24.1796875" style="4" customWidth="1"/>
+    <col min="8" max="8" width="29.140625" style="4" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="24.140625" style="4" customWidth="1"/>
     <col min="10" max="10" width="24" style="4" customWidth="1"/>
-    <col min="11" max="11" width="18.453125" style="4" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="16.1796875" style="11" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="18.42578125" style="4" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="16.140625" style="11" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="5" style="4" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="29.1796875" style="4" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="25.54296875" style="4" customWidth="1"/>
-    <col min="16" max="16" width="23.81640625" style="4" customWidth="1"/>
-    <col min="17" max="17" width="18.453125" style="4" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="16.1796875" style="4" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="8.7265625" style="4" customWidth="1"/>
-    <col min="21" max="16384" width="8.7265625" style="4"/>
+    <col min="14" max="14" width="29.140625" style="4" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="25.5703125" style="4" customWidth="1"/>
+    <col min="16" max="16" width="23.85546875" style="4" customWidth="1"/>
+    <col min="17" max="17" width="18.42578125" style="4" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="16.140625" style="4" bestFit="1" customWidth="1"/>
+    <col min="19" max="20" width="8.7109375" style="4" customWidth="1"/>
+    <col min="21" max="21" width="9.140625" style="4" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="10" style="4" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="15.28515625" style="4" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="19.28515625" style="4" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="17" style="4" bestFit="1" customWidth="1"/>
+    <col min="26" max="16384" width="8.7109375" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A1" s="19" t="s">
+    <row r="1" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A1" s="20" t="s">
         <v>54</v>
       </c>
-      <c r="B1" s="22"/>
-      <c r="C1" s="22"/>
-      <c r="D1" s="22"/>
-      <c r="E1" s="22"/>
-      <c r="F1" s="21"/>
-      <c r="G1" s="19" t="s">
+      <c r="B1" s="23"/>
+      <c r="C1" s="23"/>
+      <c r="D1" s="23"/>
+      <c r="E1" s="23"/>
+      <c r="F1" s="22"/>
+      <c r="G1" s="20" t="s">
         <v>55</v>
       </c>
-      <c r="H1" s="22"/>
-      <c r="I1" s="22"/>
-      <c r="J1" s="22"/>
-      <c r="K1" s="22"/>
-      <c r="L1" s="21"/>
-      <c r="M1" s="17" t="s">
+      <c r="H1" s="23"/>
+      <c r="I1" s="23"/>
+      <c r="J1" s="23"/>
+      <c r="K1" s="23"/>
+      <c r="L1" s="22"/>
+      <c r="M1" s="18" t="s">
         <v>56</v>
       </c>
-      <c r="N1" s="22"/>
-      <c r="O1" s="22"/>
-      <c r="P1" s="22"/>
-      <c r="Q1" s="22"/>
-      <c r="R1" s="22"/>
-    </row>
-    <row r="2" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A2" s="17" t="s">
+      <c r="N1" s="23"/>
+      <c r="O1" s="23"/>
+      <c r="P1" s="23"/>
+      <c r="Q1" s="23"/>
+      <c r="R1" s="23"/>
+      <c r="T1" s="18"/>
+      <c r="U1" s="23"/>
+      <c r="V1" s="23"/>
+      <c r="W1" s="23"/>
+      <c r="X1" s="23"/>
+      <c r="Y1" s="23"/>
+    </row>
+    <row r="2" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A2" s="18" t="s">
         <v>10</v>
       </c>
-      <c r="B2" s="22"/>
+      <c r="B2" s="23"/>
       <c r="C2">
         <f>IFERROR(_xlfn.XLOOKUP(A1, TestMaster[Test Name], TestMaster[Test ID], "ID not found"), "")</f>
         <v>24</v>
@@ -3488,10 +3480,10 @@
         <v>11</v>
       </c>
       <c r="F2" s="7"/>
-      <c r="G2" s="17" t="s">
+      <c r="G2" s="18" t="s">
         <v>10</v>
       </c>
-      <c r="H2" s="22"/>
+      <c r="H2" s="23"/>
       <c r="I2">
         <f>IFERROR(_xlfn.XLOOKUP(G1, TestMaster[Test Name], TestMaster[Test ID], "ID not found"), "")</f>
         <v>25</v>
@@ -3500,10 +3492,10 @@
         <v>11</v>
       </c>
       <c r="L2" s="7"/>
-      <c r="M2" s="17" t="s">
+      <c r="M2" s="18" t="s">
         <v>10</v>
       </c>
-      <c r="N2" s="22"/>
+      <c r="N2" s="23"/>
       <c r="O2">
         <f>IFERROR(_xlfn.XLOOKUP(M1, TestMaster[Test Name], TestMaster[Test ID], "ID not found"), "")</f>
         <v>26</v>
@@ -3511,12 +3503,16 @@
       <c r="Q2" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="3" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A3" s="17" t="s">
+      <c r="T2" s="18"/>
+      <c r="U2" s="23"/>
+      <c r="V2"/>
+      <c r="X2"/>
+    </row>
+    <row r="3" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A3" s="18" t="s">
         <v>12</v>
       </c>
-      <c r="B3" s="22"/>
+      <c r="B3" s="23"/>
       <c r="C3" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(A1, TestMaster[Test Name], TestMaster[Test Priority], "Priority not found"), "")</f>
         <v>High</v>
@@ -3528,10 +3524,10 @@
         <f>IFERROR(_xlfn.XLOOKUP(A1, TestMaster[Test Name], TestMaster[Test Status], "Status not found"), "")</f>
         <v>Not Implemented</v>
       </c>
-      <c r="G3" s="17" t="s">
+      <c r="G3" s="18" t="s">
         <v>12</v>
       </c>
-      <c r="H3" s="22"/>
+      <c r="H3" s="23"/>
       <c r="I3" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(G1, TestMaster[Test Name], TestMaster[Test Priority], "Priority not found"), "")</f>
         <v>Medium</v>
@@ -3543,10 +3539,10 @@
         <f>IFERROR(_xlfn.XLOOKUP(G1, TestMaster[Test Name], TestMaster[Test Status], "Status not found"), "")</f>
         <v>Not Implemented</v>
       </c>
-      <c r="M3" s="17" t="s">
+      <c r="M3" s="18" t="s">
         <v>12</v>
       </c>
-      <c r="N3" s="22"/>
+      <c r="N3" s="23"/>
       <c r="O3" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(M1, TestMaster[Test Name], TestMaster[Test Priority], "Priority not found"), "")</f>
         <v>Low</v>
@@ -3558,80 +3554,103 @@
         <f>IFERROR(_xlfn.XLOOKUP(M1, TestMaster[Test Name], TestMaster[Test Status], "Status not found"), "")</f>
         <v>Not Implemented</v>
       </c>
-    </row>
-    <row r="4" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A4" s="19" t="s">
+      <c r="T3" s="18"/>
+      <c r="U3" s="23"/>
+      <c r="V3"/>
+      <c r="X3"/>
+      <c r="Y3"/>
+    </row>
+    <row r="4" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A4" s="20" t="s">
+        <v>316</v>
+      </c>
+      <c r="B4" s="23"/>
+      <c r="C4" s="23"/>
+      <c r="D4" s="23"/>
+      <c r="E4" s="23"/>
+      <c r="F4" s="22"/>
+      <c r="G4" s="20" t="s">
         <v>57</v>
       </c>
-      <c r="B4" s="22"/>
-      <c r="C4" s="22"/>
-      <c r="D4" s="22"/>
-      <c r="E4" s="22"/>
-      <c r="F4" s="21"/>
-      <c r="G4" s="19" t="s">
+      <c r="H4" s="23"/>
+      <c r="I4" s="23"/>
+      <c r="J4" s="23"/>
+      <c r="K4" s="23"/>
+      <c r="L4" s="22"/>
+      <c r="M4" s="18" t="s">
         <v>57</v>
       </c>
-      <c r="H4" s="22"/>
-      <c r="I4" s="22"/>
-      <c r="J4" s="22"/>
-      <c r="K4" s="22"/>
-      <c r="L4" s="21"/>
-      <c r="M4" s="17" t="s">
-        <v>57</v>
-      </c>
-      <c r="N4" s="22"/>
-      <c r="O4" s="22"/>
-      <c r="P4" s="22"/>
-      <c r="Q4" s="22"/>
-      <c r="R4" s="22"/>
-    </row>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A5" s="22"/>
-      <c r="B5" s="22"/>
-      <c r="C5" s="22"/>
-      <c r="D5" s="22"/>
-      <c r="E5" s="22"/>
-      <c r="F5" s="21"/>
-      <c r="G5" s="22"/>
-      <c r="H5" s="22"/>
-      <c r="I5" s="22"/>
-      <c r="J5" s="22"/>
-      <c r="K5" s="22"/>
-      <c r="L5" s="21"/>
-      <c r="M5" s="22"/>
-      <c r="N5" s="22"/>
-      <c r="O5" s="22"/>
-      <c r="P5" s="22"/>
-      <c r="Q5" s="22"/>
-      <c r="R5" s="22"/>
-    </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A6" s="19" t="s">
+      <c r="N4" s="23"/>
+      <c r="O4" s="23"/>
+      <c r="P4" s="23"/>
+      <c r="Q4" s="23"/>
+      <c r="R4" s="23"/>
+      <c r="T4" s="18"/>
+      <c r="U4" s="23"/>
+      <c r="V4" s="23"/>
+      <c r="W4" s="23"/>
+      <c r="X4" s="23"/>
+      <c r="Y4" s="23"/>
+    </row>
+    <row r="5" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A5" s="23"/>
+      <c r="B5" s="23"/>
+      <c r="C5" s="23"/>
+      <c r="D5" s="23"/>
+      <c r="E5" s="23"/>
+      <c r="F5" s="22"/>
+      <c r="G5" s="23"/>
+      <c r="H5" s="23"/>
+      <c r="I5" s="23"/>
+      <c r="J5" s="23"/>
+      <c r="K5" s="23"/>
+      <c r="L5" s="22"/>
+      <c r="M5" s="23"/>
+      <c r="N5" s="23"/>
+      <c r="O5" s="23"/>
+      <c r="P5" s="23"/>
+      <c r="Q5" s="23"/>
+      <c r="R5" s="23"/>
+      <c r="T5" s="23"/>
+      <c r="U5" s="23"/>
+      <c r="V5" s="23"/>
+      <c r="W5" s="23"/>
+      <c r="X5" s="23"/>
+      <c r="Y5" s="23"/>
+    </row>
+    <row r="6" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A6" s="20" t="s">
         <v>15</v>
       </c>
-      <c r="B6" s="22"/>
-      <c r="C6" s="22"/>
-      <c r="D6" s="22"/>
-      <c r="E6" s="22"/>
-      <c r="F6" s="21"/>
-      <c r="G6" s="19" t="s">
+      <c r="B6" s="23"/>
+      <c r="C6" s="23"/>
+      <c r="D6" s="23"/>
+      <c r="E6" s="23"/>
+      <c r="F6" s="22"/>
+      <c r="G6" s="20" t="s">
         <v>15</v>
       </c>
-      <c r="H6" s="22"/>
-      <c r="I6" s="22"/>
-      <c r="J6" s="22"/>
-      <c r="K6" s="22"/>
-      <c r="L6" s="21"/>
-      <c r="M6" s="17" t="s">
+      <c r="H6" s="23"/>
+      <c r="I6" s="23"/>
+      <c r="J6" s="23"/>
+      <c r="K6" s="23"/>
+      <c r="L6" s="22"/>
+      <c r="M6" s="18" t="s">
         <v>15</v>
       </c>
-      <c r="N6" s="22"/>
-      <c r="O6" s="22"/>
-      <c r="P6" s="22"/>
-      <c r="Q6" s="22"/>
-      <c r="R6" s="22"/>
-    </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="N6" s="23"/>
+      <c r="O6" s="23"/>
+      <c r="P6" s="23"/>
+      <c r="Q6" s="23"/>
+      <c r="R6" s="23"/>
+      <c r="T6" s="18"/>
+      <c r="U6" s="23"/>
+      <c r="V6" s="23"/>
+      <c r="W6" s="23"/>
+      <c r="X6" s="23"/>
+      <c r="Y6" s="23"/>
+    </row>
+    <row r="7" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>16</v>
       </c>
@@ -3686,8 +3705,14 @@
       <c r="R7" s="1" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="T7" s="1"/>
+      <c r="U7" s="1"/>
+      <c r="V7" s="1"/>
+      <c r="W7" s="1"/>
+      <c r="X7" s="1"/>
+      <c r="Y7" s="1"/>
+    </row>
+    <row r="8" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A8" s="4">
         <v>1</v>
       </c>
@@ -3725,7 +3750,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="9" spans="1:18" ht="43.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:25" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="4">
         <v>2</v>
       </c>
@@ -3763,7 +3788,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="10" spans="1:18" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:25" ht="29.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="4">
         <v>3</v>
       </c>
@@ -3801,7 +3826,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="11" spans="1:18" ht="43.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:25" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="4">
         <v>4</v>
       </c>
@@ -3839,7 +3864,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="12" spans="1:18" ht="43.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:25" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="4">
         <v>5</v>
       </c>
@@ -3865,7 +3890,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="13" spans="1:18" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:25" ht="29.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="4">
         <v>6</v>
       </c>
@@ -3891,7 +3916,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:25" x14ac:dyDescent="0.25">
       <c r="M14">
         <v>7</v>
       </c>
@@ -3905,7 +3930,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="15" spans="1:18" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:25" ht="29.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="M15" s="4">
         <v>8</v>
       </c>
@@ -3919,7 +3944,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:25" x14ac:dyDescent="0.25">
       <c r="M16">
         <v>9</v>
       </c>
@@ -3933,7 +3958,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="17" spans="13:16" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="13:16" ht="29.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="M17">
         <v>10</v>
       </c>
@@ -3947,7 +3972,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="18" spans="13:16" x14ac:dyDescent="0.35">
+    <row r="18" spans="13:16" x14ac:dyDescent="0.25">
       <c r="M18" s="4">
         <v>11</v>
       </c>
@@ -3961,7 +3986,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="19" spans="13:16" x14ac:dyDescent="0.35">
+    <row r="19" spans="13:16" x14ac:dyDescent="0.25">
       <c r="M19">
         <v>12</v>
       </c>
@@ -3975,7 +4000,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="20" spans="13:16" x14ac:dyDescent="0.35">
+    <row r="20" spans="13:16" x14ac:dyDescent="0.25">
       <c r="M20" s="4">
         <v>13</v>
       </c>
@@ -3989,7 +4014,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="21" spans="13:16" x14ac:dyDescent="0.35">
+    <row r="21" spans="13:16" x14ac:dyDescent="0.25">
       <c r="M21">
         <v>14</v>
       </c>
@@ -4004,7 +4029,12 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="15">
+  <mergeCells count="20">
+    <mergeCell ref="T1:Y1"/>
+    <mergeCell ref="T2:U2"/>
+    <mergeCell ref="T3:U3"/>
+    <mergeCell ref="T4:Y5"/>
+    <mergeCell ref="T6:Y6"/>
     <mergeCell ref="G1:L1"/>
     <mergeCell ref="M2:N2"/>
     <mergeCell ref="A2:B2"/>
@@ -4028,59 +4058,59 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:R25"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5" customWidth="1"/>
-    <col min="2" max="2" width="22.1796875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.54296875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="31.1796875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="18.453125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="16.1796875" style="7" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="22.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.5703125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="31.140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="18.42578125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="16.140625" style="7" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="5" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="30.453125" customWidth="1"/>
-    <col min="9" max="9" width="27.54296875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="30.26953125" customWidth="1"/>
-    <col min="11" max="11" width="18.453125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="16.1796875" style="7" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="30.42578125" customWidth="1"/>
+    <col min="9" max="9" width="27.5703125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="30.28515625" customWidth="1"/>
+    <col min="11" max="11" width="18.42578125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="16.140625" style="7" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="5" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="35.453125" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="20.54296875" customWidth="1"/>
-    <col min="16" max="16" width="31.1796875" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="18.453125" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="16.1796875" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="35.42578125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="20.5703125" customWidth="1"/>
+    <col min="16" max="16" width="31.140625" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="18.42578125" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="16.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A1" s="19" t="s">
+    <row r="1" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A1" s="20" t="s">
         <v>84</v>
       </c>
-      <c r="B1" s="18"/>
-      <c r="C1" s="18"/>
-      <c r="D1" s="18"/>
-      <c r="E1" s="18"/>
-      <c r="F1" s="21"/>
-      <c r="G1" s="23" t="s">
+      <c r="B1" s="19"/>
+      <c r="C1" s="19"/>
+      <c r="D1" s="19"/>
+      <c r="E1" s="19"/>
+      <c r="F1" s="22"/>
+      <c r="G1" s="24" t="s">
         <v>85</v>
       </c>
-      <c r="H1" s="18"/>
-      <c r="I1" s="18"/>
-      <c r="J1" s="18"/>
-      <c r="K1" s="18"/>
-      <c r="L1" s="21"/>
-      <c r="M1" s="17" t="s">
+      <c r="H1" s="19"/>
+      <c r="I1" s="19"/>
+      <c r="J1" s="19"/>
+      <c r="K1" s="19"/>
+      <c r="L1" s="22"/>
+      <c r="M1" s="18" t="s">
         <v>86</v>
       </c>
-      <c r="N1" s="18"/>
-      <c r="O1" s="18"/>
-      <c r="P1" s="18"/>
-      <c r="Q1" s="18"/>
-      <c r="R1" s="18"/>
-    </row>
-    <row r="2" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A2" s="17" t="s">
+      <c r="N1" s="19"/>
+      <c r="O1" s="19"/>
+      <c r="P1" s="19"/>
+      <c r="Q1" s="19"/>
+      <c r="R1" s="19"/>
+    </row>
+    <row r="2" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A2" s="18" t="s">
         <v>10</v>
       </c>
-      <c r="B2" s="18"/>
+      <c r="B2" s="19"/>
       <c r="C2" s="6">
         <f>IFERROR(_xlfn.XLOOKUP(A1, TestMaster[Test Name], TestMaster[Test ID], "ID not found"), "")</f>
         <v>36</v>
@@ -4088,10 +4118,10 @@
       <c r="E2" t="s">
         <v>11</v>
       </c>
-      <c r="G2" s="17" t="s">
+      <c r="G2" s="18" t="s">
         <v>10</v>
       </c>
-      <c r="H2" s="18"/>
+      <c r="H2" s="19"/>
       <c r="I2" s="6">
         <f>IFERROR(_xlfn.XLOOKUP(G1, TestMaster[Test Name], TestMaster[Test ID], "ID not found"), "")</f>
         <v>34</v>
@@ -4099,10 +4129,10 @@
       <c r="K2" t="s">
         <v>11</v>
       </c>
-      <c r="M2" s="17" t="s">
+      <c r="M2" s="18" t="s">
         <v>10</v>
       </c>
-      <c r="N2" s="18"/>
+      <c r="N2" s="19"/>
       <c r="O2" s="12">
         <f>IFERROR(_xlfn.XLOOKUP(M1, TestMaster[Test Name], TestMaster[Test ID], "ID not found"), "")</f>
         <v>35</v>
@@ -4111,11 +4141,11 @@
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A3" s="17" t="s">
+    <row r="3" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A3" s="18" t="s">
         <v>12</v>
       </c>
-      <c r="B3" s="18"/>
+      <c r="B3" s="19"/>
       <c r="C3" s="6" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(A1, TestMaster[Test Name], TestMaster[Test Priority], "Priority not found"), "")</f>
         <v>Medium</v>
@@ -4127,10 +4157,10 @@
         <f>IFERROR(_xlfn.XLOOKUP(A1, TestMaster[Test Name], TestMaster[Test Status], "Status not found"), "")</f>
         <v>Not Implemented</v>
       </c>
-      <c r="G3" s="17" t="s">
+      <c r="G3" s="18" t="s">
         <v>12</v>
       </c>
-      <c r="H3" s="18"/>
+      <c r="H3" s="19"/>
       <c r="I3" s="6" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(G1, TestMaster[Test Name], TestMaster[Test Priority], "Priority not found"), "")</f>
         <v>Medium</v>
@@ -4142,10 +4172,10 @@
         <f>IFERROR(_xlfn.XLOOKUP(G1, TestMaster[Test Name], TestMaster[Test Status], "Status not found"), "")</f>
         <v>Not Implemented</v>
       </c>
-      <c r="M3" s="17" t="s">
+      <c r="M3" s="18" t="s">
         <v>12</v>
       </c>
-      <c r="N3" s="18"/>
+      <c r="N3" s="19"/>
       <c r="O3" s="12" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(M1, TestMaster[Test Name], TestMaster[Test Priority], "Priority not found"), "")</f>
         <v>Low</v>
@@ -4158,79 +4188,79 @@
         <v>Not Implemented</v>
       </c>
     </row>
-    <row r="4" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A4" s="19" t="s">
+    <row r="4" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A4" s="20" t="s">
         <v>57</v>
       </c>
-      <c r="B4" s="18"/>
-      <c r="C4" s="18"/>
-      <c r="D4" s="18"/>
-      <c r="E4" s="18"/>
-      <c r="F4" s="21"/>
-      <c r="G4" s="23" t="s">
+      <c r="B4" s="19"/>
+      <c r="C4" s="19"/>
+      <c r="D4" s="19"/>
+      <c r="E4" s="19"/>
+      <c r="F4" s="22"/>
+      <c r="G4" s="24" t="s">
         <v>57</v>
       </c>
-      <c r="H4" s="18"/>
-      <c r="I4" s="18"/>
-      <c r="J4" s="18"/>
-      <c r="K4" s="18"/>
-      <c r="L4" s="21"/>
-      <c r="M4" s="17" t="s">
+      <c r="H4" s="19"/>
+      <c r="I4" s="19"/>
+      <c r="J4" s="19"/>
+      <c r="K4" s="19"/>
+      <c r="L4" s="22"/>
+      <c r="M4" s="18" t="s">
         <v>57</v>
       </c>
-      <c r="N4" s="18"/>
-      <c r="O4" s="18"/>
-      <c r="P4" s="18"/>
-      <c r="Q4" s="18"/>
-      <c r="R4" s="18"/>
-    </row>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A5" s="18"/>
-      <c r="B5" s="18"/>
-      <c r="C5" s="18"/>
-      <c r="D5" s="18"/>
-      <c r="E5" s="18"/>
-      <c r="F5" s="21"/>
-      <c r="G5" s="24"/>
-      <c r="H5" s="18"/>
-      <c r="I5" s="18"/>
-      <c r="J5" s="18"/>
-      <c r="K5" s="18"/>
-      <c r="L5" s="21"/>
-      <c r="M5" s="18"/>
-      <c r="N5" s="18"/>
-      <c r="O5" s="18"/>
-      <c r="P5" s="18"/>
-      <c r="Q5" s="18"/>
-      <c r="R5" s="18"/>
-    </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A6" s="19" t="s">
+      <c r="N4" s="19"/>
+      <c r="O4" s="19"/>
+      <c r="P4" s="19"/>
+      <c r="Q4" s="19"/>
+      <c r="R4" s="19"/>
+    </row>
+    <row r="5" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A5" s="19"/>
+      <c r="B5" s="19"/>
+      <c r="C5" s="19"/>
+      <c r="D5" s="19"/>
+      <c r="E5" s="19"/>
+      <c r="F5" s="22"/>
+      <c r="G5" s="25"/>
+      <c r="H5" s="19"/>
+      <c r="I5" s="19"/>
+      <c r="J5" s="19"/>
+      <c r="K5" s="19"/>
+      <c r="L5" s="22"/>
+      <c r="M5" s="19"/>
+      <c r="N5" s="19"/>
+      <c r="O5" s="19"/>
+      <c r="P5" s="19"/>
+      <c r="Q5" s="19"/>
+      <c r="R5" s="19"/>
+    </row>
+    <row r="6" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A6" s="20" t="s">
         <v>15</v>
       </c>
-      <c r="B6" s="18"/>
-      <c r="C6" s="18"/>
-      <c r="D6" s="18"/>
-      <c r="E6" s="18"/>
-      <c r="F6" s="21"/>
-      <c r="G6" s="23" t="s">
+      <c r="B6" s="19"/>
+      <c r="C6" s="19"/>
+      <c r="D6" s="19"/>
+      <c r="E6" s="19"/>
+      <c r="F6" s="22"/>
+      <c r="G6" s="24" t="s">
         <v>15</v>
       </c>
-      <c r="H6" s="18"/>
-      <c r="I6" s="18"/>
-      <c r="J6" s="18"/>
-      <c r="K6" s="18"/>
-      <c r="L6" s="21"/>
-      <c r="M6" s="17" t="s">
+      <c r="H6" s="19"/>
+      <c r="I6" s="19"/>
+      <c r="J6" s="19"/>
+      <c r="K6" s="19"/>
+      <c r="L6" s="22"/>
+      <c r="M6" s="18" t="s">
         <v>15</v>
       </c>
-      <c r="N6" s="18"/>
-      <c r="O6" s="18"/>
-      <c r="P6" s="18"/>
-      <c r="Q6" s="18"/>
-      <c r="R6" s="18"/>
-    </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="N6" s="19"/>
+      <c r="O6" s="19"/>
+      <c r="P6" s="19"/>
+      <c r="Q6" s="19"/>
+      <c r="R6" s="19"/>
+    </row>
+    <row r="7" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>16</v>
       </c>
@@ -4286,7 +4316,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A8" s="4">
         <v>1</v>
       </c>
@@ -4324,7 +4354,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="9" spans="1:18" ht="43.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:18" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="4">
         <v>2</v>
       </c>
@@ -4362,7 +4392,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="10" spans="1:18" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:18" ht="29.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="G10">
         <v>3</v>
       </c>
@@ -4388,7 +4418,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:18" x14ac:dyDescent="0.25">
       <c r="G11">
         <v>4</v>
       </c>
@@ -4414,7 +4444,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:18" x14ac:dyDescent="0.25">
       <c r="G12">
         <v>5</v>
       </c>
@@ -4440,7 +4470,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:18" x14ac:dyDescent="0.25">
       <c r="G13">
         <v>6</v>
       </c>
@@ -4466,7 +4496,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:18" x14ac:dyDescent="0.25">
       <c r="G14">
         <v>7</v>
       </c>
@@ -4486,7 +4516,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:18" x14ac:dyDescent="0.25">
       <c r="G15">
         <v>8</v>
       </c>
@@ -4512,7 +4542,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:18" x14ac:dyDescent="0.25">
       <c r="G16">
         <v>9</v>
       </c>
@@ -4538,7 +4568,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="17" spans="7:10" x14ac:dyDescent="0.35">
+    <row r="17" spans="7:10" x14ac:dyDescent="0.25">
       <c r="G17">
         <v>10</v>
       </c>
@@ -4552,7 +4582,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="18" spans="7:10" x14ac:dyDescent="0.35">
+    <row r="18" spans="7:10" x14ac:dyDescent="0.25">
       <c r="G18">
         <v>11</v>
       </c>
@@ -4566,7 +4596,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="19" spans="7:10" x14ac:dyDescent="0.35">
+    <row r="19" spans="7:10" x14ac:dyDescent="0.25">
       <c r="G19">
         <v>12</v>
       </c>
@@ -4580,7 +4610,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="20" spans="7:10" x14ac:dyDescent="0.35">
+    <row r="20" spans="7:10" x14ac:dyDescent="0.25">
       <c r="G20">
         <v>13</v>
       </c>
@@ -4594,7 +4624,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="21" spans="7:10" x14ac:dyDescent="0.35">
+    <row r="21" spans="7:10" x14ac:dyDescent="0.25">
       <c r="G21">
         <v>14</v>
       </c>
@@ -4608,7 +4638,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="22" spans="7:10" x14ac:dyDescent="0.35">
+    <row r="22" spans="7:10" x14ac:dyDescent="0.25">
       <c r="G22">
         <v>15</v>
       </c>
@@ -4622,7 +4652,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="23" spans="7:10" x14ac:dyDescent="0.35">
+    <row r="23" spans="7:10" x14ac:dyDescent="0.25">
       <c r="G23">
         <v>16</v>
       </c>
@@ -4636,7 +4666,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="24" spans="7:10" x14ac:dyDescent="0.35">
+    <row r="24" spans="7:10" x14ac:dyDescent="0.25">
       <c r="G24">
         <v>17</v>
       </c>
@@ -4650,7 +4680,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="25" spans="7:10" x14ac:dyDescent="0.35">
+    <row r="25" spans="7:10" x14ac:dyDescent="0.25">
       <c r="G25">
         <v>18</v>
       </c>
@@ -4689,59 +4719,59 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:R11"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="21.81640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.54296875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="31.1796875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="18.453125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="16.1796875" style="7" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="21.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.5703125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="31.140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="18.42578125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="16.140625" style="7" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="5" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="22.453125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="19.7265625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="28.54296875" customWidth="1"/>
-    <col min="11" max="11" width="18.453125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="16.1796875" style="7" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="22.42578125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="19.7109375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="28.5703125" customWidth="1"/>
+    <col min="11" max="11" width="18.42578125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="16.140625" style="7" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="5" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="22.453125" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="22.81640625" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="32.453125" customWidth="1"/>
-    <col min="17" max="17" width="18.453125" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="16.1796875" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="22.42578125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="22.85546875" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="32.42578125" customWidth="1"/>
+    <col min="17" max="17" width="18.42578125" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="16.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A1" s="19" t="s">
+    <row r="1" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A1" s="20" t="s">
         <v>121</v>
       </c>
-      <c r="B1" s="18"/>
-      <c r="C1" s="18"/>
-      <c r="D1" s="18"/>
-      <c r="E1" s="18"/>
-      <c r="F1" s="21"/>
-      <c r="G1" s="23" t="s">
+      <c r="B1" s="19"/>
+      <c r="C1" s="19"/>
+      <c r="D1" s="19"/>
+      <c r="E1" s="19"/>
+      <c r="F1" s="22"/>
+      <c r="G1" s="24" t="s">
         <v>122</v>
       </c>
-      <c r="H1" s="18"/>
-      <c r="I1" s="18"/>
-      <c r="J1" s="18"/>
-      <c r="K1" s="18"/>
-      <c r="L1" s="21"/>
-      <c r="M1" s="17" t="s">
+      <c r="H1" s="19"/>
+      <c r="I1" s="19"/>
+      <c r="J1" s="19"/>
+      <c r="K1" s="19"/>
+      <c r="L1" s="22"/>
+      <c r="M1" s="18" t="s">
         <v>123</v>
       </c>
-      <c r="N1" s="18"/>
-      <c r="O1" s="18"/>
-      <c r="P1" s="18"/>
-      <c r="Q1" s="18"/>
-      <c r="R1" s="18"/>
-    </row>
-    <row r="2" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A2" s="17" t="s">
+      <c r="N1" s="19"/>
+      <c r="O1" s="19"/>
+      <c r="P1" s="19"/>
+      <c r="Q1" s="19"/>
+      <c r="R1" s="19"/>
+    </row>
+    <row r="2" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A2" s="18" t="s">
         <v>10</v>
       </c>
-      <c r="B2" s="18"/>
+      <c r="B2" s="19"/>
       <c r="C2" s="6">
         <f>IFERROR(_xlfn.XLOOKUP(A1, TestMaster[Test Name], TestMaster[Test ID], "ID not found"), "")</f>
         <v>29</v>
@@ -4749,10 +4779,10 @@
       <c r="E2" t="s">
         <v>11</v>
       </c>
-      <c r="G2" s="17" t="s">
+      <c r="G2" s="18" t="s">
         <v>10</v>
       </c>
-      <c r="H2" s="18"/>
+      <c r="H2" s="19"/>
       <c r="I2" s="6">
         <f>IFERROR(_xlfn.XLOOKUP(G1, TestMaster[Test Name], TestMaster[Test ID], "ID not found"), "")</f>
         <v>27</v>
@@ -4760,10 +4790,10 @@
       <c r="K2" t="s">
         <v>11</v>
       </c>
-      <c r="M2" s="17" t="s">
+      <c r="M2" s="18" t="s">
         <v>10</v>
       </c>
-      <c r="N2" s="18"/>
+      <c r="N2" s="19"/>
       <c r="O2" s="6">
         <f>IFERROR(_xlfn.XLOOKUP(M1, TestMaster[Test Name], TestMaster[Test ID], "ID not found"), "")</f>
         <v>28</v>
@@ -4772,11 +4802,11 @@
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A3" s="17" t="s">
+    <row r="3" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A3" s="18" t="s">
         <v>12</v>
       </c>
-      <c r="B3" s="18"/>
+      <c r="B3" s="19"/>
       <c r="C3" s="6" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(A1, TestMaster[Test Name], TestMaster[Test Priority], "Priority not found"), "")</f>
         <v>Medium</v>
@@ -4788,10 +4818,10 @@
         <f>IFERROR(_xlfn.XLOOKUP(A1, TestMaster[Test Name], TestMaster[Test Status], "Status not found"), "")</f>
         <v>Not Implemented</v>
       </c>
-      <c r="G3" s="17" t="s">
+      <c r="G3" s="18" t="s">
         <v>12</v>
       </c>
-      <c r="H3" s="18"/>
+      <c r="H3" s="19"/>
       <c r="I3" s="6" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(G1, TestMaster[Test Name], TestMaster[Test Priority], "Priority not found"), "")</f>
         <v>Medium</v>
@@ -4803,10 +4833,10 @@
         <f>IFERROR(_xlfn.XLOOKUP(G1, TestMaster[Test Name], TestMaster[Test Status], "Status not found"), "")</f>
         <v>Not Implemented</v>
       </c>
-      <c r="M3" s="17" t="s">
+      <c r="M3" s="18" t="s">
         <v>12</v>
       </c>
-      <c r="N3" s="18"/>
+      <c r="N3" s="19"/>
       <c r="O3" s="6" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(M1, TestMaster[Test Name], TestMaster[Test Priority], "Priority not found"), "")</f>
         <v>Low</v>
@@ -4819,79 +4849,79 @@
         <v>Not Implemented</v>
       </c>
     </row>
-    <row r="4" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A4" s="26" t="s">
+    <row r="4" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A4" s="27" t="s">
         <v>124</v>
       </c>
-      <c r="B4" s="18"/>
-      <c r="C4" s="18"/>
-      <c r="D4" s="18"/>
-      <c r="E4" s="18"/>
-      <c r="F4" s="21"/>
-      <c r="G4" s="27" t="s">
+      <c r="B4" s="19"/>
+      <c r="C4" s="19"/>
+      <c r="D4" s="19"/>
+      <c r="E4" s="19"/>
+      <c r="F4" s="22"/>
+      <c r="G4" s="28" t="s">
         <v>57</v>
       </c>
-      <c r="H4" s="18"/>
-      <c r="I4" s="18"/>
-      <c r="J4" s="18"/>
-      <c r="K4" s="18"/>
-      <c r="L4" s="21"/>
-      <c r="M4" s="25" t="s">
+      <c r="H4" s="19"/>
+      <c r="I4" s="19"/>
+      <c r="J4" s="19"/>
+      <c r="K4" s="19"/>
+      <c r="L4" s="22"/>
+      <c r="M4" s="26" t="s">
         <v>57</v>
       </c>
-      <c r="N4" s="18"/>
-      <c r="O4" s="18"/>
-      <c r="P4" s="18"/>
-      <c r="Q4" s="18"/>
-      <c r="R4" s="18"/>
-    </row>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A5" s="18"/>
-      <c r="B5" s="18"/>
-      <c r="C5" s="18"/>
-      <c r="D5" s="18"/>
-      <c r="E5" s="18"/>
-      <c r="F5" s="21"/>
-      <c r="G5" s="24"/>
-      <c r="H5" s="18"/>
-      <c r="I5" s="18"/>
-      <c r="J5" s="18"/>
-      <c r="K5" s="18"/>
-      <c r="L5" s="21"/>
-      <c r="M5" s="18"/>
-      <c r="N5" s="18"/>
-      <c r="O5" s="18"/>
-      <c r="P5" s="18"/>
-      <c r="Q5" s="18"/>
-      <c r="R5" s="18"/>
-    </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A6" s="19" t="s">
+      <c r="N4" s="19"/>
+      <c r="O4" s="19"/>
+      <c r="P4" s="19"/>
+      <c r="Q4" s="19"/>
+      <c r="R4" s="19"/>
+    </row>
+    <row r="5" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A5" s="19"/>
+      <c r="B5" s="19"/>
+      <c r="C5" s="19"/>
+      <c r="D5" s="19"/>
+      <c r="E5" s="19"/>
+      <c r="F5" s="22"/>
+      <c r="G5" s="25"/>
+      <c r="H5" s="19"/>
+      <c r="I5" s="19"/>
+      <c r="J5" s="19"/>
+      <c r="K5" s="19"/>
+      <c r="L5" s="22"/>
+      <c r="M5" s="19"/>
+      <c r="N5" s="19"/>
+      <c r="O5" s="19"/>
+      <c r="P5" s="19"/>
+      <c r="Q5" s="19"/>
+      <c r="R5" s="19"/>
+    </row>
+    <row r="6" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A6" s="20" t="s">
         <v>125</v>
       </c>
-      <c r="B6" s="18"/>
-      <c r="C6" s="18"/>
-      <c r="D6" s="18"/>
-      <c r="E6" s="18"/>
-      <c r="F6" s="21"/>
-      <c r="G6" s="23" t="s">
+      <c r="B6" s="19"/>
+      <c r="C6" s="19"/>
+      <c r="D6" s="19"/>
+      <c r="E6" s="19"/>
+      <c r="F6" s="22"/>
+      <c r="G6" s="24" t="s">
         <v>15</v>
       </c>
-      <c r="H6" s="18"/>
-      <c r="I6" s="18"/>
-      <c r="J6" s="18"/>
-      <c r="K6" s="18"/>
-      <c r="L6" s="21"/>
-      <c r="M6" s="17" t="s">
+      <c r="H6" s="19"/>
+      <c r="I6" s="19"/>
+      <c r="J6" s="19"/>
+      <c r="K6" s="19"/>
+      <c r="L6" s="22"/>
+      <c r="M6" s="18" t="s">
         <v>15</v>
       </c>
-      <c r="N6" s="18"/>
-      <c r="O6" s="18"/>
-      <c r="P6" s="18"/>
-      <c r="Q6" s="18"/>
-      <c r="R6" s="18"/>
-    </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="N6" s="19"/>
+      <c r="O6" s="19"/>
+      <c r="P6" s="19"/>
+      <c r="Q6" s="19"/>
+      <c r="R6" s="19"/>
+    </row>
+    <row r="7" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>16</v>
       </c>
@@ -4947,7 +4977,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="8" spans="1:18" s="3" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:18" s="3" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A8" s="3">
         <v>1</v>
       </c>
@@ -4987,7 +5017,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="9" spans="1:18" s="3" customFormat="1" ht="43.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:18" s="3" customFormat="1" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="3">
         <v>2</v>
       </c>
@@ -5027,7 +5057,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="10" spans="1:18" s="3" customFormat="1" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:18" s="3" customFormat="1" ht="29.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="F10" s="13"/>
       <c r="G10" s="3">
         <v>3</v>
@@ -5055,7 +5085,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="11" spans="1:18" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:18" ht="29.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="M11" s="3">
         <v>4</v>
       </c>
@@ -5094,58 +5124,58 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:R21"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="23.26953125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="23.28515625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="41" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="15.26953125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="18.453125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="8.7265625" style="7" customWidth="1"/>
+    <col min="4" max="4" width="15.28515625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="18.42578125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="8.7109375" style="7" customWidth="1"/>
     <col min="7" max="7" width="5" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="19.1796875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="27.36328125" customWidth="1"/>
-    <col min="10" max="10" width="15.26953125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="18.453125" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="8.7265625" style="15" customWidth="1"/>
-    <col min="14" max="14" width="23.26953125" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="17.1796875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="19.140625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="27.42578125" customWidth="1"/>
+    <col min="10" max="10" width="15.28515625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="18.42578125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="8.7109375" style="15" customWidth="1"/>
+    <col min="14" max="14" width="23.28515625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="17.140625" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="41" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="18.36328125" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="18.42578125" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="8" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A1" s="19" t="s">
+    <row r="1" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A1" s="20" t="s">
         <v>136</v>
       </c>
-      <c r="B1" s="18"/>
-      <c r="C1" s="18"/>
-      <c r="D1" s="18"/>
-      <c r="E1" s="18"/>
-      <c r="F1" s="21"/>
-      <c r="G1" s="17" t="s">
+      <c r="B1" s="19"/>
+      <c r="C1" s="19"/>
+      <c r="D1" s="19"/>
+      <c r="E1" s="19"/>
+      <c r="F1" s="22"/>
+      <c r="G1" s="18" t="s">
         <v>137</v>
       </c>
-      <c r="H1" s="18"/>
-      <c r="I1" s="18"/>
-      <c r="J1" s="18"/>
-      <c r="K1" s="18"/>
-      <c r="L1" s="18"/>
-      <c r="M1" s="23" t="s">
+      <c r="H1" s="19"/>
+      <c r="I1" s="19"/>
+      <c r="J1" s="19"/>
+      <c r="K1" s="19"/>
+      <c r="L1" s="19"/>
+      <c r="M1" s="24" t="s">
         <v>138</v>
       </c>
-      <c r="N1" s="18"/>
-      <c r="O1" s="18"/>
-      <c r="P1" s="18"/>
-      <c r="Q1" s="18"/>
-      <c r="R1" s="21"/>
-    </row>
-    <row r="2" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A2" s="17" t="s">
+      <c r="N1" s="19"/>
+      <c r="O1" s="19"/>
+      <c r="P1" s="19"/>
+      <c r="Q1" s="19"/>
+      <c r="R1" s="22"/>
+    </row>
+    <row r="2" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A2" s="18" t="s">
         <v>10</v>
       </c>
-      <c r="B2" s="18"/>
+      <c r="B2" s="19"/>
       <c r="C2" s="6">
         <f>IFERROR(_xlfn.XLOOKUP(A1, TestMaster[Test Name], TestMaster[Test ID], "ID not found"), "")</f>
         <v>32</v>
@@ -5153,10 +5183,10 @@
       <c r="E2" t="s">
         <v>11</v>
       </c>
-      <c r="G2" s="17" t="s">
+      <c r="G2" s="18" t="s">
         <v>10</v>
       </c>
-      <c r="H2" s="18"/>
+      <c r="H2" s="19"/>
       <c r="I2" s="6">
         <f>IFERROR(_xlfn.XLOOKUP(G1, TestMaster[Test Name], TestMaster[Test ID], "ID not found"), "")</f>
         <v>30</v>
@@ -5164,10 +5194,10 @@
       <c r="K2" t="s">
         <v>11</v>
       </c>
-      <c r="M2" s="28" t="s">
+      <c r="M2" s="29" t="s">
         <v>10</v>
       </c>
-      <c r="N2" s="18"/>
+      <c r="N2" s="19"/>
       <c r="O2" s="6">
         <f>IFERROR(_xlfn.XLOOKUP(M1, TestMaster[Test Name], TestMaster[Test ID], "ID not found"), "")</f>
         <v>31</v>
@@ -5177,11 +5207,11 @@
       </c>
       <c r="R2" s="7"/>
     </row>
-    <row r="3" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A3" s="17" t="s">
+    <row r="3" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A3" s="18" t="s">
         <v>12</v>
       </c>
-      <c r="B3" s="18"/>
+      <c r="B3" s="19"/>
       <c r="C3" s="6" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(A1, TestMaster[Test Name], TestMaster[Test Priority], "Priority not found"), "")</f>
         <v>High</v>
@@ -5193,10 +5223,10 @@
         <f>IFERROR(_xlfn.XLOOKUP(A1, TestMaster[Test Name], TestMaster[Test Priority], "Priority not found"), "")</f>
         <v>High</v>
       </c>
-      <c r="G3" s="17" t="s">
+      <c r="G3" s="18" t="s">
         <v>12</v>
       </c>
-      <c r="H3" s="18"/>
+      <c r="H3" s="19"/>
       <c r="I3" s="6" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(G1, TestMaster[Test Name], TestMaster[Test Priority], "Priority not found"), "")</f>
         <v>High</v>
@@ -5208,10 +5238,10 @@
         <f>IFERROR(_xlfn.XLOOKUP(G1, TestMaster[Test Name], TestMaster[Test Priority], "Priority not found"), "")</f>
         <v>High</v>
       </c>
-      <c r="M3" s="28" t="s">
+      <c r="M3" s="29" t="s">
         <v>12</v>
       </c>
-      <c r="N3" s="18"/>
+      <c r="N3" s="19"/>
       <c r="O3" s="6" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(M1, TestMaster[Test Name], TestMaster[Test Priority], "Priority not found"), "")</f>
         <v>Medium</v>
@@ -5224,79 +5254,79 @@
         <v>Medium</v>
       </c>
     </row>
-    <row r="4" spans="1:18" s="2" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="26" t="s">
+    <row r="4" spans="1:18" s="2" customFormat="1" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="27" t="s">
         <v>139</v>
       </c>
-      <c r="B4" s="20"/>
-      <c r="C4" s="20"/>
-      <c r="D4" s="20"/>
-      <c r="E4" s="20"/>
-      <c r="F4" s="21"/>
-      <c r="G4" s="25" t="s">
+      <c r="B4" s="21"/>
+      <c r="C4" s="21"/>
+      <c r="D4" s="21"/>
+      <c r="E4" s="21"/>
+      <c r="F4" s="22"/>
+      <c r="G4" s="26" t="s">
         <v>140</v>
       </c>
-      <c r="H4" s="20"/>
-      <c r="I4" s="20"/>
-      <c r="J4" s="20"/>
-      <c r="K4" s="20"/>
-      <c r="L4" s="20"/>
-      <c r="M4" s="27" t="s">
+      <c r="H4" s="21"/>
+      <c r="I4" s="21"/>
+      <c r="J4" s="21"/>
+      <c r="K4" s="21"/>
+      <c r="L4" s="21"/>
+      <c r="M4" s="28" t="s">
         <v>141</v>
       </c>
-      <c r="N4" s="20"/>
-      <c r="O4" s="20"/>
-      <c r="P4" s="20"/>
-      <c r="Q4" s="20"/>
-      <c r="R4" s="21"/>
-    </row>
-    <row r="5" spans="1:18" s="2" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="20"/>
-      <c r="B5" s="20"/>
-      <c r="C5" s="20"/>
-      <c r="D5" s="20"/>
-      <c r="E5" s="20"/>
-      <c r="F5" s="21"/>
-      <c r="G5" s="20"/>
-      <c r="H5" s="20"/>
-      <c r="I5" s="20"/>
-      <c r="J5" s="20"/>
-      <c r="K5" s="20"/>
-      <c r="L5" s="20"/>
-      <c r="M5" s="24"/>
-      <c r="N5" s="20"/>
-      <c r="O5" s="20"/>
-      <c r="P5" s="20"/>
-      <c r="Q5" s="20"/>
-      <c r="R5" s="21"/>
-    </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A6" s="19" t="s">
+      <c r="N4" s="21"/>
+      <c r="O4" s="21"/>
+      <c r="P4" s="21"/>
+      <c r="Q4" s="21"/>
+      <c r="R4" s="22"/>
+    </row>
+    <row r="5" spans="1:18" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="21"/>
+      <c r="B5" s="21"/>
+      <c r="C5" s="21"/>
+      <c r="D5" s="21"/>
+      <c r="E5" s="21"/>
+      <c r="F5" s="22"/>
+      <c r="G5" s="21"/>
+      <c r="H5" s="21"/>
+      <c r="I5" s="21"/>
+      <c r="J5" s="21"/>
+      <c r="K5" s="21"/>
+      <c r="L5" s="21"/>
+      <c r="M5" s="25"/>
+      <c r="N5" s="21"/>
+      <c r="O5" s="21"/>
+      <c r="P5" s="21"/>
+      <c r="Q5" s="21"/>
+      <c r="R5" s="22"/>
+    </row>
+    <row r="6" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A6" s="20" t="s">
         <v>142</v>
       </c>
-      <c r="B6" s="18"/>
-      <c r="C6" s="18"/>
-      <c r="D6" s="18"/>
-      <c r="E6" s="18"/>
-      <c r="F6" s="21"/>
-      <c r="G6" s="17" t="s">
+      <c r="B6" s="19"/>
+      <c r="C6" s="19"/>
+      <c r="D6" s="19"/>
+      <c r="E6" s="19"/>
+      <c r="F6" s="22"/>
+      <c r="G6" s="18" t="s">
         <v>143</v>
       </c>
-      <c r="H6" s="18"/>
-      <c r="I6" s="18"/>
-      <c r="J6" s="18"/>
-      <c r="K6" s="18"/>
-      <c r="L6" s="18"/>
-      <c r="M6" s="23" t="s">
+      <c r="H6" s="19"/>
+      <c r="I6" s="19"/>
+      <c r="J6" s="19"/>
+      <c r="K6" s="19"/>
+      <c r="L6" s="19"/>
+      <c r="M6" s="24" t="s">
         <v>143</v>
       </c>
-      <c r="N6" s="18"/>
-      <c r="O6" s="18"/>
-      <c r="P6" s="18"/>
-      <c r="Q6" s="18"/>
-      <c r="R6" s="21"/>
-    </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="N6" s="19"/>
+      <c r="O6" s="19"/>
+      <c r="P6" s="19"/>
+      <c r="Q6" s="19"/>
+      <c r="R6" s="22"/>
+    </row>
+    <row r="7" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>16</v>
       </c>
@@ -5352,7 +5382,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>1</v>
       </c>
@@ -5382,7 +5412,7 @@
       </c>
       <c r="R8" s="7"/>
     </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>2</v>
       </c>
@@ -5412,7 +5442,7 @@
       </c>
       <c r="R9" s="7"/>
     </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>3</v>
       </c>
@@ -5442,7 +5472,7 @@
       </c>
       <c r="R10" s="7"/>
     </row>
-    <row r="11" spans="1:18" ht="43.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:18" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>4</v>
       </c>
@@ -5475,7 +5505,7 @@
       <c r="P11" s="2"/>
       <c r="R11" s="7"/>
     </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>5</v>
       </c>
@@ -5486,7 +5516,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>6</v>
       </c>
@@ -5500,7 +5530,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>7</v>
       </c>
@@ -5511,7 +5541,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>8</v>
       </c>
@@ -5525,7 +5555,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>9</v>
       </c>
@@ -5539,7 +5569,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>10</v>
       </c>
@@ -5553,7 +5583,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="18" spans="1:4" ht="72.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:4" ht="72.599999999999994" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>11</v>
       </c>
@@ -5567,7 +5597,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>12</v>
       </c>
@@ -5581,7 +5611,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>13</v>
       </c>
@@ -5595,7 +5625,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>14</v>
       </c>
@@ -5634,7 +5664,7 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:FD11"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="6" width="20" customWidth="1"/>
     <col min="8" max="13" width="20" customWidth="1"/>
@@ -5661,193 +5691,193 @@
     <col min="155" max="160" width="20" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:160" x14ac:dyDescent="0.35">
-      <c r="A1" s="29" t="s">
+    <row r="1" spans="1:160" x14ac:dyDescent="0.25">
+      <c r="A1" s="31" t="s">
         <v>181</v>
       </c>
-      <c r="B1" s="18"/>
-      <c r="C1" s="18"/>
-      <c r="D1" s="18"/>
-      <c r="E1" s="18"/>
-      <c r="F1" s="18"/>
-      <c r="H1" s="29" t="s">
+      <c r="B1" s="19"/>
+      <c r="C1" s="19"/>
+      <c r="D1" s="19"/>
+      <c r="E1" s="19"/>
+      <c r="F1" s="19"/>
+      <c r="H1" s="31" t="s">
         <v>182</v>
       </c>
-      <c r="I1" s="18"/>
-      <c r="J1" s="18"/>
-      <c r="K1" s="18"/>
-      <c r="L1" s="18"/>
-      <c r="M1" s="18"/>
-      <c r="O1" s="29" t="s">
+      <c r="I1" s="19"/>
+      <c r="J1" s="19"/>
+      <c r="K1" s="19"/>
+      <c r="L1" s="19"/>
+      <c r="M1" s="19"/>
+      <c r="O1" s="31" t="s">
         <v>183</v>
       </c>
-      <c r="P1" s="18"/>
-      <c r="Q1" s="18"/>
-      <c r="R1" s="18"/>
-      <c r="S1" s="18"/>
-      <c r="T1" s="18"/>
-      <c r="V1" s="29" t="s">
+      <c r="P1" s="19"/>
+      <c r="Q1" s="19"/>
+      <c r="R1" s="19"/>
+      <c r="S1" s="19"/>
+      <c r="T1" s="19"/>
+      <c r="V1" s="31" t="s">
         <v>184</v>
       </c>
-      <c r="W1" s="18"/>
-      <c r="X1" s="18"/>
-      <c r="Y1" s="18"/>
-      <c r="Z1" s="18"/>
-      <c r="AA1" s="18"/>
-      <c r="AC1" s="29" t="s">
+      <c r="W1" s="19"/>
+      <c r="X1" s="19"/>
+      <c r="Y1" s="19"/>
+      <c r="Z1" s="19"/>
+      <c r="AA1" s="19"/>
+      <c r="AC1" s="31" t="s">
         <v>185</v>
       </c>
-      <c r="AD1" s="18"/>
-      <c r="AE1" s="18"/>
-      <c r="AF1" s="18"/>
-      <c r="AG1" s="18"/>
-      <c r="AH1" s="18"/>
-      <c r="AJ1" s="29" t="s">
+      <c r="AD1" s="19"/>
+      <c r="AE1" s="19"/>
+      <c r="AF1" s="19"/>
+      <c r="AG1" s="19"/>
+      <c r="AH1" s="19"/>
+      <c r="AJ1" s="31" t="s">
         <v>186</v>
       </c>
-      <c r="AK1" s="18"/>
-      <c r="AL1" s="18"/>
-      <c r="AM1" s="18"/>
-      <c r="AN1" s="18"/>
-      <c r="AO1" s="18"/>
-      <c r="AQ1" s="29" t="s">
+      <c r="AK1" s="19"/>
+      <c r="AL1" s="19"/>
+      <c r="AM1" s="19"/>
+      <c r="AN1" s="19"/>
+      <c r="AO1" s="19"/>
+      <c r="AQ1" s="31" t="s">
         <v>187</v>
       </c>
-      <c r="AR1" s="18"/>
-      <c r="AS1" s="18"/>
-      <c r="AT1" s="18"/>
-      <c r="AU1" s="18"/>
-      <c r="AV1" s="18"/>
-      <c r="AX1" s="29" t="s">
+      <c r="AR1" s="19"/>
+      <c r="AS1" s="19"/>
+      <c r="AT1" s="19"/>
+      <c r="AU1" s="19"/>
+      <c r="AV1" s="19"/>
+      <c r="AX1" s="31" t="s">
         <v>188</v>
       </c>
-      <c r="AY1" s="18"/>
-      <c r="AZ1" s="18"/>
-      <c r="BA1" s="18"/>
-      <c r="BB1" s="18"/>
-      <c r="BC1" s="18"/>
-      <c r="BE1" s="29" t="s">
+      <c r="AY1" s="19"/>
+      <c r="AZ1" s="19"/>
+      <c r="BA1" s="19"/>
+      <c r="BB1" s="19"/>
+      <c r="BC1" s="19"/>
+      <c r="BE1" s="31" t="s">
         <v>189</v>
       </c>
-      <c r="BF1" s="18"/>
-      <c r="BG1" s="18"/>
-      <c r="BH1" s="18"/>
-      <c r="BI1" s="18"/>
-      <c r="BJ1" s="18"/>
-      <c r="BL1" s="29" t="s">
+      <c r="BF1" s="19"/>
+      <c r="BG1" s="19"/>
+      <c r="BH1" s="19"/>
+      <c r="BI1" s="19"/>
+      <c r="BJ1" s="19"/>
+      <c r="BL1" s="31" t="s">
         <v>190</v>
       </c>
-      <c r="BM1" s="18"/>
-      <c r="BN1" s="18"/>
-      <c r="BO1" s="18"/>
-      <c r="BP1" s="18"/>
-      <c r="BQ1" s="18"/>
-      <c r="BS1" s="29" t="s">
+      <c r="BM1" s="19"/>
+      <c r="BN1" s="19"/>
+      <c r="BO1" s="19"/>
+      <c r="BP1" s="19"/>
+      <c r="BQ1" s="19"/>
+      <c r="BS1" s="31" t="s">
         <v>191</v>
       </c>
-      <c r="BT1" s="18"/>
-      <c r="BU1" s="18"/>
-      <c r="BV1" s="18"/>
-      <c r="BW1" s="18"/>
-      <c r="BX1" s="18"/>
-      <c r="BZ1" s="29" t="s">
+      <c r="BT1" s="19"/>
+      <c r="BU1" s="19"/>
+      <c r="BV1" s="19"/>
+      <c r="BW1" s="19"/>
+      <c r="BX1" s="19"/>
+      <c r="BZ1" s="31" t="s">
         <v>192</v>
       </c>
-      <c r="CA1" s="18"/>
-      <c r="CB1" s="18"/>
-      <c r="CC1" s="18"/>
-      <c r="CD1" s="18"/>
-      <c r="CE1" s="18"/>
-      <c r="CG1" s="29" t="s">
+      <c r="CA1" s="19"/>
+      <c r="CB1" s="19"/>
+      <c r="CC1" s="19"/>
+      <c r="CD1" s="19"/>
+      <c r="CE1" s="19"/>
+      <c r="CG1" s="31" t="s">
         <v>193</v>
       </c>
-      <c r="CH1" s="18"/>
-      <c r="CI1" s="18"/>
-      <c r="CJ1" s="18"/>
-      <c r="CK1" s="18"/>
-      <c r="CL1" s="18"/>
-      <c r="CN1" s="29" t="s">
+      <c r="CH1" s="19"/>
+      <c r="CI1" s="19"/>
+      <c r="CJ1" s="19"/>
+      <c r="CK1" s="19"/>
+      <c r="CL1" s="19"/>
+      <c r="CN1" s="31" t="s">
         <v>194</v>
       </c>
-      <c r="CO1" s="18"/>
-      <c r="CP1" s="18"/>
-      <c r="CQ1" s="18"/>
-      <c r="CR1" s="18"/>
-      <c r="CS1" s="18"/>
-      <c r="CU1" s="29" t="s">
+      <c r="CO1" s="19"/>
+      <c r="CP1" s="19"/>
+      <c r="CQ1" s="19"/>
+      <c r="CR1" s="19"/>
+      <c r="CS1" s="19"/>
+      <c r="CU1" s="31" t="s">
         <v>195</v>
       </c>
-      <c r="CV1" s="18"/>
-      <c r="CW1" s="18"/>
-      <c r="CX1" s="18"/>
-      <c r="CY1" s="18"/>
-      <c r="CZ1" s="18"/>
-      <c r="DB1" s="29" t="s">
+      <c r="CV1" s="19"/>
+      <c r="CW1" s="19"/>
+      <c r="CX1" s="19"/>
+      <c r="CY1" s="19"/>
+      <c r="CZ1" s="19"/>
+      <c r="DB1" s="31" t="s">
         <v>196</v>
       </c>
-      <c r="DC1" s="18"/>
-      <c r="DD1" s="18"/>
-      <c r="DE1" s="18"/>
-      <c r="DF1" s="18"/>
-      <c r="DG1" s="18"/>
-      <c r="DI1" s="29" t="s">
+      <c r="DC1" s="19"/>
+      <c r="DD1" s="19"/>
+      <c r="DE1" s="19"/>
+      <c r="DF1" s="19"/>
+      <c r="DG1" s="19"/>
+      <c r="DI1" s="31" t="s">
         <v>197</v>
       </c>
-      <c r="DJ1" s="18"/>
-      <c r="DK1" s="18"/>
-      <c r="DL1" s="18"/>
-      <c r="DM1" s="18"/>
-      <c r="DN1" s="18"/>
-      <c r="DP1" s="29" t="s">
+      <c r="DJ1" s="19"/>
+      <c r="DK1" s="19"/>
+      <c r="DL1" s="19"/>
+      <c r="DM1" s="19"/>
+      <c r="DN1" s="19"/>
+      <c r="DP1" s="31" t="s">
         <v>198</v>
       </c>
-      <c r="DQ1" s="18"/>
-      <c r="DR1" s="18"/>
-      <c r="DS1" s="18"/>
-      <c r="DT1" s="18"/>
-      <c r="DU1" s="18"/>
-      <c r="DW1" s="29" t="s">
+      <c r="DQ1" s="19"/>
+      <c r="DR1" s="19"/>
+      <c r="DS1" s="19"/>
+      <c r="DT1" s="19"/>
+      <c r="DU1" s="19"/>
+      <c r="DW1" s="31" t="s">
         <v>310</v>
       </c>
-      <c r="DX1" s="18"/>
-      <c r="DY1" s="18"/>
-      <c r="DZ1" s="18"/>
-      <c r="EA1" s="18"/>
-      <c r="EB1" s="18"/>
-      <c r="ED1" s="29" t="s">
+      <c r="DX1" s="19"/>
+      <c r="DY1" s="19"/>
+      <c r="DZ1" s="19"/>
+      <c r="EA1" s="19"/>
+      <c r="EB1" s="19"/>
+      <c r="ED1" s="31" t="s">
         <v>199</v>
       </c>
-      <c r="EE1" s="18"/>
-      <c r="EF1" s="18"/>
-      <c r="EG1" s="18"/>
-      <c r="EH1" s="18"/>
-      <c r="EI1" s="18"/>
-      <c r="EK1" s="29" t="s">
+      <c r="EE1" s="19"/>
+      <c r="EF1" s="19"/>
+      <c r="EG1" s="19"/>
+      <c r="EH1" s="19"/>
+      <c r="EI1" s="19"/>
+      <c r="EK1" s="31" t="s">
         <v>200</v>
       </c>
-      <c r="EL1" s="18"/>
-      <c r="EM1" s="18"/>
-      <c r="EN1" s="18"/>
-      <c r="EO1" s="18"/>
-      <c r="EP1" s="18"/>
-      <c r="ER1" s="29" t="s">
+      <c r="EL1" s="19"/>
+      <c r="EM1" s="19"/>
+      <c r="EN1" s="19"/>
+      <c r="EO1" s="19"/>
+      <c r="EP1" s="19"/>
+      <c r="ER1" s="31" t="s">
         <v>201</v>
       </c>
-      <c r="ES1" s="18"/>
-      <c r="ET1" s="18"/>
-      <c r="EU1" s="18"/>
-      <c r="EV1" s="18"/>
-      <c r="EW1" s="18"/>
-      <c r="EY1" s="29" t="s">
+      <c r="ES1" s="19"/>
+      <c r="ET1" s="19"/>
+      <c r="EU1" s="19"/>
+      <c r="EV1" s="19"/>
+      <c r="EW1" s="19"/>
+      <c r="EY1" s="31" t="s">
         <v>202</v>
       </c>
-      <c r="EZ1" s="18"/>
-      <c r="FA1" s="18"/>
-      <c r="FB1" s="18"/>
-      <c r="FC1" s="18"/>
-      <c r="FD1" s="18"/>
-    </row>
-    <row r="2" spans="1:160" x14ac:dyDescent="0.35">
+      <c r="EZ1" s="19"/>
+      <c r="FA1" s="19"/>
+      <c r="FB1" s="19"/>
+      <c r="FC1" s="19"/>
+      <c r="FD1" s="19"/>
+    </row>
+    <row r="2" spans="1:160" x14ac:dyDescent="0.25">
       <c r="A2" s="16" t="s">
         <v>10</v>
       </c>
@@ -6010,7 +6040,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="3" spans="1:160" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:160" x14ac:dyDescent="0.25">
       <c r="A3" s="16" t="s">
         <v>11</v>
       </c>
@@ -6104,7 +6134,7 @@
       </c>
       <c r="EZ3" s="16"/>
     </row>
-    <row r="4" spans="1:160" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:160" x14ac:dyDescent="0.25">
       <c r="A4" s="16" t="s">
         <v>12</v>
       </c>
@@ -6267,7 +6297,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:160" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:160" x14ac:dyDescent="0.25">
       <c r="A5" s="16" t="s">
         <v>13</v>
       </c>
@@ -6430,471 +6460,471 @@
         <v>Pass</v>
       </c>
     </row>
-    <row r="6" spans="1:160" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:160" x14ac:dyDescent="0.25">
       <c r="A6" s="16" t="s">
         <v>57</v>
       </c>
       <c r="B6" s="30" t="s">
         <v>203</v>
       </c>
-      <c r="C6" s="18"/>
-      <c r="D6" s="18"/>
-      <c r="E6" s="18"/>
-      <c r="F6" s="18"/>
+      <c r="C6" s="19"/>
+      <c r="D6" s="19"/>
+      <c r="E6" s="19"/>
+      <c r="F6" s="19"/>
       <c r="H6" s="16" t="s">
         <v>57</v>
       </c>
       <c r="I6" s="30" t="s">
         <v>204</v>
       </c>
-      <c r="J6" s="18"/>
-      <c r="K6" s="18"/>
-      <c r="L6" s="18"/>
-      <c r="M6" s="18"/>
+      <c r="J6" s="19"/>
+      <c r="K6" s="19"/>
+      <c r="L6" s="19"/>
+      <c r="M6" s="19"/>
       <c r="O6" s="16" t="s">
         <v>57</v>
       </c>
       <c r="P6" s="30" t="s">
         <v>205</v>
       </c>
-      <c r="Q6" s="18"/>
-      <c r="R6" s="18"/>
-      <c r="S6" s="18"/>
-      <c r="T6" s="18"/>
+      <c r="Q6" s="19"/>
+      <c r="R6" s="19"/>
+      <c r="S6" s="19"/>
+      <c r="T6" s="19"/>
       <c r="V6" s="16" t="s">
         <v>57</v>
       </c>
       <c r="W6" s="30" t="s">
         <v>206</v>
       </c>
-      <c r="X6" s="18"/>
-      <c r="Y6" s="18"/>
-      <c r="Z6" s="18"/>
-      <c r="AA6" s="18"/>
+      <c r="X6" s="19"/>
+      <c r="Y6" s="19"/>
+      <c r="Z6" s="19"/>
+      <c r="AA6" s="19"/>
       <c r="AC6" s="16" t="s">
         <v>57</v>
       </c>
       <c r="AD6" s="30" t="s">
         <v>207</v>
       </c>
-      <c r="AE6" s="18"/>
-      <c r="AF6" s="18"/>
-      <c r="AG6" s="18"/>
-      <c r="AH6" s="18"/>
+      <c r="AE6" s="19"/>
+      <c r="AF6" s="19"/>
+      <c r="AG6" s="19"/>
+      <c r="AH6" s="19"/>
       <c r="AJ6" s="16" t="s">
         <v>57</v>
       </c>
       <c r="AK6" s="30" t="s">
         <v>208</v>
       </c>
-      <c r="AL6" s="18"/>
-      <c r="AM6" s="18"/>
-      <c r="AN6" s="18"/>
-      <c r="AO6" s="18"/>
+      <c r="AL6" s="19"/>
+      <c r="AM6" s="19"/>
+      <c r="AN6" s="19"/>
+      <c r="AO6" s="19"/>
       <c r="AQ6" s="16" t="s">
         <v>57</v>
       </c>
       <c r="AR6" s="30" t="s">
         <v>209</v>
       </c>
-      <c r="AS6" s="18"/>
-      <c r="AT6" s="18"/>
-      <c r="AU6" s="18"/>
-      <c r="AV6" s="18"/>
+      <c r="AS6" s="19"/>
+      <c r="AT6" s="19"/>
+      <c r="AU6" s="19"/>
+      <c r="AV6" s="19"/>
       <c r="AX6" s="16" t="s">
         <v>57</v>
       </c>
       <c r="AY6" s="30" t="s">
         <v>210</v>
       </c>
-      <c r="AZ6" s="18"/>
-      <c r="BA6" s="18"/>
-      <c r="BB6" s="18"/>
-      <c r="BC6" s="18"/>
+      <c r="AZ6" s="19"/>
+      <c r="BA6" s="19"/>
+      <c r="BB6" s="19"/>
+      <c r="BC6" s="19"/>
       <c r="BE6" s="16" t="s">
         <v>57</v>
       </c>
       <c r="BF6" s="30" t="s">
         <v>211</v>
       </c>
-      <c r="BG6" s="18"/>
-      <c r="BH6" s="18"/>
-      <c r="BI6" s="18"/>
-      <c r="BJ6" s="18"/>
+      <c r="BG6" s="19"/>
+      <c r="BH6" s="19"/>
+      <c r="BI6" s="19"/>
+      <c r="BJ6" s="19"/>
       <c r="BL6" s="16" t="s">
         <v>57</v>
       </c>
       <c r="BM6" s="30" t="s">
         <v>212</v>
       </c>
-      <c r="BN6" s="18"/>
-      <c r="BO6" s="18"/>
-      <c r="BP6" s="18"/>
-      <c r="BQ6" s="18"/>
+      <c r="BN6" s="19"/>
+      <c r="BO6" s="19"/>
+      <c r="BP6" s="19"/>
+      <c r="BQ6" s="19"/>
       <c r="BS6" s="16" t="s">
         <v>57</v>
       </c>
       <c r="BT6" s="30" t="s">
         <v>213</v>
       </c>
-      <c r="BU6" s="18"/>
-      <c r="BV6" s="18"/>
-      <c r="BW6" s="18"/>
-      <c r="BX6" s="18"/>
+      <c r="BU6" s="19"/>
+      <c r="BV6" s="19"/>
+      <c r="BW6" s="19"/>
+      <c r="BX6" s="19"/>
       <c r="BZ6" s="16" t="s">
         <v>57</v>
       </c>
       <c r="CA6" s="30" t="s">
         <v>214</v>
       </c>
-      <c r="CB6" s="18"/>
-      <c r="CC6" s="18"/>
-      <c r="CD6" s="18"/>
-      <c r="CE6" s="18"/>
+      <c r="CB6" s="19"/>
+      <c r="CC6" s="19"/>
+      <c r="CD6" s="19"/>
+      <c r="CE6" s="19"/>
       <c r="CG6" s="16" t="s">
         <v>57</v>
       </c>
       <c r="CH6" s="30" t="s">
         <v>215</v>
       </c>
-      <c r="CI6" s="18"/>
-      <c r="CJ6" s="18"/>
-      <c r="CK6" s="18"/>
-      <c r="CL6" s="18"/>
+      <c r="CI6" s="19"/>
+      <c r="CJ6" s="19"/>
+      <c r="CK6" s="19"/>
+      <c r="CL6" s="19"/>
       <c r="CN6" s="16" t="s">
         <v>57</v>
       </c>
       <c r="CO6" s="30" t="s">
         <v>216</v>
       </c>
-      <c r="CP6" s="18"/>
-      <c r="CQ6" s="18"/>
-      <c r="CR6" s="18"/>
-      <c r="CS6" s="18"/>
+      <c r="CP6" s="19"/>
+      <c r="CQ6" s="19"/>
+      <c r="CR6" s="19"/>
+      <c r="CS6" s="19"/>
       <c r="CU6" s="16" t="s">
         <v>57</v>
       </c>
       <c r="CV6" s="30" t="s">
         <v>217</v>
       </c>
-      <c r="CW6" s="18"/>
-      <c r="CX6" s="18"/>
-      <c r="CY6" s="18"/>
-      <c r="CZ6" s="18"/>
+      <c r="CW6" s="19"/>
+      <c r="CX6" s="19"/>
+      <c r="CY6" s="19"/>
+      <c r="CZ6" s="19"/>
       <c r="DB6" s="16" t="s">
         <v>57</v>
       </c>
       <c r="DC6" s="30" t="s">
         <v>218</v>
       </c>
-      <c r="DD6" s="18"/>
-      <c r="DE6" s="18"/>
-      <c r="DF6" s="18"/>
-      <c r="DG6" s="18"/>
+      <c r="DD6" s="19"/>
+      <c r="DE6" s="19"/>
+      <c r="DF6" s="19"/>
+      <c r="DG6" s="19"/>
       <c r="DI6" s="16" t="s">
         <v>57</v>
       </c>
       <c r="DJ6" s="30" t="s">
         <v>219</v>
       </c>
-      <c r="DK6" s="18"/>
-      <c r="DL6" s="18"/>
-      <c r="DM6" s="18"/>
-      <c r="DN6" s="18"/>
+      <c r="DK6" s="19"/>
+      <c r="DL6" s="19"/>
+      <c r="DM6" s="19"/>
+      <c r="DN6" s="19"/>
       <c r="DP6" s="16" t="s">
         <v>57</v>
       </c>
       <c r="DQ6" s="30" t="s">
         <v>220</v>
       </c>
-      <c r="DR6" s="18"/>
-      <c r="DS6" s="18"/>
-      <c r="DT6" s="18"/>
-      <c r="DU6" s="18"/>
+      <c r="DR6" s="19"/>
+      <c r="DS6" s="19"/>
+      <c r="DT6" s="19"/>
+      <c r="DU6" s="19"/>
       <c r="DW6" s="16" t="s">
         <v>57</v>
       </c>
       <c r="DX6" s="30" t="s">
         <v>221</v>
       </c>
-      <c r="DY6" s="18"/>
-      <c r="DZ6" s="18"/>
-      <c r="EA6" s="18"/>
-      <c r="EB6" s="18"/>
+      <c r="DY6" s="19"/>
+      <c r="DZ6" s="19"/>
+      <c r="EA6" s="19"/>
+      <c r="EB6" s="19"/>
       <c r="ED6" s="16" t="s">
         <v>57</v>
       </c>
       <c r="EE6" s="30" t="s">
         <v>222</v>
       </c>
-      <c r="EF6" s="18"/>
-      <c r="EG6" s="18"/>
-      <c r="EH6" s="18"/>
-      <c r="EI6" s="18"/>
+      <c r="EF6" s="19"/>
+      <c r="EG6" s="19"/>
+      <c r="EH6" s="19"/>
+      <c r="EI6" s="19"/>
       <c r="EK6" s="16" t="s">
         <v>57</v>
       </c>
       <c r="EL6" s="30" t="s">
         <v>223</v>
       </c>
-      <c r="EM6" s="18"/>
-      <c r="EN6" s="18"/>
-      <c r="EO6" s="18"/>
-      <c r="EP6" s="18"/>
+      <c r="EM6" s="19"/>
+      <c r="EN6" s="19"/>
+      <c r="EO6" s="19"/>
+      <c r="EP6" s="19"/>
       <c r="ER6" s="16" t="s">
         <v>57</v>
       </c>
       <c r="ES6" s="30" t="s">
         <v>224</v>
       </c>
-      <c r="ET6" s="18"/>
-      <c r="EU6" s="18"/>
-      <c r="EV6" s="18"/>
-      <c r="EW6" s="18"/>
+      <c r="ET6" s="19"/>
+      <c r="EU6" s="19"/>
+      <c r="EV6" s="19"/>
+      <c r="EW6" s="19"/>
       <c r="EY6" s="16" t="s">
         <v>57</v>
       </c>
       <c r="EZ6" s="30" t="s">
         <v>225</v>
       </c>
-      <c r="FA6" s="18"/>
-      <c r="FB6" s="18"/>
-      <c r="FC6" s="18"/>
-      <c r="FD6" s="18"/>
-    </row>
-    <row r="7" spans="1:160" x14ac:dyDescent="0.35">
+      <c r="FA6" s="19"/>
+      <c r="FB6" s="19"/>
+      <c r="FC6" s="19"/>
+      <c r="FD6" s="19"/>
+    </row>
+    <row r="7" spans="1:160" x14ac:dyDescent="0.25">
       <c r="A7" s="16" t="s">
         <v>15</v>
       </c>
       <c r="B7" s="30" t="s">
         <v>226</v>
       </c>
-      <c r="C7" s="18"/>
-      <c r="D7" s="18"/>
-      <c r="E7" s="18"/>
-      <c r="F7" s="18"/>
+      <c r="C7" s="19"/>
+      <c r="D7" s="19"/>
+      <c r="E7" s="19"/>
+      <c r="F7" s="19"/>
       <c r="H7" s="16" t="s">
         <v>15</v>
       </c>
       <c r="I7" s="30" t="s">
         <v>226</v>
       </c>
-      <c r="J7" s="18"/>
-      <c r="K7" s="18"/>
-      <c r="L7" s="18"/>
-      <c r="M7" s="18"/>
+      <c r="J7" s="19"/>
+      <c r="K7" s="19"/>
+      <c r="L7" s="19"/>
+      <c r="M7" s="19"/>
       <c r="O7" s="16" t="s">
         <v>15</v>
       </c>
       <c r="P7" s="30" t="s">
         <v>226</v>
       </c>
-      <c r="Q7" s="18"/>
-      <c r="R7" s="18"/>
-      <c r="S7" s="18"/>
-      <c r="T7" s="18"/>
+      <c r="Q7" s="19"/>
+      <c r="R7" s="19"/>
+      <c r="S7" s="19"/>
+      <c r="T7" s="19"/>
       <c r="V7" s="16" t="s">
         <v>15</v>
       </c>
       <c r="W7" s="30" t="s">
         <v>226</v>
       </c>
-      <c r="X7" s="18"/>
-      <c r="Y7" s="18"/>
-      <c r="Z7" s="18"/>
-      <c r="AA7" s="18"/>
+      <c r="X7" s="19"/>
+      <c r="Y7" s="19"/>
+      <c r="Z7" s="19"/>
+      <c r="AA7" s="19"/>
       <c r="AC7" s="16" t="s">
         <v>15</v>
       </c>
       <c r="AD7" s="30" t="s">
         <v>226</v>
       </c>
-      <c r="AE7" s="18"/>
-      <c r="AF7" s="18"/>
-      <c r="AG7" s="18"/>
-      <c r="AH7" s="18"/>
+      <c r="AE7" s="19"/>
+      <c r="AF7" s="19"/>
+      <c r="AG7" s="19"/>
+      <c r="AH7" s="19"/>
       <c r="AJ7" s="16" t="s">
         <v>15</v>
       </c>
       <c r="AK7" s="30" t="s">
         <v>226</v>
       </c>
-      <c r="AL7" s="18"/>
-      <c r="AM7" s="18"/>
-      <c r="AN7" s="18"/>
-      <c r="AO7" s="18"/>
+      <c r="AL7" s="19"/>
+      <c r="AM7" s="19"/>
+      <c r="AN7" s="19"/>
+      <c r="AO7" s="19"/>
       <c r="AQ7" s="16" t="s">
         <v>15</v>
       </c>
       <c r="AR7" s="30" t="s">
         <v>226</v>
       </c>
-      <c r="AS7" s="18"/>
-      <c r="AT7" s="18"/>
-      <c r="AU7" s="18"/>
-      <c r="AV7" s="18"/>
+      <c r="AS7" s="19"/>
+      <c r="AT7" s="19"/>
+      <c r="AU7" s="19"/>
+      <c r="AV7" s="19"/>
       <c r="AX7" s="16" t="s">
         <v>15</v>
       </c>
       <c r="AY7" s="30" t="s">
         <v>226</v>
       </c>
-      <c r="AZ7" s="18"/>
-      <c r="BA7" s="18"/>
-      <c r="BB7" s="18"/>
-      <c r="BC7" s="18"/>
+      <c r="AZ7" s="19"/>
+      <c r="BA7" s="19"/>
+      <c r="BB7" s="19"/>
+      <c r="BC7" s="19"/>
       <c r="BE7" s="16" t="s">
         <v>15</v>
       </c>
       <c r="BF7" s="30" t="s">
         <v>226</v>
       </c>
-      <c r="BG7" s="18"/>
-      <c r="BH7" s="18"/>
-      <c r="BI7" s="18"/>
-      <c r="BJ7" s="18"/>
+      <c r="BG7" s="19"/>
+      <c r="BH7" s="19"/>
+      <c r="BI7" s="19"/>
+      <c r="BJ7" s="19"/>
       <c r="BL7" s="16" t="s">
         <v>15</v>
       </c>
       <c r="BM7" s="30" t="s">
         <v>226</v>
       </c>
-      <c r="BN7" s="18"/>
-      <c r="BO7" s="18"/>
-      <c r="BP7" s="18"/>
-      <c r="BQ7" s="18"/>
+      <c r="BN7" s="19"/>
+      <c r="BO7" s="19"/>
+      <c r="BP7" s="19"/>
+      <c r="BQ7" s="19"/>
       <c r="BS7" s="16" t="s">
         <v>15</v>
       </c>
       <c r="BT7" s="30" t="s">
         <v>226</v>
       </c>
-      <c r="BU7" s="18"/>
-      <c r="BV7" s="18"/>
-      <c r="BW7" s="18"/>
-      <c r="BX7" s="18"/>
+      <c r="BU7" s="19"/>
+      <c r="BV7" s="19"/>
+      <c r="BW7" s="19"/>
+      <c r="BX7" s="19"/>
       <c r="BZ7" s="16" t="s">
         <v>15</v>
       </c>
       <c r="CA7" s="30" t="s">
         <v>226</v>
       </c>
-      <c r="CB7" s="18"/>
-      <c r="CC7" s="18"/>
-      <c r="CD7" s="18"/>
-      <c r="CE7" s="18"/>
+      <c r="CB7" s="19"/>
+      <c r="CC7" s="19"/>
+      <c r="CD7" s="19"/>
+      <c r="CE7" s="19"/>
       <c r="CG7" s="16" t="s">
         <v>15</v>
       </c>
       <c r="CH7" s="30" t="s">
         <v>226</v>
       </c>
-      <c r="CI7" s="18"/>
-      <c r="CJ7" s="18"/>
-      <c r="CK7" s="18"/>
-      <c r="CL7" s="18"/>
+      <c r="CI7" s="19"/>
+      <c r="CJ7" s="19"/>
+      <c r="CK7" s="19"/>
+      <c r="CL7" s="19"/>
       <c r="CN7" s="16" t="s">
         <v>15</v>
       </c>
       <c r="CO7" s="30" t="s">
         <v>226</v>
       </c>
-      <c r="CP7" s="18"/>
-      <c r="CQ7" s="18"/>
-      <c r="CR7" s="18"/>
-      <c r="CS7" s="18"/>
+      <c r="CP7" s="19"/>
+      <c r="CQ7" s="19"/>
+      <c r="CR7" s="19"/>
+      <c r="CS7" s="19"/>
       <c r="CU7" s="16" t="s">
         <v>15</v>
       </c>
       <c r="CV7" s="30" t="s">
         <v>226</v>
       </c>
-      <c r="CW7" s="18"/>
-      <c r="CX7" s="18"/>
-      <c r="CY7" s="18"/>
-      <c r="CZ7" s="18"/>
+      <c r="CW7" s="19"/>
+      <c r="CX7" s="19"/>
+      <c r="CY7" s="19"/>
+      <c r="CZ7" s="19"/>
       <c r="DB7" s="16" t="s">
         <v>15</v>
       </c>
       <c r="DC7" s="30" t="s">
         <v>226</v>
       </c>
-      <c r="DD7" s="18"/>
-      <c r="DE7" s="18"/>
-      <c r="DF7" s="18"/>
-      <c r="DG7" s="18"/>
+      <c r="DD7" s="19"/>
+      <c r="DE7" s="19"/>
+      <c r="DF7" s="19"/>
+      <c r="DG7" s="19"/>
       <c r="DI7" s="16" t="s">
         <v>15</v>
       </c>
       <c r="DJ7" s="30" t="s">
         <v>226</v>
       </c>
-      <c r="DK7" s="18"/>
-      <c r="DL7" s="18"/>
-      <c r="DM7" s="18"/>
-      <c r="DN7" s="18"/>
+      <c r="DK7" s="19"/>
+      <c r="DL7" s="19"/>
+      <c r="DM7" s="19"/>
+      <c r="DN7" s="19"/>
       <c r="DP7" s="16" t="s">
         <v>15</v>
       </c>
       <c r="DQ7" s="30" t="s">
         <v>226</v>
       </c>
-      <c r="DR7" s="18"/>
-      <c r="DS7" s="18"/>
-      <c r="DT7" s="18"/>
-      <c r="DU7" s="18"/>
+      <c r="DR7" s="19"/>
+      <c r="DS7" s="19"/>
+      <c r="DT7" s="19"/>
+      <c r="DU7" s="19"/>
       <c r="DW7" s="16" t="s">
         <v>15</v>
       </c>
       <c r="DX7" s="30" t="s">
         <v>226</v>
       </c>
-      <c r="DY7" s="18"/>
-      <c r="DZ7" s="18"/>
-      <c r="EA7" s="18"/>
-      <c r="EB7" s="18"/>
+      <c r="DY7" s="19"/>
+      <c r="DZ7" s="19"/>
+      <c r="EA7" s="19"/>
+      <c r="EB7" s="19"/>
       <c r="ED7" s="16" t="s">
         <v>15</v>
       </c>
       <c r="EE7" s="30" t="s">
         <v>226</v>
       </c>
-      <c r="EF7" s="18"/>
-      <c r="EG7" s="18"/>
-      <c r="EH7" s="18"/>
-      <c r="EI7" s="18"/>
+      <c r="EF7" s="19"/>
+      <c r="EG7" s="19"/>
+      <c r="EH7" s="19"/>
+      <c r="EI7" s="19"/>
       <c r="EK7" s="16" t="s">
         <v>15</v>
       </c>
       <c r="EL7" s="30" t="s">
         <v>226</v>
       </c>
-      <c r="EM7" s="18"/>
-      <c r="EN7" s="18"/>
-      <c r="EO7" s="18"/>
-      <c r="EP7" s="18"/>
+      <c r="EM7" s="19"/>
+      <c r="EN7" s="19"/>
+      <c r="EO7" s="19"/>
+      <c r="EP7" s="19"/>
       <c r="ER7" s="16" t="s">
         <v>15</v>
       </c>
       <c r="ES7" s="30" t="s">
         <v>226</v>
       </c>
-      <c r="ET7" s="18"/>
-      <c r="EU7" s="18"/>
-      <c r="EV7" s="18"/>
-      <c r="EW7" s="18"/>
+      <c r="ET7" s="19"/>
+      <c r="EU7" s="19"/>
+      <c r="EV7" s="19"/>
+      <c r="EW7" s="19"/>
       <c r="EY7" s="16" t="s">
         <v>15</v>
       </c>
       <c r="EZ7" s="30" t="s">
         <v>226</v>
       </c>
-      <c r="FA7" s="18"/>
-      <c r="FB7" s="18"/>
-      <c r="FC7" s="18"/>
-      <c r="FD7" s="18"/>
-    </row>
-    <row r="8" spans="1:160" x14ac:dyDescent="0.35">
+      <c r="FA7" s="19"/>
+      <c r="FB7" s="19"/>
+      <c r="FC7" s="19"/>
+      <c r="FD7" s="19"/>
+    </row>
+    <row r="8" spans="1:160" x14ac:dyDescent="0.25">
       <c r="A8" s="16" t="s">
         <v>16</v>
       </c>
@@ -7310,7 +7340,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="9" spans="1:160" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:160" ht="29.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="16" t="s">
         <v>227</v>
       </c>
@@ -7634,7 +7664,7 @@
       <c r="FC9" s="16"/>
       <c r="FD9" s="16"/>
     </row>
-    <row r="10" spans="1:160" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:160" ht="29.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="16" t="s">
         <v>231</v>
       </c>
@@ -7912,7 +7942,7 @@
       <c r="FC10" s="16"/>
       <c r="FD10" s="16"/>
     </row>
-    <row r="11" spans="1:160" ht="43.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:160" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="16" t="s">
         <v>246</v>
       </c>
@@ -8192,38 +8222,27 @@
     </row>
   </sheetData>
   <mergeCells count="69">
-    <mergeCell ref="EL7:EP7"/>
-    <mergeCell ref="AD7:AH7"/>
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="BL1:BQ1"/>
-    <mergeCell ref="AY7:BC7"/>
-    <mergeCell ref="CU1:CZ1"/>
-    <mergeCell ref="CH7:CL7"/>
-    <mergeCell ref="AY6:BC6"/>
-    <mergeCell ref="BT6:BX6"/>
-    <mergeCell ref="EK1:EP1"/>
-    <mergeCell ref="EZ6:FD6"/>
-    <mergeCell ref="H1:M1"/>
-    <mergeCell ref="B6:F6"/>
-    <mergeCell ref="AX1:BC1"/>
-    <mergeCell ref="AK6:AO6"/>
-    <mergeCell ref="DJ6:DN6"/>
-    <mergeCell ref="ES6:EW6"/>
-    <mergeCell ref="ED1:EI1"/>
-    <mergeCell ref="W7:AA7"/>
-    <mergeCell ref="AJ1:AO1"/>
-    <mergeCell ref="P7:T7"/>
-    <mergeCell ref="CA7:CE7"/>
-    <mergeCell ref="AR6:AV6"/>
-    <mergeCell ref="CN1:CS1"/>
-    <mergeCell ref="DC6:DG6"/>
-    <mergeCell ref="EE7:EI7"/>
-    <mergeCell ref="DB1:DG1"/>
-    <mergeCell ref="CV6:CZ6"/>
-    <mergeCell ref="CO7:CS7"/>
-    <mergeCell ref="ER1:EW1"/>
-    <mergeCell ref="DX7:EB7"/>
-    <mergeCell ref="EL6:EP6"/>
+    <mergeCell ref="EY1:FD1"/>
+    <mergeCell ref="V1:AA1"/>
+    <mergeCell ref="DX6:EB6"/>
+    <mergeCell ref="B7:F7"/>
+    <mergeCell ref="BE1:BJ1"/>
+    <mergeCell ref="AR7:AV7"/>
+    <mergeCell ref="O1:T1"/>
+    <mergeCell ref="EZ7:FD7"/>
+    <mergeCell ref="I6:M6"/>
+    <mergeCell ref="AK7:AO7"/>
+    <mergeCell ref="W6:AA6"/>
+    <mergeCell ref="CV7:CZ7"/>
+    <mergeCell ref="BS1:BX1"/>
+    <mergeCell ref="DI1:DN1"/>
+    <mergeCell ref="BF7:BJ7"/>
+    <mergeCell ref="BM6:BQ6"/>
+    <mergeCell ref="CH6:CL6"/>
+    <mergeCell ref="BF6:BJ6"/>
+    <mergeCell ref="DW1:EB1"/>
+    <mergeCell ref="DQ6:DU6"/>
+    <mergeCell ref="DJ7:DN7"/>
     <mergeCell ref="ES7:EW7"/>
     <mergeCell ref="AC1:AH1"/>
     <mergeCell ref="EE6:EI6"/>
@@ -8240,27 +8259,38 @@
     <mergeCell ref="CO6:CS6"/>
     <mergeCell ref="DP1:DU1"/>
     <mergeCell ref="DQ7:DU7"/>
-    <mergeCell ref="CH6:CL6"/>
-    <mergeCell ref="BF6:BJ6"/>
-    <mergeCell ref="DW1:EB1"/>
-    <mergeCell ref="DQ6:DU6"/>
-    <mergeCell ref="DJ7:DN7"/>
-    <mergeCell ref="EY1:FD1"/>
-    <mergeCell ref="V1:AA1"/>
-    <mergeCell ref="DX6:EB6"/>
-    <mergeCell ref="B7:F7"/>
-    <mergeCell ref="BE1:BJ1"/>
-    <mergeCell ref="AR7:AV7"/>
-    <mergeCell ref="O1:T1"/>
-    <mergeCell ref="EZ7:FD7"/>
-    <mergeCell ref="I6:M6"/>
-    <mergeCell ref="AK7:AO7"/>
-    <mergeCell ref="W6:AA6"/>
-    <mergeCell ref="CV7:CZ7"/>
-    <mergeCell ref="BS1:BX1"/>
-    <mergeCell ref="DI1:DN1"/>
-    <mergeCell ref="BF7:BJ7"/>
-    <mergeCell ref="BM6:BQ6"/>
+    <mergeCell ref="EZ6:FD6"/>
+    <mergeCell ref="H1:M1"/>
+    <mergeCell ref="B6:F6"/>
+    <mergeCell ref="AX1:BC1"/>
+    <mergeCell ref="AK6:AO6"/>
+    <mergeCell ref="DJ6:DN6"/>
+    <mergeCell ref="ES6:EW6"/>
+    <mergeCell ref="ED1:EI1"/>
+    <mergeCell ref="AJ1:AO1"/>
+    <mergeCell ref="AR6:AV6"/>
+    <mergeCell ref="CN1:CS1"/>
+    <mergeCell ref="DC6:DG6"/>
+    <mergeCell ref="DB1:DG1"/>
+    <mergeCell ref="CV6:CZ6"/>
+    <mergeCell ref="ER1:EW1"/>
+    <mergeCell ref="EL6:EP6"/>
+    <mergeCell ref="EL7:EP7"/>
+    <mergeCell ref="AD7:AH7"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="BL1:BQ1"/>
+    <mergeCell ref="AY7:BC7"/>
+    <mergeCell ref="CU1:CZ1"/>
+    <mergeCell ref="CH7:CL7"/>
+    <mergeCell ref="AY6:BC6"/>
+    <mergeCell ref="BT6:BX6"/>
+    <mergeCell ref="EK1:EP1"/>
+    <mergeCell ref="W7:AA7"/>
+    <mergeCell ref="P7:T7"/>
+    <mergeCell ref="CA7:CE7"/>
+    <mergeCell ref="EE7:EI7"/>
+    <mergeCell ref="CO7:CS7"/>
+    <mergeCell ref="DX7:EB7"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -8269,7 +8299,7 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <dimension ref="A1:FD11"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="6" width="20" customWidth="1"/>
     <col min="8" max="13" width="20" customWidth="1"/>
@@ -8296,193 +8326,193 @@
     <col min="155" max="160" width="20" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:160" x14ac:dyDescent="0.35">
-      <c r="A1" s="29" t="s">
+    <row r="1" spans="1:160" x14ac:dyDescent="0.25">
+      <c r="A1" s="31" t="s">
         <v>250</v>
       </c>
-      <c r="B1" s="18"/>
-      <c r="C1" s="18"/>
-      <c r="D1" s="18"/>
-      <c r="E1" s="18"/>
-      <c r="F1" s="18"/>
-      <c r="H1" s="29" t="s">
+      <c r="B1" s="19"/>
+      <c r="C1" s="19"/>
+      <c r="D1" s="19"/>
+      <c r="E1" s="19"/>
+      <c r="F1" s="19"/>
+      <c r="H1" s="31" t="s">
         <v>251</v>
       </c>
-      <c r="I1" s="18"/>
-      <c r="J1" s="18"/>
-      <c r="K1" s="18"/>
-      <c r="L1" s="18"/>
-      <c r="M1" s="18"/>
-      <c r="O1" s="29" t="s">
+      <c r="I1" s="19"/>
+      <c r="J1" s="19"/>
+      <c r="K1" s="19"/>
+      <c r="L1" s="19"/>
+      <c r="M1" s="19"/>
+      <c r="O1" s="31" t="s">
         <v>252</v>
       </c>
-      <c r="P1" s="18"/>
-      <c r="Q1" s="18"/>
-      <c r="R1" s="18"/>
-      <c r="S1" s="18"/>
-      <c r="T1" s="18"/>
-      <c r="V1" s="29" t="s">
+      <c r="P1" s="19"/>
+      <c r="Q1" s="19"/>
+      <c r="R1" s="19"/>
+      <c r="S1" s="19"/>
+      <c r="T1" s="19"/>
+      <c r="V1" s="31" t="s">
         <v>311</v>
       </c>
-      <c r="W1" s="18"/>
-      <c r="X1" s="18"/>
-      <c r="Y1" s="18"/>
-      <c r="Z1" s="18"/>
-      <c r="AA1" s="18"/>
-      <c r="AC1" s="29" t="s">
+      <c r="W1" s="19"/>
+      <c r="X1" s="19"/>
+      <c r="Y1" s="19"/>
+      <c r="Z1" s="19"/>
+      <c r="AA1" s="19"/>
+      <c r="AC1" s="31" t="s">
         <v>253</v>
       </c>
-      <c r="AD1" s="18"/>
-      <c r="AE1" s="18"/>
-      <c r="AF1" s="18"/>
-      <c r="AG1" s="18"/>
-      <c r="AH1" s="18"/>
-      <c r="AJ1" s="29" t="s">
+      <c r="AD1" s="19"/>
+      <c r="AE1" s="19"/>
+      <c r="AF1" s="19"/>
+      <c r="AG1" s="19"/>
+      <c r="AH1" s="19"/>
+      <c r="AJ1" s="31" t="s">
         <v>254</v>
       </c>
-      <c r="AK1" s="18"/>
-      <c r="AL1" s="18"/>
-      <c r="AM1" s="18"/>
-      <c r="AN1" s="18"/>
-      <c r="AO1" s="18"/>
-      <c r="AQ1" s="29" t="s">
+      <c r="AK1" s="19"/>
+      <c r="AL1" s="19"/>
+      <c r="AM1" s="19"/>
+      <c r="AN1" s="19"/>
+      <c r="AO1" s="19"/>
+      <c r="AQ1" s="31" t="s">
         <v>255</v>
       </c>
-      <c r="AR1" s="18"/>
-      <c r="AS1" s="18"/>
-      <c r="AT1" s="18"/>
-      <c r="AU1" s="18"/>
-      <c r="AV1" s="18"/>
-      <c r="AX1" s="29" t="s">
+      <c r="AR1" s="19"/>
+      <c r="AS1" s="19"/>
+      <c r="AT1" s="19"/>
+      <c r="AU1" s="19"/>
+      <c r="AV1" s="19"/>
+      <c r="AX1" s="31" t="s">
         <v>256</v>
       </c>
-      <c r="AY1" s="18"/>
-      <c r="AZ1" s="18"/>
-      <c r="BA1" s="18"/>
-      <c r="BB1" s="18"/>
-      <c r="BC1" s="18"/>
-      <c r="BE1" s="29" t="s">
+      <c r="AY1" s="19"/>
+      <c r="AZ1" s="19"/>
+      <c r="BA1" s="19"/>
+      <c r="BB1" s="19"/>
+      <c r="BC1" s="19"/>
+      <c r="BE1" s="31" t="s">
         <v>257</v>
       </c>
-      <c r="BF1" s="18"/>
-      <c r="BG1" s="18"/>
-      <c r="BH1" s="18"/>
-      <c r="BI1" s="18"/>
-      <c r="BJ1" s="18"/>
-      <c r="BL1" s="29" t="s">
+      <c r="BF1" s="19"/>
+      <c r="BG1" s="19"/>
+      <c r="BH1" s="19"/>
+      <c r="BI1" s="19"/>
+      <c r="BJ1" s="19"/>
+      <c r="BL1" s="31" t="s">
         <v>258</v>
       </c>
-      <c r="BM1" s="18"/>
-      <c r="BN1" s="18"/>
-      <c r="BO1" s="18"/>
-      <c r="BP1" s="18"/>
-      <c r="BQ1" s="18"/>
-      <c r="BS1" s="29" t="s">
+      <c r="BM1" s="19"/>
+      <c r="BN1" s="19"/>
+      <c r="BO1" s="19"/>
+      <c r="BP1" s="19"/>
+      <c r="BQ1" s="19"/>
+      <c r="BS1" s="31" t="s">
         <v>312</v>
       </c>
-      <c r="BT1" s="18"/>
-      <c r="BU1" s="18"/>
-      <c r="BV1" s="18"/>
-      <c r="BW1" s="18"/>
-      <c r="BX1" s="18"/>
-      <c r="BZ1" s="29" t="s">
+      <c r="BT1" s="19"/>
+      <c r="BU1" s="19"/>
+      <c r="BV1" s="19"/>
+      <c r="BW1" s="19"/>
+      <c r="BX1" s="19"/>
+      <c r="BZ1" s="31" t="s">
         <v>259</v>
       </c>
-      <c r="CA1" s="18"/>
-      <c r="CB1" s="18"/>
-      <c r="CC1" s="18"/>
-      <c r="CD1" s="18"/>
-      <c r="CE1" s="18"/>
-      <c r="CG1" s="29" t="s">
+      <c r="CA1" s="19"/>
+      <c r="CB1" s="19"/>
+      <c r="CC1" s="19"/>
+      <c r="CD1" s="19"/>
+      <c r="CE1" s="19"/>
+      <c r="CG1" s="31" t="s">
         <v>313</v>
       </c>
-      <c r="CH1" s="18"/>
-      <c r="CI1" s="18"/>
-      <c r="CJ1" s="18"/>
-      <c r="CK1" s="18"/>
-      <c r="CL1" s="18"/>
-      <c r="CN1" s="29" t="s">
+      <c r="CH1" s="19"/>
+      <c r="CI1" s="19"/>
+      <c r="CJ1" s="19"/>
+      <c r="CK1" s="19"/>
+      <c r="CL1" s="19"/>
+      <c r="CN1" s="31" t="s">
         <v>260</v>
       </c>
-      <c r="CO1" s="18"/>
-      <c r="CP1" s="18"/>
-      <c r="CQ1" s="18"/>
-      <c r="CR1" s="18"/>
-      <c r="CS1" s="18"/>
-      <c r="CU1" s="29" t="s">
+      <c r="CO1" s="19"/>
+      <c r="CP1" s="19"/>
+      <c r="CQ1" s="19"/>
+      <c r="CR1" s="19"/>
+      <c r="CS1" s="19"/>
+      <c r="CU1" s="31" t="s">
         <v>261</v>
       </c>
-      <c r="CV1" s="18"/>
-      <c r="CW1" s="18"/>
-      <c r="CX1" s="18"/>
-      <c r="CY1" s="18"/>
-      <c r="CZ1" s="18"/>
-      <c r="DB1" s="29" t="s">
+      <c r="CV1" s="19"/>
+      <c r="CW1" s="19"/>
+      <c r="CX1" s="19"/>
+      <c r="CY1" s="19"/>
+      <c r="CZ1" s="19"/>
+      <c r="DB1" s="31" t="s">
         <v>262</v>
       </c>
-      <c r="DC1" s="18"/>
-      <c r="DD1" s="18"/>
-      <c r="DE1" s="18"/>
-      <c r="DF1" s="18"/>
-      <c r="DG1" s="18"/>
-      <c r="DI1" s="29" t="s">
+      <c r="DC1" s="19"/>
+      <c r="DD1" s="19"/>
+      <c r="DE1" s="19"/>
+      <c r="DF1" s="19"/>
+      <c r="DG1" s="19"/>
+      <c r="DI1" s="31" t="s">
         <v>263</v>
       </c>
-      <c r="DJ1" s="18"/>
-      <c r="DK1" s="18"/>
-      <c r="DL1" s="18"/>
-      <c r="DM1" s="18"/>
-      <c r="DN1" s="18"/>
-      <c r="DP1" s="29" t="s">
+      <c r="DJ1" s="19"/>
+      <c r="DK1" s="19"/>
+      <c r="DL1" s="19"/>
+      <c r="DM1" s="19"/>
+      <c r="DN1" s="19"/>
+      <c r="DP1" s="31" t="s">
         <v>314</v>
       </c>
-      <c r="DQ1" s="18"/>
-      <c r="DR1" s="18"/>
-      <c r="DS1" s="18"/>
-      <c r="DT1" s="18"/>
-      <c r="DU1" s="18"/>
-      <c r="DW1" s="29" t="s">
+      <c r="DQ1" s="19"/>
+      <c r="DR1" s="19"/>
+      <c r="DS1" s="19"/>
+      <c r="DT1" s="19"/>
+      <c r="DU1" s="19"/>
+      <c r="DW1" s="31" t="s">
         <v>264</v>
       </c>
-      <c r="DX1" s="18"/>
-      <c r="DY1" s="18"/>
-      <c r="DZ1" s="18"/>
-      <c r="EA1" s="18"/>
-      <c r="EB1" s="18"/>
-      <c r="ED1" s="29" t="s">
+      <c r="DX1" s="19"/>
+      <c r="DY1" s="19"/>
+      <c r="DZ1" s="19"/>
+      <c r="EA1" s="19"/>
+      <c r="EB1" s="19"/>
+      <c r="ED1" s="31" t="s">
         <v>265</v>
       </c>
-      <c r="EE1" s="18"/>
-      <c r="EF1" s="18"/>
-      <c r="EG1" s="18"/>
-      <c r="EH1" s="18"/>
-      <c r="EI1" s="18"/>
-      <c r="EK1" s="29" t="s">
+      <c r="EE1" s="19"/>
+      <c r="EF1" s="19"/>
+      <c r="EG1" s="19"/>
+      <c r="EH1" s="19"/>
+      <c r="EI1" s="19"/>
+      <c r="EK1" s="31" t="s">
         <v>266</v>
       </c>
-      <c r="EL1" s="18"/>
-      <c r="EM1" s="18"/>
-      <c r="EN1" s="18"/>
-      <c r="EO1" s="18"/>
-      <c r="EP1" s="18"/>
-      <c r="ER1" s="29" t="s">
+      <c r="EL1" s="19"/>
+      <c r="EM1" s="19"/>
+      <c r="EN1" s="19"/>
+      <c r="EO1" s="19"/>
+      <c r="EP1" s="19"/>
+      <c r="ER1" s="31" t="s">
         <v>267</v>
       </c>
-      <c r="ES1" s="18"/>
-      <c r="ET1" s="18"/>
-      <c r="EU1" s="18"/>
-      <c r="EV1" s="18"/>
-      <c r="EW1" s="18"/>
-      <c r="EY1" s="29" t="s">
+      <c r="ES1" s="19"/>
+      <c r="ET1" s="19"/>
+      <c r="EU1" s="19"/>
+      <c r="EV1" s="19"/>
+      <c r="EW1" s="19"/>
+      <c r="EY1" s="31" t="s">
         <v>268</v>
       </c>
-      <c r="EZ1" s="18"/>
-      <c r="FA1" s="18"/>
-      <c r="FB1" s="18"/>
-      <c r="FC1" s="18"/>
-      <c r="FD1" s="18"/>
-    </row>
-    <row r="2" spans="1:160" x14ac:dyDescent="0.35">
+      <c r="EZ1" s="19"/>
+      <c r="FA1" s="19"/>
+      <c r="FB1" s="19"/>
+      <c r="FC1" s="19"/>
+      <c r="FD1" s="19"/>
+    </row>
+    <row r="2" spans="1:160" x14ac:dyDescent="0.25">
       <c r="A2" s="16" t="s">
         <v>10</v>
       </c>
@@ -8645,7 +8675,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="3" spans="1:160" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:160" x14ac:dyDescent="0.25">
       <c r="A3" s="16" t="s">
         <v>11</v>
       </c>
@@ -8739,7 +8769,7 @@
       </c>
       <c r="EZ3" s="16"/>
     </row>
-    <row r="4" spans="1:160" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:160" x14ac:dyDescent="0.25">
       <c r="A4" s="16" t="s">
         <v>12</v>
       </c>
@@ -8902,7 +8932,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:160" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:160" x14ac:dyDescent="0.25">
       <c r="A5" s="16" t="s">
         <v>13</v>
       </c>
@@ -9065,471 +9095,471 @@
         <v>Pass</v>
       </c>
     </row>
-    <row r="6" spans="1:160" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:160" x14ac:dyDescent="0.25">
       <c r="A6" s="16" t="s">
         <v>57</v>
       </c>
       <c r="B6" s="30" t="s">
         <v>269</v>
       </c>
-      <c r="C6" s="18"/>
-      <c r="D6" s="18"/>
-      <c r="E6" s="18"/>
-      <c r="F6" s="18"/>
+      <c r="C6" s="19"/>
+      <c r="D6" s="19"/>
+      <c r="E6" s="19"/>
+      <c r="F6" s="19"/>
       <c r="H6" s="16" t="s">
         <v>57</v>
       </c>
       <c r="I6" s="30" t="s">
         <v>270</v>
       </c>
-      <c r="J6" s="18"/>
-      <c r="K6" s="18"/>
-      <c r="L6" s="18"/>
-      <c r="M6" s="18"/>
+      <c r="J6" s="19"/>
+      <c r="K6" s="19"/>
+      <c r="L6" s="19"/>
+      <c r="M6" s="19"/>
       <c r="O6" s="16" t="s">
         <v>57</v>
       </c>
       <c r="P6" s="30" t="s">
         <v>271</v>
       </c>
-      <c r="Q6" s="18"/>
-      <c r="R6" s="18"/>
-      <c r="S6" s="18"/>
-      <c r="T6" s="18"/>
+      <c r="Q6" s="19"/>
+      <c r="R6" s="19"/>
+      <c r="S6" s="19"/>
+      <c r="T6" s="19"/>
       <c r="V6" s="16" t="s">
         <v>57</v>
       </c>
       <c r="W6" s="30" t="s">
         <v>221</v>
       </c>
-      <c r="X6" s="18"/>
-      <c r="Y6" s="18"/>
-      <c r="Z6" s="18"/>
-      <c r="AA6" s="18"/>
+      <c r="X6" s="19"/>
+      <c r="Y6" s="19"/>
+      <c r="Z6" s="19"/>
+      <c r="AA6" s="19"/>
       <c r="AC6" s="16" t="s">
         <v>57</v>
       </c>
       <c r="AD6" s="30" t="s">
         <v>272</v>
       </c>
-      <c r="AE6" s="18"/>
-      <c r="AF6" s="18"/>
-      <c r="AG6" s="18"/>
-      <c r="AH6" s="18"/>
+      <c r="AE6" s="19"/>
+      <c r="AF6" s="19"/>
+      <c r="AG6" s="19"/>
+      <c r="AH6" s="19"/>
       <c r="AJ6" s="16" t="s">
         <v>57</v>
       </c>
       <c r="AK6" s="30" t="s">
         <v>273</v>
       </c>
-      <c r="AL6" s="18"/>
-      <c r="AM6" s="18"/>
-      <c r="AN6" s="18"/>
-      <c r="AO6" s="18"/>
+      <c r="AL6" s="19"/>
+      <c r="AM6" s="19"/>
+      <c r="AN6" s="19"/>
+      <c r="AO6" s="19"/>
       <c r="AQ6" s="16" t="s">
         <v>57</v>
       </c>
       <c r="AR6" s="30" t="s">
         <v>274</v>
       </c>
-      <c r="AS6" s="18"/>
-      <c r="AT6" s="18"/>
-      <c r="AU6" s="18"/>
-      <c r="AV6" s="18"/>
+      <c r="AS6" s="19"/>
+      <c r="AT6" s="19"/>
+      <c r="AU6" s="19"/>
+      <c r="AV6" s="19"/>
       <c r="AX6" s="16" t="s">
         <v>57</v>
       </c>
       <c r="AY6" s="30" t="s">
         <v>275</v>
       </c>
-      <c r="AZ6" s="18"/>
-      <c r="BA6" s="18"/>
-      <c r="BB6" s="18"/>
-      <c r="BC6" s="18"/>
+      <c r="AZ6" s="19"/>
+      <c r="BA6" s="19"/>
+      <c r="BB6" s="19"/>
+      <c r="BC6" s="19"/>
       <c r="BE6" s="16" t="s">
         <v>57</v>
       </c>
       <c r="BF6" s="30" t="s">
         <v>276</v>
       </c>
-      <c r="BG6" s="18"/>
-      <c r="BH6" s="18"/>
-      <c r="BI6" s="18"/>
-      <c r="BJ6" s="18"/>
+      <c r="BG6" s="19"/>
+      <c r="BH6" s="19"/>
+      <c r="BI6" s="19"/>
+      <c r="BJ6" s="19"/>
       <c r="BL6" s="16" t="s">
         <v>57</v>
       </c>
       <c r="BM6" s="30" t="s">
         <v>277</v>
       </c>
-      <c r="BN6" s="18"/>
-      <c r="BO6" s="18"/>
-      <c r="BP6" s="18"/>
-      <c r="BQ6" s="18"/>
+      <c r="BN6" s="19"/>
+      <c r="BO6" s="19"/>
+      <c r="BP6" s="19"/>
+      <c r="BQ6" s="19"/>
       <c r="BS6" s="16" t="s">
         <v>57</v>
       </c>
       <c r="BT6" s="30" t="s">
         <v>221</v>
       </c>
-      <c r="BU6" s="18"/>
-      <c r="BV6" s="18"/>
-      <c r="BW6" s="18"/>
-      <c r="BX6" s="18"/>
+      <c r="BU6" s="19"/>
+      <c r="BV6" s="19"/>
+      <c r="BW6" s="19"/>
+      <c r="BX6" s="19"/>
       <c r="BZ6" s="16" t="s">
         <v>57</v>
       </c>
       <c r="CA6" s="30" t="s">
         <v>278</v>
       </c>
-      <c r="CB6" s="18"/>
-      <c r="CC6" s="18"/>
-      <c r="CD6" s="18"/>
-      <c r="CE6" s="18"/>
+      <c r="CB6" s="19"/>
+      <c r="CC6" s="19"/>
+      <c r="CD6" s="19"/>
+      <c r="CE6" s="19"/>
       <c r="CG6" s="16" t="s">
         <v>57</v>
       </c>
       <c r="CH6" s="30" t="s">
         <v>221</v>
       </c>
-      <c r="CI6" s="18"/>
-      <c r="CJ6" s="18"/>
-      <c r="CK6" s="18"/>
-      <c r="CL6" s="18"/>
+      <c r="CI6" s="19"/>
+      <c r="CJ6" s="19"/>
+      <c r="CK6" s="19"/>
+      <c r="CL6" s="19"/>
       <c r="CN6" s="16" t="s">
         <v>57</v>
       </c>
       <c r="CO6" s="30" t="s">
         <v>279</v>
       </c>
-      <c r="CP6" s="18"/>
-      <c r="CQ6" s="18"/>
-      <c r="CR6" s="18"/>
-      <c r="CS6" s="18"/>
+      <c r="CP6" s="19"/>
+      <c r="CQ6" s="19"/>
+      <c r="CR6" s="19"/>
+      <c r="CS6" s="19"/>
       <c r="CU6" s="16" t="s">
         <v>57</v>
       </c>
       <c r="CV6" s="30" t="s">
         <v>280</v>
       </c>
-      <c r="CW6" s="18"/>
-      <c r="CX6" s="18"/>
-      <c r="CY6" s="18"/>
-      <c r="CZ6" s="18"/>
+      <c r="CW6" s="19"/>
+      <c r="CX6" s="19"/>
+      <c r="CY6" s="19"/>
+      <c r="CZ6" s="19"/>
       <c r="DB6" s="16" t="s">
         <v>57</v>
       </c>
       <c r="DC6" s="30" t="s">
         <v>281</v>
       </c>
-      <c r="DD6" s="18"/>
-      <c r="DE6" s="18"/>
-      <c r="DF6" s="18"/>
-      <c r="DG6" s="18"/>
+      <c r="DD6" s="19"/>
+      <c r="DE6" s="19"/>
+      <c r="DF6" s="19"/>
+      <c r="DG6" s="19"/>
       <c r="DI6" s="16" t="s">
         <v>57</v>
       </c>
       <c r="DJ6" s="30" t="s">
         <v>282</v>
       </c>
-      <c r="DK6" s="18"/>
-      <c r="DL6" s="18"/>
-      <c r="DM6" s="18"/>
-      <c r="DN6" s="18"/>
+      <c r="DK6" s="19"/>
+      <c r="DL6" s="19"/>
+      <c r="DM6" s="19"/>
+      <c r="DN6" s="19"/>
       <c r="DP6" s="16" t="s">
         <v>57</v>
       </c>
       <c r="DQ6" s="30" t="s">
         <v>221</v>
       </c>
-      <c r="DR6" s="18"/>
-      <c r="DS6" s="18"/>
-      <c r="DT6" s="18"/>
-      <c r="DU6" s="18"/>
+      <c r="DR6" s="19"/>
+      <c r="DS6" s="19"/>
+      <c r="DT6" s="19"/>
+      <c r="DU6" s="19"/>
       <c r="DW6" s="16" t="s">
         <v>57</v>
       </c>
       <c r="DX6" s="30" t="s">
         <v>283</v>
       </c>
-      <c r="DY6" s="18"/>
-      <c r="DZ6" s="18"/>
-      <c r="EA6" s="18"/>
-      <c r="EB6" s="18"/>
+      <c r="DY6" s="19"/>
+      <c r="DZ6" s="19"/>
+      <c r="EA6" s="19"/>
+      <c r="EB6" s="19"/>
       <c r="ED6" s="16" t="s">
         <v>57</v>
       </c>
       <c r="EE6" s="30" t="s">
         <v>284</v>
       </c>
-      <c r="EF6" s="18"/>
-      <c r="EG6" s="18"/>
-      <c r="EH6" s="18"/>
-      <c r="EI6" s="18"/>
+      <c r="EF6" s="19"/>
+      <c r="EG6" s="19"/>
+      <c r="EH6" s="19"/>
+      <c r="EI6" s="19"/>
       <c r="EK6" s="16" t="s">
         <v>57</v>
       </c>
       <c r="EL6" s="30" t="s">
         <v>285</v>
       </c>
-      <c r="EM6" s="18"/>
-      <c r="EN6" s="18"/>
-      <c r="EO6" s="18"/>
-      <c r="EP6" s="18"/>
+      <c r="EM6" s="19"/>
+      <c r="EN6" s="19"/>
+      <c r="EO6" s="19"/>
+      <c r="EP6" s="19"/>
       <c r="ER6" s="16" t="s">
         <v>57</v>
       </c>
       <c r="ES6" s="30" t="s">
         <v>286</v>
       </c>
-      <c r="ET6" s="18"/>
-      <c r="EU6" s="18"/>
-      <c r="EV6" s="18"/>
-      <c r="EW6" s="18"/>
+      <c r="ET6" s="19"/>
+      <c r="EU6" s="19"/>
+      <c r="EV6" s="19"/>
+      <c r="EW6" s="19"/>
       <c r="EY6" s="16" t="s">
         <v>57</v>
       </c>
       <c r="EZ6" s="30" t="s">
         <v>287</v>
       </c>
-      <c r="FA6" s="18"/>
-      <c r="FB6" s="18"/>
-      <c r="FC6" s="18"/>
-      <c r="FD6" s="18"/>
-    </row>
-    <row r="7" spans="1:160" x14ac:dyDescent="0.35">
+      <c r="FA6" s="19"/>
+      <c r="FB6" s="19"/>
+      <c r="FC6" s="19"/>
+      <c r="FD6" s="19"/>
+    </row>
+    <row r="7" spans="1:160" x14ac:dyDescent="0.25">
       <c r="A7" s="16" t="s">
         <v>15</v>
       </c>
       <c r="B7" s="30" t="s">
         <v>226</v>
       </c>
-      <c r="C7" s="18"/>
-      <c r="D7" s="18"/>
-      <c r="E7" s="18"/>
-      <c r="F7" s="18"/>
+      <c r="C7" s="19"/>
+      <c r="D7" s="19"/>
+      <c r="E7" s="19"/>
+      <c r="F7" s="19"/>
       <c r="H7" s="16" t="s">
         <v>15</v>
       </c>
       <c r="I7" s="30" t="s">
         <v>226</v>
       </c>
-      <c r="J7" s="18"/>
-      <c r="K7" s="18"/>
-      <c r="L7" s="18"/>
-      <c r="M7" s="18"/>
+      <c r="J7" s="19"/>
+      <c r="K7" s="19"/>
+      <c r="L7" s="19"/>
+      <c r="M7" s="19"/>
       <c r="O7" s="16" t="s">
         <v>15</v>
       </c>
       <c r="P7" s="30" t="s">
         <v>226</v>
       </c>
-      <c r="Q7" s="18"/>
-      <c r="R7" s="18"/>
-      <c r="S7" s="18"/>
-      <c r="T7" s="18"/>
+      <c r="Q7" s="19"/>
+      <c r="R7" s="19"/>
+      <c r="S7" s="19"/>
+      <c r="T7" s="19"/>
       <c r="V7" s="16" t="s">
         <v>15</v>
       </c>
       <c r="W7" s="30" t="s">
         <v>226</v>
       </c>
-      <c r="X7" s="18"/>
-      <c r="Y7" s="18"/>
-      <c r="Z7" s="18"/>
-      <c r="AA7" s="18"/>
+      <c r="X7" s="19"/>
+      <c r="Y7" s="19"/>
+      <c r="Z7" s="19"/>
+      <c r="AA7" s="19"/>
       <c r="AC7" s="16" t="s">
         <v>15</v>
       </c>
       <c r="AD7" s="30" t="s">
         <v>226</v>
       </c>
-      <c r="AE7" s="18"/>
-      <c r="AF7" s="18"/>
-      <c r="AG7" s="18"/>
-      <c r="AH7" s="18"/>
+      <c r="AE7" s="19"/>
+      <c r="AF7" s="19"/>
+      <c r="AG7" s="19"/>
+      <c r="AH7" s="19"/>
       <c r="AJ7" s="16" t="s">
         <v>15</v>
       </c>
       <c r="AK7" s="30" t="s">
         <v>226</v>
       </c>
-      <c r="AL7" s="18"/>
-      <c r="AM7" s="18"/>
-      <c r="AN7" s="18"/>
-      <c r="AO7" s="18"/>
+      <c r="AL7" s="19"/>
+      <c r="AM7" s="19"/>
+      <c r="AN7" s="19"/>
+      <c r="AO7" s="19"/>
       <c r="AQ7" s="16" t="s">
         <v>15</v>
       </c>
       <c r="AR7" s="30" t="s">
         <v>226</v>
       </c>
-      <c r="AS7" s="18"/>
-      <c r="AT7" s="18"/>
-      <c r="AU7" s="18"/>
-      <c r="AV7" s="18"/>
+      <c r="AS7" s="19"/>
+      <c r="AT7" s="19"/>
+      <c r="AU7" s="19"/>
+      <c r="AV7" s="19"/>
       <c r="AX7" s="16" t="s">
         <v>15</v>
       </c>
       <c r="AY7" s="30" t="s">
         <v>226</v>
       </c>
-      <c r="AZ7" s="18"/>
-      <c r="BA7" s="18"/>
-      <c r="BB7" s="18"/>
-      <c r="BC7" s="18"/>
+      <c r="AZ7" s="19"/>
+      <c r="BA7" s="19"/>
+      <c r="BB7" s="19"/>
+      <c r="BC7" s="19"/>
       <c r="BE7" s="16" t="s">
         <v>15</v>
       </c>
       <c r="BF7" s="30" t="s">
         <v>226</v>
       </c>
-      <c r="BG7" s="18"/>
-      <c r="BH7" s="18"/>
-      <c r="BI7" s="18"/>
-      <c r="BJ7" s="18"/>
+      <c r="BG7" s="19"/>
+      <c r="BH7" s="19"/>
+      <c r="BI7" s="19"/>
+      <c r="BJ7" s="19"/>
       <c r="BL7" s="16" t="s">
         <v>15</v>
       </c>
       <c r="BM7" s="30" t="s">
         <v>226</v>
       </c>
-      <c r="BN7" s="18"/>
-      <c r="BO7" s="18"/>
-      <c r="BP7" s="18"/>
-      <c r="BQ7" s="18"/>
+      <c r="BN7" s="19"/>
+      <c r="BO7" s="19"/>
+      <c r="BP7" s="19"/>
+      <c r="BQ7" s="19"/>
       <c r="BS7" s="16" t="s">
         <v>15</v>
       </c>
       <c r="BT7" s="30" t="s">
         <v>226</v>
       </c>
-      <c r="BU7" s="18"/>
-      <c r="BV7" s="18"/>
-      <c r="BW7" s="18"/>
-      <c r="BX7" s="18"/>
+      <c r="BU7" s="19"/>
+      <c r="BV7" s="19"/>
+      <c r="BW7" s="19"/>
+      <c r="BX7" s="19"/>
       <c r="BZ7" s="16" t="s">
         <v>15</v>
       </c>
       <c r="CA7" s="30" t="s">
         <v>226</v>
       </c>
-      <c r="CB7" s="18"/>
-      <c r="CC7" s="18"/>
-      <c r="CD7" s="18"/>
-      <c r="CE7" s="18"/>
+      <c r="CB7" s="19"/>
+      <c r="CC7" s="19"/>
+      <c r="CD7" s="19"/>
+      <c r="CE7" s="19"/>
       <c r="CG7" s="16" t="s">
         <v>15</v>
       </c>
       <c r="CH7" s="30" t="s">
         <v>226</v>
       </c>
-      <c r="CI7" s="18"/>
-      <c r="CJ7" s="18"/>
-      <c r="CK7" s="18"/>
-      <c r="CL7" s="18"/>
+      <c r="CI7" s="19"/>
+      <c r="CJ7" s="19"/>
+      <c r="CK7" s="19"/>
+      <c r="CL7" s="19"/>
       <c r="CN7" s="16" t="s">
         <v>15</v>
       </c>
       <c r="CO7" s="30" t="s">
         <v>226</v>
       </c>
-      <c r="CP7" s="18"/>
-      <c r="CQ7" s="18"/>
-      <c r="CR7" s="18"/>
-      <c r="CS7" s="18"/>
+      <c r="CP7" s="19"/>
+      <c r="CQ7" s="19"/>
+      <c r="CR7" s="19"/>
+      <c r="CS7" s="19"/>
       <c r="CU7" s="16" t="s">
         <v>15</v>
       </c>
       <c r="CV7" s="30" t="s">
         <v>226</v>
       </c>
-      <c r="CW7" s="18"/>
-      <c r="CX7" s="18"/>
-      <c r="CY7" s="18"/>
-      <c r="CZ7" s="18"/>
+      <c r="CW7" s="19"/>
+      <c r="CX7" s="19"/>
+      <c r="CY7" s="19"/>
+      <c r="CZ7" s="19"/>
       <c r="DB7" s="16" t="s">
         <v>15</v>
       </c>
       <c r="DC7" s="30" t="s">
         <v>226</v>
       </c>
-      <c r="DD7" s="18"/>
-      <c r="DE7" s="18"/>
-      <c r="DF7" s="18"/>
-      <c r="DG7" s="18"/>
+      <c r="DD7" s="19"/>
+      <c r="DE7" s="19"/>
+      <c r="DF7" s="19"/>
+      <c r="DG7" s="19"/>
       <c r="DI7" s="16" t="s">
         <v>15</v>
       </c>
       <c r="DJ7" s="30" t="s">
         <v>226</v>
       </c>
-      <c r="DK7" s="18"/>
-      <c r="DL7" s="18"/>
-      <c r="DM7" s="18"/>
-      <c r="DN7" s="18"/>
+      <c r="DK7" s="19"/>
+      <c r="DL7" s="19"/>
+      <c r="DM7" s="19"/>
+      <c r="DN7" s="19"/>
       <c r="DP7" s="16" t="s">
         <v>15</v>
       </c>
       <c r="DQ7" s="30" t="s">
         <v>226</v>
       </c>
-      <c r="DR7" s="18"/>
-      <c r="DS7" s="18"/>
-      <c r="DT7" s="18"/>
-      <c r="DU7" s="18"/>
+      <c r="DR7" s="19"/>
+      <c r="DS7" s="19"/>
+      <c r="DT7" s="19"/>
+      <c r="DU7" s="19"/>
       <c r="DW7" s="16" t="s">
         <v>15</v>
       </c>
       <c r="DX7" s="30" t="s">
         <v>226</v>
       </c>
-      <c r="DY7" s="18"/>
-      <c r="DZ7" s="18"/>
-      <c r="EA7" s="18"/>
-      <c r="EB7" s="18"/>
+      <c r="DY7" s="19"/>
+      <c r="DZ7" s="19"/>
+      <c r="EA7" s="19"/>
+      <c r="EB7" s="19"/>
       <c r="ED7" s="16" t="s">
         <v>15</v>
       </c>
       <c r="EE7" s="30" t="s">
         <v>226</v>
       </c>
-      <c r="EF7" s="18"/>
-      <c r="EG7" s="18"/>
-      <c r="EH7" s="18"/>
-      <c r="EI7" s="18"/>
+      <c r="EF7" s="19"/>
+      <c r="EG7" s="19"/>
+      <c r="EH7" s="19"/>
+      <c r="EI7" s="19"/>
       <c r="EK7" s="16" t="s">
         <v>15</v>
       </c>
       <c r="EL7" s="30" t="s">
         <v>226</v>
       </c>
-      <c r="EM7" s="18"/>
-      <c r="EN7" s="18"/>
-      <c r="EO7" s="18"/>
-      <c r="EP7" s="18"/>
+      <c r="EM7" s="19"/>
+      <c r="EN7" s="19"/>
+      <c r="EO7" s="19"/>
+      <c r="EP7" s="19"/>
       <c r="ER7" s="16" t="s">
         <v>15</v>
       </c>
       <c r="ES7" s="30" t="s">
         <v>226</v>
       </c>
-      <c r="ET7" s="18"/>
-      <c r="EU7" s="18"/>
-      <c r="EV7" s="18"/>
-      <c r="EW7" s="18"/>
+      <c r="ET7" s="19"/>
+      <c r="EU7" s="19"/>
+      <c r="EV7" s="19"/>
+      <c r="EW7" s="19"/>
       <c r="EY7" s="16" t="s">
         <v>15</v>
       </c>
       <c r="EZ7" s="30" t="s">
         <v>226</v>
       </c>
-      <c r="FA7" s="18"/>
-      <c r="FB7" s="18"/>
-      <c r="FC7" s="18"/>
-      <c r="FD7" s="18"/>
-    </row>
-    <row r="8" spans="1:160" x14ac:dyDescent="0.35">
+      <c r="FA7" s="19"/>
+      <c r="FB7" s="19"/>
+      <c r="FC7" s="19"/>
+      <c r="FD7" s="19"/>
+    </row>
+    <row r="8" spans="1:160" x14ac:dyDescent="0.25">
       <c r="A8" s="16" t="s">
         <v>16</v>
       </c>
@@ -9945,7 +9975,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="9" spans="1:160" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:160" ht="29.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="16" t="s">
         <v>227</v>
       </c>
@@ -10269,7 +10299,7 @@
       <c r="FC9" s="16"/>
       <c r="FD9" s="16"/>
     </row>
-    <row r="10" spans="1:160" ht="43.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:160" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="16" t="s">
         <v>231</v>
       </c>
@@ -10547,7 +10577,7 @@
       <c r="FC10" s="16"/>
       <c r="FD10" s="16"/>
     </row>
-    <row r="11" spans="1:160" ht="43.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:160" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="16" t="s">
         <v>246</v>
       </c>
@@ -10827,38 +10857,27 @@
     </row>
   </sheetData>
   <mergeCells count="69">
-    <mergeCell ref="EL7:EP7"/>
-    <mergeCell ref="AD7:AH7"/>
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="BL1:BQ1"/>
-    <mergeCell ref="AY7:BC7"/>
-    <mergeCell ref="CU1:CZ1"/>
-    <mergeCell ref="CH7:CL7"/>
-    <mergeCell ref="AY6:BC6"/>
-    <mergeCell ref="BT6:BX6"/>
-    <mergeCell ref="EK1:EP1"/>
-    <mergeCell ref="EZ6:FD6"/>
-    <mergeCell ref="H1:M1"/>
-    <mergeCell ref="B6:F6"/>
-    <mergeCell ref="AX1:BC1"/>
-    <mergeCell ref="AK6:AO6"/>
-    <mergeCell ref="DJ6:DN6"/>
-    <mergeCell ref="ES6:EW6"/>
-    <mergeCell ref="ED1:EI1"/>
-    <mergeCell ref="W7:AA7"/>
-    <mergeCell ref="AJ1:AO1"/>
-    <mergeCell ref="P7:T7"/>
-    <mergeCell ref="CA7:CE7"/>
-    <mergeCell ref="AR6:AV6"/>
-    <mergeCell ref="CN1:CS1"/>
-    <mergeCell ref="DC6:DG6"/>
-    <mergeCell ref="EE7:EI7"/>
-    <mergeCell ref="DB1:DG1"/>
-    <mergeCell ref="CV6:CZ6"/>
-    <mergeCell ref="CO7:CS7"/>
-    <mergeCell ref="ER1:EW1"/>
-    <mergeCell ref="DX7:EB7"/>
-    <mergeCell ref="EL6:EP6"/>
+    <mergeCell ref="EY1:FD1"/>
+    <mergeCell ref="V1:AA1"/>
+    <mergeCell ref="DX6:EB6"/>
+    <mergeCell ref="B7:F7"/>
+    <mergeCell ref="BE1:BJ1"/>
+    <mergeCell ref="AR7:AV7"/>
+    <mergeCell ref="O1:T1"/>
+    <mergeCell ref="EZ7:FD7"/>
+    <mergeCell ref="I6:M6"/>
+    <mergeCell ref="AK7:AO7"/>
+    <mergeCell ref="W6:AA6"/>
+    <mergeCell ref="CV7:CZ7"/>
+    <mergeCell ref="BS1:BX1"/>
+    <mergeCell ref="DI1:DN1"/>
+    <mergeCell ref="BF7:BJ7"/>
+    <mergeCell ref="BM6:BQ6"/>
+    <mergeCell ref="CH6:CL6"/>
+    <mergeCell ref="BF6:BJ6"/>
+    <mergeCell ref="DW1:EB1"/>
+    <mergeCell ref="DQ6:DU6"/>
+    <mergeCell ref="DJ7:DN7"/>
     <mergeCell ref="ES7:EW7"/>
     <mergeCell ref="AC1:AH1"/>
     <mergeCell ref="EE6:EI6"/>
@@ -10875,27 +10894,38 @@
     <mergeCell ref="CO6:CS6"/>
     <mergeCell ref="DP1:DU1"/>
     <mergeCell ref="DQ7:DU7"/>
-    <mergeCell ref="CH6:CL6"/>
-    <mergeCell ref="BF6:BJ6"/>
-    <mergeCell ref="DW1:EB1"/>
-    <mergeCell ref="DQ6:DU6"/>
-    <mergeCell ref="DJ7:DN7"/>
-    <mergeCell ref="EY1:FD1"/>
-    <mergeCell ref="V1:AA1"/>
-    <mergeCell ref="DX6:EB6"/>
-    <mergeCell ref="B7:F7"/>
-    <mergeCell ref="BE1:BJ1"/>
-    <mergeCell ref="AR7:AV7"/>
-    <mergeCell ref="O1:T1"/>
-    <mergeCell ref="EZ7:FD7"/>
-    <mergeCell ref="I6:M6"/>
-    <mergeCell ref="AK7:AO7"/>
-    <mergeCell ref="W6:AA6"/>
-    <mergeCell ref="CV7:CZ7"/>
-    <mergeCell ref="BS1:BX1"/>
-    <mergeCell ref="DI1:DN1"/>
-    <mergeCell ref="BF7:BJ7"/>
-    <mergeCell ref="BM6:BQ6"/>
+    <mergeCell ref="EZ6:FD6"/>
+    <mergeCell ref="H1:M1"/>
+    <mergeCell ref="B6:F6"/>
+    <mergeCell ref="AX1:BC1"/>
+    <mergeCell ref="AK6:AO6"/>
+    <mergeCell ref="DJ6:DN6"/>
+    <mergeCell ref="ES6:EW6"/>
+    <mergeCell ref="ED1:EI1"/>
+    <mergeCell ref="AJ1:AO1"/>
+    <mergeCell ref="AR6:AV6"/>
+    <mergeCell ref="CN1:CS1"/>
+    <mergeCell ref="DC6:DG6"/>
+    <mergeCell ref="DB1:DG1"/>
+    <mergeCell ref="CV6:CZ6"/>
+    <mergeCell ref="ER1:EW1"/>
+    <mergeCell ref="EL6:EP6"/>
+    <mergeCell ref="EL7:EP7"/>
+    <mergeCell ref="AD7:AH7"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="BL1:BQ1"/>
+    <mergeCell ref="AY7:BC7"/>
+    <mergeCell ref="CU1:CZ1"/>
+    <mergeCell ref="CH7:CL7"/>
+    <mergeCell ref="AY6:BC6"/>
+    <mergeCell ref="BT6:BX6"/>
+    <mergeCell ref="EK1:EP1"/>
+    <mergeCell ref="W7:AA7"/>
+    <mergeCell ref="P7:T7"/>
+    <mergeCell ref="CA7:CE7"/>
+    <mergeCell ref="EE7:EI7"/>
+    <mergeCell ref="CO7:CS7"/>
+    <mergeCell ref="DX7:EB7"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Test Cases.xlsx
+++ b/Test Cases.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://endresshauser-my.sharepoint.com/personal/corbin_ferguson_endress_com/Documents/ThesisBuildTool/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="95" documentId="8_{B89245B7-08D9-4A9D-8516-F6C9C7AFFDC1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E3D6DEDD-0313-44D5-8D83-AE271DD3A4B7}"/>
+  <xr:revisionPtr revIDLastSave="142" documentId="8_{B89245B7-08D9-4A9D-8516-F6C9C7AFFDC1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FAE64D01-F0F2-4298-856E-9A52D5E13865}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="25440" windowHeight="15270" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="25440" windowHeight="15270" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tests" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1789" uniqueCount="336">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1776" uniqueCount="344">
   <si>
     <t>Test ID</t>
   </si>
@@ -369,9 +369,6 @@
     <t>Select attributes to modify</t>
   </si>
   <si>
-    <t>select Name &amp; other to modify</t>
-  </si>
-  <si>
     <t xml:space="preserve">text window popup </t>
   </si>
   <si>
@@ -381,9 +378,6 @@
     <t>select Name to modify</t>
   </si>
   <si>
-    <t>Set Name</t>
-  </si>
-  <si>
     <t>NewName</t>
   </si>
   <si>
@@ -396,21 +390,12 @@
     <t>redundant name</t>
   </si>
   <si>
-    <t>Set other</t>
-  </si>
-  <si>
-    <t>NewOther</t>
-  </si>
-  <si>
     <t>move to select subelements</t>
   </si>
   <si>
     <t>existing element replaced by new element, move to next element modify</t>
   </si>
   <si>
-    <t>Select subelements</t>
-  </si>
-  <si>
     <t>Select attributes to modify for element2</t>
   </si>
   <si>
@@ -426,15 +411,6 @@
     <t>window X press</t>
   </si>
   <si>
-    <t>move to element2 select attributes window</t>
-  </si>
-  <si>
-    <t>text input for new name window appears</t>
-  </si>
-  <si>
-    <t>new name set, continue to select subelements</t>
-  </si>
-  <si>
     <t>Delete No Element Type</t>
   </si>
   <si>
@@ -1048,6 +1024,54 @@
   </si>
   <si>
     <t>text field reappears</t>
+  </si>
+  <si>
+    <t>dropdown select TemplateFBAOI, &amp; TemplateLadderAOI</t>
+  </si>
+  <si>
+    <t>select Name &amp; CreatedBy  to modify</t>
+  </si>
+  <si>
+    <t>NewUser</t>
+  </si>
+  <si>
+    <t>Routines</t>
+  </si>
+  <si>
+    <t>Select attributes to modify of routine</t>
+  </si>
+  <si>
+    <t>select CreatedBy</t>
+  </si>
+  <si>
+    <t>move to TemplateLadderAOI select attributes window</t>
+  </si>
+  <si>
+    <t>Set Name of TemplateFBAOI</t>
+  </si>
+  <si>
+    <t>Set CreatedBy of TemplateFBAOI</t>
+  </si>
+  <si>
+    <t>Select subelement routines</t>
+  </si>
+  <si>
+    <t>Set CreatedBy of routine</t>
+  </si>
+  <si>
+    <t>Set CreatedBy of TemplateLadderAOI</t>
+  </si>
+  <si>
+    <t>TestUser</t>
+  </si>
+  <si>
+    <t>Description: Test attempting to modify a file with no elements.</t>
+  </si>
+  <si>
+    <t>Verify popup window appears</t>
+  </si>
+  <si>
+    <t>"No Valid Elements Found"</t>
   </si>
 </sst>
 </file>
@@ -1469,13 +1493,13 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="4"/>
                 <c:pt idx="0">
-                  <c:v>8</c:v>
+                  <c:v>5</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>33</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>18</c:v>
+                  <c:v>21</c:v>
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>1</c:v>
@@ -2860,7 +2884,7 @@
       </c>
       <c r="H1">
         <f>COUNTIF(TestMaster[Test Status], "Not Implemented")</f>
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
@@ -2906,7 +2930,7 @@
       </c>
       <c r="H3">
         <f>COUNTIF(TestMaster[Test Status], "Fail")</f>
-        <v>18</v>
+        <v>21</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
@@ -3133,7 +3157,7 @@
       </c>
       <c r="H14">
         <f>COUNTIFS(TestMaster[Test Status], "Not Implemented", TestMaster[Namespace], G13)</f>
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
@@ -3179,7 +3203,7 @@
       </c>
       <c r="H16">
         <f>COUNTIFS(TestMaster[Test Status], "Fail", TestMaster[Namespace], G13)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
@@ -3237,7 +3261,7 @@
         <v>7</v>
       </c>
       <c r="G19" t="s">
-        <v>319</v>
+        <v>311</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
@@ -3389,7 +3413,7 @@
         <v>Nameless Module Creation</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D26" t="s">
         <v>10</v>
@@ -3518,7 +3542,7 @@
         <v>11</v>
       </c>
       <c r="E31" t="s">
-        <v>319</v>
+        <v>311</v>
       </c>
       <c r="G31" t="s">
         <v>16</v>
@@ -3540,14 +3564,14 @@
         <v>10</v>
       </c>
       <c r="E32" t="s">
-        <v>319</v>
+        <v>311</v>
       </c>
       <c r="G32" t="s">
         <v>5</v>
       </c>
       <c r="H32">
         <f>COUNTIFS(TestMaster[Test Status], "Not Implemented", TestMaster[Namespace], G31)</f>
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.25">
@@ -3566,7 +3590,7 @@
         <v>11</v>
       </c>
       <c r="E33" t="s">
-        <v>319</v>
+        <v>311</v>
       </c>
       <c r="G33" t="s">
         <v>8</v>
@@ -3599,7 +3623,7 @@
       </c>
       <c r="H34">
         <f>COUNTIFS(TestMaster[Test Status], "Fail", TestMaster[Namespace], G31)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.25">
@@ -3612,7 +3636,7 @@
         <v>Standard Element Modify</v>
       </c>
       <c r="C35" s="5" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D35" t="s">
         <v>11</v>
@@ -3657,7 +3681,7 @@
         <v>No Element to Modify</v>
       </c>
       <c r="C37" s="5" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D37" t="s">
         <v>10</v>
@@ -4701,7 +4725,7 @@
       </c>
       <c r="L3" s="7" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(G1, TestMaster[Test Name], TestMaster[Test Status], "Status not found"), "")</f>
-        <v>Not Implemented</v>
+        <v>Fail</v>
       </c>
       <c r="M3" s="17" t="s">
         <v>22</v>
@@ -5045,7 +5069,7 @@
         <v>84</v>
       </c>
       <c r="O12" s="3" t="s">
-        <v>334</v>
+        <v>326</v>
       </c>
       <c r="P12" s="3" t="s">
         <v>86</v>
@@ -5071,7 +5095,7 @@
         <v>90</v>
       </c>
       <c r="O13" s="3" t="s">
-        <v>334</v>
+        <v>326</v>
       </c>
       <c r="P13" s="3" t="s">
         <v>91</v>
@@ -5158,7 +5182,7 @@
         <v>85</v>
       </c>
       <c r="P19" t="s">
-        <v>335</v>
+        <v>327</v>
       </c>
     </row>
     <row r="20" spans="13:16" x14ac:dyDescent="0.25">
@@ -5223,18 +5247,18 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:R26"/>
+  <dimension ref="A1:R21"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5" customWidth="1"/>
     <col min="2" max="2" width="22.140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="25.5703125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="31.140625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="18.42578125" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="16.140625" style="7" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="5" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="30.42578125" customWidth="1"/>
-    <col min="9" max="9" width="27.5703125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="34.7109375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="31.85546875" customWidth="1"/>
     <col min="10" max="10" width="30.28515625" customWidth="1"/>
     <col min="11" max="11" width="18.42578125" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="16.140625" style="7" bestFit="1" customWidth="1"/>
@@ -5256,7 +5280,7 @@
       <c r="E1" s="18"/>
       <c r="F1" s="21"/>
       <c r="G1" s="23" t="s">
-        <v>331</v>
+        <v>323</v>
       </c>
       <c r="H1" s="18"/>
       <c r="I1" s="18"/>
@@ -5321,7 +5345,7 @@
       </c>
       <c r="F3" s="7" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(A1, TestMaster[Test Name], TestMaster[Test Status], "Status not found"), "")</f>
-        <v>Not Implemented</v>
+        <v>Fail</v>
       </c>
       <c r="G3" s="17" t="s">
         <v>22</v>
@@ -5336,7 +5360,7 @@
       </c>
       <c r="L3" s="7" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(G1, TestMaster[Test Name], TestMaster[Test Status], "Status not found"), "")</f>
-        <v>Not Implemented</v>
+        <v>Fail</v>
       </c>
       <c r="M3" s="17" t="s">
         <v>22</v>
@@ -5356,7 +5380,7 @@
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A4" s="19" t="s">
-        <v>68</v>
+        <v>341</v>
       </c>
       <c r="B4" s="18"/>
       <c r="C4" s="18"/>
@@ -5364,7 +5388,7 @@
       <c r="E4" s="18"/>
       <c r="F4" s="21"/>
       <c r="G4" s="23" t="s">
-        <v>332</v>
+        <v>324</v>
       </c>
       <c r="H4" s="18"/>
       <c r="I4" s="18"/>
@@ -5499,7 +5523,7 @@
         <v>1</v>
       </c>
       <c r="H8" t="s">
-        <v>333</v>
+        <v>325</v>
       </c>
       <c r="M8">
         <v>1</v>
@@ -5518,14 +5542,11 @@
       <c r="A9" s="4">
         <v>2</v>
       </c>
-      <c r="B9" s="4" t="s">
-        <v>100</v>
-      </c>
-      <c r="C9" s="4" t="s">
-        <v>70</v>
-      </c>
-      <c r="D9" s="4" t="s">
-        <v>63</v>
+      <c r="B9" t="s">
+        <v>342</v>
+      </c>
+      <c r="C9" t="s">
+        <v>343</v>
       </c>
       <c r="G9">
         <v>2</v>
@@ -5553,6 +5574,18 @@
       </c>
     </row>
     <row r="10" spans="1:18" ht="29.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10">
+        <v>3</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="D10" s="4" t="s">
+        <v>63</v>
+      </c>
       <c r="G10">
         <v>3</v>
       </c>
@@ -5586,7 +5619,7 @@
         <v>104</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>105</v>
+        <v>328</v>
       </c>
       <c r="J11" s="3" t="s">
         <v>106</v>
@@ -5595,13 +5628,13 @@
         <v>4</v>
       </c>
       <c r="N11" t="s">
+        <v>110</v>
+      </c>
+      <c r="O11" t="s">
         <v>111</v>
       </c>
-      <c r="O11" t="s">
-        <v>112</v>
-      </c>
       <c r="P11" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="12" spans="1:18" x14ac:dyDescent="0.25">
@@ -5612,22 +5645,22 @@
         <v>108</v>
       </c>
       <c r="I12" t="s">
+        <v>329</v>
+      </c>
+      <c r="J12" t="s">
         <v>109</v>
-      </c>
-      <c r="J12" t="s">
-        <v>110</v>
       </c>
       <c r="M12">
         <v>5</v>
       </c>
       <c r="N12" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="O12" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="P12" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
     </row>
     <row r="13" spans="1:18" x14ac:dyDescent="0.25">
@@ -5635,13 +5668,13 @@
         <v>6</v>
       </c>
       <c r="H13" t="s">
-        <v>113</v>
+        <v>336</v>
       </c>
       <c r="I13" t="s">
-        <v>114</v>
+        <v>330</v>
       </c>
       <c r="J13" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="M13">
         <v>6</v>
@@ -5653,7 +5686,7 @@
         <v>49</v>
       </c>
       <c r="P13" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
     </row>
     <row r="14" spans="1:18" x14ac:dyDescent="0.25">
@@ -5661,25 +5694,25 @@
         <v>7</v>
       </c>
       <c r="H14" t="s">
-        <v>118</v>
+        <v>335</v>
       </c>
       <c r="I14" t="s">
-        <v>119</v>
+        <v>112</v>
       </c>
       <c r="J14" t="s">
-        <v>120</v>
+        <v>113</v>
       </c>
       <c r="M14">
         <v>8</v>
       </c>
       <c r="N14" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="O14" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="P14" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="15" spans="1:18" x14ac:dyDescent="0.25">
@@ -5687,19 +5720,22 @@
         <v>8</v>
       </c>
       <c r="H15" t="s">
-        <v>122</v>
+        <v>337</v>
+      </c>
+      <c r="I15" t="s">
+        <v>331</v>
       </c>
       <c r="M15">
         <v>9</v>
       </c>
       <c r="N15" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
       <c r="O15" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="P15" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
     </row>
     <row r="16" spans="1:18" x14ac:dyDescent="0.25">
@@ -5707,13 +5743,13 @@
         <v>9</v>
       </c>
       <c r="H16" t="s">
-        <v>108</v>
+        <v>332</v>
       </c>
       <c r="I16" t="s">
+        <v>333</v>
+      </c>
+      <c r="J16" t="s">
         <v>109</v>
-      </c>
-      <c r="J16" t="s">
-        <v>110</v>
       </c>
       <c r="M16">
         <v>10</v>
@@ -5725,7 +5761,7 @@
         <v>52</v>
       </c>
       <c r="P16" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
     </row>
     <row r="17" spans="7:10" x14ac:dyDescent="0.25">
@@ -5733,13 +5769,13 @@
         <v>10</v>
       </c>
       <c r="H17" t="s">
-        <v>113</v>
+        <v>338</v>
       </c>
       <c r="I17" t="s">
-        <v>114</v>
+        <v>330</v>
       </c>
       <c r="J17" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
     </row>
     <row r="18" spans="7:10" x14ac:dyDescent="0.25">
@@ -5747,13 +5783,13 @@
         <v>11</v>
       </c>
       <c r="H18" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="I18" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="J18" t="s">
-        <v>120</v>
+        <v>334</v>
       </c>
     </row>
     <row r="19" spans="7:10" x14ac:dyDescent="0.25">
@@ -5761,13 +5797,13 @@
         <v>12</v>
       </c>
       <c r="H19" t="s">
-        <v>126</v>
+        <v>108</v>
       </c>
       <c r="I19" t="s">
-        <v>127</v>
+        <v>111</v>
       </c>
       <c r="J19" t="s">
-        <v>128</v>
+        <v>109</v>
       </c>
     </row>
     <row r="20" spans="7:10" x14ac:dyDescent="0.25">
@@ -5775,13 +5811,10 @@
         <v>13</v>
       </c>
       <c r="H20" t="s">
-        <v>108</v>
+        <v>339</v>
       </c>
       <c r="I20" t="s">
-        <v>112</v>
-      </c>
-      <c r="J20" t="s">
-        <v>110</v>
+        <v>340</v>
       </c>
     </row>
     <row r="21" spans="7:10" x14ac:dyDescent="0.25">
@@ -5789,79 +5822,12 @@
         <v>14</v>
       </c>
       <c r="H21" t="s">
-        <v>113</v>
+        <v>121</v>
       </c>
       <c r="I21" t="s">
-        <v>114</v>
+        <v>122</v>
       </c>
       <c r="J21" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="22" spans="7:10" x14ac:dyDescent="0.25">
-      <c r="G22">
-        <v>15</v>
-      </c>
-      <c r="H22" t="s">
-        <v>48</v>
-      </c>
-      <c r="I22" t="s">
-        <v>54</v>
-      </c>
-      <c r="J22" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="23" spans="7:10" x14ac:dyDescent="0.25">
-      <c r="G23">
-        <v>16</v>
-      </c>
-      <c r="H23" t="s">
-        <v>56</v>
-      </c>
-      <c r="I23" t="s">
-        <v>114</v>
-      </c>
-      <c r="J23" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="24" spans="7:10" x14ac:dyDescent="0.25">
-      <c r="G24">
-        <v>17</v>
-      </c>
-      <c r="H24" t="s">
-        <v>48</v>
-      </c>
-      <c r="I24" t="s">
-        <v>54</v>
-      </c>
-      <c r="J24" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="25" spans="7:10" x14ac:dyDescent="0.25">
-      <c r="G25">
-        <v>18</v>
-      </c>
-      <c r="H25" t="s">
-        <v>59</v>
-      </c>
-      <c r="I25" t="s">
-        <v>60</v>
-      </c>
-      <c r="J25" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="26" spans="7:10" x14ac:dyDescent="0.25">
-      <c r="H26" t="s">
-        <v>126</v>
-      </c>
-      <c r="I26" t="s">
-        <v>127</v>
-      </c>
-      <c r="J26" t="s">
         <v>63</v>
       </c>
     </row>
@@ -5914,7 +5880,7 @@
   <sheetData>
     <row r="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A1" s="19" t="s">
-        <v>131</v>
+        <v>123</v>
       </c>
       <c r="B1" s="18"/>
       <c r="C1" s="18"/>
@@ -5922,7 +5888,7 @@
       <c r="E1" s="18"/>
       <c r="F1" s="21"/>
       <c r="G1" s="23" t="s">
-        <v>132</v>
+        <v>124</v>
       </c>
       <c r="H1" s="18"/>
       <c r="I1" s="18"/>
@@ -5930,7 +5896,7 @@
       <c r="K1" s="18"/>
       <c r="L1" s="21"/>
       <c r="M1" s="17" t="s">
-        <v>133</v>
+        <v>125</v>
       </c>
       <c r="N1" s="18"/>
       <c r="O1" s="18"/>
@@ -6022,7 +5988,7 @@
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A4" s="26" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="B4" s="18"/>
       <c r="C4" s="18"/>
@@ -6030,7 +5996,7 @@
       <c r="E4" s="18"/>
       <c r="F4" s="21"/>
       <c r="G4" s="27" t="s">
-        <v>321</v>
+        <v>313</v>
       </c>
       <c r="H4" s="18"/>
       <c r="I4" s="18"/>
@@ -6068,7 +6034,7 @@
     </row>
     <row r="6" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A6" s="19" t="s">
-        <v>135</v>
+        <v>127</v>
       </c>
       <c r="B6" s="18"/>
       <c r="C6" s="18"/>
@@ -6076,7 +6042,7 @@
       <c r="E6" s="18"/>
       <c r="F6" s="21"/>
       <c r="G6" s="23" t="s">
-        <v>322</v>
+        <v>314</v>
       </c>
       <c r="H6" s="18"/>
       <c r="I6" s="18"/>
@@ -6153,10 +6119,10 @@
         <v>1</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>136</v>
+        <v>128</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>323</v>
+        <v>315</v>
       </c>
       <c r="D8" s="3" t="s">
         <v>98</v>
@@ -6166,10 +6132,10 @@
         <v>1</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>136</v>
+        <v>128</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>320</v>
+        <v>312</v>
       </c>
       <c r="J8" s="3" t="s">
         <v>99</v>
@@ -6179,7 +6145,7 @@
         <v>1</v>
       </c>
       <c r="N8" s="3" t="s">
-        <v>136</v>
+        <v>128</v>
       </c>
       <c r="O8" s="3" t="s">
         <v>70</v>
@@ -6196,7 +6162,7 @@
         <v>100</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>324</v>
+        <v>316</v>
       </c>
       <c r="D9" s="3" t="s">
         <v>63</v>
@@ -6209,7 +6175,7 @@
         <v>101</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>326</v>
+        <v>318</v>
       </c>
       <c r="J9" s="3" t="s">
         <v>103</v>
@@ -6222,10 +6188,10 @@
         <v>101</v>
       </c>
       <c r="O9" s="3" t="s">
-        <v>137</v>
+        <v>129</v>
       </c>
       <c r="P9" s="3" t="s">
-        <v>138</v>
+        <v>130</v>
       </c>
     </row>
     <row r="10" spans="1:18" s="3" customFormat="1" ht="29.1" customHeight="1" x14ac:dyDescent="0.25">
@@ -6234,26 +6200,26 @@
         <v>3</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>139</v>
+        <v>131</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>327</v>
+        <v>319</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>328</v>
+        <v>320</v>
       </c>
       <c r="L10" s="13"/>
       <c r="M10" s="3">
         <v>3</v>
       </c>
       <c r="N10" s="3" t="s">
-        <v>139</v>
+        <v>131</v>
       </c>
       <c r="O10" s="3" t="s">
-        <v>140</v>
+        <v>132</v>
       </c>
       <c r="P10" s="3" t="s">
-        <v>141</v>
+        <v>133</v>
       </c>
     </row>
     <row r="11" spans="1:18" ht="29.1" customHeight="1" x14ac:dyDescent="0.25">
@@ -6261,25 +6227,25 @@
         <v>4</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>325</v>
+        <v>317</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>329</v>
+        <v>321</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>330</v>
+        <v>322</v>
       </c>
       <c r="M11" s="3">
         <v>4</v>
       </c>
       <c r="N11" s="3" t="s">
-        <v>142</v>
+        <v>134</v>
       </c>
       <c r="O11" s="3" t="s">
-        <v>143</v>
+        <v>135</v>
       </c>
       <c r="P11" s="3" t="s">
-        <v>144</v>
+        <v>136</v>
       </c>
     </row>
   </sheetData>
@@ -6330,7 +6296,7 @@
   <sheetData>
     <row r="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A1" s="19" t="s">
-        <v>145</v>
+        <v>137</v>
       </c>
       <c r="B1" s="18"/>
       <c r="C1" s="18"/>
@@ -6338,7 +6304,7 @@
       <c r="E1" s="18"/>
       <c r="F1" s="21"/>
       <c r="G1" s="17" t="s">
-        <v>146</v>
+        <v>138</v>
       </c>
       <c r="H1" s="18"/>
       <c r="I1" s="18"/>
@@ -6346,7 +6312,7 @@
       <c r="K1" s="18"/>
       <c r="L1" s="18"/>
       <c r="M1" s="23" t="s">
-        <v>147</v>
+        <v>139</v>
       </c>
       <c r="N1" s="18"/>
       <c r="O1" s="18"/>
@@ -6439,7 +6405,7 @@
     </row>
     <row r="4" spans="1:18" s="2" customFormat="1" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="26" t="s">
-        <v>148</v>
+        <v>140</v>
       </c>
       <c r="B4" s="20"/>
       <c r="C4" s="20"/>
@@ -6447,7 +6413,7 @@
       <c r="E4" s="20"/>
       <c r="F4" s="21"/>
       <c r="G4" s="25" t="s">
-        <v>149</v>
+        <v>141</v>
       </c>
       <c r="H4" s="20"/>
       <c r="I4" s="20"/>
@@ -6455,7 +6421,7 @@
       <c r="K4" s="20"/>
       <c r="L4" s="20"/>
       <c r="M4" s="27" t="s">
-        <v>150</v>
+        <v>142</v>
       </c>
       <c r="N4" s="20"/>
       <c r="O4" s="20"/>
@@ -6485,7 +6451,7 @@
     </row>
     <row r="6" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A6" s="19" t="s">
-        <v>151</v>
+        <v>143</v>
       </c>
       <c r="B6" s="18"/>
       <c r="C6" s="18"/>
@@ -6493,7 +6459,7 @@
       <c r="E6" s="18"/>
       <c r="F6" s="21"/>
       <c r="G6" s="17" t="s">
-        <v>152</v>
+        <v>144</v>
       </c>
       <c r="H6" s="18"/>
       <c r="I6" s="18"/>
@@ -6501,7 +6467,7 @@
       <c r="K6" s="18"/>
       <c r="L6" s="18"/>
       <c r="M6" s="23" t="s">
-        <v>152</v>
+        <v>144</v>
       </c>
       <c r="N6" s="18"/>
       <c r="O6" s="18"/>
@@ -6570,25 +6536,25 @@
         <v>1</v>
       </c>
       <c r="B8" t="s">
-        <v>153</v>
+        <v>145</v>
       </c>
       <c r="C8" t="s">
-        <v>154</v>
+        <v>146</v>
       </c>
       <c r="D8" t="s">
-        <v>155</v>
+        <v>147</v>
       </c>
       <c r="G8">
         <v>1</v>
       </c>
       <c r="H8" t="s">
-        <v>156</v>
+        <v>148</v>
       </c>
       <c r="I8" t="s">
-        <v>157</v>
+        <v>149</v>
       </c>
       <c r="J8" t="s">
-        <v>158</v>
+        <v>150</v>
       </c>
       <c r="M8" s="15">
         <v>1</v>
@@ -6603,22 +6569,22 @@
         <v>100</v>
       </c>
       <c r="C9" t="s">
-        <v>159</v>
+        <v>151</v>
       </c>
       <c r="D9" t="s">
-        <v>160</v>
+        <v>152</v>
       </c>
       <c r="G9">
         <v>2</v>
       </c>
       <c r="H9" t="s">
-        <v>161</v>
+        <v>153</v>
       </c>
       <c r="I9" t="s">
-        <v>162</v>
+        <v>154</v>
       </c>
       <c r="J9" t="s">
-        <v>163</v>
+        <v>155</v>
       </c>
       <c r="M9" s="15">
         <v>2</v>
@@ -6630,25 +6596,25 @@
         <v>3</v>
       </c>
       <c r="B10" t="s">
-        <v>164</v>
+        <v>156</v>
       </c>
       <c r="C10" t="s">
-        <v>165</v>
+        <v>157</v>
       </c>
       <c r="D10" t="s">
-        <v>166</v>
+        <v>158</v>
       </c>
       <c r="G10">
         <v>3</v>
       </c>
       <c r="H10" t="s">
-        <v>167</v>
+        <v>159</v>
       </c>
       <c r="I10" t="s">
-        <v>168</v>
+        <v>160</v>
       </c>
       <c r="J10" t="s">
-        <v>169</v>
+        <v>161</v>
       </c>
       <c r="M10" s="15">
         <v>3</v>
@@ -6660,25 +6626,25 @@
         <v>4</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>170</v>
+        <v>162</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>171</v>
+        <v>163</v>
       </c>
       <c r="D11" t="s">
-        <v>172</v>
+        <v>164</v>
       </c>
       <c r="G11">
         <v>4</v>
       </c>
       <c r="H11" t="s">
-        <v>173</v>
+        <v>165</v>
       </c>
       <c r="I11" t="s">
         <v>70</v>
       </c>
       <c r="J11" t="s">
-        <v>174</v>
+        <v>166</v>
       </c>
       <c r="M11" s="15">
         <v>4</v>
@@ -6693,10 +6659,10 @@
         <v>5</v>
       </c>
       <c r="B12" t="s">
-        <v>153</v>
+        <v>145</v>
       </c>
       <c r="D12" t="s">
-        <v>175</v>
+        <v>167</v>
       </c>
     </row>
     <row r="13" spans="1:18" x14ac:dyDescent="0.25">
@@ -6704,13 +6670,13 @@
         <v>6</v>
       </c>
       <c r="B13" t="s">
-        <v>176</v>
+        <v>168</v>
       </c>
       <c r="C13" t="s">
-        <v>177</v>
+        <v>169</v>
       </c>
       <c r="D13" t="s">
-        <v>160</v>
+        <v>152</v>
       </c>
     </row>
     <row r="14" spans="1:18" x14ac:dyDescent="0.25">
@@ -6718,10 +6684,10 @@
         <v>7</v>
       </c>
       <c r="B14" t="s">
-        <v>178</v>
+        <v>170</v>
       </c>
       <c r="C14" t="s">
-        <v>179</v>
+        <v>171</v>
       </c>
     </row>
     <row r="15" spans="1:18" x14ac:dyDescent="0.25">
@@ -6729,13 +6695,13 @@
         <v>8</v>
       </c>
       <c r="B15" t="s">
-        <v>180</v>
+        <v>172</v>
       </c>
       <c r="C15" t="s">
         <v>62</v>
       </c>
       <c r="D15" t="s">
-        <v>181</v>
+        <v>173</v>
       </c>
     </row>
     <row r="16" spans="1:18" x14ac:dyDescent="0.25">
@@ -6743,10 +6709,10 @@
         <v>9</v>
       </c>
       <c r="B16" t="s">
-        <v>182</v>
+        <v>174</v>
       </c>
       <c r="C16" t="s">
-        <v>177</v>
+        <v>169</v>
       </c>
       <c r="D16" t="s">
         <v>63</v>
@@ -6757,13 +6723,13 @@
         <v>10</v>
       </c>
       <c r="B17" t="s">
-        <v>183</v>
+        <v>175</v>
       </c>
       <c r="C17" t="s">
-        <v>184</v>
+        <v>176</v>
       </c>
       <c r="D17" t="s">
-        <v>185</v>
+        <v>177</v>
       </c>
     </row>
     <row r="18" spans="1:4" ht="72.599999999999994" customHeight="1" x14ac:dyDescent="0.25">
@@ -6771,13 +6737,13 @@
         <v>11</v>
       </c>
       <c r="B18" t="s">
-        <v>186</v>
+        <v>178</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>187</v>
+        <v>179</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>188</v>
+        <v>180</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
@@ -6785,13 +6751,13 @@
         <v>12</v>
       </c>
       <c r="B19" t="s">
-        <v>178</v>
+        <v>170</v>
       </c>
       <c r="C19" t="s">
         <v>70</v>
       </c>
       <c r="D19" t="s">
-        <v>189</v>
+        <v>181</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
@@ -6799,13 +6765,13 @@
         <v>13</v>
       </c>
       <c r="B20" t="s">
-        <v>180</v>
+        <v>172</v>
       </c>
       <c r="C20" t="s">
         <v>45</v>
       </c>
       <c r="D20" t="s">
-        <v>181</v>
+        <v>173</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
@@ -6813,10 +6779,10 @@
         <v>14</v>
       </c>
       <c r="B21" t="s">
-        <v>182</v>
+        <v>174</v>
       </c>
       <c r="C21" t="s">
-        <v>177</v>
+        <v>169</v>
       </c>
       <c r="D21" t="s">
         <v>63</v>
@@ -6876,7 +6842,7 @@
   <sheetData>
     <row r="1" spans="1:160" x14ac:dyDescent="0.25">
       <c r="A1" s="30" t="s">
-        <v>190</v>
+        <v>182</v>
       </c>
       <c r="B1" s="18"/>
       <c r="C1" s="18"/>
@@ -6884,7 +6850,7 @@
       <c r="E1" s="18"/>
       <c r="F1" s="18"/>
       <c r="H1" s="30" t="s">
-        <v>191</v>
+        <v>183</v>
       </c>
       <c r="I1" s="18"/>
       <c r="J1" s="18"/>
@@ -6892,7 +6858,7 @@
       <c r="L1" s="18"/>
       <c r="M1" s="18"/>
       <c r="O1" s="30" t="s">
-        <v>192</v>
+        <v>184</v>
       </c>
       <c r="P1" s="18"/>
       <c r="Q1" s="18"/>
@@ -6900,7 +6866,7 @@
       <c r="S1" s="18"/>
       <c r="T1" s="18"/>
       <c r="V1" s="30" t="s">
-        <v>193</v>
+        <v>185</v>
       </c>
       <c r="W1" s="18"/>
       <c r="X1" s="18"/>
@@ -6908,7 +6874,7 @@
       <c r="Z1" s="18"/>
       <c r="AA1" s="18"/>
       <c r="AC1" s="30" t="s">
-        <v>194</v>
+        <v>186</v>
       </c>
       <c r="AD1" s="18"/>
       <c r="AE1" s="18"/>
@@ -6916,7 +6882,7 @@
       <c r="AG1" s="18"/>
       <c r="AH1" s="18"/>
       <c r="AJ1" s="30" t="s">
-        <v>195</v>
+        <v>187</v>
       </c>
       <c r="AK1" s="18"/>
       <c r="AL1" s="18"/>
@@ -6924,7 +6890,7 @@
       <c r="AN1" s="18"/>
       <c r="AO1" s="18"/>
       <c r="AQ1" s="30" t="s">
-        <v>196</v>
+        <v>188</v>
       </c>
       <c r="AR1" s="18"/>
       <c r="AS1" s="18"/>
@@ -6932,7 +6898,7 @@
       <c r="AU1" s="18"/>
       <c r="AV1" s="18"/>
       <c r="AX1" s="30" t="s">
-        <v>197</v>
+        <v>189</v>
       </c>
       <c r="AY1" s="18"/>
       <c r="AZ1" s="18"/>
@@ -6940,7 +6906,7 @@
       <c r="BB1" s="18"/>
       <c r="BC1" s="18"/>
       <c r="BE1" s="30" t="s">
-        <v>198</v>
+        <v>190</v>
       </c>
       <c r="BF1" s="18"/>
       <c r="BG1" s="18"/>
@@ -6948,7 +6914,7 @@
       <c r="BI1" s="18"/>
       <c r="BJ1" s="18"/>
       <c r="BL1" s="30" t="s">
-        <v>199</v>
+        <v>191</v>
       </c>
       <c r="BM1" s="18"/>
       <c r="BN1" s="18"/>
@@ -6956,7 +6922,7 @@
       <c r="BP1" s="18"/>
       <c r="BQ1" s="18"/>
       <c r="BS1" s="30" t="s">
-        <v>200</v>
+        <v>192</v>
       </c>
       <c r="BT1" s="18"/>
       <c r="BU1" s="18"/>
@@ -6964,7 +6930,7 @@
       <c r="BW1" s="18"/>
       <c r="BX1" s="18"/>
       <c r="BZ1" s="30" t="s">
-        <v>201</v>
+        <v>193</v>
       </c>
       <c r="CA1" s="18"/>
       <c r="CB1" s="18"/>
@@ -6972,7 +6938,7 @@
       <c r="CD1" s="18"/>
       <c r="CE1" s="18"/>
       <c r="CG1" s="30" t="s">
-        <v>202</v>
+        <v>194</v>
       </c>
       <c r="CH1" s="18"/>
       <c r="CI1" s="18"/>
@@ -6980,7 +6946,7 @@
       <c r="CK1" s="18"/>
       <c r="CL1" s="18"/>
       <c r="CN1" s="30" t="s">
-        <v>203</v>
+        <v>195</v>
       </c>
       <c r="CO1" s="18"/>
       <c r="CP1" s="18"/>
@@ -6988,7 +6954,7 @@
       <c r="CR1" s="18"/>
       <c r="CS1" s="18"/>
       <c r="CU1" s="30" t="s">
-        <v>204</v>
+        <v>196</v>
       </c>
       <c r="CV1" s="18"/>
       <c r="CW1" s="18"/>
@@ -6996,7 +6962,7 @@
       <c r="CY1" s="18"/>
       <c r="CZ1" s="18"/>
       <c r="DB1" s="30" t="s">
-        <v>205</v>
+        <v>197</v>
       </c>
       <c r="DC1" s="18"/>
       <c r="DD1" s="18"/>
@@ -7004,7 +6970,7 @@
       <c r="DF1" s="18"/>
       <c r="DG1" s="18"/>
       <c r="DI1" s="30" t="s">
-        <v>206</v>
+        <v>198</v>
       </c>
       <c r="DJ1" s="18"/>
       <c r="DK1" s="18"/>
@@ -7012,7 +6978,7 @@
       <c r="DM1" s="18"/>
       <c r="DN1" s="18"/>
       <c r="DP1" s="30" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="DQ1" s="18"/>
       <c r="DR1" s="18"/>
@@ -7020,7 +6986,7 @@
       <c r="DT1" s="18"/>
       <c r="DU1" s="18"/>
       <c r="DW1" s="30" t="s">
-        <v>208</v>
+        <v>200</v>
       </c>
       <c r="DX1" s="18"/>
       <c r="DY1" s="18"/>
@@ -7028,7 +6994,7 @@
       <c r="EA1" s="18"/>
       <c r="EB1" s="18"/>
       <c r="ED1" s="30" t="s">
-        <v>209</v>
+        <v>201</v>
       </c>
       <c r="EE1" s="18"/>
       <c r="EF1" s="18"/>
@@ -7036,7 +7002,7 @@
       <c r="EH1" s="18"/>
       <c r="EI1" s="18"/>
       <c r="EK1" s="30" t="s">
-        <v>210</v>
+        <v>202</v>
       </c>
       <c r="EL1" s="18"/>
       <c r="EM1" s="18"/>
@@ -7044,7 +7010,7 @@
       <c r="EO1" s="18"/>
       <c r="EP1" s="18"/>
       <c r="ER1" s="30" t="s">
-        <v>211</v>
+        <v>203</v>
       </c>
       <c r="ES1" s="18"/>
       <c r="ET1" s="18"/>
@@ -7052,7 +7018,7 @@
       <c r="EV1" s="18"/>
       <c r="EW1" s="18"/>
       <c r="EY1" s="30" t="s">
-        <v>212</v>
+        <v>204</v>
       </c>
       <c r="EZ1" s="18"/>
       <c r="FA1" s="18"/>
@@ -7648,7 +7614,7 @@
         <v>68</v>
       </c>
       <c r="B6" s="29" t="s">
-        <v>213</v>
+        <v>205</v>
       </c>
       <c r="C6" s="18"/>
       <c r="D6" s="18"/>
@@ -7658,7 +7624,7 @@
         <v>68</v>
       </c>
       <c r="I6" s="29" t="s">
-        <v>214</v>
+        <v>206</v>
       </c>
       <c r="J6" s="18"/>
       <c r="K6" s="18"/>
@@ -7668,7 +7634,7 @@
         <v>68</v>
       </c>
       <c r="P6" s="29" t="s">
-        <v>215</v>
+        <v>207</v>
       </c>
       <c r="Q6" s="18"/>
       <c r="R6" s="18"/>
@@ -7678,7 +7644,7 @@
         <v>68</v>
       </c>
       <c r="W6" s="29" t="s">
-        <v>216</v>
+        <v>208</v>
       </c>
       <c r="X6" s="18"/>
       <c r="Y6" s="18"/>
@@ -7688,7 +7654,7 @@
         <v>68</v>
       </c>
       <c r="AD6" s="29" t="s">
-        <v>217</v>
+        <v>209</v>
       </c>
       <c r="AE6" s="18"/>
       <c r="AF6" s="18"/>
@@ -7698,7 +7664,7 @@
         <v>68</v>
       </c>
       <c r="AK6" s="29" t="s">
-        <v>218</v>
+        <v>210</v>
       </c>
       <c r="AL6" s="18"/>
       <c r="AM6" s="18"/>
@@ -7708,7 +7674,7 @@
         <v>68</v>
       </c>
       <c r="AR6" s="29" t="s">
-        <v>219</v>
+        <v>211</v>
       </c>
       <c r="AS6" s="18"/>
       <c r="AT6" s="18"/>
@@ -7718,7 +7684,7 @@
         <v>68</v>
       </c>
       <c r="AY6" s="29" t="s">
-        <v>220</v>
+        <v>212</v>
       </c>
       <c r="AZ6" s="18"/>
       <c r="BA6" s="18"/>
@@ -7728,7 +7694,7 @@
         <v>68</v>
       </c>
       <c r="BF6" s="29" t="s">
-        <v>221</v>
+        <v>213</v>
       </c>
       <c r="BG6" s="18"/>
       <c r="BH6" s="18"/>
@@ -7738,7 +7704,7 @@
         <v>68</v>
       </c>
       <c r="BM6" s="29" t="s">
-        <v>222</v>
+        <v>214</v>
       </c>
       <c r="BN6" s="18"/>
       <c r="BO6" s="18"/>
@@ -7748,7 +7714,7 @@
         <v>68</v>
       </c>
       <c r="BT6" s="29" t="s">
-        <v>223</v>
+        <v>215</v>
       </c>
       <c r="BU6" s="18"/>
       <c r="BV6" s="18"/>
@@ -7758,7 +7724,7 @@
         <v>68</v>
       </c>
       <c r="CA6" s="29" t="s">
-        <v>224</v>
+        <v>216</v>
       </c>
       <c r="CB6" s="18"/>
       <c r="CC6" s="18"/>
@@ -7768,7 +7734,7 @@
         <v>68</v>
       </c>
       <c r="CH6" s="29" t="s">
-        <v>225</v>
+        <v>217</v>
       </c>
       <c r="CI6" s="18"/>
       <c r="CJ6" s="18"/>
@@ -7778,7 +7744,7 @@
         <v>68</v>
       </c>
       <c r="CO6" s="29" t="s">
-        <v>226</v>
+        <v>218</v>
       </c>
       <c r="CP6" s="18"/>
       <c r="CQ6" s="18"/>
@@ -7788,7 +7754,7 @@
         <v>68</v>
       </c>
       <c r="CV6" s="29" t="s">
-        <v>227</v>
+        <v>219</v>
       </c>
       <c r="CW6" s="18"/>
       <c r="CX6" s="18"/>
@@ -7798,7 +7764,7 @@
         <v>68</v>
       </c>
       <c r="DC6" s="29" t="s">
-        <v>228</v>
+        <v>220</v>
       </c>
       <c r="DD6" s="18"/>
       <c r="DE6" s="18"/>
@@ -7808,7 +7774,7 @@
         <v>68</v>
       </c>
       <c r="DJ6" s="29" t="s">
-        <v>229</v>
+        <v>221</v>
       </c>
       <c r="DK6" s="18"/>
       <c r="DL6" s="18"/>
@@ -7818,7 +7784,7 @@
         <v>68</v>
       </c>
       <c r="DQ6" s="29" t="s">
-        <v>230</v>
+        <v>222</v>
       </c>
       <c r="DR6" s="18"/>
       <c r="DS6" s="18"/>
@@ -7828,7 +7794,7 @@
         <v>68</v>
       </c>
       <c r="DX6" s="29" t="s">
-        <v>231</v>
+        <v>223</v>
       </c>
       <c r="DY6" s="18"/>
       <c r="DZ6" s="18"/>
@@ -7838,7 +7804,7 @@
         <v>68</v>
       </c>
       <c r="EE6" s="29" t="s">
-        <v>232</v>
+        <v>224</v>
       </c>
       <c r="EF6" s="18"/>
       <c r="EG6" s="18"/>
@@ -7848,7 +7814,7 @@
         <v>68</v>
       </c>
       <c r="EL6" s="29" t="s">
-        <v>233</v>
+        <v>225</v>
       </c>
       <c r="EM6" s="18"/>
       <c r="EN6" s="18"/>
@@ -7858,7 +7824,7 @@
         <v>68</v>
       </c>
       <c r="ES6" s="29" t="s">
-        <v>234</v>
+        <v>226</v>
       </c>
       <c r="ET6" s="18"/>
       <c r="EU6" s="18"/>
@@ -7868,7 +7834,7 @@
         <v>68</v>
       </c>
       <c r="EZ6" s="29" t="s">
-        <v>235</v>
+        <v>227</v>
       </c>
       <c r="FA6" s="18"/>
       <c r="FB6" s="18"/>
@@ -7880,7 +7846,7 @@
         <v>25</v>
       </c>
       <c r="B7" s="29" t="s">
-        <v>236</v>
+        <v>228</v>
       </c>
       <c r="C7" s="18"/>
       <c r="D7" s="18"/>
@@ -7890,7 +7856,7 @@
         <v>25</v>
       </c>
       <c r="I7" s="29" t="s">
-        <v>236</v>
+        <v>228</v>
       </c>
       <c r="J7" s="18"/>
       <c r="K7" s="18"/>
@@ -7900,7 +7866,7 @@
         <v>25</v>
       </c>
       <c r="P7" s="29" t="s">
-        <v>236</v>
+        <v>228</v>
       </c>
       <c r="Q7" s="18"/>
       <c r="R7" s="18"/>
@@ -7910,7 +7876,7 @@
         <v>25</v>
       </c>
       <c r="W7" s="29" t="s">
-        <v>236</v>
+        <v>228</v>
       </c>
       <c r="X7" s="18"/>
       <c r="Y7" s="18"/>
@@ -7920,7 +7886,7 @@
         <v>25</v>
       </c>
       <c r="AD7" s="29" t="s">
-        <v>236</v>
+        <v>228</v>
       </c>
       <c r="AE7" s="18"/>
       <c r="AF7" s="18"/>
@@ -7930,7 +7896,7 @@
         <v>25</v>
       </c>
       <c r="AK7" s="29" t="s">
-        <v>236</v>
+        <v>228</v>
       </c>
       <c r="AL7" s="18"/>
       <c r="AM7" s="18"/>
@@ -7940,7 +7906,7 @@
         <v>25</v>
       </c>
       <c r="AR7" s="29" t="s">
-        <v>236</v>
+        <v>228</v>
       </c>
       <c r="AS7" s="18"/>
       <c r="AT7" s="18"/>
@@ -7950,7 +7916,7 @@
         <v>25</v>
       </c>
       <c r="AY7" s="29" t="s">
-        <v>236</v>
+        <v>228</v>
       </c>
       <c r="AZ7" s="18"/>
       <c r="BA7" s="18"/>
@@ -7960,7 +7926,7 @@
         <v>25</v>
       </c>
       <c r="BF7" s="29" t="s">
-        <v>236</v>
+        <v>228</v>
       </c>
       <c r="BG7" s="18"/>
       <c r="BH7" s="18"/>
@@ -7970,7 +7936,7 @@
         <v>25</v>
       </c>
       <c r="BM7" s="29" t="s">
-        <v>236</v>
+        <v>228</v>
       </c>
       <c r="BN7" s="18"/>
       <c r="BO7" s="18"/>
@@ -7980,7 +7946,7 @@
         <v>25</v>
       </c>
       <c r="BT7" s="29" t="s">
-        <v>236</v>
+        <v>228</v>
       </c>
       <c r="BU7" s="18"/>
       <c r="BV7" s="18"/>
@@ -7990,7 +7956,7 @@
         <v>25</v>
       </c>
       <c r="CA7" s="29" t="s">
-        <v>236</v>
+        <v>228</v>
       </c>
       <c r="CB7" s="18"/>
       <c r="CC7" s="18"/>
@@ -8000,7 +7966,7 @@
         <v>25</v>
       </c>
       <c r="CH7" s="29" t="s">
-        <v>236</v>
+        <v>228</v>
       </c>
       <c r="CI7" s="18"/>
       <c r="CJ7" s="18"/>
@@ -8010,7 +7976,7 @@
         <v>25</v>
       </c>
       <c r="CO7" s="29" t="s">
-        <v>236</v>
+        <v>228</v>
       </c>
       <c r="CP7" s="18"/>
       <c r="CQ7" s="18"/>
@@ -8020,7 +7986,7 @@
         <v>25</v>
       </c>
       <c r="CV7" s="29" t="s">
-        <v>236</v>
+        <v>228</v>
       </c>
       <c r="CW7" s="18"/>
       <c r="CX7" s="18"/>
@@ -8030,7 +7996,7 @@
         <v>25</v>
       </c>
       <c r="DC7" s="29" t="s">
-        <v>236</v>
+        <v>228</v>
       </c>
       <c r="DD7" s="18"/>
       <c r="DE7" s="18"/>
@@ -8040,7 +8006,7 @@
         <v>25</v>
       </c>
       <c r="DJ7" s="29" t="s">
-        <v>236</v>
+        <v>228</v>
       </c>
       <c r="DK7" s="18"/>
       <c r="DL7" s="18"/>
@@ -8050,7 +8016,7 @@
         <v>25</v>
       </c>
       <c r="DQ7" s="29" t="s">
-        <v>236</v>
+        <v>228</v>
       </c>
       <c r="DR7" s="18"/>
       <c r="DS7" s="18"/>
@@ -8060,7 +8026,7 @@
         <v>25</v>
       </c>
       <c r="DX7" s="29" t="s">
-        <v>236</v>
+        <v>228</v>
       </c>
       <c r="DY7" s="18"/>
       <c r="DZ7" s="18"/>
@@ -8070,7 +8036,7 @@
         <v>25</v>
       </c>
       <c r="EE7" s="29" t="s">
-        <v>236</v>
+        <v>228</v>
       </c>
       <c r="EF7" s="18"/>
       <c r="EG7" s="18"/>
@@ -8080,7 +8046,7 @@
         <v>25</v>
       </c>
       <c r="EL7" s="29" t="s">
-        <v>236</v>
+        <v>228</v>
       </c>
       <c r="EM7" s="18"/>
       <c r="EN7" s="18"/>
@@ -8090,7 +8056,7 @@
         <v>25</v>
       </c>
       <c r="ES7" s="29" t="s">
-        <v>236</v>
+        <v>228</v>
       </c>
       <c r="ET7" s="18"/>
       <c r="EU7" s="18"/>
@@ -8100,7 +8066,7 @@
         <v>25</v>
       </c>
       <c r="EZ7" s="29" t="s">
-        <v>236</v>
+        <v>228</v>
       </c>
       <c r="FA7" s="18"/>
       <c r="FB7" s="18"/>
@@ -8525,880 +8491,880 @@
     </row>
     <row r="9" spans="1:160" ht="29.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="16" t="s">
-        <v>237</v>
+        <v>229</v>
       </c>
       <c r="B9" s="16" t="s">
-        <v>238</v>
+        <v>230</v>
       </c>
       <c r="C9" s="16" t="s">
-        <v>239</v>
+        <v>231</v>
       </c>
       <c r="D9" s="16" t="s">
-        <v>240</v>
+        <v>232</v>
       </c>
       <c r="E9" s="16"/>
       <c r="F9" s="16"/>
       <c r="H9" s="16" t="s">
-        <v>237</v>
+        <v>229</v>
       </c>
       <c r="I9" s="16" t="s">
-        <v>238</v>
+        <v>230</v>
       </c>
       <c r="J9" s="16" t="s">
-        <v>239</v>
+        <v>231</v>
       </c>
       <c r="K9" s="16" t="s">
-        <v>240</v>
+        <v>232</v>
       </c>
       <c r="L9" s="16"/>
       <c r="M9" s="16"/>
       <c r="O9" s="16" t="s">
-        <v>237</v>
+        <v>229</v>
       </c>
       <c r="P9" s="16" t="s">
-        <v>238</v>
+        <v>230</v>
       </c>
       <c r="Q9" s="16" t="s">
-        <v>239</v>
+        <v>231</v>
       </c>
       <c r="R9" s="16" t="s">
-        <v>240</v>
+        <v>232</v>
       </c>
       <c r="S9" s="16"/>
       <c r="T9" s="16"/>
       <c r="V9" s="16" t="s">
-        <v>237</v>
+        <v>229</v>
       </c>
       <c r="W9" s="16" t="s">
-        <v>238</v>
+        <v>230</v>
       </c>
       <c r="X9" s="16" t="s">
-        <v>239</v>
+        <v>231</v>
       </c>
       <c r="Y9" s="16" t="s">
-        <v>240</v>
+        <v>232</v>
       </c>
       <c r="Z9" s="16"/>
       <c r="AA9" s="16"/>
       <c r="AC9" s="16" t="s">
-        <v>237</v>
+        <v>229</v>
       </c>
       <c r="AD9" s="16" t="s">
-        <v>238</v>
+        <v>230</v>
       </c>
       <c r="AE9" s="16" t="s">
-        <v>239</v>
+        <v>231</v>
       </c>
       <c r="AF9" s="16" t="s">
-        <v>240</v>
+        <v>232</v>
       </c>
       <c r="AG9" s="16"/>
       <c r="AH9" s="16"/>
       <c r="AJ9" s="16" t="s">
-        <v>237</v>
+        <v>229</v>
       </c>
       <c r="AK9" s="16" t="s">
-        <v>238</v>
+        <v>230</v>
       </c>
       <c r="AL9" s="16" t="s">
-        <v>239</v>
+        <v>231</v>
       </c>
       <c r="AM9" s="16" t="s">
-        <v>240</v>
+        <v>232</v>
       </c>
       <c r="AN9" s="16"/>
       <c r="AO9" s="16"/>
       <c r="AQ9" s="16" t="s">
-        <v>237</v>
+        <v>229</v>
       </c>
       <c r="AR9" s="16" t="s">
-        <v>238</v>
+        <v>230</v>
       </c>
       <c r="AS9" s="16" t="s">
-        <v>239</v>
+        <v>231</v>
       </c>
       <c r="AT9" s="16" t="s">
-        <v>240</v>
+        <v>232</v>
       </c>
       <c r="AU9" s="16"/>
       <c r="AV9" s="16"/>
       <c r="AX9" s="16" t="s">
-        <v>237</v>
+        <v>229</v>
       </c>
       <c r="AY9" s="16" t="s">
-        <v>238</v>
+        <v>230</v>
       </c>
       <c r="AZ9" s="16" t="s">
-        <v>239</v>
+        <v>231</v>
       </c>
       <c r="BA9" s="16" t="s">
-        <v>240</v>
+        <v>232</v>
       </c>
       <c r="BB9" s="16"/>
       <c r="BC9" s="16"/>
       <c r="BE9" s="16" t="s">
-        <v>237</v>
+        <v>229</v>
       </c>
       <c r="BF9" s="16" t="s">
-        <v>238</v>
+        <v>230</v>
       </c>
       <c r="BG9" s="16" t="s">
-        <v>239</v>
+        <v>231</v>
       </c>
       <c r="BH9" s="16" t="s">
-        <v>240</v>
+        <v>232</v>
       </c>
       <c r="BI9" s="16"/>
       <c r="BJ9" s="16"/>
       <c r="BL9" s="16" t="s">
-        <v>237</v>
+        <v>229</v>
       </c>
       <c r="BM9" s="16" t="s">
-        <v>238</v>
+        <v>230</v>
       </c>
       <c r="BN9" s="16" t="s">
-        <v>239</v>
+        <v>231</v>
       </c>
       <c r="BO9" s="16" t="s">
-        <v>240</v>
+        <v>232</v>
       </c>
       <c r="BP9" s="16"/>
       <c r="BQ9" s="16"/>
       <c r="BS9" s="16" t="s">
-        <v>237</v>
+        <v>229</v>
       </c>
       <c r="BT9" s="16" t="s">
-        <v>238</v>
+        <v>230</v>
       </c>
       <c r="BU9" s="16" t="s">
-        <v>239</v>
+        <v>231</v>
       </c>
       <c r="BV9" s="16" t="s">
-        <v>240</v>
+        <v>232</v>
       </c>
       <c r="BW9" s="16"/>
       <c r="BX9" s="16"/>
       <c r="BZ9" s="16" t="s">
-        <v>237</v>
+        <v>229</v>
       </c>
       <c r="CA9" s="16" t="s">
-        <v>238</v>
+        <v>230</v>
       </c>
       <c r="CB9" s="16" t="s">
-        <v>239</v>
+        <v>231</v>
       </c>
       <c r="CC9" s="16" t="s">
-        <v>240</v>
+        <v>232</v>
       </c>
       <c r="CD9" s="16"/>
       <c r="CE9" s="16"/>
       <c r="CG9" s="16" t="s">
-        <v>237</v>
+        <v>229</v>
       </c>
       <c r="CH9" s="16" t="s">
-        <v>238</v>
+        <v>230</v>
       </c>
       <c r="CI9" s="16" t="s">
-        <v>239</v>
+        <v>231</v>
       </c>
       <c r="CJ9" s="16" t="s">
-        <v>240</v>
+        <v>232</v>
       </c>
       <c r="CK9" s="16"/>
       <c r="CL9" s="16"/>
       <c r="CN9" s="16" t="s">
-        <v>237</v>
+        <v>229</v>
       </c>
       <c r="CO9" s="16" t="s">
-        <v>238</v>
+        <v>230</v>
       </c>
       <c r="CP9" s="16" t="s">
-        <v>239</v>
+        <v>231</v>
       </c>
       <c r="CQ9" s="16" t="s">
-        <v>240</v>
+        <v>232</v>
       </c>
       <c r="CR9" s="16"/>
       <c r="CS9" s="16"/>
       <c r="CU9" s="16" t="s">
-        <v>237</v>
+        <v>229</v>
       </c>
       <c r="CV9" s="16" t="s">
-        <v>238</v>
+        <v>230</v>
       </c>
       <c r="CW9" s="16" t="s">
-        <v>239</v>
+        <v>231</v>
       </c>
       <c r="CX9" s="16" t="s">
-        <v>240</v>
+        <v>232</v>
       </c>
       <c r="CY9" s="16"/>
       <c r="CZ9" s="16"/>
       <c r="DB9" s="16" t="s">
-        <v>237</v>
+        <v>229</v>
       </c>
       <c r="DC9" s="16" t="s">
-        <v>238</v>
+        <v>230</v>
       </c>
       <c r="DD9" s="16" t="s">
-        <v>239</v>
+        <v>231</v>
       </c>
       <c r="DE9" s="16" t="s">
-        <v>240</v>
+        <v>232</v>
       </c>
       <c r="DF9" s="16"/>
       <c r="DG9" s="16"/>
       <c r="DI9" s="16" t="s">
-        <v>237</v>
+        <v>229</v>
       </c>
       <c r="DJ9" s="16" t="s">
-        <v>238</v>
+        <v>230</v>
       </c>
       <c r="DK9" s="16" t="s">
-        <v>239</v>
+        <v>231</v>
       </c>
       <c r="DL9" s="16" t="s">
-        <v>240</v>
+        <v>232</v>
       </c>
       <c r="DM9" s="16"/>
       <c r="DN9" s="16"/>
       <c r="DP9" s="16" t="s">
-        <v>237</v>
+        <v>229</v>
       </c>
       <c r="DQ9" s="16" t="s">
-        <v>238</v>
+        <v>230</v>
       </c>
       <c r="DR9" s="16" t="s">
-        <v>239</v>
+        <v>231</v>
       </c>
       <c r="DS9" s="16" t="s">
-        <v>240</v>
+        <v>232</v>
       </c>
       <c r="DT9" s="16"/>
       <c r="DU9" s="16"/>
       <c r="DW9" s="16" t="s">
-        <v>237</v>
+        <v>229</v>
       </c>
       <c r="DX9" s="16" t="s">
-        <v>238</v>
+        <v>230</v>
       </c>
       <c r="DY9" s="16" t="s">
-        <v>239</v>
+        <v>231</v>
       </c>
       <c r="DZ9" s="16" t="s">
-        <v>240</v>
+        <v>232</v>
       </c>
       <c r="EA9" s="16"/>
       <c r="EB9" s="16"/>
       <c r="ED9" s="16" t="s">
-        <v>237</v>
+        <v>229</v>
       </c>
       <c r="EE9" s="16" t="s">
-        <v>238</v>
+        <v>230</v>
       </c>
       <c r="EF9" s="16" t="s">
-        <v>239</v>
+        <v>231</v>
       </c>
       <c r="EG9" s="16" t="s">
-        <v>240</v>
+        <v>232</v>
       </c>
       <c r="EH9" s="16"/>
       <c r="EI9" s="16"/>
       <c r="EK9" s="16" t="s">
-        <v>237</v>
+        <v>229</v>
       </c>
       <c r="EL9" s="16" t="s">
-        <v>238</v>
+        <v>230</v>
       </c>
       <c r="EM9" s="16" t="s">
-        <v>239</v>
+        <v>231</v>
       </c>
       <c r="EN9" s="16" t="s">
-        <v>240</v>
+        <v>232</v>
       </c>
       <c r="EO9" s="16"/>
       <c r="EP9" s="16"/>
       <c r="ER9" s="16" t="s">
-        <v>237</v>
+        <v>229</v>
       </c>
       <c r="ES9" s="16" t="s">
-        <v>238</v>
+        <v>230</v>
       </c>
       <c r="ET9" s="16" t="s">
-        <v>239</v>
+        <v>231</v>
       </c>
       <c r="EU9" s="16" t="s">
-        <v>240</v>
+        <v>232</v>
       </c>
       <c r="EV9" s="16"/>
       <c r="EW9" s="16"/>
       <c r="EY9" s="16" t="s">
-        <v>237</v>
+        <v>229</v>
       </c>
       <c r="EZ9" s="16" t="s">
-        <v>238</v>
+        <v>230</v>
       </c>
       <c r="FA9" s="16" t="s">
-        <v>239</v>
+        <v>231</v>
       </c>
       <c r="FB9" s="16" t="s">
-        <v>240</v>
+        <v>232</v>
       </c>
       <c r="FC9" s="16"/>
       <c r="FD9" s="16"/>
     </row>
     <row r="10" spans="1:160" ht="29.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="16" t="s">
-        <v>241</v>
+        <v>233</v>
       </c>
       <c r="B10" s="16" t="s">
-        <v>242</v>
+        <v>234</v>
       </c>
       <c r="C10" s="16"/>
       <c r="D10" s="16" t="s">
-        <v>243</v>
+        <v>235</v>
       </c>
       <c r="E10" s="16"/>
       <c r="F10" s="16"/>
       <c r="H10" s="16" t="s">
-        <v>241</v>
+        <v>233</v>
       </c>
       <c r="I10" s="16" t="s">
-        <v>244</v>
+        <v>236</v>
       </c>
       <c r="J10" s="16"/>
       <c r="K10" s="16" t="s">
-        <v>243</v>
+        <v>235</v>
       </c>
       <c r="L10" s="16"/>
       <c r="M10" s="16"/>
       <c r="O10" s="16" t="s">
-        <v>241</v>
+        <v>233</v>
       </c>
       <c r="P10" s="16" t="s">
-        <v>244</v>
+        <v>236</v>
       </c>
       <c r="Q10" s="16"/>
       <c r="R10" s="16" t="s">
-        <v>243</v>
+        <v>235</v>
       </c>
       <c r="S10" s="16"/>
       <c r="T10" s="16"/>
       <c r="V10" s="16" t="s">
-        <v>241</v>
+        <v>233</v>
       </c>
       <c r="W10" s="16" t="s">
-        <v>244</v>
+        <v>236</v>
       </c>
       <c r="X10" s="16"/>
       <c r="Y10" s="16" t="s">
-        <v>243</v>
+        <v>235</v>
       </c>
       <c r="Z10" s="16"/>
       <c r="AA10" s="16"/>
       <c r="AC10" s="16" t="s">
-        <v>241</v>
+        <v>233</v>
       </c>
       <c r="AD10" s="16" t="s">
-        <v>245</v>
+        <v>237</v>
       </c>
       <c r="AE10" s="16"/>
       <c r="AF10" s="16" t="s">
-        <v>243</v>
+        <v>235</v>
       </c>
       <c r="AG10" s="16"/>
       <c r="AH10" s="16"/>
       <c r="AJ10" s="16" t="s">
-        <v>241</v>
+        <v>233</v>
       </c>
       <c r="AK10" s="16" t="s">
-        <v>245</v>
+        <v>237</v>
       </c>
       <c r="AL10" s="16"/>
       <c r="AM10" s="16" t="s">
-        <v>243</v>
+        <v>235</v>
       </c>
       <c r="AN10" s="16"/>
       <c r="AO10" s="16"/>
       <c r="AQ10" s="16" t="s">
-        <v>241</v>
+        <v>233</v>
       </c>
       <c r="AR10" s="16" t="s">
-        <v>246</v>
+        <v>238</v>
       </c>
       <c r="AS10" s="16"/>
       <c r="AT10" s="16" t="s">
-        <v>243</v>
+        <v>235</v>
       </c>
       <c r="AU10" s="16"/>
       <c r="AV10" s="16"/>
       <c r="AX10" s="16" t="s">
-        <v>241</v>
+        <v>233</v>
       </c>
       <c r="AY10" s="16" t="s">
-        <v>246</v>
+        <v>238</v>
       </c>
       <c r="AZ10" s="16"/>
       <c r="BA10" s="16" t="s">
-        <v>243</v>
+        <v>235</v>
       </c>
       <c r="BB10" s="16"/>
       <c r="BC10" s="16"/>
       <c r="BE10" s="16" t="s">
-        <v>241</v>
+        <v>233</v>
       </c>
       <c r="BF10" s="16" t="s">
-        <v>247</v>
+        <v>239</v>
       </c>
       <c r="BG10" s="16"/>
       <c r="BH10" s="16" t="s">
-        <v>243</v>
+        <v>235</v>
       </c>
       <c r="BI10" s="16"/>
       <c r="BJ10" s="16"/>
       <c r="BL10" s="16" t="s">
-        <v>241</v>
+        <v>233</v>
       </c>
       <c r="BM10" s="16" t="s">
-        <v>247</v>
+        <v>239</v>
       </c>
       <c r="BN10" s="16"/>
       <c r="BO10" s="16" t="s">
-        <v>243</v>
+        <v>235</v>
       </c>
       <c r="BP10" s="16"/>
       <c r="BQ10" s="16"/>
       <c r="BS10" s="16" t="s">
-        <v>241</v>
+        <v>233</v>
       </c>
       <c r="BT10" s="16" t="s">
-        <v>248</v>
+        <v>240</v>
       </c>
       <c r="BU10" s="16"/>
       <c r="BV10" s="16" t="s">
-        <v>243</v>
+        <v>235</v>
       </c>
       <c r="BW10" s="16"/>
       <c r="BX10" s="16"/>
       <c r="BZ10" s="16" t="s">
-        <v>241</v>
+        <v>233</v>
       </c>
       <c r="CA10" s="16" t="s">
-        <v>248</v>
+        <v>240</v>
       </c>
       <c r="CB10" s="16"/>
       <c r="CC10" s="16" t="s">
-        <v>243</v>
+        <v>235</v>
       </c>
       <c r="CD10" s="16"/>
       <c r="CE10" s="16"/>
       <c r="CG10" s="16" t="s">
+        <v>233</v>
+      </c>
+      <c r="CH10" s="16" t="s">
         <v>241</v>
-      </c>
-      <c r="CH10" s="16" t="s">
-        <v>249</v>
       </c>
       <c r="CI10" s="16"/>
       <c r="CJ10" s="16" t="s">
-        <v>243</v>
+        <v>235</v>
       </c>
       <c r="CK10" s="16"/>
       <c r="CL10" s="16"/>
       <c r="CN10" s="16" t="s">
-        <v>241</v>
+        <v>233</v>
       </c>
       <c r="CO10" s="16" t="s">
-        <v>250</v>
+        <v>242</v>
       </c>
       <c r="CP10" s="16"/>
       <c r="CQ10" s="16" t="s">
-        <v>243</v>
+        <v>235</v>
       </c>
       <c r="CR10" s="16"/>
       <c r="CS10" s="16"/>
       <c r="CU10" s="16" t="s">
-        <v>241</v>
+        <v>233</v>
       </c>
       <c r="CV10" s="16" t="s">
-        <v>250</v>
+        <v>242</v>
       </c>
       <c r="CW10" s="16"/>
       <c r="CX10" s="16" t="s">
-        <v>243</v>
+        <v>235</v>
       </c>
       <c r="CY10" s="16"/>
       <c r="CZ10" s="16"/>
       <c r="DB10" s="16" t="s">
-        <v>241</v>
+        <v>233</v>
       </c>
       <c r="DC10" s="16" t="s">
-        <v>250</v>
+        <v>242</v>
       </c>
       <c r="DD10" s="16"/>
       <c r="DE10" s="16" t="s">
-        <v>243</v>
+        <v>235</v>
       </c>
       <c r="DF10" s="16"/>
       <c r="DG10" s="16"/>
       <c r="DI10" s="16" t="s">
-        <v>241</v>
+        <v>233</v>
       </c>
       <c r="DJ10" s="16" t="s">
-        <v>251</v>
+        <v>243</v>
       </c>
       <c r="DK10" s="16"/>
       <c r="DL10" s="16" t="s">
-        <v>243</v>
+        <v>235</v>
       </c>
       <c r="DM10" s="16"/>
       <c r="DN10" s="16"/>
       <c r="DP10" s="16" t="s">
-        <v>241</v>
+        <v>233</v>
       </c>
       <c r="DQ10" s="16" t="s">
-        <v>251</v>
+        <v>243</v>
       </c>
       <c r="DR10" s="16"/>
       <c r="DS10" s="16" t="s">
-        <v>243</v>
+        <v>235</v>
       </c>
       <c r="DT10" s="16"/>
       <c r="DU10" s="16"/>
       <c r="DW10" s="16" t="s">
-        <v>241</v>
+        <v>233</v>
       </c>
       <c r="DX10" s="16" t="s">
-        <v>252</v>
+        <v>244</v>
       </c>
       <c r="DY10" s="16"/>
       <c r="DZ10" s="16" t="s">
-        <v>243</v>
+        <v>235</v>
       </c>
       <c r="EA10" s="16"/>
       <c r="EB10" s="16"/>
       <c r="ED10" s="16" t="s">
-        <v>241</v>
+        <v>233</v>
       </c>
       <c r="EE10" s="16" t="s">
-        <v>253</v>
+        <v>245</v>
       </c>
       <c r="EF10" s="16"/>
       <c r="EG10" s="16" t="s">
-        <v>243</v>
+        <v>235</v>
       </c>
       <c r="EH10" s="16"/>
       <c r="EI10" s="16"/>
       <c r="EK10" s="16" t="s">
-        <v>241</v>
+        <v>233</v>
       </c>
       <c r="EL10" s="16" t="s">
-        <v>253</v>
+        <v>245</v>
       </c>
       <c r="EM10" s="16"/>
       <c r="EN10" s="16" t="s">
-        <v>243</v>
+        <v>235</v>
       </c>
       <c r="EO10" s="16"/>
       <c r="EP10" s="16"/>
       <c r="ER10" s="16" t="s">
-        <v>241</v>
+        <v>233</v>
       </c>
       <c r="ES10" s="16" t="s">
-        <v>254</v>
+        <v>246</v>
       </c>
       <c r="ET10" s="16"/>
       <c r="EU10" s="16" t="s">
-        <v>243</v>
+        <v>235</v>
       </c>
       <c r="EV10" s="16"/>
       <c r="EW10" s="16"/>
       <c r="EY10" s="16" t="s">
-        <v>241</v>
+        <v>233</v>
       </c>
       <c r="EZ10" s="16" t="s">
-        <v>255</v>
+        <v>247</v>
       </c>
       <c r="FA10" s="16"/>
       <c r="FB10" s="16" t="s">
-        <v>243</v>
+        <v>235</v>
       </c>
       <c r="FC10" s="16"/>
       <c r="FD10" s="16"/>
     </row>
     <row r="11" spans="1:160" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="16" t="s">
-        <v>256</v>
+        <v>248</v>
       </c>
       <c r="B11" s="16" t="s">
-        <v>257</v>
+        <v>249</v>
       </c>
       <c r="C11" s="16"/>
       <c r="D11" s="16" t="s">
-        <v>258</v>
+        <v>250</v>
       </c>
       <c r="E11" s="16"/>
       <c r="F11" s="16"/>
       <c r="H11" s="16" t="s">
-        <v>256</v>
+        <v>248</v>
       </c>
       <c r="I11" s="16" t="s">
-        <v>257</v>
+        <v>249</v>
       </c>
       <c r="J11" s="16"/>
       <c r="K11" s="16" t="s">
-        <v>258</v>
+        <v>250</v>
       </c>
       <c r="L11" s="16"/>
       <c r="M11" s="16"/>
       <c r="O11" s="16" t="s">
-        <v>256</v>
+        <v>248</v>
       </c>
       <c r="P11" s="16" t="s">
-        <v>257</v>
+        <v>249</v>
       </c>
       <c r="Q11" s="16"/>
       <c r="R11" s="16" t="s">
-        <v>258</v>
+        <v>250</v>
       </c>
       <c r="S11" s="16"/>
       <c r="T11" s="16"/>
       <c r="V11" s="16" t="s">
-        <v>256</v>
+        <v>248</v>
       </c>
       <c r="W11" s="16" t="s">
-        <v>257</v>
+        <v>249</v>
       </c>
       <c r="X11" s="16"/>
       <c r="Y11" s="16" t="s">
-        <v>258</v>
+        <v>250</v>
       </c>
       <c r="Z11" s="16"/>
       <c r="AA11" s="16"/>
       <c r="AC11" s="16" t="s">
-        <v>256</v>
+        <v>248</v>
       </c>
       <c r="AD11" s="16" t="s">
-        <v>257</v>
+        <v>249</v>
       </c>
       <c r="AE11" s="16"/>
       <c r="AF11" s="16" t="s">
-        <v>258</v>
+        <v>250</v>
       </c>
       <c r="AG11" s="16"/>
       <c r="AH11" s="16"/>
       <c r="AJ11" s="16" t="s">
-        <v>256</v>
+        <v>248</v>
       </c>
       <c r="AK11" s="16" t="s">
-        <v>257</v>
+        <v>249</v>
       </c>
       <c r="AL11" s="16"/>
       <c r="AM11" s="16" t="s">
-        <v>258</v>
+        <v>250</v>
       </c>
       <c r="AN11" s="16"/>
       <c r="AO11" s="16"/>
       <c r="AQ11" s="16" t="s">
-        <v>256</v>
+        <v>248</v>
       </c>
       <c r="AR11" s="16" t="s">
-        <v>257</v>
+        <v>249</v>
       </c>
       <c r="AS11" s="16"/>
       <c r="AT11" s="16" t="s">
-        <v>258</v>
+        <v>250</v>
       </c>
       <c r="AU11" s="16"/>
       <c r="AV11" s="16"/>
       <c r="AX11" s="16" t="s">
-        <v>256</v>
+        <v>248</v>
       </c>
       <c r="AY11" s="16" t="s">
-        <v>257</v>
+        <v>249</v>
       </c>
       <c r="AZ11" s="16"/>
       <c r="BA11" s="16" t="s">
-        <v>258</v>
+        <v>250</v>
       </c>
       <c r="BB11" s="16"/>
       <c r="BC11" s="16"/>
       <c r="BE11" s="16" t="s">
-        <v>256</v>
+        <v>248</v>
       </c>
       <c r="BF11" s="16" t="s">
-        <v>257</v>
+        <v>249</v>
       </c>
       <c r="BG11" s="16"/>
       <c r="BH11" s="16" t="s">
-        <v>258</v>
+        <v>250</v>
       </c>
       <c r="BI11" s="16"/>
       <c r="BJ11" s="16"/>
       <c r="BL11" s="16" t="s">
-        <v>256</v>
+        <v>248</v>
       </c>
       <c r="BM11" s="16" t="s">
-        <v>257</v>
+        <v>249</v>
       </c>
       <c r="BN11" s="16"/>
       <c r="BO11" s="16" t="s">
-        <v>258</v>
+        <v>250</v>
       </c>
       <c r="BP11" s="16"/>
       <c r="BQ11" s="16"/>
       <c r="BS11" s="16" t="s">
-        <v>256</v>
+        <v>248</v>
       </c>
       <c r="BT11" s="16" t="s">
-        <v>257</v>
+        <v>249</v>
       </c>
       <c r="BU11" s="16"/>
       <c r="BV11" s="16" t="s">
-        <v>258</v>
+        <v>250</v>
       </c>
       <c r="BW11" s="16"/>
       <c r="BX11" s="16"/>
       <c r="BZ11" s="16" t="s">
-        <v>256</v>
+        <v>248</v>
       </c>
       <c r="CA11" s="16" t="s">
-        <v>257</v>
+        <v>249</v>
       </c>
       <c r="CB11" s="16"/>
       <c r="CC11" s="16" t="s">
-        <v>258</v>
+        <v>250</v>
       </c>
       <c r="CD11" s="16"/>
       <c r="CE11" s="16"/>
       <c r="CG11" s="16" t="s">
-        <v>256</v>
+        <v>248</v>
       </c>
       <c r="CH11" s="16" t="s">
-        <v>257</v>
+        <v>249</v>
       </c>
       <c r="CI11" s="16"/>
       <c r="CJ11" s="16" t="s">
-        <v>258</v>
+        <v>250</v>
       </c>
       <c r="CK11" s="16"/>
       <c r="CL11" s="16"/>
       <c r="CN11" s="16" t="s">
-        <v>256</v>
+        <v>248</v>
       </c>
       <c r="CO11" s="16" t="s">
-        <v>257</v>
+        <v>249</v>
       </c>
       <c r="CP11" s="16"/>
       <c r="CQ11" s="16" t="s">
-        <v>258</v>
+        <v>250</v>
       </c>
       <c r="CR11" s="16"/>
       <c r="CS11" s="16"/>
       <c r="CU11" s="16" t="s">
-        <v>256</v>
+        <v>248</v>
       </c>
       <c r="CV11" s="16" t="s">
-        <v>257</v>
+        <v>249</v>
       </c>
       <c r="CW11" s="16"/>
       <c r="CX11" s="16" t="s">
-        <v>258</v>
+        <v>250</v>
       </c>
       <c r="CY11" s="16"/>
       <c r="CZ11" s="16"/>
       <c r="DB11" s="16" t="s">
-        <v>256</v>
+        <v>248</v>
       </c>
       <c r="DC11" s="16" t="s">
-        <v>257</v>
+        <v>249</v>
       </c>
       <c r="DD11" s="16"/>
       <c r="DE11" s="16" t="s">
-        <v>258</v>
+        <v>250</v>
       </c>
       <c r="DF11" s="16"/>
       <c r="DG11" s="16"/>
       <c r="DI11" s="16" t="s">
-        <v>256</v>
+        <v>248</v>
       </c>
       <c r="DJ11" s="16" t="s">
-        <v>257</v>
+        <v>249</v>
       </c>
       <c r="DK11" s="16"/>
       <c r="DL11" s="16" t="s">
-        <v>258</v>
+        <v>250</v>
       </c>
       <c r="DM11" s="16"/>
       <c r="DN11" s="16"/>
       <c r="DP11" s="16" t="s">
-        <v>256</v>
+        <v>248</v>
       </c>
       <c r="DQ11" s="16" t="s">
-        <v>257</v>
+        <v>249</v>
       </c>
       <c r="DR11" s="16"/>
       <c r="DS11" s="16" t="s">
-        <v>258</v>
+        <v>250</v>
       </c>
       <c r="DT11" s="16"/>
       <c r="DU11" s="16"/>
       <c r="DW11" s="16" t="s">
-        <v>256</v>
+        <v>248</v>
       </c>
       <c r="DX11" s="16" t="s">
-        <v>257</v>
+        <v>249</v>
       </c>
       <c r="DY11" s="16"/>
       <c r="DZ11" s="16" t="s">
-        <v>258</v>
+        <v>250</v>
       </c>
       <c r="EA11" s="16"/>
       <c r="EB11" s="16"/>
       <c r="ED11" s="16" t="s">
-        <v>256</v>
+        <v>248</v>
       </c>
       <c r="EE11" s="16" t="s">
-        <v>257</v>
+        <v>249</v>
       </c>
       <c r="EF11" s="16"/>
       <c r="EG11" s="16" t="s">
-        <v>259</v>
+        <v>251</v>
       </c>
       <c r="EH11" s="16"/>
       <c r="EI11" s="16"/>
       <c r="EK11" s="16" t="s">
-        <v>256</v>
+        <v>248</v>
       </c>
       <c r="EL11" s="16" t="s">
-        <v>257</v>
+        <v>249</v>
       </c>
       <c r="EM11" s="16"/>
       <c r="EN11" s="16" t="s">
-        <v>258</v>
+        <v>250</v>
       </c>
       <c r="EO11" s="16"/>
       <c r="EP11" s="16"/>
       <c r="ER11" s="16" t="s">
-        <v>256</v>
+        <v>248</v>
       </c>
       <c r="ES11" s="16" t="s">
-        <v>257</v>
+        <v>249</v>
       </c>
       <c r="ET11" s="16"/>
       <c r="EU11" s="16" t="s">
-        <v>258</v>
+        <v>250</v>
       </c>
       <c r="EV11" s="16"/>
       <c r="EW11" s="16"/>
       <c r="EY11" s="16" t="s">
-        <v>256</v>
+        <v>248</v>
       </c>
       <c r="EZ11" s="16" t="s">
-        <v>257</v>
+        <v>249</v>
       </c>
       <c r="FA11" s="16"/>
       <c r="FB11" s="16" t="s">
-        <v>258</v>
+        <v>250</v>
       </c>
       <c r="FC11" s="16"/>
       <c r="FD11" s="16"/>
@@ -9511,7 +9477,7 @@
   <sheetData>
     <row r="1" spans="1:160" x14ac:dyDescent="0.25">
       <c r="A1" s="30" t="s">
-        <v>260</v>
+        <v>252</v>
       </c>
       <c r="B1" s="18"/>
       <c r="C1" s="18"/>
@@ -9519,7 +9485,7 @@
       <c r="E1" s="18"/>
       <c r="F1" s="18"/>
       <c r="H1" s="30" t="s">
-        <v>261</v>
+        <v>253</v>
       </c>
       <c r="I1" s="18"/>
       <c r="J1" s="18"/>
@@ -9527,7 +9493,7 @@
       <c r="L1" s="18"/>
       <c r="M1" s="18"/>
       <c r="O1" s="30" t="s">
-        <v>262</v>
+        <v>254</v>
       </c>
       <c r="P1" s="18"/>
       <c r="Q1" s="18"/>
@@ -9535,7 +9501,7 @@
       <c r="S1" s="18"/>
       <c r="T1" s="18"/>
       <c r="V1" s="30" t="s">
-        <v>263</v>
+        <v>255</v>
       </c>
       <c r="W1" s="18"/>
       <c r="X1" s="18"/>
@@ -9543,7 +9509,7 @@
       <c r="Z1" s="18"/>
       <c r="AA1" s="18"/>
       <c r="AC1" s="30" t="s">
-        <v>264</v>
+        <v>256</v>
       </c>
       <c r="AD1" s="18"/>
       <c r="AE1" s="18"/>
@@ -9551,7 +9517,7 @@
       <c r="AG1" s="18"/>
       <c r="AH1" s="18"/>
       <c r="AJ1" s="30" t="s">
-        <v>265</v>
+        <v>257</v>
       </c>
       <c r="AK1" s="18"/>
       <c r="AL1" s="18"/>
@@ -9559,7 +9525,7 @@
       <c r="AN1" s="18"/>
       <c r="AO1" s="18"/>
       <c r="AQ1" s="30" t="s">
-        <v>266</v>
+        <v>258</v>
       </c>
       <c r="AR1" s="18"/>
       <c r="AS1" s="18"/>
@@ -9567,7 +9533,7 @@
       <c r="AU1" s="18"/>
       <c r="AV1" s="18"/>
       <c r="AX1" s="30" t="s">
-        <v>267</v>
+        <v>259</v>
       </c>
       <c r="AY1" s="18"/>
       <c r="AZ1" s="18"/>
@@ -9575,7 +9541,7 @@
       <c r="BB1" s="18"/>
       <c r="BC1" s="18"/>
       <c r="BE1" s="30" t="s">
-        <v>268</v>
+        <v>260</v>
       </c>
       <c r="BF1" s="18"/>
       <c r="BG1" s="18"/>
@@ -9583,7 +9549,7 @@
       <c r="BI1" s="18"/>
       <c r="BJ1" s="18"/>
       <c r="BL1" s="30" t="s">
-        <v>269</v>
+        <v>261</v>
       </c>
       <c r="BM1" s="18"/>
       <c r="BN1" s="18"/>
@@ -9591,7 +9557,7 @@
       <c r="BP1" s="18"/>
       <c r="BQ1" s="18"/>
       <c r="BS1" s="30" t="s">
-        <v>270</v>
+        <v>262</v>
       </c>
       <c r="BT1" s="18"/>
       <c r="BU1" s="18"/>
@@ -9599,7 +9565,7 @@
       <c r="BW1" s="18"/>
       <c r="BX1" s="18"/>
       <c r="BZ1" s="30" t="s">
-        <v>271</v>
+        <v>263</v>
       </c>
       <c r="CA1" s="18"/>
       <c r="CB1" s="18"/>
@@ -9607,7 +9573,7 @@
       <c r="CD1" s="18"/>
       <c r="CE1" s="18"/>
       <c r="CG1" s="30" t="s">
-        <v>272</v>
+        <v>264</v>
       </c>
       <c r="CH1" s="18"/>
       <c r="CI1" s="18"/>
@@ -9615,7 +9581,7 @@
       <c r="CK1" s="18"/>
       <c r="CL1" s="18"/>
       <c r="CN1" s="30" t="s">
-        <v>273</v>
+        <v>265</v>
       </c>
       <c r="CO1" s="18"/>
       <c r="CP1" s="18"/>
@@ -9623,7 +9589,7 @@
       <c r="CR1" s="18"/>
       <c r="CS1" s="18"/>
       <c r="CU1" s="30" t="s">
-        <v>274</v>
+        <v>266</v>
       </c>
       <c r="CV1" s="18"/>
       <c r="CW1" s="18"/>
@@ -9631,7 +9597,7 @@
       <c r="CY1" s="18"/>
       <c r="CZ1" s="18"/>
       <c r="DB1" s="30" t="s">
-        <v>275</v>
+        <v>267</v>
       </c>
       <c r="DC1" s="18"/>
       <c r="DD1" s="18"/>
@@ -9639,7 +9605,7 @@
       <c r="DF1" s="18"/>
       <c r="DG1" s="18"/>
       <c r="DI1" s="30" t="s">
-        <v>276</v>
+        <v>268</v>
       </c>
       <c r="DJ1" s="18"/>
       <c r="DK1" s="18"/>
@@ -9647,7 +9613,7 @@
       <c r="DM1" s="18"/>
       <c r="DN1" s="18"/>
       <c r="DP1" s="30" t="s">
-        <v>277</v>
+        <v>269</v>
       </c>
       <c r="DQ1" s="18"/>
       <c r="DR1" s="18"/>
@@ -9655,7 +9621,7 @@
       <c r="DT1" s="18"/>
       <c r="DU1" s="18"/>
       <c r="DW1" s="30" t="s">
-        <v>278</v>
+        <v>270</v>
       </c>
       <c r="DX1" s="18"/>
       <c r="DY1" s="18"/>
@@ -9663,7 +9629,7 @@
       <c r="EA1" s="18"/>
       <c r="EB1" s="18"/>
       <c r="ED1" s="30" t="s">
-        <v>279</v>
+        <v>271</v>
       </c>
       <c r="EE1" s="18"/>
       <c r="EF1" s="18"/>
@@ -9671,7 +9637,7 @@
       <c r="EH1" s="18"/>
       <c r="EI1" s="18"/>
       <c r="EK1" s="30" t="s">
-        <v>280</v>
+        <v>272</v>
       </c>
       <c r="EL1" s="18"/>
       <c r="EM1" s="18"/>
@@ -9679,7 +9645,7 @@
       <c r="EO1" s="18"/>
       <c r="EP1" s="18"/>
       <c r="ER1" s="30" t="s">
-        <v>281</v>
+        <v>273</v>
       </c>
       <c r="ES1" s="18"/>
       <c r="ET1" s="18"/>
@@ -9687,7 +9653,7 @@
       <c r="EV1" s="18"/>
       <c r="EW1" s="18"/>
       <c r="EY1" s="30" t="s">
-        <v>282</v>
+        <v>274</v>
       </c>
       <c r="EZ1" s="18"/>
       <c r="FA1" s="18"/>
@@ -10283,7 +10249,7 @@
         <v>68</v>
       </c>
       <c r="B6" s="29" t="s">
-        <v>283</v>
+        <v>275</v>
       </c>
       <c r="C6" s="18"/>
       <c r="D6" s="18"/>
@@ -10293,7 +10259,7 @@
         <v>68</v>
       </c>
       <c r="I6" s="29" t="s">
-        <v>284</v>
+        <v>276</v>
       </c>
       <c r="J6" s="18"/>
       <c r="K6" s="18"/>
@@ -10303,7 +10269,7 @@
         <v>68</v>
       </c>
       <c r="P6" s="29" t="s">
-        <v>285</v>
+        <v>277</v>
       </c>
       <c r="Q6" s="18"/>
       <c r="R6" s="18"/>
@@ -10313,7 +10279,7 @@
         <v>68</v>
       </c>
       <c r="W6" s="29" t="s">
-        <v>286</v>
+        <v>278</v>
       </c>
       <c r="X6" s="18"/>
       <c r="Y6" s="18"/>
@@ -10323,7 +10289,7 @@
         <v>68</v>
       </c>
       <c r="AD6" s="29" t="s">
-        <v>287</v>
+        <v>279</v>
       </c>
       <c r="AE6" s="18"/>
       <c r="AF6" s="18"/>
@@ -10333,7 +10299,7 @@
         <v>68</v>
       </c>
       <c r="AK6" s="29" t="s">
-        <v>288</v>
+        <v>280</v>
       </c>
       <c r="AL6" s="18"/>
       <c r="AM6" s="18"/>
@@ -10343,7 +10309,7 @@
         <v>68</v>
       </c>
       <c r="AR6" s="29" t="s">
-        <v>289</v>
+        <v>281</v>
       </c>
       <c r="AS6" s="18"/>
       <c r="AT6" s="18"/>
@@ -10353,7 +10319,7 @@
         <v>68</v>
       </c>
       <c r="AY6" s="29" t="s">
-        <v>290</v>
+        <v>282</v>
       </c>
       <c r="AZ6" s="18"/>
       <c r="BA6" s="18"/>
@@ -10363,7 +10329,7 @@
         <v>68</v>
       </c>
       <c r="BF6" s="29" t="s">
-        <v>291</v>
+        <v>283</v>
       </c>
       <c r="BG6" s="18"/>
       <c r="BH6" s="18"/>
@@ -10373,7 +10339,7 @@
         <v>68</v>
       </c>
       <c r="BM6" s="29" t="s">
-        <v>292</v>
+        <v>284</v>
       </c>
       <c r="BN6" s="18"/>
       <c r="BO6" s="18"/>
@@ -10383,7 +10349,7 @@
         <v>68</v>
       </c>
       <c r="BT6" s="29" t="s">
-        <v>293</v>
+        <v>285</v>
       </c>
       <c r="BU6" s="18"/>
       <c r="BV6" s="18"/>
@@ -10393,7 +10359,7 @@
         <v>68</v>
       </c>
       <c r="CA6" s="29" t="s">
-        <v>294</v>
+        <v>286</v>
       </c>
       <c r="CB6" s="18"/>
       <c r="CC6" s="18"/>
@@ -10403,7 +10369,7 @@
         <v>68</v>
       </c>
       <c r="CH6" s="29" t="s">
-        <v>295</v>
+        <v>287</v>
       </c>
       <c r="CI6" s="18"/>
       <c r="CJ6" s="18"/>
@@ -10413,7 +10379,7 @@
         <v>68</v>
       </c>
       <c r="CO6" s="29" t="s">
-        <v>296</v>
+        <v>288</v>
       </c>
       <c r="CP6" s="18"/>
       <c r="CQ6" s="18"/>
@@ -10423,7 +10389,7 @@
         <v>68</v>
       </c>
       <c r="CV6" s="29" t="s">
-        <v>297</v>
+        <v>289</v>
       </c>
       <c r="CW6" s="18"/>
       <c r="CX6" s="18"/>
@@ -10433,7 +10399,7 @@
         <v>68</v>
       </c>
       <c r="DC6" s="29" t="s">
-        <v>298</v>
+        <v>290</v>
       </c>
       <c r="DD6" s="18"/>
       <c r="DE6" s="18"/>
@@ -10443,7 +10409,7 @@
         <v>68</v>
       </c>
       <c r="DJ6" s="29" t="s">
-        <v>299</v>
+        <v>291</v>
       </c>
       <c r="DK6" s="18"/>
       <c r="DL6" s="18"/>
@@ -10453,7 +10419,7 @@
         <v>68</v>
       </c>
       <c r="DQ6" s="29" t="s">
-        <v>300</v>
+        <v>292</v>
       </c>
       <c r="DR6" s="18"/>
       <c r="DS6" s="18"/>
@@ -10463,7 +10429,7 @@
         <v>68</v>
       </c>
       <c r="DX6" s="29" t="s">
-        <v>301</v>
+        <v>293</v>
       </c>
       <c r="DY6" s="18"/>
       <c r="DZ6" s="18"/>
@@ -10473,7 +10439,7 @@
         <v>68</v>
       </c>
       <c r="EE6" s="29" t="s">
-        <v>302</v>
+        <v>294</v>
       </c>
       <c r="EF6" s="18"/>
       <c r="EG6" s="18"/>
@@ -10483,7 +10449,7 @@
         <v>68</v>
       </c>
       <c r="EL6" s="29" t="s">
-        <v>303</v>
+        <v>295</v>
       </c>
       <c r="EM6" s="18"/>
       <c r="EN6" s="18"/>
@@ -10493,7 +10459,7 @@
         <v>68</v>
       </c>
       <c r="ES6" s="29" t="s">
-        <v>304</v>
+        <v>296</v>
       </c>
       <c r="ET6" s="18"/>
       <c r="EU6" s="18"/>
@@ -10503,7 +10469,7 @@
         <v>68</v>
       </c>
       <c r="EZ6" s="29" t="s">
-        <v>305</v>
+        <v>297</v>
       </c>
       <c r="FA6" s="18"/>
       <c r="FB6" s="18"/>
@@ -10515,7 +10481,7 @@
         <v>25</v>
       </c>
       <c r="B7" s="29" t="s">
-        <v>236</v>
+        <v>228</v>
       </c>
       <c r="C7" s="18"/>
       <c r="D7" s="18"/>
@@ -10525,7 +10491,7 @@
         <v>25</v>
       </c>
       <c r="I7" s="29" t="s">
-        <v>236</v>
+        <v>228</v>
       </c>
       <c r="J7" s="18"/>
       <c r="K7" s="18"/>
@@ -10535,7 +10501,7 @@
         <v>25</v>
       </c>
       <c r="P7" s="29" t="s">
-        <v>236</v>
+        <v>228</v>
       </c>
       <c r="Q7" s="18"/>
       <c r="R7" s="18"/>
@@ -10545,7 +10511,7 @@
         <v>25</v>
       </c>
       <c r="W7" s="29" t="s">
-        <v>236</v>
+        <v>228</v>
       </c>
       <c r="X7" s="18"/>
       <c r="Y7" s="18"/>
@@ -10555,7 +10521,7 @@
         <v>25</v>
       </c>
       <c r="AD7" s="29" t="s">
-        <v>236</v>
+        <v>228</v>
       </c>
       <c r="AE7" s="18"/>
       <c r="AF7" s="18"/>
@@ -10565,7 +10531,7 @@
         <v>25</v>
       </c>
       <c r="AK7" s="29" t="s">
-        <v>236</v>
+        <v>228</v>
       </c>
       <c r="AL7" s="18"/>
       <c r="AM7" s="18"/>
@@ -10575,7 +10541,7 @@
         <v>25</v>
       </c>
       <c r="AR7" s="29" t="s">
-        <v>236</v>
+        <v>228</v>
       </c>
       <c r="AS7" s="18"/>
       <c r="AT7" s="18"/>
@@ -10585,7 +10551,7 @@
         <v>25</v>
       </c>
       <c r="AY7" s="29" t="s">
-        <v>236</v>
+        <v>228</v>
       </c>
       <c r="AZ7" s="18"/>
       <c r="BA7" s="18"/>
@@ -10595,7 +10561,7 @@
         <v>25</v>
       </c>
       <c r="BF7" s="29" t="s">
-        <v>236</v>
+        <v>228</v>
       </c>
       <c r="BG7" s="18"/>
       <c r="BH7" s="18"/>
@@ -10605,7 +10571,7 @@
         <v>25</v>
       </c>
       <c r="BM7" s="29" t="s">
-        <v>236</v>
+        <v>228</v>
       </c>
       <c r="BN7" s="18"/>
       <c r="BO7" s="18"/>
@@ -10615,7 +10581,7 @@
         <v>25</v>
       </c>
       <c r="BT7" s="29" t="s">
-        <v>236</v>
+        <v>228</v>
       </c>
       <c r="BU7" s="18"/>
       <c r="BV7" s="18"/>
@@ -10625,7 +10591,7 @@
         <v>25</v>
       </c>
       <c r="CA7" s="29" t="s">
-        <v>236</v>
+        <v>228</v>
       </c>
       <c r="CB7" s="18"/>
       <c r="CC7" s="18"/>
@@ -10635,7 +10601,7 @@
         <v>25</v>
       </c>
       <c r="CH7" s="29" t="s">
-        <v>236</v>
+        <v>228</v>
       </c>
       <c r="CI7" s="18"/>
       <c r="CJ7" s="18"/>
@@ -10645,7 +10611,7 @@
         <v>25</v>
       </c>
       <c r="CO7" s="29" t="s">
-        <v>236</v>
+        <v>228</v>
       </c>
       <c r="CP7" s="18"/>
       <c r="CQ7" s="18"/>
@@ -10655,7 +10621,7 @@
         <v>25</v>
       </c>
       <c r="CV7" s="29" t="s">
-        <v>236</v>
+        <v>228</v>
       </c>
       <c r="CW7" s="18"/>
       <c r="CX7" s="18"/>
@@ -10665,7 +10631,7 @@
         <v>25</v>
       </c>
       <c r="DC7" s="29" t="s">
-        <v>236</v>
+        <v>228</v>
       </c>
       <c r="DD7" s="18"/>
       <c r="DE7" s="18"/>
@@ -10675,7 +10641,7 @@
         <v>25</v>
       </c>
       <c r="DJ7" s="29" t="s">
-        <v>236</v>
+        <v>228</v>
       </c>
       <c r="DK7" s="18"/>
       <c r="DL7" s="18"/>
@@ -10685,7 +10651,7 @@
         <v>25</v>
       </c>
       <c r="DQ7" s="29" t="s">
-        <v>236</v>
+        <v>228</v>
       </c>
       <c r="DR7" s="18"/>
       <c r="DS7" s="18"/>
@@ -10695,7 +10661,7 @@
         <v>25</v>
       </c>
       <c r="DX7" s="29" t="s">
-        <v>236</v>
+        <v>228</v>
       </c>
       <c r="DY7" s="18"/>
       <c r="DZ7" s="18"/>
@@ -10705,7 +10671,7 @@
         <v>25</v>
       </c>
       <c r="EE7" s="29" t="s">
-        <v>236</v>
+        <v>228</v>
       </c>
       <c r="EF7" s="18"/>
       <c r="EG7" s="18"/>
@@ -10715,7 +10681,7 @@
         <v>25</v>
       </c>
       <c r="EL7" s="29" t="s">
-        <v>236</v>
+        <v>228</v>
       </c>
       <c r="EM7" s="18"/>
       <c r="EN7" s="18"/>
@@ -10725,7 +10691,7 @@
         <v>25</v>
       </c>
       <c r="ES7" s="29" t="s">
-        <v>236</v>
+        <v>228</v>
       </c>
       <c r="ET7" s="18"/>
       <c r="EU7" s="18"/>
@@ -10735,7 +10701,7 @@
         <v>25</v>
       </c>
       <c r="EZ7" s="29" t="s">
-        <v>236</v>
+        <v>228</v>
       </c>
       <c r="FA7" s="18"/>
       <c r="FB7" s="18"/>
@@ -11160,880 +11126,880 @@
     </row>
     <row r="9" spans="1:160" ht="29.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="16" t="s">
-        <v>237</v>
+        <v>229</v>
       </c>
       <c r="B9" s="16" t="s">
-        <v>238</v>
+        <v>230</v>
       </c>
       <c r="C9" s="16" t="s">
-        <v>239</v>
+        <v>231</v>
       </c>
       <c r="D9" s="16" t="s">
-        <v>240</v>
+        <v>232</v>
       </c>
       <c r="E9" s="16"/>
       <c r="F9" s="16"/>
       <c r="H9" s="16" t="s">
-        <v>237</v>
+        <v>229</v>
       </c>
       <c r="I9" s="16" t="s">
-        <v>238</v>
+        <v>230</v>
       </c>
       <c r="J9" s="16" t="s">
-        <v>239</v>
+        <v>231</v>
       </c>
       <c r="K9" s="16" t="s">
-        <v>240</v>
+        <v>232</v>
       </c>
       <c r="L9" s="16"/>
       <c r="M9" s="16"/>
       <c r="O9" s="16" t="s">
-        <v>237</v>
+        <v>229</v>
       </c>
       <c r="P9" s="16" t="s">
-        <v>238</v>
+        <v>230</v>
       </c>
       <c r="Q9" s="16" t="s">
-        <v>239</v>
+        <v>231</v>
       </c>
       <c r="R9" s="16" t="s">
-        <v>240</v>
+        <v>232</v>
       </c>
       <c r="S9" s="16"/>
       <c r="T9" s="16"/>
       <c r="V9" s="16" t="s">
-        <v>237</v>
+        <v>229</v>
       </c>
       <c r="W9" s="16" t="s">
-        <v>238</v>
+        <v>230</v>
       </c>
       <c r="X9" s="16" t="s">
-        <v>239</v>
+        <v>231</v>
       </c>
       <c r="Y9" s="16" t="s">
-        <v>240</v>
+        <v>232</v>
       </c>
       <c r="Z9" s="16"/>
       <c r="AA9" s="16"/>
       <c r="AC9" s="16" t="s">
-        <v>237</v>
+        <v>229</v>
       </c>
       <c r="AD9" s="16" t="s">
-        <v>238</v>
+        <v>230</v>
       </c>
       <c r="AE9" s="16" t="s">
-        <v>239</v>
+        <v>231</v>
       </c>
       <c r="AF9" s="16" t="s">
-        <v>240</v>
+        <v>232</v>
       </c>
       <c r="AG9" s="16"/>
       <c r="AH9" s="16"/>
       <c r="AJ9" s="16" t="s">
-        <v>237</v>
+        <v>229</v>
       </c>
       <c r="AK9" s="16" t="s">
-        <v>238</v>
+        <v>230</v>
       </c>
       <c r="AL9" s="16" t="s">
-        <v>239</v>
+        <v>231</v>
       </c>
       <c r="AM9" s="16" t="s">
-        <v>240</v>
+        <v>232</v>
       </c>
       <c r="AN9" s="16"/>
       <c r="AO9" s="16"/>
       <c r="AQ9" s="16" t="s">
-        <v>237</v>
+        <v>229</v>
       </c>
       <c r="AR9" s="16" t="s">
-        <v>238</v>
+        <v>230</v>
       </c>
       <c r="AS9" s="16" t="s">
-        <v>239</v>
+        <v>231</v>
       </c>
       <c r="AT9" s="16" t="s">
-        <v>240</v>
+        <v>232</v>
       </c>
       <c r="AU9" s="16"/>
       <c r="AV9" s="16"/>
       <c r="AX9" s="16" t="s">
-        <v>237</v>
+        <v>229</v>
       </c>
       <c r="AY9" s="16" t="s">
-        <v>238</v>
+        <v>230</v>
       </c>
       <c r="AZ9" s="16" t="s">
-        <v>239</v>
+        <v>231</v>
       </c>
       <c r="BA9" s="16" t="s">
-        <v>240</v>
+        <v>232</v>
       </c>
       <c r="BB9" s="16"/>
       <c r="BC9" s="16"/>
       <c r="BE9" s="16" t="s">
-        <v>237</v>
+        <v>229</v>
       </c>
       <c r="BF9" s="16" t="s">
-        <v>238</v>
+        <v>230</v>
       </c>
       <c r="BG9" s="16" t="s">
-        <v>239</v>
+        <v>231</v>
       </c>
       <c r="BH9" s="16" t="s">
-        <v>240</v>
+        <v>232</v>
       </c>
       <c r="BI9" s="16"/>
       <c r="BJ9" s="16"/>
       <c r="BL9" s="16" t="s">
-        <v>237</v>
+        <v>229</v>
       </c>
       <c r="BM9" s="16" t="s">
-        <v>238</v>
+        <v>230</v>
       </c>
       <c r="BN9" s="16" t="s">
-        <v>239</v>
+        <v>231</v>
       </c>
       <c r="BO9" s="16" t="s">
-        <v>240</v>
+        <v>232</v>
       </c>
       <c r="BP9" s="16"/>
       <c r="BQ9" s="16"/>
       <c r="BS9" s="16" t="s">
-        <v>237</v>
+        <v>229</v>
       </c>
       <c r="BT9" s="16" t="s">
-        <v>238</v>
+        <v>230</v>
       </c>
       <c r="BU9" s="16" t="s">
-        <v>239</v>
+        <v>231</v>
       </c>
       <c r="BV9" s="16" t="s">
-        <v>240</v>
+        <v>232</v>
       </c>
       <c r="BW9" s="16"/>
       <c r="BX9" s="16"/>
       <c r="BZ9" s="16" t="s">
-        <v>237</v>
+        <v>229</v>
       </c>
       <c r="CA9" s="16" t="s">
-        <v>238</v>
+        <v>230</v>
       </c>
       <c r="CB9" s="16" t="s">
-        <v>239</v>
+        <v>231</v>
       </c>
       <c r="CC9" s="16" t="s">
-        <v>240</v>
+        <v>232</v>
       </c>
       <c r="CD9" s="16"/>
       <c r="CE9" s="16"/>
       <c r="CG9" s="16" t="s">
-        <v>237</v>
+        <v>229</v>
       </c>
       <c r="CH9" s="16" t="s">
-        <v>238</v>
+        <v>230</v>
       </c>
       <c r="CI9" s="16" t="s">
-        <v>239</v>
+        <v>231</v>
       </c>
       <c r="CJ9" s="16" t="s">
-        <v>240</v>
+        <v>232</v>
       </c>
       <c r="CK9" s="16"/>
       <c r="CL9" s="16"/>
       <c r="CN9" s="16" t="s">
-        <v>237</v>
+        <v>229</v>
       </c>
       <c r="CO9" s="16" t="s">
-        <v>238</v>
+        <v>230</v>
       </c>
       <c r="CP9" s="16" t="s">
-        <v>239</v>
+        <v>231</v>
       </c>
       <c r="CQ9" s="16" t="s">
-        <v>240</v>
+        <v>232</v>
       </c>
       <c r="CR9" s="16"/>
       <c r="CS9" s="16"/>
       <c r="CU9" s="16" t="s">
-        <v>237</v>
+        <v>229</v>
       </c>
       <c r="CV9" s="16" t="s">
-        <v>238</v>
+        <v>230</v>
       </c>
       <c r="CW9" s="16" t="s">
-        <v>239</v>
+        <v>231</v>
       </c>
       <c r="CX9" s="16" t="s">
-        <v>240</v>
+        <v>232</v>
       </c>
       <c r="CY9" s="16"/>
       <c r="CZ9" s="16"/>
       <c r="DB9" s="16" t="s">
-        <v>237</v>
+        <v>229</v>
       </c>
       <c r="DC9" s="16" t="s">
-        <v>238</v>
+        <v>230</v>
       </c>
       <c r="DD9" s="16" t="s">
-        <v>239</v>
+        <v>231</v>
       </c>
       <c r="DE9" s="16" t="s">
-        <v>240</v>
+        <v>232</v>
       </c>
       <c r="DF9" s="16"/>
       <c r="DG9" s="16"/>
       <c r="DI9" s="16" t="s">
-        <v>237</v>
+        <v>229</v>
       </c>
       <c r="DJ9" s="16" t="s">
-        <v>238</v>
+        <v>230</v>
       </c>
       <c r="DK9" s="16" t="s">
-        <v>239</v>
+        <v>231</v>
       </c>
       <c r="DL9" s="16" t="s">
-        <v>240</v>
+        <v>232</v>
       </c>
       <c r="DM9" s="16"/>
       <c r="DN9" s="16"/>
       <c r="DP9" s="16" t="s">
-        <v>237</v>
+        <v>229</v>
       </c>
       <c r="DQ9" s="16" t="s">
-        <v>238</v>
+        <v>230</v>
       </c>
       <c r="DR9" s="16" t="s">
-        <v>239</v>
+        <v>231</v>
       </c>
       <c r="DS9" s="16" t="s">
-        <v>240</v>
+        <v>232</v>
       </c>
       <c r="DT9" s="16"/>
       <c r="DU9" s="16"/>
       <c r="DW9" s="16" t="s">
-        <v>237</v>
+        <v>229</v>
       </c>
       <c r="DX9" s="16" t="s">
-        <v>238</v>
+        <v>230</v>
       </c>
       <c r="DY9" s="16" t="s">
-        <v>239</v>
+        <v>231</v>
       </c>
       <c r="DZ9" s="16" t="s">
-        <v>240</v>
+        <v>232</v>
       </c>
       <c r="EA9" s="16"/>
       <c r="EB9" s="16"/>
       <c r="ED9" s="16" t="s">
-        <v>237</v>
+        <v>229</v>
       </c>
       <c r="EE9" s="16" t="s">
-        <v>238</v>
+        <v>230</v>
       </c>
       <c r="EF9" s="16" t="s">
-        <v>239</v>
+        <v>231</v>
       </c>
       <c r="EG9" s="16" t="s">
-        <v>240</v>
+        <v>232</v>
       </c>
       <c r="EH9" s="16"/>
       <c r="EI9" s="16"/>
       <c r="EK9" s="16" t="s">
-        <v>237</v>
+        <v>229</v>
       </c>
       <c r="EL9" s="16" t="s">
-        <v>238</v>
+        <v>230</v>
       </c>
       <c r="EM9" s="16" t="s">
-        <v>239</v>
+        <v>231</v>
       </c>
       <c r="EN9" s="16" t="s">
-        <v>240</v>
+        <v>232</v>
       </c>
       <c r="EO9" s="16"/>
       <c r="EP9" s="16"/>
       <c r="ER9" s="16" t="s">
-        <v>237</v>
+        <v>229</v>
       </c>
       <c r="ES9" s="16" t="s">
-        <v>238</v>
+        <v>230</v>
       </c>
       <c r="ET9" s="16" t="s">
-        <v>239</v>
+        <v>231</v>
       </c>
       <c r="EU9" s="16" t="s">
-        <v>240</v>
+        <v>232</v>
       </c>
       <c r="EV9" s="16"/>
       <c r="EW9" s="16"/>
       <c r="EY9" s="16" t="s">
-        <v>237</v>
+        <v>229</v>
       </c>
       <c r="EZ9" s="16" t="s">
-        <v>238</v>
+        <v>230</v>
       </c>
       <c r="FA9" s="16" t="s">
-        <v>239</v>
+        <v>231</v>
       </c>
       <c r="FB9" s="16" t="s">
-        <v>240</v>
+        <v>232</v>
       </c>
       <c r="FC9" s="16"/>
       <c r="FD9" s="16"/>
     </row>
     <row r="10" spans="1:160" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="16" t="s">
-        <v>241</v>
+        <v>233</v>
       </c>
       <c r="B10" s="16" t="s">
-        <v>306</v>
+        <v>298</v>
       </c>
       <c r="C10" s="16"/>
       <c r="D10" s="16" t="s">
-        <v>243</v>
+        <v>235</v>
       </c>
       <c r="E10" s="16"/>
       <c r="F10" s="16"/>
       <c r="H10" s="16" t="s">
-        <v>241</v>
+        <v>233</v>
       </c>
       <c r="I10" s="16" t="s">
-        <v>307</v>
+        <v>299</v>
       </c>
       <c r="J10" s="16"/>
       <c r="K10" s="16" t="s">
-        <v>243</v>
+        <v>235</v>
       </c>
       <c r="L10" s="16"/>
       <c r="M10" s="16"/>
       <c r="O10" s="16" t="s">
-        <v>241</v>
+        <v>233</v>
       </c>
       <c r="P10" s="16" t="s">
-        <v>308</v>
+        <v>300</v>
       </c>
       <c r="Q10" s="16"/>
       <c r="R10" s="16" t="s">
-        <v>243</v>
+        <v>235</v>
       </c>
       <c r="S10" s="16"/>
       <c r="T10" s="16"/>
       <c r="V10" s="16" t="s">
-        <v>241</v>
+        <v>233</v>
       </c>
       <c r="W10" s="16" t="s">
-        <v>252</v>
+        <v>244</v>
       </c>
       <c r="X10" s="16"/>
       <c r="Y10" s="16" t="s">
-        <v>243</v>
+        <v>235</v>
       </c>
       <c r="Z10" s="16"/>
       <c r="AA10" s="16"/>
       <c r="AC10" s="16" t="s">
-        <v>241</v>
+        <v>233</v>
       </c>
       <c r="AD10" s="16" t="s">
-        <v>309</v>
+        <v>301</v>
       </c>
       <c r="AE10" s="16"/>
       <c r="AF10" s="16" t="s">
-        <v>243</v>
+        <v>235</v>
       </c>
       <c r="AG10" s="16"/>
       <c r="AH10" s="16"/>
       <c r="AJ10" s="16" t="s">
-        <v>241</v>
+        <v>233</v>
       </c>
       <c r="AK10" s="16" t="s">
-        <v>309</v>
+        <v>301</v>
       </c>
       <c r="AL10" s="16"/>
       <c r="AM10" s="16" t="s">
-        <v>243</v>
+        <v>235</v>
       </c>
       <c r="AN10" s="16"/>
       <c r="AO10" s="16"/>
       <c r="AQ10" s="16" t="s">
-        <v>241</v>
+        <v>233</v>
       </c>
       <c r="AR10" s="16" t="s">
-        <v>309</v>
+        <v>301</v>
       </c>
       <c r="AS10" s="16"/>
       <c r="AT10" s="16" t="s">
-        <v>243</v>
+        <v>235</v>
       </c>
       <c r="AU10" s="16"/>
       <c r="AV10" s="16"/>
       <c r="AX10" s="16" t="s">
-        <v>241</v>
+        <v>233</v>
       </c>
       <c r="AY10" s="16" t="s">
-        <v>309</v>
+        <v>301</v>
       </c>
       <c r="AZ10" s="16"/>
       <c r="BA10" s="16" t="s">
-        <v>243</v>
+        <v>235</v>
       </c>
       <c r="BB10" s="16"/>
       <c r="BC10" s="16"/>
       <c r="BE10" s="16" t="s">
-        <v>241</v>
+        <v>233</v>
       </c>
       <c r="BF10" s="16" t="s">
-        <v>309</v>
+        <v>301</v>
       </c>
       <c r="BG10" s="16"/>
       <c r="BH10" s="16" t="s">
-        <v>243</v>
+        <v>235</v>
       </c>
       <c r="BI10" s="16"/>
       <c r="BJ10" s="16"/>
       <c r="BL10" s="16" t="s">
-        <v>241</v>
+        <v>233</v>
       </c>
       <c r="BM10" s="16" t="s">
-        <v>310</v>
+        <v>302</v>
       </c>
       <c r="BN10" s="16"/>
       <c r="BO10" s="16" t="s">
-        <v>243</v>
+        <v>235</v>
       </c>
       <c r="BP10" s="16"/>
       <c r="BQ10" s="16"/>
       <c r="BS10" s="16" t="s">
-        <v>241</v>
+        <v>233</v>
       </c>
       <c r="BT10" s="16" t="s">
-        <v>252</v>
+        <v>244</v>
       </c>
       <c r="BU10" s="16"/>
       <c r="BV10" s="16" t="s">
-        <v>243</v>
+        <v>235</v>
       </c>
       <c r="BW10" s="16"/>
       <c r="BX10" s="16"/>
       <c r="BZ10" s="16" t="s">
-        <v>241</v>
+        <v>233</v>
       </c>
       <c r="CA10" s="16" t="s">
-        <v>310</v>
+        <v>302</v>
       </c>
       <c r="CB10" s="16"/>
       <c r="CC10" s="16" t="s">
-        <v>243</v>
+        <v>235</v>
       </c>
       <c r="CD10" s="16"/>
       <c r="CE10" s="16"/>
       <c r="CG10" s="16" t="s">
-        <v>241</v>
+        <v>233</v>
       </c>
       <c r="CH10" s="16" t="s">
-        <v>252</v>
+        <v>244</v>
       </c>
       <c r="CI10" s="16"/>
       <c r="CJ10" s="16" t="s">
-        <v>243</v>
+        <v>235</v>
       </c>
       <c r="CK10" s="16"/>
       <c r="CL10" s="16"/>
       <c r="CN10" s="16" t="s">
-        <v>241</v>
+        <v>233</v>
       </c>
       <c r="CO10" s="16" t="s">
-        <v>311</v>
+        <v>303</v>
       </c>
       <c r="CP10" s="16"/>
       <c r="CQ10" s="16" t="s">
-        <v>243</v>
+        <v>235</v>
       </c>
       <c r="CR10" s="16"/>
       <c r="CS10" s="16"/>
       <c r="CU10" s="16" t="s">
-        <v>241</v>
+        <v>233</v>
       </c>
       <c r="CV10" s="16" t="s">
-        <v>311</v>
+        <v>303</v>
       </c>
       <c r="CW10" s="16"/>
       <c r="CX10" s="16" t="s">
-        <v>243</v>
+        <v>235</v>
       </c>
       <c r="CY10" s="16"/>
       <c r="CZ10" s="16"/>
       <c r="DB10" s="16" t="s">
-        <v>241</v>
+        <v>233</v>
       </c>
       <c r="DC10" s="16" t="s">
-        <v>312</v>
+        <v>304</v>
       </c>
       <c r="DD10" s="16"/>
       <c r="DE10" s="16" t="s">
-        <v>243</v>
+        <v>235</v>
       </c>
       <c r="DF10" s="16"/>
       <c r="DG10" s="16"/>
       <c r="DI10" s="16" t="s">
-        <v>241</v>
+        <v>233</v>
       </c>
       <c r="DJ10" s="16" t="s">
-        <v>313</v>
+        <v>305</v>
       </c>
       <c r="DK10" s="16"/>
       <c r="DL10" s="16" t="s">
-        <v>243</v>
+        <v>235</v>
       </c>
       <c r="DM10" s="16"/>
       <c r="DN10" s="16"/>
       <c r="DP10" s="16" t="s">
-        <v>241</v>
+        <v>233</v>
       </c>
       <c r="DQ10" s="16" t="s">
-        <v>252</v>
+        <v>244</v>
       </c>
       <c r="DR10" s="16"/>
       <c r="DS10" s="16" t="s">
-        <v>243</v>
+        <v>235</v>
       </c>
       <c r="DT10" s="16"/>
       <c r="DU10" s="16"/>
       <c r="DW10" s="16" t="s">
-        <v>241</v>
+        <v>233</v>
       </c>
       <c r="DX10" s="16" t="s">
-        <v>313</v>
+        <v>305</v>
       </c>
       <c r="DY10" s="16"/>
       <c r="DZ10" s="16" t="s">
-        <v>243</v>
+        <v>235</v>
       </c>
       <c r="EA10" s="16"/>
       <c r="EB10" s="16"/>
       <c r="ED10" s="16" t="s">
-        <v>241</v>
+        <v>233</v>
       </c>
       <c r="EE10" s="16" t="s">
-        <v>313</v>
+        <v>305</v>
       </c>
       <c r="EF10" s="16"/>
       <c r="EG10" s="16" t="s">
-        <v>243</v>
+        <v>235</v>
       </c>
       <c r="EH10" s="16"/>
       <c r="EI10" s="16"/>
       <c r="EK10" s="16" t="s">
-        <v>241</v>
+        <v>233</v>
       </c>
       <c r="EL10" s="16" t="s">
-        <v>314</v>
+        <v>306</v>
       </c>
       <c r="EM10" s="16"/>
       <c r="EN10" s="16" t="s">
-        <v>243</v>
+        <v>235</v>
       </c>
       <c r="EO10" s="16"/>
       <c r="EP10" s="16"/>
       <c r="ER10" s="16" t="s">
-        <v>241</v>
+        <v>233</v>
       </c>
       <c r="ES10" s="16" t="s">
-        <v>315</v>
+        <v>307</v>
       </c>
       <c r="ET10" s="16"/>
       <c r="EU10" s="16" t="s">
-        <v>243</v>
+        <v>235</v>
       </c>
       <c r="EV10" s="16"/>
       <c r="EW10" s="16"/>
       <c r="EY10" s="16" t="s">
-        <v>241</v>
+        <v>233</v>
       </c>
       <c r="EZ10" s="16" t="s">
-        <v>316</v>
+        <v>308</v>
       </c>
       <c r="FA10" s="16"/>
       <c r="FB10" s="16" t="s">
-        <v>243</v>
+        <v>235</v>
       </c>
       <c r="FC10" s="16"/>
       <c r="FD10" s="16"/>
     </row>
     <row r="11" spans="1:160" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="16" t="s">
-        <v>256</v>
+        <v>248</v>
       </c>
       <c r="B11" s="16" t="s">
-        <v>257</v>
+        <v>249</v>
       </c>
       <c r="C11" s="16"/>
       <c r="D11" s="16" t="s">
-        <v>258</v>
+        <v>250</v>
       </c>
       <c r="E11" s="16"/>
       <c r="F11" s="16"/>
       <c r="H11" s="16" t="s">
-        <v>256</v>
+        <v>248</v>
       </c>
       <c r="I11" s="16" t="s">
-        <v>257</v>
+        <v>249</v>
       </c>
       <c r="J11" s="16"/>
       <c r="K11" s="16" t="s">
-        <v>258</v>
+        <v>250</v>
       </c>
       <c r="L11" s="16"/>
       <c r="M11" s="16"/>
       <c r="O11" s="16" t="s">
-        <v>256</v>
+        <v>248</v>
       </c>
       <c r="P11" s="16" t="s">
-        <v>257</v>
+        <v>249</v>
       </c>
       <c r="Q11" s="16"/>
       <c r="R11" s="16" t="s">
-        <v>258</v>
+        <v>250</v>
       </c>
       <c r="S11" s="16"/>
       <c r="T11" s="16"/>
       <c r="V11" s="16" t="s">
-        <v>256</v>
+        <v>248</v>
       </c>
       <c r="W11" s="16" t="s">
-        <v>257</v>
+        <v>249</v>
       </c>
       <c r="X11" s="16"/>
       <c r="Y11" s="16" t="s">
-        <v>258</v>
+        <v>250</v>
       </c>
       <c r="Z11" s="16"/>
       <c r="AA11" s="16"/>
       <c r="AC11" s="16" t="s">
-        <v>256</v>
+        <v>248</v>
       </c>
       <c r="AD11" s="16" t="s">
-        <v>257</v>
+        <v>249</v>
       </c>
       <c r="AE11" s="16"/>
       <c r="AF11" s="16" t="s">
-        <v>259</v>
+        <v>251</v>
       </c>
       <c r="AG11" s="16"/>
       <c r="AH11" s="16"/>
       <c r="AJ11" s="16" t="s">
-        <v>256</v>
+        <v>248</v>
       </c>
       <c r="AK11" s="16" t="s">
-        <v>257</v>
+        <v>249</v>
       </c>
       <c r="AL11" s="16"/>
       <c r="AM11" s="16" t="s">
-        <v>258</v>
+        <v>250</v>
       </c>
       <c r="AN11" s="16"/>
       <c r="AO11" s="16"/>
       <c r="AQ11" s="16" t="s">
-        <v>256</v>
+        <v>248</v>
       </c>
       <c r="AR11" s="16" t="s">
-        <v>257</v>
+        <v>249</v>
       </c>
       <c r="AS11" s="16"/>
       <c r="AT11" s="16" t="s">
-        <v>258</v>
+        <v>250</v>
       </c>
       <c r="AU11" s="16"/>
       <c r="AV11" s="16"/>
       <c r="AX11" s="16" t="s">
-        <v>256</v>
+        <v>248</v>
       </c>
       <c r="AY11" s="16" t="s">
-        <v>257</v>
+        <v>249</v>
       </c>
       <c r="AZ11" s="16"/>
       <c r="BA11" s="16" t="s">
-        <v>258</v>
+        <v>250</v>
       </c>
       <c r="BB11" s="16"/>
       <c r="BC11" s="16"/>
       <c r="BE11" s="16" t="s">
-        <v>256</v>
+        <v>248</v>
       </c>
       <c r="BF11" s="16" t="s">
-        <v>257</v>
+        <v>249</v>
       </c>
       <c r="BG11" s="16"/>
       <c r="BH11" s="16" t="s">
-        <v>258</v>
+        <v>250</v>
       </c>
       <c r="BI11" s="16"/>
       <c r="BJ11" s="16"/>
       <c r="BL11" s="16" t="s">
-        <v>256</v>
+        <v>248</v>
       </c>
       <c r="BM11" s="16" t="s">
-        <v>257</v>
+        <v>249</v>
       </c>
       <c r="BN11" s="16"/>
       <c r="BO11" s="16" t="s">
-        <v>258</v>
+        <v>250</v>
       </c>
       <c r="BP11" s="16"/>
       <c r="BQ11" s="16"/>
       <c r="BS11" s="16" t="s">
-        <v>256</v>
+        <v>248</v>
       </c>
       <c r="BT11" s="16" t="s">
-        <v>257</v>
+        <v>249</v>
       </c>
       <c r="BU11" s="16"/>
       <c r="BV11" s="16" t="s">
-        <v>258</v>
+        <v>250</v>
       </c>
       <c r="BW11" s="16"/>
       <c r="BX11" s="16"/>
       <c r="BZ11" s="16" t="s">
-        <v>256</v>
+        <v>248</v>
       </c>
       <c r="CA11" s="16" t="s">
-        <v>257</v>
+        <v>249</v>
       </c>
       <c r="CB11" s="16"/>
       <c r="CC11" s="16" t="s">
-        <v>259</v>
+        <v>251</v>
       </c>
       <c r="CD11" s="16"/>
       <c r="CE11" s="16"/>
       <c r="CG11" s="16" t="s">
-        <v>256</v>
+        <v>248</v>
       </c>
       <c r="CH11" s="16" t="s">
-        <v>257</v>
+        <v>249</v>
       </c>
       <c r="CI11" s="16"/>
       <c r="CJ11" s="16" t="s">
-        <v>258</v>
+        <v>250</v>
       </c>
       <c r="CK11" s="16"/>
       <c r="CL11" s="16"/>
       <c r="CN11" s="16" t="s">
-        <v>256</v>
+        <v>248</v>
       </c>
       <c r="CO11" s="16" t="s">
-        <v>257</v>
+        <v>249</v>
       </c>
       <c r="CP11" s="16"/>
       <c r="CQ11" s="16" t="s">
-        <v>317</v>
+        <v>309</v>
       </c>
       <c r="CR11" s="16"/>
       <c r="CS11" s="16"/>
       <c r="CU11" s="16" t="s">
-        <v>256</v>
+        <v>248</v>
       </c>
       <c r="CV11" s="16" t="s">
-        <v>257</v>
+        <v>249</v>
       </c>
       <c r="CW11" s="16"/>
       <c r="CX11" s="16" t="s">
-        <v>258</v>
+        <v>250</v>
       </c>
       <c r="CY11" s="16"/>
       <c r="CZ11" s="16"/>
       <c r="DB11" s="16" t="s">
-        <v>256</v>
+        <v>248</v>
       </c>
       <c r="DC11" s="16" t="s">
-        <v>257</v>
+        <v>249</v>
       </c>
       <c r="DD11" s="16"/>
       <c r="DE11" s="16" t="s">
-        <v>258</v>
+        <v>250</v>
       </c>
       <c r="DF11" s="16"/>
       <c r="DG11" s="16"/>
       <c r="DI11" s="16" t="s">
-        <v>256</v>
+        <v>248</v>
       </c>
       <c r="DJ11" s="16" t="s">
-        <v>257</v>
+        <v>249</v>
       </c>
       <c r="DK11" s="16"/>
       <c r="DL11" s="16" t="s">
-        <v>258</v>
+        <v>250</v>
       </c>
       <c r="DM11" s="16"/>
       <c r="DN11" s="16"/>
       <c r="DP11" s="16" t="s">
-        <v>256</v>
+        <v>248</v>
       </c>
       <c r="DQ11" s="16" t="s">
-        <v>257</v>
+        <v>249</v>
       </c>
       <c r="DR11" s="16"/>
       <c r="DS11" s="16" t="s">
-        <v>258</v>
+        <v>250</v>
       </c>
       <c r="DT11" s="16"/>
       <c r="DU11" s="16"/>
       <c r="DW11" s="16" t="s">
-        <v>256</v>
+        <v>248</v>
       </c>
       <c r="DX11" s="16" t="s">
-        <v>257</v>
+        <v>249</v>
       </c>
       <c r="DY11" s="16"/>
       <c r="DZ11" s="16" t="s">
-        <v>318</v>
+        <v>310</v>
       </c>
       <c r="EA11" s="16"/>
       <c r="EB11" s="16"/>
       <c r="ED11" s="16" t="s">
-        <v>256</v>
+        <v>248</v>
       </c>
       <c r="EE11" s="16" t="s">
-        <v>257</v>
+        <v>249</v>
       </c>
       <c r="EF11" s="16"/>
       <c r="EG11" s="16" t="s">
-        <v>258</v>
+        <v>250</v>
       </c>
       <c r="EH11" s="16"/>
       <c r="EI11" s="16"/>
       <c r="EK11" s="16" t="s">
-        <v>256</v>
+        <v>248</v>
       </c>
       <c r="EL11" s="16" t="s">
-        <v>257</v>
+        <v>249</v>
       </c>
       <c r="EM11" s="16"/>
       <c r="EN11" s="16" t="s">
-        <v>258</v>
+        <v>250</v>
       </c>
       <c r="EO11" s="16"/>
       <c r="EP11" s="16"/>
       <c r="ER11" s="16" t="s">
-        <v>256</v>
+        <v>248</v>
       </c>
       <c r="ES11" s="16" t="s">
-        <v>257</v>
+        <v>249</v>
       </c>
       <c r="ET11" s="16"/>
       <c r="EU11" s="16" t="s">
-        <v>258</v>
+        <v>250</v>
       </c>
       <c r="EV11" s="16"/>
       <c r="EW11" s="16"/>
       <c r="EY11" s="16" t="s">
-        <v>256</v>
+        <v>248</v>
       </c>
       <c r="EZ11" s="16" t="s">
-        <v>257</v>
+        <v>249</v>
       </c>
       <c r="FA11" s="16"/>
       <c r="FB11" s="16" t="s">
-        <v>258</v>
+        <v>250</v>
       </c>
       <c r="FC11" s="16"/>
       <c r="FD11" s="16"/>

--- a/Test Cases.xlsx
+++ b/Test Cases.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://endresshauser-my.sharepoint.com/personal/corbin_ferguson_endress_com/Documents/ThesisBuildTool/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="142" documentId="8_{B89245B7-08D9-4A9D-8516-F6C9C7AFFDC1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FAE64D01-F0F2-4298-856E-9A52D5E13865}"/>
+  <xr:revisionPtr revIDLastSave="169" documentId="8_{B89245B7-08D9-4A9D-8516-F6C9C7AFFDC1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3B726949-1BFA-4762-879E-7852579E08BA}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="25440" windowHeight="15270" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1776" uniqueCount="344">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1752" uniqueCount="351">
   <si>
     <t>Test ID</t>
   </si>
@@ -99,9 +99,6 @@
     <t>Textinput REGEX works</t>
   </si>
   <si>
-    <t>Import Select Redundant Name</t>
-  </si>
-  <si>
     <t>Test Case ID:</t>
   </si>
   <si>
@@ -192,9 +189,6 @@
     <t>"Replace" button press</t>
   </si>
   <si>
-    <t>existing element replaced by new element, move to Add Another window</t>
-  </si>
-  <si>
     <t>quantity select window opens</t>
   </si>
   <si>
@@ -216,9 +210,6 @@
     <t>TemplateFBAOI</t>
   </si>
   <si>
-    <t>name still redundant, choose new resolution method</t>
-  </si>
-  <si>
     <t>Set nonredundant Name</t>
   </si>
   <si>
@@ -1072,6 +1063,36 @@
   </si>
   <si>
     <t>"No Valid Elements Found"</t>
+  </si>
+  <si>
+    <t>Import Element</t>
+  </si>
+  <si>
+    <t>Select element type with ambiguous parent</t>
+  </si>
+  <si>
+    <t>"Routine" selected from dropdown</t>
+  </si>
+  <si>
+    <t>template select for routines elements opens</t>
+  </si>
+  <si>
+    <t>"Logic" element selected for template</t>
+  </si>
+  <si>
+    <t>ambiguous parent window opens</t>
+  </si>
+  <si>
+    <t>Select parent element</t>
+  </si>
+  <si>
+    <t>new element name</t>
+  </si>
+  <si>
+    <t>TestRoutine</t>
+  </si>
+  <si>
+    <t>move to name Select window</t>
   </si>
 </sst>
 </file>
@@ -1493,13 +1514,13 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="4"/>
                 <c:pt idx="0">
-                  <c:v>5</c:v>
+                  <c:v>4</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>33</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>21</c:v>
+                  <c:v>22</c:v>
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>1</c:v>
@@ -2884,7 +2905,7 @@
       </c>
       <c r="H1">
         <f>COUNTIF(TestMaster[Test Status], "Not Implemented")</f>
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
@@ -2930,7 +2951,7 @@
       </c>
       <c r="H3">
         <f>COUNTIF(TestMaster[Test Status], "Fail")</f>
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
@@ -3261,7 +3282,7 @@
         <v>7</v>
       </c>
       <c r="G19" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
@@ -3426,7 +3447,7 @@
       </c>
       <c r="H26">
         <f>COUNTIFS(TestMaster[Test Status], "Not Implemented", TestMaster[Namespace], G25)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.25">
@@ -3478,7 +3499,7 @@
       </c>
       <c r="H28">
         <f>COUNTIFS(TestMaster[Test Status], "Fail", TestMaster[Namespace], G25)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
@@ -3542,7 +3563,7 @@
         <v>11</v>
       </c>
       <c r="E31" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="G31" t="s">
         <v>16</v>
@@ -3564,7 +3585,7 @@
         <v>10</v>
       </c>
       <c r="E32" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="G32" t="s">
         <v>5</v>
@@ -3590,7 +3611,7 @@
         <v>11</v>
       </c>
       <c r="E33" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="G33" t="s">
         <v>8</v>
@@ -3607,10 +3628,10 @@
       </c>
       <c r="B34" t="str">
         <f>Import!A1</f>
-        <v>Import Select Redundant Name</v>
+        <v>Import Element</v>
       </c>
       <c r="C34" s="5" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D34" t="s">
         <v>10</v>
@@ -4225,7 +4246,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="19" t="s">
-        <v>19</v>
+        <v>341</v>
       </c>
       <c r="B1" s="18"/>
       <c r="C1" s="18"/>
@@ -4235,7 +4256,7 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="17" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B2" s="18"/>
       <c r="C2" s="6">
@@ -4243,12 +4264,12 @@
         <v>33</v>
       </c>
       <c r="E2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="17" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B3" s="18"/>
       <c r="C3" s="8" t="str">
@@ -4256,16 +4277,16 @@
         <v>Medium</v>
       </c>
       <c r="E3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F3" s="7" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(A1, TestMaster[Test Name], TestMaster[Test Status], "Status not found"), "")</f>
-        <v>Not Implemented</v>
+        <v>Fail</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="19" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B4" s="18"/>
       <c r="C4" s="18"/>
@@ -4283,7 +4304,7 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="19" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B6" s="18"/>
       <c r="C6" s="18"/>
@@ -4293,22 +4314,22 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B7" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="B7" s="1" t="s">
+      <c r="C7" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="C7" s="1" t="s">
+      <c r="D7" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="D7" s="9" t="s">
+      <c r="E7" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="E7" s="1" t="s">
+      <c r="F7" s="10" t="s">
         <v>30</v>
-      </c>
-      <c r="F7" s="10" t="s">
-        <v>31</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
@@ -4316,13 +4337,13 @@
         <v>1</v>
       </c>
       <c r="B8" t="s">
+        <v>31</v>
+      </c>
+      <c r="C8" t="s">
         <v>32</v>
       </c>
-      <c r="C8" t="s">
+      <c r="D8" s="2" t="s">
         <v>33</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>34</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="29.1" customHeight="1" x14ac:dyDescent="0.25">
@@ -4331,13 +4352,13 @@
         <v>2</v>
       </c>
       <c r="B9" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="C9" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="C9" s="3" t="s">
+      <c r="D9" s="3" t="s">
         <v>36</v>
-      </c>
-      <c r="D9" s="3" t="s">
-        <v>37</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -4346,13 +4367,13 @@
         <v>3</v>
       </c>
       <c r="B10" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="C10" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="C10" s="3" t="s">
+      <c r="D10" s="3" t="s">
         <v>39</v>
-      </c>
-      <c r="D10" s="3" t="s">
-        <v>40</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -4361,13 +4382,13 @@
         <v>4</v>
       </c>
       <c r="B11" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="C11" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="C11" s="3" t="s">
+      <c r="D11" s="3" t="s">
         <v>42</v>
-      </c>
-      <c r="D11" s="3" t="s">
-        <v>43</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
@@ -4376,13 +4397,13 @@
         <v>5</v>
       </c>
       <c r="B12" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="C12" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="C12" s="3" t="s">
+      <c r="D12" s="2" t="s">
         <v>45</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>46</v>
       </c>
     </row>
     <row r="13" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -4391,13 +4412,13 @@
         <v>6</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>38</v>
+        <v>342</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="D13" s="3" t="s">
-        <v>40</v>
+        <v>343</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>344</v>
       </c>
     </row>
     <row r="14" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -4406,13 +4427,13 @@
         <v>7</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>42</v>
+        <v>345</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>47</v>
+        <v>346</v>
       </c>
     </row>
     <row r="15" spans="1:6" ht="29.1" customHeight="1" x14ac:dyDescent="0.25">
@@ -4420,14 +4441,14 @@
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
-      <c r="B15" t="s">
-        <v>48</v>
-      </c>
-      <c r="C15" t="s">
-        <v>49</v>
+      <c r="B15" s="3" t="s">
+        <v>347</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>55</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>50</v>
+        <v>350</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
@@ -4436,10 +4457,10 @@
         <v>9</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>44</v>
+        <v>348</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>45</v>
+        <v>349</v>
       </c>
       <c r="D16" s="2" t="s">
         <v>46</v>
@@ -4451,13 +4472,13 @@
         <v>10</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="D17" s="3" t="s">
-        <v>40</v>
+        <v>59</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>60</v>
       </c>
     </row>
     <row r="18" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -4465,119 +4486,48 @@
         <f t="shared" si="0"/>
         <v>11</v>
       </c>
-      <c r="B18" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="C18" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="D18" s="3" t="s">
-        <v>51</v>
-      </c>
+      <c r="C18" s="3"/>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" s="4">
         <f t="shared" si="0"/>
         <v>12</v>
       </c>
-      <c r="B19" t="s">
-        <v>48</v>
-      </c>
-      <c r="C19" t="s">
-        <v>52</v>
-      </c>
-      <c r="D19" s="2" t="s">
-        <v>53</v>
-      </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" s="4">
         <f t="shared" si="0"/>
         <v>13</v>
       </c>
-      <c r="B20" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="C20" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="D20" s="2" t="s">
-        <v>46</v>
-      </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21" s="4">
         <f t="shared" si="0"/>
         <v>14</v>
       </c>
-      <c r="B21" t="s">
-        <v>48</v>
-      </c>
-      <c r="C21" t="s">
-        <v>54</v>
-      </c>
-      <c r="D21" s="2" t="s">
-        <v>55</v>
-      </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A22" s="4">
         <f t="shared" si="0"/>
         <v>15</v>
       </c>
-      <c r="B22" t="s">
-        <v>56</v>
-      </c>
-      <c r="C22" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="D22" s="2" t="s">
-        <v>58</v>
-      </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A23" s="4">
         <f t="shared" si="0"/>
         <v>16</v>
       </c>
-      <c r="B23" t="s">
-        <v>48</v>
-      </c>
-      <c r="C23" t="s">
-        <v>54</v>
-      </c>
-      <c r="D23" s="2" t="s">
-        <v>55</v>
-      </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A24" s="4">
         <f t="shared" si="0"/>
         <v>17</v>
       </c>
-      <c r="B24" t="s">
-        <v>59</v>
-      </c>
-      <c r="C24" t="s">
-        <v>60</v>
-      </c>
-      <c r="D24" s="2" t="s">
-        <v>61</v>
-      </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A25" s="4">
         <f t="shared" si="0"/>
         <v>18</v>
-      </c>
-      <c r="B25" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="C25" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="D25" s="2" t="s">
-        <v>63</v>
       </c>
     </row>
   </sheetData>
@@ -4627,7 +4577,7 @@
   <sheetData>
     <row r="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A1" s="19" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="B1" s="22"/>
       <c r="C1" s="22"/>
@@ -4635,7 +4585,7 @@
       <c r="E1" s="22"/>
       <c r="F1" s="21"/>
       <c r="G1" s="19" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="H1" s="22"/>
       <c r="I1" s="22"/>
@@ -4643,7 +4593,7 @@
       <c r="K1" s="22"/>
       <c r="L1" s="21"/>
       <c r="M1" s="17" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="N1" s="22"/>
       <c r="O1" s="22"/>
@@ -4659,7 +4609,7 @@
     </row>
     <row r="2" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A2" s="17" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B2" s="22"/>
       <c r="C2">
@@ -4667,11 +4617,11 @@
         <v>24</v>
       </c>
       <c r="E2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F2" s="7"/>
       <c r="G2" s="17" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="H2" s="22"/>
       <c r="I2">
@@ -4679,11 +4629,11 @@
         <v>25</v>
       </c>
       <c r="K2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="L2" s="7"/>
       <c r="M2" s="17" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="N2" s="22"/>
       <c r="O2">
@@ -4691,14 +4641,14 @@
         <v>26</v>
       </c>
       <c r="Q2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="T2" s="17"/>
       <c r="U2" s="22"/>
     </row>
     <row r="3" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A3" s="17" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B3" s="22"/>
       <c r="C3" t="str">
@@ -4706,14 +4656,14 @@
         <v>High</v>
       </c>
       <c r="E3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F3" s="7" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(A1, TestMaster[Test Name], TestMaster[Test Status], "Status not found"), "")</f>
         <v>Pass</v>
       </c>
       <c r="G3" s="17" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="H3" s="22"/>
       <c r="I3" t="str">
@@ -4721,14 +4671,14 @@
         <v>Medium</v>
       </c>
       <c r="K3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="L3" s="7" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(G1, TestMaster[Test Name], TestMaster[Test Status], "Status not found"), "")</f>
         <v>Fail</v>
       </c>
       <c r="M3" s="17" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="N3" s="22"/>
       <c r="O3" t="str">
@@ -4736,7 +4686,7 @@
         <v>Low</v>
       </c>
       <c r="Q3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="R3" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(M1, TestMaster[Test Name], TestMaster[Test Status], "Status not found"), "")</f>
@@ -4747,7 +4697,7 @@
     </row>
     <row r="4" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A4" s="19" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="B4" s="22"/>
       <c r="C4" s="22"/>
@@ -4755,7 +4705,7 @@
       <c r="E4" s="22"/>
       <c r="F4" s="21"/>
       <c r="G4" s="19" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="H4" s="22"/>
       <c r="I4" s="22"/>
@@ -4763,7 +4713,7 @@
       <c r="K4" s="22"/>
       <c r="L4" s="21"/>
       <c r="M4" s="17" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="N4" s="22"/>
       <c r="O4" s="22"/>
@@ -4805,7 +4755,7 @@
     </row>
     <row r="6" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A6" s="19" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B6" s="22"/>
       <c r="C6" s="22"/>
@@ -4813,7 +4763,7 @@
       <c r="E6" s="22"/>
       <c r="F6" s="21"/>
       <c r="G6" s="19" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H6" s="22"/>
       <c r="I6" s="22"/>
@@ -4821,7 +4771,7 @@
       <c r="K6" s="22"/>
       <c r="L6" s="21"/>
       <c r="M6" s="17" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="N6" s="22"/>
       <c r="O6" s="22"/>
@@ -4837,58 +4787,58 @@
     </row>
     <row r="7" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B7" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="B7" s="1" t="s">
+      <c r="C7" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="C7" s="1" t="s">
+      <c r="D7" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D7" s="1" t="s">
+      <c r="E7" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="E7" s="1" t="s">
+      <c r="F7" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="F7" s="10" t="s">
-        <v>31</v>
-      </c>
       <c r="G7" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="H7" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="H7" s="1" t="s">
+      <c r="I7" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="I7" s="1" t="s">
+      <c r="J7" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="J7" s="1" t="s">
+      <c r="K7" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="K7" s="1" t="s">
+      <c r="L7" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="L7" s="10" t="s">
-        <v>31</v>
-      </c>
       <c r="M7" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="N7" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="N7" s="1" t="s">
+      <c r="O7" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="O7" s="1" t="s">
+      <c r="P7" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="P7" s="1" t="s">
+      <c r="Q7" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="Q7" s="1" t="s">
+      <c r="R7" s="1" t="s">
         <v>30</v>
-      </c>
-      <c r="R7" s="1" t="s">
-        <v>31</v>
       </c>
       <c r="T7" s="1"/>
       <c r="U7" s="1"/>
@@ -4902,37 +4852,37 @@
         <v>1</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G8" s="4">
         <v>1</v>
       </c>
       <c r="H8" s="4" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="M8" s="4">
         <v>1</v>
       </c>
       <c r="N8" s="4" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="O8" s="3" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="P8" s="3" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="9" spans="1:25" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -4940,37 +4890,37 @@
         <v>2</v>
       </c>
       <c r="B9" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="C9" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="C9" s="3" t="s">
+      <c r="D9" s="3" t="s">
         <v>39</v>
-      </c>
-      <c r="D9" s="3" t="s">
-        <v>40</v>
       </c>
       <c r="G9" s="4">
         <v>2</v>
       </c>
       <c r="H9" s="4" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="M9" s="4">
         <v>2</v>
       </c>
       <c r="N9" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="O9" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="O9" s="3" t="s">
+      <c r="P9" s="3" t="s">
         <v>39</v>
-      </c>
-      <c r="P9" s="3" t="s">
-        <v>40</v>
       </c>
     </row>
     <row r="10" spans="1:25" ht="29.1" customHeight="1" x14ac:dyDescent="0.25">
@@ -4978,37 +4928,37 @@
         <v>3</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="G10" s="4">
         <v>3</v>
       </c>
       <c r="H10" s="4" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="M10" s="4">
         <v>3</v>
       </c>
       <c r="N10" s="4" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="O10" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="P10" s="3" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
     <row r="11" spans="1:25" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -5016,37 +4966,37 @@
         <v>4</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="G11" s="4">
         <v>4</v>
       </c>
       <c r="H11" s="4" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="I11" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="J11" s="3" t="s">
         <v>76</v>
-      </c>
-      <c r="J11" s="3" t="s">
-        <v>79</v>
       </c>
       <c r="M11" s="4">
         <v>4</v>
       </c>
       <c r="N11" s="4" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="O11" s="3" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="P11" s="3" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
     </row>
     <row r="12" spans="1:25" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -5054,25 +5004,25 @@
         <v>5</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="M12" s="4">
         <v>5</v>
       </c>
       <c r="N12" s="4" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="O12" s="3" t="s">
-        <v>326</v>
+        <v>323</v>
       </c>
       <c r="P12" s="3" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
     </row>
     <row r="13" spans="1:25" ht="29.1" customHeight="1" x14ac:dyDescent="0.25">
@@ -5080,25 +5030,25 @@
         <v>6</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="M13" s="4">
         <v>6</v>
       </c>
       <c r="N13" s="4" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="O13" s="3" t="s">
-        <v>326</v>
+        <v>323</v>
       </c>
       <c r="P13" s="3" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
     </row>
     <row r="14" spans="1:25" x14ac:dyDescent="0.25">
@@ -5106,13 +5056,13 @@
         <v>7</v>
       </c>
       <c r="N14" t="s">
+        <v>47</v>
+      </c>
+      <c r="O14" t="s">
         <v>48</v>
       </c>
-      <c r="O14" t="s">
-        <v>49</v>
-      </c>
       <c r="P14" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
     </row>
     <row r="15" spans="1:25" ht="29.1" customHeight="1" x14ac:dyDescent="0.25">
@@ -5120,13 +5070,13 @@
         <v>8</v>
       </c>
       <c r="N15" s="4" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="O15" s="4" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="P15" s="3" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
     </row>
     <row r="16" spans="1:25" x14ac:dyDescent="0.25">
@@ -5134,13 +5084,13 @@
         <v>9</v>
       </c>
       <c r="N16" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="O16" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="P16" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
     <row r="17" spans="13:16" ht="29.1" customHeight="1" x14ac:dyDescent="0.25">
@@ -5148,13 +5098,13 @@
         <v>10</v>
       </c>
       <c r="N17" s="4" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="O17" s="4" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="P17" s="3" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
     </row>
     <row r="18" spans="13:16" x14ac:dyDescent="0.25">
@@ -5162,13 +5112,13 @@
         <v>11</v>
       </c>
       <c r="N18" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="O18" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="P18" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
     </row>
     <row r="19" spans="13:16" x14ac:dyDescent="0.25">
@@ -5176,13 +5126,13 @@
         <v>12</v>
       </c>
       <c r="N19" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="O19" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="P19" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
     </row>
     <row r="20" spans="13:16" x14ac:dyDescent="0.25">
@@ -5190,13 +5140,13 @@
         <v>13</v>
       </c>
       <c r="N20" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="O20" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="P20" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
     </row>
     <row r="21" spans="13:16" x14ac:dyDescent="0.25">
@@ -5204,13 +5154,13 @@
         <v>14</v>
       </c>
       <c r="N21" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="O21" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="P21" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="22" spans="13:16" x14ac:dyDescent="0.25">
@@ -5272,7 +5222,7 @@
   <sheetData>
     <row r="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A1" s="19" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="B1" s="18"/>
       <c r="C1" s="18"/>
@@ -5280,7 +5230,7 @@
       <c r="E1" s="18"/>
       <c r="F1" s="21"/>
       <c r="G1" s="23" t="s">
-        <v>323</v>
+        <v>320</v>
       </c>
       <c r="H1" s="18"/>
       <c r="I1" s="18"/>
@@ -5288,7 +5238,7 @@
       <c r="K1" s="18"/>
       <c r="L1" s="21"/>
       <c r="M1" s="17" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="N1" s="18"/>
       <c r="O1" s="18"/>
@@ -5298,7 +5248,7 @@
     </row>
     <row r="2" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A2" s="17" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B2" s="18"/>
       <c r="C2" s="6">
@@ -5306,10 +5256,10 @@
         <v>36</v>
       </c>
       <c r="E2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G2" s="17" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="H2" s="18"/>
       <c r="I2" s="6">
@@ -5317,10 +5267,10 @@
         <v>34</v>
       </c>
       <c r="K2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="M2" s="17" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="N2" s="18"/>
       <c r="O2" s="12">
@@ -5328,12 +5278,12 @@
         <v>35</v>
       </c>
       <c r="Q2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="3" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A3" s="17" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B3" s="18"/>
       <c r="C3" s="6" t="str">
@@ -5341,14 +5291,14 @@
         <v>Medium</v>
       </c>
       <c r="E3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F3" s="7" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(A1, TestMaster[Test Name], TestMaster[Test Status], "Status not found"), "")</f>
         <v>Fail</v>
       </c>
       <c r="G3" s="17" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="H3" s="18"/>
       <c r="I3" s="6" t="str">
@@ -5356,14 +5306,14 @@
         <v>High</v>
       </c>
       <c r="K3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="L3" s="7" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(G1, TestMaster[Test Name], TestMaster[Test Status], "Status not found"), "")</f>
         <v>Fail</v>
       </c>
       <c r="M3" s="17" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="N3" s="18"/>
       <c r="O3" s="12" t="str">
@@ -5371,7 +5321,7 @@
         <v>Low</v>
       </c>
       <c r="Q3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="R3" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(M1, TestMaster[Test Name], TestMaster[Test Status], "Status not found"), "")</f>
@@ -5380,7 +5330,7 @@
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A4" s="19" t="s">
-        <v>341</v>
+        <v>338</v>
       </c>
       <c r="B4" s="18"/>
       <c r="C4" s="18"/>
@@ -5388,7 +5338,7 @@
       <c r="E4" s="18"/>
       <c r="F4" s="21"/>
       <c r="G4" s="23" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="H4" s="18"/>
       <c r="I4" s="18"/>
@@ -5396,7 +5346,7 @@
       <c r="K4" s="18"/>
       <c r="L4" s="21"/>
       <c r="M4" s="17" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="N4" s="18"/>
       <c r="O4" s="18"/>
@@ -5426,7 +5376,7 @@
     </row>
     <row r="6" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A6" s="19" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B6" s="18"/>
       <c r="C6" s="18"/>
@@ -5434,7 +5384,7 @@
       <c r="E6" s="18"/>
       <c r="F6" s="21"/>
       <c r="G6" s="23" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H6" s="18"/>
       <c r="I6" s="18"/>
@@ -5442,7 +5392,7 @@
       <c r="K6" s="18"/>
       <c r="L6" s="21"/>
       <c r="M6" s="17" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="N6" s="18"/>
       <c r="O6" s="18"/>
@@ -5452,58 +5402,58 @@
     </row>
     <row r="7" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B7" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="B7" s="1" t="s">
+      <c r="C7" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="C7" s="1" t="s">
+      <c r="D7" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D7" s="1" t="s">
+      <c r="E7" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="E7" s="1" t="s">
+      <c r="F7" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="F7" s="10" t="s">
-        <v>31</v>
-      </c>
       <c r="G7" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="H7" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="H7" s="1" t="s">
+      <c r="I7" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="I7" s="1" t="s">
+      <c r="J7" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="J7" s="1" t="s">
+      <c r="K7" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="K7" s="1" t="s">
+      <c r="L7" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="L7" s="10" t="s">
-        <v>31</v>
-      </c>
       <c r="M7" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="N7" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="N7" s="1" t="s">
+      <c r="O7" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="O7" s="1" t="s">
+      <c r="P7" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="P7" s="1" t="s">
+      <c r="Q7" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="Q7" s="1" t="s">
+      <c r="R7" s="1" t="s">
         <v>30</v>
-      </c>
-      <c r="R7" s="1" t="s">
-        <v>31</v>
       </c>
     </row>
     <row r="8" spans="1:18" x14ac:dyDescent="0.25">
@@ -5511,31 +5461,31 @@
         <v>1</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="G8">
         <v>1</v>
       </c>
       <c r="H8" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="M8">
         <v>1</v>
       </c>
       <c r="N8" s="4" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="O8" s="4" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="P8" s="4" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
     </row>
     <row r="9" spans="1:18" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -5543,34 +5493,34 @@
         <v>2</v>
       </c>
       <c r="B9" t="s">
-        <v>342</v>
+        <v>339</v>
       </c>
       <c r="C9" t="s">
-        <v>343</v>
+        <v>340</v>
       </c>
       <c r="G9">
         <v>2</v>
       </c>
       <c r="H9" s="4" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="I9" s="4" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="J9" s="4" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="M9">
         <v>2</v>
       </c>
       <c r="N9" s="3" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="O9" s="3" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="P9" s="3" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
     </row>
     <row r="10" spans="1:18" ht="29.1" customHeight="1" x14ac:dyDescent="0.25">
@@ -5578,37 +5528,37 @@
         <v>3</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="G10">
         <v>3</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="M10">
         <v>3</v>
       </c>
       <c r="N10" s="3" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="O10" s="3" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="P10" s="3" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
     </row>
     <row r="11" spans="1:18" ht="30" x14ac:dyDescent="0.25">
@@ -5616,25 +5566,25 @@
         <v>4</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>328</v>
+        <v>325</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="M11">
         <v>4</v>
       </c>
       <c r="N11" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="O11" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="P11" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
     </row>
     <row r="12" spans="1:18" x14ac:dyDescent="0.25">
@@ -5642,25 +5592,25 @@
         <v>5</v>
       </c>
       <c r="H12" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="I12" t="s">
-        <v>329</v>
+        <v>326</v>
       </c>
       <c r="J12" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="M12">
         <v>5</v>
       </c>
       <c r="N12" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="O12" t="s">
+        <v>109</v>
+      </c>
+      <c r="P12" t="s">
         <v>112</v>
-      </c>
-      <c r="P12" t="s">
-        <v>115</v>
       </c>
     </row>
     <row r="13" spans="1:18" x14ac:dyDescent="0.25">
@@ -5668,25 +5618,25 @@
         <v>6</v>
       </c>
       <c r="H13" t="s">
-        <v>336</v>
+        <v>333</v>
       </c>
       <c r="I13" t="s">
-        <v>330</v>
+        <v>327</v>
       </c>
       <c r="J13" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="M13">
         <v>6</v>
       </c>
       <c r="N13" t="s">
+        <v>47</v>
+      </c>
+      <c r="O13" t="s">
         <v>48</v>
       </c>
-      <c r="O13" t="s">
-        <v>49</v>
-      </c>
       <c r="P13" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
     </row>
     <row r="14" spans="1:18" x14ac:dyDescent="0.25">
@@ -5694,25 +5644,25 @@
         <v>7</v>
       </c>
       <c r="H14" t="s">
-        <v>335</v>
+        <v>332</v>
       </c>
       <c r="I14" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="J14" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="M14">
         <v>8</v>
       </c>
       <c r="N14" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="O14" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="P14" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
     </row>
     <row r="15" spans="1:18" x14ac:dyDescent="0.25">
@@ -5720,22 +5670,22 @@
         <v>8</v>
       </c>
       <c r="H15" t="s">
-        <v>337</v>
+        <v>334</v>
       </c>
       <c r="I15" t="s">
-        <v>331</v>
+        <v>328</v>
       </c>
       <c r="M15">
         <v>9</v>
       </c>
       <c r="N15" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="O15" t="s">
+        <v>109</v>
+      </c>
+      <c r="P15" t="s">
         <v>112</v>
-      </c>
-      <c r="P15" t="s">
-        <v>115</v>
       </c>
     </row>
     <row r="16" spans="1:18" x14ac:dyDescent="0.25">
@@ -5743,25 +5693,25 @@
         <v>9</v>
       </c>
       <c r="H16" t="s">
-        <v>332</v>
+        <v>329</v>
       </c>
       <c r="I16" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="J16" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="M16">
         <v>10</v>
       </c>
       <c r="N16" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="O16" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="P16" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
     </row>
     <row r="17" spans="7:10" x14ac:dyDescent="0.25">
@@ -5769,13 +5719,13 @@
         <v>10</v>
       </c>
       <c r="H17" t="s">
-        <v>338</v>
+        <v>335</v>
       </c>
       <c r="I17" t="s">
-        <v>330</v>
+        <v>327</v>
       </c>
       <c r="J17" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
     </row>
     <row r="18" spans="7:10" x14ac:dyDescent="0.25">
@@ -5783,13 +5733,13 @@
         <v>11</v>
       </c>
       <c r="H18" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="I18" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="J18" t="s">
-        <v>334</v>
+        <v>331</v>
       </c>
     </row>
     <row r="19" spans="7:10" x14ac:dyDescent="0.25">
@@ -5797,13 +5747,13 @@
         <v>12</v>
       </c>
       <c r="H19" t="s">
+        <v>105</v>
+      </c>
+      <c r="I19" t="s">
         <v>108</v>
       </c>
-      <c r="I19" t="s">
-        <v>111</v>
-      </c>
       <c r="J19" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
     </row>
     <row r="20" spans="7:10" x14ac:dyDescent="0.25">
@@ -5811,10 +5761,10 @@
         <v>13</v>
       </c>
       <c r="H20" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
       <c r="I20" t="s">
-        <v>340</v>
+        <v>337</v>
       </c>
     </row>
     <row r="21" spans="7:10" x14ac:dyDescent="0.25">
@@ -5822,13 +5772,13 @@
         <v>14</v>
       </c>
       <c r="H21" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="I21" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="J21" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
     </row>
   </sheetData>
@@ -5880,7 +5830,7 @@
   <sheetData>
     <row r="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A1" s="19" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="B1" s="18"/>
       <c r="C1" s="18"/>
@@ -5888,7 +5838,7 @@
       <c r="E1" s="18"/>
       <c r="F1" s="21"/>
       <c r="G1" s="23" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="H1" s="18"/>
       <c r="I1" s="18"/>
@@ -5896,7 +5846,7 @@
       <c r="K1" s="18"/>
       <c r="L1" s="21"/>
       <c r="M1" s="17" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="N1" s="18"/>
       <c r="O1" s="18"/>
@@ -5906,7 +5856,7 @@
     </row>
     <row r="2" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A2" s="17" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B2" s="18"/>
       <c r="C2" s="6">
@@ -5914,10 +5864,10 @@
         <v>29</v>
       </c>
       <c r="E2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G2" s="17" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="H2" s="18"/>
       <c r="I2" s="6">
@@ -5925,10 +5875,10 @@
         <v>27</v>
       </c>
       <c r="K2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="M2" s="17" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="N2" s="18"/>
       <c r="O2" s="6">
@@ -5936,12 +5886,12 @@
         <v>28</v>
       </c>
       <c r="Q2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="3" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A3" s="17" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B3" s="18"/>
       <c r="C3" s="6" t="str">
@@ -5949,14 +5899,14 @@
         <v>Medium</v>
       </c>
       <c r="E3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F3" s="7" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(A1, TestMaster[Test Name], TestMaster[Test Status], "Status not found"), "")</f>
         <v>Fail</v>
       </c>
       <c r="G3" s="17" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="H3" s="18"/>
       <c r="I3" s="6" t="str">
@@ -5964,14 +5914,14 @@
         <v>High</v>
       </c>
       <c r="K3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="L3" s="7" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(G1, TestMaster[Test Name], TestMaster[Test Status], "Status not found"), "")</f>
         <v>Fail</v>
       </c>
       <c r="M3" s="17" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="N3" s="18"/>
       <c r="O3" s="6" t="str">
@@ -5979,7 +5929,7 @@
         <v>Low</v>
       </c>
       <c r="Q3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="R3" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(M1, TestMaster[Test Name], TestMaster[Test Status], "Status not found"), "")</f>
@@ -5988,7 +5938,7 @@
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A4" s="26" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="B4" s="18"/>
       <c r="C4" s="18"/>
@@ -5996,7 +5946,7 @@
       <c r="E4" s="18"/>
       <c r="F4" s="21"/>
       <c r="G4" s="27" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="H4" s="18"/>
       <c r="I4" s="18"/>
@@ -6004,7 +5954,7 @@
       <c r="K4" s="18"/>
       <c r="L4" s="21"/>
       <c r="M4" s="25" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="N4" s="18"/>
       <c r="O4" s="18"/>
@@ -6034,7 +5984,7 @@
     </row>
     <row r="6" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A6" s="19" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="B6" s="18"/>
       <c r="C6" s="18"/>
@@ -6042,7 +5992,7 @@
       <c r="E6" s="18"/>
       <c r="F6" s="21"/>
       <c r="G6" s="23" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="H6" s="18"/>
       <c r="I6" s="18"/>
@@ -6050,7 +6000,7 @@
       <c r="K6" s="18"/>
       <c r="L6" s="21"/>
       <c r="M6" s="17" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="N6" s="18"/>
       <c r="O6" s="18"/>
@@ -6060,58 +6010,58 @@
     </row>
     <row r="7" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B7" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="B7" s="1" t="s">
+      <c r="C7" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="C7" s="1" t="s">
+      <c r="D7" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D7" s="1" t="s">
+      <c r="E7" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="E7" s="1" t="s">
+      <c r="F7" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="F7" s="10" t="s">
-        <v>31</v>
-      </c>
       <c r="G7" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="H7" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="H7" s="1" t="s">
+      <c r="I7" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="I7" s="1" t="s">
+      <c r="J7" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="J7" s="1" t="s">
+      <c r="K7" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="K7" s="1" t="s">
+      <c r="L7" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="L7" s="10" t="s">
-        <v>31</v>
-      </c>
       <c r="M7" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="N7" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="N7" s="1" t="s">
+      <c r="O7" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="O7" s="1" t="s">
+      <c r="P7" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="P7" s="1" t="s">
+      <c r="Q7" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="Q7" s="1" t="s">
+      <c r="R7" s="1" t="s">
         <v>30</v>
-      </c>
-      <c r="R7" s="1" t="s">
-        <v>31</v>
       </c>
     </row>
     <row r="8" spans="1:18" s="3" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -6119,39 +6069,39 @@
         <v>1</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="F8" s="13"/>
       <c r="G8" s="3">
         <v>1</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="L8" s="13"/>
       <c r="M8" s="3">
         <v>1</v>
       </c>
       <c r="N8" s="3" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="O8" s="3" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="P8" s="3" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
     </row>
     <row r="9" spans="1:18" s="3" customFormat="1" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -6159,39 +6109,39 @@
         <v>2</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>316</v>
+        <v>313</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="F9" s="13"/>
       <c r="G9" s="3">
         <v>2</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="L9" s="13"/>
       <c r="M9" s="3">
         <v>2</v>
       </c>
       <c r="N9" s="3" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="O9" s="3" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="P9" s="3" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
     </row>
     <row r="10" spans="1:18" s="3" customFormat="1" ht="29.1" customHeight="1" x14ac:dyDescent="0.25">
@@ -6200,26 +6150,26 @@
         <v>3</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>319</v>
+        <v>316</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="L10" s="13"/>
       <c r="M10" s="3">
         <v>3</v>
       </c>
       <c r="N10" s="3" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="O10" s="3" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="P10" s="3" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
     </row>
     <row r="11" spans="1:18" ht="29.1" customHeight="1" x14ac:dyDescent="0.25">
@@ -6227,25 +6177,25 @@
         <v>4</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>321</v>
+        <v>318</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="M11" s="3">
         <v>4</v>
       </c>
       <c r="N11" s="3" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="O11" s="3" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="P11" s="3" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
     </row>
   </sheetData>
@@ -6296,7 +6246,7 @@
   <sheetData>
     <row r="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A1" s="19" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="B1" s="18"/>
       <c r="C1" s="18"/>
@@ -6304,7 +6254,7 @@
       <c r="E1" s="18"/>
       <c r="F1" s="21"/>
       <c r="G1" s="17" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="H1" s="18"/>
       <c r="I1" s="18"/>
@@ -6312,7 +6262,7 @@
       <c r="K1" s="18"/>
       <c r="L1" s="18"/>
       <c r="M1" s="23" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="N1" s="18"/>
       <c r="O1" s="18"/>
@@ -6322,7 +6272,7 @@
     </row>
     <row r="2" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A2" s="17" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B2" s="18"/>
       <c r="C2" s="6">
@@ -6330,10 +6280,10 @@
         <v>32</v>
       </c>
       <c r="E2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G2" s="17" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="H2" s="18"/>
       <c r="I2" s="6">
@@ -6341,10 +6291,10 @@
         <v>30</v>
       </c>
       <c r="K2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="M2" s="28" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="N2" s="18"/>
       <c r="O2" s="6">
@@ -6352,13 +6302,13 @@
         <v>31</v>
       </c>
       <c r="Q2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="R2" s="7"/>
     </row>
     <row r="3" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A3" s="17" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B3" s="18"/>
       <c r="C3" s="6" t="str">
@@ -6366,14 +6316,14 @@
         <v>High</v>
       </c>
       <c r="E3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F3" s="7" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(A1, TestMaster[Test Name], TestMaster[Test Priority], "Priority not found"), "")</f>
         <v>High</v>
       </c>
       <c r="G3" s="17" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="H3" s="18"/>
       <c r="I3" s="6" t="str">
@@ -6381,14 +6331,14 @@
         <v>High</v>
       </c>
       <c r="K3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="L3" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(G1, TestMaster[Test Name], TestMaster[Test Priority], "Priority not found"), "")</f>
         <v>High</v>
       </c>
       <c r="M3" s="28" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="N3" s="18"/>
       <c r="O3" s="6" t="str">
@@ -6396,7 +6346,7 @@
         <v>Medium</v>
       </c>
       <c r="Q3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="R3" s="7" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(M1, TestMaster[Test Name], TestMaster[Test Priority], "Priority not found"), "")</f>
@@ -6405,7 +6355,7 @@
     </row>
     <row r="4" spans="1:18" s="2" customFormat="1" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="26" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="B4" s="20"/>
       <c r="C4" s="20"/>
@@ -6413,7 +6363,7 @@
       <c r="E4" s="20"/>
       <c r="F4" s="21"/>
       <c r="G4" s="25" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="H4" s="20"/>
       <c r="I4" s="20"/>
@@ -6421,7 +6371,7 @@
       <c r="K4" s="20"/>
       <c r="L4" s="20"/>
       <c r="M4" s="27" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="N4" s="20"/>
       <c r="O4" s="20"/>
@@ -6451,7 +6401,7 @@
     </row>
     <row r="6" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A6" s="19" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="B6" s="18"/>
       <c r="C6" s="18"/>
@@ -6459,7 +6409,7 @@
       <c r="E6" s="18"/>
       <c r="F6" s="21"/>
       <c r="G6" s="17" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="H6" s="18"/>
       <c r="I6" s="18"/>
@@ -6467,7 +6417,7 @@
       <c r="K6" s="18"/>
       <c r="L6" s="18"/>
       <c r="M6" s="23" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="N6" s="18"/>
       <c r="O6" s="18"/>
@@ -6477,58 +6427,58 @@
     </row>
     <row r="7" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B7" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="B7" s="1" t="s">
+      <c r="C7" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="C7" s="1" t="s">
+      <c r="D7" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D7" s="1" t="s">
+      <c r="E7" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="E7" s="1" t="s">
+      <c r="F7" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="F7" s="10" t="s">
-        <v>31</v>
-      </c>
       <c r="G7" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="H7" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="H7" s="1" t="s">
+      <c r="I7" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="I7" s="1" t="s">
+      <c r="J7" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="J7" s="1" t="s">
+      <c r="K7" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="K7" s="1" t="s">
+      <c r="L7" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="L7" s="1" t="s">
-        <v>31</v>
-      </c>
       <c r="M7" s="14" t="s">
+        <v>25</v>
+      </c>
+      <c r="N7" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="N7" s="1" t="s">
+      <c r="O7" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="O7" s="1" t="s">
+      <c r="P7" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="P7" s="1" t="s">
+      <c r="Q7" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="Q7" s="1" t="s">
+      <c r="R7" s="10" t="s">
         <v>30</v>
-      </c>
-      <c r="R7" s="10" t="s">
-        <v>31</v>
       </c>
     </row>
     <row r="8" spans="1:18" x14ac:dyDescent="0.25">
@@ -6536,25 +6486,25 @@
         <v>1</v>
       </c>
       <c r="B8" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="C8" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="D8" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="G8">
         <v>1</v>
       </c>
       <c r="H8" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="I8" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="J8" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="M8" s="15">
         <v>1</v>
@@ -6566,25 +6516,25 @@
         <v>2</v>
       </c>
       <c r="B9" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="C9" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="D9" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="G9">
         <v>2</v>
       </c>
       <c r="H9" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="I9" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="J9" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="M9" s="15">
         <v>2</v>
@@ -6596,25 +6546,25 @@
         <v>3</v>
       </c>
       <c r="B10" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="C10" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="D10" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="G10">
         <v>3</v>
       </c>
       <c r="H10" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="I10" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="J10" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="M10" s="15">
         <v>3</v>
@@ -6626,25 +6576,25 @@
         <v>4</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="D11" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="G11">
         <v>4</v>
       </c>
       <c r="H11" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="I11" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="J11" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="M11" s="15">
         <v>4</v>
@@ -6659,10 +6609,10 @@
         <v>5</v>
       </c>
       <c r="B12" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="D12" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
     </row>
     <row r="13" spans="1:18" x14ac:dyDescent="0.25">
@@ -6670,13 +6620,13 @@
         <v>6</v>
       </c>
       <c r="B13" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="C13" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="D13" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
     </row>
     <row r="14" spans="1:18" x14ac:dyDescent="0.25">
@@ -6684,10 +6634,10 @@
         <v>7</v>
       </c>
       <c r="B14" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="C14" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
     </row>
     <row r="15" spans="1:18" x14ac:dyDescent="0.25">
@@ -6695,13 +6645,13 @@
         <v>8</v>
       </c>
       <c r="B15" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="C15" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="D15" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
     </row>
     <row r="16" spans="1:18" x14ac:dyDescent="0.25">
@@ -6709,13 +6659,13 @@
         <v>9</v>
       </c>
       <c r="B16" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="C16" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="D16" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
@@ -6723,13 +6673,13 @@
         <v>10</v>
       </c>
       <c r="B17" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="C17" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="D17" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
     </row>
     <row r="18" spans="1:4" ht="72.599999999999994" customHeight="1" x14ac:dyDescent="0.25">
@@ -6737,13 +6687,13 @@
         <v>11</v>
       </c>
       <c r="B18" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
@@ -6751,13 +6701,13 @@
         <v>12</v>
       </c>
       <c r="B19" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="C19" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="D19" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
@@ -6765,13 +6715,13 @@
         <v>13</v>
       </c>
       <c r="B20" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="C20" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D20" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
@@ -6779,13 +6729,13 @@
         <v>14</v>
       </c>
       <c r="B21" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="C21" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="D21" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
     </row>
   </sheetData>
@@ -6842,7 +6792,7 @@
   <sheetData>
     <row r="1" spans="1:160" x14ac:dyDescent="0.25">
       <c r="A1" s="30" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="B1" s="18"/>
       <c r="C1" s="18"/>
@@ -6850,7 +6800,7 @@
       <c r="E1" s="18"/>
       <c r="F1" s="18"/>
       <c r="H1" s="30" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="I1" s="18"/>
       <c r="J1" s="18"/>
@@ -6858,7 +6808,7 @@
       <c r="L1" s="18"/>
       <c r="M1" s="18"/>
       <c r="O1" s="30" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="P1" s="18"/>
       <c r="Q1" s="18"/>
@@ -6866,7 +6816,7 @@
       <c r="S1" s="18"/>
       <c r="T1" s="18"/>
       <c r="V1" s="30" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="W1" s="18"/>
       <c r="X1" s="18"/>
@@ -6874,7 +6824,7 @@
       <c r="Z1" s="18"/>
       <c r="AA1" s="18"/>
       <c r="AC1" s="30" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="AD1" s="18"/>
       <c r="AE1" s="18"/>
@@ -6882,7 +6832,7 @@
       <c r="AG1" s="18"/>
       <c r="AH1" s="18"/>
       <c r="AJ1" s="30" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="AK1" s="18"/>
       <c r="AL1" s="18"/>
@@ -6890,7 +6840,7 @@
       <c r="AN1" s="18"/>
       <c r="AO1" s="18"/>
       <c r="AQ1" s="30" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="AR1" s="18"/>
       <c r="AS1" s="18"/>
@@ -6898,7 +6848,7 @@
       <c r="AU1" s="18"/>
       <c r="AV1" s="18"/>
       <c r="AX1" s="30" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="AY1" s="18"/>
       <c r="AZ1" s="18"/>
@@ -6906,7 +6856,7 @@
       <c r="BB1" s="18"/>
       <c r="BC1" s="18"/>
       <c r="BE1" s="30" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="BF1" s="18"/>
       <c r="BG1" s="18"/>
@@ -6914,7 +6864,7 @@
       <c r="BI1" s="18"/>
       <c r="BJ1" s="18"/>
       <c r="BL1" s="30" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="BM1" s="18"/>
       <c r="BN1" s="18"/>
@@ -6922,7 +6872,7 @@
       <c r="BP1" s="18"/>
       <c r="BQ1" s="18"/>
       <c r="BS1" s="30" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="BT1" s="18"/>
       <c r="BU1" s="18"/>
@@ -6930,7 +6880,7 @@
       <c r="BW1" s="18"/>
       <c r="BX1" s="18"/>
       <c r="BZ1" s="30" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="CA1" s="18"/>
       <c r="CB1" s="18"/>
@@ -6938,7 +6888,7 @@
       <c r="CD1" s="18"/>
       <c r="CE1" s="18"/>
       <c r="CG1" s="30" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="CH1" s="18"/>
       <c r="CI1" s="18"/>
@@ -6946,7 +6896,7 @@
       <c r="CK1" s="18"/>
       <c r="CL1" s="18"/>
       <c r="CN1" s="30" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="CO1" s="18"/>
       <c r="CP1" s="18"/>
@@ -6954,7 +6904,7 @@
       <c r="CR1" s="18"/>
       <c r="CS1" s="18"/>
       <c r="CU1" s="30" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="CV1" s="18"/>
       <c r="CW1" s="18"/>
@@ -6962,7 +6912,7 @@
       <c r="CY1" s="18"/>
       <c r="CZ1" s="18"/>
       <c r="DB1" s="30" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="DC1" s="18"/>
       <c r="DD1" s="18"/>
@@ -6970,7 +6920,7 @@
       <c r="DF1" s="18"/>
       <c r="DG1" s="18"/>
       <c r="DI1" s="30" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="DJ1" s="18"/>
       <c r="DK1" s="18"/>
@@ -6978,7 +6928,7 @@
       <c r="DM1" s="18"/>
       <c r="DN1" s="18"/>
       <c r="DP1" s="30" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="DQ1" s="18"/>
       <c r="DR1" s="18"/>
@@ -6986,7 +6936,7 @@
       <c r="DT1" s="18"/>
       <c r="DU1" s="18"/>
       <c r="DW1" s="30" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="DX1" s="18"/>
       <c r="DY1" s="18"/>
@@ -6994,7 +6944,7 @@
       <c r="EA1" s="18"/>
       <c r="EB1" s="18"/>
       <c r="ED1" s="30" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="EE1" s="18"/>
       <c r="EF1" s="18"/>
@@ -7002,7 +6952,7 @@
       <c r="EH1" s="18"/>
       <c r="EI1" s="18"/>
       <c r="EK1" s="30" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="EL1" s="18"/>
       <c r="EM1" s="18"/>
@@ -7010,7 +6960,7 @@
       <c r="EO1" s="18"/>
       <c r="EP1" s="18"/>
       <c r="ER1" s="30" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="ES1" s="18"/>
       <c r="ET1" s="18"/>
@@ -7018,7 +6968,7 @@
       <c r="EV1" s="18"/>
       <c r="EW1" s="18"/>
       <c r="EY1" s="30" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="EZ1" s="18"/>
       <c r="FA1" s="18"/>
@@ -7028,161 +6978,161 @@
     </row>
     <row r="2" spans="1:160" x14ac:dyDescent="0.25">
       <c r="A2" s="16" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B2" s="16">
         <f>IFERROR(_xlfn.XLOOKUP(A1, TestMaster[Test Name], TestMaster[Test ID], "ID not found"), "")</f>
         <v>9</v>
       </c>
       <c r="H2" s="16" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I2" s="16">
         <f>IFERROR(_xlfn.SINGLE(_xlfn.XLOOKUP(H1, TestMaster[Test Name], TestMaster[Test ID], "ID not found")), "")</f>
         <v>22</v>
       </c>
       <c r="O2" s="16" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="P2" s="16">
         <f>IFERROR(_xlfn.SINGLE(_xlfn.XLOOKUP(O1, TestMaster[Test Name], TestMaster[Test ID], "ID not found")), "")</f>
         <v>21</v>
       </c>
       <c r="V2" s="16" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="W2" s="16">
         <f>IFERROR(_xlfn.SINGLE(_xlfn.XLOOKUP(V1, TestMaster[Test Name], TestMaster[Test ID], "ID not found")), "")</f>
         <v>23</v>
       </c>
       <c r="AC2" s="16" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AD2" s="16">
         <f>IFERROR(_xlfn.SINGLE(_xlfn.XLOOKUP(AC1, TestMaster[Test Name], TestMaster[Test ID], "ID not found")), "")</f>
         <v>15</v>
       </c>
       <c r="AJ2" s="16" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AK2" s="16">
         <f>IFERROR(_xlfn.SINGLE(_xlfn.XLOOKUP(AJ1, TestMaster[Test Name], TestMaster[Test ID], "ID not found")), "")</f>
         <v>14</v>
       </c>
       <c r="AQ2" s="16" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AR2" s="16">
         <f>IFERROR(_xlfn.SINGLE(_xlfn.XLOOKUP(AQ1, TestMaster[Test Name], TestMaster[Test ID], "ID not found")), "")</f>
         <v>17</v>
       </c>
       <c r="AX2" s="16" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AY2" s="16">
         <f>IFERROR(_xlfn.SINGLE(_xlfn.XLOOKUP(AX1, TestMaster[Test Name], TestMaster[Test ID], "ID not found")), "")</f>
         <v>16</v>
       </c>
       <c r="BE2" s="16" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="BF2" s="16">
         <f>IFERROR(_xlfn.SINGLE(_xlfn.XLOOKUP(BE1, TestMaster[Test Name], TestMaster[Test ID], "ID not found")), "")</f>
         <v>11</v>
       </c>
       <c r="BL2" s="16" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="BM2" s="16">
         <f>IFERROR(_xlfn.SINGLE(_xlfn.XLOOKUP(BL1, TestMaster[Test Name], TestMaster[Test ID], "ID not found")), "")</f>
         <v>10</v>
       </c>
       <c r="BS2" s="16" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="BT2" s="16">
         <f>IFERROR(_xlfn.SINGLE(_xlfn.XLOOKUP(BS1, TestMaster[Test Name], TestMaster[Test ID], "ID not found")), "")</f>
         <v>13</v>
       </c>
       <c r="BZ2" s="16" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="CA2" s="16">
         <f>IFERROR(_xlfn.SINGLE(_xlfn.XLOOKUP(BZ1, TestMaster[Test Name], TestMaster[Test ID], "ID not found")), "")</f>
         <v>12</v>
       </c>
       <c r="CG2" s="16" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="CH2" s="16">
         <f>IFERROR(_xlfn.SINGLE(_xlfn.XLOOKUP(CG1, TestMaster[Test Name], TestMaster[Test ID], "ID not found")), "")</f>
         <v>4</v>
       </c>
       <c r="CN2" s="16" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="CO2" s="16">
         <f>IFERROR(_xlfn.SINGLE(_xlfn.XLOOKUP(CN1, TestMaster[Test Name], TestMaster[Test ID], "ID not found")), "")</f>
         <v>7</v>
       </c>
       <c r="CU2" s="16" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="CV2" s="16">
         <f>IFERROR(_xlfn.SINGLE(_xlfn.XLOOKUP(CU1, TestMaster[Test Name], TestMaster[Test ID], "ID not found")), "")</f>
         <v>6</v>
       </c>
       <c r="DB2" s="16" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="DC2" s="16">
         <f>IFERROR(_xlfn.SINGLE(_xlfn.XLOOKUP(DB1, TestMaster[Test Name], TestMaster[Test ID], "ID not found")), "")</f>
         <v>8</v>
       </c>
       <c r="DI2" s="16" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="DJ2" s="16">
         <f>IFERROR(_xlfn.SINGLE(_xlfn.XLOOKUP(DI1, TestMaster[Test Name], TestMaster[Test ID], "ID not found")), "")</f>
         <v>2</v>
       </c>
       <c r="DP2" s="16" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="DQ2" s="16">
         <f>IFERROR(_xlfn.SINGLE(_xlfn.XLOOKUP(DP1, TestMaster[Test Name], TestMaster[Test ID], "ID not found")), "")</f>
         <v>1</v>
       </c>
       <c r="DW2" s="16" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="DX2" s="16">
         <f>IFERROR(_xlfn.SINGLE(_xlfn.XLOOKUP(DW1, TestMaster[Test Name], TestMaster[Test ID], "ID not found")), "")</f>
         <v>3</v>
       </c>
       <c r="ED2" s="16" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="EE2" s="16">
         <f>IFERROR(_xlfn.SINGLE(_xlfn.XLOOKUP(ED1, TestMaster[Test Name], TestMaster[Test ID], "ID not found")), "")</f>
         <v>18</v>
       </c>
       <c r="EK2" s="16" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="EL2" s="16">
         <f>IFERROR(_xlfn.SINGLE(_xlfn.XLOOKUP(EK1, TestMaster[Test Name], TestMaster[Test ID], "ID not found")), "")</f>
         <v>19</v>
       </c>
       <c r="ER2" s="16" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="ES2" s="16">
         <f>IFERROR(_xlfn.SINGLE(_xlfn.XLOOKUP(ER1, TestMaster[Test Name], TestMaster[Test ID], "ID not found")), "")</f>
         <v>5</v>
       </c>
       <c r="EY2" s="16" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="EZ2" s="16">
         <f>IFERROR(_xlfn.SINGLE(_xlfn.XLOOKUP(EY1, TestMaster[Test Name], TestMaster[Test ID], "ID not found")), "")</f>
@@ -7191,255 +7141,255 @@
     </row>
     <row r="3" spans="1:160" x14ac:dyDescent="0.25">
       <c r="A3" s="16" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B3" s="16"/>
       <c r="H3" s="16" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I3" s="16"/>
       <c r="O3" s="16" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="P3" s="16"/>
       <c r="V3" s="16" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="W3" s="16"/>
       <c r="AC3" s="16" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AD3" s="16"/>
       <c r="AJ3" s="16" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AK3" s="16"/>
       <c r="AQ3" s="16" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AR3" s="16"/>
       <c r="AX3" s="16" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AY3" s="16"/>
       <c r="BE3" s="16" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BF3" s="16"/>
       <c r="BL3" s="16" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BM3" s="16"/>
       <c r="BS3" s="16" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BT3" s="16"/>
       <c r="BZ3" s="16" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="CA3" s="16"/>
       <c r="CG3" s="16" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="CH3" s="16"/>
       <c r="CN3" s="16" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="CO3" s="16"/>
       <c r="CU3" s="16" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="CV3" s="16"/>
       <c r="DB3" s="16" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="DC3" s="16"/>
       <c r="DI3" s="16" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="DJ3" s="16"/>
       <c r="DP3" s="16" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="DQ3" s="16"/>
       <c r="DW3" s="16" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="DX3" s="16"/>
       <c r="ED3" s="16" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="EE3" s="16"/>
       <c r="EK3" s="16" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="EL3" s="16"/>
       <c r="ER3" s="16" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="ES3" s="16"/>
       <c r="EY3" s="16" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="EZ3" s="16"/>
     </row>
     <row r="4" spans="1:160" x14ac:dyDescent="0.25">
       <c r="A4" s="16" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B4" s="16" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(A1, TestMaster[Test Name], TestMaster[Test Priority], "Priority not found"), "")</f>
         <v>Medium</v>
       </c>
       <c r="H4" s="16" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I4" s="16" t="str">
         <f>IFERROR(_xlfn.SINGLE(_xlfn.XLOOKUP(H1, TestMaster[Test Name], TestMaster[Test Priority], "Priority not found")), "")</f>
         <v>Medium</v>
       </c>
       <c r="O4" s="16" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="P4" s="16" t="str">
         <f>IFERROR(_xlfn.SINGLE(_xlfn.XLOOKUP(O1, TestMaster[Test Name], TestMaster[Test Priority], "Priority not found")), "")</f>
         <v>Medium</v>
       </c>
       <c r="V4" s="16" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="W4" s="16" t="str">
         <f>IFERROR(_xlfn.SINGLE(_xlfn.XLOOKUP(V1, TestMaster[Test Name], TestMaster[Test Priority], "Priority not found")), "")</f>
         <v>Medium</v>
       </c>
       <c r="AC4" s="16" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AD4" s="16">
         <f>IFERROR(_xlfn.SINGLE(_xlfn.XLOOKUP(AC1, TestMaster[Test Name], TestMaster[Test Priority], "Priority not found")), "")</f>
         <v>0</v>
       </c>
       <c r="AJ4" s="16" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AK4" s="16">
         <f>IFERROR(_xlfn.SINGLE(_xlfn.XLOOKUP(AJ1, TestMaster[Test Name], TestMaster[Test Priority], "Priority not found")), "")</f>
         <v>0</v>
       </c>
       <c r="AQ4" s="16" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AR4" s="16">
         <f>IFERROR(_xlfn.SINGLE(_xlfn.XLOOKUP(AQ1, TestMaster[Test Name], TestMaster[Test Priority], "Priority not found")), "")</f>
         <v>0</v>
       </c>
       <c r="AX4" s="16" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AY4" s="16">
         <f>IFERROR(_xlfn.SINGLE(_xlfn.XLOOKUP(AX1, TestMaster[Test Name], TestMaster[Test Priority], "Priority not found")), "")</f>
         <v>0</v>
       </c>
       <c r="BE4" s="16" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BF4" s="16">
         <f>IFERROR(_xlfn.SINGLE(_xlfn.XLOOKUP(BE1, TestMaster[Test Name], TestMaster[Test Priority], "Priority not found")), "")</f>
         <v>0</v>
       </c>
       <c r="BL4" s="16" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BM4" s="16">
         <f>IFERROR(_xlfn.SINGLE(_xlfn.XLOOKUP(BL1, TestMaster[Test Name], TestMaster[Test Priority], "Priority not found")), "")</f>
         <v>0</v>
       </c>
       <c r="BS4" s="16" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BT4" s="16">
         <f>IFERROR(_xlfn.SINGLE(_xlfn.XLOOKUP(BS1, TestMaster[Test Name], TestMaster[Test Priority], "Priority not found")), "")</f>
         <v>0</v>
       </c>
       <c r="BZ4" s="16" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="CA4" s="16">
         <f>IFERROR(_xlfn.SINGLE(_xlfn.XLOOKUP(BZ1, TestMaster[Test Name], TestMaster[Test Priority], "Priority not found")), "")</f>
         <v>0</v>
       </c>
       <c r="CG4" s="16" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="CH4" s="16">
         <f>IFERROR(_xlfn.SINGLE(_xlfn.XLOOKUP(CG1, TestMaster[Test Name], TestMaster[Test Priority], "Priority not found")), "")</f>
         <v>0</v>
       </c>
       <c r="CN4" s="16" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="CO4" s="16">
         <f>IFERROR(_xlfn.SINGLE(_xlfn.XLOOKUP(CN1, TestMaster[Test Name], TestMaster[Test Priority], "Priority not found")), "")</f>
         <v>0</v>
       </c>
       <c r="CU4" s="16" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="CV4" s="16">
         <f>IFERROR(_xlfn.SINGLE(_xlfn.XLOOKUP(CU1, TestMaster[Test Name], TestMaster[Test Priority], "Priority not found")), "")</f>
         <v>0</v>
       </c>
       <c r="DB4" s="16" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="DC4" s="16">
         <f>IFERROR(_xlfn.SINGLE(_xlfn.XLOOKUP(DB1, TestMaster[Test Name], TestMaster[Test Priority], "Priority not found")), "")</f>
         <v>0</v>
       </c>
       <c r="DI4" s="16" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="DJ4" s="16">
         <f>IFERROR(_xlfn.SINGLE(_xlfn.XLOOKUP(DI1, TestMaster[Test Name], TestMaster[Test Priority], "Priority not found")), "")</f>
         <v>0</v>
       </c>
       <c r="DP4" s="16" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="DQ4" s="16">
         <f>IFERROR(_xlfn.SINGLE(_xlfn.XLOOKUP(DP1, TestMaster[Test Name], TestMaster[Test Priority], "Priority not found")), "")</f>
         <v>0</v>
       </c>
       <c r="DW4" s="16" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="DX4" s="16">
         <f>IFERROR(_xlfn.SINGLE(_xlfn.XLOOKUP(DW1, TestMaster[Test Name], TestMaster[Test Priority], "Priority not found")), "")</f>
         <v>0</v>
       </c>
       <c r="ED4" s="16" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="EE4" s="16">
         <f>IFERROR(_xlfn.SINGLE(_xlfn.XLOOKUP(ED1, TestMaster[Test Name], TestMaster[Test Priority], "Priority not found")), "")</f>
         <v>0</v>
       </c>
       <c r="EK4" s="16" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="EL4" s="16">
         <f>IFERROR(_xlfn.SINGLE(_xlfn.XLOOKUP(EK1, TestMaster[Test Name], TestMaster[Test Priority], "Priority not found")), "")</f>
         <v>0</v>
       </c>
       <c r="ER4" s="16" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="ES4" s="16">
         <f>IFERROR(_xlfn.SINGLE(_xlfn.XLOOKUP(ER1, TestMaster[Test Name], TestMaster[Test Priority], "Priority not found")), "")</f>
         <v>0</v>
       </c>
       <c r="EY4" s="16" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="EZ4" s="16">
         <f>IFERROR(_xlfn.SINGLE(_xlfn.XLOOKUP(EY1, TestMaster[Test Name], TestMaster[Test Priority], "Priority not found")), "")</f>
@@ -7448,161 +7398,161 @@
     </row>
     <row r="5" spans="1:160" x14ac:dyDescent="0.25">
       <c r="A5" s="16" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B5" s="16" t="str">
         <f>IFERROR(_xlfn.SINGLE(_xlfn.XLOOKUP(A1, TestMaster[Test Name], TestMaster[Test Status], "Status not found")), "")</f>
         <v>Fail</v>
       </c>
       <c r="H5" s="16" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="I5" s="16" t="str">
         <f>IFERROR(_xlfn.SINGLE(_xlfn.XLOOKUP(H1, TestMaster[Test Name], TestMaster[Test Status], "Status not found")), "")</f>
         <v>Pass</v>
       </c>
       <c r="O5" s="16" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="P5" s="16" t="str">
         <f>IFERROR(_xlfn.SINGLE(_xlfn.XLOOKUP(O1, TestMaster[Test Name], TestMaster[Test Status], "Status not found")), "")</f>
         <v>Pass</v>
       </c>
       <c r="V5" s="16" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="W5" s="16" t="str">
         <f>IFERROR(_xlfn.SINGLE(_xlfn.XLOOKUP(V1, TestMaster[Test Name], TestMaster[Test Status], "Status not found")), "")</f>
         <v>Pass</v>
       </c>
       <c r="AC5" s="16" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AD5" s="16" t="str">
         <f>IFERROR(_xlfn.SINGLE(_xlfn.XLOOKUP(AC1, TestMaster[Test Name], TestMaster[Test Status], "Status not found")), "")</f>
         <v>Fail</v>
       </c>
       <c r="AJ5" s="16" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AK5" s="16" t="str">
         <f>IFERROR(_xlfn.SINGLE(_xlfn.XLOOKUP(AJ1, TestMaster[Test Name], TestMaster[Test Status], "Status not found")), "")</f>
         <v>Fail</v>
       </c>
       <c r="AQ5" s="16" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AR5" s="16" t="str">
         <f>IFERROR(_xlfn.SINGLE(_xlfn.XLOOKUP(AQ1, TestMaster[Test Name], TestMaster[Test Status], "Status not found")), "")</f>
         <v>Pass</v>
       </c>
       <c r="AX5" s="16" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AY5" s="16" t="str">
         <f>IFERROR(_xlfn.SINGLE(_xlfn.XLOOKUP(AX1, TestMaster[Test Name], TestMaster[Test Status], "Status not found")), "")</f>
         <v>Pass</v>
       </c>
       <c r="BE5" s="16" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BF5" s="16" t="str">
         <f>IFERROR(_xlfn.SINGLE(_xlfn.XLOOKUP(BE1, TestMaster[Test Name], TestMaster[Test Status], "Status not found")), "")</f>
         <v>Pass</v>
       </c>
       <c r="BL5" s="16" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BM5" s="16" t="str">
         <f>IFERROR(_xlfn.SINGLE(_xlfn.XLOOKUP(BL1, TestMaster[Test Name], TestMaster[Test Status], "Status not found")), "")</f>
         <v>Pass</v>
       </c>
       <c r="BS5" s="16" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BT5" s="16" t="str">
         <f>IFERROR(_xlfn.SINGLE(_xlfn.XLOOKUP(BS1, TestMaster[Test Name], TestMaster[Test Status], "Status not found")), "")</f>
         <v>Fail</v>
       </c>
       <c r="BZ5" s="16" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="CA5" s="16" t="str">
         <f>IFERROR(_xlfn.SINGLE(_xlfn.XLOOKUP(BZ1, TestMaster[Test Name], TestMaster[Test Status], "Status not found")), "")</f>
         <v>Fail</v>
       </c>
       <c r="CG5" s="16" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="CH5" s="16" t="str">
         <f>IFERROR(_xlfn.SINGLE(_xlfn.XLOOKUP(CG1, TestMaster[Test Name], TestMaster[Test Status], "Status not found")), "")</f>
         <v>Fail</v>
       </c>
       <c r="CN5" s="16" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="CO5" s="16" t="str">
         <f>IFERROR(_xlfn.SINGLE(_xlfn.XLOOKUP(CN1, TestMaster[Test Name], TestMaster[Test Status], "Status not found")), "")</f>
         <v>Fail</v>
       </c>
       <c r="CU5" s="16" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="CV5" s="16" t="str">
         <f>IFERROR(_xlfn.SINGLE(_xlfn.XLOOKUP(CU1, TestMaster[Test Name], TestMaster[Test Status], "Status not found")), "")</f>
         <v>Pass</v>
       </c>
       <c r="DB5" s="16" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="DC5" s="16" t="str">
         <f>IFERROR(_xlfn.SINGLE(_xlfn.XLOOKUP(DB1, TestMaster[Test Name], TestMaster[Test Status], "Status not found")), "")</f>
         <v>Fail</v>
       </c>
       <c r="DI5" s="16" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="DJ5" s="16" t="str">
         <f>IFERROR(_xlfn.SINGLE(_xlfn.XLOOKUP(DI1, TestMaster[Test Name], TestMaster[Test Status], "Status not found")), "")</f>
         <v>Fail</v>
       </c>
       <c r="DP5" s="16" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="DQ5" s="16" t="str">
         <f>IFERROR(_xlfn.SINGLE(_xlfn.XLOOKUP(DP1, TestMaster[Test Name], TestMaster[Test Status], "Status not found")), "")</f>
         <v>Fail</v>
       </c>
       <c r="DW5" s="16" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="DX5" s="16" t="str">
         <f>IFERROR(_xlfn.SINGLE(_xlfn.XLOOKUP(DW1, TestMaster[Test Name], TestMaster[Test Status], "Status not found")), "")</f>
         <v>Fail</v>
       </c>
       <c r="ED5" s="16" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="EE5" s="16" t="str">
         <f>IFERROR(_xlfn.SINGLE(_xlfn.XLOOKUP(ED1, TestMaster[Test Name], TestMaster[Test Status], "Status not found")), "")</f>
         <v>Pass</v>
       </c>
       <c r="EK5" s="16" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="EL5" s="16" t="str">
         <f>IFERROR(_xlfn.SINGLE(_xlfn.XLOOKUP(EK1, TestMaster[Test Name], TestMaster[Test Status], "Status not found")), "")</f>
         <v>Pass</v>
       </c>
       <c r="ER5" s="16" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="ES5" s="16" t="str">
         <f>IFERROR(_xlfn.SINGLE(_xlfn.XLOOKUP(ER1, TestMaster[Test Name], TestMaster[Test Status], "Status not found")), "")</f>
         <v>Pass</v>
       </c>
       <c r="EY5" s="16" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="EZ5" s="16" t="str">
         <f>IFERROR(_xlfn.SINGLE(_xlfn.XLOOKUP(EY1, TestMaster[Test Name], TestMaster[Test Status], "Status not found")), "")</f>
@@ -7611,230 +7561,230 @@
     </row>
     <row r="6" spans="1:160" x14ac:dyDescent="0.25">
       <c r="A6" s="16" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="B6" s="29" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="C6" s="18"/>
       <c r="D6" s="18"/>
       <c r="E6" s="18"/>
       <c r="F6" s="18"/>
       <c r="H6" s="16" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="I6" s="29" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="J6" s="18"/>
       <c r="K6" s="18"/>
       <c r="L6" s="18"/>
       <c r="M6" s="18"/>
       <c r="O6" s="16" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="P6" s="29" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="Q6" s="18"/>
       <c r="R6" s="18"/>
       <c r="S6" s="18"/>
       <c r="T6" s="18"/>
       <c r="V6" s="16" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="W6" s="29" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="X6" s="18"/>
       <c r="Y6" s="18"/>
       <c r="Z6" s="18"/>
       <c r="AA6" s="18"/>
       <c r="AC6" s="16" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="AD6" s="29" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="AE6" s="18"/>
       <c r="AF6" s="18"/>
       <c r="AG6" s="18"/>
       <c r="AH6" s="18"/>
       <c r="AJ6" s="16" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="AK6" s="29" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="AL6" s="18"/>
       <c r="AM6" s="18"/>
       <c r="AN6" s="18"/>
       <c r="AO6" s="18"/>
       <c r="AQ6" s="16" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="AR6" s="29" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="AS6" s="18"/>
       <c r="AT6" s="18"/>
       <c r="AU6" s="18"/>
       <c r="AV6" s="18"/>
       <c r="AX6" s="16" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="AY6" s="29" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="AZ6" s="18"/>
       <c r="BA6" s="18"/>
       <c r="BB6" s="18"/>
       <c r="BC6" s="18"/>
       <c r="BE6" s="16" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="BF6" s="29" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="BG6" s="18"/>
       <c r="BH6" s="18"/>
       <c r="BI6" s="18"/>
       <c r="BJ6" s="18"/>
       <c r="BL6" s="16" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="BM6" s="29" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="BN6" s="18"/>
       <c r="BO6" s="18"/>
       <c r="BP6" s="18"/>
       <c r="BQ6" s="18"/>
       <c r="BS6" s="16" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="BT6" s="29" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="BU6" s="18"/>
       <c r="BV6" s="18"/>
       <c r="BW6" s="18"/>
       <c r="BX6" s="18"/>
       <c r="BZ6" s="16" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="CA6" s="29" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="CB6" s="18"/>
       <c r="CC6" s="18"/>
       <c r="CD6" s="18"/>
       <c r="CE6" s="18"/>
       <c r="CG6" s="16" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="CH6" s="29" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="CI6" s="18"/>
       <c r="CJ6" s="18"/>
       <c r="CK6" s="18"/>
       <c r="CL6" s="18"/>
       <c r="CN6" s="16" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="CO6" s="29" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="CP6" s="18"/>
       <c r="CQ6" s="18"/>
       <c r="CR6" s="18"/>
       <c r="CS6" s="18"/>
       <c r="CU6" s="16" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="CV6" s="29" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="CW6" s="18"/>
       <c r="CX6" s="18"/>
       <c r="CY6" s="18"/>
       <c r="CZ6" s="18"/>
       <c r="DB6" s="16" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="DC6" s="29" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="DD6" s="18"/>
       <c r="DE6" s="18"/>
       <c r="DF6" s="18"/>
       <c r="DG6" s="18"/>
       <c r="DI6" s="16" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="DJ6" s="29" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="DK6" s="18"/>
       <c r="DL6" s="18"/>
       <c r="DM6" s="18"/>
       <c r="DN6" s="18"/>
       <c r="DP6" s="16" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="DQ6" s="29" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="DR6" s="18"/>
       <c r="DS6" s="18"/>
       <c r="DT6" s="18"/>
       <c r="DU6" s="18"/>
       <c r="DW6" s="16" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="DX6" s="29" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="DY6" s="18"/>
       <c r="DZ6" s="18"/>
       <c r="EA6" s="18"/>
       <c r="EB6" s="18"/>
       <c r="ED6" s="16" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="EE6" s="29" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="EF6" s="18"/>
       <c r="EG6" s="18"/>
       <c r="EH6" s="18"/>
       <c r="EI6" s="18"/>
       <c r="EK6" s="16" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="EL6" s="29" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="EM6" s="18"/>
       <c r="EN6" s="18"/>
       <c r="EO6" s="18"/>
       <c r="EP6" s="18"/>
       <c r="ER6" s="16" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="ES6" s="29" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="ET6" s="18"/>
       <c r="EU6" s="18"/>
       <c r="EV6" s="18"/>
       <c r="EW6" s="18"/>
       <c r="EY6" s="16" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="EZ6" s="29" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="FA6" s="18"/>
       <c r="FB6" s="18"/>
@@ -7843,230 +7793,230 @@
     </row>
     <row r="7" spans="1:160" x14ac:dyDescent="0.25">
       <c r="A7" s="16" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B7" s="29" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="C7" s="18"/>
       <c r="D7" s="18"/>
       <c r="E7" s="18"/>
       <c r="F7" s="18"/>
       <c r="H7" s="16" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I7" s="29" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="J7" s="18"/>
       <c r="K7" s="18"/>
       <c r="L7" s="18"/>
       <c r="M7" s="18"/>
       <c r="O7" s="16" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="P7" s="29" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="Q7" s="18"/>
       <c r="R7" s="18"/>
       <c r="S7" s="18"/>
       <c r="T7" s="18"/>
       <c r="V7" s="16" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="W7" s="29" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="X7" s="18"/>
       <c r="Y7" s="18"/>
       <c r="Z7" s="18"/>
       <c r="AA7" s="18"/>
       <c r="AC7" s="16" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AD7" s="29" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="AE7" s="18"/>
       <c r="AF7" s="18"/>
       <c r="AG7" s="18"/>
       <c r="AH7" s="18"/>
       <c r="AJ7" s="16" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AK7" s="29" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="AL7" s="18"/>
       <c r="AM7" s="18"/>
       <c r="AN7" s="18"/>
       <c r="AO7" s="18"/>
       <c r="AQ7" s="16" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AR7" s="29" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="AS7" s="18"/>
       <c r="AT7" s="18"/>
       <c r="AU7" s="18"/>
       <c r="AV7" s="18"/>
       <c r="AX7" s="16" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AY7" s="29" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="AZ7" s="18"/>
       <c r="BA7" s="18"/>
       <c r="BB7" s="18"/>
       <c r="BC7" s="18"/>
       <c r="BE7" s="16" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BF7" s="29" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="BG7" s="18"/>
       <c r="BH7" s="18"/>
       <c r="BI7" s="18"/>
       <c r="BJ7" s="18"/>
       <c r="BL7" s="16" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BM7" s="29" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="BN7" s="18"/>
       <c r="BO7" s="18"/>
       <c r="BP7" s="18"/>
       <c r="BQ7" s="18"/>
       <c r="BS7" s="16" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BT7" s="29" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="BU7" s="18"/>
       <c r="BV7" s="18"/>
       <c r="BW7" s="18"/>
       <c r="BX7" s="18"/>
       <c r="BZ7" s="16" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="CA7" s="29" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="CB7" s="18"/>
       <c r="CC7" s="18"/>
       <c r="CD7" s="18"/>
       <c r="CE7" s="18"/>
       <c r="CG7" s="16" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="CH7" s="29" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="CI7" s="18"/>
       <c r="CJ7" s="18"/>
       <c r="CK7" s="18"/>
       <c r="CL7" s="18"/>
       <c r="CN7" s="16" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="CO7" s="29" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="CP7" s="18"/>
       <c r="CQ7" s="18"/>
       <c r="CR7" s="18"/>
       <c r="CS7" s="18"/>
       <c r="CU7" s="16" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="CV7" s="29" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="CW7" s="18"/>
       <c r="CX7" s="18"/>
       <c r="CY7" s="18"/>
       <c r="CZ7" s="18"/>
       <c r="DB7" s="16" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="DC7" s="29" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="DD7" s="18"/>
       <c r="DE7" s="18"/>
       <c r="DF7" s="18"/>
       <c r="DG7" s="18"/>
       <c r="DI7" s="16" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="DJ7" s="29" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="DK7" s="18"/>
       <c r="DL7" s="18"/>
       <c r="DM7" s="18"/>
       <c r="DN7" s="18"/>
       <c r="DP7" s="16" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="DQ7" s="29" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="DR7" s="18"/>
       <c r="DS7" s="18"/>
       <c r="DT7" s="18"/>
       <c r="DU7" s="18"/>
       <c r="DW7" s="16" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="DX7" s="29" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="DY7" s="18"/>
       <c r="DZ7" s="18"/>
       <c r="EA7" s="18"/>
       <c r="EB7" s="18"/>
       <c r="ED7" s="16" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="EE7" s="29" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="EF7" s="18"/>
       <c r="EG7" s="18"/>
       <c r="EH7" s="18"/>
       <c r="EI7" s="18"/>
       <c r="EK7" s="16" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="EL7" s="29" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="EM7" s="18"/>
       <c r="EN7" s="18"/>
       <c r="EO7" s="18"/>
       <c r="EP7" s="18"/>
       <c r="ER7" s="16" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="ES7" s="29" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="ET7" s="18"/>
       <c r="EU7" s="18"/>
       <c r="EV7" s="18"/>
       <c r="EW7" s="18"/>
       <c r="EY7" s="16" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="EZ7" s="29" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="FA7" s="18"/>
       <c r="FB7" s="18"/>
@@ -8075,1296 +8025,1296 @@
     </row>
     <row r="8" spans="1:160" x14ac:dyDescent="0.25">
       <c r="A8" s="16" t="s">
+        <v>25</v>
+      </c>
+      <c r="B8" s="16" t="s">
         <v>26</v>
       </c>
-      <c r="B8" s="16" t="s">
+      <c r="C8" s="16" t="s">
         <v>27</v>
       </c>
-      <c r="C8" s="16" t="s">
+      <c r="D8" s="16" t="s">
         <v>28</v>
       </c>
-      <c r="D8" s="16" t="s">
+      <c r="E8" s="16" t="s">
         <v>29</v>
       </c>
-      <c r="E8" s="16" t="s">
+      <c r="F8" s="16" t="s">
         <v>30</v>
       </c>
-      <c r="F8" s="16" t="s">
-        <v>31</v>
-      </c>
       <c r="H8" s="16" t="s">
+        <v>25</v>
+      </c>
+      <c r="I8" s="16" t="s">
         <v>26</v>
       </c>
-      <c r="I8" s="16" t="s">
+      <c r="J8" s="16" t="s">
         <v>27</v>
       </c>
-      <c r="J8" s="16" t="s">
+      <c r="K8" s="16" t="s">
         <v>28</v>
       </c>
-      <c r="K8" s="16" t="s">
+      <c r="L8" s="16" t="s">
         <v>29</v>
       </c>
-      <c r="L8" s="16" t="s">
+      <c r="M8" s="16" t="s">
         <v>30</v>
       </c>
-      <c r="M8" s="16" t="s">
-        <v>31</v>
-      </c>
       <c r="O8" s="16" t="s">
+        <v>25</v>
+      </c>
+      <c r="P8" s="16" t="s">
         <v>26</v>
       </c>
-      <c r="P8" s="16" t="s">
+      <c r="Q8" s="16" t="s">
         <v>27</v>
       </c>
-      <c r="Q8" s="16" t="s">
+      <c r="R8" s="16" t="s">
         <v>28</v>
       </c>
-      <c r="R8" s="16" t="s">
+      <c r="S8" s="16" t="s">
         <v>29</v>
       </c>
-      <c r="S8" s="16" t="s">
+      <c r="T8" s="16" t="s">
         <v>30</v>
       </c>
-      <c r="T8" s="16" t="s">
-        <v>31</v>
-      </c>
       <c r="V8" s="16" t="s">
+        <v>25</v>
+      </c>
+      <c r="W8" s="16" t="s">
         <v>26</v>
       </c>
-      <c r="W8" s="16" t="s">
+      <c r="X8" s="16" t="s">
         <v>27</v>
       </c>
-      <c r="X8" s="16" t="s">
+      <c r="Y8" s="16" t="s">
         <v>28</v>
       </c>
-      <c r="Y8" s="16" t="s">
+      <c r="Z8" s="16" t="s">
         <v>29</v>
       </c>
-      <c r="Z8" s="16" t="s">
+      <c r="AA8" s="16" t="s">
         <v>30</v>
       </c>
-      <c r="AA8" s="16" t="s">
-        <v>31</v>
-      </c>
       <c r="AC8" s="16" t="s">
+        <v>25</v>
+      </c>
+      <c r="AD8" s="16" t="s">
         <v>26</v>
       </c>
-      <c r="AD8" s="16" t="s">
+      <c r="AE8" s="16" t="s">
         <v>27</v>
       </c>
-      <c r="AE8" s="16" t="s">
+      <c r="AF8" s="16" t="s">
         <v>28</v>
       </c>
-      <c r="AF8" s="16" t="s">
+      <c r="AG8" s="16" t="s">
         <v>29</v>
       </c>
-      <c r="AG8" s="16" t="s">
+      <c r="AH8" s="16" t="s">
         <v>30</v>
       </c>
-      <c r="AH8" s="16" t="s">
-        <v>31</v>
-      </c>
       <c r="AJ8" s="16" t="s">
+        <v>25</v>
+      </c>
+      <c r="AK8" s="16" t="s">
         <v>26</v>
       </c>
-      <c r="AK8" s="16" t="s">
+      <c r="AL8" s="16" t="s">
         <v>27</v>
       </c>
-      <c r="AL8" s="16" t="s">
+      <c r="AM8" s="16" t="s">
         <v>28</v>
       </c>
-      <c r="AM8" s="16" t="s">
+      <c r="AN8" s="16" t="s">
         <v>29</v>
       </c>
-      <c r="AN8" s="16" t="s">
+      <c r="AO8" s="16" t="s">
         <v>30</v>
       </c>
-      <c r="AO8" s="16" t="s">
-        <v>31</v>
-      </c>
       <c r="AQ8" s="16" t="s">
+        <v>25</v>
+      </c>
+      <c r="AR8" s="16" t="s">
         <v>26</v>
       </c>
-      <c r="AR8" s="16" t="s">
+      <c r="AS8" s="16" t="s">
         <v>27</v>
       </c>
-      <c r="AS8" s="16" t="s">
+      <c r="AT8" s="16" t="s">
         <v>28</v>
       </c>
-      <c r="AT8" s="16" t="s">
+      <c r="AU8" s="16" t="s">
         <v>29</v>
       </c>
-      <c r="AU8" s="16" t="s">
+      <c r="AV8" s="16" t="s">
         <v>30</v>
       </c>
-      <c r="AV8" s="16" t="s">
-        <v>31</v>
-      </c>
       <c r="AX8" s="16" t="s">
+        <v>25</v>
+      </c>
+      <c r="AY8" s="16" t="s">
         <v>26</v>
       </c>
-      <c r="AY8" s="16" t="s">
+      <c r="AZ8" s="16" t="s">
         <v>27</v>
       </c>
-      <c r="AZ8" s="16" t="s">
+      <c r="BA8" s="16" t="s">
         <v>28</v>
       </c>
-      <c r="BA8" s="16" t="s">
+      <c r="BB8" s="16" t="s">
         <v>29</v>
       </c>
-      <c r="BB8" s="16" t="s">
+      <c r="BC8" s="16" t="s">
         <v>30</v>
       </c>
-      <c r="BC8" s="16" t="s">
-        <v>31</v>
-      </c>
       <c r="BE8" s="16" t="s">
+        <v>25</v>
+      </c>
+      <c r="BF8" s="16" t="s">
         <v>26</v>
       </c>
-      <c r="BF8" s="16" t="s">
+      <c r="BG8" s="16" t="s">
         <v>27</v>
       </c>
-      <c r="BG8" s="16" t="s">
+      <c r="BH8" s="16" t="s">
         <v>28</v>
       </c>
-      <c r="BH8" s="16" t="s">
+      <c r="BI8" s="16" t="s">
         <v>29</v>
       </c>
-      <c r="BI8" s="16" t="s">
+      <c r="BJ8" s="16" t="s">
         <v>30</v>
       </c>
-      <c r="BJ8" s="16" t="s">
-        <v>31</v>
-      </c>
       <c r="BL8" s="16" t="s">
+        <v>25</v>
+      </c>
+      <c r="BM8" s="16" t="s">
         <v>26</v>
       </c>
-      <c r="BM8" s="16" t="s">
+      <c r="BN8" s="16" t="s">
         <v>27</v>
       </c>
-      <c r="BN8" s="16" t="s">
+      <c r="BO8" s="16" t="s">
         <v>28</v>
       </c>
-      <c r="BO8" s="16" t="s">
+      <c r="BP8" s="16" t="s">
         <v>29</v>
       </c>
-      <c r="BP8" s="16" t="s">
+      <c r="BQ8" s="16" t="s">
         <v>30</v>
       </c>
-      <c r="BQ8" s="16" t="s">
-        <v>31</v>
-      </c>
       <c r="BS8" s="16" t="s">
+        <v>25</v>
+      </c>
+      <c r="BT8" s="16" t="s">
         <v>26</v>
       </c>
-      <c r="BT8" s="16" t="s">
+      <c r="BU8" s="16" t="s">
         <v>27</v>
       </c>
-      <c r="BU8" s="16" t="s">
+      <c r="BV8" s="16" t="s">
         <v>28</v>
       </c>
-      <c r="BV8" s="16" t="s">
+      <c r="BW8" s="16" t="s">
         <v>29</v>
       </c>
-      <c r="BW8" s="16" t="s">
+      <c r="BX8" s="16" t="s">
         <v>30</v>
       </c>
-      <c r="BX8" s="16" t="s">
-        <v>31</v>
-      </c>
       <c r="BZ8" s="16" t="s">
+        <v>25</v>
+      </c>
+      <c r="CA8" s="16" t="s">
         <v>26</v>
       </c>
-      <c r="CA8" s="16" t="s">
+      <c r="CB8" s="16" t="s">
         <v>27</v>
       </c>
-      <c r="CB8" s="16" t="s">
+      <c r="CC8" s="16" t="s">
         <v>28</v>
       </c>
-      <c r="CC8" s="16" t="s">
+      <c r="CD8" s="16" t="s">
         <v>29</v>
       </c>
-      <c r="CD8" s="16" t="s">
+      <c r="CE8" s="16" t="s">
         <v>30</v>
       </c>
-      <c r="CE8" s="16" t="s">
-        <v>31</v>
-      </c>
       <c r="CG8" s="16" t="s">
+        <v>25</v>
+      </c>
+      <c r="CH8" s="16" t="s">
         <v>26</v>
       </c>
-      <c r="CH8" s="16" t="s">
+      <c r="CI8" s="16" t="s">
         <v>27</v>
       </c>
-      <c r="CI8" s="16" t="s">
+      <c r="CJ8" s="16" t="s">
         <v>28</v>
       </c>
-      <c r="CJ8" s="16" t="s">
+      <c r="CK8" s="16" t="s">
         <v>29</v>
       </c>
-      <c r="CK8" s="16" t="s">
+      <c r="CL8" s="16" t="s">
         <v>30</v>
       </c>
-      <c r="CL8" s="16" t="s">
-        <v>31</v>
-      </c>
       <c r="CN8" s="16" t="s">
+        <v>25</v>
+      </c>
+      <c r="CO8" s="16" t="s">
         <v>26</v>
       </c>
-      <c r="CO8" s="16" t="s">
+      <c r="CP8" s="16" t="s">
         <v>27</v>
       </c>
-      <c r="CP8" s="16" t="s">
+      <c r="CQ8" s="16" t="s">
         <v>28</v>
       </c>
-      <c r="CQ8" s="16" t="s">
+      <c r="CR8" s="16" t="s">
         <v>29</v>
       </c>
-      <c r="CR8" s="16" t="s">
+      <c r="CS8" s="16" t="s">
         <v>30</v>
       </c>
-      <c r="CS8" s="16" t="s">
-        <v>31</v>
-      </c>
       <c r="CU8" s="16" t="s">
+        <v>25</v>
+      </c>
+      <c r="CV8" s="16" t="s">
         <v>26</v>
       </c>
-      <c r="CV8" s="16" t="s">
+      <c r="CW8" s="16" t="s">
         <v>27</v>
       </c>
-      <c r="CW8" s="16" t="s">
+      <c r="CX8" s="16" t="s">
         <v>28</v>
       </c>
-      <c r="CX8" s="16" t="s">
+      <c r="CY8" s="16" t="s">
         <v>29</v>
       </c>
-      <c r="CY8" s="16" t="s">
+      <c r="CZ8" s="16" t="s">
         <v>30</v>
       </c>
-      <c r="CZ8" s="16" t="s">
-        <v>31</v>
-      </c>
       <c r="DB8" s="16" t="s">
+        <v>25</v>
+      </c>
+      <c r="DC8" s="16" t="s">
         <v>26</v>
       </c>
-      <c r="DC8" s="16" t="s">
+      <c r="DD8" s="16" t="s">
         <v>27</v>
       </c>
-      <c r="DD8" s="16" t="s">
+      <c r="DE8" s="16" t="s">
         <v>28</v>
       </c>
-      <c r="DE8" s="16" t="s">
+      <c r="DF8" s="16" t="s">
         <v>29</v>
       </c>
-      <c r="DF8" s="16" t="s">
+      <c r="DG8" s="16" t="s">
         <v>30</v>
       </c>
-      <c r="DG8" s="16" t="s">
-        <v>31</v>
-      </c>
       <c r="DI8" s="16" t="s">
+        <v>25</v>
+      </c>
+      <c r="DJ8" s="16" t="s">
         <v>26</v>
       </c>
-      <c r="DJ8" s="16" t="s">
+      <c r="DK8" s="16" t="s">
         <v>27</v>
       </c>
-      <c r="DK8" s="16" t="s">
+      <c r="DL8" s="16" t="s">
         <v>28</v>
       </c>
-      <c r="DL8" s="16" t="s">
+      <c r="DM8" s="16" t="s">
         <v>29</v>
       </c>
-      <c r="DM8" s="16" t="s">
+      <c r="DN8" s="16" t="s">
         <v>30</v>
       </c>
-      <c r="DN8" s="16" t="s">
-        <v>31</v>
-      </c>
       <c r="DP8" s="16" t="s">
+        <v>25</v>
+      </c>
+      <c r="DQ8" s="16" t="s">
         <v>26</v>
       </c>
-      <c r="DQ8" s="16" t="s">
+      <c r="DR8" s="16" t="s">
         <v>27</v>
       </c>
-      <c r="DR8" s="16" t="s">
+      <c r="DS8" s="16" t="s">
         <v>28</v>
       </c>
-      <c r="DS8" s="16" t="s">
+      <c r="DT8" s="16" t="s">
         <v>29</v>
       </c>
-      <c r="DT8" s="16" t="s">
+      <c r="DU8" s="16" t="s">
         <v>30</v>
       </c>
-      <c r="DU8" s="16" t="s">
-        <v>31</v>
-      </c>
       <c r="DW8" s="16" t="s">
+        <v>25</v>
+      </c>
+      <c r="DX8" s="16" t="s">
         <v>26</v>
       </c>
-      <c r="DX8" s="16" t="s">
+      <c r="DY8" s="16" t="s">
         <v>27</v>
       </c>
-      <c r="DY8" s="16" t="s">
+      <c r="DZ8" s="16" t="s">
         <v>28</v>
       </c>
-      <c r="DZ8" s="16" t="s">
+      <c r="EA8" s="16" t="s">
         <v>29</v>
       </c>
-      <c r="EA8" s="16" t="s">
+      <c r="EB8" s="16" t="s">
         <v>30</v>
       </c>
-      <c r="EB8" s="16" t="s">
-        <v>31</v>
-      </c>
       <c r="ED8" s="16" t="s">
+        <v>25</v>
+      </c>
+      <c r="EE8" s="16" t="s">
         <v>26</v>
       </c>
-      <c r="EE8" s="16" t="s">
+      <c r="EF8" s="16" t="s">
         <v>27</v>
       </c>
-      <c r="EF8" s="16" t="s">
+      <c r="EG8" s="16" t="s">
         <v>28</v>
       </c>
-      <c r="EG8" s="16" t="s">
+      <c r="EH8" s="16" t="s">
         <v>29</v>
       </c>
-      <c r="EH8" s="16" t="s">
+      <c r="EI8" s="16" t="s">
         <v>30</v>
       </c>
-      <c r="EI8" s="16" t="s">
-        <v>31</v>
-      </c>
       <c r="EK8" s="16" t="s">
+        <v>25</v>
+      </c>
+      <c r="EL8" s="16" t="s">
         <v>26</v>
       </c>
-      <c r="EL8" s="16" t="s">
+      <c r="EM8" s="16" t="s">
         <v>27</v>
       </c>
-      <c r="EM8" s="16" t="s">
+      <c r="EN8" s="16" t="s">
         <v>28</v>
       </c>
-      <c r="EN8" s="16" t="s">
+      <c r="EO8" s="16" t="s">
         <v>29</v>
       </c>
-      <c r="EO8" s="16" t="s">
+      <c r="EP8" s="16" t="s">
         <v>30</v>
       </c>
-      <c r="EP8" s="16" t="s">
-        <v>31</v>
-      </c>
       <c r="ER8" s="16" t="s">
+        <v>25</v>
+      </c>
+      <c r="ES8" s="16" t="s">
         <v>26</v>
       </c>
-      <c r="ES8" s="16" t="s">
+      <c r="ET8" s="16" t="s">
         <v>27</v>
       </c>
-      <c r="ET8" s="16" t="s">
+      <c r="EU8" s="16" t="s">
         <v>28</v>
       </c>
-      <c r="EU8" s="16" t="s">
+      <c r="EV8" s="16" t="s">
         <v>29</v>
       </c>
-      <c r="EV8" s="16" t="s">
+      <c r="EW8" s="16" t="s">
         <v>30</v>
       </c>
-      <c r="EW8" s="16" t="s">
-        <v>31</v>
-      </c>
       <c r="EY8" s="16" t="s">
+        <v>25</v>
+      </c>
+      <c r="EZ8" s="16" t="s">
         <v>26</v>
       </c>
-      <c r="EZ8" s="16" t="s">
+      <c r="FA8" s="16" t="s">
         <v>27</v>
       </c>
-      <c r="FA8" s="16" t="s">
+      <c r="FB8" s="16" t="s">
         <v>28</v>
       </c>
-      <c r="FB8" s="16" t="s">
+      <c r="FC8" s="16" t="s">
         <v>29</v>
       </c>
-      <c r="FC8" s="16" t="s">
+      <c r="FD8" s="16" t="s">
         <v>30</v>
-      </c>
-      <c r="FD8" s="16" t="s">
-        <v>31</v>
       </c>
     </row>
     <row r="9" spans="1:160" ht="29.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="16" t="s">
+        <v>226</v>
+      </c>
+      <c r="B9" s="16" t="s">
+        <v>227</v>
+      </c>
+      <c r="C9" s="16" t="s">
+        <v>228</v>
+      </c>
+      <c r="D9" s="16" t="s">
         <v>229</v>
-      </c>
-      <c r="B9" s="16" t="s">
-        <v>230</v>
-      </c>
-      <c r="C9" s="16" t="s">
-        <v>231</v>
-      </c>
-      <c r="D9" s="16" t="s">
-        <v>232</v>
       </c>
       <c r="E9" s="16"/>
       <c r="F9" s="16"/>
       <c r="H9" s="16" t="s">
+        <v>226</v>
+      </c>
+      <c r="I9" s="16" t="s">
+        <v>227</v>
+      </c>
+      <c r="J9" s="16" t="s">
+        <v>228</v>
+      </c>
+      <c r="K9" s="16" t="s">
         <v>229</v>
-      </c>
-      <c r="I9" s="16" t="s">
-        <v>230</v>
-      </c>
-      <c r="J9" s="16" t="s">
-        <v>231</v>
-      </c>
-      <c r="K9" s="16" t="s">
-        <v>232</v>
       </c>
       <c r="L9" s="16"/>
       <c r="M9" s="16"/>
       <c r="O9" s="16" t="s">
+        <v>226</v>
+      </c>
+      <c r="P9" s="16" t="s">
+        <v>227</v>
+      </c>
+      <c r="Q9" s="16" t="s">
+        <v>228</v>
+      </c>
+      <c r="R9" s="16" t="s">
         <v>229</v>
-      </c>
-      <c r="P9" s="16" t="s">
-        <v>230</v>
-      </c>
-      <c r="Q9" s="16" t="s">
-        <v>231</v>
-      </c>
-      <c r="R9" s="16" t="s">
-        <v>232</v>
       </c>
       <c r="S9" s="16"/>
       <c r="T9" s="16"/>
       <c r="V9" s="16" t="s">
+        <v>226</v>
+      </c>
+      <c r="W9" s="16" t="s">
+        <v>227</v>
+      </c>
+      <c r="X9" s="16" t="s">
+        <v>228</v>
+      </c>
+      <c r="Y9" s="16" t="s">
         <v>229</v>
-      </c>
-      <c r="W9" s="16" t="s">
-        <v>230</v>
-      </c>
-      <c r="X9" s="16" t="s">
-        <v>231</v>
-      </c>
-      <c r="Y9" s="16" t="s">
-        <v>232</v>
       </c>
       <c r="Z9" s="16"/>
       <c r="AA9" s="16"/>
       <c r="AC9" s="16" t="s">
+        <v>226</v>
+      </c>
+      <c r="AD9" s="16" t="s">
+        <v>227</v>
+      </c>
+      <c r="AE9" s="16" t="s">
+        <v>228</v>
+      </c>
+      <c r="AF9" s="16" t="s">
         <v>229</v>
-      </c>
-      <c r="AD9" s="16" t="s">
-        <v>230</v>
-      </c>
-      <c r="AE9" s="16" t="s">
-        <v>231</v>
-      </c>
-      <c r="AF9" s="16" t="s">
-        <v>232</v>
       </c>
       <c r="AG9" s="16"/>
       <c r="AH9" s="16"/>
       <c r="AJ9" s="16" t="s">
+        <v>226</v>
+      </c>
+      <c r="AK9" s="16" t="s">
+        <v>227</v>
+      </c>
+      <c r="AL9" s="16" t="s">
+        <v>228</v>
+      </c>
+      <c r="AM9" s="16" t="s">
         <v>229</v>
-      </c>
-      <c r="AK9" s="16" t="s">
-        <v>230</v>
-      </c>
-      <c r="AL9" s="16" t="s">
-        <v>231</v>
-      </c>
-      <c r="AM9" s="16" t="s">
-        <v>232</v>
       </c>
       <c r="AN9" s="16"/>
       <c r="AO9" s="16"/>
       <c r="AQ9" s="16" t="s">
+        <v>226</v>
+      </c>
+      <c r="AR9" s="16" t="s">
+        <v>227</v>
+      </c>
+      <c r="AS9" s="16" t="s">
+        <v>228</v>
+      </c>
+      <c r="AT9" s="16" t="s">
         <v>229</v>
-      </c>
-      <c r="AR9" s="16" t="s">
-        <v>230</v>
-      </c>
-      <c r="AS9" s="16" t="s">
-        <v>231</v>
-      </c>
-      <c r="AT9" s="16" t="s">
-        <v>232</v>
       </c>
       <c r="AU9" s="16"/>
       <c r="AV9" s="16"/>
       <c r="AX9" s="16" t="s">
+        <v>226</v>
+      </c>
+      <c r="AY9" s="16" t="s">
+        <v>227</v>
+      </c>
+      <c r="AZ9" s="16" t="s">
+        <v>228</v>
+      </c>
+      <c r="BA9" s="16" t="s">
         <v>229</v>
-      </c>
-      <c r="AY9" s="16" t="s">
-        <v>230</v>
-      </c>
-      <c r="AZ9" s="16" t="s">
-        <v>231</v>
-      </c>
-      <c r="BA9" s="16" t="s">
-        <v>232</v>
       </c>
       <c r="BB9" s="16"/>
       <c r="BC9" s="16"/>
       <c r="BE9" s="16" t="s">
+        <v>226</v>
+      </c>
+      <c r="BF9" s="16" t="s">
+        <v>227</v>
+      </c>
+      <c r="BG9" s="16" t="s">
+        <v>228</v>
+      </c>
+      <c r="BH9" s="16" t="s">
         <v>229</v>
-      </c>
-      <c r="BF9" s="16" t="s">
-        <v>230</v>
-      </c>
-      <c r="BG9" s="16" t="s">
-        <v>231</v>
-      </c>
-      <c r="BH9" s="16" t="s">
-        <v>232</v>
       </c>
       <c r="BI9" s="16"/>
       <c r="BJ9" s="16"/>
       <c r="BL9" s="16" t="s">
+        <v>226</v>
+      </c>
+      <c r="BM9" s="16" t="s">
+        <v>227</v>
+      </c>
+      <c r="BN9" s="16" t="s">
+        <v>228</v>
+      </c>
+      <c r="BO9" s="16" t="s">
         <v>229</v>
-      </c>
-      <c r="BM9" s="16" t="s">
-        <v>230</v>
-      </c>
-      <c r="BN9" s="16" t="s">
-        <v>231</v>
-      </c>
-      <c r="BO9" s="16" t="s">
-        <v>232</v>
       </c>
       <c r="BP9" s="16"/>
       <c r="BQ9" s="16"/>
       <c r="BS9" s="16" t="s">
+        <v>226</v>
+      </c>
+      <c r="BT9" s="16" t="s">
+        <v>227</v>
+      </c>
+      <c r="BU9" s="16" t="s">
+        <v>228</v>
+      </c>
+      <c r="BV9" s="16" t="s">
         <v>229</v>
-      </c>
-      <c r="BT9" s="16" t="s">
-        <v>230</v>
-      </c>
-      <c r="BU9" s="16" t="s">
-        <v>231</v>
-      </c>
-      <c r="BV9" s="16" t="s">
-        <v>232</v>
       </c>
       <c r="BW9" s="16"/>
       <c r="BX9" s="16"/>
       <c r="BZ9" s="16" t="s">
+        <v>226</v>
+      </c>
+      <c r="CA9" s="16" t="s">
+        <v>227</v>
+      </c>
+      <c r="CB9" s="16" t="s">
+        <v>228</v>
+      </c>
+      <c r="CC9" s="16" t="s">
         <v>229</v>
-      </c>
-      <c r="CA9" s="16" t="s">
-        <v>230</v>
-      </c>
-      <c r="CB9" s="16" t="s">
-        <v>231</v>
-      </c>
-      <c r="CC9" s="16" t="s">
-        <v>232</v>
       </c>
       <c r="CD9" s="16"/>
       <c r="CE9" s="16"/>
       <c r="CG9" s="16" t="s">
+        <v>226</v>
+      </c>
+      <c r="CH9" s="16" t="s">
+        <v>227</v>
+      </c>
+      <c r="CI9" s="16" t="s">
+        <v>228</v>
+      </c>
+      <c r="CJ9" s="16" t="s">
         <v>229</v>
-      </c>
-      <c r="CH9" s="16" t="s">
-        <v>230</v>
-      </c>
-      <c r="CI9" s="16" t="s">
-        <v>231</v>
-      </c>
-      <c r="CJ9" s="16" t="s">
-        <v>232</v>
       </c>
       <c r="CK9" s="16"/>
       <c r="CL9" s="16"/>
       <c r="CN9" s="16" t="s">
+        <v>226</v>
+      </c>
+      <c r="CO9" s="16" t="s">
+        <v>227</v>
+      </c>
+      <c r="CP9" s="16" t="s">
+        <v>228</v>
+      </c>
+      <c r="CQ9" s="16" t="s">
         <v>229</v>
-      </c>
-      <c r="CO9" s="16" t="s">
-        <v>230</v>
-      </c>
-      <c r="CP9" s="16" t="s">
-        <v>231</v>
-      </c>
-      <c r="CQ9" s="16" t="s">
-        <v>232</v>
       </c>
       <c r="CR9" s="16"/>
       <c r="CS9" s="16"/>
       <c r="CU9" s="16" t="s">
+        <v>226</v>
+      </c>
+      <c r="CV9" s="16" t="s">
+        <v>227</v>
+      </c>
+      <c r="CW9" s="16" t="s">
+        <v>228</v>
+      </c>
+      <c r="CX9" s="16" t="s">
         <v>229</v>
-      </c>
-      <c r="CV9" s="16" t="s">
-        <v>230</v>
-      </c>
-      <c r="CW9" s="16" t="s">
-        <v>231</v>
-      </c>
-      <c r="CX9" s="16" t="s">
-        <v>232</v>
       </c>
       <c r="CY9" s="16"/>
       <c r="CZ9" s="16"/>
       <c r="DB9" s="16" t="s">
+        <v>226</v>
+      </c>
+      <c r="DC9" s="16" t="s">
+        <v>227</v>
+      </c>
+      <c r="DD9" s="16" t="s">
+        <v>228</v>
+      </c>
+      <c r="DE9" s="16" t="s">
         <v>229</v>
-      </c>
-      <c r="DC9" s="16" t="s">
-        <v>230</v>
-      </c>
-      <c r="DD9" s="16" t="s">
-        <v>231</v>
-      </c>
-      <c r="DE9" s="16" t="s">
-        <v>232</v>
       </c>
       <c r="DF9" s="16"/>
       <c r="DG9" s="16"/>
       <c r="DI9" s="16" t="s">
+        <v>226</v>
+      </c>
+      <c r="DJ9" s="16" t="s">
+        <v>227</v>
+      </c>
+      <c r="DK9" s="16" t="s">
+        <v>228</v>
+      </c>
+      <c r="DL9" s="16" t="s">
         <v>229</v>
-      </c>
-      <c r="DJ9" s="16" t="s">
-        <v>230</v>
-      </c>
-      <c r="DK9" s="16" t="s">
-        <v>231</v>
-      </c>
-      <c r="DL9" s="16" t="s">
-        <v>232</v>
       </c>
       <c r="DM9" s="16"/>
       <c r="DN9" s="16"/>
       <c r="DP9" s="16" t="s">
+        <v>226</v>
+      </c>
+      <c r="DQ9" s="16" t="s">
+        <v>227</v>
+      </c>
+      <c r="DR9" s="16" t="s">
+        <v>228</v>
+      </c>
+      <c r="DS9" s="16" t="s">
         <v>229</v>
-      </c>
-      <c r="DQ9" s="16" t="s">
-        <v>230</v>
-      </c>
-      <c r="DR9" s="16" t="s">
-        <v>231</v>
-      </c>
-      <c r="DS9" s="16" t="s">
-        <v>232</v>
       </c>
       <c r="DT9" s="16"/>
       <c r="DU9" s="16"/>
       <c r="DW9" s="16" t="s">
+        <v>226</v>
+      </c>
+      <c r="DX9" s="16" t="s">
+        <v>227</v>
+      </c>
+      <c r="DY9" s="16" t="s">
+        <v>228</v>
+      </c>
+      <c r="DZ9" s="16" t="s">
         <v>229</v>
-      </c>
-      <c r="DX9" s="16" t="s">
-        <v>230</v>
-      </c>
-      <c r="DY9" s="16" t="s">
-        <v>231</v>
-      </c>
-      <c r="DZ9" s="16" t="s">
-        <v>232</v>
       </c>
       <c r="EA9" s="16"/>
       <c r="EB9" s="16"/>
       <c r="ED9" s="16" t="s">
+        <v>226</v>
+      </c>
+      <c r="EE9" s="16" t="s">
+        <v>227</v>
+      </c>
+      <c r="EF9" s="16" t="s">
+        <v>228</v>
+      </c>
+      <c r="EG9" s="16" t="s">
         <v>229</v>
-      </c>
-      <c r="EE9" s="16" t="s">
-        <v>230</v>
-      </c>
-      <c r="EF9" s="16" t="s">
-        <v>231</v>
-      </c>
-      <c r="EG9" s="16" t="s">
-        <v>232</v>
       </c>
       <c r="EH9" s="16"/>
       <c r="EI9" s="16"/>
       <c r="EK9" s="16" t="s">
+        <v>226</v>
+      </c>
+      <c r="EL9" s="16" t="s">
+        <v>227</v>
+      </c>
+      <c r="EM9" s="16" t="s">
+        <v>228</v>
+      </c>
+      <c r="EN9" s="16" t="s">
         <v>229</v>
-      </c>
-      <c r="EL9" s="16" t="s">
-        <v>230</v>
-      </c>
-      <c r="EM9" s="16" t="s">
-        <v>231</v>
-      </c>
-      <c r="EN9" s="16" t="s">
-        <v>232</v>
       </c>
       <c r="EO9" s="16"/>
       <c r="EP9" s="16"/>
       <c r="ER9" s="16" t="s">
+        <v>226</v>
+      </c>
+      <c r="ES9" s="16" t="s">
+        <v>227</v>
+      </c>
+      <c r="ET9" s="16" t="s">
+        <v>228</v>
+      </c>
+      <c r="EU9" s="16" t="s">
         <v>229</v>
-      </c>
-      <c r="ES9" s="16" t="s">
-        <v>230</v>
-      </c>
-      <c r="ET9" s="16" t="s">
-        <v>231</v>
-      </c>
-      <c r="EU9" s="16" t="s">
-        <v>232</v>
       </c>
       <c r="EV9" s="16"/>
       <c r="EW9" s="16"/>
       <c r="EY9" s="16" t="s">
+        <v>226</v>
+      </c>
+      <c r="EZ9" s="16" t="s">
+        <v>227</v>
+      </c>
+      <c r="FA9" s="16" t="s">
+        <v>228</v>
+      </c>
+      <c r="FB9" s="16" t="s">
         <v>229</v>
-      </c>
-      <c r="EZ9" s="16" t="s">
-        <v>230</v>
-      </c>
-      <c r="FA9" s="16" t="s">
-        <v>231</v>
-      </c>
-      <c r="FB9" s="16" t="s">
-        <v>232</v>
       </c>
       <c r="FC9" s="16"/>
       <c r="FD9" s="16"/>
     </row>
     <row r="10" spans="1:160" ht="29.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="16" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="B10" s="16" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="C10" s="16"/>
       <c r="D10" s="16" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="E10" s="16"/>
       <c r="F10" s="16"/>
       <c r="H10" s="16" t="s">
+        <v>230</v>
+      </c>
+      <c r="I10" s="16" t="s">
         <v>233</v>
-      </c>
-      <c r="I10" s="16" t="s">
-        <v>236</v>
       </c>
       <c r="J10" s="16"/>
       <c r="K10" s="16" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="L10" s="16"/>
       <c r="M10" s="16"/>
       <c r="O10" s="16" t="s">
+        <v>230</v>
+      </c>
+      <c r="P10" s="16" t="s">
         <v>233</v>
-      </c>
-      <c r="P10" s="16" t="s">
-        <v>236</v>
       </c>
       <c r="Q10" s="16"/>
       <c r="R10" s="16" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="S10" s="16"/>
       <c r="T10" s="16"/>
       <c r="V10" s="16" t="s">
+        <v>230</v>
+      </c>
+      <c r="W10" s="16" t="s">
         <v>233</v>
-      </c>
-      <c r="W10" s="16" t="s">
-        <v>236</v>
       </c>
       <c r="X10" s="16"/>
       <c r="Y10" s="16" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="Z10" s="16"/>
       <c r="AA10" s="16"/>
       <c r="AC10" s="16" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="AD10" s="16" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="AE10" s="16"/>
       <c r="AF10" s="16" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="AG10" s="16"/>
       <c r="AH10" s="16"/>
       <c r="AJ10" s="16" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="AK10" s="16" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="AL10" s="16"/>
       <c r="AM10" s="16" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="AN10" s="16"/>
       <c r="AO10" s="16"/>
       <c r="AQ10" s="16" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="AR10" s="16" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="AS10" s="16"/>
       <c r="AT10" s="16" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="AU10" s="16"/>
       <c r="AV10" s="16"/>
       <c r="AX10" s="16" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="AY10" s="16" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="AZ10" s="16"/>
       <c r="BA10" s="16" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="BB10" s="16"/>
       <c r="BC10" s="16"/>
       <c r="BE10" s="16" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="BF10" s="16" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="BG10" s="16"/>
       <c r="BH10" s="16" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="BI10" s="16"/>
       <c r="BJ10" s="16"/>
       <c r="BL10" s="16" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="BM10" s="16" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="BN10" s="16"/>
       <c r="BO10" s="16" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="BP10" s="16"/>
       <c r="BQ10" s="16"/>
       <c r="BS10" s="16" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="BT10" s="16" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="BU10" s="16"/>
       <c r="BV10" s="16" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="BW10" s="16"/>
       <c r="BX10" s="16"/>
       <c r="BZ10" s="16" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="CA10" s="16" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="CB10" s="16"/>
       <c r="CC10" s="16" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="CD10" s="16"/>
       <c r="CE10" s="16"/>
       <c r="CG10" s="16" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="CH10" s="16" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="CI10" s="16"/>
       <c r="CJ10" s="16" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="CK10" s="16"/>
       <c r="CL10" s="16"/>
       <c r="CN10" s="16" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="CO10" s="16" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="CP10" s="16"/>
       <c r="CQ10" s="16" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="CR10" s="16"/>
       <c r="CS10" s="16"/>
       <c r="CU10" s="16" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="CV10" s="16" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="CW10" s="16"/>
       <c r="CX10" s="16" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="CY10" s="16"/>
       <c r="CZ10" s="16"/>
       <c r="DB10" s="16" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="DC10" s="16" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="DD10" s="16"/>
       <c r="DE10" s="16" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="DF10" s="16"/>
       <c r="DG10" s="16"/>
       <c r="DI10" s="16" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="DJ10" s="16" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="DK10" s="16"/>
       <c r="DL10" s="16" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="DM10" s="16"/>
       <c r="DN10" s="16"/>
       <c r="DP10" s="16" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="DQ10" s="16" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="DR10" s="16"/>
       <c r="DS10" s="16" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="DT10" s="16"/>
       <c r="DU10" s="16"/>
       <c r="DW10" s="16" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="DX10" s="16" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="DY10" s="16"/>
       <c r="DZ10" s="16" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="EA10" s="16"/>
       <c r="EB10" s="16"/>
       <c r="ED10" s="16" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="EE10" s="16" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="EF10" s="16"/>
       <c r="EG10" s="16" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="EH10" s="16"/>
       <c r="EI10" s="16"/>
       <c r="EK10" s="16" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="EL10" s="16" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="EM10" s="16"/>
       <c r="EN10" s="16" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="EO10" s="16"/>
       <c r="EP10" s="16"/>
       <c r="ER10" s="16" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="ES10" s="16" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="ET10" s="16"/>
       <c r="EU10" s="16" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="EV10" s="16"/>
       <c r="EW10" s="16"/>
       <c r="EY10" s="16" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="EZ10" s="16" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="FA10" s="16"/>
       <c r="FB10" s="16" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="FC10" s="16"/>
       <c r="FD10" s="16"/>
     </row>
     <row r="11" spans="1:160" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="16" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="B11" s="16" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="C11" s="16"/>
       <c r="D11" s="16" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="E11" s="16"/>
       <c r="F11" s="16"/>
       <c r="H11" s="16" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="I11" s="16" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="J11" s="16"/>
       <c r="K11" s="16" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="L11" s="16"/>
       <c r="M11" s="16"/>
       <c r="O11" s="16" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="P11" s="16" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="Q11" s="16"/>
       <c r="R11" s="16" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="S11" s="16"/>
       <c r="T11" s="16"/>
       <c r="V11" s="16" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="W11" s="16" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="X11" s="16"/>
       <c r="Y11" s="16" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="Z11" s="16"/>
       <c r="AA11" s="16"/>
       <c r="AC11" s="16" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="AD11" s="16" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="AE11" s="16"/>
       <c r="AF11" s="16" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="AG11" s="16"/>
       <c r="AH11" s="16"/>
       <c r="AJ11" s="16" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="AK11" s="16" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="AL11" s="16"/>
       <c r="AM11" s="16" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="AN11" s="16"/>
       <c r="AO11" s="16"/>
       <c r="AQ11" s="16" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="AR11" s="16" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="AS11" s="16"/>
       <c r="AT11" s="16" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="AU11" s="16"/>
       <c r="AV11" s="16"/>
       <c r="AX11" s="16" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="AY11" s="16" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="AZ11" s="16"/>
       <c r="BA11" s="16" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="BB11" s="16"/>
       <c r="BC11" s="16"/>
       <c r="BE11" s="16" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="BF11" s="16" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="BG11" s="16"/>
       <c r="BH11" s="16" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="BI11" s="16"/>
       <c r="BJ11" s="16"/>
       <c r="BL11" s="16" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="BM11" s="16" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="BN11" s="16"/>
       <c r="BO11" s="16" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="BP11" s="16"/>
       <c r="BQ11" s="16"/>
       <c r="BS11" s="16" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="BT11" s="16" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="BU11" s="16"/>
       <c r="BV11" s="16" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="BW11" s="16"/>
       <c r="BX11" s="16"/>
       <c r="BZ11" s="16" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="CA11" s="16" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="CB11" s="16"/>
       <c r="CC11" s="16" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="CD11" s="16"/>
       <c r="CE11" s="16"/>
       <c r="CG11" s="16" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="CH11" s="16" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="CI11" s="16"/>
       <c r="CJ11" s="16" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="CK11" s="16"/>
       <c r="CL11" s="16"/>
       <c r="CN11" s="16" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="CO11" s="16" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="CP11" s="16"/>
       <c r="CQ11" s="16" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="CR11" s="16"/>
       <c r="CS11" s="16"/>
       <c r="CU11" s="16" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="CV11" s="16" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="CW11" s="16"/>
       <c r="CX11" s="16" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="CY11" s="16"/>
       <c r="CZ11" s="16"/>
       <c r="DB11" s="16" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="DC11" s="16" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="DD11" s="16"/>
       <c r="DE11" s="16" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="DF11" s="16"/>
       <c r="DG11" s="16"/>
       <c r="DI11" s="16" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="DJ11" s="16" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="DK11" s="16"/>
       <c r="DL11" s="16" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="DM11" s="16"/>
       <c r="DN11" s="16"/>
       <c r="DP11" s="16" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="DQ11" s="16" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="DR11" s="16"/>
       <c r="DS11" s="16" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="DT11" s="16"/>
       <c r="DU11" s="16"/>
       <c r="DW11" s="16" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="DX11" s="16" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="DY11" s="16"/>
       <c r="DZ11" s="16" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="EA11" s="16"/>
       <c r="EB11" s="16"/>
       <c r="ED11" s="16" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="EE11" s="16" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="EF11" s="16"/>
       <c r="EG11" s="16" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="EH11" s="16"/>
       <c r="EI11" s="16"/>
       <c r="EK11" s="16" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="EL11" s="16" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="EM11" s="16"/>
       <c r="EN11" s="16" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="EO11" s="16"/>
       <c r="EP11" s="16"/>
       <c r="ER11" s="16" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="ES11" s="16" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="ET11" s="16"/>
       <c r="EU11" s="16" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="EV11" s="16"/>
       <c r="EW11" s="16"/>
       <c r="EY11" s="16" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="EZ11" s="16" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="FA11" s="16"/>
       <c r="FB11" s="16" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="FC11" s="16"/>
       <c r="FD11" s="16"/>
@@ -9477,7 +9427,7 @@
   <sheetData>
     <row r="1" spans="1:160" x14ac:dyDescent="0.25">
       <c r="A1" s="30" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="B1" s="18"/>
       <c r="C1" s="18"/>
@@ -9485,7 +9435,7 @@
       <c r="E1" s="18"/>
       <c r="F1" s="18"/>
       <c r="H1" s="30" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="I1" s="18"/>
       <c r="J1" s="18"/>
@@ -9493,7 +9443,7 @@
       <c r="L1" s="18"/>
       <c r="M1" s="18"/>
       <c r="O1" s="30" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="P1" s="18"/>
       <c r="Q1" s="18"/>
@@ -9501,7 +9451,7 @@
       <c r="S1" s="18"/>
       <c r="T1" s="18"/>
       <c r="V1" s="30" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="W1" s="18"/>
       <c r="X1" s="18"/>
@@ -9509,7 +9459,7 @@
       <c r="Z1" s="18"/>
       <c r="AA1" s="18"/>
       <c r="AC1" s="30" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="AD1" s="18"/>
       <c r="AE1" s="18"/>
@@ -9517,7 +9467,7 @@
       <c r="AG1" s="18"/>
       <c r="AH1" s="18"/>
       <c r="AJ1" s="30" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="AK1" s="18"/>
       <c r="AL1" s="18"/>
@@ -9525,7 +9475,7 @@
       <c r="AN1" s="18"/>
       <c r="AO1" s="18"/>
       <c r="AQ1" s="30" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="AR1" s="18"/>
       <c r="AS1" s="18"/>
@@ -9533,7 +9483,7 @@
       <c r="AU1" s="18"/>
       <c r="AV1" s="18"/>
       <c r="AX1" s="30" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="AY1" s="18"/>
       <c r="AZ1" s="18"/>
@@ -9541,7 +9491,7 @@
       <c r="BB1" s="18"/>
       <c r="BC1" s="18"/>
       <c r="BE1" s="30" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="BF1" s="18"/>
       <c r="BG1" s="18"/>
@@ -9549,7 +9499,7 @@
       <c r="BI1" s="18"/>
       <c r="BJ1" s="18"/>
       <c r="BL1" s="30" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="BM1" s="18"/>
       <c r="BN1" s="18"/>
@@ -9557,7 +9507,7 @@
       <c r="BP1" s="18"/>
       <c r="BQ1" s="18"/>
       <c r="BS1" s="30" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="BT1" s="18"/>
       <c r="BU1" s="18"/>
@@ -9565,7 +9515,7 @@
       <c r="BW1" s="18"/>
       <c r="BX1" s="18"/>
       <c r="BZ1" s="30" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="CA1" s="18"/>
       <c r="CB1" s="18"/>
@@ -9573,7 +9523,7 @@
       <c r="CD1" s="18"/>
       <c r="CE1" s="18"/>
       <c r="CG1" s="30" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="CH1" s="18"/>
       <c r="CI1" s="18"/>
@@ -9581,7 +9531,7 @@
       <c r="CK1" s="18"/>
       <c r="CL1" s="18"/>
       <c r="CN1" s="30" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="CO1" s="18"/>
       <c r="CP1" s="18"/>
@@ -9589,7 +9539,7 @@
       <c r="CR1" s="18"/>
       <c r="CS1" s="18"/>
       <c r="CU1" s="30" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="CV1" s="18"/>
       <c r="CW1" s="18"/>
@@ -9597,7 +9547,7 @@
       <c r="CY1" s="18"/>
       <c r="CZ1" s="18"/>
       <c r="DB1" s="30" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="DC1" s="18"/>
       <c r="DD1" s="18"/>
@@ -9605,7 +9555,7 @@
       <c r="DF1" s="18"/>
       <c r="DG1" s="18"/>
       <c r="DI1" s="30" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="DJ1" s="18"/>
       <c r="DK1" s="18"/>
@@ -9613,7 +9563,7 @@
       <c r="DM1" s="18"/>
       <c r="DN1" s="18"/>
       <c r="DP1" s="30" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="DQ1" s="18"/>
       <c r="DR1" s="18"/>
@@ -9621,7 +9571,7 @@
       <c r="DT1" s="18"/>
       <c r="DU1" s="18"/>
       <c r="DW1" s="30" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="DX1" s="18"/>
       <c r="DY1" s="18"/>
@@ -9629,7 +9579,7 @@
       <c r="EA1" s="18"/>
       <c r="EB1" s="18"/>
       <c r="ED1" s="30" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="EE1" s="18"/>
       <c r="EF1" s="18"/>
@@ -9637,7 +9587,7 @@
       <c r="EH1" s="18"/>
       <c r="EI1" s="18"/>
       <c r="EK1" s="30" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="EL1" s="18"/>
       <c r="EM1" s="18"/>
@@ -9645,7 +9595,7 @@
       <c r="EO1" s="18"/>
       <c r="EP1" s="18"/>
       <c r="ER1" s="30" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="ES1" s="18"/>
       <c r="ET1" s="18"/>
@@ -9653,7 +9603,7 @@
       <c r="EV1" s="18"/>
       <c r="EW1" s="18"/>
       <c r="EY1" s="30" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="EZ1" s="18"/>
       <c r="FA1" s="18"/>
@@ -9663,161 +9613,161 @@
     </row>
     <row r="2" spans="1:160" x14ac:dyDescent="0.25">
       <c r="A2" s="16" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B2" s="16">
         <f>IFERROR(_xlfn.XLOOKUP(A1, TestMaster[Test Name], TestMaster[Test ID], "ID not found"), "")</f>
         <v>42</v>
       </c>
       <c r="H2" s="16" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I2" s="16">
         <f>IFERROR(_xlfn.SINGLE(_xlfn.XLOOKUP(H1, TestMaster[Test Name], TestMaster[Test ID], "ID not found")), "")</f>
         <v>51</v>
       </c>
       <c r="O2" s="16" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="P2" s="16">
         <f>IFERROR(_xlfn.SINGLE(_xlfn.XLOOKUP(O1, TestMaster[Test Name], TestMaster[Test ID], "ID not found")), "")</f>
         <v>50</v>
       </c>
       <c r="V2" s="16" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="W2" s="16">
         <f>IFERROR(_xlfn.SINGLE(_xlfn.XLOOKUP(V1, TestMaster[Test Name], TestMaster[Test ID], "ID not found")), "")</f>
         <v>53</v>
       </c>
       <c r="AC2" s="16" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AD2" s="16">
         <f>IFERROR(_xlfn.SINGLE(_xlfn.XLOOKUP(AC1, TestMaster[Test Name], TestMaster[Test ID], "ID not found")), "")</f>
         <v>37</v>
       </c>
       <c r="AJ2" s="16" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AK2" s="16">
         <f>IFERROR(_xlfn.SINGLE(_xlfn.XLOOKUP(AJ1, TestMaster[Test Name], TestMaster[Test ID], "ID not found")), "")</f>
         <v>40</v>
       </c>
       <c r="AQ2" s="16" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AR2" s="16">
         <f>IFERROR(_xlfn.SINGLE(_xlfn.XLOOKUP(AQ1, TestMaster[Test Name], TestMaster[Test ID], "ID not found")), "")</f>
         <v>38</v>
       </c>
       <c r="AX2" s="16" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AY2" s="16">
         <f>IFERROR(_xlfn.SINGLE(_xlfn.XLOOKUP(AX1, TestMaster[Test Name], TestMaster[Test ID], "ID not found")), "")</f>
         <v>41</v>
       </c>
       <c r="BE2" s="16" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="BF2" s="16">
         <f>IFERROR(_xlfn.SINGLE(_xlfn.XLOOKUP(BE1, TestMaster[Test Name], TestMaster[Test ID], "ID not found")), "")</f>
         <v>39</v>
       </c>
       <c r="BL2" s="16" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="BM2" s="16">
         <f>IFERROR(_xlfn.SINGLE(_xlfn.XLOOKUP(BL1, TestMaster[Test Name], TestMaster[Test ID], "ID not found")), "")</f>
         <v>45</v>
       </c>
       <c r="BS2" s="16" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="BT2" s="16">
         <f>IFERROR(_xlfn.SINGLE(_xlfn.XLOOKUP(BS1, TestMaster[Test Name], TestMaster[Test ID], "ID not found")), "")</f>
         <v>47</v>
       </c>
       <c r="BZ2" s="16" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="CA2" s="16">
         <f>IFERROR(_xlfn.SINGLE(_xlfn.XLOOKUP(BZ1, TestMaster[Test Name], TestMaster[Test ID], "ID not found")), "")</f>
         <v>44</v>
       </c>
       <c r="CG2" s="16" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="CH2" s="16">
         <f>IFERROR(_xlfn.SINGLE(_xlfn.XLOOKUP(CG1, TestMaster[Test Name], TestMaster[Test ID], "ID not found")), "")</f>
         <v>46</v>
       </c>
       <c r="CN2" s="16" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="CO2" s="16">
         <f>IFERROR(_xlfn.SINGLE(_xlfn.XLOOKUP(CN1, TestMaster[Test Name], TestMaster[Test ID], "ID not found")), "")</f>
         <v>48</v>
       </c>
       <c r="CU2" s="16" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="CV2" s="16">
         <f>IFERROR(_xlfn.SINGLE(_xlfn.XLOOKUP(CU1, TestMaster[Test Name], TestMaster[Test ID], "ID not found")), "")</f>
         <v>49</v>
       </c>
       <c r="DB2" s="16" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="DC2" s="16">
         <f>IFERROR(_xlfn.SINGLE(_xlfn.XLOOKUP(DB1, TestMaster[Test Name], TestMaster[Test ID], "ID not found")), "")</f>
         <v>58</v>
       </c>
       <c r="DI2" s="16" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="DJ2" s="16">
         <f>IFERROR(_xlfn.SINGLE(_xlfn.XLOOKUP(DI1, TestMaster[Test Name], TestMaster[Test ID], "ID not found")), "")</f>
         <v>54</v>
       </c>
       <c r="DP2" s="16" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="DQ2" s="16">
         <f>IFERROR(_xlfn.SINGLE(_xlfn.XLOOKUP(DP1, TestMaster[Test Name], TestMaster[Test ID], "ID not found")), "")</f>
         <v>57</v>
       </c>
       <c r="DW2" s="16" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="DX2" s="16">
         <f>IFERROR(_xlfn.SINGLE(_xlfn.XLOOKUP(DW1, TestMaster[Test Name], TestMaster[Test ID], "ID not found")), "")</f>
         <v>56</v>
       </c>
       <c r="ED2" s="16" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="EE2" s="16">
         <f>IFERROR(_xlfn.SINGLE(_xlfn.XLOOKUP(ED1, TestMaster[Test Name], TestMaster[Test ID], "ID not found")), "")</f>
         <v>55</v>
       </c>
       <c r="EK2" s="16" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="EL2" s="16">
         <f>IFERROR(_xlfn.SINGLE(_xlfn.XLOOKUP(EK1, TestMaster[Test Name], TestMaster[Test ID], "ID not found")), "")</f>
         <v>52</v>
       </c>
       <c r="ER2" s="16" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="ES2" s="16">
         <f>IFERROR(_xlfn.SINGLE(_xlfn.XLOOKUP(ER1, TestMaster[Test Name], TestMaster[Test ID], "ID not found")), "")</f>
         <v>59</v>
       </c>
       <c r="EY2" s="16" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="EZ2" s="16">
         <f>IFERROR(_xlfn.SINGLE(_xlfn.XLOOKUP(EY1, TestMaster[Test Name], TestMaster[Test ID], "ID not found")), "")</f>
@@ -9826,255 +9776,255 @@
     </row>
     <row r="3" spans="1:160" x14ac:dyDescent="0.25">
       <c r="A3" s="16" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B3" s="16"/>
       <c r="H3" s="16" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I3" s="16"/>
       <c r="O3" s="16" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="P3" s="16"/>
       <c r="V3" s="16" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="W3" s="16"/>
       <c r="AC3" s="16" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AD3" s="16"/>
       <c r="AJ3" s="16" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AK3" s="16"/>
       <c r="AQ3" s="16" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AR3" s="16"/>
       <c r="AX3" s="16" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AY3" s="16"/>
       <c r="BE3" s="16" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BF3" s="16"/>
       <c r="BL3" s="16" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BM3" s="16"/>
       <c r="BS3" s="16" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BT3" s="16"/>
       <c r="BZ3" s="16" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="CA3" s="16"/>
       <c r="CG3" s="16" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="CH3" s="16"/>
       <c r="CN3" s="16" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="CO3" s="16"/>
       <c r="CU3" s="16" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="CV3" s="16"/>
       <c r="DB3" s="16" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="DC3" s="16"/>
       <c r="DI3" s="16" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="DJ3" s="16"/>
       <c r="DP3" s="16" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="DQ3" s="16"/>
       <c r="DW3" s="16" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="DX3" s="16"/>
       <c r="ED3" s="16" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="EE3" s="16"/>
       <c r="EK3" s="16" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="EL3" s="16"/>
       <c r="ER3" s="16" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="ES3" s="16"/>
       <c r="EY3" s="16" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="EZ3" s="16"/>
     </row>
     <row r="4" spans="1:160" x14ac:dyDescent="0.25">
       <c r="A4" s="16" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B4" s="16">
         <f>IFERROR(_xlfn.SINGLE(_xlfn.XLOOKUP(A1, TestMaster[Test Name], TestMaster[Test Priority], "Priority not found")), "")</f>
         <v>0</v>
       </c>
       <c r="H4" s="16" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I4" s="16">
         <f>IFERROR(_xlfn.SINGLE(_xlfn.XLOOKUP(H1, TestMaster[Test Name], TestMaster[Test Priority], "Priority not found")), "")</f>
         <v>0</v>
       </c>
       <c r="O4" s="16" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="P4" s="16">
         <f>IFERROR(_xlfn.SINGLE(_xlfn.XLOOKUP(O1, TestMaster[Test Name], TestMaster[Test Priority], "Priority not found")), "")</f>
         <v>0</v>
       </c>
       <c r="V4" s="16" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="W4" s="16">
         <f>IFERROR(_xlfn.SINGLE(_xlfn.XLOOKUP(V1, TestMaster[Test Name], TestMaster[Test Priority], "Priority not found")), "")</f>
         <v>0</v>
       </c>
       <c r="AC4" s="16" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AD4" s="16">
         <f>IFERROR(_xlfn.SINGLE(_xlfn.XLOOKUP(AC1, TestMaster[Test Name], TestMaster[Test Priority], "Priority not found")), "")</f>
         <v>0</v>
       </c>
       <c r="AJ4" s="16" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AK4" s="16">
         <f>IFERROR(_xlfn.SINGLE(_xlfn.XLOOKUP(AJ1, TestMaster[Test Name], TestMaster[Test Priority], "Priority not found")), "")</f>
         <v>0</v>
       </c>
       <c r="AQ4" s="16" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AR4" s="16">
         <f>IFERROR(_xlfn.SINGLE(_xlfn.XLOOKUP(AQ1, TestMaster[Test Name], TestMaster[Test Priority], "Priority not found")), "")</f>
         <v>0</v>
       </c>
       <c r="AX4" s="16" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AY4" s="16">
         <f>IFERROR(_xlfn.SINGLE(_xlfn.XLOOKUP(AX1, TestMaster[Test Name], TestMaster[Test Priority], "Priority not found")), "")</f>
         <v>0</v>
       </c>
       <c r="BE4" s="16" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BF4" s="16">
         <f>IFERROR(_xlfn.SINGLE(_xlfn.XLOOKUP(BE1, TestMaster[Test Name], TestMaster[Test Priority], "Priority not found")), "")</f>
         <v>0</v>
       </c>
       <c r="BL4" s="16" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BM4" s="16">
         <f>IFERROR(_xlfn.SINGLE(_xlfn.XLOOKUP(BL1, TestMaster[Test Name], TestMaster[Test Priority], "Priority not found")), "")</f>
         <v>0</v>
       </c>
       <c r="BS4" s="16" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BT4" s="16">
         <f>IFERROR(_xlfn.SINGLE(_xlfn.XLOOKUP(BS1, TestMaster[Test Name], TestMaster[Test Priority], "Priority not found")), "")</f>
         <v>0</v>
       </c>
       <c r="BZ4" s="16" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="CA4" s="16">
         <f>IFERROR(_xlfn.SINGLE(_xlfn.XLOOKUP(BZ1, TestMaster[Test Name], TestMaster[Test Priority], "Priority not found")), "")</f>
         <v>0</v>
       </c>
       <c r="CG4" s="16" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="CH4" s="16">
         <f>IFERROR(_xlfn.SINGLE(_xlfn.XLOOKUP(CG1, TestMaster[Test Name], TestMaster[Test Priority], "Priority not found")), "")</f>
         <v>0</v>
       </c>
       <c r="CN4" s="16" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="CO4" s="16">
         <f>IFERROR(_xlfn.SINGLE(_xlfn.XLOOKUP(CN1, TestMaster[Test Name], TestMaster[Test Priority], "Priority not found")), "")</f>
         <v>0</v>
       </c>
       <c r="CU4" s="16" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="CV4" s="16">
         <f>IFERROR(_xlfn.SINGLE(_xlfn.XLOOKUP(CU1, TestMaster[Test Name], TestMaster[Test Priority], "Priority not found")), "")</f>
         <v>0</v>
       </c>
       <c r="DB4" s="16" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="DC4" s="16">
         <f>IFERROR(_xlfn.SINGLE(_xlfn.XLOOKUP(DB1, TestMaster[Test Name], TestMaster[Test Priority], "Priority not found")), "")</f>
         <v>0</v>
       </c>
       <c r="DI4" s="16" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="DJ4" s="16">
         <f>IFERROR(_xlfn.SINGLE(_xlfn.XLOOKUP(DI1, TestMaster[Test Name], TestMaster[Test Priority], "Priority not found")), "")</f>
         <v>0</v>
       </c>
       <c r="DP4" s="16" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="DQ4" s="16">
         <f>IFERROR(_xlfn.SINGLE(_xlfn.XLOOKUP(DP1, TestMaster[Test Name], TestMaster[Test Priority], "Priority not found")), "")</f>
         <v>0</v>
       </c>
       <c r="DW4" s="16" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="DX4" s="16">
         <f>IFERROR(_xlfn.SINGLE(_xlfn.XLOOKUP(DW1, TestMaster[Test Name], TestMaster[Test Priority], "Priority not found")), "")</f>
         <v>0</v>
       </c>
       <c r="ED4" s="16" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="EE4" s="16">
         <f>IFERROR(_xlfn.SINGLE(_xlfn.XLOOKUP(ED1, TestMaster[Test Name], TestMaster[Test Priority], "Priority not found")), "")</f>
         <v>0</v>
       </c>
       <c r="EK4" s="16" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="EL4" s="16">
         <f>IFERROR(_xlfn.SINGLE(_xlfn.XLOOKUP(EK1, TestMaster[Test Name], TestMaster[Test Priority], "Priority not found")), "")</f>
         <v>0</v>
       </c>
       <c r="ER4" s="16" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="ES4" s="16">
         <f>IFERROR(_xlfn.SINGLE(_xlfn.XLOOKUP(ER1, TestMaster[Test Name], TestMaster[Test Priority], "Priority not found")), "")</f>
         <v>0</v>
       </c>
       <c r="EY4" s="16" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="EZ4" s="16">
         <f>IFERROR(_xlfn.SINGLE(_xlfn.XLOOKUP(EY1, TestMaster[Test Name], TestMaster[Test Priority], "Priority not found")), "")</f>
@@ -10083,161 +10033,161 @@
     </row>
     <row r="5" spans="1:160" x14ac:dyDescent="0.25">
       <c r="A5" s="16" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B5" s="16" t="str">
         <f>IFERROR(_xlfn.SINGLE(_xlfn.XLOOKUP(A1, TestMaster[Test Name], TestMaster[Test Status], "Status not found")), "")</f>
         <v>Pass</v>
       </c>
       <c r="H5" s="16" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="I5" s="16" t="str">
         <f>IFERROR(_xlfn.SINGLE(_xlfn.XLOOKUP(H1, TestMaster[Test Name], TestMaster[Test Status], "Status not found")), "")</f>
         <v>Pass</v>
       </c>
       <c r="O5" s="16" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="P5" s="16" t="str">
         <f>IFERROR(_xlfn.SINGLE(_xlfn.XLOOKUP(O1, TestMaster[Test Name], TestMaster[Test Status], "Status not found")), "")</f>
         <v>Pass</v>
       </c>
       <c r="V5" s="16" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="W5" s="16" t="str">
         <f>IFERROR(_xlfn.SINGLE(_xlfn.XLOOKUP(V1, TestMaster[Test Name], TestMaster[Test Status], "Status not found")), "")</f>
         <v>Pass</v>
       </c>
       <c r="AC5" s="16" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AD5" s="16" t="str">
         <f>IFERROR(_xlfn.SINGLE(_xlfn.XLOOKUP(AC1, TestMaster[Test Name], TestMaster[Test Status], "Status not found")), "")</f>
         <v>Pass</v>
       </c>
       <c r="AJ5" s="16" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AK5" s="16" t="str">
         <f>IFERROR(_xlfn.SINGLE(_xlfn.XLOOKUP(AJ1, TestMaster[Test Name], TestMaster[Test Status], "Status not found")), "")</f>
         <v>Pass</v>
       </c>
       <c r="AQ5" s="16" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AR5" s="16" t="str">
         <f>IFERROR(_xlfn.SINGLE(_xlfn.XLOOKUP(AQ1, TestMaster[Test Name], TestMaster[Test Status], "Status not found")), "")</f>
         <v>Fail</v>
       </c>
       <c r="AX5" s="16" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AY5" s="16" t="str">
         <f>IFERROR(_xlfn.SINGLE(_xlfn.XLOOKUP(AX1, TestMaster[Test Name], TestMaster[Test Status], "Status not found")), "")</f>
         <v>Pass</v>
       </c>
       <c r="BE5" s="16" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BF5" s="16" t="str">
         <f>IFERROR(_xlfn.SINGLE(_xlfn.XLOOKUP(BE1, TestMaster[Test Name], TestMaster[Test Status], "Status not found")), "")</f>
         <v>Pass</v>
       </c>
       <c r="BL5" s="16" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BM5" s="16" t="str">
         <f>IFERROR(_xlfn.SINGLE(_xlfn.XLOOKUP(BL1, TestMaster[Test Name], TestMaster[Test Status], "Status not found")), "")</f>
         <v>Pass</v>
       </c>
       <c r="BS5" s="16" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BT5" s="16" t="str">
         <f>IFERROR(_xlfn.SINGLE(_xlfn.XLOOKUP(BS1, TestMaster[Test Name], TestMaster[Test Status], "Status not found")), "")</f>
         <v>Pass</v>
       </c>
       <c r="BZ5" s="16" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="CA5" s="16" t="str">
         <f>IFERROR(_xlfn.SINGLE(_xlfn.XLOOKUP(BZ1, TestMaster[Test Name], TestMaster[Test Status], "Status not found")), "")</f>
         <v>Pass</v>
       </c>
       <c r="CG5" s="16" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="CH5" s="16" t="str">
         <f>IFERROR(_xlfn.SINGLE(_xlfn.XLOOKUP(CG1, TestMaster[Test Name], TestMaster[Test Status], "Status not found")), "")</f>
         <v>Fail</v>
       </c>
       <c r="CN5" s="16" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="CO5" s="16" t="str">
         <f>IFERROR(_xlfn.SINGLE(_xlfn.XLOOKUP(CN1, TestMaster[Test Name], TestMaster[Test Status], "Status not found")), "")</f>
         <v>Pass</v>
       </c>
       <c r="CU5" s="16" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="CV5" s="16" t="str">
         <f>IFERROR(_xlfn.SINGLE(_xlfn.XLOOKUP(CU1, TestMaster[Test Name], TestMaster[Test Status], "Status not found")), "")</f>
         <v>Fail</v>
       </c>
       <c r="DB5" s="16" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="DC5" s="16" t="str">
         <f>IFERROR(_xlfn.SINGLE(_xlfn.XLOOKUP(DB1, TestMaster[Test Name], TestMaster[Test Status], "Status not found")), "")</f>
         <v>Pass</v>
       </c>
       <c r="DI5" s="16" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="DJ5" s="16" t="str">
         <f>IFERROR(_xlfn.SINGLE(_xlfn.XLOOKUP(DI1, TestMaster[Test Name], TestMaster[Test Status], "Status not found")), "")</f>
         <v>Pass</v>
       </c>
       <c r="DP5" s="16" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="DQ5" s="16" t="str">
         <f>IFERROR(_xlfn.SINGLE(_xlfn.XLOOKUP(DP1, TestMaster[Test Name], TestMaster[Test Status], "Status not found")), "")</f>
         <v>Pass</v>
       </c>
       <c r="DW5" s="16" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="DX5" s="16" t="str">
         <f>IFERROR(_xlfn.SINGLE(_xlfn.XLOOKUP(DW1, TestMaster[Test Name], TestMaster[Test Status], "Status not found")), "")</f>
         <v>Pass</v>
       </c>
       <c r="ED5" s="16" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="EE5" s="16" t="str">
         <f>IFERROR(_xlfn.SINGLE(_xlfn.XLOOKUP(ED1, TestMaster[Test Name], TestMaster[Test Status], "Status not found")), "")</f>
         <v>Skipped</v>
       </c>
       <c r="EK5" s="16" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="EL5" s="16" t="str">
         <f>IFERROR(_xlfn.SINGLE(_xlfn.XLOOKUP(EK1, TestMaster[Test Name], TestMaster[Test Status], "Status not found")), "")</f>
         <v>Pass</v>
       </c>
       <c r="ER5" s="16" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="ES5" s="16" t="str">
         <f>IFERROR(_xlfn.SINGLE(_xlfn.XLOOKUP(ER1, TestMaster[Test Name], TestMaster[Test Status], "Status not found")), "")</f>
         <v>Pass</v>
       </c>
       <c r="EY5" s="16" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="EZ5" s="16" t="str">
         <f>IFERROR(_xlfn.SINGLE(_xlfn.XLOOKUP(EY1, TestMaster[Test Name], TestMaster[Test Status], "Status not found")), "")</f>
@@ -10246,230 +10196,230 @@
     </row>
     <row r="6" spans="1:160" x14ac:dyDescent="0.25">
       <c r="A6" s="16" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="B6" s="29" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="C6" s="18"/>
       <c r="D6" s="18"/>
       <c r="E6" s="18"/>
       <c r="F6" s="18"/>
       <c r="H6" s="16" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="I6" s="29" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="J6" s="18"/>
       <c r="K6" s="18"/>
       <c r="L6" s="18"/>
       <c r="M6" s="18"/>
       <c r="O6" s="16" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="P6" s="29" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="Q6" s="18"/>
       <c r="R6" s="18"/>
       <c r="S6" s="18"/>
       <c r="T6" s="18"/>
       <c r="V6" s="16" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="W6" s="29" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="X6" s="18"/>
       <c r="Y6" s="18"/>
       <c r="Z6" s="18"/>
       <c r="AA6" s="18"/>
       <c r="AC6" s="16" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="AD6" s="29" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
       <c r="AE6" s="18"/>
       <c r="AF6" s="18"/>
       <c r="AG6" s="18"/>
       <c r="AH6" s="18"/>
       <c r="AJ6" s="16" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="AK6" s="29" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="AL6" s="18"/>
       <c r="AM6" s="18"/>
       <c r="AN6" s="18"/>
       <c r="AO6" s="18"/>
       <c r="AQ6" s="16" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="AR6" s="29" t="s">
-        <v>281</v>
+        <v>278</v>
       </c>
       <c r="AS6" s="18"/>
       <c r="AT6" s="18"/>
       <c r="AU6" s="18"/>
       <c r="AV6" s="18"/>
       <c r="AX6" s="16" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="AY6" s="29" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="AZ6" s="18"/>
       <c r="BA6" s="18"/>
       <c r="BB6" s="18"/>
       <c r="BC6" s="18"/>
       <c r="BE6" s="16" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="BF6" s="29" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="BG6" s="18"/>
       <c r="BH6" s="18"/>
       <c r="BI6" s="18"/>
       <c r="BJ6" s="18"/>
       <c r="BL6" s="16" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="BM6" s="29" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="BN6" s="18"/>
       <c r="BO6" s="18"/>
       <c r="BP6" s="18"/>
       <c r="BQ6" s="18"/>
       <c r="BS6" s="16" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="BT6" s="29" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
       <c r="BU6" s="18"/>
       <c r="BV6" s="18"/>
       <c r="BW6" s="18"/>
       <c r="BX6" s="18"/>
       <c r="BZ6" s="16" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="CA6" s="29" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="CB6" s="18"/>
       <c r="CC6" s="18"/>
       <c r="CD6" s="18"/>
       <c r="CE6" s="18"/>
       <c r="CG6" s="16" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="CH6" s="29" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="CI6" s="18"/>
       <c r="CJ6" s="18"/>
       <c r="CK6" s="18"/>
       <c r="CL6" s="18"/>
       <c r="CN6" s="16" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="CO6" s="29" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="CP6" s="18"/>
       <c r="CQ6" s="18"/>
       <c r="CR6" s="18"/>
       <c r="CS6" s="18"/>
       <c r="CU6" s="16" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="CV6" s="29" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="CW6" s="18"/>
       <c r="CX6" s="18"/>
       <c r="CY6" s="18"/>
       <c r="CZ6" s="18"/>
       <c r="DB6" s="16" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="DC6" s="29" t="s">
-        <v>290</v>
+        <v>287</v>
       </c>
       <c r="DD6" s="18"/>
       <c r="DE6" s="18"/>
       <c r="DF6" s="18"/>
       <c r="DG6" s="18"/>
       <c r="DI6" s="16" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="DJ6" s="29" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="DK6" s="18"/>
       <c r="DL6" s="18"/>
       <c r="DM6" s="18"/>
       <c r="DN6" s="18"/>
       <c r="DP6" s="16" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="DQ6" s="29" t="s">
-        <v>292</v>
+        <v>289</v>
       </c>
       <c r="DR6" s="18"/>
       <c r="DS6" s="18"/>
       <c r="DT6" s="18"/>
       <c r="DU6" s="18"/>
       <c r="DW6" s="16" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="DX6" s="29" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="DY6" s="18"/>
       <c r="DZ6" s="18"/>
       <c r="EA6" s="18"/>
       <c r="EB6" s="18"/>
       <c r="ED6" s="16" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="EE6" s="29" t="s">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="EF6" s="18"/>
       <c r="EG6" s="18"/>
       <c r="EH6" s="18"/>
       <c r="EI6" s="18"/>
       <c r="EK6" s="16" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="EL6" s="29" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="EM6" s="18"/>
       <c r="EN6" s="18"/>
       <c r="EO6" s="18"/>
       <c r="EP6" s="18"/>
       <c r="ER6" s="16" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="ES6" s="29" t="s">
-        <v>296</v>
+        <v>293</v>
       </c>
       <c r="ET6" s="18"/>
       <c r="EU6" s="18"/>
       <c r="EV6" s="18"/>
       <c r="EW6" s="18"/>
       <c r="EY6" s="16" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="EZ6" s="29" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="FA6" s="18"/>
       <c r="FB6" s="18"/>
@@ -10478,230 +10428,230 @@
     </row>
     <row r="7" spans="1:160" x14ac:dyDescent="0.25">
       <c r="A7" s="16" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B7" s="29" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="C7" s="18"/>
       <c r="D7" s="18"/>
       <c r="E7" s="18"/>
       <c r="F7" s="18"/>
       <c r="H7" s="16" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I7" s="29" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="J7" s="18"/>
       <c r="K7" s="18"/>
       <c r="L7" s="18"/>
       <c r="M7" s="18"/>
       <c r="O7" s="16" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="P7" s="29" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="Q7" s="18"/>
       <c r="R7" s="18"/>
       <c r="S7" s="18"/>
       <c r="T7" s="18"/>
       <c r="V7" s="16" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="W7" s="29" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="X7" s="18"/>
       <c r="Y7" s="18"/>
       <c r="Z7" s="18"/>
       <c r="AA7" s="18"/>
       <c r="AC7" s="16" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AD7" s="29" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="AE7" s="18"/>
       <c r="AF7" s="18"/>
       <c r="AG7" s="18"/>
       <c r="AH7" s="18"/>
       <c r="AJ7" s="16" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AK7" s="29" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="AL7" s="18"/>
       <c r="AM7" s="18"/>
       <c r="AN7" s="18"/>
       <c r="AO7" s="18"/>
       <c r="AQ7" s="16" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AR7" s="29" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="AS7" s="18"/>
       <c r="AT7" s="18"/>
       <c r="AU7" s="18"/>
       <c r="AV7" s="18"/>
       <c r="AX7" s="16" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AY7" s="29" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="AZ7" s="18"/>
       <c r="BA7" s="18"/>
       <c r="BB7" s="18"/>
       <c r="BC7" s="18"/>
       <c r="BE7" s="16" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BF7" s="29" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="BG7" s="18"/>
       <c r="BH7" s="18"/>
       <c r="BI7" s="18"/>
       <c r="BJ7" s="18"/>
       <c r="BL7" s="16" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BM7" s="29" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="BN7" s="18"/>
       <c r="BO7" s="18"/>
       <c r="BP7" s="18"/>
       <c r="BQ7" s="18"/>
       <c r="BS7" s="16" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BT7" s="29" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="BU7" s="18"/>
       <c r="BV7" s="18"/>
       <c r="BW7" s="18"/>
       <c r="BX7" s="18"/>
       <c r="BZ7" s="16" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="CA7" s="29" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="CB7" s="18"/>
       <c r="CC7" s="18"/>
       <c r="CD7" s="18"/>
       <c r="CE7" s="18"/>
       <c r="CG7" s="16" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="CH7" s="29" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="CI7" s="18"/>
       <c r="CJ7" s="18"/>
       <c r="CK7" s="18"/>
       <c r="CL7" s="18"/>
       <c r="CN7" s="16" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="CO7" s="29" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="CP7" s="18"/>
       <c r="CQ7" s="18"/>
       <c r="CR7" s="18"/>
       <c r="CS7" s="18"/>
       <c r="CU7" s="16" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="CV7" s="29" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="CW7" s="18"/>
       <c r="CX7" s="18"/>
       <c r="CY7" s="18"/>
       <c r="CZ7" s="18"/>
       <c r="DB7" s="16" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="DC7" s="29" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="DD7" s="18"/>
       <c r="DE7" s="18"/>
       <c r="DF7" s="18"/>
       <c r="DG7" s="18"/>
       <c r="DI7" s="16" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="DJ7" s="29" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="DK7" s="18"/>
       <c r="DL7" s="18"/>
       <c r="DM7" s="18"/>
       <c r="DN7" s="18"/>
       <c r="DP7" s="16" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="DQ7" s="29" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="DR7" s="18"/>
       <c r="DS7" s="18"/>
       <c r="DT7" s="18"/>
       <c r="DU7" s="18"/>
       <c r="DW7" s="16" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="DX7" s="29" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="DY7" s="18"/>
       <c r="DZ7" s="18"/>
       <c r="EA7" s="18"/>
       <c r="EB7" s="18"/>
       <c r="ED7" s="16" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="EE7" s="29" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="EF7" s="18"/>
       <c r="EG7" s="18"/>
       <c r="EH7" s="18"/>
       <c r="EI7" s="18"/>
       <c r="EK7" s="16" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="EL7" s="29" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="EM7" s="18"/>
       <c r="EN7" s="18"/>
       <c r="EO7" s="18"/>
       <c r="EP7" s="18"/>
       <c r="ER7" s="16" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="ES7" s="29" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="ET7" s="18"/>
       <c r="EU7" s="18"/>
       <c r="EV7" s="18"/>
       <c r="EW7" s="18"/>
       <c r="EY7" s="16" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="EZ7" s="29" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="FA7" s="18"/>
       <c r="FB7" s="18"/>
@@ -10710,1296 +10660,1296 @@
     </row>
     <row r="8" spans="1:160" x14ac:dyDescent="0.25">
       <c r="A8" s="16" t="s">
+        <v>25</v>
+      </c>
+      <c r="B8" s="16" t="s">
         <v>26</v>
       </c>
-      <c r="B8" s="16" t="s">
+      <c r="C8" s="16" t="s">
         <v>27</v>
       </c>
-      <c r="C8" s="16" t="s">
+      <c r="D8" s="16" t="s">
         <v>28</v>
       </c>
-      <c r="D8" s="16" t="s">
+      <c r="E8" s="16" t="s">
         <v>29</v>
       </c>
-      <c r="E8" s="16" t="s">
+      <c r="F8" s="16" t="s">
         <v>30</v>
       </c>
-      <c r="F8" s="16" t="s">
-        <v>31</v>
-      </c>
       <c r="H8" s="16" t="s">
+        <v>25</v>
+      </c>
+      <c r="I8" s="16" t="s">
         <v>26</v>
       </c>
-      <c r="I8" s="16" t="s">
+      <c r="J8" s="16" t="s">
         <v>27</v>
       </c>
-      <c r="J8" s="16" t="s">
+      <c r="K8" s="16" t="s">
         <v>28</v>
       </c>
-      <c r="K8" s="16" t="s">
+      <c r="L8" s="16" t="s">
         <v>29</v>
       </c>
-      <c r="L8" s="16" t="s">
+      <c r="M8" s="16" t="s">
         <v>30</v>
       </c>
-      <c r="M8" s="16" t="s">
-        <v>31</v>
-      </c>
       <c r="O8" s="16" t="s">
+        <v>25</v>
+      </c>
+      <c r="P8" s="16" t="s">
         <v>26</v>
       </c>
-      <c r="P8" s="16" t="s">
+      <c r="Q8" s="16" t="s">
         <v>27</v>
       </c>
-      <c r="Q8" s="16" t="s">
+      <c r="R8" s="16" t="s">
         <v>28</v>
       </c>
-      <c r="R8" s="16" t="s">
+      <c r="S8" s="16" t="s">
         <v>29</v>
       </c>
-      <c r="S8" s="16" t="s">
+      <c r="T8" s="16" t="s">
         <v>30</v>
       </c>
-      <c r="T8" s="16" t="s">
-        <v>31</v>
-      </c>
       <c r="V8" s="16" t="s">
+        <v>25</v>
+      </c>
+      <c r="W8" s="16" t="s">
         <v>26</v>
       </c>
-      <c r="W8" s="16" t="s">
+      <c r="X8" s="16" t="s">
         <v>27</v>
       </c>
-      <c r="X8" s="16" t="s">
+      <c r="Y8" s="16" t="s">
         <v>28</v>
       </c>
-      <c r="Y8" s="16" t="s">
+      <c r="Z8" s="16" t="s">
         <v>29</v>
       </c>
-      <c r="Z8" s="16" t="s">
+      <c r="AA8" s="16" t="s">
         <v>30</v>
       </c>
-      <c r="AA8" s="16" t="s">
-        <v>31</v>
-      </c>
       <c r="AC8" s="16" t="s">
+        <v>25</v>
+      </c>
+      <c r="AD8" s="16" t="s">
         <v>26</v>
       </c>
-      <c r="AD8" s="16" t="s">
+      <c r="AE8" s="16" t="s">
         <v>27</v>
       </c>
-      <c r="AE8" s="16" t="s">
+      <c r="AF8" s="16" t="s">
         <v>28</v>
       </c>
-      <c r="AF8" s="16" t="s">
+      <c r="AG8" s="16" t="s">
         <v>29</v>
       </c>
-      <c r="AG8" s="16" t="s">
+      <c r="AH8" s="16" t="s">
         <v>30</v>
       </c>
-      <c r="AH8" s="16" t="s">
-        <v>31</v>
-      </c>
       <c r="AJ8" s="16" t="s">
+        <v>25</v>
+      </c>
+      <c r="AK8" s="16" t="s">
         <v>26</v>
       </c>
-      <c r="AK8" s="16" t="s">
+      <c r="AL8" s="16" t="s">
         <v>27</v>
       </c>
-      <c r="AL8" s="16" t="s">
+      <c r="AM8" s="16" t="s">
         <v>28</v>
       </c>
-      <c r="AM8" s="16" t="s">
+      <c r="AN8" s="16" t="s">
         <v>29</v>
       </c>
-      <c r="AN8" s="16" t="s">
+      <c r="AO8" s="16" t="s">
         <v>30</v>
       </c>
-      <c r="AO8" s="16" t="s">
-        <v>31</v>
-      </c>
       <c r="AQ8" s="16" t="s">
+        <v>25</v>
+      </c>
+      <c r="AR8" s="16" t="s">
         <v>26</v>
       </c>
-      <c r="AR8" s="16" t="s">
+      <c r="AS8" s="16" t="s">
         <v>27</v>
       </c>
-      <c r="AS8" s="16" t="s">
+      <c r="AT8" s="16" t="s">
         <v>28</v>
       </c>
-      <c r="AT8" s="16" t="s">
+      <c r="AU8" s="16" t="s">
         <v>29</v>
       </c>
-      <c r="AU8" s="16" t="s">
+      <c r="AV8" s="16" t="s">
         <v>30</v>
       </c>
-      <c r="AV8" s="16" t="s">
-        <v>31</v>
-      </c>
       <c r="AX8" s="16" t="s">
+        <v>25</v>
+      </c>
+      <c r="AY8" s="16" t="s">
         <v>26</v>
       </c>
-      <c r="AY8" s="16" t="s">
+      <c r="AZ8" s="16" t="s">
         <v>27</v>
       </c>
-      <c r="AZ8" s="16" t="s">
+      <c r="BA8" s="16" t="s">
         <v>28</v>
       </c>
-      <c r="BA8" s="16" t="s">
+      <c r="BB8" s="16" t="s">
         <v>29</v>
       </c>
-      <c r="BB8" s="16" t="s">
+      <c r="BC8" s="16" t="s">
         <v>30</v>
       </c>
-      <c r="BC8" s="16" t="s">
-        <v>31</v>
-      </c>
       <c r="BE8" s="16" t="s">
+        <v>25</v>
+      </c>
+      <c r="BF8" s="16" t="s">
         <v>26</v>
       </c>
-      <c r="BF8" s="16" t="s">
+      <c r="BG8" s="16" t="s">
         <v>27</v>
       </c>
-      <c r="BG8" s="16" t="s">
+      <c r="BH8" s="16" t="s">
         <v>28</v>
       </c>
-      <c r="BH8" s="16" t="s">
+      <c r="BI8" s="16" t="s">
         <v>29</v>
       </c>
-      <c r="BI8" s="16" t="s">
+      <c r="BJ8" s="16" t="s">
         <v>30</v>
       </c>
-      <c r="BJ8" s="16" t="s">
-        <v>31</v>
-      </c>
       <c r="BL8" s="16" t="s">
+        <v>25</v>
+      </c>
+      <c r="BM8" s="16" t="s">
         <v>26</v>
       </c>
-      <c r="BM8" s="16" t="s">
+      <c r="BN8" s="16" t="s">
         <v>27</v>
       </c>
-      <c r="BN8" s="16" t="s">
+      <c r="BO8" s="16" t="s">
         <v>28</v>
       </c>
-      <c r="BO8" s="16" t="s">
+      <c r="BP8" s="16" t="s">
         <v>29</v>
       </c>
-      <c r="BP8" s="16" t="s">
+      <c r="BQ8" s="16" t="s">
         <v>30</v>
       </c>
-      <c r="BQ8" s="16" t="s">
-        <v>31</v>
-      </c>
       <c r="BS8" s="16" t="s">
+        <v>25</v>
+      </c>
+      <c r="BT8" s="16" t="s">
         <v>26</v>
       </c>
-      <c r="BT8" s="16" t="s">
+      <c r="BU8" s="16" t="s">
         <v>27</v>
       </c>
-      <c r="BU8" s="16" t="s">
+      <c r="BV8" s="16" t="s">
         <v>28</v>
       </c>
-      <c r="BV8" s="16" t="s">
+      <c r="BW8" s="16" t="s">
         <v>29</v>
       </c>
-      <c r="BW8" s="16" t="s">
+      <c r="BX8" s="16" t="s">
         <v>30</v>
       </c>
-      <c r="BX8" s="16" t="s">
-        <v>31</v>
-      </c>
       <c r="BZ8" s="16" t="s">
+        <v>25</v>
+      </c>
+      <c r="CA8" s="16" t="s">
         <v>26</v>
       </c>
-      <c r="CA8" s="16" t="s">
+      <c r="CB8" s="16" t="s">
         <v>27</v>
       </c>
-      <c r="CB8" s="16" t="s">
+      <c r="CC8" s="16" t="s">
         <v>28</v>
       </c>
-      <c r="CC8" s="16" t="s">
+      <c r="CD8" s="16" t="s">
         <v>29</v>
       </c>
-      <c r="CD8" s="16" t="s">
+      <c r="CE8" s="16" t="s">
         <v>30</v>
       </c>
-      <c r="CE8" s="16" t="s">
-        <v>31</v>
-      </c>
       <c r="CG8" s="16" t="s">
+        <v>25</v>
+      </c>
+      <c r="CH8" s="16" t="s">
         <v>26</v>
       </c>
-      <c r="CH8" s="16" t="s">
+      <c r="CI8" s="16" t="s">
         <v>27</v>
       </c>
-      <c r="CI8" s="16" t="s">
+      <c r="CJ8" s="16" t="s">
         <v>28</v>
       </c>
-      <c r="CJ8" s="16" t="s">
+      <c r="CK8" s="16" t="s">
         <v>29</v>
       </c>
-      <c r="CK8" s="16" t="s">
+      <c r="CL8" s="16" t="s">
         <v>30</v>
       </c>
-      <c r="CL8" s="16" t="s">
-        <v>31</v>
-      </c>
       <c r="CN8" s="16" t="s">
+        <v>25</v>
+      </c>
+      <c r="CO8" s="16" t="s">
         <v>26</v>
       </c>
-      <c r="CO8" s="16" t="s">
+      <c r="CP8" s="16" t="s">
         <v>27</v>
       </c>
-      <c r="CP8" s="16" t="s">
+      <c r="CQ8" s="16" t="s">
         <v>28</v>
       </c>
-      <c r="CQ8" s="16" t="s">
+      <c r="CR8" s="16" t="s">
         <v>29</v>
       </c>
-      <c r="CR8" s="16" t="s">
+      <c r="CS8" s="16" t="s">
         <v>30</v>
       </c>
-      <c r="CS8" s="16" t="s">
-        <v>31</v>
-      </c>
       <c r="CU8" s="16" t="s">
+        <v>25</v>
+      </c>
+      <c r="CV8" s="16" t="s">
         <v>26</v>
       </c>
-      <c r="CV8" s="16" t="s">
+      <c r="CW8" s="16" t="s">
         <v>27</v>
       </c>
-      <c r="CW8" s="16" t="s">
+      <c r="CX8" s="16" t="s">
         <v>28</v>
       </c>
-      <c r="CX8" s="16" t="s">
+      <c r="CY8" s="16" t="s">
         <v>29</v>
       </c>
-      <c r="CY8" s="16" t="s">
+      <c r="CZ8" s="16" t="s">
         <v>30</v>
       </c>
-      <c r="CZ8" s="16" t="s">
-        <v>31</v>
-      </c>
       <c r="DB8" s="16" t="s">
+        <v>25</v>
+      </c>
+      <c r="DC8" s="16" t="s">
         <v>26</v>
       </c>
-      <c r="DC8" s="16" t="s">
+      <c r="DD8" s="16" t="s">
         <v>27</v>
       </c>
-      <c r="DD8" s="16" t="s">
+      <c r="DE8" s="16" t="s">
         <v>28</v>
       </c>
-      <c r="DE8" s="16" t="s">
+      <c r="DF8" s="16" t="s">
         <v>29</v>
       </c>
-      <c r="DF8" s="16" t="s">
+      <c r="DG8" s="16" t="s">
         <v>30</v>
       </c>
-      <c r="DG8" s="16" t="s">
-        <v>31</v>
-      </c>
       <c r="DI8" s="16" t="s">
+        <v>25</v>
+      </c>
+      <c r="DJ8" s="16" t="s">
         <v>26</v>
       </c>
-      <c r="DJ8" s="16" t="s">
+      <c r="DK8" s="16" t="s">
         <v>27</v>
       </c>
-      <c r="DK8" s="16" t="s">
+      <c r="DL8" s="16" t="s">
         <v>28</v>
       </c>
-      <c r="DL8" s="16" t="s">
+      <c r="DM8" s="16" t="s">
         <v>29</v>
       </c>
-      <c r="DM8" s="16" t="s">
+      <c r="DN8" s="16" t="s">
         <v>30</v>
       </c>
-      <c r="DN8" s="16" t="s">
-        <v>31</v>
-      </c>
       <c r="DP8" s="16" t="s">
+        <v>25</v>
+      </c>
+      <c r="DQ8" s="16" t="s">
         <v>26</v>
       </c>
-      <c r="DQ8" s="16" t="s">
+      <c r="DR8" s="16" t="s">
         <v>27</v>
       </c>
-      <c r="DR8" s="16" t="s">
+      <c r="DS8" s="16" t="s">
         <v>28</v>
       </c>
-      <c r="DS8" s="16" t="s">
+      <c r="DT8" s="16" t="s">
         <v>29</v>
       </c>
-      <c r="DT8" s="16" t="s">
+      <c r="DU8" s="16" t="s">
         <v>30</v>
       </c>
-      <c r="DU8" s="16" t="s">
-        <v>31</v>
-      </c>
       <c r="DW8" s="16" t="s">
+        <v>25</v>
+      </c>
+      <c r="DX8" s="16" t="s">
         <v>26</v>
       </c>
-      <c r="DX8" s="16" t="s">
+      <c r="DY8" s="16" t="s">
         <v>27</v>
       </c>
-      <c r="DY8" s="16" t="s">
+      <c r="DZ8" s="16" t="s">
         <v>28</v>
       </c>
-      <c r="DZ8" s="16" t="s">
+      <c r="EA8" s="16" t="s">
         <v>29</v>
       </c>
-      <c r="EA8" s="16" t="s">
+      <c r="EB8" s="16" t="s">
         <v>30</v>
       </c>
-      <c r="EB8" s="16" t="s">
-        <v>31</v>
-      </c>
       <c r="ED8" s="16" t="s">
+        <v>25</v>
+      </c>
+      <c r="EE8" s="16" t="s">
         <v>26</v>
       </c>
-      <c r="EE8" s="16" t="s">
+      <c r="EF8" s="16" t="s">
         <v>27</v>
       </c>
-      <c r="EF8" s="16" t="s">
+      <c r="EG8" s="16" t="s">
         <v>28</v>
       </c>
-      <c r="EG8" s="16" t="s">
+      <c r="EH8" s="16" t="s">
         <v>29</v>
       </c>
-      <c r="EH8" s="16" t="s">
+      <c r="EI8" s="16" t="s">
         <v>30</v>
       </c>
-      <c r="EI8" s="16" t="s">
-        <v>31</v>
-      </c>
       <c r="EK8" s="16" t="s">
+        <v>25</v>
+      </c>
+      <c r="EL8" s="16" t="s">
         <v>26</v>
       </c>
-      <c r="EL8" s="16" t="s">
+      <c r="EM8" s="16" t="s">
         <v>27</v>
       </c>
-      <c r="EM8" s="16" t="s">
+      <c r="EN8" s="16" t="s">
         <v>28</v>
       </c>
-      <c r="EN8" s="16" t="s">
+      <c r="EO8" s="16" t="s">
         <v>29</v>
       </c>
-      <c r="EO8" s="16" t="s">
+      <c r="EP8" s="16" t="s">
         <v>30</v>
       </c>
-      <c r="EP8" s="16" t="s">
-        <v>31</v>
-      </c>
       <c r="ER8" s="16" t="s">
+        <v>25</v>
+      </c>
+      <c r="ES8" s="16" t="s">
         <v>26</v>
       </c>
-      <c r="ES8" s="16" t="s">
+      <c r="ET8" s="16" t="s">
         <v>27</v>
       </c>
-      <c r="ET8" s="16" t="s">
+      <c r="EU8" s="16" t="s">
         <v>28</v>
       </c>
-      <c r="EU8" s="16" t="s">
+      <c r="EV8" s="16" t="s">
         <v>29</v>
       </c>
-      <c r="EV8" s="16" t="s">
+      <c r="EW8" s="16" t="s">
         <v>30</v>
       </c>
-      <c r="EW8" s="16" t="s">
-        <v>31</v>
-      </c>
       <c r="EY8" s="16" t="s">
+        <v>25</v>
+      </c>
+      <c r="EZ8" s="16" t="s">
         <v>26</v>
       </c>
-      <c r="EZ8" s="16" t="s">
+      <c r="FA8" s="16" t="s">
         <v>27</v>
       </c>
-      <c r="FA8" s="16" t="s">
+      <c r="FB8" s="16" t="s">
         <v>28</v>
       </c>
-      <c r="FB8" s="16" t="s">
+      <c r="FC8" s="16" t="s">
         <v>29</v>
       </c>
-      <c r="FC8" s="16" t="s">
+      <c r="FD8" s="16" t="s">
         <v>30</v>
-      </c>
-      <c r="FD8" s="16" t="s">
-        <v>31</v>
       </c>
     </row>
     <row r="9" spans="1:160" ht="29.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="16" t="s">
+        <v>226</v>
+      </c>
+      <c r="B9" s="16" t="s">
+        <v>227</v>
+      </c>
+      <c r="C9" s="16" t="s">
+        <v>228</v>
+      </c>
+      <c r="D9" s="16" t="s">
         <v>229</v>
-      </c>
-      <c r="B9" s="16" t="s">
-        <v>230</v>
-      </c>
-      <c r="C9" s="16" t="s">
-        <v>231</v>
-      </c>
-      <c r="D9" s="16" t="s">
-        <v>232</v>
       </c>
       <c r="E9" s="16"/>
       <c r="F9" s="16"/>
       <c r="H9" s="16" t="s">
+        <v>226</v>
+      </c>
+      <c r="I9" s="16" t="s">
+        <v>227</v>
+      </c>
+      <c r="J9" s="16" t="s">
+        <v>228</v>
+      </c>
+      <c r="K9" s="16" t="s">
         <v>229</v>
-      </c>
-      <c r="I9" s="16" t="s">
-        <v>230</v>
-      </c>
-      <c r="J9" s="16" t="s">
-        <v>231</v>
-      </c>
-      <c r="K9" s="16" t="s">
-        <v>232</v>
       </c>
       <c r="L9" s="16"/>
       <c r="M9" s="16"/>
       <c r="O9" s="16" t="s">
+        <v>226</v>
+      </c>
+      <c r="P9" s="16" t="s">
+        <v>227</v>
+      </c>
+      <c r="Q9" s="16" t="s">
+        <v>228</v>
+      </c>
+      <c r="R9" s="16" t="s">
         <v>229</v>
-      </c>
-      <c r="P9" s="16" t="s">
-        <v>230</v>
-      </c>
-      <c r="Q9" s="16" t="s">
-        <v>231</v>
-      </c>
-      <c r="R9" s="16" t="s">
-        <v>232</v>
       </c>
       <c r="S9" s="16"/>
       <c r="T9" s="16"/>
       <c r="V9" s="16" t="s">
+        <v>226</v>
+      </c>
+      <c r="W9" s="16" t="s">
+        <v>227</v>
+      </c>
+      <c r="X9" s="16" t="s">
+        <v>228</v>
+      </c>
+      <c r="Y9" s="16" t="s">
         <v>229</v>
-      </c>
-      <c r="W9" s="16" t="s">
-        <v>230</v>
-      </c>
-      <c r="X9" s="16" t="s">
-        <v>231</v>
-      </c>
-      <c r="Y9" s="16" t="s">
-        <v>232</v>
       </c>
       <c r="Z9" s="16"/>
       <c r="AA9" s="16"/>
       <c r="AC9" s="16" t="s">
+        <v>226</v>
+      </c>
+      <c r="AD9" s="16" t="s">
+        <v>227</v>
+      </c>
+      <c r="AE9" s="16" t="s">
+        <v>228</v>
+      </c>
+      <c r="AF9" s="16" t="s">
         <v>229</v>
-      </c>
-      <c r="AD9" s="16" t="s">
-        <v>230</v>
-      </c>
-      <c r="AE9" s="16" t="s">
-        <v>231</v>
-      </c>
-      <c r="AF9" s="16" t="s">
-        <v>232</v>
       </c>
       <c r="AG9" s="16"/>
       <c r="AH9" s="16"/>
       <c r="AJ9" s="16" t="s">
+        <v>226</v>
+      </c>
+      <c r="AK9" s="16" t="s">
+        <v>227</v>
+      </c>
+      <c r="AL9" s="16" t="s">
+        <v>228</v>
+      </c>
+      <c r="AM9" s="16" t="s">
         <v>229</v>
-      </c>
-      <c r="AK9" s="16" t="s">
-        <v>230</v>
-      </c>
-      <c r="AL9" s="16" t="s">
-        <v>231</v>
-      </c>
-      <c r="AM9" s="16" t="s">
-        <v>232</v>
       </c>
       <c r="AN9" s="16"/>
       <c r="AO9" s="16"/>
       <c r="AQ9" s="16" t="s">
+        <v>226</v>
+      </c>
+      <c r="AR9" s="16" t="s">
+        <v>227</v>
+      </c>
+      <c r="AS9" s="16" t="s">
+        <v>228</v>
+      </c>
+      <c r="AT9" s="16" t="s">
         <v>229</v>
-      </c>
-      <c r="AR9" s="16" t="s">
-        <v>230</v>
-      </c>
-      <c r="AS9" s="16" t="s">
-        <v>231</v>
-      </c>
-      <c r="AT9" s="16" t="s">
-        <v>232</v>
       </c>
       <c r="AU9" s="16"/>
       <c r="AV9" s="16"/>
       <c r="AX9" s="16" t="s">
+        <v>226</v>
+      </c>
+      <c r="AY9" s="16" t="s">
+        <v>227</v>
+      </c>
+      <c r="AZ9" s="16" t="s">
+        <v>228</v>
+      </c>
+      <c r="BA9" s="16" t="s">
         <v>229</v>
-      </c>
-      <c r="AY9" s="16" t="s">
-        <v>230</v>
-      </c>
-      <c r="AZ9" s="16" t="s">
-        <v>231</v>
-      </c>
-      <c r="BA9" s="16" t="s">
-        <v>232</v>
       </c>
       <c r="BB9" s="16"/>
       <c r="BC9" s="16"/>
       <c r="BE9" s="16" t="s">
+        <v>226</v>
+      </c>
+      <c r="BF9" s="16" t="s">
+        <v>227</v>
+      </c>
+      <c r="BG9" s="16" t="s">
+        <v>228</v>
+      </c>
+      <c r="BH9" s="16" t="s">
         <v>229</v>
-      </c>
-      <c r="BF9" s="16" t="s">
-        <v>230</v>
-      </c>
-      <c r="BG9" s="16" t="s">
-        <v>231</v>
-      </c>
-      <c r="BH9" s="16" t="s">
-        <v>232</v>
       </c>
       <c r="BI9" s="16"/>
       <c r="BJ9" s="16"/>
       <c r="BL9" s="16" t="s">
+        <v>226</v>
+      </c>
+      <c r="BM9" s="16" t="s">
+        <v>227</v>
+      </c>
+      <c r="BN9" s="16" t="s">
+        <v>228</v>
+      </c>
+      <c r="BO9" s="16" t="s">
         <v>229</v>
-      </c>
-      <c r="BM9" s="16" t="s">
-        <v>230</v>
-      </c>
-      <c r="BN9" s="16" t="s">
-        <v>231</v>
-      </c>
-      <c r="BO9" s="16" t="s">
-        <v>232</v>
       </c>
       <c r="BP9" s="16"/>
       <c r="BQ9" s="16"/>
       <c r="BS9" s="16" t="s">
+        <v>226</v>
+      </c>
+      <c r="BT9" s="16" t="s">
+        <v>227</v>
+      </c>
+      <c r="BU9" s="16" t="s">
+        <v>228</v>
+      </c>
+      <c r="BV9" s="16" t="s">
         <v>229</v>
-      </c>
-      <c r="BT9" s="16" t="s">
-        <v>230</v>
-      </c>
-      <c r="BU9" s="16" t="s">
-        <v>231</v>
-      </c>
-      <c r="BV9" s="16" t="s">
-        <v>232</v>
       </c>
       <c r="BW9" s="16"/>
       <c r="BX9" s="16"/>
       <c r="BZ9" s="16" t="s">
+        <v>226</v>
+      </c>
+      <c r="CA9" s="16" t="s">
+        <v>227</v>
+      </c>
+      <c r="CB9" s="16" t="s">
+        <v>228</v>
+      </c>
+      <c r="CC9" s="16" t="s">
         <v>229</v>
-      </c>
-      <c r="CA9" s="16" t="s">
-        <v>230</v>
-      </c>
-      <c r="CB9" s="16" t="s">
-        <v>231</v>
-      </c>
-      <c r="CC9" s="16" t="s">
-        <v>232</v>
       </c>
       <c r="CD9" s="16"/>
       <c r="CE9" s="16"/>
       <c r="CG9" s="16" t="s">
+        <v>226</v>
+      </c>
+      <c r="CH9" s="16" t="s">
+        <v>227</v>
+      </c>
+      <c r="CI9" s="16" t="s">
+        <v>228</v>
+      </c>
+      <c r="CJ9" s="16" t="s">
         <v>229</v>
-      </c>
-      <c r="CH9" s="16" t="s">
-        <v>230</v>
-      </c>
-      <c r="CI9" s="16" t="s">
-        <v>231</v>
-      </c>
-      <c r="CJ9" s="16" t="s">
-        <v>232</v>
       </c>
       <c r="CK9" s="16"/>
       <c r="CL9" s="16"/>
       <c r="CN9" s="16" t="s">
+        <v>226</v>
+      </c>
+      <c r="CO9" s="16" t="s">
+        <v>227</v>
+      </c>
+      <c r="CP9" s="16" t="s">
+        <v>228</v>
+      </c>
+      <c r="CQ9" s="16" t="s">
         <v>229</v>
-      </c>
-      <c r="CO9" s="16" t="s">
-        <v>230</v>
-      </c>
-      <c r="CP9" s="16" t="s">
-        <v>231</v>
-      </c>
-      <c r="CQ9" s="16" t="s">
-        <v>232</v>
       </c>
       <c r="CR9" s="16"/>
       <c r="CS9" s="16"/>
       <c r="CU9" s="16" t="s">
+        <v>226</v>
+      </c>
+      <c r="CV9" s="16" t="s">
+        <v>227</v>
+      </c>
+      <c r="CW9" s="16" t="s">
+        <v>228</v>
+      </c>
+      <c r="CX9" s="16" t="s">
         <v>229</v>
-      </c>
-      <c r="CV9" s="16" t="s">
-        <v>230</v>
-      </c>
-      <c r="CW9" s="16" t="s">
-        <v>231</v>
-      </c>
-      <c r="CX9" s="16" t="s">
-        <v>232</v>
       </c>
       <c r="CY9" s="16"/>
       <c r="CZ9" s="16"/>
       <c r="DB9" s="16" t="s">
+        <v>226</v>
+      </c>
+      <c r="DC9" s="16" t="s">
+        <v>227</v>
+      </c>
+      <c r="DD9" s="16" t="s">
+        <v>228</v>
+      </c>
+      <c r="DE9" s="16" t="s">
         <v>229</v>
-      </c>
-      <c r="DC9" s="16" t="s">
-        <v>230</v>
-      </c>
-      <c r="DD9" s="16" t="s">
-        <v>231</v>
-      </c>
-      <c r="DE9" s="16" t="s">
-        <v>232</v>
       </c>
       <c r="DF9" s="16"/>
       <c r="DG9" s="16"/>
       <c r="DI9" s="16" t="s">
+        <v>226</v>
+      </c>
+      <c r="DJ9" s="16" t="s">
+        <v>227</v>
+      </c>
+      <c r="DK9" s="16" t="s">
+        <v>228</v>
+      </c>
+      <c r="DL9" s="16" t="s">
         <v>229</v>
-      </c>
-      <c r="DJ9" s="16" t="s">
-        <v>230</v>
-      </c>
-      <c r="DK9" s="16" t="s">
-        <v>231</v>
-      </c>
-      <c r="DL9" s="16" t="s">
-        <v>232</v>
       </c>
       <c r="DM9" s="16"/>
       <c r="DN9" s="16"/>
       <c r="DP9" s="16" t="s">
+        <v>226</v>
+      </c>
+      <c r="DQ9" s="16" t="s">
+        <v>227</v>
+      </c>
+      <c r="DR9" s="16" t="s">
+        <v>228</v>
+      </c>
+      <c r="DS9" s="16" t="s">
         <v>229</v>
-      </c>
-      <c r="DQ9" s="16" t="s">
-        <v>230</v>
-      </c>
-      <c r="DR9" s="16" t="s">
-        <v>231</v>
-      </c>
-      <c r="DS9" s="16" t="s">
-        <v>232</v>
       </c>
       <c r="DT9" s="16"/>
       <c r="DU9" s="16"/>
       <c r="DW9" s="16" t="s">
+        <v>226</v>
+      </c>
+      <c r="DX9" s="16" t="s">
+        <v>227</v>
+      </c>
+      <c r="DY9" s="16" t="s">
+        <v>228</v>
+      </c>
+      <c r="DZ9" s="16" t="s">
         <v>229</v>
-      </c>
-      <c r="DX9" s="16" t="s">
-        <v>230</v>
-      </c>
-      <c r="DY9" s="16" t="s">
-        <v>231</v>
-      </c>
-      <c r="DZ9" s="16" t="s">
-        <v>232</v>
       </c>
       <c r="EA9" s="16"/>
       <c r="EB9" s="16"/>
       <c r="ED9" s="16" t="s">
+        <v>226</v>
+      </c>
+      <c r="EE9" s="16" t="s">
+        <v>227</v>
+      </c>
+      <c r="EF9" s="16" t="s">
+        <v>228</v>
+      </c>
+      <c r="EG9" s="16" t="s">
         <v>229</v>
-      </c>
-      <c r="EE9" s="16" t="s">
-        <v>230</v>
-      </c>
-      <c r="EF9" s="16" t="s">
-        <v>231</v>
-      </c>
-      <c r="EG9" s="16" t="s">
-        <v>232</v>
       </c>
       <c r="EH9" s="16"/>
       <c r="EI9" s="16"/>
       <c r="EK9" s="16" t="s">
+        <v>226</v>
+      </c>
+      <c r="EL9" s="16" t="s">
+        <v>227</v>
+      </c>
+      <c r="EM9" s="16" t="s">
+        <v>228</v>
+      </c>
+      <c r="EN9" s="16" t="s">
         <v>229</v>
-      </c>
-      <c r="EL9" s="16" t="s">
-        <v>230</v>
-      </c>
-      <c r="EM9" s="16" t="s">
-        <v>231</v>
-      </c>
-      <c r="EN9" s="16" t="s">
-        <v>232</v>
       </c>
       <c r="EO9" s="16"/>
       <c r="EP9" s="16"/>
       <c r="ER9" s="16" t="s">
+        <v>226</v>
+      </c>
+      <c r="ES9" s="16" t="s">
+        <v>227</v>
+      </c>
+      <c r="ET9" s="16" t="s">
+        <v>228</v>
+      </c>
+      <c r="EU9" s="16" t="s">
         <v>229</v>
-      </c>
-      <c r="ES9" s="16" t="s">
-        <v>230</v>
-      </c>
-      <c r="ET9" s="16" t="s">
-        <v>231</v>
-      </c>
-      <c r="EU9" s="16" t="s">
-        <v>232</v>
       </c>
       <c r="EV9" s="16"/>
       <c r="EW9" s="16"/>
       <c r="EY9" s="16" t="s">
+        <v>226</v>
+      </c>
+      <c r="EZ9" s="16" t="s">
+        <v>227</v>
+      </c>
+      <c r="FA9" s="16" t="s">
+        <v>228</v>
+      </c>
+      <c r="FB9" s="16" t="s">
         <v>229</v>
-      </c>
-      <c r="EZ9" s="16" t="s">
-        <v>230</v>
-      </c>
-      <c r="FA9" s="16" t="s">
-        <v>231</v>
-      </c>
-      <c r="FB9" s="16" t="s">
-        <v>232</v>
       </c>
       <c r="FC9" s="16"/>
       <c r="FD9" s="16"/>
     </row>
     <row r="10" spans="1:160" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="16" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="B10" s="16" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="C10" s="16"/>
       <c r="D10" s="16" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="E10" s="16"/>
       <c r="F10" s="16"/>
       <c r="H10" s="16" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="I10" s="16" t="s">
-        <v>299</v>
+        <v>296</v>
       </c>
       <c r="J10" s="16"/>
       <c r="K10" s="16" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="L10" s="16"/>
       <c r="M10" s="16"/>
       <c r="O10" s="16" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="P10" s="16" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="Q10" s="16"/>
       <c r="R10" s="16" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="S10" s="16"/>
       <c r="T10" s="16"/>
       <c r="V10" s="16" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="W10" s="16" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="X10" s="16"/>
       <c r="Y10" s="16" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="Z10" s="16"/>
       <c r="AA10" s="16"/>
       <c r="AC10" s="16" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="AD10" s="16" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="AE10" s="16"/>
       <c r="AF10" s="16" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="AG10" s="16"/>
       <c r="AH10" s="16"/>
       <c r="AJ10" s="16" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="AK10" s="16" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="AL10" s="16"/>
       <c r="AM10" s="16" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="AN10" s="16"/>
       <c r="AO10" s="16"/>
       <c r="AQ10" s="16" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="AR10" s="16" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="AS10" s="16"/>
       <c r="AT10" s="16" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="AU10" s="16"/>
       <c r="AV10" s="16"/>
       <c r="AX10" s="16" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="AY10" s="16" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="AZ10" s="16"/>
       <c r="BA10" s="16" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="BB10" s="16"/>
       <c r="BC10" s="16"/>
       <c r="BE10" s="16" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="BF10" s="16" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="BG10" s="16"/>
       <c r="BH10" s="16" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="BI10" s="16"/>
       <c r="BJ10" s="16"/>
       <c r="BL10" s="16" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="BM10" s="16" t="s">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="BN10" s="16"/>
       <c r="BO10" s="16" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="BP10" s="16"/>
       <c r="BQ10" s="16"/>
       <c r="BS10" s="16" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="BT10" s="16" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="BU10" s="16"/>
       <c r="BV10" s="16" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="BW10" s="16"/>
       <c r="BX10" s="16"/>
       <c r="BZ10" s="16" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="CA10" s="16" t="s">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="CB10" s="16"/>
       <c r="CC10" s="16" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="CD10" s="16"/>
       <c r="CE10" s="16"/>
       <c r="CG10" s="16" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="CH10" s="16" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="CI10" s="16"/>
       <c r="CJ10" s="16" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="CK10" s="16"/>
       <c r="CL10" s="16"/>
       <c r="CN10" s="16" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="CO10" s="16" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="CP10" s="16"/>
       <c r="CQ10" s="16" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="CR10" s="16"/>
       <c r="CS10" s="16"/>
       <c r="CU10" s="16" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="CV10" s="16" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="CW10" s="16"/>
       <c r="CX10" s="16" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="CY10" s="16"/>
       <c r="CZ10" s="16"/>
       <c r="DB10" s="16" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="DC10" s="16" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="DD10" s="16"/>
       <c r="DE10" s="16" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="DF10" s="16"/>
       <c r="DG10" s="16"/>
       <c r="DI10" s="16" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="DJ10" s="16" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="DK10" s="16"/>
       <c r="DL10" s="16" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="DM10" s="16"/>
       <c r="DN10" s="16"/>
       <c r="DP10" s="16" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="DQ10" s="16" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="DR10" s="16"/>
       <c r="DS10" s="16" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="DT10" s="16"/>
       <c r="DU10" s="16"/>
       <c r="DW10" s="16" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="DX10" s="16" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="DY10" s="16"/>
       <c r="DZ10" s="16" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="EA10" s="16"/>
       <c r="EB10" s="16"/>
       <c r="ED10" s="16" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="EE10" s="16" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="EF10" s="16"/>
       <c r="EG10" s="16" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="EH10" s="16"/>
       <c r="EI10" s="16"/>
       <c r="EK10" s="16" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="EL10" s="16" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="EM10" s="16"/>
       <c r="EN10" s="16" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="EO10" s="16"/>
       <c r="EP10" s="16"/>
       <c r="ER10" s="16" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="ES10" s="16" t="s">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="ET10" s="16"/>
       <c r="EU10" s="16" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="EV10" s="16"/>
       <c r="EW10" s="16"/>
       <c r="EY10" s="16" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="EZ10" s="16" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="FA10" s="16"/>
       <c r="FB10" s="16" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="FC10" s="16"/>
       <c r="FD10" s="16"/>
     </row>
     <row r="11" spans="1:160" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="16" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="B11" s="16" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="C11" s="16"/>
       <c r="D11" s="16" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="E11" s="16"/>
       <c r="F11" s="16"/>
       <c r="H11" s="16" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="I11" s="16" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="J11" s="16"/>
       <c r="K11" s="16" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="L11" s="16"/>
       <c r="M11" s="16"/>
       <c r="O11" s="16" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="P11" s="16" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="Q11" s="16"/>
       <c r="R11" s="16" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="S11" s="16"/>
       <c r="T11" s="16"/>
       <c r="V11" s="16" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="W11" s="16" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="X11" s="16"/>
       <c r="Y11" s="16" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="Z11" s="16"/>
       <c r="AA11" s="16"/>
       <c r="AC11" s="16" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="AD11" s="16" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="AE11" s="16"/>
       <c r="AF11" s="16" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="AG11" s="16"/>
       <c r="AH11" s="16"/>
       <c r="AJ11" s="16" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="AK11" s="16" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="AL11" s="16"/>
       <c r="AM11" s="16" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="AN11" s="16"/>
       <c r="AO11" s="16"/>
       <c r="AQ11" s="16" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="AR11" s="16" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="AS11" s="16"/>
       <c r="AT11" s="16" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="AU11" s="16"/>
       <c r="AV11" s="16"/>
       <c r="AX11" s="16" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="AY11" s="16" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="AZ11" s="16"/>
       <c r="BA11" s="16" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="BB11" s="16"/>
       <c r="BC11" s="16"/>
       <c r="BE11" s="16" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="BF11" s="16" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="BG11" s="16"/>
       <c r="BH11" s="16" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="BI11" s="16"/>
       <c r="BJ11" s="16"/>
       <c r="BL11" s="16" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="BM11" s="16" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="BN11" s="16"/>
       <c r="BO11" s="16" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="BP11" s="16"/>
       <c r="BQ11" s="16"/>
       <c r="BS11" s="16" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="BT11" s="16" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="BU11" s="16"/>
       <c r="BV11" s="16" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="BW11" s="16"/>
       <c r="BX11" s="16"/>
       <c r="BZ11" s="16" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="CA11" s="16" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="CB11" s="16"/>
       <c r="CC11" s="16" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="CD11" s="16"/>
       <c r="CE11" s="16"/>
       <c r="CG11" s="16" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="CH11" s="16" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="CI11" s="16"/>
       <c r="CJ11" s="16" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="CK11" s="16"/>
       <c r="CL11" s="16"/>
       <c r="CN11" s="16" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="CO11" s="16" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="CP11" s="16"/>
       <c r="CQ11" s="16" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="CR11" s="16"/>
       <c r="CS11" s="16"/>
       <c r="CU11" s="16" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="CV11" s="16" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="CW11" s="16"/>
       <c r="CX11" s="16" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="CY11" s="16"/>
       <c r="CZ11" s="16"/>
       <c r="DB11" s="16" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="DC11" s="16" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="DD11" s="16"/>
       <c r="DE11" s="16" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="DF11" s="16"/>
       <c r="DG11" s="16"/>
       <c r="DI11" s="16" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="DJ11" s="16" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="DK11" s="16"/>
       <c r="DL11" s="16" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="DM11" s="16"/>
       <c r="DN11" s="16"/>
       <c r="DP11" s="16" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="DQ11" s="16" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="DR11" s="16"/>
       <c r="DS11" s="16" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="DT11" s="16"/>
       <c r="DU11" s="16"/>
       <c r="DW11" s="16" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="DX11" s="16" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="DY11" s="16"/>
       <c r="DZ11" s="16" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="EA11" s="16"/>
       <c r="EB11" s="16"/>
       <c r="ED11" s="16" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="EE11" s="16" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="EF11" s="16"/>
       <c r="EG11" s="16" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="EH11" s="16"/>
       <c r="EI11" s="16"/>
       <c r="EK11" s="16" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="EL11" s="16" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="EM11" s="16"/>
       <c r="EN11" s="16" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="EO11" s="16"/>
       <c r="EP11" s="16"/>
       <c r="ER11" s="16" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="ES11" s="16" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="ET11" s="16"/>
       <c r="EU11" s="16" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="EV11" s="16"/>
       <c r="EW11" s="16"/>
       <c r="EY11" s="16" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="EZ11" s="16" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="FA11" s="16"/>
       <c r="FB11" s="16" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="FC11" s="16"/>
       <c r="FD11" s="16"/>

--- a/Test Cases.xlsx
+++ b/Test Cases.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://endresshauser-my.sharepoint.com/personal/corbin_ferguson_endress_com/Documents/ThesisBuildTool/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="169" documentId="8_{B89245B7-08D9-4A9D-8516-F6C9C7AFFDC1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3B726949-1BFA-4762-879E-7852579E08BA}"/>
+  <xr:revisionPtr revIDLastSave="176" documentId="8_{B89245B7-08D9-4A9D-8516-F6C9C7AFFDC1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CEDDDC1D-E355-4653-B530-E778081C02BB}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="25440" windowHeight="15270" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="25440" windowHeight="15270" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tests" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1752" uniqueCount="351">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1752" uniqueCount="350">
   <si>
     <t>Test ID</t>
   </si>
@@ -180,9 +180,6 @@
     <t>open to type select window</t>
   </si>
   <si>
-    <t>move to add another window</t>
-  </si>
-  <si>
     <t>Select Resolution Style</t>
   </si>
   <si>
@@ -1083,16 +1080,16 @@
     <t>ambiguous parent window opens</t>
   </si>
   <si>
-    <t>Select parent element</t>
-  </si>
-  <si>
-    <t>new element name</t>
-  </si>
-  <si>
-    <t>TestRoutine</t>
-  </si>
-  <si>
     <t>move to name Select window</t>
+  </si>
+  <si>
+    <t>Select parent element for extract</t>
+  </si>
+  <si>
+    <t>Select parent element for insert</t>
+  </si>
+  <si>
+    <t>TemplateLadderAOI</t>
   </si>
 </sst>
 </file>
@@ -3282,7 +3279,7 @@
         <v>7</v>
       </c>
       <c r="G19" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
@@ -3563,7 +3560,7 @@
         <v>11</v>
       </c>
       <c r="E31" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="G31" t="s">
         <v>16</v>
@@ -3585,7 +3582,7 @@
         <v>10</v>
       </c>
       <c r="E32" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="G32" t="s">
         <v>5</v>
@@ -3611,7 +3608,7 @@
         <v>11</v>
       </c>
       <c r="E33" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="G33" t="s">
         <v>8</v>
@@ -4246,7 +4243,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="19" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="B1" s="18"/>
       <c r="C1" s="18"/>
@@ -4412,13 +4409,13 @@
         <v>6</v>
       </c>
       <c r="B13" s="3" t="s">
+        <v>341</v>
+      </c>
+      <c r="C13" s="3" t="s">
         <v>342</v>
       </c>
-      <c r="C13" s="3" t="s">
+      <c r="D13" s="2" t="s">
         <v>343</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>344</v>
       </c>
     </row>
     <row r="14" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -4430,10 +4427,10 @@
         <v>40</v>
       </c>
       <c r="C14" s="3" t="s">
+        <v>344</v>
+      </c>
+      <c r="D14" s="3" t="s">
         <v>345</v>
-      </c>
-      <c r="D14" s="3" t="s">
-        <v>346</v>
       </c>
     </row>
     <row r="15" spans="1:6" ht="29.1" customHeight="1" x14ac:dyDescent="0.25">
@@ -4445,13 +4442,13 @@
         <v>347</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>55</v>
+        <v>349</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A16" s="4">
         <f t="shared" si="0"/>
         <v>9</v>
@@ -4460,10 +4457,10 @@
         <v>348</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>349</v>
+        <v>54</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
     </row>
     <row r="17" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -4475,10 +4472,10 @@
         <v>43</v>
       </c>
       <c r="C17" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="D17" s="2" t="s">
         <v>59</v>
-      </c>
-      <c r="D17" s="2" t="s">
-        <v>60</v>
       </c>
     </row>
     <row r="18" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -4577,7 +4574,7 @@
   <sheetData>
     <row r="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A1" s="19" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B1" s="22"/>
       <c r="C1" s="22"/>
@@ -4585,7 +4582,7 @@
       <c r="E1" s="22"/>
       <c r="F1" s="21"/>
       <c r="G1" s="19" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="H1" s="22"/>
       <c r="I1" s="22"/>
@@ -4593,7 +4590,7 @@
       <c r="K1" s="22"/>
       <c r="L1" s="21"/>
       <c r="M1" s="17" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="N1" s="22"/>
       <c r="O1" s="22"/>
@@ -4697,7 +4694,7 @@
     </row>
     <row r="4" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A4" s="19" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B4" s="22"/>
       <c r="C4" s="22"/>
@@ -4705,7 +4702,7 @@
       <c r="E4" s="22"/>
       <c r="F4" s="21"/>
       <c r="G4" s="19" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="H4" s="22"/>
       <c r="I4" s="22"/>
@@ -4713,7 +4710,7 @@
       <c r="K4" s="22"/>
       <c r="L4" s="21"/>
       <c r="M4" s="17" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="N4" s="22"/>
       <c r="O4" s="22"/>
@@ -4852,10 +4849,10 @@
         <v>1</v>
       </c>
       <c r="B8" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="C8" s="3" t="s">
         <v>66</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>67</v>
       </c>
       <c r="D8" s="3" t="s">
         <v>36</v>
@@ -4864,10 +4861,10 @@
         <v>1</v>
       </c>
       <c r="H8" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="I8" s="3" t="s">
         <v>66</v>
-      </c>
-      <c r="I8" s="3" t="s">
-        <v>67</v>
       </c>
       <c r="J8" s="3" t="s">
         <v>36</v>
@@ -4876,10 +4873,10 @@
         <v>1</v>
       </c>
       <c r="N8" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="O8" s="3" t="s">
         <v>66</v>
-      </c>
-      <c r="O8" s="3" t="s">
-        <v>67</v>
       </c>
       <c r="P8" s="3" t="s">
         <v>36</v>
@@ -4905,10 +4902,10 @@
         <v>37</v>
       </c>
       <c r="I9" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="J9" s="3" t="s">
         <v>68</v>
-      </c>
-      <c r="J9" s="3" t="s">
-        <v>69</v>
       </c>
       <c r="M9" s="4">
         <v>2</v>
@@ -4928,37 +4925,37 @@
         <v>3</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C10" s="3" t="s">
         <v>41</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="G10" s="4">
         <v>3</v>
       </c>
       <c r="H10" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="I10" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="I10" s="3" t="s">
-        <v>71</v>
-      </c>
       <c r="J10" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="M10" s="4">
         <v>3</v>
       </c>
       <c r="N10" s="4" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="O10" s="3" t="s">
         <v>41</v>
       </c>
       <c r="P10" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="11" spans="1:25" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -4966,37 +4963,37 @@
         <v>4</v>
       </c>
       <c r="B11" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="C11" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="C11" s="3" t="s">
+      <c r="D11" s="3" t="s">
         <v>73</v>
-      </c>
-      <c r="D11" s="3" t="s">
-        <v>74</v>
       </c>
       <c r="G11" s="4">
         <v>4</v>
       </c>
       <c r="H11" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="I11" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="J11" s="3" t="s">
         <v>75</v>
-      </c>
-      <c r="I11" s="3" t="s">
-        <v>73</v>
-      </c>
-      <c r="J11" s="3" t="s">
-        <v>76</v>
       </c>
       <c r="M11" s="4">
         <v>4</v>
       </c>
       <c r="N11" s="4" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="O11" s="3" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="P11" s="3" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="12" spans="1:25" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -5004,25 +5001,25 @@
         <v>5</v>
       </c>
       <c r="B12" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="C12" s="3" t="s">
         <v>78</v>
       </c>
-      <c r="C12" s="3" t="s">
+      <c r="D12" s="3" t="s">
         <v>79</v>
-      </c>
-      <c r="D12" s="3" t="s">
-        <v>80</v>
       </c>
       <c r="M12" s="4">
         <v>5</v>
       </c>
       <c r="N12" s="4" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="O12" s="3" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="P12" s="3" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="13" spans="1:25" ht="29.1" customHeight="1" x14ac:dyDescent="0.25">
@@ -5030,25 +5027,25 @@
         <v>6</v>
       </c>
       <c r="B13" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="C13" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="C13" s="3" t="s">
+      <c r="D13" s="3" t="s">
         <v>85</v>
-      </c>
-      <c r="D13" s="3" t="s">
-        <v>86</v>
       </c>
       <c r="M13" s="4">
         <v>6</v>
       </c>
       <c r="N13" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="O13" s="3" t="s">
+        <v>322</v>
+      </c>
+      <c r="P13" s="3" t="s">
         <v>87</v>
-      </c>
-      <c r="O13" s="3" t="s">
-        <v>323</v>
-      </c>
-      <c r="P13" s="3" t="s">
-        <v>88</v>
       </c>
     </row>
     <row r="14" spans="1:25" x14ac:dyDescent="0.25">
@@ -5056,13 +5053,13 @@
         <v>7</v>
       </c>
       <c r="N14" t="s">
+        <v>46</v>
+      </c>
+      <c r="O14" t="s">
         <v>47</v>
       </c>
-      <c r="O14" t="s">
-        <v>48</v>
-      </c>
       <c r="P14" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="15" spans="1:25" ht="29.1" customHeight="1" x14ac:dyDescent="0.25">
@@ -5070,13 +5067,13 @@
         <v>8</v>
       </c>
       <c r="N15" s="4" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="O15" s="4" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="P15" s="3" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="16" spans="1:25" x14ac:dyDescent="0.25">
@@ -5084,13 +5081,13 @@
         <v>9</v>
       </c>
       <c r="N16" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="O16" t="s">
+        <v>49</v>
+      </c>
+      <c r="P16" t="s">
         <v>50</v>
-      </c>
-      <c r="P16" t="s">
-        <v>51</v>
       </c>
     </row>
     <row r="17" spans="13:16" ht="29.1" customHeight="1" x14ac:dyDescent="0.25">
@@ -5098,13 +5095,13 @@
         <v>10</v>
       </c>
       <c r="N17" s="4" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="O17" s="4" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="P17" s="3" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="18" spans="13:16" x14ac:dyDescent="0.25">
@@ -5112,13 +5109,13 @@
         <v>11</v>
       </c>
       <c r="N18" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="O18" t="s">
+        <v>51</v>
+      </c>
+      <c r="P18" t="s">
         <v>52</v>
-      </c>
-      <c r="P18" t="s">
-        <v>53</v>
       </c>
     </row>
     <row r="19" spans="13:16" x14ac:dyDescent="0.25">
@@ -5126,13 +5123,13 @@
         <v>12</v>
       </c>
       <c r="N19" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="O19" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="P19" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
     </row>
     <row r="20" spans="13:16" x14ac:dyDescent="0.25">
@@ -5140,13 +5137,13 @@
         <v>13</v>
       </c>
       <c r="N20" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="O20" t="s">
+        <v>51</v>
+      </c>
+      <c r="P20" t="s">
         <v>52</v>
-      </c>
-      <c r="P20" t="s">
-        <v>53</v>
       </c>
     </row>
     <row r="21" spans="13:16" x14ac:dyDescent="0.25">
@@ -5154,13 +5151,13 @@
         <v>14</v>
       </c>
       <c r="N21" t="s">
+        <v>55</v>
+      </c>
+      <c r="O21" t="s">
         <v>56</v>
       </c>
-      <c r="O21" t="s">
+      <c r="P21" t="s">
         <v>57</v>
-      </c>
-      <c r="P21" t="s">
-        <v>58</v>
       </c>
     </row>
     <row r="22" spans="13:16" x14ac:dyDescent="0.25">
@@ -5222,7 +5219,7 @@
   <sheetData>
     <row r="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A1" s="19" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B1" s="18"/>
       <c r="C1" s="18"/>
@@ -5230,7 +5227,7 @@
       <c r="E1" s="18"/>
       <c r="F1" s="21"/>
       <c r="G1" s="23" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="H1" s="18"/>
       <c r="I1" s="18"/>
@@ -5238,7 +5235,7 @@
       <c r="K1" s="18"/>
       <c r="L1" s="21"/>
       <c r="M1" s="17" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="N1" s="18"/>
       <c r="O1" s="18"/>
@@ -5330,7 +5327,7 @@
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A4" s="19" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="B4" s="18"/>
       <c r="C4" s="18"/>
@@ -5338,7 +5335,7 @@
       <c r="E4" s="18"/>
       <c r="F4" s="21"/>
       <c r="G4" s="23" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="H4" s="18"/>
       <c r="I4" s="18"/>
@@ -5346,7 +5343,7 @@
       <c r="K4" s="18"/>
       <c r="L4" s="21"/>
       <c r="M4" s="17" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="N4" s="18"/>
       <c r="O4" s="18"/>
@@ -5461,31 +5458,31 @@
         <v>1</v>
       </c>
       <c r="B8" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="D8" s="4" t="s">
         <v>94</v>
-      </c>
-      <c r="C8" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="D8" s="4" t="s">
-        <v>95</v>
       </c>
       <c r="G8">
         <v>1</v>
       </c>
       <c r="H8" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="M8">
         <v>1</v>
       </c>
       <c r="N8" s="4" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="O8" s="4" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="P8" s="4" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="9" spans="1:18" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -5493,34 +5490,34 @@
         <v>2</v>
       </c>
       <c r="B9" t="s">
+        <v>338</v>
+      </c>
+      <c r="C9" t="s">
         <v>339</v>
-      </c>
-      <c r="C9" t="s">
-        <v>340</v>
       </c>
       <c r="G9">
         <v>2</v>
       </c>
       <c r="H9" s="4" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="I9" s="4" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="J9" s="4" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="M9">
         <v>2</v>
       </c>
       <c r="N9" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="O9" s="3" t="s">
         <v>98</v>
       </c>
-      <c r="O9" s="3" t="s">
+      <c r="P9" s="3" t="s">
         <v>99</v>
-      </c>
-      <c r="P9" s="3" t="s">
-        <v>100</v>
       </c>
     </row>
     <row r="10" spans="1:18" ht="29.1" customHeight="1" x14ac:dyDescent="0.25">
@@ -5528,37 +5525,37 @@
         <v>3</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="G10">
         <v>3</v>
       </c>
       <c r="H10" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="I10" s="3" t="s">
         <v>98</v>
       </c>
-      <c r="I10" s="3" t="s">
+      <c r="J10" s="3" t="s">
         <v>99</v>
-      </c>
-      <c r="J10" s="3" t="s">
-        <v>100</v>
       </c>
       <c r="M10">
         <v>3</v>
       </c>
       <c r="N10" s="3" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="O10" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="P10" s="3" t="s">
         <v>102</v>
-      </c>
-      <c r="P10" s="3" t="s">
-        <v>103</v>
       </c>
     </row>
     <row r="11" spans="1:18" ht="30" x14ac:dyDescent="0.25">
@@ -5566,25 +5563,25 @@
         <v>4</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="M11">
         <v>4</v>
       </c>
       <c r="N11" t="s">
+        <v>106</v>
+      </c>
+      <c r="O11" t="s">
         <v>107</v>
       </c>
-      <c r="O11" t="s">
-        <v>108</v>
-      </c>
       <c r="P11" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="12" spans="1:18" x14ac:dyDescent="0.25">
@@ -5592,25 +5589,25 @@
         <v>5</v>
       </c>
       <c r="H12" t="s">
+        <v>104</v>
+      </c>
+      <c r="I12" t="s">
+        <v>325</v>
+      </c>
+      <c r="J12" t="s">
         <v>105</v>
-      </c>
-      <c r="I12" t="s">
-        <v>326</v>
-      </c>
-      <c r="J12" t="s">
-        <v>106</v>
       </c>
       <c r="M12">
         <v>5</v>
       </c>
       <c r="N12" t="s">
+        <v>110</v>
+      </c>
+      <c r="O12" t="s">
+        <v>108</v>
+      </c>
+      <c r="P12" t="s">
         <v>111</v>
-      </c>
-      <c r="O12" t="s">
-        <v>109</v>
-      </c>
-      <c r="P12" t="s">
-        <v>112</v>
       </c>
     </row>
     <row r="13" spans="1:18" x14ac:dyDescent="0.25">
@@ -5618,25 +5615,25 @@
         <v>6</v>
       </c>
       <c r="H13" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="I13" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="J13" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="M13">
         <v>6</v>
       </c>
       <c r="N13" t="s">
+        <v>46</v>
+      </c>
+      <c r="O13" t="s">
         <v>47</v>
       </c>
-      <c r="O13" t="s">
-        <v>48</v>
-      </c>
       <c r="P13" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="14" spans="1:18" x14ac:dyDescent="0.25">
@@ -5644,25 +5641,25 @@
         <v>7</v>
       </c>
       <c r="H14" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="I14" t="s">
+        <v>108</v>
+      </c>
+      <c r="J14" t="s">
         <v>109</v>
-      </c>
-      <c r="J14" t="s">
-        <v>110</v>
       </c>
       <c r="M14">
         <v>8</v>
       </c>
       <c r="N14" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="O14" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="P14" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="15" spans="1:18" x14ac:dyDescent="0.25">
@@ -5670,22 +5667,22 @@
         <v>8</v>
       </c>
       <c r="H15" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="I15" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="M15">
         <v>9</v>
       </c>
       <c r="N15" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="O15" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="P15" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="16" spans="1:18" x14ac:dyDescent="0.25">
@@ -5693,25 +5690,25 @@
         <v>9</v>
       </c>
       <c r="H16" t="s">
+        <v>328</v>
+      </c>
+      <c r="I16" t="s">
         <v>329</v>
       </c>
-      <c r="I16" t="s">
-        <v>330</v>
-      </c>
       <c r="J16" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="M16">
         <v>10</v>
       </c>
       <c r="N16" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="O16" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="P16" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="17" spans="7:10" x14ac:dyDescent="0.25">
@@ -5719,13 +5716,13 @@
         <v>10</v>
       </c>
       <c r="H17" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="I17" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="J17" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="18" spans="7:10" x14ac:dyDescent="0.25">
@@ -5733,13 +5730,13 @@
         <v>11</v>
       </c>
       <c r="H18" t="s">
+        <v>117</v>
+      </c>
+      <c r="I18" t="s">
         <v>118</v>
       </c>
-      <c r="I18" t="s">
-        <v>119</v>
-      </c>
       <c r="J18" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
     </row>
     <row r="19" spans="7:10" x14ac:dyDescent="0.25">
@@ -5747,13 +5744,13 @@
         <v>12</v>
       </c>
       <c r="H19" t="s">
+        <v>104</v>
+      </c>
+      <c r="I19" t="s">
+        <v>107</v>
+      </c>
+      <c r="J19" t="s">
         <v>105</v>
-      </c>
-      <c r="I19" t="s">
-        <v>108</v>
-      </c>
-      <c r="J19" t="s">
-        <v>106</v>
       </c>
     </row>
     <row r="20" spans="7:10" x14ac:dyDescent="0.25">
@@ -5761,10 +5758,10 @@
         <v>13</v>
       </c>
       <c r="H20" t="s">
+        <v>335</v>
+      </c>
+      <c r="I20" t="s">
         <v>336</v>
-      </c>
-      <c r="I20" t="s">
-        <v>337</v>
       </c>
     </row>
     <row r="21" spans="7:10" x14ac:dyDescent="0.25">
@@ -5772,13 +5769,13 @@
         <v>14</v>
       </c>
       <c r="H21" t="s">
+        <v>117</v>
+      </c>
+      <c r="I21" t="s">
         <v>118</v>
       </c>
-      <c r="I21" t="s">
-        <v>119</v>
-      </c>
       <c r="J21" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
   </sheetData>
@@ -5830,7 +5827,7 @@
   <sheetData>
     <row r="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A1" s="19" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B1" s="18"/>
       <c r="C1" s="18"/>
@@ -5838,7 +5835,7 @@
       <c r="E1" s="18"/>
       <c r="F1" s="21"/>
       <c r="G1" s="23" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="H1" s="18"/>
       <c r="I1" s="18"/>
@@ -5846,7 +5843,7 @@
       <c r="K1" s="18"/>
       <c r="L1" s="21"/>
       <c r="M1" s="17" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="N1" s="18"/>
       <c r="O1" s="18"/>
@@ -5938,7 +5935,7 @@
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A4" s="26" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B4" s="18"/>
       <c r="C4" s="18"/>
@@ -5946,7 +5943,7 @@
       <c r="E4" s="18"/>
       <c r="F4" s="21"/>
       <c r="G4" s="27" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="H4" s="18"/>
       <c r="I4" s="18"/>
@@ -5954,7 +5951,7 @@
       <c r="K4" s="18"/>
       <c r="L4" s="21"/>
       <c r="M4" s="25" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="N4" s="18"/>
       <c r="O4" s="18"/>
@@ -5984,7 +5981,7 @@
     </row>
     <row r="6" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A6" s="19" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B6" s="18"/>
       <c r="C6" s="18"/>
@@ -5992,7 +5989,7 @@
       <c r="E6" s="18"/>
       <c r="F6" s="21"/>
       <c r="G6" s="23" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="H6" s="18"/>
       <c r="I6" s="18"/>
@@ -6069,39 +6066,39 @@
         <v>1</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="F8" s="13"/>
       <c r="G8" s="3">
         <v>1</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="L8" s="13"/>
       <c r="M8" s="3">
         <v>1</v>
       </c>
       <c r="N8" s="3" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="O8" s="3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="P8" s="3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="9" spans="1:18" s="3" customFormat="1" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -6109,39 +6106,39 @@
         <v>2</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F9" s="13"/>
       <c r="G9" s="3">
         <v>2</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="L9" s="13"/>
       <c r="M9" s="3">
         <v>2</v>
       </c>
       <c r="N9" s="3" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="O9" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="P9" s="3" t="s">
         <v>126</v>
-      </c>
-      <c r="P9" s="3" t="s">
-        <v>127</v>
       </c>
     </row>
     <row r="10" spans="1:18" s="3" customFormat="1" ht="29.1" customHeight="1" x14ac:dyDescent="0.25">
@@ -6150,26 +6147,26 @@
         <v>3</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="I10" s="3" t="s">
+        <v>315</v>
+      </c>
+      <c r="J10" s="3" t="s">
         <v>316</v>
-      </c>
-      <c r="J10" s="3" t="s">
-        <v>317</v>
       </c>
       <c r="L10" s="13"/>
       <c r="M10" s="3">
         <v>3</v>
       </c>
       <c r="N10" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="O10" s="3" t="s">
         <v>128</v>
       </c>
-      <c r="O10" s="3" t="s">
+      <c r="P10" s="3" t="s">
         <v>129</v>
-      </c>
-      <c r="P10" s="3" t="s">
-        <v>130</v>
       </c>
     </row>
     <row r="11" spans="1:18" ht="29.1" customHeight="1" x14ac:dyDescent="0.25">
@@ -6177,25 +6174,25 @@
         <v>4</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="I11" s="3" t="s">
+        <v>317</v>
+      </c>
+      <c r="J11" s="3" t="s">
         <v>318</v>
-      </c>
-      <c r="J11" s="3" t="s">
-        <v>319</v>
       </c>
       <c r="M11" s="3">
         <v>4</v>
       </c>
       <c r="N11" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="O11" s="3" t="s">
         <v>131</v>
       </c>
-      <c r="O11" s="3" t="s">
+      <c r="P11" s="3" t="s">
         <v>132</v>
-      </c>
-      <c r="P11" s="3" t="s">
-        <v>133</v>
       </c>
     </row>
   </sheetData>
@@ -6246,7 +6243,7 @@
   <sheetData>
     <row r="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A1" s="19" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B1" s="18"/>
       <c r="C1" s="18"/>
@@ -6254,7 +6251,7 @@
       <c r="E1" s="18"/>
       <c r="F1" s="21"/>
       <c r="G1" s="17" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="H1" s="18"/>
       <c r="I1" s="18"/>
@@ -6262,7 +6259,7 @@
       <c r="K1" s="18"/>
       <c r="L1" s="18"/>
       <c r="M1" s="23" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="N1" s="18"/>
       <c r="O1" s="18"/>
@@ -6355,7 +6352,7 @@
     </row>
     <row r="4" spans="1:18" s="2" customFormat="1" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="26" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B4" s="20"/>
       <c r="C4" s="20"/>
@@ -6363,7 +6360,7 @@
       <c r="E4" s="20"/>
       <c r="F4" s="21"/>
       <c r="G4" s="25" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="H4" s="20"/>
       <c r="I4" s="20"/>
@@ -6371,7 +6368,7 @@
       <c r="K4" s="20"/>
       <c r="L4" s="20"/>
       <c r="M4" s="27" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="N4" s="20"/>
       <c r="O4" s="20"/>
@@ -6401,7 +6398,7 @@
     </row>
     <row r="6" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A6" s="19" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B6" s="18"/>
       <c r="C6" s="18"/>
@@ -6409,7 +6406,7 @@
       <c r="E6" s="18"/>
       <c r="F6" s="21"/>
       <c r="G6" s="17" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="H6" s="18"/>
       <c r="I6" s="18"/>
@@ -6417,7 +6414,7 @@
       <c r="K6" s="18"/>
       <c r="L6" s="18"/>
       <c r="M6" s="23" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="N6" s="18"/>
       <c r="O6" s="18"/>
@@ -6486,25 +6483,25 @@
         <v>1</v>
       </c>
       <c r="B8" t="s">
+        <v>141</v>
+      </c>
+      <c r="C8" t="s">
         <v>142</v>
       </c>
-      <c r="C8" t="s">
+      <c r="D8" t="s">
         <v>143</v>
-      </c>
-      <c r="D8" t="s">
-        <v>144</v>
       </c>
       <c r="G8">
         <v>1</v>
       </c>
       <c r="H8" t="s">
+        <v>144</v>
+      </c>
+      <c r="I8" t="s">
         <v>145</v>
       </c>
-      <c r="I8" t="s">
+      <c r="J8" t="s">
         <v>146</v>
-      </c>
-      <c r="J8" t="s">
-        <v>147</v>
       </c>
       <c r="M8" s="15">
         <v>1</v>
@@ -6516,25 +6513,25 @@
         <v>2</v>
       </c>
       <c r="B9" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C9" t="s">
+        <v>147</v>
+      </c>
+      <c r="D9" t="s">
         <v>148</v>
-      </c>
-      <c r="D9" t="s">
-        <v>149</v>
       </c>
       <c r="G9">
         <v>2</v>
       </c>
       <c r="H9" t="s">
+        <v>149</v>
+      </c>
+      <c r="I9" t="s">
         <v>150</v>
       </c>
-      <c r="I9" t="s">
+      <c r="J9" t="s">
         <v>151</v>
-      </c>
-      <c r="J9" t="s">
-        <v>152</v>
       </c>
       <c r="M9" s="15">
         <v>2</v>
@@ -6546,25 +6543,25 @@
         <v>3</v>
       </c>
       <c r="B10" t="s">
+        <v>152</v>
+      </c>
+      <c r="C10" t="s">
         <v>153</v>
       </c>
-      <c r="C10" t="s">
+      <c r="D10" t="s">
         <v>154</v>
-      </c>
-      <c r="D10" t="s">
-        <v>155</v>
       </c>
       <c r="G10">
         <v>3</v>
       </c>
       <c r="H10" t="s">
+        <v>155</v>
+      </c>
+      <c r="I10" t="s">
         <v>156</v>
       </c>
-      <c r="I10" t="s">
+      <c r="J10" t="s">
         <v>157</v>
-      </c>
-      <c r="J10" t="s">
-        <v>158</v>
       </c>
       <c r="M10" s="15">
         <v>3</v>
@@ -6576,25 +6573,25 @@
         <v>4</v>
       </c>
       <c r="B11" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="C11" s="2" t="s">
         <v>159</v>
       </c>
-      <c r="C11" s="2" t="s">
+      <c r="D11" t="s">
         <v>160</v>
-      </c>
-      <c r="D11" t="s">
-        <v>161</v>
       </c>
       <c r="G11">
         <v>4</v>
       </c>
       <c r="H11" t="s">
+        <v>161</v>
+      </c>
+      <c r="I11" t="s">
+        <v>66</v>
+      </c>
+      <c r="J11" t="s">
         <v>162</v>
-      </c>
-      <c r="I11" t="s">
-        <v>67</v>
-      </c>
-      <c r="J11" t="s">
-        <v>163</v>
       </c>
       <c r="M11" s="15">
         <v>4</v>
@@ -6609,10 +6606,10 @@
         <v>5</v>
       </c>
       <c r="B12" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="D12" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
     </row>
     <row r="13" spans="1:18" x14ac:dyDescent="0.25">
@@ -6620,13 +6617,13 @@
         <v>6</v>
       </c>
       <c r="B13" t="s">
+        <v>164</v>
+      </c>
+      <c r="C13" t="s">
         <v>165</v>
       </c>
-      <c r="C13" t="s">
-        <v>166</v>
-      </c>
       <c r="D13" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="14" spans="1:18" x14ac:dyDescent="0.25">
@@ -6634,10 +6631,10 @@
         <v>7</v>
       </c>
       <c r="B14" t="s">
+        <v>166</v>
+      </c>
+      <c r="C14" t="s">
         <v>167</v>
-      </c>
-      <c r="C14" t="s">
-        <v>168</v>
       </c>
     </row>
     <row r="15" spans="1:18" x14ac:dyDescent="0.25">
@@ -6645,13 +6642,13 @@
         <v>8</v>
       </c>
       <c r="B15" t="s">
+        <v>168</v>
+      </c>
+      <c r="C15" t="s">
+        <v>58</v>
+      </c>
+      <c r="D15" t="s">
         <v>169</v>
-      </c>
-      <c r="C15" t="s">
-        <v>59</v>
-      </c>
-      <c r="D15" t="s">
-        <v>170</v>
       </c>
     </row>
     <row r="16" spans="1:18" x14ac:dyDescent="0.25">
@@ -6659,13 +6656,13 @@
         <v>9</v>
       </c>
       <c r="B16" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C16" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="D16" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
@@ -6673,13 +6670,13 @@
         <v>10</v>
       </c>
       <c r="B17" t="s">
+        <v>171</v>
+      </c>
+      <c r="C17" t="s">
         <v>172</v>
       </c>
-      <c r="C17" t="s">
+      <c r="D17" t="s">
         <v>173</v>
-      </c>
-      <c r="D17" t="s">
-        <v>174</v>
       </c>
     </row>
     <row r="18" spans="1:4" ht="72.599999999999994" customHeight="1" x14ac:dyDescent="0.25">
@@ -6687,13 +6684,13 @@
         <v>11</v>
       </c>
       <c r="B18" t="s">
+        <v>174</v>
+      </c>
+      <c r="C18" s="2" t="s">
         <v>175</v>
       </c>
-      <c r="C18" s="2" t="s">
+      <c r="D18" s="2" t="s">
         <v>176</v>
-      </c>
-      <c r="D18" s="2" t="s">
-        <v>177</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
@@ -6701,13 +6698,13 @@
         <v>12</v>
       </c>
       <c r="B19" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C19" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D19" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
@@ -6715,13 +6712,13 @@
         <v>13</v>
       </c>
       <c r="B20" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C20" t="s">
         <v>44</v>
       </c>
       <c r="D20" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
@@ -6729,13 +6726,13 @@
         <v>14</v>
       </c>
       <c r="B21" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C21" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="D21" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
   </sheetData>
@@ -6792,7 +6789,7 @@
   <sheetData>
     <row r="1" spans="1:160" x14ac:dyDescent="0.25">
       <c r="A1" s="30" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B1" s="18"/>
       <c r="C1" s="18"/>
@@ -6800,7 +6797,7 @@
       <c r="E1" s="18"/>
       <c r="F1" s="18"/>
       <c r="H1" s="30" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="I1" s="18"/>
       <c r="J1" s="18"/>
@@ -6808,7 +6805,7 @@
       <c r="L1" s="18"/>
       <c r="M1" s="18"/>
       <c r="O1" s="30" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="P1" s="18"/>
       <c r="Q1" s="18"/>
@@ -6816,7 +6813,7 @@
       <c r="S1" s="18"/>
       <c r="T1" s="18"/>
       <c r="V1" s="30" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="W1" s="18"/>
       <c r="X1" s="18"/>
@@ -6824,7 +6821,7 @@
       <c r="Z1" s="18"/>
       <c r="AA1" s="18"/>
       <c r="AC1" s="30" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="AD1" s="18"/>
       <c r="AE1" s="18"/>
@@ -6832,7 +6829,7 @@
       <c r="AG1" s="18"/>
       <c r="AH1" s="18"/>
       <c r="AJ1" s="30" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="AK1" s="18"/>
       <c r="AL1" s="18"/>
@@ -6840,7 +6837,7 @@
       <c r="AN1" s="18"/>
       <c r="AO1" s="18"/>
       <c r="AQ1" s="30" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="AR1" s="18"/>
       <c r="AS1" s="18"/>
@@ -6848,7 +6845,7 @@
       <c r="AU1" s="18"/>
       <c r="AV1" s="18"/>
       <c r="AX1" s="30" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="AY1" s="18"/>
       <c r="AZ1" s="18"/>
@@ -6856,7 +6853,7 @@
       <c r="BB1" s="18"/>
       <c r="BC1" s="18"/>
       <c r="BE1" s="30" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="BF1" s="18"/>
       <c r="BG1" s="18"/>
@@ -6864,7 +6861,7 @@
       <c r="BI1" s="18"/>
       <c r="BJ1" s="18"/>
       <c r="BL1" s="30" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="BM1" s="18"/>
       <c r="BN1" s="18"/>
@@ -6872,7 +6869,7 @@
       <c r="BP1" s="18"/>
       <c r="BQ1" s="18"/>
       <c r="BS1" s="30" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="BT1" s="18"/>
       <c r="BU1" s="18"/>
@@ -6880,7 +6877,7 @@
       <c r="BW1" s="18"/>
       <c r="BX1" s="18"/>
       <c r="BZ1" s="30" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="CA1" s="18"/>
       <c r="CB1" s="18"/>
@@ -6888,7 +6885,7 @@
       <c r="CD1" s="18"/>
       <c r="CE1" s="18"/>
       <c r="CG1" s="30" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="CH1" s="18"/>
       <c r="CI1" s="18"/>
@@ -6896,7 +6893,7 @@
       <c r="CK1" s="18"/>
       <c r="CL1" s="18"/>
       <c r="CN1" s="30" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="CO1" s="18"/>
       <c r="CP1" s="18"/>
@@ -6904,7 +6901,7 @@
       <c r="CR1" s="18"/>
       <c r="CS1" s="18"/>
       <c r="CU1" s="30" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="CV1" s="18"/>
       <c r="CW1" s="18"/>
@@ -6912,7 +6909,7 @@
       <c r="CY1" s="18"/>
       <c r="CZ1" s="18"/>
       <c r="DB1" s="30" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="DC1" s="18"/>
       <c r="DD1" s="18"/>
@@ -6920,7 +6917,7 @@
       <c r="DF1" s="18"/>
       <c r="DG1" s="18"/>
       <c r="DI1" s="30" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="DJ1" s="18"/>
       <c r="DK1" s="18"/>
@@ -6928,7 +6925,7 @@
       <c r="DM1" s="18"/>
       <c r="DN1" s="18"/>
       <c r="DP1" s="30" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="DQ1" s="18"/>
       <c r="DR1" s="18"/>
@@ -6936,7 +6933,7 @@
       <c r="DT1" s="18"/>
       <c r="DU1" s="18"/>
       <c r="DW1" s="30" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="DX1" s="18"/>
       <c r="DY1" s="18"/>
@@ -6944,7 +6941,7 @@
       <c r="EA1" s="18"/>
       <c r="EB1" s="18"/>
       <c r="ED1" s="30" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="EE1" s="18"/>
       <c r="EF1" s="18"/>
@@ -6952,7 +6949,7 @@
       <c r="EH1" s="18"/>
       <c r="EI1" s="18"/>
       <c r="EK1" s="30" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="EL1" s="18"/>
       <c r="EM1" s="18"/>
@@ -6960,7 +6957,7 @@
       <c r="EO1" s="18"/>
       <c r="EP1" s="18"/>
       <c r="ER1" s="30" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="ES1" s="18"/>
       <c r="ET1" s="18"/>
@@ -6968,7 +6965,7 @@
       <c r="EV1" s="18"/>
       <c r="EW1" s="18"/>
       <c r="EY1" s="30" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="EZ1" s="18"/>
       <c r="FA1" s="18"/>
@@ -7561,230 +7558,230 @@
     </row>
     <row r="6" spans="1:160" x14ac:dyDescent="0.25">
       <c r="A6" s="16" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B6" s="29" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="C6" s="18"/>
       <c r="D6" s="18"/>
       <c r="E6" s="18"/>
       <c r="F6" s="18"/>
       <c r="H6" s="16" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="I6" s="29" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="J6" s="18"/>
       <c r="K6" s="18"/>
       <c r="L6" s="18"/>
       <c r="M6" s="18"/>
       <c r="O6" s="16" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="P6" s="29" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="Q6" s="18"/>
       <c r="R6" s="18"/>
       <c r="S6" s="18"/>
       <c r="T6" s="18"/>
       <c r="V6" s="16" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="W6" s="29" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="X6" s="18"/>
       <c r="Y6" s="18"/>
       <c r="Z6" s="18"/>
       <c r="AA6" s="18"/>
       <c r="AC6" s="16" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="AD6" s="29" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="AE6" s="18"/>
       <c r="AF6" s="18"/>
       <c r="AG6" s="18"/>
       <c r="AH6" s="18"/>
       <c r="AJ6" s="16" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="AK6" s="29" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="AL6" s="18"/>
       <c r="AM6" s="18"/>
       <c r="AN6" s="18"/>
       <c r="AO6" s="18"/>
       <c r="AQ6" s="16" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="AR6" s="29" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="AS6" s="18"/>
       <c r="AT6" s="18"/>
       <c r="AU6" s="18"/>
       <c r="AV6" s="18"/>
       <c r="AX6" s="16" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="AY6" s="29" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="AZ6" s="18"/>
       <c r="BA6" s="18"/>
       <c r="BB6" s="18"/>
       <c r="BC6" s="18"/>
       <c r="BE6" s="16" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="BF6" s="29" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="BG6" s="18"/>
       <c r="BH6" s="18"/>
       <c r="BI6" s="18"/>
       <c r="BJ6" s="18"/>
       <c r="BL6" s="16" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="BM6" s="29" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="BN6" s="18"/>
       <c r="BO6" s="18"/>
       <c r="BP6" s="18"/>
       <c r="BQ6" s="18"/>
       <c r="BS6" s="16" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="BT6" s="29" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="BU6" s="18"/>
       <c r="BV6" s="18"/>
       <c r="BW6" s="18"/>
       <c r="BX6" s="18"/>
       <c r="BZ6" s="16" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="CA6" s="29" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="CB6" s="18"/>
       <c r="CC6" s="18"/>
       <c r="CD6" s="18"/>
       <c r="CE6" s="18"/>
       <c r="CG6" s="16" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="CH6" s="29" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="CI6" s="18"/>
       <c r="CJ6" s="18"/>
       <c r="CK6" s="18"/>
       <c r="CL6" s="18"/>
       <c r="CN6" s="16" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="CO6" s="29" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="CP6" s="18"/>
       <c r="CQ6" s="18"/>
       <c r="CR6" s="18"/>
       <c r="CS6" s="18"/>
       <c r="CU6" s="16" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="CV6" s="29" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="CW6" s="18"/>
       <c r="CX6" s="18"/>
       <c r="CY6" s="18"/>
       <c r="CZ6" s="18"/>
       <c r="DB6" s="16" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="DC6" s="29" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="DD6" s="18"/>
       <c r="DE6" s="18"/>
       <c r="DF6" s="18"/>
       <c r="DG6" s="18"/>
       <c r="DI6" s="16" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="DJ6" s="29" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="DK6" s="18"/>
       <c r="DL6" s="18"/>
       <c r="DM6" s="18"/>
       <c r="DN6" s="18"/>
       <c r="DP6" s="16" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="DQ6" s="29" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="DR6" s="18"/>
       <c r="DS6" s="18"/>
       <c r="DT6" s="18"/>
       <c r="DU6" s="18"/>
       <c r="DW6" s="16" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="DX6" s="29" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="DY6" s="18"/>
       <c r="DZ6" s="18"/>
       <c r="EA6" s="18"/>
       <c r="EB6" s="18"/>
       <c r="ED6" s="16" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="EE6" s="29" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="EF6" s="18"/>
       <c r="EG6" s="18"/>
       <c r="EH6" s="18"/>
       <c r="EI6" s="18"/>
       <c r="EK6" s="16" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="EL6" s="29" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="EM6" s="18"/>
       <c r="EN6" s="18"/>
       <c r="EO6" s="18"/>
       <c r="EP6" s="18"/>
       <c r="ER6" s="16" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="ES6" s="29" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="ET6" s="18"/>
       <c r="EU6" s="18"/>
       <c r="EV6" s="18"/>
       <c r="EW6" s="18"/>
       <c r="EY6" s="16" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="EZ6" s="29" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="FA6" s="18"/>
       <c r="FB6" s="18"/>
@@ -7796,7 +7793,7 @@
         <v>24</v>
       </c>
       <c r="B7" s="29" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="C7" s="18"/>
       <c r="D7" s="18"/>
@@ -7806,7 +7803,7 @@
         <v>24</v>
       </c>
       <c r="I7" s="29" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="J7" s="18"/>
       <c r="K7" s="18"/>
@@ -7816,7 +7813,7 @@
         <v>24</v>
       </c>
       <c r="P7" s="29" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="Q7" s="18"/>
       <c r="R7" s="18"/>
@@ -7826,7 +7823,7 @@
         <v>24</v>
       </c>
       <c r="W7" s="29" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="X7" s="18"/>
       <c r="Y7" s="18"/>
@@ -7836,7 +7833,7 @@
         <v>24</v>
       </c>
       <c r="AD7" s="29" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="AE7" s="18"/>
       <c r="AF7" s="18"/>
@@ -7846,7 +7843,7 @@
         <v>24</v>
       </c>
       <c r="AK7" s="29" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="AL7" s="18"/>
       <c r="AM7" s="18"/>
@@ -7856,7 +7853,7 @@
         <v>24</v>
       </c>
       <c r="AR7" s="29" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="AS7" s="18"/>
       <c r="AT7" s="18"/>
@@ -7866,7 +7863,7 @@
         <v>24</v>
       </c>
       <c r="AY7" s="29" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="AZ7" s="18"/>
       <c r="BA7" s="18"/>
@@ -7876,7 +7873,7 @@
         <v>24</v>
       </c>
       <c r="BF7" s="29" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="BG7" s="18"/>
       <c r="BH7" s="18"/>
@@ -7886,7 +7883,7 @@
         <v>24</v>
       </c>
       <c r="BM7" s="29" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="BN7" s="18"/>
       <c r="BO7" s="18"/>
@@ -7896,7 +7893,7 @@
         <v>24</v>
       </c>
       <c r="BT7" s="29" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="BU7" s="18"/>
       <c r="BV7" s="18"/>
@@ -7906,7 +7903,7 @@
         <v>24</v>
       </c>
       <c r="CA7" s="29" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="CB7" s="18"/>
       <c r="CC7" s="18"/>
@@ -7916,7 +7913,7 @@
         <v>24</v>
       </c>
       <c r="CH7" s="29" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="CI7" s="18"/>
       <c r="CJ7" s="18"/>
@@ -7926,7 +7923,7 @@
         <v>24</v>
       </c>
       <c r="CO7" s="29" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="CP7" s="18"/>
       <c r="CQ7" s="18"/>
@@ -7936,7 +7933,7 @@
         <v>24</v>
       </c>
       <c r="CV7" s="29" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="CW7" s="18"/>
       <c r="CX7" s="18"/>
@@ -7946,7 +7943,7 @@
         <v>24</v>
       </c>
       <c r="DC7" s="29" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="DD7" s="18"/>
       <c r="DE7" s="18"/>
@@ -7956,7 +7953,7 @@
         <v>24</v>
       </c>
       <c r="DJ7" s="29" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="DK7" s="18"/>
       <c r="DL7" s="18"/>
@@ -7966,7 +7963,7 @@
         <v>24</v>
       </c>
       <c r="DQ7" s="29" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="DR7" s="18"/>
       <c r="DS7" s="18"/>
@@ -7976,7 +7973,7 @@
         <v>24</v>
       </c>
       <c r="DX7" s="29" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="DY7" s="18"/>
       <c r="DZ7" s="18"/>
@@ -7986,7 +7983,7 @@
         <v>24</v>
       </c>
       <c r="EE7" s="29" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="EF7" s="18"/>
       <c r="EG7" s="18"/>
@@ -7996,7 +7993,7 @@
         <v>24</v>
       </c>
       <c r="EL7" s="29" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="EM7" s="18"/>
       <c r="EN7" s="18"/>
@@ -8006,7 +8003,7 @@
         <v>24</v>
       </c>
       <c r="ES7" s="29" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="ET7" s="18"/>
       <c r="EU7" s="18"/>
@@ -8016,7 +8013,7 @@
         <v>24</v>
       </c>
       <c r="EZ7" s="29" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="FA7" s="18"/>
       <c r="FB7" s="18"/>
@@ -8441,880 +8438,880 @@
     </row>
     <row r="9" spans="1:160" ht="29.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="16" t="s">
+        <v>225</v>
+      </c>
+      <c r="B9" s="16" t="s">
         <v>226</v>
       </c>
-      <c r="B9" s="16" t="s">
+      <c r="C9" s="16" t="s">
         <v>227</v>
       </c>
-      <c r="C9" s="16" t="s">
+      <c r="D9" s="16" t="s">
         <v>228</v>
-      </c>
-      <c r="D9" s="16" t="s">
-        <v>229</v>
       </c>
       <c r="E9" s="16"/>
       <c r="F9" s="16"/>
       <c r="H9" s="16" t="s">
+        <v>225</v>
+      </c>
+      <c r="I9" s="16" t="s">
         <v>226</v>
       </c>
-      <c r="I9" s="16" t="s">
+      <c r="J9" s="16" t="s">
         <v>227</v>
       </c>
-      <c r="J9" s="16" t="s">
+      <c r="K9" s="16" t="s">
         <v>228</v>
-      </c>
-      <c r="K9" s="16" t="s">
-        <v>229</v>
       </c>
       <c r="L9" s="16"/>
       <c r="M9" s="16"/>
       <c r="O9" s="16" t="s">
+        <v>225</v>
+      </c>
+      <c r="P9" s="16" t="s">
         <v>226</v>
       </c>
-      <c r="P9" s="16" t="s">
+      <c r="Q9" s="16" t="s">
         <v>227</v>
       </c>
-      <c r="Q9" s="16" t="s">
+      <c r="R9" s="16" t="s">
         <v>228</v>
-      </c>
-      <c r="R9" s="16" t="s">
-        <v>229</v>
       </c>
       <c r="S9" s="16"/>
       <c r="T9" s="16"/>
       <c r="V9" s="16" t="s">
+        <v>225</v>
+      </c>
+      <c r="W9" s="16" t="s">
         <v>226</v>
       </c>
-      <c r="W9" s="16" t="s">
+      <c r="X9" s="16" t="s">
         <v>227</v>
       </c>
-      <c r="X9" s="16" t="s">
+      <c r="Y9" s="16" t="s">
         <v>228</v>
-      </c>
-      <c r="Y9" s="16" t="s">
-        <v>229</v>
       </c>
       <c r="Z9" s="16"/>
       <c r="AA9" s="16"/>
       <c r="AC9" s="16" t="s">
+        <v>225</v>
+      </c>
+      <c r="AD9" s="16" t="s">
         <v>226</v>
       </c>
-      <c r="AD9" s="16" t="s">
+      <c r="AE9" s="16" t="s">
         <v>227</v>
       </c>
-      <c r="AE9" s="16" t="s">
+      <c r="AF9" s="16" t="s">
         <v>228</v>
-      </c>
-      <c r="AF9" s="16" t="s">
-        <v>229</v>
       </c>
       <c r="AG9" s="16"/>
       <c r="AH9" s="16"/>
       <c r="AJ9" s="16" t="s">
+        <v>225</v>
+      </c>
+      <c r="AK9" s="16" t="s">
         <v>226</v>
       </c>
-      <c r="AK9" s="16" t="s">
+      <c r="AL9" s="16" t="s">
         <v>227</v>
       </c>
-      <c r="AL9" s="16" t="s">
+      <c r="AM9" s="16" t="s">
         <v>228</v>
-      </c>
-      <c r="AM9" s="16" t="s">
-        <v>229</v>
       </c>
       <c r="AN9" s="16"/>
       <c r="AO9" s="16"/>
       <c r="AQ9" s="16" t="s">
+        <v>225</v>
+      </c>
+      <c r="AR9" s="16" t="s">
         <v>226</v>
       </c>
-      <c r="AR9" s="16" t="s">
+      <c r="AS9" s="16" t="s">
         <v>227</v>
       </c>
-      <c r="AS9" s="16" t="s">
+      <c r="AT9" s="16" t="s">
         <v>228</v>
-      </c>
-      <c r="AT9" s="16" t="s">
-        <v>229</v>
       </c>
       <c r="AU9" s="16"/>
       <c r="AV9" s="16"/>
       <c r="AX9" s="16" t="s">
+        <v>225</v>
+      </c>
+      <c r="AY9" s="16" t="s">
         <v>226</v>
       </c>
-      <c r="AY9" s="16" t="s">
+      <c r="AZ9" s="16" t="s">
         <v>227</v>
       </c>
-      <c r="AZ9" s="16" t="s">
+      <c r="BA9" s="16" t="s">
         <v>228</v>
-      </c>
-      <c r="BA9" s="16" t="s">
-        <v>229</v>
       </c>
       <c r="BB9" s="16"/>
       <c r="BC9" s="16"/>
       <c r="BE9" s="16" t="s">
+        <v>225</v>
+      </c>
+      <c r="BF9" s="16" t="s">
         <v>226</v>
       </c>
-      <c r="BF9" s="16" t="s">
+      <c r="BG9" s="16" t="s">
         <v>227</v>
       </c>
-      <c r="BG9" s="16" t="s">
+      <c r="BH9" s="16" t="s">
         <v>228</v>
-      </c>
-      <c r="BH9" s="16" t="s">
-        <v>229</v>
       </c>
       <c r="BI9" s="16"/>
       <c r="BJ9" s="16"/>
       <c r="BL9" s="16" t="s">
+        <v>225</v>
+      </c>
+      <c r="BM9" s="16" t="s">
         <v>226</v>
       </c>
-      <c r="BM9" s="16" t="s">
+      <c r="BN9" s="16" t="s">
         <v>227</v>
       </c>
-      <c r="BN9" s="16" t="s">
+      <c r="BO9" s="16" t="s">
         <v>228</v>
-      </c>
-      <c r="BO9" s="16" t="s">
-        <v>229</v>
       </c>
       <c r="BP9" s="16"/>
       <c r="BQ9" s="16"/>
       <c r="BS9" s="16" t="s">
+        <v>225</v>
+      </c>
+      <c r="BT9" s="16" t="s">
         <v>226</v>
       </c>
-      <c r="BT9" s="16" t="s">
+      <c r="BU9" s="16" t="s">
         <v>227</v>
       </c>
-      <c r="BU9" s="16" t="s">
+      <c r="BV9" s="16" t="s">
         <v>228</v>
-      </c>
-      <c r="BV9" s="16" t="s">
-        <v>229</v>
       </c>
       <c r="BW9" s="16"/>
       <c r="BX9" s="16"/>
       <c r="BZ9" s="16" t="s">
+        <v>225</v>
+      </c>
+      <c r="CA9" s="16" t="s">
         <v>226</v>
       </c>
-      <c r="CA9" s="16" t="s">
+      <c r="CB9" s="16" t="s">
         <v>227</v>
       </c>
-      <c r="CB9" s="16" t="s">
+      <c r="CC9" s="16" t="s">
         <v>228</v>
-      </c>
-      <c r="CC9" s="16" t="s">
-        <v>229</v>
       </c>
       <c r="CD9" s="16"/>
       <c r="CE9" s="16"/>
       <c r="CG9" s="16" t="s">
+        <v>225</v>
+      </c>
+      <c r="CH9" s="16" t="s">
         <v>226</v>
       </c>
-      <c r="CH9" s="16" t="s">
+      <c r="CI9" s="16" t="s">
         <v>227</v>
       </c>
-      <c r="CI9" s="16" t="s">
+      <c r="CJ9" s="16" t="s">
         <v>228</v>
-      </c>
-      <c r="CJ9" s="16" t="s">
-        <v>229</v>
       </c>
       <c r="CK9" s="16"/>
       <c r="CL9" s="16"/>
       <c r="CN9" s="16" t="s">
+        <v>225</v>
+      </c>
+      <c r="CO9" s="16" t="s">
         <v>226</v>
       </c>
-      <c r="CO9" s="16" t="s">
+      <c r="CP9" s="16" t="s">
         <v>227</v>
       </c>
-      <c r="CP9" s="16" t="s">
+      <c r="CQ9" s="16" t="s">
         <v>228</v>
-      </c>
-      <c r="CQ9" s="16" t="s">
-        <v>229</v>
       </c>
       <c r="CR9" s="16"/>
       <c r="CS9" s="16"/>
       <c r="CU9" s="16" t="s">
+        <v>225</v>
+      </c>
+      <c r="CV9" s="16" t="s">
         <v>226</v>
       </c>
-      <c r="CV9" s="16" t="s">
+      <c r="CW9" s="16" t="s">
         <v>227</v>
       </c>
-      <c r="CW9" s="16" t="s">
+      <c r="CX9" s="16" t="s">
         <v>228</v>
-      </c>
-      <c r="CX9" s="16" t="s">
-        <v>229</v>
       </c>
       <c r="CY9" s="16"/>
       <c r="CZ9" s="16"/>
       <c r="DB9" s="16" t="s">
+        <v>225</v>
+      </c>
+      <c r="DC9" s="16" t="s">
         <v>226</v>
       </c>
-      <c r="DC9" s="16" t="s">
+      <c r="DD9" s="16" t="s">
         <v>227</v>
       </c>
-      <c r="DD9" s="16" t="s">
+      <c r="DE9" s="16" t="s">
         <v>228</v>
-      </c>
-      <c r="DE9" s="16" t="s">
-        <v>229</v>
       </c>
       <c r="DF9" s="16"/>
       <c r="DG9" s="16"/>
       <c r="DI9" s="16" t="s">
+        <v>225</v>
+      </c>
+      <c r="DJ9" s="16" t="s">
         <v>226</v>
       </c>
-      <c r="DJ9" s="16" t="s">
+      <c r="DK9" s="16" t="s">
         <v>227</v>
       </c>
-      <c r="DK9" s="16" t="s">
+      <c r="DL9" s="16" t="s">
         <v>228</v>
-      </c>
-      <c r="DL9" s="16" t="s">
-        <v>229</v>
       </c>
       <c r="DM9" s="16"/>
       <c r="DN9" s="16"/>
       <c r="DP9" s="16" t="s">
+        <v>225</v>
+      </c>
+      <c r="DQ9" s="16" t="s">
         <v>226</v>
       </c>
-      <c r="DQ9" s="16" t="s">
+      <c r="DR9" s="16" t="s">
         <v>227</v>
       </c>
-      <c r="DR9" s="16" t="s">
+      <c r="DS9" s="16" t="s">
         <v>228</v>
-      </c>
-      <c r="DS9" s="16" t="s">
-        <v>229</v>
       </c>
       <c r="DT9" s="16"/>
       <c r="DU9" s="16"/>
       <c r="DW9" s="16" t="s">
+        <v>225</v>
+      </c>
+      <c r="DX9" s="16" t="s">
         <v>226</v>
       </c>
-      <c r="DX9" s="16" t="s">
+      <c r="DY9" s="16" t="s">
         <v>227</v>
       </c>
-      <c r="DY9" s="16" t="s">
+      <c r="DZ9" s="16" t="s">
         <v>228</v>
-      </c>
-      <c r="DZ9" s="16" t="s">
-        <v>229</v>
       </c>
       <c r="EA9" s="16"/>
       <c r="EB9" s="16"/>
       <c r="ED9" s="16" t="s">
+        <v>225</v>
+      </c>
+      <c r="EE9" s="16" t="s">
         <v>226</v>
       </c>
-      <c r="EE9" s="16" t="s">
+      <c r="EF9" s="16" t="s">
         <v>227</v>
       </c>
-      <c r="EF9" s="16" t="s">
+      <c r="EG9" s="16" t="s">
         <v>228</v>
-      </c>
-      <c r="EG9" s="16" t="s">
-        <v>229</v>
       </c>
       <c r="EH9" s="16"/>
       <c r="EI9" s="16"/>
       <c r="EK9" s="16" t="s">
+        <v>225</v>
+      </c>
+      <c r="EL9" s="16" t="s">
         <v>226</v>
       </c>
-      <c r="EL9" s="16" t="s">
+      <c r="EM9" s="16" t="s">
         <v>227</v>
       </c>
-      <c r="EM9" s="16" t="s">
+      <c r="EN9" s="16" t="s">
         <v>228</v>
-      </c>
-      <c r="EN9" s="16" t="s">
-        <v>229</v>
       </c>
       <c r="EO9" s="16"/>
       <c r="EP9" s="16"/>
       <c r="ER9" s="16" t="s">
+        <v>225</v>
+      </c>
+      <c r="ES9" s="16" t="s">
         <v>226</v>
       </c>
-      <c r="ES9" s="16" t="s">
+      <c r="ET9" s="16" t="s">
         <v>227</v>
       </c>
-      <c r="ET9" s="16" t="s">
+      <c r="EU9" s="16" t="s">
         <v>228</v>
-      </c>
-      <c r="EU9" s="16" t="s">
-        <v>229</v>
       </c>
       <c r="EV9" s="16"/>
       <c r="EW9" s="16"/>
       <c r="EY9" s="16" t="s">
+        <v>225</v>
+      </c>
+      <c r="EZ9" s="16" t="s">
         <v>226</v>
       </c>
-      <c r="EZ9" s="16" t="s">
+      <c r="FA9" s="16" t="s">
         <v>227</v>
       </c>
-      <c r="FA9" s="16" t="s">
+      <c r="FB9" s="16" t="s">
         <v>228</v>
-      </c>
-      <c r="FB9" s="16" t="s">
-        <v>229</v>
       </c>
       <c r="FC9" s="16"/>
       <c r="FD9" s="16"/>
     </row>
     <row r="10" spans="1:160" ht="29.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="16" t="s">
+        <v>229</v>
+      </c>
+      <c r="B10" s="16" t="s">
         <v>230</v>
-      </c>
-      <c r="B10" s="16" t="s">
-        <v>231</v>
       </c>
       <c r="C10" s="16"/>
       <c r="D10" s="16" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="E10" s="16"/>
       <c r="F10" s="16"/>
       <c r="H10" s="16" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="I10" s="16" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="J10" s="16"/>
       <c r="K10" s="16" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="L10" s="16"/>
       <c r="M10" s="16"/>
       <c r="O10" s="16" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="P10" s="16" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="Q10" s="16"/>
       <c r="R10" s="16" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="S10" s="16"/>
       <c r="T10" s="16"/>
       <c r="V10" s="16" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="W10" s="16" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="X10" s="16"/>
       <c r="Y10" s="16" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="Z10" s="16"/>
       <c r="AA10" s="16"/>
       <c r="AC10" s="16" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="AD10" s="16" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="AE10" s="16"/>
       <c r="AF10" s="16" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="AG10" s="16"/>
       <c r="AH10" s="16"/>
       <c r="AJ10" s="16" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="AK10" s="16" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="AL10" s="16"/>
       <c r="AM10" s="16" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="AN10" s="16"/>
       <c r="AO10" s="16"/>
       <c r="AQ10" s="16" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="AR10" s="16" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="AS10" s="16"/>
       <c r="AT10" s="16" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="AU10" s="16"/>
       <c r="AV10" s="16"/>
       <c r="AX10" s="16" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="AY10" s="16" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="AZ10" s="16"/>
       <c r="BA10" s="16" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="BB10" s="16"/>
       <c r="BC10" s="16"/>
       <c r="BE10" s="16" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="BF10" s="16" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="BG10" s="16"/>
       <c r="BH10" s="16" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="BI10" s="16"/>
       <c r="BJ10" s="16"/>
       <c r="BL10" s="16" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="BM10" s="16" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="BN10" s="16"/>
       <c r="BO10" s="16" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="BP10" s="16"/>
       <c r="BQ10" s="16"/>
       <c r="BS10" s="16" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="BT10" s="16" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="BU10" s="16"/>
       <c r="BV10" s="16" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="BW10" s="16"/>
       <c r="BX10" s="16"/>
       <c r="BZ10" s="16" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="CA10" s="16" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="CB10" s="16"/>
       <c r="CC10" s="16" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="CD10" s="16"/>
       <c r="CE10" s="16"/>
       <c r="CG10" s="16" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="CH10" s="16" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="CI10" s="16"/>
       <c r="CJ10" s="16" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="CK10" s="16"/>
       <c r="CL10" s="16"/>
       <c r="CN10" s="16" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="CO10" s="16" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="CP10" s="16"/>
       <c r="CQ10" s="16" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="CR10" s="16"/>
       <c r="CS10" s="16"/>
       <c r="CU10" s="16" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="CV10" s="16" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="CW10" s="16"/>
       <c r="CX10" s="16" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="CY10" s="16"/>
       <c r="CZ10" s="16"/>
       <c r="DB10" s="16" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="DC10" s="16" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="DD10" s="16"/>
       <c r="DE10" s="16" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="DF10" s="16"/>
       <c r="DG10" s="16"/>
       <c r="DI10" s="16" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="DJ10" s="16" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="DK10" s="16"/>
       <c r="DL10" s="16" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="DM10" s="16"/>
       <c r="DN10" s="16"/>
       <c r="DP10" s="16" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="DQ10" s="16" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="DR10" s="16"/>
       <c r="DS10" s="16" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="DT10" s="16"/>
       <c r="DU10" s="16"/>
       <c r="DW10" s="16" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="DX10" s="16" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="DY10" s="16"/>
       <c r="DZ10" s="16" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="EA10" s="16"/>
       <c r="EB10" s="16"/>
       <c r="ED10" s="16" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="EE10" s="16" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="EF10" s="16"/>
       <c r="EG10" s="16" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="EH10" s="16"/>
       <c r="EI10" s="16"/>
       <c r="EK10" s="16" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="EL10" s="16" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="EM10" s="16"/>
       <c r="EN10" s="16" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="EO10" s="16"/>
       <c r="EP10" s="16"/>
       <c r="ER10" s="16" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="ES10" s="16" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="ET10" s="16"/>
       <c r="EU10" s="16" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="EV10" s="16"/>
       <c r="EW10" s="16"/>
       <c r="EY10" s="16" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="EZ10" s="16" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="FA10" s="16"/>
       <c r="FB10" s="16" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="FC10" s="16"/>
       <c r="FD10" s="16"/>
     </row>
     <row r="11" spans="1:160" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="16" t="s">
+        <v>244</v>
+      </c>
+      <c r="B11" s="16" t="s">
         <v>245</v>
-      </c>
-      <c r="B11" s="16" t="s">
-        <v>246</v>
       </c>
       <c r="C11" s="16"/>
       <c r="D11" s="16" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="E11" s="16"/>
       <c r="F11" s="16"/>
       <c r="H11" s="16" t="s">
+        <v>244</v>
+      </c>
+      <c r="I11" s="16" t="s">
         <v>245</v>
-      </c>
-      <c r="I11" s="16" t="s">
-        <v>246</v>
       </c>
       <c r="J11" s="16"/>
       <c r="K11" s="16" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="L11" s="16"/>
       <c r="M11" s="16"/>
       <c r="O11" s="16" t="s">
+        <v>244</v>
+      </c>
+      <c r="P11" s="16" t="s">
         <v>245</v>
-      </c>
-      <c r="P11" s="16" t="s">
-        <v>246</v>
       </c>
       <c r="Q11" s="16"/>
       <c r="R11" s="16" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="S11" s="16"/>
       <c r="T11" s="16"/>
       <c r="V11" s="16" t="s">
+        <v>244</v>
+      </c>
+      <c r="W11" s="16" t="s">
         <v>245</v>
-      </c>
-      <c r="W11" s="16" t="s">
-        <v>246</v>
       </c>
       <c r="X11" s="16"/>
       <c r="Y11" s="16" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="Z11" s="16"/>
       <c r="AA11" s="16"/>
       <c r="AC11" s="16" t="s">
+        <v>244</v>
+      </c>
+      <c r="AD11" s="16" t="s">
         <v>245</v>
-      </c>
-      <c r="AD11" s="16" t="s">
-        <v>246</v>
       </c>
       <c r="AE11" s="16"/>
       <c r="AF11" s="16" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="AG11" s="16"/>
       <c r="AH11" s="16"/>
       <c r="AJ11" s="16" t="s">
+        <v>244</v>
+      </c>
+      <c r="AK11" s="16" t="s">
         <v>245</v>
-      </c>
-      <c r="AK11" s="16" t="s">
-        <v>246</v>
       </c>
       <c r="AL11" s="16"/>
       <c r="AM11" s="16" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="AN11" s="16"/>
       <c r="AO11" s="16"/>
       <c r="AQ11" s="16" t="s">
+        <v>244</v>
+      </c>
+      <c r="AR11" s="16" t="s">
         <v>245</v>
-      </c>
-      <c r="AR11" s="16" t="s">
-        <v>246</v>
       </c>
       <c r="AS11" s="16"/>
       <c r="AT11" s="16" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="AU11" s="16"/>
       <c r="AV11" s="16"/>
       <c r="AX11" s="16" t="s">
+        <v>244</v>
+      </c>
+      <c r="AY11" s="16" t="s">
         <v>245</v>
-      </c>
-      <c r="AY11" s="16" t="s">
-        <v>246</v>
       </c>
       <c r="AZ11" s="16"/>
       <c r="BA11" s="16" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="BB11" s="16"/>
       <c r="BC11" s="16"/>
       <c r="BE11" s="16" t="s">
+        <v>244</v>
+      </c>
+      <c r="BF11" s="16" t="s">
         <v>245</v>
-      </c>
-      <c r="BF11" s="16" t="s">
-        <v>246</v>
       </c>
       <c r="BG11" s="16"/>
       <c r="BH11" s="16" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="BI11" s="16"/>
       <c r="BJ11" s="16"/>
       <c r="BL11" s="16" t="s">
+        <v>244</v>
+      </c>
+      <c r="BM11" s="16" t="s">
         <v>245</v>
-      </c>
-      <c r="BM11" s="16" t="s">
-        <v>246</v>
       </c>
       <c r="BN11" s="16"/>
       <c r="BO11" s="16" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="BP11" s="16"/>
       <c r="BQ11" s="16"/>
       <c r="BS11" s="16" t="s">
+        <v>244</v>
+      </c>
+      <c r="BT11" s="16" t="s">
         <v>245</v>
-      </c>
-      <c r="BT11" s="16" t="s">
-        <v>246</v>
       </c>
       <c r="BU11" s="16"/>
       <c r="BV11" s="16" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="BW11" s="16"/>
       <c r="BX11" s="16"/>
       <c r="BZ11" s="16" t="s">
+        <v>244</v>
+      </c>
+      <c r="CA11" s="16" t="s">
         <v>245</v>
-      </c>
-      <c r="CA11" s="16" t="s">
-        <v>246</v>
       </c>
       <c r="CB11" s="16"/>
       <c r="CC11" s="16" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="CD11" s="16"/>
       <c r="CE11" s="16"/>
       <c r="CG11" s="16" t="s">
+        <v>244</v>
+      </c>
+      <c r="CH11" s="16" t="s">
         <v>245</v>
-      </c>
-      <c r="CH11" s="16" t="s">
-        <v>246</v>
       </c>
       <c r="CI11" s="16"/>
       <c r="CJ11" s="16" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="CK11" s="16"/>
       <c r="CL11" s="16"/>
       <c r="CN11" s="16" t="s">
+        <v>244</v>
+      </c>
+      <c r="CO11" s="16" t="s">
         <v>245</v>
-      </c>
-      <c r="CO11" s="16" t="s">
-        <v>246</v>
       </c>
       <c r="CP11" s="16"/>
       <c r="CQ11" s="16" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="CR11" s="16"/>
       <c r="CS11" s="16"/>
       <c r="CU11" s="16" t="s">
+        <v>244</v>
+      </c>
+      <c r="CV11" s="16" t="s">
         <v>245</v>
-      </c>
-      <c r="CV11" s="16" t="s">
-        <v>246</v>
       </c>
       <c r="CW11" s="16"/>
       <c r="CX11" s="16" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="CY11" s="16"/>
       <c r="CZ11" s="16"/>
       <c r="DB11" s="16" t="s">
+        <v>244</v>
+      </c>
+      <c r="DC11" s="16" t="s">
         <v>245</v>
-      </c>
-      <c r="DC11" s="16" t="s">
-        <v>246</v>
       </c>
       <c r="DD11" s="16"/>
       <c r="DE11" s="16" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="DF11" s="16"/>
       <c r="DG11" s="16"/>
       <c r="DI11" s="16" t="s">
+        <v>244</v>
+      </c>
+      <c r="DJ11" s="16" t="s">
         <v>245</v>
-      </c>
-      <c r="DJ11" s="16" t="s">
-        <v>246</v>
       </c>
       <c r="DK11" s="16"/>
       <c r="DL11" s="16" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="DM11" s="16"/>
       <c r="DN11" s="16"/>
       <c r="DP11" s="16" t="s">
+        <v>244</v>
+      </c>
+      <c r="DQ11" s="16" t="s">
         <v>245</v>
-      </c>
-      <c r="DQ11" s="16" t="s">
-        <v>246</v>
       </c>
       <c r="DR11" s="16"/>
       <c r="DS11" s="16" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="DT11" s="16"/>
       <c r="DU11" s="16"/>
       <c r="DW11" s="16" t="s">
+        <v>244</v>
+      </c>
+      <c r="DX11" s="16" t="s">
         <v>245</v>
-      </c>
-      <c r="DX11" s="16" t="s">
-        <v>246</v>
       </c>
       <c r="DY11" s="16"/>
       <c r="DZ11" s="16" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="EA11" s="16"/>
       <c r="EB11" s="16"/>
       <c r="ED11" s="16" t="s">
+        <v>244</v>
+      </c>
+      <c r="EE11" s="16" t="s">
         <v>245</v>
-      </c>
-      <c r="EE11" s="16" t="s">
-        <v>246</v>
       </c>
       <c r="EF11" s="16"/>
       <c r="EG11" s="16" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="EH11" s="16"/>
       <c r="EI11" s="16"/>
       <c r="EK11" s="16" t="s">
+        <v>244</v>
+      </c>
+      <c r="EL11" s="16" t="s">
         <v>245</v>
-      </c>
-      <c r="EL11" s="16" t="s">
-        <v>246</v>
       </c>
       <c r="EM11" s="16"/>
       <c r="EN11" s="16" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="EO11" s="16"/>
       <c r="EP11" s="16"/>
       <c r="ER11" s="16" t="s">
+        <v>244</v>
+      </c>
+      <c r="ES11" s="16" t="s">
         <v>245</v>
-      </c>
-      <c r="ES11" s="16" t="s">
-        <v>246</v>
       </c>
       <c r="ET11" s="16"/>
       <c r="EU11" s="16" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="EV11" s="16"/>
       <c r="EW11" s="16"/>
       <c r="EY11" s="16" t="s">
+        <v>244</v>
+      </c>
+      <c r="EZ11" s="16" t="s">
         <v>245</v>
-      </c>
-      <c r="EZ11" s="16" t="s">
-        <v>246</v>
       </c>
       <c r="FA11" s="16"/>
       <c r="FB11" s="16" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="FC11" s="16"/>
       <c r="FD11" s="16"/>
@@ -9427,7 +9424,7 @@
   <sheetData>
     <row r="1" spans="1:160" x14ac:dyDescent="0.25">
       <c r="A1" s="30" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="B1" s="18"/>
       <c r="C1" s="18"/>
@@ -9435,7 +9432,7 @@
       <c r="E1" s="18"/>
       <c r="F1" s="18"/>
       <c r="H1" s="30" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="I1" s="18"/>
       <c r="J1" s="18"/>
@@ -9443,7 +9440,7 @@
       <c r="L1" s="18"/>
       <c r="M1" s="18"/>
       <c r="O1" s="30" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="P1" s="18"/>
       <c r="Q1" s="18"/>
@@ -9451,7 +9448,7 @@
       <c r="S1" s="18"/>
       <c r="T1" s="18"/>
       <c r="V1" s="30" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="W1" s="18"/>
       <c r="X1" s="18"/>
@@ -9459,7 +9456,7 @@
       <c r="Z1" s="18"/>
       <c r="AA1" s="18"/>
       <c r="AC1" s="30" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="AD1" s="18"/>
       <c r="AE1" s="18"/>
@@ -9467,7 +9464,7 @@
       <c r="AG1" s="18"/>
       <c r="AH1" s="18"/>
       <c r="AJ1" s="30" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="AK1" s="18"/>
       <c r="AL1" s="18"/>
@@ -9475,7 +9472,7 @@
       <c r="AN1" s="18"/>
       <c r="AO1" s="18"/>
       <c r="AQ1" s="30" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="AR1" s="18"/>
       <c r="AS1" s="18"/>
@@ -9483,7 +9480,7 @@
       <c r="AU1" s="18"/>
       <c r="AV1" s="18"/>
       <c r="AX1" s="30" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="AY1" s="18"/>
       <c r="AZ1" s="18"/>
@@ -9491,7 +9488,7 @@
       <c r="BB1" s="18"/>
       <c r="BC1" s="18"/>
       <c r="BE1" s="30" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="BF1" s="18"/>
       <c r="BG1" s="18"/>
@@ -9499,7 +9496,7 @@
       <c r="BI1" s="18"/>
       <c r="BJ1" s="18"/>
       <c r="BL1" s="30" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="BM1" s="18"/>
       <c r="BN1" s="18"/>
@@ -9507,7 +9504,7 @@
       <c r="BP1" s="18"/>
       <c r="BQ1" s="18"/>
       <c r="BS1" s="30" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="BT1" s="18"/>
       <c r="BU1" s="18"/>
@@ -9515,7 +9512,7 @@
       <c r="BW1" s="18"/>
       <c r="BX1" s="18"/>
       <c r="BZ1" s="30" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="CA1" s="18"/>
       <c r="CB1" s="18"/>
@@ -9523,7 +9520,7 @@
       <c r="CD1" s="18"/>
       <c r="CE1" s="18"/>
       <c r="CG1" s="30" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="CH1" s="18"/>
       <c r="CI1" s="18"/>
@@ -9531,7 +9528,7 @@
       <c r="CK1" s="18"/>
       <c r="CL1" s="18"/>
       <c r="CN1" s="30" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="CO1" s="18"/>
       <c r="CP1" s="18"/>
@@ -9539,7 +9536,7 @@
       <c r="CR1" s="18"/>
       <c r="CS1" s="18"/>
       <c r="CU1" s="30" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="CV1" s="18"/>
       <c r="CW1" s="18"/>
@@ -9547,7 +9544,7 @@
       <c r="CY1" s="18"/>
       <c r="CZ1" s="18"/>
       <c r="DB1" s="30" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="DC1" s="18"/>
       <c r="DD1" s="18"/>
@@ -9555,7 +9552,7 @@
       <c r="DF1" s="18"/>
       <c r="DG1" s="18"/>
       <c r="DI1" s="30" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="DJ1" s="18"/>
       <c r="DK1" s="18"/>
@@ -9563,7 +9560,7 @@
       <c r="DM1" s="18"/>
       <c r="DN1" s="18"/>
       <c r="DP1" s="30" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="DQ1" s="18"/>
       <c r="DR1" s="18"/>
@@ -9571,7 +9568,7 @@
       <c r="DT1" s="18"/>
       <c r="DU1" s="18"/>
       <c r="DW1" s="30" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="DX1" s="18"/>
       <c r="DY1" s="18"/>
@@ -9579,7 +9576,7 @@
       <c r="EA1" s="18"/>
       <c r="EB1" s="18"/>
       <c r="ED1" s="30" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="EE1" s="18"/>
       <c r="EF1" s="18"/>
@@ -9587,7 +9584,7 @@
       <c r="EH1" s="18"/>
       <c r="EI1" s="18"/>
       <c r="EK1" s="30" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="EL1" s="18"/>
       <c r="EM1" s="18"/>
@@ -9595,7 +9592,7 @@
       <c r="EO1" s="18"/>
       <c r="EP1" s="18"/>
       <c r="ER1" s="30" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="ES1" s="18"/>
       <c r="ET1" s="18"/>
@@ -9603,7 +9600,7 @@
       <c r="EV1" s="18"/>
       <c r="EW1" s="18"/>
       <c r="EY1" s="30" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="EZ1" s="18"/>
       <c r="FA1" s="18"/>
@@ -10196,230 +10193,230 @@
     </row>
     <row r="6" spans="1:160" x14ac:dyDescent="0.25">
       <c r="A6" s="16" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B6" s="29" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="C6" s="18"/>
       <c r="D6" s="18"/>
       <c r="E6" s="18"/>
       <c r="F6" s="18"/>
       <c r="H6" s="16" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="I6" s="29" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="J6" s="18"/>
       <c r="K6" s="18"/>
       <c r="L6" s="18"/>
       <c r="M6" s="18"/>
       <c r="O6" s="16" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="P6" s="29" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="Q6" s="18"/>
       <c r="R6" s="18"/>
       <c r="S6" s="18"/>
       <c r="T6" s="18"/>
       <c r="V6" s="16" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="W6" s="29" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="X6" s="18"/>
       <c r="Y6" s="18"/>
       <c r="Z6" s="18"/>
       <c r="AA6" s="18"/>
       <c r="AC6" s="16" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="AD6" s="29" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="AE6" s="18"/>
       <c r="AF6" s="18"/>
       <c r="AG6" s="18"/>
       <c r="AH6" s="18"/>
       <c r="AJ6" s="16" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="AK6" s="29" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="AL6" s="18"/>
       <c r="AM6" s="18"/>
       <c r="AN6" s="18"/>
       <c r="AO6" s="18"/>
       <c r="AQ6" s="16" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="AR6" s="29" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="AS6" s="18"/>
       <c r="AT6" s="18"/>
       <c r="AU6" s="18"/>
       <c r="AV6" s="18"/>
       <c r="AX6" s="16" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="AY6" s="29" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="AZ6" s="18"/>
       <c r="BA6" s="18"/>
       <c r="BB6" s="18"/>
       <c r="BC6" s="18"/>
       <c r="BE6" s="16" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="BF6" s="29" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="BG6" s="18"/>
       <c r="BH6" s="18"/>
       <c r="BI6" s="18"/>
       <c r="BJ6" s="18"/>
       <c r="BL6" s="16" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="BM6" s="29" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="BN6" s="18"/>
       <c r="BO6" s="18"/>
       <c r="BP6" s="18"/>
       <c r="BQ6" s="18"/>
       <c r="BS6" s="16" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="BT6" s="29" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="BU6" s="18"/>
       <c r="BV6" s="18"/>
       <c r="BW6" s="18"/>
       <c r="BX6" s="18"/>
       <c r="BZ6" s="16" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="CA6" s="29" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="CB6" s="18"/>
       <c r="CC6" s="18"/>
       <c r="CD6" s="18"/>
       <c r="CE6" s="18"/>
       <c r="CG6" s="16" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="CH6" s="29" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="CI6" s="18"/>
       <c r="CJ6" s="18"/>
       <c r="CK6" s="18"/>
       <c r="CL6" s="18"/>
       <c r="CN6" s="16" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="CO6" s="29" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="CP6" s="18"/>
       <c r="CQ6" s="18"/>
       <c r="CR6" s="18"/>
       <c r="CS6" s="18"/>
       <c r="CU6" s="16" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="CV6" s="29" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="CW6" s="18"/>
       <c r="CX6" s="18"/>
       <c r="CY6" s="18"/>
       <c r="CZ6" s="18"/>
       <c r="DB6" s="16" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="DC6" s="29" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="DD6" s="18"/>
       <c r="DE6" s="18"/>
       <c r="DF6" s="18"/>
       <c r="DG6" s="18"/>
       <c r="DI6" s="16" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="DJ6" s="29" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="DK6" s="18"/>
       <c r="DL6" s="18"/>
       <c r="DM6" s="18"/>
       <c r="DN6" s="18"/>
       <c r="DP6" s="16" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="DQ6" s="29" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="DR6" s="18"/>
       <c r="DS6" s="18"/>
       <c r="DT6" s="18"/>
       <c r="DU6" s="18"/>
       <c r="DW6" s="16" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="DX6" s="29" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="DY6" s="18"/>
       <c r="DZ6" s="18"/>
       <c r="EA6" s="18"/>
       <c r="EB6" s="18"/>
       <c r="ED6" s="16" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="EE6" s="29" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="EF6" s="18"/>
       <c r="EG6" s="18"/>
       <c r="EH6" s="18"/>
       <c r="EI6" s="18"/>
       <c r="EK6" s="16" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="EL6" s="29" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="EM6" s="18"/>
       <c r="EN6" s="18"/>
       <c r="EO6" s="18"/>
       <c r="EP6" s="18"/>
       <c r="ER6" s="16" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="ES6" s="29" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="ET6" s="18"/>
       <c r="EU6" s="18"/>
       <c r="EV6" s="18"/>
       <c r="EW6" s="18"/>
       <c r="EY6" s="16" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="EZ6" s="29" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="FA6" s="18"/>
       <c r="FB6" s="18"/>
@@ -10431,7 +10428,7 @@
         <v>24</v>
       </c>
       <c r="B7" s="29" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="C7" s="18"/>
       <c r="D7" s="18"/>
@@ -10441,7 +10438,7 @@
         <v>24</v>
       </c>
       <c r="I7" s="29" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="J7" s="18"/>
       <c r="K7" s="18"/>
@@ -10451,7 +10448,7 @@
         <v>24</v>
       </c>
       <c r="P7" s="29" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="Q7" s="18"/>
       <c r="R7" s="18"/>
@@ -10461,7 +10458,7 @@
         <v>24</v>
       </c>
       <c r="W7" s="29" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="X7" s="18"/>
       <c r="Y7" s="18"/>
@@ -10471,7 +10468,7 @@
         <v>24</v>
       </c>
       <c r="AD7" s="29" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="AE7" s="18"/>
       <c r="AF7" s="18"/>
@@ -10481,7 +10478,7 @@
         <v>24</v>
       </c>
       <c r="AK7" s="29" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="AL7" s="18"/>
       <c r="AM7" s="18"/>
@@ -10491,7 +10488,7 @@
         <v>24</v>
       </c>
       <c r="AR7" s="29" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="AS7" s="18"/>
       <c r="AT7" s="18"/>
@@ -10501,7 +10498,7 @@
         <v>24</v>
       </c>
       <c r="AY7" s="29" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="AZ7" s="18"/>
       <c r="BA7" s="18"/>
@@ -10511,7 +10508,7 @@
         <v>24</v>
       </c>
       <c r="BF7" s="29" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="BG7" s="18"/>
       <c r="BH7" s="18"/>
@@ -10521,7 +10518,7 @@
         <v>24</v>
       </c>
       <c r="BM7" s="29" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="BN7" s="18"/>
       <c r="BO7" s="18"/>
@@ -10531,7 +10528,7 @@
         <v>24</v>
       </c>
       <c r="BT7" s="29" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="BU7" s="18"/>
       <c r="BV7" s="18"/>
@@ -10541,7 +10538,7 @@
         <v>24</v>
       </c>
       <c r="CA7" s="29" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="CB7" s="18"/>
       <c r="CC7" s="18"/>
@@ -10551,7 +10548,7 @@
         <v>24</v>
       </c>
       <c r="CH7" s="29" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="CI7" s="18"/>
       <c r="CJ7" s="18"/>
@@ -10561,7 +10558,7 @@
         <v>24</v>
       </c>
       <c r="CO7" s="29" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="CP7" s="18"/>
       <c r="CQ7" s="18"/>
@@ -10571,7 +10568,7 @@
         <v>24</v>
       </c>
       <c r="CV7" s="29" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="CW7" s="18"/>
       <c r="CX7" s="18"/>
@@ -10581,7 +10578,7 @@
         <v>24</v>
       </c>
       <c r="DC7" s="29" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="DD7" s="18"/>
       <c r="DE7" s="18"/>
@@ -10591,7 +10588,7 @@
         <v>24</v>
       </c>
       <c r="DJ7" s="29" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="DK7" s="18"/>
       <c r="DL7" s="18"/>
@@ -10601,7 +10598,7 @@
         <v>24</v>
       </c>
       <c r="DQ7" s="29" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="DR7" s="18"/>
       <c r="DS7" s="18"/>
@@ -10611,7 +10608,7 @@
         <v>24</v>
       </c>
       <c r="DX7" s="29" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="DY7" s="18"/>
       <c r="DZ7" s="18"/>
@@ -10621,7 +10618,7 @@
         <v>24</v>
       </c>
       <c r="EE7" s="29" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="EF7" s="18"/>
       <c r="EG7" s="18"/>
@@ -10631,7 +10628,7 @@
         <v>24</v>
       </c>
       <c r="EL7" s="29" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="EM7" s="18"/>
       <c r="EN7" s="18"/>
@@ -10641,7 +10638,7 @@
         <v>24</v>
       </c>
       <c r="ES7" s="29" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="ET7" s="18"/>
       <c r="EU7" s="18"/>
@@ -10651,7 +10648,7 @@
         <v>24</v>
       </c>
       <c r="EZ7" s="29" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="FA7" s="18"/>
       <c r="FB7" s="18"/>
@@ -11076,880 +11073,880 @@
     </row>
     <row r="9" spans="1:160" ht="29.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="16" t="s">
+        <v>225</v>
+      </c>
+      <c r="B9" s="16" t="s">
         <v>226</v>
       </c>
-      <c r="B9" s="16" t="s">
+      <c r="C9" s="16" t="s">
         <v>227</v>
       </c>
-      <c r="C9" s="16" t="s">
+      <c r="D9" s="16" t="s">
         <v>228</v>
-      </c>
-      <c r="D9" s="16" t="s">
-        <v>229</v>
       </c>
       <c r="E9" s="16"/>
       <c r="F9" s="16"/>
       <c r="H9" s="16" t="s">
+        <v>225</v>
+      </c>
+      <c r="I9" s="16" t="s">
         <v>226</v>
       </c>
-      <c r="I9" s="16" t="s">
+      <c r="J9" s="16" t="s">
         <v>227</v>
       </c>
-      <c r="J9" s="16" t="s">
+      <c r="K9" s="16" t="s">
         <v>228</v>
-      </c>
-      <c r="K9" s="16" t="s">
-        <v>229</v>
       </c>
       <c r="L9" s="16"/>
       <c r="M9" s="16"/>
       <c r="O9" s="16" t="s">
+        <v>225</v>
+      </c>
+      <c r="P9" s="16" t="s">
         <v>226</v>
       </c>
-      <c r="P9" s="16" t="s">
+      <c r="Q9" s="16" t="s">
         <v>227</v>
       </c>
-      <c r="Q9" s="16" t="s">
+      <c r="R9" s="16" t="s">
         <v>228</v>
-      </c>
-      <c r="R9" s="16" t="s">
-        <v>229</v>
       </c>
       <c r="S9" s="16"/>
       <c r="T9" s="16"/>
       <c r="V9" s="16" t="s">
+        <v>225</v>
+      </c>
+      <c r="W9" s="16" t="s">
         <v>226</v>
       </c>
-      <c r="W9" s="16" t="s">
+      <c r="X9" s="16" t="s">
         <v>227</v>
       </c>
-      <c r="X9" s="16" t="s">
+      <c r="Y9" s="16" t="s">
         <v>228</v>
-      </c>
-      <c r="Y9" s="16" t="s">
-        <v>229</v>
       </c>
       <c r="Z9" s="16"/>
       <c r="AA9" s="16"/>
       <c r="AC9" s="16" t="s">
+        <v>225</v>
+      </c>
+      <c r="AD9" s="16" t="s">
         <v>226</v>
       </c>
-      <c r="AD9" s="16" t="s">
+      <c r="AE9" s="16" t="s">
         <v>227</v>
       </c>
-      <c r="AE9" s="16" t="s">
+      <c r="AF9" s="16" t="s">
         <v>228</v>
-      </c>
-      <c r="AF9" s="16" t="s">
-        <v>229</v>
       </c>
       <c r="AG9" s="16"/>
       <c r="AH9" s="16"/>
       <c r="AJ9" s="16" t="s">
+        <v>225</v>
+      </c>
+      <c r="AK9" s="16" t="s">
         <v>226</v>
       </c>
-      <c r="AK9" s="16" t="s">
+      <c r="AL9" s="16" t="s">
         <v>227</v>
       </c>
-      <c r="AL9" s="16" t="s">
+      <c r="AM9" s="16" t="s">
         <v>228</v>
-      </c>
-      <c r="AM9" s="16" t="s">
-        <v>229</v>
       </c>
       <c r="AN9" s="16"/>
       <c r="AO9" s="16"/>
       <c r="AQ9" s="16" t="s">
+        <v>225</v>
+      </c>
+      <c r="AR9" s="16" t="s">
         <v>226</v>
       </c>
-      <c r="AR9" s="16" t="s">
+      <c r="AS9" s="16" t="s">
         <v>227</v>
       </c>
-      <c r="AS9" s="16" t="s">
+      <c r="AT9" s="16" t="s">
         <v>228</v>
-      </c>
-      <c r="AT9" s="16" t="s">
-        <v>229</v>
       </c>
       <c r="AU9" s="16"/>
       <c r="AV9" s="16"/>
       <c r="AX9" s="16" t="s">
+        <v>225</v>
+      </c>
+      <c r="AY9" s="16" t="s">
         <v>226</v>
       </c>
-      <c r="AY9" s="16" t="s">
+      <c r="AZ9" s="16" t="s">
         <v>227</v>
       </c>
-      <c r="AZ9" s="16" t="s">
+      <c r="BA9" s="16" t="s">
         <v>228</v>
-      </c>
-      <c r="BA9" s="16" t="s">
-        <v>229</v>
       </c>
       <c r="BB9" s="16"/>
       <c r="BC9" s="16"/>
       <c r="BE9" s="16" t="s">
+        <v>225</v>
+      </c>
+      <c r="BF9" s="16" t="s">
         <v>226</v>
       </c>
-      <c r="BF9" s="16" t="s">
+      <c r="BG9" s="16" t="s">
         <v>227</v>
       </c>
-      <c r="BG9" s="16" t="s">
+      <c r="BH9" s="16" t="s">
         <v>228</v>
-      </c>
-      <c r="BH9" s="16" t="s">
-        <v>229</v>
       </c>
       <c r="BI9" s="16"/>
       <c r="BJ9" s="16"/>
       <c r="BL9" s="16" t="s">
+        <v>225</v>
+      </c>
+      <c r="BM9" s="16" t="s">
         <v>226</v>
       </c>
-      <c r="BM9" s="16" t="s">
+      <c r="BN9" s="16" t="s">
         <v>227</v>
       </c>
-      <c r="BN9" s="16" t="s">
+      <c r="BO9" s="16" t="s">
         <v>228</v>
-      </c>
-      <c r="BO9" s="16" t="s">
-        <v>229</v>
       </c>
       <c r="BP9" s="16"/>
       <c r="BQ9" s="16"/>
       <c r="BS9" s="16" t="s">
+        <v>225</v>
+      </c>
+      <c r="BT9" s="16" t="s">
         <v>226</v>
       </c>
-      <c r="BT9" s="16" t="s">
+      <c r="BU9" s="16" t="s">
         <v>227</v>
       </c>
-      <c r="BU9" s="16" t="s">
+      <c r="BV9" s="16" t="s">
         <v>228</v>
-      </c>
-      <c r="BV9" s="16" t="s">
-        <v>229</v>
       </c>
       <c r="BW9" s="16"/>
       <c r="BX9" s="16"/>
       <c r="BZ9" s="16" t="s">
+        <v>225</v>
+      </c>
+      <c r="CA9" s="16" t="s">
         <v>226</v>
       </c>
-      <c r="CA9" s="16" t="s">
+      <c r="CB9" s="16" t="s">
         <v>227</v>
       </c>
-      <c r="CB9" s="16" t="s">
+      <c r="CC9" s="16" t="s">
         <v>228</v>
-      </c>
-      <c r="CC9" s="16" t="s">
-        <v>229</v>
       </c>
       <c r="CD9" s="16"/>
       <c r="CE9" s="16"/>
       <c r="CG9" s="16" t="s">
+        <v>225</v>
+      </c>
+      <c r="CH9" s="16" t="s">
         <v>226</v>
       </c>
-      <c r="CH9" s="16" t="s">
+      <c r="CI9" s="16" t="s">
         <v>227</v>
       </c>
-      <c r="CI9" s="16" t="s">
+      <c r="CJ9" s="16" t="s">
         <v>228</v>
-      </c>
-      <c r="CJ9" s="16" t="s">
-        <v>229</v>
       </c>
       <c r="CK9" s="16"/>
       <c r="CL9" s="16"/>
       <c r="CN9" s="16" t="s">
+        <v>225</v>
+      </c>
+      <c r="CO9" s="16" t="s">
         <v>226</v>
       </c>
-      <c r="CO9" s="16" t="s">
+      <c r="CP9" s="16" t="s">
         <v>227</v>
       </c>
-      <c r="CP9" s="16" t="s">
+      <c r="CQ9" s="16" t="s">
         <v>228</v>
-      </c>
-      <c r="CQ9" s="16" t="s">
-        <v>229</v>
       </c>
       <c r="CR9" s="16"/>
       <c r="CS9" s="16"/>
       <c r="CU9" s="16" t="s">
+        <v>225</v>
+      </c>
+      <c r="CV9" s="16" t="s">
         <v>226</v>
       </c>
-      <c r="CV9" s="16" t="s">
+      <c r="CW9" s="16" t="s">
         <v>227</v>
       </c>
-      <c r="CW9" s="16" t="s">
+      <c r="CX9" s="16" t="s">
         <v>228</v>
-      </c>
-      <c r="CX9" s="16" t="s">
-        <v>229</v>
       </c>
       <c r="CY9" s="16"/>
       <c r="CZ9" s="16"/>
       <c r="DB9" s="16" t="s">
+        <v>225</v>
+      </c>
+      <c r="DC9" s="16" t="s">
         <v>226</v>
       </c>
-      <c r="DC9" s="16" t="s">
+      <c r="DD9" s="16" t="s">
         <v>227</v>
       </c>
-      <c r="DD9" s="16" t="s">
+      <c r="DE9" s="16" t="s">
         <v>228</v>
-      </c>
-      <c r="DE9" s="16" t="s">
-        <v>229</v>
       </c>
       <c r="DF9" s="16"/>
       <c r="DG9" s="16"/>
       <c r="DI9" s="16" t="s">
+        <v>225</v>
+      </c>
+      <c r="DJ9" s="16" t="s">
         <v>226</v>
       </c>
-      <c r="DJ9" s="16" t="s">
+      <c r="DK9" s="16" t="s">
         <v>227</v>
       </c>
-      <c r="DK9" s="16" t="s">
+      <c r="DL9" s="16" t="s">
         <v>228</v>
-      </c>
-      <c r="DL9" s="16" t="s">
-        <v>229</v>
       </c>
       <c r="DM9" s="16"/>
       <c r="DN9" s="16"/>
       <c r="DP9" s="16" t="s">
+        <v>225</v>
+      </c>
+      <c r="DQ9" s="16" t="s">
         <v>226</v>
       </c>
-      <c r="DQ9" s="16" t="s">
+      <c r="DR9" s="16" t="s">
         <v>227</v>
       </c>
-      <c r="DR9" s="16" t="s">
+      <c r="DS9" s="16" t="s">
         <v>228</v>
-      </c>
-      <c r="DS9" s="16" t="s">
-        <v>229</v>
       </c>
       <c r="DT9" s="16"/>
       <c r="DU9" s="16"/>
       <c r="DW9" s="16" t="s">
+        <v>225</v>
+      </c>
+      <c r="DX9" s="16" t="s">
         <v>226</v>
       </c>
-      <c r="DX9" s="16" t="s">
+      <c r="DY9" s="16" t="s">
         <v>227</v>
       </c>
-      <c r="DY9" s="16" t="s">
+      <c r="DZ9" s="16" t="s">
         <v>228</v>
-      </c>
-      <c r="DZ9" s="16" t="s">
-        <v>229</v>
       </c>
       <c r="EA9" s="16"/>
       <c r="EB9" s="16"/>
       <c r="ED9" s="16" t="s">
+        <v>225</v>
+      </c>
+      <c r="EE9" s="16" t="s">
         <v>226</v>
       </c>
-      <c r="EE9" s="16" t="s">
+      <c r="EF9" s="16" t="s">
         <v>227</v>
       </c>
-      <c r="EF9" s="16" t="s">
+      <c r="EG9" s="16" t="s">
         <v>228</v>
-      </c>
-      <c r="EG9" s="16" t="s">
-        <v>229</v>
       </c>
       <c r="EH9" s="16"/>
       <c r="EI9" s="16"/>
       <c r="EK9" s="16" t="s">
+        <v>225</v>
+      </c>
+      <c r="EL9" s="16" t="s">
         <v>226</v>
       </c>
-      <c r="EL9" s="16" t="s">
+      <c r="EM9" s="16" t="s">
         <v>227</v>
       </c>
-      <c r="EM9" s="16" t="s">
+      <c r="EN9" s="16" t="s">
         <v>228</v>
-      </c>
-      <c r="EN9" s="16" t="s">
-        <v>229</v>
       </c>
       <c r="EO9" s="16"/>
       <c r="EP9" s="16"/>
       <c r="ER9" s="16" t="s">
+        <v>225</v>
+      </c>
+      <c r="ES9" s="16" t="s">
         <v>226</v>
       </c>
-      <c r="ES9" s="16" t="s">
+      <c r="ET9" s="16" t="s">
         <v>227</v>
       </c>
-      <c r="ET9" s="16" t="s">
+      <c r="EU9" s="16" t="s">
         <v>228</v>
-      </c>
-      <c r="EU9" s="16" t="s">
-        <v>229</v>
       </c>
       <c r="EV9" s="16"/>
       <c r="EW9" s="16"/>
       <c r="EY9" s="16" t="s">
+        <v>225</v>
+      </c>
+      <c r="EZ9" s="16" t="s">
         <v>226</v>
       </c>
-      <c r="EZ9" s="16" t="s">
+      <c r="FA9" s="16" t="s">
         <v>227</v>
       </c>
-      <c r="FA9" s="16" t="s">
+      <c r="FB9" s="16" t="s">
         <v>228</v>
-      </c>
-      <c r="FB9" s="16" t="s">
-        <v>229</v>
       </c>
       <c r="FC9" s="16"/>
       <c r="FD9" s="16"/>
     </row>
     <row r="10" spans="1:160" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="16" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="B10" s="16" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="C10" s="16"/>
       <c r="D10" s="16" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="E10" s="16"/>
       <c r="F10" s="16"/>
       <c r="H10" s="16" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="I10" s="16" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="J10" s="16"/>
       <c r="K10" s="16" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="L10" s="16"/>
       <c r="M10" s="16"/>
       <c r="O10" s="16" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="P10" s="16" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="Q10" s="16"/>
       <c r="R10" s="16" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="S10" s="16"/>
       <c r="T10" s="16"/>
       <c r="V10" s="16" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="W10" s="16" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="X10" s="16"/>
       <c r="Y10" s="16" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="Z10" s="16"/>
       <c r="AA10" s="16"/>
       <c r="AC10" s="16" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="AD10" s="16" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="AE10" s="16"/>
       <c r="AF10" s="16" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="AG10" s="16"/>
       <c r="AH10" s="16"/>
       <c r="AJ10" s="16" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="AK10" s="16" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="AL10" s="16"/>
       <c r="AM10" s="16" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="AN10" s="16"/>
       <c r="AO10" s="16"/>
       <c r="AQ10" s="16" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="AR10" s="16" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="AS10" s="16"/>
       <c r="AT10" s="16" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="AU10" s="16"/>
       <c r="AV10" s="16"/>
       <c r="AX10" s="16" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="AY10" s="16" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="AZ10" s="16"/>
       <c r="BA10" s="16" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="BB10" s="16"/>
       <c r="BC10" s="16"/>
       <c r="BE10" s="16" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="BF10" s="16" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="BG10" s="16"/>
       <c r="BH10" s="16" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="BI10" s="16"/>
       <c r="BJ10" s="16"/>
       <c r="BL10" s="16" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="BM10" s="16" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="BN10" s="16"/>
       <c r="BO10" s="16" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="BP10" s="16"/>
       <c r="BQ10" s="16"/>
       <c r="BS10" s="16" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="BT10" s="16" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="BU10" s="16"/>
       <c r="BV10" s="16" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="BW10" s="16"/>
       <c r="BX10" s="16"/>
       <c r="BZ10" s="16" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="CA10" s="16" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="CB10" s="16"/>
       <c r="CC10" s="16" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="CD10" s="16"/>
       <c r="CE10" s="16"/>
       <c r="CG10" s="16" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="CH10" s="16" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="CI10" s="16"/>
       <c r="CJ10" s="16" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="CK10" s="16"/>
       <c r="CL10" s="16"/>
       <c r="CN10" s="16" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="CO10" s="16" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="CP10" s="16"/>
       <c r="CQ10" s="16" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="CR10" s="16"/>
       <c r="CS10" s="16"/>
       <c r="CU10" s="16" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="CV10" s="16" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="CW10" s="16"/>
       <c r="CX10" s="16" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="CY10" s="16"/>
       <c r="CZ10" s="16"/>
       <c r="DB10" s="16" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="DC10" s="16" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="DD10" s="16"/>
       <c r="DE10" s="16" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="DF10" s="16"/>
       <c r="DG10" s="16"/>
       <c r="DI10" s="16" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="DJ10" s="16" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="DK10" s="16"/>
       <c r="DL10" s="16" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="DM10" s="16"/>
       <c r="DN10" s="16"/>
       <c r="DP10" s="16" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="DQ10" s="16" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="DR10" s="16"/>
       <c r="DS10" s="16" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="DT10" s="16"/>
       <c r="DU10" s="16"/>
       <c r="DW10" s="16" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="DX10" s="16" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="DY10" s="16"/>
       <c r="DZ10" s="16" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="EA10" s="16"/>
       <c r="EB10" s="16"/>
       <c r="ED10" s="16" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="EE10" s="16" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="EF10" s="16"/>
       <c r="EG10" s="16" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="EH10" s="16"/>
       <c r="EI10" s="16"/>
       <c r="EK10" s="16" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="EL10" s="16" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="EM10" s="16"/>
       <c r="EN10" s="16" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="EO10" s="16"/>
       <c r="EP10" s="16"/>
       <c r="ER10" s="16" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="ES10" s="16" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="ET10" s="16"/>
       <c r="EU10" s="16" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="EV10" s="16"/>
       <c r="EW10" s="16"/>
       <c r="EY10" s="16" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="EZ10" s="16" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="FA10" s="16"/>
       <c r="FB10" s="16" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="FC10" s="16"/>
       <c r="FD10" s="16"/>
     </row>
     <row r="11" spans="1:160" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="16" t="s">
+        <v>244</v>
+      </c>
+      <c r="B11" s="16" t="s">
         <v>245</v>
-      </c>
-      <c r="B11" s="16" t="s">
-        <v>246</v>
       </c>
       <c r="C11" s="16"/>
       <c r="D11" s="16" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="E11" s="16"/>
       <c r="F11" s="16"/>
       <c r="H11" s="16" t="s">
+        <v>244</v>
+      </c>
+      <c r="I11" s="16" t="s">
         <v>245</v>
-      </c>
-      <c r="I11" s="16" t="s">
-        <v>246</v>
       </c>
       <c r="J11" s="16"/>
       <c r="K11" s="16" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="L11" s="16"/>
       <c r="M11" s="16"/>
       <c r="O11" s="16" t="s">
+        <v>244</v>
+      </c>
+      <c r="P11" s="16" t="s">
         <v>245</v>
-      </c>
-      <c r="P11" s="16" t="s">
-        <v>246</v>
       </c>
       <c r="Q11" s="16"/>
       <c r="R11" s="16" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="S11" s="16"/>
       <c r="T11" s="16"/>
       <c r="V11" s="16" t="s">
+        <v>244</v>
+      </c>
+      <c r="W11" s="16" t="s">
         <v>245</v>
-      </c>
-      <c r="W11" s="16" t="s">
-        <v>246</v>
       </c>
       <c r="X11" s="16"/>
       <c r="Y11" s="16" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="Z11" s="16"/>
       <c r="AA11" s="16"/>
       <c r="AC11" s="16" t="s">
+        <v>244</v>
+      </c>
+      <c r="AD11" s="16" t="s">
         <v>245</v>
-      </c>
-      <c r="AD11" s="16" t="s">
-        <v>246</v>
       </c>
       <c r="AE11" s="16"/>
       <c r="AF11" s="16" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="AG11" s="16"/>
       <c r="AH11" s="16"/>
       <c r="AJ11" s="16" t="s">
+        <v>244</v>
+      </c>
+      <c r="AK11" s="16" t="s">
         <v>245</v>
-      </c>
-      <c r="AK11" s="16" t="s">
-        <v>246</v>
       </c>
       <c r="AL11" s="16"/>
       <c r="AM11" s="16" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="AN11" s="16"/>
       <c r="AO11" s="16"/>
       <c r="AQ11" s="16" t="s">
+        <v>244</v>
+      </c>
+      <c r="AR11" s="16" t="s">
         <v>245</v>
-      </c>
-      <c r="AR11" s="16" t="s">
-        <v>246</v>
       </c>
       <c r="AS11" s="16"/>
       <c r="AT11" s="16" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="AU11" s="16"/>
       <c r="AV11" s="16"/>
       <c r="AX11" s="16" t="s">
+        <v>244</v>
+      </c>
+      <c r="AY11" s="16" t="s">
         <v>245</v>
-      </c>
-      <c r="AY11" s="16" t="s">
-        <v>246</v>
       </c>
       <c r="AZ11" s="16"/>
       <c r="BA11" s="16" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="BB11" s="16"/>
       <c r="BC11" s="16"/>
       <c r="BE11" s="16" t="s">
+        <v>244</v>
+      </c>
+      <c r="BF11" s="16" t="s">
         <v>245</v>
-      </c>
-      <c r="BF11" s="16" t="s">
-        <v>246</v>
       </c>
       <c r="BG11" s="16"/>
       <c r="BH11" s="16" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="BI11" s="16"/>
       <c r="BJ11" s="16"/>
       <c r="BL11" s="16" t="s">
+        <v>244</v>
+      </c>
+      <c r="BM11" s="16" t="s">
         <v>245</v>
-      </c>
-      <c r="BM11" s="16" t="s">
-        <v>246</v>
       </c>
       <c r="BN11" s="16"/>
       <c r="BO11" s="16" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="BP11" s="16"/>
       <c r="BQ11" s="16"/>
       <c r="BS11" s="16" t="s">
+        <v>244</v>
+      </c>
+      <c r="BT11" s="16" t="s">
         <v>245</v>
-      </c>
-      <c r="BT11" s="16" t="s">
-        <v>246</v>
       </c>
       <c r="BU11" s="16"/>
       <c r="BV11" s="16" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="BW11" s="16"/>
       <c r="BX11" s="16"/>
       <c r="BZ11" s="16" t="s">
+        <v>244</v>
+      </c>
+      <c r="CA11" s="16" t="s">
         <v>245</v>
-      </c>
-      <c r="CA11" s="16" t="s">
-        <v>246</v>
       </c>
       <c r="CB11" s="16"/>
       <c r="CC11" s="16" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="CD11" s="16"/>
       <c r="CE11" s="16"/>
       <c r="CG11" s="16" t="s">
+        <v>244</v>
+      </c>
+      <c r="CH11" s="16" t="s">
         <v>245</v>
-      </c>
-      <c r="CH11" s="16" t="s">
-        <v>246</v>
       </c>
       <c r="CI11" s="16"/>
       <c r="CJ11" s="16" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="CK11" s="16"/>
       <c r="CL11" s="16"/>
       <c r="CN11" s="16" t="s">
+        <v>244</v>
+      </c>
+      <c r="CO11" s="16" t="s">
         <v>245</v>
-      </c>
-      <c r="CO11" s="16" t="s">
-        <v>246</v>
       </c>
       <c r="CP11" s="16"/>
       <c r="CQ11" s="16" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="CR11" s="16"/>
       <c r="CS11" s="16"/>
       <c r="CU11" s="16" t="s">
+        <v>244</v>
+      </c>
+      <c r="CV11" s="16" t="s">
         <v>245</v>
-      </c>
-      <c r="CV11" s="16" t="s">
-        <v>246</v>
       </c>
       <c r="CW11" s="16"/>
       <c r="CX11" s="16" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="CY11" s="16"/>
       <c r="CZ11" s="16"/>
       <c r="DB11" s="16" t="s">
+        <v>244</v>
+      </c>
+      <c r="DC11" s="16" t="s">
         <v>245</v>
-      </c>
-      <c r="DC11" s="16" t="s">
-        <v>246</v>
       </c>
       <c r="DD11" s="16"/>
       <c r="DE11" s="16" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="DF11" s="16"/>
       <c r="DG11" s="16"/>
       <c r="DI11" s="16" t="s">
+        <v>244</v>
+      </c>
+      <c r="DJ11" s="16" t="s">
         <v>245</v>
-      </c>
-      <c r="DJ11" s="16" t="s">
-        <v>246</v>
       </c>
       <c r="DK11" s="16"/>
       <c r="DL11" s="16" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="DM11" s="16"/>
       <c r="DN11" s="16"/>
       <c r="DP11" s="16" t="s">
+        <v>244</v>
+      </c>
+      <c r="DQ11" s="16" t="s">
         <v>245</v>
-      </c>
-      <c r="DQ11" s="16" t="s">
-        <v>246</v>
       </c>
       <c r="DR11" s="16"/>
       <c r="DS11" s="16" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="DT11" s="16"/>
       <c r="DU11" s="16"/>
       <c r="DW11" s="16" t="s">
+        <v>244</v>
+      </c>
+      <c r="DX11" s="16" t="s">
         <v>245</v>
-      </c>
-      <c r="DX11" s="16" t="s">
-        <v>246</v>
       </c>
       <c r="DY11" s="16"/>
       <c r="DZ11" s="16" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="EA11" s="16"/>
       <c r="EB11" s="16"/>
       <c r="ED11" s="16" t="s">
+        <v>244</v>
+      </c>
+      <c r="EE11" s="16" t="s">
         <v>245</v>
-      </c>
-      <c r="EE11" s="16" t="s">
-        <v>246</v>
       </c>
       <c r="EF11" s="16"/>
       <c r="EG11" s="16" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="EH11" s="16"/>
       <c r="EI11" s="16"/>
       <c r="EK11" s="16" t="s">
+        <v>244</v>
+      </c>
+      <c r="EL11" s="16" t="s">
         <v>245</v>
-      </c>
-      <c r="EL11" s="16" t="s">
-        <v>246</v>
       </c>
       <c r="EM11" s="16"/>
       <c r="EN11" s="16" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="EO11" s="16"/>
       <c r="EP11" s="16"/>
       <c r="ER11" s="16" t="s">
+        <v>244</v>
+      </c>
+      <c r="ES11" s="16" t="s">
         <v>245</v>
-      </c>
-      <c r="ES11" s="16" t="s">
-        <v>246</v>
       </c>
       <c r="ET11" s="16"/>
       <c r="EU11" s="16" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="EV11" s="16"/>
       <c r="EW11" s="16"/>
       <c r="EY11" s="16" t="s">
+        <v>244</v>
+      </c>
+      <c r="EZ11" s="16" t="s">
         <v>245</v>
-      </c>
-      <c r="EZ11" s="16" t="s">
-        <v>246</v>
       </c>
       <c r="FA11" s="16"/>
       <c r="FB11" s="16" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="FC11" s="16"/>
       <c r="FD11" s="16"/>

--- a/Test Cases.xlsx
+++ b/Test Cases.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://endresshauser-my.sharepoint.com/personal/corbin_ferguson_endress_com/Documents/ThesisBuildTool/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="176" documentId="8_{B89245B7-08D9-4A9D-8516-F6C9C7AFFDC1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CEDDDC1D-E355-4653-B530-E778081C02BB}"/>
+  <xr:revisionPtr revIDLastSave="180" documentId="8_{B89245B7-08D9-4A9D-8516-F6C9C7AFFDC1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1DD4BC04-1BC5-48F9-A728-AFBCA4180E4B}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="25440" windowHeight="15270" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="25440" windowHeight="15270" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tests" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1752" uniqueCount="350">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1753" uniqueCount="351">
   <si>
     <t>Test ID</t>
   </si>
@@ -1090,13 +1090,16 @@
   </si>
   <si>
     <t>TemplateLadderAOI</t>
+  </si>
+  <si>
+    <t>Validation Error Window inaction</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1117,6 +1120,15 @@
       <sz val="11"/>
       <name val="Calibri"/>
       <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <u/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -1168,7 +1180,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -1236,12 +1248,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1668,6 +1681,11 @@
               </a:ln>
               <a:effectLst/>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000001-CEBA-4C51-82C8-E12FF664C920}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="1"/>
@@ -1723,6 +1741,11 @@
               </a:ln>
               <a:effectLst/>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000007-CEBA-4C51-82C8-E12FF664C920}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dLbls>
             <c:dLbl>
@@ -2578,17 +2601,21 @@
 </xdr:wsDr>
 </file>
 
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+</file>
+
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="TestMaster" displayName="TestMaster" ref="A1:E72">
-  <autoFilter ref="A1:E72" xr:uid="{00000000-0009-0000-0100-000001000000}">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="TestMaster" displayName="TestMaster" ref="A1:E73">
+  <autoFilter ref="A1:E73" xr:uid="{00000000-0009-0000-0100-000001000000}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
     <filterColumn colId="2" hiddenButton="1"/>
     <filterColumn colId="3" hiddenButton="1"/>
     <filterColumn colId="4" hiddenButton="1"/>
   </autoFilter>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:E72">
-    <sortCondition ref="E1:E72"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:E73">
+    <sortCondition ref="E1:E73"/>
   </sortState>
   <tableColumns count="5">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Test ID" totalsRowLabel="Total" dataDxfId="5">
@@ -2868,7 +2895,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H72"/>
+  <dimension ref="A1:H73"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9" style="6" bestFit="1" customWidth="1"/>
@@ -3620,7 +3647,7 @@
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A34" s="6">
-        <f t="shared" ref="A34:A65" si="1">ROW()-1</f>
+        <f t="shared" ref="A34:A66" si="1">ROW()-1</f>
         <v>33</v>
       </c>
       <c r="B34" t="str">
@@ -3691,24 +3718,11 @@
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A37" s="6">
-        <f t="shared" si="1"/>
+        <f>ROW()-1</f>
         <v>36</v>
       </c>
-      <c r="B37" t="str">
-        <f>Modify!A1</f>
-        <v>No Element to Modify</v>
-      </c>
-      <c r="C37" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="D37" t="s">
-        <v>10</v>
-      </c>
-      <c r="E37" t="s">
-        <v>16</v>
-      </c>
-      <c r="G37" t="s">
-        <v>17</v>
+      <c r="B37" s="31" t="s">
+        <v>350</v>
       </c>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.25">
@@ -3717,21 +3731,20 @@
         <v>37</v>
       </c>
       <c r="B38" t="str">
-        <f>'Unit XMLHandlerTests'!AC1</f>
-        <v>Check For Dependencies Adds Dependent Elements When Dependencies Exist</v>
+        <f>Modify!A1</f>
+        <v>No Element to Modify</v>
       </c>
       <c r="C38" s="5" t="s">
-        <v>8</v>
+        <v>6</v>
+      </c>
+      <c r="D38" t="s">
+        <v>10</v>
       </c>
       <c r="E38" t="s">
+        <v>16</v>
+      </c>
+      <c r="G38" t="s">
         <v>17</v>
-      </c>
-      <c r="G38" t="s">
-        <v>5</v>
-      </c>
-      <c r="H38">
-        <f>COUNTIFS(TestMaster[Test Status], "Not Implemented", TestMaster[Namespace], G37)</f>
-        <v>0</v>
       </c>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.25">
@@ -3740,21 +3753,21 @@
         <v>38</v>
       </c>
       <c r="B39" t="str">
-        <f>'Unit XMLHandlerTests'!AQ1</f>
-        <v>Check For Dependencies Handles Parent Module When Not Local</v>
+        <f>'Unit XMLHandlerTests'!AC1</f>
+        <v>Check For Dependencies Adds Dependent Elements When Dependencies Exist</v>
       </c>
       <c r="C39" s="5" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E39" t="s">
         <v>17</v>
       </c>
       <c r="G39" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="H39">
-        <f>COUNTIFS(TestMaster[Test Status], "Pass", TestMaster[Namespace], G37)</f>
-        <v>19</v>
+        <f>COUNTIFS(TestMaster[Test Status], "Not Implemented", TestMaster[Namespace], G38)</f>
+        <v>0</v>
       </c>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.25">
@@ -3763,21 +3776,21 @@
         <v>39</v>
       </c>
       <c r="B40" t="str">
-        <f>'Unit XMLHandlerTests'!BE1</f>
-        <v>Check For Dependencies Handles Task With Scheduled Programs</v>
+        <f>'Unit XMLHandlerTests'!AQ1</f>
+        <v>Check For Dependencies Handles Parent Module When Not Local</v>
       </c>
       <c r="C40" s="5" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E40" t="s">
         <v>17</v>
       </c>
       <c r="G40" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="H40">
-        <f>COUNTIFS(TestMaster[Test Status], "Fail", TestMaster[Namespace], G37)</f>
-        <v>3</v>
+        <f>COUNTIFS(TestMaster[Test Status], "Pass", TestMaster[Namespace], G38)</f>
+        <v>19</v>
       </c>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.25">
@@ -3786,8 +3799,8 @@
         <v>40</v>
       </c>
       <c r="B41" t="str">
-        <f>'Unit XMLHandlerTests'!AJ1</f>
-        <v>Check For Dependencies Skips Dependencies When Already Exist</v>
+        <f>'Unit XMLHandlerTests'!BE1</f>
+        <v>Check For Dependencies Handles Task With Scheduled Programs</v>
       </c>
       <c r="C41" s="5" t="s">
         <v>8</v>
@@ -3796,11 +3809,11 @@
         <v>17</v>
       </c>
       <c r="G41" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="H41">
-        <f>COUNTIFS(TestMaster[Test Status], "Skipped", TestMaster[Namespace], G37)</f>
-        <v>1</v>
+        <f>COUNTIFS(TestMaster[Test Status], "Fail", TestMaster[Namespace], G38)</f>
+        <v>3</v>
       </c>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.25">
@@ -3809,14 +3822,21 @@
         <v>41</v>
       </c>
       <c r="B42" t="str">
-        <f>'Unit XMLHandlerTests'!AX1</f>
-        <v>Check For Dependencies With List Processes All Elements</v>
+        <f>'Unit XMLHandlerTests'!AJ1</f>
+        <v>Check For Dependencies Skips Dependencies When Already Exist</v>
       </c>
       <c r="C42" s="5" t="s">
         <v>8</v>
       </c>
       <c r="E42" t="s">
         <v>17</v>
+      </c>
+      <c r="G42" t="s">
+        <v>9</v>
+      </c>
+      <c r="H42">
+        <f>COUNTIFS(TestMaster[Test Status], "Skipped", TestMaster[Namespace], G38)</f>
+        <v>1</v>
       </c>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.25">
@@ -3825,8 +3845,8 @@
         <v>42</v>
       </c>
       <c r="B43" t="str">
-        <f>'Unit XMLHandlerTests'!A1</f>
-        <v>Constructor Sets Validator And Disambiguator</v>
+        <f>'Unit XMLHandlerTests'!AX1</f>
+        <v>Check For Dependencies With List Processes All Elements</v>
       </c>
       <c r="C43" s="5" t="s">
         <v>8</v>
@@ -3841,8 +3861,8 @@
         <v>43</v>
       </c>
       <c r="B44" t="str">
-        <f>'Unit XMLHandlerTests'!EY1</f>
-        <v>Element Info Is Initialized</v>
+        <f>'Unit XMLHandlerTests'!A1</f>
+        <v>Constructor Sets Validator And Disambiguator</v>
       </c>
       <c r="C44" s="5" t="s">
         <v>8</v>
@@ -3857,8 +3877,8 @@
         <v>44</v>
       </c>
       <c r="B45" t="str">
-        <f>'Unit XMLHandlerTests'!BZ1</f>
-        <v>Find Pathto Root Schema Handles Ambiguous Path With Disambiguator</v>
+        <f>'Unit XMLHandlerTests'!EY1</f>
+        <v>Element Info Is Initialized</v>
       </c>
       <c r="C45" s="5" t="s">
         <v>8</v>
@@ -3873,8 +3893,8 @@
         <v>45</v>
       </c>
       <c r="B46" t="str">
-        <f>'Unit XMLHandlerTests'!BL1</f>
-        <v>Find Pathto Root Schema Returns Path Queue For Valid Element</v>
+        <f>'Unit XMLHandlerTests'!BZ1</f>
+        <v>Find Pathto Root Schema Handles Ambiguous Path With Disambiguator</v>
       </c>
       <c r="C46" s="5" t="s">
         <v>8</v>
@@ -3889,11 +3909,11 @@
         <v>46</v>
       </c>
       <c r="B47" t="str">
-        <f>'Unit XMLHandlerTests'!CG1</f>
-        <v>FindPathtoRootSchema Throws Exception When Ambiguous And No Disambiguator</v>
+        <f>'Unit XMLHandlerTests'!BL1</f>
+        <v>Find Pathto Root Schema Returns Path Queue For Valid Element</v>
       </c>
       <c r="C47" s="5" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E47" t="s">
         <v>17</v>
@@ -3905,11 +3925,11 @@
         <v>47</v>
       </c>
       <c r="B48" t="str">
-        <f>'Unit XMLHandlerTests'!BS1</f>
-        <v>FindPathtoRootSchema Throws Exception When Starting At Root</v>
+        <f>'Unit XMLHandlerTests'!CG1</f>
+        <v>FindPathtoRootSchema Throws Exception When Ambiguous And No Disambiguator</v>
       </c>
       <c r="C48" s="5" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E48" t="s">
         <v>17</v>
@@ -3921,8 +3941,8 @@
         <v>48</v>
       </c>
       <c r="B49" t="str">
-        <f>'Unit XMLHandlerTests'!CN1</f>
-        <v>Get Attributes Returns All Attributes For Element</v>
+        <f>'Unit XMLHandlerTests'!BS1</f>
+        <v>FindPathtoRootSchema Throws Exception When Starting At Root</v>
       </c>
       <c r="C49" s="5" t="s">
         <v>8</v>
@@ -3937,11 +3957,11 @@
         <v>49</v>
       </c>
       <c r="B50" t="str">
-        <f>'Unit XMLHandlerTests'!CU1</f>
-        <v>Get Attributes With Multiple Elements Returns List Of Attribute Lists</v>
+        <f>'Unit XMLHandlerTests'!CN1</f>
+        <v>Get Attributes Returns All Attributes For Element</v>
       </c>
       <c r="C50" s="5" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E50" t="s">
         <v>17</v>
@@ -3953,11 +3973,11 @@
         <v>50</v>
       </c>
       <c r="B51" t="str">
-        <f>'Unit XMLHandlerTests'!O1</f>
-        <v>Get Element Types Returns Valid Types From Document</v>
+        <f>'Unit XMLHandlerTests'!CU1</f>
+        <v>Get Attributes With Multiple Elements Returns List Of Attribute Lists</v>
       </c>
       <c r="C51" s="5" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E51" t="s">
         <v>17</v>
@@ -3969,8 +3989,8 @@
         <v>51</v>
       </c>
       <c r="B52" t="str">
-        <f>'Unit XMLHandlerTests'!H1</f>
-        <v>Get Simple Elements Returns List Of Elements Excluding Custom Properties</v>
+        <f>'Unit XMLHandlerTests'!O1</f>
+        <v>Get Element Types Returns Valid Types From Document</v>
       </c>
       <c r="C52" s="5" t="s">
         <v>8</v>
@@ -3985,8 +4005,8 @@
         <v>52</v>
       </c>
       <c r="B53" t="str">
-        <f>'Unit XMLHandlerTests'!EK1</f>
-        <v>Get Validator Returns Validation Service</v>
+        <f>'Unit XMLHandlerTests'!H1</f>
+        <v>Get Simple Elements Returns List Of Elements Excluding Custom Properties</v>
       </c>
       <c r="C53" s="5" t="s">
         <v>8</v>
@@ -4001,8 +4021,8 @@
         <v>53</v>
       </c>
       <c r="B54" t="str">
-        <f>'Unit XMLHandlerTests'!V1</f>
-        <v>GetElementTypes Throws EmptyListException When No Valid Elements</v>
+        <f>'Unit XMLHandlerTests'!EK1</f>
+        <v>Get Validator Returns Validation Service</v>
       </c>
       <c r="C54" s="5" t="s">
         <v>8</v>
@@ -4017,8 +4037,8 @@
         <v>54</v>
       </c>
       <c r="B55" t="str">
-        <f>'Unit XMLHandlerTests'!DI1</f>
-        <v>Insert Element Adds Element To Document</v>
+        <f>'Unit XMLHandlerTests'!V1</f>
+        <v>GetElementTypes Throws EmptyListException When No Valid Elements</v>
       </c>
       <c r="C55" s="5" t="s">
         <v>8</v>
@@ -4033,11 +4053,11 @@
         <v>55</v>
       </c>
       <c r="B56" t="str">
-        <f>'Unit XMLHandlerTests'!ED1</f>
-        <v>Insert Element Handles Modules With Catalog Number</v>
+        <f>'Unit XMLHandlerTests'!DI1</f>
+        <v>Insert Element Adds Element To Document</v>
       </c>
       <c r="C56" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E56" t="s">
         <v>17</v>
@@ -4049,11 +4069,11 @@
         <v>56</v>
       </c>
       <c r="B57" t="str">
-        <f>'Unit XMLHandlerTests'!DW1</f>
-        <v>Insert Element With List Inserts All Elements</v>
+        <f>'Unit XMLHandlerTests'!ED1</f>
+        <v>Insert Element Handles Modules With Catalog Number</v>
       </c>
       <c r="C57" s="5" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E57" t="s">
         <v>17</v>
@@ -4065,8 +4085,8 @@
         <v>57</v>
       </c>
       <c r="B58" t="str">
-        <f>'Unit XMLHandlerTests'!DP1</f>
-        <v>InsertElement Throws Exception When Element Already Exists</v>
+        <f>'Unit XMLHandlerTests'!DW1</f>
+        <v>Insert Element With List Inserts All Elements</v>
       </c>
       <c r="C58" s="5" t="s">
         <v>8</v>
@@ -4081,8 +4101,8 @@
         <v>58</v>
       </c>
       <c r="B59" t="str">
-        <f>'Unit XMLHandlerTests'!DB1</f>
-        <v>Load Basic File Returns XDocument</v>
+        <f>'Unit XMLHandlerTests'!DP1</f>
+        <v>InsertElement Throws Exception When Element Already Exists</v>
       </c>
       <c r="C59" s="5" t="s">
         <v>8</v>
@@ -4097,8 +4117,8 @@
         <v>59</v>
       </c>
       <c r="B60" t="str">
-        <f>'Unit XMLHandlerTests'!ER1</f>
-        <v>Namespace Is Correct</v>
+        <f>'Unit XMLHandlerTests'!DB1</f>
+        <v>Load Basic File Returns XDocument</v>
       </c>
       <c r="C60" s="5" t="s">
         <v>8</v>
@@ -4112,11 +4132,15 @@
         <f t="shared" si="1"/>
         <v>60</v>
       </c>
-      <c r="B61" t="s">
-        <v>18</v>
+      <c r="B61" t="str">
+        <f>'Unit XMLHandlerTests'!ER1</f>
+        <v>Namespace Is Correct</v>
       </c>
       <c r="C61" s="5" t="s">
-        <v>5</v>
+        <v>8</v>
+      </c>
+      <c r="E61" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="62" spans="1:5" x14ac:dyDescent="0.25">
@@ -4124,6 +4148,12 @@
         <f t="shared" si="1"/>
         <v>61</v>
       </c>
+      <c r="B62" t="s">
+        <v>18</v>
+      </c>
+      <c r="C62" s="5" t="s">
+        <v>5</v>
+      </c>
     </row>
     <row r="63" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A63" s="6">
@@ -4145,13 +4175,13 @@
     </row>
     <row r="66" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A66" s="6">
-        <f t="shared" ref="A66:A72" si="2">ROW()-1</f>
+        <f t="shared" si="1"/>
         <v>65</v>
       </c>
     </row>
     <row r="67" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A67" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" ref="A67:A73" si="2">ROW()-1</f>
         <v>66</v>
       </c>
     </row>
@@ -4183,6 +4213,12 @@
       <c r="A72" s="6">
         <f t="shared" si="2"/>
         <v>71</v>
+      </c>
+    </row>
+    <row r="73" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A73" s="6">
+        <f t="shared" si="2"/>
+        <v>72</v>
       </c>
     </row>
   </sheetData>
@@ -4213,10 +4249,10 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B51 D2:D48 D50:D1048576" xr:uid="{00000000-0002-0000-0000-000000000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B52 D2:D49 D51:D1048576" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>"Low,Medium,High"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B50 C2:C1048576" xr:uid="{00000000-0002-0000-0000-000001000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B51 C2:C1048576" xr:uid="{00000000-0002-0000-0000-000001000000}">
       <formula1>$G:$G</formula1>
     </dataValidation>
   </dataValidations>
@@ -5167,11 +5203,6 @@
     </row>
   </sheetData>
   <mergeCells count="20">
-    <mergeCell ref="G6:L6"/>
-    <mergeCell ref="M4:R5"/>
-    <mergeCell ref="M6:R6"/>
-    <mergeCell ref="M2:N2"/>
-    <mergeCell ref="T6:Y6"/>
     <mergeCell ref="A2:B2"/>
     <mergeCell ref="T2:U2"/>
     <mergeCell ref="M3:N3"/>
@@ -5187,6 +5218,11 @@
     <mergeCell ref="T3:U3"/>
     <mergeCell ref="G1:L1"/>
     <mergeCell ref="G2:H2"/>
+    <mergeCell ref="G6:L6"/>
+    <mergeCell ref="M4:R5"/>
+    <mergeCell ref="M6:R6"/>
+    <mergeCell ref="M2:N2"/>
+    <mergeCell ref="T6:Y6"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -5250,7 +5286,7 @@
       <c r="B2" s="18"/>
       <c r="C2" s="6">
         <f>IFERROR(_xlfn.XLOOKUP(A1, TestMaster[Test Name], TestMaster[Test ID], "ID not found"), "")</f>
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E2" t="s">
         <v>20</v>
@@ -6788,7 +6824,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:160" x14ac:dyDescent="0.25">
-      <c r="A1" s="30" t="s">
+      <c r="A1" s="29" t="s">
         <v>178</v>
       </c>
       <c r="B1" s="18"/>
@@ -6796,7 +6832,7 @@
       <c r="D1" s="18"/>
       <c r="E1" s="18"/>
       <c r="F1" s="18"/>
-      <c r="H1" s="30" t="s">
+      <c r="H1" s="29" t="s">
         <v>179</v>
       </c>
       <c r="I1" s="18"/>
@@ -6804,7 +6840,7 @@
       <c r="K1" s="18"/>
       <c r="L1" s="18"/>
       <c r="M1" s="18"/>
-      <c r="O1" s="30" t="s">
+      <c r="O1" s="29" t="s">
         <v>180</v>
       </c>
       <c r="P1" s="18"/>
@@ -6812,7 +6848,7 @@
       <c r="R1" s="18"/>
       <c r="S1" s="18"/>
       <c r="T1" s="18"/>
-      <c r="V1" s="30" t="s">
+      <c r="V1" s="29" t="s">
         <v>181</v>
       </c>
       <c r="W1" s="18"/>
@@ -6820,7 +6856,7 @@
       <c r="Y1" s="18"/>
       <c r="Z1" s="18"/>
       <c r="AA1" s="18"/>
-      <c r="AC1" s="30" t="s">
+      <c r="AC1" s="29" t="s">
         <v>182</v>
       </c>
       <c r="AD1" s="18"/>
@@ -6828,7 +6864,7 @@
       <c r="AF1" s="18"/>
       <c r="AG1" s="18"/>
       <c r="AH1" s="18"/>
-      <c r="AJ1" s="30" t="s">
+      <c r="AJ1" s="29" t="s">
         <v>183</v>
       </c>
       <c r="AK1" s="18"/>
@@ -6836,7 +6872,7 @@
       <c r="AM1" s="18"/>
       <c r="AN1" s="18"/>
       <c r="AO1" s="18"/>
-      <c r="AQ1" s="30" t="s">
+      <c r="AQ1" s="29" t="s">
         <v>184</v>
       </c>
       <c r="AR1" s="18"/>
@@ -6844,7 +6880,7 @@
       <c r="AT1" s="18"/>
       <c r="AU1" s="18"/>
       <c r="AV1" s="18"/>
-      <c r="AX1" s="30" t="s">
+      <c r="AX1" s="29" t="s">
         <v>185</v>
       </c>
       <c r="AY1" s="18"/>
@@ -6852,7 +6888,7 @@
       <c r="BA1" s="18"/>
       <c r="BB1" s="18"/>
       <c r="BC1" s="18"/>
-      <c r="BE1" s="30" t="s">
+      <c r="BE1" s="29" t="s">
         <v>186</v>
       </c>
       <c r="BF1" s="18"/>
@@ -6860,7 +6896,7 @@
       <c r="BH1" s="18"/>
       <c r="BI1" s="18"/>
       <c r="BJ1" s="18"/>
-      <c r="BL1" s="30" t="s">
+      <c r="BL1" s="29" t="s">
         <v>187</v>
       </c>
       <c r="BM1" s="18"/>
@@ -6868,7 +6904,7 @@
       <c r="BO1" s="18"/>
       <c r="BP1" s="18"/>
       <c r="BQ1" s="18"/>
-      <c r="BS1" s="30" t="s">
+      <c r="BS1" s="29" t="s">
         <v>188</v>
       </c>
       <c r="BT1" s="18"/>
@@ -6876,7 +6912,7 @@
       <c r="BV1" s="18"/>
       <c r="BW1" s="18"/>
       <c r="BX1" s="18"/>
-      <c r="BZ1" s="30" t="s">
+      <c r="BZ1" s="29" t="s">
         <v>189</v>
       </c>
       <c r="CA1" s="18"/>
@@ -6884,7 +6920,7 @@
       <c r="CC1" s="18"/>
       <c r="CD1" s="18"/>
       <c r="CE1" s="18"/>
-      <c r="CG1" s="30" t="s">
+      <c r="CG1" s="29" t="s">
         <v>190</v>
       </c>
       <c r="CH1" s="18"/>
@@ -6892,7 +6928,7 @@
       <c r="CJ1" s="18"/>
       <c r="CK1" s="18"/>
       <c r="CL1" s="18"/>
-      <c r="CN1" s="30" t="s">
+      <c r="CN1" s="29" t="s">
         <v>191</v>
       </c>
       <c r="CO1" s="18"/>
@@ -6900,7 +6936,7 @@
       <c r="CQ1" s="18"/>
       <c r="CR1" s="18"/>
       <c r="CS1" s="18"/>
-      <c r="CU1" s="30" t="s">
+      <c r="CU1" s="29" t="s">
         <v>192</v>
       </c>
       <c r="CV1" s="18"/>
@@ -6908,7 +6944,7 @@
       <c r="CX1" s="18"/>
       <c r="CY1" s="18"/>
       <c r="CZ1" s="18"/>
-      <c r="DB1" s="30" t="s">
+      <c r="DB1" s="29" t="s">
         <v>193</v>
       </c>
       <c r="DC1" s="18"/>
@@ -6916,7 +6952,7 @@
       <c r="DE1" s="18"/>
       <c r="DF1" s="18"/>
       <c r="DG1" s="18"/>
-      <c r="DI1" s="30" t="s">
+      <c r="DI1" s="29" t="s">
         <v>194</v>
       </c>
       <c r="DJ1" s="18"/>
@@ -6924,7 +6960,7 @@
       <c r="DL1" s="18"/>
       <c r="DM1" s="18"/>
       <c r="DN1" s="18"/>
-      <c r="DP1" s="30" t="s">
+      <c r="DP1" s="29" t="s">
         <v>195</v>
       </c>
       <c r="DQ1" s="18"/>
@@ -6932,7 +6968,7 @@
       <c r="DS1" s="18"/>
       <c r="DT1" s="18"/>
       <c r="DU1" s="18"/>
-      <c r="DW1" s="30" t="s">
+      <c r="DW1" s="29" t="s">
         <v>196</v>
       </c>
       <c r="DX1" s="18"/>
@@ -6940,7 +6976,7 @@
       <c r="DZ1" s="18"/>
       <c r="EA1" s="18"/>
       <c r="EB1" s="18"/>
-      <c r="ED1" s="30" t="s">
+      <c r="ED1" s="29" t="s">
         <v>197</v>
       </c>
       <c r="EE1" s="18"/>
@@ -6948,7 +6984,7 @@
       <c r="EG1" s="18"/>
       <c r="EH1" s="18"/>
       <c r="EI1" s="18"/>
-      <c r="EK1" s="30" t="s">
+      <c r="EK1" s="29" t="s">
         <v>198</v>
       </c>
       <c r="EL1" s="18"/>
@@ -6956,7 +6992,7 @@
       <c r="EN1" s="18"/>
       <c r="EO1" s="18"/>
       <c r="EP1" s="18"/>
-      <c r="ER1" s="30" t="s">
+      <c r="ER1" s="29" t="s">
         <v>199</v>
       </c>
       <c r="ES1" s="18"/>
@@ -6964,7 +7000,7 @@
       <c r="EU1" s="18"/>
       <c r="EV1" s="18"/>
       <c r="EW1" s="18"/>
-      <c r="EY1" s="30" t="s">
+      <c r="EY1" s="29" t="s">
         <v>200</v>
       </c>
       <c r="EZ1" s="18"/>
@@ -7560,7 +7596,7 @@
       <c r="A6" s="16" t="s">
         <v>64</v>
       </c>
-      <c r="B6" s="29" t="s">
+      <c r="B6" s="30" t="s">
         <v>201</v>
       </c>
       <c r="C6" s="18"/>
@@ -7570,7 +7606,7 @@
       <c r="H6" s="16" t="s">
         <v>64</v>
       </c>
-      <c r="I6" s="29" t="s">
+      <c r="I6" s="30" t="s">
         <v>202</v>
       </c>
       <c r="J6" s="18"/>
@@ -7580,7 +7616,7 @@
       <c r="O6" s="16" t="s">
         <v>64</v>
       </c>
-      <c r="P6" s="29" t="s">
+      <c r="P6" s="30" t="s">
         <v>203</v>
       </c>
       <c r="Q6" s="18"/>
@@ -7590,7 +7626,7 @@
       <c r="V6" s="16" t="s">
         <v>64</v>
       </c>
-      <c r="W6" s="29" t="s">
+      <c r="W6" s="30" t="s">
         <v>204</v>
       </c>
       <c r="X6" s="18"/>
@@ -7600,7 +7636,7 @@
       <c r="AC6" s="16" t="s">
         <v>64</v>
       </c>
-      <c r="AD6" s="29" t="s">
+      <c r="AD6" s="30" t="s">
         <v>205</v>
       </c>
       <c r="AE6" s="18"/>
@@ -7610,7 +7646,7 @@
       <c r="AJ6" s="16" t="s">
         <v>64</v>
       </c>
-      <c r="AK6" s="29" t="s">
+      <c r="AK6" s="30" t="s">
         <v>206</v>
       </c>
       <c r="AL6" s="18"/>
@@ -7620,7 +7656,7 @@
       <c r="AQ6" s="16" t="s">
         <v>64</v>
       </c>
-      <c r="AR6" s="29" t="s">
+      <c r="AR6" s="30" t="s">
         <v>207</v>
       </c>
       <c r="AS6" s="18"/>
@@ -7630,7 +7666,7 @@
       <c r="AX6" s="16" t="s">
         <v>64</v>
       </c>
-      <c r="AY6" s="29" t="s">
+      <c r="AY6" s="30" t="s">
         <v>208</v>
       </c>
       <c r="AZ6" s="18"/>
@@ -7640,7 +7676,7 @@
       <c r="BE6" s="16" t="s">
         <v>64</v>
       </c>
-      <c r="BF6" s="29" t="s">
+      <c r="BF6" s="30" t="s">
         <v>209</v>
       </c>
       <c r="BG6" s="18"/>
@@ -7650,7 +7686,7 @@
       <c r="BL6" s="16" t="s">
         <v>64</v>
       </c>
-      <c r="BM6" s="29" t="s">
+      <c r="BM6" s="30" t="s">
         <v>210</v>
       </c>
       <c r="BN6" s="18"/>
@@ -7660,7 +7696,7 @@
       <c r="BS6" s="16" t="s">
         <v>64</v>
       </c>
-      <c r="BT6" s="29" t="s">
+      <c r="BT6" s="30" t="s">
         <v>211</v>
       </c>
       <c r="BU6" s="18"/>
@@ -7670,7 +7706,7 @@
       <c r="BZ6" s="16" t="s">
         <v>64</v>
       </c>
-      <c r="CA6" s="29" t="s">
+      <c r="CA6" s="30" t="s">
         <v>212</v>
       </c>
       <c r="CB6" s="18"/>
@@ -7680,7 +7716,7 @@
       <c r="CG6" s="16" t="s">
         <v>64</v>
       </c>
-      <c r="CH6" s="29" t="s">
+      <c r="CH6" s="30" t="s">
         <v>213</v>
       </c>
       <c r="CI6" s="18"/>
@@ -7690,7 +7726,7 @@
       <c r="CN6" s="16" t="s">
         <v>64</v>
       </c>
-      <c r="CO6" s="29" t="s">
+      <c r="CO6" s="30" t="s">
         <v>214</v>
       </c>
       <c r="CP6" s="18"/>
@@ -7700,7 +7736,7 @@
       <c r="CU6" s="16" t="s">
         <v>64</v>
       </c>
-      <c r="CV6" s="29" t="s">
+      <c r="CV6" s="30" t="s">
         <v>215</v>
       </c>
       <c r="CW6" s="18"/>
@@ -7710,7 +7746,7 @@
       <c r="DB6" s="16" t="s">
         <v>64</v>
       </c>
-      <c r="DC6" s="29" t="s">
+      <c r="DC6" s="30" t="s">
         <v>216</v>
       </c>
       <c r="DD6" s="18"/>
@@ -7720,7 +7756,7 @@
       <c r="DI6" s="16" t="s">
         <v>64</v>
       </c>
-      <c r="DJ6" s="29" t="s">
+      <c r="DJ6" s="30" t="s">
         <v>217</v>
       </c>
       <c r="DK6" s="18"/>
@@ -7730,7 +7766,7 @@
       <c r="DP6" s="16" t="s">
         <v>64</v>
       </c>
-      <c r="DQ6" s="29" t="s">
+      <c r="DQ6" s="30" t="s">
         <v>218</v>
       </c>
       <c r="DR6" s="18"/>
@@ -7740,7 +7776,7 @@
       <c r="DW6" s="16" t="s">
         <v>64</v>
       </c>
-      <c r="DX6" s="29" t="s">
+      <c r="DX6" s="30" t="s">
         <v>219</v>
       </c>
       <c r="DY6" s="18"/>
@@ -7750,7 +7786,7 @@
       <c r="ED6" s="16" t="s">
         <v>64</v>
       </c>
-      <c r="EE6" s="29" t="s">
+      <c r="EE6" s="30" t="s">
         <v>220</v>
       </c>
       <c r="EF6" s="18"/>
@@ -7760,7 +7796,7 @@
       <c r="EK6" s="16" t="s">
         <v>64</v>
       </c>
-      <c r="EL6" s="29" t="s">
+      <c r="EL6" s="30" t="s">
         <v>221</v>
       </c>
       <c r="EM6" s="18"/>
@@ -7770,7 +7806,7 @@
       <c r="ER6" s="16" t="s">
         <v>64</v>
       </c>
-      <c r="ES6" s="29" t="s">
+      <c r="ES6" s="30" t="s">
         <v>222</v>
       </c>
       <c r="ET6" s="18"/>
@@ -7780,7 +7816,7 @@
       <c r="EY6" s="16" t="s">
         <v>64</v>
       </c>
-      <c r="EZ6" s="29" t="s">
+      <c r="EZ6" s="30" t="s">
         <v>223</v>
       </c>
       <c r="FA6" s="18"/>
@@ -7792,7 +7828,7 @@
       <c r="A7" s="16" t="s">
         <v>24</v>
       </c>
-      <c r="B7" s="29" t="s">
+      <c r="B7" s="30" t="s">
         <v>224</v>
       </c>
       <c r="C7" s="18"/>
@@ -7802,7 +7838,7 @@
       <c r="H7" s="16" t="s">
         <v>24</v>
       </c>
-      <c r="I7" s="29" t="s">
+      <c r="I7" s="30" t="s">
         <v>224</v>
       </c>
       <c r="J7" s="18"/>
@@ -7812,7 +7848,7 @@
       <c r="O7" s="16" t="s">
         <v>24</v>
       </c>
-      <c r="P7" s="29" t="s">
+      <c r="P7" s="30" t="s">
         <v>224</v>
       </c>
       <c r="Q7" s="18"/>
@@ -7822,7 +7858,7 @@
       <c r="V7" s="16" t="s">
         <v>24</v>
       </c>
-      <c r="W7" s="29" t="s">
+      <c r="W7" s="30" t="s">
         <v>224</v>
       </c>
       <c r="X7" s="18"/>
@@ -7832,7 +7868,7 @@
       <c r="AC7" s="16" t="s">
         <v>24</v>
       </c>
-      <c r="AD7" s="29" t="s">
+      <c r="AD7" s="30" t="s">
         <v>224</v>
       </c>
       <c r="AE7" s="18"/>
@@ -7842,7 +7878,7 @@
       <c r="AJ7" s="16" t="s">
         <v>24</v>
       </c>
-      <c r="AK7" s="29" t="s">
+      <c r="AK7" s="30" t="s">
         <v>224</v>
       </c>
       <c r="AL7" s="18"/>
@@ -7852,7 +7888,7 @@
       <c r="AQ7" s="16" t="s">
         <v>24</v>
       </c>
-      <c r="AR7" s="29" t="s">
+      <c r="AR7" s="30" t="s">
         <v>224</v>
       </c>
       <c r="AS7" s="18"/>
@@ -7862,7 +7898,7 @@
       <c r="AX7" s="16" t="s">
         <v>24</v>
       </c>
-      <c r="AY7" s="29" t="s">
+      <c r="AY7" s="30" t="s">
         <v>224</v>
       </c>
       <c r="AZ7" s="18"/>
@@ -7872,7 +7908,7 @@
       <c r="BE7" s="16" t="s">
         <v>24</v>
       </c>
-      <c r="BF7" s="29" t="s">
+      <c r="BF7" s="30" t="s">
         <v>224</v>
       </c>
       <c r="BG7" s="18"/>
@@ -7882,7 +7918,7 @@
       <c r="BL7" s="16" t="s">
         <v>24</v>
       </c>
-      <c r="BM7" s="29" t="s">
+      <c r="BM7" s="30" t="s">
         <v>224</v>
       </c>
       <c r="BN7" s="18"/>
@@ -7892,7 +7928,7 @@
       <c r="BS7" s="16" t="s">
         <v>24</v>
       </c>
-      <c r="BT7" s="29" t="s">
+      <c r="BT7" s="30" t="s">
         <v>224</v>
       </c>
       <c r="BU7" s="18"/>
@@ -7902,7 +7938,7 @@
       <c r="BZ7" s="16" t="s">
         <v>24</v>
       </c>
-      <c r="CA7" s="29" t="s">
+      <c r="CA7" s="30" t="s">
         <v>224</v>
       </c>
       <c r="CB7" s="18"/>
@@ -7912,7 +7948,7 @@
       <c r="CG7" s="16" t="s">
         <v>24</v>
       </c>
-      <c r="CH7" s="29" t="s">
+      <c r="CH7" s="30" t="s">
         <v>224</v>
       </c>
       <c r="CI7" s="18"/>
@@ -7922,7 +7958,7 @@
       <c r="CN7" s="16" t="s">
         <v>24</v>
       </c>
-      <c r="CO7" s="29" t="s">
+      <c r="CO7" s="30" t="s">
         <v>224</v>
       </c>
       <c r="CP7" s="18"/>
@@ -7932,7 +7968,7 @@
       <c r="CU7" s="16" t="s">
         <v>24</v>
       </c>
-      <c r="CV7" s="29" t="s">
+      <c r="CV7" s="30" t="s">
         <v>224</v>
       </c>
       <c r="CW7" s="18"/>
@@ -7942,7 +7978,7 @@
       <c r="DB7" s="16" t="s">
         <v>24</v>
       </c>
-      <c r="DC7" s="29" t="s">
+      <c r="DC7" s="30" t="s">
         <v>224</v>
       </c>
       <c r="DD7" s="18"/>
@@ -7952,7 +7988,7 @@
       <c r="DI7" s="16" t="s">
         <v>24</v>
       </c>
-      <c r="DJ7" s="29" t="s">
+      <c r="DJ7" s="30" t="s">
         <v>224</v>
       </c>
       <c r="DK7" s="18"/>
@@ -7962,7 +7998,7 @@
       <c r="DP7" s="16" t="s">
         <v>24</v>
       </c>
-      <c r="DQ7" s="29" t="s">
+      <c r="DQ7" s="30" t="s">
         <v>224</v>
       </c>
       <c r="DR7" s="18"/>
@@ -7972,7 +8008,7 @@
       <c r="DW7" s="16" t="s">
         <v>24</v>
       </c>
-      <c r="DX7" s="29" t="s">
+      <c r="DX7" s="30" t="s">
         <v>224</v>
       </c>
       <c r="DY7" s="18"/>
@@ -7982,7 +8018,7 @@
       <c r="ED7" s="16" t="s">
         <v>24</v>
       </c>
-      <c r="EE7" s="29" t="s">
+      <c r="EE7" s="30" t="s">
         <v>224</v>
       </c>
       <c r="EF7" s="18"/>
@@ -7992,7 +8028,7 @@
       <c r="EK7" s="16" t="s">
         <v>24</v>
       </c>
-      <c r="EL7" s="29" t="s">
+      <c r="EL7" s="30" t="s">
         <v>224</v>
       </c>
       <c r="EM7" s="18"/>
@@ -8002,7 +8038,7 @@
       <c r="ER7" s="16" t="s">
         <v>24</v>
       </c>
-      <c r="ES7" s="29" t="s">
+      <c r="ES7" s="30" t="s">
         <v>224</v>
       </c>
       <c r="ET7" s="18"/>
@@ -8012,7 +8048,7 @@
       <c r="EY7" s="16" t="s">
         <v>24</v>
       </c>
-      <c r="EZ7" s="29" t="s">
+      <c r="EZ7" s="30" t="s">
         <v>224</v>
       </c>
       <c r="FA7" s="18"/>
@@ -9318,6 +9354,59 @@
     </row>
   </sheetData>
   <mergeCells count="69">
+    <mergeCell ref="EL7:EP7"/>
+    <mergeCell ref="AD7:AH7"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="BL1:BQ1"/>
+    <mergeCell ref="AY7:BC7"/>
+    <mergeCell ref="CU1:CZ1"/>
+    <mergeCell ref="CH7:CL7"/>
+    <mergeCell ref="AY6:BC6"/>
+    <mergeCell ref="BT6:BX6"/>
+    <mergeCell ref="W7:AA7"/>
+    <mergeCell ref="P7:T7"/>
+    <mergeCell ref="CA7:CE7"/>
+    <mergeCell ref="EE7:EI7"/>
+    <mergeCell ref="CO7:CS7"/>
+    <mergeCell ref="EL6:EP6"/>
+    <mergeCell ref="DX7:EB7"/>
+    <mergeCell ref="EZ6:FD6"/>
+    <mergeCell ref="EK1:EP1"/>
+    <mergeCell ref="H1:M1"/>
+    <mergeCell ref="B6:F6"/>
+    <mergeCell ref="AX1:BC1"/>
+    <mergeCell ref="AK6:AO6"/>
+    <mergeCell ref="DJ6:DN6"/>
+    <mergeCell ref="ES6:EW6"/>
+    <mergeCell ref="ED1:EI1"/>
+    <mergeCell ref="AJ1:AO1"/>
+    <mergeCell ref="AR6:AV6"/>
+    <mergeCell ref="CN1:CS1"/>
+    <mergeCell ref="DC6:DG6"/>
+    <mergeCell ref="DB1:DG1"/>
+    <mergeCell ref="CV6:CZ6"/>
+    <mergeCell ref="ER1:EW1"/>
+    <mergeCell ref="ES7:EW7"/>
+    <mergeCell ref="AC1:AH1"/>
+    <mergeCell ref="EE6:EI6"/>
+    <mergeCell ref="I7:M7"/>
+    <mergeCell ref="BT7:BX7"/>
+    <mergeCell ref="P6:T6"/>
+    <mergeCell ref="CG1:CL1"/>
+    <mergeCell ref="BM7:BQ7"/>
+    <mergeCell ref="CA6:CE6"/>
+    <mergeCell ref="AQ1:AV1"/>
+    <mergeCell ref="AD6:AH6"/>
+    <mergeCell ref="DC7:DG7"/>
+    <mergeCell ref="BZ1:CE1"/>
+    <mergeCell ref="CO6:CS6"/>
+    <mergeCell ref="DP1:DU1"/>
+    <mergeCell ref="DQ7:DU7"/>
+    <mergeCell ref="CH6:CL6"/>
+    <mergeCell ref="BF6:BJ6"/>
+    <mergeCell ref="DW1:EB1"/>
+    <mergeCell ref="DQ6:DU6"/>
+    <mergeCell ref="DJ7:DN7"/>
     <mergeCell ref="EY1:FD1"/>
     <mergeCell ref="V1:AA1"/>
     <mergeCell ref="DX6:EB6"/>
@@ -9334,59 +9423,6 @@
     <mergeCell ref="DI1:DN1"/>
     <mergeCell ref="BF7:BJ7"/>
     <mergeCell ref="BM6:BQ6"/>
-    <mergeCell ref="CH6:CL6"/>
-    <mergeCell ref="BF6:BJ6"/>
-    <mergeCell ref="DW1:EB1"/>
-    <mergeCell ref="DQ6:DU6"/>
-    <mergeCell ref="DJ7:DN7"/>
-    <mergeCell ref="ES7:EW7"/>
-    <mergeCell ref="AC1:AH1"/>
-    <mergeCell ref="EE6:EI6"/>
-    <mergeCell ref="I7:M7"/>
-    <mergeCell ref="BT7:BX7"/>
-    <mergeCell ref="P6:T6"/>
-    <mergeCell ref="CG1:CL1"/>
-    <mergeCell ref="BM7:BQ7"/>
-    <mergeCell ref="CA6:CE6"/>
-    <mergeCell ref="AQ1:AV1"/>
-    <mergeCell ref="AD6:AH6"/>
-    <mergeCell ref="DC7:DG7"/>
-    <mergeCell ref="BZ1:CE1"/>
-    <mergeCell ref="CO6:CS6"/>
-    <mergeCell ref="DP1:DU1"/>
-    <mergeCell ref="DQ7:DU7"/>
-    <mergeCell ref="EZ6:FD6"/>
-    <mergeCell ref="EK1:EP1"/>
-    <mergeCell ref="H1:M1"/>
-    <mergeCell ref="B6:F6"/>
-    <mergeCell ref="AX1:BC1"/>
-    <mergeCell ref="AK6:AO6"/>
-    <mergeCell ref="DJ6:DN6"/>
-    <mergeCell ref="ES6:EW6"/>
-    <mergeCell ref="ED1:EI1"/>
-    <mergeCell ref="AJ1:AO1"/>
-    <mergeCell ref="AR6:AV6"/>
-    <mergeCell ref="CN1:CS1"/>
-    <mergeCell ref="DC6:DG6"/>
-    <mergeCell ref="DB1:DG1"/>
-    <mergeCell ref="CV6:CZ6"/>
-    <mergeCell ref="ER1:EW1"/>
-    <mergeCell ref="EL7:EP7"/>
-    <mergeCell ref="AD7:AH7"/>
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="BL1:BQ1"/>
-    <mergeCell ref="AY7:BC7"/>
-    <mergeCell ref="CU1:CZ1"/>
-    <mergeCell ref="CH7:CL7"/>
-    <mergeCell ref="AY6:BC6"/>
-    <mergeCell ref="BT6:BX6"/>
-    <mergeCell ref="W7:AA7"/>
-    <mergeCell ref="P7:T7"/>
-    <mergeCell ref="CA7:CE7"/>
-    <mergeCell ref="EE7:EI7"/>
-    <mergeCell ref="CO7:CS7"/>
-    <mergeCell ref="EL6:EP6"/>
-    <mergeCell ref="DX7:EB7"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -9423,7 +9459,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:160" x14ac:dyDescent="0.25">
-      <c r="A1" s="30" t="s">
+      <c r="A1" s="29" t="s">
         <v>248</v>
       </c>
       <c r="B1" s="18"/>
@@ -9431,7 +9467,7 @@
       <c r="D1" s="18"/>
       <c r="E1" s="18"/>
       <c r="F1" s="18"/>
-      <c r="H1" s="30" t="s">
+      <c r="H1" s="29" t="s">
         <v>249</v>
       </c>
       <c r="I1" s="18"/>
@@ -9439,7 +9475,7 @@
       <c r="K1" s="18"/>
       <c r="L1" s="18"/>
       <c r="M1" s="18"/>
-      <c r="O1" s="30" t="s">
+      <c r="O1" s="29" t="s">
         <v>250</v>
       </c>
       <c r="P1" s="18"/>
@@ -9447,7 +9483,7 @@
       <c r="R1" s="18"/>
       <c r="S1" s="18"/>
       <c r="T1" s="18"/>
-      <c r="V1" s="30" t="s">
+      <c r="V1" s="29" t="s">
         <v>251</v>
       </c>
       <c r="W1" s="18"/>
@@ -9455,7 +9491,7 @@
       <c r="Y1" s="18"/>
       <c r="Z1" s="18"/>
       <c r="AA1" s="18"/>
-      <c r="AC1" s="30" t="s">
+      <c r="AC1" s="29" t="s">
         <v>252</v>
       </c>
       <c r="AD1" s="18"/>
@@ -9463,7 +9499,7 @@
       <c r="AF1" s="18"/>
       <c r="AG1" s="18"/>
       <c r="AH1" s="18"/>
-      <c r="AJ1" s="30" t="s">
+      <c r="AJ1" s="29" t="s">
         <v>253</v>
       </c>
       <c r="AK1" s="18"/>
@@ -9471,7 +9507,7 @@
       <c r="AM1" s="18"/>
       <c r="AN1" s="18"/>
       <c r="AO1" s="18"/>
-      <c r="AQ1" s="30" t="s">
+      <c r="AQ1" s="29" t="s">
         <v>254</v>
       </c>
       <c r="AR1" s="18"/>
@@ -9479,7 +9515,7 @@
       <c r="AT1" s="18"/>
       <c r="AU1" s="18"/>
       <c r="AV1" s="18"/>
-      <c r="AX1" s="30" t="s">
+      <c r="AX1" s="29" t="s">
         <v>255</v>
       </c>
       <c r="AY1" s="18"/>
@@ -9487,7 +9523,7 @@
       <c r="BA1" s="18"/>
       <c r="BB1" s="18"/>
       <c r="BC1" s="18"/>
-      <c r="BE1" s="30" t="s">
+      <c r="BE1" s="29" t="s">
         <v>256</v>
       </c>
       <c r="BF1" s="18"/>
@@ -9495,7 +9531,7 @@
       <c r="BH1" s="18"/>
       <c r="BI1" s="18"/>
       <c r="BJ1" s="18"/>
-      <c r="BL1" s="30" t="s">
+      <c r="BL1" s="29" t="s">
         <v>257</v>
       </c>
       <c r="BM1" s="18"/>
@@ -9503,7 +9539,7 @@
       <c r="BO1" s="18"/>
       <c r="BP1" s="18"/>
       <c r="BQ1" s="18"/>
-      <c r="BS1" s="30" t="s">
+      <c r="BS1" s="29" t="s">
         <v>258</v>
       </c>
       <c r="BT1" s="18"/>
@@ -9511,7 +9547,7 @@
       <c r="BV1" s="18"/>
       <c r="BW1" s="18"/>
       <c r="BX1" s="18"/>
-      <c r="BZ1" s="30" t="s">
+      <c r="BZ1" s="29" t="s">
         <v>259</v>
       </c>
       <c r="CA1" s="18"/>
@@ -9519,7 +9555,7 @@
       <c r="CC1" s="18"/>
       <c r="CD1" s="18"/>
       <c r="CE1" s="18"/>
-      <c r="CG1" s="30" t="s">
+      <c r="CG1" s="29" t="s">
         <v>260</v>
       </c>
       <c r="CH1" s="18"/>
@@ -9527,7 +9563,7 @@
       <c r="CJ1" s="18"/>
       <c r="CK1" s="18"/>
       <c r="CL1" s="18"/>
-      <c r="CN1" s="30" t="s">
+      <c r="CN1" s="29" t="s">
         <v>261</v>
       </c>
       <c r="CO1" s="18"/>
@@ -9535,7 +9571,7 @@
       <c r="CQ1" s="18"/>
       <c r="CR1" s="18"/>
       <c r="CS1" s="18"/>
-      <c r="CU1" s="30" t="s">
+      <c r="CU1" s="29" t="s">
         <v>262</v>
       </c>
       <c r="CV1" s="18"/>
@@ -9543,7 +9579,7 @@
       <c r="CX1" s="18"/>
       <c r="CY1" s="18"/>
       <c r="CZ1" s="18"/>
-      <c r="DB1" s="30" t="s">
+      <c r="DB1" s="29" t="s">
         <v>263</v>
       </c>
       <c r="DC1" s="18"/>
@@ -9551,7 +9587,7 @@
       <c r="DE1" s="18"/>
       <c r="DF1" s="18"/>
       <c r="DG1" s="18"/>
-      <c r="DI1" s="30" t="s">
+      <c r="DI1" s="29" t="s">
         <v>264</v>
       </c>
       <c r="DJ1" s="18"/>
@@ -9559,7 +9595,7 @@
       <c r="DL1" s="18"/>
       <c r="DM1" s="18"/>
       <c r="DN1" s="18"/>
-      <c r="DP1" s="30" t="s">
+      <c r="DP1" s="29" t="s">
         <v>265</v>
       </c>
       <c r="DQ1" s="18"/>
@@ -9567,7 +9603,7 @@
       <c r="DS1" s="18"/>
       <c r="DT1" s="18"/>
       <c r="DU1" s="18"/>
-      <c r="DW1" s="30" t="s">
+      <c r="DW1" s="29" t="s">
         <v>266</v>
       </c>
       <c r="DX1" s="18"/>
@@ -9575,7 +9611,7 @@
       <c r="DZ1" s="18"/>
       <c r="EA1" s="18"/>
       <c r="EB1" s="18"/>
-      <c r="ED1" s="30" t="s">
+      <c r="ED1" s="29" t="s">
         <v>267</v>
       </c>
       <c r="EE1" s="18"/>
@@ -9583,7 +9619,7 @@
       <c r="EG1" s="18"/>
       <c r="EH1" s="18"/>
       <c r="EI1" s="18"/>
-      <c r="EK1" s="30" t="s">
+      <c r="EK1" s="29" t="s">
         <v>268</v>
       </c>
       <c r="EL1" s="18"/>
@@ -9591,7 +9627,7 @@
       <c r="EN1" s="18"/>
       <c r="EO1" s="18"/>
       <c r="EP1" s="18"/>
-      <c r="ER1" s="30" t="s">
+      <c r="ER1" s="29" t="s">
         <v>269</v>
       </c>
       <c r="ES1" s="18"/>
@@ -9599,7 +9635,7 @@
       <c r="EU1" s="18"/>
       <c r="EV1" s="18"/>
       <c r="EW1" s="18"/>
-      <c r="EY1" s="30" t="s">
+      <c r="EY1" s="29" t="s">
         <v>270</v>
       </c>
       <c r="EZ1" s="18"/>
@@ -9614,161 +9650,161 @@
       </c>
       <c r="B2" s="16">
         <f>IFERROR(_xlfn.XLOOKUP(A1, TestMaster[Test Name], TestMaster[Test ID], "ID not found"), "")</f>
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="H2" s="16" t="s">
         <v>19</v>
       </c>
       <c r="I2" s="16">
         <f>IFERROR(_xlfn.SINGLE(_xlfn.XLOOKUP(H1, TestMaster[Test Name], TestMaster[Test ID], "ID not found")), "")</f>
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="O2" s="16" t="s">
         <v>19</v>
       </c>
       <c r="P2" s="16">
         <f>IFERROR(_xlfn.SINGLE(_xlfn.XLOOKUP(O1, TestMaster[Test Name], TestMaster[Test ID], "ID not found")), "")</f>
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="V2" s="16" t="s">
         <v>19</v>
       </c>
       <c r="W2" s="16">
         <f>IFERROR(_xlfn.SINGLE(_xlfn.XLOOKUP(V1, TestMaster[Test Name], TestMaster[Test ID], "ID not found")), "")</f>
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="AC2" s="16" t="s">
         <v>19</v>
       </c>
       <c r="AD2" s="16">
         <f>IFERROR(_xlfn.SINGLE(_xlfn.XLOOKUP(AC1, TestMaster[Test Name], TestMaster[Test ID], "ID not found")), "")</f>
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="AJ2" s="16" t="s">
         <v>19</v>
       </c>
       <c r="AK2" s="16">
         <f>IFERROR(_xlfn.SINGLE(_xlfn.XLOOKUP(AJ1, TestMaster[Test Name], TestMaster[Test ID], "ID not found")), "")</f>
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="AQ2" s="16" t="s">
         <v>19</v>
       </c>
       <c r="AR2" s="16">
         <f>IFERROR(_xlfn.SINGLE(_xlfn.XLOOKUP(AQ1, TestMaster[Test Name], TestMaster[Test ID], "ID not found")), "")</f>
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="AX2" s="16" t="s">
         <v>19</v>
       </c>
       <c r="AY2" s="16">
         <f>IFERROR(_xlfn.SINGLE(_xlfn.XLOOKUP(AX1, TestMaster[Test Name], TestMaster[Test ID], "ID not found")), "")</f>
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="BE2" s="16" t="s">
         <v>19</v>
       </c>
       <c r="BF2" s="16">
         <f>IFERROR(_xlfn.SINGLE(_xlfn.XLOOKUP(BE1, TestMaster[Test Name], TestMaster[Test ID], "ID not found")), "")</f>
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="BL2" s="16" t="s">
         <v>19</v>
       </c>
       <c r="BM2" s="16">
         <f>IFERROR(_xlfn.SINGLE(_xlfn.XLOOKUP(BL1, TestMaster[Test Name], TestMaster[Test ID], "ID not found")), "")</f>
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="BS2" s="16" t="s">
         <v>19</v>
       </c>
       <c r="BT2" s="16">
         <f>IFERROR(_xlfn.SINGLE(_xlfn.XLOOKUP(BS1, TestMaster[Test Name], TestMaster[Test ID], "ID not found")), "")</f>
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="BZ2" s="16" t="s">
         <v>19</v>
       </c>
       <c r="CA2" s="16">
         <f>IFERROR(_xlfn.SINGLE(_xlfn.XLOOKUP(BZ1, TestMaster[Test Name], TestMaster[Test ID], "ID not found")), "")</f>
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="CG2" s="16" t="s">
         <v>19</v>
       </c>
       <c r="CH2" s="16">
         <f>IFERROR(_xlfn.SINGLE(_xlfn.XLOOKUP(CG1, TestMaster[Test Name], TestMaster[Test ID], "ID not found")), "")</f>
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="CN2" s="16" t="s">
         <v>19</v>
       </c>
       <c r="CO2" s="16">
         <f>IFERROR(_xlfn.SINGLE(_xlfn.XLOOKUP(CN1, TestMaster[Test Name], TestMaster[Test ID], "ID not found")), "")</f>
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="CU2" s="16" t="s">
         <v>19</v>
       </c>
       <c r="CV2" s="16">
         <f>IFERROR(_xlfn.SINGLE(_xlfn.XLOOKUP(CU1, TestMaster[Test Name], TestMaster[Test ID], "ID not found")), "")</f>
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="DB2" s="16" t="s">
         <v>19</v>
       </c>
       <c r="DC2" s="16">
         <f>IFERROR(_xlfn.SINGLE(_xlfn.XLOOKUP(DB1, TestMaster[Test Name], TestMaster[Test ID], "ID not found")), "")</f>
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="DI2" s="16" t="s">
         <v>19</v>
       </c>
       <c r="DJ2" s="16">
         <f>IFERROR(_xlfn.SINGLE(_xlfn.XLOOKUP(DI1, TestMaster[Test Name], TestMaster[Test ID], "ID not found")), "")</f>
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="DP2" s="16" t="s">
         <v>19</v>
       </c>
       <c r="DQ2" s="16">
         <f>IFERROR(_xlfn.SINGLE(_xlfn.XLOOKUP(DP1, TestMaster[Test Name], TestMaster[Test ID], "ID not found")), "")</f>
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="DW2" s="16" t="s">
         <v>19</v>
       </c>
       <c r="DX2" s="16">
         <f>IFERROR(_xlfn.SINGLE(_xlfn.XLOOKUP(DW1, TestMaster[Test Name], TestMaster[Test ID], "ID not found")), "")</f>
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="ED2" s="16" t="s">
         <v>19</v>
       </c>
       <c r="EE2" s="16">
         <f>IFERROR(_xlfn.SINGLE(_xlfn.XLOOKUP(ED1, TestMaster[Test Name], TestMaster[Test ID], "ID not found")), "")</f>
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="EK2" s="16" t="s">
         <v>19</v>
       </c>
       <c r="EL2" s="16">
         <f>IFERROR(_xlfn.SINGLE(_xlfn.XLOOKUP(EK1, TestMaster[Test Name], TestMaster[Test ID], "ID not found")), "")</f>
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="ER2" s="16" t="s">
         <v>19</v>
       </c>
       <c r="ES2" s="16">
         <f>IFERROR(_xlfn.SINGLE(_xlfn.XLOOKUP(ER1, TestMaster[Test Name], TestMaster[Test ID], "ID not found")), "")</f>
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="EY2" s="16" t="s">
         <v>19</v>
       </c>
       <c r="EZ2" s="16">
         <f>IFERROR(_xlfn.SINGLE(_xlfn.XLOOKUP(EY1, TestMaster[Test Name], TestMaster[Test ID], "ID not found")), "")</f>
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="3" spans="1:160" x14ac:dyDescent="0.25">
@@ -10195,7 +10231,7 @@
       <c r="A6" s="16" t="s">
         <v>64</v>
       </c>
-      <c r="B6" s="29" t="s">
+      <c r="B6" s="30" t="s">
         <v>271</v>
       </c>
       <c r="C6" s="18"/>
@@ -10205,7 +10241,7 @@
       <c r="H6" s="16" t="s">
         <v>64</v>
       </c>
-      <c r="I6" s="29" t="s">
+      <c r="I6" s="30" t="s">
         <v>272</v>
       </c>
       <c r="J6" s="18"/>
@@ -10215,7 +10251,7 @@
       <c r="O6" s="16" t="s">
         <v>64</v>
       </c>
-      <c r="P6" s="29" t="s">
+      <c r="P6" s="30" t="s">
         <v>273</v>
       </c>
       <c r="Q6" s="18"/>
@@ -10225,7 +10261,7 @@
       <c r="V6" s="16" t="s">
         <v>64</v>
       </c>
-      <c r="W6" s="29" t="s">
+      <c r="W6" s="30" t="s">
         <v>274</v>
       </c>
       <c r="X6" s="18"/>
@@ -10235,7 +10271,7 @@
       <c r="AC6" s="16" t="s">
         <v>64</v>
       </c>
-      <c r="AD6" s="29" t="s">
+      <c r="AD6" s="30" t="s">
         <v>275</v>
       </c>
       <c r="AE6" s="18"/>
@@ -10245,7 +10281,7 @@
       <c r="AJ6" s="16" t="s">
         <v>64</v>
       </c>
-      <c r="AK6" s="29" t="s">
+      <c r="AK6" s="30" t="s">
         <v>276</v>
       </c>
       <c r="AL6" s="18"/>
@@ -10255,7 +10291,7 @@
       <c r="AQ6" s="16" t="s">
         <v>64</v>
       </c>
-      <c r="AR6" s="29" t="s">
+      <c r="AR6" s="30" t="s">
         <v>277</v>
       </c>
       <c r="AS6" s="18"/>
@@ -10265,7 +10301,7 @@
       <c r="AX6" s="16" t="s">
         <v>64</v>
       </c>
-      <c r="AY6" s="29" t="s">
+      <c r="AY6" s="30" t="s">
         <v>278</v>
       </c>
       <c r="AZ6" s="18"/>
@@ -10275,7 +10311,7 @@
       <c r="BE6" s="16" t="s">
         <v>64</v>
       </c>
-      <c r="BF6" s="29" t="s">
+      <c r="BF6" s="30" t="s">
         <v>279</v>
       </c>
       <c r="BG6" s="18"/>
@@ -10285,7 +10321,7 @@
       <c r="BL6" s="16" t="s">
         <v>64</v>
       </c>
-      <c r="BM6" s="29" t="s">
+      <c r="BM6" s="30" t="s">
         <v>280</v>
       </c>
       <c r="BN6" s="18"/>
@@ -10295,7 +10331,7 @@
       <c r="BS6" s="16" t="s">
         <v>64</v>
       </c>
-      <c r="BT6" s="29" t="s">
+      <c r="BT6" s="30" t="s">
         <v>281</v>
       </c>
       <c r="BU6" s="18"/>
@@ -10305,7 +10341,7 @@
       <c r="BZ6" s="16" t="s">
         <v>64</v>
       </c>
-      <c r="CA6" s="29" t="s">
+      <c r="CA6" s="30" t="s">
         <v>282</v>
       </c>
       <c r="CB6" s="18"/>
@@ -10315,7 +10351,7 @@
       <c r="CG6" s="16" t="s">
         <v>64</v>
       </c>
-      <c r="CH6" s="29" t="s">
+      <c r="CH6" s="30" t="s">
         <v>283</v>
       </c>
       <c r="CI6" s="18"/>
@@ -10325,7 +10361,7 @@
       <c r="CN6" s="16" t="s">
         <v>64</v>
       </c>
-      <c r="CO6" s="29" t="s">
+      <c r="CO6" s="30" t="s">
         <v>284</v>
       </c>
       <c r="CP6" s="18"/>
@@ -10335,7 +10371,7 @@
       <c r="CU6" s="16" t="s">
         <v>64</v>
       </c>
-      <c r="CV6" s="29" t="s">
+      <c r="CV6" s="30" t="s">
         <v>285</v>
       </c>
       <c r="CW6" s="18"/>
@@ -10345,7 +10381,7 @@
       <c r="DB6" s="16" t="s">
         <v>64</v>
       </c>
-      <c r="DC6" s="29" t="s">
+      <c r="DC6" s="30" t="s">
         <v>286</v>
       </c>
       <c r="DD6" s="18"/>
@@ -10355,7 +10391,7 @@
       <c r="DI6" s="16" t="s">
         <v>64</v>
       </c>
-      <c r="DJ6" s="29" t="s">
+      <c r="DJ6" s="30" t="s">
         <v>287</v>
       </c>
       <c r="DK6" s="18"/>
@@ -10365,7 +10401,7 @@
       <c r="DP6" s="16" t="s">
         <v>64</v>
       </c>
-      <c r="DQ6" s="29" t="s">
+      <c r="DQ6" s="30" t="s">
         <v>288</v>
       </c>
       <c r="DR6" s="18"/>
@@ -10375,7 +10411,7 @@
       <c r="DW6" s="16" t="s">
         <v>64</v>
       </c>
-      <c r="DX6" s="29" t="s">
+      <c r="DX6" s="30" t="s">
         <v>289</v>
       </c>
       <c r="DY6" s="18"/>
@@ -10385,7 +10421,7 @@
       <c r="ED6" s="16" t="s">
         <v>64</v>
       </c>
-      <c r="EE6" s="29" t="s">
+      <c r="EE6" s="30" t="s">
         <v>290</v>
       </c>
       <c r="EF6" s="18"/>
@@ -10395,7 +10431,7 @@
       <c r="EK6" s="16" t="s">
         <v>64</v>
       </c>
-      <c r="EL6" s="29" t="s">
+      <c r="EL6" s="30" t="s">
         <v>291</v>
       </c>
       <c r="EM6" s="18"/>
@@ -10405,7 +10441,7 @@
       <c r="ER6" s="16" t="s">
         <v>64</v>
       </c>
-      <c r="ES6" s="29" t="s">
+      <c r="ES6" s="30" t="s">
         <v>292</v>
       </c>
       <c r="ET6" s="18"/>
@@ -10415,7 +10451,7 @@
       <c r="EY6" s="16" t="s">
         <v>64</v>
       </c>
-      <c r="EZ6" s="29" t="s">
+      <c r="EZ6" s="30" t="s">
         <v>293</v>
       </c>
       <c r="FA6" s="18"/>
@@ -10427,7 +10463,7 @@
       <c r="A7" s="16" t="s">
         <v>24</v>
       </c>
-      <c r="B7" s="29" t="s">
+      <c r="B7" s="30" t="s">
         <v>224</v>
       </c>
       <c r="C7" s="18"/>
@@ -10437,7 +10473,7 @@
       <c r="H7" s="16" t="s">
         <v>24</v>
       </c>
-      <c r="I7" s="29" t="s">
+      <c r="I7" s="30" t="s">
         <v>224</v>
       </c>
       <c r="J7" s="18"/>
@@ -10447,7 +10483,7 @@
       <c r="O7" s="16" t="s">
         <v>24</v>
       </c>
-      <c r="P7" s="29" t="s">
+      <c r="P7" s="30" t="s">
         <v>224</v>
       </c>
       <c r="Q7" s="18"/>
@@ -10457,7 +10493,7 @@
       <c r="V7" s="16" t="s">
         <v>24</v>
       </c>
-      <c r="W7" s="29" t="s">
+      <c r="W7" s="30" t="s">
         <v>224</v>
       </c>
       <c r="X7" s="18"/>
@@ -10467,7 +10503,7 @@
       <c r="AC7" s="16" t="s">
         <v>24</v>
       </c>
-      <c r="AD7" s="29" t="s">
+      <c r="AD7" s="30" t="s">
         <v>224</v>
       </c>
       <c r="AE7" s="18"/>
@@ -10477,7 +10513,7 @@
       <c r="AJ7" s="16" t="s">
         <v>24</v>
       </c>
-      <c r="AK7" s="29" t="s">
+      <c r="AK7" s="30" t="s">
         <v>224</v>
       </c>
       <c r="AL7" s="18"/>
@@ -10487,7 +10523,7 @@
       <c r="AQ7" s="16" t="s">
         <v>24</v>
       </c>
-      <c r="AR7" s="29" t="s">
+      <c r="AR7" s="30" t="s">
         <v>224</v>
       </c>
       <c r="AS7" s="18"/>
@@ -10497,7 +10533,7 @@
       <c r="AX7" s="16" t="s">
         <v>24</v>
       </c>
-      <c r="AY7" s="29" t="s">
+      <c r="AY7" s="30" t="s">
         <v>224</v>
       </c>
       <c r="AZ7" s="18"/>
@@ -10507,7 +10543,7 @@
       <c r="BE7" s="16" t="s">
         <v>24</v>
       </c>
-      <c r="BF7" s="29" t="s">
+      <c r="BF7" s="30" t="s">
         <v>224</v>
       </c>
       <c r="BG7" s="18"/>
@@ -10517,7 +10553,7 @@
       <c r="BL7" s="16" t="s">
         <v>24</v>
       </c>
-      <c r="BM7" s="29" t="s">
+      <c r="BM7" s="30" t="s">
         <v>224</v>
       </c>
       <c r="BN7" s="18"/>
@@ -10527,7 +10563,7 @@
       <c r="BS7" s="16" t="s">
         <v>24</v>
       </c>
-      <c r="BT7" s="29" t="s">
+      <c r="BT7" s="30" t="s">
         <v>224</v>
       </c>
       <c r="BU7" s="18"/>
@@ -10537,7 +10573,7 @@
       <c r="BZ7" s="16" t="s">
         <v>24</v>
       </c>
-      <c r="CA7" s="29" t="s">
+      <c r="CA7" s="30" t="s">
         <v>224</v>
       </c>
       <c r="CB7" s="18"/>
@@ -10547,7 +10583,7 @@
       <c r="CG7" s="16" t="s">
         <v>24</v>
       </c>
-      <c r="CH7" s="29" t="s">
+      <c r="CH7" s="30" t="s">
         <v>224</v>
       </c>
       <c r="CI7" s="18"/>
@@ -10557,7 +10593,7 @@
       <c r="CN7" s="16" t="s">
         <v>24</v>
       </c>
-      <c r="CO7" s="29" t="s">
+      <c r="CO7" s="30" t="s">
         <v>224</v>
       </c>
       <c r="CP7" s="18"/>
@@ -10567,7 +10603,7 @@
       <c r="CU7" s="16" t="s">
         <v>24</v>
       </c>
-      <c r="CV7" s="29" t="s">
+      <c r="CV7" s="30" t="s">
         <v>224</v>
       </c>
       <c r="CW7" s="18"/>
@@ -10577,7 +10613,7 @@
       <c r="DB7" s="16" t="s">
         <v>24</v>
       </c>
-      <c r="DC7" s="29" t="s">
+      <c r="DC7" s="30" t="s">
         <v>224</v>
       </c>
       <c r="DD7" s="18"/>
@@ -10587,7 +10623,7 @@
       <c r="DI7" s="16" t="s">
         <v>24</v>
       </c>
-      <c r="DJ7" s="29" t="s">
+      <c r="DJ7" s="30" t="s">
         <v>224</v>
       </c>
       <c r="DK7" s="18"/>
@@ -10597,7 +10633,7 @@
       <c r="DP7" s="16" t="s">
         <v>24</v>
       </c>
-      <c r="DQ7" s="29" t="s">
+      <c r="DQ7" s="30" t="s">
         <v>224</v>
       </c>
       <c r="DR7" s="18"/>
@@ -10607,7 +10643,7 @@
       <c r="DW7" s="16" t="s">
         <v>24</v>
       </c>
-      <c r="DX7" s="29" t="s">
+      <c r="DX7" s="30" t="s">
         <v>224</v>
       </c>
       <c r="DY7" s="18"/>
@@ -10617,7 +10653,7 @@
       <c r="ED7" s="16" t="s">
         <v>24</v>
       </c>
-      <c r="EE7" s="29" t="s">
+      <c r="EE7" s="30" t="s">
         <v>224</v>
       </c>
       <c r="EF7" s="18"/>
@@ -10627,7 +10663,7 @@
       <c r="EK7" s="16" t="s">
         <v>24</v>
       </c>
-      <c r="EL7" s="29" t="s">
+      <c r="EL7" s="30" t="s">
         <v>224</v>
       </c>
       <c r="EM7" s="18"/>
@@ -10637,7 +10673,7 @@
       <c r="ER7" s="16" t="s">
         <v>24</v>
       </c>
-      <c r="ES7" s="29" t="s">
+      <c r="ES7" s="30" t="s">
         <v>224</v>
       </c>
       <c r="ET7" s="18"/>
@@ -10647,7 +10683,7 @@
       <c r="EY7" s="16" t="s">
         <v>24</v>
       </c>
-      <c r="EZ7" s="29" t="s">
+      <c r="EZ7" s="30" t="s">
         <v>224</v>
       </c>
       <c r="FA7" s="18"/>
@@ -11953,6 +11989,59 @@
     </row>
   </sheetData>
   <mergeCells count="69">
+    <mergeCell ref="EL7:EP7"/>
+    <mergeCell ref="AD7:AH7"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="BL1:BQ1"/>
+    <mergeCell ref="AY7:BC7"/>
+    <mergeCell ref="CU1:CZ1"/>
+    <mergeCell ref="CH7:CL7"/>
+    <mergeCell ref="AY6:BC6"/>
+    <mergeCell ref="BT6:BX6"/>
+    <mergeCell ref="W7:AA7"/>
+    <mergeCell ref="P7:T7"/>
+    <mergeCell ref="CA7:CE7"/>
+    <mergeCell ref="EE7:EI7"/>
+    <mergeCell ref="CO7:CS7"/>
+    <mergeCell ref="EL6:EP6"/>
+    <mergeCell ref="DX7:EB7"/>
+    <mergeCell ref="EZ6:FD6"/>
+    <mergeCell ref="EK1:EP1"/>
+    <mergeCell ref="H1:M1"/>
+    <mergeCell ref="B6:F6"/>
+    <mergeCell ref="AX1:BC1"/>
+    <mergeCell ref="AK6:AO6"/>
+    <mergeCell ref="DJ6:DN6"/>
+    <mergeCell ref="ES6:EW6"/>
+    <mergeCell ref="ED1:EI1"/>
+    <mergeCell ref="AJ1:AO1"/>
+    <mergeCell ref="AR6:AV6"/>
+    <mergeCell ref="CN1:CS1"/>
+    <mergeCell ref="DC6:DG6"/>
+    <mergeCell ref="DB1:DG1"/>
+    <mergeCell ref="CV6:CZ6"/>
+    <mergeCell ref="ER1:EW1"/>
+    <mergeCell ref="ES7:EW7"/>
+    <mergeCell ref="AC1:AH1"/>
+    <mergeCell ref="EE6:EI6"/>
+    <mergeCell ref="I7:M7"/>
+    <mergeCell ref="BT7:BX7"/>
+    <mergeCell ref="P6:T6"/>
+    <mergeCell ref="CG1:CL1"/>
+    <mergeCell ref="BM7:BQ7"/>
+    <mergeCell ref="CA6:CE6"/>
+    <mergeCell ref="AQ1:AV1"/>
+    <mergeCell ref="AD6:AH6"/>
+    <mergeCell ref="DC7:DG7"/>
+    <mergeCell ref="BZ1:CE1"/>
+    <mergeCell ref="CO6:CS6"/>
+    <mergeCell ref="DP1:DU1"/>
+    <mergeCell ref="DQ7:DU7"/>
+    <mergeCell ref="CH6:CL6"/>
+    <mergeCell ref="BF6:BJ6"/>
+    <mergeCell ref="DW1:EB1"/>
+    <mergeCell ref="DQ6:DU6"/>
+    <mergeCell ref="DJ7:DN7"/>
     <mergeCell ref="EY1:FD1"/>
     <mergeCell ref="V1:AA1"/>
     <mergeCell ref="DX6:EB6"/>
@@ -11969,59 +12058,6 @@
     <mergeCell ref="DI1:DN1"/>
     <mergeCell ref="BF7:BJ7"/>
     <mergeCell ref="BM6:BQ6"/>
-    <mergeCell ref="CH6:CL6"/>
-    <mergeCell ref="BF6:BJ6"/>
-    <mergeCell ref="DW1:EB1"/>
-    <mergeCell ref="DQ6:DU6"/>
-    <mergeCell ref="DJ7:DN7"/>
-    <mergeCell ref="ES7:EW7"/>
-    <mergeCell ref="AC1:AH1"/>
-    <mergeCell ref="EE6:EI6"/>
-    <mergeCell ref="I7:M7"/>
-    <mergeCell ref="BT7:BX7"/>
-    <mergeCell ref="P6:T6"/>
-    <mergeCell ref="CG1:CL1"/>
-    <mergeCell ref="BM7:BQ7"/>
-    <mergeCell ref="CA6:CE6"/>
-    <mergeCell ref="AQ1:AV1"/>
-    <mergeCell ref="AD6:AH6"/>
-    <mergeCell ref="DC7:DG7"/>
-    <mergeCell ref="BZ1:CE1"/>
-    <mergeCell ref="CO6:CS6"/>
-    <mergeCell ref="DP1:DU1"/>
-    <mergeCell ref="DQ7:DU7"/>
-    <mergeCell ref="EZ6:FD6"/>
-    <mergeCell ref="EK1:EP1"/>
-    <mergeCell ref="H1:M1"/>
-    <mergeCell ref="B6:F6"/>
-    <mergeCell ref="AX1:BC1"/>
-    <mergeCell ref="AK6:AO6"/>
-    <mergeCell ref="DJ6:DN6"/>
-    <mergeCell ref="ES6:EW6"/>
-    <mergeCell ref="ED1:EI1"/>
-    <mergeCell ref="AJ1:AO1"/>
-    <mergeCell ref="AR6:AV6"/>
-    <mergeCell ref="CN1:CS1"/>
-    <mergeCell ref="DC6:DG6"/>
-    <mergeCell ref="DB1:DG1"/>
-    <mergeCell ref="CV6:CZ6"/>
-    <mergeCell ref="ER1:EW1"/>
-    <mergeCell ref="EL7:EP7"/>
-    <mergeCell ref="AD7:AH7"/>
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="BL1:BQ1"/>
-    <mergeCell ref="AY7:BC7"/>
-    <mergeCell ref="CU1:CZ1"/>
-    <mergeCell ref="CH7:CL7"/>
-    <mergeCell ref="AY6:BC6"/>
-    <mergeCell ref="BT6:BX6"/>
-    <mergeCell ref="W7:AA7"/>
-    <mergeCell ref="P7:T7"/>
-    <mergeCell ref="CA7:CE7"/>
-    <mergeCell ref="EE7:EI7"/>
-    <mergeCell ref="CO7:CS7"/>
-    <mergeCell ref="EL6:EP6"/>
-    <mergeCell ref="DX7:EB7"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Test Cases.xlsx
+++ b/Test Cases.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://endresshauser-my.sharepoint.com/personal/corbin_ferguson_endress_com/Documents/ThesisBuildTool/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="180" documentId="8_{B89245B7-08D9-4A9D-8516-F6C9C7AFFDC1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1DD4BC04-1BC5-48F9-A728-AFBCA4180E4B}"/>
+  <xr:revisionPtr revIDLastSave="182" documentId="8_{B89245B7-08D9-4A9D-8516-F6C9C7AFFDC1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8BEB568B-2EAC-49CC-9ACA-DD10EAC98080}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="25440" windowHeight="15270" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="25440" windowHeight="15270" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tests" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1753" uniqueCount="351">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1753" uniqueCount="352">
   <si>
     <t>Test ID</t>
   </si>
@@ -228,9 +228,6 @@
     <t>Nameless Module Creation</t>
   </si>
   <si>
-    <t>Redundant Element Creation</t>
-  </si>
-  <si>
     <t>Description: Test that the standard creation of multiple elements works.</t>
   </si>
   <si>
@@ -1093,6 +1090,12 @@
   </si>
   <si>
     <t>Validation Error Window inaction</t>
+  </si>
+  <si>
+    <t>Description: Test that the creation of multiple elements that clash works.</t>
+  </si>
+  <si>
+    <t>Clashing Element Creation</t>
   </si>
 </sst>
 </file>
@@ -3306,7 +3309,7 @@
         <v>7</v>
       </c>
       <c r="G19" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
@@ -3481,7 +3484,7 @@
       </c>
       <c r="B27" t="str">
         <f>Create!M1</f>
-        <v>Redundant Element Creation</v>
+        <v>Clashing Element Creation</v>
       </c>
       <c r="C27" s="5" t="s">
         <v>5</v>
@@ -3587,7 +3590,7 @@
         <v>11</v>
       </c>
       <c r="E31" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="G31" t="s">
         <v>16</v>
@@ -3609,7 +3612,7 @@
         <v>10</v>
       </c>
       <c r="E32" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="G32" t="s">
         <v>5</v>
@@ -3635,7 +3638,7 @@
         <v>11</v>
       </c>
       <c r="E33" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="G33" t="s">
         <v>8</v>
@@ -3722,7 +3725,7 @@
         <v>36</v>
       </c>
       <c r="B37" s="31" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.25">
@@ -4279,7 +4282,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="19" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="B1" s="18"/>
       <c r="C1" s="18"/>
@@ -4445,13 +4448,13 @@
         <v>6</v>
       </c>
       <c r="B13" s="3" t="s">
+        <v>340</v>
+      </c>
+      <c r="C13" s="3" t="s">
         <v>341</v>
       </c>
-      <c r="C13" s="3" t="s">
+      <c r="D13" s="2" t="s">
         <v>342</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>343</v>
       </c>
     </row>
     <row r="14" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -4463,10 +4466,10 @@
         <v>40</v>
       </c>
       <c r="C14" s="3" t="s">
+        <v>343</v>
+      </c>
+      <c r="D14" s="3" t="s">
         <v>344</v>
-      </c>
-      <c r="D14" s="3" t="s">
-        <v>345</v>
       </c>
     </row>
     <row r="15" spans="1:6" ht="29.1" customHeight="1" x14ac:dyDescent="0.25">
@@ -4475,13 +4478,13 @@
         <v>8</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
     </row>
     <row r="16" spans="1:6" ht="30" x14ac:dyDescent="0.25">
@@ -4490,7 +4493,7 @@
         <v>9</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="C16" s="3" t="s">
         <v>54</v>
@@ -4626,7 +4629,7 @@
       <c r="K1" s="22"/>
       <c r="L1" s="21"/>
       <c r="M1" s="17" t="s">
-        <v>62</v>
+        <v>351</v>
       </c>
       <c r="N1" s="22"/>
       <c r="O1" s="22"/>
@@ -4730,7 +4733,7 @@
     </row>
     <row r="4" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A4" s="19" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B4" s="22"/>
       <c r="C4" s="22"/>
@@ -4738,7 +4741,7 @@
       <c r="E4" s="22"/>
       <c r="F4" s="21"/>
       <c r="G4" s="19" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="H4" s="22"/>
       <c r="I4" s="22"/>
@@ -4746,7 +4749,7 @@
       <c r="K4" s="22"/>
       <c r="L4" s="21"/>
       <c r="M4" s="17" t="s">
-        <v>64</v>
+        <v>350</v>
       </c>
       <c r="N4" s="22"/>
       <c r="O4" s="22"/>
@@ -4885,10 +4888,10 @@
         <v>1</v>
       </c>
       <c r="B8" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="C8" s="3" t="s">
         <v>65</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>66</v>
       </c>
       <c r="D8" s="3" t="s">
         <v>36</v>
@@ -4897,10 +4900,10 @@
         <v>1</v>
       </c>
       <c r="H8" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="I8" s="3" t="s">
         <v>65</v>
-      </c>
-      <c r="I8" s="3" t="s">
-        <v>66</v>
       </c>
       <c r="J8" s="3" t="s">
         <v>36</v>
@@ -4909,10 +4912,10 @@
         <v>1</v>
       </c>
       <c r="N8" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="O8" s="3" t="s">
         <v>65</v>
-      </c>
-      <c r="O8" s="3" t="s">
-        <v>66</v>
       </c>
       <c r="P8" s="3" t="s">
         <v>36</v>
@@ -4938,10 +4941,10 @@
         <v>37</v>
       </c>
       <c r="I9" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="J9" s="3" t="s">
         <v>67</v>
-      </c>
-      <c r="J9" s="3" t="s">
-        <v>68</v>
       </c>
       <c r="M9" s="4">
         <v>2</v>
@@ -4961,7 +4964,7 @@
         <v>3</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C10" s="3" t="s">
         <v>41</v>
@@ -4973,10 +4976,10 @@
         <v>3</v>
       </c>
       <c r="H10" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="I10" s="3" t="s">
         <v>69</v>
-      </c>
-      <c r="I10" s="3" t="s">
-        <v>70</v>
       </c>
       <c r="J10" s="3" t="s">
         <v>48</v>
@@ -4985,7 +4988,7 @@
         <v>3</v>
       </c>
       <c r="N10" s="4" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="O10" s="3" t="s">
         <v>41</v>
@@ -4999,37 +5002,37 @@
         <v>4</v>
       </c>
       <c r="B11" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="C11" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="C11" s="3" t="s">
+      <c r="D11" s="3" t="s">
         <v>72</v>
-      </c>
-      <c r="D11" s="3" t="s">
-        <v>73</v>
       </c>
       <c r="G11" s="4">
         <v>4</v>
       </c>
       <c r="H11" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="I11" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="J11" s="3" t="s">
         <v>74</v>
-      </c>
-      <c r="I11" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="J11" s="3" t="s">
-        <v>75</v>
       </c>
       <c r="M11" s="4">
         <v>4</v>
       </c>
       <c r="N11" s="4" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="O11" s="3" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="P11" s="3" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="12" spans="1:25" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -5037,25 +5040,25 @@
         <v>5</v>
       </c>
       <c r="B12" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="C12" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="C12" s="3" t="s">
+      <c r="D12" s="3" t="s">
         <v>78</v>
-      </c>
-      <c r="D12" s="3" t="s">
-        <v>79</v>
       </c>
       <c r="M12" s="4">
         <v>5</v>
       </c>
       <c r="N12" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="O12" s="3" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="P12" s="3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="13" spans="1:25" ht="29.1" customHeight="1" x14ac:dyDescent="0.25">
@@ -5063,25 +5066,25 @@
         <v>6</v>
       </c>
       <c r="B13" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="C13" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="C13" s="3" t="s">
+      <c r="D13" s="3" t="s">
         <v>84</v>
-      </c>
-      <c r="D13" s="3" t="s">
-        <v>85</v>
       </c>
       <c r="M13" s="4">
         <v>6</v>
       </c>
       <c r="N13" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="O13" s="3" t="s">
+        <v>321</v>
+      </c>
+      <c r="P13" s="3" t="s">
         <v>86</v>
-      </c>
-      <c r="O13" s="3" t="s">
-        <v>322</v>
-      </c>
-      <c r="P13" s="3" t="s">
-        <v>87</v>
       </c>
     </row>
     <row r="14" spans="1:25" x14ac:dyDescent="0.25">
@@ -5095,7 +5098,7 @@
         <v>47</v>
       </c>
       <c r="P14" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="15" spans="1:25" ht="29.1" customHeight="1" x14ac:dyDescent="0.25">
@@ -5103,13 +5106,13 @@
         <v>8</v>
       </c>
       <c r="N15" s="4" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="O15" s="4" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="P15" s="3" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="16" spans="1:25" x14ac:dyDescent="0.25">
@@ -5131,13 +5134,13 @@
         <v>10</v>
       </c>
       <c r="N17" s="4" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="O17" s="4" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="P17" s="3" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="18" spans="13:16" x14ac:dyDescent="0.25">
@@ -5162,10 +5165,10 @@
         <v>53</v>
       </c>
       <c r="O19" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="P19" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
     </row>
     <row r="20" spans="13:16" x14ac:dyDescent="0.25">
@@ -5255,7 +5258,7 @@
   <sheetData>
     <row r="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A1" s="19" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B1" s="18"/>
       <c r="C1" s="18"/>
@@ -5263,7 +5266,7 @@
       <c r="E1" s="18"/>
       <c r="F1" s="21"/>
       <c r="G1" s="23" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="H1" s="18"/>
       <c r="I1" s="18"/>
@@ -5271,7 +5274,7 @@
       <c r="K1" s="18"/>
       <c r="L1" s="21"/>
       <c r="M1" s="17" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="N1" s="18"/>
       <c r="O1" s="18"/>
@@ -5363,7 +5366,7 @@
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A4" s="19" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="B4" s="18"/>
       <c r="C4" s="18"/>
@@ -5371,7 +5374,7 @@
       <c r="E4" s="18"/>
       <c r="F4" s="21"/>
       <c r="G4" s="23" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="H4" s="18"/>
       <c r="I4" s="18"/>
@@ -5379,7 +5382,7 @@
       <c r="K4" s="18"/>
       <c r="L4" s="21"/>
       <c r="M4" s="17" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="N4" s="18"/>
       <c r="O4" s="18"/>
@@ -5494,31 +5497,31 @@
         <v>1</v>
       </c>
       <c r="B8" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="D8" s="4" t="s">
         <v>93</v>
-      </c>
-      <c r="C8" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="D8" s="4" t="s">
-        <v>94</v>
       </c>
       <c r="G8">
         <v>1</v>
       </c>
       <c r="H8" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="M8">
         <v>1</v>
       </c>
       <c r="N8" s="4" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="O8" s="4" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="P8" s="4" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="9" spans="1:18" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -5526,34 +5529,34 @@
         <v>2</v>
       </c>
       <c r="B9" t="s">
+        <v>337</v>
+      </c>
+      <c r="C9" t="s">
         <v>338</v>
-      </c>
-      <c r="C9" t="s">
-        <v>339</v>
       </c>
       <c r="G9">
         <v>2</v>
       </c>
       <c r="H9" s="4" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="I9" s="4" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="J9" s="4" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="M9">
         <v>2</v>
       </c>
       <c r="N9" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="O9" s="3" t="s">
         <v>97</v>
       </c>
-      <c r="O9" s="3" t="s">
+      <c r="P9" s="3" t="s">
         <v>98</v>
-      </c>
-      <c r="P9" s="3" t="s">
-        <v>99</v>
       </c>
     </row>
     <row r="10" spans="1:18" ht="29.1" customHeight="1" x14ac:dyDescent="0.25">
@@ -5561,10 +5564,10 @@
         <v>3</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D10" s="4" t="s">
         <v>59</v>
@@ -5573,25 +5576,25 @@
         <v>3</v>
       </c>
       <c r="H10" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="I10" s="3" t="s">
         <v>97</v>
       </c>
-      <c r="I10" s="3" t="s">
+      <c r="J10" s="3" t="s">
         <v>98</v>
-      </c>
-      <c r="J10" s="3" t="s">
-        <v>99</v>
       </c>
       <c r="M10">
         <v>3</v>
       </c>
       <c r="N10" s="3" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="O10" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="P10" s="3" t="s">
         <v>101</v>
-      </c>
-      <c r="P10" s="3" t="s">
-        <v>102</v>
       </c>
     </row>
     <row r="11" spans="1:18" ht="30" x14ac:dyDescent="0.25">
@@ -5599,25 +5602,25 @@
         <v>4</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="M11">
         <v>4</v>
       </c>
       <c r="N11" t="s">
+        <v>105</v>
+      </c>
+      <c r="O11" t="s">
         <v>106</v>
       </c>
-      <c r="O11" t="s">
-        <v>107</v>
-      </c>
       <c r="P11" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="12" spans="1:18" x14ac:dyDescent="0.25">
@@ -5625,25 +5628,25 @@
         <v>5</v>
       </c>
       <c r="H12" t="s">
+        <v>103</v>
+      </c>
+      <c r="I12" t="s">
+        <v>324</v>
+      </c>
+      <c r="J12" t="s">
         <v>104</v>
-      </c>
-      <c r="I12" t="s">
-        <v>325</v>
-      </c>
-      <c r="J12" t="s">
-        <v>105</v>
       </c>
       <c r="M12">
         <v>5</v>
       </c>
       <c r="N12" t="s">
+        <v>109</v>
+      </c>
+      <c r="O12" t="s">
+        <v>107</v>
+      </c>
+      <c r="P12" t="s">
         <v>110</v>
-      </c>
-      <c r="O12" t="s">
-        <v>108</v>
-      </c>
-      <c r="P12" t="s">
-        <v>111</v>
       </c>
     </row>
     <row r="13" spans="1:18" x14ac:dyDescent="0.25">
@@ -5651,13 +5654,13 @@
         <v>6</v>
       </c>
       <c r="H13" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="I13" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="J13" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="M13">
         <v>6</v>
@@ -5669,7 +5672,7 @@
         <v>47</v>
       </c>
       <c r="P13" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="14" spans="1:18" x14ac:dyDescent="0.25">
@@ -5677,25 +5680,25 @@
         <v>7</v>
       </c>
       <c r="H14" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="I14" t="s">
+        <v>107</v>
+      </c>
+      <c r="J14" t="s">
         <v>108</v>
-      </c>
-      <c r="J14" t="s">
-        <v>109</v>
       </c>
       <c r="M14">
         <v>8</v>
       </c>
       <c r="N14" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="O14" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="P14" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="15" spans="1:18" x14ac:dyDescent="0.25">
@@ -5703,22 +5706,22 @@
         <v>8</v>
       </c>
       <c r="H15" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="I15" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="M15">
         <v>9</v>
       </c>
       <c r="N15" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="O15" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="P15" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="16" spans="1:18" x14ac:dyDescent="0.25">
@@ -5726,13 +5729,13 @@
         <v>9</v>
       </c>
       <c r="H16" t="s">
+        <v>327</v>
+      </c>
+      <c r="I16" t="s">
         <v>328</v>
       </c>
-      <c r="I16" t="s">
-        <v>329</v>
-      </c>
       <c r="J16" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="M16">
         <v>10</v>
@@ -5744,7 +5747,7 @@
         <v>49</v>
       </c>
       <c r="P16" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="17" spans="7:10" x14ac:dyDescent="0.25">
@@ -5752,13 +5755,13 @@
         <v>10</v>
       </c>
       <c r="H17" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="I17" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="J17" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="18" spans="7:10" x14ac:dyDescent="0.25">
@@ -5766,13 +5769,13 @@
         <v>11</v>
       </c>
       <c r="H18" t="s">
+        <v>116</v>
+      </c>
+      <c r="I18" t="s">
         <v>117</v>
       </c>
-      <c r="I18" t="s">
-        <v>118</v>
-      </c>
       <c r="J18" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
     </row>
     <row r="19" spans="7:10" x14ac:dyDescent="0.25">
@@ -5780,13 +5783,13 @@
         <v>12</v>
       </c>
       <c r="H19" t="s">
+        <v>103</v>
+      </c>
+      <c r="I19" t="s">
+        <v>106</v>
+      </c>
+      <c r="J19" t="s">
         <v>104</v>
-      </c>
-      <c r="I19" t="s">
-        <v>107</v>
-      </c>
-      <c r="J19" t="s">
-        <v>105</v>
       </c>
     </row>
     <row r="20" spans="7:10" x14ac:dyDescent="0.25">
@@ -5794,10 +5797,10 @@
         <v>13</v>
       </c>
       <c r="H20" t="s">
+        <v>334</v>
+      </c>
+      <c r="I20" t="s">
         <v>335</v>
-      </c>
-      <c r="I20" t="s">
-        <v>336</v>
       </c>
     </row>
     <row r="21" spans="7:10" x14ac:dyDescent="0.25">
@@ -5805,10 +5808,10 @@
         <v>14</v>
       </c>
       <c r="H21" t="s">
+        <v>116</v>
+      </c>
+      <c r="I21" t="s">
         <v>117</v>
-      </c>
-      <c r="I21" t="s">
-        <v>118</v>
       </c>
       <c r="J21" t="s">
         <v>59</v>
@@ -5863,7 +5866,7 @@
   <sheetData>
     <row r="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A1" s="19" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B1" s="18"/>
       <c r="C1" s="18"/>
@@ -5871,7 +5874,7 @@
       <c r="E1" s="18"/>
       <c r="F1" s="21"/>
       <c r="G1" s="23" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="H1" s="18"/>
       <c r="I1" s="18"/>
@@ -5879,7 +5882,7 @@
       <c r="K1" s="18"/>
       <c r="L1" s="21"/>
       <c r="M1" s="17" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="N1" s="18"/>
       <c r="O1" s="18"/>
@@ -5971,7 +5974,7 @@
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A4" s="26" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B4" s="18"/>
       <c r="C4" s="18"/>
@@ -5979,7 +5982,7 @@
       <c r="E4" s="18"/>
       <c r="F4" s="21"/>
       <c r="G4" s="27" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="H4" s="18"/>
       <c r="I4" s="18"/>
@@ -5987,7 +5990,7 @@
       <c r="K4" s="18"/>
       <c r="L4" s="21"/>
       <c r="M4" s="25" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="N4" s="18"/>
       <c r="O4" s="18"/>
@@ -6017,7 +6020,7 @@
     </row>
     <row r="6" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A6" s="19" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B6" s="18"/>
       <c r="C6" s="18"/>
@@ -6025,7 +6028,7 @@
       <c r="E6" s="18"/>
       <c r="F6" s="21"/>
       <c r="G6" s="23" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="H6" s="18"/>
       <c r="I6" s="18"/>
@@ -6102,39 +6105,39 @@
         <v>1</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="F8" s="13"/>
       <c r="G8" s="3">
         <v>1</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="L8" s="13"/>
       <c r="M8" s="3">
         <v>1</v>
       </c>
       <c r="N8" s="3" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="O8" s="3" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="P8" s="3" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="9" spans="1:18" s="3" customFormat="1" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -6142,10 +6145,10 @@
         <v>2</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="D9" s="3" t="s">
         <v>59</v>
@@ -6155,26 +6158,26 @@
         <v>2</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="L9" s="13"/>
       <c r="M9" s="3">
         <v>2</v>
       </c>
       <c r="N9" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="O9" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="P9" s="3" t="s">
         <v>125</v>
-      </c>
-      <c r="P9" s="3" t="s">
-        <v>126</v>
       </c>
     </row>
     <row r="10" spans="1:18" s="3" customFormat="1" ht="29.1" customHeight="1" x14ac:dyDescent="0.25">
@@ -6183,26 +6186,26 @@
         <v>3</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="I10" s="3" t="s">
+        <v>314</v>
+      </c>
+      <c r="J10" s="3" t="s">
         <v>315</v>
-      </c>
-      <c r="J10" s="3" t="s">
-        <v>316</v>
       </c>
       <c r="L10" s="13"/>
       <c r="M10" s="3">
         <v>3</v>
       </c>
       <c r="N10" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="O10" s="3" t="s">
         <v>127</v>
       </c>
-      <c r="O10" s="3" t="s">
+      <c r="P10" s="3" t="s">
         <v>128</v>
-      </c>
-      <c r="P10" s="3" t="s">
-        <v>129</v>
       </c>
     </row>
     <row r="11" spans="1:18" ht="29.1" customHeight="1" x14ac:dyDescent="0.25">
@@ -6210,25 +6213,25 @@
         <v>4</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="I11" s="3" t="s">
+        <v>316</v>
+      </c>
+      <c r="J11" s="3" t="s">
         <v>317</v>
-      </c>
-      <c r="J11" s="3" t="s">
-        <v>318</v>
       </c>
       <c r="M11" s="3">
         <v>4</v>
       </c>
       <c r="N11" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="O11" s="3" t="s">
         <v>130</v>
       </c>
-      <c r="O11" s="3" t="s">
+      <c r="P11" s="3" t="s">
         <v>131</v>
-      </c>
-      <c r="P11" s="3" t="s">
-        <v>132</v>
       </c>
     </row>
   </sheetData>
@@ -6279,7 +6282,7 @@
   <sheetData>
     <row r="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A1" s="19" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B1" s="18"/>
       <c r="C1" s="18"/>
@@ -6287,7 +6290,7 @@
       <c r="E1" s="18"/>
       <c r="F1" s="21"/>
       <c r="G1" s="17" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="H1" s="18"/>
       <c r="I1" s="18"/>
@@ -6295,7 +6298,7 @@
       <c r="K1" s="18"/>
       <c r="L1" s="18"/>
       <c r="M1" s="23" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="N1" s="18"/>
       <c r="O1" s="18"/>
@@ -6388,7 +6391,7 @@
     </row>
     <row r="4" spans="1:18" s="2" customFormat="1" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="26" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B4" s="20"/>
       <c r="C4" s="20"/>
@@ -6396,7 +6399,7 @@
       <c r="E4" s="20"/>
       <c r="F4" s="21"/>
       <c r="G4" s="25" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="H4" s="20"/>
       <c r="I4" s="20"/>
@@ -6404,7 +6407,7 @@
       <c r="K4" s="20"/>
       <c r="L4" s="20"/>
       <c r="M4" s="27" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="N4" s="20"/>
       <c r="O4" s="20"/>
@@ -6434,7 +6437,7 @@
     </row>
     <row r="6" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A6" s="19" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B6" s="18"/>
       <c r="C6" s="18"/>
@@ -6442,7 +6445,7 @@
       <c r="E6" s="18"/>
       <c r="F6" s="21"/>
       <c r="G6" s="17" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="H6" s="18"/>
       <c r="I6" s="18"/>
@@ -6450,7 +6453,7 @@
       <c r="K6" s="18"/>
       <c r="L6" s="18"/>
       <c r="M6" s="23" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="N6" s="18"/>
       <c r="O6" s="18"/>
@@ -6519,25 +6522,25 @@
         <v>1</v>
       </c>
       <c r="B8" t="s">
+        <v>140</v>
+      </c>
+      <c r="C8" t="s">
         <v>141</v>
       </c>
-      <c r="C8" t="s">
+      <c r="D8" t="s">
         <v>142</v>
-      </c>
-      <c r="D8" t="s">
-        <v>143</v>
       </c>
       <c r="G8">
         <v>1</v>
       </c>
       <c r="H8" t="s">
+        <v>143</v>
+      </c>
+      <c r="I8" t="s">
         <v>144</v>
       </c>
-      <c r="I8" t="s">
+      <c r="J8" t="s">
         <v>145</v>
-      </c>
-      <c r="J8" t="s">
-        <v>146</v>
       </c>
       <c r="M8" s="15">
         <v>1</v>
@@ -6549,25 +6552,25 @@
         <v>2</v>
       </c>
       <c r="B9" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C9" t="s">
+        <v>146</v>
+      </c>
+      <c r="D9" t="s">
         <v>147</v>
-      </c>
-      <c r="D9" t="s">
-        <v>148</v>
       </c>
       <c r="G9">
         <v>2</v>
       </c>
       <c r="H9" t="s">
+        <v>148</v>
+      </c>
+      <c r="I9" t="s">
         <v>149</v>
       </c>
-      <c r="I9" t="s">
+      <c r="J9" t="s">
         <v>150</v>
-      </c>
-      <c r="J9" t="s">
-        <v>151</v>
       </c>
       <c r="M9" s="15">
         <v>2</v>
@@ -6579,25 +6582,25 @@
         <v>3</v>
       </c>
       <c r="B10" t="s">
+        <v>151</v>
+      </c>
+      <c r="C10" t="s">
         <v>152</v>
       </c>
-      <c r="C10" t="s">
+      <c r="D10" t="s">
         <v>153</v>
-      </c>
-      <c r="D10" t="s">
-        <v>154</v>
       </c>
       <c r="G10">
         <v>3</v>
       </c>
       <c r="H10" t="s">
+        <v>154</v>
+      </c>
+      <c r="I10" t="s">
         <v>155</v>
       </c>
-      <c r="I10" t="s">
+      <c r="J10" t="s">
         <v>156</v>
-      </c>
-      <c r="J10" t="s">
-        <v>157</v>
       </c>
       <c r="M10" s="15">
         <v>3</v>
@@ -6609,25 +6612,25 @@
         <v>4</v>
       </c>
       <c r="B11" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="C11" s="2" t="s">
         <v>158</v>
       </c>
-      <c r="C11" s="2" t="s">
+      <c r="D11" t="s">
         <v>159</v>
-      </c>
-      <c r="D11" t="s">
-        <v>160</v>
       </c>
       <c r="G11">
         <v>4</v>
       </c>
       <c r="H11" t="s">
+        <v>160</v>
+      </c>
+      <c r="I11" t="s">
+        <v>65</v>
+      </c>
+      <c r="J11" t="s">
         <v>161</v>
-      </c>
-      <c r="I11" t="s">
-        <v>66</v>
-      </c>
-      <c r="J11" t="s">
-        <v>162</v>
       </c>
       <c r="M11" s="15">
         <v>4</v>
@@ -6642,10 +6645,10 @@
         <v>5</v>
       </c>
       <c r="B12" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D12" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
     </row>
     <row r="13" spans="1:18" x14ac:dyDescent="0.25">
@@ -6653,13 +6656,13 @@
         <v>6</v>
       </c>
       <c r="B13" t="s">
+        <v>163</v>
+      </c>
+      <c r="C13" t="s">
         <v>164</v>
       </c>
-      <c r="C13" t="s">
-        <v>165</v>
-      </c>
       <c r="D13" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
     </row>
     <row r="14" spans="1:18" x14ac:dyDescent="0.25">
@@ -6667,10 +6670,10 @@
         <v>7</v>
       </c>
       <c r="B14" t="s">
+        <v>165</v>
+      </c>
+      <c r="C14" t="s">
         <v>166</v>
-      </c>
-      <c r="C14" t="s">
-        <v>167</v>
       </c>
     </row>
     <row r="15" spans="1:18" x14ac:dyDescent="0.25">
@@ -6678,13 +6681,13 @@
         <v>8</v>
       </c>
       <c r="B15" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C15" t="s">
         <v>58</v>
       </c>
       <c r="D15" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
     </row>
     <row r="16" spans="1:18" x14ac:dyDescent="0.25">
@@ -6692,10 +6695,10 @@
         <v>9</v>
       </c>
       <c r="B16" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C16" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="D16" t="s">
         <v>59</v>
@@ -6706,13 +6709,13 @@
         <v>10</v>
       </c>
       <c r="B17" t="s">
+        <v>170</v>
+      </c>
+      <c r="C17" t="s">
         <v>171</v>
       </c>
-      <c r="C17" t="s">
+      <c r="D17" t="s">
         <v>172</v>
-      </c>
-      <c r="D17" t="s">
-        <v>173</v>
       </c>
     </row>
     <row r="18" spans="1:4" ht="72.599999999999994" customHeight="1" x14ac:dyDescent="0.25">
@@ -6720,13 +6723,13 @@
         <v>11</v>
       </c>
       <c r="B18" t="s">
+        <v>173</v>
+      </c>
+      <c r="C18" s="2" t="s">
         <v>174</v>
       </c>
-      <c r="C18" s="2" t="s">
+      <c r="D18" s="2" t="s">
         <v>175</v>
-      </c>
-      <c r="D18" s="2" t="s">
-        <v>176</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
@@ -6734,13 +6737,13 @@
         <v>12</v>
       </c>
       <c r="B19" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C19" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D19" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
@@ -6748,13 +6751,13 @@
         <v>13</v>
       </c>
       <c r="B20" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C20" t="s">
         <v>44</v>
       </c>
       <c r="D20" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
@@ -6762,10 +6765,10 @@
         <v>14</v>
       </c>
       <c r="B21" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C21" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="D21" t="s">
         <v>59</v>
@@ -6825,7 +6828,7 @@
   <sheetData>
     <row r="1" spans="1:160" x14ac:dyDescent="0.25">
       <c r="A1" s="29" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B1" s="18"/>
       <c r="C1" s="18"/>
@@ -6833,7 +6836,7 @@
       <c r="E1" s="18"/>
       <c r="F1" s="18"/>
       <c r="H1" s="29" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="I1" s="18"/>
       <c r="J1" s="18"/>
@@ -6841,7 +6844,7 @@
       <c r="L1" s="18"/>
       <c r="M1" s="18"/>
       <c r="O1" s="29" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="P1" s="18"/>
       <c r="Q1" s="18"/>
@@ -6849,7 +6852,7 @@
       <c r="S1" s="18"/>
       <c r="T1" s="18"/>
       <c r="V1" s="29" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="W1" s="18"/>
       <c r="X1" s="18"/>
@@ -6857,7 +6860,7 @@
       <c r="Z1" s="18"/>
       <c r="AA1" s="18"/>
       <c r="AC1" s="29" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="AD1" s="18"/>
       <c r="AE1" s="18"/>
@@ -6865,7 +6868,7 @@
       <c r="AG1" s="18"/>
       <c r="AH1" s="18"/>
       <c r="AJ1" s="29" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="AK1" s="18"/>
       <c r="AL1" s="18"/>
@@ -6873,7 +6876,7 @@
       <c r="AN1" s="18"/>
       <c r="AO1" s="18"/>
       <c r="AQ1" s="29" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="AR1" s="18"/>
       <c r="AS1" s="18"/>
@@ -6881,7 +6884,7 @@
       <c r="AU1" s="18"/>
       <c r="AV1" s="18"/>
       <c r="AX1" s="29" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="AY1" s="18"/>
       <c r="AZ1" s="18"/>
@@ -6889,7 +6892,7 @@
       <c r="BB1" s="18"/>
       <c r="BC1" s="18"/>
       <c r="BE1" s="29" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="BF1" s="18"/>
       <c r="BG1" s="18"/>
@@ -6897,7 +6900,7 @@
       <c r="BI1" s="18"/>
       <c r="BJ1" s="18"/>
       <c r="BL1" s="29" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="BM1" s="18"/>
       <c r="BN1" s="18"/>
@@ -6905,7 +6908,7 @@
       <c r="BP1" s="18"/>
       <c r="BQ1" s="18"/>
       <c r="BS1" s="29" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="BT1" s="18"/>
       <c r="BU1" s="18"/>
@@ -6913,7 +6916,7 @@
       <c r="BW1" s="18"/>
       <c r="BX1" s="18"/>
       <c r="BZ1" s="29" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="CA1" s="18"/>
       <c r="CB1" s="18"/>
@@ -6921,7 +6924,7 @@
       <c r="CD1" s="18"/>
       <c r="CE1" s="18"/>
       <c r="CG1" s="29" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="CH1" s="18"/>
       <c r="CI1" s="18"/>
@@ -6929,7 +6932,7 @@
       <c r="CK1" s="18"/>
       <c r="CL1" s="18"/>
       <c r="CN1" s="29" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="CO1" s="18"/>
       <c r="CP1" s="18"/>
@@ -6937,7 +6940,7 @@
       <c r="CR1" s="18"/>
       <c r="CS1" s="18"/>
       <c r="CU1" s="29" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="CV1" s="18"/>
       <c r="CW1" s="18"/>
@@ -6945,7 +6948,7 @@
       <c r="CY1" s="18"/>
       <c r="CZ1" s="18"/>
       <c r="DB1" s="29" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="DC1" s="18"/>
       <c r="DD1" s="18"/>
@@ -6953,7 +6956,7 @@
       <c r="DF1" s="18"/>
       <c r="DG1" s="18"/>
       <c r="DI1" s="29" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="DJ1" s="18"/>
       <c r="DK1" s="18"/>
@@ -6961,7 +6964,7 @@
       <c r="DM1" s="18"/>
       <c r="DN1" s="18"/>
       <c r="DP1" s="29" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="DQ1" s="18"/>
       <c r="DR1" s="18"/>
@@ -6969,7 +6972,7 @@
       <c r="DT1" s="18"/>
       <c r="DU1" s="18"/>
       <c r="DW1" s="29" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="DX1" s="18"/>
       <c r="DY1" s="18"/>
@@ -6977,7 +6980,7 @@
       <c r="EA1" s="18"/>
       <c r="EB1" s="18"/>
       <c r="ED1" s="29" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="EE1" s="18"/>
       <c r="EF1" s="18"/>
@@ -6985,7 +6988,7 @@
       <c r="EH1" s="18"/>
       <c r="EI1" s="18"/>
       <c r="EK1" s="29" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="EL1" s="18"/>
       <c r="EM1" s="18"/>
@@ -6993,7 +6996,7 @@
       <c r="EO1" s="18"/>
       <c r="EP1" s="18"/>
       <c r="ER1" s="29" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="ES1" s="18"/>
       <c r="ET1" s="18"/>
@@ -7001,7 +7004,7 @@
       <c r="EV1" s="18"/>
       <c r="EW1" s="18"/>
       <c r="EY1" s="29" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="EZ1" s="18"/>
       <c r="FA1" s="18"/>
@@ -7594,230 +7597,230 @@
     </row>
     <row r="6" spans="1:160" x14ac:dyDescent="0.25">
       <c r="A6" s="16" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B6" s="30" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="C6" s="18"/>
       <c r="D6" s="18"/>
       <c r="E6" s="18"/>
       <c r="F6" s="18"/>
       <c r="H6" s="16" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="I6" s="30" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="J6" s="18"/>
       <c r="K6" s="18"/>
       <c r="L6" s="18"/>
       <c r="M6" s="18"/>
       <c r="O6" s="16" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="P6" s="30" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="Q6" s="18"/>
       <c r="R6" s="18"/>
       <c r="S6" s="18"/>
       <c r="T6" s="18"/>
       <c r="V6" s="16" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="W6" s="30" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="X6" s="18"/>
       <c r="Y6" s="18"/>
       <c r="Z6" s="18"/>
       <c r="AA6" s="18"/>
       <c r="AC6" s="16" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="AD6" s="30" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="AE6" s="18"/>
       <c r="AF6" s="18"/>
       <c r="AG6" s="18"/>
       <c r="AH6" s="18"/>
       <c r="AJ6" s="16" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="AK6" s="30" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="AL6" s="18"/>
       <c r="AM6" s="18"/>
       <c r="AN6" s="18"/>
       <c r="AO6" s="18"/>
       <c r="AQ6" s="16" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="AR6" s="30" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="AS6" s="18"/>
       <c r="AT6" s="18"/>
       <c r="AU6" s="18"/>
       <c r="AV6" s="18"/>
       <c r="AX6" s="16" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="AY6" s="30" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="AZ6" s="18"/>
       <c r="BA6" s="18"/>
       <c r="BB6" s="18"/>
       <c r="BC6" s="18"/>
       <c r="BE6" s="16" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="BF6" s="30" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="BG6" s="18"/>
       <c r="BH6" s="18"/>
       <c r="BI6" s="18"/>
       <c r="BJ6" s="18"/>
       <c r="BL6" s="16" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="BM6" s="30" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="BN6" s="18"/>
       <c r="BO6" s="18"/>
       <c r="BP6" s="18"/>
       <c r="BQ6" s="18"/>
       <c r="BS6" s="16" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="BT6" s="30" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="BU6" s="18"/>
       <c r="BV6" s="18"/>
       <c r="BW6" s="18"/>
       <c r="BX6" s="18"/>
       <c r="BZ6" s="16" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="CA6" s="30" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="CB6" s="18"/>
       <c r="CC6" s="18"/>
       <c r="CD6" s="18"/>
       <c r="CE6" s="18"/>
       <c r="CG6" s="16" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="CH6" s="30" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="CI6" s="18"/>
       <c r="CJ6" s="18"/>
       <c r="CK6" s="18"/>
       <c r="CL6" s="18"/>
       <c r="CN6" s="16" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="CO6" s="30" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="CP6" s="18"/>
       <c r="CQ6" s="18"/>
       <c r="CR6" s="18"/>
       <c r="CS6" s="18"/>
       <c r="CU6" s="16" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="CV6" s="30" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="CW6" s="18"/>
       <c r="CX6" s="18"/>
       <c r="CY6" s="18"/>
       <c r="CZ6" s="18"/>
       <c r="DB6" s="16" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="DC6" s="30" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="DD6" s="18"/>
       <c r="DE6" s="18"/>
       <c r="DF6" s="18"/>
       <c r="DG6" s="18"/>
       <c r="DI6" s="16" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="DJ6" s="30" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="DK6" s="18"/>
       <c r="DL6" s="18"/>
       <c r="DM6" s="18"/>
       <c r="DN6" s="18"/>
       <c r="DP6" s="16" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="DQ6" s="30" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="DR6" s="18"/>
       <c r="DS6" s="18"/>
       <c r="DT6" s="18"/>
       <c r="DU6" s="18"/>
       <c r="DW6" s="16" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="DX6" s="30" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="DY6" s="18"/>
       <c r="DZ6" s="18"/>
       <c r="EA6" s="18"/>
       <c r="EB6" s="18"/>
       <c r="ED6" s="16" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="EE6" s="30" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="EF6" s="18"/>
       <c r="EG6" s="18"/>
       <c r="EH6" s="18"/>
       <c r="EI6" s="18"/>
       <c r="EK6" s="16" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="EL6" s="30" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="EM6" s="18"/>
       <c r="EN6" s="18"/>
       <c r="EO6" s="18"/>
       <c r="EP6" s="18"/>
       <c r="ER6" s="16" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="ES6" s="30" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="ET6" s="18"/>
       <c r="EU6" s="18"/>
       <c r="EV6" s="18"/>
       <c r="EW6" s="18"/>
       <c r="EY6" s="16" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="EZ6" s="30" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="FA6" s="18"/>
       <c r="FB6" s="18"/>
@@ -7829,7 +7832,7 @@
         <v>24</v>
       </c>
       <c r="B7" s="30" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="C7" s="18"/>
       <c r="D7" s="18"/>
@@ -7839,7 +7842,7 @@
         <v>24</v>
       </c>
       <c r="I7" s="30" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="J7" s="18"/>
       <c r="K7" s="18"/>
@@ -7849,7 +7852,7 @@
         <v>24</v>
       </c>
       <c r="P7" s="30" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="Q7" s="18"/>
       <c r="R7" s="18"/>
@@ -7859,7 +7862,7 @@
         <v>24</v>
       </c>
       <c r="W7" s="30" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="X7" s="18"/>
       <c r="Y7" s="18"/>
@@ -7869,7 +7872,7 @@
         <v>24</v>
       </c>
       <c r="AD7" s="30" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="AE7" s="18"/>
       <c r="AF7" s="18"/>
@@ -7879,7 +7882,7 @@
         <v>24</v>
       </c>
       <c r="AK7" s="30" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="AL7" s="18"/>
       <c r="AM7" s="18"/>
@@ -7889,7 +7892,7 @@
         <v>24</v>
       </c>
       <c r="AR7" s="30" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="AS7" s="18"/>
       <c r="AT7" s="18"/>
@@ -7899,7 +7902,7 @@
         <v>24</v>
       </c>
       <c r="AY7" s="30" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="AZ7" s="18"/>
       <c r="BA7" s="18"/>
@@ -7909,7 +7912,7 @@
         <v>24</v>
       </c>
       <c r="BF7" s="30" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="BG7" s="18"/>
       <c r="BH7" s="18"/>
@@ -7919,7 +7922,7 @@
         <v>24</v>
       </c>
       <c r="BM7" s="30" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="BN7" s="18"/>
       <c r="BO7" s="18"/>
@@ -7929,7 +7932,7 @@
         <v>24</v>
       </c>
       <c r="BT7" s="30" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="BU7" s="18"/>
       <c r="BV7" s="18"/>
@@ -7939,7 +7942,7 @@
         <v>24</v>
       </c>
       <c r="CA7" s="30" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="CB7" s="18"/>
       <c r="CC7" s="18"/>
@@ -7949,7 +7952,7 @@
         <v>24</v>
       </c>
       <c r="CH7" s="30" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="CI7" s="18"/>
       <c r="CJ7" s="18"/>
@@ -7959,7 +7962,7 @@
         <v>24</v>
       </c>
       <c r="CO7" s="30" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="CP7" s="18"/>
       <c r="CQ7" s="18"/>
@@ -7969,7 +7972,7 @@
         <v>24</v>
       </c>
       <c r="CV7" s="30" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="CW7" s="18"/>
       <c r="CX7" s="18"/>
@@ -7979,7 +7982,7 @@
         <v>24</v>
       </c>
       <c r="DC7" s="30" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="DD7" s="18"/>
       <c r="DE7" s="18"/>
@@ -7989,7 +7992,7 @@
         <v>24</v>
       </c>
       <c r="DJ7" s="30" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="DK7" s="18"/>
       <c r="DL7" s="18"/>
@@ -7999,7 +8002,7 @@
         <v>24</v>
       </c>
       <c r="DQ7" s="30" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="DR7" s="18"/>
       <c r="DS7" s="18"/>
@@ -8009,7 +8012,7 @@
         <v>24</v>
       </c>
       <c r="DX7" s="30" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="DY7" s="18"/>
       <c r="DZ7" s="18"/>
@@ -8019,7 +8022,7 @@
         <v>24</v>
       </c>
       <c r="EE7" s="30" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="EF7" s="18"/>
       <c r="EG7" s="18"/>
@@ -8029,7 +8032,7 @@
         <v>24</v>
       </c>
       <c r="EL7" s="30" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="EM7" s="18"/>
       <c r="EN7" s="18"/>
@@ -8039,7 +8042,7 @@
         <v>24</v>
       </c>
       <c r="ES7" s="30" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="ET7" s="18"/>
       <c r="EU7" s="18"/>
@@ -8049,7 +8052,7 @@
         <v>24</v>
       </c>
       <c r="EZ7" s="30" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="FA7" s="18"/>
       <c r="FB7" s="18"/>
@@ -8474,880 +8477,880 @@
     </row>
     <row r="9" spans="1:160" ht="29.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="16" t="s">
+        <v>224</v>
+      </c>
+      <c r="B9" s="16" t="s">
         <v>225</v>
       </c>
-      <c r="B9" s="16" t="s">
+      <c r="C9" s="16" t="s">
         <v>226</v>
       </c>
-      <c r="C9" s="16" t="s">
+      <c r="D9" s="16" t="s">
         <v>227</v>
-      </c>
-      <c r="D9" s="16" t="s">
-        <v>228</v>
       </c>
       <c r="E9" s="16"/>
       <c r="F9" s="16"/>
       <c r="H9" s="16" t="s">
+        <v>224</v>
+      </c>
+      <c r="I9" s="16" t="s">
         <v>225</v>
       </c>
-      <c r="I9" s="16" t="s">
+      <c r="J9" s="16" t="s">
         <v>226</v>
       </c>
-      <c r="J9" s="16" t="s">
+      <c r="K9" s="16" t="s">
         <v>227</v>
-      </c>
-      <c r="K9" s="16" t="s">
-        <v>228</v>
       </c>
       <c r="L9" s="16"/>
       <c r="M9" s="16"/>
       <c r="O9" s="16" t="s">
+        <v>224</v>
+      </c>
+      <c r="P9" s="16" t="s">
         <v>225</v>
       </c>
-      <c r="P9" s="16" t="s">
+      <c r="Q9" s="16" t="s">
         <v>226</v>
       </c>
-      <c r="Q9" s="16" t="s">
+      <c r="R9" s="16" t="s">
         <v>227</v>
-      </c>
-      <c r="R9" s="16" t="s">
-        <v>228</v>
       </c>
       <c r="S9" s="16"/>
       <c r="T9" s="16"/>
       <c r="V9" s="16" t="s">
+        <v>224</v>
+      </c>
+      <c r="W9" s="16" t="s">
         <v>225</v>
       </c>
-      <c r="W9" s="16" t="s">
+      <c r="X9" s="16" t="s">
         <v>226</v>
       </c>
-      <c r="X9" s="16" t="s">
+      <c r="Y9" s="16" t="s">
         <v>227</v>
-      </c>
-      <c r="Y9" s="16" t="s">
-        <v>228</v>
       </c>
       <c r="Z9" s="16"/>
       <c r="AA9" s="16"/>
       <c r="AC9" s="16" t="s">
+        <v>224</v>
+      </c>
+      <c r="AD9" s="16" t="s">
         <v>225</v>
       </c>
-      <c r="AD9" s="16" t="s">
+      <c r="AE9" s="16" t="s">
         <v>226</v>
       </c>
-      <c r="AE9" s="16" t="s">
+      <c r="AF9" s="16" t="s">
         <v>227</v>
-      </c>
-      <c r="AF9" s="16" t="s">
-        <v>228</v>
       </c>
       <c r="AG9" s="16"/>
       <c r="AH9" s="16"/>
       <c r="AJ9" s="16" t="s">
+        <v>224</v>
+      </c>
+      <c r="AK9" s="16" t="s">
         <v>225</v>
       </c>
-      <c r="AK9" s="16" t="s">
+      <c r="AL9" s="16" t="s">
         <v>226</v>
       </c>
-      <c r="AL9" s="16" t="s">
+      <c r="AM9" s="16" t="s">
         <v>227</v>
-      </c>
-      <c r="AM9" s="16" t="s">
-        <v>228</v>
       </c>
       <c r="AN9" s="16"/>
       <c r="AO9" s="16"/>
       <c r="AQ9" s="16" t="s">
+        <v>224</v>
+      </c>
+      <c r="AR9" s="16" t="s">
         <v>225</v>
       </c>
-      <c r="AR9" s="16" t="s">
+      <c r="AS9" s="16" t="s">
         <v>226</v>
       </c>
-      <c r="AS9" s="16" t="s">
+      <c r="AT9" s="16" t="s">
         <v>227</v>
-      </c>
-      <c r="AT9" s="16" t="s">
-        <v>228</v>
       </c>
       <c r="AU9" s="16"/>
       <c r="AV9" s="16"/>
       <c r="AX9" s="16" t="s">
+        <v>224</v>
+      </c>
+      <c r="AY9" s="16" t="s">
         <v>225</v>
       </c>
-      <c r="AY9" s="16" t="s">
+      <c r="AZ9" s="16" t="s">
         <v>226</v>
       </c>
-      <c r="AZ9" s="16" t="s">
+      <c r="BA9" s="16" t="s">
         <v>227</v>
-      </c>
-      <c r="BA9" s="16" t="s">
-        <v>228</v>
       </c>
       <c r="BB9" s="16"/>
       <c r="BC9" s="16"/>
       <c r="BE9" s="16" t="s">
+        <v>224</v>
+      </c>
+      <c r="BF9" s="16" t="s">
         <v>225</v>
       </c>
-      <c r="BF9" s="16" t="s">
+      <c r="BG9" s="16" t="s">
         <v>226</v>
       </c>
-      <c r="BG9" s="16" t="s">
+      <c r="BH9" s="16" t="s">
         <v>227</v>
-      </c>
-      <c r="BH9" s="16" t="s">
-        <v>228</v>
       </c>
       <c r="BI9" s="16"/>
       <c r="BJ9" s="16"/>
       <c r="BL9" s="16" t="s">
+        <v>224</v>
+      </c>
+      <c r="BM9" s="16" t="s">
         <v>225</v>
       </c>
-      <c r="BM9" s="16" t="s">
+      <c r="BN9" s="16" t="s">
         <v>226</v>
       </c>
-      <c r="BN9" s="16" t="s">
+      <c r="BO9" s="16" t="s">
         <v>227</v>
-      </c>
-      <c r="BO9" s="16" t="s">
-        <v>228</v>
       </c>
       <c r="BP9" s="16"/>
       <c r="BQ9" s="16"/>
       <c r="BS9" s="16" t="s">
+        <v>224</v>
+      </c>
+      <c r="BT9" s="16" t="s">
         <v>225</v>
       </c>
-      <c r="BT9" s="16" t="s">
+      <c r="BU9" s="16" t="s">
         <v>226</v>
       </c>
-      <c r="BU9" s="16" t="s">
+      <c r="BV9" s="16" t="s">
         <v>227</v>
-      </c>
-      <c r="BV9" s="16" t="s">
-        <v>228</v>
       </c>
       <c r="BW9" s="16"/>
       <c r="BX9" s="16"/>
       <c r="BZ9" s="16" t="s">
+        <v>224</v>
+      </c>
+      <c r="CA9" s="16" t="s">
         <v>225</v>
       </c>
-      <c r="CA9" s="16" t="s">
+      <c r="CB9" s="16" t="s">
         <v>226</v>
       </c>
-      <c r="CB9" s="16" t="s">
+      <c r="CC9" s="16" t="s">
         <v>227</v>
-      </c>
-      <c r="CC9" s="16" t="s">
-        <v>228</v>
       </c>
       <c r="CD9" s="16"/>
       <c r="CE9" s="16"/>
       <c r="CG9" s="16" t="s">
+        <v>224</v>
+      </c>
+      <c r="CH9" s="16" t="s">
         <v>225</v>
       </c>
-      <c r="CH9" s="16" t="s">
+      <c r="CI9" s="16" t="s">
         <v>226</v>
       </c>
-      <c r="CI9" s="16" t="s">
+      <c r="CJ9" s="16" t="s">
         <v>227</v>
-      </c>
-      <c r="CJ9" s="16" t="s">
-        <v>228</v>
       </c>
       <c r="CK9" s="16"/>
       <c r="CL9" s="16"/>
       <c r="CN9" s="16" t="s">
+        <v>224</v>
+      </c>
+      <c r="CO9" s="16" t="s">
         <v>225</v>
       </c>
-      <c r="CO9" s="16" t="s">
+      <c r="CP9" s="16" t="s">
         <v>226</v>
       </c>
-      <c r="CP9" s="16" t="s">
+      <c r="CQ9" s="16" t="s">
         <v>227</v>
-      </c>
-      <c r="CQ9" s="16" t="s">
-        <v>228</v>
       </c>
       <c r="CR9" s="16"/>
       <c r="CS9" s="16"/>
       <c r="CU9" s="16" t="s">
+        <v>224</v>
+      </c>
+      <c r="CV9" s="16" t="s">
         <v>225</v>
       </c>
-      <c r="CV9" s="16" t="s">
+      <c r="CW9" s="16" t="s">
         <v>226</v>
       </c>
-      <c r="CW9" s="16" t="s">
+      <c r="CX9" s="16" t="s">
         <v>227</v>
-      </c>
-      <c r="CX9" s="16" t="s">
-        <v>228</v>
       </c>
       <c r="CY9" s="16"/>
       <c r="CZ9" s="16"/>
       <c r="DB9" s="16" t="s">
+        <v>224</v>
+      </c>
+      <c r="DC9" s="16" t="s">
         <v>225</v>
       </c>
-      <c r="DC9" s="16" t="s">
+      <c r="DD9" s="16" t="s">
         <v>226</v>
       </c>
-      <c r="DD9" s="16" t="s">
+      <c r="DE9" s="16" t="s">
         <v>227</v>
-      </c>
-      <c r="DE9" s="16" t="s">
-        <v>228</v>
       </c>
       <c r="DF9" s="16"/>
       <c r="DG9" s="16"/>
       <c r="DI9" s="16" t="s">
+        <v>224</v>
+      </c>
+      <c r="DJ9" s="16" t="s">
         <v>225</v>
       </c>
-      <c r="DJ9" s="16" t="s">
+      <c r="DK9" s="16" t="s">
         <v>226</v>
       </c>
-      <c r="DK9" s="16" t="s">
+      <c r="DL9" s="16" t="s">
         <v>227</v>
-      </c>
-      <c r="DL9" s="16" t="s">
-        <v>228</v>
       </c>
       <c r="DM9" s="16"/>
       <c r="DN9" s="16"/>
       <c r="DP9" s="16" t="s">
+        <v>224</v>
+      </c>
+      <c r="DQ9" s="16" t="s">
         <v>225</v>
       </c>
-      <c r="DQ9" s="16" t="s">
+      <c r="DR9" s="16" t="s">
         <v>226</v>
       </c>
-      <c r="DR9" s="16" t="s">
+      <c r="DS9" s="16" t="s">
         <v>227</v>
-      </c>
-      <c r="DS9" s="16" t="s">
-        <v>228</v>
       </c>
       <c r="DT9" s="16"/>
       <c r="DU9" s="16"/>
       <c r="DW9" s="16" t="s">
+        <v>224</v>
+      </c>
+      <c r="DX9" s="16" t="s">
         <v>225</v>
       </c>
-      <c r="DX9" s="16" t="s">
+      <c r="DY9" s="16" t="s">
         <v>226</v>
       </c>
-      <c r="DY9" s="16" t="s">
+      <c r="DZ9" s="16" t="s">
         <v>227</v>
-      </c>
-      <c r="DZ9" s="16" t="s">
-        <v>228</v>
       </c>
       <c r="EA9" s="16"/>
       <c r="EB9" s="16"/>
       <c r="ED9" s="16" t="s">
+        <v>224</v>
+      </c>
+      <c r="EE9" s="16" t="s">
         <v>225</v>
       </c>
-      <c r="EE9" s="16" t="s">
+      <c r="EF9" s="16" t="s">
         <v>226</v>
       </c>
-      <c r="EF9" s="16" t="s">
+      <c r="EG9" s="16" t="s">
         <v>227</v>
-      </c>
-      <c r="EG9" s="16" t="s">
-        <v>228</v>
       </c>
       <c r="EH9" s="16"/>
       <c r="EI9" s="16"/>
       <c r="EK9" s="16" t="s">
+        <v>224</v>
+      </c>
+      <c r="EL9" s="16" t="s">
         <v>225</v>
       </c>
-      <c r="EL9" s="16" t="s">
+      <c r="EM9" s="16" t="s">
         <v>226</v>
       </c>
-      <c r="EM9" s="16" t="s">
+      <c r="EN9" s="16" t="s">
         <v>227</v>
-      </c>
-      <c r="EN9" s="16" t="s">
-        <v>228</v>
       </c>
       <c r="EO9" s="16"/>
       <c r="EP9" s="16"/>
       <c r="ER9" s="16" t="s">
+        <v>224</v>
+      </c>
+      <c r="ES9" s="16" t="s">
         <v>225</v>
       </c>
-      <c r="ES9" s="16" t="s">
+      <c r="ET9" s="16" t="s">
         <v>226</v>
       </c>
-      <c r="ET9" s="16" t="s">
+      <c r="EU9" s="16" t="s">
         <v>227</v>
-      </c>
-      <c r="EU9" s="16" t="s">
-        <v>228</v>
       </c>
       <c r="EV9" s="16"/>
       <c r="EW9" s="16"/>
       <c r="EY9" s="16" t="s">
+        <v>224</v>
+      </c>
+      <c r="EZ9" s="16" t="s">
         <v>225</v>
       </c>
-      <c r="EZ9" s="16" t="s">
+      <c r="FA9" s="16" t="s">
         <v>226</v>
       </c>
-      <c r="FA9" s="16" t="s">
+      <c r="FB9" s="16" t="s">
         <v>227</v>
-      </c>
-      <c r="FB9" s="16" t="s">
-        <v>228</v>
       </c>
       <c r="FC9" s="16"/>
       <c r="FD9" s="16"/>
     </row>
     <row r="10" spans="1:160" ht="29.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="16" t="s">
+        <v>228</v>
+      </c>
+      <c r="B10" s="16" t="s">
         <v>229</v>
-      </c>
-      <c r="B10" s="16" t="s">
-        <v>230</v>
       </c>
       <c r="C10" s="16"/>
       <c r="D10" s="16" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="E10" s="16"/>
       <c r="F10" s="16"/>
       <c r="H10" s="16" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="I10" s="16" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="J10" s="16"/>
       <c r="K10" s="16" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="L10" s="16"/>
       <c r="M10" s="16"/>
       <c r="O10" s="16" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="P10" s="16" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="Q10" s="16"/>
       <c r="R10" s="16" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="S10" s="16"/>
       <c r="T10" s="16"/>
       <c r="V10" s="16" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="W10" s="16" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="X10" s="16"/>
       <c r="Y10" s="16" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="Z10" s="16"/>
       <c r="AA10" s="16"/>
       <c r="AC10" s="16" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="AD10" s="16" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="AE10" s="16"/>
       <c r="AF10" s="16" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="AG10" s="16"/>
       <c r="AH10" s="16"/>
       <c r="AJ10" s="16" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="AK10" s="16" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="AL10" s="16"/>
       <c r="AM10" s="16" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="AN10" s="16"/>
       <c r="AO10" s="16"/>
       <c r="AQ10" s="16" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="AR10" s="16" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="AS10" s="16"/>
       <c r="AT10" s="16" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="AU10" s="16"/>
       <c r="AV10" s="16"/>
       <c r="AX10" s="16" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="AY10" s="16" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="AZ10" s="16"/>
       <c r="BA10" s="16" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="BB10" s="16"/>
       <c r="BC10" s="16"/>
       <c r="BE10" s="16" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="BF10" s="16" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="BG10" s="16"/>
       <c r="BH10" s="16" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="BI10" s="16"/>
       <c r="BJ10" s="16"/>
       <c r="BL10" s="16" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="BM10" s="16" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="BN10" s="16"/>
       <c r="BO10" s="16" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="BP10" s="16"/>
       <c r="BQ10" s="16"/>
       <c r="BS10" s="16" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="BT10" s="16" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="BU10" s="16"/>
       <c r="BV10" s="16" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="BW10" s="16"/>
       <c r="BX10" s="16"/>
       <c r="BZ10" s="16" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="CA10" s="16" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="CB10" s="16"/>
       <c r="CC10" s="16" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="CD10" s="16"/>
       <c r="CE10" s="16"/>
       <c r="CG10" s="16" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="CH10" s="16" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="CI10" s="16"/>
       <c r="CJ10" s="16" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="CK10" s="16"/>
       <c r="CL10" s="16"/>
       <c r="CN10" s="16" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="CO10" s="16" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="CP10" s="16"/>
       <c r="CQ10" s="16" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="CR10" s="16"/>
       <c r="CS10" s="16"/>
       <c r="CU10" s="16" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="CV10" s="16" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="CW10" s="16"/>
       <c r="CX10" s="16" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="CY10" s="16"/>
       <c r="CZ10" s="16"/>
       <c r="DB10" s="16" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="DC10" s="16" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="DD10" s="16"/>
       <c r="DE10" s="16" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="DF10" s="16"/>
       <c r="DG10" s="16"/>
       <c r="DI10" s="16" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="DJ10" s="16" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="DK10" s="16"/>
       <c r="DL10" s="16" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="DM10" s="16"/>
       <c r="DN10" s="16"/>
       <c r="DP10" s="16" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="DQ10" s="16" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="DR10" s="16"/>
       <c r="DS10" s="16" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="DT10" s="16"/>
       <c r="DU10" s="16"/>
       <c r="DW10" s="16" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="DX10" s="16" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="DY10" s="16"/>
       <c r="DZ10" s="16" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="EA10" s="16"/>
       <c r="EB10" s="16"/>
       <c r="ED10" s="16" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="EE10" s="16" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="EF10" s="16"/>
       <c r="EG10" s="16" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="EH10" s="16"/>
       <c r="EI10" s="16"/>
       <c r="EK10" s="16" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="EL10" s="16" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="EM10" s="16"/>
       <c r="EN10" s="16" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="EO10" s="16"/>
       <c r="EP10" s="16"/>
       <c r="ER10" s="16" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="ES10" s="16" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="ET10" s="16"/>
       <c r="EU10" s="16" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="EV10" s="16"/>
       <c r="EW10" s="16"/>
       <c r="EY10" s="16" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="EZ10" s="16" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="FA10" s="16"/>
       <c r="FB10" s="16" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="FC10" s="16"/>
       <c r="FD10" s="16"/>
     </row>
     <row r="11" spans="1:160" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="16" t="s">
+        <v>243</v>
+      </c>
+      <c r="B11" s="16" t="s">
         <v>244</v>
-      </c>
-      <c r="B11" s="16" t="s">
-        <v>245</v>
       </c>
       <c r="C11" s="16"/>
       <c r="D11" s="16" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="E11" s="16"/>
       <c r="F11" s="16"/>
       <c r="H11" s="16" t="s">
+        <v>243</v>
+      </c>
+      <c r="I11" s="16" t="s">
         <v>244</v>
-      </c>
-      <c r="I11" s="16" t="s">
-        <v>245</v>
       </c>
       <c r="J11" s="16"/>
       <c r="K11" s="16" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="L11" s="16"/>
       <c r="M11" s="16"/>
       <c r="O11" s="16" t="s">
+        <v>243</v>
+      </c>
+      <c r="P11" s="16" t="s">
         <v>244</v>
-      </c>
-      <c r="P11" s="16" t="s">
-        <v>245</v>
       </c>
       <c r="Q11" s="16"/>
       <c r="R11" s="16" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="S11" s="16"/>
       <c r="T11" s="16"/>
       <c r="V11" s="16" t="s">
+        <v>243</v>
+      </c>
+      <c r="W11" s="16" t="s">
         <v>244</v>
-      </c>
-      <c r="W11" s="16" t="s">
-        <v>245</v>
       </c>
       <c r="X11" s="16"/>
       <c r="Y11" s="16" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="Z11" s="16"/>
       <c r="AA11" s="16"/>
       <c r="AC11" s="16" t="s">
+        <v>243</v>
+      </c>
+      <c r="AD11" s="16" t="s">
         <v>244</v>
-      </c>
-      <c r="AD11" s="16" t="s">
-        <v>245</v>
       </c>
       <c r="AE11" s="16"/>
       <c r="AF11" s="16" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="AG11" s="16"/>
       <c r="AH11" s="16"/>
       <c r="AJ11" s="16" t="s">
+        <v>243</v>
+      </c>
+      <c r="AK11" s="16" t="s">
         <v>244</v>
-      </c>
-      <c r="AK11" s="16" t="s">
-        <v>245</v>
       </c>
       <c r="AL11" s="16"/>
       <c r="AM11" s="16" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="AN11" s="16"/>
       <c r="AO11" s="16"/>
       <c r="AQ11" s="16" t="s">
+        <v>243</v>
+      </c>
+      <c r="AR11" s="16" t="s">
         <v>244</v>
-      </c>
-      <c r="AR11" s="16" t="s">
-        <v>245</v>
       </c>
       <c r="AS11" s="16"/>
       <c r="AT11" s="16" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="AU11" s="16"/>
       <c r="AV11" s="16"/>
       <c r="AX11" s="16" t="s">
+        <v>243</v>
+      </c>
+      <c r="AY11" s="16" t="s">
         <v>244</v>
-      </c>
-      <c r="AY11" s="16" t="s">
-        <v>245</v>
       </c>
       <c r="AZ11" s="16"/>
       <c r="BA11" s="16" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="BB11" s="16"/>
       <c r="BC11" s="16"/>
       <c r="BE11" s="16" t="s">
+        <v>243</v>
+      </c>
+      <c r="BF11" s="16" t="s">
         <v>244</v>
-      </c>
-      <c r="BF11" s="16" t="s">
-        <v>245</v>
       </c>
       <c r="BG11" s="16"/>
       <c r="BH11" s="16" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="BI11" s="16"/>
       <c r="BJ11" s="16"/>
       <c r="BL11" s="16" t="s">
+        <v>243</v>
+      </c>
+      <c r="BM11" s="16" t="s">
         <v>244</v>
-      </c>
-      <c r="BM11" s="16" t="s">
-        <v>245</v>
       </c>
       <c r="BN11" s="16"/>
       <c r="BO11" s="16" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="BP11" s="16"/>
       <c r="BQ11" s="16"/>
       <c r="BS11" s="16" t="s">
+        <v>243</v>
+      </c>
+      <c r="BT11" s="16" t="s">
         <v>244</v>
-      </c>
-      <c r="BT11" s="16" t="s">
-        <v>245</v>
       </c>
       <c r="BU11" s="16"/>
       <c r="BV11" s="16" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="BW11" s="16"/>
       <c r="BX11" s="16"/>
       <c r="BZ11" s="16" t="s">
+        <v>243</v>
+      </c>
+      <c r="CA11" s="16" t="s">
         <v>244</v>
-      </c>
-      <c r="CA11" s="16" t="s">
-        <v>245</v>
       </c>
       <c r="CB11" s="16"/>
       <c r="CC11" s="16" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="CD11" s="16"/>
       <c r="CE11" s="16"/>
       <c r="CG11" s="16" t="s">
+        <v>243</v>
+      </c>
+      <c r="CH11" s="16" t="s">
         <v>244</v>
-      </c>
-      <c r="CH11" s="16" t="s">
-        <v>245</v>
       </c>
       <c r="CI11" s="16"/>
       <c r="CJ11" s="16" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="CK11" s="16"/>
       <c r="CL11" s="16"/>
       <c r="CN11" s="16" t="s">
+        <v>243</v>
+      </c>
+      <c r="CO11" s="16" t="s">
         <v>244</v>
-      </c>
-      <c r="CO11" s="16" t="s">
-        <v>245</v>
       </c>
       <c r="CP11" s="16"/>
       <c r="CQ11" s="16" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="CR11" s="16"/>
       <c r="CS11" s="16"/>
       <c r="CU11" s="16" t="s">
+        <v>243</v>
+      </c>
+      <c r="CV11" s="16" t="s">
         <v>244</v>
-      </c>
-      <c r="CV11" s="16" t="s">
-        <v>245</v>
       </c>
       <c r="CW11" s="16"/>
       <c r="CX11" s="16" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="CY11" s="16"/>
       <c r="CZ11" s="16"/>
       <c r="DB11" s="16" t="s">
+        <v>243</v>
+      </c>
+      <c r="DC11" s="16" t="s">
         <v>244</v>
-      </c>
-      <c r="DC11" s="16" t="s">
-        <v>245</v>
       </c>
       <c r="DD11" s="16"/>
       <c r="DE11" s="16" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="DF11" s="16"/>
       <c r="DG11" s="16"/>
       <c r="DI11" s="16" t="s">
+        <v>243</v>
+      </c>
+      <c r="DJ11" s="16" t="s">
         <v>244</v>
-      </c>
-      <c r="DJ11" s="16" t="s">
-        <v>245</v>
       </c>
       <c r="DK11" s="16"/>
       <c r="DL11" s="16" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="DM11" s="16"/>
       <c r="DN11" s="16"/>
       <c r="DP11" s="16" t="s">
+        <v>243</v>
+      </c>
+      <c r="DQ11" s="16" t="s">
         <v>244</v>
-      </c>
-      <c r="DQ11" s="16" t="s">
-        <v>245</v>
       </c>
       <c r="DR11" s="16"/>
       <c r="DS11" s="16" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="DT11" s="16"/>
       <c r="DU11" s="16"/>
       <c r="DW11" s="16" t="s">
+        <v>243</v>
+      </c>
+      <c r="DX11" s="16" t="s">
         <v>244</v>
-      </c>
-      <c r="DX11" s="16" t="s">
-        <v>245</v>
       </c>
       <c r="DY11" s="16"/>
       <c r="DZ11" s="16" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="EA11" s="16"/>
       <c r="EB11" s="16"/>
       <c r="ED11" s="16" t="s">
+        <v>243</v>
+      </c>
+      <c r="EE11" s="16" t="s">
         <v>244</v>
-      </c>
-      <c r="EE11" s="16" t="s">
-        <v>245</v>
       </c>
       <c r="EF11" s="16"/>
       <c r="EG11" s="16" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="EH11" s="16"/>
       <c r="EI11" s="16"/>
       <c r="EK11" s="16" t="s">
+        <v>243</v>
+      </c>
+      <c r="EL11" s="16" t="s">
         <v>244</v>
-      </c>
-      <c r="EL11" s="16" t="s">
-        <v>245</v>
       </c>
       <c r="EM11" s="16"/>
       <c r="EN11" s="16" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="EO11" s="16"/>
       <c r="EP11" s="16"/>
       <c r="ER11" s="16" t="s">
+        <v>243</v>
+      </c>
+      <c r="ES11" s="16" t="s">
         <v>244</v>
-      </c>
-      <c r="ES11" s="16" t="s">
-        <v>245</v>
       </c>
       <c r="ET11" s="16"/>
       <c r="EU11" s="16" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="EV11" s="16"/>
       <c r="EW11" s="16"/>
       <c r="EY11" s="16" t="s">
+        <v>243</v>
+      </c>
+      <c r="EZ11" s="16" t="s">
         <v>244</v>
-      </c>
-      <c r="EZ11" s="16" t="s">
-        <v>245</v>
       </c>
       <c r="FA11" s="16"/>
       <c r="FB11" s="16" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="FC11" s="16"/>
       <c r="FD11" s="16"/>
@@ -9460,7 +9463,7 @@
   <sheetData>
     <row r="1" spans="1:160" x14ac:dyDescent="0.25">
       <c r="A1" s="29" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="B1" s="18"/>
       <c r="C1" s="18"/>
@@ -9468,7 +9471,7 @@
       <c r="E1" s="18"/>
       <c r="F1" s="18"/>
       <c r="H1" s="29" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="I1" s="18"/>
       <c r="J1" s="18"/>
@@ -9476,7 +9479,7 @@
       <c r="L1" s="18"/>
       <c r="M1" s="18"/>
       <c r="O1" s="29" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="P1" s="18"/>
       <c r="Q1" s="18"/>
@@ -9484,7 +9487,7 @@
       <c r="S1" s="18"/>
       <c r="T1" s="18"/>
       <c r="V1" s="29" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="W1" s="18"/>
       <c r="X1" s="18"/>
@@ -9492,7 +9495,7 @@
       <c r="Z1" s="18"/>
       <c r="AA1" s="18"/>
       <c r="AC1" s="29" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="AD1" s="18"/>
       <c r="AE1" s="18"/>
@@ -9500,7 +9503,7 @@
       <c r="AG1" s="18"/>
       <c r="AH1" s="18"/>
       <c r="AJ1" s="29" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="AK1" s="18"/>
       <c r="AL1" s="18"/>
@@ -9508,7 +9511,7 @@
       <c r="AN1" s="18"/>
       <c r="AO1" s="18"/>
       <c r="AQ1" s="29" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="AR1" s="18"/>
       <c r="AS1" s="18"/>
@@ -9516,7 +9519,7 @@
       <c r="AU1" s="18"/>
       <c r="AV1" s="18"/>
       <c r="AX1" s="29" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="AY1" s="18"/>
       <c r="AZ1" s="18"/>
@@ -9524,7 +9527,7 @@
       <c r="BB1" s="18"/>
       <c r="BC1" s="18"/>
       <c r="BE1" s="29" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="BF1" s="18"/>
       <c r="BG1" s="18"/>
@@ -9532,7 +9535,7 @@
       <c r="BI1" s="18"/>
       <c r="BJ1" s="18"/>
       <c r="BL1" s="29" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="BM1" s="18"/>
       <c r="BN1" s="18"/>
@@ -9540,7 +9543,7 @@
       <c r="BP1" s="18"/>
       <c r="BQ1" s="18"/>
       <c r="BS1" s="29" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="BT1" s="18"/>
       <c r="BU1" s="18"/>
@@ -9548,7 +9551,7 @@
       <c r="BW1" s="18"/>
       <c r="BX1" s="18"/>
       <c r="BZ1" s="29" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="CA1" s="18"/>
       <c r="CB1" s="18"/>
@@ -9556,7 +9559,7 @@
       <c r="CD1" s="18"/>
       <c r="CE1" s="18"/>
       <c r="CG1" s="29" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="CH1" s="18"/>
       <c r="CI1" s="18"/>
@@ -9564,7 +9567,7 @@
       <c r="CK1" s="18"/>
       <c r="CL1" s="18"/>
       <c r="CN1" s="29" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="CO1" s="18"/>
       <c r="CP1" s="18"/>
@@ -9572,7 +9575,7 @@
       <c r="CR1" s="18"/>
       <c r="CS1" s="18"/>
       <c r="CU1" s="29" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="CV1" s="18"/>
       <c r="CW1" s="18"/>
@@ -9580,7 +9583,7 @@
       <c r="CY1" s="18"/>
       <c r="CZ1" s="18"/>
       <c r="DB1" s="29" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="DC1" s="18"/>
       <c r="DD1" s="18"/>
@@ -9588,7 +9591,7 @@
       <c r="DF1" s="18"/>
       <c r="DG1" s="18"/>
       <c r="DI1" s="29" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="DJ1" s="18"/>
       <c r="DK1" s="18"/>
@@ -9596,7 +9599,7 @@
       <c r="DM1" s="18"/>
       <c r="DN1" s="18"/>
       <c r="DP1" s="29" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="DQ1" s="18"/>
       <c r="DR1" s="18"/>
@@ -9604,7 +9607,7 @@
       <c r="DT1" s="18"/>
       <c r="DU1" s="18"/>
       <c r="DW1" s="29" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="DX1" s="18"/>
       <c r="DY1" s="18"/>
@@ -9612,7 +9615,7 @@
       <c r="EA1" s="18"/>
       <c r="EB1" s="18"/>
       <c r="ED1" s="29" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="EE1" s="18"/>
       <c r="EF1" s="18"/>
@@ -9620,7 +9623,7 @@
       <c r="EH1" s="18"/>
       <c r="EI1" s="18"/>
       <c r="EK1" s="29" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="EL1" s="18"/>
       <c r="EM1" s="18"/>
@@ -9628,7 +9631,7 @@
       <c r="EO1" s="18"/>
       <c r="EP1" s="18"/>
       <c r="ER1" s="29" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="ES1" s="18"/>
       <c r="ET1" s="18"/>
@@ -9636,7 +9639,7 @@
       <c r="EV1" s="18"/>
       <c r="EW1" s="18"/>
       <c r="EY1" s="29" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="EZ1" s="18"/>
       <c r="FA1" s="18"/>
@@ -10229,230 +10232,230 @@
     </row>
     <row r="6" spans="1:160" x14ac:dyDescent="0.25">
       <c r="A6" s="16" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B6" s="30" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="C6" s="18"/>
       <c r="D6" s="18"/>
       <c r="E6" s="18"/>
       <c r="F6" s="18"/>
       <c r="H6" s="16" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="I6" s="30" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="J6" s="18"/>
       <c r="K6" s="18"/>
       <c r="L6" s="18"/>
       <c r="M6" s="18"/>
       <c r="O6" s="16" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="P6" s="30" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="Q6" s="18"/>
       <c r="R6" s="18"/>
       <c r="S6" s="18"/>
       <c r="T6" s="18"/>
       <c r="V6" s="16" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="W6" s="30" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="X6" s="18"/>
       <c r="Y6" s="18"/>
       <c r="Z6" s="18"/>
       <c r="AA6" s="18"/>
       <c r="AC6" s="16" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="AD6" s="30" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="AE6" s="18"/>
       <c r="AF6" s="18"/>
       <c r="AG6" s="18"/>
       <c r="AH6" s="18"/>
       <c r="AJ6" s="16" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="AK6" s="30" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="AL6" s="18"/>
       <c r="AM6" s="18"/>
       <c r="AN6" s="18"/>
       <c r="AO6" s="18"/>
       <c r="AQ6" s="16" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="AR6" s="30" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="AS6" s="18"/>
       <c r="AT6" s="18"/>
       <c r="AU6" s="18"/>
       <c r="AV6" s="18"/>
       <c r="AX6" s="16" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="AY6" s="30" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="AZ6" s="18"/>
       <c r="BA6" s="18"/>
       <c r="BB6" s="18"/>
       <c r="BC6" s="18"/>
       <c r="BE6" s="16" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="BF6" s="30" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="BG6" s="18"/>
       <c r="BH6" s="18"/>
       <c r="BI6" s="18"/>
       <c r="BJ6" s="18"/>
       <c r="BL6" s="16" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="BM6" s="30" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="BN6" s="18"/>
       <c r="BO6" s="18"/>
       <c r="BP6" s="18"/>
       <c r="BQ6" s="18"/>
       <c r="BS6" s="16" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="BT6" s="30" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="BU6" s="18"/>
       <c r="BV6" s="18"/>
       <c r="BW6" s="18"/>
       <c r="BX6" s="18"/>
       <c r="BZ6" s="16" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="CA6" s="30" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="CB6" s="18"/>
       <c r="CC6" s="18"/>
       <c r="CD6" s="18"/>
       <c r="CE6" s="18"/>
       <c r="CG6" s="16" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="CH6" s="30" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="CI6" s="18"/>
       <c r="CJ6" s="18"/>
       <c r="CK6" s="18"/>
       <c r="CL6" s="18"/>
       <c r="CN6" s="16" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="CO6" s="30" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="CP6" s="18"/>
       <c r="CQ6" s="18"/>
       <c r="CR6" s="18"/>
       <c r="CS6" s="18"/>
       <c r="CU6" s="16" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="CV6" s="30" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="CW6" s="18"/>
       <c r="CX6" s="18"/>
       <c r="CY6" s="18"/>
       <c r="CZ6" s="18"/>
       <c r="DB6" s="16" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="DC6" s="30" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="DD6" s="18"/>
       <c r="DE6" s="18"/>
       <c r="DF6" s="18"/>
       <c r="DG6" s="18"/>
       <c r="DI6" s="16" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="DJ6" s="30" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="DK6" s="18"/>
       <c r="DL6" s="18"/>
       <c r="DM6" s="18"/>
       <c r="DN6" s="18"/>
       <c r="DP6" s="16" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="DQ6" s="30" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="DR6" s="18"/>
       <c r="DS6" s="18"/>
       <c r="DT6" s="18"/>
       <c r="DU6" s="18"/>
       <c r="DW6" s="16" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="DX6" s="30" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="DY6" s="18"/>
       <c r="DZ6" s="18"/>
       <c r="EA6" s="18"/>
       <c r="EB6" s="18"/>
       <c r="ED6" s="16" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="EE6" s="30" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="EF6" s="18"/>
       <c r="EG6" s="18"/>
       <c r="EH6" s="18"/>
       <c r="EI6" s="18"/>
       <c r="EK6" s="16" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="EL6" s="30" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="EM6" s="18"/>
       <c r="EN6" s="18"/>
       <c r="EO6" s="18"/>
       <c r="EP6" s="18"/>
       <c r="ER6" s="16" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="ES6" s="30" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="ET6" s="18"/>
       <c r="EU6" s="18"/>
       <c r="EV6" s="18"/>
       <c r="EW6" s="18"/>
       <c r="EY6" s="16" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="EZ6" s="30" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="FA6" s="18"/>
       <c r="FB6" s="18"/>
@@ -10464,7 +10467,7 @@
         <v>24</v>
       </c>
       <c r="B7" s="30" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="C7" s="18"/>
       <c r="D7" s="18"/>
@@ -10474,7 +10477,7 @@
         <v>24</v>
       </c>
       <c r="I7" s="30" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="J7" s="18"/>
       <c r="K7" s="18"/>
@@ -10484,7 +10487,7 @@
         <v>24</v>
       </c>
       <c r="P7" s="30" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="Q7" s="18"/>
       <c r="R7" s="18"/>
@@ -10494,7 +10497,7 @@
         <v>24</v>
       </c>
       <c r="W7" s="30" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="X7" s="18"/>
       <c r="Y7" s="18"/>
@@ -10504,7 +10507,7 @@
         <v>24</v>
       </c>
       <c r="AD7" s="30" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="AE7" s="18"/>
       <c r="AF7" s="18"/>
@@ -10514,7 +10517,7 @@
         <v>24</v>
       </c>
       <c r="AK7" s="30" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="AL7" s="18"/>
       <c r="AM7" s="18"/>
@@ -10524,7 +10527,7 @@
         <v>24</v>
       </c>
       <c r="AR7" s="30" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="AS7" s="18"/>
       <c r="AT7" s="18"/>
@@ -10534,7 +10537,7 @@
         <v>24</v>
       </c>
       <c r="AY7" s="30" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="AZ7" s="18"/>
       <c r="BA7" s="18"/>
@@ -10544,7 +10547,7 @@
         <v>24</v>
       </c>
       <c r="BF7" s="30" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="BG7" s="18"/>
       <c r="BH7" s="18"/>
@@ -10554,7 +10557,7 @@
         <v>24</v>
       </c>
       <c r="BM7" s="30" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="BN7" s="18"/>
       <c r="BO7" s="18"/>
@@ -10564,7 +10567,7 @@
         <v>24</v>
       </c>
       <c r="BT7" s="30" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="BU7" s="18"/>
       <c r="BV7" s="18"/>
@@ -10574,7 +10577,7 @@
         <v>24</v>
       </c>
       <c r="CA7" s="30" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="CB7" s="18"/>
       <c r="CC7" s="18"/>
@@ -10584,7 +10587,7 @@
         <v>24</v>
       </c>
       <c r="CH7" s="30" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="CI7" s="18"/>
       <c r="CJ7" s="18"/>
@@ -10594,7 +10597,7 @@
         <v>24</v>
       </c>
       <c r="CO7" s="30" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="CP7" s="18"/>
       <c r="CQ7" s="18"/>
@@ -10604,7 +10607,7 @@
         <v>24</v>
       </c>
       <c r="CV7" s="30" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="CW7" s="18"/>
       <c r="CX7" s="18"/>
@@ -10614,7 +10617,7 @@
         <v>24</v>
       </c>
       <c r="DC7" s="30" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="DD7" s="18"/>
       <c r="DE7" s="18"/>
@@ -10624,7 +10627,7 @@
         <v>24</v>
       </c>
       <c r="DJ7" s="30" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="DK7" s="18"/>
       <c r="DL7" s="18"/>
@@ -10634,7 +10637,7 @@
         <v>24</v>
       </c>
       <c r="DQ7" s="30" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="DR7" s="18"/>
       <c r="DS7" s="18"/>
@@ -10644,7 +10647,7 @@
         <v>24</v>
       </c>
       <c r="DX7" s="30" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="DY7" s="18"/>
       <c r="DZ7" s="18"/>
@@ -10654,7 +10657,7 @@
         <v>24</v>
       </c>
       <c r="EE7" s="30" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="EF7" s="18"/>
       <c r="EG7" s="18"/>
@@ -10664,7 +10667,7 @@
         <v>24</v>
       </c>
       <c r="EL7" s="30" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="EM7" s="18"/>
       <c r="EN7" s="18"/>
@@ -10674,7 +10677,7 @@
         <v>24</v>
       </c>
       <c r="ES7" s="30" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="ET7" s="18"/>
       <c r="EU7" s="18"/>
@@ -10684,7 +10687,7 @@
         <v>24</v>
       </c>
       <c r="EZ7" s="30" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="FA7" s="18"/>
       <c r="FB7" s="18"/>
@@ -11109,880 +11112,880 @@
     </row>
     <row r="9" spans="1:160" ht="29.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="16" t="s">
+        <v>224</v>
+      </c>
+      <c r="B9" s="16" t="s">
         <v>225</v>
       </c>
-      <c r="B9" s="16" t="s">
+      <c r="C9" s="16" t="s">
         <v>226</v>
       </c>
-      <c r="C9" s="16" t="s">
+      <c r="D9" s="16" t="s">
         <v>227</v>
-      </c>
-      <c r="D9" s="16" t="s">
-        <v>228</v>
       </c>
       <c r="E9" s="16"/>
       <c r="F9" s="16"/>
       <c r="H9" s="16" t="s">
+        <v>224</v>
+      </c>
+      <c r="I9" s="16" t="s">
         <v>225</v>
       </c>
-      <c r="I9" s="16" t="s">
+      <c r="J9" s="16" t="s">
         <v>226</v>
       </c>
-      <c r="J9" s="16" t="s">
+      <c r="K9" s="16" t="s">
         <v>227</v>
-      </c>
-      <c r="K9" s="16" t="s">
-        <v>228</v>
       </c>
       <c r="L9" s="16"/>
       <c r="M9" s="16"/>
       <c r="O9" s="16" t="s">
+        <v>224</v>
+      </c>
+      <c r="P9" s="16" t="s">
         <v>225</v>
       </c>
-      <c r="P9" s="16" t="s">
+      <c r="Q9" s="16" t="s">
         <v>226</v>
       </c>
-      <c r="Q9" s="16" t="s">
+      <c r="R9" s="16" t="s">
         <v>227</v>
-      </c>
-      <c r="R9" s="16" t="s">
-        <v>228</v>
       </c>
       <c r="S9" s="16"/>
       <c r="T9" s="16"/>
       <c r="V9" s="16" t="s">
+        <v>224</v>
+      </c>
+      <c r="W9" s="16" t="s">
         <v>225</v>
       </c>
-      <c r="W9" s="16" t="s">
+      <c r="X9" s="16" t="s">
         <v>226</v>
       </c>
-      <c r="X9" s="16" t="s">
+      <c r="Y9" s="16" t="s">
         <v>227</v>
-      </c>
-      <c r="Y9" s="16" t="s">
-        <v>228</v>
       </c>
       <c r="Z9" s="16"/>
       <c r="AA9" s="16"/>
       <c r="AC9" s="16" t="s">
+        <v>224</v>
+      </c>
+      <c r="AD9" s="16" t="s">
         <v>225</v>
       </c>
-      <c r="AD9" s="16" t="s">
+      <c r="AE9" s="16" t="s">
         <v>226</v>
       </c>
-      <c r="AE9" s="16" t="s">
+      <c r="AF9" s="16" t="s">
         <v>227</v>
-      </c>
-      <c r="AF9" s="16" t="s">
-        <v>228</v>
       </c>
       <c r="AG9" s="16"/>
       <c r="AH9" s="16"/>
       <c r="AJ9" s="16" t="s">
+        <v>224</v>
+      </c>
+      <c r="AK9" s="16" t="s">
         <v>225</v>
       </c>
-      <c r="AK9" s="16" t="s">
+      <c r="AL9" s="16" t="s">
         <v>226</v>
       </c>
-      <c r="AL9" s="16" t="s">
+      <c r="AM9" s="16" t="s">
         <v>227</v>
-      </c>
-      <c r="AM9" s="16" t="s">
-        <v>228</v>
       </c>
       <c r="AN9" s="16"/>
       <c r="AO9" s="16"/>
       <c r="AQ9" s="16" t="s">
+        <v>224</v>
+      </c>
+      <c r="AR9" s="16" t="s">
         <v>225</v>
       </c>
-      <c r="AR9" s="16" t="s">
+      <c r="AS9" s="16" t="s">
         <v>226</v>
       </c>
-      <c r="AS9" s="16" t="s">
+      <c r="AT9" s="16" t="s">
         <v>227</v>
-      </c>
-      <c r="AT9" s="16" t="s">
-        <v>228</v>
       </c>
       <c r="AU9" s="16"/>
       <c r="AV9" s="16"/>
       <c r="AX9" s="16" t="s">
+        <v>224</v>
+      </c>
+      <c r="AY9" s="16" t="s">
         <v>225</v>
       </c>
-      <c r="AY9" s="16" t="s">
+      <c r="AZ9" s="16" t="s">
         <v>226</v>
       </c>
-      <c r="AZ9" s="16" t="s">
+      <c r="BA9" s="16" t="s">
         <v>227</v>
-      </c>
-      <c r="BA9" s="16" t="s">
-        <v>228</v>
       </c>
       <c r="BB9" s="16"/>
       <c r="BC9" s="16"/>
       <c r="BE9" s="16" t="s">
+        <v>224</v>
+      </c>
+      <c r="BF9" s="16" t="s">
         <v>225</v>
       </c>
-      <c r="BF9" s="16" t="s">
+      <c r="BG9" s="16" t="s">
         <v>226</v>
       </c>
-      <c r="BG9" s="16" t="s">
+      <c r="BH9" s="16" t="s">
         <v>227</v>
-      </c>
-      <c r="BH9" s="16" t="s">
-        <v>228</v>
       </c>
       <c r="BI9" s="16"/>
       <c r="BJ9" s="16"/>
       <c r="BL9" s="16" t="s">
+        <v>224</v>
+      </c>
+      <c r="BM9" s="16" t="s">
         <v>225</v>
       </c>
-      <c r="BM9" s="16" t="s">
+      <c r="BN9" s="16" t="s">
         <v>226</v>
       </c>
-      <c r="BN9" s="16" t="s">
+      <c r="BO9" s="16" t="s">
         <v>227</v>
-      </c>
-      <c r="BO9" s="16" t="s">
-        <v>228</v>
       </c>
       <c r="BP9" s="16"/>
       <c r="BQ9" s="16"/>
       <c r="BS9" s="16" t="s">
+        <v>224</v>
+      </c>
+      <c r="BT9" s="16" t="s">
         <v>225</v>
       </c>
-      <c r="BT9" s="16" t="s">
+      <c r="BU9" s="16" t="s">
         <v>226</v>
       </c>
-      <c r="BU9" s="16" t="s">
+      <c r="BV9" s="16" t="s">
         <v>227</v>
-      </c>
-      <c r="BV9" s="16" t="s">
-        <v>228</v>
       </c>
       <c r="BW9" s="16"/>
       <c r="BX9" s="16"/>
       <c r="BZ9" s="16" t="s">
+        <v>224</v>
+      </c>
+      <c r="CA9" s="16" t="s">
         <v>225</v>
       </c>
-      <c r="CA9" s="16" t="s">
+      <c r="CB9" s="16" t="s">
         <v>226</v>
       </c>
-      <c r="CB9" s="16" t="s">
+      <c r="CC9" s="16" t="s">
         <v>227</v>
-      </c>
-      <c r="CC9" s="16" t="s">
-        <v>228</v>
       </c>
       <c r="CD9" s="16"/>
       <c r="CE9" s="16"/>
       <c r="CG9" s="16" t="s">
+        <v>224</v>
+      </c>
+      <c r="CH9" s="16" t="s">
         <v>225</v>
       </c>
-      <c r="CH9" s="16" t="s">
+      <c r="CI9" s="16" t="s">
         <v>226</v>
       </c>
-      <c r="CI9" s="16" t="s">
+      <c r="CJ9" s="16" t="s">
         <v>227</v>
-      </c>
-      <c r="CJ9" s="16" t="s">
-        <v>228</v>
       </c>
       <c r="CK9" s="16"/>
       <c r="CL9" s="16"/>
       <c r="CN9" s="16" t="s">
+        <v>224</v>
+      </c>
+      <c r="CO9" s="16" t="s">
         <v>225</v>
       </c>
-      <c r="CO9" s="16" t="s">
+      <c r="CP9" s="16" t="s">
         <v>226</v>
       </c>
-      <c r="CP9" s="16" t="s">
+      <c r="CQ9" s="16" t="s">
         <v>227</v>
-      </c>
-      <c r="CQ9" s="16" t="s">
-        <v>228</v>
       </c>
       <c r="CR9" s="16"/>
       <c r="CS9" s="16"/>
       <c r="CU9" s="16" t="s">
+        <v>224</v>
+      </c>
+      <c r="CV9" s="16" t="s">
         <v>225</v>
       </c>
-      <c r="CV9" s="16" t="s">
+      <c r="CW9" s="16" t="s">
         <v>226</v>
       </c>
-      <c r="CW9" s="16" t="s">
+      <c r="CX9" s="16" t="s">
         <v>227</v>
-      </c>
-      <c r="CX9" s="16" t="s">
-        <v>228</v>
       </c>
       <c r="CY9" s="16"/>
       <c r="CZ9" s="16"/>
       <c r="DB9" s="16" t="s">
+        <v>224</v>
+      </c>
+      <c r="DC9" s="16" t="s">
         <v>225</v>
       </c>
-      <c r="DC9" s="16" t="s">
+      <c r="DD9" s="16" t="s">
         <v>226</v>
       </c>
-      <c r="DD9" s="16" t="s">
+      <c r="DE9" s="16" t="s">
         <v>227</v>
-      </c>
-      <c r="DE9" s="16" t="s">
-        <v>228</v>
       </c>
       <c r="DF9" s="16"/>
       <c r="DG9" s="16"/>
       <c r="DI9" s="16" t="s">
+        <v>224</v>
+      </c>
+      <c r="DJ9" s="16" t="s">
         <v>225</v>
       </c>
-      <c r="DJ9" s="16" t="s">
+      <c r="DK9" s="16" t="s">
         <v>226</v>
       </c>
-      <c r="DK9" s="16" t="s">
+      <c r="DL9" s="16" t="s">
         <v>227</v>
-      </c>
-      <c r="DL9" s="16" t="s">
-        <v>228</v>
       </c>
       <c r="DM9" s="16"/>
       <c r="DN9" s="16"/>
       <c r="DP9" s="16" t="s">
+        <v>224</v>
+      </c>
+      <c r="DQ9" s="16" t="s">
         <v>225</v>
       </c>
-      <c r="DQ9" s="16" t="s">
+      <c r="DR9" s="16" t="s">
         <v>226</v>
       </c>
-      <c r="DR9" s="16" t="s">
+      <c r="DS9" s="16" t="s">
         <v>227</v>
-      </c>
-      <c r="DS9" s="16" t="s">
-        <v>228</v>
       </c>
       <c r="DT9" s="16"/>
       <c r="DU9" s="16"/>
       <c r="DW9" s="16" t="s">
+        <v>224</v>
+      </c>
+      <c r="DX9" s="16" t="s">
         <v>225</v>
       </c>
-      <c r="DX9" s="16" t="s">
+      <c r="DY9" s="16" t="s">
         <v>226</v>
       </c>
-      <c r="DY9" s="16" t="s">
+      <c r="DZ9" s="16" t="s">
         <v>227</v>
-      </c>
-      <c r="DZ9" s="16" t="s">
-        <v>228</v>
       </c>
       <c r="EA9" s="16"/>
       <c r="EB9" s="16"/>
       <c r="ED9" s="16" t="s">
+        <v>224</v>
+      </c>
+      <c r="EE9" s="16" t="s">
         <v>225</v>
       </c>
-      <c r="EE9" s="16" t="s">
+      <c r="EF9" s="16" t="s">
         <v>226</v>
       </c>
-      <c r="EF9" s="16" t="s">
+      <c r="EG9" s="16" t="s">
         <v>227</v>
-      </c>
-      <c r="EG9" s="16" t="s">
-        <v>228</v>
       </c>
       <c r="EH9" s="16"/>
       <c r="EI9" s="16"/>
       <c r="EK9" s="16" t="s">
+        <v>224</v>
+      </c>
+      <c r="EL9" s="16" t="s">
         <v>225</v>
       </c>
-      <c r="EL9" s="16" t="s">
+      <c r="EM9" s="16" t="s">
         <v>226</v>
       </c>
-      <c r="EM9" s="16" t="s">
+      <c r="EN9" s="16" t="s">
         <v>227</v>
-      </c>
-      <c r="EN9" s="16" t="s">
-        <v>228</v>
       </c>
       <c r="EO9" s="16"/>
       <c r="EP9" s="16"/>
       <c r="ER9" s="16" t="s">
+        <v>224</v>
+      </c>
+      <c r="ES9" s="16" t="s">
         <v>225</v>
       </c>
-      <c r="ES9" s="16" t="s">
+      <c r="ET9" s="16" t="s">
         <v>226</v>
       </c>
-      <c r="ET9" s="16" t="s">
+      <c r="EU9" s="16" t="s">
         <v>227</v>
-      </c>
-      <c r="EU9" s="16" t="s">
-        <v>228</v>
       </c>
       <c r="EV9" s="16"/>
       <c r="EW9" s="16"/>
       <c r="EY9" s="16" t="s">
+        <v>224</v>
+      </c>
+      <c r="EZ9" s="16" t="s">
         <v>225</v>
       </c>
-      <c r="EZ9" s="16" t="s">
+      <c r="FA9" s="16" t="s">
         <v>226</v>
       </c>
-      <c r="FA9" s="16" t="s">
+      <c r="FB9" s="16" t="s">
         <v>227</v>
-      </c>
-      <c r="FB9" s="16" t="s">
-        <v>228</v>
       </c>
       <c r="FC9" s="16"/>
       <c r="FD9" s="16"/>
     </row>
     <row r="10" spans="1:160" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="16" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="B10" s="16" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="C10" s="16"/>
       <c r="D10" s="16" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="E10" s="16"/>
       <c r="F10" s="16"/>
       <c r="H10" s="16" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="I10" s="16" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="J10" s="16"/>
       <c r="K10" s="16" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="L10" s="16"/>
       <c r="M10" s="16"/>
       <c r="O10" s="16" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="P10" s="16" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="Q10" s="16"/>
       <c r="R10" s="16" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="S10" s="16"/>
       <c r="T10" s="16"/>
       <c r="V10" s="16" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="W10" s="16" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="X10" s="16"/>
       <c r="Y10" s="16" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="Z10" s="16"/>
       <c r="AA10" s="16"/>
       <c r="AC10" s="16" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="AD10" s="16" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="AE10" s="16"/>
       <c r="AF10" s="16" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="AG10" s="16"/>
       <c r="AH10" s="16"/>
       <c r="AJ10" s="16" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="AK10" s="16" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="AL10" s="16"/>
       <c r="AM10" s="16" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="AN10" s="16"/>
       <c r="AO10" s="16"/>
       <c r="AQ10" s="16" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="AR10" s="16" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="AS10" s="16"/>
       <c r="AT10" s="16" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="AU10" s="16"/>
       <c r="AV10" s="16"/>
       <c r="AX10" s="16" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="AY10" s="16" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="AZ10" s="16"/>
       <c r="BA10" s="16" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="BB10" s="16"/>
       <c r="BC10" s="16"/>
       <c r="BE10" s="16" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="BF10" s="16" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="BG10" s="16"/>
       <c r="BH10" s="16" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="BI10" s="16"/>
       <c r="BJ10" s="16"/>
       <c r="BL10" s="16" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="BM10" s="16" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="BN10" s="16"/>
       <c r="BO10" s="16" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="BP10" s="16"/>
       <c r="BQ10" s="16"/>
       <c r="BS10" s="16" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="BT10" s="16" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="BU10" s="16"/>
       <c r="BV10" s="16" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="BW10" s="16"/>
       <c r="BX10" s="16"/>
       <c r="BZ10" s="16" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="CA10" s="16" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="CB10" s="16"/>
       <c r="CC10" s="16" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="CD10" s="16"/>
       <c r="CE10" s="16"/>
       <c r="CG10" s="16" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="CH10" s="16" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="CI10" s="16"/>
       <c r="CJ10" s="16" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="CK10" s="16"/>
       <c r="CL10" s="16"/>
       <c r="CN10" s="16" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="CO10" s="16" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="CP10" s="16"/>
       <c r="CQ10" s="16" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="CR10" s="16"/>
       <c r="CS10" s="16"/>
       <c r="CU10" s="16" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="CV10" s="16" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="CW10" s="16"/>
       <c r="CX10" s="16" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="CY10" s="16"/>
       <c r="CZ10" s="16"/>
       <c r="DB10" s="16" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="DC10" s="16" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="DD10" s="16"/>
       <c r="DE10" s="16" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="DF10" s="16"/>
       <c r="DG10" s="16"/>
       <c r="DI10" s="16" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="DJ10" s="16" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="DK10" s="16"/>
       <c r="DL10" s="16" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="DM10" s="16"/>
       <c r="DN10" s="16"/>
       <c r="DP10" s="16" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="DQ10" s="16" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="DR10" s="16"/>
       <c r="DS10" s="16" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="DT10" s="16"/>
       <c r="DU10" s="16"/>
       <c r="DW10" s="16" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="DX10" s="16" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="DY10" s="16"/>
       <c r="DZ10" s="16" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="EA10" s="16"/>
       <c r="EB10" s="16"/>
       <c r="ED10" s="16" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="EE10" s="16" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="EF10" s="16"/>
       <c r="EG10" s="16" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="EH10" s="16"/>
       <c r="EI10" s="16"/>
       <c r="EK10" s="16" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="EL10" s="16" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="EM10" s="16"/>
       <c r="EN10" s="16" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="EO10" s="16"/>
       <c r="EP10" s="16"/>
       <c r="ER10" s="16" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="ES10" s="16" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="ET10" s="16"/>
       <c r="EU10" s="16" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="EV10" s="16"/>
       <c r="EW10" s="16"/>
       <c r="EY10" s="16" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="EZ10" s="16" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="FA10" s="16"/>
       <c r="FB10" s="16" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="FC10" s="16"/>
       <c r="FD10" s="16"/>
     </row>
     <row r="11" spans="1:160" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="16" t="s">
+        <v>243</v>
+      </c>
+      <c r="B11" s="16" t="s">
         <v>244</v>
-      </c>
-      <c r="B11" s="16" t="s">
-        <v>245</v>
       </c>
       <c r="C11" s="16"/>
       <c r="D11" s="16" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="E11" s="16"/>
       <c r="F11" s="16"/>
       <c r="H11" s="16" t="s">
+        <v>243</v>
+      </c>
+      <c r="I11" s="16" t="s">
         <v>244</v>
-      </c>
-      <c r="I11" s="16" t="s">
-        <v>245</v>
       </c>
       <c r="J11" s="16"/>
       <c r="K11" s="16" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="L11" s="16"/>
       <c r="M11" s="16"/>
       <c r="O11" s="16" t="s">
+        <v>243</v>
+      </c>
+      <c r="P11" s="16" t="s">
         <v>244</v>
-      </c>
-      <c r="P11" s="16" t="s">
-        <v>245</v>
       </c>
       <c r="Q11" s="16"/>
       <c r="R11" s="16" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="S11" s="16"/>
       <c r="T11" s="16"/>
       <c r="V11" s="16" t="s">
+        <v>243</v>
+      </c>
+      <c r="W11" s="16" t="s">
         <v>244</v>
-      </c>
-      <c r="W11" s="16" t="s">
-        <v>245</v>
       </c>
       <c r="X11" s="16"/>
       <c r="Y11" s="16" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="Z11" s="16"/>
       <c r="AA11" s="16"/>
       <c r="AC11" s="16" t="s">
+        <v>243</v>
+      </c>
+      <c r="AD11" s="16" t="s">
         <v>244</v>
-      </c>
-      <c r="AD11" s="16" t="s">
-        <v>245</v>
       </c>
       <c r="AE11" s="16"/>
       <c r="AF11" s="16" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="AG11" s="16"/>
       <c r="AH11" s="16"/>
       <c r="AJ11" s="16" t="s">
+        <v>243</v>
+      </c>
+      <c r="AK11" s="16" t="s">
         <v>244</v>
-      </c>
-      <c r="AK11" s="16" t="s">
-        <v>245</v>
       </c>
       <c r="AL11" s="16"/>
       <c r="AM11" s="16" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="AN11" s="16"/>
       <c r="AO11" s="16"/>
       <c r="AQ11" s="16" t="s">
+        <v>243</v>
+      </c>
+      <c r="AR11" s="16" t="s">
         <v>244</v>
-      </c>
-      <c r="AR11" s="16" t="s">
-        <v>245</v>
       </c>
       <c r="AS11" s="16"/>
       <c r="AT11" s="16" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="AU11" s="16"/>
       <c r="AV11" s="16"/>
       <c r="AX11" s="16" t="s">
+        <v>243</v>
+      </c>
+      <c r="AY11" s="16" t="s">
         <v>244</v>
-      </c>
-      <c r="AY11" s="16" t="s">
-        <v>245</v>
       </c>
       <c r="AZ11" s="16"/>
       <c r="BA11" s="16" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="BB11" s="16"/>
       <c r="BC11" s="16"/>
       <c r="BE11" s="16" t="s">
+        <v>243</v>
+      </c>
+      <c r="BF11" s="16" t="s">
         <v>244</v>
-      </c>
-      <c r="BF11" s="16" t="s">
-        <v>245</v>
       </c>
       <c r="BG11" s="16"/>
       <c r="BH11" s="16" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="BI11" s="16"/>
       <c r="BJ11" s="16"/>
       <c r="BL11" s="16" t="s">
+        <v>243</v>
+      </c>
+      <c r="BM11" s="16" t="s">
         <v>244</v>
-      </c>
-      <c r="BM11" s="16" t="s">
-        <v>245</v>
       </c>
       <c r="BN11" s="16"/>
       <c r="BO11" s="16" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="BP11" s="16"/>
       <c r="BQ11" s="16"/>
       <c r="BS11" s="16" t="s">
+        <v>243</v>
+      </c>
+      <c r="BT11" s="16" t="s">
         <v>244</v>
-      </c>
-      <c r="BT11" s="16" t="s">
-        <v>245</v>
       </c>
       <c r="BU11" s="16"/>
       <c r="BV11" s="16" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="BW11" s="16"/>
       <c r="BX11" s="16"/>
       <c r="BZ11" s="16" t="s">
+        <v>243</v>
+      </c>
+      <c r="CA11" s="16" t="s">
         <v>244</v>
-      </c>
-      <c r="CA11" s="16" t="s">
-        <v>245</v>
       </c>
       <c r="CB11" s="16"/>
       <c r="CC11" s="16" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="CD11" s="16"/>
       <c r="CE11" s="16"/>
       <c r="CG11" s="16" t="s">
+        <v>243</v>
+      </c>
+      <c r="CH11" s="16" t="s">
         <v>244</v>
-      </c>
-      <c r="CH11" s="16" t="s">
-        <v>245</v>
       </c>
       <c r="CI11" s="16"/>
       <c r="CJ11" s="16" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="CK11" s="16"/>
       <c r="CL11" s="16"/>
       <c r="CN11" s="16" t="s">
+        <v>243</v>
+      </c>
+      <c r="CO11" s="16" t="s">
         <v>244</v>
-      </c>
-      <c r="CO11" s="16" t="s">
-        <v>245</v>
       </c>
       <c r="CP11" s="16"/>
       <c r="CQ11" s="16" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="CR11" s="16"/>
       <c r="CS11" s="16"/>
       <c r="CU11" s="16" t="s">
+        <v>243</v>
+      </c>
+      <c r="CV11" s="16" t="s">
         <v>244</v>
-      </c>
-      <c r="CV11" s="16" t="s">
-        <v>245</v>
       </c>
       <c r="CW11" s="16"/>
       <c r="CX11" s="16" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="CY11" s="16"/>
       <c r="CZ11" s="16"/>
       <c r="DB11" s="16" t="s">
+        <v>243</v>
+      </c>
+      <c r="DC11" s="16" t="s">
         <v>244</v>
-      </c>
-      <c r="DC11" s="16" t="s">
-        <v>245</v>
       </c>
       <c r="DD11" s="16"/>
       <c r="DE11" s="16" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="DF11" s="16"/>
       <c r="DG11" s="16"/>
       <c r="DI11" s="16" t="s">
+        <v>243</v>
+      </c>
+      <c r="DJ11" s="16" t="s">
         <v>244</v>
-      </c>
-      <c r="DJ11" s="16" t="s">
-        <v>245</v>
       </c>
       <c r="DK11" s="16"/>
       <c r="DL11" s="16" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="DM11" s="16"/>
       <c r="DN11" s="16"/>
       <c r="DP11" s="16" t="s">
+        <v>243</v>
+      </c>
+      <c r="DQ11" s="16" t="s">
         <v>244</v>
-      </c>
-      <c r="DQ11" s="16" t="s">
-        <v>245</v>
       </c>
       <c r="DR11" s="16"/>
       <c r="DS11" s="16" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="DT11" s="16"/>
       <c r="DU11" s="16"/>
       <c r="DW11" s="16" t="s">
+        <v>243</v>
+      </c>
+      <c r="DX11" s="16" t="s">
         <v>244</v>
-      </c>
-      <c r="DX11" s="16" t="s">
-        <v>245</v>
       </c>
       <c r="DY11" s="16"/>
       <c r="DZ11" s="16" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="EA11" s="16"/>
       <c r="EB11" s="16"/>
       <c r="ED11" s="16" t="s">
+        <v>243</v>
+      </c>
+      <c r="EE11" s="16" t="s">
         <v>244</v>
-      </c>
-      <c r="EE11" s="16" t="s">
-        <v>245</v>
       </c>
       <c r="EF11" s="16"/>
       <c r="EG11" s="16" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="EH11" s="16"/>
       <c r="EI11" s="16"/>
       <c r="EK11" s="16" t="s">
+        <v>243</v>
+      </c>
+      <c r="EL11" s="16" t="s">
         <v>244</v>
-      </c>
-      <c r="EL11" s="16" t="s">
-        <v>245</v>
       </c>
       <c r="EM11" s="16"/>
       <c r="EN11" s="16" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="EO11" s="16"/>
       <c r="EP11" s="16"/>
       <c r="ER11" s="16" t="s">
+        <v>243</v>
+      </c>
+      <c r="ES11" s="16" t="s">
         <v>244</v>
-      </c>
-      <c r="ES11" s="16" t="s">
-        <v>245</v>
       </c>
       <c r="ET11" s="16"/>
       <c r="EU11" s="16" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="EV11" s="16"/>
       <c r="EW11" s="16"/>
       <c r="EY11" s="16" t="s">
+        <v>243</v>
+      </c>
+      <c r="EZ11" s="16" t="s">
         <v>244</v>
-      </c>
-      <c r="EZ11" s="16" t="s">
-        <v>245</v>
       </c>
       <c r="FA11" s="16"/>
       <c r="FB11" s="16" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="FC11" s="16"/>
       <c r="FD11" s="16"/>

--- a/Test Cases.xlsx
+++ b/Test Cases.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://endresshauser-my.sharepoint.com/personal/corbin_ferguson_endress_com/Documents/ThesisBuildTool/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="182" documentId="8_{B89245B7-08D9-4A9D-8516-F6C9C7AFFDC1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8BEB568B-2EAC-49CC-9ACA-DD10EAC98080}"/>
+  <xr:revisionPtr revIDLastSave="307" documentId="8_{B89245B7-08D9-4A9D-8516-F6C9C7AFFDC1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0D8059F2-F8F6-42BB-9850-F98902EB790B}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="25440" windowHeight="15270" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="25440" windowHeight="15270" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tests" sheetId="1" r:id="rId1"/>
@@ -23,6 +23,7 @@
     <sheet name="Unit XMLHandlerTests" sheetId="8" r:id="rId8"/>
   </sheets>
   <calcPr calcId="191029"/>
+  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -40,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1753" uniqueCount="352">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1795" uniqueCount="379">
   <si>
     <t>Test ID</t>
   </si>
@@ -315,9 +316,6 @@
     <t>No Element to Modify</t>
   </si>
   <si>
-    <t>Modify into Redundant Element Name</t>
-  </si>
-  <si>
     <t>"Modify" button pressed</t>
   </si>
   <si>
@@ -342,24 +340,15 @@
     <t>Select element to modify</t>
   </si>
   <si>
-    <t>dropdown select element1, &amp; element2</t>
-  </si>
-  <si>
     <t>select attributes window appears</t>
   </si>
   <si>
-    <t>Select element to modify for element1</t>
-  </si>
-  <si>
     <t>Select attributes to modify</t>
   </si>
   <si>
     <t xml:space="preserve">text window popup </t>
   </si>
   <si>
-    <t>Select attributes to modify for element1</t>
-  </si>
-  <si>
     <t>select Name to modify</t>
   </si>
   <si>
@@ -369,27 +358,12 @@
     <t>continue to next attribute</t>
   </si>
   <si>
-    <t>Set Name for element1</t>
-  </si>
-  <si>
     <t>redundant name</t>
   </si>
   <si>
     <t>move to select subelements</t>
   </si>
   <si>
-    <t>existing element replaced by new element, move to next element modify</t>
-  </si>
-  <si>
-    <t>Select attributes to modify for element2</t>
-  </si>
-  <si>
-    <t>Set Name for element2</t>
-  </si>
-  <si>
-    <t>cancel element modification, return to action select window</t>
-  </si>
-  <si>
     <t>Close select subelements window</t>
   </si>
   <si>
@@ -1089,20 +1063,128 @@
     <t>TemplateLadderAOI</t>
   </si>
   <si>
-    <t>Validation Error Window inaction</t>
-  </si>
-  <si>
     <t>Description: Test that the creation of multiple elements that clash works.</t>
   </si>
   <si>
     <t>Clashing Element Creation</t>
+  </si>
+  <si>
+    <t>Redundant Modify Element</t>
+  </si>
+  <si>
+    <t>Description: Test that modifying an element to give it a name that already exists fails.</t>
+  </si>
+  <si>
+    <t>dropdown select TemplateFBAOI</t>
+  </si>
+  <si>
+    <t>existing element replaced by new element, return to actionSelect</t>
+  </si>
+  <si>
+    <t>Set Name for TemplateFBAOI</t>
+  </si>
+  <si>
+    <t>Select AddOnInstructionDefinition to modify</t>
+  </si>
+  <si>
+    <t>Get all mainmenu buttons</t>
+  </si>
+  <si>
+    <t>Exclude "ExitActionSelect", and inbuilt windows window buttons</t>
+  </si>
+  <si>
+    <t>ImportElementButton, "CreateElementButton", "ModifyElementButton", "DeleteElementButton", "NewFileButton", "LoadFileButton", "ValidateFileButton", "SaveFileButton"</t>
+  </si>
+  <si>
+    <t>Invoke button from list</t>
+  </si>
+  <si>
+    <t>button invoke</t>
+  </si>
+  <si>
+    <t>popup window appears and takes control</t>
+  </si>
+  <si>
+    <t>verify that ActionSelect is no longer enabled</t>
+  </si>
+  <si>
+    <t>actionSelect.isEnabled</t>
+  </si>
+  <si>
+    <t>Close popup window</t>
+  </si>
+  <si>
+    <t>invoke "Close button"</t>
+  </si>
+  <si>
+    <t>close window, return control to action select</t>
+  </si>
+  <si>
+    <t>repeat steps 2-4 for all buttons in list</t>
+  </si>
+  <si>
+    <t>Validation Error Window</t>
+  </si>
+  <si>
+    <t>Description: Test that when the user modifies the file in a way that is not valid for the schema, an error window appears.</t>
+  </si>
+  <si>
+    <t>Preconditions: Default file loaded</t>
+  </si>
+  <si>
+    <t>Select attributes to modify for TemplateFBAOI</t>
+  </si>
+  <si>
+    <t>dropdown select type Task</t>
+  </si>
+  <si>
+    <t>"Create" button pressed</t>
+  </si>
+  <si>
+    <t>"TemplateContinuous" element selected for template</t>
+  </si>
+  <si>
+    <t>genTaskWithError</t>
+  </si>
+  <si>
+    <t>new element created, move to error window</t>
+  </si>
+  <si>
+    <t>Detected Errors window appears</t>
+  </si>
+  <si>
+    <t>User Inputs Quantity to create of 2</t>
+  </si>
+  <si>
+    <t>illegal2ndtask</t>
+  </si>
+  <si>
+    <t>new element created, move to next name</t>
+  </si>
+  <si>
+    <t>"ERROR</t>
+  </si>
+  <si>
+    <t>text containing "ERROR" found</t>
+  </si>
+  <si>
+    <t>Press Ok</t>
+  </si>
+  <si>
+    <t>OK button press</t>
+  </si>
+  <si>
+    <t>CreateElementButton button press</t>
+  </si>
+  <si>
+    <t>return to actionSelect</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1123,15 +1205,6 @@
       <sz val="11"/>
       <name val="Calibri"/>
       <family val="2"/>
-    </font>
-    <font>
-      <b/>
-      <u/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -1183,7 +1256,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -1251,13 +1324,12 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1527,13 +1599,13 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="4"/>
                 <c:pt idx="0">
-                  <c:v>4</c:v>
+                  <c:v>2</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>33</c:v>
+                  <c:v>40</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>22</c:v>
+                  <c:v>18</c:v>
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>1</c:v>
@@ -2932,7 +3004,7 @@
       </c>
       <c r="H1">
         <f>COUNTIF(TestMaster[Test Status], "Not Implemented")</f>
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
@@ -2955,7 +3027,7 @@
       </c>
       <c r="H2">
         <f>COUNTIF(TestMaster[Test Status], "Pass")</f>
-        <v>33</v>
+        <v>40</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
@@ -2978,7 +3050,7 @@
       </c>
       <c r="H3">
         <f>COUNTIF(TestMaster[Test Status], "Fail")</f>
-        <v>22</v>
+        <v>18</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
@@ -3205,7 +3277,7 @@
       </c>
       <c r="H14">
         <f>COUNTIFS(TestMaster[Test Status], "Not Implemented", TestMaster[Namespace], G13)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
@@ -3228,7 +3300,7 @@
       </c>
       <c r="H15">
         <f>COUNTIFS(TestMaster[Test Status], "Pass", TestMaster[Namespace], G13)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
@@ -3309,7 +3381,7 @@
         <v>7</v>
       </c>
       <c r="G19" t="s">
-        <v>306</v>
+        <v>297</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
@@ -3332,7 +3404,7 @@
       </c>
       <c r="H20">
         <f>COUNTIFS(TestMaster[Test Status], "Not Implemented", TestMaster[Namespace], G19)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
@@ -3355,7 +3427,7 @@
       </c>
       <c r="H21">
         <f>COUNTIFS(TestMaster[Test Status], "Pass", TestMaster[Namespace], G19)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
@@ -3381,7 +3453,7 @@
       </c>
       <c r="H22">
         <f>COUNTIFS(TestMaster[Test Status], "Fail", TestMaster[Namespace], G19)</f>
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
@@ -3461,7 +3533,7 @@
         <v>Nameless Module Creation</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D26" t="s">
         <v>10</v>
@@ -3487,7 +3559,7 @@
         <v>Clashing Element Creation</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D27" t="s">
         <v>13</v>
@@ -3513,7 +3585,7 @@
         <v>Delete Element Found</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D28" t="s">
         <v>11</v>
@@ -3539,7 +3611,7 @@
         <v>Delete Module by Port</v>
       </c>
       <c r="C29" s="5" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D29" t="s">
         <v>13</v>
@@ -3565,7 +3637,7 @@
         <v>Delete No Element Type</v>
       </c>
       <c r="C30" s="5" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D30" t="s">
         <v>10</v>
@@ -3590,7 +3662,7 @@
         <v>11</v>
       </c>
       <c r="E31" t="s">
-        <v>306</v>
+        <v>297</v>
       </c>
       <c r="G31" t="s">
         <v>16</v>
@@ -3606,20 +3678,20 @@
         <v>ActionSelectLosecontrol</v>
       </c>
       <c r="C32" s="5" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D32" t="s">
         <v>10</v>
       </c>
       <c r="E32" t="s">
-        <v>306</v>
+        <v>297</v>
       </c>
       <c r="G32" t="s">
         <v>5</v>
       </c>
       <c r="H32">
         <f>COUNTIFS(TestMaster[Test Status], "Not Implemented", TestMaster[Namespace], G31)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.25">
@@ -3638,14 +3710,14 @@
         <v>11</v>
       </c>
       <c r="E33" t="s">
-        <v>306</v>
+        <v>297</v>
       </c>
       <c r="G33" t="s">
         <v>8</v>
       </c>
       <c r="H33">
         <f>COUNTIFS(TestMaster[Test Status], "Pass", TestMaster[Namespace], G31)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.25">
@@ -3671,7 +3743,7 @@
       </c>
       <c r="H34">
         <f>COUNTIFS(TestMaster[Test Status], "Fail", TestMaster[Namespace], G31)</f>
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.25">
@@ -3684,7 +3756,7 @@
         <v>Standard Element Modify</v>
       </c>
       <c r="C35" s="5" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D35" t="s">
         <v>11</v>
@@ -3707,10 +3779,10 @@
       </c>
       <c r="B36" t="str">
         <f>Modify!M1</f>
-        <v>Modify into Redundant Element Name</v>
+        <v>Redundant Modify Element</v>
       </c>
       <c r="C36" s="5" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D36" t="s">
         <v>13</v>
@@ -3724,8 +3796,18 @@
         <f>ROW()-1</f>
         <v>36</v>
       </c>
-      <c r="B37" s="31" t="s">
-        <v>349</v>
+      <c r="B37" t="str">
+        <f>'File Manipulation'!S1</f>
+        <v>Validation Error Window</v>
+      </c>
+      <c r="C37" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="D37" t="s">
+        <v>10</v>
+      </c>
+      <c r="E37" t="s">
+        <v>297</v>
       </c>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.25">
@@ -3738,7 +3820,7 @@
         <v>No Element to Modify</v>
       </c>
       <c r="C38" s="5" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D38" t="s">
         <v>10</v>
@@ -4282,7 +4364,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="19" t="s">
-        <v>339</v>
+        <v>330</v>
       </c>
       <c r="B1" s="18"/>
       <c r="C1" s="18"/>
@@ -4448,13 +4530,13 @@
         <v>6</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>340</v>
+        <v>331</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>341</v>
+        <v>332</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>342</v>
+        <v>333</v>
       </c>
     </row>
     <row r="14" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -4466,10 +4548,10 @@
         <v>40</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>343</v>
+        <v>334</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>344</v>
+        <v>335</v>
       </c>
     </row>
     <row r="15" spans="1:6" ht="29.1" customHeight="1" x14ac:dyDescent="0.25">
@@ -4478,13 +4560,13 @@
         <v>8</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>346</v>
+        <v>337</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>348</v>
+        <v>339</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>345</v>
+        <v>336</v>
       </c>
     </row>
     <row r="16" spans="1:6" ht="30" x14ac:dyDescent="0.25">
@@ -4493,7 +4575,7 @@
         <v>9</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>347</v>
+        <v>338</v>
       </c>
       <c r="C16" s="3" t="s">
         <v>54</v>
@@ -4629,7 +4711,7 @@
       <c r="K1" s="22"/>
       <c r="L1" s="21"/>
       <c r="M1" s="17" t="s">
-        <v>351</v>
+        <v>341</v>
       </c>
       <c r="N1" s="22"/>
       <c r="O1" s="22"/>
@@ -4711,7 +4793,7 @@
       </c>
       <c r="L3" s="7" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(G1, TestMaster[Test Name], TestMaster[Test Status], "Status not found"), "")</f>
-        <v>Fail</v>
+        <v>Pass</v>
       </c>
       <c r="M3" s="17" t="s">
         <v>21</v>
@@ -4726,7 +4808,7 @@
       </c>
       <c r="R3" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(M1, TestMaster[Test Name], TestMaster[Test Status], "Status not found"), "")</f>
-        <v>Not Implemented</v>
+        <v>Fail</v>
       </c>
       <c r="T3" s="17"/>
       <c r="U3" s="22"/>
@@ -4749,7 +4831,7 @@
       <c r="K4" s="22"/>
       <c r="L4" s="21"/>
       <c r="M4" s="17" t="s">
-        <v>350</v>
+        <v>340</v>
       </c>
       <c r="N4" s="22"/>
       <c r="O4" s="22"/>
@@ -5055,7 +5137,7 @@
         <v>79</v>
       </c>
       <c r="O12" s="3" t="s">
-        <v>321</v>
+        <v>312</v>
       </c>
       <c r="P12" s="3" t="s">
         <v>81</v>
@@ -5081,7 +5163,7 @@
         <v>85</v>
       </c>
       <c r="O13" s="3" t="s">
-        <v>321</v>
+        <v>312</v>
       </c>
       <c r="P13" s="3" t="s">
         <v>86</v>
@@ -5168,7 +5250,7 @@
         <v>80</v>
       </c>
       <c r="P19" t="s">
-        <v>322</v>
+        <v>313</v>
       </c>
     </row>
     <row r="20" spans="13:16" x14ac:dyDescent="0.25">
@@ -5206,6 +5288,10 @@
     </row>
   </sheetData>
   <mergeCells count="20">
+    <mergeCell ref="M4:R5"/>
+    <mergeCell ref="M6:R6"/>
+    <mergeCell ref="M2:N2"/>
+    <mergeCell ref="T6:Y6"/>
     <mergeCell ref="A2:B2"/>
     <mergeCell ref="T2:U2"/>
     <mergeCell ref="M3:N3"/>
@@ -5222,10 +5308,6 @@
     <mergeCell ref="G1:L1"/>
     <mergeCell ref="G2:H2"/>
     <mergeCell ref="G6:L6"/>
-    <mergeCell ref="M4:R5"/>
-    <mergeCell ref="M6:R6"/>
-    <mergeCell ref="M2:N2"/>
-    <mergeCell ref="T6:Y6"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -5266,7 +5348,7 @@
       <c r="E1" s="18"/>
       <c r="F1" s="21"/>
       <c r="G1" s="23" t="s">
-        <v>318</v>
+        <v>309</v>
       </c>
       <c r="H1" s="18"/>
       <c r="I1" s="18"/>
@@ -5274,7 +5356,7 @@
       <c r="K1" s="18"/>
       <c r="L1" s="21"/>
       <c r="M1" s="17" t="s">
-        <v>91</v>
+        <v>342</v>
       </c>
       <c r="N1" s="18"/>
       <c r="O1" s="18"/>
@@ -5331,7 +5413,7 @@
       </c>
       <c r="F3" s="7" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(A1, TestMaster[Test Name], TestMaster[Test Status], "Status not found"), "")</f>
-        <v>Fail</v>
+        <v>Pass</v>
       </c>
       <c r="G3" s="17" t="s">
         <v>21</v>
@@ -5346,7 +5428,7 @@
       </c>
       <c r="L3" s="7" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(G1, TestMaster[Test Name], TestMaster[Test Status], "Status not found"), "")</f>
-        <v>Fail</v>
+        <v>Pass</v>
       </c>
       <c r="M3" s="17" t="s">
         <v>21</v>
@@ -5361,12 +5443,12 @@
       </c>
       <c r="R3" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(M1, TestMaster[Test Name], TestMaster[Test Status], "Status not found"), "")</f>
-        <v>Not Implemented</v>
+        <v>Fail</v>
       </c>
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A4" s="19" t="s">
-        <v>336</v>
+        <v>327</v>
       </c>
       <c r="B4" s="18"/>
       <c r="C4" s="18"/>
@@ -5374,7 +5456,7 @@
       <c r="E4" s="18"/>
       <c r="F4" s="21"/>
       <c r="G4" s="23" t="s">
-        <v>319</v>
+        <v>310</v>
       </c>
       <c r="H4" s="18"/>
       <c r="I4" s="18"/>
@@ -5382,7 +5464,7 @@
       <c r="K4" s="18"/>
       <c r="L4" s="21"/>
       <c r="M4" s="17" t="s">
-        <v>63</v>
+        <v>343</v>
       </c>
       <c r="N4" s="18"/>
       <c r="O4" s="18"/>
@@ -5497,31 +5579,31 @@
         <v>1</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C8" s="4" t="s">
         <v>65</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="G8">
         <v>1</v>
       </c>
       <c r="H8" t="s">
-        <v>320</v>
+        <v>311</v>
       </c>
       <c r="M8">
         <v>1</v>
       </c>
       <c r="N8" s="4" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="O8" s="4" t="s">
         <v>65</v>
       </c>
       <c r="P8" s="4" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="9" spans="1:18" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -5529,34 +5611,34 @@
         <v>2</v>
       </c>
       <c r="B9" t="s">
-        <v>337</v>
+        <v>328</v>
       </c>
       <c r="C9" t="s">
-        <v>338</v>
+        <v>329</v>
       </c>
       <c r="G9">
         <v>2</v>
       </c>
       <c r="H9" s="4" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="I9" s="4" t="s">
         <v>65</v>
       </c>
       <c r="J9" s="4" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="M9">
         <v>2</v>
       </c>
       <c r="N9" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="O9" s="3" t="s">
         <v>96</v>
       </c>
-      <c r="O9" s="3" t="s">
+      <c r="P9" s="3" t="s">
         <v>97</v>
-      </c>
-      <c r="P9" s="3" t="s">
-        <v>98</v>
       </c>
     </row>
     <row r="10" spans="1:18" ht="29.1" customHeight="1" x14ac:dyDescent="0.25">
@@ -5564,7 +5646,7 @@
         <v>3</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C10" s="4" t="s">
         <v>65</v>
@@ -5576,25 +5658,25 @@
         <v>3</v>
       </c>
       <c r="H10" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="I10" s="3" t="s">
         <v>96</v>
       </c>
-      <c r="I10" s="3" t="s">
+      <c r="J10" s="3" t="s">
         <v>97</v>
-      </c>
-      <c r="J10" s="3" t="s">
-        <v>98</v>
       </c>
       <c r="M10">
         <v>3</v>
       </c>
       <c r="N10" s="3" t="s">
-        <v>102</v>
+        <v>347</v>
       </c>
       <c r="O10" s="3" t="s">
-        <v>100</v>
+        <v>344</v>
       </c>
       <c r="P10" s="3" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
     </row>
     <row r="11" spans="1:18" ht="30" x14ac:dyDescent="0.25">
@@ -5602,25 +5684,25 @@
         <v>4</v>
       </c>
       <c r="H11" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="I11" s="3" t="s">
+        <v>314</v>
+      </c>
+      <c r="J11" s="3" t="s">
         <v>99</v>
-      </c>
-      <c r="I11" s="3" t="s">
-        <v>323</v>
-      </c>
-      <c r="J11" s="3" t="s">
-        <v>101</v>
       </c>
       <c r="M11">
         <v>4</v>
       </c>
       <c r="N11" t="s">
-        <v>105</v>
+        <v>363</v>
       </c>
       <c r="O11" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="P11" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
     </row>
     <row r="12" spans="1:18" x14ac:dyDescent="0.25">
@@ -5628,25 +5710,25 @@
         <v>5</v>
       </c>
       <c r="H12" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="I12" t="s">
-        <v>324</v>
+        <v>315</v>
       </c>
       <c r="J12" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="M12">
         <v>5</v>
       </c>
       <c r="N12" t="s">
-        <v>109</v>
+        <v>346</v>
       </c>
       <c r="O12" t="s">
-        <v>107</v>
+        <v>339</v>
       </c>
       <c r="P12" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
     </row>
     <row r="13" spans="1:18" x14ac:dyDescent="0.25">
@@ -5654,13 +5736,13 @@
         <v>6</v>
       </c>
       <c r="H13" t="s">
-        <v>331</v>
+        <v>322</v>
       </c>
       <c r="I13" t="s">
-        <v>325</v>
+        <v>316</v>
       </c>
       <c r="J13" t="s">
-        <v>111</v>
+        <v>106</v>
       </c>
       <c r="M13">
         <v>6</v>
@@ -5672,7 +5754,7 @@
         <v>47</v>
       </c>
       <c r="P13" t="s">
-        <v>112</v>
+        <v>345</v>
       </c>
     </row>
     <row r="14" spans="1:18" x14ac:dyDescent="0.25">
@@ -5680,24 +5762,12 @@
         <v>7</v>
       </c>
       <c r="H14" t="s">
-        <v>330</v>
+        <v>321</v>
       </c>
       <c r="I14" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="J14" t="s">
-        <v>108</v>
-      </c>
-      <c r="M14">
-        <v>8</v>
-      </c>
-      <c r="N14" t="s">
-        <v>113</v>
-      </c>
-      <c r="O14" t="s">
-        <v>106</v>
-      </c>
-      <c r="P14" t="s">
         <v>104</v>
       </c>
     </row>
@@ -5706,22 +5776,10 @@
         <v>8</v>
       </c>
       <c r="H15" t="s">
-        <v>332</v>
+        <v>323</v>
       </c>
       <c r="I15" t="s">
-        <v>326</v>
-      </c>
-      <c r="M15">
-        <v>9</v>
-      </c>
-      <c r="N15" t="s">
-        <v>114</v>
-      </c>
-      <c r="O15" t="s">
-        <v>107</v>
-      </c>
-      <c r="P15" t="s">
-        <v>110</v>
+        <v>317</v>
       </c>
     </row>
     <row r="16" spans="1:18" x14ac:dyDescent="0.25">
@@ -5729,25 +5787,13 @@
         <v>9</v>
       </c>
       <c r="H16" t="s">
-        <v>327</v>
+        <v>318</v>
       </c>
       <c r="I16" t="s">
-        <v>328</v>
+        <v>319</v>
       </c>
       <c r="J16" t="s">
-        <v>104</v>
-      </c>
-      <c r="M16">
-        <v>10</v>
-      </c>
-      <c r="N16" t="s">
-        <v>46</v>
-      </c>
-      <c r="O16" t="s">
-        <v>49</v>
-      </c>
-      <c r="P16" t="s">
-        <v>115</v>
+        <v>101</v>
       </c>
     </row>
     <row r="17" spans="7:10" x14ac:dyDescent="0.25">
@@ -5755,13 +5801,13 @@
         <v>10</v>
       </c>
       <c r="H17" t="s">
-        <v>333</v>
+        <v>324</v>
       </c>
       <c r="I17" t="s">
-        <v>325</v>
+        <v>316</v>
       </c>
       <c r="J17" t="s">
-        <v>111</v>
+        <v>106</v>
       </c>
     </row>
     <row r="18" spans="7:10" x14ac:dyDescent="0.25">
@@ -5769,13 +5815,13 @@
         <v>11</v>
       </c>
       <c r="H18" t="s">
-        <v>116</v>
+        <v>107</v>
       </c>
       <c r="I18" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="J18" t="s">
-        <v>329</v>
+        <v>320</v>
       </c>
     </row>
     <row r="19" spans="7:10" x14ac:dyDescent="0.25">
@@ -5783,13 +5829,13 @@
         <v>12</v>
       </c>
       <c r="H19" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="I19" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="J19" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
     </row>
     <row r="20" spans="7:10" x14ac:dyDescent="0.25">
@@ -5797,10 +5843,10 @@
         <v>13</v>
       </c>
       <c r="H20" t="s">
-        <v>334</v>
+        <v>325</v>
       </c>
       <c r="I20" t="s">
-        <v>335</v>
+        <v>326</v>
       </c>
     </row>
     <row r="21" spans="7:10" x14ac:dyDescent="0.25">
@@ -5808,10 +5854,10 @@
         <v>14</v>
       </c>
       <c r="H21" t="s">
-        <v>116</v>
+        <v>107</v>
       </c>
       <c r="I21" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="J21" t="s">
         <v>59</v>
@@ -5866,7 +5912,7 @@
   <sheetData>
     <row r="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A1" s="19" t="s">
-        <v>118</v>
+        <v>109</v>
       </c>
       <c r="B1" s="18"/>
       <c r="C1" s="18"/>
@@ -5874,7 +5920,7 @@
       <c r="E1" s="18"/>
       <c r="F1" s="21"/>
       <c r="G1" s="23" t="s">
-        <v>119</v>
+        <v>110</v>
       </c>
       <c r="H1" s="18"/>
       <c r="I1" s="18"/>
@@ -5882,7 +5928,7 @@
       <c r="K1" s="18"/>
       <c r="L1" s="21"/>
       <c r="M1" s="17" t="s">
-        <v>120</v>
+        <v>111</v>
       </c>
       <c r="N1" s="18"/>
       <c r="O1" s="18"/>
@@ -5939,7 +5985,7 @@
       </c>
       <c r="F3" s="7" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(A1, TestMaster[Test Name], TestMaster[Test Status], "Status not found"), "")</f>
-        <v>Fail</v>
+        <v>Pass</v>
       </c>
       <c r="G3" s="17" t="s">
         <v>21</v>
@@ -5954,7 +6000,7 @@
       </c>
       <c r="L3" s="7" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(G1, TestMaster[Test Name], TestMaster[Test Status], "Status not found"), "")</f>
-        <v>Fail</v>
+        <v>Pass</v>
       </c>
       <c r="M3" s="17" t="s">
         <v>21</v>
@@ -5969,12 +6015,12 @@
       </c>
       <c r="R3" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(M1, TestMaster[Test Name], TestMaster[Test Status], "Status not found"), "")</f>
-        <v>Not Implemented</v>
+        <v>Pass</v>
       </c>
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A4" s="26" t="s">
-        <v>121</v>
+        <v>112</v>
       </c>
       <c r="B4" s="18"/>
       <c r="C4" s="18"/>
@@ -5982,7 +6028,7 @@
       <c r="E4" s="18"/>
       <c r="F4" s="21"/>
       <c r="G4" s="27" t="s">
-        <v>308</v>
+        <v>299</v>
       </c>
       <c r="H4" s="18"/>
       <c r="I4" s="18"/>
@@ -6020,7 +6066,7 @@
     </row>
     <row r="6" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A6" s="19" t="s">
-        <v>122</v>
+        <v>113</v>
       </c>
       <c r="B6" s="18"/>
       <c r="C6" s="18"/>
@@ -6028,7 +6074,7 @@
       <c r="E6" s="18"/>
       <c r="F6" s="21"/>
       <c r="G6" s="23" t="s">
-        <v>309</v>
+        <v>300</v>
       </c>
       <c r="H6" s="18"/>
       <c r="I6" s="18"/>
@@ -6105,39 +6151,39 @@
         <v>1</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>123</v>
+        <v>114</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>310</v>
+        <v>301</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="F8" s="13"/>
       <c r="G8" s="3">
         <v>1</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>123</v>
+        <v>114</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>307</v>
+        <v>298</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="L8" s="13"/>
       <c r="M8" s="3">
         <v>1</v>
       </c>
       <c r="N8" s="3" t="s">
-        <v>123</v>
+        <v>114</v>
       </c>
       <c r="O8" s="3" t="s">
         <v>65</v>
       </c>
       <c r="P8" s="3" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="9" spans="1:18" s="3" customFormat="1" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -6145,10 +6191,10 @@
         <v>2</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>311</v>
+        <v>302</v>
       </c>
       <c r="D9" s="3" t="s">
         <v>59</v>
@@ -6158,26 +6204,26 @@
         <v>2</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>313</v>
+        <v>304</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="L9" s="13"/>
       <c r="M9" s="3">
         <v>2</v>
       </c>
       <c r="N9" s="3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="O9" s="3" t="s">
-        <v>124</v>
+        <v>115</v>
       </c>
       <c r="P9" s="3" t="s">
-        <v>125</v>
+        <v>116</v>
       </c>
     </row>
     <row r="10" spans="1:18" s="3" customFormat="1" ht="29.1" customHeight="1" x14ac:dyDescent="0.25">
@@ -6186,26 +6232,26 @@
         <v>3</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>126</v>
+        <v>117</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>314</v>
+        <v>305</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>315</v>
+        <v>306</v>
       </c>
       <c r="L10" s="13"/>
       <c r="M10" s="3">
         <v>3</v>
       </c>
       <c r="N10" s="3" t="s">
-        <v>126</v>
+        <v>117</v>
       </c>
       <c r="O10" s="3" t="s">
-        <v>127</v>
+        <v>118</v>
       </c>
       <c r="P10" s="3" t="s">
-        <v>128</v>
+        <v>119</v>
       </c>
     </row>
     <row r="11" spans="1:18" ht="29.1" customHeight="1" x14ac:dyDescent="0.25">
@@ -6213,25 +6259,25 @@
         <v>4</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>312</v>
+        <v>303</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>316</v>
+        <v>307</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>317</v>
+        <v>308</v>
       </c>
       <c r="M11" s="3">
         <v>4</v>
       </c>
       <c r="N11" s="3" t="s">
-        <v>129</v>
+        <v>120</v>
       </c>
       <c r="O11" s="3" t="s">
-        <v>130</v>
+        <v>121</v>
       </c>
       <c r="P11" s="3" t="s">
-        <v>131</v>
+        <v>122</v>
       </c>
     </row>
   </sheetData>
@@ -6258,7 +6304,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
-  <dimension ref="A1:R21"/>
+  <dimension ref="A1:X21"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5" bestFit="1" customWidth="1"/>
@@ -6273,16 +6319,22 @@
     <col min="10" max="10" width="15.28515625" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="18.42578125" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="8.7109375" style="15" customWidth="1"/>
-    <col min="14" max="14" width="23.28515625" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="17.140625" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="41" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="24.42578125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="30.42578125" customWidth="1"/>
+    <col min="16" max="16" width="45.42578125" customWidth="1"/>
     <col min="17" max="17" width="18.42578125" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="8" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="5" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="31.5703125" customWidth="1"/>
+    <col min="21" max="21" width="20" customWidth="1"/>
+    <col min="22" max="22" width="31.42578125" customWidth="1"/>
+    <col min="23" max="23" width="19.28515625" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="10.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A1" s="19" t="s">
-        <v>132</v>
+        <v>123</v>
       </c>
       <c r="B1" s="18"/>
       <c r="C1" s="18"/>
@@ -6290,7 +6342,7 @@
       <c r="E1" s="18"/>
       <c r="F1" s="21"/>
       <c r="G1" s="17" t="s">
-        <v>133</v>
+        <v>124</v>
       </c>
       <c r="H1" s="18"/>
       <c r="I1" s="18"/>
@@ -6298,15 +6350,23 @@
       <c r="K1" s="18"/>
       <c r="L1" s="18"/>
       <c r="M1" s="23" t="s">
-        <v>134</v>
+        <v>125</v>
       </c>
       <c r="N1" s="18"/>
       <c r="O1" s="18"/>
       <c r="P1" s="18"/>
       <c r="Q1" s="18"/>
       <c r="R1" s="21"/>
-    </row>
-    <row r="2" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S1" s="28" t="s">
+        <v>360</v>
+      </c>
+      <c r="T1" s="17"/>
+      <c r="U1" s="17"/>
+      <c r="V1" s="17"/>
+      <c r="W1" s="17"/>
+      <c r="X1" s="19"/>
+    </row>
+    <row r="2" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A2" s="17" t="s">
         <v>19</v>
       </c>
@@ -6341,8 +6401,20 @@
         <v>20</v>
       </c>
       <c r="R2" s="7"/>
-    </row>
-    <row r="3" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S2" s="28" t="s">
+        <v>19</v>
+      </c>
+      <c r="T2" s="18"/>
+      <c r="U2" s="6">
+        <f>IFERROR(_xlfn.XLOOKUP(S1, TestMaster[Test Name], TestMaster[Test ID], "ID not found"), "")</f>
+        <v>36</v>
+      </c>
+      <c r="W2" t="s">
+        <v>20</v>
+      </c>
+      <c r="X2" s="7"/>
+    </row>
+    <row r="3" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A3" s="17" t="s">
         <v>21</v>
       </c>
@@ -6388,10 +6460,25 @@
         <f>IFERROR(_xlfn.XLOOKUP(M1, TestMaster[Test Name], TestMaster[Test Priority], "Priority not found"), "")</f>
         <v>Medium</v>
       </c>
-    </row>
-    <row r="4" spans="1:18" s="2" customFormat="1" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="S3" s="28" t="s">
+        <v>21</v>
+      </c>
+      <c r="T3" s="18"/>
+      <c r="U3" s="6" t="str">
+        <f>IFERROR(_xlfn.XLOOKUP(S1, TestMaster[Test Name], TestMaster[Test Priority], "Priority not found"), "")</f>
+        <v>Medium</v>
+      </c>
+      <c r="W3" t="s">
+        <v>22</v>
+      </c>
+      <c r="X3" s="7" t="str">
+        <f>IFERROR(_xlfn.XLOOKUP(S1, TestMaster[Test Name], TestMaster[Test Priority], "Priority not found"), "")</f>
+        <v>Medium</v>
+      </c>
+    </row>
+    <row r="4" spans="1:24" s="2" customFormat="1" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="26" t="s">
-        <v>135</v>
+        <v>126</v>
       </c>
       <c r="B4" s="20"/>
       <c r="C4" s="20"/>
@@ -6399,7 +6486,7 @@
       <c r="E4" s="20"/>
       <c r="F4" s="21"/>
       <c r="G4" s="25" t="s">
-        <v>136</v>
+        <v>127</v>
       </c>
       <c r="H4" s="20"/>
       <c r="I4" s="20"/>
@@ -6407,15 +6494,23 @@
       <c r="K4" s="20"/>
       <c r="L4" s="20"/>
       <c r="M4" s="27" t="s">
-        <v>137</v>
+        <v>128</v>
       </c>
       <c r="N4" s="20"/>
       <c r="O4" s="20"/>
       <c r="P4" s="20"/>
       <c r="Q4" s="20"/>
       <c r="R4" s="21"/>
-    </row>
-    <row r="5" spans="1:18" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="S4" s="27" t="s">
+        <v>361</v>
+      </c>
+      <c r="T4" s="20"/>
+      <c r="U4" s="20"/>
+      <c r="V4" s="20"/>
+      <c r="W4" s="20"/>
+      <c r="X4" s="21"/>
+    </row>
+    <row r="5" spans="1:24" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="20"/>
       <c r="B5" s="20"/>
       <c r="C5" s="20"/>
@@ -6434,10 +6529,16 @@
       <c r="P5" s="20"/>
       <c r="Q5" s="20"/>
       <c r="R5" s="21"/>
-    </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S5" s="24"/>
+      <c r="T5" s="20"/>
+      <c r="U5" s="20"/>
+      <c r="V5" s="20"/>
+      <c r="W5" s="20"/>
+      <c r="X5" s="21"/>
+    </row>
+    <row r="6" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A6" s="19" t="s">
-        <v>138</v>
+        <v>129</v>
       </c>
       <c r="B6" s="18"/>
       <c r="C6" s="18"/>
@@ -6445,7 +6546,7 @@
       <c r="E6" s="18"/>
       <c r="F6" s="21"/>
       <c r="G6" s="17" t="s">
-        <v>139</v>
+        <v>130</v>
       </c>
       <c r="H6" s="18"/>
       <c r="I6" s="18"/>
@@ -6453,15 +6554,23 @@
       <c r="K6" s="18"/>
       <c r="L6" s="18"/>
       <c r="M6" s="23" t="s">
-        <v>139</v>
+        <v>130</v>
       </c>
       <c r="N6" s="18"/>
       <c r="O6" s="18"/>
       <c r="P6" s="18"/>
       <c r="Q6" s="18"/>
       <c r="R6" s="21"/>
-    </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S6" s="23" t="s">
+        <v>362</v>
+      </c>
+      <c r="T6" s="18"/>
+      <c r="U6" s="18"/>
+      <c r="V6" s="18"/>
+      <c r="W6" s="18"/>
+      <c r="X6" s="21"/>
+    </row>
+    <row r="7" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>25</v>
       </c>
@@ -6516,266 +6625,435 @@
       <c r="R7" s="10" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S7" s="14" t="s">
+        <v>25</v>
+      </c>
+      <c r="T7" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="U7" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="V7" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="W7" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="X7" s="10" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="8" spans="1:24" ht="75" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>1</v>
       </c>
       <c r="B8" t="s">
-        <v>140</v>
+        <v>131</v>
       </c>
       <c r="C8" t="s">
-        <v>141</v>
+        <v>132</v>
       </c>
       <c r="D8" t="s">
-        <v>142</v>
+        <v>133</v>
       </c>
       <c r="G8">
         <v>1</v>
       </c>
       <c r="H8" t="s">
-        <v>143</v>
+        <v>134</v>
       </c>
       <c r="I8" t="s">
-        <v>144</v>
+        <v>135</v>
       </c>
       <c r="J8" t="s">
-        <v>145</v>
+        <v>136</v>
       </c>
       <c r="M8" s="15">
         <v>1</v>
       </c>
+      <c r="N8" t="s">
+        <v>348</v>
+      </c>
+      <c r="O8" s="2" t="s">
+        <v>349</v>
+      </c>
+      <c r="P8" s="2" t="s">
+        <v>350</v>
+      </c>
       <c r="R8" s="7"/>
-    </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S8" s="15">
+        <v>1</v>
+      </c>
+      <c r="T8" s="4" t="s">
+        <v>365</v>
+      </c>
+      <c r="U8" s="3" t="s">
+        <v>377</v>
+      </c>
+      <c r="V8" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="X8" s="7"/>
+    </row>
+    <row r="9" spans="1:24" ht="45" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>2</v>
       </c>
       <c r="B9" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C9" t="s">
-        <v>146</v>
+        <v>137</v>
       </c>
       <c r="D9" t="s">
-        <v>147</v>
+        <v>138</v>
       </c>
       <c r="G9">
         <v>2</v>
       </c>
       <c r="H9" t="s">
-        <v>148</v>
+        <v>139</v>
       </c>
       <c r="I9" t="s">
-        <v>149</v>
+        <v>140</v>
       </c>
       <c r="J9" t="s">
-        <v>150</v>
+        <v>141</v>
       </c>
       <c r="M9" s="15">
         <v>2</v>
       </c>
+      <c r="N9" t="s">
+        <v>351</v>
+      </c>
+      <c r="O9" t="s">
+        <v>352</v>
+      </c>
+      <c r="P9" t="s">
+        <v>353</v>
+      </c>
       <c r="R9" s="7"/>
-    </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S9" s="15">
+        <v>2</v>
+      </c>
+      <c r="T9" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="U9" s="3" t="s">
+        <v>364</v>
+      </c>
+      <c r="V9" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="X9" s="7"/>
+    </row>
+    <row r="10" spans="1:24" ht="60" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>3</v>
       </c>
       <c r="B10" t="s">
-        <v>151</v>
+        <v>142</v>
       </c>
       <c r="C10" t="s">
-        <v>152</v>
+        <v>143</v>
       </c>
       <c r="D10" t="s">
-        <v>153</v>
+        <v>144</v>
       </c>
       <c r="G10">
         <v>3</v>
       </c>
       <c r="H10" t="s">
-        <v>154</v>
+        <v>145</v>
       </c>
       <c r="I10" t="s">
-        <v>155</v>
+        <v>146</v>
       </c>
       <c r="J10" t="s">
-        <v>156</v>
+        <v>147</v>
       </c>
       <c r="M10" s="15">
         <v>3</v>
       </c>
+      <c r="N10" t="s">
+        <v>354</v>
+      </c>
+      <c r="O10" t="s">
+        <v>355</v>
+      </c>
+      <c r="P10" t="b">
+        <v>1</v>
+      </c>
       <c r="R10" s="7"/>
-    </row>
-    <row r="11" spans="1:18" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="S10" s="4">
+        <v>3</v>
+      </c>
+      <c r="T10" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="U10" s="3" t="s">
+        <v>366</v>
+      </c>
+      <c r="V10" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="X10" s="7"/>
+    </row>
+    <row r="11" spans="1:24" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>4</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>157</v>
+        <v>148</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>158</v>
+        <v>149</v>
       </c>
       <c r="D11" t="s">
-        <v>159</v>
+        <v>150</v>
       </c>
       <c r="G11">
         <v>4</v>
       </c>
       <c r="H11" t="s">
-        <v>160</v>
+        <v>151</v>
       </c>
       <c r="I11" t="s">
         <v>65</v>
       </c>
       <c r="J11" t="s">
-        <v>161</v>
+        <v>152</v>
       </c>
       <c r="M11" s="15">
         <v>4</v>
       </c>
-      <c r="N11" s="2"/>
-      <c r="O11" s="2"/>
-      <c r="P11" s="2"/>
+      <c r="N11" s="2" t="s">
+        <v>356</v>
+      </c>
+      <c r="O11" s="2" t="s">
+        <v>357</v>
+      </c>
+      <c r="P11" s="2" t="s">
+        <v>358</v>
+      </c>
       <c r="R11" s="7"/>
-    </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S11" s="4">
+        <v>4</v>
+      </c>
+      <c r="T11" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="U11" s="3" t="s">
+        <v>370</v>
+      </c>
+      <c r="V11" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="X11" s="7"/>
+    </row>
+    <row r="12" spans="1:24" ht="30" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>5</v>
       </c>
       <c r="B12" t="s">
-        <v>140</v>
+        <v>131</v>
       </c>
       <c r="D12" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.25">
+        <v>153</v>
+      </c>
+      <c r="M12" s="15">
+        <v>5</v>
+      </c>
+      <c r="N12" t="s">
+        <v>359</v>
+      </c>
+      <c r="R12" s="7"/>
+      <c r="S12" s="4">
+        <v>5</v>
+      </c>
+      <c r="T12" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="U12" s="3" t="s">
+        <v>367</v>
+      </c>
+      <c r="V12" s="3" t="s">
+        <v>372</v>
+      </c>
+      <c r="X12" s="7"/>
+    </row>
+    <row r="13" spans="1:24" ht="30" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>6</v>
       </c>
       <c r="B13" t="s">
-        <v>163</v>
+        <v>154</v>
       </c>
       <c r="C13" t="s">
-        <v>164</v>
+        <v>155</v>
       </c>
       <c r="D13" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.25">
+        <v>138</v>
+      </c>
+      <c r="R13" s="7"/>
+      <c r="S13" s="4">
+        <v>6</v>
+      </c>
+      <c r="T13" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="U13" s="3" t="s">
+        <v>371</v>
+      </c>
+      <c r="V13" s="3" t="s">
+        <v>368</v>
+      </c>
+      <c r="X13" s="7"/>
+    </row>
+    <row r="14" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>7</v>
       </c>
       <c r="B14" t="s">
-        <v>165</v>
+        <v>156</v>
       </c>
       <c r="C14" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.25">
+        <v>157</v>
+      </c>
+      <c r="R14" s="7"/>
+      <c r="S14" s="4">
+        <v>7</v>
+      </c>
+      <c r="T14" s="4" t="s">
+        <v>369</v>
+      </c>
+      <c r="U14" s="3" t="s">
+        <v>373</v>
+      </c>
+      <c r="V14" s="3" t="s">
+        <v>374</v>
+      </c>
+      <c r="X14" s="7"/>
+    </row>
+    <row r="15" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>8</v>
       </c>
       <c r="B15" t="s">
-        <v>167</v>
+        <v>158</v>
       </c>
       <c r="C15" t="s">
         <v>58</v>
       </c>
       <c r="D15" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.25">
+        <v>159</v>
+      </c>
+      <c r="R15" s="7"/>
+      <c r="S15" s="4">
+        <v>8</v>
+      </c>
+      <c r="T15" s="4" t="s">
+        <v>375</v>
+      </c>
+      <c r="U15" s="3" t="s">
+        <v>376</v>
+      </c>
+      <c r="V15" s="3" t="s">
+        <v>378</v>
+      </c>
+      <c r="X15" s="7"/>
+    </row>
+    <row r="16" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>9</v>
       </c>
       <c r="B16" t="s">
-        <v>169</v>
+        <v>160</v>
       </c>
       <c r="C16" t="s">
-        <v>164</v>
+        <v>155</v>
       </c>
       <c r="D16" t="s">
         <v>59</v>
       </c>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="R16" s="7"/>
+      <c r="X16" s="7"/>
+    </row>
+    <row r="17" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>10</v>
       </c>
       <c r="B17" t="s">
-        <v>170</v>
+        <v>161</v>
       </c>
       <c r="C17" t="s">
-        <v>171</v>
+        <v>162</v>
       </c>
       <c r="D17" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" ht="72.599999999999994" customHeight="1" x14ac:dyDescent="0.25">
+        <v>163</v>
+      </c>
+      <c r="R17" s="7"/>
+      <c r="X17" s="7"/>
+    </row>
+    <row r="18" spans="1:24" ht="72.599999999999994" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>11</v>
       </c>
       <c r="B18" t="s">
-        <v>173</v>
+        <v>164</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>174</v>
+        <v>165</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="19" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>12</v>
       </c>
       <c r="B19" t="s">
-        <v>165</v>
+        <v>156</v>
       </c>
       <c r="C19" t="s">
         <v>65</v>
       </c>
       <c r="D19" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="20" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>13</v>
       </c>
       <c r="B20" t="s">
-        <v>167</v>
+        <v>158</v>
       </c>
       <c r="C20" t="s">
         <v>44</v>
       </c>
       <c r="D20" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="21" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>14</v>
       </c>
       <c r="B21" t="s">
-        <v>169</v>
+        <v>160</v>
       </c>
       <c r="C21" t="s">
-        <v>164</v>
+        <v>155</v>
       </c>
       <c r="D21" t="s">
         <v>59</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="15">
+  <mergeCells count="20">
     <mergeCell ref="G1:L1"/>
     <mergeCell ref="M2:N2"/>
     <mergeCell ref="A2:B2"/>
@@ -6791,6 +7069,11 @@
     <mergeCell ref="A3:B3"/>
     <mergeCell ref="G3:H3"/>
     <mergeCell ref="M6:R6"/>
+    <mergeCell ref="S2:T2"/>
+    <mergeCell ref="S3:T3"/>
+    <mergeCell ref="S4:X5"/>
+    <mergeCell ref="S6:X6"/>
+    <mergeCell ref="S1:X1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -6827,184 +7110,184 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:160" x14ac:dyDescent="0.25">
-      <c r="A1" s="29" t="s">
-        <v>177</v>
+      <c r="A1" s="30" t="s">
+        <v>168</v>
       </c>
       <c r="B1" s="18"/>
       <c r="C1" s="18"/>
       <c r="D1" s="18"/>
       <c r="E1" s="18"/>
       <c r="F1" s="18"/>
-      <c r="H1" s="29" t="s">
-        <v>178</v>
+      <c r="H1" s="30" t="s">
+        <v>169</v>
       </c>
       <c r="I1" s="18"/>
       <c r="J1" s="18"/>
       <c r="K1" s="18"/>
       <c r="L1" s="18"/>
       <c r="M1" s="18"/>
-      <c r="O1" s="29" t="s">
-        <v>179</v>
+      <c r="O1" s="30" t="s">
+        <v>170</v>
       </c>
       <c r="P1" s="18"/>
       <c r="Q1" s="18"/>
       <c r="R1" s="18"/>
       <c r="S1" s="18"/>
       <c r="T1" s="18"/>
-      <c r="V1" s="29" t="s">
-        <v>180</v>
+      <c r="V1" s="30" t="s">
+        <v>171</v>
       </c>
       <c r="W1" s="18"/>
       <c r="X1" s="18"/>
       <c r="Y1" s="18"/>
       <c r="Z1" s="18"/>
       <c r="AA1" s="18"/>
-      <c r="AC1" s="29" t="s">
-        <v>181</v>
+      <c r="AC1" s="30" t="s">
+        <v>172</v>
       </c>
       <c r="AD1" s="18"/>
       <c r="AE1" s="18"/>
       <c r="AF1" s="18"/>
       <c r="AG1" s="18"/>
       <c r="AH1" s="18"/>
-      <c r="AJ1" s="29" t="s">
-        <v>182</v>
+      <c r="AJ1" s="30" t="s">
+        <v>173</v>
       </c>
       <c r="AK1" s="18"/>
       <c r="AL1" s="18"/>
       <c r="AM1" s="18"/>
       <c r="AN1" s="18"/>
       <c r="AO1" s="18"/>
-      <c r="AQ1" s="29" t="s">
-        <v>183</v>
+      <c r="AQ1" s="30" t="s">
+        <v>174</v>
       </c>
       <c r="AR1" s="18"/>
       <c r="AS1" s="18"/>
       <c r="AT1" s="18"/>
       <c r="AU1" s="18"/>
       <c r="AV1" s="18"/>
-      <c r="AX1" s="29" t="s">
-        <v>184</v>
+      <c r="AX1" s="30" t="s">
+        <v>175</v>
       </c>
       <c r="AY1" s="18"/>
       <c r="AZ1" s="18"/>
       <c r="BA1" s="18"/>
       <c r="BB1" s="18"/>
       <c r="BC1" s="18"/>
-      <c r="BE1" s="29" t="s">
-        <v>185</v>
+      <c r="BE1" s="30" t="s">
+        <v>176</v>
       </c>
       <c r="BF1" s="18"/>
       <c r="BG1" s="18"/>
       <c r="BH1" s="18"/>
       <c r="BI1" s="18"/>
       <c r="BJ1" s="18"/>
-      <c r="BL1" s="29" t="s">
-        <v>186</v>
+      <c r="BL1" s="30" t="s">
+        <v>177</v>
       </c>
       <c r="BM1" s="18"/>
       <c r="BN1" s="18"/>
       <c r="BO1" s="18"/>
       <c r="BP1" s="18"/>
       <c r="BQ1" s="18"/>
-      <c r="BS1" s="29" t="s">
-        <v>187</v>
+      <c r="BS1" s="30" t="s">
+        <v>178</v>
       </c>
       <c r="BT1" s="18"/>
       <c r="BU1" s="18"/>
       <c r="BV1" s="18"/>
       <c r="BW1" s="18"/>
       <c r="BX1" s="18"/>
-      <c r="BZ1" s="29" t="s">
-        <v>188</v>
+      <c r="BZ1" s="30" t="s">
+        <v>179</v>
       </c>
       <c r="CA1" s="18"/>
       <c r="CB1" s="18"/>
       <c r="CC1" s="18"/>
       <c r="CD1" s="18"/>
       <c r="CE1" s="18"/>
-      <c r="CG1" s="29" t="s">
-        <v>189</v>
+      <c r="CG1" s="30" t="s">
+        <v>180</v>
       </c>
       <c r="CH1" s="18"/>
       <c r="CI1" s="18"/>
       <c r="CJ1" s="18"/>
       <c r="CK1" s="18"/>
       <c r="CL1" s="18"/>
-      <c r="CN1" s="29" t="s">
-        <v>190</v>
+      <c r="CN1" s="30" t="s">
+        <v>181</v>
       </c>
       <c r="CO1" s="18"/>
       <c r="CP1" s="18"/>
       <c r="CQ1" s="18"/>
       <c r="CR1" s="18"/>
       <c r="CS1" s="18"/>
-      <c r="CU1" s="29" t="s">
-        <v>191</v>
+      <c r="CU1" s="30" t="s">
+        <v>182</v>
       </c>
       <c r="CV1" s="18"/>
       <c r="CW1" s="18"/>
       <c r="CX1" s="18"/>
       <c r="CY1" s="18"/>
       <c r="CZ1" s="18"/>
-      <c r="DB1" s="29" t="s">
-        <v>192</v>
+      <c r="DB1" s="30" t="s">
+        <v>183</v>
       </c>
       <c r="DC1" s="18"/>
       <c r="DD1" s="18"/>
       <c r="DE1" s="18"/>
       <c r="DF1" s="18"/>
       <c r="DG1" s="18"/>
-      <c r="DI1" s="29" t="s">
-        <v>193</v>
+      <c r="DI1" s="30" t="s">
+        <v>184</v>
       </c>
       <c r="DJ1" s="18"/>
       <c r="DK1" s="18"/>
       <c r="DL1" s="18"/>
       <c r="DM1" s="18"/>
       <c r="DN1" s="18"/>
-      <c r="DP1" s="29" t="s">
-        <v>194</v>
+      <c r="DP1" s="30" t="s">
+        <v>185</v>
       </c>
       <c r="DQ1" s="18"/>
       <c r="DR1" s="18"/>
       <c r="DS1" s="18"/>
       <c r="DT1" s="18"/>
       <c r="DU1" s="18"/>
-      <c r="DW1" s="29" t="s">
-        <v>195</v>
+      <c r="DW1" s="30" t="s">
+        <v>186</v>
       </c>
       <c r="DX1" s="18"/>
       <c r="DY1" s="18"/>
       <c r="DZ1" s="18"/>
       <c r="EA1" s="18"/>
       <c r="EB1" s="18"/>
-      <c r="ED1" s="29" t="s">
-        <v>196</v>
+      <c r="ED1" s="30" t="s">
+        <v>187</v>
       </c>
       <c r="EE1" s="18"/>
       <c r="EF1" s="18"/>
       <c r="EG1" s="18"/>
       <c r="EH1" s="18"/>
       <c r="EI1" s="18"/>
-      <c r="EK1" s="29" t="s">
-        <v>197</v>
+      <c r="EK1" s="30" t="s">
+        <v>188</v>
       </c>
       <c r="EL1" s="18"/>
       <c r="EM1" s="18"/>
       <c r="EN1" s="18"/>
       <c r="EO1" s="18"/>
       <c r="EP1" s="18"/>
-      <c r="ER1" s="29" t="s">
-        <v>198</v>
+      <c r="ER1" s="30" t="s">
+        <v>189</v>
       </c>
       <c r="ES1" s="18"/>
       <c r="ET1" s="18"/>
       <c r="EU1" s="18"/>
       <c r="EV1" s="18"/>
       <c r="EW1" s="18"/>
-      <c r="EY1" s="29" t="s">
-        <v>199</v>
+      <c r="EY1" s="30" t="s">
+        <v>190</v>
       </c>
       <c r="EZ1" s="18"/>
       <c r="FA1" s="18"/>
@@ -7599,8 +7882,8 @@
       <c r="A6" s="16" t="s">
         <v>63</v>
       </c>
-      <c r="B6" s="30" t="s">
-        <v>200</v>
+      <c r="B6" s="29" t="s">
+        <v>191</v>
       </c>
       <c r="C6" s="18"/>
       <c r="D6" s="18"/>
@@ -7609,8 +7892,8 @@
       <c r="H6" s="16" t="s">
         <v>63</v>
       </c>
-      <c r="I6" s="30" t="s">
-        <v>201</v>
+      <c r="I6" s="29" t="s">
+        <v>192</v>
       </c>
       <c r="J6" s="18"/>
       <c r="K6" s="18"/>
@@ -7619,8 +7902,8 @@
       <c r="O6" s="16" t="s">
         <v>63</v>
       </c>
-      <c r="P6" s="30" t="s">
-        <v>202</v>
+      <c r="P6" s="29" t="s">
+        <v>193</v>
       </c>
       <c r="Q6" s="18"/>
       <c r="R6" s="18"/>
@@ -7629,8 +7912,8 @@
       <c r="V6" s="16" t="s">
         <v>63</v>
       </c>
-      <c r="W6" s="30" t="s">
-        <v>203</v>
+      <c r="W6" s="29" t="s">
+        <v>194</v>
       </c>
       <c r="X6" s="18"/>
       <c r="Y6" s="18"/>
@@ -7639,8 +7922,8 @@
       <c r="AC6" s="16" t="s">
         <v>63</v>
       </c>
-      <c r="AD6" s="30" t="s">
-        <v>204</v>
+      <c r="AD6" s="29" t="s">
+        <v>195</v>
       </c>
       <c r="AE6" s="18"/>
       <c r="AF6" s="18"/>
@@ -7649,8 +7932,8 @@
       <c r="AJ6" s="16" t="s">
         <v>63</v>
       </c>
-      <c r="AK6" s="30" t="s">
-        <v>205</v>
+      <c r="AK6" s="29" t="s">
+        <v>196</v>
       </c>
       <c r="AL6" s="18"/>
       <c r="AM6" s="18"/>
@@ -7659,8 +7942,8 @@
       <c r="AQ6" s="16" t="s">
         <v>63</v>
       </c>
-      <c r="AR6" s="30" t="s">
-        <v>206</v>
+      <c r="AR6" s="29" t="s">
+        <v>197</v>
       </c>
       <c r="AS6" s="18"/>
       <c r="AT6" s="18"/>
@@ -7669,8 +7952,8 @@
       <c r="AX6" s="16" t="s">
         <v>63</v>
       </c>
-      <c r="AY6" s="30" t="s">
-        <v>207</v>
+      <c r="AY6" s="29" t="s">
+        <v>198</v>
       </c>
       <c r="AZ6" s="18"/>
       <c r="BA6" s="18"/>
@@ -7679,8 +7962,8 @@
       <c r="BE6" s="16" t="s">
         <v>63</v>
       </c>
-      <c r="BF6" s="30" t="s">
-        <v>208</v>
+      <c r="BF6" s="29" t="s">
+        <v>199</v>
       </c>
       <c r="BG6" s="18"/>
       <c r="BH6" s="18"/>
@@ -7689,8 +7972,8 @@
       <c r="BL6" s="16" t="s">
         <v>63</v>
       </c>
-      <c r="BM6" s="30" t="s">
-        <v>209</v>
+      <c r="BM6" s="29" t="s">
+        <v>200</v>
       </c>
       <c r="BN6" s="18"/>
       <c r="BO6" s="18"/>
@@ -7699,8 +7982,8 @@
       <c r="BS6" s="16" t="s">
         <v>63</v>
       </c>
-      <c r="BT6" s="30" t="s">
-        <v>210</v>
+      <c r="BT6" s="29" t="s">
+        <v>201</v>
       </c>
       <c r="BU6" s="18"/>
       <c r="BV6" s="18"/>
@@ -7709,8 +7992,8 @@
       <c r="BZ6" s="16" t="s">
         <v>63</v>
       </c>
-      <c r="CA6" s="30" t="s">
-        <v>211</v>
+      <c r="CA6" s="29" t="s">
+        <v>202</v>
       </c>
       <c r="CB6" s="18"/>
       <c r="CC6" s="18"/>
@@ -7719,8 +8002,8 @@
       <c r="CG6" s="16" t="s">
         <v>63</v>
       </c>
-      <c r="CH6" s="30" t="s">
-        <v>212</v>
+      <c r="CH6" s="29" t="s">
+        <v>203</v>
       </c>
       <c r="CI6" s="18"/>
       <c r="CJ6" s="18"/>
@@ -7729,8 +8012,8 @@
       <c r="CN6" s="16" t="s">
         <v>63</v>
       </c>
-      <c r="CO6" s="30" t="s">
-        <v>213</v>
+      <c r="CO6" s="29" t="s">
+        <v>204</v>
       </c>
       <c r="CP6" s="18"/>
       <c r="CQ6" s="18"/>
@@ -7739,8 +8022,8 @@
       <c r="CU6" s="16" t="s">
         <v>63</v>
       </c>
-      <c r="CV6" s="30" t="s">
-        <v>214</v>
+      <c r="CV6" s="29" t="s">
+        <v>205</v>
       </c>
       <c r="CW6" s="18"/>
       <c r="CX6" s="18"/>
@@ -7749,8 +8032,8 @@
       <c r="DB6" s="16" t="s">
         <v>63</v>
       </c>
-      <c r="DC6" s="30" t="s">
-        <v>215</v>
+      <c r="DC6" s="29" t="s">
+        <v>206</v>
       </c>
       <c r="DD6" s="18"/>
       <c r="DE6" s="18"/>
@@ -7759,8 +8042,8 @@
       <c r="DI6" s="16" t="s">
         <v>63</v>
       </c>
-      <c r="DJ6" s="30" t="s">
-        <v>216</v>
+      <c r="DJ6" s="29" t="s">
+        <v>207</v>
       </c>
       <c r="DK6" s="18"/>
       <c r="DL6" s="18"/>
@@ -7769,8 +8052,8 @@
       <c r="DP6" s="16" t="s">
         <v>63</v>
       </c>
-      <c r="DQ6" s="30" t="s">
-        <v>217</v>
+      <c r="DQ6" s="29" t="s">
+        <v>208</v>
       </c>
       <c r="DR6" s="18"/>
       <c r="DS6" s="18"/>
@@ -7779,8 +8062,8 @@
       <c r="DW6" s="16" t="s">
         <v>63</v>
       </c>
-      <c r="DX6" s="30" t="s">
-        <v>218</v>
+      <c r="DX6" s="29" t="s">
+        <v>209</v>
       </c>
       <c r="DY6" s="18"/>
       <c r="DZ6" s="18"/>
@@ -7789,8 +8072,8 @@
       <c r="ED6" s="16" t="s">
         <v>63</v>
       </c>
-      <c r="EE6" s="30" t="s">
-        <v>219</v>
+      <c r="EE6" s="29" t="s">
+        <v>210</v>
       </c>
       <c r="EF6" s="18"/>
       <c r="EG6" s="18"/>
@@ -7799,8 +8082,8 @@
       <c r="EK6" s="16" t="s">
         <v>63</v>
       </c>
-      <c r="EL6" s="30" t="s">
-        <v>220</v>
+      <c r="EL6" s="29" t="s">
+        <v>211</v>
       </c>
       <c r="EM6" s="18"/>
       <c r="EN6" s="18"/>
@@ -7809,8 +8092,8 @@
       <c r="ER6" s="16" t="s">
         <v>63</v>
       </c>
-      <c r="ES6" s="30" t="s">
-        <v>221</v>
+      <c r="ES6" s="29" t="s">
+        <v>212</v>
       </c>
       <c r="ET6" s="18"/>
       <c r="EU6" s="18"/>
@@ -7819,8 +8102,8 @@
       <c r="EY6" s="16" t="s">
         <v>63</v>
       </c>
-      <c r="EZ6" s="30" t="s">
-        <v>222</v>
+      <c r="EZ6" s="29" t="s">
+        <v>213</v>
       </c>
       <c r="FA6" s="18"/>
       <c r="FB6" s="18"/>
@@ -7831,8 +8114,8 @@
       <c r="A7" s="16" t="s">
         <v>24</v>
       </c>
-      <c r="B7" s="30" t="s">
-        <v>223</v>
+      <c r="B7" s="29" t="s">
+        <v>214</v>
       </c>
       <c r="C7" s="18"/>
       <c r="D7" s="18"/>
@@ -7841,8 +8124,8 @@
       <c r="H7" s="16" t="s">
         <v>24</v>
       </c>
-      <c r="I7" s="30" t="s">
-        <v>223</v>
+      <c r="I7" s="29" t="s">
+        <v>214</v>
       </c>
       <c r="J7" s="18"/>
       <c r="K7" s="18"/>
@@ -7851,8 +8134,8 @@
       <c r="O7" s="16" t="s">
         <v>24</v>
       </c>
-      <c r="P7" s="30" t="s">
-        <v>223</v>
+      <c r="P7" s="29" t="s">
+        <v>214</v>
       </c>
       <c r="Q7" s="18"/>
       <c r="R7" s="18"/>
@@ -7861,8 +8144,8 @@
       <c r="V7" s="16" t="s">
         <v>24</v>
       </c>
-      <c r="W7" s="30" t="s">
-        <v>223</v>
+      <c r="W7" s="29" t="s">
+        <v>214</v>
       </c>
       <c r="X7" s="18"/>
       <c r="Y7" s="18"/>
@@ -7871,8 +8154,8 @@
       <c r="AC7" s="16" t="s">
         <v>24</v>
       </c>
-      <c r="AD7" s="30" t="s">
-        <v>223</v>
+      <c r="AD7" s="29" t="s">
+        <v>214</v>
       </c>
       <c r="AE7" s="18"/>
       <c r="AF7" s="18"/>
@@ -7881,8 +8164,8 @@
       <c r="AJ7" s="16" t="s">
         <v>24</v>
       </c>
-      <c r="AK7" s="30" t="s">
-        <v>223</v>
+      <c r="AK7" s="29" t="s">
+        <v>214</v>
       </c>
       <c r="AL7" s="18"/>
       <c r="AM7" s="18"/>
@@ -7891,8 +8174,8 @@
       <c r="AQ7" s="16" t="s">
         <v>24</v>
       </c>
-      <c r="AR7" s="30" t="s">
-        <v>223</v>
+      <c r="AR7" s="29" t="s">
+        <v>214</v>
       </c>
       <c r="AS7" s="18"/>
       <c r="AT7" s="18"/>
@@ -7901,8 +8184,8 @@
       <c r="AX7" s="16" t="s">
         <v>24</v>
       </c>
-      <c r="AY7" s="30" t="s">
-        <v>223</v>
+      <c r="AY7" s="29" t="s">
+        <v>214</v>
       </c>
       <c r="AZ7" s="18"/>
       <c r="BA7" s="18"/>
@@ -7911,8 +8194,8 @@
       <c r="BE7" s="16" t="s">
         <v>24</v>
       </c>
-      <c r="BF7" s="30" t="s">
-        <v>223</v>
+      <c r="BF7" s="29" t="s">
+        <v>214</v>
       </c>
       <c r="BG7" s="18"/>
       <c r="BH7" s="18"/>
@@ -7921,8 +8204,8 @@
       <c r="BL7" s="16" t="s">
         <v>24</v>
       </c>
-      <c r="BM7" s="30" t="s">
-        <v>223</v>
+      <c r="BM7" s="29" t="s">
+        <v>214</v>
       </c>
       <c r="BN7" s="18"/>
       <c r="BO7" s="18"/>
@@ -7931,8 +8214,8 @@
       <c r="BS7" s="16" t="s">
         <v>24</v>
       </c>
-      <c r="BT7" s="30" t="s">
-        <v>223</v>
+      <c r="BT7" s="29" t="s">
+        <v>214</v>
       </c>
       <c r="BU7" s="18"/>
       <c r="BV7" s="18"/>
@@ -7941,8 +8224,8 @@
       <c r="BZ7" s="16" t="s">
         <v>24</v>
       </c>
-      <c r="CA7" s="30" t="s">
-        <v>223</v>
+      <c r="CA7" s="29" t="s">
+        <v>214</v>
       </c>
       <c r="CB7" s="18"/>
       <c r="CC7" s="18"/>
@@ -7951,8 +8234,8 @@
       <c r="CG7" s="16" t="s">
         <v>24</v>
       </c>
-      <c r="CH7" s="30" t="s">
-        <v>223</v>
+      <c r="CH7" s="29" t="s">
+        <v>214</v>
       </c>
       <c r="CI7" s="18"/>
       <c r="CJ7" s="18"/>
@@ -7961,8 +8244,8 @@
       <c r="CN7" s="16" t="s">
         <v>24</v>
       </c>
-      <c r="CO7" s="30" t="s">
-        <v>223</v>
+      <c r="CO7" s="29" t="s">
+        <v>214</v>
       </c>
       <c r="CP7" s="18"/>
       <c r="CQ7" s="18"/>
@@ -7971,8 +8254,8 @@
       <c r="CU7" s="16" t="s">
         <v>24</v>
       </c>
-      <c r="CV7" s="30" t="s">
-        <v>223</v>
+      <c r="CV7" s="29" t="s">
+        <v>214</v>
       </c>
       <c r="CW7" s="18"/>
       <c r="CX7" s="18"/>
@@ -7981,8 +8264,8 @@
       <c r="DB7" s="16" t="s">
         <v>24</v>
       </c>
-      <c r="DC7" s="30" t="s">
-        <v>223</v>
+      <c r="DC7" s="29" t="s">
+        <v>214</v>
       </c>
       <c r="DD7" s="18"/>
       <c r="DE7" s="18"/>
@@ -7991,8 +8274,8 @@
       <c r="DI7" s="16" t="s">
         <v>24</v>
       </c>
-      <c r="DJ7" s="30" t="s">
-        <v>223</v>
+      <c r="DJ7" s="29" t="s">
+        <v>214</v>
       </c>
       <c r="DK7" s="18"/>
       <c r="DL7" s="18"/>
@@ -8001,8 +8284,8 @@
       <c r="DP7" s="16" t="s">
         <v>24</v>
       </c>
-      <c r="DQ7" s="30" t="s">
-        <v>223</v>
+      <c r="DQ7" s="29" t="s">
+        <v>214</v>
       </c>
       <c r="DR7" s="18"/>
       <c r="DS7" s="18"/>
@@ -8011,8 +8294,8 @@
       <c r="DW7" s="16" t="s">
         <v>24</v>
       </c>
-      <c r="DX7" s="30" t="s">
-        <v>223</v>
+      <c r="DX7" s="29" t="s">
+        <v>214</v>
       </c>
       <c r="DY7" s="18"/>
       <c r="DZ7" s="18"/>
@@ -8021,8 +8304,8 @@
       <c r="ED7" s="16" t="s">
         <v>24</v>
       </c>
-      <c r="EE7" s="30" t="s">
-        <v>223</v>
+      <c r="EE7" s="29" t="s">
+        <v>214</v>
       </c>
       <c r="EF7" s="18"/>
       <c r="EG7" s="18"/>
@@ -8031,8 +8314,8 @@
       <c r="EK7" s="16" t="s">
         <v>24</v>
       </c>
-      <c r="EL7" s="30" t="s">
-        <v>223</v>
+      <c r="EL7" s="29" t="s">
+        <v>214</v>
       </c>
       <c r="EM7" s="18"/>
       <c r="EN7" s="18"/>
@@ -8041,8 +8324,8 @@
       <c r="ER7" s="16" t="s">
         <v>24</v>
       </c>
-      <c r="ES7" s="30" t="s">
-        <v>223</v>
+      <c r="ES7" s="29" t="s">
+        <v>214</v>
       </c>
       <c r="ET7" s="18"/>
       <c r="EU7" s="18"/>
@@ -8051,8 +8334,8 @@
       <c r="EY7" s="16" t="s">
         <v>24</v>
       </c>
-      <c r="EZ7" s="30" t="s">
-        <v>223</v>
+      <c r="EZ7" s="29" t="s">
+        <v>214</v>
       </c>
       <c r="FA7" s="18"/>
       <c r="FB7" s="18"/>
@@ -8477,886 +8760,939 @@
     </row>
     <row r="9" spans="1:160" ht="29.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="16" t="s">
-        <v>224</v>
+        <v>215</v>
       </c>
       <c r="B9" s="16" t="s">
-        <v>225</v>
+        <v>216</v>
       </c>
       <c r="C9" s="16" t="s">
-        <v>226</v>
+        <v>217</v>
       </c>
       <c r="D9" s="16" t="s">
-        <v>227</v>
+        <v>218</v>
       </c>
       <c r="E9" s="16"/>
       <c r="F9" s="16"/>
       <c r="H9" s="16" t="s">
-        <v>224</v>
+        <v>215</v>
       </c>
       <c r="I9" s="16" t="s">
-        <v>225</v>
+        <v>216</v>
       </c>
       <c r="J9" s="16" t="s">
-        <v>226</v>
+        <v>217</v>
       </c>
       <c r="K9" s="16" t="s">
-        <v>227</v>
+        <v>218</v>
       </c>
       <c r="L9" s="16"/>
       <c r="M9" s="16"/>
       <c r="O9" s="16" t="s">
-        <v>224</v>
+        <v>215</v>
       </c>
       <c r="P9" s="16" t="s">
-        <v>225</v>
+        <v>216</v>
       </c>
       <c r="Q9" s="16" t="s">
-        <v>226</v>
+        <v>217</v>
       </c>
       <c r="R9" s="16" t="s">
-        <v>227</v>
+        <v>218</v>
       </c>
       <c r="S9" s="16"/>
       <c r="T9" s="16"/>
       <c r="V9" s="16" t="s">
-        <v>224</v>
+        <v>215</v>
       </c>
       <c r="W9" s="16" t="s">
-        <v>225</v>
+        <v>216</v>
       </c>
       <c r="X9" s="16" t="s">
-        <v>226</v>
+        <v>217</v>
       </c>
       <c r="Y9" s="16" t="s">
-        <v>227</v>
+        <v>218</v>
       </c>
       <c r="Z9" s="16"/>
       <c r="AA9" s="16"/>
       <c r="AC9" s="16" t="s">
-        <v>224</v>
+        <v>215</v>
       </c>
       <c r="AD9" s="16" t="s">
-        <v>225</v>
+        <v>216</v>
       </c>
       <c r="AE9" s="16" t="s">
-        <v>226</v>
+        <v>217</v>
       </c>
       <c r="AF9" s="16" t="s">
-        <v>227</v>
+        <v>218</v>
       </c>
       <c r="AG9" s="16"/>
       <c r="AH9" s="16"/>
       <c r="AJ9" s="16" t="s">
-        <v>224</v>
+        <v>215</v>
       </c>
       <c r="AK9" s="16" t="s">
-        <v>225</v>
+        <v>216</v>
       </c>
       <c r="AL9" s="16" t="s">
-        <v>226</v>
+        <v>217</v>
       </c>
       <c r="AM9" s="16" t="s">
-        <v>227</v>
+        <v>218</v>
       </c>
       <c r="AN9" s="16"/>
       <c r="AO9" s="16"/>
       <c r="AQ9" s="16" t="s">
-        <v>224</v>
+        <v>215</v>
       </c>
       <c r="AR9" s="16" t="s">
-        <v>225</v>
+        <v>216</v>
       </c>
       <c r="AS9" s="16" t="s">
-        <v>226</v>
+        <v>217</v>
       </c>
       <c r="AT9" s="16" t="s">
-        <v>227</v>
+        <v>218</v>
       </c>
       <c r="AU9" s="16"/>
       <c r="AV9" s="16"/>
       <c r="AX9" s="16" t="s">
-        <v>224</v>
+        <v>215</v>
       </c>
       <c r="AY9" s="16" t="s">
-        <v>225</v>
+        <v>216</v>
       </c>
       <c r="AZ9" s="16" t="s">
-        <v>226</v>
+        <v>217</v>
       </c>
       <c r="BA9" s="16" t="s">
-        <v>227</v>
+        <v>218</v>
       </c>
       <c r="BB9" s="16"/>
       <c r="BC9" s="16"/>
       <c r="BE9" s="16" t="s">
-        <v>224</v>
+        <v>215</v>
       </c>
       <c r="BF9" s="16" t="s">
-        <v>225</v>
+        <v>216</v>
       </c>
       <c r="BG9" s="16" t="s">
-        <v>226</v>
+        <v>217</v>
       </c>
       <c r="BH9" s="16" t="s">
-        <v>227</v>
+        <v>218</v>
       </c>
       <c r="BI9" s="16"/>
       <c r="BJ9" s="16"/>
       <c r="BL9" s="16" t="s">
-        <v>224</v>
+        <v>215</v>
       </c>
       <c r="BM9" s="16" t="s">
-        <v>225</v>
+        <v>216</v>
       </c>
       <c r="BN9" s="16" t="s">
-        <v>226</v>
+        <v>217</v>
       </c>
       <c r="BO9" s="16" t="s">
-        <v>227</v>
+        <v>218</v>
       </c>
       <c r="BP9" s="16"/>
       <c r="BQ9" s="16"/>
       <c r="BS9" s="16" t="s">
-        <v>224</v>
+        <v>215</v>
       </c>
       <c r="BT9" s="16" t="s">
-        <v>225</v>
+        <v>216</v>
       </c>
       <c r="BU9" s="16" t="s">
-        <v>226</v>
+        <v>217</v>
       </c>
       <c r="BV9" s="16" t="s">
-        <v>227</v>
+        <v>218</v>
       </c>
       <c r="BW9" s="16"/>
       <c r="BX9" s="16"/>
       <c r="BZ9" s="16" t="s">
-        <v>224</v>
+        <v>215</v>
       </c>
       <c r="CA9" s="16" t="s">
-        <v>225</v>
+        <v>216</v>
       </c>
       <c r="CB9" s="16" t="s">
-        <v>226</v>
+        <v>217</v>
       </c>
       <c r="CC9" s="16" t="s">
-        <v>227</v>
+        <v>218</v>
       </c>
       <c r="CD9" s="16"/>
       <c r="CE9" s="16"/>
       <c r="CG9" s="16" t="s">
-        <v>224</v>
+        <v>215</v>
       </c>
       <c r="CH9" s="16" t="s">
-        <v>225</v>
+        <v>216</v>
       </c>
       <c r="CI9" s="16" t="s">
-        <v>226</v>
+        <v>217</v>
       </c>
       <c r="CJ9" s="16" t="s">
-        <v>227</v>
+        <v>218</v>
       </c>
       <c r="CK9" s="16"/>
       <c r="CL9" s="16"/>
       <c r="CN9" s="16" t="s">
-        <v>224</v>
+        <v>215</v>
       </c>
       <c r="CO9" s="16" t="s">
-        <v>225</v>
+        <v>216</v>
       </c>
       <c r="CP9" s="16" t="s">
-        <v>226</v>
+        <v>217</v>
       </c>
       <c r="CQ9" s="16" t="s">
-        <v>227</v>
+        <v>218</v>
       </c>
       <c r="CR9" s="16"/>
       <c r="CS9" s="16"/>
       <c r="CU9" s="16" t="s">
-        <v>224</v>
+        <v>215</v>
       </c>
       <c r="CV9" s="16" t="s">
-        <v>225</v>
+        <v>216</v>
       </c>
       <c r="CW9" s="16" t="s">
-        <v>226</v>
+        <v>217</v>
       </c>
       <c r="CX9" s="16" t="s">
-        <v>227</v>
+        <v>218</v>
       </c>
       <c r="CY9" s="16"/>
       <c r="CZ9" s="16"/>
       <c r="DB9" s="16" t="s">
-        <v>224</v>
+        <v>215</v>
       </c>
       <c r="DC9" s="16" t="s">
-        <v>225</v>
+        <v>216</v>
       </c>
       <c r="DD9" s="16" t="s">
-        <v>226</v>
+        <v>217</v>
       </c>
       <c r="DE9" s="16" t="s">
-        <v>227</v>
+        <v>218</v>
       </c>
       <c r="DF9" s="16"/>
       <c r="DG9" s="16"/>
       <c r="DI9" s="16" t="s">
-        <v>224</v>
+        <v>215</v>
       </c>
       <c r="DJ9" s="16" t="s">
-        <v>225</v>
+        <v>216</v>
       </c>
       <c r="DK9" s="16" t="s">
-        <v>226</v>
+        <v>217</v>
       </c>
       <c r="DL9" s="16" t="s">
-        <v>227</v>
+        <v>218</v>
       </c>
       <c r="DM9" s="16"/>
       <c r="DN9" s="16"/>
       <c r="DP9" s="16" t="s">
-        <v>224</v>
+        <v>215</v>
       </c>
       <c r="DQ9" s="16" t="s">
-        <v>225</v>
+        <v>216</v>
       </c>
       <c r="DR9" s="16" t="s">
-        <v>226</v>
+        <v>217</v>
       </c>
       <c r="DS9" s="16" t="s">
-        <v>227</v>
+        <v>218</v>
       </c>
       <c r="DT9" s="16"/>
       <c r="DU9" s="16"/>
       <c r="DW9" s="16" t="s">
-        <v>224</v>
+        <v>215</v>
       </c>
       <c r="DX9" s="16" t="s">
-        <v>225</v>
+        <v>216</v>
       </c>
       <c r="DY9" s="16" t="s">
-        <v>226</v>
+        <v>217</v>
       </c>
       <c r="DZ9" s="16" t="s">
-        <v>227</v>
+        <v>218</v>
       </c>
       <c r="EA9" s="16"/>
       <c r="EB9" s="16"/>
       <c r="ED9" s="16" t="s">
-        <v>224</v>
+        <v>215</v>
       </c>
       <c r="EE9" s="16" t="s">
-        <v>225</v>
+        <v>216</v>
       </c>
       <c r="EF9" s="16" t="s">
-        <v>226</v>
+        <v>217</v>
       </c>
       <c r="EG9" s="16" t="s">
-        <v>227</v>
+        <v>218</v>
       </c>
       <c r="EH9" s="16"/>
       <c r="EI9" s="16"/>
       <c r="EK9" s="16" t="s">
-        <v>224</v>
+        <v>215</v>
       </c>
       <c r="EL9" s="16" t="s">
-        <v>225</v>
+        <v>216</v>
       </c>
       <c r="EM9" s="16" t="s">
-        <v>226</v>
+        <v>217</v>
       </c>
       <c r="EN9" s="16" t="s">
-        <v>227</v>
+        <v>218</v>
       </c>
       <c r="EO9" s="16"/>
       <c r="EP9" s="16"/>
       <c r="ER9" s="16" t="s">
-        <v>224</v>
+        <v>215</v>
       </c>
       <c r="ES9" s="16" t="s">
-        <v>225</v>
+        <v>216</v>
       </c>
       <c r="ET9" s="16" t="s">
-        <v>226</v>
+        <v>217</v>
       </c>
       <c r="EU9" s="16" t="s">
-        <v>227</v>
+        <v>218</v>
       </c>
       <c r="EV9" s="16"/>
       <c r="EW9" s="16"/>
       <c r="EY9" s="16" t="s">
-        <v>224</v>
+        <v>215</v>
       </c>
       <c r="EZ9" s="16" t="s">
-        <v>225</v>
+        <v>216</v>
       </c>
       <c r="FA9" s="16" t="s">
-        <v>226</v>
+        <v>217</v>
       </c>
       <c r="FB9" s="16" t="s">
-        <v>227</v>
+        <v>218</v>
       </c>
       <c r="FC9" s="16"/>
       <c r="FD9" s="16"/>
     </row>
     <row r="10" spans="1:160" ht="29.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="16" t="s">
-        <v>228</v>
+        <v>219</v>
       </c>
       <c r="B10" s="16" t="s">
-        <v>229</v>
+        <v>220</v>
       </c>
       <c r="C10" s="16"/>
       <c r="D10" s="16" t="s">
-        <v>230</v>
+        <v>221</v>
       </c>
       <c r="E10" s="16"/>
       <c r="F10" s="16"/>
       <c r="H10" s="16" t="s">
-        <v>228</v>
+        <v>219</v>
       </c>
       <c r="I10" s="16" t="s">
-        <v>231</v>
+        <v>222</v>
       </c>
       <c r="J10" s="16"/>
       <c r="K10" s="16" t="s">
-        <v>230</v>
+        <v>221</v>
       </c>
       <c r="L10" s="16"/>
       <c r="M10" s="16"/>
       <c r="O10" s="16" t="s">
-        <v>228</v>
+        <v>219</v>
       </c>
       <c r="P10" s="16" t="s">
-        <v>231</v>
+        <v>222</v>
       </c>
       <c r="Q10" s="16"/>
       <c r="R10" s="16" t="s">
-        <v>230</v>
+        <v>221</v>
       </c>
       <c r="S10" s="16"/>
       <c r="T10" s="16"/>
       <c r="V10" s="16" t="s">
-        <v>228</v>
+        <v>219</v>
       </c>
       <c r="W10" s="16" t="s">
-        <v>231</v>
+        <v>222</v>
       </c>
       <c r="X10" s="16"/>
       <c r="Y10" s="16" t="s">
-        <v>230</v>
+        <v>221</v>
       </c>
       <c r="Z10" s="16"/>
       <c r="AA10" s="16"/>
       <c r="AC10" s="16" t="s">
-        <v>228</v>
+        <v>219</v>
       </c>
       <c r="AD10" s="16" t="s">
-        <v>232</v>
+        <v>223</v>
       </c>
       <c r="AE10" s="16"/>
       <c r="AF10" s="16" t="s">
-        <v>230</v>
+        <v>221</v>
       </c>
       <c r="AG10" s="16"/>
       <c r="AH10" s="16"/>
       <c r="AJ10" s="16" t="s">
-        <v>228</v>
+        <v>219</v>
       </c>
       <c r="AK10" s="16" t="s">
-        <v>232</v>
+        <v>223</v>
       </c>
       <c r="AL10" s="16"/>
       <c r="AM10" s="16" t="s">
-        <v>230</v>
+        <v>221</v>
       </c>
       <c r="AN10" s="16"/>
       <c r="AO10" s="16"/>
       <c r="AQ10" s="16" t="s">
-        <v>228</v>
+        <v>219</v>
       </c>
       <c r="AR10" s="16" t="s">
-        <v>233</v>
+        <v>224</v>
       </c>
       <c r="AS10" s="16"/>
       <c r="AT10" s="16" t="s">
-        <v>230</v>
+        <v>221</v>
       </c>
       <c r="AU10" s="16"/>
       <c r="AV10" s="16"/>
       <c r="AX10" s="16" t="s">
-        <v>228</v>
+        <v>219</v>
       </c>
       <c r="AY10" s="16" t="s">
-        <v>233</v>
+        <v>224</v>
       </c>
       <c r="AZ10" s="16"/>
       <c r="BA10" s="16" t="s">
-        <v>230</v>
+        <v>221</v>
       </c>
       <c r="BB10" s="16"/>
       <c r="BC10" s="16"/>
       <c r="BE10" s="16" t="s">
-        <v>228</v>
+        <v>219</v>
       </c>
       <c r="BF10" s="16" t="s">
-        <v>234</v>
+        <v>225</v>
       </c>
       <c r="BG10" s="16"/>
       <c r="BH10" s="16" t="s">
-        <v>230</v>
+        <v>221</v>
       </c>
       <c r="BI10" s="16"/>
       <c r="BJ10" s="16"/>
       <c r="BL10" s="16" t="s">
-        <v>228</v>
+        <v>219</v>
       </c>
       <c r="BM10" s="16" t="s">
-        <v>234</v>
+        <v>225</v>
       </c>
       <c r="BN10" s="16"/>
       <c r="BO10" s="16" t="s">
-        <v>230</v>
+        <v>221</v>
       </c>
       <c r="BP10" s="16"/>
       <c r="BQ10" s="16"/>
       <c r="BS10" s="16" t="s">
-        <v>228</v>
+        <v>219</v>
       </c>
       <c r="BT10" s="16" t="s">
-        <v>235</v>
+        <v>226</v>
       </c>
       <c r="BU10" s="16"/>
       <c r="BV10" s="16" t="s">
-        <v>230</v>
+        <v>221</v>
       </c>
       <c r="BW10" s="16"/>
       <c r="BX10" s="16"/>
       <c r="BZ10" s="16" t="s">
-        <v>228</v>
+        <v>219</v>
       </c>
       <c r="CA10" s="16" t="s">
-        <v>235</v>
+        <v>226</v>
       </c>
       <c r="CB10" s="16"/>
       <c r="CC10" s="16" t="s">
-        <v>230</v>
+        <v>221</v>
       </c>
       <c r="CD10" s="16"/>
       <c r="CE10" s="16"/>
       <c r="CG10" s="16" t="s">
-        <v>228</v>
+        <v>219</v>
       </c>
       <c r="CH10" s="16" t="s">
-        <v>236</v>
+        <v>227</v>
       </c>
       <c r="CI10" s="16"/>
       <c r="CJ10" s="16" t="s">
-        <v>230</v>
+        <v>221</v>
       </c>
       <c r="CK10" s="16"/>
       <c r="CL10" s="16"/>
       <c r="CN10" s="16" t="s">
+        <v>219</v>
+      </c>
+      <c r="CO10" s="16" t="s">
         <v>228</v>
-      </c>
-      <c r="CO10" s="16" t="s">
-        <v>237</v>
       </c>
       <c r="CP10" s="16"/>
       <c r="CQ10" s="16" t="s">
-        <v>230</v>
+        <v>221</v>
       </c>
       <c r="CR10" s="16"/>
       <c r="CS10" s="16"/>
       <c r="CU10" s="16" t="s">
+        <v>219</v>
+      </c>
+      <c r="CV10" s="16" t="s">
         <v>228</v>
-      </c>
-      <c r="CV10" s="16" t="s">
-        <v>237</v>
       </c>
       <c r="CW10" s="16"/>
       <c r="CX10" s="16" t="s">
-        <v>230</v>
+        <v>221</v>
       </c>
       <c r="CY10" s="16"/>
       <c r="CZ10" s="16"/>
       <c r="DB10" s="16" t="s">
+        <v>219</v>
+      </c>
+      <c r="DC10" s="16" t="s">
         <v>228</v>
-      </c>
-      <c r="DC10" s="16" t="s">
-        <v>237</v>
       </c>
       <c r="DD10" s="16"/>
       <c r="DE10" s="16" t="s">
-        <v>230</v>
+        <v>221</v>
       </c>
       <c r="DF10" s="16"/>
       <c r="DG10" s="16"/>
       <c r="DI10" s="16" t="s">
-        <v>228</v>
+        <v>219</v>
       </c>
       <c r="DJ10" s="16" t="s">
-        <v>238</v>
+        <v>229</v>
       </c>
       <c r="DK10" s="16"/>
       <c r="DL10" s="16" t="s">
-        <v>230</v>
+        <v>221</v>
       </c>
       <c r="DM10" s="16"/>
       <c r="DN10" s="16"/>
       <c r="DP10" s="16" t="s">
-        <v>228</v>
+        <v>219</v>
       </c>
       <c r="DQ10" s="16" t="s">
-        <v>238</v>
+        <v>229</v>
       </c>
       <c r="DR10" s="16"/>
       <c r="DS10" s="16" t="s">
-        <v>230</v>
+        <v>221</v>
       </c>
       <c r="DT10" s="16"/>
       <c r="DU10" s="16"/>
       <c r="DW10" s="16" t="s">
-        <v>228</v>
+        <v>219</v>
       </c>
       <c r="DX10" s="16" t="s">
-        <v>239</v>
+        <v>230</v>
       </c>
       <c r="DY10" s="16"/>
       <c r="DZ10" s="16" t="s">
-        <v>230</v>
+        <v>221</v>
       </c>
       <c r="EA10" s="16"/>
       <c r="EB10" s="16"/>
       <c r="ED10" s="16" t="s">
-        <v>228</v>
+        <v>219</v>
       </c>
       <c r="EE10" s="16" t="s">
-        <v>240</v>
+        <v>231</v>
       </c>
       <c r="EF10" s="16"/>
       <c r="EG10" s="16" t="s">
-        <v>230</v>
+        <v>221</v>
       </c>
       <c r="EH10" s="16"/>
       <c r="EI10" s="16"/>
       <c r="EK10" s="16" t="s">
-        <v>228</v>
+        <v>219</v>
       </c>
       <c r="EL10" s="16" t="s">
-        <v>240</v>
+        <v>231</v>
       </c>
       <c r="EM10" s="16"/>
       <c r="EN10" s="16" t="s">
-        <v>230</v>
+        <v>221</v>
       </c>
       <c r="EO10" s="16"/>
       <c r="EP10" s="16"/>
       <c r="ER10" s="16" t="s">
-        <v>228</v>
+        <v>219</v>
       </c>
       <c r="ES10" s="16" t="s">
-        <v>241</v>
+        <v>232</v>
       </c>
       <c r="ET10" s="16"/>
       <c r="EU10" s="16" t="s">
-        <v>230</v>
+        <v>221</v>
       </c>
       <c r="EV10" s="16"/>
       <c r="EW10" s="16"/>
       <c r="EY10" s="16" t="s">
-        <v>228</v>
+        <v>219</v>
       </c>
       <c r="EZ10" s="16" t="s">
-        <v>242</v>
+        <v>233</v>
       </c>
       <c r="FA10" s="16"/>
       <c r="FB10" s="16" t="s">
-        <v>230</v>
+        <v>221</v>
       </c>
       <c r="FC10" s="16"/>
       <c r="FD10" s="16"/>
     </row>
     <row r="11" spans="1:160" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="16" t="s">
-        <v>243</v>
+        <v>234</v>
       </c>
       <c r="B11" s="16" t="s">
-        <v>244</v>
+        <v>235</v>
       </c>
       <c r="C11" s="16"/>
       <c r="D11" s="16" t="s">
-        <v>245</v>
+        <v>236</v>
       </c>
       <c r="E11" s="16"/>
       <c r="F11" s="16"/>
       <c r="H11" s="16" t="s">
-        <v>243</v>
+        <v>234</v>
       </c>
       <c r="I11" s="16" t="s">
-        <v>244</v>
+        <v>235</v>
       </c>
       <c r="J11" s="16"/>
       <c r="K11" s="16" t="s">
-        <v>245</v>
+        <v>236</v>
       </c>
       <c r="L11" s="16"/>
       <c r="M11" s="16"/>
       <c r="O11" s="16" t="s">
-        <v>243</v>
+        <v>234</v>
       </c>
       <c r="P11" s="16" t="s">
-        <v>244</v>
+        <v>235</v>
       </c>
       <c r="Q11" s="16"/>
       <c r="R11" s="16" t="s">
-        <v>245</v>
+        <v>236</v>
       </c>
       <c r="S11" s="16"/>
       <c r="T11" s="16"/>
       <c r="V11" s="16" t="s">
-        <v>243</v>
+        <v>234</v>
       </c>
       <c r="W11" s="16" t="s">
-        <v>244</v>
+        <v>235</v>
       </c>
       <c r="X11" s="16"/>
       <c r="Y11" s="16" t="s">
-        <v>245</v>
+        <v>236</v>
       </c>
       <c r="Z11" s="16"/>
       <c r="AA11" s="16"/>
       <c r="AC11" s="16" t="s">
-        <v>243</v>
+        <v>234</v>
       </c>
       <c r="AD11" s="16" t="s">
-        <v>244</v>
+        <v>235</v>
       </c>
       <c r="AE11" s="16"/>
       <c r="AF11" s="16" t="s">
-        <v>245</v>
+        <v>236</v>
       </c>
       <c r="AG11" s="16"/>
       <c r="AH11" s="16"/>
       <c r="AJ11" s="16" t="s">
-        <v>243</v>
+        <v>234</v>
       </c>
       <c r="AK11" s="16" t="s">
-        <v>244</v>
+        <v>235</v>
       </c>
       <c r="AL11" s="16"/>
       <c r="AM11" s="16" t="s">
-        <v>245</v>
+        <v>236</v>
       </c>
       <c r="AN11" s="16"/>
       <c r="AO11" s="16"/>
       <c r="AQ11" s="16" t="s">
-        <v>243</v>
+        <v>234</v>
       </c>
       <c r="AR11" s="16" t="s">
-        <v>244</v>
+        <v>235</v>
       </c>
       <c r="AS11" s="16"/>
       <c r="AT11" s="16" t="s">
-        <v>245</v>
+        <v>236</v>
       </c>
       <c r="AU11" s="16"/>
       <c r="AV11" s="16"/>
       <c r="AX11" s="16" t="s">
-        <v>243</v>
+        <v>234</v>
       </c>
       <c r="AY11" s="16" t="s">
-        <v>244</v>
+        <v>235</v>
       </c>
       <c r="AZ11" s="16"/>
       <c r="BA11" s="16" t="s">
-        <v>245</v>
+        <v>236</v>
       </c>
       <c r="BB11" s="16"/>
       <c r="BC11" s="16"/>
       <c r="BE11" s="16" t="s">
-        <v>243</v>
+        <v>234</v>
       </c>
       <c r="BF11" s="16" t="s">
-        <v>244</v>
+        <v>235</v>
       </c>
       <c r="BG11" s="16"/>
       <c r="BH11" s="16" t="s">
-        <v>245</v>
+        <v>236</v>
       </c>
       <c r="BI11" s="16"/>
       <c r="BJ11" s="16"/>
       <c r="BL11" s="16" t="s">
-        <v>243</v>
+        <v>234</v>
       </c>
       <c r="BM11" s="16" t="s">
-        <v>244</v>
+        <v>235</v>
       </c>
       <c r="BN11" s="16"/>
       <c r="BO11" s="16" t="s">
-        <v>245</v>
+        <v>236</v>
       </c>
       <c r="BP11" s="16"/>
       <c r="BQ11" s="16"/>
       <c r="BS11" s="16" t="s">
-        <v>243</v>
+        <v>234</v>
       </c>
       <c r="BT11" s="16" t="s">
-        <v>244</v>
+        <v>235</v>
       </c>
       <c r="BU11" s="16"/>
       <c r="BV11" s="16" t="s">
-        <v>245</v>
+        <v>236</v>
       </c>
       <c r="BW11" s="16"/>
       <c r="BX11" s="16"/>
       <c r="BZ11" s="16" t="s">
-        <v>243</v>
+        <v>234</v>
       </c>
       <c r="CA11" s="16" t="s">
-        <v>244</v>
+        <v>235</v>
       </c>
       <c r="CB11" s="16"/>
       <c r="CC11" s="16" t="s">
-        <v>245</v>
+        <v>236</v>
       </c>
       <c r="CD11" s="16"/>
       <c r="CE11" s="16"/>
       <c r="CG11" s="16" t="s">
-        <v>243</v>
+        <v>234</v>
       </c>
       <c r="CH11" s="16" t="s">
-        <v>244</v>
+        <v>235</v>
       </c>
       <c r="CI11" s="16"/>
       <c r="CJ11" s="16" t="s">
-        <v>245</v>
+        <v>236</v>
       </c>
       <c r="CK11" s="16"/>
       <c r="CL11" s="16"/>
       <c r="CN11" s="16" t="s">
-        <v>243</v>
+        <v>234</v>
       </c>
       <c r="CO11" s="16" t="s">
-        <v>244</v>
+        <v>235</v>
       </c>
       <c r="CP11" s="16"/>
       <c r="CQ11" s="16" t="s">
-        <v>245</v>
+        <v>236</v>
       </c>
       <c r="CR11" s="16"/>
       <c r="CS11" s="16"/>
       <c r="CU11" s="16" t="s">
-        <v>243</v>
+        <v>234</v>
       </c>
       <c r="CV11" s="16" t="s">
-        <v>244</v>
+        <v>235</v>
       </c>
       <c r="CW11" s="16"/>
       <c r="CX11" s="16" t="s">
-        <v>245</v>
+        <v>236</v>
       </c>
       <c r="CY11" s="16"/>
       <c r="CZ11" s="16"/>
       <c r="DB11" s="16" t="s">
-        <v>243</v>
+        <v>234</v>
       </c>
       <c r="DC11" s="16" t="s">
-        <v>244</v>
+        <v>235</v>
       </c>
       <c r="DD11" s="16"/>
       <c r="DE11" s="16" t="s">
-        <v>245</v>
+        <v>236</v>
       </c>
       <c r="DF11" s="16"/>
       <c r="DG11" s="16"/>
       <c r="DI11" s="16" t="s">
-        <v>243</v>
+        <v>234</v>
       </c>
       <c r="DJ11" s="16" t="s">
-        <v>244</v>
+        <v>235</v>
       </c>
       <c r="DK11" s="16"/>
       <c r="DL11" s="16" t="s">
-        <v>245</v>
+        <v>236</v>
       </c>
       <c r="DM11" s="16"/>
       <c r="DN11" s="16"/>
       <c r="DP11" s="16" t="s">
-        <v>243</v>
+        <v>234</v>
       </c>
       <c r="DQ11" s="16" t="s">
-        <v>244</v>
+        <v>235</v>
       </c>
       <c r="DR11" s="16"/>
       <c r="DS11" s="16" t="s">
-        <v>245</v>
+        <v>236</v>
       </c>
       <c r="DT11" s="16"/>
       <c r="DU11" s="16"/>
       <c r="DW11" s="16" t="s">
-        <v>243</v>
+        <v>234</v>
       </c>
       <c r="DX11" s="16" t="s">
-        <v>244</v>
+        <v>235</v>
       </c>
       <c r="DY11" s="16"/>
       <c r="DZ11" s="16" t="s">
-        <v>245</v>
+        <v>236</v>
       </c>
       <c r="EA11" s="16"/>
       <c r="EB11" s="16"/>
       <c r="ED11" s="16" t="s">
-        <v>243</v>
+        <v>234</v>
       </c>
       <c r="EE11" s="16" t="s">
-        <v>244</v>
+        <v>235</v>
       </c>
       <c r="EF11" s="16"/>
       <c r="EG11" s="16" t="s">
-        <v>246</v>
+        <v>237</v>
       </c>
       <c r="EH11" s="16"/>
       <c r="EI11" s="16"/>
       <c r="EK11" s="16" t="s">
-        <v>243</v>
+        <v>234</v>
       </c>
       <c r="EL11" s="16" t="s">
-        <v>244</v>
+        <v>235</v>
       </c>
       <c r="EM11" s="16"/>
       <c r="EN11" s="16" t="s">
-        <v>245</v>
+        <v>236</v>
       </c>
       <c r="EO11" s="16"/>
       <c r="EP11" s="16"/>
       <c r="ER11" s="16" t="s">
-        <v>243</v>
+        <v>234</v>
       </c>
       <c r="ES11" s="16" t="s">
-        <v>244</v>
+        <v>235</v>
       </c>
       <c r="ET11" s="16"/>
       <c r="EU11" s="16" t="s">
-        <v>245</v>
+        <v>236</v>
       </c>
       <c r="EV11" s="16"/>
       <c r="EW11" s="16"/>
       <c r="EY11" s="16" t="s">
-        <v>243</v>
+        <v>234</v>
       </c>
       <c r="EZ11" s="16" t="s">
-        <v>244</v>
+        <v>235</v>
       </c>
       <c r="FA11" s="16"/>
       <c r="FB11" s="16" t="s">
-        <v>245</v>
+        <v>236</v>
       </c>
       <c r="FC11" s="16"/>
       <c r="FD11" s="16"/>
     </row>
   </sheetData>
   <mergeCells count="69">
+    <mergeCell ref="EY1:FD1"/>
+    <mergeCell ref="V1:AA1"/>
+    <mergeCell ref="DX6:EB6"/>
+    <mergeCell ref="B7:F7"/>
+    <mergeCell ref="BE1:BJ1"/>
+    <mergeCell ref="AR7:AV7"/>
+    <mergeCell ref="O1:T1"/>
+    <mergeCell ref="EZ7:FD7"/>
+    <mergeCell ref="I6:M6"/>
+    <mergeCell ref="AK7:AO7"/>
+    <mergeCell ref="W6:AA6"/>
+    <mergeCell ref="CV7:CZ7"/>
+    <mergeCell ref="BS1:BX1"/>
+    <mergeCell ref="DI1:DN1"/>
+    <mergeCell ref="BF7:BJ7"/>
+    <mergeCell ref="BM6:BQ6"/>
+    <mergeCell ref="CH6:CL6"/>
+    <mergeCell ref="BF6:BJ6"/>
+    <mergeCell ref="DW1:EB1"/>
+    <mergeCell ref="DQ6:DU6"/>
+    <mergeCell ref="DJ7:DN7"/>
+    <mergeCell ref="ES7:EW7"/>
+    <mergeCell ref="AC1:AH1"/>
+    <mergeCell ref="EE6:EI6"/>
+    <mergeCell ref="I7:M7"/>
+    <mergeCell ref="BT7:BX7"/>
+    <mergeCell ref="P6:T6"/>
+    <mergeCell ref="CG1:CL1"/>
+    <mergeCell ref="BM7:BQ7"/>
+    <mergeCell ref="CA6:CE6"/>
+    <mergeCell ref="AQ1:AV1"/>
+    <mergeCell ref="AD6:AH6"/>
+    <mergeCell ref="DC7:DG7"/>
+    <mergeCell ref="BZ1:CE1"/>
+    <mergeCell ref="CO6:CS6"/>
+    <mergeCell ref="DP1:DU1"/>
+    <mergeCell ref="DQ7:DU7"/>
+    <mergeCell ref="EZ6:FD6"/>
+    <mergeCell ref="EK1:EP1"/>
+    <mergeCell ref="H1:M1"/>
+    <mergeCell ref="B6:F6"/>
+    <mergeCell ref="AX1:BC1"/>
+    <mergeCell ref="AK6:AO6"/>
+    <mergeCell ref="DJ6:DN6"/>
+    <mergeCell ref="ES6:EW6"/>
+    <mergeCell ref="ED1:EI1"/>
+    <mergeCell ref="AJ1:AO1"/>
+    <mergeCell ref="AR6:AV6"/>
+    <mergeCell ref="CN1:CS1"/>
+    <mergeCell ref="DC6:DG6"/>
+    <mergeCell ref="DB1:DG1"/>
+    <mergeCell ref="CV6:CZ6"/>
+    <mergeCell ref="ER1:EW1"/>
     <mergeCell ref="EL7:EP7"/>
     <mergeCell ref="AD7:AH7"/>
     <mergeCell ref="A1:F1"/>
@@ -9373,59 +9709,6 @@
     <mergeCell ref="CO7:CS7"/>
     <mergeCell ref="EL6:EP6"/>
     <mergeCell ref="DX7:EB7"/>
-    <mergeCell ref="EZ6:FD6"/>
-    <mergeCell ref="EK1:EP1"/>
-    <mergeCell ref="H1:M1"/>
-    <mergeCell ref="B6:F6"/>
-    <mergeCell ref="AX1:BC1"/>
-    <mergeCell ref="AK6:AO6"/>
-    <mergeCell ref="DJ6:DN6"/>
-    <mergeCell ref="ES6:EW6"/>
-    <mergeCell ref="ED1:EI1"/>
-    <mergeCell ref="AJ1:AO1"/>
-    <mergeCell ref="AR6:AV6"/>
-    <mergeCell ref="CN1:CS1"/>
-    <mergeCell ref="DC6:DG6"/>
-    <mergeCell ref="DB1:DG1"/>
-    <mergeCell ref="CV6:CZ6"/>
-    <mergeCell ref="ER1:EW1"/>
-    <mergeCell ref="ES7:EW7"/>
-    <mergeCell ref="AC1:AH1"/>
-    <mergeCell ref="EE6:EI6"/>
-    <mergeCell ref="I7:M7"/>
-    <mergeCell ref="BT7:BX7"/>
-    <mergeCell ref="P6:T6"/>
-    <mergeCell ref="CG1:CL1"/>
-    <mergeCell ref="BM7:BQ7"/>
-    <mergeCell ref="CA6:CE6"/>
-    <mergeCell ref="AQ1:AV1"/>
-    <mergeCell ref="AD6:AH6"/>
-    <mergeCell ref="DC7:DG7"/>
-    <mergeCell ref="BZ1:CE1"/>
-    <mergeCell ref="CO6:CS6"/>
-    <mergeCell ref="DP1:DU1"/>
-    <mergeCell ref="DQ7:DU7"/>
-    <mergeCell ref="CH6:CL6"/>
-    <mergeCell ref="BF6:BJ6"/>
-    <mergeCell ref="DW1:EB1"/>
-    <mergeCell ref="DQ6:DU6"/>
-    <mergeCell ref="DJ7:DN7"/>
-    <mergeCell ref="EY1:FD1"/>
-    <mergeCell ref="V1:AA1"/>
-    <mergeCell ref="DX6:EB6"/>
-    <mergeCell ref="B7:F7"/>
-    <mergeCell ref="BE1:BJ1"/>
-    <mergeCell ref="AR7:AV7"/>
-    <mergeCell ref="O1:T1"/>
-    <mergeCell ref="EZ7:FD7"/>
-    <mergeCell ref="I6:M6"/>
-    <mergeCell ref="AK7:AO7"/>
-    <mergeCell ref="W6:AA6"/>
-    <mergeCell ref="CV7:CZ7"/>
-    <mergeCell ref="BS1:BX1"/>
-    <mergeCell ref="DI1:DN1"/>
-    <mergeCell ref="BF7:BJ7"/>
-    <mergeCell ref="BM6:BQ6"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -9462,184 +9745,184 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:160" x14ac:dyDescent="0.25">
-      <c r="A1" s="29" t="s">
-        <v>247</v>
+      <c r="A1" s="30" t="s">
+        <v>238</v>
       </c>
       <c r="B1" s="18"/>
       <c r="C1" s="18"/>
       <c r="D1" s="18"/>
       <c r="E1" s="18"/>
       <c r="F1" s="18"/>
-      <c r="H1" s="29" t="s">
-        <v>248</v>
+      <c r="H1" s="30" t="s">
+        <v>239</v>
       </c>
       <c r="I1" s="18"/>
       <c r="J1" s="18"/>
       <c r="K1" s="18"/>
       <c r="L1" s="18"/>
       <c r="M1" s="18"/>
-      <c r="O1" s="29" t="s">
-        <v>249</v>
+      <c r="O1" s="30" t="s">
+        <v>240</v>
       </c>
       <c r="P1" s="18"/>
       <c r="Q1" s="18"/>
       <c r="R1" s="18"/>
       <c r="S1" s="18"/>
       <c r="T1" s="18"/>
-      <c r="V1" s="29" t="s">
-        <v>250</v>
+      <c r="V1" s="30" t="s">
+        <v>241</v>
       </c>
       <c r="W1" s="18"/>
       <c r="X1" s="18"/>
       <c r="Y1" s="18"/>
       <c r="Z1" s="18"/>
       <c r="AA1" s="18"/>
-      <c r="AC1" s="29" t="s">
-        <v>251</v>
+      <c r="AC1" s="30" t="s">
+        <v>242</v>
       </c>
       <c r="AD1" s="18"/>
       <c r="AE1" s="18"/>
       <c r="AF1" s="18"/>
       <c r="AG1" s="18"/>
       <c r="AH1" s="18"/>
-      <c r="AJ1" s="29" t="s">
-        <v>252</v>
+      <c r="AJ1" s="30" t="s">
+        <v>243</v>
       </c>
       <c r="AK1" s="18"/>
       <c r="AL1" s="18"/>
       <c r="AM1" s="18"/>
       <c r="AN1" s="18"/>
       <c r="AO1" s="18"/>
-      <c r="AQ1" s="29" t="s">
-        <v>253</v>
+      <c r="AQ1" s="30" t="s">
+        <v>244</v>
       </c>
       <c r="AR1" s="18"/>
       <c r="AS1" s="18"/>
       <c r="AT1" s="18"/>
       <c r="AU1" s="18"/>
       <c r="AV1" s="18"/>
-      <c r="AX1" s="29" t="s">
-        <v>254</v>
+      <c r="AX1" s="30" t="s">
+        <v>245</v>
       </c>
       <c r="AY1" s="18"/>
       <c r="AZ1" s="18"/>
       <c r="BA1" s="18"/>
       <c r="BB1" s="18"/>
       <c r="BC1" s="18"/>
-      <c r="BE1" s="29" t="s">
-        <v>255</v>
+      <c r="BE1" s="30" t="s">
+        <v>246</v>
       </c>
       <c r="BF1" s="18"/>
       <c r="BG1" s="18"/>
       <c r="BH1" s="18"/>
       <c r="BI1" s="18"/>
       <c r="BJ1" s="18"/>
-      <c r="BL1" s="29" t="s">
-        <v>256</v>
+      <c r="BL1" s="30" t="s">
+        <v>247</v>
       </c>
       <c r="BM1" s="18"/>
       <c r="BN1" s="18"/>
       <c r="BO1" s="18"/>
       <c r="BP1" s="18"/>
       <c r="BQ1" s="18"/>
-      <c r="BS1" s="29" t="s">
-        <v>257</v>
+      <c r="BS1" s="30" t="s">
+        <v>248</v>
       </c>
       <c r="BT1" s="18"/>
       <c r="BU1" s="18"/>
       <c r="BV1" s="18"/>
       <c r="BW1" s="18"/>
       <c r="BX1" s="18"/>
-      <c r="BZ1" s="29" t="s">
-        <v>258</v>
+      <c r="BZ1" s="30" t="s">
+        <v>249</v>
       </c>
       <c r="CA1" s="18"/>
       <c r="CB1" s="18"/>
       <c r="CC1" s="18"/>
       <c r="CD1" s="18"/>
       <c r="CE1" s="18"/>
-      <c r="CG1" s="29" t="s">
-        <v>259</v>
+      <c r="CG1" s="30" t="s">
+        <v>250</v>
       </c>
       <c r="CH1" s="18"/>
       <c r="CI1" s="18"/>
       <c r="CJ1" s="18"/>
       <c r="CK1" s="18"/>
       <c r="CL1" s="18"/>
-      <c r="CN1" s="29" t="s">
-        <v>260</v>
+      <c r="CN1" s="30" t="s">
+        <v>251</v>
       </c>
       <c r="CO1" s="18"/>
       <c r="CP1" s="18"/>
       <c r="CQ1" s="18"/>
       <c r="CR1" s="18"/>
       <c r="CS1" s="18"/>
-      <c r="CU1" s="29" t="s">
-        <v>261</v>
+      <c r="CU1" s="30" t="s">
+        <v>252</v>
       </c>
       <c r="CV1" s="18"/>
       <c r="CW1" s="18"/>
       <c r="CX1" s="18"/>
       <c r="CY1" s="18"/>
       <c r="CZ1" s="18"/>
-      <c r="DB1" s="29" t="s">
-        <v>262</v>
+      <c r="DB1" s="30" t="s">
+        <v>253</v>
       </c>
       <c r="DC1" s="18"/>
       <c r="DD1" s="18"/>
       <c r="DE1" s="18"/>
       <c r="DF1" s="18"/>
       <c r="DG1" s="18"/>
-      <c r="DI1" s="29" t="s">
-        <v>263</v>
+      <c r="DI1" s="30" t="s">
+        <v>254</v>
       </c>
       <c r="DJ1" s="18"/>
       <c r="DK1" s="18"/>
       <c r="DL1" s="18"/>
       <c r="DM1" s="18"/>
       <c r="DN1" s="18"/>
-      <c r="DP1" s="29" t="s">
-        <v>264</v>
+      <c r="DP1" s="30" t="s">
+        <v>255</v>
       </c>
       <c r="DQ1" s="18"/>
       <c r="DR1" s="18"/>
       <c r="DS1" s="18"/>
       <c r="DT1" s="18"/>
       <c r="DU1" s="18"/>
-      <c r="DW1" s="29" t="s">
-        <v>265</v>
+      <c r="DW1" s="30" t="s">
+        <v>256</v>
       </c>
       <c r="DX1" s="18"/>
       <c r="DY1" s="18"/>
       <c r="DZ1" s="18"/>
       <c r="EA1" s="18"/>
       <c r="EB1" s="18"/>
-      <c r="ED1" s="29" t="s">
-        <v>266</v>
+      <c r="ED1" s="30" t="s">
+        <v>257</v>
       </c>
       <c r="EE1" s="18"/>
       <c r="EF1" s="18"/>
       <c r="EG1" s="18"/>
       <c r="EH1" s="18"/>
       <c r="EI1" s="18"/>
-      <c r="EK1" s="29" t="s">
-        <v>267</v>
+      <c r="EK1" s="30" t="s">
+        <v>258</v>
       </c>
       <c r="EL1" s="18"/>
       <c r="EM1" s="18"/>
       <c r="EN1" s="18"/>
       <c r="EO1" s="18"/>
       <c r="EP1" s="18"/>
-      <c r="ER1" s="29" t="s">
-        <v>268</v>
+      <c r="ER1" s="30" t="s">
+        <v>259</v>
       </c>
       <c r="ES1" s="18"/>
       <c r="ET1" s="18"/>
       <c r="EU1" s="18"/>
       <c r="EV1" s="18"/>
       <c r="EW1" s="18"/>
-      <c r="EY1" s="29" t="s">
-        <v>269</v>
+      <c r="EY1" s="30" t="s">
+        <v>260</v>
       </c>
       <c r="EZ1" s="18"/>
       <c r="FA1" s="18"/>
@@ -10234,8 +10517,8 @@
       <c r="A6" s="16" t="s">
         <v>63</v>
       </c>
-      <c r="B6" s="30" t="s">
-        <v>270</v>
+      <c r="B6" s="29" t="s">
+        <v>261</v>
       </c>
       <c r="C6" s="18"/>
       <c r="D6" s="18"/>
@@ -10244,8 +10527,8 @@
       <c r="H6" s="16" t="s">
         <v>63</v>
       </c>
-      <c r="I6" s="30" t="s">
-        <v>271</v>
+      <c r="I6" s="29" t="s">
+        <v>262</v>
       </c>
       <c r="J6" s="18"/>
       <c r="K6" s="18"/>
@@ -10254,8 +10537,8 @@
       <c r="O6" s="16" t="s">
         <v>63</v>
       </c>
-      <c r="P6" s="30" t="s">
-        <v>272</v>
+      <c r="P6" s="29" t="s">
+        <v>263</v>
       </c>
       <c r="Q6" s="18"/>
       <c r="R6" s="18"/>
@@ -10264,8 +10547,8 @@
       <c r="V6" s="16" t="s">
         <v>63</v>
       </c>
-      <c r="W6" s="30" t="s">
-        <v>273</v>
+      <c r="W6" s="29" t="s">
+        <v>264</v>
       </c>
       <c r="X6" s="18"/>
       <c r="Y6" s="18"/>
@@ -10274,8 +10557,8 @@
       <c r="AC6" s="16" t="s">
         <v>63</v>
       </c>
-      <c r="AD6" s="30" t="s">
-        <v>274</v>
+      <c r="AD6" s="29" t="s">
+        <v>265</v>
       </c>
       <c r="AE6" s="18"/>
       <c r="AF6" s="18"/>
@@ -10284,8 +10567,8 @@
       <c r="AJ6" s="16" t="s">
         <v>63</v>
       </c>
-      <c r="AK6" s="30" t="s">
-        <v>275</v>
+      <c r="AK6" s="29" t="s">
+        <v>266</v>
       </c>
       <c r="AL6" s="18"/>
       <c r="AM6" s="18"/>
@@ -10294,8 +10577,8 @@
       <c r="AQ6" s="16" t="s">
         <v>63</v>
       </c>
-      <c r="AR6" s="30" t="s">
-        <v>276</v>
+      <c r="AR6" s="29" t="s">
+        <v>267</v>
       </c>
       <c r="AS6" s="18"/>
       <c r="AT6" s="18"/>
@@ -10304,8 +10587,8 @@
       <c r="AX6" s="16" t="s">
         <v>63</v>
       </c>
-      <c r="AY6" s="30" t="s">
-        <v>277</v>
+      <c r="AY6" s="29" t="s">
+        <v>268</v>
       </c>
       <c r="AZ6" s="18"/>
       <c r="BA6" s="18"/>
@@ -10314,8 +10597,8 @@
       <c r="BE6" s="16" t="s">
         <v>63</v>
       </c>
-      <c r="BF6" s="30" t="s">
-        <v>278</v>
+      <c r="BF6" s="29" t="s">
+        <v>269</v>
       </c>
       <c r="BG6" s="18"/>
       <c r="BH6" s="18"/>
@@ -10324,8 +10607,8 @@
       <c r="BL6" s="16" t="s">
         <v>63</v>
       </c>
-      <c r="BM6" s="30" t="s">
-        <v>279</v>
+      <c r="BM6" s="29" t="s">
+        <v>270</v>
       </c>
       <c r="BN6" s="18"/>
       <c r="BO6" s="18"/>
@@ -10334,8 +10617,8 @@
       <c r="BS6" s="16" t="s">
         <v>63</v>
       </c>
-      <c r="BT6" s="30" t="s">
-        <v>280</v>
+      <c r="BT6" s="29" t="s">
+        <v>271</v>
       </c>
       <c r="BU6" s="18"/>
       <c r="BV6" s="18"/>
@@ -10344,8 +10627,8 @@
       <c r="BZ6" s="16" t="s">
         <v>63</v>
       </c>
-      <c r="CA6" s="30" t="s">
-        <v>281</v>
+      <c r="CA6" s="29" t="s">
+        <v>272</v>
       </c>
       <c r="CB6" s="18"/>
       <c r="CC6" s="18"/>
@@ -10354,8 +10637,8 @@
       <c r="CG6" s="16" t="s">
         <v>63</v>
       </c>
-      <c r="CH6" s="30" t="s">
-        <v>282</v>
+      <c r="CH6" s="29" t="s">
+        <v>273</v>
       </c>
       <c r="CI6" s="18"/>
       <c r="CJ6" s="18"/>
@@ -10364,8 +10647,8 @@
       <c r="CN6" s="16" t="s">
         <v>63</v>
       </c>
-      <c r="CO6" s="30" t="s">
-        <v>283</v>
+      <c r="CO6" s="29" t="s">
+        <v>274</v>
       </c>
       <c r="CP6" s="18"/>
       <c r="CQ6" s="18"/>
@@ -10374,8 +10657,8 @@
       <c r="CU6" s="16" t="s">
         <v>63</v>
       </c>
-      <c r="CV6" s="30" t="s">
-        <v>284</v>
+      <c r="CV6" s="29" t="s">
+        <v>275</v>
       </c>
       <c r="CW6" s="18"/>
       <c r="CX6" s="18"/>
@@ -10384,8 +10667,8 @@
       <c r="DB6" s="16" t="s">
         <v>63</v>
       </c>
-      <c r="DC6" s="30" t="s">
-        <v>285</v>
+      <c r="DC6" s="29" t="s">
+        <v>276</v>
       </c>
       <c r="DD6" s="18"/>
       <c r="DE6" s="18"/>
@@ -10394,8 +10677,8 @@
       <c r="DI6" s="16" t="s">
         <v>63</v>
       </c>
-      <c r="DJ6" s="30" t="s">
-        <v>286</v>
+      <c r="DJ6" s="29" t="s">
+        <v>277</v>
       </c>
       <c r="DK6" s="18"/>
       <c r="DL6" s="18"/>
@@ -10404,8 +10687,8 @@
       <c r="DP6" s="16" t="s">
         <v>63</v>
       </c>
-      <c r="DQ6" s="30" t="s">
-        <v>287</v>
+      <c r="DQ6" s="29" t="s">
+        <v>278</v>
       </c>
       <c r="DR6" s="18"/>
       <c r="DS6" s="18"/>
@@ -10414,8 +10697,8 @@
       <c r="DW6" s="16" t="s">
         <v>63</v>
       </c>
-      <c r="DX6" s="30" t="s">
-        <v>288</v>
+      <c r="DX6" s="29" t="s">
+        <v>279</v>
       </c>
       <c r="DY6" s="18"/>
       <c r="DZ6" s="18"/>
@@ -10424,8 +10707,8 @@
       <c r="ED6" s="16" t="s">
         <v>63</v>
       </c>
-      <c r="EE6" s="30" t="s">
-        <v>289</v>
+      <c r="EE6" s="29" t="s">
+        <v>280</v>
       </c>
       <c r="EF6" s="18"/>
       <c r="EG6" s="18"/>
@@ -10434,8 +10717,8 @@
       <c r="EK6" s="16" t="s">
         <v>63</v>
       </c>
-      <c r="EL6" s="30" t="s">
-        <v>290</v>
+      <c r="EL6" s="29" t="s">
+        <v>281</v>
       </c>
       <c r="EM6" s="18"/>
       <c r="EN6" s="18"/>
@@ -10444,8 +10727,8 @@
       <c r="ER6" s="16" t="s">
         <v>63</v>
       </c>
-      <c r="ES6" s="30" t="s">
-        <v>291</v>
+      <c r="ES6" s="29" t="s">
+        <v>282</v>
       </c>
       <c r="ET6" s="18"/>
       <c r="EU6" s="18"/>
@@ -10454,8 +10737,8 @@
       <c r="EY6" s="16" t="s">
         <v>63</v>
       </c>
-      <c r="EZ6" s="30" t="s">
-        <v>292</v>
+      <c r="EZ6" s="29" t="s">
+        <v>283</v>
       </c>
       <c r="FA6" s="18"/>
       <c r="FB6" s="18"/>
@@ -10466,8 +10749,8 @@
       <c r="A7" s="16" t="s">
         <v>24</v>
       </c>
-      <c r="B7" s="30" t="s">
-        <v>223</v>
+      <c r="B7" s="29" t="s">
+        <v>214</v>
       </c>
       <c r="C7" s="18"/>
       <c r="D7" s="18"/>
@@ -10476,8 +10759,8 @@
       <c r="H7" s="16" t="s">
         <v>24</v>
       </c>
-      <c r="I7" s="30" t="s">
-        <v>223</v>
+      <c r="I7" s="29" t="s">
+        <v>214</v>
       </c>
       <c r="J7" s="18"/>
       <c r="K7" s="18"/>
@@ -10486,8 +10769,8 @@
       <c r="O7" s="16" t="s">
         <v>24</v>
       </c>
-      <c r="P7" s="30" t="s">
-        <v>223</v>
+      <c r="P7" s="29" t="s">
+        <v>214</v>
       </c>
       <c r="Q7" s="18"/>
       <c r="R7" s="18"/>
@@ -10496,8 +10779,8 @@
       <c r="V7" s="16" t="s">
         <v>24</v>
       </c>
-      <c r="W7" s="30" t="s">
-        <v>223</v>
+      <c r="W7" s="29" t="s">
+        <v>214</v>
       </c>
       <c r="X7" s="18"/>
       <c r="Y7" s="18"/>
@@ -10506,8 +10789,8 @@
       <c r="AC7" s="16" t="s">
         <v>24</v>
       </c>
-      <c r="AD7" s="30" t="s">
-        <v>223</v>
+      <c r="AD7" s="29" t="s">
+        <v>214</v>
       </c>
       <c r="AE7" s="18"/>
       <c r="AF7" s="18"/>
@@ -10516,8 +10799,8 @@
       <c r="AJ7" s="16" t="s">
         <v>24</v>
       </c>
-      <c r="AK7" s="30" t="s">
-        <v>223</v>
+      <c r="AK7" s="29" t="s">
+        <v>214</v>
       </c>
       <c r="AL7" s="18"/>
       <c r="AM7" s="18"/>
@@ -10526,8 +10809,8 @@
       <c r="AQ7" s="16" t="s">
         <v>24</v>
       </c>
-      <c r="AR7" s="30" t="s">
-        <v>223</v>
+      <c r="AR7" s="29" t="s">
+        <v>214</v>
       </c>
       <c r="AS7" s="18"/>
       <c r="AT7" s="18"/>
@@ -10536,8 +10819,8 @@
       <c r="AX7" s="16" t="s">
         <v>24</v>
       </c>
-      <c r="AY7" s="30" t="s">
-        <v>223</v>
+      <c r="AY7" s="29" t="s">
+        <v>214</v>
       </c>
       <c r="AZ7" s="18"/>
       <c r="BA7" s="18"/>
@@ -10546,8 +10829,8 @@
       <c r="BE7" s="16" t="s">
         <v>24</v>
       </c>
-      <c r="BF7" s="30" t="s">
-        <v>223</v>
+      <c r="BF7" s="29" t="s">
+        <v>214</v>
       </c>
       <c r="BG7" s="18"/>
       <c r="BH7" s="18"/>
@@ -10556,8 +10839,8 @@
       <c r="BL7" s="16" t="s">
         <v>24</v>
       </c>
-      <c r="BM7" s="30" t="s">
-        <v>223</v>
+      <c r="BM7" s="29" t="s">
+        <v>214</v>
       </c>
       <c r="BN7" s="18"/>
       <c r="BO7" s="18"/>
@@ -10566,8 +10849,8 @@
       <c r="BS7" s="16" t="s">
         <v>24</v>
       </c>
-      <c r="BT7" s="30" t="s">
-        <v>223</v>
+      <c r="BT7" s="29" t="s">
+        <v>214</v>
       </c>
       <c r="BU7" s="18"/>
       <c r="BV7" s="18"/>
@@ -10576,8 +10859,8 @@
       <c r="BZ7" s="16" t="s">
         <v>24</v>
       </c>
-      <c r="CA7" s="30" t="s">
-        <v>223</v>
+      <c r="CA7" s="29" t="s">
+        <v>214</v>
       </c>
       <c r="CB7" s="18"/>
       <c r="CC7" s="18"/>
@@ -10586,8 +10869,8 @@
       <c r="CG7" s="16" t="s">
         <v>24</v>
       </c>
-      <c r="CH7" s="30" t="s">
-        <v>223</v>
+      <c r="CH7" s="29" t="s">
+        <v>214</v>
       </c>
       <c r="CI7" s="18"/>
       <c r="CJ7" s="18"/>
@@ -10596,8 +10879,8 @@
       <c r="CN7" s="16" t="s">
         <v>24</v>
       </c>
-      <c r="CO7" s="30" t="s">
-        <v>223</v>
+      <c r="CO7" s="29" t="s">
+        <v>214</v>
       </c>
       <c r="CP7" s="18"/>
       <c r="CQ7" s="18"/>
@@ -10606,8 +10889,8 @@
       <c r="CU7" s="16" t="s">
         <v>24</v>
       </c>
-      <c r="CV7" s="30" t="s">
-        <v>223</v>
+      <c r="CV7" s="29" t="s">
+        <v>214</v>
       </c>
       <c r="CW7" s="18"/>
       <c r="CX7" s="18"/>
@@ -10616,8 +10899,8 @@
       <c r="DB7" s="16" t="s">
         <v>24</v>
       </c>
-      <c r="DC7" s="30" t="s">
-        <v>223</v>
+      <c r="DC7" s="29" t="s">
+        <v>214</v>
       </c>
       <c r="DD7" s="18"/>
       <c r="DE7" s="18"/>
@@ -10626,8 +10909,8 @@
       <c r="DI7" s="16" t="s">
         <v>24</v>
       </c>
-      <c r="DJ7" s="30" t="s">
-        <v>223</v>
+      <c r="DJ7" s="29" t="s">
+        <v>214</v>
       </c>
       <c r="DK7" s="18"/>
       <c r="DL7" s="18"/>
@@ -10636,8 +10919,8 @@
       <c r="DP7" s="16" t="s">
         <v>24</v>
       </c>
-      <c r="DQ7" s="30" t="s">
-        <v>223</v>
+      <c r="DQ7" s="29" t="s">
+        <v>214</v>
       </c>
       <c r="DR7" s="18"/>
       <c r="DS7" s="18"/>
@@ -10646,8 +10929,8 @@
       <c r="DW7" s="16" t="s">
         <v>24</v>
       </c>
-      <c r="DX7" s="30" t="s">
-        <v>223</v>
+      <c r="DX7" s="29" t="s">
+        <v>214</v>
       </c>
       <c r="DY7" s="18"/>
       <c r="DZ7" s="18"/>
@@ -10656,8 +10939,8 @@
       <c r="ED7" s="16" t="s">
         <v>24</v>
       </c>
-      <c r="EE7" s="30" t="s">
-        <v>223</v>
+      <c r="EE7" s="29" t="s">
+        <v>214</v>
       </c>
       <c r="EF7" s="18"/>
       <c r="EG7" s="18"/>
@@ -10666,8 +10949,8 @@
       <c r="EK7" s="16" t="s">
         <v>24</v>
       </c>
-      <c r="EL7" s="30" t="s">
-        <v>223</v>
+      <c r="EL7" s="29" t="s">
+        <v>214</v>
       </c>
       <c r="EM7" s="18"/>
       <c r="EN7" s="18"/>
@@ -10676,8 +10959,8 @@
       <c r="ER7" s="16" t="s">
         <v>24</v>
       </c>
-      <c r="ES7" s="30" t="s">
-        <v>223</v>
+      <c r="ES7" s="29" t="s">
+        <v>214</v>
       </c>
       <c r="ET7" s="18"/>
       <c r="EU7" s="18"/>
@@ -10686,8 +10969,8 @@
       <c r="EY7" s="16" t="s">
         <v>24</v>
       </c>
-      <c r="EZ7" s="30" t="s">
-        <v>223</v>
+      <c r="EZ7" s="29" t="s">
+        <v>214</v>
       </c>
       <c r="FA7" s="18"/>
       <c r="FB7" s="18"/>
@@ -11112,886 +11395,939 @@
     </row>
     <row r="9" spans="1:160" ht="29.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="16" t="s">
-        <v>224</v>
+        <v>215</v>
       </c>
       <c r="B9" s="16" t="s">
-        <v>225</v>
+        <v>216</v>
       </c>
       <c r="C9" s="16" t="s">
-        <v>226</v>
+        <v>217</v>
       </c>
       <c r="D9" s="16" t="s">
-        <v>227</v>
+        <v>218</v>
       </c>
       <c r="E9" s="16"/>
       <c r="F9" s="16"/>
       <c r="H9" s="16" t="s">
-        <v>224</v>
+        <v>215</v>
       </c>
       <c r="I9" s="16" t="s">
-        <v>225</v>
+        <v>216</v>
       </c>
       <c r="J9" s="16" t="s">
-        <v>226</v>
+        <v>217</v>
       </c>
       <c r="K9" s="16" t="s">
-        <v>227</v>
+        <v>218</v>
       </c>
       <c r="L9" s="16"/>
       <c r="M9" s="16"/>
       <c r="O9" s="16" t="s">
-        <v>224</v>
+        <v>215</v>
       </c>
       <c r="P9" s="16" t="s">
-        <v>225</v>
+        <v>216</v>
       </c>
       <c r="Q9" s="16" t="s">
-        <v>226</v>
+        <v>217</v>
       </c>
       <c r="R9" s="16" t="s">
-        <v>227</v>
+        <v>218</v>
       </c>
       <c r="S9" s="16"/>
       <c r="T9" s="16"/>
       <c r="V9" s="16" t="s">
-        <v>224</v>
+        <v>215</v>
       </c>
       <c r="W9" s="16" t="s">
-        <v>225</v>
+        <v>216</v>
       </c>
       <c r="X9" s="16" t="s">
-        <v>226</v>
+        <v>217</v>
       </c>
       <c r="Y9" s="16" t="s">
-        <v>227</v>
+        <v>218</v>
       </c>
       <c r="Z9" s="16"/>
       <c r="AA9" s="16"/>
       <c r="AC9" s="16" t="s">
-        <v>224</v>
+        <v>215</v>
       </c>
       <c r="AD9" s="16" t="s">
-        <v>225</v>
+        <v>216</v>
       </c>
       <c r="AE9" s="16" t="s">
-        <v>226</v>
+        <v>217</v>
       </c>
       <c r="AF9" s="16" t="s">
-        <v>227</v>
+        <v>218</v>
       </c>
       <c r="AG9" s="16"/>
       <c r="AH9" s="16"/>
       <c r="AJ9" s="16" t="s">
-        <v>224</v>
+        <v>215</v>
       </c>
       <c r="AK9" s="16" t="s">
-        <v>225</v>
+        <v>216</v>
       </c>
       <c r="AL9" s="16" t="s">
-        <v>226</v>
+        <v>217</v>
       </c>
       <c r="AM9" s="16" t="s">
-        <v>227</v>
+        <v>218</v>
       </c>
       <c r="AN9" s="16"/>
       <c r="AO9" s="16"/>
       <c r="AQ9" s="16" t="s">
-        <v>224</v>
+        <v>215</v>
       </c>
       <c r="AR9" s="16" t="s">
-        <v>225</v>
+        <v>216</v>
       </c>
       <c r="AS9" s="16" t="s">
-        <v>226</v>
+        <v>217</v>
       </c>
       <c r="AT9" s="16" t="s">
-        <v>227</v>
+        <v>218</v>
       </c>
       <c r="AU9" s="16"/>
       <c r="AV9" s="16"/>
       <c r="AX9" s="16" t="s">
-        <v>224</v>
+        <v>215</v>
       </c>
       <c r="AY9" s="16" t="s">
-        <v>225</v>
+        <v>216</v>
       </c>
       <c r="AZ9" s="16" t="s">
-        <v>226</v>
+        <v>217</v>
       </c>
       <c r="BA9" s="16" t="s">
-        <v>227</v>
+        <v>218</v>
       </c>
       <c r="BB9" s="16"/>
       <c r="BC9" s="16"/>
       <c r="BE9" s="16" t="s">
-        <v>224</v>
+        <v>215</v>
       </c>
       <c r="BF9" s="16" t="s">
-        <v>225</v>
+        <v>216</v>
       </c>
       <c r="BG9" s="16" t="s">
-        <v>226</v>
+        <v>217</v>
       </c>
       <c r="BH9" s="16" t="s">
-        <v>227</v>
+        <v>218</v>
       </c>
       <c r="BI9" s="16"/>
       <c r="BJ9" s="16"/>
       <c r="BL9" s="16" t="s">
-        <v>224</v>
+        <v>215</v>
       </c>
       <c r="BM9" s="16" t="s">
-        <v>225</v>
+        <v>216</v>
       </c>
       <c r="BN9" s="16" t="s">
-        <v>226</v>
+        <v>217</v>
       </c>
       <c r="BO9" s="16" t="s">
-        <v>227</v>
+        <v>218</v>
       </c>
       <c r="BP9" s="16"/>
       <c r="BQ9" s="16"/>
       <c r="BS9" s="16" t="s">
-        <v>224</v>
+        <v>215</v>
       </c>
       <c r="BT9" s="16" t="s">
-        <v>225</v>
+        <v>216</v>
       </c>
       <c r="BU9" s="16" t="s">
-        <v>226</v>
+        <v>217</v>
       </c>
       <c r="BV9" s="16" t="s">
-        <v>227</v>
+        <v>218</v>
       </c>
       <c r="BW9" s="16"/>
       <c r="BX9" s="16"/>
       <c r="BZ9" s="16" t="s">
-        <v>224</v>
+        <v>215</v>
       </c>
       <c r="CA9" s="16" t="s">
-        <v>225</v>
+        <v>216</v>
       </c>
       <c r="CB9" s="16" t="s">
-        <v>226</v>
+        <v>217</v>
       </c>
       <c r="CC9" s="16" t="s">
-        <v>227</v>
+        <v>218</v>
       </c>
       <c r="CD9" s="16"/>
       <c r="CE9" s="16"/>
       <c r="CG9" s="16" t="s">
-        <v>224</v>
+        <v>215</v>
       </c>
       <c r="CH9" s="16" t="s">
-        <v>225</v>
+        <v>216</v>
       </c>
       <c r="CI9" s="16" t="s">
-        <v>226</v>
+        <v>217</v>
       </c>
       <c r="CJ9" s="16" t="s">
-        <v>227</v>
+        <v>218</v>
       </c>
       <c r="CK9" s="16"/>
       <c r="CL9" s="16"/>
       <c r="CN9" s="16" t="s">
-        <v>224</v>
+        <v>215</v>
       </c>
       <c r="CO9" s="16" t="s">
-        <v>225</v>
+        <v>216</v>
       </c>
       <c r="CP9" s="16" t="s">
-        <v>226</v>
+        <v>217</v>
       </c>
       <c r="CQ9" s="16" t="s">
-        <v>227</v>
+        <v>218</v>
       </c>
       <c r="CR9" s="16"/>
       <c r="CS9" s="16"/>
       <c r="CU9" s="16" t="s">
-        <v>224</v>
+        <v>215</v>
       </c>
       <c r="CV9" s="16" t="s">
-        <v>225</v>
+        <v>216</v>
       </c>
       <c r="CW9" s="16" t="s">
-        <v>226</v>
+        <v>217</v>
       </c>
       <c r="CX9" s="16" t="s">
-        <v>227</v>
+        <v>218</v>
       </c>
       <c r="CY9" s="16"/>
       <c r="CZ9" s="16"/>
       <c r="DB9" s="16" t="s">
-        <v>224</v>
+        <v>215</v>
       </c>
       <c r="DC9" s="16" t="s">
-        <v>225</v>
+        <v>216</v>
       </c>
       <c r="DD9" s="16" t="s">
-        <v>226</v>
+        <v>217</v>
       </c>
       <c r="DE9" s="16" t="s">
-        <v>227</v>
+        <v>218</v>
       </c>
       <c r="DF9" s="16"/>
       <c r="DG9" s="16"/>
       <c r="DI9" s="16" t="s">
-        <v>224</v>
+        <v>215</v>
       </c>
       <c r="DJ9" s="16" t="s">
-        <v>225</v>
+        <v>216</v>
       </c>
       <c r="DK9" s="16" t="s">
-        <v>226</v>
+        <v>217</v>
       </c>
       <c r="DL9" s="16" t="s">
-        <v>227</v>
+        <v>218</v>
       </c>
       <c r="DM9" s="16"/>
       <c r="DN9" s="16"/>
       <c r="DP9" s="16" t="s">
-        <v>224</v>
+        <v>215</v>
       </c>
       <c r="DQ9" s="16" t="s">
-        <v>225</v>
+        <v>216</v>
       </c>
       <c r="DR9" s="16" t="s">
-        <v>226</v>
+        <v>217</v>
       </c>
       <c r="DS9" s="16" t="s">
-        <v>227</v>
+        <v>218</v>
       </c>
       <c r="DT9" s="16"/>
       <c r="DU9" s="16"/>
       <c r="DW9" s="16" t="s">
-        <v>224</v>
+        <v>215</v>
       </c>
       <c r="DX9" s="16" t="s">
-        <v>225</v>
+        <v>216</v>
       </c>
       <c r="DY9" s="16" t="s">
-        <v>226</v>
+        <v>217</v>
       </c>
       <c r="DZ9" s="16" t="s">
-        <v>227</v>
+        <v>218</v>
       </c>
       <c r="EA9" s="16"/>
       <c r="EB9" s="16"/>
       <c r="ED9" s="16" t="s">
-        <v>224</v>
+        <v>215</v>
       </c>
       <c r="EE9" s="16" t="s">
-        <v>225</v>
+        <v>216</v>
       </c>
       <c r="EF9" s="16" t="s">
-        <v>226</v>
+        <v>217</v>
       </c>
       <c r="EG9" s="16" t="s">
-        <v>227</v>
+        <v>218</v>
       </c>
       <c r="EH9" s="16"/>
       <c r="EI9" s="16"/>
       <c r="EK9" s="16" t="s">
-        <v>224</v>
+        <v>215</v>
       </c>
       <c r="EL9" s="16" t="s">
-        <v>225</v>
+        <v>216</v>
       </c>
       <c r="EM9" s="16" t="s">
-        <v>226</v>
+        <v>217</v>
       </c>
       <c r="EN9" s="16" t="s">
-        <v>227</v>
+        <v>218</v>
       </c>
       <c r="EO9" s="16"/>
       <c r="EP9" s="16"/>
       <c r="ER9" s="16" t="s">
-        <v>224</v>
+        <v>215</v>
       </c>
       <c r="ES9" s="16" t="s">
-        <v>225</v>
+        <v>216</v>
       </c>
       <c r="ET9" s="16" t="s">
-        <v>226</v>
+        <v>217</v>
       </c>
       <c r="EU9" s="16" t="s">
-        <v>227</v>
+        <v>218</v>
       </c>
       <c r="EV9" s="16"/>
       <c r="EW9" s="16"/>
       <c r="EY9" s="16" t="s">
-        <v>224</v>
+        <v>215</v>
       </c>
       <c r="EZ9" s="16" t="s">
-        <v>225</v>
+        <v>216</v>
       </c>
       <c r="FA9" s="16" t="s">
-        <v>226</v>
+        <v>217</v>
       </c>
       <c r="FB9" s="16" t="s">
-        <v>227</v>
+        <v>218</v>
       </c>
       <c r="FC9" s="16"/>
       <c r="FD9" s="16"/>
     </row>
     <row r="10" spans="1:160" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="16" t="s">
-        <v>228</v>
+        <v>219</v>
       </c>
       <c r="B10" s="16" t="s">
-        <v>293</v>
+        <v>284</v>
       </c>
       <c r="C10" s="16"/>
       <c r="D10" s="16" t="s">
-        <v>230</v>
+        <v>221</v>
       </c>
       <c r="E10" s="16"/>
       <c r="F10" s="16"/>
       <c r="H10" s="16" t="s">
-        <v>228</v>
+        <v>219</v>
       </c>
       <c r="I10" s="16" t="s">
-        <v>294</v>
+        <v>285</v>
       </c>
       <c r="J10" s="16"/>
       <c r="K10" s="16" t="s">
-        <v>230</v>
+        <v>221</v>
       </c>
       <c r="L10" s="16"/>
       <c r="M10" s="16"/>
       <c r="O10" s="16" t="s">
-        <v>228</v>
+        <v>219</v>
       </c>
       <c r="P10" s="16" t="s">
-        <v>295</v>
+        <v>286</v>
       </c>
       <c r="Q10" s="16"/>
       <c r="R10" s="16" t="s">
-        <v>230</v>
+        <v>221</v>
       </c>
       <c r="S10" s="16"/>
       <c r="T10" s="16"/>
       <c r="V10" s="16" t="s">
-        <v>228</v>
+        <v>219</v>
       </c>
       <c r="W10" s="16" t="s">
-        <v>239</v>
+        <v>230</v>
       </c>
       <c r="X10" s="16"/>
       <c r="Y10" s="16" t="s">
-        <v>230</v>
+        <v>221</v>
       </c>
       <c r="Z10" s="16"/>
       <c r="AA10" s="16"/>
       <c r="AC10" s="16" t="s">
-        <v>228</v>
+        <v>219</v>
       </c>
       <c r="AD10" s="16" t="s">
-        <v>296</v>
+        <v>287</v>
       </c>
       <c r="AE10" s="16"/>
       <c r="AF10" s="16" t="s">
-        <v>230</v>
+        <v>221</v>
       </c>
       <c r="AG10" s="16"/>
       <c r="AH10" s="16"/>
       <c r="AJ10" s="16" t="s">
-        <v>228</v>
+        <v>219</v>
       </c>
       <c r="AK10" s="16" t="s">
-        <v>296</v>
+        <v>287</v>
       </c>
       <c r="AL10" s="16"/>
       <c r="AM10" s="16" t="s">
-        <v>230</v>
+        <v>221</v>
       </c>
       <c r="AN10" s="16"/>
       <c r="AO10" s="16"/>
       <c r="AQ10" s="16" t="s">
-        <v>228</v>
+        <v>219</v>
       </c>
       <c r="AR10" s="16" t="s">
-        <v>296</v>
+        <v>287</v>
       </c>
       <c r="AS10" s="16"/>
       <c r="AT10" s="16" t="s">
-        <v>230</v>
+        <v>221</v>
       </c>
       <c r="AU10" s="16"/>
       <c r="AV10" s="16"/>
       <c r="AX10" s="16" t="s">
-        <v>228</v>
+        <v>219</v>
       </c>
       <c r="AY10" s="16" t="s">
-        <v>296</v>
+        <v>287</v>
       </c>
       <c r="AZ10" s="16"/>
       <c r="BA10" s="16" t="s">
-        <v>230</v>
+        <v>221</v>
       </c>
       <c r="BB10" s="16"/>
       <c r="BC10" s="16"/>
       <c r="BE10" s="16" t="s">
-        <v>228</v>
+        <v>219</v>
       </c>
       <c r="BF10" s="16" t="s">
-        <v>296</v>
+        <v>287</v>
       </c>
       <c r="BG10" s="16"/>
       <c r="BH10" s="16" t="s">
-        <v>230</v>
+        <v>221</v>
       </c>
       <c r="BI10" s="16"/>
       <c r="BJ10" s="16"/>
       <c r="BL10" s="16" t="s">
-        <v>228</v>
+        <v>219</v>
       </c>
       <c r="BM10" s="16" t="s">
-        <v>297</v>
+        <v>288</v>
       </c>
       <c r="BN10" s="16"/>
       <c r="BO10" s="16" t="s">
-        <v>230</v>
+        <v>221</v>
       </c>
       <c r="BP10" s="16"/>
       <c r="BQ10" s="16"/>
       <c r="BS10" s="16" t="s">
-        <v>228</v>
+        <v>219</v>
       </c>
       <c r="BT10" s="16" t="s">
-        <v>239</v>
+        <v>230</v>
       </c>
       <c r="BU10" s="16"/>
       <c r="BV10" s="16" t="s">
-        <v>230</v>
+        <v>221</v>
       </c>
       <c r="BW10" s="16"/>
       <c r="BX10" s="16"/>
       <c r="BZ10" s="16" t="s">
-        <v>228</v>
+        <v>219</v>
       </c>
       <c r="CA10" s="16" t="s">
-        <v>297</v>
+        <v>288</v>
       </c>
       <c r="CB10" s="16"/>
       <c r="CC10" s="16" t="s">
-        <v>230</v>
+        <v>221</v>
       </c>
       <c r="CD10" s="16"/>
       <c r="CE10" s="16"/>
       <c r="CG10" s="16" t="s">
-        <v>228</v>
+        <v>219</v>
       </c>
       <c r="CH10" s="16" t="s">
-        <v>239</v>
+        <v>230</v>
       </c>
       <c r="CI10" s="16"/>
       <c r="CJ10" s="16" t="s">
-        <v>230</v>
+        <v>221</v>
       </c>
       <c r="CK10" s="16"/>
       <c r="CL10" s="16"/>
       <c r="CN10" s="16" t="s">
-        <v>228</v>
+        <v>219</v>
       </c>
       <c r="CO10" s="16" t="s">
-        <v>298</v>
+        <v>289</v>
       </c>
       <c r="CP10" s="16"/>
       <c r="CQ10" s="16" t="s">
-        <v>230</v>
+        <v>221</v>
       </c>
       <c r="CR10" s="16"/>
       <c r="CS10" s="16"/>
       <c r="CU10" s="16" t="s">
-        <v>228</v>
+        <v>219</v>
       </c>
       <c r="CV10" s="16" t="s">
-        <v>298</v>
+        <v>289</v>
       </c>
       <c r="CW10" s="16"/>
       <c r="CX10" s="16" t="s">
-        <v>230</v>
+        <v>221</v>
       </c>
       <c r="CY10" s="16"/>
       <c r="CZ10" s="16"/>
       <c r="DB10" s="16" t="s">
-        <v>228</v>
+        <v>219</v>
       </c>
       <c r="DC10" s="16" t="s">
-        <v>299</v>
+        <v>290</v>
       </c>
       <c r="DD10" s="16"/>
       <c r="DE10" s="16" t="s">
-        <v>230</v>
+        <v>221</v>
       </c>
       <c r="DF10" s="16"/>
       <c r="DG10" s="16"/>
       <c r="DI10" s="16" t="s">
-        <v>228</v>
+        <v>219</v>
       </c>
       <c r="DJ10" s="16" t="s">
-        <v>300</v>
+        <v>291</v>
       </c>
       <c r="DK10" s="16"/>
       <c r="DL10" s="16" t="s">
-        <v>230</v>
+        <v>221</v>
       </c>
       <c r="DM10" s="16"/>
       <c r="DN10" s="16"/>
       <c r="DP10" s="16" t="s">
-        <v>228</v>
+        <v>219</v>
       </c>
       <c r="DQ10" s="16" t="s">
-        <v>239</v>
+        <v>230</v>
       </c>
       <c r="DR10" s="16"/>
       <c r="DS10" s="16" t="s">
-        <v>230</v>
+        <v>221</v>
       </c>
       <c r="DT10" s="16"/>
       <c r="DU10" s="16"/>
       <c r="DW10" s="16" t="s">
-        <v>228</v>
+        <v>219</v>
       </c>
       <c r="DX10" s="16" t="s">
-        <v>300</v>
+        <v>291</v>
       </c>
       <c r="DY10" s="16"/>
       <c r="DZ10" s="16" t="s">
-        <v>230</v>
+        <v>221</v>
       </c>
       <c r="EA10" s="16"/>
       <c r="EB10" s="16"/>
       <c r="ED10" s="16" t="s">
-        <v>228</v>
+        <v>219</v>
       </c>
       <c r="EE10" s="16" t="s">
-        <v>300</v>
+        <v>291</v>
       </c>
       <c r="EF10" s="16"/>
       <c r="EG10" s="16" t="s">
-        <v>230</v>
+        <v>221</v>
       </c>
       <c r="EH10" s="16"/>
       <c r="EI10" s="16"/>
       <c r="EK10" s="16" t="s">
-        <v>228</v>
+        <v>219</v>
       </c>
       <c r="EL10" s="16" t="s">
-        <v>301</v>
+        <v>292</v>
       </c>
       <c r="EM10" s="16"/>
       <c r="EN10" s="16" t="s">
-        <v>230</v>
+        <v>221</v>
       </c>
       <c r="EO10" s="16"/>
       <c r="EP10" s="16"/>
       <c r="ER10" s="16" t="s">
-        <v>228</v>
+        <v>219</v>
       </c>
       <c r="ES10" s="16" t="s">
-        <v>302</v>
+        <v>293</v>
       </c>
       <c r="ET10" s="16"/>
       <c r="EU10" s="16" t="s">
-        <v>230</v>
+        <v>221</v>
       </c>
       <c r="EV10" s="16"/>
       <c r="EW10" s="16"/>
       <c r="EY10" s="16" t="s">
-        <v>228</v>
+        <v>219</v>
       </c>
       <c r="EZ10" s="16" t="s">
-        <v>303</v>
+        <v>294</v>
       </c>
       <c r="FA10" s="16"/>
       <c r="FB10" s="16" t="s">
-        <v>230</v>
+        <v>221</v>
       </c>
       <c r="FC10" s="16"/>
       <c r="FD10" s="16"/>
     </row>
     <row r="11" spans="1:160" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="16" t="s">
-        <v>243</v>
+        <v>234</v>
       </c>
       <c r="B11" s="16" t="s">
-        <v>244</v>
+        <v>235</v>
       </c>
       <c r="C11" s="16"/>
       <c r="D11" s="16" t="s">
-        <v>245</v>
+        <v>236</v>
       </c>
       <c r="E11" s="16"/>
       <c r="F11" s="16"/>
       <c r="H11" s="16" t="s">
-        <v>243</v>
+        <v>234</v>
       </c>
       <c r="I11" s="16" t="s">
-        <v>244</v>
+        <v>235</v>
       </c>
       <c r="J11" s="16"/>
       <c r="K11" s="16" t="s">
-        <v>245</v>
+        <v>236</v>
       </c>
       <c r="L11" s="16"/>
       <c r="M11" s="16"/>
       <c r="O11" s="16" t="s">
-        <v>243</v>
+        <v>234</v>
       </c>
       <c r="P11" s="16" t="s">
-        <v>244</v>
+        <v>235</v>
       </c>
       <c r="Q11" s="16"/>
       <c r="R11" s="16" t="s">
-        <v>245</v>
+        <v>236</v>
       </c>
       <c r="S11" s="16"/>
       <c r="T11" s="16"/>
       <c r="V11" s="16" t="s">
-        <v>243</v>
+        <v>234</v>
       </c>
       <c r="W11" s="16" t="s">
-        <v>244</v>
+        <v>235</v>
       </c>
       <c r="X11" s="16"/>
       <c r="Y11" s="16" t="s">
-        <v>245</v>
+        <v>236</v>
       </c>
       <c r="Z11" s="16"/>
       <c r="AA11" s="16"/>
       <c r="AC11" s="16" t="s">
-        <v>243</v>
+        <v>234</v>
       </c>
       <c r="AD11" s="16" t="s">
-        <v>244</v>
+        <v>235</v>
       </c>
       <c r="AE11" s="16"/>
       <c r="AF11" s="16" t="s">
-        <v>246</v>
+        <v>237</v>
       </c>
       <c r="AG11" s="16"/>
       <c r="AH11" s="16"/>
       <c r="AJ11" s="16" t="s">
-        <v>243</v>
+        <v>234</v>
       </c>
       <c r="AK11" s="16" t="s">
-        <v>244</v>
+        <v>235</v>
       </c>
       <c r="AL11" s="16"/>
       <c r="AM11" s="16" t="s">
-        <v>245</v>
+        <v>236</v>
       </c>
       <c r="AN11" s="16"/>
       <c r="AO11" s="16"/>
       <c r="AQ11" s="16" t="s">
-        <v>243</v>
+        <v>234</v>
       </c>
       <c r="AR11" s="16" t="s">
-        <v>244</v>
+        <v>235</v>
       </c>
       <c r="AS11" s="16"/>
       <c r="AT11" s="16" t="s">
-        <v>245</v>
+        <v>236</v>
       </c>
       <c r="AU11" s="16"/>
       <c r="AV11" s="16"/>
       <c r="AX11" s="16" t="s">
-        <v>243</v>
+        <v>234</v>
       </c>
       <c r="AY11" s="16" t="s">
-        <v>244</v>
+        <v>235</v>
       </c>
       <c r="AZ11" s="16"/>
       <c r="BA11" s="16" t="s">
-        <v>245</v>
+        <v>236</v>
       </c>
       <c r="BB11" s="16"/>
       <c r="BC11" s="16"/>
       <c r="BE11" s="16" t="s">
-        <v>243</v>
+        <v>234</v>
       </c>
       <c r="BF11" s="16" t="s">
-        <v>244</v>
+        <v>235</v>
       </c>
       <c r="BG11" s="16"/>
       <c r="BH11" s="16" t="s">
-        <v>245</v>
+        <v>236</v>
       </c>
       <c r="BI11" s="16"/>
       <c r="BJ11" s="16"/>
       <c r="BL11" s="16" t="s">
-        <v>243</v>
+        <v>234</v>
       </c>
       <c r="BM11" s="16" t="s">
-        <v>244</v>
+        <v>235</v>
       </c>
       <c r="BN11" s="16"/>
       <c r="BO11" s="16" t="s">
-        <v>245</v>
+        <v>236</v>
       </c>
       <c r="BP11" s="16"/>
       <c r="BQ11" s="16"/>
       <c r="BS11" s="16" t="s">
-        <v>243</v>
+        <v>234</v>
       </c>
       <c r="BT11" s="16" t="s">
-        <v>244</v>
+        <v>235</v>
       </c>
       <c r="BU11" s="16"/>
       <c r="BV11" s="16" t="s">
-        <v>245</v>
+        <v>236</v>
       </c>
       <c r="BW11" s="16"/>
       <c r="BX11" s="16"/>
       <c r="BZ11" s="16" t="s">
-        <v>243</v>
+        <v>234</v>
       </c>
       <c r="CA11" s="16" t="s">
-        <v>244</v>
+        <v>235</v>
       </c>
       <c r="CB11" s="16"/>
       <c r="CC11" s="16" t="s">
-        <v>246</v>
+        <v>237</v>
       </c>
       <c r="CD11" s="16"/>
       <c r="CE11" s="16"/>
       <c r="CG11" s="16" t="s">
-        <v>243</v>
+        <v>234</v>
       </c>
       <c r="CH11" s="16" t="s">
-        <v>244</v>
+        <v>235</v>
       </c>
       <c r="CI11" s="16"/>
       <c r="CJ11" s="16" t="s">
-        <v>245</v>
+        <v>236</v>
       </c>
       <c r="CK11" s="16"/>
       <c r="CL11" s="16"/>
       <c r="CN11" s="16" t="s">
-        <v>243</v>
+        <v>234</v>
       </c>
       <c r="CO11" s="16" t="s">
-        <v>244</v>
+        <v>235</v>
       </c>
       <c r="CP11" s="16"/>
       <c r="CQ11" s="16" t="s">
-        <v>304</v>
+        <v>295</v>
       </c>
       <c r="CR11" s="16"/>
       <c r="CS11" s="16"/>
       <c r="CU11" s="16" t="s">
-        <v>243</v>
+        <v>234</v>
       </c>
       <c r="CV11" s="16" t="s">
-        <v>244</v>
+        <v>235</v>
       </c>
       <c r="CW11" s="16"/>
       <c r="CX11" s="16" t="s">
-        <v>245</v>
+        <v>236</v>
       </c>
       <c r="CY11" s="16"/>
       <c r="CZ11" s="16"/>
       <c r="DB11" s="16" t="s">
-        <v>243</v>
+        <v>234</v>
       </c>
       <c r="DC11" s="16" t="s">
-        <v>244</v>
+        <v>235</v>
       </c>
       <c r="DD11" s="16"/>
       <c r="DE11" s="16" t="s">
-        <v>245</v>
+        <v>236</v>
       </c>
       <c r="DF11" s="16"/>
       <c r="DG11" s="16"/>
       <c r="DI11" s="16" t="s">
-        <v>243</v>
+        <v>234</v>
       </c>
       <c r="DJ11" s="16" t="s">
-        <v>244</v>
+        <v>235</v>
       </c>
       <c r="DK11" s="16"/>
       <c r="DL11" s="16" t="s">
-        <v>245</v>
+        <v>236</v>
       </c>
       <c r="DM11" s="16"/>
       <c r="DN11" s="16"/>
       <c r="DP11" s="16" t="s">
-        <v>243</v>
+        <v>234</v>
       </c>
       <c r="DQ11" s="16" t="s">
-        <v>244</v>
+        <v>235</v>
       </c>
       <c r="DR11" s="16"/>
       <c r="DS11" s="16" t="s">
-        <v>245</v>
+        <v>236</v>
       </c>
       <c r="DT11" s="16"/>
       <c r="DU11" s="16"/>
       <c r="DW11" s="16" t="s">
-        <v>243</v>
+        <v>234</v>
       </c>
       <c r="DX11" s="16" t="s">
-        <v>244</v>
+        <v>235</v>
       </c>
       <c r="DY11" s="16"/>
       <c r="DZ11" s="16" t="s">
-        <v>305</v>
+        <v>296</v>
       </c>
       <c r="EA11" s="16"/>
       <c r="EB11" s="16"/>
       <c r="ED11" s="16" t="s">
-        <v>243</v>
+        <v>234</v>
       </c>
       <c r="EE11" s="16" t="s">
-        <v>244</v>
+        <v>235</v>
       </c>
       <c r="EF11" s="16"/>
       <c r="EG11" s="16" t="s">
-        <v>245</v>
+        <v>236</v>
       </c>
       <c r="EH11" s="16"/>
       <c r="EI11" s="16"/>
       <c r="EK11" s="16" t="s">
-        <v>243</v>
+        <v>234</v>
       </c>
       <c r="EL11" s="16" t="s">
-        <v>244</v>
+        <v>235</v>
       </c>
       <c r="EM11" s="16"/>
       <c r="EN11" s="16" t="s">
-        <v>245</v>
+        <v>236</v>
       </c>
       <c r="EO11" s="16"/>
       <c r="EP11" s="16"/>
       <c r="ER11" s="16" t="s">
-        <v>243</v>
+        <v>234</v>
       </c>
       <c r="ES11" s="16" t="s">
-        <v>244</v>
+        <v>235</v>
       </c>
       <c r="ET11" s="16"/>
       <c r="EU11" s="16" t="s">
-        <v>245</v>
+        <v>236</v>
       </c>
       <c r="EV11" s="16"/>
       <c r="EW11" s="16"/>
       <c r="EY11" s="16" t="s">
-        <v>243</v>
+        <v>234</v>
       </c>
       <c r="EZ11" s="16" t="s">
-        <v>244</v>
+        <v>235</v>
       </c>
       <c r="FA11" s="16"/>
       <c r="FB11" s="16" t="s">
-        <v>245</v>
+        <v>236</v>
       </c>
       <c r="FC11" s="16"/>
       <c r="FD11" s="16"/>
     </row>
   </sheetData>
   <mergeCells count="69">
+    <mergeCell ref="EY1:FD1"/>
+    <mergeCell ref="V1:AA1"/>
+    <mergeCell ref="DX6:EB6"/>
+    <mergeCell ref="B7:F7"/>
+    <mergeCell ref="BE1:BJ1"/>
+    <mergeCell ref="AR7:AV7"/>
+    <mergeCell ref="O1:T1"/>
+    <mergeCell ref="EZ7:FD7"/>
+    <mergeCell ref="I6:M6"/>
+    <mergeCell ref="AK7:AO7"/>
+    <mergeCell ref="W6:AA6"/>
+    <mergeCell ref="CV7:CZ7"/>
+    <mergeCell ref="BS1:BX1"/>
+    <mergeCell ref="DI1:DN1"/>
+    <mergeCell ref="BF7:BJ7"/>
+    <mergeCell ref="BM6:BQ6"/>
+    <mergeCell ref="CH6:CL6"/>
+    <mergeCell ref="BF6:BJ6"/>
+    <mergeCell ref="DW1:EB1"/>
+    <mergeCell ref="DQ6:DU6"/>
+    <mergeCell ref="DJ7:DN7"/>
+    <mergeCell ref="ES7:EW7"/>
+    <mergeCell ref="AC1:AH1"/>
+    <mergeCell ref="EE6:EI6"/>
+    <mergeCell ref="I7:M7"/>
+    <mergeCell ref="BT7:BX7"/>
+    <mergeCell ref="P6:T6"/>
+    <mergeCell ref="CG1:CL1"/>
+    <mergeCell ref="BM7:BQ7"/>
+    <mergeCell ref="CA6:CE6"/>
+    <mergeCell ref="AQ1:AV1"/>
+    <mergeCell ref="AD6:AH6"/>
+    <mergeCell ref="DC7:DG7"/>
+    <mergeCell ref="BZ1:CE1"/>
+    <mergeCell ref="CO6:CS6"/>
+    <mergeCell ref="DP1:DU1"/>
+    <mergeCell ref="DQ7:DU7"/>
+    <mergeCell ref="EZ6:FD6"/>
+    <mergeCell ref="EK1:EP1"/>
+    <mergeCell ref="H1:M1"/>
+    <mergeCell ref="B6:F6"/>
+    <mergeCell ref="AX1:BC1"/>
+    <mergeCell ref="AK6:AO6"/>
+    <mergeCell ref="DJ6:DN6"/>
+    <mergeCell ref="ES6:EW6"/>
+    <mergeCell ref="ED1:EI1"/>
+    <mergeCell ref="AJ1:AO1"/>
+    <mergeCell ref="AR6:AV6"/>
+    <mergeCell ref="CN1:CS1"/>
+    <mergeCell ref="DC6:DG6"/>
+    <mergeCell ref="DB1:DG1"/>
+    <mergeCell ref="CV6:CZ6"/>
+    <mergeCell ref="ER1:EW1"/>
     <mergeCell ref="EL7:EP7"/>
     <mergeCell ref="AD7:AH7"/>
     <mergeCell ref="A1:F1"/>
@@ -12008,59 +12344,6 @@
     <mergeCell ref="CO7:CS7"/>
     <mergeCell ref="EL6:EP6"/>
     <mergeCell ref="DX7:EB7"/>
-    <mergeCell ref="EZ6:FD6"/>
-    <mergeCell ref="EK1:EP1"/>
-    <mergeCell ref="H1:M1"/>
-    <mergeCell ref="B6:F6"/>
-    <mergeCell ref="AX1:BC1"/>
-    <mergeCell ref="AK6:AO6"/>
-    <mergeCell ref="DJ6:DN6"/>
-    <mergeCell ref="ES6:EW6"/>
-    <mergeCell ref="ED1:EI1"/>
-    <mergeCell ref="AJ1:AO1"/>
-    <mergeCell ref="AR6:AV6"/>
-    <mergeCell ref="CN1:CS1"/>
-    <mergeCell ref="DC6:DG6"/>
-    <mergeCell ref="DB1:DG1"/>
-    <mergeCell ref="CV6:CZ6"/>
-    <mergeCell ref="ER1:EW1"/>
-    <mergeCell ref="ES7:EW7"/>
-    <mergeCell ref="AC1:AH1"/>
-    <mergeCell ref="EE6:EI6"/>
-    <mergeCell ref="I7:M7"/>
-    <mergeCell ref="BT7:BX7"/>
-    <mergeCell ref="P6:T6"/>
-    <mergeCell ref="CG1:CL1"/>
-    <mergeCell ref="BM7:BQ7"/>
-    <mergeCell ref="CA6:CE6"/>
-    <mergeCell ref="AQ1:AV1"/>
-    <mergeCell ref="AD6:AH6"/>
-    <mergeCell ref="DC7:DG7"/>
-    <mergeCell ref="BZ1:CE1"/>
-    <mergeCell ref="CO6:CS6"/>
-    <mergeCell ref="DP1:DU1"/>
-    <mergeCell ref="DQ7:DU7"/>
-    <mergeCell ref="CH6:CL6"/>
-    <mergeCell ref="BF6:BJ6"/>
-    <mergeCell ref="DW1:EB1"/>
-    <mergeCell ref="DQ6:DU6"/>
-    <mergeCell ref="DJ7:DN7"/>
-    <mergeCell ref="EY1:FD1"/>
-    <mergeCell ref="V1:AA1"/>
-    <mergeCell ref="DX6:EB6"/>
-    <mergeCell ref="B7:F7"/>
-    <mergeCell ref="BE1:BJ1"/>
-    <mergeCell ref="AR7:AV7"/>
-    <mergeCell ref="O1:T1"/>
-    <mergeCell ref="EZ7:FD7"/>
-    <mergeCell ref="I6:M6"/>
-    <mergeCell ref="AK7:AO7"/>
-    <mergeCell ref="W6:AA6"/>
-    <mergeCell ref="CV7:CZ7"/>
-    <mergeCell ref="BS1:BX1"/>
-    <mergeCell ref="DI1:DN1"/>
-    <mergeCell ref="BF7:BJ7"/>
-    <mergeCell ref="BM6:BQ6"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Test Cases.xlsx
+++ b/Test Cases.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://endresshauser-my.sharepoint.com/personal/corbin_ferguson_endress_com/Documents/ThesisBuildTool/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="307" documentId="8_{B89245B7-08D9-4A9D-8516-F6C9C7AFFDC1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0D8059F2-F8F6-42BB-9850-F98902EB790B}"/>
+  <xr:revisionPtr revIDLastSave="309" documentId="8_{B89245B7-08D9-4A9D-8516-F6C9C7AFFDC1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{92FDCF3B-C2E3-4220-A9E3-B5C0674B9B45}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="25440" windowHeight="15270" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="25440" windowHeight="15270" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tests" sheetId="1" r:id="rId1"/>
@@ -1599,10 +1599,10 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="4"/>
                 <c:pt idx="0">
-                  <c:v>2</c:v>
+                  <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>40</c:v>
+                  <c:v>41</c:v>
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>18</c:v>
@@ -3004,7 +3004,7 @@
       </c>
       <c r="H1">
         <f>COUNTIF(TestMaster[Test Status], "Not Implemented")</f>
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
@@ -3027,7 +3027,7 @@
       </c>
       <c r="H2">
         <f>COUNTIF(TestMaster[Test Status], "Pass")</f>
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
@@ -3404,7 +3404,7 @@
       </c>
       <c r="H20">
         <f>COUNTIFS(TestMaster[Test Status], "Not Implemented", TestMaster[Namespace], G19)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
@@ -3427,7 +3427,7 @@
       </c>
       <c r="H21">
         <f>COUNTIFS(TestMaster[Test Status], "Pass", TestMaster[Namespace], G19)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
@@ -3801,7 +3801,7 @@
         <v>Validation Error Window</v>
       </c>
       <c r="C37" s="5" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D37" t="s">
         <v>10</v>

--- a/Test Cases.xlsx
+++ b/Test Cases.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://endresshauser-my.sharepoint.com/personal/corbin_ferguson_endress_com/Documents/ThesisBuildTool/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="309" documentId="8_{B89245B7-08D9-4A9D-8516-F6C9C7AFFDC1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{92FDCF3B-C2E3-4220-A9E3-B5C0674B9B45}"/>
+  <xr:revisionPtr revIDLastSave="325" documentId="8_{B89245B7-08D9-4A9D-8516-F6C9C7AFFDC1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{96FEFAAE-FE66-441B-92CD-2D085DA1D9DF}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="25440" windowHeight="15270" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,6 @@
     <sheet name="Unit XMLHandlerTests" sheetId="8" r:id="rId8"/>
   </sheets>
   <calcPr calcId="191029"/>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -41,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1795" uniqueCount="379">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1801" uniqueCount="386">
   <si>
     <t>Test ID</t>
   </si>
@@ -205,9 +204,6 @@
     <t>Set still redundant Name</t>
   </si>
   <si>
-    <t>TemplateFBAOI</t>
-  </si>
-  <si>
     <t>Set nonredundant Name</t>
   </si>
   <si>
@@ -1178,6 +1174,30 @@
   </si>
   <si>
     <t>return to actionSelect</t>
+  </si>
+  <si>
+    <t>"TemplateFBAOI" and "TemplateLadderAOI" element selected for template</t>
+  </si>
+  <si>
+    <t>Select parent type for insert</t>
+  </si>
+  <si>
+    <t>move to parent select type</t>
+  </si>
+  <si>
+    <t>Element Clash from import</t>
+  </si>
+  <si>
+    <t>"Cancel" selected from dropdown</t>
+  </si>
+  <si>
+    <t>clashing elements window appears</t>
+  </si>
+  <si>
+    <t>"TemplateFBAOI" selected from dropdown</t>
+  </si>
+  <si>
+    <t>"TemplateLadderAOI" selected from dropdown</t>
   </si>
 </sst>
 </file>
@@ -1324,11 +1344,11 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1602,10 +1622,10 @@
                   <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>41</c:v>
+                  <c:v>43</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>18</c:v>
+                  <c:v>16</c:v>
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>1</c:v>
@@ -3027,7 +3047,7 @@
       </c>
       <c r="H2">
         <f>COUNTIF(TestMaster[Test Status], "Pass")</f>
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
@@ -3050,7 +3070,7 @@
       </c>
       <c r="H3">
         <f>COUNTIF(TestMaster[Test Status], "Fail")</f>
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
@@ -3300,7 +3320,7 @@
       </c>
       <c r="H15">
         <f>COUNTIFS(TestMaster[Test Status], "Pass", TestMaster[Namespace], G13)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
@@ -3323,7 +3343,7 @@
       </c>
       <c r="H16">
         <f>COUNTIFS(TestMaster[Test Status], "Fail", TestMaster[Namespace], G13)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
@@ -3381,7 +3401,7 @@
         <v>7</v>
       </c>
       <c r="G19" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
@@ -3559,7 +3579,7 @@
         <v>Clashing Element Creation</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D27" t="s">
         <v>13</v>
@@ -3662,7 +3682,7 @@
         <v>11</v>
       </c>
       <c r="E31" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="G31" t="s">
         <v>16</v>
@@ -3684,7 +3704,7 @@
         <v>10</v>
       </c>
       <c r="E32" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="G32" t="s">
         <v>5</v>
@@ -3710,7 +3730,7 @@
         <v>11</v>
       </c>
       <c r="E33" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="G33" t="s">
         <v>8</v>
@@ -3807,7 +3827,7 @@
         <v>10</v>
       </c>
       <c r="E37" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.25">
@@ -3875,7 +3895,7 @@
       </c>
       <c r="H40">
         <f>COUNTIFS(TestMaster[Test Status], "Pass", TestMaster[Namespace], G38)</f>
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.25">
@@ -3898,7 +3918,7 @@
       </c>
       <c r="H41">
         <f>COUNTIFS(TestMaster[Test Status], "Fail", TestMaster[Namespace], G38)</f>
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.25">
@@ -4062,7 +4082,7 @@
         <v>Get Attributes With Multiple Elements Returns List Of Attribute Lists</v>
       </c>
       <c r="C51" s="5" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E51" t="s">
         <v>17</v>
@@ -4364,7 +4384,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="19" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="B1" s="18"/>
       <c r="C1" s="18"/>
@@ -4503,7 +4523,7 @@
         <v>40</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>41</v>
+        <v>378</v>
       </c>
       <c r="D11" s="3" t="s">
         <v>42</v>
@@ -4530,13 +4550,13 @@
         <v>6</v>
       </c>
       <c r="B13" s="3" t="s">
+        <v>330</v>
+      </c>
+      <c r="C13" s="3" t="s">
         <v>331</v>
       </c>
-      <c r="C13" s="3" t="s">
+      <c r="D13" s="2" t="s">
         <v>332</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>333</v>
       </c>
     </row>
     <row r="14" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -4548,10 +4568,10 @@
         <v>40</v>
       </c>
       <c r="C14" s="3" t="s">
+        <v>333</v>
+      </c>
+      <c r="D14" s="3" t="s">
         <v>334</v>
-      </c>
-      <c r="D14" s="3" t="s">
-        <v>335</v>
       </c>
     </row>
     <row r="15" spans="1:6" ht="29.1" customHeight="1" x14ac:dyDescent="0.25">
@@ -4560,13 +4580,13 @@
         <v>8</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>339</v>
+        <v>385</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
     </row>
     <row r="16" spans="1:6" ht="30" x14ac:dyDescent="0.25">
@@ -4575,13 +4595,13 @@
         <v>9</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>338</v>
+        <v>379</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>54</v>
+        <v>38</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>42</v>
+        <v>380</v>
       </c>
     </row>
     <row r="17" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -4590,13 +4610,13 @@
         <v>10</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>43</v>
+        <v>337</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>58</v>
+        <v>384</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>59</v>
+        <v>383</v>
       </c>
     </row>
     <row r="18" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -4604,12 +4624,29 @@
         <f t="shared" si="0"/>
         <v>11</v>
       </c>
-      <c r="C18" s="3"/>
+      <c r="B18" s="3" t="s">
+        <v>381</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>382</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>42</v>
+      </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" s="4">
         <f t="shared" si="0"/>
         <v>12</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>58</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
@@ -4695,7 +4732,7 @@
   <sheetData>
     <row r="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A1" s="19" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B1" s="22"/>
       <c r="C1" s="22"/>
@@ -4703,7 +4740,7 @@
       <c r="E1" s="22"/>
       <c r="F1" s="21"/>
       <c r="G1" s="19" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="H1" s="22"/>
       <c r="I1" s="22"/>
@@ -4711,7 +4748,7 @@
       <c r="K1" s="22"/>
       <c r="L1" s="21"/>
       <c r="M1" s="17" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="N1" s="22"/>
       <c r="O1" s="22"/>
@@ -4808,14 +4845,14 @@
       </c>
       <c r="R3" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(M1, TestMaster[Test Name], TestMaster[Test Status], "Status not found"), "")</f>
-        <v>Fail</v>
+        <v>Pass</v>
       </c>
       <c r="T3" s="17"/>
       <c r="U3" s="22"/>
     </row>
     <row r="4" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A4" s="19" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B4" s="22"/>
       <c r="C4" s="22"/>
@@ -4823,7 +4860,7 @@
       <c r="E4" s="22"/>
       <c r="F4" s="21"/>
       <c r="G4" s="19" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="H4" s="22"/>
       <c r="I4" s="22"/>
@@ -4831,7 +4868,7 @@
       <c r="K4" s="22"/>
       <c r="L4" s="21"/>
       <c r="M4" s="17" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="N4" s="22"/>
       <c r="O4" s="22"/>
@@ -4970,10 +5007,10 @@
         <v>1</v>
       </c>
       <c r="B8" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="C8" s="3" t="s">
         <v>64</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>65</v>
       </c>
       <c r="D8" s="3" t="s">
         <v>36</v>
@@ -4982,10 +5019,10 @@
         <v>1</v>
       </c>
       <c r="H8" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="I8" s="3" t="s">
         <v>64</v>
-      </c>
-      <c r="I8" s="3" t="s">
-        <v>65</v>
       </c>
       <c r="J8" s="3" t="s">
         <v>36</v>
@@ -4994,10 +5031,10 @@
         <v>1</v>
       </c>
       <c r="N8" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="O8" s="3" t="s">
         <v>64</v>
-      </c>
-      <c r="O8" s="3" t="s">
-        <v>65</v>
       </c>
       <c r="P8" s="3" t="s">
         <v>36</v>
@@ -5023,10 +5060,10 @@
         <v>37</v>
       </c>
       <c r="I9" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="J9" s="3" t="s">
         <v>66</v>
-      </c>
-      <c r="J9" s="3" t="s">
-        <v>67</v>
       </c>
       <c r="M9" s="4">
         <v>2</v>
@@ -5046,7 +5083,7 @@
         <v>3</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C10" s="3" t="s">
         <v>41</v>
@@ -5058,10 +5095,10 @@
         <v>3</v>
       </c>
       <c r="H10" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="I10" s="3" t="s">
         <v>68</v>
-      </c>
-      <c r="I10" s="3" t="s">
-        <v>69</v>
       </c>
       <c r="J10" s="3" t="s">
         <v>48</v>
@@ -5070,7 +5107,7 @@
         <v>3</v>
       </c>
       <c r="N10" s="4" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="O10" s="3" t="s">
         <v>41</v>
@@ -5084,37 +5121,37 @@
         <v>4</v>
       </c>
       <c r="B11" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="C11" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="C11" s="3" t="s">
+      <c r="D11" s="3" t="s">
         <v>71</v>
-      </c>
-      <c r="D11" s="3" t="s">
-        <v>72</v>
       </c>
       <c r="G11" s="4">
         <v>4</v>
       </c>
       <c r="H11" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="I11" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="J11" s="3" t="s">
         <v>73</v>
-      </c>
-      <c r="I11" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="J11" s="3" t="s">
-        <v>74</v>
       </c>
       <c r="M11" s="4">
         <v>4</v>
       </c>
       <c r="N11" s="4" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="O11" s="3" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="P11" s="3" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="12" spans="1:25" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -5122,25 +5159,25 @@
         <v>5</v>
       </c>
       <c r="B12" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="C12" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="C12" s="3" t="s">
+      <c r="D12" s="3" t="s">
         <v>77</v>
-      </c>
-      <c r="D12" s="3" t="s">
-        <v>78</v>
       </c>
       <c r="M12" s="4">
         <v>5</v>
       </c>
       <c r="N12" s="4" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="O12" s="3" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="P12" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="13" spans="1:25" ht="29.1" customHeight="1" x14ac:dyDescent="0.25">
@@ -5148,25 +5185,25 @@
         <v>6</v>
       </c>
       <c r="B13" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="C13" s="3" t="s">
         <v>82</v>
       </c>
-      <c r="C13" s="3" t="s">
+      <c r="D13" s="3" t="s">
         <v>83</v>
-      </c>
-      <c r="D13" s="3" t="s">
-        <v>84</v>
       </c>
       <c r="M13" s="4">
         <v>6</v>
       </c>
       <c r="N13" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="O13" s="3" t="s">
+        <v>311</v>
+      </c>
+      <c r="P13" s="3" t="s">
         <v>85</v>
-      </c>
-      <c r="O13" s="3" t="s">
-        <v>312</v>
-      </c>
-      <c r="P13" s="3" t="s">
-        <v>86</v>
       </c>
     </row>
     <row r="14" spans="1:25" x14ac:dyDescent="0.25">
@@ -5180,7 +5217,7 @@
         <v>47</v>
       </c>
       <c r="P14" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="15" spans="1:25" ht="29.1" customHeight="1" x14ac:dyDescent="0.25">
@@ -5188,13 +5225,13 @@
         <v>8</v>
       </c>
       <c r="N15" s="4" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="O15" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="P15" s="3" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="16" spans="1:25" x14ac:dyDescent="0.25">
@@ -5216,13 +5253,13 @@
         <v>10</v>
       </c>
       <c r="N17" s="4" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="O17" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="P17" s="3" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="18" spans="13:16" x14ac:dyDescent="0.25">
@@ -5247,10 +5284,10 @@
         <v>53</v>
       </c>
       <c r="O19" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="P19" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
     </row>
     <row r="20" spans="13:16" x14ac:dyDescent="0.25">
@@ -5272,13 +5309,13 @@
         <v>14</v>
       </c>
       <c r="N21" t="s">
+        <v>54</v>
+      </c>
+      <c r="O21" t="s">
         <v>55</v>
       </c>
-      <c r="O21" t="s">
+      <c r="P21" t="s">
         <v>56</v>
-      </c>
-      <c r="P21" t="s">
-        <v>57</v>
       </c>
     </row>
     <row r="22" spans="13:16" x14ac:dyDescent="0.25">
@@ -5288,6 +5325,19 @@
     </row>
   </sheetData>
   <mergeCells count="20">
+    <mergeCell ref="T1:Y1"/>
+    <mergeCell ref="T4:Y5"/>
+    <mergeCell ref="A3:B3"/>
+    <mergeCell ref="G3:H3"/>
+    <mergeCell ref="T3:U3"/>
+    <mergeCell ref="G1:L1"/>
+    <mergeCell ref="G2:H2"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A6:F6"/>
+    <mergeCell ref="M1:R1"/>
+    <mergeCell ref="A4:F5"/>
+    <mergeCell ref="G4:L5"/>
+    <mergeCell ref="G6:L6"/>
     <mergeCell ref="M4:R5"/>
     <mergeCell ref="M6:R6"/>
     <mergeCell ref="M2:N2"/>
@@ -5295,19 +5345,6 @@
     <mergeCell ref="A2:B2"/>
     <mergeCell ref="T2:U2"/>
     <mergeCell ref="M3:N3"/>
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A6:F6"/>
-    <mergeCell ref="M1:R1"/>
-    <mergeCell ref="A4:F5"/>
-    <mergeCell ref="G4:L5"/>
-    <mergeCell ref="T1:Y1"/>
-    <mergeCell ref="T4:Y5"/>
-    <mergeCell ref="A3:B3"/>
-    <mergeCell ref="G3:H3"/>
-    <mergeCell ref="T3:U3"/>
-    <mergeCell ref="G1:L1"/>
-    <mergeCell ref="G2:H2"/>
-    <mergeCell ref="G6:L6"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -5340,7 +5377,7 @@
   <sheetData>
     <row r="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A1" s="19" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B1" s="18"/>
       <c r="C1" s="18"/>
@@ -5348,7 +5385,7 @@
       <c r="E1" s="18"/>
       <c r="F1" s="21"/>
       <c r="G1" s="23" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="H1" s="18"/>
       <c r="I1" s="18"/>
@@ -5356,7 +5393,7 @@
       <c r="K1" s="18"/>
       <c r="L1" s="21"/>
       <c r="M1" s="17" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="N1" s="18"/>
       <c r="O1" s="18"/>
@@ -5448,7 +5485,7 @@
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A4" s="19" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="B4" s="18"/>
       <c r="C4" s="18"/>
@@ -5456,7 +5493,7 @@
       <c r="E4" s="18"/>
       <c r="F4" s="21"/>
       <c r="G4" s="23" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="H4" s="18"/>
       <c r="I4" s="18"/>
@@ -5464,7 +5501,7 @@
       <c r="K4" s="18"/>
       <c r="L4" s="21"/>
       <c r="M4" s="17" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="N4" s="18"/>
       <c r="O4" s="18"/>
@@ -5579,31 +5616,31 @@
         <v>1</v>
       </c>
       <c r="B8" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="D8" s="4" t="s">
         <v>91</v>
-      </c>
-      <c r="C8" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="D8" s="4" t="s">
-        <v>92</v>
       </c>
       <c r="G8">
         <v>1</v>
       </c>
       <c r="H8" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="M8">
         <v>1</v>
       </c>
       <c r="N8" s="4" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="O8" s="4" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="P8" s="4" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="9" spans="1:18" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -5611,34 +5648,34 @@
         <v>2</v>
       </c>
       <c r="B9" t="s">
+        <v>327</v>
+      </c>
+      <c r="C9" t="s">
         <v>328</v>
-      </c>
-      <c r="C9" t="s">
-        <v>329</v>
       </c>
       <c r="G9">
         <v>2</v>
       </c>
       <c r="H9" s="4" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="I9" s="4" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="J9" s="4" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="M9">
         <v>2</v>
       </c>
       <c r="N9" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="O9" s="3" t="s">
         <v>95</v>
       </c>
-      <c r="O9" s="3" t="s">
+      <c r="P9" s="3" t="s">
         <v>96</v>
-      </c>
-      <c r="P9" s="3" t="s">
-        <v>97</v>
       </c>
     </row>
     <row r="10" spans="1:18" ht="29.1" customHeight="1" x14ac:dyDescent="0.25">
@@ -5646,37 +5683,37 @@
         <v>3</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="G10">
         <v>3</v>
       </c>
       <c r="H10" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="I10" s="3" t="s">
         <v>95</v>
       </c>
-      <c r="I10" s="3" t="s">
+      <c r="J10" s="3" t="s">
         <v>96</v>
-      </c>
-      <c r="J10" s="3" t="s">
-        <v>97</v>
       </c>
       <c r="M10">
         <v>3</v>
       </c>
       <c r="N10" s="3" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="O10" s="3" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="P10" s="3" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="11" spans="1:18" ht="30" x14ac:dyDescent="0.25">
@@ -5684,25 +5721,25 @@
         <v>4</v>
       </c>
       <c r="H11" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="I11" s="3" t="s">
+        <v>313</v>
+      </c>
+      <c r="J11" s="3" t="s">
         <v>98</v>
-      </c>
-      <c r="I11" s="3" t="s">
-        <v>314</v>
-      </c>
-      <c r="J11" s="3" t="s">
-        <v>99</v>
       </c>
       <c r="M11">
         <v>4</v>
       </c>
       <c r="N11" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="O11" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="P11" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="12" spans="1:18" x14ac:dyDescent="0.25">
@@ -5710,25 +5747,25 @@
         <v>5</v>
       </c>
       <c r="H12" t="s">
+        <v>99</v>
+      </c>
+      <c r="I12" t="s">
+        <v>314</v>
+      </c>
+      <c r="J12" t="s">
         <v>100</v>
-      </c>
-      <c r="I12" t="s">
-        <v>315</v>
-      </c>
-      <c r="J12" t="s">
-        <v>101</v>
       </c>
       <c r="M12">
         <v>5</v>
       </c>
       <c r="N12" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="O12" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="P12" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="13" spans="1:18" x14ac:dyDescent="0.25">
@@ -5736,13 +5773,13 @@
         <v>6</v>
       </c>
       <c r="H13" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="I13" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="J13" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="M13">
         <v>6</v>
@@ -5754,7 +5791,7 @@
         <v>47</v>
       </c>
       <c r="P13" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
     </row>
     <row r="14" spans="1:18" x14ac:dyDescent="0.25">
@@ -5762,13 +5799,13 @@
         <v>7</v>
       </c>
       <c r="H14" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="I14" t="s">
+        <v>102</v>
+      </c>
+      <c r="J14" t="s">
         <v>103</v>
-      </c>
-      <c r="J14" t="s">
-        <v>104</v>
       </c>
     </row>
     <row r="15" spans="1:18" x14ac:dyDescent="0.25">
@@ -5776,10 +5813,10 @@
         <v>8</v>
       </c>
       <c r="H15" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="I15" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
     </row>
     <row r="16" spans="1:18" x14ac:dyDescent="0.25">
@@ -5787,13 +5824,13 @@
         <v>9</v>
       </c>
       <c r="H16" t="s">
+        <v>317</v>
+      </c>
+      <c r="I16" t="s">
         <v>318</v>
       </c>
-      <c r="I16" t="s">
-        <v>319</v>
-      </c>
       <c r="J16" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="17" spans="7:10" x14ac:dyDescent="0.25">
@@ -5801,13 +5838,13 @@
         <v>10</v>
       </c>
       <c r="H17" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="I17" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="J17" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="18" spans="7:10" x14ac:dyDescent="0.25">
@@ -5815,13 +5852,13 @@
         <v>11</v>
       </c>
       <c r="H18" t="s">
+        <v>106</v>
+      </c>
+      <c r="I18" t="s">
         <v>107</v>
       </c>
-      <c r="I18" t="s">
-        <v>108</v>
-      </c>
       <c r="J18" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
     </row>
     <row r="19" spans="7:10" x14ac:dyDescent="0.25">
@@ -5829,13 +5866,13 @@
         <v>12</v>
       </c>
       <c r="H19" t="s">
+        <v>99</v>
+      </c>
+      <c r="I19" t="s">
+        <v>101</v>
+      </c>
+      <c r="J19" t="s">
         <v>100</v>
-      </c>
-      <c r="I19" t="s">
-        <v>102</v>
-      </c>
-      <c r="J19" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="20" spans="7:10" x14ac:dyDescent="0.25">
@@ -5843,10 +5880,10 @@
         <v>13</v>
       </c>
       <c r="H20" t="s">
+        <v>324</v>
+      </c>
+      <c r="I20" t="s">
         <v>325</v>
-      </c>
-      <c r="I20" t="s">
-        <v>326</v>
       </c>
     </row>
     <row r="21" spans="7:10" x14ac:dyDescent="0.25">
@@ -5854,13 +5891,13 @@
         <v>14</v>
       </c>
       <c r="H21" t="s">
+        <v>106</v>
+      </c>
+      <c r="I21" t="s">
         <v>107</v>
       </c>
-      <c r="I21" t="s">
-        <v>108</v>
-      </c>
       <c r="J21" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
   </sheetData>
@@ -5912,7 +5949,7 @@
   <sheetData>
     <row r="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A1" s="19" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B1" s="18"/>
       <c r="C1" s="18"/>
@@ -5920,7 +5957,7 @@
       <c r="E1" s="18"/>
       <c r="F1" s="21"/>
       <c r="G1" s="23" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="H1" s="18"/>
       <c r="I1" s="18"/>
@@ -5928,7 +5965,7 @@
       <c r="K1" s="18"/>
       <c r="L1" s="21"/>
       <c r="M1" s="17" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="N1" s="18"/>
       <c r="O1" s="18"/>
@@ -6020,7 +6057,7 @@
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A4" s="26" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B4" s="18"/>
       <c r="C4" s="18"/>
@@ -6028,7 +6065,7 @@
       <c r="E4" s="18"/>
       <c r="F4" s="21"/>
       <c r="G4" s="27" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="H4" s="18"/>
       <c r="I4" s="18"/>
@@ -6036,7 +6073,7 @@
       <c r="K4" s="18"/>
       <c r="L4" s="21"/>
       <c r="M4" s="25" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="N4" s="18"/>
       <c r="O4" s="18"/>
@@ -6066,7 +6103,7 @@
     </row>
     <row r="6" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A6" s="19" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B6" s="18"/>
       <c r="C6" s="18"/>
@@ -6074,7 +6111,7 @@
       <c r="E6" s="18"/>
       <c r="F6" s="21"/>
       <c r="G6" s="23" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="H6" s="18"/>
       <c r="I6" s="18"/>
@@ -6151,39 +6188,39 @@
         <v>1</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="F8" s="13"/>
       <c r="G8" s="3">
         <v>1</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="L8" s="13"/>
       <c r="M8" s="3">
         <v>1</v>
       </c>
       <c r="N8" s="3" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="O8" s="3" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="P8" s="3" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="9" spans="1:18" s="3" customFormat="1" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -6191,39 +6228,39 @@
         <v>2</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="F9" s="13"/>
       <c r="G9" s="3">
         <v>2</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="L9" s="13"/>
       <c r="M9" s="3">
         <v>2</v>
       </c>
       <c r="N9" s="3" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="O9" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="P9" s="3" t="s">
         <v>115</v>
-      </c>
-      <c r="P9" s="3" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="10" spans="1:18" s="3" customFormat="1" ht="29.1" customHeight="1" x14ac:dyDescent="0.25">
@@ -6232,26 +6269,26 @@
         <v>3</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="I10" s="3" t="s">
+        <v>304</v>
+      </c>
+      <c r="J10" s="3" t="s">
         <v>305</v>
-      </c>
-      <c r="J10" s="3" t="s">
-        <v>306</v>
       </c>
       <c r="L10" s="13"/>
       <c r="M10" s="3">
         <v>3</v>
       </c>
       <c r="N10" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="O10" s="3" t="s">
         <v>117</v>
       </c>
-      <c r="O10" s="3" t="s">
+      <c r="P10" s="3" t="s">
         <v>118</v>
-      </c>
-      <c r="P10" s="3" t="s">
-        <v>119</v>
       </c>
     </row>
     <row r="11" spans="1:18" ht="29.1" customHeight="1" x14ac:dyDescent="0.25">
@@ -6259,25 +6296,25 @@
         <v>4</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="I11" s="3" t="s">
+        <v>306</v>
+      </c>
+      <c r="J11" s="3" t="s">
         <v>307</v>
-      </c>
-      <c r="J11" s="3" t="s">
-        <v>308</v>
       </c>
       <c r="M11" s="3">
         <v>4</v>
       </c>
       <c r="N11" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="O11" s="3" t="s">
         <v>120</v>
       </c>
-      <c r="O11" s="3" t="s">
+      <c r="P11" s="3" t="s">
         <v>121</v>
-      </c>
-      <c r="P11" s="3" t="s">
-        <v>122</v>
       </c>
     </row>
   </sheetData>
@@ -6334,7 +6371,7 @@
   <sheetData>
     <row r="1" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A1" s="19" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B1" s="18"/>
       <c r="C1" s="18"/>
@@ -6342,7 +6379,7 @@
       <c r="E1" s="18"/>
       <c r="F1" s="21"/>
       <c r="G1" s="17" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="H1" s="18"/>
       <c r="I1" s="18"/>
@@ -6350,7 +6387,7 @@
       <c r="K1" s="18"/>
       <c r="L1" s="18"/>
       <c r="M1" s="23" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="N1" s="18"/>
       <c r="O1" s="18"/>
@@ -6358,7 +6395,7 @@
       <c r="Q1" s="18"/>
       <c r="R1" s="21"/>
       <c r="S1" s="28" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="T1" s="17"/>
       <c r="U1" s="17"/>
@@ -6478,7 +6515,7 @@
     </row>
     <row r="4" spans="1:24" s="2" customFormat="1" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="26" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B4" s="20"/>
       <c r="C4" s="20"/>
@@ -6486,7 +6523,7 @@
       <c r="E4" s="20"/>
       <c r="F4" s="21"/>
       <c r="G4" s="25" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="H4" s="20"/>
       <c r="I4" s="20"/>
@@ -6494,7 +6531,7 @@
       <c r="K4" s="20"/>
       <c r="L4" s="20"/>
       <c r="M4" s="27" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="N4" s="20"/>
       <c r="O4" s="20"/>
@@ -6502,7 +6539,7 @@
       <c r="Q4" s="20"/>
       <c r="R4" s="21"/>
       <c r="S4" s="27" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="T4" s="20"/>
       <c r="U4" s="20"/>
@@ -6538,7 +6575,7 @@
     </row>
     <row r="6" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A6" s="19" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B6" s="18"/>
       <c r="C6" s="18"/>
@@ -6546,7 +6583,7 @@
       <c r="E6" s="18"/>
       <c r="F6" s="21"/>
       <c r="G6" s="17" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="H6" s="18"/>
       <c r="I6" s="18"/>
@@ -6554,7 +6591,7 @@
       <c r="K6" s="18"/>
       <c r="L6" s="18"/>
       <c r="M6" s="23" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="N6" s="18"/>
       <c r="O6" s="18"/>
@@ -6562,7 +6599,7 @@
       <c r="Q6" s="18"/>
       <c r="R6" s="21"/>
       <c r="S6" s="23" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="T6" s="18"/>
       <c r="U6" s="18"/>
@@ -6649,50 +6686,50 @@
         <v>1</v>
       </c>
       <c r="B8" t="s">
+        <v>130</v>
+      </c>
+      <c r="C8" t="s">
         <v>131</v>
       </c>
-      <c r="C8" t="s">
+      <c r="D8" t="s">
         <v>132</v>
-      </c>
-      <c r="D8" t="s">
-        <v>133</v>
       </c>
       <c r="G8">
         <v>1</v>
       </c>
       <c r="H8" t="s">
+        <v>133</v>
+      </c>
+      <c r="I8" t="s">
         <v>134</v>
       </c>
-      <c r="I8" t="s">
+      <c r="J8" t="s">
         <v>135</v>
-      </c>
-      <c r="J8" t="s">
-        <v>136</v>
       </c>
       <c r="M8" s="15">
         <v>1</v>
       </c>
       <c r="N8" t="s">
+        <v>347</v>
+      </c>
+      <c r="O8" s="2" t="s">
         <v>348</v>
       </c>
-      <c r="O8" s="2" t="s">
+      <c r="P8" s="2" t="s">
         <v>349</v>
-      </c>
-      <c r="P8" s="2" t="s">
-        <v>350</v>
       </c>
       <c r="R8" s="7"/>
       <c r="S8" s="15">
         <v>1</v>
       </c>
       <c r="T8" s="4" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="U8" s="3" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="V8" s="4" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="X8" s="7"/>
     </row>
@@ -6701,86 +6738,86 @@
         <v>2</v>
       </c>
       <c r="B9" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C9" t="s">
+        <v>136</v>
+      </c>
+      <c r="D9" t="s">
         <v>137</v>
-      </c>
-      <c r="D9" t="s">
-        <v>138</v>
       </c>
       <c r="G9">
         <v>2</v>
       </c>
       <c r="H9" t="s">
+        <v>138</v>
+      </c>
+      <c r="I9" t="s">
         <v>139</v>
       </c>
-      <c r="I9" t="s">
+      <c r="J9" t="s">
         <v>140</v>
-      </c>
-      <c r="J9" t="s">
-        <v>141</v>
       </c>
       <c r="M9" s="15">
         <v>2</v>
       </c>
       <c r="N9" t="s">
+        <v>350</v>
+      </c>
+      <c r="O9" t="s">
         <v>351</v>
       </c>
-      <c r="O9" t="s">
+      <c r="P9" t="s">
         <v>352</v>
-      </c>
-      <c r="P9" t="s">
-        <v>353</v>
       </c>
       <c r="R9" s="7"/>
       <c r="S9" s="15">
         <v>2</v>
       </c>
       <c r="T9" s="3" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="U9" s="3" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="V9" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="X9" s="7"/>
     </row>
-    <row r="10" spans="1:24" ht="60" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:24" ht="45" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>3</v>
       </c>
       <c r="B10" t="s">
+        <v>141</v>
+      </c>
+      <c r="C10" t="s">
         <v>142</v>
       </c>
-      <c r="C10" t="s">
+      <c r="D10" t="s">
         <v>143</v>
-      </c>
-      <c r="D10" t="s">
-        <v>144</v>
       </c>
       <c r="G10">
         <v>3</v>
       </c>
       <c r="H10" t="s">
+        <v>144</v>
+      </c>
+      <c r="I10" t="s">
         <v>145</v>
       </c>
-      <c r="I10" t="s">
+      <c r="J10" t="s">
         <v>146</v>
-      </c>
-      <c r="J10" t="s">
-        <v>147</v>
       </c>
       <c r="M10" s="15">
         <v>3</v>
       </c>
       <c r="N10" t="s">
+        <v>353</v>
+      </c>
+      <c r="O10" t="s">
         <v>354</v>
-      </c>
-      <c r="O10" t="s">
-        <v>355</v>
       </c>
       <c r="P10" t="b">
         <v>1</v>
@@ -6790,10 +6827,10 @@
         <v>3</v>
       </c>
       <c r="T10" s="4" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="U10" s="3" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="V10" s="3" t="s">
         <v>48</v>
@@ -6805,50 +6842,50 @@
         <v>4</v>
       </c>
       <c r="B11" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="C11" s="2" t="s">
         <v>148</v>
       </c>
-      <c r="C11" s="2" t="s">
+      <c r="D11" t="s">
         <v>149</v>
-      </c>
-      <c r="D11" t="s">
-        <v>150</v>
       </c>
       <c r="G11">
         <v>4</v>
       </c>
       <c r="H11" t="s">
+        <v>150</v>
+      </c>
+      <c r="I11" t="s">
+        <v>64</v>
+      </c>
+      <c r="J11" t="s">
         <v>151</v>
-      </c>
-      <c r="I11" t="s">
-        <v>65</v>
-      </c>
-      <c r="J11" t="s">
-        <v>152</v>
       </c>
       <c r="M11" s="15">
         <v>4</v>
       </c>
       <c r="N11" s="2" t="s">
+        <v>355</v>
+      </c>
+      <c r="O11" s="2" t="s">
         <v>356</v>
       </c>
-      <c r="O11" s="2" t="s">
+      <c r="P11" s="2" t="s">
         <v>357</v>
-      </c>
-      <c r="P11" s="2" t="s">
-        <v>358</v>
       </c>
       <c r="R11" s="7"/>
       <c r="S11" s="4">
         <v>4</v>
       </c>
       <c r="T11" s="4" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="U11" s="3" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="V11" s="3" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="X11" s="7"/>
     </row>
@@ -6857,29 +6894,29 @@
         <v>5</v>
       </c>
       <c r="B12" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="D12" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="M12" s="15">
         <v>5</v>
       </c>
       <c r="N12" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="R12" s="7"/>
       <c r="S12" s="4">
         <v>5</v>
       </c>
       <c r="T12" s="4" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="U12" s="3" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="V12" s="3" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="X12" s="7"/>
     </row>
@@ -6888,26 +6925,26 @@
         <v>6</v>
       </c>
       <c r="B13" t="s">
+        <v>153</v>
+      </c>
+      <c r="C13" t="s">
         <v>154</v>
       </c>
-      <c r="C13" t="s">
-        <v>155</v>
-      </c>
       <c r="D13" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="R13" s="7"/>
       <c r="S13" s="4">
         <v>6</v>
       </c>
       <c r="T13" s="4" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="U13" s="3" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="V13" s="3" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="X13" s="7"/>
     </row>
@@ -6916,23 +6953,23 @@
         <v>7</v>
       </c>
       <c r="B14" t="s">
+        <v>155</v>
+      </c>
+      <c r="C14" t="s">
         <v>156</v>
-      </c>
-      <c r="C14" t="s">
-        <v>157</v>
       </c>
       <c r="R14" s="7"/>
       <c r="S14" s="4">
         <v>7</v>
       </c>
       <c r="T14" s="4" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="U14" s="3" t="s">
+        <v>372</v>
+      </c>
+      <c r="V14" s="3" t="s">
         <v>373</v>
-      </c>
-      <c r="V14" s="3" t="s">
-        <v>374</v>
       </c>
       <c r="X14" s="7"/>
     </row>
@@ -6941,26 +6978,26 @@
         <v>8</v>
       </c>
       <c r="B15" t="s">
+        <v>157</v>
+      </c>
+      <c r="C15" t="s">
+        <v>57</v>
+      </c>
+      <c r="D15" t="s">
         <v>158</v>
-      </c>
-      <c r="C15" t="s">
-        <v>58</v>
-      </c>
-      <c r="D15" t="s">
-        <v>159</v>
       </c>
       <c r="R15" s="7"/>
       <c r="S15" s="4">
         <v>8</v>
       </c>
       <c r="T15" s="4" t="s">
+        <v>374</v>
+      </c>
+      <c r="U15" s="3" t="s">
         <v>375</v>
       </c>
-      <c r="U15" s="3" t="s">
-        <v>376</v>
-      </c>
       <c r="V15" s="3" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="X15" s="7"/>
     </row>
@@ -6969,13 +7006,13 @@
         <v>9</v>
       </c>
       <c r="B16" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C16" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="D16" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="R16" s="7"/>
       <c r="X16" s="7"/>
@@ -6985,13 +7022,13 @@
         <v>10</v>
       </c>
       <c r="B17" t="s">
+        <v>160</v>
+      </c>
+      <c r="C17" t="s">
         <v>161</v>
       </c>
-      <c r="C17" t="s">
+      <c r="D17" t="s">
         <v>162</v>
-      </c>
-      <c r="D17" t="s">
-        <v>163</v>
       </c>
       <c r="R17" s="7"/>
       <c r="X17" s="7"/>
@@ -7001,13 +7038,13 @@
         <v>11</v>
       </c>
       <c r="B18" t="s">
+        <v>163</v>
+      </c>
+      <c r="C18" s="2" t="s">
         <v>164</v>
       </c>
-      <c r="C18" s="2" t="s">
+      <c r="D18" s="2" t="s">
         <v>165</v>
-      </c>
-      <c r="D18" s="2" t="s">
-        <v>166</v>
       </c>
     </row>
     <row r="19" spans="1:24" x14ac:dyDescent="0.25">
@@ -7015,13 +7052,13 @@
         <v>12</v>
       </c>
       <c r="B19" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C19" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D19" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
     <row r="20" spans="1:24" x14ac:dyDescent="0.25">
@@ -7029,13 +7066,13 @@
         <v>13</v>
       </c>
       <c r="B20" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C20" t="s">
         <v>44</v>
       </c>
       <c r="D20" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="21" spans="1:24" x14ac:dyDescent="0.25">
@@ -7043,17 +7080,22 @@
         <v>14</v>
       </c>
       <c r="B21" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C21" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="D21" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="20">
+    <mergeCell ref="S2:T2"/>
+    <mergeCell ref="S3:T3"/>
+    <mergeCell ref="S4:X5"/>
+    <mergeCell ref="S6:X6"/>
+    <mergeCell ref="S1:X1"/>
     <mergeCell ref="G1:L1"/>
     <mergeCell ref="M2:N2"/>
     <mergeCell ref="A2:B2"/>
@@ -7069,11 +7111,6 @@
     <mergeCell ref="A3:B3"/>
     <mergeCell ref="G3:H3"/>
     <mergeCell ref="M6:R6"/>
-    <mergeCell ref="S2:T2"/>
-    <mergeCell ref="S3:T3"/>
-    <mergeCell ref="S4:X5"/>
-    <mergeCell ref="S6:X6"/>
-    <mergeCell ref="S1:X1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -7110,184 +7147,184 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:160" x14ac:dyDescent="0.25">
-      <c r="A1" s="30" t="s">
-        <v>168</v>
+      <c r="A1" s="29" t="s">
+        <v>167</v>
       </c>
       <c r="B1" s="18"/>
       <c r="C1" s="18"/>
       <c r="D1" s="18"/>
       <c r="E1" s="18"/>
       <c r="F1" s="18"/>
-      <c r="H1" s="30" t="s">
-        <v>169</v>
+      <c r="H1" s="29" t="s">
+        <v>168</v>
       </c>
       <c r="I1" s="18"/>
       <c r="J1" s="18"/>
       <c r="K1" s="18"/>
       <c r="L1" s="18"/>
       <c r="M1" s="18"/>
-      <c r="O1" s="30" t="s">
-        <v>170</v>
+      <c r="O1" s="29" t="s">
+        <v>169</v>
       </c>
       <c r="P1" s="18"/>
       <c r="Q1" s="18"/>
       <c r="R1" s="18"/>
       <c r="S1" s="18"/>
       <c r="T1" s="18"/>
-      <c r="V1" s="30" t="s">
-        <v>171</v>
+      <c r="V1" s="29" t="s">
+        <v>170</v>
       </c>
       <c r="W1" s="18"/>
       <c r="X1" s="18"/>
       <c r="Y1" s="18"/>
       <c r="Z1" s="18"/>
       <c r="AA1" s="18"/>
-      <c r="AC1" s="30" t="s">
-        <v>172</v>
+      <c r="AC1" s="29" t="s">
+        <v>171</v>
       </c>
       <c r="AD1" s="18"/>
       <c r="AE1" s="18"/>
       <c r="AF1" s="18"/>
       <c r="AG1" s="18"/>
       <c r="AH1" s="18"/>
-      <c r="AJ1" s="30" t="s">
-        <v>173</v>
+      <c r="AJ1" s="29" t="s">
+        <v>172</v>
       </c>
       <c r="AK1" s="18"/>
       <c r="AL1" s="18"/>
       <c r="AM1" s="18"/>
       <c r="AN1" s="18"/>
       <c r="AO1" s="18"/>
-      <c r="AQ1" s="30" t="s">
-        <v>174</v>
+      <c r="AQ1" s="29" t="s">
+        <v>173</v>
       </c>
       <c r="AR1" s="18"/>
       <c r="AS1" s="18"/>
       <c r="AT1" s="18"/>
       <c r="AU1" s="18"/>
       <c r="AV1" s="18"/>
-      <c r="AX1" s="30" t="s">
-        <v>175</v>
+      <c r="AX1" s="29" t="s">
+        <v>174</v>
       </c>
       <c r="AY1" s="18"/>
       <c r="AZ1" s="18"/>
       <c r="BA1" s="18"/>
       <c r="BB1" s="18"/>
       <c r="BC1" s="18"/>
-      <c r="BE1" s="30" t="s">
-        <v>176</v>
+      <c r="BE1" s="29" t="s">
+        <v>175</v>
       </c>
       <c r="BF1" s="18"/>
       <c r="BG1" s="18"/>
       <c r="BH1" s="18"/>
       <c r="BI1" s="18"/>
       <c r="BJ1" s="18"/>
-      <c r="BL1" s="30" t="s">
-        <v>177</v>
+      <c r="BL1" s="29" t="s">
+        <v>176</v>
       </c>
       <c r="BM1" s="18"/>
       <c r="BN1" s="18"/>
       <c r="BO1" s="18"/>
       <c r="BP1" s="18"/>
       <c r="BQ1" s="18"/>
-      <c r="BS1" s="30" t="s">
-        <v>178</v>
+      <c r="BS1" s="29" t="s">
+        <v>177</v>
       </c>
       <c r="BT1" s="18"/>
       <c r="BU1" s="18"/>
       <c r="BV1" s="18"/>
       <c r="BW1" s="18"/>
       <c r="BX1" s="18"/>
-      <c r="BZ1" s="30" t="s">
-        <v>179</v>
+      <c r="BZ1" s="29" t="s">
+        <v>178</v>
       </c>
       <c r="CA1" s="18"/>
       <c r="CB1" s="18"/>
       <c r="CC1" s="18"/>
       <c r="CD1" s="18"/>
       <c r="CE1" s="18"/>
-      <c r="CG1" s="30" t="s">
-        <v>180</v>
+      <c r="CG1" s="29" t="s">
+        <v>179</v>
       </c>
       <c r="CH1" s="18"/>
       <c r="CI1" s="18"/>
       <c r="CJ1" s="18"/>
       <c r="CK1" s="18"/>
       <c r="CL1" s="18"/>
-      <c r="CN1" s="30" t="s">
-        <v>181</v>
+      <c r="CN1" s="29" t="s">
+        <v>180</v>
       </c>
       <c r="CO1" s="18"/>
       <c r="CP1" s="18"/>
       <c r="CQ1" s="18"/>
       <c r="CR1" s="18"/>
       <c r="CS1" s="18"/>
-      <c r="CU1" s="30" t="s">
-        <v>182</v>
+      <c r="CU1" s="29" t="s">
+        <v>181</v>
       </c>
       <c r="CV1" s="18"/>
       <c r="CW1" s="18"/>
       <c r="CX1" s="18"/>
       <c r="CY1" s="18"/>
       <c r="CZ1" s="18"/>
-      <c r="DB1" s="30" t="s">
-        <v>183</v>
+      <c r="DB1" s="29" t="s">
+        <v>182</v>
       </c>
       <c r="DC1" s="18"/>
       <c r="DD1" s="18"/>
       <c r="DE1" s="18"/>
       <c r="DF1" s="18"/>
       <c r="DG1" s="18"/>
-      <c r="DI1" s="30" t="s">
-        <v>184</v>
+      <c r="DI1" s="29" t="s">
+        <v>183</v>
       </c>
       <c r="DJ1" s="18"/>
       <c r="DK1" s="18"/>
       <c r="DL1" s="18"/>
       <c r="DM1" s="18"/>
       <c r="DN1" s="18"/>
-      <c r="DP1" s="30" t="s">
-        <v>185</v>
+      <c r="DP1" s="29" t="s">
+        <v>184</v>
       </c>
       <c r="DQ1" s="18"/>
       <c r="DR1" s="18"/>
       <c r="DS1" s="18"/>
       <c r="DT1" s="18"/>
       <c r="DU1" s="18"/>
-      <c r="DW1" s="30" t="s">
-        <v>186</v>
+      <c r="DW1" s="29" t="s">
+        <v>185</v>
       </c>
       <c r="DX1" s="18"/>
       <c r="DY1" s="18"/>
       <c r="DZ1" s="18"/>
       <c r="EA1" s="18"/>
       <c r="EB1" s="18"/>
-      <c r="ED1" s="30" t="s">
-        <v>187</v>
+      <c r="ED1" s="29" t="s">
+        <v>186</v>
       </c>
       <c r="EE1" s="18"/>
       <c r="EF1" s="18"/>
       <c r="EG1" s="18"/>
       <c r="EH1" s="18"/>
       <c r="EI1" s="18"/>
-      <c r="EK1" s="30" t="s">
-        <v>188</v>
+      <c r="EK1" s="29" t="s">
+        <v>187</v>
       </c>
       <c r="EL1" s="18"/>
       <c r="EM1" s="18"/>
       <c r="EN1" s="18"/>
       <c r="EO1" s="18"/>
       <c r="EP1" s="18"/>
-      <c r="ER1" s="30" t="s">
-        <v>189</v>
+      <c r="ER1" s="29" t="s">
+        <v>188</v>
       </c>
       <c r="ES1" s="18"/>
       <c r="ET1" s="18"/>
       <c r="EU1" s="18"/>
       <c r="EV1" s="18"/>
       <c r="EW1" s="18"/>
-      <c r="EY1" s="30" t="s">
-        <v>190</v>
+      <c r="EY1" s="29" t="s">
+        <v>189</v>
       </c>
       <c r="EZ1" s="18"/>
       <c r="FA1" s="18"/>
@@ -7880,230 +7917,230 @@
     </row>
     <row r="6" spans="1:160" x14ac:dyDescent="0.25">
       <c r="A6" s="16" t="s">
-        <v>63</v>
-      </c>
-      <c r="B6" s="29" t="s">
-        <v>191</v>
+        <v>62</v>
+      </c>
+      <c r="B6" s="30" t="s">
+        <v>190</v>
       </c>
       <c r="C6" s="18"/>
       <c r="D6" s="18"/>
       <c r="E6" s="18"/>
       <c r="F6" s="18"/>
       <c r="H6" s="16" t="s">
-        <v>63</v>
-      </c>
-      <c r="I6" s="29" t="s">
-        <v>192</v>
+        <v>62</v>
+      </c>
+      <c r="I6" s="30" t="s">
+        <v>191</v>
       </c>
       <c r="J6" s="18"/>
       <c r="K6" s="18"/>
       <c r="L6" s="18"/>
       <c r="M6" s="18"/>
       <c r="O6" s="16" t="s">
-        <v>63</v>
-      </c>
-      <c r="P6" s="29" t="s">
-        <v>193</v>
+        <v>62</v>
+      </c>
+      <c r="P6" s="30" t="s">
+        <v>192</v>
       </c>
       <c r="Q6" s="18"/>
       <c r="R6" s="18"/>
       <c r="S6" s="18"/>
       <c r="T6" s="18"/>
       <c r="V6" s="16" t="s">
-        <v>63</v>
-      </c>
-      <c r="W6" s="29" t="s">
-        <v>194</v>
+        <v>62</v>
+      </c>
+      <c r="W6" s="30" t="s">
+        <v>193</v>
       </c>
       <c r="X6" s="18"/>
       <c r="Y6" s="18"/>
       <c r="Z6" s="18"/>
       <c r="AA6" s="18"/>
       <c r="AC6" s="16" t="s">
-        <v>63</v>
-      </c>
-      <c r="AD6" s="29" t="s">
-        <v>195</v>
+        <v>62</v>
+      </c>
+      <c r="AD6" s="30" t="s">
+        <v>194</v>
       </c>
       <c r="AE6" s="18"/>
       <c r="AF6" s="18"/>
       <c r="AG6" s="18"/>
       <c r="AH6" s="18"/>
       <c r="AJ6" s="16" t="s">
-        <v>63</v>
-      </c>
-      <c r="AK6" s="29" t="s">
-        <v>196</v>
+        <v>62</v>
+      </c>
+      <c r="AK6" s="30" t="s">
+        <v>195</v>
       </c>
       <c r="AL6" s="18"/>
       <c r="AM6" s="18"/>
       <c r="AN6" s="18"/>
       <c r="AO6" s="18"/>
       <c r="AQ6" s="16" t="s">
-        <v>63</v>
-      </c>
-      <c r="AR6" s="29" t="s">
-        <v>197</v>
+        <v>62</v>
+      </c>
+      <c r="AR6" s="30" t="s">
+        <v>196</v>
       </c>
       <c r="AS6" s="18"/>
       <c r="AT6" s="18"/>
       <c r="AU6" s="18"/>
       <c r="AV6" s="18"/>
       <c r="AX6" s="16" t="s">
-        <v>63</v>
-      </c>
-      <c r="AY6" s="29" t="s">
-        <v>198</v>
+        <v>62</v>
+      </c>
+      <c r="AY6" s="30" t="s">
+        <v>197</v>
       </c>
       <c r="AZ6" s="18"/>
       <c r="BA6" s="18"/>
       <c r="BB6" s="18"/>
       <c r="BC6" s="18"/>
       <c r="BE6" s="16" t="s">
-        <v>63</v>
-      </c>
-      <c r="BF6" s="29" t="s">
-        <v>199</v>
+        <v>62</v>
+      </c>
+      <c r="BF6" s="30" t="s">
+        <v>198</v>
       </c>
       <c r="BG6" s="18"/>
       <c r="BH6" s="18"/>
       <c r="BI6" s="18"/>
       <c r="BJ6" s="18"/>
       <c r="BL6" s="16" t="s">
-        <v>63</v>
-      </c>
-      <c r="BM6" s="29" t="s">
-        <v>200</v>
+        <v>62</v>
+      </c>
+      <c r="BM6" s="30" t="s">
+        <v>199</v>
       </c>
       <c r="BN6" s="18"/>
       <c r="BO6" s="18"/>
       <c r="BP6" s="18"/>
       <c r="BQ6" s="18"/>
       <c r="BS6" s="16" t="s">
-        <v>63</v>
-      </c>
-      <c r="BT6" s="29" t="s">
-        <v>201</v>
+        <v>62</v>
+      </c>
+      <c r="BT6" s="30" t="s">
+        <v>200</v>
       </c>
       <c r="BU6" s="18"/>
       <c r="BV6" s="18"/>
       <c r="BW6" s="18"/>
       <c r="BX6" s="18"/>
       <c r="BZ6" s="16" t="s">
-        <v>63</v>
-      </c>
-      <c r="CA6" s="29" t="s">
-        <v>202</v>
+        <v>62</v>
+      </c>
+      <c r="CA6" s="30" t="s">
+        <v>201</v>
       </c>
       <c r="CB6" s="18"/>
       <c r="CC6" s="18"/>
       <c r="CD6" s="18"/>
       <c r="CE6" s="18"/>
       <c r="CG6" s="16" t="s">
-        <v>63</v>
-      </c>
-      <c r="CH6" s="29" t="s">
-        <v>203</v>
+        <v>62</v>
+      </c>
+      <c r="CH6" s="30" t="s">
+        <v>202</v>
       </c>
       <c r="CI6" s="18"/>
       <c r="CJ6" s="18"/>
       <c r="CK6" s="18"/>
       <c r="CL6" s="18"/>
       <c r="CN6" s="16" t="s">
-        <v>63</v>
-      </c>
-      <c r="CO6" s="29" t="s">
-        <v>204</v>
+        <v>62</v>
+      </c>
+      <c r="CO6" s="30" t="s">
+        <v>203</v>
       </c>
       <c r="CP6" s="18"/>
       <c r="CQ6" s="18"/>
       <c r="CR6" s="18"/>
       <c r="CS6" s="18"/>
       <c r="CU6" s="16" t="s">
-        <v>63</v>
-      </c>
-      <c r="CV6" s="29" t="s">
-        <v>205</v>
+        <v>62</v>
+      </c>
+      <c r="CV6" s="30" t="s">
+        <v>204</v>
       </c>
       <c r="CW6" s="18"/>
       <c r="CX6" s="18"/>
       <c r="CY6" s="18"/>
       <c r="CZ6" s="18"/>
       <c r="DB6" s="16" t="s">
-        <v>63</v>
-      </c>
-      <c r="DC6" s="29" t="s">
-        <v>206</v>
+        <v>62</v>
+      </c>
+      <c r="DC6" s="30" t="s">
+        <v>205</v>
       </c>
       <c r="DD6" s="18"/>
       <c r="DE6" s="18"/>
       <c r="DF6" s="18"/>
       <c r="DG6" s="18"/>
       <c r="DI6" s="16" t="s">
-        <v>63</v>
-      </c>
-      <c r="DJ6" s="29" t="s">
-        <v>207</v>
+        <v>62</v>
+      </c>
+      <c r="DJ6" s="30" t="s">
+        <v>206</v>
       </c>
       <c r="DK6" s="18"/>
       <c r="DL6" s="18"/>
       <c r="DM6" s="18"/>
       <c r="DN6" s="18"/>
       <c r="DP6" s="16" t="s">
-        <v>63</v>
-      </c>
-      <c r="DQ6" s="29" t="s">
-        <v>208</v>
+        <v>62</v>
+      </c>
+      <c r="DQ6" s="30" t="s">
+        <v>207</v>
       </c>
       <c r="DR6" s="18"/>
       <c r="DS6" s="18"/>
       <c r="DT6" s="18"/>
       <c r="DU6" s="18"/>
       <c r="DW6" s="16" t="s">
-        <v>63</v>
-      </c>
-      <c r="DX6" s="29" t="s">
-        <v>209</v>
+        <v>62</v>
+      </c>
+      <c r="DX6" s="30" t="s">
+        <v>208</v>
       </c>
       <c r="DY6" s="18"/>
       <c r="DZ6" s="18"/>
       <c r="EA6" s="18"/>
       <c r="EB6" s="18"/>
       <c r="ED6" s="16" t="s">
-        <v>63</v>
-      </c>
-      <c r="EE6" s="29" t="s">
-        <v>210</v>
+        <v>62</v>
+      </c>
+      <c r="EE6" s="30" t="s">
+        <v>209</v>
       </c>
       <c r="EF6" s="18"/>
       <c r="EG6" s="18"/>
       <c r="EH6" s="18"/>
       <c r="EI6" s="18"/>
       <c r="EK6" s="16" t="s">
-        <v>63</v>
-      </c>
-      <c r="EL6" s="29" t="s">
-        <v>211</v>
+        <v>62</v>
+      </c>
+      <c r="EL6" s="30" t="s">
+        <v>210</v>
       </c>
       <c r="EM6" s="18"/>
       <c r="EN6" s="18"/>
       <c r="EO6" s="18"/>
       <c r="EP6" s="18"/>
       <c r="ER6" s="16" t="s">
-        <v>63</v>
-      </c>
-      <c r="ES6" s="29" t="s">
-        <v>212</v>
+        <v>62</v>
+      </c>
+      <c r="ES6" s="30" t="s">
+        <v>211</v>
       </c>
       <c r="ET6" s="18"/>
       <c r="EU6" s="18"/>
       <c r="EV6" s="18"/>
       <c r="EW6" s="18"/>
       <c r="EY6" s="16" t="s">
-        <v>63</v>
-      </c>
-      <c r="EZ6" s="29" t="s">
-        <v>213</v>
+        <v>62</v>
+      </c>
+      <c r="EZ6" s="30" t="s">
+        <v>212</v>
       </c>
       <c r="FA6" s="18"/>
       <c r="FB6" s="18"/>
@@ -8114,8 +8151,8 @@
       <c r="A7" s="16" t="s">
         <v>24</v>
       </c>
-      <c r="B7" s="29" t="s">
-        <v>214</v>
+      <c r="B7" s="30" t="s">
+        <v>213</v>
       </c>
       <c r="C7" s="18"/>
       <c r="D7" s="18"/>
@@ -8124,8 +8161,8 @@
       <c r="H7" s="16" t="s">
         <v>24</v>
       </c>
-      <c r="I7" s="29" t="s">
-        <v>214</v>
+      <c r="I7" s="30" t="s">
+        <v>213</v>
       </c>
       <c r="J7" s="18"/>
       <c r="K7" s="18"/>
@@ -8134,8 +8171,8 @@
       <c r="O7" s="16" t="s">
         <v>24</v>
       </c>
-      <c r="P7" s="29" t="s">
-        <v>214</v>
+      <c r="P7" s="30" t="s">
+        <v>213</v>
       </c>
       <c r="Q7" s="18"/>
       <c r="R7" s="18"/>
@@ -8144,8 +8181,8 @@
       <c r="V7" s="16" t="s">
         <v>24</v>
       </c>
-      <c r="W7" s="29" t="s">
-        <v>214</v>
+      <c r="W7" s="30" t="s">
+        <v>213</v>
       </c>
       <c r="X7" s="18"/>
       <c r="Y7" s="18"/>
@@ -8154,8 +8191,8 @@
       <c r="AC7" s="16" t="s">
         <v>24</v>
       </c>
-      <c r="AD7" s="29" t="s">
-        <v>214</v>
+      <c r="AD7" s="30" t="s">
+        <v>213</v>
       </c>
       <c r="AE7" s="18"/>
       <c r="AF7" s="18"/>
@@ -8164,8 +8201,8 @@
       <c r="AJ7" s="16" t="s">
         <v>24</v>
       </c>
-      <c r="AK7" s="29" t="s">
-        <v>214</v>
+      <c r="AK7" s="30" t="s">
+        <v>213</v>
       </c>
       <c r="AL7" s="18"/>
       <c r="AM7" s="18"/>
@@ -8174,8 +8211,8 @@
       <c r="AQ7" s="16" t="s">
         <v>24</v>
       </c>
-      <c r="AR7" s="29" t="s">
-        <v>214</v>
+      <c r="AR7" s="30" t="s">
+        <v>213</v>
       </c>
       <c r="AS7" s="18"/>
       <c r="AT7" s="18"/>
@@ -8184,8 +8221,8 @@
       <c r="AX7" s="16" t="s">
         <v>24</v>
       </c>
-      <c r="AY7" s="29" t="s">
-        <v>214</v>
+      <c r="AY7" s="30" t="s">
+        <v>213</v>
       </c>
       <c r="AZ7" s="18"/>
       <c r="BA7" s="18"/>
@@ -8194,8 +8231,8 @@
       <c r="BE7" s="16" t="s">
         <v>24</v>
       </c>
-      <c r="BF7" s="29" t="s">
-        <v>214</v>
+      <c r="BF7" s="30" t="s">
+        <v>213</v>
       </c>
       <c r="BG7" s="18"/>
       <c r="BH7" s="18"/>
@@ -8204,8 +8241,8 @@
       <c r="BL7" s="16" t="s">
         <v>24</v>
       </c>
-      <c r="BM7" s="29" t="s">
-        <v>214</v>
+      <c r="BM7" s="30" t="s">
+        <v>213</v>
       </c>
       <c r="BN7" s="18"/>
       <c r="BO7" s="18"/>
@@ -8214,8 +8251,8 @@
       <c r="BS7" s="16" t="s">
         <v>24</v>
       </c>
-      <c r="BT7" s="29" t="s">
-        <v>214</v>
+      <c r="BT7" s="30" t="s">
+        <v>213</v>
       </c>
       <c r="BU7" s="18"/>
       <c r="BV7" s="18"/>
@@ -8224,8 +8261,8 @@
       <c r="BZ7" s="16" t="s">
         <v>24</v>
       </c>
-      <c r="CA7" s="29" t="s">
-        <v>214</v>
+      <c r="CA7" s="30" t="s">
+        <v>213</v>
       </c>
       <c r="CB7" s="18"/>
       <c r="CC7" s="18"/>
@@ -8234,8 +8271,8 @@
       <c r="CG7" s="16" t="s">
         <v>24</v>
       </c>
-      <c r="CH7" s="29" t="s">
-        <v>214</v>
+      <c r="CH7" s="30" t="s">
+        <v>213</v>
       </c>
       <c r="CI7" s="18"/>
       <c r="CJ7" s="18"/>
@@ -8244,8 +8281,8 @@
       <c r="CN7" s="16" t="s">
         <v>24</v>
       </c>
-      <c r="CO7" s="29" t="s">
-        <v>214</v>
+      <c r="CO7" s="30" t="s">
+        <v>213</v>
       </c>
       <c r="CP7" s="18"/>
       <c r="CQ7" s="18"/>
@@ -8254,8 +8291,8 @@
       <c r="CU7" s="16" t="s">
         <v>24</v>
       </c>
-      <c r="CV7" s="29" t="s">
-        <v>214</v>
+      <c r="CV7" s="30" t="s">
+        <v>213</v>
       </c>
       <c r="CW7" s="18"/>
       <c r="CX7" s="18"/>
@@ -8264,8 +8301,8 @@
       <c r="DB7" s="16" t="s">
         <v>24</v>
       </c>
-      <c r="DC7" s="29" t="s">
-        <v>214</v>
+      <c r="DC7" s="30" t="s">
+        <v>213</v>
       </c>
       <c r="DD7" s="18"/>
       <c r="DE7" s="18"/>
@@ -8274,8 +8311,8 @@
       <c r="DI7" s="16" t="s">
         <v>24</v>
       </c>
-      <c r="DJ7" s="29" t="s">
-        <v>214</v>
+      <c r="DJ7" s="30" t="s">
+        <v>213</v>
       </c>
       <c r="DK7" s="18"/>
       <c r="DL7" s="18"/>
@@ -8284,8 +8321,8 @@
       <c r="DP7" s="16" t="s">
         <v>24</v>
       </c>
-      <c r="DQ7" s="29" t="s">
-        <v>214</v>
+      <c r="DQ7" s="30" t="s">
+        <v>213</v>
       </c>
       <c r="DR7" s="18"/>
       <c r="DS7" s="18"/>
@@ -8294,8 +8331,8 @@
       <c r="DW7" s="16" t="s">
         <v>24</v>
       </c>
-      <c r="DX7" s="29" t="s">
-        <v>214</v>
+      <c r="DX7" s="30" t="s">
+        <v>213</v>
       </c>
       <c r="DY7" s="18"/>
       <c r="DZ7" s="18"/>
@@ -8304,8 +8341,8 @@
       <c r="ED7" s="16" t="s">
         <v>24</v>
       </c>
-      <c r="EE7" s="29" t="s">
-        <v>214</v>
+      <c r="EE7" s="30" t="s">
+        <v>213</v>
       </c>
       <c r="EF7" s="18"/>
       <c r="EG7" s="18"/>
@@ -8314,8 +8351,8 @@
       <c r="EK7" s="16" t="s">
         <v>24</v>
       </c>
-      <c r="EL7" s="29" t="s">
-        <v>214</v>
+      <c r="EL7" s="30" t="s">
+        <v>213</v>
       </c>
       <c r="EM7" s="18"/>
       <c r="EN7" s="18"/>
@@ -8324,8 +8361,8 @@
       <c r="ER7" s="16" t="s">
         <v>24</v>
       </c>
-      <c r="ES7" s="29" t="s">
-        <v>214</v>
+      <c r="ES7" s="30" t="s">
+        <v>213</v>
       </c>
       <c r="ET7" s="18"/>
       <c r="EU7" s="18"/>
@@ -8334,8 +8371,8 @@
       <c r="EY7" s="16" t="s">
         <v>24</v>
       </c>
-      <c r="EZ7" s="29" t="s">
-        <v>214</v>
+      <c r="EZ7" s="30" t="s">
+        <v>213</v>
       </c>
       <c r="FA7" s="18"/>
       <c r="FB7" s="18"/>
@@ -8760,886 +8797,939 @@
     </row>
     <row r="9" spans="1:160" ht="29.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="16" t="s">
+        <v>214</v>
+      </c>
+      <c r="B9" s="16" t="s">
         <v>215</v>
       </c>
-      <c r="B9" s="16" t="s">
+      <c r="C9" s="16" t="s">
         <v>216</v>
       </c>
-      <c r="C9" s="16" t="s">
+      <c r="D9" s="16" t="s">
         <v>217</v>
-      </c>
-      <c r="D9" s="16" t="s">
-        <v>218</v>
       </c>
       <c r="E9" s="16"/>
       <c r="F9" s="16"/>
       <c r="H9" s="16" t="s">
+        <v>214</v>
+      </c>
+      <c r="I9" s="16" t="s">
         <v>215</v>
       </c>
-      <c r="I9" s="16" t="s">
+      <c r="J9" s="16" t="s">
         <v>216</v>
       </c>
-      <c r="J9" s="16" t="s">
+      <c r="K9" s="16" t="s">
         <v>217</v>
-      </c>
-      <c r="K9" s="16" t="s">
-        <v>218</v>
       </c>
       <c r="L9" s="16"/>
       <c r="M9" s="16"/>
       <c r="O9" s="16" t="s">
+        <v>214</v>
+      </c>
+      <c r="P9" s="16" t="s">
         <v>215</v>
       </c>
-      <c r="P9" s="16" t="s">
+      <c r="Q9" s="16" t="s">
         <v>216</v>
       </c>
-      <c r="Q9" s="16" t="s">
+      <c r="R9" s="16" t="s">
         <v>217</v>
-      </c>
-      <c r="R9" s="16" t="s">
-        <v>218</v>
       </c>
       <c r="S9" s="16"/>
       <c r="T9" s="16"/>
       <c r="V9" s="16" t="s">
+        <v>214</v>
+      </c>
+      <c r="W9" s="16" t="s">
         <v>215</v>
       </c>
-      <c r="W9" s="16" t="s">
+      <c r="X9" s="16" t="s">
         <v>216</v>
       </c>
-      <c r="X9" s="16" t="s">
+      <c r="Y9" s="16" t="s">
         <v>217</v>
-      </c>
-      <c r="Y9" s="16" t="s">
-        <v>218</v>
       </c>
       <c r="Z9" s="16"/>
       <c r="AA9" s="16"/>
       <c r="AC9" s="16" t="s">
+        <v>214</v>
+      </c>
+      <c r="AD9" s="16" t="s">
         <v>215</v>
       </c>
-      <c r="AD9" s="16" t="s">
+      <c r="AE9" s="16" t="s">
         <v>216</v>
       </c>
-      <c r="AE9" s="16" t="s">
+      <c r="AF9" s="16" t="s">
         <v>217</v>
-      </c>
-      <c r="AF9" s="16" t="s">
-        <v>218</v>
       </c>
       <c r="AG9" s="16"/>
       <c r="AH9" s="16"/>
       <c r="AJ9" s="16" t="s">
+        <v>214</v>
+      </c>
+      <c r="AK9" s="16" t="s">
         <v>215</v>
       </c>
-      <c r="AK9" s="16" t="s">
+      <c r="AL9" s="16" t="s">
         <v>216</v>
       </c>
-      <c r="AL9" s="16" t="s">
+      <c r="AM9" s="16" t="s">
         <v>217</v>
-      </c>
-      <c r="AM9" s="16" t="s">
-        <v>218</v>
       </c>
       <c r="AN9" s="16"/>
       <c r="AO9" s="16"/>
       <c r="AQ9" s="16" t="s">
+        <v>214</v>
+      </c>
+      <c r="AR9" s="16" t="s">
         <v>215</v>
       </c>
-      <c r="AR9" s="16" t="s">
+      <c r="AS9" s="16" t="s">
         <v>216</v>
       </c>
-      <c r="AS9" s="16" t="s">
+      <c r="AT9" s="16" t="s">
         <v>217</v>
-      </c>
-      <c r="AT9" s="16" t="s">
-        <v>218</v>
       </c>
       <c r="AU9" s="16"/>
       <c r="AV9" s="16"/>
       <c r="AX9" s="16" t="s">
+        <v>214</v>
+      </c>
+      <c r="AY9" s="16" t="s">
         <v>215</v>
       </c>
-      <c r="AY9" s="16" t="s">
+      <c r="AZ9" s="16" t="s">
         <v>216</v>
       </c>
-      <c r="AZ9" s="16" t="s">
+      <c r="BA9" s="16" t="s">
         <v>217</v>
-      </c>
-      <c r="BA9" s="16" t="s">
-        <v>218</v>
       </c>
       <c r="BB9" s="16"/>
       <c r="BC9" s="16"/>
       <c r="BE9" s="16" t="s">
+        <v>214</v>
+      </c>
+      <c r="BF9" s="16" t="s">
         <v>215</v>
       </c>
-      <c r="BF9" s="16" t="s">
+      <c r="BG9" s="16" t="s">
         <v>216</v>
       </c>
-      <c r="BG9" s="16" t="s">
+      <c r="BH9" s="16" t="s">
         <v>217</v>
-      </c>
-      <c r="BH9" s="16" t="s">
-        <v>218</v>
       </c>
       <c r="BI9" s="16"/>
       <c r="BJ9" s="16"/>
       <c r="BL9" s="16" t="s">
+        <v>214</v>
+      </c>
+      <c r="BM9" s="16" t="s">
         <v>215</v>
       </c>
-      <c r="BM9" s="16" t="s">
+      <c r="BN9" s="16" t="s">
         <v>216</v>
       </c>
-      <c r="BN9" s="16" t="s">
+      <c r="BO9" s="16" t="s">
         <v>217</v>
-      </c>
-      <c r="BO9" s="16" t="s">
-        <v>218</v>
       </c>
       <c r="BP9" s="16"/>
       <c r="BQ9" s="16"/>
       <c r="BS9" s="16" t="s">
+        <v>214</v>
+      </c>
+      <c r="BT9" s="16" t="s">
         <v>215</v>
       </c>
-      <c r="BT9" s="16" t="s">
+      <c r="BU9" s="16" t="s">
         <v>216</v>
       </c>
-      <c r="BU9" s="16" t="s">
+      <c r="BV9" s="16" t="s">
         <v>217</v>
-      </c>
-      <c r="BV9" s="16" t="s">
-        <v>218</v>
       </c>
       <c r="BW9" s="16"/>
       <c r="BX9" s="16"/>
       <c r="BZ9" s="16" t="s">
+        <v>214</v>
+      </c>
+      <c r="CA9" s="16" t="s">
         <v>215</v>
       </c>
-      <c r="CA9" s="16" t="s">
+      <c r="CB9" s="16" t="s">
         <v>216</v>
       </c>
-      <c r="CB9" s="16" t="s">
+      <c r="CC9" s="16" t="s">
         <v>217</v>
-      </c>
-      <c r="CC9" s="16" t="s">
-        <v>218</v>
       </c>
       <c r="CD9" s="16"/>
       <c r="CE9" s="16"/>
       <c r="CG9" s="16" t="s">
+        <v>214</v>
+      </c>
+      <c r="CH9" s="16" t="s">
         <v>215</v>
       </c>
-      <c r="CH9" s="16" t="s">
+      <c r="CI9" s="16" t="s">
         <v>216</v>
       </c>
-      <c r="CI9" s="16" t="s">
+      <c r="CJ9" s="16" t="s">
         <v>217</v>
-      </c>
-      <c r="CJ9" s="16" t="s">
-        <v>218</v>
       </c>
       <c r="CK9" s="16"/>
       <c r="CL9" s="16"/>
       <c r="CN9" s="16" t="s">
+        <v>214</v>
+      </c>
+      <c r="CO9" s="16" t="s">
         <v>215</v>
       </c>
-      <c r="CO9" s="16" t="s">
+      <c r="CP9" s="16" t="s">
         <v>216</v>
       </c>
-      <c r="CP9" s="16" t="s">
+      <c r="CQ9" s="16" t="s">
         <v>217</v>
-      </c>
-      <c r="CQ9" s="16" t="s">
-        <v>218</v>
       </c>
       <c r="CR9" s="16"/>
       <c r="CS9" s="16"/>
       <c r="CU9" s="16" t="s">
+        <v>214</v>
+      </c>
+      <c r="CV9" s="16" t="s">
         <v>215</v>
       </c>
-      <c r="CV9" s="16" t="s">
+      <c r="CW9" s="16" t="s">
         <v>216</v>
       </c>
-      <c r="CW9" s="16" t="s">
+      <c r="CX9" s="16" t="s">
         <v>217</v>
-      </c>
-      <c r="CX9" s="16" t="s">
-        <v>218</v>
       </c>
       <c r="CY9" s="16"/>
       <c r="CZ9" s="16"/>
       <c r="DB9" s="16" t="s">
+        <v>214</v>
+      </c>
+      <c r="DC9" s="16" t="s">
         <v>215</v>
       </c>
-      <c r="DC9" s="16" t="s">
+      <c r="DD9" s="16" t="s">
         <v>216</v>
       </c>
-      <c r="DD9" s="16" t="s">
+      <c r="DE9" s="16" t="s">
         <v>217</v>
-      </c>
-      <c r="DE9" s="16" t="s">
-        <v>218</v>
       </c>
       <c r="DF9" s="16"/>
       <c r="DG9" s="16"/>
       <c r="DI9" s="16" t="s">
+        <v>214</v>
+      </c>
+      <c r="DJ9" s="16" t="s">
         <v>215</v>
       </c>
-      <c r="DJ9" s="16" t="s">
+      <c r="DK9" s="16" t="s">
         <v>216</v>
       </c>
-      <c r="DK9" s="16" t="s">
+      <c r="DL9" s="16" t="s">
         <v>217</v>
-      </c>
-      <c r="DL9" s="16" t="s">
-        <v>218</v>
       </c>
       <c r="DM9" s="16"/>
       <c r="DN9" s="16"/>
       <c r="DP9" s="16" t="s">
+        <v>214</v>
+      </c>
+      <c r="DQ9" s="16" t="s">
         <v>215</v>
       </c>
-      <c r="DQ9" s="16" t="s">
+      <c r="DR9" s="16" t="s">
         <v>216</v>
       </c>
-      <c r="DR9" s="16" t="s">
+      <c r="DS9" s="16" t="s">
         <v>217</v>
-      </c>
-      <c r="DS9" s="16" t="s">
-        <v>218</v>
       </c>
       <c r="DT9" s="16"/>
       <c r="DU9" s="16"/>
       <c r="DW9" s="16" t="s">
+        <v>214</v>
+      </c>
+      <c r="DX9" s="16" t="s">
         <v>215</v>
       </c>
-      <c r="DX9" s="16" t="s">
+      <c r="DY9" s="16" t="s">
         <v>216</v>
       </c>
-      <c r="DY9" s="16" t="s">
+      <c r="DZ9" s="16" t="s">
         <v>217</v>
-      </c>
-      <c r="DZ9" s="16" t="s">
-        <v>218</v>
       </c>
       <c r="EA9" s="16"/>
       <c r="EB9" s="16"/>
       <c r="ED9" s="16" t="s">
+        <v>214</v>
+      </c>
+      <c r="EE9" s="16" t="s">
         <v>215</v>
       </c>
-      <c r="EE9" s="16" t="s">
+      <c r="EF9" s="16" t="s">
         <v>216</v>
       </c>
-      <c r="EF9" s="16" t="s">
+      <c r="EG9" s="16" t="s">
         <v>217</v>
-      </c>
-      <c r="EG9" s="16" t="s">
-        <v>218</v>
       </c>
       <c r="EH9" s="16"/>
       <c r="EI9" s="16"/>
       <c r="EK9" s="16" t="s">
+        <v>214</v>
+      </c>
+      <c r="EL9" s="16" t="s">
         <v>215</v>
       </c>
-      <c r="EL9" s="16" t="s">
+      <c r="EM9" s="16" t="s">
         <v>216</v>
       </c>
-      <c r="EM9" s="16" t="s">
+      <c r="EN9" s="16" t="s">
         <v>217</v>
-      </c>
-      <c r="EN9" s="16" t="s">
-        <v>218</v>
       </c>
       <c r="EO9" s="16"/>
       <c r="EP9" s="16"/>
       <c r="ER9" s="16" t="s">
+        <v>214</v>
+      </c>
+      <c r="ES9" s="16" t="s">
         <v>215</v>
       </c>
-      <c r="ES9" s="16" t="s">
+      <c r="ET9" s="16" t="s">
         <v>216</v>
       </c>
-      <c r="ET9" s="16" t="s">
+      <c r="EU9" s="16" t="s">
         <v>217</v>
-      </c>
-      <c r="EU9" s="16" t="s">
-        <v>218</v>
       </c>
       <c r="EV9" s="16"/>
       <c r="EW9" s="16"/>
       <c r="EY9" s="16" t="s">
+        <v>214</v>
+      </c>
+      <c r="EZ9" s="16" t="s">
         <v>215</v>
       </c>
-      <c r="EZ9" s="16" t="s">
+      <c r="FA9" s="16" t="s">
         <v>216</v>
       </c>
-      <c r="FA9" s="16" t="s">
+      <c r="FB9" s="16" t="s">
         <v>217</v>
-      </c>
-      <c r="FB9" s="16" t="s">
-        <v>218</v>
       </c>
       <c r="FC9" s="16"/>
       <c r="FD9" s="16"/>
     </row>
     <row r="10" spans="1:160" ht="29.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="16" t="s">
+        <v>218</v>
+      </c>
+      <c r="B10" s="16" t="s">
         <v>219</v>
-      </c>
-      <c r="B10" s="16" t="s">
-        <v>220</v>
       </c>
       <c r="C10" s="16"/>
       <c r="D10" s="16" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="E10" s="16"/>
       <c r="F10" s="16"/>
       <c r="H10" s="16" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="I10" s="16" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="J10" s="16"/>
       <c r="K10" s="16" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="L10" s="16"/>
       <c r="M10" s="16"/>
       <c r="O10" s="16" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="P10" s="16" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="Q10" s="16"/>
       <c r="R10" s="16" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="S10" s="16"/>
       <c r="T10" s="16"/>
       <c r="V10" s="16" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="W10" s="16" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="X10" s="16"/>
       <c r="Y10" s="16" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="Z10" s="16"/>
       <c r="AA10" s="16"/>
       <c r="AC10" s="16" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="AD10" s="16" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="AE10" s="16"/>
       <c r="AF10" s="16" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="AG10" s="16"/>
       <c r="AH10" s="16"/>
       <c r="AJ10" s="16" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="AK10" s="16" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="AL10" s="16"/>
       <c r="AM10" s="16" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="AN10" s="16"/>
       <c r="AO10" s="16"/>
       <c r="AQ10" s="16" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="AR10" s="16" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="AS10" s="16"/>
       <c r="AT10" s="16" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="AU10" s="16"/>
       <c r="AV10" s="16"/>
       <c r="AX10" s="16" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="AY10" s="16" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="AZ10" s="16"/>
       <c r="BA10" s="16" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="BB10" s="16"/>
       <c r="BC10" s="16"/>
       <c r="BE10" s="16" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="BF10" s="16" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="BG10" s="16"/>
       <c r="BH10" s="16" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="BI10" s="16"/>
       <c r="BJ10" s="16"/>
       <c r="BL10" s="16" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="BM10" s="16" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="BN10" s="16"/>
       <c r="BO10" s="16" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="BP10" s="16"/>
       <c r="BQ10" s="16"/>
       <c r="BS10" s="16" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="BT10" s="16" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="BU10" s="16"/>
       <c r="BV10" s="16" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="BW10" s="16"/>
       <c r="BX10" s="16"/>
       <c r="BZ10" s="16" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="CA10" s="16" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="CB10" s="16"/>
       <c r="CC10" s="16" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="CD10" s="16"/>
       <c r="CE10" s="16"/>
       <c r="CG10" s="16" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="CH10" s="16" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="CI10" s="16"/>
       <c r="CJ10" s="16" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="CK10" s="16"/>
       <c r="CL10" s="16"/>
       <c r="CN10" s="16" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="CO10" s="16" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="CP10" s="16"/>
       <c r="CQ10" s="16" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="CR10" s="16"/>
       <c r="CS10" s="16"/>
       <c r="CU10" s="16" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="CV10" s="16" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="CW10" s="16"/>
       <c r="CX10" s="16" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="CY10" s="16"/>
       <c r="CZ10" s="16"/>
       <c r="DB10" s="16" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="DC10" s="16" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="DD10" s="16"/>
       <c r="DE10" s="16" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="DF10" s="16"/>
       <c r="DG10" s="16"/>
       <c r="DI10" s="16" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="DJ10" s="16" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="DK10" s="16"/>
       <c r="DL10" s="16" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="DM10" s="16"/>
       <c r="DN10" s="16"/>
       <c r="DP10" s="16" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="DQ10" s="16" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="DR10" s="16"/>
       <c r="DS10" s="16" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="DT10" s="16"/>
       <c r="DU10" s="16"/>
       <c r="DW10" s="16" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="DX10" s="16" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="DY10" s="16"/>
       <c r="DZ10" s="16" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="EA10" s="16"/>
       <c r="EB10" s="16"/>
       <c r="ED10" s="16" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="EE10" s="16" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="EF10" s="16"/>
       <c r="EG10" s="16" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="EH10" s="16"/>
       <c r="EI10" s="16"/>
       <c r="EK10" s="16" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="EL10" s="16" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="EM10" s="16"/>
       <c r="EN10" s="16" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="EO10" s="16"/>
       <c r="EP10" s="16"/>
       <c r="ER10" s="16" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="ES10" s="16" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="ET10" s="16"/>
       <c r="EU10" s="16" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="EV10" s="16"/>
       <c r="EW10" s="16"/>
       <c r="EY10" s="16" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="EZ10" s="16" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="FA10" s="16"/>
       <c r="FB10" s="16" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="FC10" s="16"/>
       <c r="FD10" s="16"/>
     </row>
     <row r="11" spans="1:160" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="16" t="s">
+        <v>233</v>
+      </c>
+      <c r="B11" s="16" t="s">
         <v>234</v>
-      </c>
-      <c r="B11" s="16" t="s">
-        <v>235</v>
       </c>
       <c r="C11" s="16"/>
       <c r="D11" s="16" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="E11" s="16"/>
       <c r="F11" s="16"/>
       <c r="H11" s="16" t="s">
+        <v>233</v>
+      </c>
+      <c r="I11" s="16" t="s">
         <v>234</v>
-      </c>
-      <c r="I11" s="16" t="s">
-        <v>235</v>
       </c>
       <c r="J11" s="16"/>
       <c r="K11" s="16" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="L11" s="16"/>
       <c r="M11" s="16"/>
       <c r="O11" s="16" t="s">
+        <v>233</v>
+      </c>
+      <c r="P11" s="16" t="s">
         <v>234</v>
-      </c>
-      <c r="P11" s="16" t="s">
-        <v>235</v>
       </c>
       <c r="Q11" s="16"/>
       <c r="R11" s="16" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="S11" s="16"/>
       <c r="T11" s="16"/>
       <c r="V11" s="16" t="s">
+        <v>233</v>
+      </c>
+      <c r="W11" s="16" t="s">
         <v>234</v>
-      </c>
-      <c r="W11" s="16" t="s">
-        <v>235</v>
       </c>
       <c r="X11" s="16"/>
       <c r="Y11" s="16" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="Z11" s="16"/>
       <c r="AA11" s="16"/>
       <c r="AC11" s="16" t="s">
+        <v>233</v>
+      </c>
+      <c r="AD11" s="16" t="s">
         <v>234</v>
-      </c>
-      <c r="AD11" s="16" t="s">
-        <v>235</v>
       </c>
       <c r="AE11" s="16"/>
       <c r="AF11" s="16" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="AG11" s="16"/>
       <c r="AH11" s="16"/>
       <c r="AJ11" s="16" t="s">
+        <v>233</v>
+      </c>
+      <c r="AK11" s="16" t="s">
         <v>234</v>
-      </c>
-      <c r="AK11" s="16" t="s">
-        <v>235</v>
       </c>
       <c r="AL11" s="16"/>
       <c r="AM11" s="16" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="AN11" s="16"/>
       <c r="AO11" s="16"/>
       <c r="AQ11" s="16" t="s">
+        <v>233</v>
+      </c>
+      <c r="AR11" s="16" t="s">
         <v>234</v>
-      </c>
-      <c r="AR11" s="16" t="s">
-        <v>235</v>
       </c>
       <c r="AS11" s="16"/>
       <c r="AT11" s="16" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="AU11" s="16"/>
       <c r="AV11" s="16"/>
       <c r="AX11" s="16" t="s">
+        <v>233</v>
+      </c>
+      <c r="AY11" s="16" t="s">
         <v>234</v>
-      </c>
-      <c r="AY11" s="16" t="s">
-        <v>235</v>
       </c>
       <c r="AZ11" s="16"/>
       <c r="BA11" s="16" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="BB11" s="16"/>
       <c r="BC11" s="16"/>
       <c r="BE11" s="16" t="s">
+        <v>233</v>
+      </c>
+      <c r="BF11" s="16" t="s">
         <v>234</v>
-      </c>
-      <c r="BF11" s="16" t="s">
-        <v>235</v>
       </c>
       <c r="BG11" s="16"/>
       <c r="BH11" s="16" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="BI11" s="16"/>
       <c r="BJ11" s="16"/>
       <c r="BL11" s="16" t="s">
+        <v>233</v>
+      </c>
+      <c r="BM11" s="16" t="s">
         <v>234</v>
-      </c>
-      <c r="BM11" s="16" t="s">
-        <v>235</v>
       </c>
       <c r="BN11" s="16"/>
       <c r="BO11" s="16" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="BP11" s="16"/>
       <c r="BQ11" s="16"/>
       <c r="BS11" s="16" t="s">
+        <v>233</v>
+      </c>
+      <c r="BT11" s="16" t="s">
         <v>234</v>
-      </c>
-      <c r="BT11" s="16" t="s">
-        <v>235</v>
       </c>
       <c r="BU11" s="16"/>
       <c r="BV11" s="16" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="BW11" s="16"/>
       <c r="BX11" s="16"/>
       <c r="BZ11" s="16" t="s">
+        <v>233</v>
+      </c>
+      <c r="CA11" s="16" t="s">
         <v>234</v>
-      </c>
-      <c r="CA11" s="16" t="s">
-        <v>235</v>
       </c>
       <c r="CB11" s="16"/>
       <c r="CC11" s="16" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="CD11" s="16"/>
       <c r="CE11" s="16"/>
       <c r="CG11" s="16" t="s">
+        <v>233</v>
+      </c>
+      <c r="CH11" s="16" t="s">
         <v>234</v>
-      </c>
-      <c r="CH11" s="16" t="s">
-        <v>235</v>
       </c>
       <c r="CI11" s="16"/>
       <c r="CJ11" s="16" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="CK11" s="16"/>
       <c r="CL11" s="16"/>
       <c r="CN11" s="16" t="s">
+        <v>233</v>
+      </c>
+      <c r="CO11" s="16" t="s">
         <v>234</v>
-      </c>
-      <c r="CO11" s="16" t="s">
-        <v>235</v>
       </c>
       <c r="CP11" s="16"/>
       <c r="CQ11" s="16" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="CR11" s="16"/>
       <c r="CS11" s="16"/>
       <c r="CU11" s="16" t="s">
+        <v>233</v>
+      </c>
+      <c r="CV11" s="16" t="s">
         <v>234</v>
-      </c>
-      <c r="CV11" s="16" t="s">
-        <v>235</v>
       </c>
       <c r="CW11" s="16"/>
       <c r="CX11" s="16" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="CY11" s="16"/>
       <c r="CZ11" s="16"/>
       <c r="DB11" s="16" t="s">
+        <v>233</v>
+      </c>
+      <c r="DC11" s="16" t="s">
         <v>234</v>
-      </c>
-      <c r="DC11" s="16" t="s">
-        <v>235</v>
       </c>
       <c r="DD11" s="16"/>
       <c r="DE11" s="16" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="DF11" s="16"/>
       <c r="DG11" s="16"/>
       <c r="DI11" s="16" t="s">
+        <v>233</v>
+      </c>
+      <c r="DJ11" s="16" t="s">
         <v>234</v>
-      </c>
-      <c r="DJ11" s="16" t="s">
-        <v>235</v>
       </c>
       <c r="DK11" s="16"/>
       <c r="DL11" s="16" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="DM11" s="16"/>
       <c r="DN11" s="16"/>
       <c r="DP11" s="16" t="s">
+        <v>233</v>
+      </c>
+      <c r="DQ11" s="16" t="s">
         <v>234</v>
-      </c>
-      <c r="DQ11" s="16" t="s">
-        <v>235</v>
       </c>
       <c r="DR11" s="16"/>
       <c r="DS11" s="16" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="DT11" s="16"/>
       <c r="DU11" s="16"/>
       <c r="DW11" s="16" t="s">
+        <v>233</v>
+      </c>
+      <c r="DX11" s="16" t="s">
         <v>234</v>
-      </c>
-      <c r="DX11" s="16" t="s">
-        <v>235</v>
       </c>
       <c r="DY11" s="16"/>
       <c r="DZ11" s="16" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="EA11" s="16"/>
       <c r="EB11" s="16"/>
       <c r="ED11" s="16" t="s">
+        <v>233</v>
+      </c>
+      <c r="EE11" s="16" t="s">
         <v>234</v>
-      </c>
-      <c r="EE11" s="16" t="s">
-        <v>235</v>
       </c>
       <c r="EF11" s="16"/>
       <c r="EG11" s="16" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="EH11" s="16"/>
       <c r="EI11" s="16"/>
       <c r="EK11" s="16" t="s">
+        <v>233</v>
+      </c>
+      <c r="EL11" s="16" t="s">
         <v>234</v>
-      </c>
-      <c r="EL11" s="16" t="s">
-        <v>235</v>
       </c>
       <c r="EM11" s="16"/>
       <c r="EN11" s="16" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="EO11" s="16"/>
       <c r="EP11" s="16"/>
       <c r="ER11" s="16" t="s">
+        <v>233</v>
+      </c>
+      <c r="ES11" s="16" t="s">
         <v>234</v>
-      </c>
-      <c r="ES11" s="16" t="s">
-        <v>235</v>
       </c>
       <c r="ET11" s="16"/>
       <c r="EU11" s="16" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="EV11" s="16"/>
       <c r="EW11" s="16"/>
       <c r="EY11" s="16" t="s">
+        <v>233</v>
+      </c>
+      <c r="EZ11" s="16" t="s">
         <v>234</v>
-      </c>
-      <c r="EZ11" s="16" t="s">
-        <v>235</v>
       </c>
       <c r="FA11" s="16"/>
       <c r="FB11" s="16" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="FC11" s="16"/>
       <c r="FD11" s="16"/>
     </row>
   </sheetData>
   <mergeCells count="69">
+    <mergeCell ref="EL7:EP7"/>
+    <mergeCell ref="AD7:AH7"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="BL1:BQ1"/>
+    <mergeCell ref="AY7:BC7"/>
+    <mergeCell ref="CU1:CZ1"/>
+    <mergeCell ref="CH7:CL7"/>
+    <mergeCell ref="AY6:BC6"/>
+    <mergeCell ref="BT6:BX6"/>
+    <mergeCell ref="W7:AA7"/>
+    <mergeCell ref="P7:T7"/>
+    <mergeCell ref="CA7:CE7"/>
+    <mergeCell ref="EE7:EI7"/>
+    <mergeCell ref="CO7:CS7"/>
+    <mergeCell ref="EL6:EP6"/>
+    <mergeCell ref="DX7:EB7"/>
+    <mergeCell ref="EZ6:FD6"/>
+    <mergeCell ref="EK1:EP1"/>
+    <mergeCell ref="H1:M1"/>
+    <mergeCell ref="B6:F6"/>
+    <mergeCell ref="AX1:BC1"/>
+    <mergeCell ref="AK6:AO6"/>
+    <mergeCell ref="DJ6:DN6"/>
+    <mergeCell ref="ES6:EW6"/>
+    <mergeCell ref="ED1:EI1"/>
+    <mergeCell ref="AJ1:AO1"/>
+    <mergeCell ref="AR6:AV6"/>
+    <mergeCell ref="CN1:CS1"/>
+    <mergeCell ref="DC6:DG6"/>
+    <mergeCell ref="DB1:DG1"/>
+    <mergeCell ref="CV6:CZ6"/>
+    <mergeCell ref="ER1:EW1"/>
+    <mergeCell ref="ES7:EW7"/>
+    <mergeCell ref="AC1:AH1"/>
+    <mergeCell ref="EE6:EI6"/>
+    <mergeCell ref="I7:M7"/>
+    <mergeCell ref="BT7:BX7"/>
+    <mergeCell ref="P6:T6"/>
+    <mergeCell ref="CG1:CL1"/>
+    <mergeCell ref="BM7:BQ7"/>
+    <mergeCell ref="CA6:CE6"/>
+    <mergeCell ref="AQ1:AV1"/>
+    <mergeCell ref="AD6:AH6"/>
+    <mergeCell ref="DC7:DG7"/>
+    <mergeCell ref="BZ1:CE1"/>
+    <mergeCell ref="CO6:CS6"/>
+    <mergeCell ref="DP1:DU1"/>
+    <mergeCell ref="DQ7:DU7"/>
+    <mergeCell ref="CH6:CL6"/>
+    <mergeCell ref="BF6:BJ6"/>
+    <mergeCell ref="DW1:EB1"/>
+    <mergeCell ref="DQ6:DU6"/>
+    <mergeCell ref="DJ7:DN7"/>
     <mergeCell ref="EY1:FD1"/>
     <mergeCell ref="V1:AA1"/>
     <mergeCell ref="DX6:EB6"/>
@@ -9656,59 +9746,6 @@
     <mergeCell ref="DI1:DN1"/>
     <mergeCell ref="BF7:BJ7"/>
     <mergeCell ref="BM6:BQ6"/>
-    <mergeCell ref="CH6:CL6"/>
-    <mergeCell ref="BF6:BJ6"/>
-    <mergeCell ref="DW1:EB1"/>
-    <mergeCell ref="DQ6:DU6"/>
-    <mergeCell ref="DJ7:DN7"/>
-    <mergeCell ref="ES7:EW7"/>
-    <mergeCell ref="AC1:AH1"/>
-    <mergeCell ref="EE6:EI6"/>
-    <mergeCell ref="I7:M7"/>
-    <mergeCell ref="BT7:BX7"/>
-    <mergeCell ref="P6:T6"/>
-    <mergeCell ref="CG1:CL1"/>
-    <mergeCell ref="BM7:BQ7"/>
-    <mergeCell ref="CA6:CE6"/>
-    <mergeCell ref="AQ1:AV1"/>
-    <mergeCell ref="AD6:AH6"/>
-    <mergeCell ref="DC7:DG7"/>
-    <mergeCell ref="BZ1:CE1"/>
-    <mergeCell ref="CO6:CS6"/>
-    <mergeCell ref="DP1:DU1"/>
-    <mergeCell ref="DQ7:DU7"/>
-    <mergeCell ref="EZ6:FD6"/>
-    <mergeCell ref="EK1:EP1"/>
-    <mergeCell ref="H1:M1"/>
-    <mergeCell ref="B6:F6"/>
-    <mergeCell ref="AX1:BC1"/>
-    <mergeCell ref="AK6:AO6"/>
-    <mergeCell ref="DJ6:DN6"/>
-    <mergeCell ref="ES6:EW6"/>
-    <mergeCell ref="ED1:EI1"/>
-    <mergeCell ref="AJ1:AO1"/>
-    <mergeCell ref="AR6:AV6"/>
-    <mergeCell ref="CN1:CS1"/>
-    <mergeCell ref="DC6:DG6"/>
-    <mergeCell ref="DB1:DG1"/>
-    <mergeCell ref="CV6:CZ6"/>
-    <mergeCell ref="ER1:EW1"/>
-    <mergeCell ref="EL7:EP7"/>
-    <mergeCell ref="AD7:AH7"/>
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="BL1:BQ1"/>
-    <mergeCell ref="AY7:BC7"/>
-    <mergeCell ref="CU1:CZ1"/>
-    <mergeCell ref="CH7:CL7"/>
-    <mergeCell ref="AY6:BC6"/>
-    <mergeCell ref="BT6:BX6"/>
-    <mergeCell ref="W7:AA7"/>
-    <mergeCell ref="P7:T7"/>
-    <mergeCell ref="CA7:CE7"/>
-    <mergeCell ref="EE7:EI7"/>
-    <mergeCell ref="CO7:CS7"/>
-    <mergeCell ref="EL6:EP6"/>
-    <mergeCell ref="DX7:EB7"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -9745,184 +9782,184 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:160" x14ac:dyDescent="0.25">
-      <c r="A1" s="30" t="s">
-        <v>238</v>
+      <c r="A1" s="29" t="s">
+        <v>237</v>
       </c>
       <c r="B1" s="18"/>
       <c r="C1" s="18"/>
       <c r="D1" s="18"/>
       <c r="E1" s="18"/>
       <c r="F1" s="18"/>
-      <c r="H1" s="30" t="s">
-        <v>239</v>
+      <c r="H1" s="29" t="s">
+        <v>238</v>
       </c>
       <c r="I1" s="18"/>
       <c r="J1" s="18"/>
       <c r="K1" s="18"/>
       <c r="L1" s="18"/>
       <c r="M1" s="18"/>
-      <c r="O1" s="30" t="s">
-        <v>240</v>
+      <c r="O1" s="29" t="s">
+        <v>239</v>
       </c>
       <c r="P1" s="18"/>
       <c r="Q1" s="18"/>
       <c r="R1" s="18"/>
       <c r="S1" s="18"/>
       <c r="T1" s="18"/>
-      <c r="V1" s="30" t="s">
-        <v>241</v>
+      <c r="V1" s="29" t="s">
+        <v>240</v>
       </c>
       <c r="W1" s="18"/>
       <c r="X1" s="18"/>
       <c r="Y1" s="18"/>
       <c r="Z1" s="18"/>
       <c r="AA1" s="18"/>
-      <c r="AC1" s="30" t="s">
-        <v>242</v>
+      <c r="AC1" s="29" t="s">
+        <v>241</v>
       </c>
       <c r="AD1" s="18"/>
       <c r="AE1" s="18"/>
       <c r="AF1" s="18"/>
       <c r="AG1" s="18"/>
       <c r="AH1" s="18"/>
-      <c r="AJ1" s="30" t="s">
-        <v>243</v>
+      <c r="AJ1" s="29" t="s">
+        <v>242</v>
       </c>
       <c r="AK1" s="18"/>
       <c r="AL1" s="18"/>
       <c r="AM1" s="18"/>
       <c r="AN1" s="18"/>
       <c r="AO1" s="18"/>
-      <c r="AQ1" s="30" t="s">
-        <v>244</v>
+      <c r="AQ1" s="29" t="s">
+        <v>243</v>
       </c>
       <c r="AR1" s="18"/>
       <c r="AS1" s="18"/>
       <c r="AT1" s="18"/>
       <c r="AU1" s="18"/>
       <c r="AV1" s="18"/>
-      <c r="AX1" s="30" t="s">
-        <v>245</v>
+      <c r="AX1" s="29" t="s">
+        <v>244</v>
       </c>
       <c r="AY1" s="18"/>
       <c r="AZ1" s="18"/>
       <c r="BA1" s="18"/>
       <c r="BB1" s="18"/>
       <c r="BC1" s="18"/>
-      <c r="BE1" s="30" t="s">
-        <v>246</v>
+      <c r="BE1" s="29" t="s">
+        <v>245</v>
       </c>
       <c r="BF1" s="18"/>
       <c r="BG1" s="18"/>
       <c r="BH1" s="18"/>
       <c r="BI1" s="18"/>
       <c r="BJ1" s="18"/>
-      <c r="BL1" s="30" t="s">
-        <v>247</v>
+      <c r="BL1" s="29" t="s">
+        <v>246</v>
       </c>
       <c r="BM1" s="18"/>
       <c r="BN1" s="18"/>
       <c r="BO1" s="18"/>
       <c r="BP1" s="18"/>
       <c r="BQ1" s="18"/>
-      <c r="BS1" s="30" t="s">
-        <v>248</v>
+      <c r="BS1" s="29" t="s">
+        <v>247</v>
       </c>
       <c r="BT1" s="18"/>
       <c r="BU1" s="18"/>
       <c r="BV1" s="18"/>
       <c r="BW1" s="18"/>
       <c r="BX1" s="18"/>
-      <c r="BZ1" s="30" t="s">
-        <v>249</v>
+      <c r="BZ1" s="29" t="s">
+        <v>248</v>
       </c>
       <c r="CA1" s="18"/>
       <c r="CB1" s="18"/>
       <c r="CC1" s="18"/>
       <c r="CD1" s="18"/>
       <c r="CE1" s="18"/>
-      <c r="CG1" s="30" t="s">
-        <v>250</v>
+      <c r="CG1" s="29" t="s">
+        <v>249</v>
       </c>
       <c r="CH1" s="18"/>
       <c r="CI1" s="18"/>
       <c r="CJ1" s="18"/>
       <c r="CK1" s="18"/>
       <c r="CL1" s="18"/>
-      <c r="CN1" s="30" t="s">
-        <v>251</v>
+      <c r="CN1" s="29" t="s">
+        <v>250</v>
       </c>
       <c r="CO1" s="18"/>
       <c r="CP1" s="18"/>
       <c r="CQ1" s="18"/>
       <c r="CR1" s="18"/>
       <c r="CS1" s="18"/>
-      <c r="CU1" s="30" t="s">
-        <v>252</v>
+      <c r="CU1" s="29" t="s">
+        <v>251</v>
       </c>
       <c r="CV1" s="18"/>
       <c r="CW1" s="18"/>
       <c r="CX1" s="18"/>
       <c r="CY1" s="18"/>
       <c r="CZ1" s="18"/>
-      <c r="DB1" s="30" t="s">
-        <v>253</v>
+      <c r="DB1" s="29" t="s">
+        <v>252</v>
       </c>
       <c r="DC1" s="18"/>
       <c r="DD1" s="18"/>
       <c r="DE1" s="18"/>
       <c r="DF1" s="18"/>
       <c r="DG1" s="18"/>
-      <c r="DI1" s="30" t="s">
-        <v>254</v>
+      <c r="DI1" s="29" t="s">
+        <v>253</v>
       </c>
       <c r="DJ1" s="18"/>
       <c r="DK1" s="18"/>
       <c r="DL1" s="18"/>
       <c r="DM1" s="18"/>
       <c r="DN1" s="18"/>
-      <c r="DP1" s="30" t="s">
-        <v>255</v>
+      <c r="DP1" s="29" t="s">
+        <v>254</v>
       </c>
       <c r="DQ1" s="18"/>
       <c r="DR1" s="18"/>
       <c r="DS1" s="18"/>
       <c r="DT1" s="18"/>
       <c r="DU1" s="18"/>
-      <c r="DW1" s="30" t="s">
-        <v>256</v>
+      <c r="DW1" s="29" t="s">
+        <v>255</v>
       </c>
       <c r="DX1" s="18"/>
       <c r="DY1" s="18"/>
       <c r="DZ1" s="18"/>
       <c r="EA1" s="18"/>
       <c r="EB1" s="18"/>
-      <c r="ED1" s="30" t="s">
-        <v>257</v>
+      <c r="ED1" s="29" t="s">
+        <v>256</v>
       </c>
       <c r="EE1" s="18"/>
       <c r="EF1" s="18"/>
       <c r="EG1" s="18"/>
       <c r="EH1" s="18"/>
       <c r="EI1" s="18"/>
-      <c r="EK1" s="30" t="s">
-        <v>258</v>
+      <c r="EK1" s="29" t="s">
+        <v>257</v>
       </c>
       <c r="EL1" s="18"/>
       <c r="EM1" s="18"/>
       <c r="EN1" s="18"/>
       <c r="EO1" s="18"/>
       <c r="EP1" s="18"/>
-      <c r="ER1" s="30" t="s">
-        <v>259</v>
+      <c r="ER1" s="29" t="s">
+        <v>258</v>
       </c>
       <c r="ES1" s="18"/>
       <c r="ET1" s="18"/>
       <c r="EU1" s="18"/>
       <c r="EV1" s="18"/>
       <c r="EW1" s="18"/>
-      <c r="EY1" s="30" t="s">
-        <v>260</v>
+      <c r="EY1" s="29" t="s">
+        <v>259</v>
       </c>
       <c r="EZ1" s="18"/>
       <c r="FA1" s="18"/>
@@ -10454,7 +10491,7 @@
       </c>
       <c r="CV5" s="16" t="str">
         <f>IFERROR(_xlfn.SINGLE(_xlfn.XLOOKUP(CU1, TestMaster[Test Name], TestMaster[Test Status], "Status not found")), "")</f>
-        <v>Fail</v>
+        <v>Pass</v>
       </c>
       <c r="DB5" s="16" t="s">
         <v>22</v>
@@ -10515,230 +10552,230 @@
     </row>
     <row r="6" spans="1:160" x14ac:dyDescent="0.25">
       <c r="A6" s="16" t="s">
-        <v>63</v>
-      </c>
-      <c r="B6" s="29" t="s">
-        <v>261</v>
+        <v>62</v>
+      </c>
+      <c r="B6" s="30" t="s">
+        <v>260</v>
       </c>
       <c r="C6" s="18"/>
       <c r="D6" s="18"/>
       <c r="E6" s="18"/>
       <c r="F6" s="18"/>
       <c r="H6" s="16" t="s">
-        <v>63</v>
-      </c>
-      <c r="I6" s="29" t="s">
-        <v>262</v>
+        <v>62</v>
+      </c>
+      <c r="I6" s="30" t="s">
+        <v>261</v>
       </c>
       <c r="J6" s="18"/>
       <c r="K6" s="18"/>
       <c r="L6" s="18"/>
       <c r="M6" s="18"/>
       <c r="O6" s="16" t="s">
-        <v>63</v>
-      </c>
-      <c r="P6" s="29" t="s">
-        <v>263</v>
+        <v>62</v>
+      </c>
+      <c r="P6" s="30" t="s">
+        <v>262</v>
       </c>
       <c r="Q6" s="18"/>
       <c r="R6" s="18"/>
       <c r="S6" s="18"/>
       <c r="T6" s="18"/>
       <c r="V6" s="16" t="s">
-        <v>63</v>
-      </c>
-      <c r="W6" s="29" t="s">
-        <v>264</v>
+        <v>62</v>
+      </c>
+      <c r="W6" s="30" t="s">
+        <v>263</v>
       </c>
       <c r="X6" s="18"/>
       <c r="Y6" s="18"/>
       <c r="Z6" s="18"/>
       <c r="AA6" s="18"/>
       <c r="AC6" s="16" t="s">
-        <v>63</v>
-      </c>
-      <c r="AD6" s="29" t="s">
-        <v>265</v>
+        <v>62</v>
+      </c>
+      <c r="AD6" s="30" t="s">
+        <v>264</v>
       </c>
       <c r="AE6" s="18"/>
       <c r="AF6" s="18"/>
       <c r="AG6" s="18"/>
       <c r="AH6" s="18"/>
       <c r="AJ6" s="16" t="s">
-        <v>63</v>
-      </c>
-      <c r="AK6" s="29" t="s">
-        <v>266</v>
+        <v>62</v>
+      </c>
+      <c r="AK6" s="30" t="s">
+        <v>265</v>
       </c>
       <c r="AL6" s="18"/>
       <c r="AM6" s="18"/>
       <c r="AN6" s="18"/>
       <c r="AO6" s="18"/>
       <c r="AQ6" s="16" t="s">
-        <v>63</v>
-      </c>
-      <c r="AR6" s="29" t="s">
-        <v>267</v>
+        <v>62</v>
+      </c>
+      <c r="AR6" s="30" t="s">
+        <v>266</v>
       </c>
       <c r="AS6" s="18"/>
       <c r="AT6" s="18"/>
       <c r="AU6" s="18"/>
       <c r="AV6" s="18"/>
       <c r="AX6" s="16" t="s">
-        <v>63</v>
-      </c>
-      <c r="AY6" s="29" t="s">
-        <v>268</v>
+        <v>62</v>
+      </c>
+      <c r="AY6" s="30" t="s">
+        <v>267</v>
       </c>
       <c r="AZ6" s="18"/>
       <c r="BA6" s="18"/>
       <c r="BB6" s="18"/>
       <c r="BC6" s="18"/>
       <c r="BE6" s="16" t="s">
-        <v>63</v>
-      </c>
-      <c r="BF6" s="29" t="s">
-        <v>269</v>
+        <v>62</v>
+      </c>
+      <c r="BF6" s="30" t="s">
+        <v>268</v>
       </c>
       <c r="BG6" s="18"/>
       <c r="BH6" s="18"/>
       <c r="BI6" s="18"/>
       <c r="BJ6" s="18"/>
       <c r="BL6" s="16" t="s">
-        <v>63</v>
-      </c>
-      <c r="BM6" s="29" t="s">
-        <v>270</v>
+        <v>62</v>
+      </c>
+      <c r="BM6" s="30" t="s">
+        <v>269</v>
       </c>
       <c r="BN6" s="18"/>
       <c r="BO6" s="18"/>
       <c r="BP6" s="18"/>
       <c r="BQ6" s="18"/>
       <c r="BS6" s="16" t="s">
-        <v>63</v>
-      </c>
-      <c r="BT6" s="29" t="s">
-        <v>271</v>
+        <v>62</v>
+      </c>
+      <c r="BT6" s="30" t="s">
+        <v>270</v>
       </c>
       <c r="BU6" s="18"/>
       <c r="BV6" s="18"/>
       <c r="BW6" s="18"/>
       <c r="BX6" s="18"/>
       <c r="BZ6" s="16" t="s">
-        <v>63</v>
-      </c>
-      <c r="CA6" s="29" t="s">
-        <v>272</v>
+        <v>62</v>
+      </c>
+      <c r="CA6" s="30" t="s">
+        <v>271</v>
       </c>
       <c r="CB6" s="18"/>
       <c r="CC6" s="18"/>
       <c r="CD6" s="18"/>
       <c r="CE6" s="18"/>
       <c r="CG6" s="16" t="s">
-        <v>63</v>
-      </c>
-      <c r="CH6" s="29" t="s">
-        <v>273</v>
+        <v>62</v>
+      </c>
+      <c r="CH6" s="30" t="s">
+        <v>272</v>
       </c>
       <c r="CI6" s="18"/>
       <c r="CJ6" s="18"/>
       <c r="CK6" s="18"/>
       <c r="CL6" s="18"/>
       <c r="CN6" s="16" t="s">
-        <v>63</v>
-      </c>
-      <c r="CO6" s="29" t="s">
-        <v>274</v>
+        <v>62</v>
+      </c>
+      <c r="CO6" s="30" t="s">
+        <v>273</v>
       </c>
       <c r="CP6" s="18"/>
       <c r="CQ6" s="18"/>
       <c r="CR6" s="18"/>
       <c r="CS6" s="18"/>
       <c r="CU6" s="16" t="s">
-        <v>63</v>
-      </c>
-      <c r="CV6" s="29" t="s">
-        <v>275</v>
+        <v>62</v>
+      </c>
+      <c r="CV6" s="30" t="s">
+        <v>274</v>
       </c>
       <c r="CW6" s="18"/>
       <c r="CX6" s="18"/>
       <c r="CY6" s="18"/>
       <c r="CZ6" s="18"/>
       <c r="DB6" s="16" t="s">
-        <v>63</v>
-      </c>
-      <c r="DC6" s="29" t="s">
-        <v>276</v>
+        <v>62</v>
+      </c>
+      <c r="DC6" s="30" t="s">
+        <v>275</v>
       </c>
       <c r="DD6" s="18"/>
       <c r="DE6" s="18"/>
       <c r="DF6" s="18"/>
       <c r="DG6" s="18"/>
       <c r="DI6" s="16" t="s">
-        <v>63</v>
-      </c>
-      <c r="DJ6" s="29" t="s">
-        <v>277</v>
+        <v>62</v>
+      </c>
+      <c r="DJ6" s="30" t="s">
+        <v>276</v>
       </c>
       <c r="DK6" s="18"/>
       <c r="DL6" s="18"/>
       <c r="DM6" s="18"/>
       <c r="DN6" s="18"/>
       <c r="DP6" s="16" t="s">
-        <v>63</v>
-      </c>
-      <c r="DQ6" s="29" t="s">
-        <v>278</v>
+        <v>62</v>
+      </c>
+      <c r="DQ6" s="30" t="s">
+        <v>277</v>
       </c>
       <c r="DR6" s="18"/>
       <c r="DS6" s="18"/>
       <c r="DT6" s="18"/>
       <c r="DU6" s="18"/>
       <c r="DW6" s="16" t="s">
-        <v>63</v>
-      </c>
-      <c r="DX6" s="29" t="s">
-        <v>279</v>
+        <v>62</v>
+      </c>
+      <c r="DX6" s="30" t="s">
+        <v>278</v>
       </c>
       <c r="DY6" s="18"/>
       <c r="DZ6" s="18"/>
       <c r="EA6" s="18"/>
       <c r="EB6" s="18"/>
       <c r="ED6" s="16" t="s">
-        <v>63</v>
-      </c>
-      <c r="EE6" s="29" t="s">
-        <v>280</v>
+        <v>62</v>
+      </c>
+      <c r="EE6" s="30" t="s">
+        <v>279</v>
       </c>
       <c r="EF6" s="18"/>
       <c r="EG6" s="18"/>
       <c r="EH6" s="18"/>
       <c r="EI6" s="18"/>
       <c r="EK6" s="16" t="s">
-        <v>63</v>
-      </c>
-      <c r="EL6" s="29" t="s">
-        <v>281</v>
+        <v>62</v>
+      </c>
+      <c r="EL6" s="30" t="s">
+        <v>280</v>
       </c>
       <c r="EM6" s="18"/>
       <c r="EN6" s="18"/>
       <c r="EO6" s="18"/>
       <c r="EP6" s="18"/>
       <c r="ER6" s="16" t="s">
-        <v>63</v>
-      </c>
-      <c r="ES6" s="29" t="s">
-        <v>282</v>
+        <v>62</v>
+      </c>
+      <c r="ES6" s="30" t="s">
+        <v>281</v>
       </c>
       <c r="ET6" s="18"/>
       <c r="EU6" s="18"/>
       <c r="EV6" s="18"/>
       <c r="EW6" s="18"/>
       <c r="EY6" s="16" t="s">
-        <v>63</v>
-      </c>
-      <c r="EZ6" s="29" t="s">
-        <v>283</v>
+        <v>62</v>
+      </c>
+      <c r="EZ6" s="30" t="s">
+        <v>282</v>
       </c>
       <c r="FA6" s="18"/>
       <c r="FB6" s="18"/>
@@ -10749,8 +10786,8 @@
       <c r="A7" s="16" t="s">
         <v>24</v>
       </c>
-      <c r="B7" s="29" t="s">
-        <v>214</v>
+      <c r="B7" s="30" t="s">
+        <v>213</v>
       </c>
       <c r="C7" s="18"/>
       <c r="D7" s="18"/>
@@ -10759,8 +10796,8 @@
       <c r="H7" s="16" t="s">
         <v>24</v>
       </c>
-      <c r="I7" s="29" t="s">
-        <v>214</v>
+      <c r="I7" s="30" t="s">
+        <v>213</v>
       </c>
       <c r="J7" s="18"/>
       <c r="K7" s="18"/>
@@ -10769,8 +10806,8 @@
       <c r="O7" s="16" t="s">
         <v>24</v>
       </c>
-      <c r="P7" s="29" t="s">
-        <v>214</v>
+      <c r="P7" s="30" t="s">
+        <v>213</v>
       </c>
       <c r="Q7" s="18"/>
       <c r="R7" s="18"/>
@@ -10779,8 +10816,8 @@
       <c r="V7" s="16" t="s">
         <v>24</v>
       </c>
-      <c r="W7" s="29" t="s">
-        <v>214</v>
+      <c r="W7" s="30" t="s">
+        <v>213</v>
       </c>
       <c r="X7" s="18"/>
       <c r="Y7" s="18"/>
@@ -10789,8 +10826,8 @@
       <c r="AC7" s="16" t="s">
         <v>24</v>
       </c>
-      <c r="AD7" s="29" t="s">
-        <v>214</v>
+      <c r="AD7" s="30" t="s">
+        <v>213</v>
       </c>
       <c r="AE7" s="18"/>
       <c r="AF7" s="18"/>
@@ -10799,8 +10836,8 @@
       <c r="AJ7" s="16" t="s">
         <v>24</v>
       </c>
-      <c r="AK7" s="29" t="s">
-        <v>214</v>
+      <c r="AK7" s="30" t="s">
+        <v>213</v>
       </c>
       <c r="AL7" s="18"/>
       <c r="AM7" s="18"/>
@@ -10809,8 +10846,8 @@
       <c r="AQ7" s="16" t="s">
         <v>24</v>
       </c>
-      <c r="AR7" s="29" t="s">
-        <v>214</v>
+      <c r="AR7" s="30" t="s">
+        <v>213</v>
       </c>
       <c r="AS7" s="18"/>
       <c r="AT7" s="18"/>
@@ -10819,8 +10856,8 @@
       <c r="AX7" s="16" t="s">
         <v>24</v>
       </c>
-      <c r="AY7" s="29" t="s">
-        <v>214</v>
+      <c r="AY7" s="30" t="s">
+        <v>213</v>
       </c>
       <c r="AZ7" s="18"/>
       <c r="BA7" s="18"/>
@@ -10829,8 +10866,8 @@
       <c r="BE7" s="16" t="s">
         <v>24</v>
       </c>
-      <c r="BF7" s="29" t="s">
-        <v>214</v>
+      <c r="BF7" s="30" t="s">
+        <v>213</v>
       </c>
       <c r="BG7" s="18"/>
       <c r="BH7" s="18"/>
@@ -10839,8 +10876,8 @@
       <c r="BL7" s="16" t="s">
         <v>24</v>
       </c>
-      <c r="BM7" s="29" t="s">
-        <v>214</v>
+      <c r="BM7" s="30" t="s">
+        <v>213</v>
       </c>
       <c r="BN7" s="18"/>
       <c r="BO7" s="18"/>
@@ -10849,8 +10886,8 @@
       <c r="BS7" s="16" t="s">
         <v>24</v>
       </c>
-      <c r="BT7" s="29" t="s">
-        <v>214</v>
+      <c r="BT7" s="30" t="s">
+        <v>213</v>
       </c>
       <c r="BU7" s="18"/>
       <c r="BV7" s="18"/>
@@ -10859,8 +10896,8 @@
       <c r="BZ7" s="16" t="s">
         <v>24</v>
       </c>
-      <c r="CA7" s="29" t="s">
-        <v>214</v>
+      <c r="CA7" s="30" t="s">
+        <v>213</v>
       </c>
       <c r="CB7" s="18"/>
       <c r="CC7" s="18"/>
@@ -10869,8 +10906,8 @@
       <c r="CG7" s="16" t="s">
         <v>24</v>
       </c>
-      <c r="CH7" s="29" t="s">
-        <v>214</v>
+      <c r="CH7" s="30" t="s">
+        <v>213</v>
       </c>
       <c r="CI7" s="18"/>
       <c r="CJ7" s="18"/>
@@ -10879,8 +10916,8 @@
       <c r="CN7" s="16" t="s">
         <v>24</v>
       </c>
-      <c r="CO7" s="29" t="s">
-        <v>214</v>
+      <c r="CO7" s="30" t="s">
+        <v>213</v>
       </c>
       <c r="CP7" s="18"/>
       <c r="CQ7" s="18"/>
@@ -10889,8 +10926,8 @@
       <c r="CU7" s="16" t="s">
         <v>24</v>
       </c>
-      <c r="CV7" s="29" t="s">
-        <v>214</v>
+      <c r="CV7" s="30" t="s">
+        <v>213</v>
       </c>
       <c r="CW7" s="18"/>
       <c r="CX7" s="18"/>
@@ -10899,8 +10936,8 @@
       <c r="DB7" s="16" t="s">
         <v>24</v>
       </c>
-      <c r="DC7" s="29" t="s">
-        <v>214</v>
+      <c r="DC7" s="30" t="s">
+        <v>213</v>
       </c>
       <c r="DD7" s="18"/>
       <c r="DE7" s="18"/>
@@ -10909,8 +10946,8 @@
       <c r="DI7" s="16" t="s">
         <v>24</v>
       </c>
-      <c r="DJ7" s="29" t="s">
-        <v>214</v>
+      <c r="DJ7" s="30" t="s">
+        <v>213</v>
       </c>
       <c r="DK7" s="18"/>
       <c r="DL7" s="18"/>
@@ -10919,8 +10956,8 @@
       <c r="DP7" s="16" t="s">
         <v>24</v>
       </c>
-      <c r="DQ7" s="29" t="s">
-        <v>214</v>
+      <c r="DQ7" s="30" t="s">
+        <v>213</v>
       </c>
       <c r="DR7" s="18"/>
       <c r="DS7" s="18"/>
@@ -10929,8 +10966,8 @@
       <c r="DW7" s="16" t="s">
         <v>24</v>
       </c>
-      <c r="DX7" s="29" t="s">
-        <v>214</v>
+      <c r="DX7" s="30" t="s">
+        <v>213</v>
       </c>
       <c r="DY7" s="18"/>
       <c r="DZ7" s="18"/>
@@ -10939,8 +10976,8 @@
       <c r="ED7" s="16" t="s">
         <v>24</v>
       </c>
-      <c r="EE7" s="29" t="s">
-        <v>214</v>
+      <c r="EE7" s="30" t="s">
+        <v>213</v>
       </c>
       <c r="EF7" s="18"/>
       <c r="EG7" s="18"/>
@@ -10949,8 +10986,8 @@
       <c r="EK7" s="16" t="s">
         <v>24</v>
       </c>
-      <c r="EL7" s="29" t="s">
-        <v>214</v>
+      <c r="EL7" s="30" t="s">
+        <v>213</v>
       </c>
       <c r="EM7" s="18"/>
       <c r="EN7" s="18"/>
@@ -10959,8 +10996,8 @@
       <c r="ER7" s="16" t="s">
         <v>24</v>
       </c>
-      <c r="ES7" s="29" t="s">
-        <v>214</v>
+      <c r="ES7" s="30" t="s">
+        <v>213</v>
       </c>
       <c r="ET7" s="18"/>
       <c r="EU7" s="18"/>
@@ -10969,8 +11006,8 @@
       <c r="EY7" s="16" t="s">
         <v>24</v>
       </c>
-      <c r="EZ7" s="29" t="s">
-        <v>214</v>
+      <c r="EZ7" s="30" t="s">
+        <v>213</v>
       </c>
       <c r="FA7" s="18"/>
       <c r="FB7" s="18"/>
@@ -11395,886 +11432,939 @@
     </row>
     <row r="9" spans="1:160" ht="29.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="16" t="s">
+        <v>214</v>
+      </c>
+      <c r="B9" s="16" t="s">
         <v>215</v>
       </c>
-      <c r="B9" s="16" t="s">
+      <c r="C9" s="16" t="s">
         <v>216</v>
       </c>
-      <c r="C9" s="16" t="s">
+      <c r="D9" s="16" t="s">
         <v>217</v>
-      </c>
-      <c r="D9" s="16" t="s">
-        <v>218</v>
       </c>
       <c r="E9" s="16"/>
       <c r="F9" s="16"/>
       <c r="H9" s="16" t="s">
+        <v>214</v>
+      </c>
+      <c r="I9" s="16" t="s">
         <v>215</v>
       </c>
-      <c r="I9" s="16" t="s">
+      <c r="J9" s="16" t="s">
         <v>216</v>
       </c>
-      <c r="J9" s="16" t="s">
+      <c r="K9" s="16" t="s">
         <v>217</v>
-      </c>
-      <c r="K9" s="16" t="s">
-        <v>218</v>
       </c>
       <c r="L9" s="16"/>
       <c r="M9" s="16"/>
       <c r="O9" s="16" t="s">
+        <v>214</v>
+      </c>
+      <c r="P9" s="16" t="s">
         <v>215</v>
       </c>
-      <c r="P9" s="16" t="s">
+      <c r="Q9" s="16" t="s">
         <v>216</v>
       </c>
-      <c r="Q9" s="16" t="s">
+      <c r="R9" s="16" t="s">
         <v>217</v>
-      </c>
-      <c r="R9" s="16" t="s">
-        <v>218</v>
       </c>
       <c r="S9" s="16"/>
       <c r="T9" s="16"/>
       <c r="V9" s="16" t="s">
+        <v>214</v>
+      </c>
+      <c r="W9" s="16" t="s">
         <v>215</v>
       </c>
-      <c r="W9" s="16" t="s">
+      <c r="X9" s="16" t="s">
         <v>216</v>
       </c>
-      <c r="X9" s="16" t="s">
+      <c r="Y9" s="16" t="s">
         <v>217</v>
-      </c>
-      <c r="Y9" s="16" t="s">
-        <v>218</v>
       </c>
       <c r="Z9" s="16"/>
       <c r="AA9" s="16"/>
       <c r="AC9" s="16" t="s">
+        <v>214</v>
+      </c>
+      <c r="AD9" s="16" t="s">
         <v>215</v>
       </c>
-      <c r="AD9" s="16" t="s">
+      <c r="AE9" s="16" t="s">
         <v>216</v>
       </c>
-      <c r="AE9" s="16" t="s">
+      <c r="AF9" s="16" t="s">
         <v>217</v>
-      </c>
-      <c r="AF9" s="16" t="s">
-        <v>218</v>
       </c>
       <c r="AG9" s="16"/>
       <c r="AH9" s="16"/>
       <c r="AJ9" s="16" t="s">
+        <v>214</v>
+      </c>
+      <c r="AK9" s="16" t="s">
         <v>215</v>
       </c>
-      <c r="AK9" s="16" t="s">
+      <c r="AL9" s="16" t="s">
         <v>216</v>
       </c>
-      <c r="AL9" s="16" t="s">
+      <c r="AM9" s="16" t="s">
         <v>217</v>
-      </c>
-      <c r="AM9" s="16" t="s">
-        <v>218</v>
       </c>
       <c r="AN9" s="16"/>
       <c r="AO9" s="16"/>
       <c r="AQ9" s="16" t="s">
+        <v>214</v>
+      </c>
+      <c r="AR9" s="16" t="s">
         <v>215</v>
       </c>
-      <c r="AR9" s="16" t="s">
+      <c r="AS9" s="16" t="s">
         <v>216</v>
       </c>
-      <c r="AS9" s="16" t="s">
+      <c r="AT9" s="16" t="s">
         <v>217</v>
-      </c>
-      <c r="AT9" s="16" t="s">
-        <v>218</v>
       </c>
       <c r="AU9" s="16"/>
       <c r="AV9" s="16"/>
       <c r="AX9" s="16" t="s">
+        <v>214</v>
+      </c>
+      <c r="AY9" s="16" t="s">
         <v>215</v>
       </c>
-      <c r="AY9" s="16" t="s">
+      <c r="AZ9" s="16" t="s">
         <v>216</v>
       </c>
-      <c r="AZ9" s="16" t="s">
+      <c r="BA9" s="16" t="s">
         <v>217</v>
-      </c>
-      <c r="BA9" s="16" t="s">
-        <v>218</v>
       </c>
       <c r="BB9" s="16"/>
       <c r="BC9" s="16"/>
       <c r="BE9" s="16" t="s">
+        <v>214</v>
+      </c>
+      <c r="BF9" s="16" t="s">
         <v>215</v>
       </c>
-      <c r="BF9" s="16" t="s">
+      <c r="BG9" s="16" t="s">
         <v>216</v>
       </c>
-      <c r="BG9" s="16" t="s">
+      <c r="BH9" s="16" t="s">
         <v>217</v>
-      </c>
-      <c r="BH9" s="16" t="s">
-        <v>218</v>
       </c>
       <c r="BI9" s="16"/>
       <c r="BJ9" s="16"/>
       <c r="BL9" s="16" t="s">
+        <v>214</v>
+      </c>
+      <c r="BM9" s="16" t="s">
         <v>215</v>
       </c>
-      <c r="BM9" s="16" t="s">
+      <c r="BN9" s="16" t="s">
         <v>216</v>
       </c>
-      <c r="BN9" s="16" t="s">
+      <c r="BO9" s="16" t="s">
         <v>217</v>
-      </c>
-      <c r="BO9" s="16" t="s">
-        <v>218</v>
       </c>
       <c r="BP9" s="16"/>
       <c r="BQ9" s="16"/>
       <c r="BS9" s="16" t="s">
+        <v>214</v>
+      </c>
+      <c r="BT9" s="16" t="s">
         <v>215</v>
       </c>
-      <c r="BT9" s="16" t="s">
+      <c r="BU9" s="16" t="s">
         <v>216</v>
       </c>
-      <c r="BU9" s="16" t="s">
+      <c r="BV9" s="16" t="s">
         <v>217</v>
-      </c>
-      <c r="BV9" s="16" t="s">
-        <v>218</v>
       </c>
       <c r="BW9" s="16"/>
       <c r="BX9" s="16"/>
       <c r="BZ9" s="16" t="s">
+        <v>214</v>
+      </c>
+      <c r="CA9" s="16" t="s">
         <v>215</v>
       </c>
-      <c r="CA9" s="16" t="s">
+      <c r="CB9" s="16" t="s">
         <v>216</v>
       </c>
-      <c r="CB9" s="16" t="s">
+      <c r="CC9" s="16" t="s">
         <v>217</v>
-      </c>
-      <c r="CC9" s="16" t="s">
-        <v>218</v>
       </c>
       <c r="CD9" s="16"/>
       <c r="CE9" s="16"/>
       <c r="CG9" s="16" t="s">
+        <v>214</v>
+      </c>
+      <c r="CH9" s="16" t="s">
         <v>215</v>
       </c>
-      <c r="CH9" s="16" t="s">
+      <c r="CI9" s="16" t="s">
         <v>216</v>
       </c>
-      <c r="CI9" s="16" t="s">
+      <c r="CJ9" s="16" t="s">
         <v>217</v>
-      </c>
-      <c r="CJ9" s="16" t="s">
-        <v>218</v>
       </c>
       <c r="CK9" s="16"/>
       <c r="CL9" s="16"/>
       <c r="CN9" s="16" t="s">
+        <v>214</v>
+      </c>
+      <c r="CO9" s="16" t="s">
         <v>215</v>
       </c>
-      <c r="CO9" s="16" t="s">
+      <c r="CP9" s="16" t="s">
         <v>216</v>
       </c>
-      <c r="CP9" s="16" t="s">
+      <c r="CQ9" s="16" t="s">
         <v>217</v>
-      </c>
-      <c r="CQ9" s="16" t="s">
-        <v>218</v>
       </c>
       <c r="CR9" s="16"/>
       <c r="CS9" s="16"/>
       <c r="CU9" s="16" t="s">
+        <v>214</v>
+      </c>
+      <c r="CV9" s="16" t="s">
         <v>215</v>
       </c>
-      <c r="CV9" s="16" t="s">
+      <c r="CW9" s="16" t="s">
         <v>216</v>
       </c>
-      <c r="CW9" s="16" t="s">
+      <c r="CX9" s="16" t="s">
         <v>217</v>
-      </c>
-      <c r="CX9" s="16" t="s">
-        <v>218</v>
       </c>
       <c r="CY9" s="16"/>
       <c r="CZ9" s="16"/>
       <c r="DB9" s="16" t="s">
+        <v>214</v>
+      </c>
+      <c r="DC9" s="16" t="s">
         <v>215</v>
       </c>
-      <c r="DC9" s="16" t="s">
+      <c r="DD9" s="16" t="s">
         <v>216</v>
       </c>
-      <c r="DD9" s="16" t="s">
+      <c r="DE9" s="16" t="s">
         <v>217</v>
-      </c>
-      <c r="DE9" s="16" t="s">
-        <v>218</v>
       </c>
       <c r="DF9" s="16"/>
       <c r="DG9" s="16"/>
       <c r="DI9" s="16" t="s">
+        <v>214</v>
+      </c>
+      <c r="DJ9" s="16" t="s">
         <v>215</v>
       </c>
-      <c r="DJ9" s="16" t="s">
+      <c r="DK9" s="16" t="s">
         <v>216</v>
       </c>
-      <c r="DK9" s="16" t="s">
+      <c r="DL9" s="16" t="s">
         <v>217</v>
-      </c>
-      <c r="DL9" s="16" t="s">
-        <v>218</v>
       </c>
       <c r="DM9" s="16"/>
       <c r="DN9" s="16"/>
       <c r="DP9" s="16" t="s">
+        <v>214</v>
+      </c>
+      <c r="DQ9" s="16" t="s">
         <v>215</v>
       </c>
-      <c r="DQ9" s="16" t="s">
+      <c r="DR9" s="16" t="s">
         <v>216</v>
       </c>
-      <c r="DR9" s="16" t="s">
+      <c r="DS9" s="16" t="s">
         <v>217</v>
-      </c>
-      <c r="DS9" s="16" t="s">
-        <v>218</v>
       </c>
       <c r="DT9" s="16"/>
       <c r="DU9" s="16"/>
       <c r="DW9" s="16" t="s">
+        <v>214</v>
+      </c>
+      <c r="DX9" s="16" t="s">
         <v>215</v>
       </c>
-      <c r="DX9" s="16" t="s">
+      <c r="DY9" s="16" t="s">
         <v>216</v>
       </c>
-      <c r="DY9" s="16" t="s">
+      <c r="DZ9" s="16" t="s">
         <v>217</v>
-      </c>
-      <c r="DZ9" s="16" t="s">
-        <v>218</v>
       </c>
       <c r="EA9" s="16"/>
       <c r="EB9" s="16"/>
       <c r="ED9" s="16" t="s">
+        <v>214</v>
+      </c>
+      <c r="EE9" s="16" t="s">
         <v>215</v>
       </c>
-      <c r="EE9" s="16" t="s">
+      <c r="EF9" s="16" t="s">
         <v>216</v>
       </c>
-      <c r="EF9" s="16" t="s">
+      <c r="EG9" s="16" t="s">
         <v>217</v>
-      </c>
-      <c r="EG9" s="16" t="s">
-        <v>218</v>
       </c>
       <c r="EH9" s="16"/>
       <c r="EI9" s="16"/>
       <c r="EK9" s="16" t="s">
+        <v>214</v>
+      </c>
+      <c r="EL9" s="16" t="s">
         <v>215</v>
       </c>
-      <c r="EL9" s="16" t="s">
+      <c r="EM9" s="16" t="s">
         <v>216</v>
       </c>
-      <c r="EM9" s="16" t="s">
+      <c r="EN9" s="16" t="s">
         <v>217</v>
-      </c>
-      <c r="EN9" s="16" t="s">
-        <v>218</v>
       </c>
       <c r="EO9" s="16"/>
       <c r="EP9" s="16"/>
       <c r="ER9" s="16" t="s">
+        <v>214</v>
+      </c>
+      <c r="ES9" s="16" t="s">
         <v>215</v>
       </c>
-      <c r="ES9" s="16" t="s">
+      <c r="ET9" s="16" t="s">
         <v>216</v>
       </c>
-      <c r="ET9" s="16" t="s">
+      <c r="EU9" s="16" t="s">
         <v>217</v>
-      </c>
-      <c r="EU9" s="16" t="s">
-        <v>218</v>
       </c>
       <c r="EV9" s="16"/>
       <c r="EW9" s="16"/>
       <c r="EY9" s="16" t="s">
+        <v>214</v>
+      </c>
+      <c r="EZ9" s="16" t="s">
         <v>215</v>
       </c>
-      <c r="EZ9" s="16" t="s">
+      <c r="FA9" s="16" t="s">
         <v>216</v>
       </c>
-      <c r="FA9" s="16" t="s">
+      <c r="FB9" s="16" t="s">
         <v>217</v>
-      </c>
-      <c r="FB9" s="16" t="s">
-        <v>218</v>
       </c>
       <c r="FC9" s="16"/>
       <c r="FD9" s="16"/>
     </row>
     <row r="10" spans="1:160" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="16" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B10" s="16" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="C10" s="16"/>
       <c r="D10" s="16" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="E10" s="16"/>
       <c r="F10" s="16"/>
       <c r="H10" s="16" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="I10" s="16" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="J10" s="16"/>
       <c r="K10" s="16" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="L10" s="16"/>
       <c r="M10" s="16"/>
       <c r="O10" s="16" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="P10" s="16" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="Q10" s="16"/>
       <c r="R10" s="16" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="S10" s="16"/>
       <c r="T10" s="16"/>
       <c r="V10" s="16" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="W10" s="16" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="X10" s="16"/>
       <c r="Y10" s="16" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="Z10" s="16"/>
       <c r="AA10" s="16"/>
       <c r="AC10" s="16" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="AD10" s="16" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="AE10" s="16"/>
       <c r="AF10" s="16" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="AG10" s="16"/>
       <c r="AH10" s="16"/>
       <c r="AJ10" s="16" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="AK10" s="16" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="AL10" s="16"/>
       <c r="AM10" s="16" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="AN10" s="16"/>
       <c r="AO10" s="16"/>
       <c r="AQ10" s="16" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="AR10" s="16" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="AS10" s="16"/>
       <c r="AT10" s="16" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="AU10" s="16"/>
       <c r="AV10" s="16"/>
       <c r="AX10" s="16" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="AY10" s="16" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="AZ10" s="16"/>
       <c r="BA10" s="16" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="BB10" s="16"/>
       <c r="BC10" s="16"/>
       <c r="BE10" s="16" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="BF10" s="16" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="BG10" s="16"/>
       <c r="BH10" s="16" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="BI10" s="16"/>
       <c r="BJ10" s="16"/>
       <c r="BL10" s="16" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="BM10" s="16" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="BN10" s="16"/>
       <c r="BO10" s="16" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="BP10" s="16"/>
       <c r="BQ10" s="16"/>
       <c r="BS10" s="16" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="BT10" s="16" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="BU10" s="16"/>
       <c r="BV10" s="16" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="BW10" s="16"/>
       <c r="BX10" s="16"/>
       <c r="BZ10" s="16" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="CA10" s="16" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="CB10" s="16"/>
       <c r="CC10" s="16" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="CD10" s="16"/>
       <c r="CE10" s="16"/>
       <c r="CG10" s="16" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="CH10" s="16" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="CI10" s="16"/>
       <c r="CJ10" s="16" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="CK10" s="16"/>
       <c r="CL10" s="16"/>
       <c r="CN10" s="16" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="CO10" s="16" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="CP10" s="16"/>
       <c r="CQ10" s="16" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="CR10" s="16"/>
       <c r="CS10" s="16"/>
       <c r="CU10" s="16" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="CV10" s="16" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="CW10" s="16"/>
       <c r="CX10" s="16" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="CY10" s="16"/>
       <c r="CZ10" s="16"/>
       <c r="DB10" s="16" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="DC10" s="16" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="DD10" s="16"/>
       <c r="DE10" s="16" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="DF10" s="16"/>
       <c r="DG10" s="16"/>
       <c r="DI10" s="16" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="DJ10" s="16" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="DK10" s="16"/>
       <c r="DL10" s="16" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="DM10" s="16"/>
       <c r="DN10" s="16"/>
       <c r="DP10" s="16" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="DQ10" s="16" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="DR10" s="16"/>
       <c r="DS10" s="16" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="DT10" s="16"/>
       <c r="DU10" s="16"/>
       <c r="DW10" s="16" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="DX10" s="16" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="DY10" s="16"/>
       <c r="DZ10" s="16" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="EA10" s="16"/>
       <c r="EB10" s="16"/>
       <c r="ED10" s="16" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="EE10" s="16" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="EF10" s="16"/>
       <c r="EG10" s="16" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="EH10" s="16"/>
       <c r="EI10" s="16"/>
       <c r="EK10" s="16" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="EL10" s="16" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="EM10" s="16"/>
       <c r="EN10" s="16" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="EO10" s="16"/>
       <c r="EP10" s="16"/>
       <c r="ER10" s="16" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="ES10" s="16" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="ET10" s="16"/>
       <c r="EU10" s="16" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="EV10" s="16"/>
       <c r="EW10" s="16"/>
       <c r="EY10" s="16" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="EZ10" s="16" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="FA10" s="16"/>
       <c r="FB10" s="16" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="FC10" s="16"/>
       <c r="FD10" s="16"/>
     </row>
     <row r="11" spans="1:160" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="16" t="s">
+        <v>233</v>
+      </c>
+      <c r="B11" s="16" t="s">
         <v>234</v>
-      </c>
-      <c r="B11" s="16" t="s">
-        <v>235</v>
       </c>
       <c r="C11" s="16"/>
       <c r="D11" s="16" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="E11" s="16"/>
       <c r="F11" s="16"/>
       <c r="H11" s="16" t="s">
+        <v>233</v>
+      </c>
+      <c r="I11" s="16" t="s">
         <v>234</v>
-      </c>
-      <c r="I11" s="16" t="s">
-        <v>235</v>
       </c>
       <c r="J11" s="16"/>
       <c r="K11" s="16" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="L11" s="16"/>
       <c r="M11" s="16"/>
       <c r="O11" s="16" t="s">
+        <v>233</v>
+      </c>
+      <c r="P11" s="16" t="s">
         <v>234</v>
-      </c>
-      <c r="P11" s="16" t="s">
-        <v>235</v>
       </c>
       <c r="Q11" s="16"/>
       <c r="R11" s="16" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="S11" s="16"/>
       <c r="T11" s="16"/>
       <c r="V11" s="16" t="s">
+        <v>233</v>
+      </c>
+      <c r="W11" s="16" t="s">
         <v>234</v>
-      </c>
-      <c r="W11" s="16" t="s">
-        <v>235</v>
       </c>
       <c r="X11" s="16"/>
       <c r="Y11" s="16" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="Z11" s="16"/>
       <c r="AA11" s="16"/>
       <c r="AC11" s="16" t="s">
+        <v>233</v>
+      </c>
+      <c r="AD11" s="16" t="s">
         <v>234</v>
-      </c>
-      <c r="AD11" s="16" t="s">
-        <v>235</v>
       </c>
       <c r="AE11" s="16"/>
       <c r="AF11" s="16" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="AG11" s="16"/>
       <c r="AH11" s="16"/>
       <c r="AJ11" s="16" t="s">
+        <v>233</v>
+      </c>
+      <c r="AK11" s="16" t="s">
         <v>234</v>
-      </c>
-      <c r="AK11" s="16" t="s">
-        <v>235</v>
       </c>
       <c r="AL11" s="16"/>
       <c r="AM11" s="16" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="AN11" s="16"/>
       <c r="AO11" s="16"/>
       <c r="AQ11" s="16" t="s">
+        <v>233</v>
+      </c>
+      <c r="AR11" s="16" t="s">
         <v>234</v>
-      </c>
-      <c r="AR11" s="16" t="s">
-        <v>235</v>
       </c>
       <c r="AS11" s="16"/>
       <c r="AT11" s="16" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="AU11" s="16"/>
       <c r="AV11" s="16"/>
       <c r="AX11" s="16" t="s">
+        <v>233</v>
+      </c>
+      <c r="AY11" s="16" t="s">
         <v>234</v>
-      </c>
-      <c r="AY11" s="16" t="s">
-        <v>235</v>
       </c>
       <c r="AZ11" s="16"/>
       <c r="BA11" s="16" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="BB11" s="16"/>
       <c r="BC11" s="16"/>
       <c r="BE11" s="16" t="s">
+        <v>233</v>
+      </c>
+      <c r="BF11" s="16" t="s">
         <v>234</v>
-      </c>
-      <c r="BF11" s="16" t="s">
-        <v>235</v>
       </c>
       <c r="BG11" s="16"/>
       <c r="BH11" s="16" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="BI11" s="16"/>
       <c r="BJ11" s="16"/>
       <c r="BL11" s="16" t="s">
+        <v>233</v>
+      </c>
+      <c r="BM11" s="16" t="s">
         <v>234</v>
-      </c>
-      <c r="BM11" s="16" t="s">
-        <v>235</v>
       </c>
       <c r="BN11" s="16"/>
       <c r="BO11" s="16" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="BP11" s="16"/>
       <c r="BQ11" s="16"/>
       <c r="BS11" s="16" t="s">
+        <v>233</v>
+      </c>
+      <c r="BT11" s="16" t="s">
         <v>234</v>
-      </c>
-      <c r="BT11" s="16" t="s">
-        <v>235</v>
       </c>
       <c r="BU11" s="16"/>
       <c r="BV11" s="16" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="BW11" s="16"/>
       <c r="BX11" s="16"/>
       <c r="BZ11" s="16" t="s">
+        <v>233</v>
+      </c>
+      <c r="CA11" s="16" t="s">
         <v>234</v>
-      </c>
-      <c r="CA11" s="16" t="s">
-        <v>235</v>
       </c>
       <c r="CB11" s="16"/>
       <c r="CC11" s="16" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="CD11" s="16"/>
       <c r="CE11" s="16"/>
       <c r="CG11" s="16" t="s">
+        <v>233</v>
+      </c>
+      <c r="CH11" s="16" t="s">
         <v>234</v>
-      </c>
-      <c r="CH11" s="16" t="s">
-        <v>235</v>
       </c>
       <c r="CI11" s="16"/>
       <c r="CJ11" s="16" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="CK11" s="16"/>
       <c r="CL11" s="16"/>
       <c r="CN11" s="16" t="s">
+        <v>233</v>
+      </c>
+      <c r="CO11" s="16" t="s">
         <v>234</v>
-      </c>
-      <c r="CO11" s="16" t="s">
-        <v>235</v>
       </c>
       <c r="CP11" s="16"/>
       <c r="CQ11" s="16" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="CR11" s="16"/>
       <c r="CS11" s="16"/>
       <c r="CU11" s="16" t="s">
+        <v>233</v>
+      </c>
+      <c r="CV11" s="16" t="s">
         <v>234</v>
-      </c>
-      <c r="CV11" s="16" t="s">
-        <v>235</v>
       </c>
       <c r="CW11" s="16"/>
       <c r="CX11" s="16" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="CY11" s="16"/>
       <c r="CZ11" s="16"/>
       <c r="DB11" s="16" t="s">
+        <v>233</v>
+      </c>
+      <c r="DC11" s="16" t="s">
         <v>234</v>
-      </c>
-      <c r="DC11" s="16" t="s">
-        <v>235</v>
       </c>
       <c r="DD11" s="16"/>
       <c r="DE11" s="16" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="DF11" s="16"/>
       <c r="DG11" s="16"/>
       <c r="DI11" s="16" t="s">
+        <v>233</v>
+      </c>
+      <c r="DJ11" s="16" t="s">
         <v>234</v>
-      </c>
-      <c r="DJ11" s="16" t="s">
-        <v>235</v>
       </c>
       <c r="DK11" s="16"/>
       <c r="DL11" s="16" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="DM11" s="16"/>
       <c r="DN11" s="16"/>
       <c r="DP11" s="16" t="s">
+        <v>233</v>
+      </c>
+      <c r="DQ11" s="16" t="s">
         <v>234</v>
-      </c>
-      <c r="DQ11" s="16" t="s">
-        <v>235</v>
       </c>
       <c r="DR11" s="16"/>
       <c r="DS11" s="16" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="DT11" s="16"/>
       <c r="DU11" s="16"/>
       <c r="DW11" s="16" t="s">
+        <v>233</v>
+      </c>
+      <c r="DX11" s="16" t="s">
         <v>234</v>
-      </c>
-      <c r="DX11" s="16" t="s">
-        <v>235</v>
       </c>
       <c r="DY11" s="16"/>
       <c r="DZ11" s="16" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="EA11" s="16"/>
       <c r="EB11" s="16"/>
       <c r="ED11" s="16" t="s">
+        <v>233</v>
+      </c>
+      <c r="EE11" s="16" t="s">
         <v>234</v>
-      </c>
-      <c r="EE11" s="16" t="s">
-        <v>235</v>
       </c>
       <c r="EF11" s="16"/>
       <c r="EG11" s="16" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="EH11" s="16"/>
       <c r="EI11" s="16"/>
       <c r="EK11" s="16" t="s">
+        <v>233</v>
+      </c>
+      <c r="EL11" s="16" t="s">
         <v>234</v>
-      </c>
-      <c r="EL11" s="16" t="s">
-        <v>235</v>
       </c>
       <c r="EM11" s="16"/>
       <c r="EN11" s="16" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="EO11" s="16"/>
       <c r="EP11" s="16"/>
       <c r="ER11" s="16" t="s">
+        <v>233</v>
+      </c>
+      <c r="ES11" s="16" t="s">
         <v>234</v>
-      </c>
-      <c r="ES11" s="16" t="s">
-        <v>235</v>
       </c>
       <c r="ET11" s="16"/>
       <c r="EU11" s="16" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="EV11" s="16"/>
       <c r="EW11" s="16"/>
       <c r="EY11" s="16" t="s">
+        <v>233</v>
+      </c>
+      <c r="EZ11" s="16" t="s">
         <v>234</v>
-      </c>
-      <c r="EZ11" s="16" t="s">
-        <v>235</v>
       </c>
       <c r="FA11" s="16"/>
       <c r="FB11" s="16" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="FC11" s="16"/>
       <c r="FD11" s="16"/>
     </row>
   </sheetData>
   <mergeCells count="69">
+    <mergeCell ref="EL7:EP7"/>
+    <mergeCell ref="AD7:AH7"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="BL1:BQ1"/>
+    <mergeCell ref="AY7:BC7"/>
+    <mergeCell ref="CU1:CZ1"/>
+    <mergeCell ref="CH7:CL7"/>
+    <mergeCell ref="AY6:BC6"/>
+    <mergeCell ref="BT6:BX6"/>
+    <mergeCell ref="W7:AA7"/>
+    <mergeCell ref="P7:T7"/>
+    <mergeCell ref="CA7:CE7"/>
+    <mergeCell ref="EE7:EI7"/>
+    <mergeCell ref="CO7:CS7"/>
+    <mergeCell ref="EL6:EP6"/>
+    <mergeCell ref="DX7:EB7"/>
+    <mergeCell ref="EZ6:FD6"/>
+    <mergeCell ref="EK1:EP1"/>
+    <mergeCell ref="H1:M1"/>
+    <mergeCell ref="B6:F6"/>
+    <mergeCell ref="AX1:BC1"/>
+    <mergeCell ref="AK6:AO6"/>
+    <mergeCell ref="DJ6:DN6"/>
+    <mergeCell ref="ES6:EW6"/>
+    <mergeCell ref="ED1:EI1"/>
+    <mergeCell ref="AJ1:AO1"/>
+    <mergeCell ref="AR6:AV6"/>
+    <mergeCell ref="CN1:CS1"/>
+    <mergeCell ref="DC6:DG6"/>
+    <mergeCell ref="DB1:DG1"/>
+    <mergeCell ref="CV6:CZ6"/>
+    <mergeCell ref="ER1:EW1"/>
+    <mergeCell ref="ES7:EW7"/>
+    <mergeCell ref="AC1:AH1"/>
+    <mergeCell ref="EE6:EI6"/>
+    <mergeCell ref="I7:M7"/>
+    <mergeCell ref="BT7:BX7"/>
+    <mergeCell ref="P6:T6"/>
+    <mergeCell ref="CG1:CL1"/>
+    <mergeCell ref="BM7:BQ7"/>
+    <mergeCell ref="CA6:CE6"/>
+    <mergeCell ref="AQ1:AV1"/>
+    <mergeCell ref="AD6:AH6"/>
+    <mergeCell ref="DC7:DG7"/>
+    <mergeCell ref="BZ1:CE1"/>
+    <mergeCell ref="CO6:CS6"/>
+    <mergeCell ref="DP1:DU1"/>
+    <mergeCell ref="DQ7:DU7"/>
+    <mergeCell ref="CH6:CL6"/>
+    <mergeCell ref="BF6:BJ6"/>
+    <mergeCell ref="DW1:EB1"/>
+    <mergeCell ref="DQ6:DU6"/>
+    <mergeCell ref="DJ7:DN7"/>
     <mergeCell ref="EY1:FD1"/>
     <mergeCell ref="V1:AA1"/>
     <mergeCell ref="DX6:EB6"/>
@@ -12291,59 +12381,6 @@
     <mergeCell ref="DI1:DN1"/>
     <mergeCell ref="BF7:BJ7"/>
     <mergeCell ref="BM6:BQ6"/>
-    <mergeCell ref="CH6:CL6"/>
-    <mergeCell ref="BF6:BJ6"/>
-    <mergeCell ref="DW1:EB1"/>
-    <mergeCell ref="DQ6:DU6"/>
-    <mergeCell ref="DJ7:DN7"/>
-    <mergeCell ref="ES7:EW7"/>
-    <mergeCell ref="AC1:AH1"/>
-    <mergeCell ref="EE6:EI6"/>
-    <mergeCell ref="I7:M7"/>
-    <mergeCell ref="BT7:BX7"/>
-    <mergeCell ref="P6:T6"/>
-    <mergeCell ref="CG1:CL1"/>
-    <mergeCell ref="BM7:BQ7"/>
-    <mergeCell ref="CA6:CE6"/>
-    <mergeCell ref="AQ1:AV1"/>
-    <mergeCell ref="AD6:AH6"/>
-    <mergeCell ref="DC7:DG7"/>
-    <mergeCell ref="BZ1:CE1"/>
-    <mergeCell ref="CO6:CS6"/>
-    <mergeCell ref="DP1:DU1"/>
-    <mergeCell ref="DQ7:DU7"/>
-    <mergeCell ref="EZ6:FD6"/>
-    <mergeCell ref="EK1:EP1"/>
-    <mergeCell ref="H1:M1"/>
-    <mergeCell ref="B6:F6"/>
-    <mergeCell ref="AX1:BC1"/>
-    <mergeCell ref="AK6:AO6"/>
-    <mergeCell ref="DJ6:DN6"/>
-    <mergeCell ref="ES6:EW6"/>
-    <mergeCell ref="ED1:EI1"/>
-    <mergeCell ref="AJ1:AO1"/>
-    <mergeCell ref="AR6:AV6"/>
-    <mergeCell ref="CN1:CS1"/>
-    <mergeCell ref="DC6:DG6"/>
-    <mergeCell ref="DB1:DG1"/>
-    <mergeCell ref="CV6:CZ6"/>
-    <mergeCell ref="ER1:EW1"/>
-    <mergeCell ref="EL7:EP7"/>
-    <mergeCell ref="AD7:AH7"/>
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="BL1:BQ1"/>
-    <mergeCell ref="AY7:BC7"/>
-    <mergeCell ref="CU1:CZ1"/>
-    <mergeCell ref="CH7:CL7"/>
-    <mergeCell ref="AY6:BC6"/>
-    <mergeCell ref="BT6:BX6"/>
-    <mergeCell ref="W7:AA7"/>
-    <mergeCell ref="P7:T7"/>
-    <mergeCell ref="CA7:CE7"/>
-    <mergeCell ref="EE7:EI7"/>
-    <mergeCell ref="CO7:CS7"/>
-    <mergeCell ref="EL6:EP6"/>
-    <mergeCell ref="DX7:EB7"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Test Cases.xlsx
+++ b/Test Cases.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://endresshauser-my.sharepoint.com/personal/corbin_ferguson_endress_com/Documents/ThesisBuildTool/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="325" documentId="8_{B89245B7-08D9-4A9D-8516-F6C9C7AFFDC1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{96FEFAAE-FE66-441B-92CD-2D085DA1D9DF}"/>
+  <xr:revisionPtr revIDLastSave="326" documentId="8_{B89245B7-08D9-4A9D-8516-F6C9C7AFFDC1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F37B63AB-F228-42AF-AB56-3D48E2C602AF}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="25440" windowHeight="15270" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="25440" windowHeight="15270" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tests" sheetId="1" r:id="rId1"/>
@@ -1188,9 +1188,6 @@
     <t>Element Clash from import</t>
   </si>
   <si>
-    <t>"Cancel" selected from dropdown</t>
-  </si>
-  <si>
     <t>clashing elements window appears</t>
   </si>
   <si>
@@ -1198,6 +1195,9 @@
   </si>
   <si>
     <t>"TemplateLadderAOI" selected from dropdown</t>
+  </si>
+  <si>
+    <t>"Replace" selected from dropdown</t>
   </si>
 </sst>
 </file>
@@ -4583,7 +4583,7 @@
         <v>336</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="D15" s="2" t="s">
         <v>335</v>
@@ -4613,10 +4613,10 @@
         <v>337</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
     </row>
     <row r="18" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -4628,7 +4628,7 @@
         <v>381</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>42</v>
